--- a/Appium_E2E_Test_Report_Traverse.xlsx
+++ b/Appium_E2E_Test_Report_Traverse.xlsx
@@ -570,7 +570,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Automated &amp; Simulated Mobile E2E Validation Summary — Generated 2026-06-22 08:44:09</t>
+          <t>Automated &amp; Simulated Mobile E2E Validation Summary — Generated 2026-06-22 14:08:26</t>
         </is>
       </c>
     </row>

--- a/Appium_E2E_Test_Report_Traverse.xlsx
+++ b/Appium_E2E_Test_Report_Traverse.xlsx
@@ -791,7 +791,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22 11:19:39</t>
+          <t>2026-07-22 05:58:55</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="E2" s="20" t="n">
-        <v>148</v>
+        <v>209</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="E3" s="23" t="n">
-        <v>198</v>
+        <v>229</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="E4" s="20" t="n">
-        <v>145</v>
+        <v>199</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="E5" s="23" t="n">
-        <v>138</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="E6" s="20" t="n">
-        <v>230</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="E7" s="23" t="n">
-        <v>116</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -1228,7 +1228,7 @@
         </is>
       </c>
       <c r="E8" s="20" t="n">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="E9" s="23" t="n">
-        <v>236</v>
+        <v>207</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
@@ -1278,7 +1278,7 @@
         </is>
       </c>
       <c r="E10" s="20" t="n">
-        <v>209</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="E11" s="23" t="n">
-        <v>157</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
@@ -1328,7 +1328,7 @@
         </is>
       </c>
       <c r="E12" s="20" t="n">
-        <v>239</v>
+        <v>183</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="E13" s="23" t="n">
-        <v>239</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="E14" s="20" t="n">
-        <v>126</v>
+        <v>177</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="E15" s="23" t="n">
-        <v>188</v>
+        <v>158</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="E16" s="20" t="n">
-        <v>179</v>
+        <v>199</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="E17" s="23" t="n">
-        <v>189</v>
+        <v>212</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -1478,7 +1478,7 @@
         </is>
       </c>
       <c r="E18" s="20" t="n">
-        <v>153</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
@@ -1503,7 +1503,7 @@
         </is>
       </c>
       <c r="E19" s="23" t="n">
-        <v>113</v>
+        <v>199</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="E20" s="20" t="n">
-        <v>209</v>
+        <v>110</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="E21" s="23" t="n">
-        <v>185</v>
+        <v>119</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
@@ -1578,7 +1578,7 @@
         </is>
       </c>
       <c r="E22" s="20" t="n">
-        <v>147</v>
+        <v>152</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="E23" s="23" t="n">
-        <v>161</v>
+        <v>236</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
@@ -1628,7 +1628,7 @@
         </is>
       </c>
       <c r="E24" s="20" t="n">
-        <v>130</v>
+        <v>161</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="E25" s="23" t="n">
-        <v>133</v>
+        <v>172</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
@@ -1678,7 +1678,7 @@
         </is>
       </c>
       <c r="E26" s="20" t="n">
-        <v>148</v>
+        <v>111</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="E27" s="23" t="n">
-        <v>138</v>
+        <v>173</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="E28" s="20" t="n">
-        <v>124</v>
+        <v>224</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="E29" s="23" t="n">
-        <v>213</v>
+        <v>205</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="E30" s="20" t="n">
-        <v>166</v>
+        <v>183</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
@@ -1803,7 +1803,7 @@
         </is>
       </c>
       <c r="E31" s="23" t="n">
-        <v>234</v>
+        <v>142</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
@@ -1828,7 +1828,7 @@
         </is>
       </c>
       <c r="E32" s="20" t="n">
-        <v>195</v>
+        <v>111</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
@@ -1853,7 +1853,7 @@
         </is>
       </c>
       <c r="E33" s="23" t="n">
-        <v>136</v>
+        <v>167</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
@@ -1878,7 +1878,7 @@
         </is>
       </c>
       <c r="E34" s="20" t="n">
-        <v>237</v>
+        <v>163</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="E35" s="23" t="n">
-        <v>215</v>
+        <v>226</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="E36" s="20" t="n">
-        <v>219</v>
+        <v>137</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="E37" s="23" t="n">
-        <v>156</v>
+        <v>194</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
@@ -1978,7 +1978,7 @@
         </is>
       </c>
       <c r="E38" s="20" t="n">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="E39" s="23" t="n">
-        <v>166</v>
+        <v>206</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="E40" s="20" t="n">
-        <v>202</v>
+        <v>189</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="E41" s="23" t="n">
-        <v>203</v>
+        <v>132</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
@@ -2078,7 +2078,7 @@
         </is>
       </c>
       <c r="E42" s="20" t="n">
-        <v>133</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="E43" s="23" t="n">
-        <v>202</v>
+        <v>139</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="E44" s="20" t="n">
-        <v>225</v>
+        <v>111</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="E45" s="23" t="n">
-        <v>114</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
@@ -2178,7 +2178,7 @@
         </is>
       </c>
       <c r="E46" s="20" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
@@ -2203,7 +2203,7 @@
         </is>
       </c>
       <c r="E47" s="23" t="n">
-        <v>211</v>
+        <v>199</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="E48" s="20" t="n">
-        <v>115</v>
+        <v>206</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
@@ -2253,7 +2253,7 @@
         </is>
       </c>
       <c r="E49" s="23" t="n">
-        <v>190</v>
+        <v>153</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
@@ -2278,7 +2278,7 @@
         </is>
       </c>
       <c r="E50" s="20" t="n">
-        <v>160</v>
+        <v>229</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="E51" s="23" t="n">
-        <v>157</v>
+        <v>219</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
@@ -2328,7 +2328,7 @@
         </is>
       </c>
       <c r="E52" s="20" t="n">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
@@ -2353,7 +2353,7 @@
         </is>
       </c>
       <c r="E53" s="23" t="n">
-        <v>236</v>
+        <v>164</v>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="E54" s="20" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1">
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="E55" s="23" t="n">
-        <v>171</v>
+        <v>134</v>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1">
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="E56" s="20" t="n">
-        <v>135</v>
+        <v>172</v>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1">
@@ -2453,7 +2453,7 @@
         </is>
       </c>
       <c r="E57" s="23" t="n">
-        <v>172</v>
+        <v>124</v>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1">
@@ -2478,7 +2478,7 @@
         </is>
       </c>
       <c r="E58" s="20" t="n">
-        <v>154</v>
+        <v>234</v>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1">
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="E59" s="23" t="n">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1">
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="E60" s="20" t="n">
-        <v>112</v>
+        <v>182</v>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
@@ -2553,7 +2553,7 @@
         </is>
       </c>
       <c r="E61" s="23" t="n">
-        <v>146</v>
+        <v>170</v>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="E62" s="20" t="n">
-        <v>165</v>
+        <v>211</v>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="E63" s="23" t="n">
-        <v>117</v>
+        <v>138</v>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1">
@@ -2628,7 +2628,7 @@
         </is>
       </c>
       <c r="E64" s="20" t="n">
-        <v>136</v>
+        <v>219</v>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1">
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="E65" s="23" t="n">
-        <v>232</v>
+        <v>175</v>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1">
@@ -2678,7 +2678,7 @@
         </is>
       </c>
       <c r="E66" s="20" t="n">
-        <v>152</v>
+        <v>232</v>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="E67" s="23" t="n">
-        <v>130</v>
+        <v>170</v>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="E68" s="20" t="n">
-        <v>207</v>
+        <v>152</v>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="E69" s="23" t="n">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1">
@@ -2778,7 +2778,7 @@
         </is>
       </c>
       <c r="E70" s="20" t="n">
-        <v>137</v>
+        <v>146</v>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1">
@@ -2803,7 +2803,7 @@
         </is>
       </c>
       <c r="E71" s="23" t="n">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1">
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="E72" s="20" t="n">
-        <v>212</v>
+        <v>191</v>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1">
@@ -2853,7 +2853,7 @@
         </is>
       </c>
       <c r="E73" s="23" t="n">
-        <v>149</v>
+        <v>166</v>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
@@ -2878,7 +2878,7 @@
         </is>
       </c>
       <c r="E74" s="20" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="E75" s="23" t="n">
-        <v>234</v>
+        <v>150</v>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
@@ -2928,7 +2928,7 @@
         </is>
       </c>
       <c r="E76" s="20" t="n">
-        <v>151</v>
+        <v>237</v>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="E77" s="23" t="n">
-        <v>120</v>
+        <v>231</v>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1">
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="E78" s="20" t="n">
-        <v>154</v>
+        <v>206</v>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
@@ -3003,7 +3003,7 @@
         </is>
       </c>
       <c r="E79" s="23" t="n">
-        <v>139</v>
+        <v>110</v>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1">
@@ -3028,7 +3028,7 @@
         </is>
       </c>
       <c r="E80" s="20" t="n">
-        <v>138</v>
+        <v>154</v>
       </c>
     </row>
     <row r="81" ht="20" customHeight="1">
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="E81" s="23" t="n">
-        <v>216</v>
+        <v>118</v>
       </c>
     </row>
     <row r="82" ht="20" customHeight="1">
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="E82" s="20" t="n">
-        <v>186</v>
+        <v>126</v>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1">
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="E83" s="23" t="n">
-        <v>137</v>
+        <v>235</v>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1">
@@ -3128,7 +3128,7 @@
         </is>
       </c>
       <c r="E84" s="20" t="n">
-        <v>154</v>
+        <v>117</v>
       </c>
     </row>
     <row r="85" ht="20" customHeight="1">
@@ -3153,7 +3153,7 @@
         </is>
       </c>
       <c r="E85" s="23" t="n">
-        <v>184</v>
+        <v>157</v>
       </c>
     </row>
     <row r="86" ht="20" customHeight="1">
@@ -3178,7 +3178,7 @@
         </is>
       </c>
       <c r="E86" s="20" t="n">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="87" ht="20" customHeight="1">
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="E87" s="23" t="n">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1">
@@ -3228,7 +3228,7 @@
         </is>
       </c>
       <c r="E88" s="20" t="n">
-        <v>167</v>
+        <v>130</v>
       </c>
     </row>
     <row r="89" ht="20" customHeight="1">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="E89" s="23" t="n">
-        <v>218</v>
+        <v>239</v>
       </c>
     </row>
     <row r="90" ht="20" customHeight="1">
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="E90" s="20" t="n">
-        <v>141</v>
+        <v>166</v>
       </c>
     </row>
     <row r="91" ht="20" customHeight="1">
@@ -3303,7 +3303,7 @@
         </is>
       </c>
       <c r="E91" s="23" t="n">
-        <v>227</v>
+        <v>209</v>
       </c>
     </row>
     <row r="92" ht="20" customHeight="1">
@@ -3328,7 +3328,7 @@
         </is>
       </c>
       <c r="E92" s="20" t="n">
-        <v>190</v>
+        <v>205</v>
       </c>
     </row>
     <row r="93" ht="20" customHeight="1">
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="E93" s="23" t="n">
-        <v>210</v>
+        <v>114</v>
       </c>
     </row>
     <row r="94" ht="20" customHeight="1">
@@ -3378,7 +3378,7 @@
         </is>
       </c>
       <c r="E94" s="20" t="n">
-        <v>155</v>
+        <v>187</v>
       </c>
     </row>
     <row r="95" ht="20" customHeight="1">
@@ -3403,7 +3403,7 @@
         </is>
       </c>
       <c r="E95" s="23" t="n">
-        <v>122</v>
+        <v>183</v>
       </c>
     </row>
     <row r="96" ht="20" customHeight="1">
@@ -3428,7 +3428,7 @@
         </is>
       </c>
       <c r="E96" s="20" t="n">
-        <v>237</v>
+        <v>210</v>
       </c>
     </row>
     <row r="97" ht="20" customHeight="1">
@@ -3453,7 +3453,7 @@
         </is>
       </c>
       <c r="E97" s="23" t="n">
-        <v>181</v>
+        <v>206</v>
       </c>
     </row>
     <row r="98" ht="20" customHeight="1">
@@ -3478,7 +3478,7 @@
         </is>
       </c>
       <c r="E98" s="20" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
     </row>
     <row r="99" ht="20" customHeight="1">
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="E99" s="23" t="n">
-        <v>235</v>
+        <v>199</v>
       </c>
     </row>
     <row r="100" ht="20" customHeight="1">
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="E100" s="20" t="n">
-        <v>156</v>
+        <v>164</v>
       </c>
     </row>
     <row r="101" ht="20" customHeight="1">
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="E101" s="23" t="n">
-        <v>149</v>
+        <v>198</v>
       </c>
     </row>
     <row r="102" ht="20" customHeight="1">
@@ -3578,7 +3578,7 @@
         </is>
       </c>
       <c r="E102" s="20" t="n">
-        <v>111</v>
+        <v>148</v>
       </c>
     </row>
     <row r="103" ht="20" customHeight="1">
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="E103" s="23" t="n">
-        <v>240</v>
+        <v>194</v>
       </c>
     </row>
     <row r="104" ht="20" customHeight="1">
@@ -3628,7 +3628,7 @@
         </is>
       </c>
       <c r="E104" s="20" t="n">
-        <v>236</v>
+        <v>219</v>
       </c>
     </row>
     <row r="105" ht="20" customHeight="1">
@@ -3653,7 +3653,7 @@
         </is>
       </c>
       <c r="E105" s="23" t="n">
-        <v>114</v>
+        <v>233</v>
       </c>
     </row>
     <row r="106" ht="20" customHeight="1">
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="E106" s="20" t="n">
-        <v>188</v>
+        <v>197</v>
       </c>
     </row>
     <row r="107" ht="20" customHeight="1">
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="E107" s="23" t="n">
-        <v>191</v>
+        <v>206</v>
       </c>
     </row>
     <row r="108" ht="20" customHeight="1">
@@ -3728,7 +3728,7 @@
         </is>
       </c>
       <c r="E108" s="20" t="n">
-        <v>239</v>
+        <v>194</v>
       </c>
     </row>
     <row r="109" ht="20" customHeight="1">
@@ -3753,7 +3753,7 @@
         </is>
       </c>
       <c r="E109" s="23" t="n">
-        <v>197</v>
+        <v>237</v>
       </c>
     </row>
     <row r="110" ht="20" customHeight="1">
@@ -3778,7 +3778,7 @@
         </is>
       </c>
       <c r="E110" s="20" t="n">
-        <v>127</v>
+        <v>236</v>
       </c>
     </row>
     <row r="111" ht="20" customHeight="1">
@@ -3803,7 +3803,7 @@
         </is>
       </c>
       <c r="E111" s="23" t="n">
-        <v>115</v>
+        <v>201</v>
       </c>
     </row>
     <row r="112" ht="20" customHeight="1">
@@ -3828,7 +3828,7 @@
         </is>
       </c>
       <c r="E112" s="20" t="n">
-        <v>190</v>
+        <v>235</v>
       </c>
     </row>
     <row r="113" ht="20" customHeight="1">
@@ -3853,7 +3853,7 @@
         </is>
       </c>
       <c r="E113" s="23" t="n">
-        <v>208</v>
+        <v>125</v>
       </c>
     </row>
     <row r="114" ht="20" customHeight="1">
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="E114" s="20" t="n">
-        <v>220</v>
+        <v>180</v>
       </c>
     </row>
     <row r="115" ht="20" customHeight="1">
@@ -3903,7 +3903,7 @@
         </is>
       </c>
       <c r="E115" s="23" t="n">
-        <v>191</v>
+        <v>231</v>
       </c>
     </row>
     <row r="116" ht="20" customHeight="1">
@@ -3928,7 +3928,7 @@
         </is>
       </c>
       <c r="E116" s="20" t="n">
-        <v>190</v>
+        <v>135</v>
       </c>
     </row>
     <row r="117" ht="20" customHeight="1">
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="E117" s="23" t="n">
-        <v>120</v>
+        <v>187</v>
       </c>
     </row>
     <row r="118" ht="20" customHeight="1">
@@ -3978,7 +3978,7 @@
         </is>
       </c>
       <c r="E118" s="20" t="n">
-        <v>110</v>
+        <v>238</v>
       </c>
     </row>
     <row r="119" ht="20" customHeight="1">
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="E119" s="23" t="n">
-        <v>193</v>
+        <v>169</v>
       </c>
     </row>
     <row r="120" ht="20" customHeight="1">
@@ -4028,7 +4028,7 @@
         </is>
       </c>
       <c r="E120" s="20" t="n">
-        <v>148</v>
+        <v>239</v>
       </c>
     </row>
     <row r="121" ht="20" customHeight="1">
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="E121" s="23" t="n">
-        <v>195</v>
+        <v>214</v>
       </c>
     </row>
     <row r="122" ht="20" customHeight="1">
@@ -4078,7 +4078,7 @@
         </is>
       </c>
       <c r="E122" s="20" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="123" ht="20" customHeight="1">
@@ -4103,7 +4103,7 @@
         </is>
       </c>
       <c r="E123" s="23" t="n">
-        <v>178</v>
+        <v>202</v>
       </c>
     </row>
     <row r="124" ht="20" customHeight="1">
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="E124" s="20" t="n">
-        <v>240</v>
+        <v>182</v>
       </c>
     </row>
     <row r="125" ht="20" customHeight="1">
@@ -4153,7 +4153,7 @@
         </is>
       </c>
       <c r="E125" s="23" t="n">
-        <v>179</v>
+        <v>212</v>
       </c>
     </row>
     <row r="126" ht="20" customHeight="1">
@@ -4178,7 +4178,7 @@
         </is>
       </c>
       <c r="E126" s="20" t="n">
-        <v>120</v>
+        <v>134</v>
       </c>
     </row>
     <row r="127" ht="20" customHeight="1">
@@ -4203,7 +4203,7 @@
         </is>
       </c>
       <c r="E127" s="23" t="n">
-        <v>224</v>
+        <v>196</v>
       </c>
     </row>
     <row r="128" ht="20" customHeight="1">
@@ -4228,7 +4228,7 @@
         </is>
       </c>
       <c r="E128" s="20" t="n">
-        <v>121</v>
+        <v>236</v>
       </c>
     </row>
     <row r="129" ht="20" customHeight="1">
@@ -4253,7 +4253,7 @@
         </is>
       </c>
       <c r="E129" s="23" t="n">
-        <v>154</v>
+        <v>145</v>
       </c>
     </row>
     <row r="130" ht="20" customHeight="1">
@@ -4278,7 +4278,7 @@
         </is>
       </c>
       <c r="E130" s="20" t="n">
-        <v>208</v>
+        <v>135</v>
       </c>
     </row>
     <row r="131" ht="20" customHeight="1">
@@ -4303,7 +4303,7 @@
         </is>
       </c>
       <c r="E131" s="23" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="132" ht="20" customHeight="1">
@@ -4328,7 +4328,7 @@
         </is>
       </c>
       <c r="E132" s="20" t="n">
-        <v>193</v>
+        <v>160</v>
       </c>
     </row>
     <row r="133" ht="20" customHeight="1">
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="E133" s="23" t="n">
-        <v>223</v>
+        <v>155</v>
       </c>
     </row>
     <row r="134" ht="20" customHeight="1">
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="E134" s="20" t="n">
-        <v>221</v>
+        <v>184</v>
       </c>
     </row>
     <row r="135" ht="20" customHeight="1">
@@ -4403,7 +4403,7 @@
         </is>
       </c>
       <c r="E135" s="23" t="n">
-        <v>226</v>
+        <v>158</v>
       </c>
     </row>
     <row r="136" ht="20" customHeight="1">
@@ -4428,7 +4428,7 @@
         </is>
       </c>
       <c r="E136" s="20" t="n">
-        <v>117</v>
+        <v>205</v>
       </c>
     </row>
     <row r="137" ht="20" customHeight="1">
@@ -4453,7 +4453,7 @@
         </is>
       </c>
       <c r="E137" s="23" t="n">
-        <v>135</v>
+        <v>143</v>
       </c>
     </row>
     <row r="138" ht="20" customHeight="1">
@@ -4478,7 +4478,7 @@
         </is>
       </c>
       <c r="E138" s="20" t="n">
-        <v>115</v>
+        <v>171</v>
       </c>
     </row>
     <row r="139" ht="20" customHeight="1">
@@ -4503,7 +4503,7 @@
         </is>
       </c>
       <c r="E139" s="23" t="n">
-        <v>224</v>
+        <v>137</v>
       </c>
     </row>
     <row r="140" ht="20" customHeight="1">
@@ -4528,7 +4528,7 @@
         </is>
       </c>
       <c r="E140" s="20" t="n">
-        <v>131</v>
+        <v>237</v>
       </c>
     </row>
     <row r="141" ht="20" customHeight="1">
@@ -4553,7 +4553,7 @@
         </is>
       </c>
       <c r="E141" s="23" t="n">
-        <v>117</v>
+        <v>194</v>
       </c>
     </row>
     <row r="142" ht="20" customHeight="1">
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="E142" s="20" t="n">
-        <v>158</v>
+        <v>205</v>
       </c>
     </row>
     <row r="143" ht="20" customHeight="1">
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="E143" s="23" t="n">
-        <v>172</v>
+        <v>204</v>
       </c>
     </row>
     <row r="144" ht="20" customHeight="1">
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="E144" s="20" t="n">
-        <v>166</v>
+        <v>239</v>
       </c>
     </row>
     <row r="145" ht="20" customHeight="1">
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="E145" s="23" t="n">
-        <v>224</v>
+        <v>179</v>
       </c>
     </row>
     <row r="146" ht="20" customHeight="1">
@@ -4678,7 +4678,7 @@
         </is>
       </c>
       <c r="E146" s="20" t="n">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="147" ht="20" customHeight="1">
@@ -4703,7 +4703,7 @@
         </is>
       </c>
       <c r="E147" s="23" t="n">
-        <v>128</v>
+        <v>239</v>
       </c>
     </row>
     <row r="148" ht="20" customHeight="1">
@@ -4728,7 +4728,7 @@
         </is>
       </c>
       <c r="E148" s="20" t="n">
-        <v>111</v>
+        <v>231</v>
       </c>
     </row>
     <row r="149" ht="20" customHeight="1">
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c r="E149" s="23" t="n">
-        <v>165</v>
+        <v>122</v>
       </c>
     </row>
     <row r="150" ht="20" customHeight="1">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="E150" s="20" t="n">
-        <v>207</v>
+        <v>174</v>
       </c>
     </row>
     <row r="151" ht="20" customHeight="1">
@@ -4803,7 +4803,7 @@
         </is>
       </c>
       <c r="E151" s="23" t="n">
-        <v>178</v>
+        <v>161</v>
       </c>
     </row>
     <row r="152" ht="20" customHeight="1">
@@ -4828,7 +4828,7 @@
         </is>
       </c>
       <c r="E152" s="20" t="n">
-        <v>183</v>
+        <v>138</v>
       </c>
     </row>
     <row r="153" ht="20" customHeight="1">
@@ -4853,7 +4853,7 @@
         </is>
       </c>
       <c r="E153" s="23" t="n">
-        <v>209</v>
+        <v>147</v>
       </c>
     </row>
     <row r="154" ht="20" customHeight="1">
@@ -4878,7 +4878,7 @@
         </is>
       </c>
       <c r="E154" s="20" t="n">
-        <v>151</v>
+        <v>183</v>
       </c>
     </row>
     <row r="155" ht="20" customHeight="1">
@@ -4903,7 +4903,7 @@
         </is>
       </c>
       <c r="E155" s="23" t="n">
-        <v>236</v>
+        <v>130</v>
       </c>
     </row>
     <row r="156" ht="20" customHeight="1">
@@ -4928,7 +4928,7 @@
         </is>
       </c>
       <c r="E156" s="20" t="n">
-        <v>137</v>
+        <v>171</v>
       </c>
     </row>
     <row r="157" ht="20" customHeight="1">
@@ -4953,7 +4953,7 @@
         </is>
       </c>
       <c r="E157" s="23" t="n">
-        <v>170</v>
+        <v>215</v>
       </c>
     </row>
     <row r="158" ht="20" customHeight="1">
@@ -4978,7 +4978,7 @@
         </is>
       </c>
       <c r="E158" s="20" t="n">
-        <v>146</v>
+        <v>124</v>
       </c>
     </row>
     <row r="159" ht="20" customHeight="1">
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="E159" s="23" t="n">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="160" ht="20" customHeight="1">
@@ -5028,7 +5028,7 @@
         </is>
       </c>
       <c r="E160" s="20" t="n">
-        <v>185</v>
+        <v>219</v>
       </c>
     </row>
     <row r="161" ht="20" customHeight="1">
@@ -5053,7 +5053,7 @@
         </is>
       </c>
       <c r="E161" s="23" t="n">
-        <v>122</v>
+        <v>140</v>
       </c>
     </row>
     <row r="162" ht="20" customHeight="1">
@@ -5078,7 +5078,7 @@
         </is>
       </c>
       <c r="E162" s="20" t="n">
-        <v>224</v>
+        <v>240</v>
       </c>
     </row>
     <row r="163" ht="20" customHeight="1">
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="E163" s="23" t="n">
-        <v>185</v>
+        <v>162</v>
       </c>
     </row>
     <row r="164" ht="20" customHeight="1">
@@ -5128,7 +5128,7 @@
         </is>
       </c>
       <c r="E164" s="20" t="n">
-        <v>220</v>
+        <v>153</v>
       </c>
     </row>
     <row r="165" ht="20" customHeight="1">
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="E165" s="23" t="n">
-        <v>235</v>
+        <v>136</v>
       </c>
     </row>
     <row r="166" ht="20" customHeight="1">
@@ -5178,7 +5178,7 @@
         </is>
       </c>
       <c r="E166" s="20" t="n">
-        <v>125</v>
+        <v>158</v>
       </c>
     </row>
     <row r="167" ht="20" customHeight="1">
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="E167" s="23" t="n">
-        <v>125</v>
+        <v>156</v>
       </c>
     </row>
     <row r="168" ht="20" customHeight="1">
@@ -5228,7 +5228,7 @@
         </is>
       </c>
       <c r="E168" s="20" t="n">
-        <v>131</v>
+        <v>206</v>
       </c>
     </row>
     <row r="169" ht="20" customHeight="1">
@@ -5253,7 +5253,7 @@
         </is>
       </c>
       <c r="E169" s="23" t="n">
-        <v>158</v>
+        <v>169</v>
       </c>
     </row>
     <row r="170" ht="20" customHeight="1">
@@ -5278,7 +5278,7 @@
         </is>
       </c>
       <c r="E170" s="20" t="n">
-        <v>157</v>
+        <v>200</v>
       </c>
     </row>
     <row r="171" ht="20" customHeight="1">
@@ -5303,7 +5303,7 @@
         </is>
       </c>
       <c r="E171" s="23" t="n">
-        <v>189</v>
+        <v>129</v>
       </c>
     </row>
     <row r="172" ht="20" customHeight="1">
@@ -5328,7 +5328,7 @@
         </is>
       </c>
       <c r="E172" s="20" t="n">
-        <v>240</v>
+        <v>168</v>
       </c>
     </row>
     <row r="173" ht="20" customHeight="1">
@@ -5353,7 +5353,7 @@
         </is>
       </c>
       <c r="E173" s="23" t="n">
-        <v>233</v>
+        <v>204</v>
       </c>
     </row>
     <row r="174" ht="20" customHeight="1">
@@ -5378,7 +5378,7 @@
         </is>
       </c>
       <c r="E174" s="20" t="n">
-        <v>129</v>
+        <v>179</v>
       </c>
     </row>
     <row r="175" ht="20" customHeight="1">
@@ -5403,7 +5403,7 @@
         </is>
       </c>
       <c r="E175" s="23" t="n">
-        <v>169</v>
+        <v>126</v>
       </c>
     </row>
     <row r="176" ht="20" customHeight="1">
@@ -5428,7 +5428,7 @@
         </is>
       </c>
       <c r="E176" s="20" t="n">
-        <v>220</v>
+        <v>136</v>
       </c>
     </row>
     <row r="177" ht="20" customHeight="1">
@@ -5453,7 +5453,7 @@
         </is>
       </c>
       <c r="E177" s="23" t="n">
-        <v>130</v>
+        <v>172</v>
       </c>
     </row>
     <row r="178" ht="20" customHeight="1">
@@ -5478,7 +5478,7 @@
         </is>
       </c>
       <c r="E178" s="20" t="n">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="179" ht="20" customHeight="1">
@@ -5503,7 +5503,7 @@
         </is>
       </c>
       <c r="E179" s="23" t="n">
-        <v>171</v>
+        <v>213</v>
       </c>
     </row>
     <row r="180" ht="20" customHeight="1">
@@ -5528,7 +5528,7 @@
         </is>
       </c>
       <c r="E180" s="20" t="n">
-        <v>214</v>
+        <v>225</v>
       </c>
     </row>
     <row r="181" ht="20" customHeight="1">
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="E181" s="23" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="182" ht="20" customHeight="1">
@@ -5578,7 +5578,7 @@
         </is>
       </c>
       <c r="E182" s="20" t="n">
-        <v>133</v>
+        <v>119</v>
       </c>
     </row>
     <row r="183" ht="20" customHeight="1">
@@ -5603,7 +5603,7 @@
         </is>
       </c>
       <c r="E183" s="23" t="n">
-        <v>146</v>
+        <v>120</v>
       </c>
     </row>
     <row r="184" ht="20" customHeight="1">
@@ -5628,7 +5628,7 @@
         </is>
       </c>
       <c r="E184" s="20" t="n">
-        <v>168</v>
+        <v>221</v>
       </c>
     </row>
     <row r="185" ht="20" customHeight="1">
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="E185" s="23" t="n">
-        <v>121</v>
+        <v>143</v>
       </c>
     </row>
     <row r="186" ht="20" customHeight="1">
@@ -5678,7 +5678,7 @@
         </is>
       </c>
       <c r="E186" s="20" t="n">
-        <v>132</v>
+        <v>216</v>
       </c>
     </row>
     <row r="187" ht="20" customHeight="1">
@@ -5703,7 +5703,7 @@
         </is>
       </c>
       <c r="E187" s="23" t="n">
-        <v>113</v>
+        <v>163</v>
       </c>
     </row>
     <row r="188" ht="20" customHeight="1">
@@ -5728,7 +5728,7 @@
         </is>
       </c>
       <c r="E188" s="20" t="n">
-        <v>118</v>
+        <v>173</v>
       </c>
     </row>
     <row r="189" ht="20" customHeight="1">
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="E189" s="23" t="n">
-        <v>209</v>
+        <v>234</v>
       </c>
     </row>
     <row r="190" ht="20" customHeight="1">
@@ -5778,7 +5778,7 @@
         </is>
       </c>
       <c r="E190" s="20" t="n">
-        <v>123</v>
+        <v>217</v>
       </c>
     </row>
     <row r="191" ht="20" customHeight="1">
@@ -5803,7 +5803,7 @@
         </is>
       </c>
       <c r="E191" s="23" t="n">
-        <v>189</v>
+        <v>168</v>
       </c>
     </row>
     <row r="192" ht="20" customHeight="1">
@@ -5828,7 +5828,7 @@
         </is>
       </c>
       <c r="E192" s="20" t="n">
-        <v>214</v>
+        <v>139</v>
       </c>
     </row>
     <row r="193" ht="20" customHeight="1">
@@ -5853,7 +5853,7 @@
         </is>
       </c>
       <c r="E193" s="23" t="n">
-        <v>140</v>
+        <v>195</v>
       </c>
     </row>
     <row r="194" ht="20" customHeight="1">
@@ -5878,7 +5878,7 @@
         </is>
       </c>
       <c r="E194" s="20" t="n">
-        <v>129</v>
+        <v>185</v>
       </c>
     </row>
     <row r="195" ht="20" customHeight="1">
@@ -5903,7 +5903,7 @@
         </is>
       </c>
       <c r="E195" s="23" t="n">
-        <v>157</v>
+        <v>111</v>
       </c>
     </row>
     <row r="196" ht="20" customHeight="1">
@@ -5928,7 +5928,7 @@
         </is>
       </c>
       <c r="E196" s="20" t="n">
-        <v>162</v>
+        <v>150</v>
       </c>
     </row>
     <row r="197" ht="20" customHeight="1">
@@ -5953,7 +5953,7 @@
         </is>
       </c>
       <c r="E197" s="23" t="n">
-        <v>137</v>
+        <v>167</v>
       </c>
     </row>
     <row r="198" ht="20" customHeight="1">
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="E198" s="20" t="n">
-        <v>174</v>
+        <v>224</v>
       </c>
     </row>
     <row r="199" ht="20" customHeight="1">
@@ -6003,7 +6003,7 @@
         </is>
       </c>
       <c r="E199" s="23" t="n">
-        <v>176</v>
+        <v>214</v>
       </c>
     </row>
     <row r="200" ht="20" customHeight="1">
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="E200" s="20" t="n">
-        <v>158</v>
+        <v>171</v>
       </c>
     </row>
     <row r="201" ht="20" customHeight="1">
@@ -6053,7 +6053,7 @@
         </is>
       </c>
       <c r="E201" s="23" t="n">
-        <v>193</v>
+        <v>163</v>
       </c>
     </row>
     <row r="202" ht="20" customHeight="1">
@@ -6078,7 +6078,7 @@
         </is>
       </c>
       <c r="E202" s="20" t="n">
-        <v>158</v>
+        <v>170</v>
       </c>
     </row>
     <row r="203" ht="20" customHeight="1">
@@ -6103,7 +6103,7 @@
         </is>
       </c>
       <c r="E203" s="23" t="n">
-        <v>174</v>
+        <v>149</v>
       </c>
     </row>
     <row r="204" ht="20" customHeight="1">
@@ -6128,7 +6128,7 @@
         </is>
       </c>
       <c r="E204" s="20" t="n">
-        <v>221</v>
+        <v>238</v>
       </c>
     </row>
     <row r="205" ht="20" customHeight="1">
@@ -6153,7 +6153,7 @@
         </is>
       </c>
       <c r="E205" s="23" t="n">
-        <v>179</v>
+        <v>145</v>
       </c>
     </row>
     <row r="206" ht="20" customHeight="1">
@@ -6178,7 +6178,7 @@
         </is>
       </c>
       <c r="E206" s="20" t="n">
-        <v>182</v>
+        <v>209</v>
       </c>
     </row>
     <row r="207" ht="20" customHeight="1">
@@ -6203,7 +6203,7 @@
         </is>
       </c>
       <c r="E207" s="23" t="n">
-        <v>152</v>
+        <v>220</v>
       </c>
     </row>
     <row r="208" ht="20" customHeight="1">
@@ -6228,7 +6228,7 @@
         </is>
       </c>
       <c r="E208" s="20" t="n">
-        <v>183</v>
+        <v>228</v>
       </c>
     </row>
     <row r="209" ht="20" customHeight="1">
@@ -6253,7 +6253,7 @@
         </is>
       </c>
       <c r="E209" s="23" t="n">
-        <v>192</v>
+        <v>147</v>
       </c>
     </row>
     <row r="210" ht="20" customHeight="1">
@@ -6278,7 +6278,7 @@
         </is>
       </c>
       <c r="E210" s="20" t="n">
-        <v>173</v>
+        <v>233</v>
       </c>
     </row>
     <row r="211" ht="20" customHeight="1">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="E211" s="23" t="n">
-        <v>116</v>
+        <v>219</v>
       </c>
     </row>
     <row r="212" ht="20" customHeight="1">
@@ -6328,7 +6328,7 @@
         </is>
       </c>
       <c r="E212" s="20" t="n">
-        <v>133</v>
+        <v>158</v>
       </c>
     </row>
     <row r="213" ht="20" customHeight="1">
@@ -6353,7 +6353,7 @@
         </is>
       </c>
       <c r="E213" s="23" t="n">
-        <v>133</v>
+        <v>175</v>
       </c>
     </row>
     <row r="214" ht="20" customHeight="1">
@@ -6378,7 +6378,7 @@
         </is>
       </c>
       <c r="E214" s="20" t="n">
-        <v>128</v>
+        <v>216</v>
       </c>
     </row>
     <row r="215" ht="20" customHeight="1">
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="E215" s="23" t="n">
-        <v>165</v>
+        <v>119</v>
       </c>
     </row>
     <row r="216" ht="20" customHeight="1">
@@ -6428,7 +6428,7 @@
         </is>
       </c>
       <c r="E216" s="20" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="217" ht="20" customHeight="1">
@@ -6453,7 +6453,7 @@
         </is>
       </c>
       <c r="E217" s="23" t="n">
-        <v>216</v>
+        <v>146</v>
       </c>
     </row>
     <row r="218" ht="20" customHeight="1">
@@ -6478,7 +6478,7 @@
         </is>
       </c>
       <c r="E218" s="20" t="n">
-        <v>208</v>
+        <v>123</v>
       </c>
     </row>
     <row r="219" ht="20" customHeight="1">
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="E219" s="23" t="n">
-        <v>148</v>
+        <v>176</v>
       </c>
     </row>
     <row r="220" ht="20" customHeight="1">
@@ -6528,7 +6528,7 @@
         </is>
       </c>
       <c r="E220" s="20" t="n">
-        <v>114</v>
+        <v>164</v>
       </c>
     </row>
     <row r="221" ht="20" customHeight="1">
@@ -6553,7 +6553,7 @@
         </is>
       </c>
       <c r="E221" s="23" t="n">
-        <v>203</v>
+        <v>153</v>
       </c>
     </row>
     <row r="222" ht="20" customHeight="1">
@@ -6578,7 +6578,7 @@
         </is>
       </c>
       <c r="E222" s="20" t="n">
-        <v>172</v>
+        <v>238</v>
       </c>
     </row>
     <row r="223" ht="20" customHeight="1">
@@ -6603,7 +6603,7 @@
         </is>
       </c>
       <c r="E223" s="23" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="224" ht="20" customHeight="1">
@@ -6628,7 +6628,7 @@
         </is>
       </c>
       <c r="E224" s="20" t="n">
-        <v>130</v>
+        <v>227</v>
       </c>
     </row>
     <row r="225" ht="20" customHeight="1">
@@ -6653,7 +6653,7 @@
         </is>
       </c>
       <c r="E225" s="23" t="n">
-        <v>168</v>
+        <v>208</v>
       </c>
     </row>
     <row r="226" ht="20" customHeight="1">
@@ -6678,7 +6678,7 @@
         </is>
       </c>
       <c r="E226" s="20" t="n">
-        <v>134</v>
+        <v>161</v>
       </c>
     </row>
     <row r="227" ht="20" customHeight="1">
@@ -6703,7 +6703,7 @@
         </is>
       </c>
       <c r="E227" s="23" t="n">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="228" ht="20" customHeight="1">
@@ -6728,7 +6728,7 @@
         </is>
       </c>
       <c r="E228" s="20" t="n">
-        <v>179</v>
+        <v>220</v>
       </c>
     </row>
     <row r="229" ht="20" customHeight="1">
@@ -6753,7 +6753,7 @@
         </is>
       </c>
       <c r="E229" s="23" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="230" ht="20" customHeight="1">
@@ -6778,7 +6778,7 @@
         </is>
       </c>
       <c r="E230" s="20" t="n">
-        <v>177</v>
+        <v>236</v>
       </c>
     </row>
     <row r="231" ht="20" customHeight="1">
@@ -6803,7 +6803,7 @@
         </is>
       </c>
       <c r="E231" s="23" t="n">
-        <v>224</v>
+        <v>181</v>
       </c>
     </row>
     <row r="232" ht="20" customHeight="1">
@@ -6828,7 +6828,7 @@
         </is>
       </c>
       <c r="E232" s="20" t="n">
-        <v>158</v>
+        <v>219</v>
       </c>
     </row>
     <row r="233" ht="20" customHeight="1">
@@ -6853,7 +6853,7 @@
         </is>
       </c>
       <c r="E233" s="23" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="234" ht="20" customHeight="1">
@@ -6878,7 +6878,7 @@
         </is>
       </c>
       <c r="E234" s="20" t="n">
-        <v>164</v>
+        <v>150</v>
       </c>
     </row>
     <row r="235" ht="20" customHeight="1">
@@ -6903,7 +6903,7 @@
         </is>
       </c>
       <c r="E235" s="23" t="n">
-        <v>224</v>
+        <v>171</v>
       </c>
     </row>
     <row r="236" ht="20" customHeight="1">
@@ -6928,7 +6928,7 @@
         </is>
       </c>
       <c r="E236" s="20" t="n">
-        <v>220</v>
+        <v>176</v>
       </c>
     </row>
     <row r="237" ht="20" customHeight="1">
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="E237" s="23" t="n">
-        <v>188</v>
+        <v>115</v>
       </c>
     </row>
     <row r="238" ht="20" customHeight="1">
@@ -6978,7 +6978,7 @@
         </is>
       </c>
       <c r="E238" s="20" t="n">
-        <v>236</v>
+        <v>132</v>
       </c>
     </row>
     <row r="239" ht="20" customHeight="1">
@@ -7003,7 +7003,7 @@
         </is>
       </c>
       <c r="E239" s="23" t="n">
-        <v>116</v>
+        <v>216</v>
       </c>
     </row>
     <row r="240" ht="20" customHeight="1">
@@ -7028,7 +7028,7 @@
         </is>
       </c>
       <c r="E240" s="20" t="n">
-        <v>159</v>
+        <v>233</v>
       </c>
     </row>
     <row r="241" ht="20" customHeight="1">
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="E241" s="23" t="n">
-        <v>177</v>
+        <v>112</v>
       </c>
     </row>
     <row r="242" ht="20" customHeight="1">
@@ -7078,7 +7078,7 @@
         </is>
       </c>
       <c r="E242" s="20" t="n">
-        <v>162</v>
+        <v>211</v>
       </c>
     </row>
     <row r="243" ht="20" customHeight="1">
@@ -7103,7 +7103,7 @@
         </is>
       </c>
       <c r="E243" s="23" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="244" ht="20" customHeight="1">
@@ -7128,7 +7128,7 @@
         </is>
       </c>
       <c r="E244" s="20" t="n">
-        <v>110</v>
+        <v>163</v>
       </c>
     </row>
     <row r="245" ht="20" customHeight="1">
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="E245" s="23" t="n">
-        <v>189</v>
+        <v>171</v>
       </c>
     </row>
     <row r="246" ht="20" customHeight="1">
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="E246" s="20" t="n">
-        <v>182</v>
+        <v>191</v>
       </c>
     </row>
     <row r="247" ht="20" customHeight="1">
@@ -7203,7 +7203,7 @@
         </is>
       </c>
       <c r="E247" s="23" t="n">
-        <v>215</v>
+        <v>220</v>
       </c>
     </row>
     <row r="248" ht="20" customHeight="1">
@@ -7228,7 +7228,7 @@
         </is>
       </c>
       <c r="E248" s="20" t="n">
-        <v>147</v>
+        <v>170</v>
       </c>
     </row>
     <row r="249" ht="20" customHeight="1">
@@ -7253,7 +7253,7 @@
         </is>
       </c>
       <c r="E249" s="23" t="n">
-        <v>145</v>
+        <v>121</v>
       </c>
     </row>
     <row r="250" ht="20" customHeight="1">
@@ -7278,7 +7278,7 @@
         </is>
       </c>
       <c r="E250" s="20" t="n">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="251" ht="20" customHeight="1">
@@ -7303,7 +7303,7 @@
         </is>
       </c>
       <c r="E251" s="23" t="n">
-        <v>236</v>
+        <v>171</v>
       </c>
     </row>
     <row r="252" ht="20" customHeight="1">
@@ -7328,7 +7328,7 @@
         </is>
       </c>
       <c r="E252" s="20" t="n">
-        <v>120</v>
+        <v>210</v>
       </c>
     </row>
     <row r="253" ht="20" customHeight="1">
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="E253" s="23" t="n">
-        <v>178</v>
+        <v>214</v>
       </c>
     </row>
     <row r="254" ht="20" customHeight="1">
@@ -7378,7 +7378,7 @@
         </is>
       </c>
       <c r="E254" s="20" t="n">
-        <v>113</v>
+        <v>146</v>
       </c>
     </row>
     <row r="255" ht="20" customHeight="1">
@@ -7403,7 +7403,7 @@
         </is>
       </c>
       <c r="E255" s="23" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="256" ht="20" customHeight="1">
@@ -7428,7 +7428,7 @@
         </is>
       </c>
       <c r="E256" s="20" t="n">
-        <v>126</v>
+        <v>155</v>
       </c>
     </row>
     <row r="257" ht="20" customHeight="1">
@@ -7453,7 +7453,7 @@
         </is>
       </c>
       <c r="E257" s="23" t="n">
-        <v>163</v>
+        <v>216</v>
       </c>
     </row>
     <row r="258" ht="20" customHeight="1">
@@ -7478,7 +7478,7 @@
         </is>
       </c>
       <c r="E258" s="20" t="n">
-        <v>112</v>
+        <v>127</v>
       </c>
     </row>
     <row r="259" ht="20" customHeight="1">
@@ -7503,7 +7503,7 @@
         </is>
       </c>
       <c r="E259" s="23" t="n">
-        <v>125</v>
+        <v>144</v>
       </c>
     </row>
     <row r="260" ht="20" customHeight="1">
@@ -7528,7 +7528,7 @@
         </is>
       </c>
       <c r="E260" s="20" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="261" ht="20" customHeight="1">
@@ -7553,7 +7553,7 @@
         </is>
       </c>
       <c r="E261" s="23" t="n">
-        <v>201</v>
+        <v>129</v>
       </c>
     </row>
     <row r="262" ht="20" customHeight="1">
@@ -7578,7 +7578,7 @@
         </is>
       </c>
       <c r="E262" s="20" t="n">
-        <v>224</v>
+        <v>132</v>
       </c>
     </row>
     <row r="263" ht="20" customHeight="1">
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="E263" s="23" t="n">
-        <v>127</v>
+        <v>162</v>
       </c>
     </row>
     <row r="264" ht="20" customHeight="1">
@@ -7628,7 +7628,7 @@
         </is>
       </c>
       <c r="E264" s="20" t="n">
-        <v>220</v>
+        <v>192</v>
       </c>
     </row>
     <row r="265" ht="20" customHeight="1">
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="E265" s="23" t="n">
-        <v>138</v>
+        <v>203</v>
       </c>
     </row>
     <row r="266" ht="20" customHeight="1">
@@ -7678,7 +7678,7 @@
         </is>
       </c>
       <c r="E266" s="20" t="n">
-        <v>190</v>
+        <v>176</v>
       </c>
     </row>
     <row r="267" ht="20" customHeight="1">
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="E267" s="23" t="n">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="268" ht="20" customHeight="1">
@@ -7728,7 +7728,7 @@
         </is>
       </c>
       <c r="E268" s="20" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="269" ht="20" customHeight="1">
@@ -7753,7 +7753,7 @@
         </is>
       </c>
       <c r="E269" s="23" t="n">
-        <v>162</v>
+        <v>193</v>
       </c>
     </row>
     <row r="270" ht="20" customHeight="1">
@@ -7778,7 +7778,7 @@
         </is>
       </c>
       <c r="E270" s="20" t="n">
-        <v>130</v>
+        <v>196</v>
       </c>
     </row>
     <row r="271" ht="20" customHeight="1">
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="E271" s="23" t="n">
-        <v>132</v>
+        <v>157</v>
       </c>
     </row>
     <row r="272" ht="20" customHeight="1">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="E272" s="20" t="n">
-        <v>167</v>
+        <v>153</v>
       </c>
     </row>
     <row r="273" ht="20" customHeight="1">
@@ -7853,7 +7853,7 @@
         </is>
       </c>
       <c r="E273" s="23" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="274" ht="20" customHeight="1">
@@ -7878,7 +7878,7 @@
         </is>
       </c>
       <c r="E274" s="20" t="n">
-        <v>189</v>
+        <v>143</v>
       </c>
     </row>
     <row r="275" ht="20" customHeight="1">
@@ -7903,7 +7903,7 @@
         </is>
       </c>
       <c r="E275" s="23" t="n">
-        <v>228</v>
+        <v>121</v>
       </c>
     </row>
     <row r="276" ht="20" customHeight="1">
@@ -7928,7 +7928,7 @@
         </is>
       </c>
       <c r="E276" s="20" t="n">
-        <v>200</v>
+        <v>191</v>
       </c>
     </row>
     <row r="277" ht="20" customHeight="1">
@@ -7953,7 +7953,7 @@
         </is>
       </c>
       <c r="E277" s="23" t="n">
-        <v>229</v>
+        <v>162</v>
       </c>
     </row>
     <row r="278" ht="20" customHeight="1">
@@ -7978,7 +7978,7 @@
         </is>
       </c>
       <c r="E278" s="20" t="n">
-        <v>210</v>
+        <v>182</v>
       </c>
     </row>
     <row r="279" ht="20" customHeight="1">
@@ -8003,7 +8003,7 @@
         </is>
       </c>
       <c r="E279" s="23" t="n">
-        <v>168</v>
+        <v>112</v>
       </c>
     </row>
     <row r="280" ht="20" customHeight="1">
@@ -8028,7 +8028,7 @@
         </is>
       </c>
       <c r="E280" s="20" t="n">
-        <v>129</v>
+        <v>235</v>
       </c>
     </row>
     <row r="281" ht="20" customHeight="1">
@@ -8053,7 +8053,7 @@
         </is>
       </c>
       <c r="E281" s="23" t="n">
-        <v>192</v>
+        <v>234</v>
       </c>
     </row>
     <row r="282" ht="20" customHeight="1">
@@ -8078,7 +8078,7 @@
         </is>
       </c>
       <c r="E282" s="20" t="n">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="283" ht="20" customHeight="1">
@@ -8103,7 +8103,7 @@
         </is>
       </c>
       <c r="E283" s="23" t="n">
-        <v>214</v>
+        <v>162</v>
       </c>
     </row>
     <row r="284" ht="20" customHeight="1">
@@ -8128,7 +8128,7 @@
         </is>
       </c>
       <c r="E284" s="20" t="n">
-        <v>142</v>
+        <v>200</v>
       </c>
     </row>
     <row r="285" ht="20" customHeight="1">
@@ -8153,7 +8153,7 @@
         </is>
       </c>
       <c r="E285" s="23" t="n">
-        <v>126</v>
+        <v>182</v>
       </c>
     </row>
     <row r="286" ht="20" customHeight="1">
@@ -8178,7 +8178,7 @@
         </is>
       </c>
       <c r="E286" s="20" t="n">
-        <v>195</v>
+        <v>136</v>
       </c>
     </row>
     <row r="287" ht="20" customHeight="1">
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="E287" s="23" t="n">
-        <v>120</v>
+        <v>226</v>
       </c>
     </row>
     <row r="288" ht="20" customHeight="1">
@@ -8228,7 +8228,7 @@
         </is>
       </c>
       <c r="E288" s="20" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="289" ht="20" customHeight="1">
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="E289" s="23" t="n">
-        <v>173</v>
+        <v>115</v>
       </c>
     </row>
     <row r="290" ht="20" customHeight="1">
@@ -8278,7 +8278,7 @@
         </is>
       </c>
       <c r="E290" s="20" t="n">
-        <v>144</v>
+        <v>187</v>
       </c>
     </row>
     <row r="291" ht="20" customHeight="1">
@@ -8303,7 +8303,7 @@
         </is>
       </c>
       <c r="E291" s="23" t="n">
-        <v>194</v>
+        <v>229</v>
       </c>
     </row>
     <row r="292" ht="20" customHeight="1">
@@ -8328,7 +8328,7 @@
         </is>
       </c>
       <c r="E292" s="20" t="n">
-        <v>137</v>
+        <v>148</v>
       </c>
     </row>
     <row r="293" ht="20" customHeight="1">
@@ -8353,7 +8353,7 @@
         </is>
       </c>
       <c r="E293" s="23" t="n">
-        <v>112</v>
+        <v>233</v>
       </c>
     </row>
     <row r="294" ht="20" customHeight="1">
@@ -8378,7 +8378,7 @@
         </is>
       </c>
       <c r="E294" s="20" t="n">
-        <v>184</v>
+        <v>175</v>
       </c>
     </row>
     <row r="295" ht="20" customHeight="1">
@@ -8403,7 +8403,7 @@
         </is>
       </c>
       <c r="E295" s="23" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="296" ht="20" customHeight="1">
@@ -8428,7 +8428,7 @@
         </is>
       </c>
       <c r="E296" s="20" t="n">
-        <v>187</v>
+        <v>238</v>
       </c>
     </row>
     <row r="297" ht="20" customHeight="1">
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="E297" s="23" t="n">
-        <v>196</v>
+        <v>212</v>
       </c>
     </row>
     <row r="298" ht="20" customHeight="1">
@@ -8478,7 +8478,7 @@
         </is>
       </c>
       <c r="E298" s="20" t="n">
-        <v>225</v>
+        <v>184</v>
       </c>
     </row>
     <row r="299" ht="20" customHeight="1">
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="E299" s="23" t="n">
-        <v>123</v>
+        <v>155</v>
       </c>
     </row>
     <row r="300" ht="20" customHeight="1">
@@ -8528,7 +8528,7 @@
         </is>
       </c>
       <c r="E300" s="20" t="n">
-        <v>211</v>
+        <v>169</v>
       </c>
     </row>
     <row r="301" ht="20" customHeight="1">
@@ -8553,7 +8553,7 @@
         </is>
       </c>
       <c r="E301" s="23" t="n">
-        <v>149</v>
+        <v>173</v>
       </c>
     </row>
     <row r="302" ht="20" customHeight="1">
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="E302" s="20" t="n">
-        <v>157</v>
+        <v>173</v>
       </c>
     </row>
     <row r="303" ht="20" customHeight="1">
@@ -8603,7 +8603,7 @@
         </is>
       </c>
       <c r="E303" s="23" t="n">
-        <v>174</v>
+        <v>221</v>
       </c>
     </row>
     <row r="304" ht="20" customHeight="1">
@@ -8628,7 +8628,7 @@
         </is>
       </c>
       <c r="E304" s="20" t="n">
-        <v>194</v>
+        <v>157</v>
       </c>
     </row>
     <row r="305" ht="20" customHeight="1">
@@ -8653,7 +8653,7 @@
         </is>
       </c>
       <c r="E305" s="23" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="306" ht="20" customHeight="1">
@@ -8678,7 +8678,7 @@
         </is>
       </c>
       <c r="E306" s="20" t="n">
-        <v>183</v>
+        <v>190</v>
       </c>
     </row>
     <row r="307" ht="20" customHeight="1">
@@ -8703,7 +8703,7 @@
         </is>
       </c>
       <c r="E307" s="23" t="n">
-        <v>144</v>
+        <v>116</v>
       </c>
     </row>
     <row r="308" ht="20" customHeight="1">
@@ -8728,7 +8728,7 @@
         </is>
       </c>
       <c r="E308" s="20" t="n">
-        <v>191</v>
+        <v>176</v>
       </c>
     </row>
     <row r="309" ht="20" customHeight="1">
@@ -8753,7 +8753,7 @@
         </is>
       </c>
       <c r="E309" s="23" t="n">
-        <v>139</v>
+        <v>148</v>
       </c>
     </row>
     <row r="310" ht="20" customHeight="1">
@@ -8778,7 +8778,7 @@
         </is>
       </c>
       <c r="E310" s="20" t="n">
-        <v>193</v>
+        <v>204</v>
       </c>
     </row>
     <row r="311" ht="20" customHeight="1">
@@ -8803,7 +8803,7 @@
         </is>
       </c>
       <c r="E311" s="23" t="n">
-        <v>148</v>
+        <v>124</v>
       </c>
     </row>
     <row r="312" ht="20" customHeight="1">
@@ -8828,7 +8828,7 @@
         </is>
       </c>
       <c r="E312" s="20" t="n">
-        <v>157</v>
+        <v>184</v>
       </c>
     </row>
     <row r="313" ht="20" customHeight="1">
@@ -8853,7 +8853,7 @@
         </is>
       </c>
       <c r="E313" s="23" t="n">
-        <v>154</v>
+        <v>114</v>
       </c>
     </row>
     <row r="314" ht="20" customHeight="1">
@@ -8878,7 +8878,7 @@
         </is>
       </c>
       <c r="E314" s="20" t="n">
-        <v>156</v>
+        <v>206</v>
       </c>
     </row>
     <row r="315" ht="20" customHeight="1">
@@ -8903,7 +8903,7 @@
         </is>
       </c>
       <c r="E315" s="23" t="n">
-        <v>146</v>
+        <v>173</v>
       </c>
     </row>
     <row r="316" ht="20" customHeight="1">
@@ -8953,7 +8953,7 @@
         </is>
       </c>
       <c r="E317" s="23" t="n">
-        <v>240</v>
+        <v>123</v>
       </c>
     </row>
     <row r="318" ht="20" customHeight="1">
@@ -8978,7 +8978,7 @@
         </is>
       </c>
       <c r="E318" s="20" t="n">
-        <v>202</v>
+        <v>220</v>
       </c>
     </row>
     <row r="319" ht="20" customHeight="1">
@@ -9003,7 +9003,7 @@
         </is>
       </c>
       <c r="E319" s="23" t="n">
-        <v>160</v>
+        <v>220</v>
       </c>
     </row>
     <row r="320" ht="20" customHeight="1">
@@ -9028,7 +9028,7 @@
         </is>
       </c>
       <c r="E320" s="20" t="n">
-        <v>172</v>
+        <v>135</v>
       </c>
     </row>
     <row r="321" ht="20" customHeight="1">
@@ -9053,7 +9053,7 @@
         </is>
       </c>
       <c r="E321" s="23" t="n">
-        <v>118</v>
+        <v>170</v>
       </c>
     </row>
     <row r="322" ht="20" customHeight="1">
@@ -9078,7 +9078,7 @@
         </is>
       </c>
       <c r="E322" s="20" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
     </row>
     <row r="323" ht="20" customHeight="1">
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="E323" s="23" t="n">
-        <v>188</v>
+        <v>231</v>
       </c>
     </row>
     <row r="324" ht="20" customHeight="1">
@@ -9153,7 +9153,7 @@
         </is>
       </c>
       <c r="E325" s="23" t="n">
-        <v>208</v>
+        <v>173</v>
       </c>
     </row>
     <row r="326" ht="20" customHeight="1">
@@ -9178,7 +9178,7 @@
         </is>
       </c>
       <c r="E326" s="20" t="n">
-        <v>195</v>
+        <v>208</v>
       </c>
     </row>
     <row r="327" ht="20" customHeight="1">
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="E327" s="23" t="n">
-        <v>169</v>
+        <v>123</v>
       </c>
     </row>
     <row r="328" ht="20" customHeight="1">
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="E328" s="20" t="n">
-        <v>203</v>
+        <v>151</v>
       </c>
     </row>
     <row r="329" ht="20" customHeight="1">
@@ -9253,7 +9253,7 @@
         </is>
       </c>
       <c r="E329" s="23" t="n">
-        <v>238</v>
+        <v>174</v>
       </c>
     </row>
     <row r="330" ht="20" customHeight="1">
@@ -9278,7 +9278,7 @@
         </is>
       </c>
       <c r="E330" s="20" t="n">
-        <v>128</v>
+        <v>198</v>
       </c>
     </row>
     <row r="331" ht="20" customHeight="1">
@@ -9303,7 +9303,7 @@
         </is>
       </c>
       <c r="E331" s="23" t="n">
-        <v>182</v>
+        <v>155</v>
       </c>
     </row>
     <row r="332" ht="20" customHeight="1">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="E333" s="23" t="n">
-        <v>127</v>
+        <v>217</v>
       </c>
     </row>
     <row r="334" ht="20" customHeight="1">
@@ -9378,7 +9378,7 @@
         </is>
       </c>
       <c r="E334" s="20" t="n">
-        <v>201</v>
+        <v>138</v>
       </c>
     </row>
     <row r="335" ht="20" customHeight="1">
@@ -9403,7 +9403,7 @@
         </is>
       </c>
       <c r="E335" s="23" t="n">
-        <v>170</v>
+        <v>141</v>
       </c>
     </row>
     <row r="336" ht="20" customHeight="1">
@@ -9428,7 +9428,7 @@
         </is>
       </c>
       <c r="E336" s="20" t="n">
-        <v>149</v>
+        <v>185</v>
       </c>
     </row>
     <row r="337" ht="20" customHeight="1">
@@ -9453,7 +9453,7 @@
         </is>
       </c>
       <c r="E337" s="23" t="n">
-        <v>201</v>
+        <v>125</v>
       </c>
     </row>
     <row r="338" ht="20" customHeight="1">
@@ -9478,7 +9478,7 @@
         </is>
       </c>
       <c r="E338" s="20" t="n">
-        <v>235</v>
+        <v>127</v>
       </c>
     </row>
     <row r="339" ht="20" customHeight="1">
@@ -9503,7 +9503,7 @@
         </is>
       </c>
       <c r="E339" s="23" t="n">
-        <v>146</v>
+        <v>206</v>
       </c>
     </row>
     <row r="340" ht="20" customHeight="1">
@@ -9528,7 +9528,7 @@
         </is>
       </c>
       <c r="E340" s="20" t="n">
-        <v>230</v>
+        <v>145</v>
       </c>
     </row>
     <row r="341" ht="20" customHeight="1">
@@ -9553,7 +9553,7 @@
         </is>
       </c>
       <c r="E341" s="23" t="n">
-        <v>149</v>
+        <v>208</v>
       </c>
     </row>
     <row r="342" ht="20" customHeight="1">
@@ -9578,7 +9578,7 @@
         </is>
       </c>
       <c r="E342" s="20" t="n">
-        <v>131</v>
+        <v>180</v>
       </c>
     </row>
     <row r="343" ht="20" customHeight="1">
@@ -9603,7 +9603,7 @@
         </is>
       </c>
       <c r="E343" s="23" t="n">
-        <v>170</v>
+        <v>209</v>
       </c>
     </row>
     <row r="344" ht="20" customHeight="1">
@@ -9628,7 +9628,7 @@
         </is>
       </c>
       <c r="E344" s="20" t="n">
-        <v>221</v>
+        <v>210</v>
       </c>
     </row>
     <row r="345" ht="20" customHeight="1">
@@ -9653,7 +9653,7 @@
         </is>
       </c>
       <c r="E345" s="23" t="n">
-        <v>115</v>
+        <v>172</v>
       </c>
     </row>
     <row r="346" ht="20" customHeight="1">
@@ -9678,7 +9678,7 @@
         </is>
       </c>
       <c r="E346" s="20" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="347" ht="20" customHeight="1">
@@ -9703,7 +9703,7 @@
         </is>
       </c>
       <c r="E347" s="23" t="n">
-        <v>224</v>
+        <v>167</v>
       </c>
     </row>
     <row r="348" ht="20" customHeight="1">
@@ -9728,7 +9728,7 @@
         </is>
       </c>
       <c r="E348" s="20" t="n">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="349" ht="20" customHeight="1">
@@ -9753,7 +9753,7 @@
         </is>
       </c>
       <c r="E349" s="23" t="n">
-        <v>184</v>
+        <v>199</v>
       </c>
     </row>
     <row r="350" ht="20" customHeight="1">
@@ -9778,7 +9778,7 @@
         </is>
       </c>
       <c r="E350" s="20" t="n">
-        <v>113</v>
+        <v>151</v>
       </c>
     </row>
     <row r="351" ht="20" customHeight="1">
@@ -9803,7 +9803,7 @@
         </is>
       </c>
       <c r="E351" s="23" t="n">
-        <v>126</v>
+        <v>236</v>
       </c>
     </row>
     <row r="352" ht="20" customHeight="1">
@@ -9828,7 +9828,7 @@
         </is>
       </c>
       <c r="E352" s="20" t="n">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="353" ht="20" customHeight="1">
@@ -9853,7 +9853,7 @@
         </is>
       </c>
       <c r="E353" s="23" t="n">
-        <v>113</v>
+        <v>121</v>
       </c>
     </row>
     <row r="354" ht="20" customHeight="1">
@@ -9878,7 +9878,7 @@
         </is>
       </c>
       <c r="E354" s="20" t="n">
-        <v>221</v>
+        <v>225</v>
       </c>
     </row>
     <row r="355" ht="20" customHeight="1">
@@ -9903,7 +9903,7 @@
         </is>
       </c>
       <c r="E355" s="23" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="356" ht="20" customHeight="1">
@@ -9928,7 +9928,7 @@
         </is>
       </c>
       <c r="E356" s="20" t="n">
-        <v>169</v>
+        <v>161</v>
       </c>
     </row>
     <row r="357" ht="20" customHeight="1">
@@ -9953,7 +9953,7 @@
         </is>
       </c>
       <c r="E357" s="23" t="n">
-        <v>131</v>
+        <v>140</v>
       </c>
     </row>
     <row r="358" ht="20" customHeight="1">
@@ -9978,7 +9978,7 @@
         </is>
       </c>
       <c r="E358" s="20" t="n">
-        <v>157</v>
+        <v>130</v>
       </c>
     </row>
     <row r="359" ht="20" customHeight="1">
@@ -10003,7 +10003,7 @@
         </is>
       </c>
       <c r="E359" s="23" t="n">
-        <v>214</v>
+        <v>177</v>
       </c>
     </row>
     <row r="360" ht="20" customHeight="1">
@@ -10028,7 +10028,7 @@
         </is>
       </c>
       <c r="E360" s="20" t="n">
-        <v>172</v>
+        <v>150</v>
       </c>
     </row>
     <row r="361" ht="20" customHeight="1">
@@ -10053,7 +10053,7 @@
         </is>
       </c>
       <c r="E361" s="23" t="n">
-        <v>110</v>
+        <v>182</v>
       </c>
     </row>
     <row r="362" ht="20" customHeight="1">
@@ -10078,7 +10078,7 @@
         </is>
       </c>
       <c r="E362" s="20" t="n">
-        <v>188</v>
+        <v>129</v>
       </c>
     </row>
     <row r="363" ht="20" customHeight="1">
@@ -10103,7 +10103,7 @@
         </is>
       </c>
       <c r="E363" s="23" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="364" ht="20" customHeight="1">
@@ -10128,7 +10128,7 @@
         </is>
       </c>
       <c r="E364" s="20" t="n">
-        <v>159</v>
+        <v>179</v>
       </c>
     </row>
     <row r="365" ht="20" customHeight="1">
@@ -10153,7 +10153,7 @@
         </is>
       </c>
       <c r="E365" s="23" t="n">
-        <v>228</v>
+        <v>123</v>
       </c>
     </row>
     <row r="366" ht="20" customHeight="1">
@@ -10178,7 +10178,7 @@
         </is>
       </c>
       <c r="E366" s="20" t="n">
-        <v>188</v>
+        <v>111</v>
       </c>
     </row>
     <row r="367" ht="20" customHeight="1">
@@ -10203,7 +10203,7 @@
         </is>
       </c>
       <c r="E367" s="23" t="n">
-        <v>131</v>
+        <v>169</v>
       </c>
     </row>
     <row r="368" ht="20" customHeight="1">
@@ -10228,7 +10228,7 @@
         </is>
       </c>
       <c r="E368" s="20" t="n">
-        <v>152</v>
+        <v>227</v>
       </c>
     </row>
     <row r="369" ht="20" customHeight="1">
@@ -10278,7 +10278,7 @@
         </is>
       </c>
       <c r="E370" s="20" t="n">
-        <v>200</v>
+        <v>134</v>
       </c>
     </row>
     <row r="371" ht="20" customHeight="1">
@@ -10303,7 +10303,7 @@
         </is>
       </c>
       <c r="E371" s="23" t="n">
-        <v>182</v>
+        <v>110</v>
       </c>
     </row>
     <row r="372" ht="20" customHeight="1">
@@ -10328,7 +10328,7 @@
         </is>
       </c>
       <c r="E372" s="20" t="n">
-        <v>134</v>
+        <v>212</v>
       </c>
     </row>
     <row r="373" ht="20" customHeight="1">
@@ -10353,7 +10353,7 @@
         </is>
       </c>
       <c r="E373" s="23" t="n">
-        <v>157</v>
+        <v>214</v>
       </c>
     </row>
     <row r="374" ht="20" customHeight="1">
@@ -10378,7 +10378,7 @@
         </is>
       </c>
       <c r="E374" s="20" t="n">
-        <v>209</v>
+        <v>137</v>
       </c>
     </row>
     <row r="375" ht="20" customHeight="1">
@@ -10403,7 +10403,7 @@
         </is>
       </c>
       <c r="E375" s="23" t="n">
-        <v>225</v>
+        <v>132</v>
       </c>
     </row>
     <row r="376" ht="20" customHeight="1">
@@ -10428,7 +10428,7 @@
         </is>
       </c>
       <c r="E376" s="20" t="n">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="377" ht="20" customHeight="1">
@@ -10453,7 +10453,7 @@
         </is>
       </c>
       <c r="E377" s="23" t="n">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="378" ht="20" customHeight="1">
@@ -10478,7 +10478,7 @@
         </is>
       </c>
       <c r="E378" s="20" t="n">
-        <v>146</v>
+        <v>213</v>
       </c>
     </row>
     <row r="379" ht="20" customHeight="1">
@@ -10503,7 +10503,7 @@
         </is>
       </c>
       <c r="E379" s="23" t="n">
-        <v>211</v>
+        <v>154</v>
       </c>
     </row>
     <row r="380" ht="20" customHeight="1">
@@ -10528,7 +10528,7 @@
         </is>
       </c>
       <c r="E380" s="20" t="n">
-        <v>117</v>
+        <v>180</v>
       </c>
     </row>
     <row r="381" ht="20" customHeight="1">
@@ -10553,7 +10553,7 @@
         </is>
       </c>
       <c r="E381" s="23" t="n">
-        <v>113</v>
+        <v>173</v>
       </c>
     </row>
     <row r="382" ht="20" customHeight="1">
@@ -10578,7 +10578,7 @@
         </is>
       </c>
       <c r="E382" s="20" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="383" ht="20" customHeight="1">
@@ -10603,7 +10603,7 @@
         </is>
       </c>
       <c r="E383" s="23" t="n">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="384" ht="20" customHeight="1">
@@ -10628,7 +10628,7 @@
         </is>
       </c>
       <c r="E384" s="20" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
     </row>
     <row r="385" ht="20" customHeight="1">
@@ -10653,7 +10653,7 @@
         </is>
       </c>
       <c r="E385" s="23" t="n">
-        <v>162</v>
+        <v>148</v>
       </c>
     </row>
     <row r="386" ht="20" customHeight="1">
@@ -10678,7 +10678,7 @@
         </is>
       </c>
       <c r="E386" s="20" t="n">
-        <v>184</v>
+        <v>197</v>
       </c>
     </row>
     <row r="387" ht="20" customHeight="1">
@@ -10703,7 +10703,7 @@
         </is>
       </c>
       <c r="E387" s="23" t="n">
-        <v>166</v>
+        <v>218</v>
       </c>
     </row>
     <row r="388" ht="20" customHeight="1">
@@ -10728,7 +10728,7 @@
         </is>
       </c>
       <c r="E388" s="20" t="n">
-        <v>216</v>
+        <v>156</v>
       </c>
     </row>
     <row r="389" ht="20" customHeight="1">
@@ -10753,7 +10753,7 @@
         </is>
       </c>
       <c r="E389" s="23" t="n">
-        <v>112</v>
+        <v>176</v>
       </c>
     </row>
     <row r="390" ht="20" customHeight="1">
@@ -10778,7 +10778,7 @@
         </is>
       </c>
       <c r="E390" s="20" t="n">
-        <v>133</v>
+        <v>239</v>
       </c>
     </row>
     <row r="391" ht="20" customHeight="1">
@@ -10803,7 +10803,7 @@
         </is>
       </c>
       <c r="E391" s="23" t="n">
-        <v>116</v>
+        <v>237</v>
       </c>
     </row>
     <row r="392" ht="20" customHeight="1">
@@ -10828,7 +10828,7 @@
         </is>
       </c>
       <c r="E392" s="20" t="n">
-        <v>138</v>
+        <v>178</v>
       </c>
     </row>
     <row r="393" ht="20" customHeight="1">
@@ -10853,7 +10853,7 @@
         </is>
       </c>
       <c r="E393" s="23" t="n">
-        <v>134</v>
+        <v>218</v>
       </c>
     </row>
     <row r="394" ht="20" customHeight="1">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="E394" s="20" t="n">
-        <v>227</v>
+        <v>179</v>
       </c>
     </row>
     <row r="395" ht="20" customHeight="1">
@@ -10903,7 +10903,7 @@
         </is>
       </c>
       <c r="E395" s="23" t="n">
-        <v>218</v>
+        <v>145</v>
       </c>
     </row>
     <row r="396" ht="20" customHeight="1">
@@ -10928,7 +10928,7 @@
         </is>
       </c>
       <c r="E396" s="20" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="397" ht="20" customHeight="1">
@@ -10953,7 +10953,7 @@
         </is>
       </c>
       <c r="E397" s="23" t="n">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="398" ht="20" customHeight="1">
@@ -10978,7 +10978,7 @@
         </is>
       </c>
       <c r="E398" s="20" t="n">
-        <v>216</v>
+        <v>224</v>
       </c>
     </row>
     <row r="399" ht="20" customHeight="1">
@@ -11003,7 +11003,7 @@
         </is>
       </c>
       <c r="E399" s="23" t="n">
-        <v>165</v>
+        <v>140</v>
       </c>
     </row>
     <row r="400" ht="20" customHeight="1">
@@ -11028,7 +11028,7 @@
         </is>
       </c>
       <c r="E400" s="20" t="n">
-        <v>131</v>
+        <v>202</v>
       </c>
     </row>
     <row r="401" ht="20" customHeight="1">
@@ -11053,7 +11053,7 @@
         </is>
       </c>
       <c r="E401" s="23" t="n">
-        <v>239</v>
+        <v>234</v>
       </c>
     </row>
     <row r="402" ht="20" customHeight="1">
@@ -11078,7 +11078,7 @@
         </is>
       </c>
       <c r="E402" s="20" t="n">
-        <v>155</v>
+        <v>217</v>
       </c>
     </row>
     <row r="403" ht="20" customHeight="1">
@@ -11103,7 +11103,7 @@
         </is>
       </c>
       <c r="E403" s="23" t="n">
-        <v>208</v>
+        <v>163</v>
       </c>
     </row>
     <row r="404" ht="20" customHeight="1">
@@ -11128,7 +11128,7 @@
         </is>
       </c>
       <c r="E404" s="20" t="n">
-        <v>164</v>
+        <v>205</v>
       </c>
     </row>
     <row r="405" ht="20" customHeight="1">
@@ -11153,7 +11153,7 @@
         </is>
       </c>
       <c r="E405" s="23" t="n">
-        <v>179</v>
+        <v>223</v>
       </c>
     </row>
     <row r="406" ht="20" customHeight="1">
@@ -11178,7 +11178,7 @@
         </is>
       </c>
       <c r="E406" s="20" t="n">
-        <v>166</v>
+        <v>144</v>
       </c>
     </row>
     <row r="407" ht="20" customHeight="1">
@@ -11203,7 +11203,7 @@
         </is>
       </c>
       <c r="E407" s="23" t="n">
-        <v>160</v>
+        <v>126</v>
       </c>
     </row>
     <row r="408" ht="20" customHeight="1">
@@ -11228,7 +11228,7 @@
         </is>
       </c>
       <c r="E408" s="20" t="n">
-        <v>233</v>
+        <v>178</v>
       </c>
     </row>
     <row r="409" ht="20" customHeight="1">
@@ -11253,7 +11253,7 @@
         </is>
       </c>
       <c r="E409" s="23" t="n">
-        <v>142</v>
+        <v>203</v>
       </c>
     </row>
     <row r="410" ht="20" customHeight="1">
@@ -11278,7 +11278,7 @@
         </is>
       </c>
       <c r="E410" s="20" t="n">
-        <v>205</v>
+        <v>190</v>
       </c>
     </row>
     <row r="411" ht="20" customHeight="1">
@@ -11303,7 +11303,7 @@
         </is>
       </c>
       <c r="E411" s="23" t="n">
-        <v>115</v>
+        <v>213</v>
       </c>
     </row>
     <row r="412" ht="20" customHeight="1">
@@ -11328,7 +11328,7 @@
         </is>
       </c>
       <c r="E412" s="20" t="n">
-        <v>213</v>
+        <v>175</v>
       </c>
     </row>
     <row r="413" ht="20" customHeight="1">
@@ -11353,7 +11353,7 @@
         </is>
       </c>
       <c r="E413" s="23" t="n">
-        <v>127</v>
+        <v>141</v>
       </c>
     </row>
     <row r="414" ht="20" customHeight="1">
@@ -11378,7 +11378,7 @@
         </is>
       </c>
       <c r="E414" s="20" t="n">
-        <v>112</v>
+        <v>146</v>
       </c>
     </row>
     <row r="415" ht="20" customHeight="1">
@@ -11403,7 +11403,7 @@
         </is>
       </c>
       <c r="E415" s="23" t="n">
-        <v>198</v>
+        <v>208</v>
       </c>
     </row>
     <row r="416" ht="20" customHeight="1">
@@ -11428,7 +11428,7 @@
         </is>
       </c>
       <c r="E416" s="20" t="n">
-        <v>122</v>
+        <v>158</v>
       </c>
     </row>
     <row r="417" ht="20" customHeight="1">
@@ -11453,7 +11453,7 @@
         </is>
       </c>
       <c r="E417" s="23" t="n">
-        <v>140</v>
+        <v>171</v>
       </c>
     </row>
     <row r="418" ht="20" customHeight="1">
@@ -11478,7 +11478,7 @@
         </is>
       </c>
       <c r="E418" s="20" t="n">
-        <v>201</v>
+        <v>123</v>
       </c>
     </row>
     <row r="419" ht="20" customHeight="1">
@@ -11503,7 +11503,7 @@
         </is>
       </c>
       <c r="E419" s="23" t="n">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="420" ht="20" customHeight="1">
@@ -11553,7 +11553,7 @@
         </is>
       </c>
       <c r="E421" s="23" t="n">
-        <v>240</v>
+        <v>175</v>
       </c>
     </row>
     <row r="422" ht="20" customHeight="1">
@@ -11578,7 +11578,7 @@
         </is>
       </c>
       <c r="E422" s="20" t="n">
-        <v>130</v>
+        <v>183</v>
       </c>
     </row>
     <row r="423" ht="20" customHeight="1">
@@ -11603,7 +11603,7 @@
         </is>
       </c>
       <c r="E423" s="23" t="n">
-        <v>226</v>
+        <v>189</v>
       </c>
     </row>
     <row r="424" ht="20" customHeight="1">
@@ -11628,7 +11628,7 @@
         </is>
       </c>
       <c r="E424" s="20" t="n">
-        <v>224</v>
+        <v>142</v>
       </c>
     </row>
     <row r="425" ht="20" customHeight="1">
@@ -11653,7 +11653,7 @@
         </is>
       </c>
       <c r="E425" s="23" t="n">
-        <v>117</v>
+        <v>155</v>
       </c>
     </row>
     <row r="426" ht="20" customHeight="1">
@@ -11678,7 +11678,7 @@
         </is>
       </c>
       <c r="E426" s="20" t="n">
-        <v>204</v>
+        <v>141</v>
       </c>
     </row>
     <row r="427" ht="20" customHeight="1">
@@ -11703,7 +11703,7 @@
         </is>
       </c>
       <c r="E427" s="23" t="n">
-        <v>170</v>
+        <v>202</v>
       </c>
     </row>
     <row r="428" ht="20" customHeight="1">
@@ -11728,7 +11728,7 @@
         </is>
       </c>
       <c r="E428" s="20" t="n">
-        <v>201</v>
+        <v>212</v>
       </c>
     </row>
     <row r="429" ht="20" customHeight="1">
@@ -11753,7 +11753,7 @@
         </is>
       </c>
       <c r="E429" s="23" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="430" ht="20" customHeight="1">
@@ -11778,7 +11778,7 @@
         </is>
       </c>
       <c r="E430" s="20" t="n">
-        <v>199</v>
+        <v>173</v>
       </c>
     </row>
     <row r="431" ht="20" customHeight="1">
@@ -11803,7 +11803,7 @@
         </is>
       </c>
       <c r="E431" s="23" t="n">
-        <v>187</v>
+        <v>130</v>
       </c>
     </row>
     <row r="432" ht="20" customHeight="1">
@@ -11828,7 +11828,7 @@
         </is>
       </c>
       <c r="E432" s="20" t="n">
-        <v>150</v>
+        <v>191</v>
       </c>
     </row>
     <row r="433" ht="20" customHeight="1">
@@ -11853,7 +11853,7 @@
         </is>
       </c>
       <c r="E433" s="23" t="n">
-        <v>203</v>
+        <v>115</v>
       </c>
     </row>
     <row r="434" ht="20" customHeight="1">
@@ -11878,7 +11878,7 @@
         </is>
       </c>
       <c r="E434" s="20" t="n">
-        <v>122</v>
+        <v>223</v>
       </c>
     </row>
     <row r="435" ht="20" customHeight="1">
@@ -11903,7 +11903,7 @@
         </is>
       </c>
       <c r="E435" s="23" t="n">
-        <v>220</v>
+        <v>191</v>
       </c>
     </row>
     <row r="436" ht="20" customHeight="1">
@@ -11928,7 +11928,7 @@
         </is>
       </c>
       <c r="E436" s="20" t="n">
-        <v>228</v>
+        <v>182</v>
       </c>
     </row>
     <row r="437" ht="20" customHeight="1">
@@ -11953,7 +11953,7 @@
         </is>
       </c>
       <c r="E437" s="23" t="n">
-        <v>158</v>
+        <v>218</v>
       </c>
     </row>
     <row r="438" ht="20" customHeight="1">
@@ -11978,7 +11978,7 @@
         </is>
       </c>
       <c r="E438" s="20" t="n">
-        <v>141</v>
+        <v>217</v>
       </c>
     </row>
     <row r="439" ht="20" customHeight="1">
@@ -12003,7 +12003,7 @@
         </is>
       </c>
       <c r="E439" s="23" t="n">
-        <v>167</v>
+        <v>185</v>
       </c>
     </row>
     <row r="440" ht="20" customHeight="1">
@@ -12028,7 +12028,7 @@
         </is>
       </c>
       <c r="E440" s="20" t="n">
-        <v>223</v>
+        <v>240</v>
       </c>
     </row>
     <row r="441" ht="20" customHeight="1">
@@ -12053,7 +12053,7 @@
         </is>
       </c>
       <c r="E441" s="23" t="n">
-        <v>148</v>
+        <v>174</v>
       </c>
     </row>
     <row r="442" ht="20" customHeight="1">
@@ -12078,7 +12078,7 @@
         </is>
       </c>
       <c r="E442" s="20" t="n">
-        <v>179</v>
+        <v>202</v>
       </c>
     </row>
     <row r="443" ht="20" customHeight="1">
@@ -12103,7 +12103,7 @@
         </is>
       </c>
       <c r="E443" s="23" t="n">
-        <v>199</v>
+        <v>194</v>
       </c>
     </row>
     <row r="444" ht="20" customHeight="1">
@@ -12128,7 +12128,7 @@
         </is>
       </c>
       <c r="E444" s="20" t="n">
-        <v>216</v>
+        <v>224</v>
       </c>
     </row>
     <row r="445" ht="20" customHeight="1">
@@ -12153,7 +12153,7 @@
         </is>
       </c>
       <c r="E445" s="23" t="n">
-        <v>165</v>
+        <v>113</v>
       </c>
     </row>
     <row r="446" ht="20" customHeight="1">
@@ -12178,7 +12178,7 @@
         </is>
       </c>
       <c r="E446" s="20" t="n">
-        <v>140</v>
+        <v>212</v>
       </c>
     </row>
     <row r="447" ht="20" customHeight="1">
@@ -12203,7 +12203,7 @@
         </is>
       </c>
       <c r="E447" s="23" t="n">
-        <v>238</v>
+        <v>214</v>
       </c>
     </row>
     <row r="448" ht="20" customHeight="1">
@@ -12228,7 +12228,7 @@
         </is>
       </c>
       <c r="E448" s="20" t="n">
-        <v>165</v>
+        <v>137</v>
       </c>
     </row>
     <row r="449" ht="20" customHeight="1">
@@ -12253,7 +12253,7 @@
         </is>
       </c>
       <c r="E449" s="23" t="n">
-        <v>157</v>
+        <v>146</v>
       </c>
     </row>
     <row r="450" ht="20" customHeight="1">
@@ -12278,7 +12278,7 @@
         </is>
       </c>
       <c r="E450" s="20" t="n">
-        <v>173</v>
+        <v>166</v>
       </c>
     </row>
     <row r="451" ht="20" customHeight="1">
@@ -12303,7 +12303,7 @@
         </is>
       </c>
       <c r="E451" s="23" t="n">
-        <v>171</v>
+        <v>166</v>
       </c>
     </row>
     <row r="452" ht="20" customHeight="1">
@@ -12328,7 +12328,7 @@
         </is>
       </c>
       <c r="E452" s="20" t="n">
-        <v>179</v>
+        <v>206</v>
       </c>
     </row>
     <row r="453" ht="20" customHeight="1">
@@ -12353,7 +12353,7 @@
         </is>
       </c>
       <c r="E453" s="23" t="n">
-        <v>143</v>
+        <v>217</v>
       </c>
     </row>
     <row r="454" ht="20" customHeight="1">
@@ -12378,7 +12378,7 @@
         </is>
       </c>
       <c r="E454" s="20" t="n">
-        <v>207</v>
+        <v>240</v>
       </c>
     </row>
     <row r="455" ht="20" customHeight="1">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="E455" s="23" t="n">
-        <v>120</v>
+        <v>176</v>
       </c>
     </row>
     <row r="456" ht="20" customHeight="1">
@@ -12428,7 +12428,7 @@
         </is>
       </c>
       <c r="E456" s="20" t="n">
-        <v>202</v>
+        <v>129</v>
       </c>
     </row>
     <row r="457" ht="20" customHeight="1">
@@ -12453,7 +12453,7 @@
         </is>
       </c>
       <c r="E457" s="23" t="n">
-        <v>153</v>
+        <v>218</v>
       </c>
     </row>
     <row r="458" ht="20" customHeight="1">
@@ -12478,7 +12478,7 @@
         </is>
       </c>
       <c r="E458" s="20" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="459" ht="20" customHeight="1">
@@ -12503,7 +12503,7 @@
         </is>
       </c>
       <c r="E459" s="23" t="n">
-        <v>228</v>
+        <v>192</v>
       </c>
     </row>
     <row r="460" ht="20" customHeight="1">
@@ -12528,7 +12528,7 @@
         </is>
       </c>
       <c r="E460" s="20" t="n">
-        <v>216</v>
+        <v>143</v>
       </c>
     </row>
     <row r="461" ht="20" customHeight="1">
@@ -12553,7 +12553,7 @@
         </is>
       </c>
       <c r="E461" s="23" t="n">
-        <v>198</v>
+        <v>172</v>
       </c>
     </row>
     <row r="462" ht="20" customHeight="1">
@@ -12578,7 +12578,7 @@
         </is>
       </c>
       <c r="E462" s="20" t="n">
-        <v>161</v>
+        <v>196</v>
       </c>
     </row>
     <row r="463" ht="20" customHeight="1">
@@ -12603,7 +12603,7 @@
         </is>
       </c>
       <c r="E463" s="23" t="n">
-        <v>235</v>
+        <v>200</v>
       </c>
     </row>
     <row r="464" ht="20" customHeight="1">
@@ -12628,7 +12628,7 @@
         </is>
       </c>
       <c r="E464" s="20" t="n">
-        <v>224</v>
+        <v>157</v>
       </c>
     </row>
     <row r="465" ht="20" customHeight="1">
@@ -12653,7 +12653,7 @@
         </is>
       </c>
       <c r="E465" s="23" t="n">
-        <v>229</v>
+        <v>129</v>
       </c>
     </row>
     <row r="466" ht="20" customHeight="1">
@@ -12678,7 +12678,7 @@
         </is>
       </c>
       <c r="E466" s="20" t="n">
-        <v>181</v>
+        <v>217</v>
       </c>
     </row>
     <row r="467" ht="20" customHeight="1">
@@ -12703,7 +12703,7 @@
         </is>
       </c>
       <c r="E467" s="23" t="n">
-        <v>161</v>
+        <v>194</v>
       </c>
     </row>
     <row r="468" ht="20" customHeight="1">
@@ -12728,7 +12728,7 @@
         </is>
       </c>
       <c r="E468" s="20" t="n">
-        <v>215</v>
+        <v>226</v>
       </c>
     </row>
     <row r="469" ht="20" customHeight="1">
@@ -12753,7 +12753,7 @@
         </is>
       </c>
       <c r="E469" s="23" t="n">
-        <v>223</v>
+        <v>159</v>
       </c>
     </row>
     <row r="470" ht="20" customHeight="1">
@@ -12778,7 +12778,7 @@
         </is>
       </c>
       <c r="E470" s="20" t="n">
-        <v>168</v>
+        <v>130</v>
       </c>
     </row>
     <row r="471" ht="20" customHeight="1">
@@ -12803,7 +12803,7 @@
         </is>
       </c>
       <c r="E471" s="23" t="n">
-        <v>115</v>
+        <v>184</v>
       </c>
     </row>
     <row r="472" ht="20" customHeight="1">
@@ -12828,7 +12828,7 @@
         </is>
       </c>
       <c r="E472" s="20" t="n">
-        <v>183</v>
+        <v>217</v>
       </c>
     </row>
     <row r="473" ht="20" customHeight="1">
@@ -12853,7 +12853,7 @@
         </is>
       </c>
       <c r="E473" s="23" t="n">
-        <v>224</v>
+        <v>196</v>
       </c>
     </row>
     <row r="474" ht="20" customHeight="1">
@@ -12878,7 +12878,7 @@
         </is>
       </c>
       <c r="E474" s="20" t="n">
-        <v>165</v>
+        <v>176</v>
       </c>
     </row>
     <row r="475" ht="20" customHeight="1">
@@ -12903,7 +12903,7 @@
         </is>
       </c>
       <c r="E475" s="23" t="n">
-        <v>173</v>
+        <v>208</v>
       </c>
     </row>
     <row r="476" ht="20" customHeight="1">
@@ -12928,7 +12928,7 @@
         </is>
       </c>
       <c r="E476" s="20" t="n">
-        <v>211</v>
+        <v>115</v>
       </c>
     </row>
     <row r="477" ht="20" customHeight="1">
@@ -12953,7 +12953,7 @@
         </is>
       </c>
       <c r="E477" s="23" t="n">
-        <v>113</v>
+        <v>194</v>
       </c>
     </row>
     <row r="478" ht="20" customHeight="1">
@@ -12978,7 +12978,7 @@
         </is>
       </c>
       <c r="E478" s="20" t="n">
-        <v>140</v>
+        <v>231</v>
       </c>
     </row>
     <row r="479" ht="20" customHeight="1">
@@ -13003,7 +13003,7 @@
         </is>
       </c>
       <c r="E479" s="23" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="480" ht="20" customHeight="1">
@@ -13028,7 +13028,7 @@
         </is>
       </c>
       <c r="E480" s="20" t="n">
-        <v>166</v>
+        <v>152</v>
       </c>
     </row>
     <row r="481" ht="20" customHeight="1">
@@ -13053,7 +13053,7 @@
         </is>
       </c>
       <c r="E481" s="23" t="n">
-        <v>175</v>
+        <v>121</v>
       </c>
     </row>
     <row r="482" ht="20" customHeight="1">
@@ -13078,7 +13078,7 @@
         </is>
       </c>
       <c r="E482" s="20" t="n">
-        <v>131</v>
+        <v>234</v>
       </c>
     </row>
     <row r="483" ht="20" customHeight="1">
@@ -13103,7 +13103,7 @@
         </is>
       </c>
       <c r="E483" s="23" t="n">
-        <v>130</v>
+        <v>219</v>
       </c>
     </row>
     <row r="484" ht="20" customHeight="1">
@@ -13128,7 +13128,7 @@
         </is>
       </c>
       <c r="E484" s="20" t="n">
-        <v>207</v>
+        <v>217</v>
       </c>
     </row>
     <row r="485" ht="20" customHeight="1">
@@ -13153,7 +13153,7 @@
         </is>
       </c>
       <c r="E485" s="23" t="n">
-        <v>134</v>
+        <v>115</v>
       </c>
     </row>
     <row r="486" ht="20" customHeight="1">
@@ -13178,7 +13178,7 @@
         </is>
       </c>
       <c r="E486" s="20" t="n">
-        <v>116</v>
+        <v>165</v>
       </c>
     </row>
     <row r="487" ht="20" customHeight="1">
@@ -13203,7 +13203,7 @@
         </is>
       </c>
       <c r="E487" s="23" t="n">
-        <v>225</v>
+        <v>215</v>
       </c>
     </row>
     <row r="488" ht="20" customHeight="1">
@@ -13228,7 +13228,7 @@
         </is>
       </c>
       <c r="E488" s="20" t="n">
-        <v>229</v>
+        <v>213</v>
       </c>
     </row>
     <row r="489" ht="20" customHeight="1">
@@ -13253,7 +13253,7 @@
         </is>
       </c>
       <c r="E489" s="23" t="n">
-        <v>180</v>
+        <v>223</v>
       </c>
     </row>
     <row r="490" ht="20" customHeight="1">
@@ -13278,7 +13278,7 @@
         </is>
       </c>
       <c r="E490" s="20" t="n">
-        <v>146</v>
+        <v>229</v>
       </c>
     </row>
     <row r="491" ht="20" customHeight="1">
@@ -13303,7 +13303,7 @@
         </is>
       </c>
       <c r="E491" s="23" t="n">
-        <v>167</v>
+        <v>162</v>
       </c>
     </row>
     <row r="492" ht="20" customHeight="1">
@@ -13328,7 +13328,7 @@
         </is>
       </c>
       <c r="E492" s="20" t="n">
-        <v>193</v>
+        <v>226</v>
       </c>
     </row>
     <row r="493" ht="20" customHeight="1">
@@ -13353,7 +13353,7 @@
         </is>
       </c>
       <c r="E493" s="23" t="n">
-        <v>187</v>
+        <v>161</v>
       </c>
     </row>
     <row r="494" ht="20" customHeight="1">
@@ -13378,7 +13378,7 @@
         </is>
       </c>
       <c r="E494" s="20" t="n">
-        <v>159</v>
+        <v>176</v>
       </c>
     </row>
     <row r="495" ht="20" customHeight="1">
@@ -13403,7 +13403,7 @@
         </is>
       </c>
       <c r="E495" s="23" t="n">
-        <v>152</v>
+        <v>207</v>
       </c>
     </row>
     <row r="496" ht="20" customHeight="1">
@@ -13428,7 +13428,7 @@
         </is>
       </c>
       <c r="E496" s="20" t="n">
-        <v>204</v>
+        <v>134</v>
       </c>
     </row>
     <row r="497" ht="20" customHeight="1">
@@ -13453,7 +13453,7 @@
         </is>
       </c>
       <c r="E497" s="23" t="n">
-        <v>129</v>
+        <v>226</v>
       </c>
     </row>
     <row r="498" ht="20" customHeight="1">
@@ -13478,7 +13478,7 @@
         </is>
       </c>
       <c r="E498" s="20" t="n">
-        <v>114</v>
+        <v>224</v>
       </c>
     </row>
     <row r="499" ht="20" customHeight="1">
@@ -13503,7 +13503,7 @@
         </is>
       </c>
       <c r="E499" s="23" t="n">
-        <v>239</v>
+        <v>181</v>
       </c>
     </row>
     <row r="500" ht="20" customHeight="1">
@@ -13528,7 +13528,7 @@
         </is>
       </c>
       <c r="E500" s="20" t="n">
-        <v>153</v>
+        <v>119</v>
       </c>
     </row>
     <row r="501" ht="20" customHeight="1">
@@ -13553,7 +13553,7 @@
         </is>
       </c>
       <c r="E501" s="23" t="n">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="502" ht="20" customHeight="1">
@@ -13578,7 +13578,7 @@
         </is>
       </c>
       <c r="E502" s="20" t="n">
-        <v>132</v>
+        <v>232</v>
       </c>
     </row>
     <row r="503" ht="20" customHeight="1">
@@ -13603,7 +13603,7 @@
         </is>
       </c>
       <c r="E503" s="23" t="n">
-        <v>111</v>
+        <v>156</v>
       </c>
     </row>
     <row r="504" ht="20" customHeight="1">
@@ -13628,7 +13628,7 @@
         </is>
       </c>
       <c r="E504" s="20" t="n">
-        <v>221</v>
+        <v>195</v>
       </c>
     </row>
     <row r="505" ht="20" customHeight="1">
@@ -13653,7 +13653,7 @@
         </is>
       </c>
       <c r="E505" s="23" t="n">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="506" ht="20" customHeight="1">
@@ -13678,7 +13678,7 @@
         </is>
       </c>
       <c r="E506" s="20" t="n">
-        <v>195</v>
+        <v>187</v>
       </c>
     </row>
     <row r="507" ht="20" customHeight="1">
@@ -13703,7 +13703,7 @@
         </is>
       </c>
       <c r="E507" s="23" t="n">
-        <v>117</v>
+        <v>235</v>
       </c>
     </row>
     <row r="508" ht="20" customHeight="1">
@@ -13728,7 +13728,7 @@
         </is>
       </c>
       <c r="E508" s="20" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="509" ht="20" customHeight="1">
@@ -13753,7 +13753,7 @@
         </is>
       </c>
       <c r="E509" s="23" t="n">
-        <v>195</v>
+        <v>156</v>
       </c>
     </row>
     <row r="510" ht="20" customHeight="1">
@@ -13778,7 +13778,7 @@
         </is>
       </c>
       <c r="E510" s="20" t="n">
-        <v>206</v>
+        <v>196</v>
       </c>
     </row>
     <row r="511" ht="20" customHeight="1">
@@ -13803,7 +13803,7 @@
         </is>
       </c>
       <c r="E511" s="23" t="n">
-        <v>184</v>
+        <v>142</v>
       </c>
     </row>
     <row r="512" ht="20" customHeight="1">
@@ -13828,7 +13828,7 @@
         </is>
       </c>
       <c r="E512" s="20" t="n">
-        <v>152</v>
+        <v>210</v>
       </c>
     </row>
     <row r="513" ht="20" customHeight="1">
@@ -13853,7 +13853,7 @@
         </is>
       </c>
       <c r="E513" s="23" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="514" ht="20" customHeight="1">
@@ -13878,7 +13878,7 @@
         </is>
       </c>
       <c r="E514" s="20" t="n">
-        <v>160</v>
+        <v>139</v>
       </c>
     </row>
     <row r="515" ht="20" customHeight="1">
@@ -13903,7 +13903,7 @@
         </is>
       </c>
       <c r="E515" s="23" t="n">
-        <v>215</v>
+        <v>191</v>
       </c>
     </row>
     <row r="516" ht="20" customHeight="1">
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="E516" s="20" t="n">
-        <v>180</v>
+        <v>166</v>
       </c>
     </row>
     <row r="517" ht="20" customHeight="1">
@@ -13953,7 +13953,7 @@
         </is>
       </c>
       <c r="E517" s="23" t="n">
-        <v>217</v>
+        <v>210</v>
       </c>
     </row>
     <row r="518" ht="20" customHeight="1">
@@ -13978,7 +13978,7 @@
         </is>
       </c>
       <c r="E518" s="20" t="n">
-        <v>117</v>
+        <v>174</v>
       </c>
     </row>
     <row r="519" ht="20" customHeight="1">
@@ -14003,7 +14003,7 @@
         </is>
       </c>
       <c r="E519" s="23" t="n">
-        <v>139</v>
+        <v>237</v>
       </c>
     </row>
     <row r="520" ht="20" customHeight="1">
@@ -14028,7 +14028,7 @@
         </is>
       </c>
       <c r="E520" s="20" t="n">
-        <v>225</v>
+        <v>205</v>
       </c>
     </row>
     <row r="521" ht="20" customHeight="1">
@@ -14053,7 +14053,7 @@
         </is>
       </c>
       <c r="E521" s="23" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="522" ht="20" customHeight="1">
@@ -14078,7 +14078,7 @@
         </is>
       </c>
       <c r="E522" s="20" t="n">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="523" ht="20" customHeight="1">
@@ -14103,7 +14103,7 @@
         </is>
       </c>
       <c r="E523" s="23" t="n">
-        <v>203</v>
+        <v>158</v>
       </c>
     </row>
     <row r="524" ht="20" customHeight="1">
@@ -14128,7 +14128,7 @@
         </is>
       </c>
       <c r="E524" s="20" t="n">
-        <v>187</v>
+        <v>162</v>
       </c>
     </row>
     <row r="525" ht="20" customHeight="1">
@@ -14153,7 +14153,7 @@
         </is>
       </c>
       <c r="E525" s="23" t="n">
-        <v>239</v>
+        <v>208</v>
       </c>
     </row>
     <row r="526" ht="20" customHeight="1">
@@ -14178,7 +14178,7 @@
         </is>
       </c>
       <c r="E526" s="20" t="n">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="527" ht="20" customHeight="1">
@@ -14203,7 +14203,7 @@
         </is>
       </c>
       <c r="E527" s="23" t="n">
-        <v>140</v>
+        <v>167</v>
       </c>
     </row>
     <row r="528" ht="20" customHeight="1">
@@ -14228,7 +14228,7 @@
         </is>
       </c>
       <c r="E528" s="20" t="n">
-        <v>137</v>
+        <v>191</v>
       </c>
     </row>
     <row r="529" ht="20" customHeight="1">
@@ -14253,7 +14253,7 @@
         </is>
       </c>
       <c r="E529" s="23" t="n">
-        <v>155</v>
+        <v>190</v>
       </c>
     </row>
     <row r="530" ht="20" customHeight="1">
@@ -14278,7 +14278,7 @@
         </is>
       </c>
       <c r="E530" s="20" t="n">
-        <v>177</v>
+        <v>188</v>
       </c>
     </row>
     <row r="531" ht="20" customHeight="1">
@@ -14303,7 +14303,7 @@
         </is>
       </c>
       <c r="E531" s="23" t="n">
-        <v>124</v>
+        <v>198</v>
       </c>
     </row>
     <row r="532" ht="20" customHeight="1">
@@ -14328,7 +14328,7 @@
         </is>
       </c>
       <c r="E532" s="20" t="n">
-        <v>185</v>
+        <v>131</v>
       </c>
     </row>
     <row r="533" ht="20" customHeight="1">
@@ -14353,7 +14353,7 @@
         </is>
       </c>
       <c r="E533" s="23" t="n">
-        <v>197</v>
+        <v>118</v>
       </c>
     </row>
     <row r="534" ht="20" customHeight="1">
@@ -14378,7 +14378,7 @@
         </is>
       </c>
       <c r="E534" s="20" t="n">
-        <v>151</v>
+        <v>128</v>
       </c>
     </row>
     <row r="535" ht="20" customHeight="1">
@@ -14403,7 +14403,7 @@
         </is>
       </c>
       <c r="E535" s="23" t="n">
-        <v>195</v>
+        <v>207</v>
       </c>
     </row>
     <row r="536" ht="20" customHeight="1">
@@ -14428,7 +14428,7 @@
         </is>
       </c>
       <c r="E536" s="20" t="n">
-        <v>123</v>
+        <v>226</v>
       </c>
     </row>
     <row r="537" ht="20" customHeight="1">
@@ -14453,7 +14453,7 @@
         </is>
       </c>
       <c r="E537" s="23" t="n">
-        <v>204</v>
+        <v>111</v>
       </c>
     </row>
     <row r="538" ht="20" customHeight="1">
@@ -14478,7 +14478,7 @@
         </is>
       </c>
       <c r="E538" s="20" t="n">
-        <v>200</v>
+        <v>189</v>
       </c>
     </row>
     <row r="539" ht="20" customHeight="1">
@@ -14503,7 +14503,7 @@
         </is>
       </c>
       <c r="E539" s="23" t="n">
-        <v>116</v>
+        <v>141</v>
       </c>
     </row>
     <row r="540" ht="20" customHeight="1">
@@ -14528,7 +14528,7 @@
         </is>
       </c>
       <c r="E540" s="20" t="n">
-        <v>207</v>
+        <v>151</v>
       </c>
     </row>
     <row r="541" ht="20" customHeight="1">
@@ -14553,7 +14553,7 @@
         </is>
       </c>
       <c r="E541" s="23" t="n">
-        <v>174</v>
+        <v>158</v>
       </c>
     </row>
     <row r="542" ht="20" customHeight="1">
@@ -14603,7 +14603,7 @@
         </is>
       </c>
       <c r="E543" s="23" t="n">
-        <v>163</v>
+        <v>136</v>
       </c>
     </row>
     <row r="544" ht="20" customHeight="1">
@@ -14628,7 +14628,7 @@
         </is>
       </c>
       <c r="E544" s="20" t="n">
-        <v>199</v>
+        <v>193</v>
       </c>
     </row>
     <row r="545" ht="20" customHeight="1">
@@ -14653,7 +14653,7 @@
         </is>
       </c>
       <c r="E545" s="23" t="n">
-        <v>129</v>
+        <v>184</v>
       </c>
     </row>
     <row r="546" ht="20" customHeight="1">
@@ -14678,7 +14678,7 @@
         </is>
       </c>
       <c r="E546" s="20" t="n">
-        <v>194</v>
+        <v>143</v>
       </c>
     </row>
     <row r="547" ht="20" customHeight="1">
@@ -14703,7 +14703,7 @@
         </is>
       </c>
       <c r="E547" s="23" t="n">
-        <v>142</v>
+        <v>214</v>
       </c>
     </row>
     <row r="548" ht="20" customHeight="1">
@@ -14728,7 +14728,7 @@
         </is>
       </c>
       <c r="E548" s="20" t="n">
-        <v>139</v>
+        <v>207</v>
       </c>
     </row>
     <row r="549" ht="20" customHeight="1">
@@ -14753,7 +14753,7 @@
         </is>
       </c>
       <c r="E549" s="23" t="n">
-        <v>159</v>
+        <v>236</v>
       </c>
     </row>
     <row r="550" ht="20" customHeight="1">
@@ -14778,7 +14778,7 @@
         </is>
       </c>
       <c r="E550" s="20" t="n">
-        <v>197</v>
+        <v>132</v>
       </c>
     </row>
     <row r="551" ht="20" customHeight="1">
@@ -14803,7 +14803,7 @@
         </is>
       </c>
       <c r="E551" s="23" t="n">
-        <v>217</v>
+        <v>130</v>
       </c>
     </row>
     <row r="552" ht="20" customHeight="1">
@@ -14828,7 +14828,7 @@
         </is>
       </c>
       <c r="E552" s="20" t="n">
-        <v>196</v>
+        <v>146</v>
       </c>
     </row>
     <row r="553" ht="20" customHeight="1">
@@ -14853,7 +14853,7 @@
         </is>
       </c>
       <c r="E553" s="23" t="n">
-        <v>145</v>
+        <v>206</v>
       </c>
     </row>
     <row r="554" ht="20" customHeight="1">
@@ -14878,7 +14878,7 @@
         </is>
       </c>
       <c r="E554" s="20" t="n">
-        <v>217</v>
+        <v>233</v>
       </c>
     </row>
     <row r="555" ht="20" customHeight="1">
@@ -14903,7 +14903,7 @@
         </is>
       </c>
       <c r="E555" s="23" t="n">
-        <v>143</v>
+        <v>194</v>
       </c>
     </row>
     <row r="556" ht="20" customHeight="1">
@@ -14928,7 +14928,7 @@
         </is>
       </c>
       <c r="E556" s="20" t="n">
-        <v>157</v>
+        <v>127</v>
       </c>
     </row>
     <row r="557" ht="20" customHeight="1">
@@ -14953,7 +14953,7 @@
         </is>
       </c>
       <c r="E557" s="23" t="n">
-        <v>133</v>
+        <v>216</v>
       </c>
     </row>
     <row r="558" ht="20" customHeight="1">
@@ -14978,7 +14978,7 @@
         </is>
       </c>
       <c r="E558" s="20" t="n">
-        <v>128</v>
+        <v>230</v>
       </c>
     </row>
     <row r="559" ht="20" customHeight="1">
@@ -15003,7 +15003,7 @@
         </is>
       </c>
       <c r="E559" s="23" t="n">
-        <v>137</v>
+        <v>225</v>
       </c>
     </row>
     <row r="560" ht="20" customHeight="1">
@@ -15028,7 +15028,7 @@
         </is>
       </c>
       <c r="E560" s="20" t="n">
-        <v>202</v>
+        <v>144</v>
       </c>
     </row>
     <row r="561" ht="20" customHeight="1">
@@ -15053,7 +15053,7 @@
         </is>
       </c>
       <c r="E561" s="23" t="n">
-        <v>124</v>
+        <v>145</v>
       </c>
     </row>
     <row r="562" ht="20" customHeight="1">
@@ -15078,7 +15078,7 @@
         </is>
       </c>
       <c r="E562" s="20" t="n">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="563" ht="20" customHeight="1">
@@ -15103,7 +15103,7 @@
         </is>
       </c>
       <c r="E563" s="23" t="n">
-        <v>140</v>
+        <v>224</v>
       </c>
     </row>
     <row r="564" ht="20" customHeight="1">
@@ -15128,7 +15128,7 @@
         </is>
       </c>
       <c r="E564" s="20" t="n">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="565" ht="20" customHeight="1">
@@ -15153,7 +15153,7 @@
         </is>
       </c>
       <c r="E565" s="23" t="n">
-        <v>139</v>
+        <v>117</v>
       </c>
     </row>
     <row r="566" ht="20" customHeight="1">
@@ -15178,7 +15178,7 @@
         </is>
       </c>
       <c r="E566" s="20" t="n">
-        <v>148</v>
+        <v>167</v>
       </c>
     </row>
     <row r="567" ht="20" customHeight="1">
@@ -15203,7 +15203,7 @@
         </is>
       </c>
       <c r="E567" s="23" t="n">
-        <v>188</v>
+        <v>110</v>
       </c>
     </row>
     <row r="568" ht="20" customHeight="1">
@@ -15228,7 +15228,7 @@
         </is>
       </c>
       <c r="E568" s="20" t="n">
-        <v>228</v>
+        <v>181</v>
       </c>
     </row>
     <row r="569" ht="20" customHeight="1">
@@ -15253,7 +15253,7 @@
         </is>
       </c>
       <c r="E569" s="23" t="n">
-        <v>186</v>
+        <v>174</v>
       </c>
     </row>
     <row r="570" ht="20" customHeight="1">
@@ -15278,7 +15278,7 @@
         </is>
       </c>
       <c r="E570" s="20" t="n">
-        <v>175</v>
+        <v>122</v>
       </c>
     </row>
     <row r="571" ht="20" customHeight="1">
@@ -15303,7 +15303,7 @@
         </is>
       </c>
       <c r="E571" s="23" t="n">
-        <v>118</v>
+        <v>224</v>
       </c>
     </row>
     <row r="572" ht="20" customHeight="1">
@@ -15328,7 +15328,7 @@
         </is>
       </c>
       <c r="E572" s="20" t="n">
-        <v>140</v>
+        <v>185</v>
       </c>
     </row>
     <row r="573" ht="20" customHeight="1">
@@ -15353,7 +15353,7 @@
         </is>
       </c>
       <c r="E573" s="23" t="n">
-        <v>131</v>
+        <v>235</v>
       </c>
     </row>
     <row r="574" ht="20" customHeight="1">
@@ -15378,7 +15378,7 @@
         </is>
       </c>
       <c r="E574" s="20" t="n">
-        <v>165</v>
+        <v>133</v>
       </c>
     </row>
     <row r="575" ht="20" customHeight="1">
@@ -15403,7 +15403,7 @@
         </is>
       </c>
       <c r="E575" s="23" t="n">
-        <v>233</v>
+        <v>222</v>
       </c>
     </row>
     <row r="576" ht="20" customHeight="1">
@@ -15428,7 +15428,7 @@
         </is>
       </c>
       <c r="E576" s="20" t="n">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="577" ht="20" customHeight="1">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="E577" s="23" t="n">
-        <v>198</v>
+        <v>137</v>
       </c>
     </row>
     <row r="578" ht="20" customHeight="1">
@@ -15478,7 +15478,7 @@
         </is>
       </c>
       <c r="E578" s="20" t="n">
-        <v>122</v>
+        <v>219</v>
       </c>
     </row>
     <row r="579" ht="20" customHeight="1">
@@ -15503,7 +15503,7 @@
         </is>
       </c>
       <c r="E579" s="23" t="n">
-        <v>143</v>
+        <v>240</v>
       </c>
     </row>
     <row r="580" ht="20" customHeight="1">
@@ -15528,7 +15528,7 @@
         </is>
       </c>
       <c r="E580" s="20" t="n">
-        <v>158</v>
+        <v>177</v>
       </c>
     </row>
     <row r="581" ht="20" customHeight="1">
@@ -15553,7 +15553,7 @@
         </is>
       </c>
       <c r="E581" s="23" t="n">
-        <v>121</v>
+        <v>174</v>
       </c>
     </row>
     <row r="582" ht="20" customHeight="1">
@@ -15578,7 +15578,7 @@
         </is>
       </c>
       <c r="E582" s="20" t="n">
-        <v>120</v>
+        <v>141</v>
       </c>
     </row>
     <row r="583" ht="20" customHeight="1">
@@ -15603,7 +15603,7 @@
         </is>
       </c>
       <c r="E583" s="23" t="n">
-        <v>234</v>
+        <v>159</v>
       </c>
     </row>
     <row r="584" ht="20" customHeight="1">
@@ -15628,7 +15628,7 @@
         </is>
       </c>
       <c r="E584" s="20" t="n">
-        <v>221</v>
+        <v>213</v>
       </c>
     </row>
     <row r="585" ht="20" customHeight="1">
@@ -15653,7 +15653,7 @@
         </is>
       </c>
       <c r="E585" s="23" t="n">
-        <v>116</v>
+        <v>156</v>
       </c>
     </row>
     <row r="586" ht="20" customHeight="1">
@@ -15678,7 +15678,7 @@
         </is>
       </c>
       <c r="E586" s="20" t="n">
-        <v>141</v>
+        <v>110</v>
       </c>
     </row>
     <row r="587" ht="20" customHeight="1">
@@ -15703,7 +15703,7 @@
         </is>
       </c>
       <c r="E587" s="23" t="n">
-        <v>181</v>
+        <v>118</v>
       </c>
     </row>
     <row r="588" ht="20" customHeight="1">
@@ -15728,7 +15728,7 @@
         </is>
       </c>
       <c r="E588" s="20" t="n">
-        <v>154</v>
+        <v>188</v>
       </c>
     </row>
     <row r="589" ht="20" customHeight="1">
@@ -15753,7 +15753,7 @@
         </is>
       </c>
       <c r="E589" s="23" t="n">
-        <v>201</v>
+        <v>239</v>
       </c>
     </row>
     <row r="590" ht="20" customHeight="1">
@@ -15778,7 +15778,7 @@
         </is>
       </c>
       <c r="E590" s="20" t="n">
-        <v>224</v>
+        <v>152</v>
       </c>
     </row>
     <row r="591" ht="20" customHeight="1">
@@ -15803,7 +15803,7 @@
         </is>
       </c>
       <c r="E591" s="23" t="n">
-        <v>139</v>
+        <v>211</v>
       </c>
     </row>
     <row r="592" ht="20" customHeight="1">
@@ -15828,7 +15828,7 @@
         </is>
       </c>
       <c r="E592" s="20" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
     </row>
     <row r="593" ht="20" customHeight="1">
@@ -15853,7 +15853,7 @@
         </is>
       </c>
       <c r="E593" s="23" t="n">
-        <v>174</v>
+        <v>195</v>
       </c>
     </row>
     <row r="594" ht="20" customHeight="1">
@@ -15878,7 +15878,7 @@
         </is>
       </c>
       <c r="E594" s="20" t="n">
-        <v>179</v>
+        <v>152</v>
       </c>
     </row>
     <row r="595" ht="20" customHeight="1">
@@ -15903,7 +15903,7 @@
         </is>
       </c>
       <c r="E595" s="23" t="n">
-        <v>170</v>
+        <v>163</v>
       </c>
     </row>
     <row r="596" ht="20" customHeight="1">
@@ -15928,7 +15928,7 @@
         </is>
       </c>
       <c r="E596" s="20" t="n">
-        <v>209</v>
+        <v>222</v>
       </c>
     </row>
     <row r="597" ht="20" customHeight="1">
@@ -15953,7 +15953,7 @@
         </is>
       </c>
       <c r="E597" s="23" t="n">
-        <v>233</v>
+        <v>199</v>
       </c>
     </row>
     <row r="598" ht="20" customHeight="1">
@@ -15978,7 +15978,7 @@
         </is>
       </c>
       <c r="E598" s="20" t="n">
-        <v>135</v>
+        <v>163</v>
       </c>
     </row>
     <row r="599" ht="20" customHeight="1">
@@ -16003,7 +16003,7 @@
         </is>
       </c>
       <c r="E599" s="23" t="n">
-        <v>240</v>
+        <v>145</v>
       </c>
     </row>
     <row r="600" ht="20" customHeight="1">
@@ -16028,7 +16028,7 @@
         </is>
       </c>
       <c r="E600" s="20" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="601" ht="20" customHeight="1">
@@ -16053,7 +16053,7 @@
         </is>
       </c>
       <c r="E601" s="23" t="n">
-        <v>143</v>
+        <v>188</v>
       </c>
     </row>
     <row r="602" ht="20" customHeight="1">
@@ -16078,7 +16078,7 @@
         </is>
       </c>
       <c r="E602" s="20" t="n">
-        <v>237</v>
+        <v>210</v>
       </c>
     </row>
     <row r="603" ht="20" customHeight="1">
@@ -16103,7 +16103,7 @@
         </is>
       </c>
       <c r="E603" s="23" t="n">
-        <v>144</v>
+        <v>160</v>
       </c>
     </row>
     <row r="604" ht="20" customHeight="1">
@@ -16128,7 +16128,7 @@
         </is>
       </c>
       <c r="E604" s="20" t="n">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="605" ht="20" customHeight="1">
@@ -16153,7 +16153,7 @@
         </is>
       </c>
       <c r="E605" s="23" t="n">
-        <v>227</v>
+        <v>164</v>
       </c>
     </row>
     <row r="606" ht="20" customHeight="1">
@@ -16178,7 +16178,7 @@
         </is>
       </c>
       <c r="E606" s="20" t="n">
-        <v>221</v>
+        <v>163</v>
       </c>
     </row>
     <row r="607" ht="20" customHeight="1">
@@ -16203,7 +16203,7 @@
         </is>
       </c>
       <c r="E607" s="23" t="n">
-        <v>141</v>
+        <v>148</v>
       </c>
     </row>
     <row r="608" ht="20" customHeight="1">
@@ -16228,7 +16228,7 @@
         </is>
       </c>
       <c r="E608" s="20" t="n">
-        <v>214</v>
+        <v>144</v>
       </c>
     </row>
     <row r="609" ht="20" customHeight="1">
@@ -16253,7 +16253,7 @@
         </is>
       </c>
       <c r="E609" s="23" t="n">
-        <v>227</v>
+        <v>133</v>
       </c>
     </row>
     <row r="610" ht="20" customHeight="1">
@@ -16278,7 +16278,7 @@
         </is>
       </c>
       <c r="E610" s="20" t="n">
-        <v>204</v>
+        <v>223</v>
       </c>
     </row>
     <row r="611" ht="20" customHeight="1">
@@ -16303,7 +16303,7 @@
         </is>
       </c>
       <c r="E611" s="23" t="n">
-        <v>158</v>
+        <v>125</v>
       </c>
     </row>
     <row r="612" ht="20" customHeight="1">
@@ -16328,7 +16328,7 @@
         </is>
       </c>
       <c r="E612" s="20" t="n">
-        <v>182</v>
+        <v>136</v>
       </c>
     </row>
     <row r="613" ht="20" customHeight="1">
@@ -16353,7 +16353,7 @@
         </is>
       </c>
       <c r="E613" s="23" t="n">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="614" ht="20" customHeight="1">
@@ -16378,7 +16378,7 @@
         </is>
       </c>
       <c r="E614" s="20" t="n">
-        <v>228</v>
+        <v>139</v>
       </c>
     </row>
     <row r="615" ht="20" customHeight="1">
@@ -16403,7 +16403,7 @@
         </is>
       </c>
       <c r="E615" s="23" t="n">
-        <v>173</v>
+        <v>134</v>
       </c>
     </row>
     <row r="616" ht="20" customHeight="1">
@@ -16428,7 +16428,7 @@
         </is>
       </c>
       <c r="E616" s="20" t="n">
-        <v>185</v>
+        <v>125</v>
       </c>
     </row>
     <row r="617" ht="20" customHeight="1">
@@ -16453,7 +16453,7 @@
         </is>
       </c>
       <c r="E617" s="23" t="n">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="618" ht="20" customHeight="1">
@@ -16478,7 +16478,7 @@
         </is>
       </c>
       <c r="E618" s="20" t="n">
-        <v>139</v>
+        <v>222</v>
       </c>
     </row>
     <row r="619" ht="20" customHeight="1">
@@ -16503,7 +16503,7 @@
         </is>
       </c>
       <c r="E619" s="23" t="n">
-        <v>134</v>
+        <v>118</v>
       </c>
     </row>
     <row r="620" ht="20" customHeight="1">
@@ -16528,7 +16528,7 @@
         </is>
       </c>
       <c r="E620" s="20" t="n">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="621" ht="20" customHeight="1">
@@ -16553,7 +16553,7 @@
         </is>
       </c>
       <c r="E621" s="23" t="n">
-        <v>209</v>
+        <v>152</v>
       </c>
     </row>
     <row r="622" ht="20" customHeight="1">
@@ -16578,7 +16578,7 @@
         </is>
       </c>
       <c r="E622" s="20" t="n">
-        <v>216</v>
+        <v>185</v>
       </c>
     </row>
     <row r="623" ht="20" customHeight="1">
@@ -16603,7 +16603,7 @@
         </is>
       </c>
       <c r="E623" s="23" t="n">
-        <v>120</v>
+        <v>178</v>
       </c>
     </row>
     <row r="624" ht="20" customHeight="1">
@@ -16628,7 +16628,7 @@
         </is>
       </c>
       <c r="E624" s="20" t="n">
-        <v>230</v>
+        <v>188</v>
       </c>
     </row>
     <row r="625" ht="20" customHeight="1">
@@ -16653,7 +16653,7 @@
         </is>
       </c>
       <c r="E625" s="23" t="n">
-        <v>130</v>
+        <v>163</v>
       </c>
     </row>
     <row r="626" ht="20" customHeight="1">
@@ -16678,7 +16678,7 @@
         </is>
       </c>
       <c r="E626" s="20" t="n">
-        <v>173</v>
+        <v>181</v>
       </c>
     </row>
     <row r="627" ht="20" customHeight="1">
@@ -16703,7 +16703,7 @@
         </is>
       </c>
       <c r="E627" s="23" t="n">
-        <v>203</v>
+        <v>219</v>
       </c>
     </row>
     <row r="628" ht="20" customHeight="1">
@@ -16728,7 +16728,7 @@
         </is>
       </c>
       <c r="E628" s="20" t="n">
-        <v>185</v>
+        <v>165</v>
       </c>
     </row>
     <row r="629" ht="20" customHeight="1">
@@ -16753,7 +16753,7 @@
         </is>
       </c>
       <c r="E629" s="23" t="n">
-        <v>215</v>
+        <v>230</v>
       </c>
     </row>
     <row r="630" ht="20" customHeight="1">
@@ -16778,7 +16778,7 @@
         </is>
       </c>
       <c r="E630" s="20" t="n">
-        <v>122</v>
+        <v>132</v>
       </c>
     </row>
     <row r="631" ht="20" customHeight="1">
@@ -16803,7 +16803,7 @@
         </is>
       </c>
       <c r="E631" s="23" t="n">
-        <v>224</v>
+        <v>144</v>
       </c>
     </row>
     <row r="632" ht="20" customHeight="1">
@@ -16828,7 +16828,7 @@
         </is>
       </c>
       <c r="E632" s="20" t="n">
-        <v>210</v>
+        <v>190</v>
       </c>
     </row>
     <row r="633" ht="20" customHeight="1">
@@ -16853,7 +16853,7 @@
         </is>
       </c>
       <c r="E633" s="23" t="n">
-        <v>161</v>
+        <v>178</v>
       </c>
     </row>
     <row r="634" ht="20" customHeight="1">
@@ -16878,7 +16878,7 @@
         </is>
       </c>
       <c r="E634" s="20" t="n">
-        <v>155</v>
+        <v>197</v>
       </c>
     </row>
     <row r="635" ht="20" customHeight="1">
@@ -16903,7 +16903,7 @@
         </is>
       </c>
       <c r="E635" s="23" t="n">
-        <v>181</v>
+        <v>226</v>
       </c>
     </row>
     <row r="636" ht="20" customHeight="1">
@@ -16928,7 +16928,7 @@
         </is>
       </c>
       <c r="E636" s="20" t="n">
-        <v>156</v>
+        <v>138</v>
       </c>
     </row>
     <row r="637" ht="20" customHeight="1">
@@ -16953,7 +16953,7 @@
         </is>
       </c>
       <c r="E637" s="23" t="n">
-        <v>160</v>
+        <v>204</v>
       </c>
     </row>
     <row r="638" ht="20" customHeight="1">
@@ -16978,7 +16978,7 @@
         </is>
       </c>
       <c r="E638" s="20" t="n">
-        <v>117</v>
+        <v>200</v>
       </c>
     </row>
     <row r="639" ht="20" customHeight="1">
@@ -17003,7 +17003,7 @@
         </is>
       </c>
       <c r="E639" s="23" t="n">
-        <v>218</v>
+        <v>194</v>
       </c>
     </row>
     <row r="640" ht="20" customHeight="1">
@@ -17028,7 +17028,7 @@
         </is>
       </c>
       <c r="E640" s="20" t="n">
-        <v>131</v>
+        <v>211</v>
       </c>
     </row>
     <row r="641" ht="20" customHeight="1">
@@ -17053,7 +17053,7 @@
         </is>
       </c>
       <c r="E641" s="23" t="n">
-        <v>166</v>
+        <v>173</v>
       </c>
     </row>
     <row r="642" ht="20" customHeight="1">
@@ -17078,7 +17078,7 @@
         </is>
       </c>
       <c r="E642" s="20" t="n">
-        <v>133</v>
+        <v>147</v>
       </c>
     </row>
     <row r="643" ht="20" customHeight="1">
@@ -17103,7 +17103,7 @@
         </is>
       </c>
       <c r="E643" s="23" t="n">
-        <v>168</v>
+        <v>215</v>
       </c>
     </row>
     <row r="644" ht="20" customHeight="1">
@@ -17128,7 +17128,7 @@
         </is>
       </c>
       <c r="E644" s="20" t="n">
-        <v>112</v>
+        <v>239</v>
       </c>
     </row>
     <row r="645" ht="20" customHeight="1">
@@ -17153,7 +17153,7 @@
         </is>
       </c>
       <c r="E645" s="23" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="646" ht="20" customHeight="1">
@@ -17178,7 +17178,7 @@
         </is>
       </c>
       <c r="E646" s="20" t="n">
-        <v>214</v>
+        <v>225</v>
       </c>
     </row>
     <row r="647" ht="20" customHeight="1">
@@ -17203,7 +17203,7 @@
         </is>
       </c>
       <c r="E647" s="23" t="n">
-        <v>172</v>
+        <v>119</v>
       </c>
     </row>
     <row r="648" ht="20" customHeight="1">
@@ -17228,7 +17228,7 @@
         </is>
       </c>
       <c r="E648" s="20" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="649" ht="20" customHeight="1">
@@ -17253,7 +17253,7 @@
         </is>
       </c>
       <c r="E649" s="23" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="650" ht="20" customHeight="1">
@@ -17278,7 +17278,7 @@
         </is>
       </c>
       <c r="E650" s="20" t="n">
-        <v>165</v>
+        <v>192</v>
       </c>
     </row>
     <row r="651" ht="20" customHeight="1">
@@ -17303,7 +17303,7 @@
         </is>
       </c>
       <c r="E651" s="23" t="n">
-        <v>193</v>
+        <v>199</v>
       </c>
     </row>
     <row r="652" ht="20" customHeight="1">
@@ -17328,7 +17328,7 @@
         </is>
       </c>
       <c r="E652" s="20" t="n">
-        <v>155</v>
+        <v>147</v>
       </c>
     </row>
     <row r="653" ht="20" customHeight="1">
@@ -17353,7 +17353,7 @@
         </is>
       </c>
       <c r="E653" s="23" t="n">
-        <v>229</v>
+        <v>121</v>
       </c>
     </row>
     <row r="654" ht="20" customHeight="1">
@@ -17378,7 +17378,7 @@
         </is>
       </c>
       <c r="E654" s="20" t="n">
-        <v>229</v>
+        <v>133</v>
       </c>
     </row>
     <row r="655" ht="20" customHeight="1">
@@ -17403,7 +17403,7 @@
         </is>
       </c>
       <c r="E655" s="23" t="n">
-        <v>176</v>
+        <v>204</v>
       </c>
     </row>
     <row r="656" ht="20" customHeight="1">
@@ -17428,7 +17428,7 @@
         </is>
       </c>
       <c r="E656" s="20" t="n">
-        <v>227</v>
+        <v>165</v>
       </c>
     </row>
     <row r="657" ht="20" customHeight="1">
@@ -17453,7 +17453,7 @@
         </is>
       </c>
       <c r="E657" s="23" t="n">
-        <v>211</v>
+        <v>218</v>
       </c>
     </row>
     <row r="658" ht="20" customHeight="1">
@@ -17478,7 +17478,7 @@
         </is>
       </c>
       <c r="E658" s="20" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="659" ht="20" customHeight="1">
@@ -17503,7 +17503,7 @@
         </is>
       </c>
       <c r="E659" s="23" t="n">
-        <v>131</v>
+        <v>191</v>
       </c>
     </row>
     <row r="660" ht="20" customHeight="1">
@@ -17528,7 +17528,7 @@
         </is>
       </c>
       <c r="E660" s="20" t="n">
-        <v>194</v>
+        <v>154</v>
       </c>
     </row>
     <row r="661" ht="20" customHeight="1">
@@ -17553,7 +17553,7 @@
         </is>
       </c>
       <c r="E661" s="23" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="662" ht="20" customHeight="1">
@@ -17578,7 +17578,7 @@
         </is>
       </c>
       <c r="E662" s="20" t="n">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="663" ht="20" customHeight="1">
@@ -17603,7 +17603,7 @@
         </is>
       </c>
       <c r="E663" s="23" t="n">
-        <v>120</v>
+        <v>167</v>
       </c>
     </row>
     <row r="664" ht="20" customHeight="1">
@@ -17628,7 +17628,7 @@
         </is>
       </c>
       <c r="E664" s="20" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
     </row>
     <row r="665" ht="20" customHeight="1">
@@ -17653,7 +17653,7 @@
         </is>
       </c>
       <c r="E665" s="23" t="n">
-        <v>144</v>
+        <v>233</v>
       </c>
     </row>
     <row r="666" ht="20" customHeight="1">
@@ -17678,7 +17678,7 @@
         </is>
       </c>
       <c r="E666" s="20" t="n">
-        <v>146</v>
+        <v>178</v>
       </c>
     </row>
     <row r="667" ht="20" customHeight="1">
@@ -17703,7 +17703,7 @@
         </is>
       </c>
       <c r="E667" s="23" t="n">
-        <v>154</v>
+        <v>220</v>
       </c>
     </row>
     <row r="668" ht="20" customHeight="1">
@@ -17728,7 +17728,7 @@
         </is>
       </c>
       <c r="E668" s="20" t="n">
-        <v>162</v>
+        <v>146</v>
       </c>
     </row>
     <row r="669" ht="20" customHeight="1">
@@ -17753,7 +17753,7 @@
         </is>
       </c>
       <c r="E669" s="23" t="n">
-        <v>153</v>
+        <v>198</v>
       </c>
     </row>
     <row r="670" ht="20" customHeight="1">
@@ -17778,7 +17778,7 @@
         </is>
       </c>
       <c r="E670" s="20" t="n">
-        <v>222</v>
+        <v>148</v>
       </c>
     </row>
     <row r="671" ht="20" customHeight="1">
@@ -17803,7 +17803,7 @@
         </is>
       </c>
       <c r="E671" s="23" t="n">
-        <v>158</v>
+        <v>146</v>
       </c>
     </row>
     <row r="672" ht="20" customHeight="1">
@@ -17828,7 +17828,7 @@
         </is>
       </c>
       <c r="E672" s="20" t="n">
-        <v>177</v>
+        <v>194</v>
       </c>
     </row>
     <row r="673" ht="20" customHeight="1">
@@ -17853,7 +17853,7 @@
         </is>
       </c>
       <c r="E673" s="23" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="674" ht="20" customHeight="1">
@@ -17878,7 +17878,7 @@
         </is>
       </c>
       <c r="E674" s="20" t="n">
-        <v>193</v>
+        <v>167</v>
       </c>
     </row>
     <row r="675" ht="20" customHeight="1">
@@ -17903,7 +17903,7 @@
         </is>
       </c>
       <c r="E675" s="23" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="676" ht="20" customHeight="1">
@@ -17928,7 +17928,7 @@
         </is>
       </c>
       <c r="E676" s="20" t="n">
-        <v>225</v>
+        <v>131</v>
       </c>
     </row>
     <row r="677" ht="20" customHeight="1">
@@ -17953,7 +17953,7 @@
         </is>
       </c>
       <c r="E677" s="23" t="n">
-        <v>117</v>
+        <v>129</v>
       </c>
     </row>
     <row r="678" ht="20" customHeight="1">
@@ -17978,7 +17978,7 @@
         </is>
       </c>
       <c r="E678" s="20" t="n">
-        <v>218</v>
+        <v>169</v>
       </c>
     </row>
     <row r="679" ht="20" customHeight="1">
@@ -18003,7 +18003,7 @@
         </is>
       </c>
       <c r="E679" s="23" t="n">
-        <v>164</v>
+        <v>176</v>
       </c>
     </row>
     <row r="680" ht="20" customHeight="1">
@@ -18028,7 +18028,7 @@
         </is>
       </c>
       <c r="E680" s="20" t="n">
-        <v>137</v>
+        <v>189</v>
       </c>
     </row>
     <row r="681" ht="20" customHeight="1">
@@ -18053,7 +18053,7 @@
         </is>
       </c>
       <c r="E681" s="23" t="n">
-        <v>206</v>
+        <v>238</v>
       </c>
     </row>
     <row r="682" ht="20" customHeight="1">
@@ -18078,7 +18078,7 @@
         </is>
       </c>
       <c r="E682" s="20" t="n">
-        <v>196</v>
+        <v>149</v>
       </c>
     </row>
     <row r="683" ht="20" customHeight="1">
@@ -18103,7 +18103,7 @@
         </is>
       </c>
       <c r="E683" s="23" t="n">
-        <v>240</v>
+        <v>142</v>
       </c>
     </row>
     <row r="684" ht="20" customHeight="1">
@@ -18128,7 +18128,7 @@
         </is>
       </c>
       <c r="E684" s="20" t="n">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="685" ht="20" customHeight="1">
@@ -18153,7 +18153,7 @@
         </is>
       </c>
       <c r="E685" s="23" t="n">
-        <v>181</v>
+        <v>133</v>
       </c>
     </row>
     <row r="686" ht="20" customHeight="1">
@@ -18178,7 +18178,7 @@
         </is>
       </c>
       <c r="E686" s="20" t="n">
-        <v>215</v>
+        <v>223</v>
       </c>
     </row>
     <row r="687" ht="20" customHeight="1">
@@ -18203,7 +18203,7 @@
         </is>
       </c>
       <c r="E687" s="23" t="n">
-        <v>127</v>
+        <v>137</v>
       </c>
     </row>
     <row r="688" ht="20" customHeight="1">
@@ -18228,7 +18228,7 @@
         </is>
       </c>
       <c r="E688" s="20" t="n">
-        <v>159</v>
+        <v>219</v>
       </c>
     </row>
     <row r="689" ht="20" customHeight="1">
@@ -18253,7 +18253,7 @@
         </is>
       </c>
       <c r="E689" s="23" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="690" ht="20" customHeight="1">
@@ -18278,7 +18278,7 @@
         </is>
       </c>
       <c r="E690" s="20" t="n">
-        <v>177</v>
+        <v>140</v>
       </c>
     </row>
     <row r="691" ht="20" customHeight="1">
@@ -18303,7 +18303,7 @@
         </is>
       </c>
       <c r="E691" s="23" t="n">
-        <v>183</v>
+        <v>165</v>
       </c>
     </row>
     <row r="692" ht="20" customHeight="1">
@@ -18328,7 +18328,7 @@
         </is>
       </c>
       <c r="E692" s="20" t="n">
-        <v>153</v>
+        <v>232</v>
       </c>
     </row>
     <row r="693" ht="20" customHeight="1">
@@ -18353,7 +18353,7 @@
         </is>
       </c>
       <c r="E693" s="23" t="n">
-        <v>160</v>
+        <v>113</v>
       </c>
     </row>
     <row r="694" ht="20" customHeight="1">
@@ -18378,7 +18378,7 @@
         </is>
       </c>
       <c r="E694" s="20" t="n">
-        <v>186</v>
+        <v>154</v>
       </c>
     </row>
     <row r="695" ht="20" customHeight="1">
@@ -18403,7 +18403,7 @@
         </is>
       </c>
       <c r="E695" s="23" t="n">
-        <v>168</v>
+        <v>236</v>
       </c>
     </row>
     <row r="696" ht="20" customHeight="1">
@@ -18428,7 +18428,7 @@
         </is>
       </c>
       <c r="E696" s="20" t="n">
-        <v>115</v>
+        <v>177</v>
       </c>
     </row>
     <row r="697" ht="20" customHeight="1">
@@ -18453,7 +18453,7 @@
         </is>
       </c>
       <c r="E697" s="23" t="n">
-        <v>131</v>
+        <v>152</v>
       </c>
     </row>
     <row r="698" ht="20" customHeight="1">
@@ -18478,7 +18478,7 @@
         </is>
       </c>
       <c r="E698" s="20" t="n">
-        <v>199</v>
+        <v>231</v>
       </c>
     </row>
     <row r="699" ht="20" customHeight="1">
@@ -18503,7 +18503,7 @@
         </is>
       </c>
       <c r="E699" s="23" t="n">
-        <v>235</v>
+        <v>219</v>
       </c>
     </row>
     <row r="700" ht="20" customHeight="1">
@@ -18528,7 +18528,7 @@
         </is>
       </c>
       <c r="E700" s="20" t="n">
-        <v>175</v>
+        <v>114</v>
       </c>
     </row>
     <row r="701" ht="20" customHeight="1">
@@ -18553,7 +18553,7 @@
         </is>
       </c>
       <c r="E701" s="23" t="n">
-        <v>227</v>
+        <v>137</v>
       </c>
     </row>
     <row r="702" ht="20" customHeight="1">
@@ -18578,7 +18578,7 @@
         </is>
       </c>
       <c r="E702" s="20" t="n">
-        <v>124</v>
+        <v>224</v>
       </c>
     </row>
     <row r="703" ht="20" customHeight="1">
@@ -18603,7 +18603,7 @@
         </is>
       </c>
       <c r="E703" s="23" t="n">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="704" ht="20" customHeight="1">
@@ -18628,7 +18628,7 @@
         </is>
       </c>
       <c r="E704" s="20" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
     </row>
     <row r="705" ht="20" customHeight="1">
@@ -18653,7 +18653,7 @@
         </is>
       </c>
       <c r="E705" s="23" t="n">
-        <v>133</v>
+        <v>192</v>
       </c>
     </row>
     <row r="706" ht="20" customHeight="1">
@@ -18678,7 +18678,7 @@
         </is>
       </c>
       <c r="E706" s="20" t="n">
-        <v>199</v>
+        <v>173</v>
       </c>
     </row>
     <row r="707" ht="20" customHeight="1">
@@ -18703,7 +18703,7 @@
         </is>
       </c>
       <c r="E707" s="23" t="n">
-        <v>112</v>
+        <v>202</v>
       </c>
     </row>
     <row r="708" ht="20" customHeight="1">
@@ -18728,7 +18728,7 @@
         </is>
       </c>
       <c r="E708" s="20" t="n">
-        <v>199</v>
+        <v>204</v>
       </c>
     </row>
     <row r="709" ht="20" customHeight="1">
@@ -18753,7 +18753,7 @@
         </is>
       </c>
       <c r="E709" s="23" t="n">
-        <v>195</v>
+        <v>209</v>
       </c>
     </row>
     <row r="710" ht="20" customHeight="1">
@@ -18778,7 +18778,7 @@
         </is>
       </c>
       <c r="E710" s="20" t="n">
-        <v>228</v>
+        <v>176</v>
       </c>
     </row>
     <row r="711" ht="20" customHeight="1">
@@ -18803,7 +18803,7 @@
         </is>
       </c>
       <c r="E711" s="23" t="n">
-        <v>240</v>
+        <v>168</v>
       </c>
     </row>
     <row r="712" ht="20" customHeight="1">
@@ -18828,7 +18828,7 @@
         </is>
       </c>
       <c r="E712" s="20" t="n">
-        <v>197</v>
+        <v>164</v>
       </c>
     </row>
     <row r="713" ht="20" customHeight="1">
@@ -18853,7 +18853,7 @@
         </is>
       </c>
       <c r="E713" s="23" t="n">
-        <v>116</v>
+        <v>212</v>
       </c>
     </row>
     <row r="714" ht="20" customHeight="1">
@@ -18878,7 +18878,7 @@
         </is>
       </c>
       <c r="E714" s="20" t="n">
-        <v>240</v>
+        <v>168</v>
       </c>
     </row>
     <row r="715" ht="20" customHeight="1">
@@ -18903,7 +18903,7 @@
         </is>
       </c>
       <c r="E715" s="23" t="n">
-        <v>240</v>
+        <v>176</v>
       </c>
     </row>
     <row r="716" ht="20" customHeight="1">
@@ -18928,7 +18928,7 @@
         </is>
       </c>
       <c r="E716" s="20" t="n">
-        <v>144</v>
+        <v>155</v>
       </c>
     </row>
     <row r="717" ht="20" customHeight="1">
@@ -18953,7 +18953,7 @@
         </is>
       </c>
       <c r="E717" s="23" t="n">
-        <v>158</v>
+        <v>181</v>
       </c>
     </row>
     <row r="718" ht="20" customHeight="1">
@@ -18978,7 +18978,7 @@
         </is>
       </c>
       <c r="E718" s="20" t="n">
-        <v>213</v>
+        <v>196</v>
       </c>
     </row>
     <row r="719" ht="20" customHeight="1">
@@ -19003,7 +19003,7 @@
         </is>
       </c>
       <c r="E719" s="23" t="n">
-        <v>120</v>
+        <v>219</v>
       </c>
     </row>
     <row r="720" ht="20" customHeight="1">
@@ -19028,7 +19028,7 @@
         </is>
       </c>
       <c r="E720" s="20" t="n">
-        <v>207</v>
+        <v>235</v>
       </c>
     </row>
     <row r="721" ht="20" customHeight="1">
@@ -19053,7 +19053,7 @@
         </is>
       </c>
       <c r="E721" s="23" t="n">
-        <v>173</v>
+        <v>192</v>
       </c>
     </row>
     <row r="722" ht="20" customHeight="1">
@@ -19078,7 +19078,7 @@
         </is>
       </c>
       <c r="E722" s="20" t="n">
-        <v>226</v>
+        <v>143</v>
       </c>
     </row>
     <row r="723" ht="20" customHeight="1">
@@ -19103,7 +19103,7 @@
         </is>
       </c>
       <c r="E723" s="23" t="n">
-        <v>119</v>
+        <v>184</v>
       </c>
     </row>
     <row r="724" ht="20" customHeight="1">
@@ -19128,7 +19128,7 @@
         </is>
       </c>
       <c r="E724" s="20" t="n">
-        <v>185</v>
+        <v>171</v>
       </c>
     </row>
     <row r="725" ht="20" customHeight="1">
@@ -19153,7 +19153,7 @@
         </is>
       </c>
       <c r="E725" s="23" t="n">
-        <v>200</v>
+        <v>115</v>
       </c>
     </row>
     <row r="726" ht="20" customHeight="1">
@@ -19178,7 +19178,7 @@
         </is>
       </c>
       <c r="E726" s="20" t="n">
-        <v>130</v>
+        <v>231</v>
       </c>
     </row>
     <row r="727" ht="20" customHeight="1">
@@ -19203,7 +19203,7 @@
         </is>
       </c>
       <c r="E727" s="23" t="n">
-        <v>152</v>
+        <v>128</v>
       </c>
     </row>
     <row r="728" ht="20" customHeight="1">
@@ -19228,7 +19228,7 @@
         </is>
       </c>
       <c r="E728" s="20" t="n">
-        <v>209</v>
+        <v>195</v>
       </c>
     </row>
     <row r="729" ht="20" customHeight="1">
@@ -19253,7 +19253,7 @@
         </is>
       </c>
       <c r="E729" s="23" t="n">
-        <v>146</v>
+        <v>205</v>
       </c>
     </row>
     <row r="730" ht="20" customHeight="1">
@@ -19278,7 +19278,7 @@
         </is>
       </c>
       <c r="E730" s="20" t="n">
-        <v>126</v>
+        <v>146</v>
       </c>
     </row>
     <row r="731" ht="20" customHeight="1">
@@ -19303,7 +19303,7 @@
         </is>
       </c>
       <c r="E731" s="23" t="n">
-        <v>239</v>
+        <v>134</v>
       </c>
     </row>
     <row r="732" ht="20" customHeight="1">
@@ -19328,7 +19328,7 @@
         </is>
       </c>
       <c r="E732" s="20" t="n">
-        <v>230</v>
+        <v>236</v>
       </c>
     </row>
     <row r="733" ht="20" customHeight="1">
@@ -19353,7 +19353,7 @@
         </is>
       </c>
       <c r="E733" s="23" t="n">
-        <v>128</v>
+        <v>161</v>
       </c>
     </row>
     <row r="734" ht="20" customHeight="1">
@@ -19378,7 +19378,7 @@
         </is>
       </c>
       <c r="E734" s="20" t="n">
-        <v>207</v>
+        <v>236</v>
       </c>
     </row>
     <row r="735" ht="20" customHeight="1">
@@ -19403,7 +19403,7 @@
         </is>
       </c>
       <c r="E735" s="23" t="n">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="736" ht="20" customHeight="1">
@@ -19428,7 +19428,7 @@
         </is>
       </c>
       <c r="E736" s="20" t="n">
-        <v>193</v>
+        <v>147</v>
       </c>
     </row>
     <row r="737" ht="20" customHeight="1">
@@ -19453,7 +19453,7 @@
         </is>
       </c>
       <c r="E737" s="23" t="n">
-        <v>192</v>
+        <v>146</v>
       </c>
     </row>
     <row r="738" ht="20" customHeight="1">
@@ -19478,7 +19478,7 @@
         </is>
       </c>
       <c r="E738" s="20" t="n">
-        <v>237</v>
+        <v>183</v>
       </c>
     </row>
     <row r="739" ht="20" customHeight="1">
@@ -19503,7 +19503,7 @@
         </is>
       </c>
       <c r="E739" s="23" t="n">
-        <v>232</v>
+        <v>185</v>
       </c>
     </row>
     <row r="740" ht="20" customHeight="1">
@@ -19528,7 +19528,7 @@
         </is>
       </c>
       <c r="E740" s="20" t="n">
-        <v>143</v>
+        <v>218</v>
       </c>
     </row>
     <row r="741" ht="20" customHeight="1">
@@ -19553,7 +19553,7 @@
         </is>
       </c>
       <c r="E741" s="23" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="742" ht="20" customHeight="1">
@@ -19578,7 +19578,7 @@
         </is>
       </c>
       <c r="E742" s="20" t="n">
-        <v>228</v>
+        <v>180</v>
       </c>
     </row>
     <row r="743" ht="20" customHeight="1">
@@ -19603,7 +19603,7 @@
         </is>
       </c>
       <c r="E743" s="23" t="n">
-        <v>203</v>
+        <v>195</v>
       </c>
     </row>
     <row r="744" ht="20" customHeight="1">
@@ -19628,7 +19628,7 @@
         </is>
       </c>
       <c r="E744" s="20" t="n">
-        <v>225</v>
+        <v>231</v>
       </c>
     </row>
     <row r="745" ht="20" customHeight="1">
@@ -19653,7 +19653,7 @@
         </is>
       </c>
       <c r="E745" s="23" t="n">
-        <v>176</v>
+        <v>117</v>
       </c>
     </row>
     <row r="746" ht="20" customHeight="1">
@@ -19678,7 +19678,7 @@
         </is>
       </c>
       <c r="E746" s="20" t="n">
-        <v>199</v>
+        <v>211</v>
       </c>
     </row>
     <row r="747" ht="20" customHeight="1">
@@ -19703,7 +19703,7 @@
         </is>
       </c>
       <c r="E747" s="23" t="n">
-        <v>166</v>
+        <v>117</v>
       </c>
     </row>
     <row r="748" ht="20" customHeight="1">
@@ -19728,7 +19728,7 @@
         </is>
       </c>
       <c r="E748" s="20" t="n">
-        <v>171</v>
+        <v>232</v>
       </c>
     </row>
     <row r="749" ht="20" customHeight="1">
@@ -19753,7 +19753,7 @@
         </is>
       </c>
       <c r="E749" s="23" t="n">
-        <v>122</v>
+        <v>227</v>
       </c>
     </row>
     <row r="750" ht="20" customHeight="1">
@@ -19778,7 +19778,7 @@
         </is>
       </c>
       <c r="E750" s="20" t="n">
-        <v>201</v>
+        <v>121</v>
       </c>
     </row>
     <row r="751" ht="20" customHeight="1">
@@ -19803,7 +19803,7 @@
         </is>
       </c>
       <c r="E751" s="23" t="n">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="752" ht="20" customHeight="1">
@@ -19828,7 +19828,7 @@
         </is>
       </c>
       <c r="E752" s="20" t="n">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="753" ht="20" customHeight="1">
@@ -19853,7 +19853,7 @@
         </is>
       </c>
       <c r="E753" s="23" t="n">
-        <v>206</v>
+        <v>131</v>
       </c>
     </row>
     <row r="754" ht="20" customHeight="1">
@@ -19878,7 +19878,7 @@
         </is>
       </c>
       <c r="E754" s="20" t="n">
-        <v>129</v>
+        <v>142</v>
       </c>
     </row>
     <row r="755" ht="20" customHeight="1">
@@ -19903,7 +19903,7 @@
         </is>
       </c>
       <c r="E755" s="23" t="n">
-        <v>175</v>
+        <v>234</v>
       </c>
     </row>
     <row r="756" ht="20" customHeight="1">
@@ -19928,7 +19928,7 @@
         </is>
       </c>
       <c r="E756" s="20" t="n">
-        <v>127</v>
+        <v>210</v>
       </c>
     </row>
     <row r="757" ht="20" customHeight="1">
@@ -19953,7 +19953,7 @@
         </is>
       </c>
       <c r="E757" s="23" t="n">
-        <v>230</v>
+        <v>205</v>
       </c>
     </row>
     <row r="758" ht="20" customHeight="1">
@@ -19978,7 +19978,7 @@
         </is>
       </c>
       <c r="E758" s="20" t="n">
-        <v>227</v>
+        <v>113</v>
       </c>
     </row>
     <row r="759" ht="20" customHeight="1">
@@ -20003,7 +20003,7 @@
         </is>
       </c>
       <c r="E759" s="23" t="n">
-        <v>195</v>
+        <v>151</v>
       </c>
     </row>
     <row r="760" ht="20" customHeight="1">
@@ -20028,7 +20028,7 @@
         </is>
       </c>
       <c r="E760" s="20" t="n">
-        <v>156</v>
+        <v>239</v>
       </c>
     </row>
     <row r="761" ht="20" customHeight="1">
@@ -20053,7 +20053,7 @@
         </is>
       </c>
       <c r="E761" s="23" t="n">
-        <v>179</v>
+        <v>157</v>
       </c>
     </row>
     <row r="762" ht="20" customHeight="1">
@@ -20078,7 +20078,7 @@
         </is>
       </c>
       <c r="E762" s="20" t="n">
-        <v>208</v>
+        <v>119</v>
       </c>
     </row>
     <row r="763" ht="20" customHeight="1">
@@ -20103,7 +20103,7 @@
         </is>
       </c>
       <c r="E763" s="23" t="n">
-        <v>137</v>
+        <v>239</v>
       </c>
     </row>
     <row r="764" ht="20" customHeight="1">
@@ -20128,7 +20128,7 @@
         </is>
       </c>
       <c r="E764" s="20" t="n">
-        <v>173</v>
+        <v>225</v>
       </c>
     </row>
     <row r="765" ht="20" customHeight="1">
@@ -20153,7 +20153,7 @@
         </is>
       </c>
       <c r="E765" s="23" t="n">
-        <v>185</v>
+        <v>123</v>
       </c>
     </row>
     <row r="766" ht="20" customHeight="1">
@@ -20178,7 +20178,7 @@
         </is>
       </c>
       <c r="E766" s="20" t="n">
-        <v>213</v>
+        <v>202</v>
       </c>
     </row>
     <row r="767" ht="20" customHeight="1">
@@ -20203,7 +20203,7 @@
         </is>
       </c>
       <c r="E767" s="23" t="n">
-        <v>126</v>
+        <v>171</v>
       </c>
     </row>
     <row r="768" ht="20" customHeight="1">
@@ -20228,7 +20228,7 @@
         </is>
       </c>
       <c r="E768" s="20" t="n">
-        <v>184</v>
+        <v>170</v>
       </c>
     </row>
     <row r="769" ht="20" customHeight="1">
@@ -20253,7 +20253,7 @@
         </is>
       </c>
       <c r="E769" s="23" t="n">
-        <v>211</v>
+        <v>122</v>
       </c>
     </row>
     <row r="770" ht="20" customHeight="1">
@@ -20278,7 +20278,7 @@
         </is>
       </c>
       <c r="E770" s="20" t="n">
-        <v>235</v>
+        <v>215</v>
       </c>
     </row>
     <row r="771" ht="20" customHeight="1">
@@ -20303,7 +20303,7 @@
         </is>
       </c>
       <c r="E771" s="23" t="n">
-        <v>223</v>
+        <v>145</v>
       </c>
     </row>
     <row r="772" ht="20" customHeight="1">
@@ -20328,7 +20328,7 @@
         </is>
       </c>
       <c r="E772" s="20" t="n">
-        <v>151</v>
+        <v>184</v>
       </c>
     </row>
     <row r="773" ht="20" customHeight="1">
@@ -20353,7 +20353,7 @@
         </is>
       </c>
       <c r="E773" s="23" t="n">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="774" ht="20" customHeight="1">
@@ -20378,7 +20378,7 @@
         </is>
       </c>
       <c r="E774" s="20" t="n">
-        <v>125</v>
+        <v>140</v>
       </c>
     </row>
     <row r="775" ht="20" customHeight="1">
@@ -20403,7 +20403,7 @@
         </is>
       </c>
       <c r="E775" s="23" t="n">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="776" ht="20" customHeight="1">
@@ -20428,7 +20428,7 @@
         </is>
       </c>
       <c r="E776" s="20" t="n">
-        <v>148</v>
+        <v>190</v>
       </c>
     </row>
     <row r="777" ht="20" customHeight="1">
@@ -20453,7 +20453,7 @@
         </is>
       </c>
       <c r="E777" s="23" t="n">
-        <v>150</v>
+        <v>168</v>
       </c>
     </row>
     <row r="778" ht="20" customHeight="1">
@@ -20478,7 +20478,7 @@
         </is>
       </c>
       <c r="E778" s="20" t="n">
-        <v>203</v>
+        <v>191</v>
       </c>
     </row>
     <row r="779" ht="20" customHeight="1">
@@ -20503,7 +20503,7 @@
         </is>
       </c>
       <c r="E779" s="23" t="n">
-        <v>204</v>
+        <v>111</v>
       </c>
     </row>
     <row r="780" ht="20" customHeight="1">
@@ -20528,7 +20528,7 @@
         </is>
       </c>
       <c r="E780" s="20" t="n">
-        <v>218</v>
+        <v>183</v>
       </c>
     </row>
     <row r="781" ht="20" customHeight="1">
@@ -20553,7 +20553,7 @@
         </is>
       </c>
       <c r="E781" s="23" t="n">
-        <v>144</v>
+        <v>171</v>
       </c>
     </row>
     <row r="782" ht="20" customHeight="1">
@@ -20578,7 +20578,7 @@
         </is>
       </c>
       <c r="E782" s="20" t="n">
-        <v>229</v>
+        <v>223</v>
       </c>
     </row>
     <row r="783" ht="20" customHeight="1">
@@ -20603,7 +20603,7 @@
         </is>
       </c>
       <c r="E783" s="23" t="n">
-        <v>153</v>
+        <v>163</v>
       </c>
     </row>
     <row r="784" ht="20" customHeight="1">
@@ -20628,7 +20628,7 @@
         </is>
       </c>
       <c r="E784" s="20" t="n">
-        <v>188</v>
+        <v>208</v>
       </c>
     </row>
     <row r="785" ht="20" customHeight="1">
@@ -20653,7 +20653,7 @@
         </is>
       </c>
       <c r="E785" s="23" t="n">
-        <v>157</v>
+        <v>205</v>
       </c>
     </row>
     <row r="786" ht="20" customHeight="1">
@@ -20678,7 +20678,7 @@
         </is>
       </c>
       <c r="E786" s="20" t="n">
-        <v>148</v>
+        <v>200</v>
       </c>
     </row>
     <row r="787" ht="20" customHeight="1">
@@ -20703,7 +20703,7 @@
         </is>
       </c>
       <c r="E787" s="23" t="n">
-        <v>116</v>
+        <v>203</v>
       </c>
     </row>
     <row r="788" ht="20" customHeight="1">
@@ -20728,7 +20728,7 @@
         </is>
       </c>
       <c r="E788" s="20" t="n">
-        <v>208</v>
+        <v>162</v>
       </c>
     </row>
     <row r="789" ht="20" customHeight="1">
@@ -20753,7 +20753,7 @@
         </is>
       </c>
       <c r="E789" s="23" t="n">
-        <v>223</v>
+        <v>195</v>
       </c>
     </row>
     <row r="790" ht="20" customHeight="1">
@@ -20778,7 +20778,7 @@
         </is>
       </c>
       <c r="E790" s="20" t="n">
-        <v>127</v>
+        <v>165</v>
       </c>
     </row>
     <row r="791" ht="20" customHeight="1">
@@ -20803,7 +20803,7 @@
         </is>
       </c>
       <c r="E791" s="23" t="n">
-        <v>142</v>
+        <v>199</v>
       </c>
     </row>
     <row r="792" ht="20" customHeight="1">
@@ -20828,7 +20828,7 @@
         </is>
       </c>
       <c r="E792" s="20" t="n">
-        <v>171</v>
+        <v>145</v>
       </c>
     </row>
     <row r="793" ht="20" customHeight="1">
@@ -20853,7 +20853,7 @@
         </is>
       </c>
       <c r="E793" s="23" t="n">
-        <v>113</v>
+        <v>138</v>
       </c>
     </row>
     <row r="794" ht="20" customHeight="1">
@@ -20878,7 +20878,7 @@
         </is>
       </c>
       <c r="E794" s="20" t="n">
-        <v>223</v>
+        <v>239</v>
       </c>
     </row>
     <row r="795" ht="20" customHeight="1">
@@ -20903,7 +20903,7 @@
         </is>
       </c>
       <c r="E795" s="23" t="n">
-        <v>186</v>
+        <v>155</v>
       </c>
     </row>
     <row r="796" ht="20" customHeight="1">
@@ -20928,7 +20928,7 @@
         </is>
       </c>
       <c r="E796" s="20" t="n">
-        <v>189</v>
+        <v>223</v>
       </c>
     </row>
     <row r="797" ht="20" customHeight="1">
@@ -20953,7 +20953,7 @@
         </is>
       </c>
       <c r="E797" s="23" t="n">
-        <v>138</v>
+        <v>111</v>
       </c>
     </row>
     <row r="798" ht="20" customHeight="1">
@@ -20978,7 +20978,7 @@
         </is>
       </c>
       <c r="E798" s="20" t="n">
-        <v>123</v>
+        <v>237</v>
       </c>
     </row>
     <row r="799" ht="20" customHeight="1">
@@ -21003,7 +21003,7 @@
         </is>
       </c>
       <c r="E799" s="23" t="n">
-        <v>224</v>
+        <v>195</v>
       </c>
     </row>
     <row r="800" ht="20" customHeight="1">
@@ -21028,7 +21028,7 @@
         </is>
       </c>
       <c r="E800" s="20" t="n">
-        <v>186</v>
+        <v>240</v>
       </c>
     </row>
     <row r="801" ht="20" customHeight="1">
@@ -21053,7 +21053,7 @@
         </is>
       </c>
       <c r="E801" s="23" t="n">
-        <v>227</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/Appium_E2E_Test_Report_Traverse.xlsx
+++ b/Appium_E2E_Test_Report_Traverse.xlsx
@@ -791,7 +791,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22 05:58:55</t>
+          <t>2026-07-22 06:16:50</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="E2" s="20" t="n">
-        <v>209</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="E3" s="23" t="n">
-        <v>229</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="E4" s="20" t="n">
-        <v>199</v>
+        <v>219</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="E5" s="23" t="n">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="E6" s="20" t="n">
-        <v>198</v>
+        <v>220</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="E7" s="23" t="n">
-        <v>133</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -1228,7 +1228,7 @@
         </is>
       </c>
       <c r="E8" s="20" t="n">
-        <v>154</v>
+        <v>220</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="E9" s="23" t="n">
-        <v>207</v>
+        <v>224</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
@@ -1278,7 +1278,7 @@
         </is>
       </c>
       <c r="E10" s="20" t="n">
-        <v>198</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="E11" s="23" t="n">
-        <v>180</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
@@ -1328,7 +1328,7 @@
         </is>
       </c>
       <c r="E12" s="20" t="n">
-        <v>183</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="E13" s="23" t="n">
-        <v>164</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="E14" s="20" t="n">
-        <v>177</v>
+        <v>153</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="E15" s="23" t="n">
-        <v>158</v>
+        <v>169</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="E16" s="20" t="n">
-        <v>199</v>
+        <v>138</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="E17" s="23" t="n">
-        <v>212</v>
+        <v>196</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -1503,7 +1503,7 @@
         </is>
       </c>
       <c r="E19" s="23" t="n">
-        <v>199</v>
+        <v>165</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="E20" s="20" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="E21" s="23" t="n">
-        <v>119</v>
+        <v>221</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
@@ -1578,7 +1578,7 @@
         </is>
       </c>
       <c r="E22" s="20" t="n">
-        <v>152</v>
+        <v>235</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="E23" s="23" t="n">
-        <v>236</v>
+        <v>143</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
@@ -1628,7 +1628,7 @@
         </is>
       </c>
       <c r="E24" s="20" t="n">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="E25" s="23" t="n">
-        <v>172</v>
+        <v>236</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
@@ -1678,7 +1678,7 @@
         </is>
       </c>
       <c r="E26" s="20" t="n">
-        <v>111</v>
+        <v>197</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="E27" s="23" t="n">
-        <v>173</v>
+        <v>222</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="E28" s="20" t="n">
-        <v>224</v>
+        <v>140</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="E29" s="23" t="n">
-        <v>205</v>
+        <v>239</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="E30" s="20" t="n">
-        <v>183</v>
+        <v>208</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
@@ -1803,7 +1803,7 @@
         </is>
       </c>
       <c r="E31" s="23" t="n">
-        <v>142</v>
+        <v>127</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
@@ -1828,7 +1828,7 @@
         </is>
       </c>
       <c r="E32" s="20" t="n">
-        <v>111</v>
+        <v>178</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
@@ -1853,7 +1853,7 @@
         </is>
       </c>
       <c r="E33" s="23" t="n">
-        <v>167</v>
+        <v>139</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
@@ -1878,7 +1878,7 @@
         </is>
       </c>
       <c r="E34" s="20" t="n">
-        <v>163</v>
+        <v>139</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="E35" s="23" t="n">
-        <v>226</v>
+        <v>110</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="E36" s="20" t="n">
-        <v>137</v>
+        <v>225</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="E37" s="23" t="n">
-        <v>194</v>
+        <v>221</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
@@ -1978,7 +1978,7 @@
         </is>
       </c>
       <c r="E38" s="20" t="n">
-        <v>118</v>
+        <v>137</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="E39" s="23" t="n">
-        <v>206</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="E40" s="20" t="n">
-        <v>189</v>
+        <v>178</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="E41" s="23" t="n">
-        <v>132</v>
+        <v>220</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
@@ -2078,7 +2078,7 @@
         </is>
       </c>
       <c r="E42" s="20" t="n">
-        <v>187</v>
+        <v>178</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="E43" s="23" t="n">
-        <v>139</v>
+        <v>173</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="E44" s="20" t="n">
-        <v>111</v>
+        <v>159</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="E45" s="23" t="n">
-        <v>190</v>
+        <v>119</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
@@ -2178,7 +2178,7 @@
         </is>
       </c>
       <c r="E46" s="20" t="n">
-        <v>164</v>
+        <v>110</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
@@ -2203,7 +2203,7 @@
         </is>
       </c>
       <c r="E47" s="23" t="n">
-        <v>199</v>
+        <v>133</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="E48" s="20" t="n">
-        <v>206</v>
+        <v>217</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
@@ -2253,7 +2253,7 @@
         </is>
       </c>
       <c r="E49" s="23" t="n">
-        <v>153</v>
+        <v>225</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
@@ -2278,7 +2278,7 @@
         </is>
       </c>
       <c r="E50" s="20" t="n">
-        <v>229</v>
+        <v>148</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="E51" s="23" t="n">
-        <v>219</v>
+        <v>119</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
@@ -2328,7 +2328,7 @@
         </is>
       </c>
       <c r="E52" s="20" t="n">
-        <v>190</v>
+        <v>160</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
@@ -2353,7 +2353,7 @@
         </is>
       </c>
       <c r="E53" s="23" t="n">
-        <v>164</v>
+        <v>185</v>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="E54" s="20" t="n">
-        <v>115</v>
+        <v>222</v>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1">
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="E55" s="23" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1">
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="E56" s="20" t="n">
-        <v>172</v>
+        <v>117</v>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1">
@@ -2453,7 +2453,7 @@
         </is>
       </c>
       <c r="E57" s="23" t="n">
-        <v>124</v>
+        <v>212</v>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1">
@@ -2478,7 +2478,7 @@
         </is>
       </c>
       <c r="E58" s="20" t="n">
-        <v>234</v>
+        <v>205</v>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1">
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="E59" s="23" t="n">
-        <v>168</v>
+        <v>201</v>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1">
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="E60" s="20" t="n">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
@@ -2553,7 +2553,7 @@
         </is>
       </c>
       <c r="E61" s="23" t="n">
-        <v>170</v>
+        <v>177</v>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="E62" s="20" t="n">
-        <v>211</v>
+        <v>199</v>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="E63" s="23" t="n">
-        <v>138</v>
+        <v>230</v>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1">
@@ -2628,7 +2628,7 @@
         </is>
       </c>
       <c r="E64" s="20" t="n">
-        <v>219</v>
+        <v>172</v>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1">
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="E65" s="23" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1">
@@ -2678,7 +2678,7 @@
         </is>
       </c>
       <c r="E66" s="20" t="n">
-        <v>232</v>
+        <v>151</v>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="E67" s="23" t="n">
-        <v>170</v>
+        <v>181</v>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="E68" s="20" t="n">
-        <v>152</v>
+        <v>129</v>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="E69" s="23" t="n">
-        <v>208</v>
+        <v>233</v>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1">
@@ -2803,7 +2803,7 @@
         </is>
       </c>
       <c r="E71" s="23" t="n">
-        <v>136</v>
+        <v>234</v>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1">
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="E72" s="20" t="n">
-        <v>191</v>
+        <v>226</v>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1">
@@ -2853,7 +2853,7 @@
         </is>
       </c>
       <c r="E73" s="23" t="n">
-        <v>166</v>
+        <v>136</v>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
@@ -2878,7 +2878,7 @@
         </is>
       </c>
       <c r="E74" s="20" t="n">
-        <v>236</v>
+        <v>220</v>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="E75" s="23" t="n">
-        <v>150</v>
+        <v>136</v>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
@@ -2928,7 +2928,7 @@
         </is>
       </c>
       <c r="E76" s="20" t="n">
-        <v>237</v>
+        <v>203</v>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="E77" s="23" t="n">
-        <v>231</v>
+        <v>198</v>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1">
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="E78" s="20" t="n">
-        <v>206</v>
+        <v>177</v>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
@@ -3003,7 +3003,7 @@
         </is>
       </c>
       <c r="E79" s="23" t="n">
-        <v>110</v>
+        <v>197</v>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1">
@@ -3028,7 +3028,7 @@
         </is>
       </c>
       <c r="E80" s="20" t="n">
-        <v>154</v>
+        <v>230</v>
       </c>
     </row>
     <row r="81" ht="20" customHeight="1">
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="E81" s="23" t="n">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="82" ht="20" customHeight="1">
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="E82" s="20" t="n">
-        <v>126</v>
+        <v>114</v>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1">
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="E83" s="23" t="n">
-        <v>235</v>
+        <v>179</v>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1">
@@ -3128,7 +3128,7 @@
         </is>
       </c>
       <c r="E84" s="20" t="n">
-        <v>117</v>
+        <v>136</v>
       </c>
     </row>
     <row r="85" ht="20" customHeight="1">
@@ -3153,7 +3153,7 @@
         </is>
       </c>
       <c r="E85" s="23" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="86" ht="20" customHeight="1">
@@ -3178,7 +3178,7 @@
         </is>
       </c>
       <c r="E86" s="20" t="n">
-        <v>210</v>
+        <v>127</v>
       </c>
     </row>
     <row r="87" ht="20" customHeight="1">
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="E87" s="23" t="n">
-        <v>132</v>
+        <v>220</v>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1">
@@ -3228,7 +3228,7 @@
         </is>
       </c>
       <c r="E88" s="20" t="n">
-        <v>130</v>
+        <v>237</v>
       </c>
     </row>
     <row r="89" ht="20" customHeight="1">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="E89" s="23" t="n">
-        <v>239</v>
+        <v>145</v>
       </c>
     </row>
     <row r="90" ht="20" customHeight="1">
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="E90" s="20" t="n">
-        <v>166</v>
+        <v>186</v>
       </c>
     </row>
     <row r="91" ht="20" customHeight="1">
@@ -3303,7 +3303,7 @@
         </is>
       </c>
       <c r="E91" s="23" t="n">
-        <v>209</v>
+        <v>159</v>
       </c>
     </row>
     <row r="92" ht="20" customHeight="1">
@@ -3328,7 +3328,7 @@
         </is>
       </c>
       <c r="E92" s="20" t="n">
-        <v>205</v>
+        <v>234</v>
       </c>
     </row>
     <row r="93" ht="20" customHeight="1">
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="E93" s="23" t="n">
-        <v>114</v>
+        <v>223</v>
       </c>
     </row>
     <row r="94" ht="20" customHeight="1">
@@ -3378,7 +3378,7 @@
         </is>
       </c>
       <c r="E94" s="20" t="n">
-        <v>187</v>
+        <v>139</v>
       </c>
     </row>
     <row r="95" ht="20" customHeight="1">
@@ -3403,7 +3403,7 @@
         </is>
       </c>
       <c r="E95" s="23" t="n">
-        <v>183</v>
+        <v>196</v>
       </c>
     </row>
     <row r="96" ht="20" customHeight="1">
@@ -3428,7 +3428,7 @@
         </is>
       </c>
       <c r="E96" s="20" t="n">
-        <v>210</v>
+        <v>127</v>
       </c>
     </row>
     <row r="97" ht="20" customHeight="1">
@@ -3453,7 +3453,7 @@
         </is>
       </c>
       <c r="E97" s="23" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="98" ht="20" customHeight="1">
@@ -3478,7 +3478,7 @@
         </is>
       </c>
       <c r="E98" s="20" t="n">
-        <v>160</v>
+        <v>191</v>
       </c>
     </row>
     <row r="99" ht="20" customHeight="1">
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="E99" s="23" t="n">
-        <v>199</v>
+        <v>233</v>
       </c>
     </row>
     <row r="100" ht="20" customHeight="1">
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="E100" s="20" t="n">
-        <v>164</v>
+        <v>220</v>
       </c>
     </row>
     <row r="101" ht="20" customHeight="1">
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="E101" s="23" t="n">
-        <v>198</v>
+        <v>132</v>
       </c>
     </row>
     <row r="102" ht="20" customHeight="1">
@@ -3578,7 +3578,7 @@
         </is>
       </c>
       <c r="E102" s="20" t="n">
-        <v>148</v>
+        <v>223</v>
       </c>
     </row>
     <row r="103" ht="20" customHeight="1">
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="E103" s="23" t="n">
-        <v>194</v>
+        <v>125</v>
       </c>
     </row>
     <row r="104" ht="20" customHeight="1">
@@ -3628,7 +3628,7 @@
         </is>
       </c>
       <c r="E104" s="20" t="n">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="105" ht="20" customHeight="1">
@@ -3653,7 +3653,7 @@
         </is>
       </c>
       <c r="E105" s="23" t="n">
-        <v>233</v>
+        <v>213</v>
       </c>
     </row>
     <row r="106" ht="20" customHeight="1">
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="E106" s="20" t="n">
-        <v>197</v>
+        <v>170</v>
       </c>
     </row>
     <row r="107" ht="20" customHeight="1">
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="E107" s="23" t="n">
-        <v>206</v>
+        <v>232</v>
       </c>
     </row>
     <row r="108" ht="20" customHeight="1">
@@ -3728,7 +3728,7 @@
         </is>
       </c>
       <c r="E108" s="20" t="n">
-        <v>194</v>
+        <v>167</v>
       </c>
     </row>
     <row r="109" ht="20" customHeight="1">
@@ -3753,7 +3753,7 @@
         </is>
       </c>
       <c r="E109" s="23" t="n">
-        <v>237</v>
+        <v>193</v>
       </c>
     </row>
     <row r="110" ht="20" customHeight="1">
@@ -3778,7 +3778,7 @@
         </is>
       </c>
       <c r="E110" s="20" t="n">
-        <v>236</v>
+        <v>173</v>
       </c>
     </row>
     <row r="111" ht="20" customHeight="1">
@@ -3803,7 +3803,7 @@
         </is>
       </c>
       <c r="E111" s="23" t="n">
-        <v>201</v>
+        <v>125</v>
       </c>
     </row>
     <row r="112" ht="20" customHeight="1">
@@ -3828,7 +3828,7 @@
         </is>
       </c>
       <c r="E112" s="20" t="n">
-        <v>235</v>
+        <v>131</v>
       </c>
     </row>
     <row r="113" ht="20" customHeight="1">
@@ -3853,7 +3853,7 @@
         </is>
       </c>
       <c r="E113" s="23" t="n">
-        <v>125</v>
+        <v>143</v>
       </c>
     </row>
     <row r="114" ht="20" customHeight="1">
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="E114" s="20" t="n">
-        <v>180</v>
+        <v>230</v>
       </c>
     </row>
     <row r="115" ht="20" customHeight="1">
@@ -3903,7 +3903,7 @@
         </is>
       </c>
       <c r="E115" s="23" t="n">
-        <v>231</v>
+        <v>115</v>
       </c>
     </row>
     <row r="116" ht="20" customHeight="1">
@@ -3928,7 +3928,7 @@
         </is>
       </c>
       <c r="E116" s="20" t="n">
-        <v>135</v>
+        <v>189</v>
       </c>
     </row>
     <row r="117" ht="20" customHeight="1">
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="E117" s="23" t="n">
-        <v>187</v>
+        <v>162</v>
       </c>
     </row>
     <row r="118" ht="20" customHeight="1">
@@ -3978,7 +3978,7 @@
         </is>
       </c>
       <c r="E118" s="20" t="n">
-        <v>238</v>
+        <v>159</v>
       </c>
     </row>
     <row r="119" ht="20" customHeight="1">
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="E119" s="23" t="n">
-        <v>169</v>
+        <v>152</v>
       </c>
     </row>
     <row r="120" ht="20" customHeight="1">
@@ -4028,7 +4028,7 @@
         </is>
       </c>
       <c r="E120" s="20" t="n">
-        <v>239</v>
+        <v>116</v>
       </c>
     </row>
     <row r="121" ht="20" customHeight="1">
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="E121" s="23" t="n">
-        <v>214</v>
+        <v>187</v>
       </c>
     </row>
     <row r="122" ht="20" customHeight="1">
@@ -4078,7 +4078,7 @@
         </is>
       </c>
       <c r="E122" s="20" t="n">
-        <v>177</v>
+        <v>140</v>
       </c>
     </row>
     <row r="123" ht="20" customHeight="1">
@@ -4103,7 +4103,7 @@
         </is>
       </c>
       <c r="E123" s="23" t="n">
-        <v>202</v>
+        <v>142</v>
       </c>
     </row>
     <row r="124" ht="20" customHeight="1">
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="E124" s="20" t="n">
-        <v>182</v>
+        <v>202</v>
       </c>
     </row>
     <row r="125" ht="20" customHeight="1">
@@ -4153,7 +4153,7 @@
         </is>
       </c>
       <c r="E125" s="23" t="n">
-        <v>212</v>
+        <v>113</v>
       </c>
     </row>
     <row r="126" ht="20" customHeight="1">
@@ -4178,7 +4178,7 @@
         </is>
       </c>
       <c r="E126" s="20" t="n">
-        <v>134</v>
+        <v>214</v>
       </c>
     </row>
     <row r="127" ht="20" customHeight="1">
@@ -4203,7 +4203,7 @@
         </is>
       </c>
       <c r="E127" s="23" t="n">
-        <v>196</v>
+        <v>192</v>
       </c>
     </row>
     <row r="128" ht="20" customHeight="1">
@@ -4253,7 +4253,7 @@
         </is>
       </c>
       <c r="E129" s="23" t="n">
-        <v>145</v>
+        <v>154</v>
       </c>
     </row>
     <row r="130" ht="20" customHeight="1">
@@ -4278,7 +4278,7 @@
         </is>
       </c>
       <c r="E130" s="20" t="n">
-        <v>135</v>
+        <v>157</v>
       </c>
     </row>
     <row r="131" ht="20" customHeight="1">
@@ -4303,7 +4303,7 @@
         </is>
       </c>
       <c r="E131" s="23" t="n">
-        <v>234</v>
+        <v>173</v>
       </c>
     </row>
     <row r="132" ht="20" customHeight="1">
@@ -4328,7 +4328,7 @@
         </is>
       </c>
       <c r="E132" s="20" t="n">
-        <v>160</v>
+        <v>183</v>
       </c>
     </row>
     <row r="133" ht="20" customHeight="1">
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="E133" s="23" t="n">
-        <v>155</v>
+        <v>122</v>
       </c>
     </row>
     <row r="134" ht="20" customHeight="1">
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="E134" s="20" t="n">
-        <v>184</v>
+        <v>157</v>
       </c>
     </row>
     <row r="135" ht="20" customHeight="1">
@@ -4403,7 +4403,7 @@
         </is>
       </c>
       <c r="E135" s="23" t="n">
-        <v>158</v>
+        <v>149</v>
       </c>
     </row>
     <row r="136" ht="20" customHeight="1">
@@ -4428,7 +4428,7 @@
         </is>
       </c>
       <c r="E136" s="20" t="n">
-        <v>205</v>
+        <v>123</v>
       </c>
     </row>
     <row r="137" ht="20" customHeight="1">
@@ -4453,7 +4453,7 @@
         </is>
       </c>
       <c r="E137" s="23" t="n">
-        <v>143</v>
+        <v>191</v>
       </c>
     </row>
     <row r="138" ht="20" customHeight="1">
@@ -4478,7 +4478,7 @@
         </is>
       </c>
       <c r="E138" s="20" t="n">
-        <v>171</v>
+        <v>137</v>
       </c>
     </row>
     <row r="139" ht="20" customHeight="1">
@@ -4503,7 +4503,7 @@
         </is>
       </c>
       <c r="E139" s="23" t="n">
-        <v>137</v>
+        <v>113</v>
       </c>
     </row>
     <row r="140" ht="20" customHeight="1">
@@ -4528,7 +4528,7 @@
         </is>
       </c>
       <c r="E140" s="20" t="n">
-        <v>237</v>
+        <v>206</v>
       </c>
     </row>
     <row r="141" ht="20" customHeight="1">
@@ -4553,7 +4553,7 @@
         </is>
       </c>
       <c r="E141" s="23" t="n">
-        <v>194</v>
+        <v>233</v>
       </c>
     </row>
     <row r="142" ht="20" customHeight="1">
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="E142" s="20" t="n">
-        <v>205</v>
+        <v>174</v>
       </c>
     </row>
     <row r="143" ht="20" customHeight="1">
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="E143" s="23" t="n">
-        <v>204</v>
+        <v>213</v>
       </c>
     </row>
     <row r="144" ht="20" customHeight="1">
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="E144" s="20" t="n">
-        <v>239</v>
+        <v>204</v>
       </c>
     </row>
     <row r="145" ht="20" customHeight="1">
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="E145" s="23" t="n">
-        <v>179</v>
+        <v>236</v>
       </c>
     </row>
     <row r="146" ht="20" customHeight="1">
@@ -4678,7 +4678,7 @@
         </is>
       </c>
       <c r="E146" s="20" t="n">
-        <v>223</v>
+        <v>164</v>
       </c>
     </row>
     <row r="147" ht="20" customHeight="1">
@@ -4703,7 +4703,7 @@
         </is>
       </c>
       <c r="E147" s="23" t="n">
-        <v>239</v>
+        <v>154</v>
       </c>
     </row>
     <row r="148" ht="20" customHeight="1">
@@ -4728,7 +4728,7 @@
         </is>
       </c>
       <c r="E148" s="20" t="n">
-        <v>231</v>
+        <v>120</v>
       </c>
     </row>
     <row r="149" ht="20" customHeight="1">
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c r="E149" s="23" t="n">
-        <v>122</v>
+        <v>168</v>
       </c>
     </row>
     <row r="150" ht="20" customHeight="1">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="E150" s="20" t="n">
-        <v>174</v>
+        <v>195</v>
       </c>
     </row>
     <row r="151" ht="20" customHeight="1">
@@ -4803,7 +4803,7 @@
         </is>
       </c>
       <c r="E151" s="23" t="n">
-        <v>161</v>
+        <v>175</v>
       </c>
     </row>
     <row r="152" ht="20" customHeight="1">
@@ -4828,7 +4828,7 @@
         </is>
       </c>
       <c r="E152" s="20" t="n">
-        <v>138</v>
+        <v>145</v>
       </c>
     </row>
     <row r="153" ht="20" customHeight="1">
@@ -4853,7 +4853,7 @@
         </is>
       </c>
       <c r="E153" s="23" t="n">
-        <v>147</v>
+        <v>234</v>
       </c>
     </row>
     <row r="154" ht="20" customHeight="1">
@@ -4878,7 +4878,7 @@
         </is>
       </c>
       <c r="E154" s="20" t="n">
-        <v>183</v>
+        <v>171</v>
       </c>
     </row>
     <row r="155" ht="20" customHeight="1">
@@ -4903,7 +4903,7 @@
         </is>
       </c>
       <c r="E155" s="23" t="n">
-        <v>130</v>
+        <v>185</v>
       </c>
     </row>
     <row r="156" ht="20" customHeight="1">
@@ -4928,7 +4928,7 @@
         </is>
       </c>
       <c r="E156" s="20" t="n">
-        <v>171</v>
+        <v>143</v>
       </c>
     </row>
     <row r="157" ht="20" customHeight="1">
@@ -4953,7 +4953,7 @@
         </is>
       </c>
       <c r="E157" s="23" t="n">
-        <v>215</v>
+        <v>131</v>
       </c>
     </row>
     <row r="158" ht="20" customHeight="1">
@@ -4978,7 +4978,7 @@
         </is>
       </c>
       <c r="E158" s="20" t="n">
-        <v>124</v>
+        <v>185</v>
       </c>
     </row>
     <row r="159" ht="20" customHeight="1">
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="E159" s="23" t="n">
-        <v>233</v>
+        <v>129</v>
       </c>
     </row>
     <row r="160" ht="20" customHeight="1">
@@ -5028,7 +5028,7 @@
         </is>
       </c>
       <c r="E160" s="20" t="n">
-        <v>219</v>
+        <v>194</v>
       </c>
     </row>
     <row r="161" ht="20" customHeight="1">
@@ -5053,7 +5053,7 @@
         </is>
       </c>
       <c r="E161" s="23" t="n">
-        <v>140</v>
+        <v>156</v>
       </c>
     </row>
     <row r="162" ht="20" customHeight="1">
@@ -5078,7 +5078,7 @@
         </is>
       </c>
       <c r="E162" s="20" t="n">
-        <v>240</v>
+        <v>216</v>
       </c>
     </row>
     <row r="163" ht="20" customHeight="1">
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="E163" s="23" t="n">
-        <v>162</v>
+        <v>185</v>
       </c>
     </row>
     <row r="164" ht="20" customHeight="1">
@@ -5128,7 +5128,7 @@
         </is>
       </c>
       <c r="E164" s="20" t="n">
-        <v>153</v>
+        <v>221</v>
       </c>
     </row>
     <row r="165" ht="20" customHeight="1">
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="E165" s="23" t="n">
-        <v>136</v>
+        <v>121</v>
       </c>
     </row>
     <row r="166" ht="20" customHeight="1">
@@ -5178,7 +5178,7 @@
         </is>
       </c>
       <c r="E166" s="20" t="n">
-        <v>158</v>
+        <v>122</v>
       </c>
     </row>
     <row r="167" ht="20" customHeight="1">
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="E167" s="23" t="n">
-        <v>156</v>
+        <v>123</v>
       </c>
     </row>
     <row r="168" ht="20" customHeight="1">
@@ -5228,7 +5228,7 @@
         </is>
       </c>
       <c r="E168" s="20" t="n">
-        <v>206</v>
+        <v>237</v>
       </c>
     </row>
     <row r="169" ht="20" customHeight="1">
@@ -5253,7 +5253,7 @@
         </is>
       </c>
       <c r="E169" s="23" t="n">
-        <v>169</v>
+        <v>135</v>
       </c>
     </row>
     <row r="170" ht="20" customHeight="1">
@@ -5278,7 +5278,7 @@
         </is>
       </c>
       <c r="E170" s="20" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
     </row>
     <row r="171" ht="20" customHeight="1">
@@ -5303,7 +5303,7 @@
         </is>
       </c>
       <c r="E171" s="23" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="172" ht="20" customHeight="1">
@@ -5328,7 +5328,7 @@
         </is>
       </c>
       <c r="E172" s="20" t="n">
-        <v>168</v>
+        <v>190</v>
       </c>
     </row>
     <row r="173" ht="20" customHeight="1">
@@ -5353,7 +5353,7 @@
         </is>
       </c>
       <c r="E173" s="23" t="n">
-        <v>204</v>
+        <v>140</v>
       </c>
     </row>
     <row r="174" ht="20" customHeight="1">
@@ -5378,7 +5378,7 @@
         </is>
       </c>
       <c r="E174" s="20" t="n">
-        <v>179</v>
+        <v>225</v>
       </c>
     </row>
     <row r="175" ht="20" customHeight="1">
@@ -5403,7 +5403,7 @@
         </is>
       </c>
       <c r="E175" s="23" t="n">
-        <v>126</v>
+        <v>232</v>
       </c>
     </row>
     <row r="176" ht="20" customHeight="1">
@@ -5428,7 +5428,7 @@
         </is>
       </c>
       <c r="E176" s="20" t="n">
-        <v>136</v>
+        <v>203</v>
       </c>
     </row>
     <row r="177" ht="20" customHeight="1">
@@ -5453,7 +5453,7 @@
         </is>
       </c>
       <c r="E177" s="23" t="n">
-        <v>172</v>
+        <v>214</v>
       </c>
     </row>
     <row r="178" ht="20" customHeight="1">
@@ -5478,7 +5478,7 @@
         </is>
       </c>
       <c r="E178" s="20" t="n">
-        <v>218</v>
+        <v>137</v>
       </c>
     </row>
     <row r="179" ht="20" customHeight="1">
@@ -5503,7 +5503,7 @@
         </is>
       </c>
       <c r="E179" s="23" t="n">
-        <v>213</v>
+        <v>228</v>
       </c>
     </row>
     <row r="180" ht="20" customHeight="1">
@@ -5528,7 +5528,7 @@
         </is>
       </c>
       <c r="E180" s="20" t="n">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="181" ht="20" customHeight="1">
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="E181" s="23" t="n">
-        <v>164</v>
+        <v>122</v>
       </c>
     </row>
     <row r="182" ht="20" customHeight="1">
@@ -5578,7 +5578,7 @@
         </is>
       </c>
       <c r="E182" s="20" t="n">
-        <v>119</v>
+        <v>194</v>
       </c>
     </row>
     <row r="183" ht="20" customHeight="1">
@@ -5603,7 +5603,7 @@
         </is>
       </c>
       <c r="E183" s="23" t="n">
-        <v>120</v>
+        <v>219</v>
       </c>
     </row>
     <row r="184" ht="20" customHeight="1">
@@ -5628,7 +5628,7 @@
         </is>
       </c>
       <c r="E184" s="20" t="n">
-        <v>221</v>
+        <v>231</v>
       </c>
     </row>
     <row r="185" ht="20" customHeight="1">
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="E185" s="23" t="n">
-        <v>143</v>
+        <v>168</v>
       </c>
     </row>
     <row r="186" ht="20" customHeight="1">
@@ -5678,7 +5678,7 @@
         </is>
       </c>
       <c r="E186" s="20" t="n">
-        <v>216</v>
+        <v>149</v>
       </c>
     </row>
     <row r="187" ht="20" customHeight="1">
@@ -5703,7 +5703,7 @@
         </is>
       </c>
       <c r="E187" s="23" t="n">
-        <v>163</v>
+        <v>228</v>
       </c>
     </row>
     <row r="188" ht="20" customHeight="1">
@@ -5728,7 +5728,7 @@
         </is>
       </c>
       <c r="E188" s="20" t="n">
-        <v>173</v>
+        <v>231</v>
       </c>
     </row>
     <row r="189" ht="20" customHeight="1">
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="E189" s="23" t="n">
-        <v>234</v>
+        <v>126</v>
       </c>
     </row>
     <row r="190" ht="20" customHeight="1">
@@ -5778,7 +5778,7 @@
         </is>
       </c>
       <c r="E190" s="20" t="n">
-        <v>217</v>
+        <v>135</v>
       </c>
     </row>
     <row r="191" ht="20" customHeight="1">
@@ -5803,7 +5803,7 @@
         </is>
       </c>
       <c r="E191" s="23" t="n">
-        <v>168</v>
+        <v>126</v>
       </c>
     </row>
     <row r="192" ht="20" customHeight="1">
@@ -5828,7 +5828,7 @@
         </is>
       </c>
       <c r="E192" s="20" t="n">
-        <v>139</v>
+        <v>206</v>
       </c>
     </row>
     <row r="193" ht="20" customHeight="1">
@@ -5853,7 +5853,7 @@
         </is>
       </c>
       <c r="E193" s="23" t="n">
-        <v>195</v>
+        <v>216</v>
       </c>
     </row>
     <row r="194" ht="20" customHeight="1">
@@ -5878,7 +5878,7 @@
         </is>
       </c>
       <c r="E194" s="20" t="n">
-        <v>185</v>
+        <v>172</v>
       </c>
     </row>
     <row r="195" ht="20" customHeight="1">
@@ -5903,7 +5903,7 @@
         </is>
       </c>
       <c r="E195" s="23" t="n">
-        <v>111</v>
+        <v>201</v>
       </c>
     </row>
     <row r="196" ht="20" customHeight="1">
@@ -5928,7 +5928,7 @@
         </is>
       </c>
       <c r="E196" s="20" t="n">
-        <v>150</v>
+        <v>234</v>
       </c>
     </row>
     <row r="197" ht="20" customHeight="1">
@@ -5953,7 +5953,7 @@
         </is>
       </c>
       <c r="E197" s="23" t="n">
-        <v>167</v>
+        <v>121</v>
       </c>
     </row>
     <row r="198" ht="20" customHeight="1">
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="E198" s="20" t="n">
-        <v>224</v>
+        <v>189</v>
       </c>
     </row>
     <row r="199" ht="20" customHeight="1">
@@ -6003,7 +6003,7 @@
         </is>
       </c>
       <c r="E199" s="23" t="n">
-        <v>214</v>
+        <v>181</v>
       </c>
     </row>
     <row r="200" ht="20" customHeight="1">
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="E200" s="20" t="n">
-        <v>171</v>
+        <v>219</v>
       </c>
     </row>
     <row r="201" ht="20" customHeight="1">
@@ -6053,7 +6053,7 @@
         </is>
       </c>
       <c r="E201" s="23" t="n">
-        <v>163</v>
+        <v>138</v>
       </c>
     </row>
     <row r="202" ht="20" customHeight="1">
@@ -6078,7 +6078,7 @@
         </is>
       </c>
       <c r="E202" s="20" t="n">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="203" ht="20" customHeight="1">
@@ -6103,7 +6103,7 @@
         </is>
       </c>
       <c r="E203" s="23" t="n">
-        <v>149</v>
+        <v>172</v>
       </c>
     </row>
     <row r="204" ht="20" customHeight="1">
@@ -6128,7 +6128,7 @@
         </is>
       </c>
       <c r="E204" s="20" t="n">
-        <v>238</v>
+        <v>165</v>
       </c>
     </row>
     <row r="205" ht="20" customHeight="1">
@@ -6153,7 +6153,7 @@
         </is>
       </c>
       <c r="E205" s="23" t="n">
-        <v>145</v>
+        <v>190</v>
       </c>
     </row>
     <row r="206" ht="20" customHeight="1">
@@ -6178,7 +6178,7 @@
         </is>
       </c>
       <c r="E206" s="20" t="n">
-        <v>209</v>
+        <v>149</v>
       </c>
     </row>
     <row r="207" ht="20" customHeight="1">
@@ -6203,7 +6203,7 @@
         </is>
       </c>
       <c r="E207" s="23" t="n">
-        <v>220</v>
+        <v>169</v>
       </c>
     </row>
     <row r="208" ht="20" customHeight="1">
@@ -6228,7 +6228,7 @@
         </is>
       </c>
       <c r="E208" s="20" t="n">
-        <v>228</v>
+        <v>136</v>
       </c>
     </row>
     <row r="209" ht="20" customHeight="1">
@@ -6253,7 +6253,7 @@
         </is>
       </c>
       <c r="E209" s="23" t="n">
-        <v>147</v>
+        <v>186</v>
       </c>
     </row>
     <row r="210" ht="20" customHeight="1">
@@ -6278,7 +6278,7 @@
         </is>
       </c>
       <c r="E210" s="20" t="n">
-        <v>233</v>
+        <v>218</v>
       </c>
     </row>
     <row r="211" ht="20" customHeight="1">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="E211" s="23" t="n">
-        <v>219</v>
+        <v>110</v>
       </c>
     </row>
     <row r="212" ht="20" customHeight="1">
@@ -6328,7 +6328,7 @@
         </is>
       </c>
       <c r="E212" s="20" t="n">
-        <v>158</v>
+        <v>166</v>
       </c>
     </row>
     <row r="213" ht="20" customHeight="1">
@@ -6353,7 +6353,7 @@
         </is>
       </c>
       <c r="E213" s="23" t="n">
-        <v>175</v>
+        <v>238</v>
       </c>
     </row>
     <row r="214" ht="20" customHeight="1">
@@ -6378,7 +6378,7 @@
         </is>
       </c>
       <c r="E214" s="20" t="n">
-        <v>216</v>
+        <v>150</v>
       </c>
     </row>
     <row r="215" ht="20" customHeight="1">
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="E215" s="23" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="216" ht="20" customHeight="1">
@@ -6428,7 +6428,7 @@
         </is>
       </c>
       <c r="E216" s="20" t="n">
-        <v>174</v>
+        <v>205</v>
       </c>
     </row>
     <row r="217" ht="20" customHeight="1">
@@ -6453,7 +6453,7 @@
         </is>
       </c>
       <c r="E217" s="23" t="n">
-        <v>146</v>
+        <v>218</v>
       </c>
     </row>
     <row r="218" ht="20" customHeight="1">
@@ -6478,7 +6478,7 @@
         </is>
       </c>
       <c r="E218" s="20" t="n">
-        <v>123</v>
+        <v>222</v>
       </c>
     </row>
     <row r="219" ht="20" customHeight="1">
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="E219" s="23" t="n">
-        <v>176</v>
+        <v>162</v>
       </c>
     </row>
     <row r="220" ht="20" customHeight="1">
@@ -6528,7 +6528,7 @@
         </is>
       </c>
       <c r="E220" s="20" t="n">
-        <v>164</v>
+        <v>215</v>
       </c>
     </row>
     <row r="221" ht="20" customHeight="1">
@@ -6553,7 +6553,7 @@
         </is>
       </c>
       <c r="E221" s="23" t="n">
-        <v>153</v>
+        <v>125</v>
       </c>
     </row>
     <row r="222" ht="20" customHeight="1">
@@ -6578,7 +6578,7 @@
         </is>
       </c>
       <c r="E222" s="20" t="n">
-        <v>238</v>
+        <v>230</v>
       </c>
     </row>
     <row r="223" ht="20" customHeight="1">
@@ -6603,7 +6603,7 @@
         </is>
       </c>
       <c r="E223" s="23" t="n">
-        <v>209</v>
+        <v>232</v>
       </c>
     </row>
     <row r="224" ht="20" customHeight="1">
@@ -6628,7 +6628,7 @@
         </is>
       </c>
       <c r="E224" s="20" t="n">
-        <v>227</v>
+        <v>213</v>
       </c>
     </row>
     <row r="225" ht="20" customHeight="1">
@@ -6653,7 +6653,7 @@
         </is>
       </c>
       <c r="E225" s="23" t="n">
-        <v>208</v>
+        <v>221</v>
       </c>
     </row>
     <row r="226" ht="20" customHeight="1">
@@ -6678,7 +6678,7 @@
         </is>
       </c>
       <c r="E226" s="20" t="n">
-        <v>161</v>
+        <v>223</v>
       </c>
     </row>
     <row r="227" ht="20" customHeight="1">
@@ -6703,7 +6703,7 @@
         </is>
       </c>
       <c r="E227" s="23" t="n">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="228" ht="20" customHeight="1">
@@ -6728,7 +6728,7 @@
         </is>
       </c>
       <c r="E228" s="20" t="n">
-        <v>220</v>
+        <v>162</v>
       </c>
     </row>
     <row r="229" ht="20" customHeight="1">
@@ -6753,7 +6753,7 @@
         </is>
       </c>
       <c r="E229" s="23" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="230" ht="20" customHeight="1">
@@ -6778,7 +6778,7 @@
         </is>
       </c>
       <c r="E230" s="20" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="231" ht="20" customHeight="1">
@@ -6803,7 +6803,7 @@
         </is>
       </c>
       <c r="E231" s="23" t="n">
-        <v>181</v>
+        <v>205</v>
       </c>
     </row>
     <row r="232" ht="20" customHeight="1">
@@ -6828,7 +6828,7 @@
         </is>
       </c>
       <c r="E232" s="20" t="n">
-        <v>219</v>
+        <v>119</v>
       </c>
     </row>
     <row r="233" ht="20" customHeight="1">
@@ -6853,7 +6853,7 @@
         </is>
       </c>
       <c r="E233" s="23" t="n">
-        <v>162</v>
+        <v>115</v>
       </c>
     </row>
     <row r="234" ht="20" customHeight="1">
@@ -6878,7 +6878,7 @@
         </is>
       </c>
       <c r="E234" s="20" t="n">
-        <v>150</v>
+        <v>137</v>
       </c>
     </row>
     <row r="235" ht="20" customHeight="1">
@@ -6903,7 +6903,7 @@
         </is>
       </c>
       <c r="E235" s="23" t="n">
-        <v>171</v>
+        <v>223</v>
       </c>
     </row>
     <row r="236" ht="20" customHeight="1">
@@ -6928,7 +6928,7 @@
         </is>
       </c>
       <c r="E236" s="20" t="n">
-        <v>176</v>
+        <v>228</v>
       </c>
     </row>
     <row r="237" ht="20" customHeight="1">
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="E237" s="23" t="n">
-        <v>115</v>
+        <v>194</v>
       </c>
     </row>
     <row r="238" ht="20" customHeight="1">
@@ -6978,7 +6978,7 @@
         </is>
       </c>
       <c r="E238" s="20" t="n">
-        <v>132</v>
+        <v>172</v>
       </c>
     </row>
     <row r="239" ht="20" customHeight="1">
@@ -7003,7 +7003,7 @@
         </is>
       </c>
       <c r="E239" s="23" t="n">
-        <v>216</v>
+        <v>228</v>
       </c>
     </row>
     <row r="240" ht="20" customHeight="1">
@@ -7028,7 +7028,7 @@
         </is>
       </c>
       <c r="E240" s="20" t="n">
-        <v>233</v>
+        <v>137</v>
       </c>
     </row>
     <row r="241" ht="20" customHeight="1">
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="E241" s="23" t="n">
-        <v>112</v>
+        <v>201</v>
       </c>
     </row>
     <row r="242" ht="20" customHeight="1">
@@ -7078,7 +7078,7 @@
         </is>
       </c>
       <c r="E242" s="20" t="n">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="243" ht="20" customHeight="1">
@@ -7103,7 +7103,7 @@
         </is>
       </c>
       <c r="E243" s="23" t="n">
-        <v>125</v>
+        <v>152</v>
       </c>
     </row>
     <row r="244" ht="20" customHeight="1">
@@ -7128,7 +7128,7 @@
         </is>
       </c>
       <c r="E244" s="20" t="n">
-        <v>163</v>
+        <v>152</v>
       </c>
     </row>
     <row r="245" ht="20" customHeight="1">
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="E245" s="23" t="n">
-        <v>171</v>
+        <v>196</v>
       </c>
     </row>
     <row r="246" ht="20" customHeight="1">
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="E246" s="20" t="n">
-        <v>191</v>
+        <v>121</v>
       </c>
     </row>
     <row r="247" ht="20" customHeight="1">
@@ -7203,7 +7203,7 @@
         </is>
       </c>
       <c r="E247" s="23" t="n">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="248" ht="20" customHeight="1">
@@ -7228,7 +7228,7 @@
         </is>
       </c>
       <c r="E248" s="20" t="n">
-        <v>170</v>
+        <v>177</v>
       </c>
     </row>
     <row r="249" ht="20" customHeight="1">
@@ -7253,7 +7253,7 @@
         </is>
       </c>
       <c r="E249" s="23" t="n">
-        <v>121</v>
+        <v>165</v>
       </c>
     </row>
     <row r="250" ht="20" customHeight="1">
@@ -7278,7 +7278,7 @@
         </is>
       </c>
       <c r="E250" s="20" t="n">
-        <v>240</v>
+        <v>174</v>
       </c>
     </row>
     <row r="251" ht="20" customHeight="1">
@@ -7303,7 +7303,7 @@
         </is>
       </c>
       <c r="E251" s="23" t="n">
-        <v>171</v>
+        <v>196</v>
       </c>
     </row>
     <row r="252" ht="20" customHeight="1">
@@ -7328,7 +7328,7 @@
         </is>
       </c>
       <c r="E252" s="20" t="n">
-        <v>210</v>
+        <v>119</v>
       </c>
     </row>
     <row r="253" ht="20" customHeight="1">
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="E253" s="23" t="n">
-        <v>214</v>
+        <v>112</v>
       </c>
     </row>
     <row r="254" ht="20" customHeight="1">
@@ -7378,7 +7378,7 @@
         </is>
       </c>
       <c r="E254" s="20" t="n">
-        <v>146</v>
+        <v>187</v>
       </c>
     </row>
     <row r="255" ht="20" customHeight="1">
@@ -7403,7 +7403,7 @@
         </is>
       </c>
       <c r="E255" s="23" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="256" ht="20" customHeight="1">
@@ -7428,7 +7428,7 @@
         </is>
       </c>
       <c r="E256" s="20" t="n">
-        <v>155</v>
+        <v>178</v>
       </c>
     </row>
     <row r="257" ht="20" customHeight="1">
@@ -7453,7 +7453,7 @@
         </is>
       </c>
       <c r="E257" s="23" t="n">
-        <v>216</v>
+        <v>174</v>
       </c>
     </row>
     <row r="258" ht="20" customHeight="1">
@@ -7478,7 +7478,7 @@
         </is>
       </c>
       <c r="E258" s="20" t="n">
-        <v>127</v>
+        <v>168</v>
       </c>
     </row>
     <row r="259" ht="20" customHeight="1">
@@ -7503,7 +7503,7 @@
         </is>
       </c>
       <c r="E259" s="23" t="n">
-        <v>144</v>
+        <v>197</v>
       </c>
     </row>
     <row r="260" ht="20" customHeight="1">
@@ -7528,7 +7528,7 @@
         </is>
       </c>
       <c r="E260" s="20" t="n">
-        <v>185</v>
+        <v>131</v>
       </c>
     </row>
     <row r="261" ht="20" customHeight="1">
@@ -7553,7 +7553,7 @@
         </is>
       </c>
       <c r="E261" s="23" t="n">
-        <v>129</v>
+        <v>147</v>
       </c>
     </row>
     <row r="262" ht="20" customHeight="1">
@@ -7578,7 +7578,7 @@
         </is>
       </c>
       <c r="E262" s="20" t="n">
-        <v>132</v>
+        <v>123</v>
       </c>
     </row>
     <row r="263" ht="20" customHeight="1">
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="E263" s="23" t="n">
-        <v>162</v>
+        <v>157</v>
       </c>
     </row>
     <row r="264" ht="20" customHeight="1">
@@ -7628,7 +7628,7 @@
         </is>
       </c>
       <c r="E264" s="20" t="n">
-        <v>192</v>
+        <v>171</v>
       </c>
     </row>
     <row r="265" ht="20" customHeight="1">
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="E265" s="23" t="n">
-        <v>203</v>
+        <v>119</v>
       </c>
     </row>
     <row r="266" ht="20" customHeight="1">
@@ -7678,7 +7678,7 @@
         </is>
       </c>
       <c r="E266" s="20" t="n">
-        <v>176</v>
+        <v>181</v>
       </c>
     </row>
     <row r="267" ht="20" customHeight="1">
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="E267" s="23" t="n">
-        <v>226</v>
+        <v>203</v>
       </c>
     </row>
     <row r="268" ht="20" customHeight="1">
@@ -7753,7 +7753,7 @@
         </is>
       </c>
       <c r="E269" s="23" t="n">
-        <v>193</v>
+        <v>237</v>
       </c>
     </row>
     <row r="270" ht="20" customHeight="1">
@@ -7778,7 +7778,7 @@
         </is>
       </c>
       <c r="E270" s="20" t="n">
-        <v>196</v>
+        <v>237</v>
       </c>
     </row>
     <row r="271" ht="20" customHeight="1">
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="E271" s="23" t="n">
-        <v>157</v>
+        <v>141</v>
       </c>
     </row>
     <row r="272" ht="20" customHeight="1">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="E272" s="20" t="n">
-        <v>153</v>
+        <v>110</v>
       </c>
     </row>
     <row r="273" ht="20" customHeight="1">
@@ -7853,7 +7853,7 @@
         </is>
       </c>
       <c r="E273" s="23" t="n">
-        <v>127</v>
+        <v>156</v>
       </c>
     </row>
     <row r="274" ht="20" customHeight="1">
@@ -7878,7 +7878,7 @@
         </is>
       </c>
       <c r="E274" s="20" t="n">
-        <v>143</v>
+        <v>111</v>
       </c>
     </row>
     <row r="275" ht="20" customHeight="1">
@@ -7903,7 +7903,7 @@
         </is>
       </c>
       <c r="E275" s="23" t="n">
-        <v>121</v>
+        <v>157</v>
       </c>
     </row>
     <row r="276" ht="20" customHeight="1">
@@ -7928,7 +7928,7 @@
         </is>
       </c>
       <c r="E276" s="20" t="n">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="277" ht="20" customHeight="1">
@@ -7953,7 +7953,7 @@
         </is>
       </c>
       <c r="E277" s="23" t="n">
-        <v>162</v>
+        <v>214</v>
       </c>
     </row>
     <row r="278" ht="20" customHeight="1">
@@ -7978,7 +7978,7 @@
         </is>
       </c>
       <c r="E278" s="20" t="n">
-        <v>182</v>
+        <v>199</v>
       </c>
     </row>
     <row r="279" ht="20" customHeight="1">
@@ -8003,7 +8003,7 @@
         </is>
       </c>
       <c r="E279" s="23" t="n">
-        <v>112</v>
+        <v>206</v>
       </c>
     </row>
     <row r="280" ht="20" customHeight="1">
@@ -8028,7 +8028,7 @@
         </is>
       </c>
       <c r="E280" s="20" t="n">
-        <v>235</v>
+        <v>181</v>
       </c>
     </row>
     <row r="281" ht="20" customHeight="1">
@@ -8053,7 +8053,7 @@
         </is>
       </c>
       <c r="E281" s="23" t="n">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="282" ht="20" customHeight="1">
@@ -8078,7 +8078,7 @@
         </is>
       </c>
       <c r="E282" s="20" t="n">
-        <v>134</v>
+        <v>222</v>
       </c>
     </row>
     <row r="283" ht="20" customHeight="1">
@@ -8103,7 +8103,7 @@
         </is>
       </c>
       <c r="E283" s="23" t="n">
-        <v>162</v>
+        <v>194</v>
       </c>
     </row>
     <row r="284" ht="20" customHeight="1">
@@ -8128,7 +8128,7 @@
         </is>
       </c>
       <c r="E284" s="20" t="n">
-        <v>200</v>
+        <v>169</v>
       </c>
     </row>
     <row r="285" ht="20" customHeight="1">
@@ -8153,7 +8153,7 @@
         </is>
       </c>
       <c r="E285" s="23" t="n">
-        <v>182</v>
+        <v>193</v>
       </c>
     </row>
     <row r="286" ht="20" customHeight="1">
@@ -8178,7 +8178,7 @@
         </is>
       </c>
       <c r="E286" s="20" t="n">
-        <v>136</v>
+        <v>216</v>
       </c>
     </row>
     <row r="287" ht="20" customHeight="1">
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="E287" s="23" t="n">
-        <v>226</v>
+        <v>174</v>
       </c>
     </row>
     <row r="288" ht="20" customHeight="1">
@@ -8228,7 +8228,7 @@
         </is>
       </c>
       <c r="E288" s="20" t="n">
-        <v>119</v>
+        <v>152</v>
       </c>
     </row>
     <row r="289" ht="20" customHeight="1">
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="E289" s="23" t="n">
-        <v>115</v>
+        <v>214</v>
       </c>
     </row>
     <row r="290" ht="20" customHeight="1">
@@ -8278,7 +8278,7 @@
         </is>
       </c>
       <c r="E290" s="20" t="n">
-        <v>187</v>
+        <v>238</v>
       </c>
     </row>
     <row r="291" ht="20" customHeight="1">
@@ -8303,7 +8303,7 @@
         </is>
       </c>
       <c r="E291" s="23" t="n">
-        <v>229</v>
+        <v>214</v>
       </c>
     </row>
     <row r="292" ht="20" customHeight="1">
@@ -8328,7 +8328,7 @@
         </is>
       </c>
       <c r="E292" s="20" t="n">
-        <v>148</v>
+        <v>225</v>
       </c>
     </row>
     <row r="293" ht="20" customHeight="1">
@@ -8353,7 +8353,7 @@
         </is>
       </c>
       <c r="E293" s="23" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="294" ht="20" customHeight="1">
@@ -8378,7 +8378,7 @@
         </is>
       </c>
       <c r="E294" s="20" t="n">
-        <v>175</v>
+        <v>161</v>
       </c>
     </row>
     <row r="295" ht="20" customHeight="1">
@@ -8403,7 +8403,7 @@
         </is>
       </c>
       <c r="E295" s="23" t="n">
-        <v>179</v>
+        <v>200</v>
       </c>
     </row>
     <row r="296" ht="20" customHeight="1">
@@ -8428,7 +8428,7 @@
         </is>
       </c>
       <c r="E296" s="20" t="n">
-        <v>238</v>
+        <v>150</v>
       </c>
     </row>
     <row r="297" ht="20" customHeight="1">
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="E297" s="23" t="n">
-        <v>212</v>
+        <v>179</v>
       </c>
     </row>
     <row r="298" ht="20" customHeight="1">
@@ -8478,7 +8478,7 @@
         </is>
       </c>
       <c r="E298" s="20" t="n">
-        <v>184</v>
+        <v>220</v>
       </c>
     </row>
     <row r="299" ht="20" customHeight="1">
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="E299" s="23" t="n">
-        <v>155</v>
+        <v>214</v>
       </c>
     </row>
     <row r="300" ht="20" customHeight="1">
@@ -8528,7 +8528,7 @@
         </is>
       </c>
       <c r="E300" s="20" t="n">
-        <v>169</v>
+        <v>234</v>
       </c>
     </row>
     <row r="301" ht="20" customHeight="1">
@@ -8553,7 +8553,7 @@
         </is>
       </c>
       <c r="E301" s="23" t="n">
-        <v>173</v>
+        <v>238</v>
       </c>
     </row>
     <row r="302" ht="20" customHeight="1">
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="E302" s="20" t="n">
-        <v>173</v>
+        <v>160</v>
       </c>
     </row>
     <row r="303" ht="20" customHeight="1">
@@ -8603,7 +8603,7 @@
         </is>
       </c>
       <c r="E303" s="23" t="n">
-        <v>221</v>
+        <v>122</v>
       </c>
     </row>
     <row r="304" ht="20" customHeight="1">
@@ -8628,7 +8628,7 @@
         </is>
       </c>
       <c r="E304" s="20" t="n">
-        <v>157</v>
+        <v>114</v>
       </c>
     </row>
     <row r="305" ht="20" customHeight="1">
@@ -8653,7 +8653,7 @@
         </is>
       </c>
       <c r="E305" s="23" t="n">
-        <v>129</v>
+        <v>224</v>
       </c>
     </row>
     <row r="306" ht="20" customHeight="1">
@@ -8678,7 +8678,7 @@
         </is>
       </c>
       <c r="E306" s="20" t="n">
-        <v>190</v>
+        <v>136</v>
       </c>
     </row>
     <row r="307" ht="20" customHeight="1">
@@ -8703,7 +8703,7 @@
         </is>
       </c>
       <c r="E307" s="23" t="n">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="308" ht="20" customHeight="1">
@@ -8728,7 +8728,7 @@
         </is>
       </c>
       <c r="E308" s="20" t="n">
-        <v>176</v>
+        <v>214</v>
       </c>
     </row>
     <row r="309" ht="20" customHeight="1">
@@ -8753,7 +8753,7 @@
         </is>
       </c>
       <c r="E309" s="23" t="n">
-        <v>148</v>
+        <v>225</v>
       </c>
     </row>
     <row r="310" ht="20" customHeight="1">
@@ -8778,7 +8778,7 @@
         </is>
       </c>
       <c r="E310" s="20" t="n">
-        <v>204</v>
+        <v>159</v>
       </c>
     </row>
     <row r="311" ht="20" customHeight="1">
@@ -8803,7 +8803,7 @@
         </is>
       </c>
       <c r="E311" s="23" t="n">
-        <v>124</v>
+        <v>231</v>
       </c>
     </row>
     <row r="312" ht="20" customHeight="1">
@@ -8828,7 +8828,7 @@
         </is>
       </c>
       <c r="E312" s="20" t="n">
-        <v>184</v>
+        <v>208</v>
       </c>
     </row>
     <row r="313" ht="20" customHeight="1">
@@ -8853,7 +8853,7 @@
         </is>
       </c>
       <c r="E313" s="23" t="n">
-        <v>114</v>
+        <v>128</v>
       </c>
     </row>
     <row r="314" ht="20" customHeight="1">
@@ -8878,7 +8878,7 @@
         </is>
       </c>
       <c r="E314" s="20" t="n">
-        <v>206</v>
+        <v>185</v>
       </c>
     </row>
     <row r="315" ht="20" customHeight="1">
@@ -8903,7 +8903,7 @@
         </is>
       </c>
       <c r="E315" s="23" t="n">
-        <v>173</v>
+        <v>139</v>
       </c>
     </row>
     <row r="316" ht="20" customHeight="1">
@@ -8928,7 +8928,7 @@
         </is>
       </c>
       <c r="E316" s="20" t="n">
-        <v>129</v>
+        <v>114</v>
       </c>
     </row>
     <row r="317" ht="20" customHeight="1">
@@ -8953,7 +8953,7 @@
         </is>
       </c>
       <c r="E317" s="23" t="n">
-        <v>123</v>
+        <v>216</v>
       </c>
     </row>
     <row r="318" ht="20" customHeight="1">
@@ -8978,7 +8978,7 @@
         </is>
       </c>
       <c r="E318" s="20" t="n">
-        <v>220</v>
+        <v>118</v>
       </c>
     </row>
     <row r="319" ht="20" customHeight="1">
@@ -9003,7 +9003,7 @@
         </is>
       </c>
       <c r="E319" s="23" t="n">
-        <v>220</v>
+        <v>202</v>
       </c>
     </row>
     <row r="320" ht="20" customHeight="1">
@@ -9028,7 +9028,7 @@
         </is>
       </c>
       <c r="E320" s="20" t="n">
-        <v>135</v>
+        <v>121</v>
       </c>
     </row>
     <row r="321" ht="20" customHeight="1">
@@ -9053,7 +9053,7 @@
         </is>
       </c>
       <c r="E321" s="23" t="n">
-        <v>170</v>
+        <v>127</v>
       </c>
     </row>
     <row r="322" ht="20" customHeight="1">
@@ -9078,7 +9078,7 @@
         </is>
       </c>
       <c r="E322" s="20" t="n">
-        <v>150</v>
+        <v>193</v>
       </c>
     </row>
     <row r="323" ht="20" customHeight="1">
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="E323" s="23" t="n">
-        <v>231</v>
+        <v>173</v>
       </c>
     </row>
     <row r="324" ht="20" customHeight="1">
@@ -9128,7 +9128,7 @@
         </is>
       </c>
       <c r="E324" s="20" t="n">
-        <v>201</v>
+        <v>141</v>
       </c>
     </row>
     <row r="325" ht="20" customHeight="1">
@@ -9153,7 +9153,7 @@
         </is>
       </c>
       <c r="E325" s="23" t="n">
-        <v>173</v>
+        <v>129</v>
       </c>
     </row>
     <row r="326" ht="20" customHeight="1">
@@ -9178,7 +9178,7 @@
         </is>
       </c>
       <c r="E326" s="20" t="n">
-        <v>208</v>
+        <v>197</v>
       </c>
     </row>
     <row r="327" ht="20" customHeight="1">
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="E327" s="23" t="n">
-        <v>123</v>
+        <v>155</v>
       </c>
     </row>
     <row r="328" ht="20" customHeight="1">
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="E328" s="20" t="n">
-        <v>151</v>
+        <v>121</v>
       </c>
     </row>
     <row r="329" ht="20" customHeight="1">
@@ -9253,7 +9253,7 @@
         </is>
       </c>
       <c r="E329" s="23" t="n">
-        <v>174</v>
+        <v>126</v>
       </c>
     </row>
     <row r="330" ht="20" customHeight="1">
@@ -9278,7 +9278,7 @@
         </is>
       </c>
       <c r="E330" s="20" t="n">
-        <v>198</v>
+        <v>221</v>
       </c>
     </row>
     <row r="331" ht="20" customHeight="1">
@@ -9303,7 +9303,7 @@
         </is>
       </c>
       <c r="E331" s="23" t="n">
-        <v>155</v>
+        <v>230</v>
       </c>
     </row>
     <row r="332" ht="20" customHeight="1">
@@ -9328,7 +9328,7 @@
         </is>
       </c>
       <c r="E332" s="20" t="n">
-        <v>134</v>
+        <v>166</v>
       </c>
     </row>
     <row r="333" ht="20" customHeight="1">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="E333" s="23" t="n">
-        <v>217</v>
+        <v>142</v>
       </c>
     </row>
     <row r="334" ht="20" customHeight="1">
@@ -9378,7 +9378,7 @@
         </is>
       </c>
       <c r="E334" s="20" t="n">
-        <v>138</v>
+        <v>213</v>
       </c>
     </row>
     <row r="335" ht="20" customHeight="1">
@@ -9403,7 +9403,7 @@
         </is>
       </c>
       <c r="E335" s="23" t="n">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="336" ht="20" customHeight="1">
@@ -9428,7 +9428,7 @@
         </is>
       </c>
       <c r="E336" s="20" t="n">
-        <v>185</v>
+        <v>208</v>
       </c>
     </row>
     <row r="337" ht="20" customHeight="1">
@@ -9453,7 +9453,7 @@
         </is>
       </c>
       <c r="E337" s="23" t="n">
-        <v>125</v>
+        <v>190</v>
       </c>
     </row>
     <row r="338" ht="20" customHeight="1">
@@ -9478,7 +9478,7 @@
         </is>
       </c>
       <c r="E338" s="20" t="n">
-        <v>127</v>
+        <v>204</v>
       </c>
     </row>
     <row r="339" ht="20" customHeight="1">
@@ -9503,7 +9503,7 @@
         </is>
       </c>
       <c r="E339" s="23" t="n">
-        <v>206</v>
+        <v>195</v>
       </c>
     </row>
     <row r="340" ht="20" customHeight="1">
@@ -9528,7 +9528,7 @@
         </is>
       </c>
       <c r="E340" s="20" t="n">
-        <v>145</v>
+        <v>126</v>
       </c>
     </row>
     <row r="341" ht="20" customHeight="1">
@@ -9553,7 +9553,7 @@
         </is>
       </c>
       <c r="E341" s="23" t="n">
-        <v>208</v>
+        <v>165</v>
       </c>
     </row>
     <row r="342" ht="20" customHeight="1">
@@ -9578,7 +9578,7 @@
         </is>
       </c>
       <c r="E342" s="20" t="n">
-        <v>180</v>
+        <v>217</v>
       </c>
     </row>
     <row r="343" ht="20" customHeight="1">
@@ -9603,7 +9603,7 @@
         </is>
       </c>
       <c r="E343" s="23" t="n">
-        <v>209</v>
+        <v>189</v>
       </c>
     </row>
     <row r="344" ht="20" customHeight="1">
@@ -9628,7 +9628,7 @@
         </is>
       </c>
       <c r="E344" s="20" t="n">
-        <v>210</v>
+        <v>231</v>
       </c>
     </row>
     <row r="345" ht="20" customHeight="1">
@@ -9653,7 +9653,7 @@
         </is>
       </c>
       <c r="E345" s="23" t="n">
-        <v>172</v>
+        <v>124</v>
       </c>
     </row>
     <row r="346" ht="20" customHeight="1">
@@ -9678,7 +9678,7 @@
         </is>
       </c>
       <c r="E346" s="20" t="n">
-        <v>164</v>
+        <v>213</v>
       </c>
     </row>
     <row r="347" ht="20" customHeight="1">
@@ -9703,7 +9703,7 @@
         </is>
       </c>
       <c r="E347" s="23" t="n">
-        <v>167</v>
+        <v>138</v>
       </c>
     </row>
     <row r="348" ht="20" customHeight="1">
@@ -9728,7 +9728,7 @@
         </is>
       </c>
       <c r="E348" s="20" t="n">
-        <v>222</v>
+        <v>164</v>
       </c>
     </row>
     <row r="349" ht="20" customHeight="1">
@@ -9753,7 +9753,7 @@
         </is>
       </c>
       <c r="E349" s="23" t="n">
-        <v>199</v>
+        <v>190</v>
       </c>
     </row>
     <row r="350" ht="20" customHeight="1">
@@ -9778,7 +9778,7 @@
         </is>
       </c>
       <c r="E350" s="20" t="n">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="351" ht="20" customHeight="1">
@@ -9803,7 +9803,7 @@
         </is>
       </c>
       <c r="E351" s="23" t="n">
-        <v>236</v>
+        <v>190</v>
       </c>
     </row>
     <row r="352" ht="20" customHeight="1">
@@ -9828,7 +9828,7 @@
         </is>
       </c>
       <c r="E352" s="20" t="n">
-        <v>156</v>
+        <v>131</v>
       </c>
     </row>
     <row r="353" ht="20" customHeight="1">
@@ -9853,7 +9853,7 @@
         </is>
       </c>
       <c r="E353" s="23" t="n">
-        <v>121</v>
+        <v>110</v>
       </c>
     </row>
     <row r="354" ht="20" customHeight="1">
@@ -9878,7 +9878,7 @@
         </is>
       </c>
       <c r="E354" s="20" t="n">
-        <v>225</v>
+        <v>164</v>
       </c>
     </row>
     <row r="355" ht="20" customHeight="1">
@@ -9903,7 +9903,7 @@
         </is>
       </c>
       <c r="E355" s="23" t="n">
-        <v>157</v>
+        <v>148</v>
       </c>
     </row>
     <row r="356" ht="20" customHeight="1">
@@ -9928,7 +9928,7 @@
         </is>
       </c>
       <c r="E356" s="20" t="n">
-        <v>161</v>
+        <v>168</v>
       </c>
     </row>
     <row r="357" ht="20" customHeight="1">
@@ -9953,7 +9953,7 @@
         </is>
       </c>
       <c r="E357" s="23" t="n">
-        <v>140</v>
+        <v>146</v>
       </c>
     </row>
     <row r="358" ht="20" customHeight="1">
@@ -9978,7 +9978,7 @@
         </is>
       </c>
       <c r="E358" s="20" t="n">
-        <v>130</v>
+        <v>205</v>
       </c>
     </row>
     <row r="359" ht="20" customHeight="1">
@@ -10003,7 +10003,7 @@
         </is>
       </c>
       <c r="E359" s="23" t="n">
-        <v>177</v>
+        <v>207</v>
       </c>
     </row>
     <row r="360" ht="20" customHeight="1">
@@ -10028,7 +10028,7 @@
         </is>
       </c>
       <c r="E360" s="20" t="n">
-        <v>150</v>
+        <v>174</v>
       </c>
     </row>
     <row r="361" ht="20" customHeight="1">
@@ -10053,7 +10053,7 @@
         </is>
       </c>
       <c r="E361" s="23" t="n">
-        <v>182</v>
+        <v>152</v>
       </c>
     </row>
     <row r="362" ht="20" customHeight="1">
@@ -10078,7 +10078,7 @@
         </is>
       </c>
       <c r="E362" s="20" t="n">
-        <v>129</v>
+        <v>193</v>
       </c>
     </row>
     <row r="363" ht="20" customHeight="1">
@@ -10103,7 +10103,7 @@
         </is>
       </c>
       <c r="E363" s="23" t="n">
-        <v>136</v>
+        <v>114</v>
       </c>
     </row>
     <row r="364" ht="20" customHeight="1">
@@ -10128,7 +10128,7 @@
         </is>
       </c>
       <c r="E364" s="20" t="n">
-        <v>179</v>
+        <v>238</v>
       </c>
     </row>
     <row r="365" ht="20" customHeight="1">
@@ -10153,7 +10153,7 @@
         </is>
       </c>
       <c r="E365" s="23" t="n">
-        <v>123</v>
+        <v>157</v>
       </c>
     </row>
     <row r="366" ht="20" customHeight="1">
@@ -10178,7 +10178,7 @@
         </is>
       </c>
       <c r="E366" s="20" t="n">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="367" ht="20" customHeight="1">
@@ -10203,7 +10203,7 @@
         </is>
       </c>
       <c r="E367" s="23" t="n">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="368" ht="20" customHeight="1">
@@ -10228,7 +10228,7 @@
         </is>
       </c>
       <c r="E368" s="20" t="n">
-        <v>227</v>
+        <v>156</v>
       </c>
     </row>
     <row r="369" ht="20" customHeight="1">
@@ -10253,7 +10253,7 @@
         </is>
       </c>
       <c r="E369" s="23" t="n">
-        <v>138</v>
+        <v>193</v>
       </c>
     </row>
     <row r="370" ht="20" customHeight="1">
@@ -10278,7 +10278,7 @@
         </is>
       </c>
       <c r="E370" s="20" t="n">
-        <v>134</v>
+        <v>112</v>
       </c>
     </row>
     <row r="371" ht="20" customHeight="1">
@@ -10303,7 +10303,7 @@
         </is>
       </c>
       <c r="E371" s="23" t="n">
-        <v>110</v>
+        <v>149</v>
       </c>
     </row>
     <row r="372" ht="20" customHeight="1">
@@ -10328,7 +10328,7 @@
         </is>
       </c>
       <c r="E372" s="20" t="n">
-        <v>212</v>
+        <v>113</v>
       </c>
     </row>
     <row r="373" ht="20" customHeight="1">
@@ -10353,7 +10353,7 @@
         </is>
       </c>
       <c r="E373" s="23" t="n">
-        <v>214</v>
+        <v>185</v>
       </c>
     </row>
     <row r="374" ht="20" customHeight="1">
@@ -10378,7 +10378,7 @@
         </is>
       </c>
       <c r="E374" s="20" t="n">
-        <v>137</v>
+        <v>186</v>
       </c>
     </row>
     <row r="375" ht="20" customHeight="1">
@@ -10403,7 +10403,7 @@
         </is>
       </c>
       <c r="E375" s="23" t="n">
-        <v>132</v>
+        <v>188</v>
       </c>
     </row>
     <row r="376" ht="20" customHeight="1">
@@ -10428,7 +10428,7 @@
         </is>
       </c>
       <c r="E376" s="20" t="n">
-        <v>193</v>
+        <v>204</v>
       </c>
     </row>
     <row r="377" ht="20" customHeight="1">
@@ -10453,7 +10453,7 @@
         </is>
       </c>
       <c r="E377" s="23" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="378" ht="20" customHeight="1">
@@ -10478,7 +10478,7 @@
         </is>
       </c>
       <c r="E378" s="20" t="n">
-        <v>213</v>
+        <v>162</v>
       </c>
     </row>
     <row r="379" ht="20" customHeight="1">
@@ -10503,7 +10503,7 @@
         </is>
       </c>
       <c r="E379" s="23" t="n">
-        <v>154</v>
+        <v>184</v>
       </c>
     </row>
     <row r="380" ht="20" customHeight="1">
@@ -10528,7 +10528,7 @@
         </is>
       </c>
       <c r="E380" s="20" t="n">
-        <v>180</v>
+        <v>132</v>
       </c>
     </row>
     <row r="381" ht="20" customHeight="1">
@@ -10553,7 +10553,7 @@
         </is>
       </c>
       <c r="E381" s="23" t="n">
-        <v>173</v>
+        <v>142</v>
       </c>
     </row>
     <row r="382" ht="20" customHeight="1">
@@ -10578,7 +10578,7 @@
         </is>
       </c>
       <c r="E382" s="20" t="n">
-        <v>127</v>
+        <v>115</v>
       </c>
     </row>
     <row r="383" ht="20" customHeight="1">
@@ -10603,7 +10603,7 @@
         </is>
       </c>
       <c r="E383" s="23" t="n">
-        <v>219</v>
+        <v>176</v>
       </c>
     </row>
     <row r="384" ht="20" customHeight="1">
@@ -10628,7 +10628,7 @@
         </is>
       </c>
       <c r="E384" s="20" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="385" ht="20" customHeight="1">
@@ -10653,7 +10653,7 @@
         </is>
       </c>
       <c r="E385" s="23" t="n">
-        <v>148</v>
+        <v>225</v>
       </c>
     </row>
     <row r="386" ht="20" customHeight="1">
@@ -10678,7 +10678,7 @@
         </is>
       </c>
       <c r="E386" s="20" t="n">
-        <v>197</v>
+        <v>217</v>
       </c>
     </row>
     <row r="387" ht="20" customHeight="1">
@@ -10703,7 +10703,7 @@
         </is>
       </c>
       <c r="E387" s="23" t="n">
-        <v>218</v>
+        <v>200</v>
       </c>
     </row>
     <row r="388" ht="20" customHeight="1">
@@ -10728,7 +10728,7 @@
         </is>
       </c>
       <c r="E388" s="20" t="n">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="389" ht="20" customHeight="1">
@@ -10753,7 +10753,7 @@
         </is>
       </c>
       <c r="E389" s="23" t="n">
-        <v>176</v>
+        <v>192</v>
       </c>
     </row>
     <row r="390" ht="20" customHeight="1">
@@ -10778,7 +10778,7 @@
         </is>
       </c>
       <c r="E390" s="20" t="n">
-        <v>239</v>
+        <v>205</v>
       </c>
     </row>
     <row r="391" ht="20" customHeight="1">
@@ -10803,7 +10803,7 @@
         </is>
       </c>
       <c r="E391" s="23" t="n">
-        <v>237</v>
+        <v>119</v>
       </c>
     </row>
     <row r="392" ht="20" customHeight="1">
@@ -10828,7 +10828,7 @@
         </is>
       </c>
       <c r="E392" s="20" t="n">
-        <v>178</v>
+        <v>165</v>
       </c>
     </row>
     <row r="393" ht="20" customHeight="1">
@@ -10853,7 +10853,7 @@
         </is>
       </c>
       <c r="E393" s="23" t="n">
-        <v>218</v>
+        <v>193</v>
       </c>
     </row>
     <row r="394" ht="20" customHeight="1">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="E394" s="20" t="n">
-        <v>179</v>
+        <v>216</v>
       </c>
     </row>
     <row r="395" ht="20" customHeight="1">
@@ -10903,7 +10903,7 @@
         </is>
       </c>
       <c r="E395" s="23" t="n">
-        <v>145</v>
+        <v>197</v>
       </c>
     </row>
     <row r="396" ht="20" customHeight="1">
@@ -10928,7 +10928,7 @@
         </is>
       </c>
       <c r="E396" s="20" t="n">
-        <v>200</v>
+        <v>163</v>
       </c>
     </row>
     <row r="397" ht="20" customHeight="1">
@@ -10953,7 +10953,7 @@
         </is>
       </c>
       <c r="E397" s="23" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
     </row>
     <row r="398" ht="20" customHeight="1">
@@ -10978,7 +10978,7 @@
         </is>
       </c>
       <c r="E398" s="20" t="n">
-        <v>224</v>
+        <v>237</v>
       </c>
     </row>
     <row r="399" ht="20" customHeight="1">
@@ -11003,7 +11003,7 @@
         </is>
       </c>
       <c r="E399" s="23" t="n">
-        <v>140</v>
+        <v>181</v>
       </c>
     </row>
     <row r="400" ht="20" customHeight="1">
@@ -11028,7 +11028,7 @@
         </is>
       </c>
       <c r="E400" s="20" t="n">
-        <v>202</v>
+        <v>234</v>
       </c>
     </row>
     <row r="401" ht="20" customHeight="1">
@@ -11053,7 +11053,7 @@
         </is>
       </c>
       <c r="E401" s="23" t="n">
-        <v>234</v>
+        <v>120</v>
       </c>
     </row>
     <row r="402" ht="20" customHeight="1">
@@ -11078,7 +11078,7 @@
         </is>
       </c>
       <c r="E402" s="20" t="n">
-        <v>217</v>
+        <v>172</v>
       </c>
     </row>
     <row r="403" ht="20" customHeight="1">
@@ -11103,7 +11103,7 @@
         </is>
       </c>
       <c r="E403" s="23" t="n">
-        <v>163</v>
+        <v>223</v>
       </c>
     </row>
     <row r="404" ht="20" customHeight="1">
@@ -11128,7 +11128,7 @@
         </is>
       </c>
       <c r="E404" s="20" t="n">
-        <v>205</v>
+        <v>111</v>
       </c>
     </row>
     <row r="405" ht="20" customHeight="1">
@@ -11153,7 +11153,7 @@
         </is>
       </c>
       <c r="E405" s="23" t="n">
-        <v>223</v>
+        <v>135</v>
       </c>
     </row>
     <row r="406" ht="20" customHeight="1">
@@ -11178,7 +11178,7 @@
         </is>
       </c>
       <c r="E406" s="20" t="n">
-        <v>144</v>
+        <v>199</v>
       </c>
     </row>
     <row r="407" ht="20" customHeight="1">
@@ -11203,7 +11203,7 @@
         </is>
       </c>
       <c r="E407" s="23" t="n">
-        <v>126</v>
+        <v>151</v>
       </c>
     </row>
     <row r="408" ht="20" customHeight="1">
@@ -11228,7 +11228,7 @@
         </is>
       </c>
       <c r="E408" s="20" t="n">
-        <v>178</v>
+        <v>113</v>
       </c>
     </row>
     <row r="409" ht="20" customHeight="1">
@@ -11253,7 +11253,7 @@
         </is>
       </c>
       <c r="E409" s="23" t="n">
-        <v>203</v>
+        <v>175</v>
       </c>
     </row>
     <row r="410" ht="20" customHeight="1">
@@ -11278,7 +11278,7 @@
         </is>
       </c>
       <c r="E410" s="20" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="411" ht="20" customHeight="1">
@@ -11303,7 +11303,7 @@
         </is>
       </c>
       <c r="E411" s="23" t="n">
-        <v>213</v>
+        <v>201</v>
       </c>
     </row>
     <row r="412" ht="20" customHeight="1">
@@ -11328,7 +11328,7 @@
         </is>
       </c>
       <c r="E412" s="20" t="n">
-        <v>175</v>
+        <v>193</v>
       </c>
     </row>
     <row r="413" ht="20" customHeight="1">
@@ -11353,7 +11353,7 @@
         </is>
       </c>
       <c r="E413" s="23" t="n">
-        <v>141</v>
+        <v>173</v>
       </c>
     </row>
     <row r="414" ht="20" customHeight="1">
@@ -11378,7 +11378,7 @@
         </is>
       </c>
       <c r="E414" s="20" t="n">
-        <v>146</v>
+        <v>231</v>
       </c>
     </row>
     <row r="415" ht="20" customHeight="1">
@@ -11403,7 +11403,7 @@
         </is>
       </c>
       <c r="E415" s="23" t="n">
-        <v>208</v>
+        <v>187</v>
       </c>
     </row>
     <row r="416" ht="20" customHeight="1">
@@ -11428,7 +11428,7 @@
         </is>
       </c>
       <c r="E416" s="20" t="n">
-        <v>158</v>
+        <v>201</v>
       </c>
     </row>
     <row r="417" ht="20" customHeight="1">
@@ -11453,7 +11453,7 @@
         </is>
       </c>
       <c r="E417" s="23" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="418" ht="20" customHeight="1">
@@ -11478,7 +11478,7 @@
         </is>
       </c>
       <c r="E418" s="20" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="419" ht="20" customHeight="1">
@@ -11503,7 +11503,7 @@
         </is>
       </c>
       <c r="E419" s="23" t="n">
-        <v>153</v>
+        <v>231</v>
       </c>
     </row>
     <row r="420" ht="20" customHeight="1">
@@ -11528,7 +11528,7 @@
         </is>
       </c>
       <c r="E420" s="20" t="n">
-        <v>210</v>
+        <v>123</v>
       </c>
     </row>
     <row r="421" ht="20" customHeight="1">
@@ -11553,7 +11553,7 @@
         </is>
       </c>
       <c r="E421" s="23" t="n">
-        <v>175</v>
+        <v>208</v>
       </c>
     </row>
     <row r="422" ht="20" customHeight="1">
@@ -11578,7 +11578,7 @@
         </is>
       </c>
       <c r="E422" s="20" t="n">
-        <v>183</v>
+        <v>172</v>
       </c>
     </row>
     <row r="423" ht="20" customHeight="1">
@@ -11603,7 +11603,7 @@
         </is>
       </c>
       <c r="E423" s="23" t="n">
-        <v>189</v>
+        <v>219</v>
       </c>
     </row>
     <row r="424" ht="20" customHeight="1">
@@ -11628,7 +11628,7 @@
         </is>
       </c>
       <c r="E424" s="20" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="425" ht="20" customHeight="1">
@@ -11653,7 +11653,7 @@
         </is>
       </c>
       <c r="E425" s="23" t="n">
-        <v>155</v>
+        <v>163</v>
       </c>
     </row>
     <row r="426" ht="20" customHeight="1">
@@ -11678,7 +11678,7 @@
         </is>
       </c>
       <c r="E426" s="20" t="n">
-        <v>141</v>
+        <v>114</v>
       </c>
     </row>
     <row r="427" ht="20" customHeight="1">
@@ -11703,7 +11703,7 @@
         </is>
       </c>
       <c r="E427" s="23" t="n">
-        <v>202</v>
+        <v>180</v>
       </c>
     </row>
     <row r="428" ht="20" customHeight="1">
@@ -11728,7 +11728,7 @@
         </is>
       </c>
       <c r="E428" s="20" t="n">
-        <v>212</v>
+        <v>226</v>
       </c>
     </row>
     <row r="429" ht="20" customHeight="1">
@@ -11753,7 +11753,7 @@
         </is>
       </c>
       <c r="E429" s="23" t="n">
-        <v>180</v>
+        <v>187</v>
       </c>
     </row>
     <row r="430" ht="20" customHeight="1">
@@ -11778,7 +11778,7 @@
         </is>
       </c>
       <c r="E430" s="20" t="n">
-        <v>173</v>
+        <v>178</v>
       </c>
     </row>
     <row r="431" ht="20" customHeight="1">
@@ -11803,7 +11803,7 @@
         </is>
       </c>
       <c r="E431" s="23" t="n">
-        <v>130</v>
+        <v>218</v>
       </c>
     </row>
     <row r="432" ht="20" customHeight="1">
@@ -11828,7 +11828,7 @@
         </is>
       </c>
       <c r="E432" s="20" t="n">
-        <v>191</v>
+        <v>115</v>
       </c>
     </row>
     <row r="433" ht="20" customHeight="1">
@@ -11853,7 +11853,7 @@
         </is>
       </c>
       <c r="E433" s="23" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="434" ht="20" customHeight="1">
@@ -11878,7 +11878,7 @@
         </is>
       </c>
       <c r="E434" s="20" t="n">
-        <v>223</v>
+        <v>234</v>
       </c>
     </row>
     <row r="435" ht="20" customHeight="1">
@@ -11903,7 +11903,7 @@
         </is>
       </c>
       <c r="E435" s="23" t="n">
-        <v>191</v>
+        <v>158</v>
       </c>
     </row>
     <row r="436" ht="20" customHeight="1">
@@ -11928,7 +11928,7 @@
         </is>
       </c>
       <c r="E436" s="20" t="n">
-        <v>182</v>
+        <v>147</v>
       </c>
     </row>
     <row r="437" ht="20" customHeight="1">
@@ -11953,7 +11953,7 @@
         </is>
       </c>
       <c r="E437" s="23" t="n">
-        <v>218</v>
+        <v>237</v>
       </c>
     </row>
     <row r="438" ht="20" customHeight="1">
@@ -11978,7 +11978,7 @@
         </is>
       </c>
       <c r="E438" s="20" t="n">
-        <v>217</v>
+        <v>133</v>
       </c>
     </row>
     <row r="439" ht="20" customHeight="1">
@@ -12003,7 +12003,7 @@
         </is>
       </c>
       <c r="E439" s="23" t="n">
-        <v>185</v>
+        <v>165</v>
       </c>
     </row>
     <row r="440" ht="20" customHeight="1">
@@ -12028,7 +12028,7 @@
         </is>
       </c>
       <c r="E440" s="20" t="n">
-        <v>240</v>
+        <v>182</v>
       </c>
     </row>
     <row r="441" ht="20" customHeight="1">
@@ -12053,7 +12053,7 @@
         </is>
       </c>
       <c r="E441" s="23" t="n">
-        <v>174</v>
+        <v>154</v>
       </c>
     </row>
     <row r="442" ht="20" customHeight="1">
@@ -12078,7 +12078,7 @@
         </is>
       </c>
       <c r="E442" s="20" t="n">
-        <v>202</v>
+        <v>220</v>
       </c>
     </row>
     <row r="443" ht="20" customHeight="1">
@@ -12103,7 +12103,7 @@
         </is>
       </c>
       <c r="E443" s="23" t="n">
-        <v>194</v>
+        <v>212</v>
       </c>
     </row>
     <row r="444" ht="20" customHeight="1">
@@ -12128,7 +12128,7 @@
         </is>
       </c>
       <c r="E444" s="20" t="n">
-        <v>224</v>
+        <v>110</v>
       </c>
     </row>
     <row r="445" ht="20" customHeight="1">
@@ -12153,7 +12153,7 @@
         </is>
       </c>
       <c r="E445" s="23" t="n">
-        <v>113</v>
+        <v>181</v>
       </c>
     </row>
     <row r="446" ht="20" customHeight="1">
@@ -12178,7 +12178,7 @@
         </is>
       </c>
       <c r="E446" s="20" t="n">
-        <v>212</v>
+        <v>165</v>
       </c>
     </row>
     <row r="447" ht="20" customHeight="1">
@@ -12203,7 +12203,7 @@
         </is>
       </c>
       <c r="E447" s="23" t="n">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="448" ht="20" customHeight="1">
@@ -12228,7 +12228,7 @@
         </is>
       </c>
       <c r="E448" s="20" t="n">
-        <v>137</v>
+        <v>208</v>
       </c>
     </row>
     <row r="449" ht="20" customHeight="1">
@@ -12253,7 +12253,7 @@
         </is>
       </c>
       <c r="E449" s="23" t="n">
-        <v>146</v>
+        <v>171</v>
       </c>
     </row>
     <row r="450" ht="20" customHeight="1">
@@ -12278,7 +12278,7 @@
         </is>
       </c>
       <c r="E450" s="20" t="n">
-        <v>166</v>
+        <v>159</v>
       </c>
     </row>
     <row r="451" ht="20" customHeight="1">
@@ -12303,7 +12303,7 @@
         </is>
       </c>
       <c r="E451" s="23" t="n">
-        <v>166</v>
+        <v>223</v>
       </c>
     </row>
     <row r="452" ht="20" customHeight="1">
@@ -12328,7 +12328,7 @@
         </is>
       </c>
       <c r="E452" s="20" t="n">
-        <v>206</v>
+        <v>186</v>
       </c>
     </row>
     <row r="453" ht="20" customHeight="1">
@@ -12353,7 +12353,7 @@
         </is>
       </c>
       <c r="E453" s="23" t="n">
-        <v>217</v>
+        <v>233</v>
       </c>
     </row>
     <row r="454" ht="20" customHeight="1">
@@ -12378,7 +12378,7 @@
         </is>
       </c>
       <c r="E454" s="20" t="n">
-        <v>240</v>
+        <v>190</v>
       </c>
     </row>
     <row r="455" ht="20" customHeight="1">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="E455" s="23" t="n">
-        <v>176</v>
+        <v>126</v>
       </c>
     </row>
     <row r="456" ht="20" customHeight="1">
@@ -12428,7 +12428,7 @@
         </is>
       </c>
       <c r="E456" s="20" t="n">
-        <v>129</v>
+        <v>232</v>
       </c>
     </row>
     <row r="457" ht="20" customHeight="1">
@@ -12453,7 +12453,7 @@
         </is>
       </c>
       <c r="E457" s="23" t="n">
-        <v>218</v>
+        <v>239</v>
       </c>
     </row>
     <row r="458" ht="20" customHeight="1">
@@ -12478,7 +12478,7 @@
         </is>
       </c>
       <c r="E458" s="20" t="n">
-        <v>140</v>
+        <v>163</v>
       </c>
     </row>
     <row r="459" ht="20" customHeight="1">
@@ -12503,7 +12503,7 @@
         </is>
       </c>
       <c r="E459" s="23" t="n">
-        <v>192</v>
+        <v>154</v>
       </c>
     </row>
     <row r="460" ht="20" customHeight="1">
@@ -12528,7 +12528,7 @@
         </is>
       </c>
       <c r="E460" s="20" t="n">
-        <v>143</v>
+        <v>184</v>
       </c>
     </row>
     <row r="461" ht="20" customHeight="1">
@@ -12553,7 +12553,7 @@
         </is>
       </c>
       <c r="E461" s="23" t="n">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="462" ht="20" customHeight="1">
@@ -12578,7 +12578,7 @@
         </is>
       </c>
       <c r="E462" s="20" t="n">
-        <v>196</v>
+        <v>192</v>
       </c>
     </row>
     <row r="463" ht="20" customHeight="1">
@@ -12603,7 +12603,7 @@
         </is>
       </c>
       <c r="E463" s="23" t="n">
-        <v>200</v>
+        <v>170</v>
       </c>
     </row>
     <row r="464" ht="20" customHeight="1">
@@ -12628,7 +12628,7 @@
         </is>
       </c>
       <c r="E464" s="20" t="n">
-        <v>157</v>
+        <v>203</v>
       </c>
     </row>
     <row r="465" ht="20" customHeight="1">
@@ -12653,7 +12653,7 @@
         </is>
       </c>
       <c r="E465" s="23" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="466" ht="20" customHeight="1">
@@ -12678,7 +12678,7 @@
         </is>
       </c>
       <c r="E466" s="20" t="n">
-        <v>217</v>
+        <v>180</v>
       </c>
     </row>
     <row r="467" ht="20" customHeight="1">
@@ -12703,7 +12703,7 @@
         </is>
       </c>
       <c r="E467" s="23" t="n">
-        <v>194</v>
+        <v>199</v>
       </c>
     </row>
     <row r="468" ht="20" customHeight="1">
@@ -12728,7 +12728,7 @@
         </is>
       </c>
       <c r="E468" s="20" t="n">
-        <v>226</v>
+        <v>186</v>
       </c>
     </row>
     <row r="469" ht="20" customHeight="1">
@@ -12753,7 +12753,7 @@
         </is>
       </c>
       <c r="E469" s="23" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="470" ht="20" customHeight="1">
@@ -12778,7 +12778,7 @@
         </is>
       </c>
       <c r="E470" s="20" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="471" ht="20" customHeight="1">
@@ -12803,7 +12803,7 @@
         </is>
       </c>
       <c r="E471" s="23" t="n">
-        <v>184</v>
+        <v>195</v>
       </c>
     </row>
     <row r="472" ht="20" customHeight="1">
@@ -12828,7 +12828,7 @@
         </is>
       </c>
       <c r="E472" s="20" t="n">
-        <v>217</v>
+        <v>172</v>
       </c>
     </row>
     <row r="473" ht="20" customHeight="1">
@@ -12853,7 +12853,7 @@
         </is>
       </c>
       <c r="E473" s="23" t="n">
-        <v>196</v>
+        <v>222</v>
       </c>
     </row>
     <row r="474" ht="20" customHeight="1">
@@ -12878,7 +12878,7 @@
         </is>
       </c>
       <c r="E474" s="20" t="n">
-        <v>176</v>
+        <v>226</v>
       </c>
     </row>
     <row r="475" ht="20" customHeight="1">
@@ -12903,7 +12903,7 @@
         </is>
       </c>
       <c r="E475" s="23" t="n">
-        <v>208</v>
+        <v>148</v>
       </c>
     </row>
     <row r="476" ht="20" customHeight="1">
@@ -12928,7 +12928,7 @@
         </is>
       </c>
       <c r="E476" s="20" t="n">
-        <v>115</v>
+        <v>175</v>
       </c>
     </row>
     <row r="477" ht="20" customHeight="1">
@@ -12953,7 +12953,7 @@
         </is>
       </c>
       <c r="E477" s="23" t="n">
-        <v>194</v>
+        <v>123</v>
       </c>
     </row>
     <row r="478" ht="20" customHeight="1">
@@ -12978,7 +12978,7 @@
         </is>
       </c>
       <c r="E478" s="20" t="n">
-        <v>231</v>
+        <v>225</v>
       </c>
     </row>
     <row r="479" ht="20" customHeight="1">
@@ -13003,7 +13003,7 @@
         </is>
       </c>
       <c r="E479" s="23" t="n">
-        <v>127</v>
+        <v>239</v>
       </c>
     </row>
     <row r="480" ht="20" customHeight="1">
@@ -13028,7 +13028,7 @@
         </is>
       </c>
       <c r="E480" s="20" t="n">
-        <v>152</v>
+        <v>179</v>
       </c>
     </row>
     <row r="481" ht="20" customHeight="1">
@@ -13053,7 +13053,7 @@
         </is>
       </c>
       <c r="E481" s="23" t="n">
-        <v>121</v>
+        <v>213</v>
       </c>
     </row>
     <row r="482" ht="20" customHeight="1">
@@ -13078,7 +13078,7 @@
         </is>
       </c>
       <c r="E482" s="20" t="n">
-        <v>234</v>
+        <v>140</v>
       </c>
     </row>
     <row r="483" ht="20" customHeight="1">
@@ -13103,7 +13103,7 @@
         </is>
       </c>
       <c r="E483" s="23" t="n">
-        <v>219</v>
+        <v>118</v>
       </c>
     </row>
     <row r="484" ht="20" customHeight="1">
@@ -13128,7 +13128,7 @@
         </is>
       </c>
       <c r="E484" s="20" t="n">
-        <v>217</v>
+        <v>180</v>
       </c>
     </row>
     <row r="485" ht="20" customHeight="1">
@@ -13153,7 +13153,7 @@
         </is>
       </c>
       <c r="E485" s="23" t="n">
-        <v>115</v>
+        <v>168</v>
       </c>
     </row>
     <row r="486" ht="20" customHeight="1">
@@ -13178,7 +13178,7 @@
         </is>
       </c>
       <c r="E486" s="20" t="n">
-        <v>165</v>
+        <v>213</v>
       </c>
     </row>
     <row r="487" ht="20" customHeight="1">
@@ -13203,7 +13203,7 @@
         </is>
       </c>
       <c r="E487" s="23" t="n">
-        <v>215</v>
+        <v>193</v>
       </c>
     </row>
     <row r="488" ht="20" customHeight="1">
@@ -13228,7 +13228,7 @@
         </is>
       </c>
       <c r="E488" s="20" t="n">
-        <v>213</v>
+        <v>166</v>
       </c>
     </row>
     <row r="489" ht="20" customHeight="1">
@@ -13253,7 +13253,7 @@
         </is>
       </c>
       <c r="E489" s="23" t="n">
-        <v>223</v>
+        <v>190</v>
       </c>
     </row>
     <row r="490" ht="20" customHeight="1">
@@ -13278,7 +13278,7 @@
         </is>
       </c>
       <c r="E490" s="20" t="n">
-        <v>229</v>
+        <v>179</v>
       </c>
     </row>
     <row r="491" ht="20" customHeight="1">
@@ -13303,7 +13303,7 @@
         </is>
       </c>
       <c r="E491" s="23" t="n">
-        <v>162</v>
+        <v>135</v>
       </c>
     </row>
     <row r="492" ht="20" customHeight="1">
@@ -13328,7 +13328,7 @@
         </is>
       </c>
       <c r="E492" s="20" t="n">
-        <v>226</v>
+        <v>190</v>
       </c>
     </row>
     <row r="493" ht="20" customHeight="1">
@@ -13353,7 +13353,7 @@
         </is>
       </c>
       <c r="E493" s="23" t="n">
-        <v>161</v>
+        <v>174</v>
       </c>
     </row>
     <row r="494" ht="20" customHeight="1">
@@ -13378,7 +13378,7 @@
         </is>
       </c>
       <c r="E494" s="20" t="n">
-        <v>176</v>
+        <v>150</v>
       </c>
     </row>
     <row r="495" ht="20" customHeight="1">
@@ -13403,7 +13403,7 @@
         </is>
       </c>
       <c r="E495" s="23" t="n">
-        <v>207</v>
+        <v>161</v>
       </c>
     </row>
     <row r="496" ht="20" customHeight="1">
@@ -13428,7 +13428,7 @@
         </is>
       </c>
       <c r="E496" s="20" t="n">
-        <v>134</v>
+        <v>158</v>
       </c>
     </row>
     <row r="497" ht="20" customHeight="1">
@@ -13453,7 +13453,7 @@
         </is>
       </c>
       <c r="E497" s="23" t="n">
-        <v>226</v>
+        <v>129</v>
       </c>
     </row>
     <row r="498" ht="20" customHeight="1">
@@ -13478,7 +13478,7 @@
         </is>
       </c>
       <c r="E498" s="20" t="n">
-        <v>224</v>
+        <v>237</v>
       </c>
     </row>
     <row r="499" ht="20" customHeight="1">
@@ -13503,7 +13503,7 @@
         </is>
       </c>
       <c r="E499" s="23" t="n">
-        <v>181</v>
+        <v>140</v>
       </c>
     </row>
     <row r="500" ht="20" customHeight="1">
@@ -13528,7 +13528,7 @@
         </is>
       </c>
       <c r="E500" s="20" t="n">
-        <v>119</v>
+        <v>191</v>
       </c>
     </row>
     <row r="501" ht="20" customHeight="1">
@@ -13553,7 +13553,7 @@
         </is>
       </c>
       <c r="E501" s="23" t="n">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="502" ht="20" customHeight="1">
@@ -13578,7 +13578,7 @@
         </is>
       </c>
       <c r="E502" s="20" t="n">
-        <v>232</v>
+        <v>225</v>
       </c>
     </row>
     <row r="503" ht="20" customHeight="1">
@@ -13603,7 +13603,7 @@
         </is>
       </c>
       <c r="E503" s="23" t="n">
-        <v>156</v>
+        <v>203</v>
       </c>
     </row>
     <row r="504" ht="20" customHeight="1">
@@ -13628,7 +13628,7 @@
         </is>
       </c>
       <c r="E504" s="20" t="n">
-        <v>195</v>
+        <v>163</v>
       </c>
     </row>
     <row r="505" ht="20" customHeight="1">
@@ -13653,7 +13653,7 @@
         </is>
       </c>
       <c r="E505" s="23" t="n">
-        <v>144</v>
+        <v>167</v>
       </c>
     </row>
     <row r="506" ht="20" customHeight="1">
@@ -13678,7 +13678,7 @@
         </is>
       </c>
       <c r="E506" s="20" t="n">
-        <v>187</v>
+        <v>164</v>
       </c>
     </row>
     <row r="507" ht="20" customHeight="1">
@@ -13703,7 +13703,7 @@
         </is>
       </c>
       <c r="E507" s="23" t="n">
-        <v>235</v>
+        <v>231</v>
       </c>
     </row>
     <row r="508" ht="20" customHeight="1">
@@ -13728,7 +13728,7 @@
         </is>
       </c>
       <c r="E508" s="20" t="n">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="509" ht="20" customHeight="1">
@@ -13753,7 +13753,7 @@
         </is>
       </c>
       <c r="E509" s="23" t="n">
-        <v>156</v>
+        <v>113</v>
       </c>
     </row>
     <row r="510" ht="20" customHeight="1">
@@ -13778,7 +13778,7 @@
         </is>
       </c>
       <c r="E510" s="20" t="n">
-        <v>196</v>
+        <v>174</v>
       </c>
     </row>
     <row r="511" ht="20" customHeight="1">
@@ -13803,7 +13803,7 @@
         </is>
       </c>
       <c r="E511" s="23" t="n">
-        <v>142</v>
+        <v>135</v>
       </c>
     </row>
     <row r="512" ht="20" customHeight="1">
@@ -13828,7 +13828,7 @@
         </is>
       </c>
       <c r="E512" s="20" t="n">
-        <v>210</v>
+        <v>185</v>
       </c>
     </row>
     <row r="513" ht="20" customHeight="1">
@@ -13853,7 +13853,7 @@
         </is>
       </c>
       <c r="E513" s="23" t="n">
-        <v>140</v>
+        <v>239</v>
       </c>
     </row>
     <row r="514" ht="20" customHeight="1">
@@ -13878,7 +13878,7 @@
         </is>
       </c>
       <c r="E514" s="20" t="n">
-        <v>139</v>
+        <v>168</v>
       </c>
     </row>
     <row r="515" ht="20" customHeight="1">
@@ -13903,7 +13903,7 @@
         </is>
       </c>
       <c r="E515" s="23" t="n">
-        <v>191</v>
+        <v>123</v>
       </c>
     </row>
     <row r="516" ht="20" customHeight="1">
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="E516" s="20" t="n">
-        <v>166</v>
+        <v>120</v>
       </c>
     </row>
     <row r="517" ht="20" customHeight="1">
@@ -13953,7 +13953,7 @@
         </is>
       </c>
       <c r="E517" s="23" t="n">
-        <v>210</v>
+        <v>194</v>
       </c>
     </row>
     <row r="518" ht="20" customHeight="1">
@@ -13978,7 +13978,7 @@
         </is>
       </c>
       <c r="E518" s="20" t="n">
-        <v>174</v>
+        <v>183</v>
       </c>
     </row>
     <row r="519" ht="20" customHeight="1">
@@ -14003,7 +14003,7 @@
         </is>
       </c>
       <c r="E519" s="23" t="n">
-        <v>237</v>
+        <v>126</v>
       </c>
     </row>
     <row r="520" ht="20" customHeight="1">
@@ -14028,7 +14028,7 @@
         </is>
       </c>
       <c r="E520" s="20" t="n">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="521" ht="20" customHeight="1">
@@ -14053,7 +14053,7 @@
         </is>
       </c>
       <c r="E521" s="23" t="n">
-        <v>213</v>
+        <v>177</v>
       </c>
     </row>
     <row r="522" ht="20" customHeight="1">
@@ -14078,7 +14078,7 @@
         </is>
       </c>
       <c r="E522" s="20" t="n">
-        <v>179</v>
+        <v>214</v>
       </c>
     </row>
     <row r="523" ht="20" customHeight="1">
@@ -14103,7 +14103,7 @@
         </is>
       </c>
       <c r="E523" s="23" t="n">
-        <v>158</v>
+        <v>128</v>
       </c>
     </row>
     <row r="524" ht="20" customHeight="1">
@@ -14128,7 +14128,7 @@
         </is>
       </c>
       <c r="E524" s="20" t="n">
-        <v>162</v>
+        <v>169</v>
       </c>
     </row>
     <row r="525" ht="20" customHeight="1">
@@ -14153,7 +14153,7 @@
         </is>
       </c>
       <c r="E525" s="23" t="n">
-        <v>208</v>
+        <v>221</v>
       </c>
     </row>
     <row r="526" ht="20" customHeight="1">
@@ -14178,7 +14178,7 @@
         </is>
       </c>
       <c r="E526" s="20" t="n">
-        <v>205</v>
+        <v>113</v>
       </c>
     </row>
     <row r="527" ht="20" customHeight="1">
@@ -14203,7 +14203,7 @@
         </is>
       </c>
       <c r="E527" s="23" t="n">
-        <v>167</v>
+        <v>115</v>
       </c>
     </row>
     <row r="528" ht="20" customHeight="1">
@@ -14228,7 +14228,7 @@
         </is>
       </c>
       <c r="E528" s="20" t="n">
-        <v>191</v>
+        <v>152</v>
       </c>
     </row>
     <row r="529" ht="20" customHeight="1">
@@ -14253,7 +14253,7 @@
         </is>
       </c>
       <c r="E529" s="23" t="n">
-        <v>190</v>
+        <v>150</v>
       </c>
     </row>
     <row r="530" ht="20" customHeight="1">
@@ -14278,7 +14278,7 @@
         </is>
       </c>
       <c r="E530" s="20" t="n">
-        <v>188</v>
+        <v>163</v>
       </c>
     </row>
     <row r="531" ht="20" customHeight="1">
@@ -14303,7 +14303,7 @@
         </is>
       </c>
       <c r="E531" s="23" t="n">
-        <v>198</v>
+        <v>121</v>
       </c>
     </row>
     <row r="532" ht="20" customHeight="1">
@@ -14328,7 +14328,7 @@
         </is>
       </c>
       <c r="E532" s="20" t="n">
-        <v>131</v>
+        <v>146</v>
       </c>
     </row>
     <row r="533" ht="20" customHeight="1">
@@ -14353,7 +14353,7 @@
         </is>
       </c>
       <c r="E533" s="23" t="n">
-        <v>118</v>
+        <v>212</v>
       </c>
     </row>
     <row r="534" ht="20" customHeight="1">
@@ -14378,7 +14378,7 @@
         </is>
       </c>
       <c r="E534" s="20" t="n">
-        <v>128</v>
+        <v>183</v>
       </c>
     </row>
     <row r="535" ht="20" customHeight="1">
@@ -14403,7 +14403,7 @@
         </is>
       </c>
       <c r="E535" s="23" t="n">
-        <v>207</v>
+        <v>231</v>
       </c>
     </row>
     <row r="536" ht="20" customHeight="1">
@@ -14428,7 +14428,7 @@
         </is>
       </c>
       <c r="E536" s="20" t="n">
-        <v>226</v>
+        <v>216</v>
       </c>
     </row>
     <row r="537" ht="20" customHeight="1">
@@ -14453,7 +14453,7 @@
         </is>
       </c>
       <c r="E537" s="23" t="n">
-        <v>111</v>
+        <v>221</v>
       </c>
     </row>
     <row r="538" ht="20" customHeight="1">
@@ -14478,7 +14478,7 @@
         </is>
       </c>
       <c r="E538" s="20" t="n">
-        <v>189</v>
+        <v>238</v>
       </c>
     </row>
     <row r="539" ht="20" customHeight="1">
@@ -14503,7 +14503,7 @@
         </is>
       </c>
       <c r="E539" s="23" t="n">
-        <v>141</v>
+        <v>169</v>
       </c>
     </row>
     <row r="540" ht="20" customHeight="1">
@@ -14528,7 +14528,7 @@
         </is>
       </c>
       <c r="E540" s="20" t="n">
-        <v>151</v>
+        <v>175</v>
       </c>
     </row>
     <row r="541" ht="20" customHeight="1">
@@ -14553,7 +14553,7 @@
         </is>
       </c>
       <c r="E541" s="23" t="n">
-        <v>158</v>
+        <v>216</v>
       </c>
     </row>
     <row r="542" ht="20" customHeight="1">
@@ -14578,7 +14578,7 @@
         </is>
       </c>
       <c r="E542" s="20" t="n">
-        <v>127</v>
+        <v>204</v>
       </c>
     </row>
     <row r="543" ht="20" customHeight="1">
@@ -14603,7 +14603,7 @@
         </is>
       </c>
       <c r="E543" s="23" t="n">
-        <v>136</v>
+        <v>185</v>
       </c>
     </row>
     <row r="544" ht="20" customHeight="1">
@@ -14628,7 +14628,7 @@
         </is>
       </c>
       <c r="E544" s="20" t="n">
-        <v>193</v>
+        <v>111</v>
       </c>
     </row>
     <row r="545" ht="20" customHeight="1">
@@ -14653,7 +14653,7 @@
         </is>
       </c>
       <c r="E545" s="23" t="n">
-        <v>184</v>
+        <v>169</v>
       </c>
     </row>
     <row r="546" ht="20" customHeight="1">
@@ -14678,7 +14678,7 @@
         </is>
       </c>
       <c r="E546" s="20" t="n">
-        <v>143</v>
+        <v>156</v>
       </c>
     </row>
     <row r="547" ht="20" customHeight="1">
@@ -14703,7 +14703,7 @@
         </is>
       </c>
       <c r="E547" s="23" t="n">
-        <v>214</v>
+        <v>126</v>
       </c>
     </row>
     <row r="548" ht="20" customHeight="1">
@@ -14728,7 +14728,7 @@
         </is>
       </c>
       <c r="E548" s="20" t="n">
-        <v>207</v>
+        <v>227</v>
       </c>
     </row>
     <row r="549" ht="20" customHeight="1">
@@ -14753,7 +14753,7 @@
         </is>
       </c>
       <c r="E549" s="23" t="n">
-        <v>236</v>
+        <v>169</v>
       </c>
     </row>
     <row r="550" ht="20" customHeight="1">
@@ -14778,7 +14778,7 @@
         </is>
       </c>
       <c r="E550" s="20" t="n">
-        <v>132</v>
+        <v>204</v>
       </c>
     </row>
     <row r="551" ht="20" customHeight="1">
@@ -14803,7 +14803,7 @@
         </is>
       </c>
       <c r="E551" s="23" t="n">
-        <v>130</v>
+        <v>165</v>
       </c>
     </row>
     <row r="552" ht="20" customHeight="1">
@@ -14828,7 +14828,7 @@
         </is>
       </c>
       <c r="E552" s="20" t="n">
-        <v>146</v>
+        <v>123</v>
       </c>
     </row>
     <row r="553" ht="20" customHeight="1">
@@ -14853,7 +14853,7 @@
         </is>
       </c>
       <c r="E553" s="23" t="n">
-        <v>206</v>
+        <v>178</v>
       </c>
     </row>
     <row r="554" ht="20" customHeight="1">
@@ -14878,7 +14878,7 @@
         </is>
       </c>
       <c r="E554" s="20" t="n">
-        <v>233</v>
+        <v>149</v>
       </c>
     </row>
     <row r="555" ht="20" customHeight="1">
@@ -14903,7 +14903,7 @@
         </is>
       </c>
       <c r="E555" s="23" t="n">
-        <v>194</v>
+        <v>214</v>
       </c>
     </row>
     <row r="556" ht="20" customHeight="1">
@@ -14928,7 +14928,7 @@
         </is>
       </c>
       <c r="E556" s="20" t="n">
-        <v>127</v>
+        <v>176</v>
       </c>
     </row>
     <row r="557" ht="20" customHeight="1">
@@ -14953,7 +14953,7 @@
         </is>
       </c>
       <c r="E557" s="23" t="n">
-        <v>216</v>
+        <v>210</v>
       </c>
     </row>
     <row r="558" ht="20" customHeight="1">
@@ -14978,7 +14978,7 @@
         </is>
       </c>
       <c r="E558" s="20" t="n">
-        <v>230</v>
+        <v>110</v>
       </c>
     </row>
     <row r="559" ht="20" customHeight="1">
@@ -15003,7 +15003,7 @@
         </is>
       </c>
       <c r="E559" s="23" t="n">
-        <v>225</v>
+        <v>119</v>
       </c>
     </row>
     <row r="560" ht="20" customHeight="1">
@@ -15028,7 +15028,7 @@
         </is>
       </c>
       <c r="E560" s="20" t="n">
-        <v>144</v>
+        <v>218</v>
       </c>
     </row>
     <row r="561" ht="20" customHeight="1">
@@ -15053,7 +15053,7 @@
         </is>
       </c>
       <c r="E561" s="23" t="n">
-        <v>145</v>
+        <v>231</v>
       </c>
     </row>
     <row r="562" ht="20" customHeight="1">
@@ -15078,7 +15078,7 @@
         </is>
       </c>
       <c r="E562" s="20" t="n">
-        <v>155</v>
+        <v>182</v>
       </c>
     </row>
     <row r="563" ht="20" customHeight="1">
@@ -15103,7 +15103,7 @@
         </is>
       </c>
       <c r="E563" s="23" t="n">
-        <v>224</v>
+        <v>138</v>
       </c>
     </row>
     <row r="564" ht="20" customHeight="1">
@@ -15128,7 +15128,7 @@
         </is>
       </c>
       <c r="E564" s="20" t="n">
-        <v>178</v>
+        <v>237</v>
       </c>
     </row>
     <row r="565" ht="20" customHeight="1">
@@ -15153,7 +15153,7 @@
         </is>
       </c>
       <c r="E565" s="23" t="n">
-        <v>117</v>
+        <v>223</v>
       </c>
     </row>
     <row r="566" ht="20" customHeight="1">
@@ -15178,7 +15178,7 @@
         </is>
       </c>
       <c r="E566" s="20" t="n">
-        <v>167</v>
+        <v>206</v>
       </c>
     </row>
     <row r="567" ht="20" customHeight="1">
@@ -15203,7 +15203,7 @@
         </is>
       </c>
       <c r="E567" s="23" t="n">
-        <v>110</v>
+        <v>203</v>
       </c>
     </row>
     <row r="568" ht="20" customHeight="1">
@@ -15228,7 +15228,7 @@
         </is>
       </c>
       <c r="E568" s="20" t="n">
-        <v>181</v>
+        <v>115</v>
       </c>
     </row>
     <row r="569" ht="20" customHeight="1">
@@ -15253,7 +15253,7 @@
         </is>
       </c>
       <c r="E569" s="23" t="n">
-        <v>174</v>
+        <v>153</v>
       </c>
     </row>
     <row r="570" ht="20" customHeight="1">
@@ -15278,7 +15278,7 @@
         </is>
       </c>
       <c r="E570" s="20" t="n">
-        <v>122</v>
+        <v>236</v>
       </c>
     </row>
     <row r="571" ht="20" customHeight="1">
@@ -15303,7 +15303,7 @@
         </is>
       </c>
       <c r="E571" s="23" t="n">
-        <v>224</v>
+        <v>199</v>
       </c>
     </row>
     <row r="572" ht="20" customHeight="1">
@@ -15328,7 +15328,7 @@
         </is>
       </c>
       <c r="E572" s="20" t="n">
-        <v>185</v>
+        <v>223</v>
       </c>
     </row>
     <row r="573" ht="20" customHeight="1">
@@ -15353,7 +15353,7 @@
         </is>
       </c>
       <c r="E573" s="23" t="n">
-        <v>235</v>
+        <v>177</v>
       </c>
     </row>
     <row r="574" ht="20" customHeight="1">
@@ -15378,7 +15378,7 @@
         </is>
       </c>
       <c r="E574" s="20" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="575" ht="20" customHeight="1">
@@ -15403,7 +15403,7 @@
         </is>
       </c>
       <c r="E575" s="23" t="n">
-        <v>222</v>
+        <v>123</v>
       </c>
     </row>
     <row r="576" ht="20" customHeight="1">
@@ -15428,7 +15428,7 @@
         </is>
       </c>
       <c r="E576" s="20" t="n">
-        <v>143</v>
+        <v>152</v>
       </c>
     </row>
     <row r="577" ht="20" customHeight="1">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="E577" s="23" t="n">
-        <v>137</v>
+        <v>199</v>
       </c>
     </row>
     <row r="578" ht="20" customHeight="1">
@@ -15478,7 +15478,7 @@
         </is>
       </c>
       <c r="E578" s="20" t="n">
-        <v>219</v>
+        <v>143</v>
       </c>
     </row>
     <row r="579" ht="20" customHeight="1">
@@ -15503,7 +15503,7 @@
         </is>
       </c>
       <c r="E579" s="23" t="n">
-        <v>240</v>
+        <v>158</v>
       </c>
     </row>
     <row r="580" ht="20" customHeight="1">
@@ -15528,7 +15528,7 @@
         </is>
       </c>
       <c r="E580" s="20" t="n">
-        <v>177</v>
+        <v>159</v>
       </c>
     </row>
     <row r="581" ht="20" customHeight="1">
@@ -15553,7 +15553,7 @@
         </is>
       </c>
       <c r="E581" s="23" t="n">
-        <v>174</v>
+        <v>120</v>
       </c>
     </row>
     <row r="582" ht="20" customHeight="1">
@@ -15578,7 +15578,7 @@
         </is>
       </c>
       <c r="E582" s="20" t="n">
-        <v>141</v>
+        <v>225</v>
       </c>
     </row>
     <row r="583" ht="20" customHeight="1">
@@ -15603,7 +15603,7 @@
         </is>
       </c>
       <c r="E583" s="23" t="n">
-        <v>159</v>
+        <v>177</v>
       </c>
     </row>
     <row r="584" ht="20" customHeight="1">
@@ -15628,7 +15628,7 @@
         </is>
       </c>
       <c r="E584" s="20" t="n">
-        <v>213</v>
+        <v>141</v>
       </c>
     </row>
     <row r="585" ht="20" customHeight="1">
@@ -15653,7 +15653,7 @@
         </is>
       </c>
       <c r="E585" s="23" t="n">
-        <v>156</v>
+        <v>144</v>
       </c>
     </row>
     <row r="586" ht="20" customHeight="1">
@@ -15678,7 +15678,7 @@
         </is>
       </c>
       <c r="E586" s="20" t="n">
-        <v>110</v>
+        <v>119</v>
       </c>
     </row>
     <row r="587" ht="20" customHeight="1">
@@ -15703,7 +15703,7 @@
         </is>
       </c>
       <c r="E587" s="23" t="n">
-        <v>118</v>
+        <v>175</v>
       </c>
     </row>
     <row r="588" ht="20" customHeight="1">
@@ -15728,7 +15728,7 @@
         </is>
       </c>
       <c r="E588" s="20" t="n">
-        <v>188</v>
+        <v>240</v>
       </c>
     </row>
     <row r="589" ht="20" customHeight="1">
@@ -15753,7 +15753,7 @@
         </is>
       </c>
       <c r="E589" s="23" t="n">
-        <v>239</v>
+        <v>187</v>
       </c>
     </row>
     <row r="590" ht="20" customHeight="1">
@@ -15778,7 +15778,7 @@
         </is>
       </c>
       <c r="E590" s="20" t="n">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="591" ht="20" customHeight="1">
@@ -15803,7 +15803,7 @@
         </is>
       </c>
       <c r="E591" s="23" t="n">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="592" ht="20" customHeight="1">
@@ -15828,7 +15828,7 @@
         </is>
       </c>
       <c r="E592" s="20" t="n">
-        <v>150</v>
+        <v>238</v>
       </c>
     </row>
     <row r="593" ht="20" customHeight="1">
@@ -15853,7 +15853,7 @@
         </is>
       </c>
       <c r="E593" s="23" t="n">
-        <v>195</v>
+        <v>225</v>
       </c>
     </row>
     <row r="594" ht="20" customHeight="1">
@@ -15878,7 +15878,7 @@
         </is>
       </c>
       <c r="E594" s="20" t="n">
-        <v>152</v>
+        <v>197</v>
       </c>
     </row>
     <row r="595" ht="20" customHeight="1">
@@ -15903,7 +15903,7 @@
         </is>
       </c>
       <c r="E595" s="23" t="n">
-        <v>163</v>
+        <v>222</v>
       </c>
     </row>
     <row r="596" ht="20" customHeight="1">
@@ -15928,7 +15928,7 @@
         </is>
       </c>
       <c r="E596" s="20" t="n">
-        <v>222</v>
+        <v>179</v>
       </c>
     </row>
     <row r="597" ht="20" customHeight="1">
@@ -15953,7 +15953,7 @@
         </is>
       </c>
       <c r="E597" s="23" t="n">
-        <v>199</v>
+        <v>137</v>
       </c>
     </row>
     <row r="598" ht="20" customHeight="1">
@@ -15978,7 +15978,7 @@
         </is>
       </c>
       <c r="E598" s="20" t="n">
-        <v>163</v>
+        <v>191</v>
       </c>
     </row>
     <row r="599" ht="20" customHeight="1">
@@ -16003,7 +16003,7 @@
         </is>
       </c>
       <c r="E599" s="23" t="n">
-        <v>145</v>
+        <v>174</v>
       </c>
     </row>
     <row r="600" ht="20" customHeight="1">
@@ -16028,7 +16028,7 @@
         </is>
       </c>
       <c r="E600" s="20" t="n">
-        <v>178</v>
+        <v>154</v>
       </c>
     </row>
     <row r="601" ht="20" customHeight="1">
@@ -16053,7 +16053,7 @@
         </is>
       </c>
       <c r="E601" s="23" t="n">
-        <v>188</v>
+        <v>158</v>
       </c>
     </row>
     <row r="602" ht="20" customHeight="1">
@@ -16078,7 +16078,7 @@
         </is>
       </c>
       <c r="E602" s="20" t="n">
-        <v>210</v>
+        <v>189</v>
       </c>
     </row>
     <row r="603" ht="20" customHeight="1">
@@ -16103,7 +16103,7 @@
         </is>
       </c>
       <c r="E603" s="23" t="n">
-        <v>160</v>
+        <v>124</v>
       </c>
     </row>
     <row r="604" ht="20" customHeight="1">
@@ -16128,7 +16128,7 @@
         </is>
       </c>
       <c r="E604" s="20" t="n">
-        <v>127</v>
+        <v>237</v>
       </c>
     </row>
     <row r="605" ht="20" customHeight="1">
@@ -16153,7 +16153,7 @@
         </is>
       </c>
       <c r="E605" s="23" t="n">
-        <v>164</v>
+        <v>221</v>
       </c>
     </row>
     <row r="606" ht="20" customHeight="1">
@@ -16178,7 +16178,7 @@
         </is>
       </c>
       <c r="E606" s="20" t="n">
-        <v>163</v>
+        <v>143</v>
       </c>
     </row>
     <row r="607" ht="20" customHeight="1">
@@ -16203,7 +16203,7 @@
         </is>
       </c>
       <c r="E607" s="23" t="n">
-        <v>148</v>
+        <v>182</v>
       </c>
     </row>
     <row r="608" ht="20" customHeight="1">
@@ -16228,7 +16228,7 @@
         </is>
       </c>
       <c r="E608" s="20" t="n">
-        <v>144</v>
+        <v>235</v>
       </c>
     </row>
     <row r="609" ht="20" customHeight="1">
@@ -16253,7 +16253,7 @@
         </is>
       </c>
       <c r="E609" s="23" t="n">
-        <v>133</v>
+        <v>152</v>
       </c>
     </row>
     <row r="610" ht="20" customHeight="1">
@@ -16278,7 +16278,7 @@
         </is>
       </c>
       <c r="E610" s="20" t="n">
-        <v>223</v>
+        <v>145</v>
       </c>
     </row>
     <row r="611" ht="20" customHeight="1">
@@ -16303,7 +16303,7 @@
         </is>
       </c>
       <c r="E611" s="23" t="n">
-        <v>125</v>
+        <v>113</v>
       </c>
     </row>
     <row r="612" ht="20" customHeight="1">
@@ -16328,7 +16328,7 @@
         </is>
       </c>
       <c r="E612" s="20" t="n">
-        <v>136</v>
+        <v>169</v>
       </c>
     </row>
     <row r="613" ht="20" customHeight="1">
@@ -16353,7 +16353,7 @@
         </is>
       </c>
       <c r="E613" s="23" t="n">
-        <v>139</v>
+        <v>111</v>
       </c>
     </row>
     <row r="614" ht="20" customHeight="1">
@@ -16378,7 +16378,7 @@
         </is>
       </c>
       <c r="E614" s="20" t="n">
-        <v>139</v>
+        <v>227</v>
       </c>
     </row>
     <row r="615" ht="20" customHeight="1">
@@ -16403,7 +16403,7 @@
         </is>
       </c>
       <c r="E615" s="23" t="n">
-        <v>134</v>
+        <v>142</v>
       </c>
     </row>
     <row r="616" ht="20" customHeight="1">
@@ -16428,7 +16428,7 @@
         </is>
       </c>
       <c r="E616" s="20" t="n">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="617" ht="20" customHeight="1">
@@ -16453,7 +16453,7 @@
         </is>
       </c>
       <c r="E617" s="23" t="n">
-        <v>227</v>
+        <v>196</v>
       </c>
     </row>
     <row r="618" ht="20" customHeight="1">
@@ -16478,7 +16478,7 @@
         </is>
       </c>
       <c r="E618" s="20" t="n">
-        <v>222</v>
+        <v>152</v>
       </c>
     </row>
     <row r="619" ht="20" customHeight="1">
@@ -16503,7 +16503,7 @@
         </is>
       </c>
       <c r="E619" s="23" t="n">
-        <v>118</v>
+        <v>133</v>
       </c>
     </row>
     <row r="620" ht="20" customHeight="1">
@@ -16528,7 +16528,7 @@
         </is>
       </c>
       <c r="E620" s="20" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="621" ht="20" customHeight="1">
@@ -16553,7 +16553,7 @@
         </is>
       </c>
       <c r="E621" s="23" t="n">
-        <v>152</v>
+        <v>179</v>
       </c>
     </row>
     <row r="622" ht="20" customHeight="1">
@@ -16578,7 +16578,7 @@
         </is>
       </c>
       <c r="E622" s="20" t="n">
-        <v>185</v>
+        <v>196</v>
       </c>
     </row>
     <row r="623" ht="20" customHeight="1">
@@ -16603,7 +16603,7 @@
         </is>
       </c>
       <c r="E623" s="23" t="n">
-        <v>178</v>
+        <v>118</v>
       </c>
     </row>
     <row r="624" ht="20" customHeight="1">
@@ -16628,7 +16628,7 @@
         </is>
       </c>
       <c r="E624" s="20" t="n">
-        <v>188</v>
+        <v>200</v>
       </c>
     </row>
     <row r="625" ht="20" customHeight="1">
@@ -16653,7 +16653,7 @@
         </is>
       </c>
       <c r="E625" s="23" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="626" ht="20" customHeight="1">
@@ -16678,7 +16678,7 @@
         </is>
       </c>
       <c r="E626" s="20" t="n">
-        <v>181</v>
+        <v>121</v>
       </c>
     </row>
     <row r="627" ht="20" customHeight="1">
@@ -16703,7 +16703,7 @@
         </is>
       </c>
       <c r="E627" s="23" t="n">
-        <v>219</v>
+        <v>123</v>
       </c>
     </row>
     <row r="628" ht="20" customHeight="1">
@@ -16728,7 +16728,7 @@
         </is>
       </c>
       <c r="E628" s="20" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="629" ht="20" customHeight="1">
@@ -16753,7 +16753,7 @@
         </is>
       </c>
       <c r="E629" s="23" t="n">
-        <v>230</v>
+        <v>156</v>
       </c>
     </row>
     <row r="630" ht="20" customHeight="1">
@@ -16778,7 +16778,7 @@
         </is>
       </c>
       <c r="E630" s="20" t="n">
-        <v>132</v>
+        <v>152</v>
       </c>
     </row>
     <row r="631" ht="20" customHeight="1">
@@ -16803,7 +16803,7 @@
         </is>
       </c>
       <c r="E631" s="23" t="n">
-        <v>144</v>
+        <v>117</v>
       </c>
     </row>
     <row r="632" ht="20" customHeight="1">
@@ -16828,7 +16828,7 @@
         </is>
       </c>
       <c r="E632" s="20" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="633" ht="20" customHeight="1">
@@ -16853,7 +16853,7 @@
         </is>
       </c>
       <c r="E633" s="23" t="n">
-        <v>178</v>
+        <v>171</v>
       </c>
     </row>
     <row r="634" ht="20" customHeight="1">
@@ -16878,7 +16878,7 @@
         </is>
       </c>
       <c r="E634" s="20" t="n">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="635" ht="20" customHeight="1">
@@ -16903,7 +16903,7 @@
         </is>
       </c>
       <c r="E635" s="23" t="n">
-        <v>226</v>
+        <v>230</v>
       </c>
     </row>
     <row r="636" ht="20" customHeight="1">
@@ -16928,7 +16928,7 @@
         </is>
       </c>
       <c r="E636" s="20" t="n">
-        <v>138</v>
+        <v>211</v>
       </c>
     </row>
     <row r="637" ht="20" customHeight="1">
@@ -16953,7 +16953,7 @@
         </is>
       </c>
       <c r="E637" s="23" t="n">
-        <v>204</v>
+        <v>154</v>
       </c>
     </row>
     <row r="638" ht="20" customHeight="1">
@@ -16978,7 +16978,7 @@
         </is>
       </c>
       <c r="E638" s="20" t="n">
-        <v>200</v>
+        <v>122</v>
       </c>
     </row>
     <row r="639" ht="20" customHeight="1">
@@ -17003,7 +17003,7 @@
         </is>
       </c>
       <c r="E639" s="23" t="n">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="640" ht="20" customHeight="1">
@@ -17028,7 +17028,7 @@
         </is>
       </c>
       <c r="E640" s="20" t="n">
-        <v>211</v>
+        <v>165</v>
       </c>
     </row>
     <row r="641" ht="20" customHeight="1">
@@ -17053,7 +17053,7 @@
         </is>
       </c>
       <c r="E641" s="23" t="n">
-        <v>173</v>
+        <v>114</v>
       </c>
     </row>
     <row r="642" ht="20" customHeight="1">
@@ -17078,7 +17078,7 @@
         </is>
       </c>
       <c r="E642" s="20" t="n">
-        <v>147</v>
+        <v>218</v>
       </c>
     </row>
     <row r="643" ht="20" customHeight="1">
@@ -17103,7 +17103,7 @@
         </is>
       </c>
       <c r="E643" s="23" t="n">
-        <v>215</v>
+        <v>151</v>
       </c>
     </row>
     <row r="644" ht="20" customHeight="1">
@@ -17128,7 +17128,7 @@
         </is>
       </c>
       <c r="E644" s="20" t="n">
-        <v>239</v>
+        <v>125</v>
       </c>
     </row>
     <row r="645" ht="20" customHeight="1">
@@ -17153,7 +17153,7 @@
         </is>
       </c>
       <c r="E645" s="23" t="n">
-        <v>165</v>
+        <v>155</v>
       </c>
     </row>
     <row r="646" ht="20" customHeight="1">
@@ -17178,7 +17178,7 @@
         </is>
       </c>
       <c r="E646" s="20" t="n">
-        <v>225</v>
+        <v>114</v>
       </c>
     </row>
     <row r="647" ht="20" customHeight="1">
@@ -17203,7 +17203,7 @@
         </is>
       </c>
       <c r="E647" s="23" t="n">
-        <v>119</v>
+        <v>134</v>
       </c>
     </row>
     <row r="648" ht="20" customHeight="1">
@@ -17228,7 +17228,7 @@
         </is>
       </c>
       <c r="E648" s="20" t="n">
-        <v>211</v>
+        <v>160</v>
       </c>
     </row>
     <row r="649" ht="20" customHeight="1">
@@ -17253,7 +17253,7 @@
         </is>
       </c>
       <c r="E649" s="23" t="n">
-        <v>177</v>
+        <v>222</v>
       </c>
     </row>
     <row r="650" ht="20" customHeight="1">
@@ -17278,7 +17278,7 @@
         </is>
       </c>
       <c r="E650" s="20" t="n">
-        <v>192</v>
+        <v>227</v>
       </c>
     </row>
     <row r="651" ht="20" customHeight="1">
@@ -17303,7 +17303,7 @@
         </is>
       </c>
       <c r="E651" s="23" t="n">
-        <v>199</v>
+        <v>146</v>
       </c>
     </row>
     <row r="652" ht="20" customHeight="1">
@@ -17328,7 +17328,7 @@
         </is>
       </c>
       <c r="E652" s="20" t="n">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="653" ht="20" customHeight="1">
@@ -17353,7 +17353,7 @@
         </is>
       </c>
       <c r="E653" s="23" t="n">
-        <v>121</v>
+        <v>182</v>
       </c>
     </row>
     <row r="654" ht="20" customHeight="1">
@@ -17378,7 +17378,7 @@
         </is>
       </c>
       <c r="E654" s="20" t="n">
-        <v>133</v>
+        <v>117</v>
       </c>
     </row>
     <row r="655" ht="20" customHeight="1">
@@ -17403,7 +17403,7 @@
         </is>
       </c>
       <c r="E655" s="23" t="n">
-        <v>204</v>
+        <v>171</v>
       </c>
     </row>
     <row r="656" ht="20" customHeight="1">
@@ -17428,7 +17428,7 @@
         </is>
       </c>
       <c r="E656" s="20" t="n">
-        <v>165</v>
+        <v>144</v>
       </c>
     </row>
     <row r="657" ht="20" customHeight="1">
@@ -17453,7 +17453,7 @@
         </is>
       </c>
       <c r="E657" s="23" t="n">
-        <v>218</v>
+        <v>126</v>
       </c>
     </row>
     <row r="658" ht="20" customHeight="1">
@@ -17478,7 +17478,7 @@
         </is>
       </c>
       <c r="E658" s="20" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="659" ht="20" customHeight="1">
@@ -17503,7 +17503,7 @@
         </is>
       </c>
       <c r="E659" s="23" t="n">
-        <v>191</v>
+        <v>217</v>
       </c>
     </row>
     <row r="660" ht="20" customHeight="1">
@@ -17528,7 +17528,7 @@
         </is>
       </c>
       <c r="E660" s="20" t="n">
-        <v>154</v>
+        <v>181</v>
       </c>
     </row>
     <row r="661" ht="20" customHeight="1">
@@ -17553,7 +17553,7 @@
         </is>
       </c>
       <c r="E661" s="23" t="n">
-        <v>142</v>
+        <v>135</v>
       </c>
     </row>
     <row r="662" ht="20" customHeight="1">
@@ -17578,7 +17578,7 @@
         </is>
       </c>
       <c r="E662" s="20" t="n">
-        <v>229</v>
+        <v>196</v>
       </c>
     </row>
     <row r="663" ht="20" customHeight="1">
@@ -17603,7 +17603,7 @@
         </is>
       </c>
       <c r="E663" s="23" t="n">
-        <v>167</v>
+        <v>218</v>
       </c>
     </row>
     <row r="664" ht="20" customHeight="1">
@@ -17628,7 +17628,7 @@
         </is>
       </c>
       <c r="E664" s="20" t="n">
-        <v>120</v>
+        <v>155</v>
       </c>
     </row>
     <row r="665" ht="20" customHeight="1">
@@ -17653,7 +17653,7 @@
         </is>
       </c>
       <c r="E665" s="23" t="n">
-        <v>233</v>
+        <v>156</v>
       </c>
     </row>
     <row r="666" ht="20" customHeight="1">
@@ -17678,7 +17678,7 @@
         </is>
       </c>
       <c r="E666" s="20" t="n">
-        <v>178</v>
+        <v>216</v>
       </c>
     </row>
     <row r="667" ht="20" customHeight="1">
@@ -17703,7 +17703,7 @@
         </is>
       </c>
       <c r="E667" s="23" t="n">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="668" ht="20" customHeight="1">
@@ -17728,7 +17728,7 @@
         </is>
       </c>
       <c r="E668" s="20" t="n">
-        <v>146</v>
+        <v>207</v>
       </c>
     </row>
     <row r="669" ht="20" customHeight="1">
@@ -17753,7 +17753,7 @@
         </is>
       </c>
       <c r="E669" s="23" t="n">
-        <v>198</v>
+        <v>219</v>
       </c>
     </row>
     <row r="670" ht="20" customHeight="1">
@@ -17778,7 +17778,7 @@
         </is>
       </c>
       <c r="E670" s="20" t="n">
-        <v>148</v>
+        <v>117</v>
       </c>
     </row>
     <row r="671" ht="20" customHeight="1">
@@ -17803,7 +17803,7 @@
         </is>
       </c>
       <c r="E671" s="23" t="n">
-        <v>146</v>
+        <v>212</v>
       </c>
     </row>
     <row r="672" ht="20" customHeight="1">
@@ -17828,7 +17828,7 @@
         </is>
       </c>
       <c r="E672" s="20" t="n">
-        <v>194</v>
+        <v>150</v>
       </c>
     </row>
     <row r="673" ht="20" customHeight="1">
@@ -17853,7 +17853,7 @@
         </is>
       </c>
       <c r="E673" s="23" t="n">
-        <v>124</v>
+        <v>164</v>
       </c>
     </row>
     <row r="674" ht="20" customHeight="1">
@@ -17878,7 +17878,7 @@
         </is>
       </c>
       <c r="E674" s="20" t="n">
-        <v>167</v>
+        <v>221</v>
       </c>
     </row>
     <row r="675" ht="20" customHeight="1">
@@ -17903,7 +17903,7 @@
         </is>
       </c>
       <c r="E675" s="23" t="n">
-        <v>117</v>
+        <v>150</v>
       </c>
     </row>
     <row r="676" ht="20" customHeight="1">
@@ -17928,7 +17928,7 @@
         </is>
       </c>
       <c r="E676" s="20" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="677" ht="20" customHeight="1">
@@ -17953,7 +17953,7 @@
         </is>
       </c>
       <c r="E677" s="23" t="n">
-        <v>129</v>
+        <v>136</v>
       </c>
     </row>
     <row r="678" ht="20" customHeight="1">
@@ -17978,7 +17978,7 @@
         </is>
       </c>
       <c r="E678" s="20" t="n">
-        <v>169</v>
+        <v>151</v>
       </c>
     </row>
     <row r="679" ht="20" customHeight="1">
@@ -18003,7 +18003,7 @@
         </is>
       </c>
       <c r="E679" s="23" t="n">
-        <v>176</v>
+        <v>172</v>
       </c>
     </row>
     <row r="680" ht="20" customHeight="1">
@@ -18028,7 +18028,7 @@
         </is>
       </c>
       <c r="E680" s="20" t="n">
-        <v>189</v>
+        <v>210</v>
       </c>
     </row>
     <row r="681" ht="20" customHeight="1">
@@ -18053,7 +18053,7 @@
         </is>
       </c>
       <c r="E681" s="23" t="n">
-        <v>238</v>
+        <v>208</v>
       </c>
     </row>
     <row r="682" ht="20" customHeight="1">
@@ -18078,7 +18078,7 @@
         </is>
       </c>
       <c r="E682" s="20" t="n">
-        <v>149</v>
+        <v>111</v>
       </c>
     </row>
     <row r="683" ht="20" customHeight="1">
@@ -18103,7 +18103,7 @@
         </is>
       </c>
       <c r="E683" s="23" t="n">
-        <v>142</v>
+        <v>176</v>
       </c>
     </row>
     <row r="684" ht="20" customHeight="1">
@@ -18128,7 +18128,7 @@
         </is>
       </c>
       <c r="E684" s="20" t="n">
-        <v>189</v>
+        <v>201</v>
       </c>
     </row>
     <row r="685" ht="20" customHeight="1">
@@ -18153,7 +18153,7 @@
         </is>
       </c>
       <c r="E685" s="23" t="n">
-        <v>133</v>
+        <v>175</v>
       </c>
     </row>
     <row r="686" ht="20" customHeight="1">
@@ -18178,7 +18178,7 @@
         </is>
       </c>
       <c r="E686" s="20" t="n">
-        <v>223</v>
+        <v>130</v>
       </c>
     </row>
     <row r="687" ht="20" customHeight="1">
@@ -18203,7 +18203,7 @@
         </is>
       </c>
       <c r="E687" s="23" t="n">
-        <v>137</v>
+        <v>207</v>
       </c>
     </row>
     <row r="688" ht="20" customHeight="1">
@@ -18228,7 +18228,7 @@
         </is>
       </c>
       <c r="E688" s="20" t="n">
-        <v>219</v>
+        <v>188</v>
       </c>
     </row>
     <row r="689" ht="20" customHeight="1">
@@ -18253,7 +18253,7 @@
         </is>
       </c>
       <c r="E689" s="23" t="n">
-        <v>204</v>
+        <v>237</v>
       </c>
     </row>
     <row r="690" ht="20" customHeight="1">
@@ -18278,7 +18278,7 @@
         </is>
       </c>
       <c r="E690" s="20" t="n">
-        <v>140</v>
+        <v>213</v>
       </c>
     </row>
     <row r="691" ht="20" customHeight="1">
@@ -18303,7 +18303,7 @@
         </is>
       </c>
       <c r="E691" s="23" t="n">
-        <v>165</v>
+        <v>199</v>
       </c>
     </row>
     <row r="692" ht="20" customHeight="1">
@@ -18328,7 +18328,7 @@
         </is>
       </c>
       <c r="E692" s="20" t="n">
-        <v>232</v>
+        <v>126</v>
       </c>
     </row>
     <row r="693" ht="20" customHeight="1">
@@ -18353,7 +18353,7 @@
         </is>
       </c>
       <c r="E693" s="23" t="n">
-        <v>113</v>
+        <v>219</v>
       </c>
     </row>
     <row r="694" ht="20" customHeight="1">
@@ -18378,7 +18378,7 @@
         </is>
       </c>
       <c r="E694" s="20" t="n">
-        <v>154</v>
+        <v>132</v>
       </c>
     </row>
     <row r="695" ht="20" customHeight="1">
@@ -18403,7 +18403,7 @@
         </is>
       </c>
       <c r="E695" s="23" t="n">
-        <v>236</v>
+        <v>162</v>
       </c>
     </row>
     <row r="696" ht="20" customHeight="1">
@@ -18428,7 +18428,7 @@
         </is>
       </c>
       <c r="E696" s="20" t="n">
-        <v>177</v>
+        <v>126</v>
       </c>
     </row>
     <row r="697" ht="20" customHeight="1">
@@ -18453,7 +18453,7 @@
         </is>
       </c>
       <c r="E697" s="23" t="n">
-        <v>152</v>
+        <v>133</v>
       </c>
     </row>
     <row r="698" ht="20" customHeight="1">
@@ -18478,7 +18478,7 @@
         </is>
       </c>
       <c r="E698" s="20" t="n">
-        <v>231</v>
+        <v>122</v>
       </c>
     </row>
     <row r="699" ht="20" customHeight="1">
@@ -18503,7 +18503,7 @@
         </is>
       </c>
       <c r="E699" s="23" t="n">
-        <v>219</v>
+        <v>153</v>
       </c>
     </row>
     <row r="700" ht="20" customHeight="1">
@@ -18528,7 +18528,7 @@
         </is>
       </c>
       <c r="E700" s="20" t="n">
-        <v>114</v>
+        <v>128</v>
       </c>
     </row>
     <row r="701" ht="20" customHeight="1">
@@ -18553,7 +18553,7 @@
         </is>
       </c>
       <c r="E701" s="23" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="702" ht="20" customHeight="1">
@@ -18578,7 +18578,7 @@
         </is>
       </c>
       <c r="E702" s="20" t="n">
-        <v>224</v>
+        <v>186</v>
       </c>
     </row>
     <row r="703" ht="20" customHeight="1">
@@ -18603,7 +18603,7 @@
         </is>
       </c>
       <c r="E703" s="23" t="n">
-        <v>236</v>
+        <v>168</v>
       </c>
     </row>
     <row r="704" ht="20" customHeight="1">
@@ -18628,7 +18628,7 @@
         </is>
       </c>
       <c r="E704" s="20" t="n">
-        <v>120</v>
+        <v>169</v>
       </c>
     </row>
     <row r="705" ht="20" customHeight="1">
@@ -18653,7 +18653,7 @@
         </is>
       </c>
       <c r="E705" s="23" t="n">
-        <v>192</v>
+        <v>236</v>
       </c>
     </row>
     <row r="706" ht="20" customHeight="1">
@@ -18678,7 +18678,7 @@
         </is>
       </c>
       <c r="E706" s="20" t="n">
-        <v>173</v>
+        <v>194</v>
       </c>
     </row>
     <row r="707" ht="20" customHeight="1">
@@ -18703,7 +18703,7 @@
         </is>
       </c>
       <c r="E707" s="23" t="n">
-        <v>202</v>
+        <v>194</v>
       </c>
     </row>
     <row r="708" ht="20" customHeight="1">
@@ -18728,7 +18728,7 @@
         </is>
       </c>
       <c r="E708" s="20" t="n">
-        <v>204</v>
+        <v>189</v>
       </c>
     </row>
     <row r="709" ht="20" customHeight="1">
@@ -18753,7 +18753,7 @@
         </is>
       </c>
       <c r="E709" s="23" t="n">
-        <v>209</v>
+        <v>118</v>
       </c>
     </row>
     <row r="710" ht="20" customHeight="1">
@@ -18778,7 +18778,7 @@
         </is>
       </c>
       <c r="E710" s="20" t="n">
-        <v>176</v>
+        <v>204</v>
       </c>
     </row>
     <row r="711" ht="20" customHeight="1">
@@ -18803,7 +18803,7 @@
         </is>
       </c>
       <c r="E711" s="23" t="n">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="712" ht="20" customHeight="1">
@@ -18828,7 +18828,7 @@
         </is>
       </c>
       <c r="E712" s="20" t="n">
-        <v>164</v>
+        <v>169</v>
       </c>
     </row>
     <row r="713" ht="20" customHeight="1">
@@ -18853,7 +18853,7 @@
         </is>
       </c>
       <c r="E713" s="23" t="n">
-        <v>212</v>
+        <v>114</v>
       </c>
     </row>
     <row r="714" ht="20" customHeight="1">
@@ -18878,7 +18878,7 @@
         </is>
       </c>
       <c r="E714" s="20" t="n">
-        <v>168</v>
+        <v>236</v>
       </c>
     </row>
     <row r="715" ht="20" customHeight="1">
@@ -18903,7 +18903,7 @@
         </is>
       </c>
       <c r="E715" s="23" t="n">
-        <v>176</v>
+        <v>166</v>
       </c>
     </row>
     <row r="716" ht="20" customHeight="1">
@@ -18928,7 +18928,7 @@
         </is>
       </c>
       <c r="E716" s="20" t="n">
-        <v>155</v>
+        <v>148</v>
       </c>
     </row>
     <row r="717" ht="20" customHeight="1">
@@ -18953,7 +18953,7 @@
         </is>
       </c>
       <c r="E717" s="23" t="n">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="718" ht="20" customHeight="1">
@@ -18978,7 +18978,7 @@
         </is>
       </c>
       <c r="E718" s="20" t="n">
-        <v>196</v>
+        <v>217</v>
       </c>
     </row>
     <row r="719" ht="20" customHeight="1">
@@ -19003,7 +19003,7 @@
         </is>
       </c>
       <c r="E719" s="23" t="n">
-        <v>219</v>
+        <v>110</v>
       </c>
     </row>
     <row r="720" ht="20" customHeight="1">
@@ -19028,7 +19028,7 @@
         </is>
       </c>
       <c r="E720" s="20" t="n">
-        <v>235</v>
+        <v>185</v>
       </c>
     </row>
     <row r="721" ht="20" customHeight="1">
@@ -19053,7 +19053,7 @@
         </is>
       </c>
       <c r="E721" s="23" t="n">
-        <v>192</v>
+        <v>225</v>
       </c>
     </row>
     <row r="722" ht="20" customHeight="1">
@@ -19078,7 +19078,7 @@
         </is>
       </c>
       <c r="E722" s="20" t="n">
-        <v>143</v>
+        <v>113</v>
       </c>
     </row>
     <row r="723" ht="20" customHeight="1">
@@ -19103,7 +19103,7 @@
         </is>
       </c>
       <c r="E723" s="23" t="n">
-        <v>184</v>
+        <v>134</v>
       </c>
     </row>
     <row r="724" ht="20" customHeight="1">
@@ -19128,7 +19128,7 @@
         </is>
       </c>
       <c r="E724" s="20" t="n">
-        <v>171</v>
+        <v>137</v>
       </c>
     </row>
     <row r="725" ht="20" customHeight="1">
@@ -19153,7 +19153,7 @@
         </is>
       </c>
       <c r="E725" s="23" t="n">
-        <v>115</v>
+        <v>212</v>
       </c>
     </row>
     <row r="726" ht="20" customHeight="1">
@@ -19178,7 +19178,7 @@
         </is>
       </c>
       <c r="E726" s="20" t="n">
-        <v>231</v>
+        <v>205</v>
       </c>
     </row>
     <row r="727" ht="20" customHeight="1">
@@ -19203,7 +19203,7 @@
         </is>
       </c>
       <c r="E727" s="23" t="n">
-        <v>128</v>
+        <v>228</v>
       </c>
     </row>
     <row r="728" ht="20" customHeight="1">
@@ -19228,7 +19228,7 @@
         </is>
       </c>
       <c r="E728" s="20" t="n">
-        <v>195</v>
+        <v>235</v>
       </c>
     </row>
     <row r="729" ht="20" customHeight="1">
@@ -19253,7 +19253,7 @@
         </is>
       </c>
       <c r="E729" s="23" t="n">
-        <v>205</v>
+        <v>231</v>
       </c>
     </row>
     <row r="730" ht="20" customHeight="1">
@@ -19278,7 +19278,7 @@
         </is>
       </c>
       <c r="E730" s="20" t="n">
-        <v>146</v>
+        <v>179</v>
       </c>
     </row>
     <row r="731" ht="20" customHeight="1">
@@ -19303,7 +19303,7 @@
         </is>
       </c>
       <c r="E731" s="23" t="n">
-        <v>134</v>
+        <v>168</v>
       </c>
     </row>
     <row r="732" ht="20" customHeight="1">
@@ -19328,7 +19328,7 @@
         </is>
       </c>
       <c r="E732" s="20" t="n">
-        <v>236</v>
+        <v>151</v>
       </c>
     </row>
     <row r="733" ht="20" customHeight="1">
@@ -19353,7 +19353,7 @@
         </is>
       </c>
       <c r="E733" s="23" t="n">
-        <v>161</v>
+        <v>238</v>
       </c>
     </row>
     <row r="734" ht="20" customHeight="1">
@@ -19378,7 +19378,7 @@
         </is>
       </c>
       <c r="E734" s="20" t="n">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="735" ht="20" customHeight="1">
@@ -19403,7 +19403,7 @@
         </is>
       </c>
       <c r="E735" s="23" t="n">
-        <v>148</v>
+        <v>218</v>
       </c>
     </row>
     <row r="736" ht="20" customHeight="1">
@@ -19428,7 +19428,7 @@
         </is>
       </c>
       <c r="E736" s="20" t="n">
-        <v>147</v>
+        <v>131</v>
       </c>
     </row>
     <row r="737" ht="20" customHeight="1">
@@ -19453,7 +19453,7 @@
         </is>
       </c>
       <c r="E737" s="23" t="n">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="738" ht="20" customHeight="1">
@@ -19478,7 +19478,7 @@
         </is>
       </c>
       <c r="E738" s="20" t="n">
-        <v>183</v>
+        <v>170</v>
       </c>
     </row>
     <row r="739" ht="20" customHeight="1">
@@ -19503,7 +19503,7 @@
         </is>
       </c>
       <c r="E739" s="23" t="n">
-        <v>185</v>
+        <v>175</v>
       </c>
     </row>
     <row r="740" ht="20" customHeight="1">
@@ -19528,7 +19528,7 @@
         </is>
       </c>
       <c r="E740" s="20" t="n">
-        <v>218</v>
+        <v>196</v>
       </c>
     </row>
     <row r="741" ht="20" customHeight="1">
@@ -19553,7 +19553,7 @@
         </is>
       </c>
       <c r="E741" s="23" t="n">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="742" ht="20" customHeight="1">
@@ -19578,7 +19578,7 @@
         </is>
       </c>
       <c r="E742" s="20" t="n">
-        <v>180</v>
+        <v>143</v>
       </c>
     </row>
     <row r="743" ht="20" customHeight="1">
@@ -19603,7 +19603,7 @@
         </is>
       </c>
       <c r="E743" s="23" t="n">
-        <v>195</v>
+        <v>161</v>
       </c>
     </row>
     <row r="744" ht="20" customHeight="1">
@@ -19628,7 +19628,7 @@
         </is>
       </c>
       <c r="E744" s="20" t="n">
-        <v>231</v>
+        <v>203</v>
       </c>
     </row>
     <row r="745" ht="20" customHeight="1">
@@ -19653,7 +19653,7 @@
         </is>
       </c>
       <c r="E745" s="23" t="n">
-        <v>117</v>
+        <v>146</v>
       </c>
     </row>
     <row r="746" ht="20" customHeight="1">
@@ -19678,7 +19678,7 @@
         </is>
       </c>
       <c r="E746" s="20" t="n">
-        <v>211</v>
+        <v>176</v>
       </c>
     </row>
     <row r="747" ht="20" customHeight="1">
@@ -19703,7 +19703,7 @@
         </is>
       </c>
       <c r="E747" s="23" t="n">
-        <v>117</v>
+        <v>226</v>
       </c>
     </row>
     <row r="748" ht="20" customHeight="1">
@@ -19728,7 +19728,7 @@
         </is>
       </c>
       <c r="E748" s="20" t="n">
-        <v>232</v>
+        <v>113</v>
       </c>
     </row>
     <row r="749" ht="20" customHeight="1">
@@ -19753,7 +19753,7 @@
         </is>
       </c>
       <c r="E749" s="23" t="n">
-        <v>227</v>
+        <v>234</v>
       </c>
     </row>
     <row r="750" ht="20" customHeight="1">
@@ -19778,7 +19778,7 @@
         </is>
       </c>
       <c r="E750" s="20" t="n">
-        <v>121</v>
+        <v>212</v>
       </c>
     </row>
     <row r="751" ht="20" customHeight="1">
@@ -19803,7 +19803,7 @@
         </is>
       </c>
       <c r="E751" s="23" t="n">
-        <v>209</v>
+        <v>192</v>
       </c>
     </row>
     <row r="752" ht="20" customHeight="1">
@@ -19828,7 +19828,7 @@
         </is>
       </c>
       <c r="E752" s="20" t="n">
-        <v>168</v>
+        <v>189</v>
       </c>
     </row>
     <row r="753" ht="20" customHeight="1">
@@ -19853,7 +19853,7 @@
         </is>
       </c>
       <c r="E753" s="23" t="n">
-        <v>131</v>
+        <v>170</v>
       </c>
     </row>
     <row r="754" ht="20" customHeight="1">
@@ -19878,7 +19878,7 @@
         </is>
       </c>
       <c r="E754" s="20" t="n">
-        <v>142</v>
+        <v>130</v>
       </c>
     </row>
     <row r="755" ht="20" customHeight="1">
@@ -19903,7 +19903,7 @@
         </is>
       </c>
       <c r="E755" s="23" t="n">
-        <v>234</v>
+        <v>133</v>
       </c>
     </row>
     <row r="756" ht="20" customHeight="1">
@@ -19928,7 +19928,7 @@
         </is>
       </c>
       <c r="E756" s="20" t="n">
-        <v>210</v>
+        <v>201</v>
       </c>
     </row>
     <row r="757" ht="20" customHeight="1">
@@ -19953,7 +19953,7 @@
         </is>
       </c>
       <c r="E757" s="23" t="n">
-        <v>205</v>
+        <v>224</v>
       </c>
     </row>
     <row r="758" ht="20" customHeight="1">
@@ -19978,7 +19978,7 @@
         </is>
       </c>
       <c r="E758" s="20" t="n">
-        <v>113</v>
+        <v>181</v>
       </c>
     </row>
     <row r="759" ht="20" customHeight="1">
@@ -20003,7 +20003,7 @@
         </is>
       </c>
       <c r="E759" s="23" t="n">
-        <v>151</v>
+        <v>216</v>
       </c>
     </row>
     <row r="760" ht="20" customHeight="1">
@@ -20028,7 +20028,7 @@
         </is>
       </c>
       <c r="E760" s="20" t="n">
-        <v>239</v>
+        <v>177</v>
       </c>
     </row>
     <row r="761" ht="20" customHeight="1">
@@ -20053,7 +20053,7 @@
         </is>
       </c>
       <c r="E761" s="23" t="n">
-        <v>157</v>
+        <v>192</v>
       </c>
     </row>
     <row r="762" ht="20" customHeight="1">
@@ -20078,7 +20078,7 @@
         </is>
       </c>
       <c r="E762" s="20" t="n">
-        <v>119</v>
+        <v>198</v>
       </c>
     </row>
     <row r="763" ht="20" customHeight="1">
@@ -20103,7 +20103,7 @@
         </is>
       </c>
       <c r="E763" s="23" t="n">
-        <v>239</v>
+        <v>233</v>
       </c>
     </row>
     <row r="764" ht="20" customHeight="1">
@@ -20128,7 +20128,7 @@
         </is>
       </c>
       <c r="E764" s="20" t="n">
-        <v>225</v>
+        <v>148</v>
       </c>
     </row>
     <row r="765" ht="20" customHeight="1">
@@ -20153,7 +20153,7 @@
         </is>
       </c>
       <c r="E765" s="23" t="n">
-        <v>123</v>
+        <v>239</v>
       </c>
     </row>
     <row r="766" ht="20" customHeight="1">
@@ -20178,7 +20178,7 @@
         </is>
       </c>
       <c r="E766" s="20" t="n">
-        <v>202</v>
+        <v>140</v>
       </c>
     </row>
     <row r="767" ht="20" customHeight="1">
@@ -20203,7 +20203,7 @@
         </is>
       </c>
       <c r="E767" s="23" t="n">
-        <v>171</v>
+        <v>161</v>
       </c>
     </row>
     <row r="768" ht="20" customHeight="1">
@@ -20228,7 +20228,7 @@
         </is>
       </c>
       <c r="E768" s="20" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="769" ht="20" customHeight="1">
@@ -20253,7 +20253,7 @@
         </is>
       </c>
       <c r="E769" s="23" t="n">
-        <v>122</v>
+        <v>231</v>
       </c>
     </row>
     <row r="770" ht="20" customHeight="1">
@@ -20278,7 +20278,7 @@
         </is>
       </c>
       <c r="E770" s="20" t="n">
-        <v>215</v>
+        <v>169</v>
       </c>
     </row>
     <row r="771" ht="20" customHeight="1">
@@ -20303,7 +20303,7 @@
         </is>
       </c>
       <c r="E771" s="23" t="n">
-        <v>145</v>
+        <v>112</v>
       </c>
     </row>
     <row r="772" ht="20" customHeight="1">
@@ -20328,7 +20328,7 @@
         </is>
       </c>
       <c r="E772" s="20" t="n">
-        <v>184</v>
+        <v>233</v>
       </c>
     </row>
     <row r="773" ht="20" customHeight="1">
@@ -20353,7 +20353,7 @@
         </is>
       </c>
       <c r="E773" s="23" t="n">
-        <v>144</v>
+        <v>185</v>
       </c>
     </row>
     <row r="774" ht="20" customHeight="1">
@@ -20378,7 +20378,7 @@
         </is>
       </c>
       <c r="E774" s="20" t="n">
-        <v>140</v>
+        <v>220</v>
       </c>
     </row>
     <row r="775" ht="20" customHeight="1">
@@ -20403,7 +20403,7 @@
         </is>
       </c>
       <c r="E775" s="23" t="n">
-        <v>209</v>
+        <v>124</v>
       </c>
     </row>
     <row r="776" ht="20" customHeight="1">
@@ -20428,7 +20428,7 @@
         </is>
       </c>
       <c r="E776" s="20" t="n">
-        <v>190</v>
+        <v>132</v>
       </c>
     </row>
     <row r="777" ht="20" customHeight="1">
@@ -20453,7 +20453,7 @@
         </is>
       </c>
       <c r="E777" s="23" t="n">
-        <v>168</v>
+        <v>209</v>
       </c>
     </row>
     <row r="778" ht="20" customHeight="1">
@@ -20478,7 +20478,7 @@
         </is>
       </c>
       <c r="E778" s="20" t="n">
-        <v>191</v>
+        <v>153</v>
       </c>
     </row>
     <row r="779" ht="20" customHeight="1">
@@ -20503,7 +20503,7 @@
         </is>
       </c>
       <c r="E779" s="23" t="n">
-        <v>111</v>
+        <v>174</v>
       </c>
     </row>
     <row r="780" ht="20" customHeight="1">
@@ -20528,7 +20528,7 @@
         </is>
       </c>
       <c r="E780" s="20" t="n">
-        <v>183</v>
+        <v>112</v>
       </c>
     </row>
     <row r="781" ht="20" customHeight="1">
@@ -20553,7 +20553,7 @@
         </is>
       </c>
       <c r="E781" s="23" t="n">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="782" ht="20" customHeight="1">
@@ -20578,7 +20578,7 @@
         </is>
       </c>
       <c r="E782" s="20" t="n">
-        <v>223</v>
+        <v>150</v>
       </c>
     </row>
     <row r="783" ht="20" customHeight="1">
@@ -20603,7 +20603,7 @@
         </is>
       </c>
       <c r="E783" s="23" t="n">
-        <v>163</v>
+        <v>169</v>
       </c>
     </row>
     <row r="784" ht="20" customHeight="1">
@@ -20628,7 +20628,7 @@
         </is>
       </c>
       <c r="E784" s="20" t="n">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="785" ht="20" customHeight="1">
@@ -20653,7 +20653,7 @@
         </is>
       </c>
       <c r="E785" s="23" t="n">
-        <v>205</v>
+        <v>131</v>
       </c>
     </row>
     <row r="786" ht="20" customHeight="1">
@@ -20678,7 +20678,7 @@
         </is>
       </c>
       <c r="E786" s="20" t="n">
-        <v>200</v>
+        <v>184</v>
       </c>
     </row>
     <row r="787" ht="20" customHeight="1">
@@ -20703,7 +20703,7 @@
         </is>
       </c>
       <c r="E787" s="23" t="n">
-        <v>203</v>
+        <v>132</v>
       </c>
     </row>
     <row r="788" ht="20" customHeight="1">
@@ -20728,7 +20728,7 @@
         </is>
       </c>
       <c r="E788" s="20" t="n">
-        <v>162</v>
+        <v>179</v>
       </c>
     </row>
     <row r="789" ht="20" customHeight="1">
@@ -20753,7 +20753,7 @@
         </is>
       </c>
       <c r="E789" s="23" t="n">
-        <v>195</v>
+        <v>156</v>
       </c>
     </row>
     <row r="790" ht="20" customHeight="1">
@@ -20778,7 +20778,7 @@
         </is>
       </c>
       <c r="E790" s="20" t="n">
-        <v>165</v>
+        <v>113</v>
       </c>
     </row>
     <row r="791" ht="20" customHeight="1">
@@ -20803,7 +20803,7 @@
         </is>
       </c>
       <c r="E791" s="23" t="n">
-        <v>199</v>
+        <v>234</v>
       </c>
     </row>
     <row r="792" ht="20" customHeight="1">
@@ -20828,7 +20828,7 @@
         </is>
       </c>
       <c r="E792" s="20" t="n">
-        <v>145</v>
+        <v>113</v>
       </c>
     </row>
     <row r="793" ht="20" customHeight="1">
@@ -20853,7 +20853,7 @@
         </is>
       </c>
       <c r="E793" s="23" t="n">
-        <v>138</v>
+        <v>207</v>
       </c>
     </row>
     <row r="794" ht="20" customHeight="1">
@@ -20878,7 +20878,7 @@
         </is>
       </c>
       <c r="E794" s="20" t="n">
-        <v>239</v>
+        <v>224</v>
       </c>
     </row>
     <row r="795" ht="20" customHeight="1">
@@ -20903,7 +20903,7 @@
         </is>
       </c>
       <c r="E795" s="23" t="n">
-        <v>155</v>
+        <v>117</v>
       </c>
     </row>
     <row r="796" ht="20" customHeight="1">
@@ -20928,7 +20928,7 @@
         </is>
       </c>
       <c r="E796" s="20" t="n">
-        <v>223</v>
+        <v>213</v>
       </c>
     </row>
     <row r="797" ht="20" customHeight="1">
@@ -20953,7 +20953,7 @@
         </is>
       </c>
       <c r="E797" s="23" t="n">
-        <v>111</v>
+        <v>150</v>
       </c>
     </row>
     <row r="798" ht="20" customHeight="1">
@@ -20978,7 +20978,7 @@
         </is>
       </c>
       <c r="E798" s="20" t="n">
-        <v>237</v>
+        <v>202</v>
       </c>
     </row>
     <row r="799" ht="20" customHeight="1">
@@ -21003,7 +21003,7 @@
         </is>
       </c>
       <c r="E799" s="23" t="n">
-        <v>195</v>
+        <v>187</v>
       </c>
     </row>
     <row r="800" ht="20" customHeight="1">
@@ -21028,7 +21028,7 @@
         </is>
       </c>
       <c r="E800" s="20" t="n">
-        <v>240</v>
+        <v>176</v>
       </c>
     </row>
     <row r="801" ht="20" customHeight="1">
@@ -21053,7 +21053,7 @@
         </is>
       </c>
       <c r="E801" s="23" t="n">
-        <v>112</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>

--- a/Appium_E2E_Test_Report_Traverse.xlsx
+++ b/Appium_E2E_Test_Report_Traverse.xlsx
@@ -791,7 +791,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22 06:16:50</t>
+          <t>2026-08-11 05:25:34</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="E2" s="20" t="n">
-        <v>129</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="E3" s="23" t="n">
-        <v>117</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="E4" s="20" t="n">
-        <v>219</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="E5" s="23" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="E6" s="20" t="n">
-        <v>220</v>
+        <v>213</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="E7" s="23" t="n">
-        <v>143</v>
+        <v>238</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -1228,7 +1228,7 @@
         </is>
       </c>
       <c r="E8" s="20" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="E9" s="23" t="n">
-        <v>224</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
@@ -1278,7 +1278,7 @@
         </is>
       </c>
       <c r="E10" s="20" t="n">
-        <v>123</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="E11" s="23" t="n">
-        <v>168</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
@@ -1328,7 +1328,7 @@
         </is>
       </c>
       <c r="E12" s="20" t="n">
-        <v>124</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="E13" s="23" t="n">
-        <v>120</v>
+        <v>171</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="E14" s="20" t="n">
-        <v>153</v>
+        <v>225</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="E15" s="23" t="n">
-        <v>169</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="E16" s="20" t="n">
-        <v>138</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="E17" s="23" t="n">
-        <v>196</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -1478,7 +1478,7 @@
         </is>
       </c>
       <c r="E18" s="20" t="n">
-        <v>131</v>
+        <v>233</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
@@ -1503,7 +1503,7 @@
         </is>
       </c>
       <c r="E19" s="23" t="n">
-        <v>165</v>
+        <v>204</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="E20" s="20" t="n">
-        <v>114</v>
+        <v>183</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="E21" s="23" t="n">
-        <v>221</v>
+        <v>230</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
@@ -1578,7 +1578,7 @@
         </is>
       </c>
       <c r="E22" s="20" t="n">
-        <v>235</v>
+        <v>188</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="E23" s="23" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
@@ -1628,7 +1628,7 @@
         </is>
       </c>
       <c r="E24" s="20" t="n">
-        <v>155</v>
+        <v>224</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="E25" s="23" t="n">
-        <v>236</v>
+        <v>133</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
@@ -1678,7 +1678,7 @@
         </is>
       </c>
       <c r="E26" s="20" t="n">
-        <v>197</v>
+        <v>182</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="E27" s="23" t="n">
-        <v>222</v>
+        <v>120</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="E28" s="20" t="n">
-        <v>140</v>
+        <v>217</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="E29" s="23" t="n">
-        <v>239</v>
+        <v>142</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="E30" s="20" t="n">
-        <v>208</v>
+        <v>219</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
@@ -1803,7 +1803,7 @@
         </is>
       </c>
       <c r="E31" s="23" t="n">
-        <v>127</v>
+        <v>178</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
@@ -1828,7 +1828,7 @@
         </is>
       </c>
       <c r="E32" s="20" t="n">
-        <v>178</v>
+        <v>157</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
@@ -1853,7 +1853,7 @@
         </is>
       </c>
       <c r="E33" s="23" t="n">
-        <v>139</v>
+        <v>239</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
@@ -1878,7 +1878,7 @@
         </is>
       </c>
       <c r="E34" s="20" t="n">
-        <v>139</v>
+        <v>200</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="E35" s="23" t="n">
-        <v>110</v>
+        <v>183</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="E36" s="20" t="n">
-        <v>225</v>
+        <v>191</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="E37" s="23" t="n">
-        <v>221</v>
+        <v>140</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
@@ -1978,7 +1978,7 @@
         </is>
       </c>
       <c r="E38" s="20" t="n">
-        <v>137</v>
+        <v>158</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="E40" s="20" t="n">
-        <v>178</v>
+        <v>195</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="E41" s="23" t="n">
-        <v>220</v>
+        <v>125</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
@@ -2078,7 +2078,7 @@
         </is>
       </c>
       <c r="E42" s="20" t="n">
-        <v>178</v>
+        <v>173</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="E43" s="23" t="n">
-        <v>173</v>
+        <v>186</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="E44" s="20" t="n">
-        <v>159</v>
+        <v>208</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="E45" s="23" t="n">
-        <v>119</v>
+        <v>157</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
@@ -2178,7 +2178,7 @@
         </is>
       </c>
       <c r="E46" s="20" t="n">
-        <v>110</v>
+        <v>195</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
@@ -2203,7 +2203,7 @@
         </is>
       </c>
       <c r="E47" s="23" t="n">
-        <v>133</v>
+        <v>178</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="E48" s="20" t="n">
-        <v>217</v>
+        <v>195</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
@@ -2253,7 +2253,7 @@
         </is>
       </c>
       <c r="E49" s="23" t="n">
-        <v>225</v>
+        <v>173</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
@@ -2278,7 +2278,7 @@
         </is>
       </c>
       <c r="E50" s="20" t="n">
-        <v>148</v>
+        <v>219</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="E51" s="23" t="n">
-        <v>119</v>
+        <v>140</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
@@ -2328,7 +2328,7 @@
         </is>
       </c>
       <c r="E52" s="20" t="n">
-        <v>160</v>
+        <v>166</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
@@ -2353,7 +2353,7 @@
         </is>
       </c>
       <c r="E53" s="23" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="E54" s="20" t="n">
-        <v>222</v>
+        <v>232</v>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1">
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="E55" s="23" t="n">
-        <v>132</v>
+        <v>144</v>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1">
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="E56" s="20" t="n">
-        <v>117</v>
+        <v>124</v>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1">
@@ -2453,7 +2453,7 @@
         </is>
       </c>
       <c r="E57" s="23" t="n">
-        <v>212</v>
+        <v>172</v>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1">
@@ -2478,7 +2478,7 @@
         </is>
       </c>
       <c r="E58" s="20" t="n">
-        <v>205</v>
+        <v>146</v>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1">
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="E59" s="23" t="n">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1">
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="E60" s="20" t="n">
-        <v>185</v>
+        <v>197</v>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
@@ -2553,7 +2553,7 @@
         </is>
       </c>
       <c r="E61" s="23" t="n">
-        <v>177</v>
+        <v>134</v>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="E62" s="20" t="n">
-        <v>199</v>
+        <v>165</v>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="E63" s="23" t="n">
-        <v>230</v>
+        <v>112</v>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1">
@@ -2628,7 +2628,7 @@
         </is>
       </c>
       <c r="E64" s="20" t="n">
-        <v>172</v>
+        <v>151</v>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1">
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="E65" s="23" t="n">
-        <v>205</v>
+        <v>179</v>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1">
@@ -2678,7 +2678,7 @@
         </is>
       </c>
       <c r="E66" s="20" t="n">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="E67" s="23" t="n">
-        <v>181</v>
+        <v>200</v>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="E68" s="20" t="n">
-        <v>129</v>
+        <v>201</v>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="E69" s="23" t="n">
-        <v>233</v>
+        <v>134</v>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1">
@@ -2778,7 +2778,7 @@
         </is>
       </c>
       <c r="E70" s="20" t="n">
-        <v>146</v>
+        <v>225</v>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1">
@@ -2803,7 +2803,7 @@
         </is>
       </c>
       <c r="E71" s="23" t="n">
-        <v>234</v>
+        <v>163</v>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1">
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="E72" s="20" t="n">
-        <v>226</v>
+        <v>138</v>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1">
@@ -2853,7 +2853,7 @@
         </is>
       </c>
       <c r="E73" s="23" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
@@ -2878,7 +2878,7 @@
         </is>
       </c>
       <c r="E74" s="20" t="n">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="E75" s="23" t="n">
-        <v>136</v>
+        <v>235</v>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
@@ -2928,7 +2928,7 @@
         </is>
       </c>
       <c r="E76" s="20" t="n">
-        <v>203</v>
+        <v>148</v>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="E77" s="23" t="n">
-        <v>198</v>
+        <v>194</v>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1">
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="E78" s="20" t="n">
-        <v>177</v>
+        <v>239</v>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
@@ -3003,7 +3003,7 @@
         </is>
       </c>
       <c r="E79" s="23" t="n">
-        <v>197</v>
+        <v>148</v>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1">
@@ -3028,7 +3028,7 @@
         </is>
       </c>
       <c r="E80" s="20" t="n">
-        <v>230</v>
+        <v>128</v>
       </c>
     </row>
     <row r="81" ht="20" customHeight="1">
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="E81" s="23" t="n">
-        <v>114</v>
+        <v>137</v>
       </c>
     </row>
     <row r="82" ht="20" customHeight="1">
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="E82" s="20" t="n">
-        <v>114</v>
+        <v>200</v>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1">
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="E83" s="23" t="n">
-        <v>179</v>
+        <v>128</v>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1">
@@ -3128,7 +3128,7 @@
         </is>
       </c>
       <c r="E84" s="20" t="n">
-        <v>136</v>
+        <v>192</v>
       </c>
     </row>
     <row r="85" ht="20" customHeight="1">
@@ -3153,7 +3153,7 @@
         </is>
       </c>
       <c r="E85" s="23" t="n">
-        <v>156</v>
+        <v>207</v>
       </c>
     </row>
     <row r="86" ht="20" customHeight="1">
@@ -3178,7 +3178,7 @@
         </is>
       </c>
       <c r="E86" s="20" t="n">
-        <v>127</v>
+        <v>141</v>
       </c>
     </row>
     <row r="87" ht="20" customHeight="1">
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="E87" s="23" t="n">
-        <v>220</v>
+        <v>153</v>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1">
@@ -3228,7 +3228,7 @@
         </is>
       </c>
       <c r="E88" s="20" t="n">
-        <v>237</v>
+        <v>231</v>
       </c>
     </row>
     <row r="89" ht="20" customHeight="1">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="E89" s="23" t="n">
-        <v>145</v>
+        <v>237</v>
       </c>
     </row>
     <row r="90" ht="20" customHeight="1">
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="E90" s="20" t="n">
-        <v>186</v>
+        <v>131</v>
       </c>
     </row>
     <row r="91" ht="20" customHeight="1">
@@ -3303,7 +3303,7 @@
         </is>
       </c>
       <c r="E91" s="23" t="n">
-        <v>159</v>
+        <v>145</v>
       </c>
     </row>
     <row r="92" ht="20" customHeight="1">
@@ -3328,7 +3328,7 @@
         </is>
       </c>
       <c r="E92" s="20" t="n">
-        <v>234</v>
+        <v>160</v>
       </c>
     </row>
     <row r="93" ht="20" customHeight="1">
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="E93" s="23" t="n">
-        <v>223</v>
+        <v>174</v>
       </c>
     </row>
     <row r="94" ht="20" customHeight="1">
@@ -3378,7 +3378,7 @@
         </is>
       </c>
       <c r="E94" s="20" t="n">
-        <v>139</v>
+        <v>177</v>
       </c>
     </row>
     <row r="95" ht="20" customHeight="1">
@@ -3403,7 +3403,7 @@
         </is>
       </c>
       <c r="E95" s="23" t="n">
-        <v>196</v>
+        <v>117</v>
       </c>
     </row>
     <row r="96" ht="20" customHeight="1">
@@ -3428,7 +3428,7 @@
         </is>
       </c>
       <c r="E96" s="20" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="97" ht="20" customHeight="1">
@@ -3453,7 +3453,7 @@
         </is>
       </c>
       <c r="E97" s="23" t="n">
-        <v>208</v>
+        <v>234</v>
       </c>
     </row>
     <row r="98" ht="20" customHeight="1">
@@ -3478,7 +3478,7 @@
         </is>
       </c>
       <c r="E98" s="20" t="n">
-        <v>191</v>
+        <v>163</v>
       </c>
     </row>
     <row r="99" ht="20" customHeight="1">
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="E99" s="23" t="n">
-        <v>233</v>
+        <v>162</v>
       </c>
     </row>
     <row r="100" ht="20" customHeight="1">
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="E100" s="20" t="n">
-        <v>220</v>
+        <v>208</v>
       </c>
     </row>
     <row r="101" ht="20" customHeight="1">
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="E101" s="23" t="n">
-        <v>132</v>
+        <v>236</v>
       </c>
     </row>
     <row r="102" ht="20" customHeight="1">
@@ -3578,7 +3578,7 @@
         </is>
       </c>
       <c r="E102" s="20" t="n">
-        <v>223</v>
+        <v>112</v>
       </c>
     </row>
     <row r="103" ht="20" customHeight="1">
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="E103" s="23" t="n">
-        <v>125</v>
+        <v>215</v>
       </c>
     </row>
     <row r="104" ht="20" customHeight="1">
@@ -3628,7 +3628,7 @@
         </is>
       </c>
       <c r="E104" s="20" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="105" ht="20" customHeight="1">
@@ -3653,7 +3653,7 @@
         </is>
       </c>
       <c r="E105" s="23" t="n">
-        <v>213</v>
+        <v>199</v>
       </c>
     </row>
     <row r="106" ht="20" customHeight="1">
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="E106" s="20" t="n">
-        <v>170</v>
+        <v>152</v>
       </c>
     </row>
     <row r="107" ht="20" customHeight="1">
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="E107" s="23" t="n">
-        <v>232</v>
+        <v>177</v>
       </c>
     </row>
     <row r="108" ht="20" customHeight="1">
@@ -3728,7 +3728,7 @@
         </is>
       </c>
       <c r="E108" s="20" t="n">
-        <v>167</v>
+        <v>174</v>
       </c>
     </row>
     <row r="109" ht="20" customHeight="1">
@@ -3753,7 +3753,7 @@
         </is>
       </c>
       <c r="E109" s="23" t="n">
-        <v>193</v>
+        <v>149</v>
       </c>
     </row>
     <row r="110" ht="20" customHeight="1">
@@ -3778,7 +3778,7 @@
         </is>
       </c>
       <c r="E110" s="20" t="n">
-        <v>173</v>
+        <v>214</v>
       </c>
     </row>
     <row r="111" ht="20" customHeight="1">
@@ -3803,7 +3803,7 @@
         </is>
       </c>
       <c r="E111" s="23" t="n">
-        <v>125</v>
+        <v>213</v>
       </c>
     </row>
     <row r="112" ht="20" customHeight="1">
@@ -3828,7 +3828,7 @@
         </is>
       </c>
       <c r="E112" s="20" t="n">
-        <v>131</v>
+        <v>207</v>
       </c>
     </row>
     <row r="113" ht="20" customHeight="1">
@@ -3853,7 +3853,7 @@
         </is>
       </c>
       <c r="E113" s="23" t="n">
-        <v>143</v>
+        <v>170</v>
       </c>
     </row>
     <row r="114" ht="20" customHeight="1">
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="E114" s="20" t="n">
-        <v>230</v>
+        <v>135</v>
       </c>
     </row>
     <row r="115" ht="20" customHeight="1">
@@ -3903,7 +3903,7 @@
         </is>
       </c>
       <c r="E115" s="23" t="n">
-        <v>115</v>
+        <v>165</v>
       </c>
     </row>
     <row r="116" ht="20" customHeight="1">
@@ -3928,7 +3928,7 @@
         </is>
       </c>
       <c r="E116" s="20" t="n">
-        <v>189</v>
+        <v>116</v>
       </c>
     </row>
     <row r="117" ht="20" customHeight="1">
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="E117" s="23" t="n">
-        <v>162</v>
+        <v>237</v>
       </c>
     </row>
     <row r="118" ht="20" customHeight="1">
@@ -3978,7 +3978,7 @@
         </is>
       </c>
       <c r="E118" s="20" t="n">
-        <v>159</v>
+        <v>135</v>
       </c>
     </row>
     <row r="119" ht="20" customHeight="1">
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="E119" s="23" t="n">
-        <v>152</v>
+        <v>196</v>
       </c>
     </row>
     <row r="120" ht="20" customHeight="1">
@@ -4028,7 +4028,7 @@
         </is>
       </c>
       <c r="E120" s="20" t="n">
-        <v>116</v>
+        <v>141</v>
       </c>
     </row>
     <row r="121" ht="20" customHeight="1">
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="E121" s="23" t="n">
-        <v>187</v>
+        <v>120</v>
       </c>
     </row>
     <row r="122" ht="20" customHeight="1">
@@ -4078,7 +4078,7 @@
         </is>
       </c>
       <c r="E122" s="20" t="n">
-        <v>140</v>
+        <v>170</v>
       </c>
     </row>
     <row r="123" ht="20" customHeight="1">
@@ -4103,7 +4103,7 @@
         </is>
       </c>
       <c r="E123" s="23" t="n">
-        <v>142</v>
+        <v>194</v>
       </c>
     </row>
     <row r="124" ht="20" customHeight="1">
@@ -4153,7 +4153,7 @@
         </is>
       </c>
       <c r="E125" s="23" t="n">
-        <v>113</v>
+        <v>214</v>
       </c>
     </row>
     <row r="126" ht="20" customHeight="1">
@@ -4178,7 +4178,7 @@
         </is>
       </c>
       <c r="E126" s="20" t="n">
-        <v>214</v>
+        <v>204</v>
       </c>
     </row>
     <row r="127" ht="20" customHeight="1">
@@ -4203,7 +4203,7 @@
         </is>
       </c>
       <c r="E127" s="23" t="n">
-        <v>192</v>
+        <v>214</v>
       </c>
     </row>
     <row r="128" ht="20" customHeight="1">
@@ -4228,7 +4228,7 @@
         </is>
       </c>
       <c r="E128" s="20" t="n">
-        <v>236</v>
+        <v>224</v>
       </c>
     </row>
     <row r="129" ht="20" customHeight="1">
@@ -4253,7 +4253,7 @@
         </is>
       </c>
       <c r="E129" s="23" t="n">
-        <v>154</v>
+        <v>174</v>
       </c>
     </row>
     <row r="130" ht="20" customHeight="1">
@@ -4278,7 +4278,7 @@
         </is>
       </c>
       <c r="E130" s="20" t="n">
-        <v>157</v>
+        <v>142</v>
       </c>
     </row>
     <row r="131" ht="20" customHeight="1">
@@ -4303,7 +4303,7 @@
         </is>
       </c>
       <c r="E131" s="23" t="n">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="132" ht="20" customHeight="1">
@@ -4328,7 +4328,7 @@
         </is>
       </c>
       <c r="E132" s="20" t="n">
-        <v>183</v>
+        <v>193</v>
       </c>
     </row>
     <row r="133" ht="20" customHeight="1">
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="E133" s="23" t="n">
-        <v>122</v>
+        <v>189</v>
       </c>
     </row>
     <row r="134" ht="20" customHeight="1">
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="E134" s="20" t="n">
-        <v>157</v>
+        <v>164</v>
       </c>
     </row>
     <row r="135" ht="20" customHeight="1">
@@ -4403,7 +4403,7 @@
         </is>
       </c>
       <c r="E135" s="23" t="n">
-        <v>149</v>
+        <v>164</v>
       </c>
     </row>
     <row r="136" ht="20" customHeight="1">
@@ -4428,7 +4428,7 @@
         </is>
       </c>
       <c r="E136" s="20" t="n">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="137" ht="20" customHeight="1">
@@ -4453,7 +4453,7 @@
         </is>
       </c>
       <c r="E137" s="23" t="n">
-        <v>191</v>
+        <v>170</v>
       </c>
     </row>
     <row r="138" ht="20" customHeight="1">
@@ -4478,7 +4478,7 @@
         </is>
       </c>
       <c r="E138" s="20" t="n">
-        <v>137</v>
+        <v>167</v>
       </c>
     </row>
     <row r="139" ht="20" customHeight="1">
@@ -4503,7 +4503,7 @@
         </is>
       </c>
       <c r="E139" s="23" t="n">
-        <v>113</v>
+        <v>148</v>
       </c>
     </row>
     <row r="140" ht="20" customHeight="1">
@@ -4528,7 +4528,7 @@
         </is>
       </c>
       <c r="E140" s="20" t="n">
-        <v>206</v>
+        <v>230</v>
       </c>
     </row>
     <row r="141" ht="20" customHeight="1">
@@ -4553,7 +4553,7 @@
         </is>
       </c>
       <c r="E141" s="23" t="n">
-        <v>233</v>
+        <v>211</v>
       </c>
     </row>
     <row r="142" ht="20" customHeight="1">
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="E142" s="20" t="n">
-        <v>174</v>
+        <v>186</v>
       </c>
     </row>
     <row r="143" ht="20" customHeight="1">
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="E143" s="23" t="n">
-        <v>213</v>
+        <v>127</v>
       </c>
     </row>
     <row r="144" ht="20" customHeight="1">
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="E144" s="20" t="n">
-        <v>204</v>
+        <v>182</v>
       </c>
     </row>
     <row r="145" ht="20" customHeight="1">
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="E145" s="23" t="n">
-        <v>236</v>
+        <v>173</v>
       </c>
     </row>
     <row r="146" ht="20" customHeight="1">
@@ -4678,7 +4678,7 @@
         </is>
       </c>
       <c r="E146" s="20" t="n">
-        <v>164</v>
+        <v>194</v>
       </c>
     </row>
     <row r="147" ht="20" customHeight="1">
@@ -4703,7 +4703,7 @@
         </is>
       </c>
       <c r="E147" s="23" t="n">
-        <v>154</v>
+        <v>162</v>
       </c>
     </row>
     <row r="148" ht="20" customHeight="1">
@@ -4728,7 +4728,7 @@
         </is>
       </c>
       <c r="E148" s="20" t="n">
-        <v>120</v>
+        <v>175</v>
       </c>
     </row>
     <row r="149" ht="20" customHeight="1">
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c r="E149" s="23" t="n">
-        <v>168</v>
+        <v>214</v>
       </c>
     </row>
     <row r="150" ht="20" customHeight="1">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="E150" s="20" t="n">
-        <v>195</v>
+        <v>163</v>
       </c>
     </row>
     <row r="151" ht="20" customHeight="1">
@@ -4803,7 +4803,7 @@
         </is>
       </c>
       <c r="E151" s="23" t="n">
-        <v>175</v>
+        <v>182</v>
       </c>
     </row>
     <row r="152" ht="20" customHeight="1">
@@ -4828,7 +4828,7 @@
         </is>
       </c>
       <c r="E152" s="20" t="n">
-        <v>145</v>
+        <v>182</v>
       </c>
     </row>
     <row r="153" ht="20" customHeight="1">
@@ -4853,7 +4853,7 @@
         </is>
       </c>
       <c r="E153" s="23" t="n">
-        <v>234</v>
+        <v>141</v>
       </c>
     </row>
     <row r="154" ht="20" customHeight="1">
@@ -4878,7 +4878,7 @@
         </is>
       </c>
       <c r="E154" s="20" t="n">
-        <v>171</v>
+        <v>237</v>
       </c>
     </row>
     <row r="155" ht="20" customHeight="1">
@@ -4903,7 +4903,7 @@
         </is>
       </c>
       <c r="E155" s="23" t="n">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="156" ht="20" customHeight="1">
@@ -4928,7 +4928,7 @@
         </is>
       </c>
       <c r="E156" s="20" t="n">
-        <v>143</v>
+        <v>237</v>
       </c>
     </row>
     <row r="157" ht="20" customHeight="1">
@@ -4953,7 +4953,7 @@
         </is>
       </c>
       <c r="E157" s="23" t="n">
-        <v>131</v>
+        <v>172</v>
       </c>
     </row>
     <row r="158" ht="20" customHeight="1">
@@ -4978,7 +4978,7 @@
         </is>
       </c>
       <c r="E158" s="20" t="n">
-        <v>185</v>
+        <v>215</v>
       </c>
     </row>
     <row r="159" ht="20" customHeight="1">
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="E159" s="23" t="n">
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
     <row r="160" ht="20" customHeight="1">
@@ -5028,7 +5028,7 @@
         </is>
       </c>
       <c r="E160" s="20" t="n">
-        <v>194</v>
+        <v>207</v>
       </c>
     </row>
     <row r="161" ht="20" customHeight="1">
@@ -5053,7 +5053,7 @@
         </is>
       </c>
       <c r="E161" s="23" t="n">
-        <v>156</v>
+        <v>212</v>
       </c>
     </row>
     <row r="162" ht="20" customHeight="1">
@@ -5078,7 +5078,7 @@
         </is>
       </c>
       <c r="E162" s="20" t="n">
-        <v>216</v>
+        <v>163</v>
       </c>
     </row>
     <row r="163" ht="20" customHeight="1">
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="E163" s="23" t="n">
-        <v>185</v>
+        <v>144</v>
       </c>
     </row>
     <row r="164" ht="20" customHeight="1">
@@ -5128,7 +5128,7 @@
         </is>
       </c>
       <c r="E164" s="20" t="n">
-        <v>221</v>
+        <v>199</v>
       </c>
     </row>
     <row r="165" ht="20" customHeight="1">
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="E165" s="23" t="n">
-        <v>121</v>
+        <v>151</v>
       </c>
     </row>
     <row r="166" ht="20" customHeight="1">
@@ -5178,7 +5178,7 @@
         </is>
       </c>
       <c r="E166" s="20" t="n">
-        <v>122</v>
+        <v>190</v>
       </c>
     </row>
     <row r="167" ht="20" customHeight="1">
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="E167" s="23" t="n">
-        <v>123</v>
+        <v>112</v>
       </c>
     </row>
     <row r="168" ht="20" customHeight="1">
@@ -5228,7 +5228,7 @@
         </is>
       </c>
       <c r="E168" s="20" t="n">
-        <v>237</v>
+        <v>119</v>
       </c>
     </row>
     <row r="169" ht="20" customHeight="1">
@@ -5253,7 +5253,7 @@
         </is>
       </c>
       <c r="E169" s="23" t="n">
-        <v>135</v>
+        <v>215</v>
       </c>
     </row>
     <row r="170" ht="20" customHeight="1">
@@ -5278,7 +5278,7 @@
         </is>
       </c>
       <c r="E170" s="20" t="n">
-        <v>220</v>
+        <v>122</v>
       </c>
     </row>
     <row r="171" ht="20" customHeight="1">
@@ -5303,7 +5303,7 @@
         </is>
       </c>
       <c r="E171" s="23" t="n">
-        <v>127</v>
+        <v>147</v>
       </c>
     </row>
     <row r="172" ht="20" customHeight="1">
@@ -5328,7 +5328,7 @@
         </is>
       </c>
       <c r="E172" s="20" t="n">
-        <v>190</v>
+        <v>115</v>
       </c>
     </row>
     <row r="173" ht="20" customHeight="1">
@@ -5353,7 +5353,7 @@
         </is>
       </c>
       <c r="E173" s="23" t="n">
-        <v>140</v>
+        <v>221</v>
       </c>
     </row>
     <row r="174" ht="20" customHeight="1">
@@ -5378,7 +5378,7 @@
         </is>
       </c>
       <c r="E174" s="20" t="n">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="175" ht="20" customHeight="1">
@@ -5403,7 +5403,7 @@
         </is>
       </c>
       <c r="E175" s="23" t="n">
-        <v>232</v>
+        <v>200</v>
       </c>
     </row>
     <row r="176" ht="20" customHeight="1">
@@ -5428,7 +5428,7 @@
         </is>
       </c>
       <c r="E176" s="20" t="n">
-        <v>203</v>
+        <v>194</v>
       </c>
     </row>
     <row r="177" ht="20" customHeight="1">
@@ -5453,7 +5453,7 @@
         </is>
       </c>
       <c r="E177" s="23" t="n">
-        <v>214</v>
+        <v>114</v>
       </c>
     </row>
     <row r="178" ht="20" customHeight="1">
@@ -5478,7 +5478,7 @@
         </is>
       </c>
       <c r="E178" s="20" t="n">
-        <v>137</v>
+        <v>186</v>
       </c>
     </row>
     <row r="179" ht="20" customHeight="1">
@@ -5503,7 +5503,7 @@
         </is>
       </c>
       <c r="E179" s="23" t="n">
-        <v>228</v>
+        <v>191</v>
       </c>
     </row>
     <row r="180" ht="20" customHeight="1">
@@ -5528,7 +5528,7 @@
         </is>
       </c>
       <c r="E180" s="20" t="n">
-        <v>228</v>
+        <v>178</v>
       </c>
     </row>
     <row r="181" ht="20" customHeight="1">
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="E181" s="23" t="n">
-        <v>122</v>
+        <v>131</v>
       </c>
     </row>
     <row r="182" ht="20" customHeight="1">
@@ -5578,7 +5578,7 @@
         </is>
       </c>
       <c r="E182" s="20" t="n">
-        <v>194</v>
+        <v>237</v>
       </c>
     </row>
     <row r="183" ht="20" customHeight="1">
@@ -5603,7 +5603,7 @@
         </is>
       </c>
       <c r="E183" s="23" t="n">
-        <v>219</v>
+        <v>118</v>
       </c>
     </row>
     <row r="184" ht="20" customHeight="1">
@@ -5628,7 +5628,7 @@
         </is>
       </c>
       <c r="E184" s="20" t="n">
-        <v>231</v>
+        <v>164</v>
       </c>
     </row>
     <row r="185" ht="20" customHeight="1">
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="E185" s="23" t="n">
-        <v>168</v>
+        <v>110</v>
       </c>
     </row>
     <row r="186" ht="20" customHeight="1">
@@ -5678,7 +5678,7 @@
         </is>
       </c>
       <c r="E186" s="20" t="n">
-        <v>149</v>
+        <v>220</v>
       </c>
     </row>
     <row r="187" ht="20" customHeight="1">
@@ -5703,7 +5703,7 @@
         </is>
       </c>
       <c r="E187" s="23" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="188" ht="20" customHeight="1">
@@ -5728,7 +5728,7 @@
         </is>
       </c>
       <c r="E188" s="20" t="n">
-        <v>231</v>
+        <v>152</v>
       </c>
     </row>
     <row r="189" ht="20" customHeight="1">
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="E189" s="23" t="n">
-        <v>126</v>
+        <v>225</v>
       </c>
     </row>
     <row r="190" ht="20" customHeight="1">
@@ -5778,7 +5778,7 @@
         </is>
       </c>
       <c r="E190" s="20" t="n">
-        <v>135</v>
+        <v>146</v>
       </c>
     </row>
     <row r="191" ht="20" customHeight="1">
@@ -5803,7 +5803,7 @@
         </is>
       </c>
       <c r="E191" s="23" t="n">
-        <v>126</v>
+        <v>208</v>
       </c>
     </row>
     <row r="192" ht="20" customHeight="1">
@@ -5828,7 +5828,7 @@
         </is>
       </c>
       <c r="E192" s="20" t="n">
-        <v>206</v>
+        <v>234</v>
       </c>
     </row>
     <row r="193" ht="20" customHeight="1">
@@ -5853,7 +5853,7 @@
         </is>
       </c>
       <c r="E193" s="23" t="n">
-        <v>216</v>
+        <v>231</v>
       </c>
     </row>
     <row r="194" ht="20" customHeight="1">
@@ -5878,7 +5878,7 @@
         </is>
       </c>
       <c r="E194" s="20" t="n">
-        <v>172</v>
+        <v>119</v>
       </c>
     </row>
     <row r="195" ht="20" customHeight="1">
@@ -5903,7 +5903,7 @@
         </is>
       </c>
       <c r="E195" s="23" t="n">
-        <v>201</v>
+        <v>163</v>
       </c>
     </row>
     <row r="196" ht="20" customHeight="1">
@@ -5928,7 +5928,7 @@
         </is>
       </c>
       <c r="E196" s="20" t="n">
-        <v>234</v>
+        <v>165</v>
       </c>
     </row>
     <row r="197" ht="20" customHeight="1">
@@ -5953,7 +5953,7 @@
         </is>
       </c>
       <c r="E197" s="23" t="n">
-        <v>121</v>
+        <v>215</v>
       </c>
     </row>
     <row r="198" ht="20" customHeight="1">
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="E198" s="20" t="n">
-        <v>189</v>
+        <v>130</v>
       </c>
     </row>
     <row r="199" ht="20" customHeight="1">
@@ -6003,7 +6003,7 @@
         </is>
       </c>
       <c r="E199" s="23" t="n">
-        <v>181</v>
+        <v>126</v>
       </c>
     </row>
     <row r="200" ht="20" customHeight="1">
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="E200" s="20" t="n">
-        <v>219</v>
+        <v>214</v>
       </c>
     </row>
     <row r="201" ht="20" customHeight="1">
@@ -6053,7 +6053,7 @@
         </is>
       </c>
       <c r="E201" s="23" t="n">
-        <v>138</v>
+        <v>162</v>
       </c>
     </row>
     <row r="202" ht="20" customHeight="1">
@@ -6078,7 +6078,7 @@
         </is>
       </c>
       <c r="E202" s="20" t="n">
-        <v>168</v>
+        <v>113</v>
       </c>
     </row>
     <row r="203" ht="20" customHeight="1">
@@ -6103,7 +6103,7 @@
         </is>
       </c>
       <c r="E203" s="23" t="n">
-        <v>172</v>
+        <v>154</v>
       </c>
     </row>
     <row r="204" ht="20" customHeight="1">
@@ -6128,7 +6128,7 @@
         </is>
       </c>
       <c r="E204" s="20" t="n">
-        <v>165</v>
+        <v>144</v>
       </c>
     </row>
     <row r="205" ht="20" customHeight="1">
@@ -6153,7 +6153,7 @@
         </is>
       </c>
       <c r="E205" s="23" t="n">
-        <v>190</v>
+        <v>195</v>
       </c>
     </row>
     <row r="206" ht="20" customHeight="1">
@@ -6178,7 +6178,7 @@
         </is>
       </c>
       <c r="E206" s="20" t="n">
-        <v>149</v>
+        <v>184</v>
       </c>
     </row>
     <row r="207" ht="20" customHeight="1">
@@ -6203,7 +6203,7 @@
         </is>
       </c>
       <c r="E207" s="23" t="n">
-        <v>169</v>
+        <v>182</v>
       </c>
     </row>
     <row r="208" ht="20" customHeight="1">
@@ -6228,7 +6228,7 @@
         </is>
       </c>
       <c r="E208" s="20" t="n">
-        <v>136</v>
+        <v>231</v>
       </c>
     </row>
     <row r="209" ht="20" customHeight="1">
@@ -6253,7 +6253,7 @@
         </is>
       </c>
       <c r="E209" s="23" t="n">
-        <v>186</v>
+        <v>193</v>
       </c>
     </row>
     <row r="210" ht="20" customHeight="1">
@@ -6278,7 +6278,7 @@
         </is>
       </c>
       <c r="E210" s="20" t="n">
-        <v>218</v>
+        <v>146</v>
       </c>
     </row>
     <row r="211" ht="20" customHeight="1">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="E211" s="23" t="n">
-        <v>110</v>
+        <v>142</v>
       </c>
     </row>
     <row r="212" ht="20" customHeight="1">
@@ -6328,7 +6328,7 @@
         </is>
       </c>
       <c r="E212" s="20" t="n">
-        <v>166</v>
+        <v>144</v>
       </c>
     </row>
     <row r="213" ht="20" customHeight="1">
@@ -6353,7 +6353,7 @@
         </is>
       </c>
       <c r="E213" s="23" t="n">
-        <v>238</v>
+        <v>150</v>
       </c>
     </row>
     <row r="214" ht="20" customHeight="1">
@@ -6378,7 +6378,7 @@
         </is>
       </c>
       <c r="E214" s="20" t="n">
-        <v>150</v>
+        <v>222</v>
       </c>
     </row>
     <row r="215" ht="20" customHeight="1">
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="E215" s="23" t="n">
-        <v>123</v>
+        <v>206</v>
       </c>
     </row>
     <row r="216" ht="20" customHeight="1">
@@ -6428,7 +6428,7 @@
         </is>
       </c>
       <c r="E216" s="20" t="n">
-        <v>205</v>
+        <v>186</v>
       </c>
     </row>
     <row r="217" ht="20" customHeight="1">
@@ -6453,7 +6453,7 @@
         </is>
       </c>
       <c r="E217" s="23" t="n">
-        <v>218</v>
+        <v>146</v>
       </c>
     </row>
     <row r="218" ht="20" customHeight="1">
@@ -6478,7 +6478,7 @@
         </is>
       </c>
       <c r="E218" s="20" t="n">
-        <v>222</v>
+        <v>129</v>
       </c>
     </row>
     <row r="219" ht="20" customHeight="1">
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="E219" s="23" t="n">
-        <v>162</v>
+        <v>199</v>
       </c>
     </row>
     <row r="220" ht="20" customHeight="1">
@@ -6528,7 +6528,7 @@
         </is>
       </c>
       <c r="E220" s="20" t="n">
-        <v>215</v>
+        <v>169</v>
       </c>
     </row>
     <row r="221" ht="20" customHeight="1">
@@ -6553,7 +6553,7 @@
         </is>
       </c>
       <c r="E221" s="23" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="222" ht="20" customHeight="1">
@@ -6578,7 +6578,7 @@
         </is>
       </c>
       <c r="E222" s="20" t="n">
-        <v>230</v>
+        <v>237</v>
       </c>
     </row>
     <row r="223" ht="20" customHeight="1">
@@ -6603,7 +6603,7 @@
         </is>
       </c>
       <c r="E223" s="23" t="n">
-        <v>232</v>
+        <v>183</v>
       </c>
     </row>
     <row r="224" ht="20" customHeight="1">
@@ -6628,7 +6628,7 @@
         </is>
       </c>
       <c r="E224" s="20" t="n">
-        <v>213</v>
+        <v>193</v>
       </c>
     </row>
     <row r="225" ht="20" customHeight="1">
@@ -6653,7 +6653,7 @@
         </is>
       </c>
       <c r="E225" s="23" t="n">
-        <v>221</v>
+        <v>225</v>
       </c>
     </row>
     <row r="226" ht="20" customHeight="1">
@@ -6678,7 +6678,7 @@
         </is>
       </c>
       <c r="E226" s="20" t="n">
-        <v>223</v>
+        <v>180</v>
       </c>
     </row>
     <row r="227" ht="20" customHeight="1">
@@ -6703,7 +6703,7 @@
         </is>
       </c>
       <c r="E227" s="23" t="n">
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
     <row r="228" ht="20" customHeight="1">
@@ -6728,7 +6728,7 @@
         </is>
       </c>
       <c r="E228" s="20" t="n">
-        <v>162</v>
+        <v>189</v>
       </c>
     </row>
     <row r="229" ht="20" customHeight="1">
@@ -6753,7 +6753,7 @@
         </is>
       </c>
       <c r="E229" s="23" t="n">
-        <v>168</v>
+        <v>235</v>
       </c>
     </row>
     <row r="230" ht="20" customHeight="1">
@@ -6778,7 +6778,7 @@
         </is>
       </c>
       <c r="E230" s="20" t="n">
-        <v>237</v>
+        <v>129</v>
       </c>
     </row>
     <row r="231" ht="20" customHeight="1">
@@ -6803,7 +6803,7 @@
         </is>
       </c>
       <c r="E231" s="23" t="n">
-        <v>205</v>
+        <v>157</v>
       </c>
     </row>
     <row r="232" ht="20" customHeight="1">
@@ -6828,7 +6828,7 @@
         </is>
       </c>
       <c r="E232" s="20" t="n">
-        <v>119</v>
+        <v>140</v>
       </c>
     </row>
     <row r="233" ht="20" customHeight="1">
@@ -6853,7 +6853,7 @@
         </is>
       </c>
       <c r="E233" s="23" t="n">
-        <v>115</v>
+        <v>197</v>
       </c>
     </row>
     <row r="234" ht="20" customHeight="1">
@@ -6878,7 +6878,7 @@
         </is>
       </c>
       <c r="E234" s="20" t="n">
-        <v>137</v>
+        <v>239</v>
       </c>
     </row>
     <row r="235" ht="20" customHeight="1">
@@ -6903,7 +6903,7 @@
         </is>
       </c>
       <c r="E235" s="23" t="n">
-        <v>223</v>
+        <v>151</v>
       </c>
     </row>
     <row r="236" ht="20" customHeight="1">
@@ -6928,7 +6928,7 @@
         </is>
       </c>
       <c r="E236" s="20" t="n">
-        <v>228</v>
+        <v>157</v>
       </c>
     </row>
     <row r="237" ht="20" customHeight="1">
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="E237" s="23" t="n">
-        <v>194</v>
+        <v>126</v>
       </c>
     </row>
     <row r="238" ht="20" customHeight="1">
@@ -6978,7 +6978,7 @@
         </is>
       </c>
       <c r="E238" s="20" t="n">
-        <v>172</v>
+        <v>196</v>
       </c>
     </row>
     <row r="239" ht="20" customHeight="1">
@@ -7003,7 +7003,7 @@
         </is>
       </c>
       <c r="E239" s="23" t="n">
-        <v>228</v>
+        <v>178</v>
       </c>
     </row>
     <row r="240" ht="20" customHeight="1">
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="E241" s="23" t="n">
-        <v>201</v>
+        <v>173</v>
       </c>
     </row>
     <row r="242" ht="20" customHeight="1">
@@ -7078,7 +7078,7 @@
         </is>
       </c>
       <c r="E242" s="20" t="n">
-        <v>209</v>
+        <v>190</v>
       </c>
     </row>
     <row r="243" ht="20" customHeight="1">
@@ -7103,7 +7103,7 @@
         </is>
       </c>
       <c r="E243" s="23" t="n">
-        <v>152</v>
+        <v>168</v>
       </c>
     </row>
     <row r="244" ht="20" customHeight="1">
@@ -7128,7 +7128,7 @@
         </is>
       </c>
       <c r="E244" s="20" t="n">
-        <v>152</v>
+        <v>216</v>
       </c>
     </row>
     <row r="245" ht="20" customHeight="1">
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="E245" s="23" t="n">
-        <v>196</v>
+        <v>168</v>
       </c>
     </row>
     <row r="246" ht="20" customHeight="1">
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="E246" s="20" t="n">
-        <v>121</v>
+        <v>158</v>
       </c>
     </row>
     <row r="247" ht="20" customHeight="1">
@@ -7203,7 +7203,7 @@
         </is>
       </c>
       <c r="E247" s="23" t="n">
-        <v>224</v>
+        <v>155</v>
       </c>
     </row>
     <row r="248" ht="20" customHeight="1">
@@ -7228,7 +7228,7 @@
         </is>
       </c>
       <c r="E248" s="20" t="n">
-        <v>177</v>
+        <v>218</v>
       </c>
     </row>
     <row r="249" ht="20" customHeight="1">
@@ -7253,7 +7253,7 @@
         </is>
       </c>
       <c r="E249" s="23" t="n">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="250" ht="20" customHeight="1">
@@ -7278,7 +7278,7 @@
         </is>
       </c>
       <c r="E250" s="20" t="n">
-        <v>174</v>
+        <v>193</v>
       </c>
     </row>
     <row r="251" ht="20" customHeight="1">
@@ -7303,7 +7303,7 @@
         </is>
       </c>
       <c r="E251" s="23" t="n">
-        <v>196</v>
+        <v>122</v>
       </c>
     </row>
     <row r="252" ht="20" customHeight="1">
@@ -7328,7 +7328,7 @@
         </is>
       </c>
       <c r="E252" s="20" t="n">
-        <v>119</v>
+        <v>178</v>
       </c>
     </row>
     <row r="253" ht="20" customHeight="1">
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="E253" s="23" t="n">
-        <v>112</v>
+        <v>191</v>
       </c>
     </row>
     <row r="254" ht="20" customHeight="1">
@@ -7378,7 +7378,7 @@
         </is>
       </c>
       <c r="E254" s="20" t="n">
-        <v>187</v>
+        <v>239</v>
       </c>
     </row>
     <row r="255" ht="20" customHeight="1">
@@ -7403,7 +7403,7 @@
         </is>
       </c>
       <c r="E255" s="23" t="n">
-        <v>136</v>
+        <v>233</v>
       </c>
     </row>
     <row r="256" ht="20" customHeight="1">
@@ -7428,7 +7428,7 @@
         </is>
       </c>
       <c r="E256" s="20" t="n">
-        <v>178</v>
+        <v>191</v>
       </c>
     </row>
     <row r="257" ht="20" customHeight="1">
@@ -7453,7 +7453,7 @@
         </is>
       </c>
       <c r="E257" s="23" t="n">
-        <v>174</v>
+        <v>117</v>
       </c>
     </row>
     <row r="258" ht="20" customHeight="1">
@@ -7478,7 +7478,7 @@
         </is>
       </c>
       <c r="E258" s="20" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="259" ht="20" customHeight="1">
@@ -7503,7 +7503,7 @@
         </is>
       </c>
       <c r="E259" s="23" t="n">
-        <v>197</v>
+        <v>134</v>
       </c>
     </row>
     <row r="260" ht="20" customHeight="1">
@@ -7528,7 +7528,7 @@
         </is>
       </c>
       <c r="E260" s="20" t="n">
-        <v>131</v>
+        <v>174</v>
       </c>
     </row>
     <row r="261" ht="20" customHeight="1">
@@ -7553,7 +7553,7 @@
         </is>
       </c>
       <c r="E261" s="23" t="n">
-        <v>147</v>
+        <v>219</v>
       </c>
     </row>
     <row r="262" ht="20" customHeight="1">
@@ -7578,7 +7578,7 @@
         </is>
       </c>
       <c r="E262" s="20" t="n">
-        <v>123</v>
+        <v>133</v>
       </c>
     </row>
     <row r="263" ht="20" customHeight="1">
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="E263" s="23" t="n">
-        <v>157</v>
+        <v>206</v>
       </c>
     </row>
     <row r="264" ht="20" customHeight="1">
@@ -7628,7 +7628,7 @@
         </is>
       </c>
       <c r="E264" s="20" t="n">
-        <v>171</v>
+        <v>235</v>
       </c>
     </row>
     <row r="265" ht="20" customHeight="1">
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="E265" s="23" t="n">
-        <v>119</v>
+        <v>144</v>
       </c>
     </row>
     <row r="266" ht="20" customHeight="1">
@@ -7678,7 +7678,7 @@
         </is>
       </c>
       <c r="E266" s="20" t="n">
-        <v>181</v>
+        <v>167</v>
       </c>
     </row>
     <row r="267" ht="20" customHeight="1">
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="E267" s="23" t="n">
-        <v>203</v>
+        <v>161</v>
       </c>
     </row>
     <row r="268" ht="20" customHeight="1">
@@ -7728,7 +7728,7 @@
         </is>
       </c>
       <c r="E268" s="20" t="n">
-        <v>230</v>
+        <v>217</v>
       </c>
     </row>
     <row r="269" ht="20" customHeight="1">
@@ -7753,7 +7753,7 @@
         </is>
       </c>
       <c r="E269" s="23" t="n">
-        <v>237</v>
+        <v>196</v>
       </c>
     </row>
     <row r="270" ht="20" customHeight="1">
@@ -7778,7 +7778,7 @@
         </is>
       </c>
       <c r="E270" s="20" t="n">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="271" ht="20" customHeight="1">
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="E271" s="23" t="n">
-        <v>141</v>
+        <v>158</v>
       </c>
     </row>
     <row r="272" ht="20" customHeight="1">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="E272" s="20" t="n">
-        <v>110</v>
+        <v>168</v>
       </c>
     </row>
     <row r="273" ht="20" customHeight="1">
@@ -7853,7 +7853,7 @@
         </is>
       </c>
       <c r="E273" s="23" t="n">
-        <v>156</v>
+        <v>126</v>
       </c>
     </row>
     <row r="274" ht="20" customHeight="1">
@@ -7878,7 +7878,7 @@
         </is>
       </c>
       <c r="E274" s="20" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="275" ht="20" customHeight="1">
@@ -7903,7 +7903,7 @@
         </is>
       </c>
       <c r="E275" s="23" t="n">
-        <v>157</v>
+        <v>152</v>
       </c>
     </row>
     <row r="276" ht="20" customHeight="1">
@@ -7928,7 +7928,7 @@
         </is>
       </c>
       <c r="E276" s="20" t="n">
-        <v>184</v>
+        <v>176</v>
       </c>
     </row>
     <row r="277" ht="20" customHeight="1">
@@ -7953,7 +7953,7 @@
         </is>
       </c>
       <c r="E277" s="23" t="n">
-        <v>214</v>
+        <v>238</v>
       </c>
     </row>
     <row r="278" ht="20" customHeight="1">
@@ -7978,7 +7978,7 @@
         </is>
       </c>
       <c r="E278" s="20" t="n">
-        <v>199</v>
+        <v>153</v>
       </c>
     </row>
     <row r="279" ht="20" customHeight="1">
@@ -8003,7 +8003,7 @@
         </is>
       </c>
       <c r="E279" s="23" t="n">
-        <v>206</v>
+        <v>216</v>
       </c>
     </row>
     <row r="280" ht="20" customHeight="1">
@@ -8028,7 +8028,7 @@
         </is>
       </c>
       <c r="E280" s="20" t="n">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="281" ht="20" customHeight="1">
@@ -8053,7 +8053,7 @@
         </is>
       </c>
       <c r="E281" s="23" t="n">
-        <v>229</v>
+        <v>215</v>
       </c>
     </row>
     <row r="282" ht="20" customHeight="1">
@@ -8078,7 +8078,7 @@
         </is>
       </c>
       <c r="E282" s="20" t="n">
-        <v>222</v>
+        <v>113</v>
       </c>
     </row>
     <row r="283" ht="20" customHeight="1">
@@ -8103,7 +8103,7 @@
         </is>
       </c>
       <c r="E283" s="23" t="n">
-        <v>194</v>
+        <v>145</v>
       </c>
     </row>
     <row r="284" ht="20" customHeight="1">
@@ -8128,7 +8128,7 @@
         </is>
       </c>
       <c r="E284" s="20" t="n">
-        <v>169</v>
+        <v>117</v>
       </c>
     </row>
     <row r="285" ht="20" customHeight="1">
@@ -8153,7 +8153,7 @@
         </is>
       </c>
       <c r="E285" s="23" t="n">
-        <v>193</v>
+        <v>180</v>
       </c>
     </row>
     <row r="286" ht="20" customHeight="1">
@@ -8178,7 +8178,7 @@
         </is>
       </c>
       <c r="E286" s="20" t="n">
-        <v>216</v>
+        <v>206</v>
       </c>
     </row>
     <row r="287" ht="20" customHeight="1">
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="E287" s="23" t="n">
-        <v>174</v>
+        <v>149</v>
       </c>
     </row>
     <row r="288" ht="20" customHeight="1">
@@ -8228,7 +8228,7 @@
         </is>
       </c>
       <c r="E288" s="20" t="n">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="289" ht="20" customHeight="1">
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="E289" s="23" t="n">
-        <v>214</v>
+        <v>204</v>
       </c>
     </row>
     <row r="290" ht="20" customHeight="1">
@@ -8278,7 +8278,7 @@
         </is>
       </c>
       <c r="E290" s="20" t="n">
-        <v>238</v>
+        <v>202</v>
       </c>
     </row>
     <row r="291" ht="20" customHeight="1">
@@ -8303,7 +8303,7 @@
         </is>
       </c>
       <c r="E291" s="23" t="n">
-        <v>214</v>
+        <v>130</v>
       </c>
     </row>
     <row r="292" ht="20" customHeight="1">
@@ -8328,7 +8328,7 @@
         </is>
       </c>
       <c r="E292" s="20" t="n">
-        <v>225</v>
+        <v>118</v>
       </c>
     </row>
     <row r="293" ht="20" customHeight="1">
@@ -8353,7 +8353,7 @@
         </is>
       </c>
       <c r="E293" s="23" t="n">
-        <v>232</v>
+        <v>160</v>
       </c>
     </row>
     <row r="294" ht="20" customHeight="1">
@@ -8378,7 +8378,7 @@
         </is>
       </c>
       <c r="E294" s="20" t="n">
-        <v>161</v>
+        <v>216</v>
       </c>
     </row>
     <row r="295" ht="20" customHeight="1">
@@ -8403,7 +8403,7 @@
         </is>
       </c>
       <c r="E295" s="23" t="n">
-        <v>200</v>
+        <v>238</v>
       </c>
     </row>
     <row r="296" ht="20" customHeight="1">
@@ -8428,7 +8428,7 @@
         </is>
       </c>
       <c r="E296" s="20" t="n">
-        <v>150</v>
+        <v>214</v>
       </c>
     </row>
     <row r="297" ht="20" customHeight="1">
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="E297" s="23" t="n">
-        <v>179</v>
+        <v>224</v>
       </c>
     </row>
     <row r="298" ht="20" customHeight="1">
@@ -8478,7 +8478,7 @@
         </is>
       </c>
       <c r="E298" s="20" t="n">
-        <v>220</v>
+        <v>194</v>
       </c>
     </row>
     <row r="299" ht="20" customHeight="1">
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="E299" s="23" t="n">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="300" ht="20" customHeight="1">
@@ -8528,7 +8528,7 @@
         </is>
       </c>
       <c r="E300" s="20" t="n">
-        <v>234</v>
+        <v>159</v>
       </c>
     </row>
     <row r="301" ht="20" customHeight="1">
@@ -8553,7 +8553,7 @@
         </is>
       </c>
       <c r="E301" s="23" t="n">
-        <v>238</v>
+        <v>204</v>
       </c>
     </row>
     <row r="302" ht="20" customHeight="1">
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="E302" s="20" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="303" ht="20" customHeight="1">
@@ -8603,7 +8603,7 @@
         </is>
       </c>
       <c r="E303" s="23" t="n">
-        <v>122</v>
+        <v>142</v>
       </c>
     </row>
     <row r="304" ht="20" customHeight="1">
@@ -8628,7 +8628,7 @@
         </is>
       </c>
       <c r="E304" s="20" t="n">
-        <v>114</v>
+        <v>138</v>
       </c>
     </row>
     <row r="305" ht="20" customHeight="1">
@@ -8653,7 +8653,7 @@
         </is>
       </c>
       <c r="E305" s="23" t="n">
-        <v>224</v>
+        <v>208</v>
       </c>
     </row>
     <row r="306" ht="20" customHeight="1">
@@ -8678,7 +8678,7 @@
         </is>
       </c>
       <c r="E306" s="20" t="n">
-        <v>136</v>
+        <v>126</v>
       </c>
     </row>
     <row r="307" ht="20" customHeight="1">
@@ -8703,7 +8703,7 @@
         </is>
       </c>
       <c r="E307" s="23" t="n">
-        <v>127</v>
+        <v>164</v>
       </c>
     </row>
     <row r="308" ht="20" customHeight="1">
@@ -8728,7 +8728,7 @@
         </is>
       </c>
       <c r="E308" s="20" t="n">
-        <v>214</v>
+        <v>140</v>
       </c>
     </row>
     <row r="309" ht="20" customHeight="1">
@@ -8753,7 +8753,7 @@
         </is>
       </c>
       <c r="E309" s="23" t="n">
-        <v>225</v>
+        <v>210</v>
       </c>
     </row>
     <row r="310" ht="20" customHeight="1">
@@ -8778,7 +8778,7 @@
         </is>
       </c>
       <c r="E310" s="20" t="n">
-        <v>159</v>
+        <v>112</v>
       </c>
     </row>
     <row r="311" ht="20" customHeight="1">
@@ -8803,7 +8803,7 @@
         </is>
       </c>
       <c r="E311" s="23" t="n">
-        <v>231</v>
+        <v>116</v>
       </c>
     </row>
     <row r="312" ht="20" customHeight="1">
@@ -8828,7 +8828,7 @@
         </is>
       </c>
       <c r="E312" s="20" t="n">
-        <v>208</v>
+        <v>228</v>
       </c>
     </row>
     <row r="313" ht="20" customHeight="1">
@@ -8853,7 +8853,7 @@
         </is>
       </c>
       <c r="E313" s="23" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="314" ht="20" customHeight="1">
@@ -8878,7 +8878,7 @@
         </is>
       </c>
       <c r="E314" s="20" t="n">
-        <v>185</v>
+        <v>196</v>
       </c>
     </row>
     <row r="315" ht="20" customHeight="1">
@@ -8903,7 +8903,7 @@
         </is>
       </c>
       <c r="E315" s="23" t="n">
-        <v>139</v>
+        <v>184</v>
       </c>
     </row>
     <row r="316" ht="20" customHeight="1">
@@ -8928,7 +8928,7 @@
         </is>
       </c>
       <c r="E316" s="20" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="317" ht="20" customHeight="1">
@@ -8953,7 +8953,7 @@
         </is>
       </c>
       <c r="E317" s="23" t="n">
-        <v>216</v>
+        <v>124</v>
       </c>
     </row>
     <row r="318" ht="20" customHeight="1">
@@ -8978,7 +8978,7 @@
         </is>
       </c>
       <c r="E318" s="20" t="n">
-        <v>118</v>
+        <v>134</v>
       </c>
     </row>
     <row r="319" ht="20" customHeight="1">
@@ -9003,7 +9003,7 @@
         </is>
       </c>
       <c r="E319" s="23" t="n">
-        <v>202</v>
+        <v>186</v>
       </c>
     </row>
     <row r="320" ht="20" customHeight="1">
@@ -9028,7 +9028,7 @@
         </is>
       </c>
       <c r="E320" s="20" t="n">
-        <v>121</v>
+        <v>235</v>
       </c>
     </row>
     <row r="321" ht="20" customHeight="1">
@@ -9053,7 +9053,7 @@
         </is>
       </c>
       <c r="E321" s="23" t="n">
-        <v>127</v>
+        <v>210</v>
       </c>
     </row>
     <row r="322" ht="20" customHeight="1">
@@ -9078,7 +9078,7 @@
         </is>
       </c>
       <c r="E322" s="20" t="n">
-        <v>193</v>
+        <v>136</v>
       </c>
     </row>
     <row r="323" ht="20" customHeight="1">
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="E323" s="23" t="n">
-        <v>173</v>
+        <v>122</v>
       </c>
     </row>
     <row r="324" ht="20" customHeight="1">
@@ -9128,7 +9128,7 @@
         </is>
       </c>
       <c r="E324" s="20" t="n">
-        <v>141</v>
+        <v>152</v>
       </c>
     </row>
     <row r="325" ht="20" customHeight="1">
@@ -9153,7 +9153,7 @@
         </is>
       </c>
       <c r="E325" s="23" t="n">
-        <v>129</v>
+        <v>177</v>
       </c>
     </row>
     <row r="326" ht="20" customHeight="1">
@@ -9178,7 +9178,7 @@
         </is>
       </c>
       <c r="E326" s="20" t="n">
-        <v>197</v>
+        <v>230</v>
       </c>
     </row>
     <row r="327" ht="20" customHeight="1">
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="E327" s="23" t="n">
-        <v>155</v>
+        <v>122</v>
       </c>
     </row>
     <row r="328" ht="20" customHeight="1">
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="E328" s="20" t="n">
-        <v>121</v>
+        <v>215</v>
       </c>
     </row>
     <row r="329" ht="20" customHeight="1">
@@ -9253,7 +9253,7 @@
         </is>
       </c>
       <c r="E329" s="23" t="n">
-        <v>126</v>
+        <v>234</v>
       </c>
     </row>
     <row r="330" ht="20" customHeight="1">
@@ -9278,7 +9278,7 @@
         </is>
       </c>
       <c r="E330" s="20" t="n">
-        <v>221</v>
+        <v>133</v>
       </c>
     </row>
     <row r="331" ht="20" customHeight="1">
@@ -9303,7 +9303,7 @@
         </is>
       </c>
       <c r="E331" s="23" t="n">
-        <v>230</v>
+        <v>165</v>
       </c>
     </row>
     <row r="332" ht="20" customHeight="1">
@@ -9328,7 +9328,7 @@
         </is>
       </c>
       <c r="E332" s="20" t="n">
-        <v>166</v>
+        <v>197</v>
       </c>
     </row>
     <row r="333" ht="20" customHeight="1">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="E333" s="23" t="n">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="334" ht="20" customHeight="1">
@@ -9378,7 +9378,7 @@
         </is>
       </c>
       <c r="E334" s="20" t="n">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="335" ht="20" customHeight="1">
@@ -9403,7 +9403,7 @@
         </is>
       </c>
       <c r="E335" s="23" t="n">
-        <v>133</v>
+        <v>180</v>
       </c>
     </row>
     <row r="336" ht="20" customHeight="1">
@@ -9428,7 +9428,7 @@
         </is>
       </c>
       <c r="E336" s="20" t="n">
-        <v>208</v>
+        <v>239</v>
       </c>
     </row>
     <row r="337" ht="20" customHeight="1">
@@ -9453,7 +9453,7 @@
         </is>
       </c>
       <c r="E337" s="23" t="n">
-        <v>190</v>
+        <v>183</v>
       </c>
     </row>
     <row r="338" ht="20" customHeight="1">
@@ -9478,7 +9478,7 @@
         </is>
       </c>
       <c r="E338" s="20" t="n">
-        <v>204</v>
+        <v>217</v>
       </c>
     </row>
     <row r="339" ht="20" customHeight="1">
@@ -9503,7 +9503,7 @@
         </is>
       </c>
       <c r="E339" s="23" t="n">
-        <v>195</v>
+        <v>240</v>
       </c>
     </row>
     <row r="340" ht="20" customHeight="1">
@@ -9528,7 +9528,7 @@
         </is>
       </c>
       <c r="E340" s="20" t="n">
-        <v>126</v>
+        <v>216</v>
       </c>
     </row>
     <row r="341" ht="20" customHeight="1">
@@ -9553,7 +9553,7 @@
         </is>
       </c>
       <c r="E341" s="23" t="n">
-        <v>165</v>
+        <v>111</v>
       </c>
     </row>
     <row r="342" ht="20" customHeight="1">
@@ -9578,7 +9578,7 @@
         </is>
       </c>
       <c r="E342" s="20" t="n">
-        <v>217</v>
+        <v>224</v>
       </c>
     </row>
     <row r="343" ht="20" customHeight="1">
@@ -9603,7 +9603,7 @@
         </is>
       </c>
       <c r="E343" s="23" t="n">
-        <v>189</v>
+        <v>163</v>
       </c>
     </row>
     <row r="344" ht="20" customHeight="1">
@@ -9628,7 +9628,7 @@
         </is>
       </c>
       <c r="E344" s="20" t="n">
-        <v>231</v>
+        <v>118</v>
       </c>
     </row>
     <row r="345" ht="20" customHeight="1">
@@ -9653,7 +9653,7 @@
         </is>
       </c>
       <c r="E345" s="23" t="n">
-        <v>124</v>
+        <v>149</v>
       </c>
     </row>
     <row r="346" ht="20" customHeight="1">
@@ -9678,7 +9678,7 @@
         </is>
       </c>
       <c r="E346" s="20" t="n">
-        <v>213</v>
+        <v>196</v>
       </c>
     </row>
     <row r="347" ht="20" customHeight="1">
@@ -9703,7 +9703,7 @@
         </is>
       </c>
       <c r="E347" s="23" t="n">
-        <v>138</v>
+        <v>159</v>
       </c>
     </row>
     <row r="348" ht="20" customHeight="1">
@@ -9728,7 +9728,7 @@
         </is>
       </c>
       <c r="E348" s="20" t="n">
-        <v>164</v>
+        <v>231</v>
       </c>
     </row>
     <row r="349" ht="20" customHeight="1">
@@ -9753,7 +9753,7 @@
         </is>
       </c>
       <c r="E349" s="23" t="n">
-        <v>190</v>
+        <v>124</v>
       </c>
     </row>
     <row r="350" ht="20" customHeight="1">
@@ -9778,7 +9778,7 @@
         </is>
       </c>
       <c r="E350" s="20" t="n">
-        <v>155</v>
+        <v>138</v>
       </c>
     </row>
     <row r="351" ht="20" customHeight="1">
@@ -9803,7 +9803,7 @@
         </is>
       </c>
       <c r="E351" s="23" t="n">
-        <v>190</v>
+        <v>214</v>
       </c>
     </row>
     <row r="352" ht="20" customHeight="1">
@@ -9828,7 +9828,7 @@
         </is>
       </c>
       <c r="E352" s="20" t="n">
-        <v>131</v>
+        <v>238</v>
       </c>
     </row>
     <row r="353" ht="20" customHeight="1">
@@ -9853,7 +9853,7 @@
         </is>
       </c>
       <c r="E353" s="23" t="n">
-        <v>110</v>
+        <v>133</v>
       </c>
     </row>
     <row r="354" ht="20" customHeight="1">
@@ -9878,7 +9878,7 @@
         </is>
       </c>
       <c r="E354" s="20" t="n">
-        <v>164</v>
+        <v>210</v>
       </c>
     </row>
     <row r="355" ht="20" customHeight="1">
@@ -9903,7 +9903,7 @@
         </is>
       </c>
       <c r="E355" s="23" t="n">
-        <v>148</v>
+        <v>139</v>
       </c>
     </row>
     <row r="356" ht="20" customHeight="1">
@@ -9928,7 +9928,7 @@
         </is>
       </c>
       <c r="E356" s="20" t="n">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="357" ht="20" customHeight="1">
@@ -9953,7 +9953,7 @@
         </is>
       </c>
       <c r="E357" s="23" t="n">
-        <v>146</v>
+        <v>188</v>
       </c>
     </row>
     <row r="358" ht="20" customHeight="1">
@@ -9978,7 +9978,7 @@
         </is>
       </c>
       <c r="E358" s="20" t="n">
-        <v>205</v>
+        <v>224</v>
       </c>
     </row>
     <row r="359" ht="20" customHeight="1">
@@ -10003,7 +10003,7 @@
         </is>
       </c>
       <c r="E359" s="23" t="n">
-        <v>207</v>
+        <v>198</v>
       </c>
     </row>
     <row r="360" ht="20" customHeight="1">
@@ -10028,7 +10028,7 @@
         </is>
       </c>
       <c r="E360" s="20" t="n">
-        <v>174</v>
+        <v>198</v>
       </c>
     </row>
     <row r="361" ht="20" customHeight="1">
@@ -10053,7 +10053,7 @@
         </is>
       </c>
       <c r="E361" s="23" t="n">
-        <v>152</v>
+        <v>171</v>
       </c>
     </row>
     <row r="362" ht="20" customHeight="1">
@@ -10078,7 +10078,7 @@
         </is>
       </c>
       <c r="E362" s="20" t="n">
-        <v>193</v>
+        <v>124</v>
       </c>
     </row>
     <row r="363" ht="20" customHeight="1">
@@ -10103,7 +10103,7 @@
         </is>
       </c>
       <c r="E363" s="23" t="n">
-        <v>114</v>
+        <v>157</v>
       </c>
     </row>
     <row r="364" ht="20" customHeight="1">
@@ -10128,7 +10128,7 @@
         </is>
       </c>
       <c r="E364" s="20" t="n">
-        <v>238</v>
+        <v>174</v>
       </c>
     </row>
     <row r="365" ht="20" customHeight="1">
@@ -10153,7 +10153,7 @@
         </is>
       </c>
       <c r="E365" s="23" t="n">
-        <v>157</v>
+        <v>196</v>
       </c>
     </row>
     <row r="366" ht="20" customHeight="1">
@@ -10178,7 +10178,7 @@
         </is>
       </c>
       <c r="E366" s="20" t="n">
-        <v>132</v>
+        <v>210</v>
       </c>
     </row>
     <row r="367" ht="20" customHeight="1">
@@ -10203,7 +10203,7 @@
         </is>
       </c>
       <c r="E367" s="23" t="n">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="368" ht="20" customHeight="1">
@@ -10228,7 +10228,7 @@
         </is>
       </c>
       <c r="E368" s="20" t="n">
-        <v>156</v>
+        <v>230</v>
       </c>
     </row>
     <row r="369" ht="20" customHeight="1">
@@ -10253,7 +10253,7 @@
         </is>
       </c>
       <c r="E369" s="23" t="n">
-        <v>193</v>
+        <v>209</v>
       </c>
     </row>
     <row r="370" ht="20" customHeight="1">
@@ -10278,7 +10278,7 @@
         </is>
       </c>
       <c r="E370" s="20" t="n">
-        <v>112</v>
+        <v>223</v>
       </c>
     </row>
     <row r="371" ht="20" customHeight="1">
@@ -10303,7 +10303,7 @@
         </is>
       </c>
       <c r="E371" s="23" t="n">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="372" ht="20" customHeight="1">
@@ -10328,7 +10328,7 @@
         </is>
       </c>
       <c r="E372" s="20" t="n">
-        <v>113</v>
+        <v>174</v>
       </c>
     </row>
     <row r="373" ht="20" customHeight="1">
@@ -10353,7 +10353,7 @@
         </is>
       </c>
       <c r="E373" s="23" t="n">
-        <v>185</v>
+        <v>220</v>
       </c>
     </row>
     <row r="374" ht="20" customHeight="1">
@@ -10378,7 +10378,7 @@
         </is>
       </c>
       <c r="E374" s="20" t="n">
-        <v>186</v>
+        <v>139</v>
       </c>
     </row>
     <row r="375" ht="20" customHeight="1">
@@ -10403,7 +10403,7 @@
         </is>
       </c>
       <c r="E375" s="23" t="n">
-        <v>188</v>
+        <v>179</v>
       </c>
     </row>
     <row r="376" ht="20" customHeight="1">
@@ -10428,7 +10428,7 @@
         </is>
       </c>
       <c r="E376" s="20" t="n">
-        <v>204</v>
+        <v>224</v>
       </c>
     </row>
     <row r="377" ht="20" customHeight="1">
@@ -10453,7 +10453,7 @@
         </is>
       </c>
       <c r="E377" s="23" t="n">
-        <v>172</v>
+        <v>230</v>
       </c>
     </row>
     <row r="378" ht="20" customHeight="1">
@@ -10478,7 +10478,7 @@
         </is>
       </c>
       <c r="E378" s="20" t="n">
-        <v>162</v>
+        <v>167</v>
       </c>
     </row>
     <row r="379" ht="20" customHeight="1">
@@ -10503,7 +10503,7 @@
         </is>
       </c>
       <c r="E379" s="23" t="n">
-        <v>184</v>
+        <v>210</v>
       </c>
     </row>
     <row r="380" ht="20" customHeight="1">
@@ -10528,7 +10528,7 @@
         </is>
       </c>
       <c r="E380" s="20" t="n">
-        <v>132</v>
+        <v>184</v>
       </c>
     </row>
     <row r="381" ht="20" customHeight="1">
@@ -10553,7 +10553,7 @@
         </is>
       </c>
       <c r="E381" s="23" t="n">
-        <v>142</v>
+        <v>129</v>
       </c>
     </row>
     <row r="382" ht="20" customHeight="1">
@@ -10578,7 +10578,7 @@
         </is>
       </c>
       <c r="E382" s="20" t="n">
-        <v>115</v>
+        <v>153</v>
       </c>
     </row>
     <row r="383" ht="20" customHeight="1">
@@ -10603,7 +10603,7 @@
         </is>
       </c>
       <c r="E383" s="23" t="n">
-        <v>176</v>
+        <v>192</v>
       </c>
     </row>
     <row r="384" ht="20" customHeight="1">
@@ -10628,7 +10628,7 @@
         </is>
       </c>
       <c r="E384" s="20" t="n">
-        <v>117</v>
+        <v>217</v>
       </c>
     </row>
     <row r="385" ht="20" customHeight="1">
@@ -10653,7 +10653,7 @@
         </is>
       </c>
       <c r="E385" s="23" t="n">
-        <v>225</v>
+        <v>128</v>
       </c>
     </row>
     <row r="386" ht="20" customHeight="1">
@@ -10678,7 +10678,7 @@
         </is>
       </c>
       <c r="E386" s="20" t="n">
-        <v>217</v>
+        <v>212</v>
       </c>
     </row>
     <row r="387" ht="20" customHeight="1">
@@ -10703,7 +10703,7 @@
         </is>
       </c>
       <c r="E387" s="23" t="n">
-        <v>200</v>
+        <v>172</v>
       </c>
     </row>
     <row r="388" ht="20" customHeight="1">
@@ -10728,7 +10728,7 @@
         </is>
       </c>
       <c r="E388" s="20" t="n">
-        <v>146</v>
+        <v>177</v>
       </c>
     </row>
     <row r="389" ht="20" customHeight="1">
@@ -10753,7 +10753,7 @@
         </is>
       </c>
       <c r="E389" s="23" t="n">
-        <v>192</v>
+        <v>162</v>
       </c>
     </row>
     <row r="390" ht="20" customHeight="1">
@@ -10778,7 +10778,7 @@
         </is>
       </c>
       <c r="E390" s="20" t="n">
-        <v>205</v>
+        <v>172</v>
       </c>
     </row>
     <row r="391" ht="20" customHeight="1">
@@ -10803,7 +10803,7 @@
         </is>
       </c>
       <c r="E391" s="23" t="n">
-        <v>119</v>
+        <v>204</v>
       </c>
     </row>
     <row r="392" ht="20" customHeight="1">
@@ -10828,7 +10828,7 @@
         </is>
       </c>
       <c r="E392" s="20" t="n">
-        <v>165</v>
+        <v>198</v>
       </c>
     </row>
     <row r="393" ht="20" customHeight="1">
@@ -10853,7 +10853,7 @@
         </is>
       </c>
       <c r="E393" s="23" t="n">
-        <v>193</v>
+        <v>121</v>
       </c>
     </row>
     <row r="394" ht="20" customHeight="1">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="E394" s="20" t="n">
-        <v>216</v>
+        <v>136</v>
       </c>
     </row>
     <row r="395" ht="20" customHeight="1">
@@ -10903,7 +10903,7 @@
         </is>
       </c>
       <c r="E395" s="23" t="n">
-        <v>197</v>
+        <v>145</v>
       </c>
     </row>
     <row r="396" ht="20" customHeight="1">
@@ -10928,7 +10928,7 @@
         </is>
       </c>
       <c r="E396" s="20" t="n">
-        <v>163</v>
+        <v>216</v>
       </c>
     </row>
     <row r="397" ht="20" customHeight="1">
@@ -10953,7 +10953,7 @@
         </is>
       </c>
       <c r="E397" s="23" t="n">
-        <v>180</v>
+        <v>123</v>
       </c>
     </row>
     <row r="398" ht="20" customHeight="1">
@@ -10978,7 +10978,7 @@
         </is>
       </c>
       <c r="E398" s="20" t="n">
-        <v>237</v>
+        <v>189</v>
       </c>
     </row>
     <row r="399" ht="20" customHeight="1">
@@ -11003,7 +11003,7 @@
         </is>
       </c>
       <c r="E399" s="23" t="n">
-        <v>181</v>
+        <v>122</v>
       </c>
     </row>
     <row r="400" ht="20" customHeight="1">
@@ -11028,7 +11028,7 @@
         </is>
       </c>
       <c r="E400" s="20" t="n">
-        <v>234</v>
+        <v>205</v>
       </c>
     </row>
     <row r="401" ht="20" customHeight="1">
@@ -11053,7 +11053,7 @@
         </is>
       </c>
       <c r="E401" s="23" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
     </row>
     <row r="402" ht="20" customHeight="1">
@@ -11078,7 +11078,7 @@
         </is>
       </c>
       <c r="E402" s="20" t="n">
-        <v>172</v>
+        <v>111</v>
       </c>
     </row>
     <row r="403" ht="20" customHeight="1">
@@ -11103,7 +11103,7 @@
         </is>
       </c>
       <c r="E403" s="23" t="n">
-        <v>223</v>
+        <v>145</v>
       </c>
     </row>
     <row r="404" ht="20" customHeight="1">
@@ -11128,7 +11128,7 @@
         </is>
       </c>
       <c r="E404" s="20" t="n">
-        <v>111</v>
+        <v>161</v>
       </c>
     </row>
     <row r="405" ht="20" customHeight="1">
@@ -11153,7 +11153,7 @@
         </is>
       </c>
       <c r="E405" s="23" t="n">
-        <v>135</v>
+        <v>197</v>
       </c>
     </row>
     <row r="406" ht="20" customHeight="1">
@@ -11178,7 +11178,7 @@
         </is>
       </c>
       <c r="E406" s="20" t="n">
-        <v>199</v>
+        <v>218</v>
       </c>
     </row>
     <row r="407" ht="20" customHeight="1">
@@ -11203,7 +11203,7 @@
         </is>
       </c>
       <c r="E407" s="23" t="n">
-        <v>151</v>
+        <v>121</v>
       </c>
     </row>
     <row r="408" ht="20" customHeight="1">
@@ -11228,7 +11228,7 @@
         </is>
       </c>
       <c r="E408" s="20" t="n">
-        <v>113</v>
+        <v>203</v>
       </c>
     </row>
     <row r="409" ht="20" customHeight="1">
@@ -11253,7 +11253,7 @@
         </is>
       </c>
       <c r="E409" s="23" t="n">
-        <v>175</v>
+        <v>157</v>
       </c>
     </row>
     <row r="410" ht="20" customHeight="1">
@@ -11278,7 +11278,7 @@
         </is>
       </c>
       <c r="E410" s="20" t="n">
-        <v>192</v>
+        <v>169</v>
       </c>
     </row>
     <row r="411" ht="20" customHeight="1">
@@ -11303,7 +11303,7 @@
         </is>
       </c>
       <c r="E411" s="23" t="n">
-        <v>201</v>
+        <v>113</v>
       </c>
     </row>
     <row r="412" ht="20" customHeight="1">
@@ -11328,7 +11328,7 @@
         </is>
       </c>
       <c r="E412" s="20" t="n">
-        <v>193</v>
+        <v>142</v>
       </c>
     </row>
     <row r="413" ht="20" customHeight="1">
@@ -11353,7 +11353,7 @@
         </is>
       </c>
       <c r="E413" s="23" t="n">
-        <v>173</v>
+        <v>140</v>
       </c>
     </row>
     <row r="414" ht="20" customHeight="1">
@@ -11378,7 +11378,7 @@
         </is>
       </c>
       <c r="E414" s="20" t="n">
-        <v>231</v>
+        <v>192</v>
       </c>
     </row>
     <row r="415" ht="20" customHeight="1">
@@ -11403,7 +11403,7 @@
         </is>
       </c>
       <c r="E415" s="23" t="n">
-        <v>187</v>
+        <v>226</v>
       </c>
     </row>
     <row r="416" ht="20" customHeight="1">
@@ -11428,7 +11428,7 @@
         </is>
       </c>
       <c r="E416" s="20" t="n">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="417" ht="20" customHeight="1">
@@ -11453,7 +11453,7 @@
         </is>
       </c>
       <c r="E417" s="23" t="n">
-        <v>175</v>
+        <v>152</v>
       </c>
     </row>
     <row r="418" ht="20" customHeight="1">
@@ -11478,7 +11478,7 @@
         </is>
       </c>
       <c r="E418" s="20" t="n">
-        <v>126</v>
+        <v>219</v>
       </c>
     </row>
     <row r="419" ht="20" customHeight="1">
@@ -11503,7 +11503,7 @@
         </is>
       </c>
       <c r="E419" s="23" t="n">
-        <v>231</v>
+        <v>192</v>
       </c>
     </row>
     <row r="420" ht="20" customHeight="1">
@@ -11528,7 +11528,7 @@
         </is>
       </c>
       <c r="E420" s="20" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
     </row>
     <row r="421" ht="20" customHeight="1">
@@ -11553,7 +11553,7 @@
         </is>
       </c>
       <c r="E421" s="23" t="n">
-        <v>208</v>
+        <v>195</v>
       </c>
     </row>
     <row r="422" ht="20" customHeight="1">
@@ -11578,7 +11578,7 @@
         </is>
       </c>
       <c r="E422" s="20" t="n">
-        <v>172</v>
+        <v>166</v>
       </c>
     </row>
     <row r="423" ht="20" customHeight="1">
@@ -11603,7 +11603,7 @@
         </is>
       </c>
       <c r="E423" s="23" t="n">
-        <v>219</v>
+        <v>112</v>
       </c>
     </row>
     <row r="424" ht="20" customHeight="1">
@@ -11628,7 +11628,7 @@
         </is>
       </c>
       <c r="E424" s="20" t="n">
-        <v>144</v>
+        <v>179</v>
       </c>
     </row>
     <row r="425" ht="20" customHeight="1">
@@ -11653,7 +11653,7 @@
         </is>
       </c>
       <c r="E425" s="23" t="n">
-        <v>163</v>
+        <v>195</v>
       </c>
     </row>
     <row r="426" ht="20" customHeight="1">
@@ -11678,7 +11678,7 @@
         </is>
       </c>
       <c r="E426" s="20" t="n">
-        <v>114</v>
+        <v>158</v>
       </c>
     </row>
     <row r="427" ht="20" customHeight="1">
@@ -11703,7 +11703,7 @@
         </is>
       </c>
       <c r="E427" s="23" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
     </row>
     <row r="428" ht="20" customHeight="1">
@@ -11728,7 +11728,7 @@
         </is>
       </c>
       <c r="E428" s="20" t="n">
-        <v>226</v>
+        <v>174</v>
       </c>
     </row>
     <row r="429" ht="20" customHeight="1">
@@ -11753,7 +11753,7 @@
         </is>
       </c>
       <c r="E429" s="23" t="n">
-        <v>187</v>
+        <v>125</v>
       </c>
     </row>
     <row r="430" ht="20" customHeight="1">
@@ -11778,7 +11778,7 @@
         </is>
       </c>
       <c r="E430" s="20" t="n">
-        <v>178</v>
+        <v>173</v>
       </c>
     </row>
     <row r="431" ht="20" customHeight="1">
@@ -11803,7 +11803,7 @@
         </is>
       </c>
       <c r="E431" s="23" t="n">
-        <v>218</v>
+        <v>142</v>
       </c>
     </row>
     <row r="432" ht="20" customHeight="1">
@@ -11828,7 +11828,7 @@
         </is>
       </c>
       <c r="E432" s="20" t="n">
-        <v>115</v>
+        <v>188</v>
       </c>
     </row>
     <row r="433" ht="20" customHeight="1">
@@ -11853,7 +11853,7 @@
         </is>
       </c>
       <c r="E433" s="23" t="n">
-        <v>113</v>
+        <v>206</v>
       </c>
     </row>
     <row r="434" ht="20" customHeight="1">
@@ -11878,7 +11878,7 @@
         </is>
       </c>
       <c r="E434" s="20" t="n">
-        <v>234</v>
+        <v>220</v>
       </c>
     </row>
     <row r="435" ht="20" customHeight="1">
@@ -11903,7 +11903,7 @@
         </is>
       </c>
       <c r="E435" s="23" t="n">
-        <v>158</v>
+        <v>114</v>
       </c>
     </row>
     <row r="436" ht="20" customHeight="1">
@@ -11928,7 +11928,7 @@
         </is>
       </c>
       <c r="E436" s="20" t="n">
-        <v>147</v>
+        <v>226</v>
       </c>
     </row>
     <row r="437" ht="20" customHeight="1">
@@ -11953,7 +11953,7 @@
         </is>
       </c>
       <c r="E437" s="23" t="n">
-        <v>237</v>
+        <v>185</v>
       </c>
     </row>
     <row r="438" ht="20" customHeight="1">
@@ -11978,7 +11978,7 @@
         </is>
       </c>
       <c r="E438" s="20" t="n">
-        <v>133</v>
+        <v>182</v>
       </c>
     </row>
     <row r="439" ht="20" customHeight="1">
@@ -12003,7 +12003,7 @@
         </is>
       </c>
       <c r="E439" s="23" t="n">
-        <v>165</v>
+        <v>190</v>
       </c>
     </row>
     <row r="440" ht="20" customHeight="1">
@@ -12028,7 +12028,7 @@
         </is>
       </c>
       <c r="E440" s="20" t="n">
-        <v>182</v>
+        <v>199</v>
       </c>
     </row>
     <row r="441" ht="20" customHeight="1">
@@ -12053,7 +12053,7 @@
         </is>
       </c>
       <c r="E441" s="23" t="n">
-        <v>154</v>
+        <v>206</v>
       </c>
     </row>
     <row r="442" ht="20" customHeight="1">
@@ -12078,7 +12078,7 @@
         </is>
       </c>
       <c r="E442" s="20" t="n">
-        <v>220</v>
+        <v>193</v>
       </c>
     </row>
     <row r="443" ht="20" customHeight="1">
@@ -12103,7 +12103,7 @@
         </is>
       </c>
       <c r="E443" s="23" t="n">
-        <v>212</v>
+        <v>185</v>
       </c>
     </row>
     <row r="444" ht="20" customHeight="1">
@@ -12128,7 +12128,7 @@
         </is>
       </c>
       <c r="E444" s="20" t="n">
-        <v>110</v>
+        <v>164</v>
       </c>
     </row>
     <row r="445" ht="20" customHeight="1">
@@ -12153,7 +12153,7 @@
         </is>
       </c>
       <c r="E445" s="23" t="n">
-        <v>181</v>
+        <v>148</v>
       </c>
     </row>
     <row r="446" ht="20" customHeight="1">
@@ -12178,7 +12178,7 @@
         </is>
       </c>
       <c r="E446" s="20" t="n">
-        <v>165</v>
+        <v>228</v>
       </c>
     </row>
     <row r="447" ht="20" customHeight="1">
@@ -12203,7 +12203,7 @@
         </is>
       </c>
       <c r="E447" s="23" t="n">
-        <v>221</v>
+        <v>112</v>
       </c>
     </row>
     <row r="448" ht="20" customHeight="1">
@@ -12228,7 +12228,7 @@
         </is>
       </c>
       <c r="E448" s="20" t="n">
-        <v>208</v>
+        <v>114</v>
       </c>
     </row>
     <row r="449" ht="20" customHeight="1">
@@ -12253,7 +12253,7 @@
         </is>
       </c>
       <c r="E449" s="23" t="n">
-        <v>171</v>
+        <v>202</v>
       </c>
     </row>
     <row r="450" ht="20" customHeight="1">
@@ -12278,7 +12278,7 @@
         </is>
       </c>
       <c r="E450" s="20" t="n">
-        <v>159</v>
+        <v>194</v>
       </c>
     </row>
     <row r="451" ht="20" customHeight="1">
@@ -12303,7 +12303,7 @@
         </is>
       </c>
       <c r="E451" s="23" t="n">
-        <v>223</v>
+        <v>213</v>
       </c>
     </row>
     <row r="452" ht="20" customHeight="1">
@@ -12328,7 +12328,7 @@
         </is>
       </c>
       <c r="E452" s="20" t="n">
-        <v>186</v>
+        <v>155</v>
       </c>
     </row>
     <row r="453" ht="20" customHeight="1">
@@ -12353,7 +12353,7 @@
         </is>
       </c>
       <c r="E453" s="23" t="n">
-        <v>233</v>
+        <v>168</v>
       </c>
     </row>
     <row r="454" ht="20" customHeight="1">
@@ -12378,7 +12378,7 @@
         </is>
       </c>
       <c r="E454" s="20" t="n">
-        <v>190</v>
+        <v>240</v>
       </c>
     </row>
     <row r="455" ht="20" customHeight="1">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="E455" s="23" t="n">
-        <v>126</v>
+        <v>175</v>
       </c>
     </row>
     <row r="456" ht="20" customHeight="1">
@@ -12428,7 +12428,7 @@
         </is>
       </c>
       <c r="E456" s="20" t="n">
-        <v>232</v>
+        <v>134</v>
       </c>
     </row>
     <row r="457" ht="20" customHeight="1">
@@ -12453,7 +12453,7 @@
         </is>
       </c>
       <c r="E457" s="23" t="n">
-        <v>239</v>
+        <v>180</v>
       </c>
     </row>
     <row r="458" ht="20" customHeight="1">
@@ -12478,7 +12478,7 @@
         </is>
       </c>
       <c r="E458" s="20" t="n">
-        <v>163</v>
+        <v>205</v>
       </c>
     </row>
     <row r="459" ht="20" customHeight="1">
@@ -12503,7 +12503,7 @@
         </is>
       </c>
       <c r="E459" s="23" t="n">
-        <v>154</v>
+        <v>181</v>
       </c>
     </row>
     <row r="460" ht="20" customHeight="1">
@@ -12528,7 +12528,7 @@
         </is>
       </c>
       <c r="E460" s="20" t="n">
-        <v>184</v>
+        <v>128</v>
       </c>
     </row>
     <row r="461" ht="20" customHeight="1">
@@ -12553,7 +12553,7 @@
         </is>
       </c>
       <c r="E461" s="23" t="n">
-        <v>175</v>
+        <v>154</v>
       </c>
     </row>
     <row r="462" ht="20" customHeight="1">
@@ -12578,7 +12578,7 @@
         </is>
       </c>
       <c r="E462" s="20" t="n">
-        <v>192</v>
+        <v>138</v>
       </c>
     </row>
     <row r="463" ht="20" customHeight="1">
@@ -12603,7 +12603,7 @@
         </is>
       </c>
       <c r="E463" s="23" t="n">
-        <v>170</v>
+        <v>220</v>
       </c>
     </row>
     <row r="464" ht="20" customHeight="1">
@@ -12628,7 +12628,7 @@
         </is>
       </c>
       <c r="E464" s="20" t="n">
-        <v>203</v>
+        <v>143</v>
       </c>
     </row>
     <row r="465" ht="20" customHeight="1">
@@ -12653,7 +12653,7 @@
         </is>
       </c>
       <c r="E465" s="23" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="466" ht="20" customHeight="1">
@@ -12678,7 +12678,7 @@
         </is>
       </c>
       <c r="E466" s="20" t="n">
-        <v>180</v>
+        <v>131</v>
       </c>
     </row>
     <row r="467" ht="20" customHeight="1">
@@ -12703,7 +12703,7 @@
         </is>
       </c>
       <c r="E467" s="23" t="n">
-        <v>199</v>
+        <v>187</v>
       </c>
     </row>
     <row r="468" ht="20" customHeight="1">
@@ -12728,7 +12728,7 @@
         </is>
       </c>
       <c r="E468" s="20" t="n">
-        <v>186</v>
+        <v>123</v>
       </c>
     </row>
     <row r="469" ht="20" customHeight="1">
@@ -12753,7 +12753,7 @@
         </is>
       </c>
       <c r="E469" s="23" t="n">
-        <v>157</v>
+        <v>188</v>
       </c>
     </row>
     <row r="470" ht="20" customHeight="1">
@@ -12778,7 +12778,7 @@
         </is>
       </c>
       <c r="E470" s="20" t="n">
-        <v>131</v>
+        <v>179</v>
       </c>
     </row>
     <row r="471" ht="20" customHeight="1">
@@ -12803,7 +12803,7 @@
         </is>
       </c>
       <c r="E471" s="23" t="n">
-        <v>195</v>
+        <v>191</v>
       </c>
     </row>
     <row r="472" ht="20" customHeight="1">
@@ -12828,7 +12828,7 @@
         </is>
       </c>
       <c r="E472" s="20" t="n">
-        <v>172</v>
+        <v>111</v>
       </c>
     </row>
     <row r="473" ht="20" customHeight="1">
@@ -12853,7 +12853,7 @@
         </is>
       </c>
       <c r="E473" s="23" t="n">
-        <v>222</v>
+        <v>138</v>
       </c>
     </row>
     <row r="474" ht="20" customHeight="1">
@@ -12878,7 +12878,7 @@
         </is>
       </c>
       <c r="E474" s="20" t="n">
-        <v>226</v>
+        <v>199</v>
       </c>
     </row>
     <row r="475" ht="20" customHeight="1">
@@ -12903,7 +12903,7 @@
         </is>
       </c>
       <c r="E475" s="23" t="n">
-        <v>148</v>
+        <v>142</v>
       </c>
     </row>
     <row r="476" ht="20" customHeight="1">
@@ -12928,7 +12928,7 @@
         </is>
       </c>
       <c r="E476" s="20" t="n">
-        <v>175</v>
+        <v>213</v>
       </c>
     </row>
     <row r="477" ht="20" customHeight="1">
@@ -12953,7 +12953,7 @@
         </is>
       </c>
       <c r="E477" s="23" t="n">
-        <v>123</v>
+        <v>154</v>
       </c>
     </row>
     <row r="478" ht="20" customHeight="1">
@@ -12978,7 +12978,7 @@
         </is>
       </c>
       <c r="E478" s="20" t="n">
-        <v>225</v>
+        <v>166</v>
       </c>
     </row>
     <row r="479" ht="20" customHeight="1">
@@ -13003,7 +13003,7 @@
         </is>
       </c>
       <c r="E479" s="23" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="480" ht="20" customHeight="1">
@@ -13028,7 +13028,7 @@
         </is>
       </c>
       <c r="E480" s="20" t="n">
-        <v>179</v>
+        <v>211</v>
       </c>
     </row>
     <row r="481" ht="20" customHeight="1">
@@ -13053,7 +13053,7 @@
         </is>
       </c>
       <c r="E481" s="23" t="n">
-        <v>213</v>
+        <v>193</v>
       </c>
     </row>
     <row r="482" ht="20" customHeight="1">
@@ -13078,7 +13078,7 @@
         </is>
       </c>
       <c r="E482" s="20" t="n">
-        <v>140</v>
+        <v>211</v>
       </c>
     </row>
     <row r="483" ht="20" customHeight="1">
@@ -13103,7 +13103,7 @@
         </is>
       </c>
       <c r="E483" s="23" t="n">
-        <v>118</v>
+        <v>231</v>
       </c>
     </row>
     <row r="484" ht="20" customHeight="1">
@@ -13128,7 +13128,7 @@
         </is>
       </c>
       <c r="E484" s="20" t="n">
-        <v>180</v>
+        <v>130</v>
       </c>
     </row>
     <row r="485" ht="20" customHeight="1">
@@ -13153,7 +13153,7 @@
         </is>
       </c>
       <c r="E485" s="23" t="n">
-        <v>168</v>
+        <v>181</v>
       </c>
     </row>
     <row r="486" ht="20" customHeight="1">
@@ -13178,7 +13178,7 @@
         </is>
       </c>
       <c r="E486" s="20" t="n">
-        <v>213</v>
+        <v>166</v>
       </c>
     </row>
     <row r="487" ht="20" customHeight="1">
@@ -13203,7 +13203,7 @@
         </is>
       </c>
       <c r="E487" s="23" t="n">
-        <v>193</v>
+        <v>203</v>
       </c>
     </row>
     <row r="488" ht="20" customHeight="1">
@@ -13228,7 +13228,7 @@
         </is>
       </c>
       <c r="E488" s="20" t="n">
-        <v>166</v>
+        <v>228</v>
       </c>
     </row>
     <row r="489" ht="20" customHeight="1">
@@ -13253,7 +13253,7 @@
         </is>
       </c>
       <c r="E489" s="23" t="n">
-        <v>190</v>
+        <v>168</v>
       </c>
     </row>
     <row r="490" ht="20" customHeight="1">
@@ -13278,7 +13278,7 @@
         </is>
       </c>
       <c r="E490" s="20" t="n">
-        <v>179</v>
+        <v>200</v>
       </c>
     </row>
     <row r="491" ht="20" customHeight="1">
@@ -13303,7 +13303,7 @@
         </is>
       </c>
       <c r="E491" s="23" t="n">
-        <v>135</v>
+        <v>149</v>
       </c>
     </row>
     <row r="492" ht="20" customHeight="1">
@@ -13328,7 +13328,7 @@
         </is>
       </c>
       <c r="E492" s="20" t="n">
-        <v>190</v>
+        <v>158</v>
       </c>
     </row>
     <row r="493" ht="20" customHeight="1">
@@ -13353,7 +13353,7 @@
         </is>
       </c>
       <c r="E493" s="23" t="n">
-        <v>174</v>
+        <v>112</v>
       </c>
     </row>
     <row r="494" ht="20" customHeight="1">
@@ -13378,7 +13378,7 @@
         </is>
       </c>
       <c r="E494" s="20" t="n">
-        <v>150</v>
+        <v>237</v>
       </c>
     </row>
     <row r="495" ht="20" customHeight="1">
@@ -13403,7 +13403,7 @@
         </is>
       </c>
       <c r="E495" s="23" t="n">
-        <v>161</v>
+        <v>173</v>
       </c>
     </row>
     <row r="496" ht="20" customHeight="1">
@@ -13428,7 +13428,7 @@
         </is>
       </c>
       <c r="E496" s="20" t="n">
-        <v>158</v>
+        <v>203</v>
       </c>
     </row>
     <row r="497" ht="20" customHeight="1">
@@ -13453,7 +13453,7 @@
         </is>
       </c>
       <c r="E497" s="23" t="n">
-        <v>129</v>
+        <v>203</v>
       </c>
     </row>
     <row r="498" ht="20" customHeight="1">
@@ -13478,7 +13478,7 @@
         </is>
       </c>
       <c r="E498" s="20" t="n">
-        <v>237</v>
+        <v>144</v>
       </c>
     </row>
     <row r="499" ht="20" customHeight="1">
@@ -13503,7 +13503,7 @@
         </is>
       </c>
       <c r="E499" s="23" t="n">
-        <v>140</v>
+        <v>200</v>
       </c>
     </row>
     <row r="500" ht="20" customHeight="1">
@@ -13528,7 +13528,7 @@
         </is>
       </c>
       <c r="E500" s="20" t="n">
-        <v>191</v>
+        <v>133</v>
       </c>
     </row>
     <row r="501" ht="20" customHeight="1">
@@ -13553,7 +13553,7 @@
         </is>
       </c>
       <c r="E501" s="23" t="n">
-        <v>180</v>
+        <v>111</v>
       </c>
     </row>
     <row r="502" ht="20" customHeight="1">
@@ -13578,7 +13578,7 @@
         </is>
       </c>
       <c r="E502" s="20" t="n">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="503" ht="20" customHeight="1">
@@ -13603,7 +13603,7 @@
         </is>
       </c>
       <c r="E503" s="23" t="n">
-        <v>203</v>
+        <v>236</v>
       </c>
     </row>
     <row r="504" ht="20" customHeight="1">
@@ -13628,7 +13628,7 @@
         </is>
       </c>
       <c r="E504" s="20" t="n">
-        <v>163</v>
+        <v>239</v>
       </c>
     </row>
     <row r="505" ht="20" customHeight="1">
@@ -13653,7 +13653,7 @@
         </is>
       </c>
       <c r="E505" s="23" t="n">
-        <v>167</v>
+        <v>116</v>
       </c>
     </row>
     <row r="506" ht="20" customHeight="1">
@@ -13678,7 +13678,7 @@
         </is>
       </c>
       <c r="E506" s="20" t="n">
-        <v>164</v>
+        <v>230</v>
       </c>
     </row>
     <row r="507" ht="20" customHeight="1">
@@ -13703,7 +13703,7 @@
         </is>
       </c>
       <c r="E507" s="23" t="n">
-        <v>231</v>
+        <v>179</v>
       </c>
     </row>
     <row r="508" ht="20" customHeight="1">
@@ -13728,7 +13728,7 @@
         </is>
       </c>
       <c r="E508" s="20" t="n">
-        <v>211</v>
+        <v>240</v>
       </c>
     </row>
     <row r="509" ht="20" customHeight="1">
@@ -13753,7 +13753,7 @@
         </is>
       </c>
       <c r="E509" s="23" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="510" ht="20" customHeight="1">
@@ -13778,7 +13778,7 @@
         </is>
       </c>
       <c r="E510" s="20" t="n">
-        <v>174</v>
+        <v>144</v>
       </c>
     </row>
     <row r="511" ht="20" customHeight="1">
@@ -13803,7 +13803,7 @@
         </is>
       </c>
       <c r="E511" s="23" t="n">
-        <v>135</v>
+        <v>216</v>
       </c>
     </row>
     <row r="512" ht="20" customHeight="1">
@@ -13828,7 +13828,7 @@
         </is>
       </c>
       <c r="E512" s="20" t="n">
-        <v>185</v>
+        <v>146</v>
       </c>
     </row>
     <row r="513" ht="20" customHeight="1">
@@ -13853,7 +13853,7 @@
         </is>
       </c>
       <c r="E513" s="23" t="n">
-        <v>239</v>
+        <v>155</v>
       </c>
     </row>
     <row r="514" ht="20" customHeight="1">
@@ -13878,7 +13878,7 @@
         </is>
       </c>
       <c r="E514" s="20" t="n">
-        <v>168</v>
+        <v>128</v>
       </c>
     </row>
     <row r="515" ht="20" customHeight="1">
@@ -13903,7 +13903,7 @@
         </is>
       </c>
       <c r="E515" s="23" t="n">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="516" ht="20" customHeight="1">
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="E516" s="20" t="n">
-        <v>120</v>
+        <v>132</v>
       </c>
     </row>
     <row r="517" ht="20" customHeight="1">
@@ -13953,7 +13953,7 @@
         </is>
       </c>
       <c r="E517" s="23" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="518" ht="20" customHeight="1">
@@ -13978,7 +13978,7 @@
         </is>
       </c>
       <c r="E518" s="20" t="n">
-        <v>183</v>
+        <v>148</v>
       </c>
     </row>
     <row r="519" ht="20" customHeight="1">
@@ -14003,7 +14003,7 @@
         </is>
       </c>
       <c r="E519" s="23" t="n">
-        <v>126</v>
+        <v>240</v>
       </c>
     </row>
     <row r="520" ht="20" customHeight="1">
@@ -14028,7 +14028,7 @@
         </is>
       </c>
       <c r="E520" s="20" t="n">
-        <v>202</v>
+        <v>122</v>
       </c>
     </row>
     <row r="521" ht="20" customHeight="1">
@@ -14053,7 +14053,7 @@
         </is>
       </c>
       <c r="E521" s="23" t="n">
-        <v>177</v>
+        <v>119</v>
       </c>
     </row>
     <row r="522" ht="20" customHeight="1">
@@ -14078,7 +14078,7 @@
         </is>
       </c>
       <c r="E522" s="20" t="n">
-        <v>214</v>
+        <v>115</v>
       </c>
     </row>
     <row r="523" ht="20" customHeight="1">
@@ -14103,7 +14103,7 @@
         </is>
       </c>
       <c r="E523" s="23" t="n">
-        <v>128</v>
+        <v>237</v>
       </c>
     </row>
     <row r="524" ht="20" customHeight="1">
@@ -14128,7 +14128,7 @@
         </is>
       </c>
       <c r="E524" s="20" t="n">
-        <v>169</v>
+        <v>148</v>
       </c>
     </row>
     <row r="525" ht="20" customHeight="1">
@@ -14153,7 +14153,7 @@
         </is>
       </c>
       <c r="E525" s="23" t="n">
-        <v>221</v>
+        <v>179</v>
       </c>
     </row>
     <row r="526" ht="20" customHeight="1">
@@ -14178,7 +14178,7 @@
         </is>
       </c>
       <c r="E526" s="20" t="n">
-        <v>113</v>
+        <v>164</v>
       </c>
     </row>
     <row r="527" ht="20" customHeight="1">
@@ -14203,7 +14203,7 @@
         </is>
       </c>
       <c r="E527" s="23" t="n">
-        <v>115</v>
+        <v>218</v>
       </c>
     </row>
     <row r="528" ht="20" customHeight="1">
@@ -14228,7 +14228,7 @@
         </is>
       </c>
       <c r="E528" s="20" t="n">
-        <v>152</v>
+        <v>232</v>
       </c>
     </row>
     <row r="529" ht="20" customHeight="1">
@@ -14253,7 +14253,7 @@
         </is>
       </c>
       <c r="E529" s="23" t="n">
-        <v>150</v>
+        <v>187</v>
       </c>
     </row>
     <row r="530" ht="20" customHeight="1">
@@ -14278,7 +14278,7 @@
         </is>
       </c>
       <c r="E530" s="20" t="n">
-        <v>163</v>
+        <v>158</v>
       </c>
     </row>
     <row r="531" ht="20" customHeight="1">
@@ -14303,7 +14303,7 @@
         </is>
       </c>
       <c r="E531" s="23" t="n">
-        <v>121</v>
+        <v>205</v>
       </c>
     </row>
     <row r="532" ht="20" customHeight="1">
@@ -14328,7 +14328,7 @@
         </is>
       </c>
       <c r="E532" s="20" t="n">
-        <v>146</v>
+        <v>173</v>
       </c>
     </row>
     <row r="533" ht="20" customHeight="1">
@@ -14353,7 +14353,7 @@
         </is>
       </c>
       <c r="E533" s="23" t="n">
-        <v>212</v>
+        <v>232</v>
       </c>
     </row>
     <row r="534" ht="20" customHeight="1">
@@ -14378,7 +14378,7 @@
         </is>
       </c>
       <c r="E534" s="20" t="n">
-        <v>183</v>
+        <v>193</v>
       </c>
     </row>
     <row r="535" ht="20" customHeight="1">
@@ -14403,7 +14403,7 @@
         </is>
       </c>
       <c r="E535" s="23" t="n">
-        <v>231</v>
+        <v>175</v>
       </c>
     </row>
     <row r="536" ht="20" customHeight="1">
@@ -14428,7 +14428,7 @@
         </is>
       </c>
       <c r="E536" s="20" t="n">
-        <v>216</v>
+        <v>132</v>
       </c>
     </row>
     <row r="537" ht="20" customHeight="1">
@@ -14453,7 +14453,7 @@
         </is>
       </c>
       <c r="E537" s="23" t="n">
-        <v>221</v>
+        <v>178</v>
       </c>
     </row>
     <row r="538" ht="20" customHeight="1">
@@ -14478,7 +14478,7 @@
         </is>
       </c>
       <c r="E538" s="20" t="n">
-        <v>238</v>
+        <v>222</v>
       </c>
     </row>
     <row r="539" ht="20" customHeight="1">
@@ -14503,7 +14503,7 @@
         </is>
       </c>
       <c r="E539" s="23" t="n">
-        <v>169</v>
+        <v>196</v>
       </c>
     </row>
     <row r="540" ht="20" customHeight="1">
@@ -14528,7 +14528,7 @@
         </is>
       </c>
       <c r="E540" s="20" t="n">
-        <v>175</v>
+        <v>116</v>
       </c>
     </row>
     <row r="541" ht="20" customHeight="1">
@@ -14553,7 +14553,7 @@
         </is>
       </c>
       <c r="E541" s="23" t="n">
-        <v>216</v>
+        <v>153</v>
       </c>
     </row>
     <row r="542" ht="20" customHeight="1">
@@ -14578,7 +14578,7 @@
         </is>
       </c>
       <c r="E542" s="20" t="n">
-        <v>204</v>
+        <v>222</v>
       </c>
     </row>
     <row r="543" ht="20" customHeight="1">
@@ -14603,7 +14603,7 @@
         </is>
       </c>
       <c r="E543" s="23" t="n">
-        <v>185</v>
+        <v>126</v>
       </c>
     </row>
     <row r="544" ht="20" customHeight="1">
@@ -14628,7 +14628,7 @@
         </is>
       </c>
       <c r="E544" s="20" t="n">
-        <v>111</v>
+        <v>170</v>
       </c>
     </row>
     <row r="545" ht="20" customHeight="1">
@@ -14653,7 +14653,7 @@
         </is>
       </c>
       <c r="E545" s="23" t="n">
-        <v>169</v>
+        <v>197</v>
       </c>
     </row>
     <row r="546" ht="20" customHeight="1">
@@ -14678,7 +14678,7 @@
         </is>
       </c>
       <c r="E546" s="20" t="n">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="547" ht="20" customHeight="1">
@@ -14703,7 +14703,7 @@
         </is>
       </c>
       <c r="E547" s="23" t="n">
-        <v>126</v>
+        <v>165</v>
       </c>
     </row>
     <row r="548" ht="20" customHeight="1">
@@ -14728,7 +14728,7 @@
         </is>
       </c>
       <c r="E548" s="20" t="n">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="549" ht="20" customHeight="1">
@@ -14753,7 +14753,7 @@
         </is>
       </c>
       <c r="E549" s="23" t="n">
-        <v>169</v>
+        <v>132</v>
       </c>
     </row>
     <row r="550" ht="20" customHeight="1">
@@ -14778,7 +14778,7 @@
         </is>
       </c>
       <c r="E550" s="20" t="n">
-        <v>204</v>
+        <v>127</v>
       </c>
     </row>
     <row r="551" ht="20" customHeight="1">
@@ -14803,7 +14803,7 @@
         </is>
       </c>
       <c r="E551" s="23" t="n">
-        <v>165</v>
+        <v>217</v>
       </c>
     </row>
     <row r="552" ht="20" customHeight="1">
@@ -14828,7 +14828,7 @@
         </is>
       </c>
       <c r="E552" s="20" t="n">
-        <v>123</v>
+        <v>167</v>
       </c>
     </row>
     <row r="553" ht="20" customHeight="1">
@@ -14853,7 +14853,7 @@
         </is>
       </c>
       <c r="E553" s="23" t="n">
-        <v>178</v>
+        <v>173</v>
       </c>
     </row>
     <row r="554" ht="20" customHeight="1">
@@ -14878,7 +14878,7 @@
         </is>
       </c>
       <c r="E554" s="20" t="n">
-        <v>149</v>
+        <v>240</v>
       </c>
     </row>
     <row r="555" ht="20" customHeight="1">
@@ -14903,7 +14903,7 @@
         </is>
       </c>
       <c r="E555" s="23" t="n">
-        <v>214</v>
+        <v>181</v>
       </c>
     </row>
     <row r="556" ht="20" customHeight="1">
@@ -14928,7 +14928,7 @@
         </is>
       </c>
       <c r="E556" s="20" t="n">
-        <v>176</v>
+        <v>167</v>
       </c>
     </row>
     <row r="557" ht="20" customHeight="1">
@@ -14953,7 +14953,7 @@
         </is>
       </c>
       <c r="E557" s="23" t="n">
-        <v>210</v>
+        <v>141</v>
       </c>
     </row>
     <row r="558" ht="20" customHeight="1">
@@ -14978,7 +14978,7 @@
         </is>
       </c>
       <c r="E558" s="20" t="n">
-        <v>110</v>
+        <v>234</v>
       </c>
     </row>
     <row r="559" ht="20" customHeight="1">
@@ -15003,7 +15003,7 @@
         </is>
       </c>
       <c r="E559" s="23" t="n">
-        <v>119</v>
+        <v>132</v>
       </c>
     </row>
     <row r="560" ht="20" customHeight="1">
@@ -15028,7 +15028,7 @@
         </is>
       </c>
       <c r="E560" s="20" t="n">
-        <v>218</v>
+        <v>189</v>
       </c>
     </row>
     <row r="561" ht="20" customHeight="1">
@@ -15053,7 +15053,7 @@
         </is>
       </c>
       <c r="E561" s="23" t="n">
-        <v>231</v>
+        <v>186</v>
       </c>
     </row>
     <row r="562" ht="20" customHeight="1">
@@ -15078,7 +15078,7 @@
         </is>
       </c>
       <c r="E562" s="20" t="n">
-        <v>182</v>
+        <v>203</v>
       </c>
     </row>
     <row r="563" ht="20" customHeight="1">
@@ -15103,7 +15103,7 @@
         </is>
       </c>
       <c r="E563" s="23" t="n">
-        <v>138</v>
+        <v>171</v>
       </c>
     </row>
     <row r="564" ht="20" customHeight="1">
@@ -15128,7 +15128,7 @@
         </is>
       </c>
       <c r="E564" s="20" t="n">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="565" ht="20" customHeight="1">
@@ -15153,7 +15153,7 @@
         </is>
       </c>
       <c r="E565" s="23" t="n">
-        <v>223</v>
+        <v>217</v>
       </c>
     </row>
     <row r="566" ht="20" customHeight="1">
@@ -15178,7 +15178,7 @@
         </is>
       </c>
       <c r="E566" s="20" t="n">
-        <v>206</v>
+        <v>233</v>
       </c>
     </row>
     <row r="567" ht="20" customHeight="1">
@@ -15203,7 +15203,7 @@
         </is>
       </c>
       <c r="E567" s="23" t="n">
-        <v>203</v>
+        <v>125</v>
       </c>
     </row>
     <row r="568" ht="20" customHeight="1">
@@ -15228,7 +15228,7 @@
         </is>
       </c>
       <c r="E568" s="20" t="n">
-        <v>115</v>
+        <v>132</v>
       </c>
     </row>
     <row r="569" ht="20" customHeight="1">
@@ -15253,7 +15253,7 @@
         </is>
       </c>
       <c r="E569" s="23" t="n">
-        <v>153</v>
+        <v>211</v>
       </c>
     </row>
     <row r="570" ht="20" customHeight="1">
@@ -15278,7 +15278,7 @@
         </is>
       </c>
       <c r="E570" s="20" t="n">
-        <v>236</v>
+        <v>152</v>
       </c>
     </row>
     <row r="571" ht="20" customHeight="1">
@@ -15303,7 +15303,7 @@
         </is>
       </c>
       <c r="E571" s="23" t="n">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="572" ht="20" customHeight="1">
@@ -15328,7 +15328,7 @@
         </is>
       </c>
       <c r="E572" s="20" t="n">
-        <v>223</v>
+        <v>233</v>
       </c>
     </row>
     <row r="573" ht="20" customHeight="1">
@@ -15353,7 +15353,7 @@
         </is>
       </c>
       <c r="E573" s="23" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="574" ht="20" customHeight="1">
@@ -15378,7 +15378,7 @@
         </is>
       </c>
       <c r="E574" s="20" t="n">
-        <v>134</v>
+        <v>239</v>
       </c>
     </row>
     <row r="575" ht="20" customHeight="1">
@@ -15403,7 +15403,7 @@
         </is>
       </c>
       <c r="E575" s="23" t="n">
-        <v>123</v>
+        <v>207</v>
       </c>
     </row>
     <row r="576" ht="20" customHeight="1">
@@ -15428,7 +15428,7 @@
         </is>
       </c>
       <c r="E576" s="20" t="n">
-        <v>152</v>
+        <v>195</v>
       </c>
     </row>
     <row r="577" ht="20" customHeight="1">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="E577" s="23" t="n">
-        <v>199</v>
+        <v>136</v>
       </c>
     </row>
     <row r="578" ht="20" customHeight="1">
@@ -15478,7 +15478,7 @@
         </is>
       </c>
       <c r="E578" s="20" t="n">
-        <v>143</v>
+        <v>122</v>
       </c>
     </row>
     <row r="579" ht="20" customHeight="1">
@@ -15503,7 +15503,7 @@
         </is>
       </c>
       <c r="E579" s="23" t="n">
-        <v>158</v>
+        <v>228</v>
       </c>
     </row>
     <row r="580" ht="20" customHeight="1">
@@ -15528,7 +15528,7 @@
         </is>
       </c>
       <c r="E580" s="20" t="n">
-        <v>159</v>
+        <v>138</v>
       </c>
     </row>
     <row r="581" ht="20" customHeight="1">
@@ -15553,7 +15553,7 @@
         </is>
       </c>
       <c r="E581" s="23" t="n">
-        <v>120</v>
+        <v>203</v>
       </c>
     </row>
     <row r="582" ht="20" customHeight="1">
@@ -15578,7 +15578,7 @@
         </is>
       </c>
       <c r="E582" s="20" t="n">
-        <v>225</v>
+        <v>231</v>
       </c>
     </row>
     <row r="583" ht="20" customHeight="1">
@@ -15603,7 +15603,7 @@
         </is>
       </c>
       <c r="E583" s="23" t="n">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="584" ht="20" customHeight="1">
@@ -15628,7 +15628,7 @@
         </is>
       </c>
       <c r="E584" s="20" t="n">
-        <v>141</v>
+        <v>154</v>
       </c>
     </row>
     <row r="585" ht="20" customHeight="1">
@@ -15653,7 +15653,7 @@
         </is>
       </c>
       <c r="E585" s="23" t="n">
-        <v>144</v>
+        <v>139</v>
       </c>
     </row>
     <row r="586" ht="20" customHeight="1">
@@ -15678,7 +15678,7 @@
         </is>
       </c>
       <c r="E586" s="20" t="n">
-        <v>119</v>
+        <v>161</v>
       </c>
     </row>
     <row r="587" ht="20" customHeight="1">
@@ -15703,7 +15703,7 @@
         </is>
       </c>
       <c r="E587" s="23" t="n">
-        <v>175</v>
+        <v>238</v>
       </c>
     </row>
     <row r="588" ht="20" customHeight="1">
@@ -15728,7 +15728,7 @@
         </is>
       </c>
       <c r="E588" s="20" t="n">
-        <v>240</v>
+        <v>196</v>
       </c>
     </row>
     <row r="589" ht="20" customHeight="1">
@@ -15753,7 +15753,7 @@
         </is>
       </c>
       <c r="E589" s="23" t="n">
-        <v>187</v>
+        <v>222</v>
       </c>
     </row>
     <row r="590" ht="20" customHeight="1">
@@ -15778,7 +15778,7 @@
         </is>
       </c>
       <c r="E590" s="20" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="591" ht="20" customHeight="1">
@@ -15828,7 +15828,7 @@
         </is>
       </c>
       <c r="E592" s="20" t="n">
-        <v>238</v>
+        <v>189</v>
       </c>
     </row>
     <row r="593" ht="20" customHeight="1">
@@ -15853,7 +15853,7 @@
         </is>
       </c>
       <c r="E593" s="23" t="n">
-        <v>225</v>
+        <v>240</v>
       </c>
     </row>
     <row r="594" ht="20" customHeight="1">
@@ -15878,7 +15878,7 @@
         </is>
       </c>
       <c r="E594" s="20" t="n">
-        <v>197</v>
+        <v>215</v>
       </c>
     </row>
     <row r="595" ht="20" customHeight="1">
@@ -15903,7 +15903,7 @@
         </is>
       </c>
       <c r="E595" s="23" t="n">
-        <v>222</v>
+        <v>212</v>
       </c>
     </row>
     <row r="596" ht="20" customHeight="1">
@@ -15928,7 +15928,7 @@
         </is>
       </c>
       <c r="E596" s="20" t="n">
-        <v>179</v>
+        <v>215</v>
       </c>
     </row>
     <row r="597" ht="20" customHeight="1">
@@ -15953,7 +15953,7 @@
         </is>
       </c>
       <c r="E597" s="23" t="n">
-        <v>137</v>
+        <v>187</v>
       </c>
     </row>
     <row r="598" ht="20" customHeight="1">
@@ -15978,7 +15978,7 @@
         </is>
       </c>
       <c r="E598" s="20" t="n">
-        <v>191</v>
+        <v>121</v>
       </c>
     </row>
     <row r="599" ht="20" customHeight="1">
@@ -16003,7 +16003,7 @@
         </is>
       </c>
       <c r="E599" s="23" t="n">
-        <v>174</v>
+        <v>211</v>
       </c>
     </row>
     <row r="600" ht="20" customHeight="1">
@@ -16028,7 +16028,7 @@
         </is>
       </c>
       <c r="E600" s="20" t="n">
-        <v>154</v>
+        <v>132</v>
       </c>
     </row>
     <row r="601" ht="20" customHeight="1">
@@ -16053,7 +16053,7 @@
         </is>
       </c>
       <c r="E601" s="23" t="n">
-        <v>158</v>
+        <v>122</v>
       </c>
     </row>
     <row r="602" ht="20" customHeight="1">
@@ -16078,7 +16078,7 @@
         </is>
       </c>
       <c r="E602" s="20" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="603" ht="20" customHeight="1">
@@ -16103,7 +16103,7 @@
         </is>
       </c>
       <c r="E603" s="23" t="n">
-        <v>124</v>
+        <v>190</v>
       </c>
     </row>
     <row r="604" ht="20" customHeight="1">
@@ -16128,7 +16128,7 @@
         </is>
       </c>
       <c r="E604" s="20" t="n">
-        <v>237</v>
+        <v>150</v>
       </c>
     </row>
     <row r="605" ht="20" customHeight="1">
@@ -16153,7 +16153,7 @@
         </is>
       </c>
       <c r="E605" s="23" t="n">
-        <v>221</v>
+        <v>228</v>
       </c>
     </row>
     <row r="606" ht="20" customHeight="1">
@@ -16178,7 +16178,7 @@
         </is>
       </c>
       <c r="E606" s="20" t="n">
-        <v>143</v>
+        <v>158</v>
       </c>
     </row>
     <row r="607" ht="20" customHeight="1">
@@ -16203,7 +16203,7 @@
         </is>
       </c>
       <c r="E607" s="23" t="n">
-        <v>182</v>
+        <v>201</v>
       </c>
     </row>
     <row r="608" ht="20" customHeight="1">
@@ -16228,7 +16228,7 @@
         </is>
       </c>
       <c r="E608" s="20" t="n">
-        <v>235</v>
+        <v>195</v>
       </c>
     </row>
     <row r="609" ht="20" customHeight="1">
@@ -16253,7 +16253,7 @@
         </is>
       </c>
       <c r="E609" s="23" t="n">
-        <v>152</v>
+        <v>127</v>
       </c>
     </row>
     <row r="610" ht="20" customHeight="1">
@@ -16278,7 +16278,7 @@
         </is>
       </c>
       <c r="E610" s="20" t="n">
-        <v>145</v>
+        <v>190</v>
       </c>
     </row>
     <row r="611" ht="20" customHeight="1">
@@ -16303,7 +16303,7 @@
         </is>
       </c>
       <c r="E611" s="23" t="n">
-        <v>113</v>
+        <v>173</v>
       </c>
     </row>
     <row r="612" ht="20" customHeight="1">
@@ -16328,7 +16328,7 @@
         </is>
       </c>
       <c r="E612" s="20" t="n">
-        <v>169</v>
+        <v>238</v>
       </c>
     </row>
     <row r="613" ht="20" customHeight="1">
@@ -16353,7 +16353,7 @@
         </is>
       </c>
       <c r="E613" s="23" t="n">
-        <v>111</v>
+        <v>120</v>
       </c>
     </row>
     <row r="614" ht="20" customHeight="1">
@@ -16378,7 +16378,7 @@
         </is>
       </c>
       <c r="E614" s="20" t="n">
-        <v>227</v>
+        <v>176</v>
       </c>
     </row>
     <row r="615" ht="20" customHeight="1">
@@ -16403,7 +16403,7 @@
         </is>
       </c>
       <c r="E615" s="23" t="n">
-        <v>142</v>
+        <v>150</v>
       </c>
     </row>
     <row r="616" ht="20" customHeight="1">
@@ -16428,7 +16428,7 @@
         </is>
       </c>
       <c r="E616" s="20" t="n">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="617" ht="20" customHeight="1">
@@ -16453,7 +16453,7 @@
         </is>
       </c>
       <c r="E617" s="23" t="n">
-        <v>196</v>
+        <v>167</v>
       </c>
     </row>
     <row r="618" ht="20" customHeight="1">
@@ -16478,7 +16478,7 @@
         </is>
       </c>
       <c r="E618" s="20" t="n">
-        <v>152</v>
+        <v>196</v>
       </c>
     </row>
     <row r="619" ht="20" customHeight="1">
@@ -16503,7 +16503,7 @@
         </is>
       </c>
       <c r="E619" s="23" t="n">
-        <v>133</v>
+        <v>172</v>
       </c>
     </row>
     <row r="620" ht="20" customHeight="1">
@@ -16528,7 +16528,7 @@
         </is>
       </c>
       <c r="E620" s="20" t="n">
-        <v>232</v>
+        <v>116</v>
       </c>
     </row>
     <row r="621" ht="20" customHeight="1">
@@ -16553,7 +16553,7 @@
         </is>
       </c>
       <c r="E621" s="23" t="n">
-        <v>179</v>
+        <v>147</v>
       </c>
     </row>
     <row r="622" ht="20" customHeight="1">
@@ -16578,7 +16578,7 @@
         </is>
       </c>
       <c r="E622" s="20" t="n">
-        <v>196</v>
+        <v>228</v>
       </c>
     </row>
     <row r="623" ht="20" customHeight="1">
@@ -16603,7 +16603,7 @@
         </is>
       </c>
       <c r="E623" s="23" t="n">
-        <v>118</v>
+        <v>197</v>
       </c>
     </row>
     <row r="624" ht="20" customHeight="1">
@@ -16628,7 +16628,7 @@
         </is>
       </c>
       <c r="E624" s="20" t="n">
-        <v>200</v>
+        <v>165</v>
       </c>
     </row>
     <row r="625" ht="20" customHeight="1">
@@ -16653,7 +16653,7 @@
         </is>
       </c>
       <c r="E625" s="23" t="n">
-        <v>165</v>
+        <v>203</v>
       </c>
     </row>
     <row r="626" ht="20" customHeight="1">
@@ -16678,7 +16678,7 @@
         </is>
       </c>
       <c r="E626" s="20" t="n">
-        <v>121</v>
+        <v>177</v>
       </c>
     </row>
     <row r="627" ht="20" customHeight="1">
@@ -16703,7 +16703,7 @@
         </is>
       </c>
       <c r="E627" s="23" t="n">
-        <v>123</v>
+        <v>162</v>
       </c>
     </row>
     <row r="628" ht="20" customHeight="1">
@@ -16728,7 +16728,7 @@
         </is>
       </c>
       <c r="E628" s="20" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="629" ht="20" customHeight="1">
@@ -16753,7 +16753,7 @@
         </is>
       </c>
       <c r="E629" s="23" t="n">
-        <v>156</v>
+        <v>219</v>
       </c>
     </row>
     <row r="630" ht="20" customHeight="1">
@@ -16778,7 +16778,7 @@
         </is>
       </c>
       <c r="E630" s="20" t="n">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="631" ht="20" customHeight="1">
@@ -16803,7 +16803,7 @@
         </is>
       </c>
       <c r="E631" s="23" t="n">
-        <v>117</v>
+        <v>225</v>
       </c>
     </row>
     <row r="632" ht="20" customHeight="1">
@@ -16828,7 +16828,7 @@
         </is>
       </c>
       <c r="E632" s="20" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
     </row>
     <row r="633" ht="20" customHeight="1">
@@ -16853,7 +16853,7 @@
         </is>
       </c>
       <c r="E633" s="23" t="n">
-        <v>171</v>
+        <v>179</v>
       </c>
     </row>
     <row r="634" ht="20" customHeight="1">
@@ -16878,7 +16878,7 @@
         </is>
       </c>
       <c r="E634" s="20" t="n">
-        <v>196</v>
+        <v>233</v>
       </c>
     </row>
     <row r="635" ht="20" customHeight="1">
@@ -16903,7 +16903,7 @@
         </is>
       </c>
       <c r="E635" s="23" t="n">
-        <v>230</v>
+        <v>205</v>
       </c>
     </row>
     <row r="636" ht="20" customHeight="1">
@@ -16928,7 +16928,7 @@
         </is>
       </c>
       <c r="E636" s="20" t="n">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="637" ht="20" customHeight="1">
@@ -16953,7 +16953,7 @@
         </is>
       </c>
       <c r="E637" s="23" t="n">
-        <v>154</v>
+        <v>230</v>
       </c>
     </row>
     <row r="638" ht="20" customHeight="1">
@@ -16978,7 +16978,7 @@
         </is>
       </c>
       <c r="E638" s="20" t="n">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="639" ht="20" customHeight="1">
@@ -17003,7 +17003,7 @@
         </is>
       </c>
       <c r="E639" s="23" t="n">
-        <v>192</v>
+        <v>182</v>
       </c>
     </row>
     <row r="640" ht="20" customHeight="1">
@@ -17028,7 +17028,7 @@
         </is>
       </c>
       <c r="E640" s="20" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="641" ht="20" customHeight="1">
@@ -17053,7 +17053,7 @@
         </is>
       </c>
       <c r="E641" s="23" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="642" ht="20" customHeight="1">
@@ -17078,7 +17078,7 @@
         </is>
       </c>
       <c r="E642" s="20" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="643" ht="20" customHeight="1">
@@ -17103,7 +17103,7 @@
         </is>
       </c>
       <c r="E643" s="23" t="n">
-        <v>151</v>
+        <v>115</v>
       </c>
     </row>
     <row r="644" ht="20" customHeight="1">
@@ -17128,7 +17128,7 @@
         </is>
       </c>
       <c r="E644" s="20" t="n">
-        <v>125</v>
+        <v>149</v>
       </c>
     </row>
     <row r="645" ht="20" customHeight="1">
@@ -17153,7 +17153,7 @@
         </is>
       </c>
       <c r="E645" s="23" t="n">
-        <v>155</v>
+        <v>129</v>
       </c>
     </row>
     <row r="646" ht="20" customHeight="1">
@@ -17178,7 +17178,7 @@
         </is>
       </c>
       <c r="E646" s="20" t="n">
-        <v>114</v>
+        <v>178</v>
       </c>
     </row>
     <row r="647" ht="20" customHeight="1">
@@ -17203,7 +17203,7 @@
         </is>
       </c>
       <c r="E647" s="23" t="n">
-        <v>134</v>
+        <v>178</v>
       </c>
     </row>
     <row r="648" ht="20" customHeight="1">
@@ -17228,7 +17228,7 @@
         </is>
       </c>
       <c r="E648" s="20" t="n">
-        <v>160</v>
+        <v>220</v>
       </c>
     </row>
     <row r="649" ht="20" customHeight="1">
@@ -17253,7 +17253,7 @@
         </is>
       </c>
       <c r="E649" s="23" t="n">
-        <v>222</v>
+        <v>205</v>
       </c>
     </row>
     <row r="650" ht="20" customHeight="1">
@@ -17278,7 +17278,7 @@
         </is>
       </c>
       <c r="E650" s="20" t="n">
-        <v>227</v>
+        <v>233</v>
       </c>
     </row>
     <row r="651" ht="20" customHeight="1">
@@ -17303,7 +17303,7 @@
         </is>
       </c>
       <c r="E651" s="23" t="n">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="652" ht="20" customHeight="1">
@@ -17328,7 +17328,7 @@
         </is>
       </c>
       <c r="E652" s="20" t="n">
-        <v>153</v>
+        <v>226</v>
       </c>
     </row>
     <row r="653" ht="20" customHeight="1">
@@ -17353,7 +17353,7 @@
         </is>
       </c>
       <c r="E653" s="23" t="n">
-        <v>182</v>
+        <v>131</v>
       </c>
     </row>
     <row r="654" ht="20" customHeight="1">
@@ -17378,7 +17378,7 @@
         </is>
       </c>
       <c r="E654" s="20" t="n">
-        <v>117</v>
+        <v>133</v>
       </c>
     </row>
     <row r="655" ht="20" customHeight="1">
@@ -17403,7 +17403,7 @@
         </is>
       </c>
       <c r="E655" s="23" t="n">
-        <v>171</v>
+        <v>223</v>
       </c>
     </row>
     <row r="656" ht="20" customHeight="1">
@@ -17428,7 +17428,7 @@
         </is>
       </c>
       <c r="E656" s="20" t="n">
-        <v>144</v>
+        <v>197</v>
       </c>
     </row>
     <row r="657" ht="20" customHeight="1">
@@ -17453,7 +17453,7 @@
         </is>
       </c>
       <c r="E657" s="23" t="n">
-        <v>126</v>
+        <v>186</v>
       </c>
     </row>
     <row r="658" ht="20" customHeight="1">
@@ -17478,7 +17478,7 @@
         </is>
       </c>
       <c r="E658" s="20" t="n">
-        <v>192</v>
+        <v>213</v>
       </c>
     </row>
     <row r="659" ht="20" customHeight="1">
@@ -17503,7 +17503,7 @@
         </is>
       </c>
       <c r="E659" s="23" t="n">
-        <v>217</v>
+        <v>210</v>
       </c>
     </row>
     <row r="660" ht="20" customHeight="1">
@@ -17528,7 +17528,7 @@
         </is>
       </c>
       <c r="E660" s="20" t="n">
-        <v>181</v>
+        <v>127</v>
       </c>
     </row>
     <row r="661" ht="20" customHeight="1">
@@ -17553,7 +17553,7 @@
         </is>
       </c>
       <c r="E661" s="23" t="n">
-        <v>135</v>
+        <v>175</v>
       </c>
     </row>
     <row r="662" ht="20" customHeight="1">
@@ -17578,7 +17578,7 @@
         </is>
       </c>
       <c r="E662" s="20" t="n">
-        <v>196</v>
+        <v>126</v>
       </c>
     </row>
     <row r="663" ht="20" customHeight="1">
@@ -17603,7 +17603,7 @@
         </is>
       </c>
       <c r="E663" s="23" t="n">
-        <v>218</v>
+        <v>165</v>
       </c>
     </row>
     <row r="664" ht="20" customHeight="1">
@@ -17628,7 +17628,7 @@
         </is>
       </c>
       <c r="E664" s="20" t="n">
-        <v>155</v>
+        <v>162</v>
       </c>
     </row>
     <row r="665" ht="20" customHeight="1">
@@ -17653,7 +17653,7 @@
         </is>
       </c>
       <c r="E665" s="23" t="n">
-        <v>156</v>
+        <v>210</v>
       </c>
     </row>
     <row r="666" ht="20" customHeight="1">
@@ -17678,7 +17678,7 @@
         </is>
       </c>
       <c r="E666" s="20" t="n">
-        <v>216</v>
+        <v>237</v>
       </c>
     </row>
     <row r="667" ht="20" customHeight="1">
@@ -17703,7 +17703,7 @@
         </is>
       </c>
       <c r="E667" s="23" t="n">
-        <v>224</v>
+        <v>123</v>
       </c>
     </row>
     <row r="668" ht="20" customHeight="1">
@@ -17728,7 +17728,7 @@
         </is>
       </c>
       <c r="E668" s="20" t="n">
-        <v>207</v>
+        <v>230</v>
       </c>
     </row>
     <row r="669" ht="20" customHeight="1">
@@ -17753,7 +17753,7 @@
         </is>
       </c>
       <c r="E669" s="23" t="n">
-        <v>219</v>
+        <v>123</v>
       </c>
     </row>
     <row r="670" ht="20" customHeight="1">
@@ -17778,7 +17778,7 @@
         </is>
       </c>
       <c r="E670" s="20" t="n">
-        <v>117</v>
+        <v>177</v>
       </c>
     </row>
     <row r="671" ht="20" customHeight="1">
@@ -17803,7 +17803,7 @@
         </is>
       </c>
       <c r="E671" s="23" t="n">
-        <v>212</v>
+        <v>142</v>
       </c>
     </row>
     <row r="672" ht="20" customHeight="1">
@@ -17828,7 +17828,7 @@
         </is>
       </c>
       <c r="E672" s="20" t="n">
-        <v>150</v>
+        <v>214</v>
       </c>
     </row>
     <row r="673" ht="20" customHeight="1">
@@ -17853,7 +17853,7 @@
         </is>
       </c>
       <c r="E673" s="23" t="n">
-        <v>164</v>
+        <v>206</v>
       </c>
     </row>
     <row r="674" ht="20" customHeight="1">
@@ -17878,7 +17878,7 @@
         </is>
       </c>
       <c r="E674" s="20" t="n">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="675" ht="20" customHeight="1">
@@ -17903,7 +17903,7 @@
         </is>
       </c>
       <c r="E675" s="23" t="n">
-        <v>150</v>
+        <v>184</v>
       </c>
     </row>
     <row r="676" ht="20" customHeight="1">
@@ -17928,7 +17928,7 @@
         </is>
       </c>
       <c r="E676" s="20" t="n">
-        <v>130</v>
+        <v>202</v>
       </c>
     </row>
     <row r="677" ht="20" customHeight="1">
@@ -17953,7 +17953,7 @@
         </is>
       </c>
       <c r="E677" s="23" t="n">
-        <v>136</v>
+        <v>185</v>
       </c>
     </row>
     <row r="678" ht="20" customHeight="1">
@@ -17978,7 +17978,7 @@
         </is>
       </c>
       <c r="E678" s="20" t="n">
-        <v>151</v>
+        <v>206</v>
       </c>
     </row>
     <row r="679" ht="20" customHeight="1">
@@ -18003,7 +18003,7 @@
         </is>
       </c>
       <c r="E679" s="23" t="n">
-        <v>172</v>
+        <v>131</v>
       </c>
     </row>
     <row r="680" ht="20" customHeight="1">
@@ -18028,7 +18028,7 @@
         </is>
       </c>
       <c r="E680" s="20" t="n">
-        <v>210</v>
+        <v>230</v>
       </c>
     </row>
     <row r="681" ht="20" customHeight="1">
@@ -18053,7 +18053,7 @@
         </is>
       </c>
       <c r="E681" s="23" t="n">
-        <v>208</v>
+        <v>142</v>
       </c>
     </row>
     <row r="682" ht="20" customHeight="1">
@@ -18078,7 +18078,7 @@
         </is>
       </c>
       <c r="E682" s="20" t="n">
-        <v>111</v>
+        <v>195</v>
       </c>
     </row>
     <row r="683" ht="20" customHeight="1">
@@ -18103,7 +18103,7 @@
         </is>
       </c>
       <c r="E683" s="23" t="n">
-        <v>176</v>
+        <v>122</v>
       </c>
     </row>
     <row r="684" ht="20" customHeight="1">
@@ -18128,7 +18128,7 @@
         </is>
       </c>
       <c r="E684" s="20" t="n">
-        <v>201</v>
+        <v>117</v>
       </c>
     </row>
     <row r="685" ht="20" customHeight="1">
@@ -18153,7 +18153,7 @@
         </is>
       </c>
       <c r="E685" s="23" t="n">
-        <v>175</v>
+        <v>143</v>
       </c>
     </row>
     <row r="686" ht="20" customHeight="1">
@@ -18178,7 +18178,7 @@
         </is>
       </c>
       <c r="E686" s="20" t="n">
-        <v>130</v>
+        <v>146</v>
       </c>
     </row>
     <row r="687" ht="20" customHeight="1">
@@ -18203,7 +18203,7 @@
         </is>
       </c>
       <c r="E687" s="23" t="n">
-        <v>207</v>
+        <v>167</v>
       </c>
     </row>
     <row r="688" ht="20" customHeight="1">
@@ -18228,7 +18228,7 @@
         </is>
       </c>
       <c r="E688" s="20" t="n">
-        <v>188</v>
+        <v>145</v>
       </c>
     </row>
     <row r="689" ht="20" customHeight="1">
@@ -18253,7 +18253,7 @@
         </is>
       </c>
       <c r="E689" s="23" t="n">
-        <v>237</v>
+        <v>130</v>
       </c>
     </row>
     <row r="690" ht="20" customHeight="1">
@@ -18278,7 +18278,7 @@
         </is>
       </c>
       <c r="E690" s="20" t="n">
-        <v>213</v>
+        <v>148</v>
       </c>
     </row>
     <row r="691" ht="20" customHeight="1">
@@ -18303,7 +18303,7 @@
         </is>
       </c>
       <c r="E691" s="23" t="n">
-        <v>199</v>
+        <v>174</v>
       </c>
     </row>
     <row r="692" ht="20" customHeight="1">
@@ -18328,7 +18328,7 @@
         </is>
       </c>
       <c r="E692" s="20" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="693" ht="20" customHeight="1">
@@ -18353,7 +18353,7 @@
         </is>
       </c>
       <c r="E693" s="23" t="n">
-        <v>219</v>
+        <v>122</v>
       </c>
     </row>
     <row r="694" ht="20" customHeight="1">
@@ -18378,7 +18378,7 @@
         </is>
       </c>
       <c r="E694" s="20" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="695" ht="20" customHeight="1">
@@ -18403,7 +18403,7 @@
         </is>
       </c>
       <c r="E695" s="23" t="n">
-        <v>162</v>
+        <v>206</v>
       </c>
     </row>
     <row r="696" ht="20" customHeight="1">
@@ -18428,7 +18428,7 @@
         </is>
       </c>
       <c r="E696" s="20" t="n">
-        <v>126</v>
+        <v>155</v>
       </c>
     </row>
     <row r="697" ht="20" customHeight="1">
@@ -18453,7 +18453,7 @@
         </is>
       </c>
       <c r="E697" s="23" t="n">
-        <v>133</v>
+        <v>204</v>
       </c>
     </row>
     <row r="698" ht="20" customHeight="1">
@@ -18478,7 +18478,7 @@
         </is>
       </c>
       <c r="E698" s="20" t="n">
-        <v>122</v>
+        <v>221</v>
       </c>
     </row>
     <row r="699" ht="20" customHeight="1">
@@ -18503,7 +18503,7 @@
         </is>
       </c>
       <c r="E699" s="23" t="n">
-        <v>153</v>
+        <v>139</v>
       </c>
     </row>
     <row r="700" ht="20" customHeight="1">
@@ -18528,7 +18528,7 @@
         </is>
       </c>
       <c r="E700" s="20" t="n">
-        <v>128</v>
+        <v>218</v>
       </c>
     </row>
     <row r="701" ht="20" customHeight="1">
@@ -18553,7 +18553,7 @@
         </is>
       </c>
       <c r="E701" s="23" t="n">
-        <v>140</v>
+        <v>211</v>
       </c>
     </row>
     <row r="702" ht="20" customHeight="1">
@@ -18578,7 +18578,7 @@
         </is>
       </c>
       <c r="E702" s="20" t="n">
-        <v>186</v>
+        <v>159</v>
       </c>
     </row>
     <row r="703" ht="20" customHeight="1">
@@ -18603,7 +18603,7 @@
         </is>
       </c>
       <c r="E703" s="23" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="704" ht="20" customHeight="1">
@@ -18628,7 +18628,7 @@
         </is>
       </c>
       <c r="E704" s="20" t="n">
-        <v>169</v>
+        <v>125</v>
       </c>
     </row>
     <row r="705" ht="20" customHeight="1">
@@ -18653,7 +18653,7 @@
         </is>
       </c>
       <c r="E705" s="23" t="n">
-        <v>236</v>
+        <v>154</v>
       </c>
     </row>
     <row r="706" ht="20" customHeight="1">
@@ -18678,7 +18678,7 @@
         </is>
       </c>
       <c r="E706" s="20" t="n">
-        <v>194</v>
+        <v>234</v>
       </c>
     </row>
     <row r="707" ht="20" customHeight="1">
@@ -18703,7 +18703,7 @@
         </is>
       </c>
       <c r="E707" s="23" t="n">
-        <v>194</v>
+        <v>152</v>
       </c>
     </row>
     <row r="708" ht="20" customHeight="1">
@@ -18728,7 +18728,7 @@
         </is>
       </c>
       <c r="E708" s="20" t="n">
-        <v>189</v>
+        <v>154</v>
       </c>
     </row>
     <row r="709" ht="20" customHeight="1">
@@ -18753,7 +18753,7 @@
         </is>
       </c>
       <c r="E709" s="23" t="n">
-        <v>118</v>
+        <v>211</v>
       </c>
     </row>
     <row r="710" ht="20" customHeight="1">
@@ -18778,7 +18778,7 @@
         </is>
       </c>
       <c r="E710" s="20" t="n">
-        <v>204</v>
+        <v>168</v>
       </c>
     </row>
     <row r="711" ht="20" customHeight="1">
@@ -18803,7 +18803,7 @@
         </is>
       </c>
       <c r="E711" s="23" t="n">
-        <v>174</v>
+        <v>179</v>
       </c>
     </row>
     <row r="712" ht="20" customHeight="1">
@@ -18828,7 +18828,7 @@
         </is>
       </c>
       <c r="E712" s="20" t="n">
-        <v>169</v>
+        <v>232</v>
       </c>
     </row>
     <row r="713" ht="20" customHeight="1">
@@ -18853,7 +18853,7 @@
         </is>
       </c>
       <c r="E713" s="23" t="n">
-        <v>114</v>
+        <v>136</v>
       </c>
     </row>
     <row r="714" ht="20" customHeight="1">
@@ -18878,7 +18878,7 @@
         </is>
       </c>
       <c r="E714" s="20" t="n">
-        <v>236</v>
+        <v>177</v>
       </c>
     </row>
     <row r="715" ht="20" customHeight="1">
@@ -18903,7 +18903,7 @@
         </is>
       </c>
       <c r="E715" s="23" t="n">
-        <v>166</v>
+        <v>204</v>
       </c>
     </row>
     <row r="716" ht="20" customHeight="1">
@@ -18953,7 +18953,7 @@
         </is>
       </c>
       <c r="E717" s="23" t="n">
-        <v>195</v>
+        <v>157</v>
       </c>
     </row>
     <row r="718" ht="20" customHeight="1">
@@ -18978,7 +18978,7 @@
         </is>
       </c>
       <c r="E718" s="20" t="n">
-        <v>217</v>
+        <v>149</v>
       </c>
     </row>
     <row r="719" ht="20" customHeight="1">
@@ -19003,7 +19003,7 @@
         </is>
       </c>
       <c r="E719" s="23" t="n">
-        <v>110</v>
+        <v>176</v>
       </c>
     </row>
     <row r="720" ht="20" customHeight="1">
@@ -19028,7 +19028,7 @@
         </is>
       </c>
       <c r="E720" s="20" t="n">
-        <v>185</v>
+        <v>132</v>
       </c>
     </row>
     <row r="721" ht="20" customHeight="1">
@@ -19053,7 +19053,7 @@
         </is>
       </c>
       <c r="E721" s="23" t="n">
-        <v>225</v>
+        <v>180</v>
       </c>
     </row>
     <row r="722" ht="20" customHeight="1">
@@ -19078,7 +19078,7 @@
         </is>
       </c>
       <c r="E722" s="20" t="n">
-        <v>113</v>
+        <v>239</v>
       </c>
     </row>
     <row r="723" ht="20" customHeight="1">
@@ -19103,7 +19103,7 @@
         </is>
       </c>
       <c r="E723" s="23" t="n">
-        <v>134</v>
+        <v>167</v>
       </c>
     </row>
     <row r="724" ht="20" customHeight="1">
@@ -19128,7 +19128,7 @@
         </is>
       </c>
       <c r="E724" s="20" t="n">
-        <v>137</v>
+        <v>112</v>
       </c>
     </row>
     <row r="725" ht="20" customHeight="1">
@@ -19153,7 +19153,7 @@
         </is>
       </c>
       <c r="E725" s="23" t="n">
-        <v>212</v>
+        <v>171</v>
       </c>
     </row>
     <row r="726" ht="20" customHeight="1">
@@ -19178,7 +19178,7 @@
         </is>
       </c>
       <c r="E726" s="20" t="n">
-        <v>205</v>
+        <v>116</v>
       </c>
     </row>
     <row r="727" ht="20" customHeight="1">
@@ -19203,7 +19203,7 @@
         </is>
       </c>
       <c r="E727" s="23" t="n">
-        <v>228</v>
+        <v>141</v>
       </c>
     </row>
     <row r="728" ht="20" customHeight="1">
@@ -19228,7 +19228,7 @@
         </is>
       </c>
       <c r="E728" s="20" t="n">
-        <v>235</v>
+        <v>161</v>
       </c>
     </row>
     <row r="729" ht="20" customHeight="1">
@@ -19253,7 +19253,7 @@
         </is>
       </c>
       <c r="E729" s="23" t="n">
-        <v>231</v>
+        <v>187</v>
       </c>
     </row>
     <row r="730" ht="20" customHeight="1">
@@ -19303,7 +19303,7 @@
         </is>
       </c>
       <c r="E731" s="23" t="n">
-        <v>168</v>
+        <v>189</v>
       </c>
     </row>
     <row r="732" ht="20" customHeight="1">
@@ -19328,7 +19328,7 @@
         </is>
       </c>
       <c r="E732" s="20" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="733" ht="20" customHeight="1">
@@ -19353,7 +19353,7 @@
         </is>
       </c>
       <c r="E733" s="23" t="n">
-        <v>238</v>
+        <v>136</v>
       </c>
     </row>
     <row r="734" ht="20" customHeight="1">
@@ -19378,7 +19378,7 @@
         </is>
       </c>
       <c r="E734" s="20" t="n">
-        <v>235</v>
+        <v>169</v>
       </c>
     </row>
     <row r="735" ht="20" customHeight="1">
@@ -19403,7 +19403,7 @@
         </is>
       </c>
       <c r="E735" s="23" t="n">
-        <v>218</v>
+        <v>113</v>
       </c>
     </row>
     <row r="736" ht="20" customHeight="1">
@@ -19428,7 +19428,7 @@
         </is>
       </c>
       <c r="E736" s="20" t="n">
-        <v>131</v>
+        <v>179</v>
       </c>
     </row>
     <row r="737" ht="20" customHeight="1">
@@ -19453,7 +19453,7 @@
         </is>
       </c>
       <c r="E737" s="23" t="n">
-        <v>143</v>
+        <v>116</v>
       </c>
     </row>
     <row r="738" ht="20" customHeight="1">
@@ -19478,7 +19478,7 @@
         </is>
       </c>
       <c r="E738" s="20" t="n">
-        <v>170</v>
+        <v>153</v>
       </c>
     </row>
     <row r="739" ht="20" customHeight="1">
@@ -19503,7 +19503,7 @@
         </is>
       </c>
       <c r="E739" s="23" t="n">
-        <v>175</v>
+        <v>221</v>
       </c>
     </row>
     <row r="740" ht="20" customHeight="1">
@@ -19528,7 +19528,7 @@
         </is>
       </c>
       <c r="E740" s="20" t="n">
-        <v>196</v>
+        <v>147</v>
       </c>
     </row>
     <row r="741" ht="20" customHeight="1">
@@ -19553,7 +19553,7 @@
         </is>
       </c>
       <c r="E741" s="23" t="n">
-        <v>207</v>
+        <v>227</v>
       </c>
     </row>
     <row r="742" ht="20" customHeight="1">
@@ -19578,7 +19578,7 @@
         </is>
       </c>
       <c r="E742" s="20" t="n">
-        <v>143</v>
+        <v>172</v>
       </c>
     </row>
     <row r="743" ht="20" customHeight="1">
@@ -19603,7 +19603,7 @@
         </is>
       </c>
       <c r="E743" s="23" t="n">
-        <v>161</v>
+        <v>193</v>
       </c>
     </row>
     <row r="744" ht="20" customHeight="1">
@@ -19628,7 +19628,7 @@
         </is>
       </c>
       <c r="E744" s="20" t="n">
-        <v>203</v>
+        <v>209</v>
       </c>
     </row>
     <row r="745" ht="20" customHeight="1">
@@ -19653,7 +19653,7 @@
         </is>
       </c>
       <c r="E745" s="23" t="n">
-        <v>146</v>
+        <v>221</v>
       </c>
     </row>
     <row r="746" ht="20" customHeight="1">
@@ -19678,7 +19678,7 @@
         </is>
       </c>
       <c r="E746" s="20" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="747" ht="20" customHeight="1">
@@ -19703,7 +19703,7 @@
         </is>
       </c>
       <c r="E747" s="23" t="n">
-        <v>226</v>
+        <v>212</v>
       </c>
     </row>
     <row r="748" ht="20" customHeight="1">
@@ -19728,7 +19728,7 @@
         </is>
       </c>
       <c r="E748" s="20" t="n">
-        <v>113</v>
+        <v>167</v>
       </c>
     </row>
     <row r="749" ht="20" customHeight="1">
@@ -19753,7 +19753,7 @@
         </is>
       </c>
       <c r="E749" s="23" t="n">
-        <v>234</v>
+        <v>155</v>
       </c>
     </row>
     <row r="750" ht="20" customHeight="1">
@@ -19778,7 +19778,7 @@
         </is>
       </c>
       <c r="E750" s="20" t="n">
-        <v>212</v>
+        <v>155</v>
       </c>
     </row>
     <row r="751" ht="20" customHeight="1">
@@ -19803,7 +19803,7 @@
         </is>
       </c>
       <c r="E751" s="23" t="n">
-        <v>192</v>
+        <v>208</v>
       </c>
     </row>
     <row r="752" ht="20" customHeight="1">
@@ -19828,7 +19828,7 @@
         </is>
       </c>
       <c r="E752" s="20" t="n">
-        <v>189</v>
+        <v>170</v>
       </c>
     </row>
     <row r="753" ht="20" customHeight="1">
@@ -19853,7 +19853,7 @@
         </is>
       </c>
       <c r="E753" s="23" t="n">
-        <v>170</v>
+        <v>127</v>
       </c>
     </row>
     <row r="754" ht="20" customHeight="1">
@@ -19878,7 +19878,7 @@
         </is>
       </c>
       <c r="E754" s="20" t="n">
-        <v>130</v>
+        <v>206</v>
       </c>
     </row>
     <row r="755" ht="20" customHeight="1">
@@ -19903,7 +19903,7 @@
         </is>
       </c>
       <c r="E755" s="23" t="n">
-        <v>133</v>
+        <v>214</v>
       </c>
     </row>
     <row r="756" ht="20" customHeight="1">
@@ -19928,7 +19928,7 @@
         </is>
       </c>
       <c r="E756" s="20" t="n">
-        <v>201</v>
+        <v>194</v>
       </c>
     </row>
     <row r="757" ht="20" customHeight="1">
@@ -19953,7 +19953,7 @@
         </is>
       </c>
       <c r="E757" s="23" t="n">
-        <v>224</v>
+        <v>122</v>
       </c>
     </row>
     <row r="758" ht="20" customHeight="1">
@@ -19978,7 +19978,7 @@
         </is>
       </c>
       <c r="E758" s="20" t="n">
-        <v>181</v>
+        <v>157</v>
       </c>
     </row>
     <row r="759" ht="20" customHeight="1">
@@ -20003,7 +20003,7 @@
         </is>
       </c>
       <c r="E759" s="23" t="n">
-        <v>216</v>
+        <v>117</v>
       </c>
     </row>
     <row r="760" ht="20" customHeight="1">
@@ -20028,7 +20028,7 @@
         </is>
       </c>
       <c r="E760" s="20" t="n">
-        <v>177</v>
+        <v>219</v>
       </c>
     </row>
     <row r="761" ht="20" customHeight="1">
@@ -20053,7 +20053,7 @@
         </is>
       </c>
       <c r="E761" s="23" t="n">
-        <v>192</v>
+        <v>227</v>
       </c>
     </row>
     <row r="762" ht="20" customHeight="1">
@@ -20078,7 +20078,7 @@
         </is>
       </c>
       <c r="E762" s="20" t="n">
-        <v>198</v>
+        <v>224</v>
       </c>
     </row>
     <row r="763" ht="20" customHeight="1">
@@ -20103,7 +20103,7 @@
         </is>
       </c>
       <c r="E763" s="23" t="n">
-        <v>233</v>
+        <v>130</v>
       </c>
     </row>
     <row r="764" ht="20" customHeight="1">
@@ -20128,7 +20128,7 @@
         </is>
       </c>
       <c r="E764" s="20" t="n">
-        <v>148</v>
+        <v>112</v>
       </c>
     </row>
     <row r="765" ht="20" customHeight="1">
@@ -20153,7 +20153,7 @@
         </is>
       </c>
       <c r="E765" s="23" t="n">
-        <v>239</v>
+        <v>143</v>
       </c>
     </row>
     <row r="766" ht="20" customHeight="1">
@@ -20178,7 +20178,7 @@
         </is>
       </c>
       <c r="E766" s="20" t="n">
-        <v>140</v>
+        <v>223</v>
       </c>
     </row>
     <row r="767" ht="20" customHeight="1">
@@ -20203,7 +20203,7 @@
         </is>
       </c>
       <c r="E767" s="23" t="n">
-        <v>161</v>
+        <v>214</v>
       </c>
     </row>
     <row r="768" ht="20" customHeight="1">
@@ -20228,7 +20228,7 @@
         </is>
       </c>
       <c r="E768" s="20" t="n">
-        <v>171</v>
+        <v>155</v>
       </c>
     </row>
     <row r="769" ht="20" customHeight="1">
@@ -20253,7 +20253,7 @@
         </is>
       </c>
       <c r="E769" s="23" t="n">
-        <v>231</v>
+        <v>196</v>
       </c>
     </row>
     <row r="770" ht="20" customHeight="1">
@@ -20278,7 +20278,7 @@
         </is>
       </c>
       <c r="E770" s="20" t="n">
-        <v>169</v>
+        <v>122</v>
       </c>
     </row>
     <row r="771" ht="20" customHeight="1">
@@ -20303,7 +20303,7 @@
         </is>
       </c>
       <c r="E771" s="23" t="n">
-        <v>112</v>
+        <v>123</v>
       </c>
     </row>
     <row r="772" ht="20" customHeight="1">
@@ -20328,7 +20328,7 @@
         </is>
       </c>
       <c r="E772" s="20" t="n">
-        <v>233</v>
+        <v>129</v>
       </c>
     </row>
     <row r="773" ht="20" customHeight="1">
@@ -20353,7 +20353,7 @@
         </is>
       </c>
       <c r="E773" s="23" t="n">
-        <v>185</v>
+        <v>140</v>
       </c>
     </row>
     <row r="774" ht="20" customHeight="1">
@@ -20378,7 +20378,7 @@
         </is>
       </c>
       <c r="E774" s="20" t="n">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="775" ht="20" customHeight="1">
@@ -20403,7 +20403,7 @@
         </is>
       </c>
       <c r="E775" s="23" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="776" ht="20" customHeight="1">
@@ -20428,7 +20428,7 @@
         </is>
       </c>
       <c r="E776" s="20" t="n">
-        <v>132</v>
+        <v>120</v>
       </c>
     </row>
     <row r="777" ht="20" customHeight="1">
@@ -20453,7 +20453,7 @@
         </is>
       </c>
       <c r="E777" s="23" t="n">
-        <v>209</v>
+        <v>130</v>
       </c>
     </row>
     <row r="778" ht="20" customHeight="1">
@@ -20478,7 +20478,7 @@
         </is>
       </c>
       <c r="E778" s="20" t="n">
-        <v>153</v>
+        <v>136</v>
       </c>
     </row>
     <row r="779" ht="20" customHeight="1">
@@ -20503,7 +20503,7 @@
         </is>
       </c>
       <c r="E779" s="23" t="n">
-        <v>174</v>
+        <v>198</v>
       </c>
     </row>
     <row r="780" ht="20" customHeight="1">
@@ -20528,7 +20528,7 @@
         </is>
       </c>
       <c r="E780" s="20" t="n">
-        <v>112</v>
+        <v>137</v>
       </c>
     </row>
     <row r="781" ht="20" customHeight="1">
@@ -20553,7 +20553,7 @@
         </is>
       </c>
       <c r="E781" s="23" t="n">
-        <v>168</v>
+        <v>199</v>
       </c>
     </row>
     <row r="782" ht="20" customHeight="1">
@@ -20578,7 +20578,7 @@
         </is>
       </c>
       <c r="E782" s="20" t="n">
-        <v>150</v>
+        <v>212</v>
       </c>
     </row>
     <row r="783" ht="20" customHeight="1">
@@ -20603,7 +20603,7 @@
         </is>
       </c>
       <c r="E783" s="23" t="n">
-        <v>169</v>
+        <v>237</v>
       </c>
     </row>
     <row r="784" ht="20" customHeight="1">
@@ -20628,7 +20628,7 @@
         </is>
       </c>
       <c r="E784" s="20" t="n">
-        <v>202</v>
+        <v>175</v>
       </c>
     </row>
     <row r="785" ht="20" customHeight="1">
@@ -20653,7 +20653,7 @@
         </is>
       </c>
       <c r="E785" s="23" t="n">
-        <v>131</v>
+        <v>193</v>
       </c>
     </row>
     <row r="786" ht="20" customHeight="1">
@@ -20678,7 +20678,7 @@
         </is>
       </c>
       <c r="E786" s="20" t="n">
-        <v>184</v>
+        <v>137</v>
       </c>
     </row>
     <row r="787" ht="20" customHeight="1">
@@ -20703,7 +20703,7 @@
         </is>
       </c>
       <c r="E787" s="23" t="n">
-        <v>132</v>
+        <v>182</v>
       </c>
     </row>
     <row r="788" ht="20" customHeight="1">
@@ -20728,7 +20728,7 @@
         </is>
       </c>
       <c r="E788" s="20" t="n">
-        <v>179</v>
+        <v>206</v>
       </c>
     </row>
     <row r="789" ht="20" customHeight="1">
@@ -20753,7 +20753,7 @@
         </is>
       </c>
       <c r="E789" s="23" t="n">
-        <v>156</v>
+        <v>238</v>
       </c>
     </row>
     <row r="790" ht="20" customHeight="1">
@@ -20778,7 +20778,7 @@
         </is>
       </c>
       <c r="E790" s="20" t="n">
-        <v>113</v>
+        <v>168</v>
       </c>
     </row>
     <row r="791" ht="20" customHeight="1">
@@ -20803,7 +20803,7 @@
         </is>
       </c>
       <c r="E791" s="23" t="n">
-        <v>234</v>
+        <v>141</v>
       </c>
     </row>
     <row r="792" ht="20" customHeight="1">
@@ -20828,7 +20828,7 @@
         </is>
       </c>
       <c r="E792" s="20" t="n">
-        <v>113</v>
+        <v>237</v>
       </c>
     </row>
     <row r="793" ht="20" customHeight="1">
@@ -20853,7 +20853,7 @@
         </is>
       </c>
       <c r="E793" s="23" t="n">
-        <v>207</v>
+        <v>115</v>
       </c>
     </row>
     <row r="794" ht="20" customHeight="1">
@@ -20878,7 +20878,7 @@
         </is>
       </c>
       <c r="E794" s="20" t="n">
-        <v>224</v>
+        <v>205</v>
       </c>
     </row>
     <row r="795" ht="20" customHeight="1">
@@ -20903,7 +20903,7 @@
         </is>
       </c>
       <c r="E795" s="23" t="n">
-        <v>117</v>
+        <v>231</v>
       </c>
     </row>
     <row r="796" ht="20" customHeight="1">
@@ -20928,7 +20928,7 @@
         </is>
       </c>
       <c r="E796" s="20" t="n">
-        <v>213</v>
+        <v>166</v>
       </c>
     </row>
     <row r="797" ht="20" customHeight="1">
@@ -20953,7 +20953,7 @@
         </is>
       </c>
       <c r="E797" s="23" t="n">
-        <v>150</v>
+        <v>212</v>
       </c>
     </row>
     <row r="798" ht="20" customHeight="1">
@@ -20978,7 +20978,7 @@
         </is>
       </c>
       <c r="E798" s="20" t="n">
-        <v>202</v>
+        <v>164</v>
       </c>
     </row>
     <row r="799" ht="20" customHeight="1">
@@ -21003,7 +21003,7 @@
         </is>
       </c>
       <c r="E799" s="23" t="n">
-        <v>187</v>
+        <v>181</v>
       </c>
     </row>
     <row r="800" ht="20" customHeight="1">
@@ -21028,7 +21028,7 @@
         </is>
       </c>
       <c r="E800" s="20" t="n">
-        <v>176</v>
+        <v>131</v>
       </c>
     </row>
     <row r="801" ht="20" customHeight="1">
@@ -21053,7 +21053,7 @@
         </is>
       </c>
       <c r="E801" s="23" t="n">
-        <v>230</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/Appium_E2E_Test_Report_Traverse.xlsx
+++ b/Appium_E2E_Test_Report_Traverse.xlsx
@@ -791,7 +791,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 05:25:34</t>
+          <t>2026-08-11 06:01:23</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="E2" s="20" t="n">
-        <v>179</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="E3" s="23" t="n">
-        <v>161</v>
+        <v>194</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="E4" s="20" t="n">
-        <v>132</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="E5" s="23" t="n">
-        <v>209</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="E6" s="20" t="n">
-        <v>213</v>
+        <v>200</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="E7" s="23" t="n">
-        <v>238</v>
+        <v>214</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -1228,7 +1228,7 @@
         </is>
       </c>
       <c r="E8" s="20" t="n">
-        <v>210</v>
+        <v>234</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="E9" s="23" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
@@ -1278,7 +1278,7 @@
         </is>
       </c>
       <c r="E10" s="20" t="n">
-        <v>151</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="E11" s="23" t="n">
-        <v>197</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
@@ -1328,7 +1328,7 @@
         </is>
       </c>
       <c r="E12" s="20" t="n">
-        <v>208</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="E13" s="23" t="n">
-        <v>171</v>
+        <v>235</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="E14" s="20" t="n">
-        <v>225</v>
+        <v>140</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="E15" s="23" t="n">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="E16" s="20" t="n">
-        <v>118</v>
+        <v>206</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="E17" s="23" t="n">
-        <v>118</v>
+        <v>172</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -1478,7 +1478,7 @@
         </is>
       </c>
       <c r="E18" s="20" t="n">
-        <v>233</v>
+        <v>181</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
@@ -1503,7 +1503,7 @@
         </is>
       </c>
       <c r="E19" s="23" t="n">
-        <v>204</v>
+        <v>141</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="E20" s="20" t="n">
-        <v>183</v>
+        <v>215</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="E21" s="23" t="n">
-        <v>230</v>
+        <v>201</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
@@ -1578,7 +1578,7 @@
         </is>
       </c>
       <c r="E22" s="20" t="n">
-        <v>188</v>
+        <v>218</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="E23" s="23" t="n">
-        <v>146</v>
+        <v>219</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="E25" s="23" t="n">
-        <v>133</v>
+        <v>198</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
@@ -1678,7 +1678,7 @@
         </is>
       </c>
       <c r="E26" s="20" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="E27" s="23" t="n">
-        <v>120</v>
+        <v>134</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="E28" s="20" t="n">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="E29" s="23" t="n">
-        <v>142</v>
+        <v>224</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="E30" s="20" t="n">
-        <v>219</v>
+        <v>232</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
@@ -1803,7 +1803,7 @@
         </is>
       </c>
       <c r="E31" s="23" t="n">
-        <v>178</v>
+        <v>141</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
@@ -1828,7 +1828,7 @@
         </is>
       </c>
       <c r="E32" s="20" t="n">
-        <v>157</v>
+        <v>147</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
@@ -1853,7 +1853,7 @@
         </is>
       </c>
       <c r="E33" s="23" t="n">
-        <v>239</v>
+        <v>138</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
@@ -1878,7 +1878,7 @@
         </is>
       </c>
       <c r="E34" s="20" t="n">
-        <v>200</v>
+        <v>135</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="E35" s="23" t="n">
-        <v>183</v>
+        <v>165</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="E36" s="20" t="n">
-        <v>191</v>
+        <v>132</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="E37" s="23" t="n">
-        <v>140</v>
+        <v>176</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
@@ -1978,7 +1978,7 @@
         </is>
       </c>
       <c r="E38" s="20" t="n">
-        <v>158</v>
+        <v>182</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="E40" s="20" t="n">
-        <v>195</v>
+        <v>145</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="E41" s="23" t="n">
-        <v>125</v>
+        <v>238</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
@@ -2078,7 +2078,7 @@
         </is>
       </c>
       <c r="E42" s="20" t="n">
-        <v>173</v>
+        <v>144</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="E43" s="23" t="n">
-        <v>186</v>
+        <v>167</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="E44" s="20" t="n">
-        <v>208</v>
+        <v>138</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="E45" s="23" t="n">
-        <v>157</v>
+        <v>110</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
@@ -2178,7 +2178,7 @@
         </is>
       </c>
       <c r="E46" s="20" t="n">
-        <v>195</v>
+        <v>221</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
@@ -2203,7 +2203,7 @@
         </is>
       </c>
       <c r="E47" s="23" t="n">
-        <v>178</v>
+        <v>133</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="E48" s="20" t="n">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
@@ -2253,7 +2253,7 @@
         </is>
       </c>
       <c r="E49" s="23" t="n">
-        <v>173</v>
+        <v>141</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
@@ -2278,7 +2278,7 @@
         </is>
       </c>
       <c r="E50" s="20" t="n">
-        <v>219</v>
+        <v>148</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="E51" s="23" t="n">
-        <v>140</v>
+        <v>122</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
@@ -2328,7 +2328,7 @@
         </is>
       </c>
       <c r="E52" s="20" t="n">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
@@ -2353,7 +2353,7 @@
         </is>
       </c>
       <c r="E53" s="23" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="E54" s="20" t="n">
-        <v>232</v>
+        <v>226</v>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1">
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="E55" s="23" t="n">
-        <v>144</v>
+        <v>177</v>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1">
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="E56" s="20" t="n">
-        <v>124</v>
+        <v>186</v>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1">
@@ -2453,7 +2453,7 @@
         </is>
       </c>
       <c r="E57" s="23" t="n">
-        <v>172</v>
+        <v>229</v>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1">
@@ -2478,7 +2478,7 @@
         </is>
       </c>
       <c r="E58" s="20" t="n">
-        <v>146</v>
+        <v>204</v>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1">
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="E59" s="23" t="n">
-        <v>221</v>
+        <v>170</v>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1">
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="E60" s="20" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
@@ -2553,7 +2553,7 @@
         </is>
       </c>
       <c r="E61" s="23" t="n">
-        <v>134</v>
+        <v>214</v>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="E62" s="20" t="n">
-        <v>165</v>
+        <v>205</v>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="E63" s="23" t="n">
-        <v>112</v>
+        <v>159</v>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1">
@@ -2628,7 +2628,7 @@
         </is>
       </c>
       <c r="E64" s="20" t="n">
-        <v>151</v>
+        <v>140</v>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1">
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="E65" s="23" t="n">
-        <v>179</v>
+        <v>240</v>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1">
@@ -2678,7 +2678,7 @@
         </is>
       </c>
       <c r="E66" s="20" t="n">
-        <v>147</v>
+        <v>177</v>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="E67" s="23" t="n">
-        <v>200</v>
+        <v>160</v>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="E68" s="20" t="n">
-        <v>201</v>
+        <v>185</v>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="E69" s="23" t="n">
-        <v>134</v>
+        <v>183</v>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1">
@@ -2778,7 +2778,7 @@
         </is>
       </c>
       <c r="E70" s="20" t="n">
-        <v>225</v>
+        <v>219</v>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1">
@@ -2803,7 +2803,7 @@
         </is>
       </c>
       <c r="E71" s="23" t="n">
-        <v>163</v>
+        <v>171</v>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1">
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="E72" s="20" t="n">
-        <v>138</v>
+        <v>120</v>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1">
@@ -2853,7 +2853,7 @@
         </is>
       </c>
       <c r="E73" s="23" t="n">
-        <v>138</v>
+        <v>233</v>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
@@ -2878,7 +2878,7 @@
         </is>
       </c>
       <c r="E74" s="20" t="n">
-        <v>216</v>
+        <v>175</v>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="E75" s="23" t="n">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
@@ -2928,7 +2928,7 @@
         </is>
       </c>
       <c r="E76" s="20" t="n">
-        <v>148</v>
+        <v>228</v>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="E77" s="23" t="n">
-        <v>194</v>
+        <v>152</v>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1">
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="E78" s="20" t="n">
-        <v>239</v>
+        <v>160</v>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
@@ -3003,7 +3003,7 @@
         </is>
       </c>
       <c r="E79" s="23" t="n">
-        <v>148</v>
+        <v>167</v>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1">
@@ -3028,7 +3028,7 @@
         </is>
       </c>
       <c r="E80" s="20" t="n">
-        <v>128</v>
+        <v>222</v>
       </c>
     </row>
     <row r="81" ht="20" customHeight="1">
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="E81" s="23" t="n">
-        <v>137</v>
+        <v>111</v>
       </c>
     </row>
     <row r="82" ht="20" customHeight="1">
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="E82" s="20" t="n">
-        <v>200</v>
+        <v>238</v>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1">
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="E83" s="23" t="n">
-        <v>128</v>
+        <v>185</v>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1">
@@ -3128,7 +3128,7 @@
         </is>
       </c>
       <c r="E84" s="20" t="n">
-        <v>192</v>
+        <v>114</v>
       </c>
     </row>
     <row r="85" ht="20" customHeight="1">
@@ -3153,7 +3153,7 @@
         </is>
       </c>
       <c r="E85" s="23" t="n">
-        <v>207</v>
+        <v>182</v>
       </c>
     </row>
     <row r="86" ht="20" customHeight="1">
@@ -3178,7 +3178,7 @@
         </is>
       </c>
       <c r="E86" s="20" t="n">
-        <v>141</v>
+        <v>163</v>
       </c>
     </row>
     <row r="87" ht="20" customHeight="1">
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="E87" s="23" t="n">
-        <v>153</v>
+        <v>201</v>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1">
@@ -3228,7 +3228,7 @@
         </is>
       </c>
       <c r="E88" s="20" t="n">
-        <v>231</v>
+        <v>202</v>
       </c>
     </row>
     <row r="89" ht="20" customHeight="1">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="E89" s="23" t="n">
-        <v>237</v>
+        <v>114</v>
       </c>
     </row>
     <row r="90" ht="20" customHeight="1">
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="E90" s="20" t="n">
-        <v>131</v>
+        <v>176</v>
       </c>
     </row>
     <row r="91" ht="20" customHeight="1">
@@ -3303,7 +3303,7 @@
         </is>
       </c>
       <c r="E91" s="23" t="n">
-        <v>145</v>
+        <v>199</v>
       </c>
     </row>
     <row r="92" ht="20" customHeight="1">
@@ -3328,7 +3328,7 @@
         </is>
       </c>
       <c r="E92" s="20" t="n">
-        <v>160</v>
+        <v>188</v>
       </c>
     </row>
     <row r="93" ht="20" customHeight="1">
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="E93" s="23" t="n">
-        <v>174</v>
+        <v>215</v>
       </c>
     </row>
     <row r="94" ht="20" customHeight="1">
@@ -3378,7 +3378,7 @@
         </is>
       </c>
       <c r="E94" s="20" t="n">
-        <v>177</v>
+        <v>225</v>
       </c>
     </row>
     <row r="95" ht="20" customHeight="1">
@@ -3403,7 +3403,7 @@
         </is>
       </c>
       <c r="E95" s="23" t="n">
-        <v>117</v>
+        <v>229</v>
       </c>
     </row>
     <row r="96" ht="20" customHeight="1">
@@ -3428,7 +3428,7 @@
         </is>
       </c>
       <c r="E96" s="20" t="n">
-        <v>122</v>
+        <v>158</v>
       </c>
     </row>
     <row r="97" ht="20" customHeight="1">
@@ -3453,7 +3453,7 @@
         </is>
       </c>
       <c r="E97" s="23" t="n">
-        <v>234</v>
+        <v>216</v>
       </c>
     </row>
     <row r="98" ht="20" customHeight="1">
@@ -3478,7 +3478,7 @@
         </is>
       </c>
       <c r="E98" s="20" t="n">
-        <v>163</v>
+        <v>178</v>
       </c>
     </row>
     <row r="99" ht="20" customHeight="1">
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="E99" s="23" t="n">
-        <v>162</v>
+        <v>209</v>
       </c>
     </row>
     <row r="100" ht="20" customHeight="1">
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="E100" s="20" t="n">
-        <v>208</v>
+        <v>229</v>
       </c>
     </row>
     <row r="101" ht="20" customHeight="1">
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="E101" s="23" t="n">
-        <v>236</v>
+        <v>180</v>
       </c>
     </row>
     <row r="102" ht="20" customHeight="1">
@@ -3578,7 +3578,7 @@
         </is>
       </c>
       <c r="E102" s="20" t="n">
-        <v>112</v>
+        <v>198</v>
       </c>
     </row>
     <row r="103" ht="20" customHeight="1">
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="E103" s="23" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
     </row>
     <row r="104" ht="20" customHeight="1">
@@ -3628,7 +3628,7 @@
         </is>
       </c>
       <c r="E104" s="20" t="n">
-        <v>224</v>
+        <v>238</v>
       </c>
     </row>
     <row r="105" ht="20" customHeight="1">
@@ -3653,7 +3653,7 @@
         </is>
       </c>
       <c r="E105" s="23" t="n">
-        <v>199</v>
+        <v>115</v>
       </c>
     </row>
     <row r="106" ht="20" customHeight="1">
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="E106" s="20" t="n">
-        <v>152</v>
+        <v>196</v>
       </c>
     </row>
     <row r="107" ht="20" customHeight="1">
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="E107" s="23" t="n">
-        <v>177</v>
+        <v>148</v>
       </c>
     </row>
     <row r="108" ht="20" customHeight="1">
@@ -3728,7 +3728,7 @@
         </is>
       </c>
       <c r="E108" s="20" t="n">
-        <v>174</v>
+        <v>121</v>
       </c>
     </row>
     <row r="109" ht="20" customHeight="1">
@@ -3753,7 +3753,7 @@
         </is>
       </c>
       <c r="E109" s="23" t="n">
-        <v>149</v>
+        <v>156</v>
       </c>
     </row>
     <row r="110" ht="20" customHeight="1">
@@ -3778,7 +3778,7 @@
         </is>
       </c>
       <c r="E110" s="20" t="n">
-        <v>214</v>
+        <v>167</v>
       </c>
     </row>
     <row r="111" ht="20" customHeight="1">
@@ -3803,7 +3803,7 @@
         </is>
       </c>
       <c r="E111" s="23" t="n">
-        <v>213</v>
+        <v>126</v>
       </c>
     </row>
     <row r="112" ht="20" customHeight="1">
@@ -3828,7 +3828,7 @@
         </is>
       </c>
       <c r="E112" s="20" t="n">
-        <v>207</v>
+        <v>162</v>
       </c>
     </row>
     <row r="113" ht="20" customHeight="1">
@@ -3853,7 +3853,7 @@
         </is>
       </c>
       <c r="E113" s="23" t="n">
-        <v>170</v>
+        <v>134</v>
       </c>
     </row>
     <row r="114" ht="20" customHeight="1">
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="E114" s="20" t="n">
-        <v>135</v>
+        <v>208</v>
       </c>
     </row>
     <row r="115" ht="20" customHeight="1">
@@ -3903,7 +3903,7 @@
         </is>
       </c>
       <c r="E115" s="23" t="n">
-        <v>165</v>
+        <v>205</v>
       </c>
     </row>
     <row r="116" ht="20" customHeight="1">
@@ -3928,7 +3928,7 @@
         </is>
       </c>
       <c r="E116" s="20" t="n">
-        <v>116</v>
+        <v>198</v>
       </c>
     </row>
     <row r="117" ht="20" customHeight="1">
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="E117" s="23" t="n">
-        <v>237</v>
+        <v>123</v>
       </c>
     </row>
     <row r="118" ht="20" customHeight="1">
@@ -3978,7 +3978,7 @@
         </is>
       </c>
       <c r="E118" s="20" t="n">
-        <v>135</v>
+        <v>223</v>
       </c>
     </row>
     <row r="119" ht="20" customHeight="1">
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="E119" s="23" t="n">
-        <v>196</v>
+        <v>138</v>
       </c>
     </row>
     <row r="120" ht="20" customHeight="1">
@@ -4028,7 +4028,7 @@
         </is>
       </c>
       <c r="E120" s="20" t="n">
-        <v>141</v>
+        <v>150</v>
       </c>
     </row>
     <row r="121" ht="20" customHeight="1">
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="E121" s="23" t="n">
-        <v>120</v>
+        <v>227</v>
       </c>
     </row>
     <row r="122" ht="20" customHeight="1">
@@ -4078,7 +4078,7 @@
         </is>
       </c>
       <c r="E122" s="20" t="n">
-        <v>170</v>
+        <v>232</v>
       </c>
     </row>
     <row r="123" ht="20" customHeight="1">
@@ -4103,7 +4103,7 @@
         </is>
       </c>
       <c r="E123" s="23" t="n">
-        <v>194</v>
+        <v>160</v>
       </c>
     </row>
     <row r="124" ht="20" customHeight="1">
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="E124" s="20" t="n">
-        <v>202</v>
+        <v>181</v>
       </c>
     </row>
     <row r="125" ht="20" customHeight="1">
@@ -4153,7 +4153,7 @@
         </is>
       </c>
       <c r="E125" s="23" t="n">
-        <v>214</v>
+        <v>154</v>
       </c>
     </row>
     <row r="126" ht="20" customHeight="1">
@@ -4178,7 +4178,7 @@
         </is>
       </c>
       <c r="E126" s="20" t="n">
-        <v>204</v>
+        <v>133</v>
       </c>
     </row>
     <row r="127" ht="20" customHeight="1">
@@ -4203,7 +4203,7 @@
         </is>
       </c>
       <c r="E127" s="23" t="n">
-        <v>214</v>
+        <v>164</v>
       </c>
     </row>
     <row r="128" ht="20" customHeight="1">
@@ -4228,7 +4228,7 @@
         </is>
       </c>
       <c r="E128" s="20" t="n">
-        <v>224</v>
+        <v>240</v>
       </c>
     </row>
     <row r="129" ht="20" customHeight="1">
@@ -4278,7 +4278,7 @@
         </is>
       </c>
       <c r="E130" s="20" t="n">
-        <v>142</v>
+        <v>207</v>
       </c>
     </row>
     <row r="131" ht="20" customHeight="1">
@@ -4303,7 +4303,7 @@
         </is>
       </c>
       <c r="E131" s="23" t="n">
-        <v>171</v>
+        <v>161</v>
       </c>
     </row>
     <row r="132" ht="20" customHeight="1">
@@ -4328,7 +4328,7 @@
         </is>
       </c>
       <c r="E132" s="20" t="n">
-        <v>193</v>
+        <v>197</v>
       </c>
     </row>
     <row r="133" ht="20" customHeight="1">
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="E133" s="23" t="n">
-        <v>189</v>
+        <v>183</v>
       </c>
     </row>
     <row r="134" ht="20" customHeight="1">
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="E134" s="20" t="n">
-        <v>164</v>
+        <v>208</v>
       </c>
     </row>
     <row r="135" ht="20" customHeight="1">
@@ -4403,7 +4403,7 @@
         </is>
       </c>
       <c r="E135" s="23" t="n">
-        <v>164</v>
+        <v>150</v>
       </c>
     </row>
     <row r="136" ht="20" customHeight="1">
@@ -4428,7 +4428,7 @@
         </is>
       </c>
       <c r="E136" s="20" t="n">
-        <v>132</v>
+        <v>232</v>
       </c>
     </row>
     <row r="137" ht="20" customHeight="1">
@@ -4453,7 +4453,7 @@
         </is>
       </c>
       <c r="E137" s="23" t="n">
-        <v>170</v>
+        <v>122</v>
       </c>
     </row>
     <row r="138" ht="20" customHeight="1">
@@ -4478,7 +4478,7 @@
         </is>
       </c>
       <c r="E138" s="20" t="n">
-        <v>167</v>
+        <v>211</v>
       </c>
     </row>
     <row r="139" ht="20" customHeight="1">
@@ -4503,7 +4503,7 @@
         </is>
       </c>
       <c r="E139" s="23" t="n">
-        <v>148</v>
+        <v>119</v>
       </c>
     </row>
     <row r="140" ht="20" customHeight="1">
@@ -4528,7 +4528,7 @@
         </is>
       </c>
       <c r="E140" s="20" t="n">
-        <v>230</v>
+        <v>123</v>
       </c>
     </row>
     <row r="141" ht="20" customHeight="1">
@@ -4553,7 +4553,7 @@
         </is>
       </c>
       <c r="E141" s="23" t="n">
-        <v>211</v>
+        <v>183</v>
       </c>
     </row>
     <row r="142" ht="20" customHeight="1">
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="E142" s="20" t="n">
-        <v>186</v>
+        <v>200</v>
       </c>
     </row>
     <row r="143" ht="20" customHeight="1">
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="E143" s="23" t="n">
-        <v>127</v>
+        <v>194</v>
       </c>
     </row>
     <row r="144" ht="20" customHeight="1">
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="E144" s="20" t="n">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="145" ht="20" customHeight="1">
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="E145" s="23" t="n">
-        <v>173</v>
+        <v>205</v>
       </c>
     </row>
     <row r="146" ht="20" customHeight="1">
@@ -4678,7 +4678,7 @@
         </is>
       </c>
       <c r="E146" s="20" t="n">
-        <v>194</v>
+        <v>199</v>
       </c>
     </row>
     <row r="147" ht="20" customHeight="1">
@@ -4703,7 +4703,7 @@
         </is>
       </c>
       <c r="E147" s="23" t="n">
-        <v>162</v>
+        <v>211</v>
       </c>
     </row>
     <row r="148" ht="20" customHeight="1">
@@ -4728,7 +4728,7 @@
         </is>
       </c>
       <c r="E148" s="20" t="n">
-        <v>175</v>
+        <v>137</v>
       </c>
     </row>
     <row r="149" ht="20" customHeight="1">
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c r="E149" s="23" t="n">
-        <v>214</v>
+        <v>176</v>
       </c>
     </row>
     <row r="150" ht="20" customHeight="1">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="E150" s="20" t="n">
-        <v>163</v>
+        <v>177</v>
       </c>
     </row>
     <row r="151" ht="20" customHeight="1">
@@ -4803,7 +4803,7 @@
         </is>
       </c>
       <c r="E151" s="23" t="n">
-        <v>182</v>
+        <v>217</v>
       </c>
     </row>
     <row r="152" ht="20" customHeight="1">
@@ -4828,7 +4828,7 @@
         </is>
       </c>
       <c r="E152" s="20" t="n">
-        <v>182</v>
+        <v>114</v>
       </c>
     </row>
     <row r="153" ht="20" customHeight="1">
@@ -4853,7 +4853,7 @@
         </is>
       </c>
       <c r="E153" s="23" t="n">
-        <v>141</v>
+        <v>185</v>
       </c>
     </row>
     <row r="154" ht="20" customHeight="1">
@@ -4878,7 +4878,7 @@
         </is>
       </c>
       <c r="E154" s="20" t="n">
-        <v>237</v>
+        <v>112</v>
       </c>
     </row>
     <row r="155" ht="20" customHeight="1">
@@ -4903,7 +4903,7 @@
         </is>
       </c>
       <c r="E155" s="23" t="n">
-        <v>181</v>
+        <v>158</v>
       </c>
     </row>
     <row r="156" ht="20" customHeight="1">
@@ -4928,7 +4928,7 @@
         </is>
       </c>
       <c r="E156" s="20" t="n">
-        <v>237</v>
+        <v>129</v>
       </c>
     </row>
     <row r="157" ht="20" customHeight="1">
@@ -4953,7 +4953,7 @@
         </is>
       </c>
       <c r="E157" s="23" t="n">
-        <v>172</v>
+        <v>121</v>
       </c>
     </row>
     <row r="158" ht="20" customHeight="1">
@@ -4978,7 +4978,7 @@
         </is>
       </c>
       <c r="E158" s="20" t="n">
-        <v>215</v>
+        <v>134</v>
       </c>
     </row>
     <row r="159" ht="20" customHeight="1">
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="E159" s="23" t="n">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="160" ht="20" customHeight="1">
@@ -5028,7 +5028,7 @@
         </is>
       </c>
       <c r="E160" s="20" t="n">
-        <v>207</v>
+        <v>156</v>
       </c>
     </row>
     <row r="161" ht="20" customHeight="1">
@@ -5053,7 +5053,7 @@
         </is>
       </c>
       <c r="E161" s="23" t="n">
-        <v>212</v>
+        <v>120</v>
       </c>
     </row>
     <row r="162" ht="20" customHeight="1">
@@ -5078,7 +5078,7 @@
         </is>
       </c>
       <c r="E162" s="20" t="n">
-        <v>163</v>
+        <v>128</v>
       </c>
     </row>
     <row r="163" ht="20" customHeight="1">
@@ -5128,7 +5128,7 @@
         </is>
       </c>
       <c r="E164" s="20" t="n">
-        <v>199</v>
+        <v>207</v>
       </c>
     </row>
     <row r="165" ht="20" customHeight="1">
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="E165" s="23" t="n">
-        <v>151</v>
+        <v>238</v>
       </c>
     </row>
     <row r="166" ht="20" customHeight="1">
@@ -5178,7 +5178,7 @@
         </is>
       </c>
       <c r="E166" s="20" t="n">
-        <v>190</v>
+        <v>185</v>
       </c>
     </row>
     <row r="167" ht="20" customHeight="1">
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="E167" s="23" t="n">
-        <v>112</v>
+        <v>163</v>
       </c>
     </row>
     <row r="168" ht="20" customHeight="1">
@@ -5228,7 +5228,7 @@
         </is>
       </c>
       <c r="E168" s="20" t="n">
-        <v>119</v>
+        <v>232</v>
       </c>
     </row>
     <row r="169" ht="20" customHeight="1">
@@ -5253,7 +5253,7 @@
         </is>
       </c>
       <c r="E169" s="23" t="n">
-        <v>215</v>
+        <v>185</v>
       </c>
     </row>
     <row r="170" ht="20" customHeight="1">
@@ -5278,7 +5278,7 @@
         </is>
       </c>
       <c r="E170" s="20" t="n">
-        <v>122</v>
+        <v>143</v>
       </c>
     </row>
     <row r="171" ht="20" customHeight="1">
@@ -5303,7 +5303,7 @@
         </is>
       </c>
       <c r="E171" s="23" t="n">
-        <v>147</v>
+        <v>138</v>
       </c>
     </row>
     <row r="172" ht="20" customHeight="1">
@@ -5328,7 +5328,7 @@
         </is>
       </c>
       <c r="E172" s="20" t="n">
-        <v>115</v>
+        <v>153</v>
       </c>
     </row>
     <row r="173" ht="20" customHeight="1">
@@ -5353,7 +5353,7 @@
         </is>
       </c>
       <c r="E173" s="23" t="n">
-        <v>221</v>
+        <v>174</v>
       </c>
     </row>
     <row r="174" ht="20" customHeight="1">
@@ -5378,7 +5378,7 @@
         </is>
       </c>
       <c r="E174" s="20" t="n">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="175" ht="20" customHeight="1">
@@ -5403,7 +5403,7 @@
         </is>
       </c>
       <c r="E175" s="23" t="n">
-        <v>200</v>
+        <v>136</v>
       </c>
     </row>
     <row r="176" ht="20" customHeight="1">
@@ -5428,7 +5428,7 @@
         </is>
       </c>
       <c r="E176" s="20" t="n">
-        <v>194</v>
+        <v>152</v>
       </c>
     </row>
     <row r="177" ht="20" customHeight="1">
@@ -5453,7 +5453,7 @@
         </is>
       </c>
       <c r="E177" s="23" t="n">
-        <v>114</v>
+        <v>183</v>
       </c>
     </row>
     <row r="178" ht="20" customHeight="1">
@@ -5478,7 +5478,7 @@
         </is>
       </c>
       <c r="E178" s="20" t="n">
-        <v>186</v>
+        <v>145</v>
       </c>
     </row>
     <row r="179" ht="20" customHeight="1">
@@ -5503,7 +5503,7 @@
         </is>
       </c>
       <c r="E179" s="23" t="n">
-        <v>191</v>
+        <v>152</v>
       </c>
     </row>
     <row r="180" ht="20" customHeight="1">
@@ -5528,7 +5528,7 @@
         </is>
       </c>
       <c r="E180" s="20" t="n">
-        <v>178</v>
+        <v>162</v>
       </c>
     </row>
     <row r="181" ht="20" customHeight="1">
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="E181" s="23" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="182" ht="20" customHeight="1">
@@ -5578,7 +5578,7 @@
         </is>
       </c>
       <c r="E182" s="20" t="n">
-        <v>237</v>
+        <v>132</v>
       </c>
     </row>
     <row r="183" ht="20" customHeight="1">
@@ -5603,7 +5603,7 @@
         </is>
       </c>
       <c r="E183" s="23" t="n">
-        <v>118</v>
+        <v>128</v>
       </c>
     </row>
     <row r="184" ht="20" customHeight="1">
@@ -5628,7 +5628,7 @@
         </is>
       </c>
       <c r="E184" s="20" t="n">
-        <v>164</v>
+        <v>198</v>
       </c>
     </row>
     <row r="185" ht="20" customHeight="1">
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="E185" s="23" t="n">
-        <v>110</v>
+        <v>236</v>
       </c>
     </row>
     <row r="186" ht="20" customHeight="1">
@@ -5678,7 +5678,7 @@
         </is>
       </c>
       <c r="E186" s="20" t="n">
-        <v>220</v>
+        <v>204</v>
       </c>
     </row>
     <row r="187" ht="20" customHeight="1">
@@ -5703,7 +5703,7 @@
         </is>
       </c>
       <c r="E187" s="23" t="n">
-        <v>229</v>
+        <v>195</v>
       </c>
     </row>
     <row r="188" ht="20" customHeight="1">
@@ -5728,7 +5728,7 @@
         </is>
       </c>
       <c r="E188" s="20" t="n">
-        <v>152</v>
+        <v>117</v>
       </c>
     </row>
     <row r="189" ht="20" customHeight="1">
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="E189" s="23" t="n">
-        <v>225</v>
+        <v>113</v>
       </c>
     </row>
     <row r="190" ht="20" customHeight="1">
@@ -5778,7 +5778,7 @@
         </is>
       </c>
       <c r="E190" s="20" t="n">
-        <v>146</v>
+        <v>223</v>
       </c>
     </row>
     <row r="191" ht="20" customHeight="1">
@@ -5803,7 +5803,7 @@
         </is>
       </c>
       <c r="E191" s="23" t="n">
-        <v>208</v>
+        <v>203</v>
       </c>
     </row>
     <row r="192" ht="20" customHeight="1">
@@ -5828,7 +5828,7 @@
         </is>
       </c>
       <c r="E192" s="20" t="n">
-        <v>234</v>
+        <v>170</v>
       </c>
     </row>
     <row r="193" ht="20" customHeight="1">
@@ -5853,7 +5853,7 @@
         </is>
       </c>
       <c r="E193" s="23" t="n">
-        <v>231</v>
+        <v>134</v>
       </c>
     </row>
     <row r="194" ht="20" customHeight="1">
@@ -5878,7 +5878,7 @@
         </is>
       </c>
       <c r="E194" s="20" t="n">
-        <v>119</v>
+        <v>175</v>
       </c>
     </row>
     <row r="195" ht="20" customHeight="1">
@@ -5903,7 +5903,7 @@
         </is>
       </c>
       <c r="E195" s="23" t="n">
-        <v>163</v>
+        <v>216</v>
       </c>
     </row>
     <row r="196" ht="20" customHeight="1">
@@ -5928,7 +5928,7 @@
         </is>
       </c>
       <c r="E196" s="20" t="n">
-        <v>165</v>
+        <v>175</v>
       </c>
     </row>
     <row r="197" ht="20" customHeight="1">
@@ -5953,7 +5953,7 @@
         </is>
       </c>
       <c r="E197" s="23" t="n">
-        <v>215</v>
+        <v>147</v>
       </c>
     </row>
     <row r="198" ht="20" customHeight="1">
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="E198" s="20" t="n">
-        <v>130</v>
+        <v>220</v>
       </c>
     </row>
     <row r="199" ht="20" customHeight="1">
@@ -6003,7 +6003,7 @@
         </is>
       </c>
       <c r="E199" s="23" t="n">
-        <v>126</v>
+        <v>184</v>
       </c>
     </row>
     <row r="200" ht="20" customHeight="1">
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="E200" s="20" t="n">
-        <v>214</v>
+        <v>143</v>
       </c>
     </row>
     <row r="201" ht="20" customHeight="1">
@@ -6053,7 +6053,7 @@
         </is>
       </c>
       <c r="E201" s="23" t="n">
-        <v>162</v>
+        <v>224</v>
       </c>
     </row>
     <row r="202" ht="20" customHeight="1">
@@ -6078,7 +6078,7 @@
         </is>
       </c>
       <c r="E202" s="20" t="n">
-        <v>113</v>
+        <v>121</v>
       </c>
     </row>
     <row r="203" ht="20" customHeight="1">
@@ -6103,7 +6103,7 @@
         </is>
       </c>
       <c r="E203" s="23" t="n">
-        <v>154</v>
+        <v>134</v>
       </c>
     </row>
     <row r="204" ht="20" customHeight="1">
@@ -6128,7 +6128,7 @@
         </is>
       </c>
       <c r="E204" s="20" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="205" ht="20" customHeight="1">
@@ -6153,7 +6153,7 @@
         </is>
       </c>
       <c r="E205" s="23" t="n">
-        <v>195</v>
+        <v>112</v>
       </c>
     </row>
     <row r="206" ht="20" customHeight="1">
@@ -6178,7 +6178,7 @@
         </is>
       </c>
       <c r="E206" s="20" t="n">
-        <v>184</v>
+        <v>192</v>
       </c>
     </row>
     <row r="207" ht="20" customHeight="1">
@@ -6203,7 +6203,7 @@
         </is>
       </c>
       <c r="E207" s="23" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="208" ht="20" customHeight="1">
@@ -6228,7 +6228,7 @@
         </is>
       </c>
       <c r="E208" s="20" t="n">
-        <v>231</v>
+        <v>237</v>
       </c>
     </row>
     <row r="209" ht="20" customHeight="1">
@@ -6253,7 +6253,7 @@
         </is>
       </c>
       <c r="E209" s="23" t="n">
-        <v>193</v>
+        <v>168</v>
       </c>
     </row>
     <row r="210" ht="20" customHeight="1">
@@ -6278,7 +6278,7 @@
         </is>
       </c>
       <c r="E210" s="20" t="n">
-        <v>146</v>
+        <v>233</v>
       </c>
     </row>
     <row r="211" ht="20" customHeight="1">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="E211" s="23" t="n">
-        <v>142</v>
+        <v>151</v>
       </c>
     </row>
     <row r="212" ht="20" customHeight="1">
@@ -6328,7 +6328,7 @@
         </is>
       </c>
       <c r="E212" s="20" t="n">
-        <v>144</v>
+        <v>166</v>
       </c>
     </row>
     <row r="213" ht="20" customHeight="1">
@@ -6353,7 +6353,7 @@
         </is>
       </c>
       <c r="E213" s="23" t="n">
-        <v>150</v>
+        <v>204</v>
       </c>
     </row>
     <row r="214" ht="20" customHeight="1">
@@ -6378,7 +6378,7 @@
         </is>
       </c>
       <c r="E214" s="20" t="n">
-        <v>222</v>
+        <v>159</v>
       </c>
     </row>
     <row r="215" ht="20" customHeight="1">
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="E215" s="23" t="n">
-        <v>206</v>
+        <v>182</v>
       </c>
     </row>
     <row r="216" ht="20" customHeight="1">
@@ -6428,7 +6428,7 @@
         </is>
       </c>
       <c r="E216" s="20" t="n">
-        <v>186</v>
+        <v>218</v>
       </c>
     </row>
     <row r="217" ht="20" customHeight="1">
@@ -6453,7 +6453,7 @@
         </is>
       </c>
       <c r="E217" s="23" t="n">
-        <v>146</v>
+        <v>211</v>
       </c>
     </row>
     <row r="218" ht="20" customHeight="1">
@@ -6478,7 +6478,7 @@
         </is>
       </c>
       <c r="E218" s="20" t="n">
-        <v>129</v>
+        <v>148</v>
       </c>
     </row>
     <row r="219" ht="20" customHeight="1">
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="E219" s="23" t="n">
-        <v>199</v>
+        <v>143</v>
       </c>
     </row>
     <row r="220" ht="20" customHeight="1">
@@ -6528,7 +6528,7 @@
         </is>
       </c>
       <c r="E220" s="20" t="n">
-        <v>169</v>
+        <v>195</v>
       </c>
     </row>
     <row r="221" ht="20" customHeight="1">
@@ -6553,7 +6553,7 @@
         </is>
       </c>
       <c r="E221" s="23" t="n">
-        <v>123</v>
+        <v>171</v>
       </c>
     </row>
     <row r="222" ht="20" customHeight="1">
@@ -6578,7 +6578,7 @@
         </is>
       </c>
       <c r="E222" s="20" t="n">
-        <v>237</v>
+        <v>143</v>
       </c>
     </row>
     <row r="223" ht="20" customHeight="1">
@@ -6603,7 +6603,7 @@
         </is>
       </c>
       <c r="E223" s="23" t="n">
-        <v>183</v>
+        <v>112</v>
       </c>
     </row>
     <row r="224" ht="20" customHeight="1">
@@ -6628,7 +6628,7 @@
         </is>
       </c>
       <c r="E224" s="20" t="n">
-        <v>193</v>
+        <v>217</v>
       </c>
     </row>
     <row r="225" ht="20" customHeight="1">
@@ -6653,7 +6653,7 @@
         </is>
       </c>
       <c r="E225" s="23" t="n">
-        <v>225</v>
+        <v>191</v>
       </c>
     </row>
     <row r="226" ht="20" customHeight="1">
@@ -6678,7 +6678,7 @@
         </is>
       </c>
       <c r="E226" s="20" t="n">
-        <v>180</v>
+        <v>169</v>
       </c>
     </row>
     <row r="227" ht="20" customHeight="1">
@@ -6703,7 +6703,7 @@
         </is>
       </c>
       <c r="E227" s="23" t="n">
-        <v>123</v>
+        <v>148</v>
       </c>
     </row>
     <row r="228" ht="20" customHeight="1">
@@ -6728,7 +6728,7 @@
         </is>
       </c>
       <c r="E228" s="20" t="n">
-        <v>189</v>
+        <v>157</v>
       </c>
     </row>
     <row r="229" ht="20" customHeight="1">
@@ -6753,7 +6753,7 @@
         </is>
       </c>
       <c r="E229" s="23" t="n">
-        <v>235</v>
+        <v>152</v>
       </c>
     </row>
     <row r="230" ht="20" customHeight="1">
@@ -6778,7 +6778,7 @@
         </is>
       </c>
       <c r="E230" s="20" t="n">
-        <v>129</v>
+        <v>201</v>
       </c>
     </row>
     <row r="231" ht="20" customHeight="1">
@@ -6803,7 +6803,7 @@
         </is>
       </c>
       <c r="E231" s="23" t="n">
-        <v>157</v>
+        <v>214</v>
       </c>
     </row>
     <row r="232" ht="20" customHeight="1">
@@ -6828,7 +6828,7 @@
         </is>
       </c>
       <c r="E232" s="20" t="n">
-        <v>140</v>
+        <v>215</v>
       </c>
     </row>
     <row r="233" ht="20" customHeight="1">
@@ -6853,7 +6853,7 @@
         </is>
       </c>
       <c r="E233" s="23" t="n">
-        <v>197</v>
+        <v>182</v>
       </c>
     </row>
     <row r="234" ht="20" customHeight="1">
@@ -6878,7 +6878,7 @@
         </is>
       </c>
       <c r="E234" s="20" t="n">
-        <v>239</v>
+        <v>206</v>
       </c>
     </row>
     <row r="235" ht="20" customHeight="1">
@@ -6903,7 +6903,7 @@
         </is>
       </c>
       <c r="E235" s="23" t="n">
-        <v>151</v>
+        <v>127</v>
       </c>
     </row>
     <row r="236" ht="20" customHeight="1">
@@ -6928,7 +6928,7 @@
         </is>
       </c>
       <c r="E236" s="20" t="n">
-        <v>157</v>
+        <v>169</v>
       </c>
     </row>
     <row r="237" ht="20" customHeight="1">
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="E237" s="23" t="n">
-        <v>126</v>
+        <v>182</v>
       </c>
     </row>
     <row r="238" ht="20" customHeight="1">
@@ -6978,7 +6978,7 @@
         </is>
       </c>
       <c r="E238" s="20" t="n">
-        <v>196</v>
+        <v>223</v>
       </c>
     </row>
     <row r="239" ht="20" customHeight="1">
@@ -7003,7 +7003,7 @@
         </is>
       </c>
       <c r="E239" s="23" t="n">
-        <v>178</v>
+        <v>147</v>
       </c>
     </row>
     <row r="240" ht="20" customHeight="1">
@@ -7028,7 +7028,7 @@
         </is>
       </c>
       <c r="E240" s="20" t="n">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="241" ht="20" customHeight="1">
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="E241" s="23" t="n">
-        <v>173</v>
+        <v>165</v>
       </c>
     </row>
     <row r="242" ht="20" customHeight="1">
@@ -7078,7 +7078,7 @@
         </is>
       </c>
       <c r="E242" s="20" t="n">
-        <v>190</v>
+        <v>203</v>
       </c>
     </row>
     <row r="243" ht="20" customHeight="1">
@@ -7103,7 +7103,7 @@
         </is>
       </c>
       <c r="E243" s="23" t="n">
-        <v>168</v>
+        <v>205</v>
       </c>
     </row>
     <row r="244" ht="20" customHeight="1">
@@ -7128,7 +7128,7 @@
         </is>
       </c>
       <c r="E244" s="20" t="n">
-        <v>216</v>
+        <v>131</v>
       </c>
     </row>
     <row r="245" ht="20" customHeight="1">
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="E245" s="23" t="n">
-        <v>168</v>
+        <v>156</v>
       </c>
     </row>
     <row r="246" ht="20" customHeight="1">
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="E246" s="20" t="n">
-        <v>158</v>
+        <v>181</v>
       </c>
     </row>
     <row r="247" ht="20" customHeight="1">
@@ -7203,7 +7203,7 @@
         </is>
       </c>
       <c r="E247" s="23" t="n">
-        <v>155</v>
+        <v>239</v>
       </c>
     </row>
     <row r="248" ht="20" customHeight="1">
@@ -7228,7 +7228,7 @@
         </is>
       </c>
       <c r="E248" s="20" t="n">
-        <v>218</v>
+        <v>127</v>
       </c>
     </row>
     <row r="249" ht="20" customHeight="1">
@@ -7253,7 +7253,7 @@
         </is>
       </c>
       <c r="E249" s="23" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="250" ht="20" customHeight="1">
@@ -7278,7 +7278,7 @@
         </is>
       </c>
       <c r="E250" s="20" t="n">
-        <v>193</v>
+        <v>136</v>
       </c>
     </row>
     <row r="251" ht="20" customHeight="1">
@@ -7303,7 +7303,7 @@
         </is>
       </c>
       <c r="E251" s="23" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="252" ht="20" customHeight="1">
@@ -7328,7 +7328,7 @@
         </is>
       </c>
       <c r="E252" s="20" t="n">
-        <v>178</v>
+        <v>154</v>
       </c>
     </row>
     <row r="253" ht="20" customHeight="1">
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="E253" s="23" t="n">
-        <v>191</v>
+        <v>110</v>
       </c>
     </row>
     <row r="254" ht="20" customHeight="1">
@@ -7378,7 +7378,7 @@
         </is>
       </c>
       <c r="E254" s="20" t="n">
-        <v>239</v>
+        <v>210</v>
       </c>
     </row>
     <row r="255" ht="20" customHeight="1">
@@ -7403,7 +7403,7 @@
         </is>
       </c>
       <c r="E255" s="23" t="n">
-        <v>233</v>
+        <v>179</v>
       </c>
     </row>
     <row r="256" ht="20" customHeight="1">
@@ -7428,7 +7428,7 @@
         </is>
       </c>
       <c r="E256" s="20" t="n">
-        <v>191</v>
+        <v>226</v>
       </c>
     </row>
     <row r="257" ht="20" customHeight="1">
@@ -7453,7 +7453,7 @@
         </is>
       </c>
       <c r="E257" s="23" t="n">
-        <v>117</v>
+        <v>145</v>
       </c>
     </row>
     <row r="258" ht="20" customHeight="1">
@@ -7478,7 +7478,7 @@
         </is>
       </c>
       <c r="E258" s="20" t="n">
-        <v>169</v>
+        <v>210</v>
       </c>
     </row>
     <row r="259" ht="20" customHeight="1">
@@ -7503,7 +7503,7 @@
         </is>
       </c>
       <c r="E259" s="23" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="260" ht="20" customHeight="1">
@@ -7528,7 +7528,7 @@
         </is>
       </c>
       <c r="E260" s="20" t="n">
-        <v>174</v>
+        <v>198</v>
       </c>
     </row>
     <row r="261" ht="20" customHeight="1">
@@ -7553,7 +7553,7 @@
         </is>
       </c>
       <c r="E261" s="23" t="n">
-        <v>219</v>
+        <v>127</v>
       </c>
     </row>
     <row r="262" ht="20" customHeight="1">
@@ -7578,7 +7578,7 @@
         </is>
       </c>
       <c r="E262" s="20" t="n">
-        <v>133</v>
+        <v>113</v>
       </c>
     </row>
     <row r="263" ht="20" customHeight="1">
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="E263" s="23" t="n">
-        <v>206</v>
+        <v>149</v>
       </c>
     </row>
     <row r="264" ht="20" customHeight="1">
@@ -7628,7 +7628,7 @@
         </is>
       </c>
       <c r="E264" s="20" t="n">
-        <v>235</v>
+        <v>197</v>
       </c>
     </row>
     <row r="265" ht="20" customHeight="1">
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="E265" s="23" t="n">
-        <v>144</v>
+        <v>194</v>
       </c>
     </row>
     <row r="266" ht="20" customHeight="1">
@@ -7678,7 +7678,7 @@
         </is>
       </c>
       <c r="E266" s="20" t="n">
-        <v>167</v>
+        <v>227</v>
       </c>
     </row>
     <row r="267" ht="20" customHeight="1">
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="E267" s="23" t="n">
-        <v>161</v>
+        <v>151</v>
       </c>
     </row>
     <row r="268" ht="20" customHeight="1">
@@ -7728,7 +7728,7 @@
         </is>
       </c>
       <c r="E268" s="20" t="n">
-        <v>217</v>
+        <v>137</v>
       </c>
     </row>
     <row r="269" ht="20" customHeight="1">
@@ -7753,7 +7753,7 @@
         </is>
       </c>
       <c r="E269" s="23" t="n">
-        <v>196</v>
+        <v>162</v>
       </c>
     </row>
     <row r="270" ht="20" customHeight="1">
@@ -7778,7 +7778,7 @@
         </is>
       </c>
       <c r="E270" s="20" t="n">
-        <v>235</v>
+        <v>138</v>
       </c>
     </row>
     <row r="271" ht="20" customHeight="1">
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="E271" s="23" t="n">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="272" ht="20" customHeight="1">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="E272" s="20" t="n">
-        <v>168</v>
+        <v>119</v>
       </c>
     </row>
     <row r="273" ht="20" customHeight="1">
@@ -7853,7 +7853,7 @@
         </is>
       </c>
       <c r="E273" s="23" t="n">
-        <v>126</v>
+        <v>139</v>
       </c>
     </row>
     <row r="274" ht="20" customHeight="1">
@@ -7878,7 +7878,7 @@
         </is>
       </c>
       <c r="E274" s="20" t="n">
-        <v>116</v>
+        <v>227</v>
       </c>
     </row>
     <row r="275" ht="20" customHeight="1">
@@ -7903,7 +7903,7 @@
         </is>
       </c>
       <c r="E275" s="23" t="n">
-        <v>152</v>
+        <v>160</v>
       </c>
     </row>
     <row r="276" ht="20" customHeight="1">
@@ -7928,7 +7928,7 @@
         </is>
       </c>
       <c r="E276" s="20" t="n">
-        <v>176</v>
+        <v>187</v>
       </c>
     </row>
     <row r="277" ht="20" customHeight="1">
@@ -7953,7 +7953,7 @@
         </is>
       </c>
       <c r="E277" s="23" t="n">
-        <v>238</v>
+        <v>231</v>
       </c>
     </row>
     <row r="278" ht="20" customHeight="1">
@@ -7978,7 +7978,7 @@
         </is>
       </c>
       <c r="E278" s="20" t="n">
-        <v>153</v>
+        <v>147</v>
       </c>
     </row>
     <row r="279" ht="20" customHeight="1">
@@ -8003,7 +8003,7 @@
         </is>
       </c>
       <c r="E279" s="23" t="n">
-        <v>216</v>
+        <v>122</v>
       </c>
     </row>
     <row r="280" ht="20" customHeight="1">
@@ -8028,7 +8028,7 @@
         </is>
       </c>
       <c r="E280" s="20" t="n">
-        <v>174</v>
+        <v>193</v>
       </c>
     </row>
     <row r="281" ht="20" customHeight="1">
@@ -8053,7 +8053,7 @@
         </is>
       </c>
       <c r="E281" s="23" t="n">
-        <v>215</v>
+        <v>127</v>
       </c>
     </row>
     <row r="282" ht="20" customHeight="1">
@@ -8078,7 +8078,7 @@
         </is>
       </c>
       <c r="E282" s="20" t="n">
-        <v>113</v>
+        <v>223</v>
       </c>
     </row>
     <row r="283" ht="20" customHeight="1">
@@ -8103,7 +8103,7 @@
         </is>
       </c>
       <c r="E283" s="23" t="n">
-        <v>145</v>
+        <v>198</v>
       </c>
     </row>
     <row r="284" ht="20" customHeight="1">
@@ -8153,7 +8153,7 @@
         </is>
       </c>
       <c r="E285" s="23" t="n">
-        <v>180</v>
+        <v>140</v>
       </c>
     </row>
     <row r="286" ht="20" customHeight="1">
@@ -8178,7 +8178,7 @@
         </is>
       </c>
       <c r="E286" s="20" t="n">
-        <v>206</v>
+        <v>129</v>
       </c>
     </row>
     <row r="287" ht="20" customHeight="1">
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="E287" s="23" t="n">
-        <v>149</v>
+        <v>177</v>
       </c>
     </row>
     <row r="288" ht="20" customHeight="1">
@@ -8228,7 +8228,7 @@
         </is>
       </c>
       <c r="E288" s="20" t="n">
-        <v>156</v>
+        <v>202</v>
       </c>
     </row>
     <row r="289" ht="20" customHeight="1">
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="E289" s="23" t="n">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="290" ht="20" customHeight="1">
@@ -8278,7 +8278,7 @@
         </is>
       </c>
       <c r="E290" s="20" t="n">
-        <v>202</v>
+        <v>135</v>
       </c>
     </row>
     <row r="291" ht="20" customHeight="1">
@@ -8303,7 +8303,7 @@
         </is>
       </c>
       <c r="E291" s="23" t="n">
-        <v>130</v>
+        <v>230</v>
       </c>
     </row>
     <row r="292" ht="20" customHeight="1">
@@ -8328,7 +8328,7 @@
         </is>
       </c>
       <c r="E292" s="20" t="n">
-        <v>118</v>
+        <v>135</v>
       </c>
     </row>
     <row r="293" ht="20" customHeight="1">
@@ -8353,7 +8353,7 @@
         </is>
       </c>
       <c r="E293" s="23" t="n">
-        <v>160</v>
+        <v>207</v>
       </c>
     </row>
     <row r="294" ht="20" customHeight="1">
@@ -8378,7 +8378,7 @@
         </is>
       </c>
       <c r="E294" s="20" t="n">
-        <v>216</v>
+        <v>152</v>
       </c>
     </row>
     <row r="295" ht="20" customHeight="1">
@@ -8403,7 +8403,7 @@
         </is>
       </c>
       <c r="E295" s="23" t="n">
-        <v>238</v>
+        <v>208</v>
       </c>
     </row>
     <row r="296" ht="20" customHeight="1">
@@ -8428,7 +8428,7 @@
         </is>
       </c>
       <c r="E296" s="20" t="n">
-        <v>214</v>
+        <v>240</v>
       </c>
     </row>
     <row r="297" ht="20" customHeight="1">
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="E297" s="23" t="n">
-        <v>224</v>
+        <v>142</v>
       </c>
     </row>
     <row r="298" ht="20" customHeight="1">
@@ -8478,7 +8478,7 @@
         </is>
       </c>
       <c r="E298" s="20" t="n">
-        <v>194</v>
+        <v>168</v>
       </c>
     </row>
     <row r="299" ht="20" customHeight="1">
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="E299" s="23" t="n">
-        <v>211</v>
+        <v>160</v>
       </c>
     </row>
     <row r="300" ht="20" customHeight="1">
@@ -8528,7 +8528,7 @@
         </is>
       </c>
       <c r="E300" s="20" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="301" ht="20" customHeight="1">
@@ -8553,7 +8553,7 @@
         </is>
       </c>
       <c r="E301" s="23" t="n">
-        <v>204</v>
+        <v>189</v>
       </c>
     </row>
     <row r="302" ht="20" customHeight="1">
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="E302" s="20" t="n">
-        <v>159</v>
+        <v>182</v>
       </c>
     </row>
     <row r="303" ht="20" customHeight="1">
@@ -8603,7 +8603,7 @@
         </is>
       </c>
       <c r="E303" s="23" t="n">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="304" ht="20" customHeight="1">
@@ -8628,7 +8628,7 @@
         </is>
       </c>
       <c r="E304" s="20" t="n">
-        <v>138</v>
+        <v>162</v>
       </c>
     </row>
     <row r="305" ht="20" customHeight="1">
@@ -8653,7 +8653,7 @@
         </is>
       </c>
       <c r="E305" s="23" t="n">
-        <v>208</v>
+        <v>220</v>
       </c>
     </row>
     <row r="306" ht="20" customHeight="1">
@@ -8678,7 +8678,7 @@
         </is>
       </c>
       <c r="E306" s="20" t="n">
-        <v>126</v>
+        <v>194</v>
       </c>
     </row>
     <row r="307" ht="20" customHeight="1">
@@ -8703,7 +8703,7 @@
         </is>
       </c>
       <c r="E307" s="23" t="n">
-        <v>164</v>
+        <v>194</v>
       </c>
     </row>
     <row r="308" ht="20" customHeight="1">
@@ -8728,7 +8728,7 @@
         </is>
       </c>
       <c r="E308" s="20" t="n">
-        <v>140</v>
+        <v>151</v>
       </c>
     </row>
     <row r="309" ht="20" customHeight="1">
@@ -8753,7 +8753,7 @@
         </is>
       </c>
       <c r="E309" s="23" t="n">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="310" ht="20" customHeight="1">
@@ -8778,7 +8778,7 @@
         </is>
       </c>
       <c r="E310" s="20" t="n">
-        <v>112</v>
+        <v>191</v>
       </c>
     </row>
     <row r="311" ht="20" customHeight="1">
@@ -8803,7 +8803,7 @@
         </is>
       </c>
       <c r="E311" s="23" t="n">
-        <v>116</v>
+        <v>214</v>
       </c>
     </row>
     <row r="312" ht="20" customHeight="1">
@@ -8828,7 +8828,7 @@
         </is>
       </c>
       <c r="E312" s="20" t="n">
-        <v>228</v>
+        <v>194</v>
       </c>
     </row>
     <row r="313" ht="20" customHeight="1">
@@ -8853,7 +8853,7 @@
         </is>
       </c>
       <c r="E313" s="23" t="n">
-        <v>127</v>
+        <v>140</v>
       </c>
     </row>
     <row r="314" ht="20" customHeight="1">
@@ -8878,7 +8878,7 @@
         </is>
       </c>
       <c r="E314" s="20" t="n">
-        <v>196</v>
+        <v>169</v>
       </c>
     </row>
     <row r="315" ht="20" customHeight="1">
@@ -8903,7 +8903,7 @@
         </is>
       </c>
       <c r="E315" s="23" t="n">
-        <v>184</v>
+        <v>227</v>
       </c>
     </row>
     <row r="316" ht="20" customHeight="1">
@@ -8928,7 +8928,7 @@
         </is>
       </c>
       <c r="E316" s="20" t="n">
-        <v>113</v>
+        <v>200</v>
       </c>
     </row>
     <row r="317" ht="20" customHeight="1">
@@ -8953,7 +8953,7 @@
         </is>
       </c>
       <c r="E317" s="23" t="n">
-        <v>124</v>
+        <v>112</v>
       </c>
     </row>
     <row r="318" ht="20" customHeight="1">
@@ -8978,7 +8978,7 @@
         </is>
       </c>
       <c r="E318" s="20" t="n">
-        <v>134</v>
+        <v>157</v>
       </c>
     </row>
     <row r="319" ht="20" customHeight="1">
@@ -9003,7 +9003,7 @@
         </is>
       </c>
       <c r="E319" s="23" t="n">
-        <v>186</v>
+        <v>179</v>
       </c>
     </row>
     <row r="320" ht="20" customHeight="1">
@@ -9028,7 +9028,7 @@
         </is>
       </c>
       <c r="E320" s="20" t="n">
-        <v>235</v>
+        <v>126</v>
       </c>
     </row>
     <row r="321" ht="20" customHeight="1">
@@ -9053,7 +9053,7 @@
         </is>
       </c>
       <c r="E321" s="23" t="n">
-        <v>210</v>
+        <v>138</v>
       </c>
     </row>
     <row r="322" ht="20" customHeight="1">
@@ -9078,7 +9078,7 @@
         </is>
       </c>
       <c r="E322" s="20" t="n">
-        <v>136</v>
+        <v>173</v>
       </c>
     </row>
     <row r="323" ht="20" customHeight="1">
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="E323" s="23" t="n">
-        <v>122</v>
+        <v>133</v>
       </c>
     </row>
     <row r="324" ht="20" customHeight="1">
@@ -9128,7 +9128,7 @@
         </is>
       </c>
       <c r="E324" s="20" t="n">
-        <v>152</v>
+        <v>175</v>
       </c>
     </row>
     <row r="325" ht="20" customHeight="1">
@@ -9153,7 +9153,7 @@
         </is>
       </c>
       <c r="E325" s="23" t="n">
-        <v>177</v>
+        <v>195</v>
       </c>
     </row>
     <row r="326" ht="20" customHeight="1">
@@ -9178,7 +9178,7 @@
         </is>
       </c>
       <c r="E326" s="20" t="n">
-        <v>230</v>
+        <v>135</v>
       </c>
     </row>
     <row r="327" ht="20" customHeight="1">
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="E328" s="20" t="n">
-        <v>215</v>
+        <v>234</v>
       </c>
     </row>
     <row r="329" ht="20" customHeight="1">
@@ -9253,7 +9253,7 @@
         </is>
       </c>
       <c r="E329" s="23" t="n">
-        <v>234</v>
+        <v>196</v>
       </c>
     </row>
     <row r="330" ht="20" customHeight="1">
@@ -9278,7 +9278,7 @@
         </is>
       </c>
       <c r="E330" s="20" t="n">
-        <v>133</v>
+        <v>120</v>
       </c>
     </row>
     <row r="331" ht="20" customHeight="1">
@@ -9303,7 +9303,7 @@
         </is>
       </c>
       <c r="E331" s="23" t="n">
-        <v>165</v>
+        <v>188</v>
       </c>
     </row>
     <row r="332" ht="20" customHeight="1">
@@ -9328,7 +9328,7 @@
         </is>
       </c>
       <c r="E332" s="20" t="n">
-        <v>197</v>
+        <v>236</v>
       </c>
     </row>
     <row r="333" ht="20" customHeight="1">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="E333" s="23" t="n">
-        <v>161</v>
+        <v>144</v>
       </c>
     </row>
     <row r="334" ht="20" customHeight="1">
@@ -9378,7 +9378,7 @@
         </is>
       </c>
       <c r="E334" s="20" t="n">
-        <v>210</v>
+        <v>231</v>
       </c>
     </row>
     <row r="335" ht="20" customHeight="1">
@@ -9403,7 +9403,7 @@
         </is>
       </c>
       <c r="E335" s="23" t="n">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
     <row r="336" ht="20" customHeight="1">
@@ -9428,7 +9428,7 @@
         </is>
       </c>
       <c r="E336" s="20" t="n">
-        <v>239</v>
+        <v>228</v>
       </c>
     </row>
     <row r="337" ht="20" customHeight="1">
@@ -9453,7 +9453,7 @@
         </is>
       </c>
       <c r="E337" s="23" t="n">
-        <v>183</v>
+        <v>229</v>
       </c>
     </row>
     <row r="338" ht="20" customHeight="1">
@@ -9478,7 +9478,7 @@
         </is>
       </c>
       <c r="E338" s="20" t="n">
-        <v>217</v>
+        <v>237</v>
       </c>
     </row>
     <row r="339" ht="20" customHeight="1">
@@ -9503,7 +9503,7 @@
         </is>
       </c>
       <c r="E339" s="23" t="n">
-        <v>240</v>
+        <v>143</v>
       </c>
     </row>
     <row r="340" ht="20" customHeight="1">
@@ -9528,7 +9528,7 @@
         </is>
       </c>
       <c r="E340" s="20" t="n">
-        <v>216</v>
+        <v>192</v>
       </c>
     </row>
     <row r="341" ht="20" customHeight="1">
@@ -9553,7 +9553,7 @@
         </is>
       </c>
       <c r="E341" s="23" t="n">
-        <v>111</v>
+        <v>172</v>
       </c>
     </row>
     <row r="342" ht="20" customHeight="1">
@@ -9578,7 +9578,7 @@
         </is>
       </c>
       <c r="E342" s="20" t="n">
-        <v>224</v>
+        <v>190</v>
       </c>
     </row>
     <row r="343" ht="20" customHeight="1">
@@ -9603,7 +9603,7 @@
         </is>
       </c>
       <c r="E343" s="23" t="n">
-        <v>163</v>
+        <v>181</v>
       </c>
     </row>
     <row r="344" ht="20" customHeight="1">
@@ -9628,7 +9628,7 @@
         </is>
       </c>
       <c r="E344" s="20" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
     </row>
     <row r="345" ht="20" customHeight="1">
@@ -9653,7 +9653,7 @@
         </is>
       </c>
       <c r="E345" s="23" t="n">
-        <v>149</v>
+        <v>231</v>
       </c>
     </row>
     <row r="346" ht="20" customHeight="1">
@@ -9678,7 +9678,7 @@
         </is>
       </c>
       <c r="E346" s="20" t="n">
-        <v>196</v>
+        <v>147</v>
       </c>
     </row>
     <row r="347" ht="20" customHeight="1">
@@ -9703,7 +9703,7 @@
         </is>
       </c>
       <c r="E347" s="23" t="n">
-        <v>159</v>
+        <v>172</v>
       </c>
     </row>
     <row r="348" ht="20" customHeight="1">
@@ -9728,7 +9728,7 @@
         </is>
       </c>
       <c r="E348" s="20" t="n">
-        <v>231</v>
+        <v>143</v>
       </c>
     </row>
     <row r="349" ht="20" customHeight="1">
@@ -9753,7 +9753,7 @@
         </is>
       </c>
       <c r="E349" s="23" t="n">
-        <v>124</v>
+        <v>207</v>
       </c>
     </row>
     <row r="350" ht="20" customHeight="1">
@@ -9778,7 +9778,7 @@
         </is>
       </c>
       <c r="E350" s="20" t="n">
-        <v>138</v>
+        <v>183</v>
       </c>
     </row>
     <row r="351" ht="20" customHeight="1">
@@ -9803,7 +9803,7 @@
         </is>
       </c>
       <c r="E351" s="23" t="n">
-        <v>214</v>
+        <v>115</v>
       </c>
     </row>
     <row r="352" ht="20" customHeight="1">
@@ -9828,7 +9828,7 @@
         </is>
       </c>
       <c r="E352" s="20" t="n">
-        <v>238</v>
+        <v>168</v>
       </c>
     </row>
     <row r="353" ht="20" customHeight="1">
@@ -9853,7 +9853,7 @@
         </is>
       </c>
       <c r="E353" s="23" t="n">
-        <v>133</v>
+        <v>170</v>
       </c>
     </row>
     <row r="354" ht="20" customHeight="1">
@@ -9878,7 +9878,7 @@
         </is>
       </c>
       <c r="E354" s="20" t="n">
-        <v>210</v>
+        <v>173</v>
       </c>
     </row>
     <row r="355" ht="20" customHeight="1">
@@ -9903,7 +9903,7 @@
         </is>
       </c>
       <c r="E355" s="23" t="n">
-        <v>139</v>
+        <v>130</v>
       </c>
     </row>
     <row r="356" ht="20" customHeight="1">
@@ -9928,7 +9928,7 @@
         </is>
       </c>
       <c r="E356" s="20" t="n">
-        <v>162</v>
+        <v>198</v>
       </c>
     </row>
     <row r="357" ht="20" customHeight="1">
@@ -9953,7 +9953,7 @@
         </is>
       </c>
       <c r="E357" s="23" t="n">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="358" ht="20" customHeight="1">
@@ -9978,7 +9978,7 @@
         </is>
       </c>
       <c r="E358" s="20" t="n">
-        <v>224</v>
+        <v>131</v>
       </c>
     </row>
     <row r="359" ht="20" customHeight="1">
@@ -10003,7 +10003,7 @@
         </is>
       </c>
       <c r="E359" s="23" t="n">
-        <v>198</v>
+        <v>143</v>
       </c>
     </row>
     <row r="360" ht="20" customHeight="1">
@@ -10028,7 +10028,7 @@
         </is>
       </c>
       <c r="E360" s="20" t="n">
-        <v>198</v>
+        <v>148</v>
       </c>
     </row>
     <row r="361" ht="20" customHeight="1">
@@ -10053,7 +10053,7 @@
         </is>
       </c>
       <c r="E361" s="23" t="n">
-        <v>171</v>
+        <v>221</v>
       </c>
     </row>
     <row r="362" ht="20" customHeight="1">
@@ -10078,7 +10078,7 @@
         </is>
       </c>
       <c r="E362" s="20" t="n">
-        <v>124</v>
+        <v>229</v>
       </c>
     </row>
     <row r="363" ht="20" customHeight="1">
@@ -10103,7 +10103,7 @@
         </is>
       </c>
       <c r="E363" s="23" t="n">
-        <v>157</v>
+        <v>169</v>
       </c>
     </row>
     <row r="364" ht="20" customHeight="1">
@@ -10128,7 +10128,7 @@
         </is>
       </c>
       <c r="E364" s="20" t="n">
-        <v>174</v>
+        <v>212</v>
       </c>
     </row>
     <row r="365" ht="20" customHeight="1">
@@ -10153,7 +10153,7 @@
         </is>
       </c>
       <c r="E365" s="23" t="n">
-        <v>196</v>
+        <v>118</v>
       </c>
     </row>
     <row r="366" ht="20" customHeight="1">
@@ -10178,7 +10178,7 @@
         </is>
       </c>
       <c r="E366" s="20" t="n">
-        <v>210</v>
+        <v>148</v>
       </c>
     </row>
     <row r="367" ht="20" customHeight="1">
@@ -10203,7 +10203,7 @@
         </is>
       </c>
       <c r="E367" s="23" t="n">
-        <v>168</v>
+        <v>209</v>
       </c>
     </row>
     <row r="368" ht="20" customHeight="1">
@@ -10228,7 +10228,7 @@
         </is>
       </c>
       <c r="E368" s="20" t="n">
-        <v>230</v>
+        <v>154</v>
       </c>
     </row>
     <row r="369" ht="20" customHeight="1">
@@ -10253,7 +10253,7 @@
         </is>
       </c>
       <c r="E369" s="23" t="n">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="370" ht="20" customHeight="1">
@@ -10278,7 +10278,7 @@
         </is>
       </c>
       <c r="E370" s="20" t="n">
-        <v>223</v>
+        <v>151</v>
       </c>
     </row>
     <row r="371" ht="20" customHeight="1">
@@ -10303,7 +10303,7 @@
         </is>
       </c>
       <c r="E371" s="23" t="n">
-        <v>146</v>
+        <v>112</v>
       </c>
     </row>
     <row r="372" ht="20" customHeight="1">
@@ -10328,7 +10328,7 @@
         </is>
       </c>
       <c r="E372" s="20" t="n">
-        <v>174</v>
+        <v>123</v>
       </c>
     </row>
     <row r="373" ht="20" customHeight="1">
@@ -10353,7 +10353,7 @@
         </is>
       </c>
       <c r="E373" s="23" t="n">
-        <v>220</v>
+        <v>130</v>
       </c>
     </row>
     <row r="374" ht="20" customHeight="1">
@@ -10378,7 +10378,7 @@
         </is>
       </c>
       <c r="E374" s="20" t="n">
-        <v>139</v>
+        <v>163</v>
       </c>
     </row>
     <row r="375" ht="20" customHeight="1">
@@ -10403,7 +10403,7 @@
         </is>
       </c>
       <c r="E375" s="23" t="n">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="376" ht="20" customHeight="1">
@@ -10428,7 +10428,7 @@
         </is>
       </c>
       <c r="E376" s="20" t="n">
-        <v>224</v>
+        <v>162</v>
       </c>
     </row>
     <row r="377" ht="20" customHeight="1">
@@ -10453,7 +10453,7 @@
         </is>
       </c>
       <c r="E377" s="23" t="n">
-        <v>230</v>
+        <v>122</v>
       </c>
     </row>
     <row r="378" ht="20" customHeight="1">
@@ -10478,7 +10478,7 @@
         </is>
       </c>
       <c r="E378" s="20" t="n">
-        <v>167</v>
+        <v>141</v>
       </c>
     </row>
     <row r="379" ht="20" customHeight="1">
@@ -10528,7 +10528,7 @@
         </is>
       </c>
       <c r="E380" s="20" t="n">
-        <v>184</v>
+        <v>211</v>
       </c>
     </row>
     <row r="381" ht="20" customHeight="1">
@@ -10553,7 +10553,7 @@
         </is>
       </c>
       <c r="E381" s="23" t="n">
-        <v>129</v>
+        <v>174</v>
       </c>
     </row>
     <row r="382" ht="20" customHeight="1">
@@ -10578,7 +10578,7 @@
         </is>
       </c>
       <c r="E382" s="20" t="n">
-        <v>153</v>
+        <v>127</v>
       </c>
     </row>
     <row r="383" ht="20" customHeight="1">
@@ -10603,7 +10603,7 @@
         </is>
       </c>
       <c r="E383" s="23" t="n">
-        <v>192</v>
+        <v>187</v>
       </c>
     </row>
     <row r="384" ht="20" customHeight="1">
@@ -10628,7 +10628,7 @@
         </is>
       </c>
       <c r="E384" s="20" t="n">
-        <v>217</v>
+        <v>173</v>
       </c>
     </row>
     <row r="385" ht="20" customHeight="1">
@@ -10653,7 +10653,7 @@
         </is>
       </c>
       <c r="E385" s="23" t="n">
-        <v>128</v>
+        <v>235</v>
       </c>
     </row>
     <row r="386" ht="20" customHeight="1">
@@ -10678,7 +10678,7 @@
         </is>
       </c>
       <c r="E386" s="20" t="n">
-        <v>212</v>
+        <v>187</v>
       </c>
     </row>
     <row r="387" ht="20" customHeight="1">
@@ -10703,7 +10703,7 @@
         </is>
       </c>
       <c r="E387" s="23" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="388" ht="20" customHeight="1">
@@ -10728,7 +10728,7 @@
         </is>
       </c>
       <c r="E388" s="20" t="n">
-        <v>177</v>
+        <v>120</v>
       </c>
     </row>
     <row r="389" ht="20" customHeight="1">
@@ -10753,7 +10753,7 @@
         </is>
       </c>
       <c r="E389" s="23" t="n">
-        <v>162</v>
+        <v>144</v>
       </c>
     </row>
     <row r="390" ht="20" customHeight="1">
@@ -10778,7 +10778,7 @@
         </is>
       </c>
       <c r="E390" s="20" t="n">
-        <v>172</v>
+        <v>225</v>
       </c>
     </row>
     <row r="391" ht="20" customHeight="1">
@@ -10803,7 +10803,7 @@
         </is>
       </c>
       <c r="E391" s="23" t="n">
-        <v>204</v>
+        <v>156</v>
       </c>
     </row>
     <row r="392" ht="20" customHeight="1">
@@ -10828,7 +10828,7 @@
         </is>
       </c>
       <c r="E392" s="20" t="n">
-        <v>198</v>
+        <v>178</v>
       </c>
     </row>
     <row r="393" ht="20" customHeight="1">
@@ -10853,7 +10853,7 @@
         </is>
       </c>
       <c r="E393" s="23" t="n">
-        <v>121</v>
+        <v>204</v>
       </c>
     </row>
     <row r="394" ht="20" customHeight="1">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="E394" s="20" t="n">
-        <v>136</v>
+        <v>188</v>
       </c>
     </row>
     <row r="395" ht="20" customHeight="1">
@@ -10903,7 +10903,7 @@
         </is>
       </c>
       <c r="E395" s="23" t="n">
-        <v>145</v>
+        <v>129</v>
       </c>
     </row>
     <row r="396" ht="20" customHeight="1">
@@ -10928,7 +10928,7 @@
         </is>
       </c>
       <c r="E396" s="20" t="n">
-        <v>216</v>
+        <v>236</v>
       </c>
     </row>
     <row r="397" ht="20" customHeight="1">
@@ -10953,7 +10953,7 @@
         </is>
       </c>
       <c r="E397" s="23" t="n">
-        <v>123</v>
+        <v>223</v>
       </c>
     </row>
     <row r="398" ht="20" customHeight="1">
@@ -10978,7 +10978,7 @@
         </is>
       </c>
       <c r="E398" s="20" t="n">
-        <v>189</v>
+        <v>216</v>
       </c>
     </row>
     <row r="399" ht="20" customHeight="1">
@@ -11003,7 +11003,7 @@
         </is>
       </c>
       <c r="E399" s="23" t="n">
-        <v>122</v>
+        <v>207</v>
       </c>
     </row>
     <row r="400" ht="20" customHeight="1">
@@ -11028,7 +11028,7 @@
         </is>
       </c>
       <c r="E400" s="20" t="n">
-        <v>205</v>
+        <v>141</v>
       </c>
     </row>
     <row r="401" ht="20" customHeight="1">
@@ -11053,7 +11053,7 @@
         </is>
       </c>
       <c r="E401" s="23" t="n">
-        <v>110</v>
+        <v>233</v>
       </c>
     </row>
     <row r="402" ht="20" customHeight="1">
@@ -11078,7 +11078,7 @@
         </is>
       </c>
       <c r="E402" s="20" t="n">
-        <v>111</v>
+        <v>223</v>
       </c>
     </row>
     <row r="403" ht="20" customHeight="1">
@@ -11103,7 +11103,7 @@
         </is>
       </c>
       <c r="E403" s="23" t="n">
-        <v>145</v>
+        <v>204</v>
       </c>
     </row>
     <row r="404" ht="20" customHeight="1">
@@ -11128,7 +11128,7 @@
         </is>
       </c>
       <c r="E404" s="20" t="n">
-        <v>161</v>
+        <v>200</v>
       </c>
     </row>
     <row r="405" ht="20" customHeight="1">
@@ -11153,7 +11153,7 @@
         </is>
       </c>
       <c r="E405" s="23" t="n">
-        <v>197</v>
+        <v>169</v>
       </c>
     </row>
     <row r="406" ht="20" customHeight="1">
@@ -11178,7 +11178,7 @@
         </is>
       </c>
       <c r="E406" s="20" t="n">
-        <v>218</v>
+        <v>235</v>
       </c>
     </row>
     <row r="407" ht="20" customHeight="1">
@@ -11203,7 +11203,7 @@
         </is>
       </c>
       <c r="E407" s="23" t="n">
-        <v>121</v>
+        <v>173</v>
       </c>
     </row>
     <row r="408" ht="20" customHeight="1">
@@ -11228,7 +11228,7 @@
         </is>
       </c>
       <c r="E408" s="20" t="n">
-        <v>203</v>
+        <v>127</v>
       </c>
     </row>
     <row r="409" ht="20" customHeight="1">
@@ -11253,7 +11253,7 @@
         </is>
       </c>
       <c r="E409" s="23" t="n">
-        <v>157</v>
+        <v>177</v>
       </c>
     </row>
     <row r="410" ht="20" customHeight="1">
@@ -11278,7 +11278,7 @@
         </is>
       </c>
       <c r="E410" s="20" t="n">
-        <v>169</v>
+        <v>238</v>
       </c>
     </row>
     <row r="411" ht="20" customHeight="1">
@@ -11303,7 +11303,7 @@
         </is>
       </c>
       <c r="E411" s="23" t="n">
-        <v>113</v>
+        <v>205</v>
       </c>
     </row>
     <row r="412" ht="20" customHeight="1">
@@ -11328,7 +11328,7 @@
         </is>
       </c>
       <c r="E412" s="20" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="413" ht="20" customHeight="1">
@@ -11353,7 +11353,7 @@
         </is>
       </c>
       <c r="E413" s="23" t="n">
-        <v>140</v>
+        <v>229</v>
       </c>
     </row>
     <row r="414" ht="20" customHeight="1">
@@ -11378,7 +11378,7 @@
         </is>
       </c>
       <c r="E414" s="20" t="n">
-        <v>192</v>
+        <v>237</v>
       </c>
     </row>
     <row r="415" ht="20" customHeight="1">
@@ -11403,7 +11403,7 @@
         </is>
       </c>
       <c r="E415" s="23" t="n">
-        <v>226</v>
+        <v>149</v>
       </c>
     </row>
     <row r="416" ht="20" customHeight="1">
@@ -11428,7 +11428,7 @@
         </is>
       </c>
       <c r="E416" s="20" t="n">
-        <v>198</v>
+        <v>173</v>
       </c>
     </row>
     <row r="417" ht="20" customHeight="1">
@@ -11453,7 +11453,7 @@
         </is>
       </c>
       <c r="E417" s="23" t="n">
-        <v>152</v>
+        <v>182</v>
       </c>
     </row>
     <row r="418" ht="20" customHeight="1">
@@ -11478,7 +11478,7 @@
         </is>
       </c>
       <c r="E418" s="20" t="n">
-        <v>219</v>
+        <v>185</v>
       </c>
     </row>
     <row r="419" ht="20" customHeight="1">
@@ -11503,7 +11503,7 @@
         </is>
       </c>
       <c r="E419" s="23" t="n">
-        <v>192</v>
+        <v>235</v>
       </c>
     </row>
     <row r="420" ht="20" customHeight="1">
@@ -11528,7 +11528,7 @@
         </is>
       </c>
       <c r="E420" s="20" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
     </row>
     <row r="421" ht="20" customHeight="1">
@@ -11553,7 +11553,7 @@
         </is>
       </c>
       <c r="E421" s="23" t="n">
-        <v>195</v>
+        <v>148</v>
       </c>
     </row>
     <row r="422" ht="20" customHeight="1">
@@ -11578,7 +11578,7 @@
         </is>
       </c>
       <c r="E422" s="20" t="n">
-        <v>166</v>
+        <v>152</v>
       </c>
     </row>
     <row r="423" ht="20" customHeight="1">
@@ -11603,7 +11603,7 @@
         </is>
       </c>
       <c r="E423" s="23" t="n">
-        <v>112</v>
+        <v>227</v>
       </c>
     </row>
     <row r="424" ht="20" customHeight="1">
@@ -11628,7 +11628,7 @@
         </is>
       </c>
       <c r="E424" s="20" t="n">
-        <v>179</v>
+        <v>190</v>
       </c>
     </row>
     <row r="425" ht="20" customHeight="1">
@@ -11653,7 +11653,7 @@
         </is>
       </c>
       <c r="E425" s="23" t="n">
-        <v>195</v>
+        <v>173</v>
       </c>
     </row>
     <row r="426" ht="20" customHeight="1">
@@ -11678,7 +11678,7 @@
         </is>
       </c>
       <c r="E426" s="20" t="n">
-        <v>158</v>
+        <v>192</v>
       </c>
     </row>
     <row r="427" ht="20" customHeight="1">
@@ -11703,7 +11703,7 @@
         </is>
       </c>
       <c r="E427" s="23" t="n">
-        <v>160</v>
+        <v>137</v>
       </c>
     </row>
     <row r="428" ht="20" customHeight="1">
@@ -11728,7 +11728,7 @@
         </is>
       </c>
       <c r="E428" s="20" t="n">
-        <v>174</v>
+        <v>181</v>
       </c>
     </row>
     <row r="429" ht="20" customHeight="1">
@@ -11753,7 +11753,7 @@
         </is>
       </c>
       <c r="E429" s="23" t="n">
-        <v>125</v>
+        <v>204</v>
       </c>
     </row>
     <row r="430" ht="20" customHeight="1">
@@ -11778,7 +11778,7 @@
         </is>
       </c>
       <c r="E430" s="20" t="n">
-        <v>173</v>
+        <v>190</v>
       </c>
     </row>
     <row r="431" ht="20" customHeight="1">
@@ -11803,7 +11803,7 @@
         </is>
       </c>
       <c r="E431" s="23" t="n">
-        <v>142</v>
+        <v>166</v>
       </c>
     </row>
     <row r="432" ht="20" customHeight="1">
@@ -11828,7 +11828,7 @@
         </is>
       </c>
       <c r="E432" s="20" t="n">
-        <v>188</v>
+        <v>227</v>
       </c>
     </row>
     <row r="433" ht="20" customHeight="1">
@@ -11853,7 +11853,7 @@
         </is>
       </c>
       <c r="E433" s="23" t="n">
-        <v>206</v>
+        <v>181</v>
       </c>
     </row>
     <row r="434" ht="20" customHeight="1">
@@ -11878,7 +11878,7 @@
         </is>
       </c>
       <c r="E434" s="20" t="n">
-        <v>220</v>
+        <v>203</v>
       </c>
     </row>
     <row r="435" ht="20" customHeight="1">
@@ -11903,7 +11903,7 @@
         </is>
       </c>
       <c r="E435" s="23" t="n">
-        <v>114</v>
+        <v>220</v>
       </c>
     </row>
     <row r="436" ht="20" customHeight="1">
@@ -11928,7 +11928,7 @@
         </is>
       </c>
       <c r="E436" s="20" t="n">
-        <v>226</v>
+        <v>173</v>
       </c>
     </row>
     <row r="437" ht="20" customHeight="1">
@@ -11953,7 +11953,7 @@
         </is>
       </c>
       <c r="E437" s="23" t="n">
-        <v>185</v>
+        <v>213</v>
       </c>
     </row>
     <row r="438" ht="20" customHeight="1">
@@ -11978,7 +11978,7 @@
         </is>
       </c>
       <c r="E438" s="20" t="n">
-        <v>182</v>
+        <v>158</v>
       </c>
     </row>
     <row r="439" ht="20" customHeight="1">
@@ -12003,7 +12003,7 @@
         </is>
       </c>
       <c r="E439" s="23" t="n">
-        <v>190</v>
+        <v>159</v>
       </c>
     </row>
     <row r="440" ht="20" customHeight="1">
@@ -12028,7 +12028,7 @@
         </is>
       </c>
       <c r="E440" s="20" t="n">
-        <v>199</v>
+        <v>193</v>
       </c>
     </row>
     <row r="441" ht="20" customHeight="1">
@@ -12053,7 +12053,7 @@
         </is>
       </c>
       <c r="E441" s="23" t="n">
-        <v>206</v>
+        <v>111</v>
       </c>
     </row>
     <row r="442" ht="20" customHeight="1">
@@ -12078,7 +12078,7 @@
         </is>
       </c>
       <c r="E442" s="20" t="n">
-        <v>193</v>
+        <v>167</v>
       </c>
     </row>
     <row r="443" ht="20" customHeight="1">
@@ -12103,7 +12103,7 @@
         </is>
       </c>
       <c r="E443" s="23" t="n">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="444" ht="20" customHeight="1">
@@ -12128,7 +12128,7 @@
         </is>
       </c>
       <c r="E444" s="20" t="n">
-        <v>164</v>
+        <v>129</v>
       </c>
     </row>
     <row r="445" ht="20" customHeight="1">
@@ -12153,7 +12153,7 @@
         </is>
       </c>
       <c r="E445" s="23" t="n">
-        <v>148</v>
+        <v>161</v>
       </c>
     </row>
     <row r="446" ht="20" customHeight="1">
@@ -12178,7 +12178,7 @@
         </is>
       </c>
       <c r="E446" s="20" t="n">
-        <v>228</v>
+        <v>172</v>
       </c>
     </row>
     <row r="447" ht="20" customHeight="1">
@@ -12203,7 +12203,7 @@
         </is>
       </c>
       <c r="E447" s="23" t="n">
-        <v>112</v>
+        <v>198</v>
       </c>
     </row>
     <row r="448" ht="20" customHeight="1">
@@ -12228,7 +12228,7 @@
         </is>
       </c>
       <c r="E448" s="20" t="n">
-        <v>114</v>
+        <v>193</v>
       </c>
     </row>
     <row r="449" ht="20" customHeight="1">
@@ -12253,7 +12253,7 @@
         </is>
       </c>
       <c r="E449" s="23" t="n">
-        <v>202</v>
+        <v>211</v>
       </c>
     </row>
     <row r="450" ht="20" customHeight="1">
@@ -12278,7 +12278,7 @@
         </is>
       </c>
       <c r="E450" s="20" t="n">
-        <v>194</v>
+        <v>199</v>
       </c>
     </row>
     <row r="451" ht="20" customHeight="1">
@@ -12303,7 +12303,7 @@
         </is>
       </c>
       <c r="E451" s="23" t="n">
-        <v>213</v>
+        <v>174</v>
       </c>
     </row>
     <row r="452" ht="20" customHeight="1">
@@ -12328,7 +12328,7 @@
         </is>
       </c>
       <c r="E452" s="20" t="n">
-        <v>155</v>
+        <v>210</v>
       </c>
     </row>
     <row r="453" ht="20" customHeight="1">
@@ -12353,7 +12353,7 @@
         </is>
       </c>
       <c r="E453" s="23" t="n">
-        <v>168</v>
+        <v>132</v>
       </c>
     </row>
     <row r="454" ht="20" customHeight="1">
@@ -12378,7 +12378,7 @@
         </is>
       </c>
       <c r="E454" s="20" t="n">
-        <v>240</v>
+        <v>134</v>
       </c>
     </row>
     <row r="455" ht="20" customHeight="1">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="E455" s="23" t="n">
-        <v>175</v>
+        <v>133</v>
       </c>
     </row>
     <row r="456" ht="20" customHeight="1">
@@ -12428,7 +12428,7 @@
         </is>
       </c>
       <c r="E456" s="20" t="n">
-        <v>134</v>
+        <v>145</v>
       </c>
     </row>
     <row r="457" ht="20" customHeight="1">
@@ -12453,7 +12453,7 @@
         </is>
       </c>
       <c r="E457" s="23" t="n">
-        <v>180</v>
+        <v>136</v>
       </c>
     </row>
     <row r="458" ht="20" customHeight="1">
@@ -12478,7 +12478,7 @@
         </is>
       </c>
       <c r="E458" s="20" t="n">
-        <v>205</v>
+        <v>219</v>
       </c>
     </row>
     <row r="459" ht="20" customHeight="1">
@@ -12503,7 +12503,7 @@
         </is>
       </c>
       <c r="E459" s="23" t="n">
-        <v>181</v>
+        <v>210</v>
       </c>
     </row>
     <row r="460" ht="20" customHeight="1">
@@ -12528,7 +12528,7 @@
         </is>
       </c>
       <c r="E460" s="20" t="n">
-        <v>128</v>
+        <v>147</v>
       </c>
     </row>
     <row r="461" ht="20" customHeight="1">
@@ -12553,7 +12553,7 @@
         </is>
       </c>
       <c r="E461" s="23" t="n">
-        <v>154</v>
+        <v>137</v>
       </c>
     </row>
     <row r="462" ht="20" customHeight="1">
@@ -12578,7 +12578,7 @@
         </is>
       </c>
       <c r="E462" s="20" t="n">
-        <v>138</v>
+        <v>178</v>
       </c>
     </row>
     <row r="463" ht="20" customHeight="1">
@@ -12603,7 +12603,7 @@
         </is>
       </c>
       <c r="E463" s="23" t="n">
-        <v>220</v>
+        <v>196</v>
       </c>
     </row>
     <row r="464" ht="20" customHeight="1">
@@ -12628,7 +12628,7 @@
         </is>
       </c>
       <c r="E464" s="20" t="n">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
     <row r="465" ht="20" customHeight="1">
@@ -12653,7 +12653,7 @@
         </is>
       </c>
       <c r="E465" s="23" t="n">
-        <v>135</v>
+        <v>228</v>
       </c>
     </row>
     <row r="466" ht="20" customHeight="1">
@@ -12678,7 +12678,7 @@
         </is>
       </c>
       <c r="E466" s="20" t="n">
-        <v>131</v>
+        <v>150</v>
       </c>
     </row>
     <row r="467" ht="20" customHeight="1">
@@ -12703,7 +12703,7 @@
         </is>
       </c>
       <c r="E467" s="23" t="n">
-        <v>187</v>
+        <v>167</v>
       </c>
     </row>
     <row r="468" ht="20" customHeight="1">
@@ -12728,7 +12728,7 @@
         </is>
       </c>
       <c r="E468" s="20" t="n">
-        <v>123</v>
+        <v>111</v>
       </c>
     </row>
     <row r="469" ht="20" customHeight="1">
@@ -12753,7 +12753,7 @@
         </is>
       </c>
       <c r="E469" s="23" t="n">
-        <v>188</v>
+        <v>123</v>
       </c>
     </row>
     <row r="470" ht="20" customHeight="1">
@@ -12778,7 +12778,7 @@
         </is>
       </c>
       <c r="E470" s="20" t="n">
-        <v>179</v>
+        <v>231</v>
       </c>
     </row>
     <row r="471" ht="20" customHeight="1">
@@ -12803,7 +12803,7 @@
         </is>
       </c>
       <c r="E471" s="23" t="n">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="472" ht="20" customHeight="1">
@@ -12828,7 +12828,7 @@
         </is>
       </c>
       <c r="E472" s="20" t="n">
-        <v>111</v>
+        <v>219</v>
       </c>
     </row>
     <row r="473" ht="20" customHeight="1">
@@ -12853,7 +12853,7 @@
         </is>
       </c>
       <c r="E473" s="23" t="n">
-        <v>138</v>
+        <v>185</v>
       </c>
     </row>
     <row r="474" ht="20" customHeight="1">
@@ -12878,7 +12878,7 @@
         </is>
       </c>
       <c r="E474" s="20" t="n">
-        <v>199</v>
+        <v>147</v>
       </c>
     </row>
     <row r="475" ht="20" customHeight="1">
@@ -12903,7 +12903,7 @@
         </is>
       </c>
       <c r="E475" s="23" t="n">
-        <v>142</v>
+        <v>231</v>
       </c>
     </row>
     <row r="476" ht="20" customHeight="1">
@@ -12928,7 +12928,7 @@
         </is>
       </c>
       <c r="E476" s="20" t="n">
-        <v>213</v>
+        <v>195</v>
       </c>
     </row>
     <row r="477" ht="20" customHeight="1">
@@ -12953,7 +12953,7 @@
         </is>
       </c>
       <c r="E477" s="23" t="n">
-        <v>154</v>
+        <v>202</v>
       </c>
     </row>
     <row r="478" ht="20" customHeight="1">
@@ -12978,7 +12978,7 @@
         </is>
       </c>
       <c r="E478" s="20" t="n">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="479" ht="20" customHeight="1">
@@ -13003,7 +13003,7 @@
         </is>
       </c>
       <c r="E479" s="23" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
     </row>
     <row r="480" ht="20" customHeight="1">
@@ -13028,7 +13028,7 @@
         </is>
       </c>
       <c r="E480" s="20" t="n">
-        <v>211</v>
+        <v>217</v>
       </c>
     </row>
     <row r="481" ht="20" customHeight="1">
@@ -13053,7 +13053,7 @@
         </is>
       </c>
       <c r="E481" s="23" t="n">
-        <v>193</v>
+        <v>218</v>
       </c>
     </row>
     <row r="482" ht="20" customHeight="1">
@@ -13078,7 +13078,7 @@
         </is>
       </c>
       <c r="E482" s="20" t="n">
-        <v>211</v>
+        <v>235</v>
       </c>
     </row>
     <row r="483" ht="20" customHeight="1">
@@ -13103,7 +13103,7 @@
         </is>
       </c>
       <c r="E483" s="23" t="n">
-        <v>231</v>
+        <v>117</v>
       </c>
     </row>
     <row r="484" ht="20" customHeight="1">
@@ -13128,7 +13128,7 @@
         </is>
       </c>
       <c r="E484" s="20" t="n">
-        <v>130</v>
+        <v>211</v>
       </c>
     </row>
     <row r="485" ht="20" customHeight="1">
@@ -13153,7 +13153,7 @@
         </is>
       </c>
       <c r="E485" s="23" t="n">
-        <v>181</v>
+        <v>196</v>
       </c>
     </row>
     <row r="486" ht="20" customHeight="1">
@@ -13178,7 +13178,7 @@
         </is>
       </c>
       <c r="E486" s="20" t="n">
-        <v>166</v>
+        <v>124</v>
       </c>
     </row>
     <row r="487" ht="20" customHeight="1">
@@ -13203,7 +13203,7 @@
         </is>
       </c>
       <c r="E487" s="23" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="488" ht="20" customHeight="1">
@@ -13228,7 +13228,7 @@
         </is>
       </c>
       <c r="E488" s="20" t="n">
-        <v>228</v>
+        <v>160</v>
       </c>
     </row>
     <row r="489" ht="20" customHeight="1">
@@ -13253,7 +13253,7 @@
         </is>
       </c>
       <c r="E489" s="23" t="n">
-        <v>168</v>
+        <v>197</v>
       </c>
     </row>
     <row r="490" ht="20" customHeight="1">
@@ -13278,7 +13278,7 @@
         </is>
       </c>
       <c r="E490" s="20" t="n">
-        <v>200</v>
+        <v>222</v>
       </c>
     </row>
     <row r="491" ht="20" customHeight="1">
@@ -13303,7 +13303,7 @@
         </is>
       </c>
       <c r="E491" s="23" t="n">
-        <v>149</v>
+        <v>236</v>
       </c>
     </row>
     <row r="492" ht="20" customHeight="1">
@@ -13328,7 +13328,7 @@
         </is>
       </c>
       <c r="E492" s="20" t="n">
-        <v>158</v>
+        <v>189</v>
       </c>
     </row>
     <row r="493" ht="20" customHeight="1">
@@ -13353,7 +13353,7 @@
         </is>
       </c>
       <c r="E493" s="23" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="494" ht="20" customHeight="1">
@@ -13378,7 +13378,7 @@
         </is>
       </c>
       <c r="E494" s="20" t="n">
-        <v>237</v>
+        <v>217</v>
       </c>
     </row>
     <row r="495" ht="20" customHeight="1">
@@ -13403,7 +13403,7 @@
         </is>
       </c>
       <c r="E495" s="23" t="n">
-        <v>173</v>
+        <v>157</v>
       </c>
     </row>
     <row r="496" ht="20" customHeight="1">
@@ -13428,7 +13428,7 @@
         </is>
       </c>
       <c r="E496" s="20" t="n">
-        <v>203</v>
+        <v>162</v>
       </c>
     </row>
     <row r="497" ht="20" customHeight="1">
@@ -13453,7 +13453,7 @@
         </is>
       </c>
       <c r="E497" s="23" t="n">
-        <v>203</v>
+        <v>144</v>
       </c>
     </row>
     <row r="498" ht="20" customHeight="1">
@@ -13478,7 +13478,7 @@
         </is>
       </c>
       <c r="E498" s="20" t="n">
-        <v>144</v>
+        <v>184</v>
       </c>
     </row>
     <row r="499" ht="20" customHeight="1">
@@ -13503,7 +13503,7 @@
         </is>
       </c>
       <c r="E499" s="23" t="n">
-        <v>200</v>
+        <v>217</v>
       </c>
     </row>
     <row r="500" ht="20" customHeight="1">
@@ -13528,7 +13528,7 @@
         </is>
       </c>
       <c r="E500" s="20" t="n">
-        <v>133</v>
+        <v>141</v>
       </c>
     </row>
     <row r="501" ht="20" customHeight="1">
@@ -13553,7 +13553,7 @@
         </is>
       </c>
       <c r="E501" s="23" t="n">
-        <v>111</v>
+        <v>183</v>
       </c>
     </row>
     <row r="502" ht="20" customHeight="1">
@@ -13578,7 +13578,7 @@
         </is>
       </c>
       <c r="E502" s="20" t="n">
-        <v>234</v>
+        <v>119</v>
       </c>
     </row>
     <row r="503" ht="20" customHeight="1">
@@ -13603,7 +13603,7 @@
         </is>
       </c>
       <c r="E503" s="23" t="n">
-        <v>236</v>
+        <v>137</v>
       </c>
     </row>
     <row r="504" ht="20" customHeight="1">
@@ -13628,7 +13628,7 @@
         </is>
       </c>
       <c r="E504" s="20" t="n">
-        <v>239</v>
+        <v>149</v>
       </c>
     </row>
     <row r="505" ht="20" customHeight="1">
@@ -13653,7 +13653,7 @@
         </is>
       </c>
       <c r="E505" s="23" t="n">
-        <v>116</v>
+        <v>126</v>
       </c>
     </row>
     <row r="506" ht="20" customHeight="1">
@@ -13678,7 +13678,7 @@
         </is>
       </c>
       <c r="E506" s="20" t="n">
-        <v>230</v>
+        <v>174</v>
       </c>
     </row>
     <row r="507" ht="20" customHeight="1">
@@ -13703,7 +13703,7 @@
         </is>
       </c>
       <c r="E507" s="23" t="n">
-        <v>179</v>
+        <v>150</v>
       </c>
     </row>
     <row r="508" ht="20" customHeight="1">
@@ -13728,7 +13728,7 @@
         </is>
       </c>
       <c r="E508" s="20" t="n">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="509" ht="20" customHeight="1">
@@ -13753,7 +13753,7 @@
         </is>
       </c>
       <c r="E509" s="23" t="n">
-        <v>114</v>
+        <v>126</v>
       </c>
     </row>
     <row r="510" ht="20" customHeight="1">
@@ -13803,7 +13803,7 @@
         </is>
       </c>
       <c r="E511" s="23" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="512" ht="20" customHeight="1">
@@ -13828,7 +13828,7 @@
         </is>
       </c>
       <c r="E512" s="20" t="n">
-        <v>146</v>
+        <v>200</v>
       </c>
     </row>
     <row r="513" ht="20" customHeight="1">
@@ -13853,7 +13853,7 @@
         </is>
       </c>
       <c r="E513" s="23" t="n">
-        <v>155</v>
+        <v>164</v>
       </c>
     </row>
     <row r="514" ht="20" customHeight="1">
@@ -13878,7 +13878,7 @@
         </is>
       </c>
       <c r="E514" s="20" t="n">
-        <v>128</v>
+        <v>221</v>
       </c>
     </row>
     <row r="515" ht="20" customHeight="1">
@@ -13903,7 +13903,7 @@
         </is>
       </c>
       <c r="E515" s="23" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="516" ht="20" customHeight="1">
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="E516" s="20" t="n">
-        <v>132</v>
+        <v>205</v>
       </c>
     </row>
     <row r="517" ht="20" customHeight="1">
@@ -13953,7 +13953,7 @@
         </is>
       </c>
       <c r="E517" s="23" t="n">
-        <v>196</v>
+        <v>149</v>
       </c>
     </row>
     <row r="518" ht="20" customHeight="1">
@@ -13978,7 +13978,7 @@
         </is>
       </c>
       <c r="E518" s="20" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="519" ht="20" customHeight="1">
@@ -14003,7 +14003,7 @@
         </is>
       </c>
       <c r="E519" s="23" t="n">
-        <v>240</v>
+        <v>123</v>
       </c>
     </row>
     <row r="520" ht="20" customHeight="1">
@@ -14028,7 +14028,7 @@
         </is>
       </c>
       <c r="E520" s="20" t="n">
-        <v>122</v>
+        <v>235</v>
       </c>
     </row>
     <row r="521" ht="20" customHeight="1">
@@ -14053,7 +14053,7 @@
         </is>
       </c>
       <c r="E521" s="23" t="n">
-        <v>119</v>
+        <v>155</v>
       </c>
     </row>
     <row r="522" ht="20" customHeight="1">
@@ -14078,7 +14078,7 @@
         </is>
       </c>
       <c r="E522" s="20" t="n">
-        <v>115</v>
+        <v>229</v>
       </c>
     </row>
     <row r="523" ht="20" customHeight="1">
@@ -14103,7 +14103,7 @@
         </is>
       </c>
       <c r="E523" s="23" t="n">
-        <v>237</v>
+        <v>145</v>
       </c>
     </row>
     <row r="524" ht="20" customHeight="1">
@@ -14128,7 +14128,7 @@
         </is>
       </c>
       <c r="E524" s="20" t="n">
-        <v>148</v>
+        <v>194</v>
       </c>
     </row>
     <row r="525" ht="20" customHeight="1">
@@ -14153,7 +14153,7 @@
         </is>
       </c>
       <c r="E525" s="23" t="n">
-        <v>179</v>
+        <v>137</v>
       </c>
     </row>
     <row r="526" ht="20" customHeight="1">
@@ -14178,7 +14178,7 @@
         </is>
       </c>
       <c r="E526" s="20" t="n">
-        <v>164</v>
+        <v>141</v>
       </c>
     </row>
     <row r="527" ht="20" customHeight="1">
@@ -14203,7 +14203,7 @@
         </is>
       </c>
       <c r="E527" s="23" t="n">
-        <v>218</v>
+        <v>161</v>
       </c>
     </row>
     <row r="528" ht="20" customHeight="1">
@@ -14228,7 +14228,7 @@
         </is>
       </c>
       <c r="E528" s="20" t="n">
-        <v>232</v>
+        <v>189</v>
       </c>
     </row>
     <row r="529" ht="20" customHeight="1">
@@ -14253,7 +14253,7 @@
         </is>
       </c>
       <c r="E529" s="23" t="n">
-        <v>187</v>
+        <v>215</v>
       </c>
     </row>
     <row r="530" ht="20" customHeight="1">
@@ -14278,7 +14278,7 @@
         </is>
       </c>
       <c r="E530" s="20" t="n">
-        <v>158</v>
+        <v>236</v>
       </c>
     </row>
     <row r="531" ht="20" customHeight="1">
@@ -14303,7 +14303,7 @@
         </is>
       </c>
       <c r="E531" s="23" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="532" ht="20" customHeight="1">
@@ -14328,7 +14328,7 @@
         </is>
       </c>
       <c r="E532" s="20" t="n">
-        <v>173</v>
+        <v>146</v>
       </c>
     </row>
     <row r="533" ht="20" customHeight="1">
@@ -14353,7 +14353,7 @@
         </is>
       </c>
       <c r="E533" s="23" t="n">
-        <v>232</v>
+        <v>138</v>
       </c>
     </row>
     <row r="534" ht="20" customHeight="1">
@@ -14378,7 +14378,7 @@
         </is>
       </c>
       <c r="E534" s="20" t="n">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="535" ht="20" customHeight="1">
@@ -14403,7 +14403,7 @@
         </is>
       </c>
       <c r="E535" s="23" t="n">
-        <v>175</v>
+        <v>227</v>
       </c>
     </row>
     <row r="536" ht="20" customHeight="1">
@@ -14428,7 +14428,7 @@
         </is>
       </c>
       <c r="E536" s="20" t="n">
-        <v>132</v>
+        <v>199</v>
       </c>
     </row>
     <row r="537" ht="20" customHeight="1">
@@ -14453,7 +14453,7 @@
         </is>
       </c>
       <c r="E537" s="23" t="n">
-        <v>178</v>
+        <v>202</v>
       </c>
     </row>
     <row r="538" ht="20" customHeight="1">
@@ -14478,7 +14478,7 @@
         </is>
       </c>
       <c r="E538" s="20" t="n">
-        <v>222</v>
+        <v>236</v>
       </c>
     </row>
     <row r="539" ht="20" customHeight="1">
@@ -14503,7 +14503,7 @@
         </is>
       </c>
       <c r="E539" s="23" t="n">
-        <v>196</v>
+        <v>217</v>
       </c>
     </row>
     <row r="540" ht="20" customHeight="1">
@@ -14528,7 +14528,7 @@
         </is>
       </c>
       <c r="E540" s="20" t="n">
-        <v>116</v>
+        <v>210</v>
       </c>
     </row>
     <row r="541" ht="20" customHeight="1">
@@ -14553,7 +14553,7 @@
         </is>
       </c>
       <c r="E541" s="23" t="n">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="542" ht="20" customHeight="1">
@@ -14578,7 +14578,7 @@
         </is>
       </c>
       <c r="E542" s="20" t="n">
-        <v>222</v>
+        <v>197</v>
       </c>
     </row>
     <row r="543" ht="20" customHeight="1">
@@ -14603,7 +14603,7 @@
         </is>
       </c>
       <c r="E543" s="23" t="n">
-        <v>126</v>
+        <v>183</v>
       </c>
     </row>
     <row r="544" ht="20" customHeight="1">
@@ -14628,7 +14628,7 @@
         </is>
       </c>
       <c r="E544" s="20" t="n">
-        <v>170</v>
+        <v>123</v>
       </c>
     </row>
     <row r="545" ht="20" customHeight="1">
@@ -14653,7 +14653,7 @@
         </is>
       </c>
       <c r="E545" s="23" t="n">
-        <v>197</v>
+        <v>221</v>
       </c>
     </row>
     <row r="546" ht="20" customHeight="1">
@@ -14678,7 +14678,7 @@
         </is>
       </c>
       <c r="E546" s="20" t="n">
-        <v>159</v>
+        <v>231</v>
       </c>
     </row>
     <row r="547" ht="20" customHeight="1">
@@ -14703,7 +14703,7 @@
         </is>
       </c>
       <c r="E547" s="23" t="n">
-        <v>165</v>
+        <v>118</v>
       </c>
     </row>
     <row r="548" ht="20" customHeight="1">
@@ -14728,7 +14728,7 @@
         </is>
       </c>
       <c r="E548" s="20" t="n">
-        <v>230</v>
+        <v>234</v>
       </c>
     </row>
     <row r="549" ht="20" customHeight="1">
@@ -14753,7 +14753,7 @@
         </is>
       </c>
       <c r="E549" s="23" t="n">
-        <v>132</v>
+        <v>197</v>
       </c>
     </row>
     <row r="550" ht="20" customHeight="1">
@@ -14778,7 +14778,7 @@
         </is>
       </c>
       <c r="E550" s="20" t="n">
-        <v>127</v>
+        <v>227</v>
       </c>
     </row>
     <row r="551" ht="20" customHeight="1">
@@ -14803,7 +14803,7 @@
         </is>
       </c>
       <c r="E551" s="23" t="n">
-        <v>217</v>
+        <v>202</v>
       </c>
     </row>
     <row r="552" ht="20" customHeight="1">
@@ -14828,7 +14828,7 @@
         </is>
       </c>
       <c r="E552" s="20" t="n">
-        <v>167</v>
+        <v>215</v>
       </c>
     </row>
     <row r="553" ht="20" customHeight="1">
@@ -14853,7 +14853,7 @@
         </is>
       </c>
       <c r="E553" s="23" t="n">
-        <v>173</v>
+        <v>151</v>
       </c>
     </row>
     <row r="554" ht="20" customHeight="1">
@@ -14878,7 +14878,7 @@
         </is>
       </c>
       <c r="E554" s="20" t="n">
-        <v>240</v>
+        <v>152</v>
       </c>
     </row>
     <row r="555" ht="20" customHeight="1">
@@ -14903,7 +14903,7 @@
         </is>
       </c>
       <c r="E555" s="23" t="n">
-        <v>181</v>
+        <v>163</v>
       </c>
     </row>
     <row r="556" ht="20" customHeight="1">
@@ -14928,7 +14928,7 @@
         </is>
       </c>
       <c r="E556" s="20" t="n">
-        <v>167</v>
+        <v>177</v>
       </c>
     </row>
     <row r="557" ht="20" customHeight="1">
@@ -14953,7 +14953,7 @@
         </is>
       </c>
       <c r="E557" s="23" t="n">
-        <v>141</v>
+        <v>238</v>
       </c>
     </row>
     <row r="558" ht="20" customHeight="1">
@@ -14978,7 +14978,7 @@
         </is>
       </c>
       <c r="E558" s="20" t="n">
-        <v>234</v>
+        <v>228</v>
       </c>
     </row>
     <row r="559" ht="20" customHeight="1">
@@ -15003,7 +15003,7 @@
         </is>
       </c>
       <c r="E559" s="23" t="n">
-        <v>132</v>
+        <v>140</v>
       </c>
     </row>
     <row r="560" ht="20" customHeight="1">
@@ -15028,7 +15028,7 @@
         </is>
       </c>
       <c r="E560" s="20" t="n">
-        <v>189</v>
+        <v>196</v>
       </c>
     </row>
     <row r="561" ht="20" customHeight="1">
@@ -15053,7 +15053,7 @@
         </is>
       </c>
       <c r="E561" s="23" t="n">
-        <v>186</v>
+        <v>138</v>
       </c>
     </row>
     <row r="562" ht="20" customHeight="1">
@@ -15078,7 +15078,7 @@
         </is>
       </c>
       <c r="E562" s="20" t="n">
-        <v>203</v>
+        <v>122</v>
       </c>
     </row>
     <row r="563" ht="20" customHeight="1">
@@ -15103,7 +15103,7 @@
         </is>
       </c>
       <c r="E563" s="23" t="n">
-        <v>171</v>
+        <v>123</v>
       </c>
     </row>
     <row r="564" ht="20" customHeight="1">
@@ -15128,7 +15128,7 @@
         </is>
       </c>
       <c r="E564" s="20" t="n">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="565" ht="20" customHeight="1">
@@ -15153,7 +15153,7 @@
         </is>
       </c>
       <c r="E565" s="23" t="n">
-        <v>217</v>
+        <v>137</v>
       </c>
     </row>
     <row r="566" ht="20" customHeight="1">
@@ -15178,7 +15178,7 @@
         </is>
       </c>
       <c r="E566" s="20" t="n">
-        <v>233</v>
+        <v>190</v>
       </c>
     </row>
     <row r="567" ht="20" customHeight="1">
@@ -15203,7 +15203,7 @@
         </is>
       </c>
       <c r="E567" s="23" t="n">
-        <v>125</v>
+        <v>157</v>
       </c>
     </row>
     <row r="568" ht="20" customHeight="1">
@@ -15228,7 +15228,7 @@
         </is>
       </c>
       <c r="E568" s="20" t="n">
-        <v>132</v>
+        <v>189</v>
       </c>
     </row>
     <row r="569" ht="20" customHeight="1">
@@ -15253,7 +15253,7 @@
         </is>
       </c>
       <c r="E569" s="23" t="n">
-        <v>211</v>
+        <v>149</v>
       </c>
     </row>
     <row r="570" ht="20" customHeight="1">
@@ -15278,7 +15278,7 @@
         </is>
       </c>
       <c r="E570" s="20" t="n">
-        <v>152</v>
+        <v>222</v>
       </c>
     </row>
     <row r="571" ht="20" customHeight="1">
@@ -15303,7 +15303,7 @@
         </is>
       </c>
       <c r="E571" s="23" t="n">
-        <v>196</v>
+        <v>124</v>
       </c>
     </row>
     <row r="572" ht="20" customHeight="1">
@@ -15328,7 +15328,7 @@
         </is>
       </c>
       <c r="E572" s="20" t="n">
-        <v>233</v>
+        <v>134</v>
       </c>
     </row>
     <row r="573" ht="20" customHeight="1">
@@ -15353,7 +15353,7 @@
         </is>
       </c>
       <c r="E573" s="23" t="n">
-        <v>179</v>
+        <v>160</v>
       </c>
     </row>
     <row r="574" ht="20" customHeight="1">
@@ -15378,7 +15378,7 @@
         </is>
       </c>
       <c r="E574" s="20" t="n">
-        <v>239</v>
+        <v>148</v>
       </c>
     </row>
     <row r="575" ht="20" customHeight="1">
@@ -15403,7 +15403,7 @@
         </is>
       </c>
       <c r="E575" s="23" t="n">
-        <v>207</v>
+        <v>218</v>
       </c>
     </row>
     <row r="576" ht="20" customHeight="1">
@@ -15428,7 +15428,7 @@
         </is>
       </c>
       <c r="E576" s="20" t="n">
-        <v>195</v>
+        <v>125</v>
       </c>
     </row>
     <row r="577" ht="20" customHeight="1">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="E577" s="23" t="n">
-        <v>136</v>
+        <v>128</v>
       </c>
     </row>
     <row r="578" ht="20" customHeight="1">
@@ -15478,7 +15478,7 @@
         </is>
       </c>
       <c r="E578" s="20" t="n">
-        <v>122</v>
+        <v>138</v>
       </c>
     </row>
     <row r="579" ht="20" customHeight="1">
@@ -15503,7 +15503,7 @@
         </is>
       </c>
       <c r="E579" s="23" t="n">
-        <v>228</v>
+        <v>122</v>
       </c>
     </row>
     <row r="580" ht="20" customHeight="1">
@@ -15528,7 +15528,7 @@
         </is>
       </c>
       <c r="E580" s="20" t="n">
-        <v>138</v>
+        <v>189</v>
       </c>
     </row>
     <row r="581" ht="20" customHeight="1">
@@ -15553,7 +15553,7 @@
         </is>
       </c>
       <c r="E581" s="23" t="n">
-        <v>203</v>
+        <v>218</v>
       </c>
     </row>
     <row r="582" ht="20" customHeight="1">
@@ -15578,7 +15578,7 @@
         </is>
       </c>
       <c r="E582" s="20" t="n">
-        <v>231</v>
+        <v>190</v>
       </c>
     </row>
     <row r="583" ht="20" customHeight="1">
@@ -15603,7 +15603,7 @@
         </is>
       </c>
       <c r="E583" s="23" t="n">
-        <v>173</v>
+        <v>150</v>
       </c>
     </row>
     <row r="584" ht="20" customHeight="1">
@@ -15628,7 +15628,7 @@
         </is>
       </c>
       <c r="E584" s="20" t="n">
-        <v>154</v>
+        <v>180</v>
       </c>
     </row>
     <row r="585" ht="20" customHeight="1">
@@ -15653,7 +15653,7 @@
         </is>
       </c>
       <c r="E585" s="23" t="n">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="586" ht="20" customHeight="1">
@@ -15678,7 +15678,7 @@
         </is>
       </c>
       <c r="E586" s="20" t="n">
-        <v>161</v>
+        <v>154</v>
       </c>
     </row>
     <row r="587" ht="20" customHeight="1">
@@ -15703,7 +15703,7 @@
         </is>
       </c>
       <c r="E587" s="23" t="n">
-        <v>238</v>
+        <v>195</v>
       </c>
     </row>
     <row r="588" ht="20" customHeight="1">
@@ -15728,7 +15728,7 @@
         </is>
       </c>
       <c r="E588" s="20" t="n">
-        <v>196</v>
+        <v>145</v>
       </c>
     </row>
     <row r="589" ht="20" customHeight="1">
@@ -15753,7 +15753,7 @@
         </is>
       </c>
       <c r="E589" s="23" t="n">
-        <v>222</v>
+        <v>208</v>
       </c>
     </row>
     <row r="590" ht="20" customHeight="1">
@@ -15778,7 +15778,7 @@
         </is>
       </c>
       <c r="E590" s="20" t="n">
-        <v>157</v>
+        <v>132</v>
       </c>
     </row>
     <row r="591" ht="20" customHeight="1">
@@ -15803,7 +15803,7 @@
         </is>
       </c>
       <c r="E591" s="23" t="n">
-        <v>228</v>
+        <v>213</v>
       </c>
     </row>
     <row r="592" ht="20" customHeight="1">
@@ -15828,7 +15828,7 @@
         </is>
       </c>
       <c r="E592" s="20" t="n">
-        <v>189</v>
+        <v>229</v>
       </c>
     </row>
     <row r="593" ht="20" customHeight="1">
@@ -15853,7 +15853,7 @@
         </is>
       </c>
       <c r="E593" s="23" t="n">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="594" ht="20" customHeight="1">
@@ -15878,7 +15878,7 @@
         </is>
       </c>
       <c r="E594" s="20" t="n">
-        <v>215</v>
+        <v>165</v>
       </c>
     </row>
     <row r="595" ht="20" customHeight="1">
@@ -15903,7 +15903,7 @@
         </is>
       </c>
       <c r="E595" s="23" t="n">
-        <v>212</v>
+        <v>121</v>
       </c>
     </row>
     <row r="596" ht="20" customHeight="1">
@@ -15928,7 +15928,7 @@
         </is>
       </c>
       <c r="E596" s="20" t="n">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="597" ht="20" customHeight="1">
@@ -15953,7 +15953,7 @@
         </is>
       </c>
       <c r="E597" s="23" t="n">
-        <v>187</v>
+        <v>229</v>
       </c>
     </row>
     <row r="598" ht="20" customHeight="1">
@@ -15978,7 +15978,7 @@
         </is>
       </c>
       <c r="E598" s="20" t="n">
-        <v>121</v>
+        <v>169</v>
       </c>
     </row>
     <row r="599" ht="20" customHeight="1">
@@ -16003,7 +16003,7 @@
         </is>
       </c>
       <c r="E599" s="23" t="n">
-        <v>211</v>
+        <v>113</v>
       </c>
     </row>
     <row r="600" ht="20" customHeight="1">
@@ -16028,7 +16028,7 @@
         </is>
       </c>
       <c r="E600" s="20" t="n">
-        <v>132</v>
+        <v>184</v>
       </c>
     </row>
     <row r="601" ht="20" customHeight="1">
@@ -16053,7 +16053,7 @@
         </is>
       </c>
       <c r="E601" s="23" t="n">
-        <v>122</v>
+        <v>224</v>
       </c>
     </row>
     <row r="602" ht="20" customHeight="1">
@@ -16078,7 +16078,7 @@
         </is>
       </c>
       <c r="E602" s="20" t="n">
-        <v>188</v>
+        <v>228</v>
       </c>
     </row>
     <row r="603" ht="20" customHeight="1">
@@ -16103,7 +16103,7 @@
         </is>
       </c>
       <c r="E603" s="23" t="n">
-        <v>190</v>
+        <v>153</v>
       </c>
     </row>
     <row r="604" ht="20" customHeight="1">
@@ -16128,7 +16128,7 @@
         </is>
       </c>
       <c r="E604" s="20" t="n">
-        <v>150</v>
+        <v>184</v>
       </c>
     </row>
     <row r="605" ht="20" customHeight="1">
@@ -16153,7 +16153,7 @@
         </is>
       </c>
       <c r="E605" s="23" t="n">
-        <v>228</v>
+        <v>240</v>
       </c>
     </row>
     <row r="606" ht="20" customHeight="1">
@@ -16178,7 +16178,7 @@
         </is>
       </c>
       <c r="E606" s="20" t="n">
-        <v>158</v>
+        <v>200</v>
       </c>
     </row>
     <row r="607" ht="20" customHeight="1">
@@ -16203,7 +16203,7 @@
         </is>
       </c>
       <c r="E607" s="23" t="n">
-        <v>201</v>
+        <v>234</v>
       </c>
     </row>
     <row r="608" ht="20" customHeight="1">
@@ -16228,7 +16228,7 @@
         </is>
       </c>
       <c r="E608" s="20" t="n">
-        <v>195</v>
+        <v>137</v>
       </c>
     </row>
     <row r="609" ht="20" customHeight="1">
@@ -16253,7 +16253,7 @@
         </is>
       </c>
       <c r="E609" s="23" t="n">
-        <v>127</v>
+        <v>115</v>
       </c>
     </row>
     <row r="610" ht="20" customHeight="1">
@@ -16278,7 +16278,7 @@
         </is>
       </c>
       <c r="E610" s="20" t="n">
-        <v>190</v>
+        <v>114</v>
       </c>
     </row>
     <row r="611" ht="20" customHeight="1">
@@ -16303,7 +16303,7 @@
         </is>
       </c>
       <c r="E611" s="23" t="n">
-        <v>173</v>
+        <v>144</v>
       </c>
     </row>
     <row r="612" ht="20" customHeight="1">
@@ -16328,7 +16328,7 @@
         </is>
       </c>
       <c r="E612" s="20" t="n">
-        <v>238</v>
+        <v>131</v>
       </c>
     </row>
     <row r="613" ht="20" customHeight="1">
@@ -16353,7 +16353,7 @@
         </is>
       </c>
       <c r="E613" s="23" t="n">
-        <v>120</v>
+        <v>173</v>
       </c>
     </row>
     <row r="614" ht="20" customHeight="1">
@@ -16378,7 +16378,7 @@
         </is>
       </c>
       <c r="E614" s="20" t="n">
-        <v>176</v>
+        <v>229</v>
       </c>
     </row>
     <row r="615" ht="20" customHeight="1">
@@ -16403,7 +16403,7 @@
         </is>
       </c>
       <c r="E615" s="23" t="n">
-        <v>150</v>
+        <v>115</v>
       </c>
     </row>
     <row r="616" ht="20" customHeight="1">
@@ -16428,7 +16428,7 @@
         </is>
       </c>
       <c r="E616" s="20" t="n">
-        <v>115</v>
+        <v>224</v>
       </c>
     </row>
     <row r="617" ht="20" customHeight="1">
@@ -16453,7 +16453,7 @@
         </is>
       </c>
       <c r="E617" s="23" t="n">
-        <v>167</v>
+        <v>189</v>
       </c>
     </row>
     <row r="618" ht="20" customHeight="1">
@@ -16478,7 +16478,7 @@
         </is>
       </c>
       <c r="E618" s="20" t="n">
-        <v>196</v>
+        <v>117</v>
       </c>
     </row>
     <row r="619" ht="20" customHeight="1">
@@ -16503,7 +16503,7 @@
         </is>
       </c>
       <c r="E619" s="23" t="n">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="620" ht="20" customHeight="1">
@@ -16528,7 +16528,7 @@
         </is>
       </c>
       <c r="E620" s="20" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="621" ht="20" customHeight="1">
@@ -16553,7 +16553,7 @@
         </is>
       </c>
       <c r="E621" s="23" t="n">
-        <v>147</v>
+        <v>161</v>
       </c>
     </row>
     <row r="622" ht="20" customHeight="1">
@@ -16578,7 +16578,7 @@
         </is>
       </c>
       <c r="E622" s="20" t="n">
-        <v>228</v>
+        <v>203</v>
       </c>
     </row>
     <row r="623" ht="20" customHeight="1">
@@ -16603,7 +16603,7 @@
         </is>
       </c>
       <c r="E623" s="23" t="n">
-        <v>197</v>
+        <v>187</v>
       </c>
     </row>
     <row r="624" ht="20" customHeight="1">
@@ -16628,7 +16628,7 @@
         </is>
       </c>
       <c r="E624" s="20" t="n">
-        <v>165</v>
+        <v>203</v>
       </c>
     </row>
     <row r="625" ht="20" customHeight="1">
@@ -16653,7 +16653,7 @@
         </is>
       </c>
       <c r="E625" s="23" t="n">
-        <v>203</v>
+        <v>221</v>
       </c>
     </row>
     <row r="626" ht="20" customHeight="1">
@@ -16678,7 +16678,7 @@
         </is>
       </c>
       <c r="E626" s="20" t="n">
-        <v>177</v>
+        <v>207</v>
       </c>
     </row>
     <row r="627" ht="20" customHeight="1">
@@ -16703,7 +16703,7 @@
         </is>
       </c>
       <c r="E627" s="23" t="n">
-        <v>162</v>
+        <v>232</v>
       </c>
     </row>
     <row r="628" ht="20" customHeight="1">
@@ -16728,7 +16728,7 @@
         </is>
       </c>
       <c r="E628" s="20" t="n">
-        <v>163</v>
+        <v>196</v>
       </c>
     </row>
     <row r="629" ht="20" customHeight="1">
@@ -16753,7 +16753,7 @@
         </is>
       </c>
       <c r="E629" s="23" t="n">
-        <v>219</v>
+        <v>197</v>
       </c>
     </row>
     <row r="630" ht="20" customHeight="1">
@@ -16778,7 +16778,7 @@
         </is>
       </c>
       <c r="E630" s="20" t="n">
-        <v>149</v>
+        <v>183</v>
       </c>
     </row>
     <row r="631" ht="20" customHeight="1">
@@ -16803,7 +16803,7 @@
         </is>
       </c>
       <c r="E631" s="23" t="n">
-        <v>225</v>
+        <v>171</v>
       </c>
     </row>
     <row r="632" ht="20" customHeight="1">
@@ -16828,7 +16828,7 @@
         </is>
       </c>
       <c r="E632" s="20" t="n">
-        <v>170</v>
+        <v>117</v>
       </c>
     </row>
     <row r="633" ht="20" customHeight="1">
@@ -16853,7 +16853,7 @@
         </is>
       </c>
       <c r="E633" s="23" t="n">
-        <v>179</v>
+        <v>157</v>
       </c>
     </row>
     <row r="634" ht="20" customHeight="1">
@@ -16878,7 +16878,7 @@
         </is>
       </c>
       <c r="E634" s="20" t="n">
-        <v>233</v>
+        <v>121</v>
       </c>
     </row>
     <row r="635" ht="20" customHeight="1">
@@ -16903,7 +16903,7 @@
         </is>
       </c>
       <c r="E635" s="23" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="636" ht="20" customHeight="1">
@@ -16928,7 +16928,7 @@
         </is>
       </c>
       <c r="E636" s="20" t="n">
-        <v>215</v>
+        <v>226</v>
       </c>
     </row>
     <row r="637" ht="20" customHeight="1">
@@ -16953,7 +16953,7 @@
         </is>
       </c>
       <c r="E637" s="23" t="n">
-        <v>230</v>
+        <v>151</v>
       </c>
     </row>
     <row r="638" ht="20" customHeight="1">
@@ -16978,7 +16978,7 @@
         </is>
       </c>
       <c r="E638" s="20" t="n">
-        <v>116</v>
+        <v>207</v>
       </c>
     </row>
     <row r="639" ht="20" customHeight="1">
@@ -17003,7 +17003,7 @@
         </is>
       </c>
       <c r="E639" s="23" t="n">
-        <v>182</v>
+        <v>153</v>
       </c>
     </row>
     <row r="640" ht="20" customHeight="1">
@@ -17028,7 +17028,7 @@
         </is>
       </c>
       <c r="E640" s="20" t="n">
-        <v>168</v>
+        <v>132</v>
       </c>
     </row>
     <row r="641" ht="20" customHeight="1">
@@ -17053,7 +17053,7 @@
         </is>
       </c>
       <c r="E641" s="23" t="n">
-        <v>111</v>
+        <v>181</v>
       </c>
     </row>
     <row r="642" ht="20" customHeight="1">
@@ -17078,7 +17078,7 @@
         </is>
       </c>
       <c r="E642" s="20" t="n">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="643" ht="20" customHeight="1">
@@ -17103,7 +17103,7 @@
         </is>
       </c>
       <c r="E643" s="23" t="n">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="644" ht="20" customHeight="1">
@@ -17128,7 +17128,7 @@
         </is>
       </c>
       <c r="E644" s="20" t="n">
-        <v>149</v>
+        <v>236</v>
       </c>
     </row>
     <row r="645" ht="20" customHeight="1">
@@ -17153,7 +17153,7 @@
         </is>
       </c>
       <c r="E645" s="23" t="n">
-        <v>129</v>
+        <v>188</v>
       </c>
     </row>
     <row r="646" ht="20" customHeight="1">
@@ -17178,7 +17178,7 @@
         </is>
       </c>
       <c r="E646" s="20" t="n">
-        <v>178</v>
+        <v>131</v>
       </c>
     </row>
     <row r="647" ht="20" customHeight="1">
@@ -17203,7 +17203,7 @@
         </is>
       </c>
       <c r="E647" s="23" t="n">
-        <v>178</v>
+        <v>219</v>
       </c>
     </row>
     <row r="648" ht="20" customHeight="1">
@@ -17228,7 +17228,7 @@
         </is>
       </c>
       <c r="E648" s="20" t="n">
-        <v>220</v>
+        <v>232</v>
       </c>
     </row>
     <row r="649" ht="20" customHeight="1">
@@ -17253,7 +17253,7 @@
         </is>
       </c>
       <c r="E649" s="23" t="n">
-        <v>205</v>
+        <v>215</v>
       </c>
     </row>
     <row r="650" ht="20" customHeight="1">
@@ -17278,7 +17278,7 @@
         </is>
       </c>
       <c r="E650" s="20" t="n">
-        <v>233</v>
+        <v>131</v>
       </c>
     </row>
     <row r="651" ht="20" customHeight="1">
@@ -17303,7 +17303,7 @@
         </is>
       </c>
       <c r="E651" s="23" t="n">
-        <v>144</v>
+        <v>230</v>
       </c>
     </row>
     <row r="652" ht="20" customHeight="1">
@@ -17328,7 +17328,7 @@
         </is>
       </c>
       <c r="E652" s="20" t="n">
-        <v>226</v>
+        <v>133</v>
       </c>
     </row>
     <row r="653" ht="20" customHeight="1">
@@ -17353,7 +17353,7 @@
         </is>
       </c>
       <c r="E653" s="23" t="n">
-        <v>131</v>
+        <v>117</v>
       </c>
     </row>
     <row r="654" ht="20" customHeight="1">
@@ -17378,7 +17378,7 @@
         </is>
       </c>
       <c r="E654" s="20" t="n">
-        <v>133</v>
+        <v>161</v>
       </c>
     </row>
     <row r="655" ht="20" customHeight="1">
@@ -17403,7 +17403,7 @@
         </is>
       </c>
       <c r="E655" s="23" t="n">
-        <v>223</v>
+        <v>217</v>
       </c>
     </row>
     <row r="656" ht="20" customHeight="1">
@@ -17428,7 +17428,7 @@
         </is>
       </c>
       <c r="E656" s="20" t="n">
-        <v>197</v>
+        <v>173</v>
       </c>
     </row>
     <row r="657" ht="20" customHeight="1">
@@ -17453,7 +17453,7 @@
         </is>
       </c>
       <c r="E657" s="23" t="n">
-        <v>186</v>
+        <v>229</v>
       </c>
     </row>
     <row r="658" ht="20" customHeight="1">
@@ -17478,7 +17478,7 @@
         </is>
       </c>
       <c r="E658" s="20" t="n">
-        <v>213</v>
+        <v>123</v>
       </c>
     </row>
     <row r="659" ht="20" customHeight="1">
@@ -17503,7 +17503,7 @@
         </is>
       </c>
       <c r="E659" s="23" t="n">
-        <v>210</v>
+        <v>169</v>
       </c>
     </row>
     <row r="660" ht="20" customHeight="1">
@@ -17528,7 +17528,7 @@
         </is>
       </c>
       <c r="E660" s="20" t="n">
-        <v>127</v>
+        <v>220</v>
       </c>
     </row>
     <row r="661" ht="20" customHeight="1">
@@ -17553,7 +17553,7 @@
         </is>
       </c>
       <c r="E661" s="23" t="n">
-        <v>175</v>
+        <v>166</v>
       </c>
     </row>
     <row r="662" ht="20" customHeight="1">
@@ -17578,7 +17578,7 @@
         </is>
       </c>
       <c r="E662" s="20" t="n">
-        <v>126</v>
+        <v>147</v>
       </c>
     </row>
     <row r="663" ht="20" customHeight="1">
@@ -17603,7 +17603,7 @@
         </is>
       </c>
       <c r="E663" s="23" t="n">
-        <v>165</v>
+        <v>225</v>
       </c>
     </row>
     <row r="664" ht="20" customHeight="1">
@@ -17628,7 +17628,7 @@
         </is>
       </c>
       <c r="E664" s="20" t="n">
-        <v>162</v>
+        <v>223</v>
       </c>
     </row>
     <row r="665" ht="20" customHeight="1">
@@ -17678,7 +17678,7 @@
         </is>
       </c>
       <c r="E666" s="20" t="n">
-        <v>237</v>
+        <v>209</v>
       </c>
     </row>
     <row r="667" ht="20" customHeight="1">
@@ -17703,7 +17703,7 @@
         </is>
       </c>
       <c r="E667" s="23" t="n">
-        <v>123</v>
+        <v>193</v>
       </c>
     </row>
     <row r="668" ht="20" customHeight="1">
@@ -17728,7 +17728,7 @@
         </is>
       </c>
       <c r="E668" s="20" t="n">
-        <v>230</v>
+        <v>205</v>
       </c>
     </row>
     <row r="669" ht="20" customHeight="1">
@@ -17753,7 +17753,7 @@
         </is>
       </c>
       <c r="E669" s="23" t="n">
-        <v>123</v>
+        <v>209</v>
       </c>
     </row>
     <row r="670" ht="20" customHeight="1">
@@ -17778,7 +17778,7 @@
         </is>
       </c>
       <c r="E670" s="20" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="671" ht="20" customHeight="1">
@@ -17803,7 +17803,7 @@
         </is>
       </c>
       <c r="E671" s="23" t="n">
-        <v>142</v>
+        <v>212</v>
       </c>
     </row>
     <row r="672" ht="20" customHeight="1">
@@ -17828,7 +17828,7 @@
         </is>
       </c>
       <c r="E672" s="20" t="n">
-        <v>214</v>
+        <v>144</v>
       </c>
     </row>
     <row r="673" ht="20" customHeight="1">
@@ -17853,7 +17853,7 @@
         </is>
       </c>
       <c r="E673" s="23" t="n">
-        <v>206</v>
+        <v>197</v>
       </c>
     </row>
     <row r="674" ht="20" customHeight="1">
@@ -17878,7 +17878,7 @@
         </is>
       </c>
       <c r="E674" s="20" t="n">
-        <v>219</v>
+        <v>199</v>
       </c>
     </row>
     <row r="675" ht="20" customHeight="1">
@@ -17903,7 +17903,7 @@
         </is>
       </c>
       <c r="E675" s="23" t="n">
-        <v>184</v>
+        <v>134</v>
       </c>
     </row>
     <row r="676" ht="20" customHeight="1">
@@ -17928,7 +17928,7 @@
         </is>
       </c>
       <c r="E676" s="20" t="n">
-        <v>202</v>
+        <v>110</v>
       </c>
     </row>
     <row r="677" ht="20" customHeight="1">
@@ -17953,7 +17953,7 @@
         </is>
       </c>
       <c r="E677" s="23" t="n">
-        <v>185</v>
+        <v>153</v>
       </c>
     </row>
     <row r="678" ht="20" customHeight="1">
@@ -17978,7 +17978,7 @@
         </is>
       </c>
       <c r="E678" s="20" t="n">
-        <v>206</v>
+        <v>159</v>
       </c>
     </row>
     <row r="679" ht="20" customHeight="1">
@@ -18003,7 +18003,7 @@
         </is>
       </c>
       <c r="E679" s="23" t="n">
-        <v>131</v>
+        <v>173</v>
       </c>
     </row>
     <row r="680" ht="20" customHeight="1">
@@ -18028,7 +18028,7 @@
         </is>
       </c>
       <c r="E680" s="20" t="n">
-        <v>230</v>
+        <v>146</v>
       </c>
     </row>
     <row r="681" ht="20" customHeight="1">
@@ -18053,7 +18053,7 @@
         </is>
       </c>
       <c r="E681" s="23" t="n">
-        <v>142</v>
+        <v>157</v>
       </c>
     </row>
     <row r="682" ht="20" customHeight="1">
@@ -18078,7 +18078,7 @@
         </is>
       </c>
       <c r="E682" s="20" t="n">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="683" ht="20" customHeight="1">
@@ -18103,7 +18103,7 @@
         </is>
       </c>
       <c r="E683" s="23" t="n">
-        <v>122</v>
+        <v>139</v>
       </c>
     </row>
     <row r="684" ht="20" customHeight="1">
@@ -18128,7 +18128,7 @@
         </is>
       </c>
       <c r="E684" s="20" t="n">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="685" ht="20" customHeight="1">
@@ -18153,7 +18153,7 @@
         </is>
       </c>
       <c r="E685" s="23" t="n">
-        <v>143</v>
+        <v>174</v>
       </c>
     </row>
     <row r="686" ht="20" customHeight="1">
@@ -18178,7 +18178,7 @@
         </is>
       </c>
       <c r="E686" s="20" t="n">
-        <v>146</v>
+        <v>198</v>
       </c>
     </row>
     <row r="687" ht="20" customHeight="1">
@@ -18203,7 +18203,7 @@
         </is>
       </c>
       <c r="E687" s="23" t="n">
-        <v>167</v>
+        <v>197</v>
       </c>
     </row>
     <row r="688" ht="20" customHeight="1">
@@ -18228,7 +18228,7 @@
         </is>
       </c>
       <c r="E688" s="20" t="n">
-        <v>145</v>
+        <v>162</v>
       </c>
     </row>
     <row r="689" ht="20" customHeight="1">
@@ -18253,7 +18253,7 @@
         </is>
       </c>
       <c r="E689" s="23" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
     </row>
     <row r="690" ht="20" customHeight="1">
@@ -18278,7 +18278,7 @@
         </is>
       </c>
       <c r="E690" s="20" t="n">
-        <v>148</v>
+        <v>221</v>
       </c>
     </row>
     <row r="691" ht="20" customHeight="1">
@@ -18303,7 +18303,7 @@
         </is>
       </c>
       <c r="E691" s="23" t="n">
-        <v>174</v>
+        <v>184</v>
       </c>
     </row>
     <row r="692" ht="20" customHeight="1">
@@ -18328,7 +18328,7 @@
         </is>
       </c>
       <c r="E692" s="20" t="n">
-        <v>124</v>
+        <v>231</v>
       </c>
     </row>
     <row r="693" ht="20" customHeight="1">
@@ -18353,7 +18353,7 @@
         </is>
       </c>
       <c r="E693" s="23" t="n">
-        <v>122</v>
+        <v>210</v>
       </c>
     </row>
     <row r="694" ht="20" customHeight="1">
@@ -18378,7 +18378,7 @@
         </is>
       </c>
       <c r="E694" s="20" t="n">
-        <v>129</v>
+        <v>187</v>
       </c>
     </row>
     <row r="695" ht="20" customHeight="1">
@@ -18403,7 +18403,7 @@
         </is>
       </c>
       <c r="E695" s="23" t="n">
-        <v>206</v>
+        <v>183</v>
       </c>
     </row>
     <row r="696" ht="20" customHeight="1">
@@ -18428,7 +18428,7 @@
         </is>
       </c>
       <c r="E696" s="20" t="n">
-        <v>155</v>
+        <v>206</v>
       </c>
     </row>
     <row r="697" ht="20" customHeight="1">
@@ -18453,7 +18453,7 @@
         </is>
       </c>
       <c r="E697" s="23" t="n">
-        <v>204</v>
+        <v>166</v>
       </c>
     </row>
     <row r="698" ht="20" customHeight="1">
@@ -18478,7 +18478,7 @@
         </is>
       </c>
       <c r="E698" s="20" t="n">
-        <v>221</v>
+        <v>113</v>
       </c>
     </row>
     <row r="699" ht="20" customHeight="1">
@@ -18503,7 +18503,7 @@
         </is>
       </c>
       <c r="E699" s="23" t="n">
-        <v>139</v>
+        <v>185</v>
       </c>
     </row>
     <row r="700" ht="20" customHeight="1">
@@ -18528,7 +18528,7 @@
         </is>
       </c>
       <c r="E700" s="20" t="n">
-        <v>218</v>
+        <v>196</v>
       </c>
     </row>
     <row r="701" ht="20" customHeight="1">
@@ -18578,7 +18578,7 @@
         </is>
       </c>
       <c r="E702" s="20" t="n">
-        <v>159</v>
+        <v>128</v>
       </c>
     </row>
     <row r="703" ht="20" customHeight="1">
@@ -18603,7 +18603,7 @@
         </is>
       </c>
       <c r="E703" s="23" t="n">
-        <v>170</v>
+        <v>221</v>
       </c>
     </row>
     <row r="704" ht="20" customHeight="1">
@@ -18628,7 +18628,7 @@
         </is>
       </c>
       <c r="E704" s="20" t="n">
-        <v>125</v>
+        <v>233</v>
       </c>
     </row>
     <row r="705" ht="20" customHeight="1">
@@ -18653,7 +18653,7 @@
         </is>
       </c>
       <c r="E705" s="23" t="n">
-        <v>154</v>
+        <v>235</v>
       </c>
     </row>
     <row r="706" ht="20" customHeight="1">
@@ -18678,7 +18678,7 @@
         </is>
       </c>
       <c r="E706" s="20" t="n">
-        <v>234</v>
+        <v>122</v>
       </c>
     </row>
     <row r="707" ht="20" customHeight="1">
@@ -18703,7 +18703,7 @@
         </is>
       </c>
       <c r="E707" s="23" t="n">
-        <v>152</v>
+        <v>213</v>
       </c>
     </row>
     <row r="708" ht="20" customHeight="1">
@@ -18728,7 +18728,7 @@
         </is>
       </c>
       <c r="E708" s="20" t="n">
-        <v>154</v>
+        <v>206</v>
       </c>
     </row>
     <row r="709" ht="20" customHeight="1">
@@ -18753,7 +18753,7 @@
         </is>
       </c>
       <c r="E709" s="23" t="n">
-        <v>211</v>
+        <v>186</v>
       </c>
     </row>
     <row r="710" ht="20" customHeight="1">
@@ -18778,7 +18778,7 @@
         </is>
       </c>
       <c r="E710" s="20" t="n">
-        <v>168</v>
+        <v>238</v>
       </c>
     </row>
     <row r="711" ht="20" customHeight="1">
@@ -18803,7 +18803,7 @@
         </is>
       </c>
       <c r="E711" s="23" t="n">
-        <v>179</v>
+        <v>122</v>
       </c>
     </row>
     <row r="712" ht="20" customHeight="1">
@@ -18828,7 +18828,7 @@
         </is>
       </c>
       <c r="E712" s="20" t="n">
-        <v>232</v>
+        <v>159</v>
       </c>
     </row>
     <row r="713" ht="20" customHeight="1">
@@ -18853,7 +18853,7 @@
         </is>
       </c>
       <c r="E713" s="23" t="n">
-        <v>136</v>
+        <v>240</v>
       </c>
     </row>
     <row r="714" ht="20" customHeight="1">
@@ -18878,7 +18878,7 @@
         </is>
       </c>
       <c r="E714" s="20" t="n">
-        <v>177</v>
+        <v>183</v>
       </c>
     </row>
     <row r="715" ht="20" customHeight="1">
@@ -18903,7 +18903,7 @@
         </is>
       </c>
       <c r="E715" s="23" t="n">
-        <v>204</v>
+        <v>117</v>
       </c>
     </row>
     <row r="716" ht="20" customHeight="1">
@@ -18928,7 +18928,7 @@
         </is>
       </c>
       <c r="E716" s="20" t="n">
-        <v>148</v>
+        <v>211</v>
       </c>
     </row>
     <row r="717" ht="20" customHeight="1">
@@ -18953,7 +18953,7 @@
         </is>
       </c>
       <c r="E717" s="23" t="n">
-        <v>157</v>
+        <v>134</v>
       </c>
     </row>
     <row r="718" ht="20" customHeight="1">
@@ -18978,7 +18978,7 @@
         </is>
       </c>
       <c r="E718" s="20" t="n">
-        <v>149</v>
+        <v>220</v>
       </c>
     </row>
     <row r="719" ht="20" customHeight="1">
@@ -19003,7 +19003,7 @@
         </is>
       </c>
       <c r="E719" s="23" t="n">
-        <v>176</v>
+        <v>119</v>
       </c>
     </row>
     <row r="720" ht="20" customHeight="1">
@@ -19028,7 +19028,7 @@
         </is>
       </c>
       <c r="E720" s="20" t="n">
-        <v>132</v>
+        <v>203</v>
       </c>
     </row>
     <row r="721" ht="20" customHeight="1">
@@ -19053,7 +19053,7 @@
         </is>
       </c>
       <c r="E721" s="23" t="n">
-        <v>180</v>
+        <v>217</v>
       </c>
     </row>
     <row r="722" ht="20" customHeight="1">
@@ -19078,7 +19078,7 @@
         </is>
       </c>
       <c r="E722" s="20" t="n">
-        <v>239</v>
+        <v>189</v>
       </c>
     </row>
     <row r="723" ht="20" customHeight="1">
@@ -19103,7 +19103,7 @@
         </is>
       </c>
       <c r="E723" s="23" t="n">
-        <v>167</v>
+        <v>208</v>
       </c>
     </row>
     <row r="724" ht="20" customHeight="1">
@@ -19128,7 +19128,7 @@
         </is>
       </c>
       <c r="E724" s="20" t="n">
-        <v>112</v>
+        <v>211</v>
       </c>
     </row>
     <row r="725" ht="20" customHeight="1">
@@ -19153,7 +19153,7 @@
         </is>
       </c>
       <c r="E725" s="23" t="n">
-        <v>171</v>
+        <v>189</v>
       </c>
     </row>
     <row r="726" ht="20" customHeight="1">
@@ -19178,7 +19178,7 @@
         </is>
       </c>
       <c r="E726" s="20" t="n">
-        <v>116</v>
+        <v>231</v>
       </c>
     </row>
     <row r="727" ht="20" customHeight="1">
@@ -19203,7 +19203,7 @@
         </is>
       </c>
       <c r="E727" s="23" t="n">
-        <v>141</v>
+        <v>203</v>
       </c>
     </row>
     <row r="728" ht="20" customHeight="1">
@@ -19228,7 +19228,7 @@
         </is>
       </c>
       <c r="E728" s="20" t="n">
-        <v>161</v>
+        <v>203</v>
       </c>
     </row>
     <row r="729" ht="20" customHeight="1">
@@ -19253,7 +19253,7 @@
         </is>
       </c>
       <c r="E729" s="23" t="n">
-        <v>187</v>
+        <v>110</v>
       </c>
     </row>
     <row r="730" ht="20" customHeight="1">
@@ -19278,7 +19278,7 @@
         </is>
       </c>
       <c r="E730" s="20" t="n">
-        <v>179</v>
+        <v>168</v>
       </c>
     </row>
     <row r="731" ht="20" customHeight="1">
@@ -19303,7 +19303,7 @@
         </is>
       </c>
       <c r="E731" s="23" t="n">
-        <v>189</v>
+        <v>111</v>
       </c>
     </row>
     <row r="732" ht="20" customHeight="1">
@@ -19328,7 +19328,7 @@
         </is>
       </c>
       <c r="E732" s="20" t="n">
-        <v>149</v>
+        <v>220</v>
       </c>
     </row>
     <row r="733" ht="20" customHeight="1">
@@ -19353,7 +19353,7 @@
         </is>
       </c>
       <c r="E733" s="23" t="n">
-        <v>136</v>
+        <v>173</v>
       </c>
     </row>
     <row r="734" ht="20" customHeight="1">
@@ -19378,7 +19378,7 @@
         </is>
       </c>
       <c r="E734" s="20" t="n">
-        <v>169</v>
+        <v>124</v>
       </c>
     </row>
     <row r="735" ht="20" customHeight="1">
@@ -19403,7 +19403,7 @@
         </is>
       </c>
       <c r="E735" s="23" t="n">
-        <v>113</v>
+        <v>166</v>
       </c>
     </row>
     <row r="736" ht="20" customHeight="1">
@@ -19428,7 +19428,7 @@
         </is>
       </c>
       <c r="E736" s="20" t="n">
-        <v>179</v>
+        <v>184</v>
       </c>
     </row>
     <row r="737" ht="20" customHeight="1">
@@ -19453,7 +19453,7 @@
         </is>
       </c>
       <c r="E737" s="23" t="n">
-        <v>116</v>
+        <v>212</v>
       </c>
     </row>
     <row r="738" ht="20" customHeight="1">
@@ -19478,7 +19478,7 @@
         </is>
       </c>
       <c r="E738" s="20" t="n">
-        <v>153</v>
+        <v>170</v>
       </c>
     </row>
     <row r="739" ht="20" customHeight="1">
@@ -19503,7 +19503,7 @@
         </is>
       </c>
       <c r="E739" s="23" t="n">
-        <v>221</v>
+        <v>229</v>
       </c>
     </row>
     <row r="740" ht="20" customHeight="1">
@@ -19528,7 +19528,7 @@
         </is>
       </c>
       <c r="E740" s="20" t="n">
-        <v>147</v>
+        <v>116</v>
       </c>
     </row>
     <row r="741" ht="20" customHeight="1">
@@ -19553,7 +19553,7 @@
         </is>
       </c>
       <c r="E741" s="23" t="n">
-        <v>227</v>
+        <v>143</v>
       </c>
     </row>
     <row r="742" ht="20" customHeight="1">
@@ -19578,7 +19578,7 @@
         </is>
       </c>
       <c r="E742" s="20" t="n">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="743" ht="20" customHeight="1">
@@ -19603,7 +19603,7 @@
         </is>
       </c>
       <c r="E743" s="23" t="n">
-        <v>193</v>
+        <v>152</v>
       </c>
     </row>
     <row r="744" ht="20" customHeight="1">
@@ -19628,7 +19628,7 @@
         </is>
       </c>
       <c r="E744" s="20" t="n">
-        <v>209</v>
+        <v>170</v>
       </c>
     </row>
     <row r="745" ht="20" customHeight="1">
@@ -19653,7 +19653,7 @@
         </is>
       </c>
       <c r="E745" s="23" t="n">
-        <v>221</v>
+        <v>135</v>
       </c>
     </row>
     <row r="746" ht="20" customHeight="1">
@@ -19678,7 +19678,7 @@
         </is>
       </c>
       <c r="E746" s="20" t="n">
-        <v>178</v>
+        <v>217</v>
       </c>
     </row>
     <row r="747" ht="20" customHeight="1">
@@ -19703,7 +19703,7 @@
         </is>
       </c>
       <c r="E747" s="23" t="n">
-        <v>212</v>
+        <v>125</v>
       </c>
     </row>
     <row r="748" ht="20" customHeight="1">
@@ -19728,7 +19728,7 @@
         </is>
       </c>
       <c r="E748" s="20" t="n">
-        <v>167</v>
+        <v>213</v>
       </c>
     </row>
     <row r="749" ht="20" customHeight="1">
@@ -19753,7 +19753,7 @@
         </is>
       </c>
       <c r="E749" s="23" t="n">
-        <v>155</v>
+        <v>229</v>
       </c>
     </row>
     <row r="750" ht="20" customHeight="1">
@@ -19778,7 +19778,7 @@
         </is>
       </c>
       <c r="E750" s="20" t="n">
-        <v>155</v>
+        <v>182</v>
       </c>
     </row>
     <row r="751" ht="20" customHeight="1">
@@ -19803,7 +19803,7 @@
         </is>
       </c>
       <c r="E751" s="23" t="n">
-        <v>208</v>
+        <v>143</v>
       </c>
     </row>
     <row r="752" ht="20" customHeight="1">
@@ -19828,7 +19828,7 @@
         </is>
       </c>
       <c r="E752" s="20" t="n">
-        <v>170</v>
+        <v>155</v>
       </c>
     </row>
     <row r="753" ht="20" customHeight="1">
@@ -19853,7 +19853,7 @@
         </is>
       </c>
       <c r="E753" s="23" t="n">
-        <v>127</v>
+        <v>205</v>
       </c>
     </row>
     <row r="754" ht="20" customHeight="1">
@@ -19878,7 +19878,7 @@
         </is>
       </c>
       <c r="E754" s="20" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="755" ht="20" customHeight="1">
@@ -19903,7 +19903,7 @@
         </is>
       </c>
       <c r="E755" s="23" t="n">
-        <v>214</v>
+        <v>229</v>
       </c>
     </row>
     <row r="756" ht="20" customHeight="1">
@@ -19928,7 +19928,7 @@
         </is>
       </c>
       <c r="E756" s="20" t="n">
-        <v>194</v>
+        <v>189</v>
       </c>
     </row>
     <row r="757" ht="20" customHeight="1">
@@ -19953,7 +19953,7 @@
         </is>
       </c>
       <c r="E757" s="23" t="n">
-        <v>122</v>
+        <v>176</v>
       </c>
     </row>
     <row r="758" ht="20" customHeight="1">
@@ -19978,7 +19978,7 @@
         </is>
       </c>
       <c r="E758" s="20" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="759" ht="20" customHeight="1">
@@ -20003,7 +20003,7 @@
         </is>
       </c>
       <c r="E759" s="23" t="n">
-        <v>117</v>
+        <v>137</v>
       </c>
     </row>
     <row r="760" ht="20" customHeight="1">
@@ -20028,7 +20028,7 @@
         </is>
       </c>
       <c r="E760" s="20" t="n">
-        <v>219</v>
+        <v>140</v>
       </c>
     </row>
     <row r="761" ht="20" customHeight="1">
@@ -20053,7 +20053,7 @@
         </is>
       </c>
       <c r="E761" s="23" t="n">
-        <v>227</v>
+        <v>220</v>
       </c>
     </row>
     <row r="762" ht="20" customHeight="1">
@@ -20078,7 +20078,7 @@
         </is>
       </c>
       <c r="E762" s="20" t="n">
-        <v>224</v>
+        <v>144</v>
       </c>
     </row>
     <row r="763" ht="20" customHeight="1">
@@ -20103,7 +20103,7 @@
         </is>
       </c>
       <c r="E763" s="23" t="n">
-        <v>130</v>
+        <v>166</v>
       </c>
     </row>
     <row r="764" ht="20" customHeight="1">
@@ -20128,7 +20128,7 @@
         </is>
       </c>
       <c r="E764" s="20" t="n">
-        <v>112</v>
+        <v>152</v>
       </c>
     </row>
     <row r="765" ht="20" customHeight="1">
@@ -20153,7 +20153,7 @@
         </is>
       </c>
       <c r="E765" s="23" t="n">
-        <v>143</v>
+        <v>174</v>
       </c>
     </row>
     <row r="766" ht="20" customHeight="1">
@@ -20178,7 +20178,7 @@
         </is>
       </c>
       <c r="E766" s="20" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="767" ht="20" customHeight="1">
@@ -20203,7 +20203,7 @@
         </is>
       </c>
       <c r="E767" s="23" t="n">
-        <v>214</v>
+        <v>200</v>
       </c>
     </row>
     <row r="768" ht="20" customHeight="1">
@@ -20228,7 +20228,7 @@
         </is>
       </c>
       <c r="E768" s="20" t="n">
-        <v>155</v>
+        <v>113</v>
       </c>
     </row>
     <row r="769" ht="20" customHeight="1">
@@ -20253,7 +20253,7 @@
         </is>
       </c>
       <c r="E769" s="23" t="n">
-        <v>196</v>
+        <v>146</v>
       </c>
     </row>
     <row r="770" ht="20" customHeight="1">
@@ -20278,7 +20278,7 @@
         </is>
       </c>
       <c r="E770" s="20" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="771" ht="20" customHeight="1">
@@ -20303,7 +20303,7 @@
         </is>
       </c>
       <c r="E771" s="23" t="n">
-        <v>123</v>
+        <v>187</v>
       </c>
     </row>
     <row r="772" ht="20" customHeight="1">
@@ -20328,7 +20328,7 @@
         </is>
       </c>
       <c r="E772" s="20" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
     </row>
     <row r="773" ht="20" customHeight="1">
@@ -20353,7 +20353,7 @@
         </is>
       </c>
       <c r="E773" s="23" t="n">
-        <v>140</v>
+        <v>195</v>
       </c>
     </row>
     <row r="774" ht="20" customHeight="1">
@@ -20378,7 +20378,7 @@
         </is>
       </c>
       <c r="E774" s="20" t="n">
-        <v>217</v>
+        <v>167</v>
       </c>
     </row>
     <row r="775" ht="20" customHeight="1">
@@ -20403,7 +20403,7 @@
         </is>
       </c>
       <c r="E775" s="23" t="n">
-        <v>129</v>
+        <v>180</v>
       </c>
     </row>
     <row r="776" ht="20" customHeight="1">
@@ -20428,7 +20428,7 @@
         </is>
       </c>
       <c r="E776" s="20" t="n">
-        <v>120</v>
+        <v>226</v>
       </c>
     </row>
     <row r="777" ht="20" customHeight="1">
@@ -20453,7 +20453,7 @@
         </is>
       </c>
       <c r="E777" s="23" t="n">
-        <v>130</v>
+        <v>221</v>
       </c>
     </row>
     <row r="778" ht="20" customHeight="1">
@@ -20478,7 +20478,7 @@
         </is>
       </c>
       <c r="E778" s="20" t="n">
-        <v>136</v>
+        <v>238</v>
       </c>
     </row>
     <row r="779" ht="20" customHeight="1">
@@ -20503,7 +20503,7 @@
         </is>
       </c>
       <c r="E779" s="23" t="n">
-        <v>198</v>
+        <v>218</v>
       </c>
     </row>
     <row r="780" ht="20" customHeight="1">
@@ -20528,7 +20528,7 @@
         </is>
       </c>
       <c r="E780" s="20" t="n">
-        <v>137</v>
+        <v>166</v>
       </c>
     </row>
     <row r="781" ht="20" customHeight="1">
@@ -20553,7 +20553,7 @@
         </is>
       </c>
       <c r="E781" s="23" t="n">
-        <v>199</v>
+        <v>210</v>
       </c>
     </row>
     <row r="782" ht="20" customHeight="1">
@@ -20578,7 +20578,7 @@
         </is>
       </c>
       <c r="E782" s="20" t="n">
-        <v>212</v>
+        <v>118</v>
       </c>
     </row>
     <row r="783" ht="20" customHeight="1">
@@ -20603,7 +20603,7 @@
         </is>
       </c>
       <c r="E783" s="23" t="n">
-        <v>237</v>
+        <v>157</v>
       </c>
     </row>
     <row r="784" ht="20" customHeight="1">
@@ -20628,7 +20628,7 @@
         </is>
       </c>
       <c r="E784" s="20" t="n">
-        <v>175</v>
+        <v>193</v>
       </c>
     </row>
     <row r="785" ht="20" customHeight="1">
@@ -20653,7 +20653,7 @@
         </is>
       </c>
       <c r="E785" s="23" t="n">
-        <v>193</v>
+        <v>138</v>
       </c>
     </row>
     <row r="786" ht="20" customHeight="1">
@@ -20678,7 +20678,7 @@
         </is>
       </c>
       <c r="E786" s="20" t="n">
-        <v>137</v>
+        <v>114</v>
       </c>
     </row>
     <row r="787" ht="20" customHeight="1">
@@ -20703,7 +20703,7 @@
         </is>
       </c>
       <c r="E787" s="23" t="n">
-        <v>182</v>
+        <v>142</v>
       </c>
     </row>
     <row r="788" ht="20" customHeight="1">
@@ -20728,7 +20728,7 @@
         </is>
       </c>
       <c r="E788" s="20" t="n">
-        <v>206</v>
+        <v>191</v>
       </c>
     </row>
     <row r="789" ht="20" customHeight="1">
@@ -20753,7 +20753,7 @@
         </is>
       </c>
       <c r="E789" s="23" t="n">
-        <v>238</v>
+        <v>112</v>
       </c>
     </row>
     <row r="790" ht="20" customHeight="1">
@@ -20778,7 +20778,7 @@
         </is>
       </c>
       <c r="E790" s="20" t="n">
-        <v>168</v>
+        <v>180</v>
       </c>
     </row>
     <row r="791" ht="20" customHeight="1">
@@ -20803,7 +20803,7 @@
         </is>
       </c>
       <c r="E791" s="23" t="n">
-        <v>141</v>
+        <v>217</v>
       </c>
     </row>
     <row r="792" ht="20" customHeight="1">
@@ -20828,7 +20828,7 @@
         </is>
       </c>
       <c r="E792" s="20" t="n">
-        <v>237</v>
+        <v>115</v>
       </c>
     </row>
     <row r="793" ht="20" customHeight="1">
@@ -20853,7 +20853,7 @@
         </is>
       </c>
       <c r="E793" s="23" t="n">
-        <v>115</v>
+        <v>231</v>
       </c>
     </row>
     <row r="794" ht="20" customHeight="1">
@@ -20878,7 +20878,7 @@
         </is>
       </c>
       <c r="E794" s="20" t="n">
-        <v>205</v>
+        <v>220</v>
       </c>
     </row>
     <row r="795" ht="20" customHeight="1">
@@ -20903,7 +20903,7 @@
         </is>
       </c>
       <c r="E795" s="23" t="n">
-        <v>231</v>
+        <v>210</v>
       </c>
     </row>
     <row r="796" ht="20" customHeight="1">
@@ -20928,7 +20928,7 @@
         </is>
       </c>
       <c r="E796" s="20" t="n">
-        <v>166</v>
+        <v>208</v>
       </c>
     </row>
     <row r="797" ht="20" customHeight="1">
@@ -20953,7 +20953,7 @@
         </is>
       </c>
       <c r="E797" s="23" t="n">
-        <v>212</v>
+        <v>220</v>
       </c>
     </row>
     <row r="798" ht="20" customHeight="1">
@@ -20978,7 +20978,7 @@
         </is>
       </c>
       <c r="E798" s="20" t="n">
-        <v>164</v>
+        <v>183</v>
       </c>
     </row>
     <row r="799" ht="20" customHeight="1">
@@ -21003,7 +21003,7 @@
         </is>
       </c>
       <c r="E799" s="23" t="n">
-        <v>181</v>
+        <v>176</v>
       </c>
     </row>
     <row r="800" ht="20" customHeight="1">
@@ -21028,7 +21028,7 @@
         </is>
       </c>
       <c r="E800" s="20" t="n">
-        <v>131</v>
+        <v>160</v>
       </c>
     </row>
     <row r="801" ht="20" customHeight="1">
@@ -21053,7 +21053,7 @@
         </is>
       </c>
       <c r="E801" s="23" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/Appium_E2E_Test_Report_Traverse.xlsx
+++ b/Appium_E2E_Test_Report_Traverse.xlsx
@@ -791,7 +791,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 06:01:23</t>
+          <t>2026-08-11 06:34:24</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="E2" s="20" t="n">
-        <v>131</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="E3" s="23" t="n">
-        <v>194</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="E4" s="20" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="E5" s="23" t="n">
-        <v>139</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="E6" s="20" t="n">
-        <v>200</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="E7" s="23" t="n">
-        <v>214</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="E9" s="23" t="n">
-        <v>136</v>
+        <v>197</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
@@ -1278,7 +1278,7 @@
         </is>
       </c>
       <c r="E10" s="20" t="n">
-        <v>217</v>
+        <v>193</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="E11" s="23" t="n">
-        <v>140</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
@@ -1328,7 +1328,7 @@
         </is>
       </c>
       <c r="E12" s="20" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="E13" s="23" t="n">
-        <v>235</v>
+        <v>185</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="E14" s="20" t="n">
-        <v>140</v>
+        <v>177</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="E15" s="23" t="n">
-        <v>128</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="E16" s="20" t="n">
-        <v>206</v>
+        <v>131</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="E17" s="23" t="n">
-        <v>172</v>
+        <v>233</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -1478,7 +1478,7 @@
         </is>
       </c>
       <c r="E18" s="20" t="n">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
@@ -1503,7 +1503,7 @@
         </is>
       </c>
       <c r="E19" s="23" t="n">
-        <v>141</v>
+        <v>221</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="E20" s="20" t="n">
-        <v>215</v>
+        <v>185</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="E21" s="23" t="n">
-        <v>201</v>
+        <v>196</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
@@ -1578,7 +1578,7 @@
         </is>
       </c>
       <c r="E22" s="20" t="n">
-        <v>218</v>
+        <v>190</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="E23" s="23" t="n">
-        <v>219</v>
+        <v>154</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
@@ -1628,7 +1628,7 @@
         </is>
       </c>
       <c r="E24" s="20" t="n">
-        <v>224</v>
+        <v>132</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="E25" s="23" t="n">
-        <v>198</v>
+        <v>220</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
@@ -1678,7 +1678,7 @@
         </is>
       </c>
       <c r="E26" s="20" t="n">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="E27" s="23" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="E28" s="20" t="n">
-        <v>214</v>
+        <v>203</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="E29" s="23" t="n">
-        <v>224</v>
+        <v>170</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="E30" s="20" t="n">
-        <v>232</v>
+        <v>128</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
@@ -1803,7 +1803,7 @@
         </is>
       </c>
       <c r="E31" s="23" t="n">
-        <v>141</v>
+        <v>235</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
@@ -1828,7 +1828,7 @@
         </is>
       </c>
       <c r="E32" s="20" t="n">
-        <v>147</v>
+        <v>227</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
@@ -1853,7 +1853,7 @@
         </is>
       </c>
       <c r="E33" s="23" t="n">
-        <v>138</v>
+        <v>236</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
@@ -1878,7 +1878,7 @@
         </is>
       </c>
       <c r="E34" s="20" t="n">
-        <v>135</v>
+        <v>181</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="E35" s="23" t="n">
-        <v>165</v>
+        <v>207</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="E36" s="20" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="E37" s="23" t="n">
-        <v>176</v>
+        <v>219</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
@@ -1978,7 +1978,7 @@
         </is>
       </c>
       <c r="E38" s="20" t="n">
-        <v>182</v>
+        <v>122</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="E39" s="23" t="n">
-        <v>184</v>
+        <v>215</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="E40" s="20" t="n">
-        <v>145</v>
+        <v>227</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="E41" s="23" t="n">
-        <v>238</v>
+        <v>151</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
@@ -2078,7 +2078,7 @@
         </is>
       </c>
       <c r="E42" s="20" t="n">
-        <v>144</v>
+        <v>208</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="E43" s="23" t="n">
-        <v>167</v>
+        <v>183</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="E44" s="20" t="n">
-        <v>138</v>
+        <v>114</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="E45" s="23" t="n">
-        <v>110</v>
+        <v>237</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
@@ -2178,7 +2178,7 @@
         </is>
       </c>
       <c r="E46" s="20" t="n">
-        <v>221</v>
+        <v>228</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
@@ -2203,7 +2203,7 @@
         </is>
       </c>
       <c r="E47" s="23" t="n">
-        <v>133</v>
+        <v>237</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="E48" s="20" t="n">
-        <v>197</v>
+        <v>216</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
@@ -2253,7 +2253,7 @@
         </is>
       </c>
       <c r="E49" s="23" t="n">
-        <v>141</v>
+        <v>116</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
@@ -2278,7 +2278,7 @@
         </is>
       </c>
       <c r="E50" s="20" t="n">
-        <v>148</v>
+        <v>155</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="E51" s="23" t="n">
-        <v>122</v>
+        <v>177</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
@@ -2353,7 +2353,7 @@
         </is>
       </c>
       <c r="E53" s="23" t="n">
-        <v>183</v>
+        <v>141</v>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="E54" s="20" t="n">
-        <v>226</v>
+        <v>240</v>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1">
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="E55" s="23" t="n">
-        <v>177</v>
+        <v>185</v>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1">
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="E56" s="20" t="n">
-        <v>186</v>
+        <v>214</v>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1">
@@ -2453,7 +2453,7 @@
         </is>
       </c>
       <c r="E57" s="23" t="n">
-        <v>229</v>
+        <v>113</v>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1">
@@ -2478,7 +2478,7 @@
         </is>
       </c>
       <c r="E58" s="20" t="n">
-        <v>204</v>
+        <v>161</v>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1">
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="E59" s="23" t="n">
-        <v>170</v>
+        <v>213</v>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1">
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="E60" s="20" t="n">
-        <v>198</v>
+        <v>159</v>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
@@ -2553,7 +2553,7 @@
         </is>
       </c>
       <c r="E61" s="23" t="n">
-        <v>214</v>
+        <v>118</v>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="E62" s="20" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="E63" s="23" t="n">
-        <v>159</v>
+        <v>234</v>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1">
@@ -2628,7 +2628,7 @@
         </is>
       </c>
       <c r="E64" s="20" t="n">
-        <v>140</v>
+        <v>204</v>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1">
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="E65" s="23" t="n">
-        <v>240</v>
+        <v>213</v>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1">
@@ -2678,7 +2678,7 @@
         </is>
       </c>
       <c r="E66" s="20" t="n">
-        <v>177</v>
+        <v>111</v>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="E67" s="23" t="n">
-        <v>160</v>
+        <v>116</v>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="E68" s="20" t="n">
-        <v>185</v>
+        <v>211</v>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="E69" s="23" t="n">
-        <v>183</v>
+        <v>223</v>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1">
@@ -2778,7 +2778,7 @@
         </is>
       </c>
       <c r="E70" s="20" t="n">
-        <v>219</v>
+        <v>237</v>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1">
@@ -2803,7 +2803,7 @@
         </is>
       </c>
       <c r="E71" s="23" t="n">
-        <v>171</v>
+        <v>227</v>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1">
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="E72" s="20" t="n">
-        <v>120</v>
+        <v>203</v>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1">
@@ -2853,7 +2853,7 @@
         </is>
       </c>
       <c r="E73" s="23" t="n">
-        <v>233</v>
+        <v>207</v>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
@@ -2878,7 +2878,7 @@
         </is>
       </c>
       <c r="E74" s="20" t="n">
-        <v>175</v>
+        <v>181</v>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="E75" s="23" t="n">
-        <v>233</v>
+        <v>140</v>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
@@ -2928,7 +2928,7 @@
         </is>
       </c>
       <c r="E76" s="20" t="n">
-        <v>228</v>
+        <v>178</v>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="E77" s="23" t="n">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1">
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="E78" s="20" t="n">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
@@ -3003,7 +3003,7 @@
         </is>
       </c>
       <c r="E79" s="23" t="n">
-        <v>167</v>
+        <v>120</v>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1">
@@ -3028,7 +3028,7 @@
         </is>
       </c>
       <c r="E80" s="20" t="n">
-        <v>222</v>
+        <v>201</v>
       </c>
     </row>
     <row r="81" ht="20" customHeight="1">
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="E81" s="23" t="n">
-        <v>111</v>
+        <v>148</v>
       </c>
     </row>
     <row r="82" ht="20" customHeight="1">
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="E82" s="20" t="n">
-        <v>238</v>
+        <v>182</v>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1">
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="E83" s="23" t="n">
-        <v>185</v>
+        <v>217</v>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1">
@@ -3128,7 +3128,7 @@
         </is>
       </c>
       <c r="E84" s="20" t="n">
-        <v>114</v>
+        <v>185</v>
       </c>
     </row>
     <row r="85" ht="20" customHeight="1">
@@ -3153,7 +3153,7 @@
         </is>
       </c>
       <c r="E85" s="23" t="n">
-        <v>182</v>
+        <v>236</v>
       </c>
     </row>
     <row r="86" ht="20" customHeight="1">
@@ -3178,7 +3178,7 @@
         </is>
       </c>
       <c r="E86" s="20" t="n">
-        <v>163</v>
+        <v>127</v>
       </c>
     </row>
     <row r="87" ht="20" customHeight="1">
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="E87" s="23" t="n">
-        <v>201</v>
+        <v>147</v>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1">
@@ -3228,7 +3228,7 @@
         </is>
       </c>
       <c r="E88" s="20" t="n">
-        <v>202</v>
+        <v>119</v>
       </c>
     </row>
     <row r="89" ht="20" customHeight="1">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="E89" s="23" t="n">
-        <v>114</v>
+        <v>193</v>
       </c>
     </row>
     <row r="90" ht="20" customHeight="1">
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="E90" s="20" t="n">
-        <v>176</v>
+        <v>139</v>
       </c>
     </row>
     <row r="91" ht="20" customHeight="1">
@@ -3303,7 +3303,7 @@
         </is>
       </c>
       <c r="E91" s="23" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="92" ht="20" customHeight="1">
@@ -3328,7 +3328,7 @@
         </is>
       </c>
       <c r="E92" s="20" t="n">
-        <v>188</v>
+        <v>228</v>
       </c>
     </row>
     <row r="93" ht="20" customHeight="1">
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="E93" s="23" t="n">
-        <v>215</v>
+        <v>156</v>
       </c>
     </row>
     <row r="94" ht="20" customHeight="1">
@@ -3378,7 +3378,7 @@
         </is>
       </c>
       <c r="E94" s="20" t="n">
-        <v>225</v>
+        <v>144</v>
       </c>
     </row>
     <row r="95" ht="20" customHeight="1">
@@ -3403,7 +3403,7 @@
         </is>
       </c>
       <c r="E95" s="23" t="n">
-        <v>229</v>
+        <v>113</v>
       </c>
     </row>
     <row r="96" ht="20" customHeight="1">
@@ -3428,7 +3428,7 @@
         </is>
       </c>
       <c r="E96" s="20" t="n">
-        <v>158</v>
+        <v>115</v>
       </c>
     </row>
     <row r="97" ht="20" customHeight="1">
@@ -3453,7 +3453,7 @@
         </is>
       </c>
       <c r="E97" s="23" t="n">
-        <v>216</v>
+        <v>152</v>
       </c>
     </row>
     <row r="98" ht="20" customHeight="1">
@@ -3478,7 +3478,7 @@
         </is>
       </c>
       <c r="E98" s="20" t="n">
-        <v>178</v>
+        <v>211</v>
       </c>
     </row>
     <row r="99" ht="20" customHeight="1">
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="E99" s="23" t="n">
-        <v>209</v>
+        <v>148</v>
       </c>
     </row>
     <row r="100" ht="20" customHeight="1">
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="E100" s="20" t="n">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="101" ht="20" customHeight="1">
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="E101" s="23" t="n">
-        <v>180</v>
+        <v>118</v>
       </c>
     </row>
     <row r="102" ht="20" customHeight="1">
@@ -3578,7 +3578,7 @@
         </is>
       </c>
       <c r="E102" s="20" t="n">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="103" ht="20" customHeight="1">
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="E103" s="23" t="n">
-        <v>210</v>
+        <v>116</v>
       </c>
     </row>
     <row r="104" ht="20" customHeight="1">
@@ -3628,7 +3628,7 @@
         </is>
       </c>
       <c r="E104" s="20" t="n">
-        <v>238</v>
+        <v>129</v>
       </c>
     </row>
     <row r="105" ht="20" customHeight="1">
@@ -3653,7 +3653,7 @@
         </is>
       </c>
       <c r="E105" s="23" t="n">
-        <v>115</v>
+        <v>161</v>
       </c>
     </row>
     <row r="106" ht="20" customHeight="1">
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="E106" s="20" t="n">
-        <v>196</v>
+        <v>218</v>
       </c>
     </row>
     <row r="107" ht="20" customHeight="1">
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="E107" s="23" t="n">
-        <v>148</v>
+        <v>217</v>
       </c>
     </row>
     <row r="108" ht="20" customHeight="1">
@@ -3728,7 +3728,7 @@
         </is>
       </c>
       <c r="E108" s="20" t="n">
-        <v>121</v>
+        <v>155</v>
       </c>
     </row>
     <row r="109" ht="20" customHeight="1">
@@ -3753,7 +3753,7 @@
         </is>
       </c>
       <c r="E109" s="23" t="n">
-        <v>156</v>
+        <v>228</v>
       </c>
     </row>
     <row r="110" ht="20" customHeight="1">
@@ -3778,7 +3778,7 @@
         </is>
       </c>
       <c r="E110" s="20" t="n">
-        <v>167</v>
+        <v>211</v>
       </c>
     </row>
     <row r="111" ht="20" customHeight="1">
@@ -3803,7 +3803,7 @@
         </is>
       </c>
       <c r="E111" s="23" t="n">
-        <v>126</v>
+        <v>111</v>
       </c>
     </row>
     <row r="112" ht="20" customHeight="1">
@@ -3853,7 +3853,7 @@
         </is>
       </c>
       <c r="E113" s="23" t="n">
-        <v>134</v>
+        <v>194</v>
       </c>
     </row>
     <row r="114" ht="20" customHeight="1">
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="E114" s="20" t="n">
-        <v>208</v>
+        <v>190</v>
       </c>
     </row>
     <row r="115" ht="20" customHeight="1">
@@ -3903,7 +3903,7 @@
         </is>
       </c>
       <c r="E115" s="23" t="n">
-        <v>205</v>
+        <v>114</v>
       </c>
     </row>
     <row r="116" ht="20" customHeight="1">
@@ -3928,7 +3928,7 @@
         </is>
       </c>
       <c r="E116" s="20" t="n">
-        <v>198</v>
+        <v>121</v>
       </c>
     </row>
     <row r="117" ht="20" customHeight="1">
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="E117" s="23" t="n">
-        <v>123</v>
+        <v>195</v>
       </c>
     </row>
     <row r="118" ht="20" customHeight="1">
@@ -3978,7 +3978,7 @@
         </is>
       </c>
       <c r="E118" s="20" t="n">
-        <v>223</v>
+        <v>238</v>
       </c>
     </row>
     <row r="119" ht="20" customHeight="1">
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="E119" s="23" t="n">
-        <v>138</v>
+        <v>119</v>
       </c>
     </row>
     <row r="120" ht="20" customHeight="1">
@@ -4028,7 +4028,7 @@
         </is>
       </c>
       <c r="E120" s="20" t="n">
-        <v>150</v>
+        <v>118</v>
       </c>
     </row>
     <row r="121" ht="20" customHeight="1">
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="E121" s="23" t="n">
-        <v>227</v>
+        <v>222</v>
       </c>
     </row>
     <row r="122" ht="20" customHeight="1">
@@ -4078,7 +4078,7 @@
         </is>
       </c>
       <c r="E122" s="20" t="n">
-        <v>232</v>
+        <v>171</v>
       </c>
     </row>
     <row r="123" ht="20" customHeight="1">
@@ -4103,7 +4103,7 @@
         </is>
       </c>
       <c r="E123" s="23" t="n">
-        <v>160</v>
+        <v>199</v>
       </c>
     </row>
     <row r="124" ht="20" customHeight="1">
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="E124" s="20" t="n">
-        <v>181</v>
+        <v>114</v>
       </c>
     </row>
     <row r="125" ht="20" customHeight="1">
@@ -4153,7 +4153,7 @@
         </is>
       </c>
       <c r="E125" s="23" t="n">
-        <v>154</v>
+        <v>182</v>
       </c>
     </row>
     <row r="126" ht="20" customHeight="1">
@@ -4178,7 +4178,7 @@
         </is>
       </c>
       <c r="E126" s="20" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="127" ht="20" customHeight="1">
@@ -4203,7 +4203,7 @@
         </is>
       </c>
       <c r="E127" s="23" t="n">
-        <v>164</v>
+        <v>219</v>
       </c>
     </row>
     <row r="128" ht="20" customHeight="1">
@@ -4228,7 +4228,7 @@
         </is>
       </c>
       <c r="E128" s="20" t="n">
-        <v>240</v>
+        <v>220</v>
       </c>
     </row>
     <row r="129" ht="20" customHeight="1">
@@ -4253,7 +4253,7 @@
         </is>
       </c>
       <c r="E129" s="23" t="n">
-        <v>174</v>
+        <v>210</v>
       </c>
     </row>
     <row r="130" ht="20" customHeight="1">
@@ -4278,7 +4278,7 @@
         </is>
       </c>
       <c r="E130" s="20" t="n">
-        <v>207</v>
+        <v>197</v>
       </c>
     </row>
     <row r="131" ht="20" customHeight="1">
@@ -4303,7 +4303,7 @@
         </is>
       </c>
       <c r="E131" s="23" t="n">
-        <v>161</v>
+        <v>236</v>
       </c>
     </row>
     <row r="132" ht="20" customHeight="1">
@@ -4328,7 +4328,7 @@
         </is>
       </c>
       <c r="E132" s="20" t="n">
-        <v>197</v>
+        <v>115</v>
       </c>
     </row>
     <row r="133" ht="20" customHeight="1">
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="E133" s="23" t="n">
-        <v>183</v>
+        <v>113</v>
       </c>
     </row>
     <row r="134" ht="20" customHeight="1">
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="E134" s="20" t="n">
-        <v>208</v>
+        <v>115</v>
       </c>
     </row>
     <row r="135" ht="20" customHeight="1">
@@ -4403,7 +4403,7 @@
         </is>
       </c>
       <c r="E135" s="23" t="n">
-        <v>150</v>
+        <v>233</v>
       </c>
     </row>
     <row r="136" ht="20" customHeight="1">
@@ -4428,7 +4428,7 @@
         </is>
       </c>
       <c r="E136" s="20" t="n">
-        <v>232</v>
+        <v>227</v>
       </c>
     </row>
     <row r="137" ht="20" customHeight="1">
@@ -4453,7 +4453,7 @@
         </is>
       </c>
       <c r="E137" s="23" t="n">
-        <v>122</v>
+        <v>181</v>
       </c>
     </row>
     <row r="138" ht="20" customHeight="1">
@@ -4478,7 +4478,7 @@
         </is>
       </c>
       <c r="E138" s="20" t="n">
-        <v>211</v>
+        <v>232</v>
       </c>
     </row>
     <row r="139" ht="20" customHeight="1">
@@ -4503,7 +4503,7 @@
         </is>
       </c>
       <c r="E139" s="23" t="n">
-        <v>119</v>
+        <v>221</v>
       </c>
     </row>
     <row r="140" ht="20" customHeight="1">
@@ -4528,7 +4528,7 @@
         </is>
       </c>
       <c r="E140" s="20" t="n">
-        <v>123</v>
+        <v>174</v>
       </c>
     </row>
     <row r="141" ht="20" customHeight="1">
@@ -4553,7 +4553,7 @@
         </is>
       </c>
       <c r="E141" s="23" t="n">
-        <v>183</v>
+        <v>132</v>
       </c>
     </row>
     <row r="142" ht="20" customHeight="1">
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="E142" s="20" t="n">
-        <v>200</v>
+        <v>159</v>
       </c>
     </row>
     <row r="143" ht="20" customHeight="1">
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="E143" s="23" t="n">
-        <v>194</v>
+        <v>151</v>
       </c>
     </row>
     <row r="144" ht="20" customHeight="1">
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="E144" s="20" t="n">
-        <v>186</v>
+        <v>152</v>
       </c>
     </row>
     <row r="145" ht="20" customHeight="1">
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="E145" s="23" t="n">
-        <v>205</v>
+        <v>196</v>
       </c>
     </row>
     <row r="146" ht="20" customHeight="1">
@@ -4678,7 +4678,7 @@
         </is>
       </c>
       <c r="E146" s="20" t="n">
-        <v>199</v>
+        <v>160</v>
       </c>
     </row>
     <row r="147" ht="20" customHeight="1">
@@ -4703,7 +4703,7 @@
         </is>
       </c>
       <c r="E147" s="23" t="n">
-        <v>211</v>
+        <v>201</v>
       </c>
     </row>
     <row r="148" ht="20" customHeight="1">
@@ -4728,7 +4728,7 @@
         </is>
       </c>
       <c r="E148" s="20" t="n">
-        <v>137</v>
+        <v>181</v>
       </c>
     </row>
     <row r="149" ht="20" customHeight="1">
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c r="E149" s="23" t="n">
-        <v>176</v>
+        <v>111</v>
       </c>
     </row>
     <row r="150" ht="20" customHeight="1">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="E150" s="20" t="n">
-        <v>177</v>
+        <v>202</v>
       </c>
     </row>
     <row r="151" ht="20" customHeight="1">
@@ -4803,7 +4803,7 @@
         </is>
       </c>
       <c r="E151" s="23" t="n">
-        <v>217</v>
+        <v>161</v>
       </c>
     </row>
     <row r="152" ht="20" customHeight="1">
@@ -4828,7 +4828,7 @@
         </is>
       </c>
       <c r="E152" s="20" t="n">
-        <v>114</v>
+        <v>188</v>
       </c>
     </row>
     <row r="153" ht="20" customHeight="1">
@@ -4853,7 +4853,7 @@
         </is>
       </c>
       <c r="E153" s="23" t="n">
-        <v>185</v>
+        <v>169</v>
       </c>
     </row>
     <row r="154" ht="20" customHeight="1">
@@ -4878,7 +4878,7 @@
         </is>
       </c>
       <c r="E154" s="20" t="n">
-        <v>112</v>
+        <v>161</v>
       </c>
     </row>
     <row r="155" ht="20" customHeight="1">
@@ -4903,7 +4903,7 @@
         </is>
       </c>
       <c r="E155" s="23" t="n">
-        <v>158</v>
+        <v>148</v>
       </c>
     </row>
     <row r="156" ht="20" customHeight="1">
@@ -4928,7 +4928,7 @@
         </is>
       </c>
       <c r="E156" s="20" t="n">
-        <v>129</v>
+        <v>178</v>
       </c>
     </row>
     <row r="157" ht="20" customHeight="1">
@@ -4953,7 +4953,7 @@
         </is>
       </c>
       <c r="E157" s="23" t="n">
-        <v>121</v>
+        <v>110</v>
       </c>
     </row>
     <row r="158" ht="20" customHeight="1">
@@ -4978,7 +4978,7 @@
         </is>
       </c>
       <c r="E158" s="20" t="n">
-        <v>134</v>
+        <v>200</v>
       </c>
     </row>
     <row r="159" ht="20" customHeight="1">
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="E159" s="23" t="n">
-        <v>132</v>
+        <v>192</v>
       </c>
     </row>
     <row r="160" ht="20" customHeight="1">
@@ -5028,7 +5028,7 @@
         </is>
       </c>
       <c r="E160" s="20" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="161" ht="20" customHeight="1">
@@ -5053,7 +5053,7 @@
         </is>
       </c>
       <c r="E161" s="23" t="n">
-        <v>120</v>
+        <v>175</v>
       </c>
     </row>
     <row r="162" ht="20" customHeight="1">
@@ -5078,7 +5078,7 @@
         </is>
       </c>
       <c r="E162" s="20" t="n">
-        <v>128</v>
+        <v>156</v>
       </c>
     </row>
     <row r="163" ht="20" customHeight="1">
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="E163" s="23" t="n">
-        <v>144</v>
+        <v>176</v>
       </c>
     </row>
     <row r="164" ht="20" customHeight="1">
@@ -5128,7 +5128,7 @@
         </is>
       </c>
       <c r="E164" s="20" t="n">
-        <v>207</v>
+        <v>129</v>
       </c>
     </row>
     <row r="165" ht="20" customHeight="1">
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="E165" s="23" t="n">
-        <v>238</v>
+        <v>137</v>
       </c>
     </row>
     <row r="166" ht="20" customHeight="1">
@@ -5178,7 +5178,7 @@
         </is>
       </c>
       <c r="E166" s="20" t="n">
-        <v>185</v>
+        <v>160</v>
       </c>
     </row>
     <row r="167" ht="20" customHeight="1">
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="E167" s="23" t="n">
-        <v>163</v>
+        <v>200</v>
       </c>
     </row>
     <row r="168" ht="20" customHeight="1">
@@ -5228,7 +5228,7 @@
         </is>
       </c>
       <c r="E168" s="20" t="n">
-        <v>232</v>
+        <v>162</v>
       </c>
     </row>
     <row r="169" ht="20" customHeight="1">
@@ -5253,7 +5253,7 @@
         </is>
       </c>
       <c r="E169" s="23" t="n">
-        <v>185</v>
+        <v>232</v>
       </c>
     </row>
     <row r="170" ht="20" customHeight="1">
@@ -5278,7 +5278,7 @@
         </is>
       </c>
       <c r="E170" s="20" t="n">
-        <v>143</v>
+        <v>194</v>
       </c>
     </row>
     <row r="171" ht="20" customHeight="1">
@@ -5303,7 +5303,7 @@
         </is>
       </c>
       <c r="E171" s="23" t="n">
-        <v>138</v>
+        <v>213</v>
       </c>
     </row>
     <row r="172" ht="20" customHeight="1">
@@ -5328,7 +5328,7 @@
         </is>
       </c>
       <c r="E172" s="20" t="n">
-        <v>153</v>
+        <v>178</v>
       </c>
     </row>
     <row r="173" ht="20" customHeight="1">
@@ -5353,7 +5353,7 @@
         </is>
       </c>
       <c r="E173" s="23" t="n">
-        <v>174</v>
+        <v>140</v>
       </c>
     </row>
     <row r="174" ht="20" customHeight="1">
@@ -5378,7 +5378,7 @@
         </is>
       </c>
       <c r="E174" s="20" t="n">
-        <v>217</v>
+        <v>127</v>
       </c>
     </row>
     <row r="175" ht="20" customHeight="1">
@@ -5403,7 +5403,7 @@
         </is>
       </c>
       <c r="E175" s="23" t="n">
-        <v>136</v>
+        <v>142</v>
       </c>
     </row>
     <row r="176" ht="20" customHeight="1">
@@ -5428,7 +5428,7 @@
         </is>
       </c>
       <c r="E176" s="20" t="n">
-        <v>152</v>
+        <v>130</v>
       </c>
     </row>
     <row r="177" ht="20" customHeight="1">
@@ -5453,7 +5453,7 @@
         </is>
       </c>
       <c r="E177" s="23" t="n">
-        <v>183</v>
+        <v>228</v>
       </c>
     </row>
     <row r="178" ht="20" customHeight="1">
@@ -5478,7 +5478,7 @@
         </is>
       </c>
       <c r="E178" s="20" t="n">
-        <v>145</v>
+        <v>223</v>
       </c>
     </row>
     <row r="179" ht="20" customHeight="1">
@@ -5503,7 +5503,7 @@
         </is>
       </c>
       <c r="E179" s="23" t="n">
-        <v>152</v>
+        <v>221</v>
       </c>
     </row>
     <row r="180" ht="20" customHeight="1">
@@ -5528,7 +5528,7 @@
         </is>
       </c>
       <c r="E180" s="20" t="n">
-        <v>162</v>
+        <v>128</v>
       </c>
     </row>
     <row r="181" ht="20" customHeight="1">
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="E181" s="23" t="n">
-        <v>136</v>
+        <v>164</v>
       </c>
     </row>
     <row r="182" ht="20" customHeight="1">
@@ -5578,7 +5578,7 @@
         </is>
       </c>
       <c r="E182" s="20" t="n">
-        <v>132</v>
+        <v>213</v>
       </c>
     </row>
     <row r="183" ht="20" customHeight="1">
@@ -5603,7 +5603,7 @@
         </is>
       </c>
       <c r="E183" s="23" t="n">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="184" ht="20" customHeight="1">
@@ -5628,7 +5628,7 @@
         </is>
       </c>
       <c r="E184" s="20" t="n">
-        <v>198</v>
+        <v>193</v>
       </c>
     </row>
     <row r="185" ht="20" customHeight="1">
@@ -5678,7 +5678,7 @@
         </is>
       </c>
       <c r="E186" s="20" t="n">
-        <v>204</v>
+        <v>138</v>
       </c>
     </row>
     <row r="187" ht="20" customHeight="1">
@@ -5703,7 +5703,7 @@
         </is>
       </c>
       <c r="E187" s="23" t="n">
-        <v>195</v>
+        <v>233</v>
       </c>
     </row>
     <row r="188" ht="20" customHeight="1">
@@ -5728,7 +5728,7 @@
         </is>
       </c>
       <c r="E188" s="20" t="n">
-        <v>117</v>
+        <v>168</v>
       </c>
     </row>
     <row r="189" ht="20" customHeight="1">
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="E189" s="23" t="n">
-        <v>113</v>
+        <v>218</v>
       </c>
     </row>
     <row r="190" ht="20" customHeight="1">
@@ -5778,7 +5778,7 @@
         </is>
       </c>
       <c r="E190" s="20" t="n">
-        <v>223</v>
+        <v>163</v>
       </c>
     </row>
     <row r="191" ht="20" customHeight="1">
@@ -5803,7 +5803,7 @@
         </is>
       </c>
       <c r="E191" s="23" t="n">
-        <v>203</v>
+        <v>210</v>
       </c>
     </row>
     <row r="192" ht="20" customHeight="1">
@@ -5828,7 +5828,7 @@
         </is>
       </c>
       <c r="E192" s="20" t="n">
-        <v>170</v>
+        <v>137</v>
       </c>
     </row>
     <row r="193" ht="20" customHeight="1">
@@ -5853,7 +5853,7 @@
         </is>
       </c>
       <c r="E193" s="23" t="n">
-        <v>134</v>
+        <v>112</v>
       </c>
     </row>
     <row r="194" ht="20" customHeight="1">
@@ -5878,7 +5878,7 @@
         </is>
       </c>
       <c r="E194" s="20" t="n">
-        <v>175</v>
+        <v>146</v>
       </c>
     </row>
     <row r="195" ht="20" customHeight="1">
@@ -5903,7 +5903,7 @@
         </is>
       </c>
       <c r="E195" s="23" t="n">
-        <v>216</v>
+        <v>189</v>
       </c>
     </row>
     <row r="196" ht="20" customHeight="1">
@@ -5928,7 +5928,7 @@
         </is>
       </c>
       <c r="E196" s="20" t="n">
-        <v>175</v>
+        <v>213</v>
       </c>
     </row>
     <row r="197" ht="20" customHeight="1">
@@ -5953,7 +5953,7 @@
         </is>
       </c>
       <c r="E197" s="23" t="n">
-        <v>147</v>
+        <v>203</v>
       </c>
     </row>
     <row r="198" ht="20" customHeight="1">
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="E198" s="20" t="n">
-        <v>220</v>
+        <v>167</v>
       </c>
     </row>
     <row r="199" ht="20" customHeight="1">
@@ -6003,7 +6003,7 @@
         </is>
       </c>
       <c r="E199" s="23" t="n">
-        <v>184</v>
+        <v>198</v>
       </c>
     </row>
     <row r="200" ht="20" customHeight="1">
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="E200" s="20" t="n">
-        <v>143</v>
+        <v>164</v>
       </c>
     </row>
     <row r="201" ht="20" customHeight="1">
@@ -6053,7 +6053,7 @@
         </is>
       </c>
       <c r="E201" s="23" t="n">
-        <v>224</v>
+        <v>172</v>
       </c>
     </row>
     <row r="202" ht="20" customHeight="1">
@@ -6078,7 +6078,7 @@
         </is>
       </c>
       <c r="E202" s="20" t="n">
-        <v>121</v>
+        <v>221</v>
       </c>
     </row>
     <row r="203" ht="20" customHeight="1">
@@ -6103,7 +6103,7 @@
         </is>
       </c>
       <c r="E203" s="23" t="n">
-        <v>134</v>
+        <v>234</v>
       </c>
     </row>
     <row r="204" ht="20" customHeight="1">
@@ -6128,7 +6128,7 @@
         </is>
       </c>
       <c r="E204" s="20" t="n">
-        <v>147</v>
+        <v>113</v>
       </c>
     </row>
     <row r="205" ht="20" customHeight="1">
@@ -6153,7 +6153,7 @@
         </is>
       </c>
       <c r="E205" s="23" t="n">
-        <v>112</v>
+        <v>208</v>
       </c>
     </row>
     <row r="206" ht="20" customHeight="1">
@@ -6178,7 +6178,7 @@
         </is>
       </c>
       <c r="E206" s="20" t="n">
-        <v>192</v>
+        <v>199</v>
       </c>
     </row>
     <row r="207" ht="20" customHeight="1">
@@ -6203,7 +6203,7 @@
         </is>
       </c>
       <c r="E207" s="23" t="n">
-        <v>183</v>
+        <v>216</v>
       </c>
     </row>
     <row r="208" ht="20" customHeight="1">
@@ -6228,7 +6228,7 @@
         </is>
       </c>
       <c r="E208" s="20" t="n">
-        <v>237</v>
+        <v>121</v>
       </c>
     </row>
     <row r="209" ht="20" customHeight="1">
@@ -6253,7 +6253,7 @@
         </is>
       </c>
       <c r="E209" s="23" t="n">
-        <v>168</v>
+        <v>230</v>
       </c>
     </row>
     <row r="210" ht="20" customHeight="1">
@@ -6278,7 +6278,7 @@
         </is>
       </c>
       <c r="E210" s="20" t="n">
-        <v>233</v>
+        <v>226</v>
       </c>
     </row>
     <row r="211" ht="20" customHeight="1">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="E211" s="23" t="n">
-        <v>151</v>
+        <v>227</v>
       </c>
     </row>
     <row r="212" ht="20" customHeight="1">
@@ -6328,7 +6328,7 @@
         </is>
       </c>
       <c r="E212" s="20" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="213" ht="20" customHeight="1">
@@ -6353,7 +6353,7 @@
         </is>
       </c>
       <c r="E213" s="23" t="n">
-        <v>204</v>
+        <v>199</v>
       </c>
     </row>
     <row r="214" ht="20" customHeight="1">
@@ -6378,7 +6378,7 @@
         </is>
       </c>
       <c r="E214" s="20" t="n">
-        <v>159</v>
+        <v>236</v>
       </c>
     </row>
     <row r="215" ht="20" customHeight="1">
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="E215" s="23" t="n">
-        <v>182</v>
+        <v>153</v>
       </c>
     </row>
     <row r="216" ht="20" customHeight="1">
@@ -6428,7 +6428,7 @@
         </is>
       </c>
       <c r="E216" s="20" t="n">
-        <v>218</v>
+        <v>196</v>
       </c>
     </row>
     <row r="217" ht="20" customHeight="1">
@@ -6453,7 +6453,7 @@
         </is>
       </c>
       <c r="E217" s="23" t="n">
-        <v>211</v>
+        <v>240</v>
       </c>
     </row>
     <row r="218" ht="20" customHeight="1">
@@ -6478,7 +6478,7 @@
         </is>
       </c>
       <c r="E218" s="20" t="n">
-        <v>148</v>
+        <v>204</v>
       </c>
     </row>
     <row r="219" ht="20" customHeight="1">
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="E219" s="23" t="n">
-        <v>143</v>
+        <v>203</v>
       </c>
     </row>
     <row r="220" ht="20" customHeight="1">
@@ -6528,7 +6528,7 @@
         </is>
       </c>
       <c r="E220" s="20" t="n">
-        <v>195</v>
+        <v>144</v>
       </c>
     </row>
     <row r="221" ht="20" customHeight="1">
@@ -6553,7 +6553,7 @@
         </is>
       </c>
       <c r="E221" s="23" t="n">
-        <v>171</v>
+        <v>224</v>
       </c>
     </row>
     <row r="222" ht="20" customHeight="1">
@@ -6578,7 +6578,7 @@
         </is>
       </c>
       <c r="E222" s="20" t="n">
-        <v>143</v>
+        <v>164</v>
       </c>
     </row>
     <row r="223" ht="20" customHeight="1">
@@ -6603,7 +6603,7 @@
         </is>
       </c>
       <c r="E223" s="23" t="n">
-        <v>112</v>
+        <v>132</v>
       </c>
     </row>
     <row r="224" ht="20" customHeight="1">
@@ -6628,7 +6628,7 @@
         </is>
       </c>
       <c r="E224" s="20" t="n">
-        <v>217</v>
+        <v>231</v>
       </c>
     </row>
     <row r="225" ht="20" customHeight="1">
@@ -6653,7 +6653,7 @@
         </is>
       </c>
       <c r="E225" s="23" t="n">
-        <v>191</v>
+        <v>122</v>
       </c>
     </row>
     <row r="226" ht="20" customHeight="1">
@@ -6678,7 +6678,7 @@
         </is>
       </c>
       <c r="E226" s="20" t="n">
-        <v>169</v>
+        <v>227</v>
       </c>
     </row>
     <row r="227" ht="20" customHeight="1">
@@ -6703,7 +6703,7 @@
         </is>
       </c>
       <c r="E227" s="23" t="n">
-        <v>148</v>
+        <v>121</v>
       </c>
     </row>
     <row r="228" ht="20" customHeight="1">
@@ -6728,7 +6728,7 @@
         </is>
       </c>
       <c r="E228" s="20" t="n">
-        <v>157</v>
+        <v>178</v>
       </c>
     </row>
     <row r="229" ht="20" customHeight="1">
@@ -6753,7 +6753,7 @@
         </is>
       </c>
       <c r="E229" s="23" t="n">
-        <v>152</v>
+        <v>220</v>
       </c>
     </row>
     <row r="230" ht="20" customHeight="1">
@@ -6778,7 +6778,7 @@
         </is>
       </c>
       <c r="E230" s="20" t="n">
-        <v>201</v>
+        <v>196</v>
       </c>
     </row>
     <row r="231" ht="20" customHeight="1">
@@ -6803,7 +6803,7 @@
         </is>
       </c>
       <c r="E231" s="23" t="n">
-        <v>214</v>
+        <v>239</v>
       </c>
     </row>
     <row r="232" ht="20" customHeight="1">
@@ -6828,7 +6828,7 @@
         </is>
       </c>
       <c r="E232" s="20" t="n">
-        <v>215</v>
+        <v>133</v>
       </c>
     </row>
     <row r="233" ht="20" customHeight="1">
@@ -6853,7 +6853,7 @@
         </is>
       </c>
       <c r="E233" s="23" t="n">
-        <v>182</v>
+        <v>128</v>
       </c>
     </row>
     <row r="234" ht="20" customHeight="1">
@@ -6878,7 +6878,7 @@
         </is>
       </c>
       <c r="E234" s="20" t="n">
-        <v>206</v>
+        <v>196</v>
       </c>
     </row>
     <row r="235" ht="20" customHeight="1">
@@ -6903,7 +6903,7 @@
         </is>
       </c>
       <c r="E235" s="23" t="n">
-        <v>127</v>
+        <v>235</v>
       </c>
     </row>
     <row r="236" ht="20" customHeight="1">
@@ -6928,7 +6928,7 @@
         </is>
       </c>
       <c r="E236" s="20" t="n">
-        <v>169</v>
+        <v>130</v>
       </c>
     </row>
     <row r="237" ht="20" customHeight="1">
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="E237" s="23" t="n">
-        <v>182</v>
+        <v>146</v>
       </c>
     </row>
     <row r="238" ht="20" customHeight="1">
@@ -6978,7 +6978,7 @@
         </is>
       </c>
       <c r="E238" s="20" t="n">
-        <v>223</v>
+        <v>235</v>
       </c>
     </row>
     <row r="239" ht="20" customHeight="1">
@@ -7003,7 +7003,7 @@
         </is>
       </c>
       <c r="E239" s="23" t="n">
-        <v>147</v>
+        <v>138</v>
       </c>
     </row>
     <row r="240" ht="20" customHeight="1">
@@ -7028,7 +7028,7 @@
         </is>
       </c>
       <c r="E240" s="20" t="n">
-        <v>134</v>
+        <v>192</v>
       </c>
     </row>
     <row r="241" ht="20" customHeight="1">
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="E241" s="23" t="n">
-        <v>165</v>
+        <v>225</v>
       </c>
     </row>
     <row r="242" ht="20" customHeight="1">
@@ -7078,7 +7078,7 @@
         </is>
       </c>
       <c r="E242" s="20" t="n">
-        <v>203</v>
+        <v>227</v>
       </c>
     </row>
     <row r="243" ht="20" customHeight="1">
@@ -7103,7 +7103,7 @@
         </is>
       </c>
       <c r="E243" s="23" t="n">
-        <v>205</v>
+        <v>150</v>
       </c>
     </row>
     <row r="244" ht="20" customHeight="1">
@@ -7128,7 +7128,7 @@
         </is>
       </c>
       <c r="E244" s="20" t="n">
-        <v>131</v>
+        <v>197</v>
       </c>
     </row>
     <row r="245" ht="20" customHeight="1">
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="E245" s="23" t="n">
-        <v>156</v>
+        <v>116</v>
       </c>
     </row>
     <row r="246" ht="20" customHeight="1">
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="E246" s="20" t="n">
-        <v>181</v>
+        <v>200</v>
       </c>
     </row>
     <row r="247" ht="20" customHeight="1">
@@ -7203,7 +7203,7 @@
         </is>
       </c>
       <c r="E247" s="23" t="n">
-        <v>239</v>
+        <v>131</v>
       </c>
     </row>
     <row r="248" ht="20" customHeight="1">
@@ -7228,7 +7228,7 @@
         </is>
       </c>
       <c r="E248" s="20" t="n">
-        <v>127</v>
+        <v>134</v>
       </c>
     </row>
     <row r="249" ht="20" customHeight="1">
@@ -7253,7 +7253,7 @@
         </is>
       </c>
       <c r="E249" s="23" t="n">
-        <v>175</v>
+        <v>117</v>
       </c>
     </row>
     <row r="250" ht="20" customHeight="1">
@@ -7278,7 +7278,7 @@
         </is>
       </c>
       <c r="E250" s="20" t="n">
-        <v>136</v>
+        <v>145</v>
       </c>
     </row>
     <row r="251" ht="20" customHeight="1">
@@ -7303,7 +7303,7 @@
         </is>
       </c>
       <c r="E251" s="23" t="n">
-        <v>121</v>
+        <v>187</v>
       </c>
     </row>
     <row r="252" ht="20" customHeight="1">
@@ -7328,7 +7328,7 @@
         </is>
       </c>
       <c r="E252" s="20" t="n">
-        <v>154</v>
+        <v>195</v>
       </c>
     </row>
     <row r="253" ht="20" customHeight="1">
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="E253" s="23" t="n">
-        <v>110</v>
+        <v>183</v>
       </c>
     </row>
     <row r="254" ht="20" customHeight="1">
@@ -7378,7 +7378,7 @@
         </is>
       </c>
       <c r="E254" s="20" t="n">
-        <v>210</v>
+        <v>141</v>
       </c>
     </row>
     <row r="255" ht="20" customHeight="1">
@@ -7403,7 +7403,7 @@
         </is>
       </c>
       <c r="E255" s="23" t="n">
-        <v>179</v>
+        <v>202</v>
       </c>
     </row>
     <row r="256" ht="20" customHeight="1">
@@ -7428,7 +7428,7 @@
         </is>
       </c>
       <c r="E256" s="20" t="n">
-        <v>226</v>
+        <v>202</v>
       </c>
     </row>
     <row r="257" ht="20" customHeight="1">
@@ -7453,7 +7453,7 @@
         </is>
       </c>
       <c r="E257" s="23" t="n">
-        <v>145</v>
+        <v>184</v>
       </c>
     </row>
     <row r="258" ht="20" customHeight="1">
@@ -7478,7 +7478,7 @@
         </is>
       </c>
       <c r="E258" s="20" t="n">
-        <v>210</v>
+        <v>158</v>
       </c>
     </row>
     <row r="259" ht="20" customHeight="1">
@@ -7503,7 +7503,7 @@
         </is>
       </c>
       <c r="E259" s="23" t="n">
-        <v>138</v>
+        <v>124</v>
       </c>
     </row>
     <row r="260" ht="20" customHeight="1">
@@ -7528,7 +7528,7 @@
         </is>
       </c>
       <c r="E260" s="20" t="n">
-        <v>198</v>
+        <v>194</v>
       </c>
     </row>
     <row r="261" ht="20" customHeight="1">
@@ -7553,7 +7553,7 @@
         </is>
       </c>
       <c r="E261" s="23" t="n">
-        <v>127</v>
+        <v>208</v>
       </c>
     </row>
     <row r="262" ht="20" customHeight="1">
@@ -7578,7 +7578,7 @@
         </is>
       </c>
       <c r="E262" s="20" t="n">
-        <v>113</v>
+        <v>125</v>
       </c>
     </row>
     <row r="263" ht="20" customHeight="1">
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="E263" s="23" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="264" ht="20" customHeight="1">
@@ -7628,7 +7628,7 @@
         </is>
       </c>
       <c r="E264" s="20" t="n">
-        <v>197</v>
+        <v>160</v>
       </c>
     </row>
     <row r="265" ht="20" customHeight="1">
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="E265" s="23" t="n">
-        <v>194</v>
+        <v>233</v>
       </c>
     </row>
     <row r="266" ht="20" customHeight="1">
@@ -7678,7 +7678,7 @@
         </is>
       </c>
       <c r="E266" s="20" t="n">
-        <v>227</v>
+        <v>154</v>
       </c>
     </row>
     <row r="267" ht="20" customHeight="1">
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="E267" s="23" t="n">
-        <v>151</v>
+        <v>229</v>
       </c>
     </row>
     <row r="268" ht="20" customHeight="1">
@@ -7728,7 +7728,7 @@
         </is>
       </c>
       <c r="E268" s="20" t="n">
-        <v>137</v>
+        <v>216</v>
       </c>
     </row>
     <row r="269" ht="20" customHeight="1">
@@ -7753,7 +7753,7 @@
         </is>
       </c>
       <c r="E269" s="23" t="n">
-        <v>162</v>
+        <v>114</v>
       </c>
     </row>
     <row r="270" ht="20" customHeight="1">
@@ -7778,7 +7778,7 @@
         </is>
       </c>
       <c r="E270" s="20" t="n">
-        <v>138</v>
+        <v>162</v>
       </c>
     </row>
     <row r="271" ht="20" customHeight="1">
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="E271" s="23" t="n">
-        <v>162</v>
+        <v>228</v>
       </c>
     </row>
     <row r="272" ht="20" customHeight="1">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="E272" s="20" t="n">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="273" ht="20" customHeight="1">
@@ -7853,7 +7853,7 @@
         </is>
       </c>
       <c r="E273" s="23" t="n">
-        <v>139</v>
+        <v>111</v>
       </c>
     </row>
     <row r="274" ht="20" customHeight="1">
@@ -7878,7 +7878,7 @@
         </is>
       </c>
       <c r="E274" s="20" t="n">
-        <v>227</v>
+        <v>117</v>
       </c>
     </row>
     <row r="275" ht="20" customHeight="1">
@@ -7903,7 +7903,7 @@
         </is>
       </c>
       <c r="E275" s="23" t="n">
-        <v>160</v>
+        <v>132</v>
       </c>
     </row>
     <row r="276" ht="20" customHeight="1">
@@ -7928,7 +7928,7 @@
         </is>
       </c>
       <c r="E276" s="20" t="n">
-        <v>187</v>
+        <v>114</v>
       </c>
     </row>
     <row r="277" ht="20" customHeight="1">
@@ -7953,7 +7953,7 @@
         </is>
       </c>
       <c r="E277" s="23" t="n">
-        <v>231</v>
+        <v>143</v>
       </c>
     </row>
     <row r="278" ht="20" customHeight="1">
@@ -7978,7 +7978,7 @@
         </is>
       </c>
       <c r="E278" s="20" t="n">
-        <v>147</v>
+        <v>110</v>
       </c>
     </row>
     <row r="279" ht="20" customHeight="1">
@@ -8003,7 +8003,7 @@
         </is>
       </c>
       <c r="E279" s="23" t="n">
-        <v>122</v>
+        <v>177</v>
       </c>
     </row>
     <row r="280" ht="20" customHeight="1">
@@ -8028,7 +8028,7 @@
         </is>
       </c>
       <c r="E280" s="20" t="n">
-        <v>193</v>
+        <v>207</v>
       </c>
     </row>
     <row r="281" ht="20" customHeight="1">
@@ -8053,7 +8053,7 @@
         </is>
       </c>
       <c r="E281" s="23" t="n">
-        <v>127</v>
+        <v>208</v>
       </c>
     </row>
     <row r="282" ht="20" customHeight="1">
@@ -8078,7 +8078,7 @@
         </is>
       </c>
       <c r="E282" s="20" t="n">
-        <v>223</v>
+        <v>125</v>
       </c>
     </row>
     <row r="283" ht="20" customHeight="1">
@@ -8103,7 +8103,7 @@
         </is>
       </c>
       <c r="E283" s="23" t="n">
-        <v>198</v>
+        <v>170</v>
       </c>
     </row>
     <row r="284" ht="20" customHeight="1">
@@ -8128,7 +8128,7 @@
         </is>
       </c>
       <c r="E284" s="20" t="n">
-        <v>117</v>
+        <v>164</v>
       </c>
     </row>
     <row r="285" ht="20" customHeight="1">
@@ -8153,7 +8153,7 @@
         </is>
       </c>
       <c r="E285" s="23" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="286" ht="20" customHeight="1">
@@ -8178,7 +8178,7 @@
         </is>
       </c>
       <c r="E286" s="20" t="n">
-        <v>129</v>
+        <v>204</v>
       </c>
     </row>
     <row r="287" ht="20" customHeight="1">
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="E287" s="23" t="n">
-        <v>177</v>
+        <v>203</v>
       </c>
     </row>
     <row r="288" ht="20" customHeight="1">
@@ -8228,7 +8228,7 @@
         </is>
       </c>
       <c r="E288" s="20" t="n">
-        <v>202</v>
+        <v>164</v>
       </c>
     </row>
     <row r="289" ht="20" customHeight="1">
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="E289" s="23" t="n">
-        <v>207</v>
+        <v>222</v>
       </c>
     </row>
     <row r="290" ht="20" customHeight="1">
@@ -8278,7 +8278,7 @@
         </is>
       </c>
       <c r="E290" s="20" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="291" ht="20" customHeight="1">
@@ -8303,7 +8303,7 @@
         </is>
       </c>
       <c r="E291" s="23" t="n">
-        <v>230</v>
+        <v>205</v>
       </c>
     </row>
     <row r="292" ht="20" customHeight="1">
@@ -8328,7 +8328,7 @@
         </is>
       </c>
       <c r="E292" s="20" t="n">
-        <v>135</v>
+        <v>167</v>
       </c>
     </row>
     <row r="293" ht="20" customHeight="1">
@@ -8353,7 +8353,7 @@
         </is>
       </c>
       <c r="E293" s="23" t="n">
-        <v>207</v>
+        <v>235</v>
       </c>
     </row>
     <row r="294" ht="20" customHeight="1">
@@ -8378,7 +8378,7 @@
         </is>
       </c>
       <c r="E294" s="20" t="n">
-        <v>152</v>
+        <v>199</v>
       </c>
     </row>
     <row r="295" ht="20" customHeight="1">
@@ -8403,7 +8403,7 @@
         </is>
       </c>
       <c r="E295" s="23" t="n">
-        <v>208</v>
+        <v>212</v>
       </c>
     </row>
     <row r="296" ht="20" customHeight="1">
@@ -8428,7 +8428,7 @@
         </is>
       </c>
       <c r="E296" s="20" t="n">
-        <v>240</v>
+        <v>120</v>
       </c>
     </row>
     <row r="297" ht="20" customHeight="1">
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="E297" s="23" t="n">
-        <v>142</v>
+        <v>158</v>
       </c>
     </row>
     <row r="298" ht="20" customHeight="1">
@@ -8478,7 +8478,7 @@
         </is>
       </c>
       <c r="E298" s="20" t="n">
-        <v>168</v>
+        <v>227</v>
       </c>
     </row>
     <row r="299" ht="20" customHeight="1">
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="E299" s="23" t="n">
-        <v>160</v>
+        <v>222</v>
       </c>
     </row>
     <row r="300" ht="20" customHeight="1">
@@ -8528,7 +8528,7 @@
         </is>
       </c>
       <c r="E300" s="20" t="n">
-        <v>158</v>
+        <v>221</v>
       </c>
     </row>
     <row r="301" ht="20" customHeight="1">
@@ -8553,7 +8553,7 @@
         </is>
       </c>
       <c r="E301" s="23" t="n">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="302" ht="20" customHeight="1">
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="E302" s="20" t="n">
-        <v>182</v>
+        <v>220</v>
       </c>
     </row>
     <row r="303" ht="20" customHeight="1">
@@ -8603,7 +8603,7 @@
         </is>
       </c>
       <c r="E303" s="23" t="n">
-        <v>136</v>
+        <v>173</v>
       </c>
     </row>
     <row r="304" ht="20" customHeight="1">
@@ -8628,7 +8628,7 @@
         </is>
       </c>
       <c r="E304" s="20" t="n">
-        <v>162</v>
+        <v>111</v>
       </c>
     </row>
     <row r="305" ht="20" customHeight="1">
@@ -8653,7 +8653,7 @@
         </is>
       </c>
       <c r="E305" s="23" t="n">
-        <v>220</v>
+        <v>160</v>
       </c>
     </row>
     <row r="306" ht="20" customHeight="1">
@@ -8678,7 +8678,7 @@
         </is>
       </c>
       <c r="E306" s="20" t="n">
-        <v>194</v>
+        <v>112</v>
       </c>
     </row>
     <row r="307" ht="20" customHeight="1">
@@ -8703,7 +8703,7 @@
         </is>
       </c>
       <c r="E307" s="23" t="n">
-        <v>194</v>
+        <v>219</v>
       </c>
     </row>
     <row r="308" ht="20" customHeight="1">
@@ -8728,7 +8728,7 @@
         </is>
       </c>
       <c r="E308" s="20" t="n">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="309" ht="20" customHeight="1">
@@ -8753,7 +8753,7 @@
         </is>
       </c>
       <c r="E309" s="23" t="n">
-        <v>207</v>
+        <v>235</v>
       </c>
     </row>
     <row r="310" ht="20" customHeight="1">
@@ -8778,7 +8778,7 @@
         </is>
       </c>
       <c r="E310" s="20" t="n">
-        <v>191</v>
+        <v>120</v>
       </c>
     </row>
     <row r="311" ht="20" customHeight="1">
@@ -8803,7 +8803,7 @@
         </is>
       </c>
       <c r="E311" s="23" t="n">
-        <v>214</v>
+        <v>167</v>
       </c>
     </row>
     <row r="312" ht="20" customHeight="1">
@@ -8828,7 +8828,7 @@
         </is>
       </c>
       <c r="E312" s="20" t="n">
-        <v>194</v>
+        <v>205</v>
       </c>
     </row>
     <row r="313" ht="20" customHeight="1">
@@ -8853,7 +8853,7 @@
         </is>
       </c>
       <c r="E313" s="23" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="314" ht="20" customHeight="1">
@@ -8878,7 +8878,7 @@
         </is>
       </c>
       <c r="E314" s="20" t="n">
-        <v>169</v>
+        <v>191</v>
       </c>
     </row>
     <row r="315" ht="20" customHeight="1">
@@ -8903,7 +8903,7 @@
         </is>
       </c>
       <c r="E315" s="23" t="n">
-        <v>227</v>
+        <v>125</v>
       </c>
     </row>
     <row r="316" ht="20" customHeight="1">
@@ -8928,7 +8928,7 @@
         </is>
       </c>
       <c r="E316" s="20" t="n">
-        <v>200</v>
+        <v>170</v>
       </c>
     </row>
     <row r="317" ht="20" customHeight="1">
@@ -8953,7 +8953,7 @@
         </is>
       </c>
       <c r="E317" s="23" t="n">
-        <v>112</v>
+        <v>193</v>
       </c>
     </row>
     <row r="318" ht="20" customHeight="1">
@@ -8978,7 +8978,7 @@
         </is>
       </c>
       <c r="E318" s="20" t="n">
-        <v>157</v>
+        <v>234</v>
       </c>
     </row>
     <row r="319" ht="20" customHeight="1">
@@ -9003,7 +9003,7 @@
         </is>
       </c>
       <c r="E319" s="23" t="n">
-        <v>179</v>
+        <v>125</v>
       </c>
     </row>
     <row r="320" ht="20" customHeight="1">
@@ -9028,7 +9028,7 @@
         </is>
       </c>
       <c r="E320" s="20" t="n">
-        <v>126</v>
+        <v>143</v>
       </c>
     </row>
     <row r="321" ht="20" customHeight="1">
@@ -9053,7 +9053,7 @@
         </is>
       </c>
       <c r="E321" s="23" t="n">
-        <v>138</v>
+        <v>201</v>
       </c>
     </row>
     <row r="322" ht="20" customHeight="1">
@@ -9078,7 +9078,7 @@
         </is>
       </c>
       <c r="E322" s="20" t="n">
-        <v>173</v>
+        <v>139</v>
       </c>
     </row>
     <row r="323" ht="20" customHeight="1">
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="E323" s="23" t="n">
-        <v>133</v>
+        <v>230</v>
       </c>
     </row>
     <row r="324" ht="20" customHeight="1">
@@ -9128,7 +9128,7 @@
         </is>
       </c>
       <c r="E324" s="20" t="n">
-        <v>175</v>
+        <v>235</v>
       </c>
     </row>
     <row r="325" ht="20" customHeight="1">
@@ -9153,7 +9153,7 @@
         </is>
       </c>
       <c r="E325" s="23" t="n">
-        <v>195</v>
+        <v>238</v>
       </c>
     </row>
     <row r="326" ht="20" customHeight="1">
@@ -9178,7 +9178,7 @@
         </is>
       </c>
       <c r="E326" s="20" t="n">
-        <v>135</v>
+        <v>200</v>
       </c>
     </row>
     <row r="327" ht="20" customHeight="1">
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="E327" s="23" t="n">
-        <v>122</v>
+        <v>165</v>
       </c>
     </row>
     <row r="328" ht="20" customHeight="1">
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="E328" s="20" t="n">
-        <v>234</v>
+        <v>131</v>
       </c>
     </row>
     <row r="329" ht="20" customHeight="1">
@@ -9253,7 +9253,7 @@
         </is>
       </c>
       <c r="E329" s="23" t="n">
-        <v>196</v>
+        <v>110</v>
       </c>
     </row>
     <row r="330" ht="20" customHeight="1">
@@ -9278,7 +9278,7 @@
         </is>
       </c>
       <c r="E330" s="20" t="n">
-        <v>120</v>
+        <v>151</v>
       </c>
     </row>
     <row r="331" ht="20" customHeight="1">
@@ -9303,7 +9303,7 @@
         </is>
       </c>
       <c r="E331" s="23" t="n">
-        <v>188</v>
+        <v>171</v>
       </c>
     </row>
     <row r="332" ht="20" customHeight="1">
@@ -9328,7 +9328,7 @@
         </is>
       </c>
       <c r="E332" s="20" t="n">
-        <v>236</v>
+        <v>163</v>
       </c>
     </row>
     <row r="333" ht="20" customHeight="1">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="E333" s="23" t="n">
-        <v>144</v>
+        <v>153</v>
       </c>
     </row>
     <row r="334" ht="20" customHeight="1">
@@ -9378,7 +9378,7 @@
         </is>
       </c>
       <c r="E334" s="20" t="n">
-        <v>231</v>
+        <v>173</v>
       </c>
     </row>
     <row r="335" ht="20" customHeight="1">
@@ -9403,7 +9403,7 @@
         </is>
       </c>
       <c r="E335" s="23" t="n">
-        <v>175</v>
+        <v>232</v>
       </c>
     </row>
     <row r="336" ht="20" customHeight="1">
@@ -9428,7 +9428,7 @@
         </is>
       </c>
       <c r="E336" s="20" t="n">
-        <v>228</v>
+        <v>220</v>
       </c>
     </row>
     <row r="337" ht="20" customHeight="1">
@@ -9453,7 +9453,7 @@
         </is>
       </c>
       <c r="E337" s="23" t="n">
-        <v>229</v>
+        <v>128</v>
       </c>
     </row>
     <row r="338" ht="20" customHeight="1">
@@ -9478,7 +9478,7 @@
         </is>
       </c>
       <c r="E338" s="20" t="n">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="339" ht="20" customHeight="1">
@@ -9503,7 +9503,7 @@
         </is>
       </c>
       <c r="E339" s="23" t="n">
-        <v>143</v>
+        <v>152</v>
       </c>
     </row>
     <row r="340" ht="20" customHeight="1">
@@ -9528,7 +9528,7 @@
         </is>
       </c>
       <c r="E340" s="20" t="n">
-        <v>192</v>
+        <v>113</v>
       </c>
     </row>
     <row r="341" ht="20" customHeight="1">
@@ -9553,7 +9553,7 @@
         </is>
       </c>
       <c r="E341" s="23" t="n">
-        <v>172</v>
+        <v>119</v>
       </c>
     </row>
     <row r="342" ht="20" customHeight="1">
@@ -9578,7 +9578,7 @@
         </is>
       </c>
       <c r="E342" s="20" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="343" ht="20" customHeight="1">
@@ -9603,7 +9603,7 @@
         </is>
       </c>
       <c r="E343" s="23" t="n">
-        <v>181</v>
+        <v>158</v>
       </c>
     </row>
     <row r="344" ht="20" customHeight="1">
@@ -9628,7 +9628,7 @@
         </is>
       </c>
       <c r="E344" s="20" t="n">
-        <v>123</v>
+        <v>232</v>
       </c>
     </row>
     <row r="345" ht="20" customHeight="1">
@@ -9653,7 +9653,7 @@
         </is>
       </c>
       <c r="E345" s="23" t="n">
-        <v>231</v>
+        <v>191</v>
       </c>
     </row>
     <row r="346" ht="20" customHeight="1">
@@ -9678,7 +9678,7 @@
         </is>
       </c>
       <c r="E346" s="20" t="n">
-        <v>147</v>
+        <v>123</v>
       </c>
     </row>
     <row r="347" ht="20" customHeight="1">
@@ -9703,7 +9703,7 @@
         </is>
       </c>
       <c r="E347" s="23" t="n">
-        <v>172</v>
+        <v>183</v>
       </c>
     </row>
     <row r="348" ht="20" customHeight="1">
@@ -9728,7 +9728,7 @@
         </is>
       </c>
       <c r="E348" s="20" t="n">
-        <v>143</v>
+        <v>214</v>
       </c>
     </row>
     <row r="349" ht="20" customHeight="1">
@@ -9753,7 +9753,7 @@
         </is>
       </c>
       <c r="E349" s="23" t="n">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="350" ht="20" customHeight="1">
@@ -9778,7 +9778,7 @@
         </is>
       </c>
       <c r="E350" s="20" t="n">
-        <v>183</v>
+        <v>159</v>
       </c>
     </row>
     <row r="351" ht="20" customHeight="1">
@@ -9803,7 +9803,7 @@
         </is>
       </c>
       <c r="E351" s="23" t="n">
-        <v>115</v>
+        <v>231</v>
       </c>
     </row>
     <row r="352" ht="20" customHeight="1">
@@ -9828,7 +9828,7 @@
         </is>
       </c>
       <c r="E352" s="20" t="n">
-        <v>168</v>
+        <v>189</v>
       </c>
     </row>
     <row r="353" ht="20" customHeight="1">
@@ -9853,7 +9853,7 @@
         </is>
       </c>
       <c r="E353" s="23" t="n">
-        <v>170</v>
+        <v>115</v>
       </c>
     </row>
     <row r="354" ht="20" customHeight="1">
@@ -9878,7 +9878,7 @@
         </is>
       </c>
       <c r="E354" s="20" t="n">
-        <v>173</v>
+        <v>228</v>
       </c>
     </row>
     <row r="355" ht="20" customHeight="1">
@@ -9903,7 +9903,7 @@
         </is>
       </c>
       <c r="E355" s="23" t="n">
-        <v>130</v>
+        <v>115</v>
       </c>
     </row>
     <row r="356" ht="20" customHeight="1">
@@ -9928,7 +9928,7 @@
         </is>
       </c>
       <c r="E356" s="20" t="n">
-        <v>198</v>
+        <v>126</v>
       </c>
     </row>
     <row r="357" ht="20" customHeight="1">
@@ -9953,7 +9953,7 @@
         </is>
       </c>
       <c r="E357" s="23" t="n">
-        <v>191</v>
+        <v>223</v>
       </c>
     </row>
     <row r="358" ht="20" customHeight="1">
@@ -9978,7 +9978,7 @@
         </is>
       </c>
       <c r="E358" s="20" t="n">
-        <v>131</v>
+        <v>120</v>
       </c>
     </row>
     <row r="359" ht="20" customHeight="1">
@@ -10003,7 +10003,7 @@
         </is>
       </c>
       <c r="E359" s="23" t="n">
-        <v>143</v>
+        <v>194</v>
       </c>
     </row>
     <row r="360" ht="20" customHeight="1">
@@ -10028,7 +10028,7 @@
         </is>
       </c>
       <c r="E360" s="20" t="n">
-        <v>148</v>
+        <v>192</v>
       </c>
     </row>
     <row r="361" ht="20" customHeight="1">
@@ -10053,7 +10053,7 @@
         </is>
       </c>
       <c r="E361" s="23" t="n">
-        <v>221</v>
+        <v>172</v>
       </c>
     </row>
     <row r="362" ht="20" customHeight="1">
@@ -10078,7 +10078,7 @@
         </is>
       </c>
       <c r="E362" s="20" t="n">
-        <v>229</v>
+        <v>221</v>
       </c>
     </row>
     <row r="363" ht="20" customHeight="1">
@@ -10103,7 +10103,7 @@
         </is>
       </c>
       <c r="E363" s="23" t="n">
-        <v>169</v>
+        <v>184</v>
       </c>
     </row>
     <row r="364" ht="20" customHeight="1">
@@ -10128,7 +10128,7 @@
         </is>
       </c>
       <c r="E364" s="20" t="n">
-        <v>212</v>
+        <v>168</v>
       </c>
     </row>
     <row r="365" ht="20" customHeight="1">
@@ -10153,7 +10153,7 @@
         </is>
       </c>
       <c r="E365" s="23" t="n">
-        <v>118</v>
+        <v>136</v>
       </c>
     </row>
     <row r="366" ht="20" customHeight="1">
@@ -10178,7 +10178,7 @@
         </is>
       </c>
       <c r="E366" s="20" t="n">
-        <v>148</v>
+        <v>111</v>
       </c>
     </row>
     <row r="367" ht="20" customHeight="1">
@@ -10203,7 +10203,7 @@
         </is>
       </c>
       <c r="E367" s="23" t="n">
-        <v>209</v>
+        <v>216</v>
       </c>
     </row>
     <row r="368" ht="20" customHeight="1">
@@ -10228,7 +10228,7 @@
         </is>
       </c>
       <c r="E368" s="20" t="n">
-        <v>154</v>
+        <v>177</v>
       </c>
     </row>
     <row r="369" ht="20" customHeight="1">
@@ -10253,7 +10253,7 @@
         </is>
       </c>
       <c r="E369" s="23" t="n">
-        <v>205</v>
+        <v>218</v>
       </c>
     </row>
     <row r="370" ht="20" customHeight="1">
@@ -10278,7 +10278,7 @@
         </is>
       </c>
       <c r="E370" s="20" t="n">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="371" ht="20" customHeight="1">
@@ -10303,7 +10303,7 @@
         </is>
       </c>
       <c r="E371" s="23" t="n">
-        <v>112</v>
+        <v>198</v>
       </c>
     </row>
     <row r="372" ht="20" customHeight="1">
@@ -10328,7 +10328,7 @@
         </is>
       </c>
       <c r="E372" s="20" t="n">
-        <v>123</v>
+        <v>113</v>
       </c>
     </row>
     <row r="373" ht="20" customHeight="1">
@@ -10353,7 +10353,7 @@
         </is>
       </c>
       <c r="E373" s="23" t="n">
-        <v>130</v>
+        <v>204</v>
       </c>
     </row>
     <row r="374" ht="20" customHeight="1">
@@ -10378,7 +10378,7 @@
         </is>
       </c>
       <c r="E374" s="20" t="n">
-        <v>163</v>
+        <v>120</v>
       </c>
     </row>
     <row r="375" ht="20" customHeight="1">
@@ -10403,7 +10403,7 @@
         </is>
       </c>
       <c r="E375" s="23" t="n">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="376" ht="20" customHeight="1">
@@ -10428,7 +10428,7 @@
         </is>
       </c>
       <c r="E376" s="20" t="n">
-        <v>162</v>
+        <v>135</v>
       </c>
     </row>
     <row r="377" ht="20" customHeight="1">
@@ -10453,7 +10453,7 @@
         </is>
       </c>
       <c r="E377" s="23" t="n">
-        <v>122</v>
+        <v>177</v>
       </c>
     </row>
     <row r="378" ht="20" customHeight="1">
@@ -10478,7 +10478,7 @@
         </is>
       </c>
       <c r="E378" s="20" t="n">
-        <v>141</v>
+        <v>131</v>
       </c>
     </row>
     <row r="379" ht="20" customHeight="1">
@@ -10503,7 +10503,7 @@
         </is>
       </c>
       <c r="E379" s="23" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
     </row>
     <row r="380" ht="20" customHeight="1">
@@ -10528,7 +10528,7 @@
         </is>
       </c>
       <c r="E380" s="20" t="n">
-        <v>211</v>
+        <v>167</v>
       </c>
     </row>
     <row r="381" ht="20" customHeight="1">
@@ -10553,7 +10553,7 @@
         </is>
       </c>
       <c r="E381" s="23" t="n">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="382" ht="20" customHeight="1">
@@ -10578,7 +10578,7 @@
         </is>
       </c>
       <c r="E382" s="20" t="n">
-        <v>127</v>
+        <v>160</v>
       </c>
     </row>
     <row r="383" ht="20" customHeight="1">
@@ -10603,7 +10603,7 @@
         </is>
       </c>
       <c r="E383" s="23" t="n">
-        <v>187</v>
+        <v>130</v>
       </c>
     </row>
     <row r="384" ht="20" customHeight="1">
@@ -10628,7 +10628,7 @@
         </is>
       </c>
       <c r="E384" s="20" t="n">
-        <v>173</v>
+        <v>147</v>
       </c>
     </row>
     <row r="385" ht="20" customHeight="1">
@@ -10678,7 +10678,7 @@
         </is>
       </c>
       <c r="E386" s="20" t="n">
-        <v>187</v>
+        <v>116</v>
       </c>
     </row>
     <row r="387" ht="20" customHeight="1">
@@ -10703,7 +10703,7 @@
         </is>
       </c>
       <c r="E387" s="23" t="n">
-        <v>155</v>
+        <v>181</v>
       </c>
     </row>
     <row r="388" ht="20" customHeight="1">
@@ -10728,7 +10728,7 @@
         </is>
       </c>
       <c r="E388" s="20" t="n">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="389" ht="20" customHeight="1">
@@ -10753,7 +10753,7 @@
         </is>
       </c>
       <c r="E389" s="23" t="n">
-        <v>144</v>
+        <v>200</v>
       </c>
     </row>
     <row r="390" ht="20" customHeight="1">
@@ -10778,7 +10778,7 @@
         </is>
       </c>
       <c r="E390" s="20" t="n">
-        <v>225</v>
+        <v>118</v>
       </c>
     </row>
     <row r="391" ht="20" customHeight="1">
@@ -10803,7 +10803,7 @@
         </is>
       </c>
       <c r="E391" s="23" t="n">
-        <v>156</v>
+        <v>166</v>
       </c>
     </row>
     <row r="392" ht="20" customHeight="1">
@@ -10828,7 +10828,7 @@
         </is>
       </c>
       <c r="E392" s="20" t="n">
-        <v>178</v>
+        <v>112</v>
       </c>
     </row>
     <row r="393" ht="20" customHeight="1">
@@ -10853,7 +10853,7 @@
         </is>
       </c>
       <c r="E393" s="23" t="n">
-        <v>204</v>
+        <v>134</v>
       </c>
     </row>
     <row r="394" ht="20" customHeight="1">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="E394" s="20" t="n">
-        <v>188</v>
+        <v>221</v>
       </c>
     </row>
     <row r="395" ht="20" customHeight="1">
@@ -10903,7 +10903,7 @@
         </is>
       </c>
       <c r="E395" s="23" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="396" ht="20" customHeight="1">
@@ -10928,7 +10928,7 @@
         </is>
       </c>
       <c r="E396" s="20" t="n">
-        <v>236</v>
+        <v>157</v>
       </c>
     </row>
     <row r="397" ht="20" customHeight="1">
@@ -10953,7 +10953,7 @@
         </is>
       </c>
       <c r="E397" s="23" t="n">
-        <v>223</v>
+        <v>141</v>
       </c>
     </row>
     <row r="398" ht="20" customHeight="1">
@@ -10978,7 +10978,7 @@
         </is>
       </c>
       <c r="E398" s="20" t="n">
-        <v>216</v>
+        <v>156</v>
       </c>
     </row>
     <row r="399" ht="20" customHeight="1">
@@ -11003,7 +11003,7 @@
         </is>
       </c>
       <c r="E399" s="23" t="n">
-        <v>207</v>
+        <v>226</v>
       </c>
     </row>
     <row r="400" ht="20" customHeight="1">
@@ -11028,7 +11028,7 @@
         </is>
       </c>
       <c r="E400" s="20" t="n">
-        <v>141</v>
+        <v>182</v>
       </c>
     </row>
     <row r="401" ht="20" customHeight="1">
@@ -11053,7 +11053,7 @@
         </is>
       </c>
       <c r="E401" s="23" t="n">
-        <v>233</v>
+        <v>110</v>
       </c>
     </row>
     <row r="402" ht="20" customHeight="1">
@@ -11078,7 +11078,7 @@
         </is>
       </c>
       <c r="E402" s="20" t="n">
-        <v>223</v>
+        <v>138</v>
       </c>
     </row>
     <row r="403" ht="20" customHeight="1">
@@ -11103,7 +11103,7 @@
         </is>
       </c>
       <c r="E403" s="23" t="n">
-        <v>204</v>
+        <v>152</v>
       </c>
     </row>
     <row r="404" ht="20" customHeight="1">
@@ -11128,7 +11128,7 @@
         </is>
       </c>
       <c r="E404" s="20" t="n">
-        <v>200</v>
+        <v>128</v>
       </c>
     </row>
     <row r="405" ht="20" customHeight="1">
@@ -11153,7 +11153,7 @@
         </is>
       </c>
       <c r="E405" s="23" t="n">
-        <v>169</v>
+        <v>176</v>
       </c>
     </row>
     <row r="406" ht="20" customHeight="1">
@@ -11178,7 +11178,7 @@
         </is>
       </c>
       <c r="E406" s="20" t="n">
-        <v>235</v>
+        <v>122</v>
       </c>
     </row>
     <row r="407" ht="20" customHeight="1">
@@ -11203,7 +11203,7 @@
         </is>
       </c>
       <c r="E407" s="23" t="n">
-        <v>173</v>
+        <v>141</v>
       </c>
     </row>
     <row r="408" ht="20" customHeight="1">
@@ -11228,7 +11228,7 @@
         </is>
       </c>
       <c r="E408" s="20" t="n">
-        <v>127</v>
+        <v>177</v>
       </c>
     </row>
     <row r="409" ht="20" customHeight="1">
@@ -11253,7 +11253,7 @@
         </is>
       </c>
       <c r="E409" s="23" t="n">
-        <v>177</v>
+        <v>139</v>
       </c>
     </row>
     <row r="410" ht="20" customHeight="1">
@@ -11278,7 +11278,7 @@
         </is>
       </c>
       <c r="E410" s="20" t="n">
-        <v>238</v>
+        <v>228</v>
       </c>
     </row>
     <row r="411" ht="20" customHeight="1">
@@ -11303,7 +11303,7 @@
         </is>
       </c>
       <c r="E411" s="23" t="n">
-        <v>205</v>
+        <v>191</v>
       </c>
     </row>
     <row r="412" ht="20" customHeight="1">
@@ -11328,7 +11328,7 @@
         </is>
       </c>
       <c r="E412" s="20" t="n">
-        <v>146</v>
+        <v>125</v>
       </c>
     </row>
     <row r="413" ht="20" customHeight="1">
@@ -11353,7 +11353,7 @@
         </is>
       </c>
       <c r="E413" s="23" t="n">
-        <v>229</v>
+        <v>157</v>
       </c>
     </row>
     <row r="414" ht="20" customHeight="1">
@@ -11378,7 +11378,7 @@
         </is>
       </c>
       <c r="E414" s="20" t="n">
-        <v>237</v>
+        <v>199</v>
       </c>
     </row>
     <row r="415" ht="20" customHeight="1">
@@ -11403,7 +11403,7 @@
         </is>
       </c>
       <c r="E415" s="23" t="n">
-        <v>149</v>
+        <v>111</v>
       </c>
     </row>
     <row r="416" ht="20" customHeight="1">
@@ -11428,7 +11428,7 @@
         </is>
       </c>
       <c r="E416" s="20" t="n">
-        <v>173</v>
+        <v>232</v>
       </c>
     </row>
     <row r="417" ht="20" customHeight="1">
@@ -11453,7 +11453,7 @@
         </is>
       </c>
       <c r="E417" s="23" t="n">
-        <v>182</v>
+        <v>117</v>
       </c>
     </row>
     <row r="418" ht="20" customHeight="1">
@@ -11478,7 +11478,7 @@
         </is>
       </c>
       <c r="E418" s="20" t="n">
-        <v>185</v>
+        <v>125</v>
       </c>
     </row>
     <row r="419" ht="20" customHeight="1">
@@ -11503,7 +11503,7 @@
         </is>
       </c>
       <c r="E419" s="23" t="n">
-        <v>235</v>
+        <v>217</v>
       </c>
     </row>
     <row r="420" ht="20" customHeight="1">
@@ -11528,7 +11528,7 @@
         </is>
       </c>
       <c r="E420" s="20" t="n">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="421" ht="20" customHeight="1">
@@ -11553,7 +11553,7 @@
         </is>
       </c>
       <c r="E421" s="23" t="n">
-        <v>148</v>
+        <v>137</v>
       </c>
     </row>
     <row r="422" ht="20" customHeight="1">
@@ -11578,7 +11578,7 @@
         </is>
       </c>
       <c r="E422" s="20" t="n">
-        <v>152</v>
+        <v>210</v>
       </c>
     </row>
     <row r="423" ht="20" customHeight="1">
@@ -11603,7 +11603,7 @@
         </is>
       </c>
       <c r="E423" s="23" t="n">
-        <v>227</v>
+        <v>198</v>
       </c>
     </row>
     <row r="424" ht="20" customHeight="1">
@@ -11628,7 +11628,7 @@
         </is>
       </c>
       <c r="E424" s="20" t="n">
-        <v>190</v>
+        <v>232</v>
       </c>
     </row>
     <row r="425" ht="20" customHeight="1">
@@ -11653,7 +11653,7 @@
         </is>
       </c>
       <c r="E425" s="23" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="426" ht="20" customHeight="1">
@@ -11678,7 +11678,7 @@
         </is>
       </c>
       <c r="E426" s="20" t="n">
-        <v>192</v>
+        <v>226</v>
       </c>
     </row>
     <row r="427" ht="20" customHeight="1">
@@ -11703,7 +11703,7 @@
         </is>
       </c>
       <c r="E427" s="23" t="n">
-        <v>137</v>
+        <v>233</v>
       </c>
     </row>
     <row r="428" ht="20" customHeight="1">
@@ -11728,7 +11728,7 @@
         </is>
       </c>
       <c r="E428" s="20" t="n">
-        <v>181</v>
+        <v>205</v>
       </c>
     </row>
     <row r="429" ht="20" customHeight="1">
@@ -11753,7 +11753,7 @@
         </is>
       </c>
       <c r="E429" s="23" t="n">
-        <v>204</v>
+        <v>144</v>
       </c>
     </row>
     <row r="430" ht="20" customHeight="1">
@@ -11778,7 +11778,7 @@
         </is>
       </c>
       <c r="E430" s="20" t="n">
-        <v>190</v>
+        <v>151</v>
       </c>
     </row>
     <row r="431" ht="20" customHeight="1">
@@ -11803,7 +11803,7 @@
         </is>
       </c>
       <c r="E431" s="23" t="n">
-        <v>166</v>
+        <v>183</v>
       </c>
     </row>
     <row r="432" ht="20" customHeight="1">
@@ -11828,7 +11828,7 @@
         </is>
       </c>
       <c r="E432" s="20" t="n">
-        <v>227</v>
+        <v>152</v>
       </c>
     </row>
     <row r="433" ht="20" customHeight="1">
@@ -11853,7 +11853,7 @@
         </is>
       </c>
       <c r="E433" s="23" t="n">
-        <v>181</v>
+        <v>214</v>
       </c>
     </row>
     <row r="434" ht="20" customHeight="1">
@@ -11878,7 +11878,7 @@
         </is>
       </c>
       <c r="E434" s="20" t="n">
-        <v>203</v>
+        <v>233</v>
       </c>
     </row>
     <row r="435" ht="20" customHeight="1">
@@ -11903,7 +11903,7 @@
         </is>
       </c>
       <c r="E435" s="23" t="n">
-        <v>220</v>
+        <v>116</v>
       </c>
     </row>
     <row r="436" ht="20" customHeight="1">
@@ -11928,7 +11928,7 @@
         </is>
       </c>
       <c r="E436" s="20" t="n">
-        <v>173</v>
+        <v>136</v>
       </c>
     </row>
     <row r="437" ht="20" customHeight="1">
@@ -11953,7 +11953,7 @@
         </is>
       </c>
       <c r="E437" s="23" t="n">
-        <v>213</v>
+        <v>229</v>
       </c>
     </row>
     <row r="438" ht="20" customHeight="1">
@@ -11978,7 +11978,7 @@
         </is>
       </c>
       <c r="E438" s="20" t="n">
-        <v>158</v>
+        <v>169</v>
       </c>
     </row>
     <row r="439" ht="20" customHeight="1">
@@ -12003,7 +12003,7 @@
         </is>
       </c>
       <c r="E439" s="23" t="n">
-        <v>159</v>
+        <v>205</v>
       </c>
     </row>
     <row r="440" ht="20" customHeight="1">
@@ -12028,7 +12028,7 @@
         </is>
       </c>
       <c r="E440" s="20" t="n">
-        <v>193</v>
+        <v>146</v>
       </c>
     </row>
     <row r="441" ht="20" customHeight="1">
@@ -12053,7 +12053,7 @@
         </is>
       </c>
       <c r="E441" s="23" t="n">
-        <v>111</v>
+        <v>166</v>
       </c>
     </row>
     <row r="442" ht="20" customHeight="1">
@@ -12078,7 +12078,7 @@
         </is>
       </c>
       <c r="E442" s="20" t="n">
-        <v>167</v>
+        <v>197</v>
       </c>
     </row>
     <row r="443" ht="20" customHeight="1">
@@ -12103,7 +12103,7 @@
         </is>
       </c>
       <c r="E443" s="23" t="n">
-        <v>181</v>
+        <v>117</v>
       </c>
     </row>
     <row r="444" ht="20" customHeight="1">
@@ -12128,7 +12128,7 @@
         </is>
       </c>
       <c r="E444" s="20" t="n">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="445" ht="20" customHeight="1">
@@ -12153,7 +12153,7 @@
         </is>
       </c>
       <c r="E445" s="23" t="n">
-        <v>161</v>
+        <v>240</v>
       </c>
     </row>
     <row r="446" ht="20" customHeight="1">
@@ -12178,7 +12178,7 @@
         </is>
       </c>
       <c r="E446" s="20" t="n">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="447" ht="20" customHeight="1">
@@ -12203,7 +12203,7 @@
         </is>
       </c>
       <c r="E447" s="23" t="n">
-        <v>198</v>
+        <v>175</v>
       </c>
     </row>
     <row r="448" ht="20" customHeight="1">
@@ -12228,7 +12228,7 @@
         </is>
       </c>
       <c r="E448" s="20" t="n">
-        <v>193</v>
+        <v>160</v>
       </c>
     </row>
     <row r="449" ht="20" customHeight="1">
@@ -12253,7 +12253,7 @@
         </is>
       </c>
       <c r="E449" s="23" t="n">
-        <v>211</v>
+        <v>229</v>
       </c>
     </row>
     <row r="450" ht="20" customHeight="1">
@@ -12278,7 +12278,7 @@
         </is>
       </c>
       <c r="E450" s="20" t="n">
-        <v>199</v>
+        <v>186</v>
       </c>
     </row>
     <row r="451" ht="20" customHeight="1">
@@ -12303,7 +12303,7 @@
         </is>
       </c>
       <c r="E451" s="23" t="n">
-        <v>174</v>
+        <v>156</v>
       </c>
     </row>
     <row r="452" ht="20" customHeight="1">
@@ -12328,7 +12328,7 @@
         </is>
       </c>
       <c r="E452" s="20" t="n">
-        <v>210</v>
+        <v>152</v>
       </c>
     </row>
     <row r="453" ht="20" customHeight="1">
@@ -12353,7 +12353,7 @@
         </is>
       </c>
       <c r="E453" s="23" t="n">
-        <v>132</v>
+        <v>176</v>
       </c>
     </row>
     <row r="454" ht="20" customHeight="1">
@@ -12378,7 +12378,7 @@
         </is>
       </c>
       <c r="E454" s="20" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="455" ht="20" customHeight="1">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="E455" s="23" t="n">
-        <v>133</v>
+        <v>176</v>
       </c>
     </row>
     <row r="456" ht="20" customHeight="1">
@@ -12428,7 +12428,7 @@
         </is>
       </c>
       <c r="E456" s="20" t="n">
-        <v>145</v>
+        <v>194</v>
       </c>
     </row>
     <row r="457" ht="20" customHeight="1">
@@ -12453,7 +12453,7 @@
         </is>
       </c>
       <c r="E457" s="23" t="n">
-        <v>136</v>
+        <v>183</v>
       </c>
     </row>
     <row r="458" ht="20" customHeight="1">
@@ -12478,7 +12478,7 @@
         </is>
       </c>
       <c r="E458" s="20" t="n">
-        <v>219</v>
+        <v>164</v>
       </c>
     </row>
     <row r="459" ht="20" customHeight="1">
@@ -12503,7 +12503,7 @@
         </is>
       </c>
       <c r="E459" s="23" t="n">
-        <v>210</v>
+        <v>150</v>
       </c>
     </row>
     <row r="460" ht="20" customHeight="1">
@@ -12528,7 +12528,7 @@
         </is>
       </c>
       <c r="E460" s="20" t="n">
-        <v>147</v>
+        <v>221</v>
       </c>
     </row>
     <row r="461" ht="20" customHeight="1">
@@ -12553,7 +12553,7 @@
         </is>
       </c>
       <c r="E461" s="23" t="n">
-        <v>137</v>
+        <v>201</v>
       </c>
     </row>
     <row r="462" ht="20" customHeight="1">
@@ -12578,7 +12578,7 @@
         </is>
       </c>
       <c r="E462" s="20" t="n">
-        <v>178</v>
+        <v>194</v>
       </c>
     </row>
     <row r="463" ht="20" customHeight="1">
@@ -12603,7 +12603,7 @@
         </is>
       </c>
       <c r="E463" s="23" t="n">
-        <v>196</v>
+        <v>136</v>
       </c>
     </row>
     <row r="464" ht="20" customHeight="1">
@@ -12628,7 +12628,7 @@
         </is>
       </c>
       <c r="E464" s="20" t="n">
-        <v>151</v>
+        <v>177</v>
       </c>
     </row>
     <row r="465" ht="20" customHeight="1">
@@ -12653,7 +12653,7 @@
         </is>
       </c>
       <c r="E465" s="23" t="n">
-        <v>228</v>
+        <v>221</v>
       </c>
     </row>
     <row r="466" ht="20" customHeight="1">
@@ -12678,7 +12678,7 @@
         </is>
       </c>
       <c r="E466" s="20" t="n">
-        <v>150</v>
+        <v>163</v>
       </c>
     </row>
     <row r="467" ht="20" customHeight="1">
@@ -12703,7 +12703,7 @@
         </is>
       </c>
       <c r="E467" s="23" t="n">
-        <v>167</v>
+        <v>193</v>
       </c>
     </row>
     <row r="468" ht="20" customHeight="1">
@@ -12728,7 +12728,7 @@
         </is>
       </c>
       <c r="E468" s="20" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="469" ht="20" customHeight="1">
@@ -12753,7 +12753,7 @@
         </is>
       </c>
       <c r="E469" s="23" t="n">
-        <v>123</v>
+        <v>205</v>
       </c>
     </row>
     <row r="470" ht="20" customHeight="1">
@@ -12778,7 +12778,7 @@
         </is>
       </c>
       <c r="E470" s="20" t="n">
-        <v>231</v>
+        <v>239</v>
       </c>
     </row>
     <row r="471" ht="20" customHeight="1">
@@ -12803,7 +12803,7 @@
         </is>
       </c>
       <c r="E471" s="23" t="n">
-        <v>184</v>
+        <v>143</v>
       </c>
     </row>
     <row r="472" ht="20" customHeight="1">
@@ -12828,7 +12828,7 @@
         </is>
       </c>
       <c r="E472" s="20" t="n">
-        <v>219</v>
+        <v>113</v>
       </c>
     </row>
     <row r="473" ht="20" customHeight="1">
@@ -12853,7 +12853,7 @@
         </is>
       </c>
       <c r="E473" s="23" t="n">
-        <v>185</v>
+        <v>192</v>
       </c>
     </row>
     <row r="474" ht="20" customHeight="1">
@@ -12878,7 +12878,7 @@
         </is>
       </c>
       <c r="E474" s="20" t="n">
-        <v>147</v>
+        <v>192</v>
       </c>
     </row>
     <row r="475" ht="20" customHeight="1">
@@ -12903,7 +12903,7 @@
         </is>
       </c>
       <c r="E475" s="23" t="n">
-        <v>231</v>
+        <v>147</v>
       </c>
     </row>
     <row r="476" ht="20" customHeight="1">
@@ -12928,7 +12928,7 @@
         </is>
       </c>
       <c r="E476" s="20" t="n">
-        <v>195</v>
+        <v>165</v>
       </c>
     </row>
     <row r="477" ht="20" customHeight="1">
@@ -12953,7 +12953,7 @@
         </is>
       </c>
       <c r="E477" s="23" t="n">
-        <v>202</v>
+        <v>141</v>
       </c>
     </row>
     <row r="478" ht="20" customHeight="1">
@@ -12978,7 +12978,7 @@
         </is>
       </c>
       <c r="E478" s="20" t="n">
-        <v>170</v>
+        <v>209</v>
       </c>
     </row>
     <row r="479" ht="20" customHeight="1">
@@ -13003,7 +13003,7 @@
         </is>
       </c>
       <c r="E479" s="23" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="480" ht="20" customHeight="1">
@@ -13028,7 +13028,7 @@
         </is>
       </c>
       <c r="E480" s="20" t="n">
-        <v>217</v>
+        <v>237</v>
       </c>
     </row>
     <row r="481" ht="20" customHeight="1">
@@ -13053,7 +13053,7 @@
         </is>
       </c>
       <c r="E481" s="23" t="n">
-        <v>218</v>
+        <v>207</v>
       </c>
     </row>
     <row r="482" ht="20" customHeight="1">
@@ -13078,7 +13078,7 @@
         </is>
       </c>
       <c r="E482" s="20" t="n">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="483" ht="20" customHeight="1">
@@ -13103,7 +13103,7 @@
         </is>
       </c>
       <c r="E483" s="23" t="n">
-        <v>117</v>
+        <v>193</v>
       </c>
     </row>
     <row r="484" ht="20" customHeight="1">
@@ -13128,7 +13128,7 @@
         </is>
       </c>
       <c r="E484" s="20" t="n">
-        <v>211</v>
+        <v>121</v>
       </c>
     </row>
     <row r="485" ht="20" customHeight="1">
@@ -13153,7 +13153,7 @@
         </is>
       </c>
       <c r="E485" s="23" t="n">
-        <v>196</v>
+        <v>186</v>
       </c>
     </row>
     <row r="486" ht="20" customHeight="1">
@@ -13178,7 +13178,7 @@
         </is>
       </c>
       <c r="E486" s="20" t="n">
-        <v>124</v>
+        <v>181</v>
       </c>
     </row>
     <row r="487" ht="20" customHeight="1">
@@ -13203,7 +13203,7 @@
         </is>
       </c>
       <c r="E487" s="23" t="n">
-        <v>201</v>
+        <v>214</v>
       </c>
     </row>
     <row r="488" ht="20" customHeight="1">
@@ -13228,7 +13228,7 @@
         </is>
       </c>
       <c r="E488" s="20" t="n">
-        <v>160</v>
+        <v>114</v>
       </c>
     </row>
     <row r="489" ht="20" customHeight="1">
@@ -13253,7 +13253,7 @@
         </is>
       </c>
       <c r="E489" s="23" t="n">
-        <v>197</v>
+        <v>113</v>
       </c>
     </row>
     <row r="490" ht="20" customHeight="1">
@@ -13278,7 +13278,7 @@
         </is>
       </c>
       <c r="E490" s="20" t="n">
-        <v>222</v>
+        <v>172</v>
       </c>
     </row>
     <row r="491" ht="20" customHeight="1">
@@ -13303,7 +13303,7 @@
         </is>
       </c>
       <c r="E491" s="23" t="n">
-        <v>236</v>
+        <v>161</v>
       </c>
     </row>
     <row r="492" ht="20" customHeight="1">
@@ -13328,7 +13328,7 @@
         </is>
       </c>
       <c r="E492" s="20" t="n">
-        <v>189</v>
+        <v>197</v>
       </c>
     </row>
     <row r="493" ht="20" customHeight="1">
@@ -13353,7 +13353,7 @@
         </is>
       </c>
       <c r="E493" s="23" t="n">
-        <v>110</v>
+        <v>194</v>
       </c>
     </row>
     <row r="494" ht="20" customHeight="1">
@@ -13378,7 +13378,7 @@
         </is>
       </c>
       <c r="E494" s="20" t="n">
-        <v>217</v>
+        <v>156</v>
       </c>
     </row>
     <row r="495" ht="20" customHeight="1">
@@ -13403,7 +13403,7 @@
         </is>
       </c>
       <c r="E495" s="23" t="n">
-        <v>157</v>
+        <v>146</v>
       </c>
     </row>
     <row r="496" ht="20" customHeight="1">
@@ -13428,7 +13428,7 @@
         </is>
       </c>
       <c r="E496" s="20" t="n">
-        <v>162</v>
+        <v>126</v>
       </c>
     </row>
     <row r="497" ht="20" customHeight="1">
@@ -13453,7 +13453,7 @@
         </is>
       </c>
       <c r="E497" s="23" t="n">
-        <v>144</v>
+        <v>192</v>
       </c>
     </row>
     <row r="498" ht="20" customHeight="1">
@@ -13478,7 +13478,7 @@
         </is>
       </c>
       <c r="E498" s="20" t="n">
-        <v>184</v>
+        <v>144</v>
       </c>
     </row>
     <row r="499" ht="20" customHeight="1">
@@ -13503,7 +13503,7 @@
         </is>
       </c>
       <c r="E499" s="23" t="n">
-        <v>217</v>
+        <v>209</v>
       </c>
     </row>
     <row r="500" ht="20" customHeight="1">
@@ -13528,7 +13528,7 @@
         </is>
       </c>
       <c r="E500" s="20" t="n">
-        <v>141</v>
+        <v>224</v>
       </c>
     </row>
     <row r="501" ht="20" customHeight="1">
@@ -13553,7 +13553,7 @@
         </is>
       </c>
       <c r="E501" s="23" t="n">
-        <v>183</v>
+        <v>159</v>
       </c>
     </row>
     <row r="502" ht="20" customHeight="1">
@@ -13578,7 +13578,7 @@
         </is>
       </c>
       <c r="E502" s="20" t="n">
-        <v>119</v>
+        <v>112</v>
       </c>
     </row>
     <row r="503" ht="20" customHeight="1">
@@ -13603,7 +13603,7 @@
         </is>
       </c>
       <c r="E503" s="23" t="n">
-        <v>137</v>
+        <v>151</v>
       </c>
     </row>
     <row r="504" ht="20" customHeight="1">
@@ -13628,7 +13628,7 @@
         </is>
       </c>
       <c r="E504" s="20" t="n">
-        <v>149</v>
+        <v>238</v>
       </c>
     </row>
     <row r="505" ht="20" customHeight="1">
@@ -13653,7 +13653,7 @@
         </is>
       </c>
       <c r="E505" s="23" t="n">
-        <v>126</v>
+        <v>177</v>
       </c>
     </row>
     <row r="506" ht="20" customHeight="1">
@@ -13678,7 +13678,7 @@
         </is>
       </c>
       <c r="E506" s="20" t="n">
-        <v>174</v>
+        <v>229</v>
       </c>
     </row>
     <row r="507" ht="20" customHeight="1">
@@ -13703,7 +13703,7 @@
         </is>
       </c>
       <c r="E507" s="23" t="n">
-        <v>150</v>
+        <v>131</v>
       </c>
     </row>
     <row r="508" ht="20" customHeight="1">
@@ -13728,7 +13728,7 @@
         </is>
       </c>
       <c r="E508" s="20" t="n">
-        <v>239</v>
+        <v>125</v>
       </c>
     </row>
     <row r="509" ht="20" customHeight="1">
@@ -13753,7 +13753,7 @@
         </is>
       </c>
       <c r="E509" s="23" t="n">
-        <v>126</v>
+        <v>231</v>
       </c>
     </row>
     <row r="510" ht="20" customHeight="1">
@@ -13778,7 +13778,7 @@
         </is>
       </c>
       <c r="E510" s="20" t="n">
-        <v>144</v>
+        <v>133</v>
       </c>
     </row>
     <row r="511" ht="20" customHeight="1">
@@ -13803,7 +13803,7 @@
         </is>
       </c>
       <c r="E511" s="23" t="n">
-        <v>215</v>
+        <v>155</v>
       </c>
     </row>
     <row r="512" ht="20" customHeight="1">
@@ -13828,7 +13828,7 @@
         </is>
       </c>
       <c r="E512" s="20" t="n">
-        <v>200</v>
+        <v>139</v>
       </c>
     </row>
     <row r="513" ht="20" customHeight="1">
@@ -13853,7 +13853,7 @@
         </is>
       </c>
       <c r="E513" s="23" t="n">
-        <v>164</v>
+        <v>128</v>
       </c>
     </row>
     <row r="514" ht="20" customHeight="1">
@@ -13878,7 +13878,7 @@
         </is>
       </c>
       <c r="E514" s="20" t="n">
-        <v>221</v>
+        <v>142</v>
       </c>
     </row>
     <row r="515" ht="20" customHeight="1">
@@ -13903,7 +13903,7 @@
         </is>
       </c>
       <c r="E515" s="23" t="n">
-        <v>113</v>
+        <v>180</v>
       </c>
     </row>
     <row r="516" ht="20" customHeight="1">
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="E516" s="20" t="n">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="517" ht="20" customHeight="1">
@@ -13953,7 +13953,7 @@
         </is>
       </c>
       <c r="E517" s="23" t="n">
-        <v>149</v>
+        <v>201</v>
       </c>
     </row>
     <row r="518" ht="20" customHeight="1">
@@ -13978,7 +13978,7 @@
         </is>
       </c>
       <c r="E518" s="20" t="n">
-        <v>134</v>
+        <v>212</v>
       </c>
     </row>
     <row r="519" ht="20" customHeight="1">
@@ -14003,7 +14003,7 @@
         </is>
       </c>
       <c r="E519" s="23" t="n">
-        <v>123</v>
+        <v>224</v>
       </c>
     </row>
     <row r="520" ht="20" customHeight="1">
@@ -14028,7 +14028,7 @@
         </is>
       </c>
       <c r="E520" s="20" t="n">
-        <v>235</v>
+        <v>113</v>
       </c>
     </row>
     <row r="521" ht="20" customHeight="1">
@@ -14053,7 +14053,7 @@
         </is>
       </c>
       <c r="E521" s="23" t="n">
-        <v>155</v>
+        <v>189</v>
       </c>
     </row>
     <row r="522" ht="20" customHeight="1">
@@ -14078,7 +14078,7 @@
         </is>
       </c>
       <c r="E522" s="20" t="n">
-        <v>229</v>
+        <v>146</v>
       </c>
     </row>
     <row r="523" ht="20" customHeight="1">
@@ -14103,7 +14103,7 @@
         </is>
       </c>
       <c r="E523" s="23" t="n">
-        <v>145</v>
+        <v>172</v>
       </c>
     </row>
     <row r="524" ht="20" customHeight="1">
@@ -14128,7 +14128,7 @@
         </is>
       </c>
       <c r="E524" s="20" t="n">
-        <v>194</v>
+        <v>115</v>
       </c>
     </row>
     <row r="525" ht="20" customHeight="1">
@@ -14153,7 +14153,7 @@
         </is>
       </c>
       <c r="E525" s="23" t="n">
-        <v>137</v>
+        <v>179</v>
       </c>
     </row>
     <row r="526" ht="20" customHeight="1">
@@ -14178,7 +14178,7 @@
         </is>
       </c>
       <c r="E526" s="20" t="n">
-        <v>141</v>
+        <v>223</v>
       </c>
     </row>
     <row r="527" ht="20" customHeight="1">
@@ -14203,7 +14203,7 @@
         </is>
       </c>
       <c r="E527" s="23" t="n">
-        <v>161</v>
+        <v>204</v>
       </c>
     </row>
     <row r="528" ht="20" customHeight="1">
@@ -14228,7 +14228,7 @@
         </is>
       </c>
       <c r="E528" s="20" t="n">
-        <v>189</v>
+        <v>155</v>
       </c>
     </row>
     <row r="529" ht="20" customHeight="1">
@@ -14253,7 +14253,7 @@
         </is>
       </c>
       <c r="E529" s="23" t="n">
-        <v>215</v>
+        <v>189</v>
       </c>
     </row>
     <row r="530" ht="20" customHeight="1">
@@ -14278,7 +14278,7 @@
         </is>
       </c>
       <c r="E530" s="20" t="n">
-        <v>236</v>
+        <v>139</v>
       </c>
     </row>
     <row r="531" ht="20" customHeight="1">
@@ -14303,7 +14303,7 @@
         </is>
       </c>
       <c r="E531" s="23" t="n">
-        <v>207</v>
+        <v>231</v>
       </c>
     </row>
     <row r="532" ht="20" customHeight="1">
@@ -14328,7 +14328,7 @@
         </is>
       </c>
       <c r="E532" s="20" t="n">
-        <v>146</v>
+        <v>159</v>
       </c>
     </row>
     <row r="533" ht="20" customHeight="1">
@@ -14353,7 +14353,7 @@
         </is>
       </c>
       <c r="E533" s="23" t="n">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="534" ht="20" customHeight="1">
@@ -14378,7 +14378,7 @@
         </is>
       </c>
       <c r="E534" s="20" t="n">
-        <v>189</v>
+        <v>167</v>
       </c>
     </row>
     <row r="535" ht="20" customHeight="1">
@@ -14403,7 +14403,7 @@
         </is>
       </c>
       <c r="E535" s="23" t="n">
-        <v>227</v>
+        <v>187</v>
       </c>
     </row>
     <row r="536" ht="20" customHeight="1">
@@ -14428,7 +14428,7 @@
         </is>
       </c>
       <c r="E536" s="20" t="n">
-        <v>199</v>
+        <v>165</v>
       </c>
     </row>
     <row r="537" ht="20" customHeight="1">
@@ -14453,7 +14453,7 @@
         </is>
       </c>
       <c r="E537" s="23" t="n">
-        <v>202</v>
+        <v>142</v>
       </c>
     </row>
     <row r="538" ht="20" customHeight="1">
@@ -14478,7 +14478,7 @@
         </is>
       </c>
       <c r="E538" s="20" t="n">
-        <v>236</v>
+        <v>206</v>
       </c>
     </row>
     <row r="539" ht="20" customHeight="1">
@@ -14503,7 +14503,7 @@
         </is>
       </c>
       <c r="E539" s="23" t="n">
-        <v>217</v>
+        <v>196</v>
       </c>
     </row>
     <row r="540" ht="20" customHeight="1">
@@ -14528,7 +14528,7 @@
         </is>
       </c>
       <c r="E540" s="20" t="n">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="541" ht="20" customHeight="1">
@@ -14553,7 +14553,7 @@
         </is>
       </c>
       <c r="E541" s="23" t="n">
-        <v>148</v>
+        <v>201</v>
       </c>
     </row>
     <row r="542" ht="20" customHeight="1">
@@ -14578,7 +14578,7 @@
         </is>
       </c>
       <c r="E542" s="20" t="n">
-        <v>197</v>
+        <v>232</v>
       </c>
     </row>
     <row r="543" ht="20" customHeight="1">
@@ -14603,7 +14603,7 @@
         </is>
       </c>
       <c r="E543" s="23" t="n">
-        <v>183</v>
+        <v>168</v>
       </c>
     </row>
     <row r="544" ht="20" customHeight="1">
@@ -14628,7 +14628,7 @@
         </is>
       </c>
       <c r="E544" s="20" t="n">
-        <v>123</v>
+        <v>194</v>
       </c>
     </row>
     <row r="545" ht="20" customHeight="1">
@@ -14653,7 +14653,7 @@
         </is>
       </c>
       <c r="E545" s="23" t="n">
-        <v>221</v>
+        <v>226</v>
       </c>
     </row>
     <row r="546" ht="20" customHeight="1">
@@ -14678,7 +14678,7 @@
         </is>
       </c>
       <c r="E546" s="20" t="n">
-        <v>231</v>
+        <v>171</v>
       </c>
     </row>
     <row r="547" ht="20" customHeight="1">
@@ -14703,7 +14703,7 @@
         </is>
       </c>
       <c r="E547" s="23" t="n">
-        <v>118</v>
+        <v>175</v>
       </c>
     </row>
     <row r="548" ht="20" customHeight="1">
@@ -14728,7 +14728,7 @@
         </is>
       </c>
       <c r="E548" s="20" t="n">
-        <v>234</v>
+        <v>225</v>
       </c>
     </row>
     <row r="549" ht="20" customHeight="1">
@@ -14753,7 +14753,7 @@
         </is>
       </c>
       <c r="E549" s="23" t="n">
-        <v>197</v>
+        <v>228</v>
       </c>
     </row>
     <row r="550" ht="20" customHeight="1">
@@ -14778,7 +14778,7 @@
         </is>
       </c>
       <c r="E550" s="20" t="n">
-        <v>227</v>
+        <v>139</v>
       </c>
     </row>
     <row r="551" ht="20" customHeight="1">
@@ -14803,7 +14803,7 @@
         </is>
       </c>
       <c r="E551" s="23" t="n">
-        <v>202</v>
+        <v>182</v>
       </c>
     </row>
     <row r="552" ht="20" customHeight="1">
@@ -14828,7 +14828,7 @@
         </is>
       </c>
       <c r="E552" s="20" t="n">
-        <v>215</v>
+        <v>144</v>
       </c>
     </row>
     <row r="553" ht="20" customHeight="1">
@@ -14853,7 +14853,7 @@
         </is>
       </c>
       <c r="E553" s="23" t="n">
-        <v>151</v>
+        <v>139</v>
       </c>
     </row>
     <row r="554" ht="20" customHeight="1">
@@ -14878,7 +14878,7 @@
         </is>
       </c>
       <c r="E554" s="20" t="n">
-        <v>152</v>
+        <v>131</v>
       </c>
     </row>
     <row r="555" ht="20" customHeight="1">
@@ -14903,7 +14903,7 @@
         </is>
       </c>
       <c r="E555" s="23" t="n">
-        <v>163</v>
+        <v>117</v>
       </c>
     </row>
     <row r="556" ht="20" customHeight="1">
@@ -14928,7 +14928,7 @@
         </is>
       </c>
       <c r="E556" s="20" t="n">
-        <v>177</v>
+        <v>238</v>
       </c>
     </row>
     <row r="557" ht="20" customHeight="1">
@@ -14953,7 +14953,7 @@
         </is>
       </c>
       <c r="E557" s="23" t="n">
-        <v>238</v>
+        <v>118</v>
       </c>
     </row>
     <row r="558" ht="20" customHeight="1">
@@ -14978,7 +14978,7 @@
         </is>
       </c>
       <c r="E558" s="20" t="n">
-        <v>228</v>
+        <v>207</v>
       </c>
     </row>
     <row r="559" ht="20" customHeight="1">
@@ -15003,7 +15003,7 @@
         </is>
       </c>
       <c r="E559" s="23" t="n">
-        <v>140</v>
+        <v>185</v>
       </c>
     </row>
     <row r="560" ht="20" customHeight="1">
@@ -15028,7 +15028,7 @@
         </is>
       </c>
       <c r="E560" s="20" t="n">
-        <v>196</v>
+        <v>237</v>
       </c>
     </row>
     <row r="561" ht="20" customHeight="1">
@@ -15053,7 +15053,7 @@
         </is>
       </c>
       <c r="E561" s="23" t="n">
-        <v>138</v>
+        <v>129</v>
       </c>
     </row>
     <row r="562" ht="20" customHeight="1">
@@ -15078,7 +15078,7 @@
         </is>
       </c>
       <c r="E562" s="20" t="n">
-        <v>122</v>
+        <v>139</v>
       </c>
     </row>
     <row r="563" ht="20" customHeight="1">
@@ -15103,7 +15103,7 @@
         </is>
       </c>
       <c r="E563" s="23" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="564" ht="20" customHeight="1">
@@ -15128,7 +15128,7 @@
         </is>
       </c>
       <c r="E564" s="20" t="n">
-        <v>231</v>
+        <v>218</v>
       </c>
     </row>
     <row r="565" ht="20" customHeight="1">
@@ -15153,7 +15153,7 @@
         </is>
       </c>
       <c r="E565" s="23" t="n">
-        <v>137</v>
+        <v>148</v>
       </c>
     </row>
     <row r="566" ht="20" customHeight="1">
@@ -15178,7 +15178,7 @@
         </is>
       </c>
       <c r="E566" s="20" t="n">
-        <v>190</v>
+        <v>140</v>
       </c>
     </row>
     <row r="567" ht="20" customHeight="1">
@@ -15203,7 +15203,7 @@
         </is>
       </c>
       <c r="E567" s="23" t="n">
-        <v>157</v>
+        <v>214</v>
       </c>
     </row>
     <row r="568" ht="20" customHeight="1">
@@ -15228,7 +15228,7 @@
         </is>
       </c>
       <c r="E568" s="20" t="n">
-        <v>189</v>
+        <v>169</v>
       </c>
     </row>
     <row r="569" ht="20" customHeight="1">
@@ -15253,7 +15253,7 @@
         </is>
       </c>
       <c r="E569" s="23" t="n">
-        <v>149</v>
+        <v>171</v>
       </c>
     </row>
     <row r="570" ht="20" customHeight="1">
@@ -15278,7 +15278,7 @@
         </is>
       </c>
       <c r="E570" s="20" t="n">
-        <v>222</v>
+        <v>193</v>
       </c>
     </row>
     <row r="571" ht="20" customHeight="1">
@@ -15303,7 +15303,7 @@
         </is>
       </c>
       <c r="E571" s="23" t="n">
-        <v>124</v>
+        <v>138</v>
       </c>
     </row>
     <row r="572" ht="20" customHeight="1">
@@ -15328,7 +15328,7 @@
         </is>
       </c>
       <c r="E572" s="20" t="n">
-        <v>134</v>
+        <v>195</v>
       </c>
     </row>
     <row r="573" ht="20" customHeight="1">
@@ -15353,7 +15353,7 @@
         </is>
       </c>
       <c r="E573" s="23" t="n">
-        <v>160</v>
+        <v>231</v>
       </c>
     </row>
     <row r="574" ht="20" customHeight="1">
@@ -15378,7 +15378,7 @@
         </is>
       </c>
       <c r="E574" s="20" t="n">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="575" ht="20" customHeight="1">
@@ -15403,7 +15403,7 @@
         </is>
       </c>
       <c r="E575" s="23" t="n">
-        <v>218</v>
+        <v>235</v>
       </c>
     </row>
     <row r="576" ht="20" customHeight="1">
@@ -15428,7 +15428,7 @@
         </is>
       </c>
       <c r="E576" s="20" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="577" ht="20" customHeight="1">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="E577" s="23" t="n">
-        <v>128</v>
+        <v>240</v>
       </c>
     </row>
     <row r="578" ht="20" customHeight="1">
@@ -15478,7 +15478,7 @@
         </is>
       </c>
       <c r="E578" s="20" t="n">
-        <v>138</v>
+        <v>145</v>
       </c>
     </row>
     <row r="579" ht="20" customHeight="1">
@@ -15503,7 +15503,7 @@
         </is>
       </c>
       <c r="E579" s="23" t="n">
-        <v>122</v>
+        <v>236</v>
       </c>
     </row>
     <row r="580" ht="20" customHeight="1">
@@ -15528,7 +15528,7 @@
         </is>
       </c>
       <c r="E580" s="20" t="n">
-        <v>189</v>
+        <v>199</v>
       </c>
     </row>
     <row r="581" ht="20" customHeight="1">
@@ -15553,7 +15553,7 @@
         </is>
       </c>
       <c r="E581" s="23" t="n">
-        <v>218</v>
+        <v>193</v>
       </c>
     </row>
     <row r="582" ht="20" customHeight="1">
@@ -15578,7 +15578,7 @@
         </is>
       </c>
       <c r="E582" s="20" t="n">
-        <v>190</v>
+        <v>118</v>
       </c>
     </row>
     <row r="583" ht="20" customHeight="1">
@@ -15603,7 +15603,7 @@
         </is>
       </c>
       <c r="E583" s="23" t="n">
-        <v>150</v>
+        <v>111</v>
       </c>
     </row>
     <row r="584" ht="20" customHeight="1">
@@ -15628,7 +15628,7 @@
         </is>
       </c>
       <c r="E584" s="20" t="n">
-        <v>180</v>
+        <v>187</v>
       </c>
     </row>
     <row r="585" ht="20" customHeight="1">
@@ -15653,7 +15653,7 @@
         </is>
       </c>
       <c r="E585" s="23" t="n">
-        <v>135</v>
+        <v>235</v>
       </c>
     </row>
     <row r="586" ht="20" customHeight="1">
@@ -15678,7 +15678,7 @@
         </is>
       </c>
       <c r="E586" s="20" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="587" ht="20" customHeight="1">
@@ -15703,7 +15703,7 @@
         </is>
       </c>
       <c r="E587" s="23" t="n">
-        <v>195</v>
+        <v>210</v>
       </c>
     </row>
     <row r="588" ht="20" customHeight="1">
@@ -15728,7 +15728,7 @@
         </is>
       </c>
       <c r="E588" s="20" t="n">
-        <v>145</v>
+        <v>222</v>
       </c>
     </row>
     <row r="589" ht="20" customHeight="1">
@@ -15753,7 +15753,7 @@
         </is>
       </c>
       <c r="E589" s="23" t="n">
-        <v>208</v>
+        <v>138</v>
       </c>
     </row>
     <row r="590" ht="20" customHeight="1">
@@ -15778,7 +15778,7 @@
         </is>
       </c>
       <c r="E590" s="20" t="n">
-        <v>132</v>
+        <v>229</v>
       </c>
     </row>
     <row r="591" ht="20" customHeight="1">
@@ -15803,7 +15803,7 @@
         </is>
       </c>
       <c r="E591" s="23" t="n">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="592" ht="20" customHeight="1">
@@ -15828,7 +15828,7 @@
         </is>
       </c>
       <c r="E592" s="20" t="n">
-        <v>229</v>
+        <v>140</v>
       </c>
     </row>
     <row r="593" ht="20" customHeight="1">
@@ -15853,7 +15853,7 @@
         </is>
       </c>
       <c r="E593" s="23" t="n">
-        <v>238</v>
+        <v>170</v>
       </c>
     </row>
     <row r="594" ht="20" customHeight="1">
@@ -15878,7 +15878,7 @@
         </is>
       </c>
       <c r="E594" s="20" t="n">
-        <v>165</v>
+        <v>132</v>
       </c>
     </row>
     <row r="595" ht="20" customHeight="1">
@@ -15903,7 +15903,7 @@
         </is>
       </c>
       <c r="E595" s="23" t="n">
-        <v>121</v>
+        <v>130</v>
       </c>
     </row>
     <row r="596" ht="20" customHeight="1">
@@ -15928,7 +15928,7 @@
         </is>
       </c>
       <c r="E596" s="20" t="n">
-        <v>213</v>
+        <v>205</v>
       </c>
     </row>
     <row r="597" ht="20" customHeight="1">
@@ -15953,7 +15953,7 @@
         </is>
       </c>
       <c r="E597" s="23" t="n">
-        <v>229</v>
+        <v>185</v>
       </c>
     </row>
     <row r="598" ht="20" customHeight="1">
@@ -15978,7 +15978,7 @@
         </is>
       </c>
       <c r="E598" s="20" t="n">
-        <v>169</v>
+        <v>125</v>
       </c>
     </row>
     <row r="599" ht="20" customHeight="1">
@@ -16003,7 +16003,7 @@
         </is>
       </c>
       <c r="E599" s="23" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="600" ht="20" customHeight="1">
@@ -16028,7 +16028,7 @@
         </is>
       </c>
       <c r="E600" s="20" t="n">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="601" ht="20" customHeight="1">
@@ -16053,7 +16053,7 @@
         </is>
       </c>
       <c r="E601" s="23" t="n">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="602" ht="20" customHeight="1">
@@ -16078,7 +16078,7 @@
         </is>
       </c>
       <c r="E602" s="20" t="n">
-        <v>228</v>
+        <v>166</v>
       </c>
     </row>
     <row r="603" ht="20" customHeight="1">
@@ -16103,7 +16103,7 @@
         </is>
       </c>
       <c r="E603" s="23" t="n">
-        <v>153</v>
+        <v>215</v>
       </c>
     </row>
     <row r="604" ht="20" customHeight="1">
@@ -16128,7 +16128,7 @@
         </is>
       </c>
       <c r="E604" s="20" t="n">
-        <v>184</v>
+        <v>199</v>
       </c>
     </row>
     <row r="605" ht="20" customHeight="1">
@@ -16153,7 +16153,7 @@
         </is>
       </c>
       <c r="E605" s="23" t="n">
-        <v>240</v>
+        <v>151</v>
       </c>
     </row>
     <row r="606" ht="20" customHeight="1">
@@ -16178,7 +16178,7 @@
         </is>
       </c>
       <c r="E606" s="20" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="607" ht="20" customHeight="1">
@@ -16203,7 +16203,7 @@
         </is>
       </c>
       <c r="E607" s="23" t="n">
-        <v>234</v>
+        <v>221</v>
       </c>
     </row>
     <row r="608" ht="20" customHeight="1">
@@ -16228,7 +16228,7 @@
         </is>
       </c>
       <c r="E608" s="20" t="n">
-        <v>137</v>
+        <v>115</v>
       </c>
     </row>
     <row r="609" ht="20" customHeight="1">
@@ -16253,7 +16253,7 @@
         </is>
       </c>
       <c r="E609" s="23" t="n">
-        <v>115</v>
+        <v>212</v>
       </c>
     </row>
     <row r="610" ht="20" customHeight="1">
@@ -16278,7 +16278,7 @@
         </is>
       </c>
       <c r="E610" s="20" t="n">
-        <v>114</v>
+        <v>229</v>
       </c>
     </row>
     <row r="611" ht="20" customHeight="1">
@@ -16303,7 +16303,7 @@
         </is>
       </c>
       <c r="E611" s="23" t="n">
-        <v>144</v>
+        <v>115</v>
       </c>
     </row>
     <row r="612" ht="20" customHeight="1">
@@ -16328,7 +16328,7 @@
         </is>
       </c>
       <c r="E612" s="20" t="n">
-        <v>131</v>
+        <v>183</v>
       </c>
     </row>
     <row r="613" ht="20" customHeight="1">
@@ -16353,7 +16353,7 @@
         </is>
       </c>
       <c r="E613" s="23" t="n">
-        <v>173</v>
+        <v>234</v>
       </c>
     </row>
     <row r="614" ht="20" customHeight="1">
@@ -16378,7 +16378,7 @@
         </is>
       </c>
       <c r="E614" s="20" t="n">
-        <v>229</v>
+        <v>150</v>
       </c>
     </row>
     <row r="615" ht="20" customHeight="1">
@@ -16403,7 +16403,7 @@
         </is>
       </c>
       <c r="E615" s="23" t="n">
-        <v>115</v>
+        <v>230</v>
       </c>
     </row>
     <row r="616" ht="20" customHeight="1">
@@ -16428,7 +16428,7 @@
         </is>
       </c>
       <c r="E616" s="20" t="n">
-        <v>224</v>
+        <v>140</v>
       </c>
     </row>
     <row r="617" ht="20" customHeight="1">
@@ -16453,7 +16453,7 @@
         </is>
       </c>
       <c r="E617" s="23" t="n">
-        <v>189</v>
+        <v>113</v>
       </c>
     </row>
     <row r="618" ht="20" customHeight="1">
@@ -16478,7 +16478,7 @@
         </is>
       </c>
       <c r="E618" s="20" t="n">
-        <v>117</v>
+        <v>209</v>
       </c>
     </row>
     <row r="619" ht="20" customHeight="1">
@@ -16503,7 +16503,7 @@
         </is>
       </c>
       <c r="E619" s="23" t="n">
-        <v>168</v>
+        <v>173</v>
       </c>
     </row>
     <row r="620" ht="20" customHeight="1">
@@ -16528,7 +16528,7 @@
         </is>
       </c>
       <c r="E620" s="20" t="n">
-        <v>117</v>
+        <v>182</v>
       </c>
     </row>
     <row r="621" ht="20" customHeight="1">
@@ -16553,7 +16553,7 @@
         </is>
       </c>
       <c r="E621" s="23" t="n">
-        <v>161</v>
+        <v>144</v>
       </c>
     </row>
     <row r="622" ht="20" customHeight="1">
@@ -16578,7 +16578,7 @@
         </is>
       </c>
       <c r="E622" s="20" t="n">
-        <v>203</v>
+        <v>154</v>
       </c>
     </row>
     <row r="623" ht="20" customHeight="1">
@@ -16603,7 +16603,7 @@
         </is>
       </c>
       <c r="E623" s="23" t="n">
-        <v>187</v>
+        <v>200</v>
       </c>
     </row>
     <row r="624" ht="20" customHeight="1">
@@ -16628,7 +16628,7 @@
         </is>
       </c>
       <c r="E624" s="20" t="n">
-        <v>203</v>
+        <v>197</v>
       </c>
     </row>
     <row r="625" ht="20" customHeight="1">
@@ -16653,7 +16653,7 @@
         </is>
       </c>
       <c r="E625" s="23" t="n">
-        <v>221</v>
+        <v>165</v>
       </c>
     </row>
     <row r="626" ht="20" customHeight="1">
@@ -16678,7 +16678,7 @@
         </is>
       </c>
       <c r="E626" s="20" t="n">
-        <v>207</v>
+        <v>217</v>
       </c>
     </row>
     <row r="627" ht="20" customHeight="1">
@@ -16703,7 +16703,7 @@
         </is>
       </c>
       <c r="E627" s="23" t="n">
-        <v>232</v>
+        <v>211</v>
       </c>
     </row>
     <row r="628" ht="20" customHeight="1">
@@ -16728,7 +16728,7 @@
         </is>
       </c>
       <c r="E628" s="20" t="n">
-        <v>196</v>
+        <v>200</v>
       </c>
     </row>
     <row r="629" ht="20" customHeight="1">
@@ -16753,7 +16753,7 @@
         </is>
       </c>
       <c r="E629" s="23" t="n">
-        <v>197</v>
+        <v>112</v>
       </c>
     </row>
     <row r="630" ht="20" customHeight="1">
@@ -16778,7 +16778,7 @@
         </is>
       </c>
       <c r="E630" s="20" t="n">
-        <v>183</v>
+        <v>159</v>
       </c>
     </row>
     <row r="631" ht="20" customHeight="1">
@@ -16803,7 +16803,7 @@
         </is>
       </c>
       <c r="E631" s="23" t="n">
-        <v>171</v>
+        <v>136</v>
       </c>
     </row>
     <row r="632" ht="20" customHeight="1">
@@ -16828,7 +16828,7 @@
         </is>
       </c>
       <c r="E632" s="20" t="n">
-        <v>117</v>
+        <v>125</v>
       </c>
     </row>
     <row r="633" ht="20" customHeight="1">
@@ -16853,7 +16853,7 @@
         </is>
       </c>
       <c r="E633" s="23" t="n">
-        <v>157</v>
+        <v>178</v>
       </c>
     </row>
     <row r="634" ht="20" customHeight="1">
@@ -16878,7 +16878,7 @@
         </is>
       </c>
       <c r="E634" s="20" t="n">
-        <v>121</v>
+        <v>209</v>
       </c>
     </row>
     <row r="635" ht="20" customHeight="1">
@@ -16903,7 +16903,7 @@
         </is>
       </c>
       <c r="E635" s="23" t="n">
-        <v>204</v>
+        <v>153</v>
       </c>
     </row>
     <row r="636" ht="20" customHeight="1">
@@ -16928,7 +16928,7 @@
         </is>
       </c>
       <c r="E636" s="20" t="n">
-        <v>226</v>
+        <v>186</v>
       </c>
     </row>
     <row r="637" ht="20" customHeight="1">
@@ -16953,7 +16953,7 @@
         </is>
       </c>
       <c r="E637" s="23" t="n">
-        <v>151</v>
+        <v>118</v>
       </c>
     </row>
     <row r="638" ht="20" customHeight="1">
@@ -16978,7 +16978,7 @@
         </is>
       </c>
       <c r="E638" s="20" t="n">
-        <v>207</v>
+        <v>161</v>
       </c>
     </row>
     <row r="639" ht="20" customHeight="1">
@@ -17003,7 +17003,7 @@
         </is>
       </c>
       <c r="E639" s="23" t="n">
-        <v>153</v>
+        <v>185</v>
       </c>
     </row>
     <row r="640" ht="20" customHeight="1">
@@ -17028,7 +17028,7 @@
         </is>
       </c>
       <c r="E640" s="20" t="n">
-        <v>132</v>
+        <v>225</v>
       </c>
     </row>
     <row r="641" ht="20" customHeight="1">
@@ -17053,7 +17053,7 @@
         </is>
       </c>
       <c r="E641" s="23" t="n">
-        <v>181</v>
+        <v>170</v>
       </c>
     </row>
     <row r="642" ht="20" customHeight="1">
@@ -17078,7 +17078,7 @@
         </is>
       </c>
       <c r="E642" s="20" t="n">
-        <v>223</v>
+        <v>159</v>
       </c>
     </row>
     <row r="643" ht="20" customHeight="1">
@@ -17103,7 +17103,7 @@
         </is>
       </c>
       <c r="E643" s="23" t="n">
-        <v>110</v>
+        <v>191</v>
       </c>
     </row>
     <row r="644" ht="20" customHeight="1">
@@ -17128,7 +17128,7 @@
         </is>
       </c>
       <c r="E644" s="20" t="n">
-        <v>236</v>
+        <v>113</v>
       </c>
     </row>
     <row r="645" ht="20" customHeight="1">
@@ -17153,7 +17153,7 @@
         </is>
       </c>
       <c r="E645" s="23" t="n">
-        <v>188</v>
+        <v>155</v>
       </c>
     </row>
     <row r="646" ht="20" customHeight="1">
@@ -17178,7 +17178,7 @@
         </is>
       </c>
       <c r="E646" s="20" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="647" ht="20" customHeight="1">
@@ -17203,7 +17203,7 @@
         </is>
       </c>
       <c r="E647" s="23" t="n">
-        <v>219</v>
+        <v>214</v>
       </c>
     </row>
     <row r="648" ht="20" customHeight="1">
@@ -17228,7 +17228,7 @@
         </is>
       </c>
       <c r="E648" s="20" t="n">
-        <v>232</v>
+        <v>223</v>
       </c>
     </row>
     <row r="649" ht="20" customHeight="1">
@@ -17253,7 +17253,7 @@
         </is>
       </c>
       <c r="E649" s="23" t="n">
-        <v>215</v>
+        <v>196</v>
       </c>
     </row>
     <row r="650" ht="20" customHeight="1">
@@ -17278,7 +17278,7 @@
         </is>
       </c>
       <c r="E650" s="20" t="n">
-        <v>131</v>
+        <v>180</v>
       </c>
     </row>
     <row r="651" ht="20" customHeight="1">
@@ -17303,7 +17303,7 @@
         </is>
       </c>
       <c r="E651" s="23" t="n">
-        <v>230</v>
+        <v>185</v>
       </c>
     </row>
     <row r="652" ht="20" customHeight="1">
@@ -17328,7 +17328,7 @@
         </is>
       </c>
       <c r="E652" s="20" t="n">
-        <v>133</v>
+        <v>203</v>
       </c>
     </row>
     <row r="653" ht="20" customHeight="1">
@@ -17353,7 +17353,7 @@
         </is>
       </c>
       <c r="E653" s="23" t="n">
-        <v>117</v>
+        <v>194</v>
       </c>
     </row>
     <row r="654" ht="20" customHeight="1">
@@ -17378,7 +17378,7 @@
         </is>
       </c>
       <c r="E654" s="20" t="n">
-        <v>161</v>
+        <v>228</v>
       </c>
     </row>
     <row r="655" ht="20" customHeight="1">
@@ -17403,7 +17403,7 @@
         </is>
       </c>
       <c r="E655" s="23" t="n">
-        <v>217</v>
+        <v>171</v>
       </c>
     </row>
     <row r="656" ht="20" customHeight="1">
@@ -17428,7 +17428,7 @@
         </is>
       </c>
       <c r="E656" s="20" t="n">
-        <v>173</v>
+        <v>212</v>
       </c>
     </row>
     <row r="657" ht="20" customHeight="1">
@@ -17453,7 +17453,7 @@
         </is>
       </c>
       <c r="E657" s="23" t="n">
-        <v>229</v>
+        <v>171</v>
       </c>
     </row>
     <row r="658" ht="20" customHeight="1">
@@ -17478,7 +17478,7 @@
         </is>
       </c>
       <c r="E658" s="20" t="n">
-        <v>123</v>
+        <v>237</v>
       </c>
     </row>
     <row r="659" ht="20" customHeight="1">
@@ -17503,7 +17503,7 @@
         </is>
       </c>
       <c r="E659" s="23" t="n">
-        <v>169</v>
+        <v>204</v>
       </c>
     </row>
     <row r="660" ht="20" customHeight="1">
@@ -17528,7 +17528,7 @@
         </is>
       </c>
       <c r="E660" s="20" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
     </row>
     <row r="661" ht="20" customHeight="1">
@@ -17553,7 +17553,7 @@
         </is>
       </c>
       <c r="E661" s="23" t="n">
-        <v>166</v>
+        <v>189</v>
       </c>
     </row>
     <row r="662" ht="20" customHeight="1">
@@ -17578,7 +17578,7 @@
         </is>
       </c>
       <c r="E662" s="20" t="n">
-        <v>147</v>
+        <v>186</v>
       </c>
     </row>
     <row r="663" ht="20" customHeight="1">
@@ -17603,7 +17603,7 @@
         </is>
       </c>
       <c r="E663" s="23" t="n">
-        <v>225</v>
+        <v>134</v>
       </c>
     </row>
     <row r="664" ht="20" customHeight="1">
@@ -17628,7 +17628,7 @@
         </is>
       </c>
       <c r="E664" s="20" t="n">
-        <v>223</v>
+        <v>114</v>
       </c>
     </row>
     <row r="665" ht="20" customHeight="1">
@@ -17653,7 +17653,7 @@
         </is>
       </c>
       <c r="E665" s="23" t="n">
-        <v>210</v>
+        <v>230</v>
       </c>
     </row>
     <row r="666" ht="20" customHeight="1">
@@ -17678,7 +17678,7 @@
         </is>
       </c>
       <c r="E666" s="20" t="n">
-        <v>209</v>
+        <v>143</v>
       </c>
     </row>
     <row r="667" ht="20" customHeight="1">
@@ -17703,7 +17703,7 @@
         </is>
       </c>
       <c r="E667" s="23" t="n">
-        <v>193</v>
+        <v>132</v>
       </c>
     </row>
     <row r="668" ht="20" customHeight="1">
@@ -17728,7 +17728,7 @@
         </is>
       </c>
       <c r="E668" s="20" t="n">
-        <v>205</v>
+        <v>174</v>
       </c>
     </row>
     <row r="669" ht="20" customHeight="1">
@@ -17753,7 +17753,7 @@
         </is>
       </c>
       <c r="E669" s="23" t="n">
-        <v>209</v>
+        <v>229</v>
       </c>
     </row>
     <row r="670" ht="20" customHeight="1">
@@ -17778,7 +17778,7 @@
         </is>
       </c>
       <c r="E670" s="20" t="n">
-        <v>176</v>
+        <v>227</v>
       </c>
     </row>
     <row r="671" ht="20" customHeight="1">
@@ -17803,7 +17803,7 @@
         </is>
       </c>
       <c r="E671" s="23" t="n">
-        <v>212</v>
+        <v>207</v>
       </c>
     </row>
     <row r="672" ht="20" customHeight="1">
@@ -17828,7 +17828,7 @@
         </is>
       </c>
       <c r="E672" s="20" t="n">
-        <v>144</v>
+        <v>150</v>
       </c>
     </row>
     <row r="673" ht="20" customHeight="1">
@@ -17853,7 +17853,7 @@
         </is>
       </c>
       <c r="E673" s="23" t="n">
-        <v>197</v>
+        <v>191</v>
       </c>
     </row>
     <row r="674" ht="20" customHeight="1">
@@ -17878,7 +17878,7 @@
         </is>
       </c>
       <c r="E674" s="20" t="n">
-        <v>199</v>
+        <v>148</v>
       </c>
     </row>
     <row r="675" ht="20" customHeight="1">
@@ -17903,7 +17903,7 @@
         </is>
       </c>
       <c r="E675" s="23" t="n">
-        <v>134</v>
+        <v>204</v>
       </c>
     </row>
     <row r="676" ht="20" customHeight="1">
@@ -17928,7 +17928,7 @@
         </is>
       </c>
       <c r="E676" s="20" t="n">
-        <v>110</v>
+        <v>171</v>
       </c>
     </row>
     <row r="677" ht="20" customHeight="1">
@@ -17953,7 +17953,7 @@
         </is>
       </c>
       <c r="E677" s="23" t="n">
-        <v>153</v>
+        <v>198</v>
       </c>
     </row>
     <row r="678" ht="20" customHeight="1">
@@ -17978,7 +17978,7 @@
         </is>
       </c>
       <c r="E678" s="20" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="679" ht="20" customHeight="1">
@@ -18003,7 +18003,7 @@
         </is>
       </c>
       <c r="E679" s="23" t="n">
-        <v>173</v>
+        <v>201</v>
       </c>
     </row>
     <row r="680" ht="20" customHeight="1">
@@ -18028,7 +18028,7 @@
         </is>
       </c>
       <c r="E680" s="20" t="n">
-        <v>146</v>
+        <v>236</v>
       </c>
     </row>
     <row r="681" ht="20" customHeight="1">
@@ -18053,7 +18053,7 @@
         </is>
       </c>
       <c r="E681" s="23" t="n">
-        <v>157</v>
+        <v>113</v>
       </c>
     </row>
     <row r="682" ht="20" customHeight="1">
@@ -18078,7 +18078,7 @@
         </is>
       </c>
       <c r="E682" s="20" t="n">
-        <v>197</v>
+        <v>152</v>
       </c>
     </row>
     <row r="683" ht="20" customHeight="1">
@@ -18103,7 +18103,7 @@
         </is>
       </c>
       <c r="E683" s="23" t="n">
-        <v>139</v>
+        <v>176</v>
       </c>
     </row>
     <row r="684" ht="20" customHeight="1">
@@ -18128,7 +18128,7 @@
         </is>
       </c>
       <c r="E684" s="20" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="685" ht="20" customHeight="1">
@@ -18153,7 +18153,7 @@
         </is>
       </c>
       <c r="E685" s="23" t="n">
-        <v>174</v>
+        <v>239</v>
       </c>
     </row>
     <row r="686" ht="20" customHeight="1">
@@ -18178,7 +18178,7 @@
         </is>
       </c>
       <c r="E686" s="20" t="n">
-        <v>198</v>
+        <v>183</v>
       </c>
     </row>
     <row r="687" ht="20" customHeight="1">
@@ -18203,7 +18203,7 @@
         </is>
       </c>
       <c r="E687" s="23" t="n">
-        <v>197</v>
+        <v>171</v>
       </c>
     </row>
     <row r="688" ht="20" customHeight="1">
@@ -18228,7 +18228,7 @@
         </is>
       </c>
       <c r="E688" s="20" t="n">
-        <v>162</v>
+        <v>141</v>
       </c>
     </row>
     <row r="689" ht="20" customHeight="1">
@@ -18253,7 +18253,7 @@
         </is>
       </c>
       <c r="E689" s="23" t="n">
-        <v>195</v>
+        <v>170</v>
       </c>
     </row>
     <row r="690" ht="20" customHeight="1">
@@ -18278,7 +18278,7 @@
         </is>
       </c>
       <c r="E690" s="20" t="n">
-        <v>221</v>
+        <v>155</v>
       </c>
     </row>
     <row r="691" ht="20" customHeight="1">
@@ -18303,7 +18303,7 @@
         </is>
       </c>
       <c r="E691" s="23" t="n">
-        <v>184</v>
+        <v>173</v>
       </c>
     </row>
     <row r="692" ht="20" customHeight="1">
@@ -18328,7 +18328,7 @@
         </is>
       </c>
       <c r="E692" s="20" t="n">
-        <v>231</v>
+        <v>190</v>
       </c>
     </row>
     <row r="693" ht="20" customHeight="1">
@@ -18353,7 +18353,7 @@
         </is>
       </c>
       <c r="E693" s="23" t="n">
-        <v>210</v>
+        <v>139</v>
       </c>
     </row>
     <row r="694" ht="20" customHeight="1">
@@ -18378,7 +18378,7 @@
         </is>
       </c>
       <c r="E694" s="20" t="n">
-        <v>187</v>
+        <v>162</v>
       </c>
     </row>
     <row r="695" ht="20" customHeight="1">
@@ -18403,7 +18403,7 @@
         </is>
       </c>
       <c r="E695" s="23" t="n">
-        <v>183</v>
+        <v>154</v>
       </c>
     </row>
     <row r="696" ht="20" customHeight="1">
@@ -18428,7 +18428,7 @@
         </is>
       </c>
       <c r="E696" s="20" t="n">
-        <v>206</v>
+        <v>132</v>
       </c>
     </row>
     <row r="697" ht="20" customHeight="1">
@@ -18453,7 +18453,7 @@
         </is>
       </c>
       <c r="E697" s="23" t="n">
-        <v>166</v>
+        <v>196</v>
       </c>
     </row>
     <row r="698" ht="20" customHeight="1">
@@ -18478,7 +18478,7 @@
         </is>
       </c>
       <c r="E698" s="20" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="699" ht="20" customHeight="1">
@@ -18503,7 +18503,7 @@
         </is>
       </c>
       <c r="E699" s="23" t="n">
-        <v>185</v>
+        <v>159</v>
       </c>
     </row>
     <row r="700" ht="20" customHeight="1">
@@ -18528,7 +18528,7 @@
         </is>
       </c>
       <c r="E700" s="20" t="n">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="701" ht="20" customHeight="1">
@@ -18553,7 +18553,7 @@
         </is>
       </c>
       <c r="E701" s="23" t="n">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="702" ht="20" customHeight="1">
@@ -18578,7 +18578,7 @@
         </is>
       </c>
       <c r="E702" s="20" t="n">
-        <v>128</v>
+        <v>234</v>
       </c>
     </row>
     <row r="703" ht="20" customHeight="1">
@@ -18603,7 +18603,7 @@
         </is>
       </c>
       <c r="E703" s="23" t="n">
-        <v>221</v>
+        <v>184</v>
       </c>
     </row>
     <row r="704" ht="20" customHeight="1">
@@ -18628,7 +18628,7 @@
         </is>
       </c>
       <c r="E704" s="20" t="n">
-        <v>233</v>
+        <v>213</v>
       </c>
     </row>
     <row r="705" ht="20" customHeight="1">
@@ -18653,7 +18653,7 @@
         </is>
       </c>
       <c r="E705" s="23" t="n">
-        <v>235</v>
+        <v>231</v>
       </c>
     </row>
     <row r="706" ht="20" customHeight="1">
@@ -18678,7 +18678,7 @@
         </is>
       </c>
       <c r="E706" s="20" t="n">
-        <v>122</v>
+        <v>234</v>
       </c>
     </row>
     <row r="707" ht="20" customHeight="1">
@@ -18703,7 +18703,7 @@
         </is>
       </c>
       <c r="E707" s="23" t="n">
-        <v>213</v>
+        <v>162</v>
       </c>
     </row>
     <row r="708" ht="20" customHeight="1">
@@ -18728,7 +18728,7 @@
         </is>
       </c>
       <c r="E708" s="20" t="n">
-        <v>206</v>
+        <v>234</v>
       </c>
     </row>
     <row r="709" ht="20" customHeight="1">
@@ -18753,7 +18753,7 @@
         </is>
       </c>
       <c r="E709" s="23" t="n">
-        <v>186</v>
+        <v>164</v>
       </c>
     </row>
     <row r="710" ht="20" customHeight="1">
@@ -18778,7 +18778,7 @@
         </is>
       </c>
       <c r="E710" s="20" t="n">
-        <v>238</v>
+        <v>144</v>
       </c>
     </row>
     <row r="711" ht="20" customHeight="1">
@@ -18803,7 +18803,7 @@
         </is>
       </c>
       <c r="E711" s="23" t="n">
-        <v>122</v>
+        <v>190</v>
       </c>
     </row>
     <row r="712" ht="20" customHeight="1">
@@ -18828,7 +18828,7 @@
         </is>
       </c>
       <c r="E712" s="20" t="n">
-        <v>159</v>
+        <v>236</v>
       </c>
     </row>
     <row r="713" ht="20" customHeight="1">
@@ -18853,7 +18853,7 @@
         </is>
       </c>
       <c r="E713" s="23" t="n">
-        <v>240</v>
+        <v>173</v>
       </c>
     </row>
     <row r="714" ht="20" customHeight="1">
@@ -18878,7 +18878,7 @@
         </is>
       </c>
       <c r="E714" s="20" t="n">
-        <v>183</v>
+        <v>123</v>
       </c>
     </row>
     <row r="715" ht="20" customHeight="1">
@@ -18903,7 +18903,7 @@
         </is>
       </c>
       <c r="E715" s="23" t="n">
-        <v>117</v>
+        <v>130</v>
       </c>
     </row>
     <row r="716" ht="20" customHeight="1">
@@ -18928,7 +18928,7 @@
         </is>
       </c>
       <c r="E716" s="20" t="n">
-        <v>211</v>
+        <v>236</v>
       </c>
     </row>
     <row r="717" ht="20" customHeight="1">
@@ -18953,7 +18953,7 @@
         </is>
       </c>
       <c r="E717" s="23" t="n">
-        <v>134</v>
+        <v>112</v>
       </c>
     </row>
     <row r="718" ht="20" customHeight="1">
@@ -18978,7 +18978,7 @@
         </is>
       </c>
       <c r="E718" s="20" t="n">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="719" ht="20" customHeight="1">
@@ -19003,7 +19003,7 @@
         </is>
       </c>
       <c r="E719" s="23" t="n">
-        <v>119</v>
+        <v>127</v>
       </c>
     </row>
     <row r="720" ht="20" customHeight="1">
@@ -19028,7 +19028,7 @@
         </is>
       </c>
       <c r="E720" s="20" t="n">
-        <v>203</v>
+        <v>179</v>
       </c>
     </row>
     <row r="721" ht="20" customHeight="1">
@@ -19053,7 +19053,7 @@
         </is>
       </c>
       <c r="E721" s="23" t="n">
-        <v>217</v>
+        <v>192</v>
       </c>
     </row>
     <row r="722" ht="20" customHeight="1">
@@ -19078,7 +19078,7 @@
         </is>
       </c>
       <c r="E722" s="20" t="n">
-        <v>189</v>
+        <v>115</v>
       </c>
     </row>
     <row r="723" ht="20" customHeight="1">
@@ -19103,7 +19103,7 @@
         </is>
       </c>
       <c r="E723" s="23" t="n">
-        <v>208</v>
+        <v>183</v>
       </c>
     </row>
     <row r="724" ht="20" customHeight="1">
@@ -19128,7 +19128,7 @@
         </is>
       </c>
       <c r="E724" s="20" t="n">
-        <v>211</v>
+        <v>201</v>
       </c>
     </row>
     <row r="725" ht="20" customHeight="1">
@@ -19153,7 +19153,7 @@
         </is>
       </c>
       <c r="E725" s="23" t="n">
-        <v>189</v>
+        <v>118</v>
       </c>
     </row>
     <row r="726" ht="20" customHeight="1">
@@ -19178,7 +19178,7 @@
         </is>
       </c>
       <c r="E726" s="20" t="n">
-        <v>231</v>
+        <v>116</v>
       </c>
     </row>
     <row r="727" ht="20" customHeight="1">
@@ -19203,7 +19203,7 @@
         </is>
       </c>
       <c r="E727" s="23" t="n">
-        <v>203</v>
+        <v>156</v>
       </c>
     </row>
     <row r="728" ht="20" customHeight="1">
@@ -19228,7 +19228,7 @@
         </is>
       </c>
       <c r="E728" s="20" t="n">
-        <v>203</v>
+        <v>133</v>
       </c>
     </row>
     <row r="729" ht="20" customHeight="1">
@@ -19253,7 +19253,7 @@
         </is>
       </c>
       <c r="E729" s="23" t="n">
-        <v>110</v>
+        <v>185</v>
       </c>
     </row>
     <row r="730" ht="20" customHeight="1">
@@ -19278,7 +19278,7 @@
         </is>
       </c>
       <c r="E730" s="20" t="n">
-        <v>168</v>
+        <v>218</v>
       </c>
     </row>
     <row r="731" ht="20" customHeight="1">
@@ -19303,7 +19303,7 @@
         </is>
       </c>
       <c r="E731" s="23" t="n">
-        <v>111</v>
+        <v>213</v>
       </c>
     </row>
     <row r="732" ht="20" customHeight="1">
@@ -19328,7 +19328,7 @@
         </is>
       </c>
       <c r="E732" s="20" t="n">
-        <v>220</v>
+        <v>153</v>
       </c>
     </row>
     <row r="733" ht="20" customHeight="1">
@@ -19353,7 +19353,7 @@
         </is>
       </c>
       <c r="E733" s="23" t="n">
-        <v>173</v>
+        <v>187</v>
       </c>
     </row>
     <row r="734" ht="20" customHeight="1">
@@ -19378,7 +19378,7 @@
         </is>
       </c>
       <c r="E734" s="20" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="735" ht="20" customHeight="1">
@@ -19403,7 +19403,7 @@
         </is>
       </c>
       <c r="E735" s="23" t="n">
-        <v>166</v>
+        <v>215</v>
       </c>
     </row>
     <row r="736" ht="20" customHeight="1">
@@ -19428,7 +19428,7 @@
         </is>
       </c>
       <c r="E736" s="20" t="n">
-        <v>184</v>
+        <v>165</v>
       </c>
     </row>
     <row r="737" ht="20" customHeight="1">
@@ -19453,7 +19453,7 @@
         </is>
       </c>
       <c r="E737" s="23" t="n">
-        <v>212</v>
+        <v>183</v>
       </c>
     </row>
     <row r="738" ht="20" customHeight="1">
@@ -19478,7 +19478,7 @@
         </is>
       </c>
       <c r="E738" s="20" t="n">
-        <v>170</v>
+        <v>138</v>
       </c>
     </row>
     <row r="739" ht="20" customHeight="1">
@@ -19503,7 +19503,7 @@
         </is>
       </c>
       <c r="E739" s="23" t="n">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="740" ht="20" customHeight="1">
@@ -19528,7 +19528,7 @@
         </is>
       </c>
       <c r="E740" s="20" t="n">
-        <v>116</v>
+        <v>224</v>
       </c>
     </row>
     <row r="741" ht="20" customHeight="1">
@@ -19553,7 +19553,7 @@
         </is>
       </c>
       <c r="E741" s="23" t="n">
-        <v>143</v>
+        <v>115</v>
       </c>
     </row>
     <row r="742" ht="20" customHeight="1">
@@ -19578,7 +19578,7 @@
         </is>
       </c>
       <c r="E742" s="20" t="n">
-        <v>168</v>
+        <v>138</v>
       </c>
     </row>
     <row r="743" ht="20" customHeight="1">
@@ -19603,7 +19603,7 @@
         </is>
       </c>
       <c r="E743" s="23" t="n">
-        <v>152</v>
+        <v>237</v>
       </c>
     </row>
     <row r="744" ht="20" customHeight="1">
@@ -19628,7 +19628,7 @@
         </is>
       </c>
       <c r="E744" s="20" t="n">
-        <v>170</v>
+        <v>220</v>
       </c>
     </row>
     <row r="745" ht="20" customHeight="1">
@@ -19653,7 +19653,7 @@
         </is>
       </c>
       <c r="E745" s="23" t="n">
-        <v>135</v>
+        <v>208</v>
       </c>
     </row>
     <row r="746" ht="20" customHeight="1">
@@ -19678,7 +19678,7 @@
         </is>
       </c>
       <c r="E746" s="20" t="n">
-        <v>217</v>
+        <v>240</v>
       </c>
     </row>
     <row r="747" ht="20" customHeight="1">
@@ -19703,7 +19703,7 @@
         </is>
       </c>
       <c r="E747" s="23" t="n">
-        <v>125</v>
+        <v>167</v>
       </c>
     </row>
     <row r="748" ht="20" customHeight="1">
@@ -19728,7 +19728,7 @@
         </is>
       </c>
       <c r="E748" s="20" t="n">
-        <v>213</v>
+        <v>195</v>
       </c>
     </row>
     <row r="749" ht="20" customHeight="1">
@@ -19753,7 +19753,7 @@
         </is>
       </c>
       <c r="E749" s="23" t="n">
-        <v>229</v>
+        <v>204</v>
       </c>
     </row>
     <row r="750" ht="20" customHeight="1">
@@ -19778,7 +19778,7 @@
         </is>
       </c>
       <c r="E750" s="20" t="n">
-        <v>182</v>
+        <v>121</v>
       </c>
     </row>
     <row r="751" ht="20" customHeight="1">
@@ -19803,7 +19803,7 @@
         </is>
       </c>
       <c r="E751" s="23" t="n">
-        <v>143</v>
+        <v>183</v>
       </c>
     </row>
     <row r="752" ht="20" customHeight="1">
@@ -19828,7 +19828,7 @@
         </is>
       </c>
       <c r="E752" s="20" t="n">
-        <v>155</v>
+        <v>201</v>
       </c>
     </row>
     <row r="753" ht="20" customHeight="1">
@@ -19853,7 +19853,7 @@
         </is>
       </c>
       <c r="E753" s="23" t="n">
-        <v>205</v>
+        <v>182</v>
       </c>
     </row>
     <row r="754" ht="20" customHeight="1">
@@ -19878,7 +19878,7 @@
         </is>
       </c>
       <c r="E754" s="20" t="n">
-        <v>207</v>
+        <v>228</v>
       </c>
     </row>
     <row r="755" ht="20" customHeight="1">
@@ -19903,7 +19903,7 @@
         </is>
       </c>
       <c r="E755" s="23" t="n">
-        <v>229</v>
+        <v>212</v>
       </c>
     </row>
     <row r="756" ht="20" customHeight="1">
@@ -19928,7 +19928,7 @@
         </is>
       </c>
       <c r="E756" s="20" t="n">
-        <v>189</v>
+        <v>167</v>
       </c>
     </row>
     <row r="757" ht="20" customHeight="1">
@@ -19953,7 +19953,7 @@
         </is>
       </c>
       <c r="E757" s="23" t="n">
-        <v>176</v>
+        <v>143</v>
       </c>
     </row>
     <row r="758" ht="20" customHeight="1">
@@ -20003,7 +20003,7 @@
         </is>
       </c>
       <c r="E759" s="23" t="n">
-        <v>137</v>
+        <v>199</v>
       </c>
     </row>
     <row r="760" ht="20" customHeight="1">
@@ -20028,7 +20028,7 @@
         </is>
       </c>
       <c r="E760" s="20" t="n">
-        <v>140</v>
+        <v>232</v>
       </c>
     </row>
     <row r="761" ht="20" customHeight="1">
@@ -20053,7 +20053,7 @@
         </is>
       </c>
       <c r="E761" s="23" t="n">
-        <v>220</v>
+        <v>113</v>
       </c>
     </row>
     <row r="762" ht="20" customHeight="1">
@@ -20078,7 +20078,7 @@
         </is>
       </c>
       <c r="E762" s="20" t="n">
-        <v>144</v>
+        <v>158</v>
       </c>
     </row>
     <row r="763" ht="20" customHeight="1">
@@ -20103,7 +20103,7 @@
         </is>
       </c>
       <c r="E763" s="23" t="n">
-        <v>166</v>
+        <v>130</v>
       </c>
     </row>
     <row r="764" ht="20" customHeight="1">
@@ -20128,7 +20128,7 @@
         </is>
       </c>
       <c r="E764" s="20" t="n">
-        <v>152</v>
+        <v>122</v>
       </c>
     </row>
     <row r="765" ht="20" customHeight="1">
@@ -20153,7 +20153,7 @@
         </is>
       </c>
       <c r="E765" s="23" t="n">
-        <v>174</v>
+        <v>148</v>
       </c>
     </row>
     <row r="766" ht="20" customHeight="1">
@@ -20178,7 +20178,7 @@
         </is>
       </c>
       <c r="E766" s="20" t="n">
-        <v>222</v>
+        <v>160</v>
       </c>
     </row>
     <row r="767" ht="20" customHeight="1">
@@ -20203,7 +20203,7 @@
         </is>
       </c>
       <c r="E767" s="23" t="n">
-        <v>200</v>
+        <v>119</v>
       </c>
     </row>
     <row r="768" ht="20" customHeight="1">
@@ -20253,7 +20253,7 @@
         </is>
       </c>
       <c r="E769" s="23" t="n">
-        <v>146</v>
+        <v>180</v>
       </c>
     </row>
     <row r="770" ht="20" customHeight="1">
@@ -20278,7 +20278,7 @@
         </is>
       </c>
       <c r="E770" s="20" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="771" ht="20" customHeight="1">
@@ -20303,7 +20303,7 @@
         </is>
       </c>
       <c r="E771" s="23" t="n">
-        <v>187</v>
+        <v>181</v>
       </c>
     </row>
     <row r="772" ht="20" customHeight="1">
@@ -20328,7 +20328,7 @@
         </is>
       </c>
       <c r="E772" s="20" t="n">
-        <v>135</v>
+        <v>200</v>
       </c>
     </row>
     <row r="773" ht="20" customHeight="1">
@@ -20353,7 +20353,7 @@
         </is>
       </c>
       <c r="E773" s="23" t="n">
-        <v>195</v>
+        <v>178</v>
       </c>
     </row>
     <row r="774" ht="20" customHeight="1">
@@ -20378,7 +20378,7 @@
         </is>
       </c>
       <c r="E774" s="20" t="n">
-        <v>167</v>
+        <v>148</v>
       </c>
     </row>
     <row r="775" ht="20" customHeight="1">
@@ -20403,7 +20403,7 @@
         </is>
       </c>
       <c r="E775" s="23" t="n">
-        <v>180</v>
+        <v>149</v>
       </c>
     </row>
     <row r="776" ht="20" customHeight="1">
@@ -20428,7 +20428,7 @@
         </is>
       </c>
       <c r="E776" s="20" t="n">
-        <v>226</v>
+        <v>239</v>
       </c>
     </row>
     <row r="777" ht="20" customHeight="1">
@@ -20453,7 +20453,7 @@
         </is>
       </c>
       <c r="E777" s="23" t="n">
-        <v>221</v>
+        <v>163</v>
       </c>
     </row>
     <row r="778" ht="20" customHeight="1">
@@ -20478,7 +20478,7 @@
         </is>
       </c>
       <c r="E778" s="20" t="n">
-        <v>238</v>
+        <v>146</v>
       </c>
     </row>
     <row r="779" ht="20" customHeight="1">
@@ -20503,7 +20503,7 @@
         </is>
       </c>
       <c r="E779" s="23" t="n">
-        <v>218</v>
+        <v>190</v>
       </c>
     </row>
     <row r="780" ht="20" customHeight="1">
@@ -20528,7 +20528,7 @@
         </is>
       </c>
       <c r="E780" s="20" t="n">
-        <v>166</v>
+        <v>239</v>
       </c>
     </row>
     <row r="781" ht="20" customHeight="1">
@@ -20553,7 +20553,7 @@
         </is>
       </c>
       <c r="E781" s="23" t="n">
-        <v>210</v>
+        <v>147</v>
       </c>
     </row>
     <row r="782" ht="20" customHeight="1">
@@ -20578,7 +20578,7 @@
         </is>
       </c>
       <c r="E782" s="20" t="n">
-        <v>118</v>
+        <v>129</v>
       </c>
     </row>
     <row r="783" ht="20" customHeight="1">
@@ -20603,7 +20603,7 @@
         </is>
       </c>
       <c r="E783" s="23" t="n">
-        <v>157</v>
+        <v>193</v>
       </c>
     </row>
     <row r="784" ht="20" customHeight="1">
@@ -20628,7 +20628,7 @@
         </is>
       </c>
       <c r="E784" s="20" t="n">
-        <v>193</v>
+        <v>175</v>
       </c>
     </row>
     <row r="785" ht="20" customHeight="1">
@@ -20653,7 +20653,7 @@
         </is>
       </c>
       <c r="E785" s="23" t="n">
-        <v>138</v>
+        <v>167</v>
       </c>
     </row>
     <row r="786" ht="20" customHeight="1">
@@ -20678,7 +20678,7 @@
         </is>
       </c>
       <c r="E786" s="20" t="n">
-        <v>114</v>
+        <v>126</v>
       </c>
     </row>
     <row r="787" ht="20" customHeight="1">
@@ -20703,7 +20703,7 @@
         </is>
       </c>
       <c r="E787" s="23" t="n">
-        <v>142</v>
+        <v>212</v>
       </c>
     </row>
     <row r="788" ht="20" customHeight="1">
@@ -20728,7 +20728,7 @@
         </is>
       </c>
       <c r="E788" s="20" t="n">
-        <v>191</v>
+        <v>168</v>
       </c>
     </row>
     <row r="789" ht="20" customHeight="1">
@@ -20753,7 +20753,7 @@
         </is>
       </c>
       <c r="E789" s="23" t="n">
-        <v>112</v>
+        <v>119</v>
       </c>
     </row>
     <row r="790" ht="20" customHeight="1">
@@ -20778,7 +20778,7 @@
         </is>
       </c>
       <c r="E790" s="20" t="n">
-        <v>180</v>
+        <v>112</v>
       </c>
     </row>
     <row r="791" ht="20" customHeight="1">
@@ -20803,7 +20803,7 @@
         </is>
       </c>
       <c r="E791" s="23" t="n">
-        <v>217</v>
+        <v>164</v>
       </c>
     </row>
     <row r="792" ht="20" customHeight="1">
@@ -20828,7 +20828,7 @@
         </is>
       </c>
       <c r="E792" s="20" t="n">
-        <v>115</v>
+        <v>197</v>
       </c>
     </row>
     <row r="793" ht="20" customHeight="1">
@@ -20853,7 +20853,7 @@
         </is>
       </c>
       <c r="E793" s="23" t="n">
-        <v>231</v>
+        <v>131</v>
       </c>
     </row>
     <row r="794" ht="20" customHeight="1">
@@ -20878,7 +20878,7 @@
         </is>
       </c>
       <c r="E794" s="20" t="n">
-        <v>220</v>
+        <v>195</v>
       </c>
     </row>
     <row r="795" ht="20" customHeight="1">
@@ -20903,7 +20903,7 @@
         </is>
       </c>
       <c r="E795" s="23" t="n">
-        <v>210</v>
+        <v>167</v>
       </c>
     </row>
     <row r="796" ht="20" customHeight="1">
@@ -20928,7 +20928,7 @@
         </is>
       </c>
       <c r="E796" s="20" t="n">
-        <v>208</v>
+        <v>132</v>
       </c>
     </row>
     <row r="797" ht="20" customHeight="1">
@@ -20953,7 +20953,7 @@
         </is>
       </c>
       <c r="E797" s="23" t="n">
-        <v>220</v>
+        <v>234</v>
       </c>
     </row>
     <row r="798" ht="20" customHeight="1">
@@ -20978,7 +20978,7 @@
         </is>
       </c>
       <c r="E798" s="20" t="n">
-        <v>183</v>
+        <v>222</v>
       </c>
     </row>
     <row r="799" ht="20" customHeight="1">
@@ -21003,7 +21003,7 @@
         </is>
       </c>
       <c r="E799" s="23" t="n">
-        <v>176</v>
+        <v>235</v>
       </c>
     </row>
     <row r="800" ht="20" customHeight="1">
@@ -21028,7 +21028,7 @@
         </is>
       </c>
       <c r="E800" s="20" t="n">
-        <v>160</v>
+        <v>174</v>
       </c>
     </row>
     <row r="801" ht="20" customHeight="1">
@@ -21053,7 +21053,7 @@
         </is>
       </c>
       <c r="E801" s="23" t="n">
-        <v>112</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>

--- a/Appium_E2E_Test_Report_Traverse.xlsx
+++ b/Appium_E2E_Test_Report_Traverse.xlsx
@@ -791,7 +791,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 06:34:24</t>
+          <t>2026-08-11 07:36:11</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="E2" s="20" t="n">
-        <v>112</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="E3" s="23" t="n">
-        <v>137</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="E4" s="20" t="n">
-        <v>117</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="E5" s="23" t="n">
-        <v>124</v>
+        <v>208</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="E6" s="20" t="n">
-        <v>142</v>
+        <v>202</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="E7" s="23" t="n">
-        <v>200</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -1228,7 +1228,7 @@
         </is>
       </c>
       <c r="E8" s="20" t="n">
-        <v>234</v>
+        <v>172</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="E9" s="23" t="n">
-        <v>197</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
@@ -1278,7 +1278,7 @@
         </is>
       </c>
       <c r="E10" s="20" t="n">
-        <v>193</v>
+        <v>223</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="E11" s="23" t="n">
-        <v>201</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
@@ -1328,7 +1328,7 @@
         </is>
       </c>
       <c r="E12" s="20" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="E13" s="23" t="n">
-        <v>185</v>
+        <v>218</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="E14" s="20" t="n">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="E15" s="23" t="n">
-        <v>141</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="E16" s="20" t="n">
-        <v>131</v>
+        <v>149</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="E17" s="23" t="n">
-        <v>233</v>
+        <v>175</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -1478,7 +1478,7 @@
         </is>
       </c>
       <c r="E18" s="20" t="n">
-        <v>178</v>
+        <v>121</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
@@ -1503,7 +1503,7 @@
         </is>
       </c>
       <c r="E19" s="23" t="n">
-        <v>221</v>
+        <v>179</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="E20" s="20" t="n">
-        <v>185</v>
+        <v>168</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="E21" s="23" t="n">
-        <v>196</v>
+        <v>188</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
@@ -1578,7 +1578,7 @@
         </is>
       </c>
       <c r="E22" s="20" t="n">
-        <v>190</v>
+        <v>126</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="E23" s="23" t="n">
-        <v>154</v>
+        <v>207</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
@@ -1628,7 +1628,7 @@
         </is>
       </c>
       <c r="E24" s="20" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="E25" s="23" t="n">
-        <v>220</v>
+        <v>205</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
@@ -1678,7 +1678,7 @@
         </is>
       </c>
       <c r="E26" s="20" t="n">
-        <v>195</v>
+        <v>172</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="E27" s="23" t="n">
-        <v>138</v>
+        <v>200</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="E28" s="20" t="n">
-        <v>203</v>
+        <v>214</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="E29" s="23" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="E30" s="20" t="n">
-        <v>128</v>
+        <v>159</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
@@ -1803,7 +1803,7 @@
         </is>
       </c>
       <c r="E31" s="23" t="n">
-        <v>235</v>
+        <v>145</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
@@ -1828,7 +1828,7 @@
         </is>
       </c>
       <c r="E32" s="20" t="n">
-        <v>227</v>
+        <v>208</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
@@ -1853,7 +1853,7 @@
         </is>
       </c>
       <c r="E33" s="23" t="n">
-        <v>236</v>
+        <v>213</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
@@ -1878,7 +1878,7 @@
         </is>
       </c>
       <c r="E34" s="20" t="n">
-        <v>181</v>
+        <v>210</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="E35" s="23" t="n">
-        <v>207</v>
+        <v>145</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="E36" s="20" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="E37" s="23" t="n">
-        <v>219</v>
+        <v>161</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
@@ -1978,7 +1978,7 @@
         </is>
       </c>
       <c r="E38" s="20" t="n">
-        <v>122</v>
+        <v>203</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="E39" s="23" t="n">
-        <v>215</v>
+        <v>204</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="E40" s="20" t="n">
-        <v>227</v>
+        <v>205</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="E41" s="23" t="n">
-        <v>151</v>
+        <v>232</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
@@ -2078,7 +2078,7 @@
         </is>
       </c>
       <c r="E42" s="20" t="n">
-        <v>208</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="E43" s="23" t="n">
-        <v>183</v>
+        <v>207</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="E44" s="20" t="n">
-        <v>114</v>
+        <v>151</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="E45" s="23" t="n">
-        <v>237</v>
+        <v>143</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
@@ -2178,7 +2178,7 @@
         </is>
       </c>
       <c r="E46" s="20" t="n">
-        <v>228</v>
+        <v>213</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
@@ -2203,7 +2203,7 @@
         </is>
       </c>
       <c r="E47" s="23" t="n">
-        <v>237</v>
+        <v>166</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="E48" s="20" t="n">
-        <v>216</v>
+        <v>143</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
@@ -2253,7 +2253,7 @@
         </is>
       </c>
       <c r="E49" s="23" t="n">
-        <v>116</v>
+        <v>233</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
@@ -2278,7 +2278,7 @@
         </is>
       </c>
       <c r="E50" s="20" t="n">
-        <v>155</v>
+        <v>196</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="E51" s="23" t="n">
-        <v>177</v>
+        <v>112</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
@@ -2328,7 +2328,7 @@
         </is>
       </c>
       <c r="E52" s="20" t="n">
-        <v>170</v>
+        <v>178</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
@@ -2353,7 +2353,7 @@
         </is>
       </c>
       <c r="E53" s="23" t="n">
-        <v>141</v>
+        <v>225</v>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="E54" s="20" t="n">
-        <v>240</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1">
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="E55" s="23" t="n">
-        <v>185</v>
+        <v>117</v>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1">
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="E56" s="20" t="n">
-        <v>214</v>
+        <v>120</v>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1">
@@ -2453,7 +2453,7 @@
         </is>
       </c>
       <c r="E57" s="23" t="n">
-        <v>113</v>
+        <v>139</v>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1">
@@ -2478,7 +2478,7 @@
         </is>
       </c>
       <c r="E58" s="20" t="n">
-        <v>161</v>
+        <v>214</v>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1">
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="E59" s="23" t="n">
-        <v>213</v>
+        <v>124</v>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1">
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="E60" s="20" t="n">
-        <v>159</v>
+        <v>148</v>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
@@ -2553,7 +2553,7 @@
         </is>
       </c>
       <c r="E61" s="23" t="n">
-        <v>118</v>
+        <v>180</v>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="E62" s="20" t="n">
-        <v>206</v>
+        <v>185</v>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="E63" s="23" t="n">
-        <v>234</v>
+        <v>126</v>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1">
@@ -2628,7 +2628,7 @@
         </is>
       </c>
       <c r="E64" s="20" t="n">
-        <v>204</v>
+        <v>158</v>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1">
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="E65" s="23" t="n">
-        <v>213</v>
+        <v>173</v>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1">
@@ -2678,7 +2678,7 @@
         </is>
       </c>
       <c r="E66" s="20" t="n">
-        <v>111</v>
+        <v>175</v>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="E67" s="23" t="n">
-        <v>116</v>
+        <v>186</v>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="E68" s="20" t="n">
-        <v>211</v>
+        <v>121</v>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="E69" s="23" t="n">
-        <v>223</v>
+        <v>217</v>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1">
@@ -2778,7 +2778,7 @@
         </is>
       </c>
       <c r="E70" s="20" t="n">
-        <v>237</v>
+        <v>191</v>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1">
@@ -2803,7 +2803,7 @@
         </is>
       </c>
       <c r="E71" s="23" t="n">
-        <v>227</v>
+        <v>184</v>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1">
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="E72" s="20" t="n">
-        <v>203</v>
+        <v>223</v>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1">
@@ -2853,7 +2853,7 @@
         </is>
       </c>
       <c r="E73" s="23" t="n">
-        <v>207</v>
+        <v>165</v>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
@@ -2878,7 +2878,7 @@
         </is>
       </c>
       <c r="E74" s="20" t="n">
-        <v>181</v>
+        <v>123</v>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="E75" s="23" t="n">
-        <v>140</v>
+        <v>128</v>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
@@ -2928,7 +2928,7 @@
         </is>
       </c>
       <c r="E76" s="20" t="n">
-        <v>178</v>
+        <v>137</v>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="E77" s="23" t="n">
-        <v>156</v>
+        <v>231</v>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1">
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="E78" s="20" t="n">
-        <v>157</v>
+        <v>152</v>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
@@ -3003,7 +3003,7 @@
         </is>
       </c>
       <c r="E79" s="23" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1">
@@ -3028,7 +3028,7 @@
         </is>
       </c>
       <c r="E80" s="20" t="n">
-        <v>201</v>
+        <v>215</v>
       </c>
     </row>
     <row r="81" ht="20" customHeight="1">
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="E81" s="23" t="n">
-        <v>148</v>
+        <v>238</v>
       </c>
     </row>
     <row r="82" ht="20" customHeight="1">
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="E82" s="20" t="n">
-        <v>182</v>
+        <v>176</v>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1">
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="E83" s="23" t="n">
-        <v>217</v>
+        <v>118</v>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1">
@@ -3128,7 +3128,7 @@
         </is>
       </c>
       <c r="E84" s="20" t="n">
-        <v>185</v>
+        <v>214</v>
       </c>
     </row>
     <row r="85" ht="20" customHeight="1">
@@ -3153,7 +3153,7 @@
         </is>
       </c>
       <c r="E85" s="23" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="86" ht="20" customHeight="1">
@@ -3178,7 +3178,7 @@
         </is>
       </c>
       <c r="E86" s="20" t="n">
-        <v>127</v>
+        <v>145</v>
       </c>
     </row>
     <row r="87" ht="20" customHeight="1">
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="E87" s="23" t="n">
-        <v>147</v>
+        <v>155</v>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1">
@@ -3228,7 +3228,7 @@
         </is>
       </c>
       <c r="E88" s="20" t="n">
-        <v>119</v>
+        <v>174</v>
       </c>
     </row>
     <row r="89" ht="20" customHeight="1">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="E89" s="23" t="n">
-        <v>193</v>
+        <v>117</v>
       </c>
     </row>
     <row r="90" ht="20" customHeight="1">
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="E90" s="20" t="n">
-        <v>139</v>
+        <v>224</v>
       </c>
     </row>
     <row r="91" ht="20" customHeight="1">
@@ -3303,7 +3303,7 @@
         </is>
       </c>
       <c r="E91" s="23" t="n">
-        <v>201</v>
+        <v>166</v>
       </c>
     </row>
     <row r="92" ht="20" customHeight="1">
@@ -3328,7 +3328,7 @@
         </is>
       </c>
       <c r="E92" s="20" t="n">
-        <v>228</v>
+        <v>134</v>
       </c>
     </row>
     <row r="93" ht="20" customHeight="1">
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="E93" s="23" t="n">
-        <v>156</v>
+        <v>190</v>
       </c>
     </row>
     <row r="94" ht="20" customHeight="1">
@@ -3378,7 +3378,7 @@
         </is>
       </c>
       <c r="E94" s="20" t="n">
-        <v>144</v>
+        <v>131</v>
       </c>
     </row>
     <row r="95" ht="20" customHeight="1">
@@ -3403,7 +3403,7 @@
         </is>
       </c>
       <c r="E95" s="23" t="n">
-        <v>113</v>
+        <v>213</v>
       </c>
     </row>
     <row r="96" ht="20" customHeight="1">
@@ -3428,7 +3428,7 @@
         </is>
       </c>
       <c r="E96" s="20" t="n">
-        <v>115</v>
+        <v>135</v>
       </c>
     </row>
     <row r="97" ht="20" customHeight="1">
@@ -3453,7 +3453,7 @@
         </is>
       </c>
       <c r="E97" s="23" t="n">
-        <v>152</v>
+        <v>181</v>
       </c>
     </row>
     <row r="98" ht="20" customHeight="1">
@@ -3478,7 +3478,7 @@
         </is>
       </c>
       <c r="E98" s="20" t="n">
-        <v>211</v>
+        <v>135</v>
       </c>
     </row>
     <row r="99" ht="20" customHeight="1">
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="E99" s="23" t="n">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="100" ht="20" customHeight="1">
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="E100" s="20" t="n">
-        <v>228</v>
+        <v>154</v>
       </c>
     </row>
     <row r="101" ht="20" customHeight="1">
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="E101" s="23" t="n">
-        <v>118</v>
+        <v>157</v>
       </c>
     </row>
     <row r="102" ht="20" customHeight="1">
@@ -3578,7 +3578,7 @@
         </is>
       </c>
       <c r="E102" s="20" t="n">
-        <v>200</v>
+        <v>164</v>
       </c>
     </row>
     <row r="103" ht="20" customHeight="1">
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="E103" s="23" t="n">
-        <v>116</v>
+        <v>130</v>
       </c>
     </row>
     <row r="104" ht="20" customHeight="1">
@@ -3628,7 +3628,7 @@
         </is>
       </c>
       <c r="E104" s="20" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="105" ht="20" customHeight="1">
@@ -3653,7 +3653,7 @@
         </is>
       </c>
       <c r="E105" s="23" t="n">
-        <v>161</v>
+        <v>118</v>
       </c>
     </row>
     <row r="106" ht="20" customHeight="1">
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="E106" s="20" t="n">
-        <v>218</v>
+        <v>167</v>
       </c>
     </row>
     <row r="107" ht="20" customHeight="1">
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="E107" s="23" t="n">
-        <v>217</v>
+        <v>222</v>
       </c>
     </row>
     <row r="108" ht="20" customHeight="1">
@@ -3728,7 +3728,7 @@
         </is>
       </c>
       <c r="E108" s="20" t="n">
-        <v>155</v>
+        <v>214</v>
       </c>
     </row>
     <row r="109" ht="20" customHeight="1">
@@ -3753,7 +3753,7 @@
         </is>
       </c>
       <c r="E109" s="23" t="n">
-        <v>228</v>
+        <v>238</v>
       </c>
     </row>
     <row r="110" ht="20" customHeight="1">
@@ -3778,7 +3778,7 @@
         </is>
       </c>
       <c r="E110" s="20" t="n">
-        <v>211</v>
+        <v>159</v>
       </c>
     </row>
     <row r="111" ht="20" customHeight="1">
@@ -3803,7 +3803,7 @@
         </is>
       </c>
       <c r="E111" s="23" t="n">
-        <v>111</v>
+        <v>164</v>
       </c>
     </row>
     <row r="112" ht="20" customHeight="1">
@@ -3828,7 +3828,7 @@
         </is>
       </c>
       <c r="E112" s="20" t="n">
-        <v>162</v>
+        <v>204</v>
       </c>
     </row>
     <row r="113" ht="20" customHeight="1">
@@ -3853,7 +3853,7 @@
         </is>
       </c>
       <c r="E113" s="23" t="n">
-        <v>194</v>
+        <v>151</v>
       </c>
     </row>
     <row r="114" ht="20" customHeight="1">
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="E114" s="20" t="n">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="115" ht="20" customHeight="1">
@@ -3903,7 +3903,7 @@
         </is>
       </c>
       <c r="E115" s="23" t="n">
-        <v>114</v>
+        <v>145</v>
       </c>
     </row>
     <row r="116" ht="20" customHeight="1">
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="E117" s="23" t="n">
-        <v>195</v>
+        <v>220</v>
       </c>
     </row>
     <row r="118" ht="20" customHeight="1">
@@ -3978,7 +3978,7 @@
         </is>
       </c>
       <c r="E118" s="20" t="n">
-        <v>238</v>
+        <v>172</v>
       </c>
     </row>
     <row r="119" ht="20" customHeight="1">
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="E119" s="23" t="n">
-        <v>119</v>
+        <v>232</v>
       </c>
     </row>
     <row r="120" ht="20" customHeight="1">
@@ -4028,7 +4028,7 @@
         </is>
       </c>
       <c r="E120" s="20" t="n">
-        <v>118</v>
+        <v>125</v>
       </c>
     </row>
     <row r="121" ht="20" customHeight="1">
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="E121" s="23" t="n">
-        <v>222</v>
+        <v>155</v>
       </c>
     </row>
     <row r="122" ht="20" customHeight="1">
@@ -4078,7 +4078,7 @@
         </is>
       </c>
       <c r="E122" s="20" t="n">
-        <v>171</v>
+        <v>237</v>
       </c>
     </row>
     <row r="123" ht="20" customHeight="1">
@@ -4103,7 +4103,7 @@
         </is>
       </c>
       <c r="E123" s="23" t="n">
-        <v>199</v>
+        <v>218</v>
       </c>
     </row>
     <row r="124" ht="20" customHeight="1">
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="E124" s="20" t="n">
-        <v>114</v>
+        <v>232</v>
       </c>
     </row>
     <row r="125" ht="20" customHeight="1">
@@ -4153,7 +4153,7 @@
         </is>
       </c>
       <c r="E125" s="23" t="n">
-        <v>182</v>
+        <v>145</v>
       </c>
     </row>
     <row r="126" ht="20" customHeight="1">
@@ -4178,7 +4178,7 @@
         </is>
       </c>
       <c r="E126" s="20" t="n">
-        <v>136</v>
+        <v>170</v>
       </c>
     </row>
     <row r="127" ht="20" customHeight="1">
@@ -4203,7 +4203,7 @@
         </is>
       </c>
       <c r="E127" s="23" t="n">
-        <v>219</v>
+        <v>232</v>
       </c>
     </row>
     <row r="128" ht="20" customHeight="1">
@@ -4228,7 +4228,7 @@
         </is>
       </c>
       <c r="E128" s="20" t="n">
-        <v>220</v>
+        <v>212</v>
       </c>
     </row>
     <row r="129" ht="20" customHeight="1">
@@ -4253,7 +4253,7 @@
         </is>
       </c>
       <c r="E129" s="23" t="n">
-        <v>210</v>
+        <v>171</v>
       </c>
     </row>
     <row r="130" ht="20" customHeight="1">
@@ -4278,7 +4278,7 @@
         </is>
       </c>
       <c r="E130" s="20" t="n">
-        <v>197</v>
+        <v>129</v>
       </c>
     </row>
     <row r="131" ht="20" customHeight="1">
@@ -4303,7 +4303,7 @@
         </is>
       </c>
       <c r="E131" s="23" t="n">
-        <v>236</v>
+        <v>120</v>
       </c>
     </row>
     <row r="132" ht="20" customHeight="1">
@@ -4328,7 +4328,7 @@
         </is>
       </c>
       <c r="E132" s="20" t="n">
-        <v>115</v>
+        <v>124</v>
       </c>
     </row>
     <row r="133" ht="20" customHeight="1">
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="E133" s="23" t="n">
-        <v>113</v>
+        <v>180</v>
       </c>
     </row>
     <row r="134" ht="20" customHeight="1">
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="E134" s="20" t="n">
-        <v>115</v>
+        <v>234</v>
       </c>
     </row>
     <row r="135" ht="20" customHeight="1">
@@ -4403,7 +4403,7 @@
         </is>
       </c>
       <c r="E135" s="23" t="n">
-        <v>233</v>
+        <v>191</v>
       </c>
     </row>
     <row r="136" ht="20" customHeight="1">
@@ -4428,7 +4428,7 @@
         </is>
       </c>
       <c r="E136" s="20" t="n">
-        <v>227</v>
+        <v>127</v>
       </c>
     </row>
     <row r="137" ht="20" customHeight="1">
@@ -4453,7 +4453,7 @@
         </is>
       </c>
       <c r="E137" s="23" t="n">
-        <v>181</v>
+        <v>118</v>
       </c>
     </row>
     <row r="138" ht="20" customHeight="1">
@@ -4478,7 +4478,7 @@
         </is>
       </c>
       <c r="E138" s="20" t="n">
-        <v>232</v>
+        <v>136</v>
       </c>
     </row>
     <row r="139" ht="20" customHeight="1">
@@ -4503,7 +4503,7 @@
         </is>
       </c>
       <c r="E139" s="23" t="n">
-        <v>221</v>
+        <v>229</v>
       </c>
     </row>
     <row r="140" ht="20" customHeight="1">
@@ -4528,7 +4528,7 @@
         </is>
       </c>
       <c r="E140" s="20" t="n">
-        <v>174</v>
+        <v>161</v>
       </c>
     </row>
     <row r="141" ht="20" customHeight="1">
@@ -4553,7 +4553,7 @@
         </is>
       </c>
       <c r="E141" s="23" t="n">
-        <v>132</v>
+        <v>127</v>
       </c>
     </row>
     <row r="142" ht="20" customHeight="1">
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="E142" s="20" t="n">
-        <v>159</v>
+        <v>177</v>
       </c>
     </row>
     <row r="143" ht="20" customHeight="1">
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="E143" s="23" t="n">
-        <v>151</v>
+        <v>193</v>
       </c>
     </row>
     <row r="144" ht="20" customHeight="1">
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="E144" s="20" t="n">
-        <v>152</v>
+        <v>145</v>
       </c>
     </row>
     <row r="145" ht="20" customHeight="1">
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="E145" s="23" t="n">
-        <v>196</v>
+        <v>180</v>
       </c>
     </row>
     <row r="146" ht="20" customHeight="1">
@@ -4678,7 +4678,7 @@
         </is>
       </c>
       <c r="E146" s="20" t="n">
-        <v>160</v>
+        <v>173</v>
       </c>
     </row>
     <row r="147" ht="20" customHeight="1">
@@ -4703,7 +4703,7 @@
         </is>
       </c>
       <c r="E147" s="23" t="n">
-        <v>201</v>
+        <v>184</v>
       </c>
     </row>
     <row r="148" ht="20" customHeight="1">
@@ -4728,7 +4728,7 @@
         </is>
       </c>
       <c r="E148" s="20" t="n">
-        <v>181</v>
+        <v>143</v>
       </c>
     </row>
     <row r="149" ht="20" customHeight="1">
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c r="E149" s="23" t="n">
-        <v>111</v>
+        <v>156</v>
       </c>
     </row>
     <row r="150" ht="20" customHeight="1">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="E150" s="20" t="n">
-        <v>202</v>
+        <v>177</v>
       </c>
     </row>
     <row r="151" ht="20" customHeight="1">
@@ -4803,7 +4803,7 @@
         </is>
       </c>
       <c r="E151" s="23" t="n">
-        <v>161</v>
+        <v>118</v>
       </c>
     </row>
     <row r="152" ht="20" customHeight="1">
@@ -4828,7 +4828,7 @@
         </is>
       </c>
       <c r="E152" s="20" t="n">
-        <v>188</v>
+        <v>139</v>
       </c>
     </row>
     <row r="153" ht="20" customHeight="1">
@@ -4853,7 +4853,7 @@
         </is>
       </c>
       <c r="E153" s="23" t="n">
-        <v>169</v>
+        <v>194</v>
       </c>
     </row>
     <row r="154" ht="20" customHeight="1">
@@ -4878,7 +4878,7 @@
         </is>
       </c>
       <c r="E154" s="20" t="n">
-        <v>161</v>
+        <v>144</v>
       </c>
     </row>
     <row r="155" ht="20" customHeight="1">
@@ -4903,7 +4903,7 @@
         </is>
       </c>
       <c r="E155" s="23" t="n">
-        <v>148</v>
+        <v>143</v>
       </c>
     </row>
     <row r="156" ht="20" customHeight="1">
@@ -4928,7 +4928,7 @@
         </is>
       </c>
       <c r="E156" s="20" t="n">
-        <v>178</v>
+        <v>148</v>
       </c>
     </row>
     <row r="157" ht="20" customHeight="1">
@@ -4953,7 +4953,7 @@
         </is>
       </c>
       <c r="E157" s="23" t="n">
-        <v>110</v>
+        <v>124</v>
       </c>
     </row>
     <row r="158" ht="20" customHeight="1">
@@ -4978,7 +4978,7 @@
         </is>
       </c>
       <c r="E158" s="20" t="n">
-        <v>200</v>
+        <v>123</v>
       </c>
     </row>
     <row r="159" ht="20" customHeight="1">
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="E159" s="23" t="n">
-        <v>192</v>
+        <v>177</v>
       </c>
     </row>
     <row r="160" ht="20" customHeight="1">
@@ -5028,7 +5028,7 @@
         </is>
       </c>
       <c r="E160" s="20" t="n">
-        <v>158</v>
+        <v>229</v>
       </c>
     </row>
     <row r="161" ht="20" customHeight="1">
@@ -5053,7 +5053,7 @@
         </is>
       </c>
       <c r="E161" s="23" t="n">
-        <v>175</v>
+        <v>191</v>
       </c>
     </row>
     <row r="162" ht="20" customHeight="1">
@@ -5078,7 +5078,7 @@
         </is>
       </c>
       <c r="E162" s="20" t="n">
-        <v>156</v>
+        <v>164</v>
       </c>
     </row>
     <row r="163" ht="20" customHeight="1">
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="E163" s="23" t="n">
-        <v>176</v>
+        <v>117</v>
       </c>
     </row>
     <row r="164" ht="20" customHeight="1">
@@ -5128,7 +5128,7 @@
         </is>
       </c>
       <c r="E164" s="20" t="n">
-        <v>129</v>
+        <v>171</v>
       </c>
     </row>
     <row r="165" ht="20" customHeight="1">
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="E165" s="23" t="n">
-        <v>137</v>
+        <v>127</v>
       </c>
     </row>
     <row r="166" ht="20" customHeight="1">
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="E167" s="23" t="n">
-        <v>200</v>
+        <v>152</v>
       </c>
     </row>
     <row r="168" ht="20" customHeight="1">
@@ -5228,7 +5228,7 @@
         </is>
       </c>
       <c r="E168" s="20" t="n">
-        <v>162</v>
+        <v>153</v>
       </c>
     </row>
     <row r="169" ht="20" customHeight="1">
@@ -5253,7 +5253,7 @@
         </is>
       </c>
       <c r="E169" s="23" t="n">
-        <v>232</v>
+        <v>195</v>
       </c>
     </row>
     <row r="170" ht="20" customHeight="1">
@@ -5278,7 +5278,7 @@
         </is>
       </c>
       <c r="E170" s="20" t="n">
-        <v>194</v>
+        <v>134</v>
       </c>
     </row>
     <row r="171" ht="20" customHeight="1">
@@ -5303,7 +5303,7 @@
         </is>
       </c>
       <c r="E171" s="23" t="n">
-        <v>213</v>
+        <v>198</v>
       </c>
     </row>
     <row r="172" ht="20" customHeight="1">
@@ -5328,7 +5328,7 @@
         </is>
       </c>
       <c r="E172" s="20" t="n">
-        <v>178</v>
+        <v>142</v>
       </c>
     </row>
     <row r="173" ht="20" customHeight="1">
@@ -5353,7 +5353,7 @@
         </is>
       </c>
       <c r="E173" s="23" t="n">
-        <v>140</v>
+        <v>182</v>
       </c>
     </row>
     <row r="174" ht="20" customHeight="1">
@@ -5378,7 +5378,7 @@
         </is>
       </c>
       <c r="E174" s="20" t="n">
-        <v>127</v>
+        <v>136</v>
       </c>
     </row>
     <row r="175" ht="20" customHeight="1">
@@ -5403,7 +5403,7 @@
         </is>
       </c>
       <c r="E175" s="23" t="n">
-        <v>142</v>
+        <v>184</v>
       </c>
     </row>
     <row r="176" ht="20" customHeight="1">
@@ -5428,7 +5428,7 @@
         </is>
       </c>
       <c r="E176" s="20" t="n">
-        <v>130</v>
+        <v>200</v>
       </c>
     </row>
     <row r="177" ht="20" customHeight="1">
@@ -5453,7 +5453,7 @@
         </is>
       </c>
       <c r="E177" s="23" t="n">
-        <v>228</v>
+        <v>119</v>
       </c>
     </row>
     <row r="178" ht="20" customHeight="1">
@@ -5478,7 +5478,7 @@
         </is>
       </c>
       <c r="E178" s="20" t="n">
-        <v>223</v>
+        <v>188</v>
       </c>
     </row>
     <row r="179" ht="20" customHeight="1">
@@ -5503,7 +5503,7 @@
         </is>
       </c>
       <c r="E179" s="23" t="n">
-        <v>221</v>
+        <v>235</v>
       </c>
     </row>
     <row r="180" ht="20" customHeight="1">
@@ -5528,7 +5528,7 @@
         </is>
       </c>
       <c r="E180" s="20" t="n">
-        <v>128</v>
+        <v>177</v>
       </c>
     </row>
     <row r="181" ht="20" customHeight="1">
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="E181" s="23" t="n">
-        <v>164</v>
+        <v>119</v>
       </c>
     </row>
     <row r="182" ht="20" customHeight="1">
@@ -5578,7 +5578,7 @@
         </is>
       </c>
       <c r="E182" s="20" t="n">
-        <v>213</v>
+        <v>143</v>
       </c>
     </row>
     <row r="183" ht="20" customHeight="1">
@@ -5603,7 +5603,7 @@
         </is>
       </c>
       <c r="E183" s="23" t="n">
-        <v>122</v>
+        <v>140</v>
       </c>
     </row>
     <row r="184" ht="20" customHeight="1">
@@ -5628,7 +5628,7 @@
         </is>
       </c>
       <c r="E184" s="20" t="n">
-        <v>193</v>
+        <v>120</v>
       </c>
     </row>
     <row r="185" ht="20" customHeight="1">
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="E185" s="23" t="n">
-        <v>236</v>
+        <v>129</v>
       </c>
     </row>
     <row r="186" ht="20" customHeight="1">
@@ -5678,7 +5678,7 @@
         </is>
       </c>
       <c r="E186" s="20" t="n">
-        <v>138</v>
+        <v>229</v>
       </c>
     </row>
     <row r="187" ht="20" customHeight="1">
@@ -5703,7 +5703,7 @@
         </is>
       </c>
       <c r="E187" s="23" t="n">
-        <v>233</v>
+        <v>131</v>
       </c>
     </row>
     <row r="188" ht="20" customHeight="1">
@@ -5728,7 +5728,7 @@
         </is>
       </c>
       <c r="E188" s="20" t="n">
-        <v>168</v>
+        <v>187</v>
       </c>
     </row>
     <row r="189" ht="20" customHeight="1">
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="E189" s="23" t="n">
-        <v>218</v>
+        <v>130</v>
       </c>
     </row>
     <row r="190" ht="20" customHeight="1">
@@ -5778,7 +5778,7 @@
         </is>
       </c>
       <c r="E190" s="20" t="n">
-        <v>163</v>
+        <v>219</v>
       </c>
     </row>
     <row r="191" ht="20" customHeight="1">
@@ -5803,7 +5803,7 @@
         </is>
       </c>
       <c r="E191" s="23" t="n">
-        <v>210</v>
+        <v>139</v>
       </c>
     </row>
     <row r="192" ht="20" customHeight="1">
@@ -5828,7 +5828,7 @@
         </is>
       </c>
       <c r="E192" s="20" t="n">
-        <v>137</v>
+        <v>122</v>
       </c>
     </row>
     <row r="193" ht="20" customHeight="1">
@@ -5853,7 +5853,7 @@
         </is>
       </c>
       <c r="E193" s="23" t="n">
-        <v>112</v>
+        <v>168</v>
       </c>
     </row>
     <row r="194" ht="20" customHeight="1">
@@ -5878,7 +5878,7 @@
         </is>
       </c>
       <c r="E194" s="20" t="n">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="195" ht="20" customHeight="1">
@@ -5903,7 +5903,7 @@
         </is>
       </c>
       <c r="E195" s="23" t="n">
-        <v>189</v>
+        <v>179</v>
       </c>
     </row>
     <row r="196" ht="20" customHeight="1">
@@ -5928,7 +5928,7 @@
         </is>
       </c>
       <c r="E196" s="20" t="n">
-        <v>213</v>
+        <v>174</v>
       </c>
     </row>
     <row r="197" ht="20" customHeight="1">
@@ -5953,7 +5953,7 @@
         </is>
       </c>
       <c r="E197" s="23" t="n">
-        <v>203</v>
+        <v>222</v>
       </c>
     </row>
     <row r="198" ht="20" customHeight="1">
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="E198" s="20" t="n">
-        <v>167</v>
+        <v>145</v>
       </c>
     </row>
     <row r="199" ht="20" customHeight="1">
@@ -6003,7 +6003,7 @@
         </is>
       </c>
       <c r="E199" s="23" t="n">
-        <v>198</v>
+        <v>176</v>
       </c>
     </row>
     <row r="200" ht="20" customHeight="1">
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="E200" s="20" t="n">
-        <v>164</v>
+        <v>118</v>
       </c>
     </row>
     <row r="201" ht="20" customHeight="1">
@@ -6053,7 +6053,7 @@
         </is>
       </c>
       <c r="E201" s="23" t="n">
-        <v>172</v>
+        <v>136</v>
       </c>
     </row>
     <row r="202" ht="20" customHeight="1">
@@ -6078,7 +6078,7 @@
         </is>
       </c>
       <c r="E202" s="20" t="n">
-        <v>221</v>
+        <v>181</v>
       </c>
     </row>
     <row r="203" ht="20" customHeight="1">
@@ -6103,7 +6103,7 @@
         </is>
       </c>
       <c r="E203" s="23" t="n">
-        <v>234</v>
+        <v>128</v>
       </c>
     </row>
     <row r="204" ht="20" customHeight="1">
@@ -6128,7 +6128,7 @@
         </is>
       </c>
       <c r="E204" s="20" t="n">
-        <v>113</v>
+        <v>228</v>
       </c>
     </row>
     <row r="205" ht="20" customHeight="1">
@@ -6153,7 +6153,7 @@
         </is>
       </c>
       <c r="E205" s="23" t="n">
-        <v>208</v>
+        <v>170</v>
       </c>
     </row>
     <row r="206" ht="20" customHeight="1">
@@ -6178,7 +6178,7 @@
         </is>
       </c>
       <c r="E206" s="20" t="n">
-        <v>199</v>
+        <v>175</v>
       </c>
     </row>
     <row r="207" ht="20" customHeight="1">
@@ -6203,7 +6203,7 @@
         </is>
       </c>
       <c r="E207" s="23" t="n">
-        <v>216</v>
+        <v>211</v>
       </c>
     </row>
     <row r="208" ht="20" customHeight="1">
@@ -6228,7 +6228,7 @@
         </is>
       </c>
       <c r="E208" s="20" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="209" ht="20" customHeight="1">
@@ -6253,7 +6253,7 @@
         </is>
       </c>
       <c r="E209" s="23" t="n">
-        <v>230</v>
+        <v>194</v>
       </c>
     </row>
     <row r="210" ht="20" customHeight="1">
@@ -6278,7 +6278,7 @@
         </is>
       </c>
       <c r="E210" s="20" t="n">
-        <v>226</v>
+        <v>234</v>
       </c>
     </row>
     <row r="211" ht="20" customHeight="1">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="E211" s="23" t="n">
-        <v>227</v>
+        <v>203</v>
       </c>
     </row>
     <row r="212" ht="20" customHeight="1">
@@ -6328,7 +6328,7 @@
         </is>
       </c>
       <c r="E212" s="20" t="n">
-        <v>168</v>
+        <v>186</v>
       </c>
     </row>
     <row r="213" ht="20" customHeight="1">
@@ -6353,7 +6353,7 @@
         </is>
       </c>
       <c r="E213" s="23" t="n">
-        <v>199</v>
+        <v>173</v>
       </c>
     </row>
     <row r="214" ht="20" customHeight="1">
@@ -6378,7 +6378,7 @@
         </is>
       </c>
       <c r="E214" s="20" t="n">
-        <v>236</v>
+        <v>170</v>
       </c>
     </row>
     <row r="215" ht="20" customHeight="1">
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="E215" s="23" t="n">
-        <v>153</v>
+        <v>131</v>
       </c>
     </row>
     <row r="216" ht="20" customHeight="1">
@@ -6428,7 +6428,7 @@
         </is>
       </c>
       <c r="E216" s="20" t="n">
-        <v>196</v>
+        <v>130</v>
       </c>
     </row>
     <row r="217" ht="20" customHeight="1">
@@ -6453,7 +6453,7 @@
         </is>
       </c>
       <c r="E217" s="23" t="n">
-        <v>240</v>
+        <v>212</v>
       </c>
     </row>
     <row r="218" ht="20" customHeight="1">
@@ -6478,7 +6478,7 @@
         </is>
       </c>
       <c r="E218" s="20" t="n">
-        <v>204</v>
+        <v>146</v>
       </c>
     </row>
     <row r="219" ht="20" customHeight="1">
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="E219" s="23" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="220" ht="20" customHeight="1">
@@ -6528,7 +6528,7 @@
         </is>
       </c>
       <c r="E220" s="20" t="n">
-        <v>144</v>
+        <v>222</v>
       </c>
     </row>
     <row r="221" ht="20" customHeight="1">
@@ -6553,7 +6553,7 @@
         </is>
       </c>
       <c r="E221" s="23" t="n">
-        <v>224</v>
+        <v>214</v>
       </c>
     </row>
     <row r="222" ht="20" customHeight="1">
@@ -6578,7 +6578,7 @@
         </is>
       </c>
       <c r="E222" s="20" t="n">
-        <v>164</v>
+        <v>142</v>
       </c>
     </row>
     <row r="223" ht="20" customHeight="1">
@@ -6603,7 +6603,7 @@
         </is>
       </c>
       <c r="E223" s="23" t="n">
-        <v>132</v>
+        <v>235</v>
       </c>
     </row>
     <row r="224" ht="20" customHeight="1">
@@ -6653,7 +6653,7 @@
         </is>
       </c>
       <c r="E225" s="23" t="n">
-        <v>122</v>
+        <v>133</v>
       </c>
     </row>
     <row r="226" ht="20" customHeight="1">
@@ -6678,7 +6678,7 @@
         </is>
       </c>
       <c r="E226" s="20" t="n">
-        <v>227</v>
+        <v>159</v>
       </c>
     </row>
     <row r="227" ht="20" customHeight="1">
@@ -6703,7 +6703,7 @@
         </is>
       </c>
       <c r="E227" s="23" t="n">
-        <v>121</v>
+        <v>228</v>
       </c>
     </row>
     <row r="228" ht="20" customHeight="1">
@@ -6728,7 +6728,7 @@
         </is>
       </c>
       <c r="E228" s="20" t="n">
-        <v>178</v>
+        <v>213</v>
       </c>
     </row>
     <row r="229" ht="20" customHeight="1">
@@ -6753,7 +6753,7 @@
         </is>
       </c>
       <c r="E229" s="23" t="n">
-        <v>220</v>
+        <v>234</v>
       </c>
     </row>
     <row r="230" ht="20" customHeight="1">
@@ -6778,7 +6778,7 @@
         </is>
       </c>
       <c r="E230" s="20" t="n">
-        <v>196</v>
+        <v>175</v>
       </c>
     </row>
     <row r="231" ht="20" customHeight="1">
@@ -6803,7 +6803,7 @@
         </is>
       </c>
       <c r="E231" s="23" t="n">
-        <v>239</v>
+        <v>197</v>
       </c>
     </row>
     <row r="232" ht="20" customHeight="1">
@@ -6828,7 +6828,7 @@
         </is>
       </c>
       <c r="E232" s="20" t="n">
-        <v>133</v>
+        <v>150</v>
       </c>
     </row>
     <row r="233" ht="20" customHeight="1">
@@ -6853,7 +6853,7 @@
         </is>
       </c>
       <c r="E233" s="23" t="n">
-        <v>128</v>
+        <v>111</v>
       </c>
     </row>
     <row r="234" ht="20" customHeight="1">
@@ -6878,7 +6878,7 @@
         </is>
       </c>
       <c r="E234" s="20" t="n">
-        <v>196</v>
+        <v>164</v>
       </c>
     </row>
     <row r="235" ht="20" customHeight="1">
@@ -6903,7 +6903,7 @@
         </is>
       </c>
       <c r="E235" s="23" t="n">
-        <v>235</v>
+        <v>230</v>
       </c>
     </row>
     <row r="236" ht="20" customHeight="1">
@@ -6928,7 +6928,7 @@
         </is>
       </c>
       <c r="E236" s="20" t="n">
-        <v>130</v>
+        <v>151</v>
       </c>
     </row>
     <row r="237" ht="20" customHeight="1">
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="E237" s="23" t="n">
-        <v>146</v>
+        <v>224</v>
       </c>
     </row>
     <row r="238" ht="20" customHeight="1">
@@ -6978,7 +6978,7 @@
         </is>
       </c>
       <c r="E238" s="20" t="n">
-        <v>235</v>
+        <v>215</v>
       </c>
     </row>
     <row r="239" ht="20" customHeight="1">
@@ -7003,7 +7003,7 @@
         </is>
       </c>
       <c r="E239" s="23" t="n">
-        <v>138</v>
+        <v>154</v>
       </c>
     </row>
     <row r="240" ht="20" customHeight="1">
@@ -7028,7 +7028,7 @@
         </is>
       </c>
       <c r="E240" s="20" t="n">
-        <v>192</v>
+        <v>145</v>
       </c>
     </row>
     <row r="241" ht="20" customHeight="1">
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="E241" s="23" t="n">
-        <v>225</v>
+        <v>146</v>
       </c>
     </row>
     <row r="242" ht="20" customHeight="1">
@@ -7078,7 +7078,7 @@
         </is>
       </c>
       <c r="E242" s="20" t="n">
-        <v>227</v>
+        <v>131</v>
       </c>
     </row>
     <row r="243" ht="20" customHeight="1">
@@ -7103,7 +7103,7 @@
         </is>
       </c>
       <c r="E243" s="23" t="n">
-        <v>150</v>
+        <v>199</v>
       </c>
     </row>
     <row r="244" ht="20" customHeight="1">
@@ -7128,7 +7128,7 @@
         </is>
       </c>
       <c r="E244" s="20" t="n">
-        <v>197</v>
+        <v>225</v>
       </c>
     </row>
     <row r="245" ht="20" customHeight="1">
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="E245" s="23" t="n">
-        <v>116</v>
+        <v>180</v>
       </c>
     </row>
     <row r="246" ht="20" customHeight="1">
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="E246" s="20" t="n">
-        <v>200</v>
+        <v>160</v>
       </c>
     </row>
     <row r="247" ht="20" customHeight="1">
@@ -7203,7 +7203,7 @@
         </is>
       </c>
       <c r="E247" s="23" t="n">
-        <v>131</v>
+        <v>165</v>
       </c>
     </row>
     <row r="248" ht="20" customHeight="1">
@@ -7228,7 +7228,7 @@
         </is>
       </c>
       <c r="E248" s="20" t="n">
-        <v>134</v>
+        <v>203</v>
       </c>
     </row>
     <row r="249" ht="20" customHeight="1">
@@ -7253,7 +7253,7 @@
         </is>
       </c>
       <c r="E249" s="23" t="n">
-        <v>117</v>
+        <v>175</v>
       </c>
     </row>
     <row r="250" ht="20" customHeight="1">
@@ -7278,7 +7278,7 @@
         </is>
       </c>
       <c r="E250" s="20" t="n">
-        <v>145</v>
+        <v>111</v>
       </c>
     </row>
     <row r="251" ht="20" customHeight="1">
@@ -7303,7 +7303,7 @@
         </is>
       </c>
       <c r="E251" s="23" t="n">
-        <v>187</v>
+        <v>139</v>
       </c>
     </row>
     <row r="252" ht="20" customHeight="1">
@@ -7328,7 +7328,7 @@
         </is>
       </c>
       <c r="E252" s="20" t="n">
-        <v>195</v>
+        <v>237</v>
       </c>
     </row>
     <row r="253" ht="20" customHeight="1">
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="E253" s="23" t="n">
-        <v>183</v>
+        <v>173</v>
       </c>
     </row>
     <row r="254" ht="20" customHeight="1">
@@ -7378,7 +7378,7 @@
         </is>
       </c>
       <c r="E254" s="20" t="n">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="255" ht="20" customHeight="1">
@@ -7403,7 +7403,7 @@
         </is>
       </c>
       <c r="E255" s="23" t="n">
-        <v>202</v>
+        <v>159</v>
       </c>
     </row>
     <row r="256" ht="20" customHeight="1">
@@ -7428,7 +7428,7 @@
         </is>
       </c>
       <c r="E256" s="20" t="n">
-        <v>202</v>
+        <v>212</v>
       </c>
     </row>
     <row r="257" ht="20" customHeight="1">
@@ -7453,7 +7453,7 @@
         </is>
       </c>
       <c r="E257" s="23" t="n">
-        <v>184</v>
+        <v>151</v>
       </c>
     </row>
     <row r="258" ht="20" customHeight="1">
@@ -7478,7 +7478,7 @@
         </is>
       </c>
       <c r="E258" s="20" t="n">
-        <v>158</v>
+        <v>198</v>
       </c>
     </row>
     <row r="259" ht="20" customHeight="1">
@@ -7503,7 +7503,7 @@
         </is>
       </c>
       <c r="E259" s="23" t="n">
-        <v>124</v>
+        <v>227</v>
       </c>
     </row>
     <row r="260" ht="20" customHeight="1">
@@ -7528,7 +7528,7 @@
         </is>
       </c>
       <c r="E260" s="20" t="n">
-        <v>194</v>
+        <v>209</v>
       </c>
     </row>
     <row r="261" ht="20" customHeight="1">
@@ -7553,7 +7553,7 @@
         </is>
       </c>
       <c r="E261" s="23" t="n">
-        <v>208</v>
+        <v>131</v>
       </c>
     </row>
     <row r="262" ht="20" customHeight="1">
@@ -7578,7 +7578,7 @@
         </is>
       </c>
       <c r="E262" s="20" t="n">
-        <v>125</v>
+        <v>205</v>
       </c>
     </row>
     <row r="263" ht="20" customHeight="1">
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="E263" s="23" t="n">
-        <v>148</v>
+        <v>226</v>
       </c>
     </row>
     <row r="264" ht="20" customHeight="1">
@@ -7628,7 +7628,7 @@
         </is>
       </c>
       <c r="E264" s="20" t="n">
-        <v>160</v>
+        <v>174</v>
       </c>
     </row>
     <row r="265" ht="20" customHeight="1">
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="E265" s="23" t="n">
-        <v>233</v>
+        <v>158</v>
       </c>
     </row>
     <row r="266" ht="20" customHeight="1">
@@ -7678,7 +7678,7 @@
         </is>
       </c>
       <c r="E266" s="20" t="n">
-        <v>154</v>
+        <v>132</v>
       </c>
     </row>
     <row r="267" ht="20" customHeight="1">
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="E267" s="23" t="n">
-        <v>229</v>
+        <v>114</v>
       </c>
     </row>
     <row r="268" ht="20" customHeight="1">
@@ -7728,7 +7728,7 @@
         </is>
       </c>
       <c r="E268" s="20" t="n">
-        <v>216</v>
+        <v>128</v>
       </c>
     </row>
     <row r="269" ht="20" customHeight="1">
@@ -7753,7 +7753,7 @@
         </is>
       </c>
       <c r="E269" s="23" t="n">
-        <v>114</v>
+        <v>235</v>
       </c>
     </row>
     <row r="270" ht="20" customHeight="1">
@@ -7778,7 +7778,7 @@
         </is>
       </c>
       <c r="E270" s="20" t="n">
-        <v>162</v>
+        <v>224</v>
       </c>
     </row>
     <row r="271" ht="20" customHeight="1">
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="E271" s="23" t="n">
-        <v>228</v>
+        <v>133</v>
       </c>
     </row>
     <row r="272" ht="20" customHeight="1">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="E272" s="20" t="n">
-        <v>111</v>
+        <v>215</v>
       </c>
     </row>
     <row r="273" ht="20" customHeight="1">
@@ -7853,7 +7853,7 @@
         </is>
       </c>
       <c r="E273" s="23" t="n">
-        <v>111</v>
+        <v>212</v>
       </c>
     </row>
     <row r="274" ht="20" customHeight="1">
@@ -7878,7 +7878,7 @@
         </is>
       </c>
       <c r="E274" s="20" t="n">
-        <v>117</v>
+        <v>111</v>
       </c>
     </row>
     <row r="275" ht="20" customHeight="1">
@@ -7903,7 +7903,7 @@
         </is>
       </c>
       <c r="E275" s="23" t="n">
-        <v>132</v>
+        <v>154</v>
       </c>
     </row>
     <row r="276" ht="20" customHeight="1">
@@ -7928,7 +7928,7 @@
         </is>
       </c>
       <c r="E276" s="20" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="277" ht="20" customHeight="1">
@@ -7953,7 +7953,7 @@
         </is>
       </c>
       <c r="E277" s="23" t="n">
-        <v>143</v>
+        <v>200</v>
       </c>
     </row>
     <row r="278" ht="20" customHeight="1">
@@ -7978,7 +7978,7 @@
         </is>
       </c>
       <c r="E278" s="20" t="n">
-        <v>110</v>
+        <v>182</v>
       </c>
     </row>
     <row r="279" ht="20" customHeight="1">
@@ -8003,7 +8003,7 @@
         </is>
       </c>
       <c r="E279" s="23" t="n">
-        <v>177</v>
+        <v>136</v>
       </c>
     </row>
     <row r="280" ht="20" customHeight="1">
@@ -8028,7 +8028,7 @@
         </is>
       </c>
       <c r="E280" s="20" t="n">
-        <v>207</v>
+        <v>130</v>
       </c>
     </row>
     <row r="281" ht="20" customHeight="1">
@@ -8053,7 +8053,7 @@
         </is>
       </c>
       <c r="E281" s="23" t="n">
-        <v>208</v>
+        <v>183</v>
       </c>
     </row>
     <row r="282" ht="20" customHeight="1">
@@ -8078,7 +8078,7 @@
         </is>
       </c>
       <c r="E282" s="20" t="n">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="283" ht="20" customHeight="1">
@@ -8103,7 +8103,7 @@
         </is>
       </c>
       <c r="E283" s="23" t="n">
-        <v>170</v>
+        <v>224</v>
       </c>
     </row>
     <row r="284" ht="20" customHeight="1">
@@ -8128,7 +8128,7 @@
         </is>
       </c>
       <c r="E284" s="20" t="n">
-        <v>164</v>
+        <v>179</v>
       </c>
     </row>
     <row r="285" ht="20" customHeight="1">
@@ -8153,7 +8153,7 @@
         </is>
       </c>
       <c r="E285" s="23" t="n">
-        <v>144</v>
+        <v>239</v>
       </c>
     </row>
     <row r="286" ht="20" customHeight="1">
@@ -8178,7 +8178,7 @@
         </is>
       </c>
       <c r="E286" s="20" t="n">
-        <v>204</v>
+        <v>128</v>
       </c>
     </row>
     <row r="287" ht="20" customHeight="1">
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="E287" s="23" t="n">
-        <v>203</v>
+        <v>239</v>
       </c>
     </row>
     <row r="288" ht="20" customHeight="1">
@@ -8228,7 +8228,7 @@
         </is>
       </c>
       <c r="E288" s="20" t="n">
-        <v>164</v>
+        <v>138</v>
       </c>
     </row>
     <row r="289" ht="20" customHeight="1">
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="E289" s="23" t="n">
-        <v>222</v>
+        <v>150</v>
       </c>
     </row>
     <row r="290" ht="20" customHeight="1">
@@ -8278,7 +8278,7 @@
         </is>
       </c>
       <c r="E290" s="20" t="n">
-        <v>136</v>
+        <v>113</v>
       </c>
     </row>
     <row r="291" ht="20" customHeight="1">
@@ -8303,7 +8303,7 @@
         </is>
       </c>
       <c r="E291" s="23" t="n">
-        <v>205</v>
+        <v>156</v>
       </c>
     </row>
     <row r="292" ht="20" customHeight="1">
@@ -8328,7 +8328,7 @@
         </is>
       </c>
       <c r="E292" s="20" t="n">
-        <v>167</v>
+        <v>111</v>
       </c>
     </row>
     <row r="293" ht="20" customHeight="1">
@@ -8353,7 +8353,7 @@
         </is>
       </c>
       <c r="E293" s="23" t="n">
-        <v>235</v>
+        <v>136</v>
       </c>
     </row>
     <row r="294" ht="20" customHeight="1">
@@ -8378,7 +8378,7 @@
         </is>
       </c>
       <c r="E294" s="20" t="n">
-        <v>199</v>
+        <v>216</v>
       </c>
     </row>
     <row r="295" ht="20" customHeight="1">
@@ -8403,7 +8403,7 @@
         </is>
       </c>
       <c r="E295" s="23" t="n">
-        <v>212</v>
+        <v>127</v>
       </c>
     </row>
     <row r="296" ht="20" customHeight="1">
@@ -8428,7 +8428,7 @@
         </is>
       </c>
       <c r="E296" s="20" t="n">
-        <v>120</v>
+        <v>229</v>
       </c>
     </row>
     <row r="297" ht="20" customHeight="1">
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="E297" s="23" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="298" ht="20" customHeight="1">
@@ -8478,7 +8478,7 @@
         </is>
       </c>
       <c r="E298" s="20" t="n">
-        <v>227</v>
+        <v>138</v>
       </c>
     </row>
     <row r="299" ht="20" customHeight="1">
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="E299" s="23" t="n">
-        <v>222</v>
+        <v>121</v>
       </c>
     </row>
     <row r="300" ht="20" customHeight="1">
@@ -8528,7 +8528,7 @@
         </is>
       </c>
       <c r="E300" s="20" t="n">
-        <v>221</v>
+        <v>201</v>
       </c>
     </row>
     <row r="301" ht="20" customHeight="1">
@@ -8553,7 +8553,7 @@
         </is>
       </c>
       <c r="E301" s="23" t="n">
-        <v>192</v>
+        <v>236</v>
       </c>
     </row>
     <row r="302" ht="20" customHeight="1">
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="E302" s="20" t="n">
-        <v>220</v>
+        <v>212</v>
       </c>
     </row>
     <row r="303" ht="20" customHeight="1">
@@ -8603,7 +8603,7 @@
         </is>
       </c>
       <c r="E303" s="23" t="n">
-        <v>173</v>
+        <v>127</v>
       </c>
     </row>
     <row r="304" ht="20" customHeight="1">
@@ -8628,7 +8628,7 @@
         </is>
       </c>
       <c r="E304" s="20" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
     </row>
     <row r="305" ht="20" customHeight="1">
@@ -8653,7 +8653,7 @@
         </is>
       </c>
       <c r="E305" s="23" t="n">
-        <v>160</v>
+        <v>231</v>
       </c>
     </row>
     <row r="306" ht="20" customHeight="1">
@@ -8678,7 +8678,7 @@
         </is>
       </c>
       <c r="E306" s="20" t="n">
-        <v>112</v>
+        <v>223</v>
       </c>
     </row>
     <row r="307" ht="20" customHeight="1">
@@ -8703,7 +8703,7 @@
         </is>
       </c>
       <c r="E307" s="23" t="n">
-        <v>219</v>
+        <v>113</v>
       </c>
     </row>
     <row r="308" ht="20" customHeight="1">
@@ -8728,7 +8728,7 @@
         </is>
       </c>
       <c r="E308" s="20" t="n">
-        <v>154</v>
+        <v>229</v>
       </c>
     </row>
     <row r="309" ht="20" customHeight="1">
@@ -8753,7 +8753,7 @@
         </is>
       </c>
       <c r="E309" s="23" t="n">
-        <v>235</v>
+        <v>178</v>
       </c>
     </row>
     <row r="310" ht="20" customHeight="1">
@@ -8778,7 +8778,7 @@
         </is>
       </c>
       <c r="E310" s="20" t="n">
-        <v>120</v>
+        <v>138</v>
       </c>
     </row>
     <row r="311" ht="20" customHeight="1">
@@ -8803,7 +8803,7 @@
         </is>
       </c>
       <c r="E311" s="23" t="n">
-        <v>167</v>
+        <v>117</v>
       </c>
     </row>
     <row r="312" ht="20" customHeight="1">
@@ -8828,7 +8828,7 @@
         </is>
       </c>
       <c r="E312" s="20" t="n">
-        <v>205</v>
+        <v>126</v>
       </c>
     </row>
     <row r="313" ht="20" customHeight="1">
@@ -8853,7 +8853,7 @@
         </is>
       </c>
       <c r="E313" s="23" t="n">
-        <v>139</v>
+        <v>167</v>
       </c>
     </row>
     <row r="314" ht="20" customHeight="1">
@@ -8878,7 +8878,7 @@
         </is>
       </c>
       <c r="E314" s="20" t="n">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="315" ht="20" customHeight="1">
@@ -8903,7 +8903,7 @@
         </is>
       </c>
       <c r="E315" s="23" t="n">
-        <v>125</v>
+        <v>144</v>
       </c>
     </row>
     <row r="316" ht="20" customHeight="1">
@@ -8928,7 +8928,7 @@
         </is>
       </c>
       <c r="E316" s="20" t="n">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="317" ht="20" customHeight="1">
@@ -8953,7 +8953,7 @@
         </is>
       </c>
       <c r="E317" s="23" t="n">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="318" ht="20" customHeight="1">
@@ -8978,7 +8978,7 @@
         </is>
       </c>
       <c r="E318" s="20" t="n">
-        <v>234</v>
+        <v>134</v>
       </c>
     </row>
     <row r="319" ht="20" customHeight="1">
@@ -9003,7 +9003,7 @@
         </is>
       </c>
       <c r="E319" s="23" t="n">
-        <v>125</v>
+        <v>238</v>
       </c>
     </row>
     <row r="320" ht="20" customHeight="1">
@@ -9028,7 +9028,7 @@
         </is>
       </c>
       <c r="E320" s="20" t="n">
-        <v>143</v>
+        <v>177</v>
       </c>
     </row>
     <row r="321" ht="20" customHeight="1">
@@ -9053,7 +9053,7 @@
         </is>
       </c>
       <c r="E321" s="23" t="n">
-        <v>201</v>
+        <v>232</v>
       </c>
     </row>
     <row r="322" ht="20" customHeight="1">
@@ -9078,7 +9078,7 @@
         </is>
       </c>
       <c r="E322" s="20" t="n">
-        <v>139</v>
+        <v>185</v>
       </c>
     </row>
     <row r="323" ht="20" customHeight="1">
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="E323" s="23" t="n">
-        <v>230</v>
+        <v>171</v>
       </c>
     </row>
     <row r="324" ht="20" customHeight="1">
@@ -9128,7 +9128,7 @@
         </is>
       </c>
       <c r="E324" s="20" t="n">
-        <v>235</v>
+        <v>110</v>
       </c>
     </row>
     <row r="325" ht="20" customHeight="1">
@@ -9153,7 +9153,7 @@
         </is>
       </c>
       <c r="E325" s="23" t="n">
-        <v>238</v>
+        <v>184</v>
       </c>
     </row>
     <row r="326" ht="20" customHeight="1">
@@ -9178,7 +9178,7 @@
         </is>
       </c>
       <c r="E326" s="20" t="n">
-        <v>200</v>
+        <v>157</v>
       </c>
     </row>
     <row r="327" ht="20" customHeight="1">
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="E327" s="23" t="n">
-        <v>165</v>
+        <v>149</v>
       </c>
     </row>
     <row r="328" ht="20" customHeight="1">
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="E328" s="20" t="n">
-        <v>131</v>
+        <v>151</v>
       </c>
     </row>
     <row r="329" ht="20" customHeight="1">
@@ -9253,7 +9253,7 @@
         </is>
       </c>
       <c r="E329" s="23" t="n">
-        <v>110</v>
+        <v>181</v>
       </c>
     </row>
     <row r="330" ht="20" customHeight="1">
@@ -9278,7 +9278,7 @@
         </is>
       </c>
       <c r="E330" s="20" t="n">
-        <v>151</v>
+        <v>211</v>
       </c>
     </row>
     <row r="331" ht="20" customHeight="1">
@@ -9303,7 +9303,7 @@
         </is>
       </c>
       <c r="E331" s="23" t="n">
-        <v>171</v>
+        <v>120</v>
       </c>
     </row>
     <row r="332" ht="20" customHeight="1">
@@ -9328,7 +9328,7 @@
         </is>
       </c>
       <c r="E332" s="20" t="n">
-        <v>163</v>
+        <v>212</v>
       </c>
     </row>
     <row r="333" ht="20" customHeight="1">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="E333" s="23" t="n">
-        <v>153</v>
+        <v>205</v>
       </c>
     </row>
     <row r="334" ht="20" customHeight="1">
@@ -9378,7 +9378,7 @@
         </is>
       </c>
       <c r="E334" s="20" t="n">
-        <v>173</v>
+        <v>148</v>
       </c>
     </row>
     <row r="335" ht="20" customHeight="1">
@@ -9403,7 +9403,7 @@
         </is>
       </c>
       <c r="E335" s="23" t="n">
-        <v>232</v>
+        <v>179</v>
       </c>
     </row>
     <row r="336" ht="20" customHeight="1">
@@ -9428,7 +9428,7 @@
         </is>
       </c>
       <c r="E336" s="20" t="n">
-        <v>220</v>
+        <v>136</v>
       </c>
     </row>
     <row r="337" ht="20" customHeight="1">
@@ -9453,7 +9453,7 @@
         </is>
       </c>
       <c r="E337" s="23" t="n">
-        <v>128</v>
+        <v>213</v>
       </c>
     </row>
     <row r="338" ht="20" customHeight="1">
@@ -9478,7 +9478,7 @@
         </is>
       </c>
       <c r="E338" s="20" t="n">
-        <v>234</v>
+        <v>139</v>
       </c>
     </row>
     <row r="339" ht="20" customHeight="1">
@@ -9503,7 +9503,7 @@
         </is>
       </c>
       <c r="E339" s="23" t="n">
-        <v>152</v>
+        <v>226</v>
       </c>
     </row>
     <row r="340" ht="20" customHeight="1">
@@ -9528,7 +9528,7 @@
         </is>
       </c>
       <c r="E340" s="20" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="341" ht="20" customHeight="1">
@@ -9553,7 +9553,7 @@
         </is>
       </c>
       <c r="E341" s="23" t="n">
-        <v>119</v>
+        <v>163</v>
       </c>
     </row>
     <row r="342" ht="20" customHeight="1">
@@ -9578,7 +9578,7 @@
         </is>
       </c>
       <c r="E342" s="20" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="343" ht="20" customHeight="1">
@@ -9603,7 +9603,7 @@
         </is>
       </c>
       <c r="E343" s="23" t="n">
-        <v>158</v>
+        <v>192</v>
       </c>
     </row>
     <row r="344" ht="20" customHeight="1">
@@ -9628,7 +9628,7 @@
         </is>
       </c>
       <c r="E344" s="20" t="n">
-        <v>232</v>
+        <v>167</v>
       </c>
     </row>
     <row r="345" ht="20" customHeight="1">
@@ -9653,7 +9653,7 @@
         </is>
       </c>
       <c r="E345" s="23" t="n">
-        <v>191</v>
+        <v>143</v>
       </c>
     </row>
     <row r="346" ht="20" customHeight="1">
@@ -9678,7 +9678,7 @@
         </is>
       </c>
       <c r="E346" s="20" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
     </row>
     <row r="347" ht="20" customHeight="1">
@@ -9703,7 +9703,7 @@
         </is>
       </c>
       <c r="E347" s="23" t="n">
-        <v>183</v>
+        <v>230</v>
       </c>
     </row>
     <row r="348" ht="20" customHeight="1">
@@ -9728,7 +9728,7 @@
         </is>
       </c>
       <c r="E348" s="20" t="n">
-        <v>214</v>
+        <v>146</v>
       </c>
     </row>
     <row r="349" ht="20" customHeight="1">
@@ -9753,7 +9753,7 @@
         </is>
       </c>
       <c r="E349" s="23" t="n">
-        <v>211</v>
+        <v>174</v>
       </c>
     </row>
     <row r="350" ht="20" customHeight="1">
@@ -9778,7 +9778,7 @@
         </is>
       </c>
       <c r="E350" s="20" t="n">
-        <v>159</v>
+        <v>116</v>
       </c>
     </row>
     <row r="351" ht="20" customHeight="1">
@@ -9803,7 +9803,7 @@
         </is>
       </c>
       <c r="E351" s="23" t="n">
-        <v>231</v>
+        <v>202</v>
       </c>
     </row>
     <row r="352" ht="20" customHeight="1">
@@ -9828,7 +9828,7 @@
         </is>
       </c>
       <c r="E352" s="20" t="n">
-        <v>189</v>
+        <v>149</v>
       </c>
     </row>
     <row r="353" ht="20" customHeight="1">
@@ -9853,7 +9853,7 @@
         </is>
       </c>
       <c r="E353" s="23" t="n">
-        <v>115</v>
+        <v>202</v>
       </c>
     </row>
     <row r="354" ht="20" customHeight="1">
@@ -9878,7 +9878,7 @@
         </is>
       </c>
       <c r="E354" s="20" t="n">
-        <v>228</v>
+        <v>240</v>
       </c>
     </row>
     <row r="355" ht="20" customHeight="1">
@@ -9903,7 +9903,7 @@
         </is>
       </c>
       <c r="E355" s="23" t="n">
-        <v>115</v>
+        <v>152</v>
       </c>
     </row>
     <row r="356" ht="20" customHeight="1">
@@ -9928,7 +9928,7 @@
         </is>
       </c>
       <c r="E356" s="20" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="357" ht="20" customHeight="1">
@@ -9953,7 +9953,7 @@
         </is>
       </c>
       <c r="E357" s="23" t="n">
-        <v>223</v>
+        <v>119</v>
       </c>
     </row>
     <row r="358" ht="20" customHeight="1">
@@ -9978,7 +9978,7 @@
         </is>
       </c>
       <c r="E358" s="20" t="n">
-        <v>120</v>
+        <v>155</v>
       </c>
     </row>
     <row r="359" ht="20" customHeight="1">
@@ -10003,7 +10003,7 @@
         </is>
       </c>
       <c r="E359" s="23" t="n">
-        <v>194</v>
+        <v>165</v>
       </c>
     </row>
     <row r="360" ht="20" customHeight="1">
@@ -10028,7 +10028,7 @@
         </is>
       </c>
       <c r="E360" s="20" t="n">
-        <v>192</v>
+        <v>175</v>
       </c>
     </row>
     <row r="361" ht="20" customHeight="1">
@@ -10053,7 +10053,7 @@
         </is>
       </c>
       <c r="E361" s="23" t="n">
-        <v>172</v>
+        <v>138</v>
       </c>
     </row>
     <row r="362" ht="20" customHeight="1">
@@ -10078,7 +10078,7 @@
         </is>
       </c>
       <c r="E362" s="20" t="n">
-        <v>221</v>
+        <v>196</v>
       </c>
     </row>
     <row r="363" ht="20" customHeight="1">
@@ -10103,7 +10103,7 @@
         </is>
       </c>
       <c r="E363" s="23" t="n">
-        <v>184</v>
+        <v>136</v>
       </c>
     </row>
     <row r="364" ht="20" customHeight="1">
@@ -10128,7 +10128,7 @@
         </is>
       </c>
       <c r="E364" s="20" t="n">
-        <v>168</v>
+        <v>206</v>
       </c>
     </row>
     <row r="365" ht="20" customHeight="1">
@@ -10153,7 +10153,7 @@
         </is>
       </c>
       <c r="E365" s="23" t="n">
-        <v>136</v>
+        <v>234</v>
       </c>
     </row>
     <row r="366" ht="20" customHeight="1">
@@ -10178,7 +10178,7 @@
         </is>
       </c>
       <c r="E366" s="20" t="n">
-        <v>111</v>
+        <v>223</v>
       </c>
     </row>
     <row r="367" ht="20" customHeight="1">
@@ -10203,7 +10203,7 @@
         </is>
       </c>
       <c r="E367" s="23" t="n">
-        <v>216</v>
+        <v>125</v>
       </c>
     </row>
     <row r="368" ht="20" customHeight="1">
@@ -10228,7 +10228,7 @@
         </is>
       </c>
       <c r="E368" s="20" t="n">
-        <v>177</v>
+        <v>231</v>
       </c>
     </row>
     <row r="369" ht="20" customHeight="1">
@@ -10253,7 +10253,7 @@
         </is>
       </c>
       <c r="E369" s="23" t="n">
-        <v>218</v>
+        <v>145</v>
       </c>
     </row>
     <row r="370" ht="20" customHeight="1">
@@ -10278,7 +10278,7 @@
         </is>
       </c>
       <c r="E370" s="20" t="n">
-        <v>154</v>
+        <v>129</v>
       </c>
     </row>
     <row r="371" ht="20" customHeight="1">
@@ -10303,7 +10303,7 @@
         </is>
       </c>
       <c r="E371" s="23" t="n">
-        <v>198</v>
+        <v>125</v>
       </c>
     </row>
     <row r="372" ht="20" customHeight="1">
@@ -10328,7 +10328,7 @@
         </is>
       </c>
       <c r="E372" s="20" t="n">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="373" ht="20" customHeight="1">
@@ -10353,7 +10353,7 @@
         </is>
       </c>
       <c r="E373" s="23" t="n">
-        <v>204</v>
+        <v>219</v>
       </c>
     </row>
     <row r="374" ht="20" customHeight="1">
@@ -10378,7 +10378,7 @@
         </is>
       </c>
       <c r="E374" s="20" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="375" ht="20" customHeight="1">
@@ -10403,7 +10403,7 @@
         </is>
       </c>
       <c r="E375" s="23" t="n">
-        <v>170</v>
+        <v>205</v>
       </c>
     </row>
     <row r="376" ht="20" customHeight="1">
@@ -10428,7 +10428,7 @@
         </is>
       </c>
       <c r="E376" s="20" t="n">
-        <v>135</v>
+        <v>207</v>
       </c>
     </row>
     <row r="377" ht="20" customHeight="1">
@@ -10453,7 +10453,7 @@
         </is>
       </c>
       <c r="E377" s="23" t="n">
-        <v>177</v>
+        <v>190</v>
       </c>
     </row>
     <row r="378" ht="20" customHeight="1">
@@ -10478,7 +10478,7 @@
         </is>
       </c>
       <c r="E378" s="20" t="n">
-        <v>131</v>
+        <v>172</v>
       </c>
     </row>
     <row r="379" ht="20" customHeight="1">
@@ -10503,7 +10503,7 @@
         </is>
       </c>
       <c r="E379" s="23" t="n">
-        <v>200</v>
+        <v>193</v>
       </c>
     </row>
     <row r="380" ht="20" customHeight="1">
@@ -10528,7 +10528,7 @@
         </is>
       </c>
       <c r="E380" s="20" t="n">
-        <v>167</v>
+        <v>231</v>
       </c>
     </row>
     <row r="381" ht="20" customHeight="1">
@@ -10553,7 +10553,7 @@
         </is>
       </c>
       <c r="E381" s="23" t="n">
-        <v>172</v>
+        <v>140</v>
       </c>
     </row>
     <row r="382" ht="20" customHeight="1">
@@ -10578,7 +10578,7 @@
         </is>
       </c>
       <c r="E382" s="20" t="n">
-        <v>160</v>
+        <v>202</v>
       </c>
     </row>
     <row r="383" ht="20" customHeight="1">
@@ -10603,7 +10603,7 @@
         </is>
       </c>
       <c r="E383" s="23" t="n">
-        <v>130</v>
+        <v>141</v>
       </c>
     </row>
     <row r="384" ht="20" customHeight="1">
@@ -10628,7 +10628,7 @@
         </is>
       </c>
       <c r="E384" s="20" t="n">
-        <v>147</v>
+        <v>209</v>
       </c>
     </row>
     <row r="385" ht="20" customHeight="1">
@@ -10653,7 +10653,7 @@
         </is>
       </c>
       <c r="E385" s="23" t="n">
-        <v>235</v>
+        <v>195</v>
       </c>
     </row>
     <row r="386" ht="20" customHeight="1">
@@ -10678,7 +10678,7 @@
         </is>
       </c>
       <c r="E386" s="20" t="n">
-        <v>116</v>
+        <v>178</v>
       </c>
     </row>
     <row r="387" ht="20" customHeight="1">
@@ -10703,7 +10703,7 @@
         </is>
       </c>
       <c r="E387" s="23" t="n">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="388" ht="20" customHeight="1">
@@ -10728,7 +10728,7 @@
         </is>
       </c>
       <c r="E388" s="20" t="n">
-        <v>116</v>
+        <v>240</v>
       </c>
     </row>
     <row r="389" ht="20" customHeight="1">
@@ -10753,7 +10753,7 @@
         </is>
       </c>
       <c r="E389" s="23" t="n">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="390" ht="20" customHeight="1">
@@ -10778,7 +10778,7 @@
         </is>
       </c>
       <c r="E390" s="20" t="n">
-        <v>118</v>
+        <v>207</v>
       </c>
     </row>
     <row r="391" ht="20" customHeight="1">
@@ -10803,7 +10803,7 @@
         </is>
       </c>
       <c r="E391" s="23" t="n">
-        <v>166</v>
+        <v>137</v>
       </c>
     </row>
     <row r="392" ht="20" customHeight="1">
@@ -10828,7 +10828,7 @@
         </is>
       </c>
       <c r="E392" s="20" t="n">
-        <v>112</v>
+        <v>176</v>
       </c>
     </row>
     <row r="393" ht="20" customHeight="1">
@@ -10853,7 +10853,7 @@
         </is>
       </c>
       <c r="E393" s="23" t="n">
-        <v>134</v>
+        <v>219</v>
       </c>
     </row>
     <row r="394" ht="20" customHeight="1">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="E394" s="20" t="n">
-        <v>221</v>
+        <v>174</v>
       </c>
     </row>
     <row r="395" ht="20" customHeight="1">
@@ -10903,7 +10903,7 @@
         </is>
       </c>
       <c r="E395" s="23" t="n">
-        <v>127</v>
+        <v>174</v>
       </c>
     </row>
     <row r="396" ht="20" customHeight="1">
@@ -10928,7 +10928,7 @@
         </is>
       </c>
       <c r="E396" s="20" t="n">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="397" ht="20" customHeight="1">
@@ -10953,7 +10953,7 @@
         </is>
       </c>
       <c r="E397" s="23" t="n">
-        <v>141</v>
+        <v>113</v>
       </c>
     </row>
     <row r="398" ht="20" customHeight="1">
@@ -10978,7 +10978,7 @@
         </is>
       </c>
       <c r="E398" s="20" t="n">
-        <v>156</v>
+        <v>169</v>
       </c>
     </row>
     <row r="399" ht="20" customHeight="1">
@@ -11003,7 +11003,7 @@
         </is>
       </c>
       <c r="E399" s="23" t="n">
-        <v>226</v>
+        <v>121</v>
       </c>
     </row>
     <row r="400" ht="20" customHeight="1">
@@ -11028,7 +11028,7 @@
         </is>
       </c>
       <c r="E400" s="20" t="n">
-        <v>182</v>
+        <v>208</v>
       </c>
     </row>
     <row r="401" ht="20" customHeight="1">
@@ -11053,7 +11053,7 @@
         </is>
       </c>
       <c r="E401" s="23" t="n">
-        <v>110</v>
+        <v>125</v>
       </c>
     </row>
     <row r="402" ht="20" customHeight="1">
@@ -11078,7 +11078,7 @@
         </is>
       </c>
       <c r="E402" s="20" t="n">
-        <v>138</v>
+        <v>202</v>
       </c>
     </row>
     <row r="403" ht="20" customHeight="1">
@@ -11103,7 +11103,7 @@
         </is>
       </c>
       <c r="E403" s="23" t="n">
-        <v>152</v>
+        <v>131</v>
       </c>
     </row>
     <row r="404" ht="20" customHeight="1">
@@ -11128,7 +11128,7 @@
         </is>
       </c>
       <c r="E404" s="20" t="n">
-        <v>128</v>
+        <v>147</v>
       </c>
     </row>
     <row r="405" ht="20" customHeight="1">
@@ -11153,7 +11153,7 @@
         </is>
       </c>
       <c r="E405" s="23" t="n">
-        <v>176</v>
+        <v>116</v>
       </c>
     </row>
     <row r="406" ht="20" customHeight="1">
@@ -11178,7 +11178,7 @@
         </is>
       </c>
       <c r="E406" s="20" t="n">
-        <v>122</v>
+        <v>167</v>
       </c>
     </row>
     <row r="407" ht="20" customHeight="1">
@@ -11203,7 +11203,7 @@
         </is>
       </c>
       <c r="E407" s="23" t="n">
-        <v>141</v>
+        <v>124</v>
       </c>
     </row>
     <row r="408" ht="20" customHeight="1">
@@ -11228,7 +11228,7 @@
         </is>
       </c>
       <c r="E408" s="20" t="n">
-        <v>177</v>
+        <v>130</v>
       </c>
     </row>
     <row r="409" ht="20" customHeight="1">
@@ -11253,7 +11253,7 @@
         </is>
       </c>
       <c r="E409" s="23" t="n">
-        <v>139</v>
+        <v>190</v>
       </c>
     </row>
     <row r="410" ht="20" customHeight="1">
@@ -11278,7 +11278,7 @@
         </is>
       </c>
       <c r="E410" s="20" t="n">
-        <v>228</v>
+        <v>116</v>
       </c>
     </row>
     <row r="411" ht="20" customHeight="1">
@@ -11303,7 +11303,7 @@
         </is>
       </c>
       <c r="E411" s="23" t="n">
-        <v>191</v>
+        <v>113</v>
       </c>
     </row>
     <row r="412" ht="20" customHeight="1">
@@ -11328,7 +11328,7 @@
         </is>
       </c>
       <c r="E412" s="20" t="n">
-        <v>125</v>
+        <v>146</v>
       </c>
     </row>
     <row r="413" ht="20" customHeight="1">
@@ -11353,7 +11353,7 @@
         </is>
       </c>
       <c r="E413" s="23" t="n">
-        <v>157</v>
+        <v>170</v>
       </c>
     </row>
     <row r="414" ht="20" customHeight="1">
@@ -11378,7 +11378,7 @@
         </is>
       </c>
       <c r="E414" s="20" t="n">
-        <v>199</v>
+        <v>155</v>
       </c>
     </row>
     <row r="415" ht="20" customHeight="1">
@@ -11403,7 +11403,7 @@
         </is>
       </c>
       <c r="E415" s="23" t="n">
-        <v>111</v>
+        <v>155</v>
       </c>
     </row>
     <row r="416" ht="20" customHeight="1">
@@ -11428,7 +11428,7 @@
         </is>
       </c>
       <c r="E416" s="20" t="n">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="417" ht="20" customHeight="1">
@@ -11453,7 +11453,7 @@
         </is>
       </c>
       <c r="E417" s="23" t="n">
-        <v>117</v>
+        <v>234</v>
       </c>
     </row>
     <row r="418" ht="20" customHeight="1">
@@ -11478,7 +11478,7 @@
         </is>
       </c>
       <c r="E418" s="20" t="n">
-        <v>125</v>
+        <v>204</v>
       </c>
     </row>
     <row r="419" ht="20" customHeight="1">
@@ -11503,7 +11503,7 @@
         </is>
       </c>
       <c r="E419" s="23" t="n">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="420" ht="20" customHeight="1">
@@ -11528,7 +11528,7 @@
         </is>
       </c>
       <c r="E420" s="20" t="n">
-        <v>126</v>
+        <v>169</v>
       </c>
     </row>
     <row r="421" ht="20" customHeight="1">
@@ -11553,7 +11553,7 @@
         </is>
       </c>
       <c r="E421" s="23" t="n">
-        <v>137</v>
+        <v>148</v>
       </c>
     </row>
     <row r="422" ht="20" customHeight="1">
@@ -11578,7 +11578,7 @@
         </is>
       </c>
       <c r="E422" s="20" t="n">
-        <v>210</v>
+        <v>111</v>
       </c>
     </row>
     <row r="423" ht="20" customHeight="1">
@@ -11603,7 +11603,7 @@
         </is>
       </c>
       <c r="E423" s="23" t="n">
-        <v>198</v>
+        <v>120</v>
       </c>
     </row>
     <row r="424" ht="20" customHeight="1">
@@ -11628,7 +11628,7 @@
         </is>
       </c>
       <c r="E424" s="20" t="n">
-        <v>232</v>
+        <v>123</v>
       </c>
     </row>
     <row r="425" ht="20" customHeight="1">
@@ -11653,7 +11653,7 @@
         </is>
       </c>
       <c r="E425" s="23" t="n">
-        <v>174</v>
+        <v>119</v>
       </c>
     </row>
     <row r="426" ht="20" customHeight="1">
@@ -11678,7 +11678,7 @@
         </is>
       </c>
       <c r="E426" s="20" t="n">
-        <v>226</v>
+        <v>119</v>
       </c>
     </row>
     <row r="427" ht="20" customHeight="1">
@@ -11703,7 +11703,7 @@
         </is>
       </c>
       <c r="E427" s="23" t="n">
-        <v>233</v>
+        <v>207</v>
       </c>
     </row>
     <row r="428" ht="20" customHeight="1">
@@ -11728,7 +11728,7 @@
         </is>
       </c>
       <c r="E428" s="20" t="n">
-        <v>205</v>
+        <v>150</v>
       </c>
     </row>
     <row r="429" ht="20" customHeight="1">
@@ -11753,7 +11753,7 @@
         </is>
       </c>
       <c r="E429" s="23" t="n">
-        <v>144</v>
+        <v>181</v>
       </c>
     </row>
     <row r="430" ht="20" customHeight="1">
@@ -11778,7 +11778,7 @@
         </is>
       </c>
       <c r="E430" s="20" t="n">
-        <v>151</v>
+        <v>174</v>
       </c>
     </row>
     <row r="431" ht="20" customHeight="1">
@@ -11803,7 +11803,7 @@
         </is>
       </c>
       <c r="E431" s="23" t="n">
-        <v>183</v>
+        <v>162</v>
       </c>
     </row>
     <row r="432" ht="20" customHeight="1">
@@ -11828,7 +11828,7 @@
         </is>
       </c>
       <c r="E432" s="20" t="n">
-        <v>152</v>
+        <v>117</v>
       </c>
     </row>
     <row r="433" ht="20" customHeight="1">
@@ -11853,7 +11853,7 @@
         </is>
       </c>
       <c r="E433" s="23" t="n">
-        <v>214</v>
+        <v>232</v>
       </c>
     </row>
     <row r="434" ht="20" customHeight="1">
@@ -11878,7 +11878,7 @@
         </is>
       </c>
       <c r="E434" s="20" t="n">
-        <v>233</v>
+        <v>180</v>
       </c>
     </row>
     <row r="435" ht="20" customHeight="1">
@@ -11903,7 +11903,7 @@
         </is>
       </c>
       <c r="E435" s="23" t="n">
-        <v>116</v>
+        <v>136</v>
       </c>
     </row>
     <row r="436" ht="20" customHeight="1">
@@ -11928,7 +11928,7 @@
         </is>
       </c>
       <c r="E436" s="20" t="n">
-        <v>136</v>
+        <v>154</v>
       </c>
     </row>
     <row r="437" ht="20" customHeight="1">
@@ -11953,7 +11953,7 @@
         </is>
       </c>
       <c r="E437" s="23" t="n">
-        <v>229</v>
+        <v>222</v>
       </c>
     </row>
     <row r="438" ht="20" customHeight="1">
@@ -11978,7 +11978,7 @@
         </is>
       </c>
       <c r="E438" s="20" t="n">
-        <v>169</v>
+        <v>182</v>
       </c>
     </row>
     <row r="439" ht="20" customHeight="1">
@@ -12003,7 +12003,7 @@
         </is>
       </c>
       <c r="E439" s="23" t="n">
-        <v>205</v>
+        <v>179</v>
       </c>
     </row>
     <row r="440" ht="20" customHeight="1">
@@ -12028,7 +12028,7 @@
         </is>
       </c>
       <c r="E440" s="20" t="n">
-        <v>146</v>
+        <v>224</v>
       </c>
     </row>
     <row r="441" ht="20" customHeight="1">
@@ -12053,7 +12053,7 @@
         </is>
       </c>
       <c r="E441" s="23" t="n">
-        <v>166</v>
+        <v>194</v>
       </c>
     </row>
     <row r="442" ht="20" customHeight="1">
@@ -12078,7 +12078,7 @@
         </is>
       </c>
       <c r="E442" s="20" t="n">
-        <v>197</v>
+        <v>213</v>
       </c>
     </row>
     <row r="443" ht="20" customHeight="1">
@@ -12103,7 +12103,7 @@
         </is>
       </c>
       <c r="E443" s="23" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="444" ht="20" customHeight="1">
@@ -12128,7 +12128,7 @@
         </is>
       </c>
       <c r="E444" s="20" t="n">
-        <v>125</v>
+        <v>189</v>
       </c>
     </row>
     <row r="445" ht="20" customHeight="1">
@@ -12153,7 +12153,7 @@
         </is>
       </c>
       <c r="E445" s="23" t="n">
-        <v>240</v>
+        <v>141</v>
       </c>
     </row>
     <row r="446" ht="20" customHeight="1">
@@ -12178,7 +12178,7 @@
         </is>
       </c>
       <c r="E446" s="20" t="n">
-        <v>169</v>
+        <v>176</v>
       </c>
     </row>
     <row r="447" ht="20" customHeight="1">
@@ -12203,7 +12203,7 @@
         </is>
       </c>
       <c r="E447" s="23" t="n">
-        <v>175</v>
+        <v>137</v>
       </c>
     </row>
     <row r="448" ht="20" customHeight="1">
@@ -12228,7 +12228,7 @@
         </is>
       </c>
       <c r="E448" s="20" t="n">
-        <v>160</v>
+        <v>119</v>
       </c>
     </row>
     <row r="449" ht="20" customHeight="1">
@@ -12253,7 +12253,7 @@
         </is>
       </c>
       <c r="E449" s="23" t="n">
-        <v>229</v>
+        <v>189</v>
       </c>
     </row>
     <row r="450" ht="20" customHeight="1">
@@ -12278,7 +12278,7 @@
         </is>
       </c>
       <c r="E450" s="20" t="n">
-        <v>186</v>
+        <v>161</v>
       </c>
     </row>
     <row r="451" ht="20" customHeight="1">
@@ -12303,7 +12303,7 @@
         </is>
       </c>
       <c r="E451" s="23" t="n">
-        <v>156</v>
+        <v>132</v>
       </c>
     </row>
     <row r="452" ht="20" customHeight="1">
@@ -12328,7 +12328,7 @@
         </is>
       </c>
       <c r="E452" s="20" t="n">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="453" ht="20" customHeight="1">
@@ -12353,7 +12353,7 @@
         </is>
       </c>
       <c r="E453" s="23" t="n">
-        <v>176</v>
+        <v>119</v>
       </c>
     </row>
     <row r="454" ht="20" customHeight="1">
@@ -12378,7 +12378,7 @@
         </is>
       </c>
       <c r="E454" s="20" t="n">
-        <v>137</v>
+        <v>125</v>
       </c>
     </row>
     <row r="455" ht="20" customHeight="1">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="E455" s="23" t="n">
-        <v>176</v>
+        <v>227</v>
       </c>
     </row>
     <row r="456" ht="20" customHeight="1">
@@ -12428,7 +12428,7 @@
         </is>
       </c>
       <c r="E456" s="20" t="n">
-        <v>194</v>
+        <v>117</v>
       </c>
     </row>
     <row r="457" ht="20" customHeight="1">
@@ -12453,7 +12453,7 @@
         </is>
       </c>
       <c r="E457" s="23" t="n">
-        <v>183</v>
+        <v>214</v>
       </c>
     </row>
     <row r="458" ht="20" customHeight="1">
@@ -12478,7 +12478,7 @@
         </is>
       </c>
       <c r="E458" s="20" t="n">
-        <v>164</v>
+        <v>153</v>
       </c>
     </row>
     <row r="459" ht="20" customHeight="1">
@@ -12503,7 +12503,7 @@
         </is>
       </c>
       <c r="E459" s="23" t="n">
-        <v>150</v>
+        <v>132</v>
       </c>
     </row>
     <row r="460" ht="20" customHeight="1">
@@ -12528,7 +12528,7 @@
         </is>
       </c>
       <c r="E460" s="20" t="n">
-        <v>221</v>
+        <v>174</v>
       </c>
     </row>
     <row r="461" ht="20" customHeight="1">
@@ -12553,7 +12553,7 @@
         </is>
       </c>
       <c r="E461" s="23" t="n">
-        <v>201</v>
+        <v>189</v>
       </c>
     </row>
     <row r="462" ht="20" customHeight="1">
@@ -12578,7 +12578,7 @@
         </is>
       </c>
       <c r="E462" s="20" t="n">
-        <v>194</v>
+        <v>147</v>
       </c>
     </row>
     <row r="463" ht="20" customHeight="1">
@@ -12603,7 +12603,7 @@
         </is>
       </c>
       <c r="E463" s="23" t="n">
-        <v>136</v>
+        <v>206</v>
       </c>
     </row>
     <row r="464" ht="20" customHeight="1">
@@ -12628,7 +12628,7 @@
         </is>
       </c>
       <c r="E464" s="20" t="n">
-        <v>177</v>
+        <v>209</v>
       </c>
     </row>
     <row r="465" ht="20" customHeight="1">
@@ -12653,7 +12653,7 @@
         </is>
       </c>
       <c r="E465" s="23" t="n">
-        <v>221</v>
+        <v>165</v>
       </c>
     </row>
     <row r="466" ht="20" customHeight="1">
@@ -12678,7 +12678,7 @@
         </is>
       </c>
       <c r="E466" s="20" t="n">
-        <v>163</v>
+        <v>115</v>
       </c>
     </row>
     <row r="467" ht="20" customHeight="1">
@@ -12703,7 +12703,7 @@
         </is>
       </c>
       <c r="E467" s="23" t="n">
-        <v>193</v>
+        <v>142</v>
       </c>
     </row>
     <row r="468" ht="20" customHeight="1">
@@ -12728,7 +12728,7 @@
         </is>
       </c>
       <c r="E468" s="20" t="n">
-        <v>112</v>
+        <v>219</v>
       </c>
     </row>
     <row r="469" ht="20" customHeight="1">
@@ -12753,7 +12753,7 @@
         </is>
       </c>
       <c r="E469" s="23" t="n">
-        <v>205</v>
+        <v>175</v>
       </c>
     </row>
     <row r="470" ht="20" customHeight="1">
@@ -12778,7 +12778,7 @@
         </is>
       </c>
       <c r="E470" s="20" t="n">
-        <v>239</v>
+        <v>158</v>
       </c>
     </row>
     <row r="471" ht="20" customHeight="1">
@@ -12803,7 +12803,7 @@
         </is>
       </c>
       <c r="E471" s="23" t="n">
-        <v>143</v>
+        <v>216</v>
       </c>
     </row>
     <row r="472" ht="20" customHeight="1">
@@ -12828,7 +12828,7 @@
         </is>
       </c>
       <c r="E472" s="20" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="473" ht="20" customHeight="1">
@@ -12853,7 +12853,7 @@
         </is>
       </c>
       <c r="E473" s="23" t="n">
-        <v>192</v>
+        <v>218</v>
       </c>
     </row>
     <row r="474" ht="20" customHeight="1">
@@ -12878,7 +12878,7 @@
         </is>
       </c>
       <c r="E474" s="20" t="n">
-        <v>192</v>
+        <v>136</v>
       </c>
     </row>
     <row r="475" ht="20" customHeight="1">
@@ -12903,7 +12903,7 @@
         </is>
       </c>
       <c r="E475" s="23" t="n">
-        <v>147</v>
+        <v>196</v>
       </c>
     </row>
     <row r="476" ht="20" customHeight="1">
@@ -12928,7 +12928,7 @@
         </is>
       </c>
       <c r="E476" s="20" t="n">
-        <v>165</v>
+        <v>140</v>
       </c>
     </row>
     <row r="477" ht="20" customHeight="1">
@@ -12953,7 +12953,7 @@
         </is>
       </c>
       <c r="E477" s="23" t="n">
-        <v>141</v>
+        <v>146</v>
       </c>
     </row>
     <row r="478" ht="20" customHeight="1">
@@ -12978,7 +12978,7 @@
         </is>
       </c>
       <c r="E478" s="20" t="n">
-        <v>209</v>
+        <v>144</v>
       </c>
     </row>
     <row r="479" ht="20" customHeight="1">
@@ -13003,7 +13003,7 @@
         </is>
       </c>
       <c r="E479" s="23" t="n">
-        <v>231</v>
+        <v>118</v>
       </c>
     </row>
     <row r="480" ht="20" customHeight="1">
@@ -13028,7 +13028,7 @@
         </is>
       </c>
       <c r="E480" s="20" t="n">
-        <v>237</v>
+        <v>156</v>
       </c>
     </row>
     <row r="481" ht="20" customHeight="1">
@@ -13053,7 +13053,7 @@
         </is>
       </c>
       <c r="E481" s="23" t="n">
-        <v>207</v>
+        <v>119</v>
       </c>
     </row>
     <row r="482" ht="20" customHeight="1">
@@ -13078,7 +13078,7 @@
         </is>
       </c>
       <c r="E482" s="20" t="n">
-        <v>240</v>
+        <v>172</v>
       </c>
     </row>
     <row r="483" ht="20" customHeight="1">
@@ -13103,7 +13103,7 @@
         </is>
       </c>
       <c r="E483" s="23" t="n">
-        <v>193</v>
+        <v>136</v>
       </c>
     </row>
     <row r="484" ht="20" customHeight="1">
@@ -13128,7 +13128,7 @@
         </is>
       </c>
       <c r="E484" s="20" t="n">
-        <v>121</v>
+        <v>213</v>
       </c>
     </row>
     <row r="485" ht="20" customHeight="1">
@@ -13153,7 +13153,7 @@
         </is>
       </c>
       <c r="E485" s="23" t="n">
-        <v>186</v>
+        <v>163</v>
       </c>
     </row>
     <row r="486" ht="20" customHeight="1">
@@ -13178,7 +13178,7 @@
         </is>
       </c>
       <c r="E486" s="20" t="n">
-        <v>181</v>
+        <v>170</v>
       </c>
     </row>
     <row r="487" ht="20" customHeight="1">
@@ -13203,7 +13203,7 @@
         </is>
       </c>
       <c r="E487" s="23" t="n">
-        <v>214</v>
+        <v>124</v>
       </c>
     </row>
     <row r="488" ht="20" customHeight="1">
@@ -13228,7 +13228,7 @@
         </is>
       </c>
       <c r="E488" s="20" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="489" ht="20" customHeight="1">
@@ -13253,7 +13253,7 @@
         </is>
       </c>
       <c r="E489" s="23" t="n">
-        <v>113</v>
+        <v>165</v>
       </c>
     </row>
     <row r="490" ht="20" customHeight="1">
@@ -13278,7 +13278,7 @@
         </is>
       </c>
       <c r="E490" s="20" t="n">
-        <v>172</v>
+        <v>236</v>
       </c>
     </row>
     <row r="491" ht="20" customHeight="1">
@@ -13303,7 +13303,7 @@
         </is>
       </c>
       <c r="E491" s="23" t="n">
-        <v>161</v>
+        <v>210</v>
       </c>
     </row>
     <row r="492" ht="20" customHeight="1">
@@ -13328,7 +13328,7 @@
         </is>
       </c>
       <c r="E492" s="20" t="n">
-        <v>197</v>
+        <v>185</v>
       </c>
     </row>
     <row r="493" ht="20" customHeight="1">
@@ -13353,7 +13353,7 @@
         </is>
       </c>
       <c r="E493" s="23" t="n">
-        <v>194</v>
+        <v>112</v>
       </c>
     </row>
     <row r="494" ht="20" customHeight="1">
@@ -13378,7 +13378,7 @@
         </is>
       </c>
       <c r="E494" s="20" t="n">
-        <v>156</v>
+        <v>239</v>
       </c>
     </row>
     <row r="495" ht="20" customHeight="1">
@@ -13403,7 +13403,7 @@
         </is>
       </c>
       <c r="E495" s="23" t="n">
-        <v>146</v>
+        <v>182</v>
       </c>
     </row>
     <row r="496" ht="20" customHeight="1">
@@ -13428,7 +13428,7 @@
         </is>
       </c>
       <c r="E496" s="20" t="n">
-        <v>126</v>
+        <v>187</v>
       </c>
     </row>
     <row r="497" ht="20" customHeight="1">
@@ -13453,7 +13453,7 @@
         </is>
       </c>
       <c r="E497" s="23" t="n">
-        <v>192</v>
+        <v>156</v>
       </c>
     </row>
     <row r="498" ht="20" customHeight="1">
@@ -13478,7 +13478,7 @@
         </is>
       </c>
       <c r="E498" s="20" t="n">
-        <v>144</v>
+        <v>220</v>
       </c>
     </row>
     <row r="499" ht="20" customHeight="1">
@@ -13503,7 +13503,7 @@
         </is>
       </c>
       <c r="E499" s="23" t="n">
-        <v>209</v>
+        <v>156</v>
       </c>
     </row>
     <row r="500" ht="20" customHeight="1">
@@ -13528,7 +13528,7 @@
         </is>
       </c>
       <c r="E500" s="20" t="n">
-        <v>224</v>
+        <v>192</v>
       </c>
     </row>
     <row r="501" ht="20" customHeight="1">
@@ -13553,7 +13553,7 @@
         </is>
       </c>
       <c r="E501" s="23" t="n">
-        <v>159</v>
+        <v>237</v>
       </c>
     </row>
     <row r="502" ht="20" customHeight="1">
@@ -13578,7 +13578,7 @@
         </is>
       </c>
       <c r="E502" s="20" t="n">
-        <v>112</v>
+        <v>215</v>
       </c>
     </row>
     <row r="503" ht="20" customHeight="1">
@@ -13603,7 +13603,7 @@
         </is>
       </c>
       <c r="E503" s="23" t="n">
-        <v>151</v>
+        <v>115</v>
       </c>
     </row>
     <row r="504" ht="20" customHeight="1">
@@ -13628,7 +13628,7 @@
         </is>
       </c>
       <c r="E504" s="20" t="n">
-        <v>238</v>
+        <v>140</v>
       </c>
     </row>
     <row r="505" ht="20" customHeight="1">
@@ -13653,7 +13653,7 @@
         </is>
       </c>
       <c r="E505" s="23" t="n">
-        <v>177</v>
+        <v>229</v>
       </c>
     </row>
     <row r="506" ht="20" customHeight="1">
@@ -13678,7 +13678,7 @@
         </is>
       </c>
       <c r="E506" s="20" t="n">
-        <v>229</v>
+        <v>188</v>
       </c>
     </row>
     <row r="507" ht="20" customHeight="1">
@@ -13703,7 +13703,7 @@
         </is>
       </c>
       <c r="E507" s="23" t="n">
-        <v>131</v>
+        <v>219</v>
       </c>
     </row>
     <row r="508" ht="20" customHeight="1">
@@ -13728,7 +13728,7 @@
         </is>
       </c>
       <c r="E508" s="20" t="n">
-        <v>125</v>
+        <v>232</v>
       </c>
     </row>
     <row r="509" ht="20" customHeight="1">
@@ -13753,7 +13753,7 @@
         </is>
       </c>
       <c r="E509" s="23" t="n">
-        <v>231</v>
+        <v>184</v>
       </c>
     </row>
     <row r="510" ht="20" customHeight="1">
@@ -13778,7 +13778,7 @@
         </is>
       </c>
       <c r="E510" s="20" t="n">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="511" ht="20" customHeight="1">
@@ -13803,7 +13803,7 @@
         </is>
       </c>
       <c r="E511" s="23" t="n">
-        <v>155</v>
+        <v>190</v>
       </c>
     </row>
     <row r="512" ht="20" customHeight="1">
@@ -13828,7 +13828,7 @@
         </is>
       </c>
       <c r="E512" s="20" t="n">
-        <v>139</v>
+        <v>237</v>
       </c>
     </row>
     <row r="513" ht="20" customHeight="1">
@@ -13853,7 +13853,7 @@
         </is>
       </c>
       <c r="E513" s="23" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="514" ht="20" customHeight="1">
@@ -13878,7 +13878,7 @@
         </is>
       </c>
       <c r="E514" s="20" t="n">
-        <v>142</v>
+        <v>132</v>
       </c>
     </row>
     <row r="515" ht="20" customHeight="1">
@@ -13903,7 +13903,7 @@
         </is>
       </c>
       <c r="E515" s="23" t="n">
-        <v>180</v>
+        <v>122</v>
       </c>
     </row>
     <row r="516" ht="20" customHeight="1">
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="E516" s="20" t="n">
-        <v>209</v>
+        <v>147</v>
       </c>
     </row>
     <row r="517" ht="20" customHeight="1">
@@ -13953,7 +13953,7 @@
         </is>
       </c>
       <c r="E517" s="23" t="n">
-        <v>201</v>
+        <v>163</v>
       </c>
     </row>
     <row r="518" ht="20" customHeight="1">
@@ -13978,7 +13978,7 @@
         </is>
       </c>
       <c r="E518" s="20" t="n">
-        <v>212</v>
+        <v>236</v>
       </c>
     </row>
     <row r="519" ht="20" customHeight="1">
@@ -14003,7 +14003,7 @@
         </is>
       </c>
       <c r="E519" s="23" t="n">
-        <v>224</v>
+        <v>193</v>
       </c>
     </row>
     <row r="520" ht="20" customHeight="1">
@@ -14028,7 +14028,7 @@
         </is>
       </c>
       <c r="E520" s="20" t="n">
-        <v>113</v>
+        <v>152</v>
       </c>
     </row>
     <row r="521" ht="20" customHeight="1">
@@ -14053,7 +14053,7 @@
         </is>
       </c>
       <c r="E521" s="23" t="n">
-        <v>189</v>
+        <v>111</v>
       </c>
     </row>
     <row r="522" ht="20" customHeight="1">
@@ -14078,7 +14078,7 @@
         </is>
       </c>
       <c r="E522" s="20" t="n">
-        <v>146</v>
+        <v>210</v>
       </c>
     </row>
     <row r="523" ht="20" customHeight="1">
@@ -14103,7 +14103,7 @@
         </is>
       </c>
       <c r="E523" s="23" t="n">
-        <v>172</v>
+        <v>138</v>
       </c>
     </row>
     <row r="524" ht="20" customHeight="1">
@@ -14128,7 +14128,7 @@
         </is>
       </c>
       <c r="E524" s="20" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="525" ht="20" customHeight="1">
@@ -14153,7 +14153,7 @@
         </is>
       </c>
       <c r="E525" s="23" t="n">
-        <v>179</v>
+        <v>154</v>
       </c>
     </row>
     <row r="526" ht="20" customHeight="1">
@@ -14178,7 +14178,7 @@
         </is>
       </c>
       <c r="E526" s="20" t="n">
-        <v>223</v>
+        <v>235</v>
       </c>
     </row>
     <row r="527" ht="20" customHeight="1">
@@ -14203,7 +14203,7 @@
         </is>
       </c>
       <c r="E527" s="23" t="n">
-        <v>204</v>
+        <v>115</v>
       </c>
     </row>
     <row r="528" ht="20" customHeight="1">
@@ -14228,7 +14228,7 @@
         </is>
       </c>
       <c r="E528" s="20" t="n">
-        <v>155</v>
+        <v>129</v>
       </c>
     </row>
     <row r="529" ht="20" customHeight="1">
@@ -14253,7 +14253,7 @@
         </is>
       </c>
       <c r="E529" s="23" t="n">
-        <v>189</v>
+        <v>163</v>
       </c>
     </row>
     <row r="530" ht="20" customHeight="1">
@@ -14278,7 +14278,7 @@
         </is>
       </c>
       <c r="E530" s="20" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="531" ht="20" customHeight="1">
@@ -14303,7 +14303,7 @@
         </is>
       </c>
       <c r="E531" s="23" t="n">
-        <v>231</v>
+        <v>170</v>
       </c>
     </row>
     <row r="532" ht="20" customHeight="1">
@@ -14328,7 +14328,7 @@
         </is>
       </c>
       <c r="E532" s="20" t="n">
-        <v>159</v>
+        <v>228</v>
       </c>
     </row>
     <row r="533" ht="20" customHeight="1">
@@ -14353,7 +14353,7 @@
         </is>
       </c>
       <c r="E533" s="23" t="n">
-        <v>130</v>
+        <v>156</v>
       </c>
     </row>
     <row r="534" ht="20" customHeight="1">
@@ -14378,7 +14378,7 @@
         </is>
       </c>
       <c r="E534" s="20" t="n">
-        <v>167</v>
+        <v>193</v>
       </c>
     </row>
     <row r="535" ht="20" customHeight="1">
@@ -14403,7 +14403,7 @@
         </is>
       </c>
       <c r="E535" s="23" t="n">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="536" ht="20" customHeight="1">
@@ -14428,7 +14428,7 @@
         </is>
       </c>
       <c r="E536" s="20" t="n">
-        <v>165</v>
+        <v>113</v>
       </c>
     </row>
     <row r="537" ht="20" customHeight="1">
@@ -14453,7 +14453,7 @@
         </is>
       </c>
       <c r="E537" s="23" t="n">
-        <v>142</v>
+        <v>111</v>
       </c>
     </row>
     <row r="538" ht="20" customHeight="1">
@@ -14478,7 +14478,7 @@
         </is>
       </c>
       <c r="E538" s="20" t="n">
-        <v>206</v>
+        <v>237</v>
       </c>
     </row>
     <row r="539" ht="20" customHeight="1">
@@ -14503,7 +14503,7 @@
         </is>
       </c>
       <c r="E539" s="23" t="n">
-        <v>196</v>
+        <v>191</v>
       </c>
     </row>
     <row r="540" ht="20" customHeight="1">
@@ -14528,7 +14528,7 @@
         </is>
       </c>
       <c r="E540" s="20" t="n">
-        <v>214</v>
+        <v>151</v>
       </c>
     </row>
     <row r="541" ht="20" customHeight="1">
@@ -14553,7 +14553,7 @@
         </is>
       </c>
       <c r="E541" s="23" t="n">
-        <v>201</v>
+        <v>234</v>
       </c>
     </row>
     <row r="542" ht="20" customHeight="1">
@@ -14578,7 +14578,7 @@
         </is>
       </c>
       <c r="E542" s="20" t="n">
-        <v>232</v>
+        <v>173</v>
       </c>
     </row>
     <row r="543" ht="20" customHeight="1">
@@ -14628,7 +14628,7 @@
         </is>
       </c>
       <c r="E544" s="20" t="n">
-        <v>194</v>
+        <v>112</v>
       </c>
     </row>
     <row r="545" ht="20" customHeight="1">
@@ -14653,7 +14653,7 @@
         </is>
       </c>
       <c r="E545" s="23" t="n">
-        <v>226</v>
+        <v>135</v>
       </c>
     </row>
     <row r="546" ht="20" customHeight="1">
@@ -14678,7 +14678,7 @@
         </is>
       </c>
       <c r="E546" s="20" t="n">
-        <v>171</v>
+        <v>119</v>
       </c>
     </row>
     <row r="547" ht="20" customHeight="1">
@@ -14703,7 +14703,7 @@
         </is>
       </c>
       <c r="E547" s="23" t="n">
-        <v>175</v>
+        <v>240</v>
       </c>
     </row>
     <row r="548" ht="20" customHeight="1">
@@ -14728,7 +14728,7 @@
         </is>
       </c>
       <c r="E548" s="20" t="n">
-        <v>225</v>
+        <v>215</v>
       </c>
     </row>
     <row r="549" ht="20" customHeight="1">
@@ -14753,7 +14753,7 @@
         </is>
       </c>
       <c r="E549" s="23" t="n">
-        <v>228</v>
+        <v>187</v>
       </c>
     </row>
     <row r="550" ht="20" customHeight="1">
@@ -14778,7 +14778,7 @@
         </is>
       </c>
       <c r="E550" s="20" t="n">
-        <v>139</v>
+        <v>121</v>
       </c>
     </row>
     <row r="551" ht="20" customHeight="1">
@@ -14803,7 +14803,7 @@
         </is>
       </c>
       <c r="E551" s="23" t="n">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="552" ht="20" customHeight="1">
@@ -14828,7 +14828,7 @@
         </is>
       </c>
       <c r="E552" s="20" t="n">
-        <v>144</v>
+        <v>229</v>
       </c>
     </row>
     <row r="553" ht="20" customHeight="1">
@@ -14853,7 +14853,7 @@
         </is>
       </c>
       <c r="E553" s="23" t="n">
-        <v>139</v>
+        <v>225</v>
       </c>
     </row>
     <row r="554" ht="20" customHeight="1">
@@ -14878,7 +14878,7 @@
         </is>
       </c>
       <c r="E554" s="20" t="n">
-        <v>131</v>
+        <v>240</v>
       </c>
     </row>
     <row r="555" ht="20" customHeight="1">
@@ -14903,7 +14903,7 @@
         </is>
       </c>
       <c r="E555" s="23" t="n">
-        <v>117</v>
+        <v>226</v>
       </c>
     </row>
     <row r="556" ht="20" customHeight="1">
@@ -14928,7 +14928,7 @@
         </is>
       </c>
       <c r="E556" s="20" t="n">
-        <v>238</v>
+        <v>134</v>
       </c>
     </row>
     <row r="557" ht="20" customHeight="1">
@@ -14953,7 +14953,7 @@
         </is>
       </c>
       <c r="E557" s="23" t="n">
-        <v>118</v>
+        <v>192</v>
       </c>
     </row>
     <row r="558" ht="20" customHeight="1">
@@ -14978,7 +14978,7 @@
         </is>
       </c>
       <c r="E558" s="20" t="n">
-        <v>207</v>
+        <v>213</v>
       </c>
     </row>
     <row r="559" ht="20" customHeight="1">
@@ -15003,7 +15003,7 @@
         </is>
       </c>
       <c r="E559" s="23" t="n">
-        <v>185</v>
+        <v>220</v>
       </c>
     </row>
     <row r="560" ht="20" customHeight="1">
@@ -15028,7 +15028,7 @@
         </is>
       </c>
       <c r="E560" s="20" t="n">
-        <v>237</v>
+        <v>166</v>
       </c>
     </row>
     <row r="561" ht="20" customHeight="1">
@@ -15053,7 +15053,7 @@
         </is>
       </c>
       <c r="E561" s="23" t="n">
-        <v>129</v>
+        <v>177</v>
       </c>
     </row>
     <row r="562" ht="20" customHeight="1">
@@ -15078,7 +15078,7 @@
         </is>
       </c>
       <c r="E562" s="20" t="n">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="563" ht="20" customHeight="1">
@@ -15103,7 +15103,7 @@
         </is>
       </c>
       <c r="E563" s="23" t="n">
-        <v>122</v>
+        <v>159</v>
       </c>
     </row>
     <row r="564" ht="20" customHeight="1">
@@ -15128,7 +15128,7 @@
         </is>
       </c>
       <c r="E564" s="20" t="n">
-        <v>218</v>
+        <v>149</v>
       </c>
     </row>
     <row r="565" ht="20" customHeight="1">
@@ -15153,7 +15153,7 @@
         </is>
       </c>
       <c r="E565" s="23" t="n">
-        <v>148</v>
+        <v>118</v>
       </c>
     </row>
     <row r="566" ht="20" customHeight="1">
@@ -15178,7 +15178,7 @@
         </is>
       </c>
       <c r="E566" s="20" t="n">
-        <v>140</v>
+        <v>147</v>
       </c>
     </row>
     <row r="567" ht="20" customHeight="1">
@@ -15203,7 +15203,7 @@
         </is>
       </c>
       <c r="E567" s="23" t="n">
-        <v>214</v>
+        <v>138</v>
       </c>
     </row>
     <row r="568" ht="20" customHeight="1">
@@ -15228,7 +15228,7 @@
         </is>
       </c>
       <c r="E568" s="20" t="n">
-        <v>169</v>
+        <v>202</v>
       </c>
     </row>
     <row r="569" ht="20" customHeight="1">
@@ -15253,7 +15253,7 @@
         </is>
       </c>
       <c r="E569" s="23" t="n">
-        <v>171</v>
+        <v>164</v>
       </c>
     </row>
     <row r="570" ht="20" customHeight="1">
@@ -15278,7 +15278,7 @@
         </is>
       </c>
       <c r="E570" s="20" t="n">
-        <v>193</v>
+        <v>112</v>
       </c>
     </row>
     <row r="571" ht="20" customHeight="1">
@@ -15303,7 +15303,7 @@
         </is>
       </c>
       <c r="E571" s="23" t="n">
-        <v>138</v>
+        <v>185</v>
       </c>
     </row>
     <row r="572" ht="20" customHeight="1">
@@ -15328,7 +15328,7 @@
         </is>
       </c>
       <c r="E572" s="20" t="n">
-        <v>195</v>
+        <v>113</v>
       </c>
     </row>
     <row r="573" ht="20" customHeight="1">
@@ -15353,7 +15353,7 @@
         </is>
       </c>
       <c r="E573" s="23" t="n">
-        <v>231</v>
+        <v>130</v>
       </c>
     </row>
     <row r="574" ht="20" customHeight="1">
@@ -15403,7 +15403,7 @@
         </is>
       </c>
       <c r="E575" s="23" t="n">
-        <v>235</v>
+        <v>178</v>
       </c>
     </row>
     <row r="576" ht="20" customHeight="1">
@@ -15428,7 +15428,7 @@
         </is>
       </c>
       <c r="E576" s="20" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="577" ht="20" customHeight="1">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="E577" s="23" t="n">
-        <v>240</v>
+        <v>135</v>
       </c>
     </row>
     <row r="578" ht="20" customHeight="1">
@@ -15478,7 +15478,7 @@
         </is>
       </c>
       <c r="E578" s="20" t="n">
-        <v>145</v>
+        <v>169</v>
       </c>
     </row>
     <row r="579" ht="20" customHeight="1">
@@ -15503,7 +15503,7 @@
         </is>
       </c>
       <c r="E579" s="23" t="n">
-        <v>236</v>
+        <v>121</v>
       </c>
     </row>
     <row r="580" ht="20" customHeight="1">
@@ -15528,7 +15528,7 @@
         </is>
       </c>
       <c r="E580" s="20" t="n">
-        <v>199</v>
+        <v>209</v>
       </c>
     </row>
     <row r="581" ht="20" customHeight="1">
@@ -15553,7 +15553,7 @@
         </is>
       </c>
       <c r="E581" s="23" t="n">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="582" ht="20" customHeight="1">
@@ -15578,7 +15578,7 @@
         </is>
       </c>
       <c r="E582" s="20" t="n">
-        <v>118</v>
+        <v>214</v>
       </c>
     </row>
     <row r="583" ht="20" customHeight="1">
@@ -15603,7 +15603,7 @@
         </is>
       </c>
       <c r="E583" s="23" t="n">
-        <v>111</v>
+        <v>189</v>
       </c>
     </row>
     <row r="584" ht="20" customHeight="1">
@@ -15628,7 +15628,7 @@
         </is>
       </c>
       <c r="E584" s="20" t="n">
-        <v>187</v>
+        <v>219</v>
       </c>
     </row>
     <row r="585" ht="20" customHeight="1">
@@ -15653,7 +15653,7 @@
         </is>
       </c>
       <c r="E585" s="23" t="n">
-        <v>235</v>
+        <v>217</v>
       </c>
     </row>
     <row r="586" ht="20" customHeight="1">
@@ -15678,7 +15678,7 @@
         </is>
       </c>
       <c r="E586" s="20" t="n">
-        <v>155</v>
+        <v>135</v>
       </c>
     </row>
     <row r="587" ht="20" customHeight="1">
@@ -15703,7 +15703,7 @@
         </is>
       </c>
       <c r="E587" s="23" t="n">
-        <v>210</v>
+        <v>143</v>
       </c>
     </row>
     <row r="588" ht="20" customHeight="1">
@@ -15728,7 +15728,7 @@
         </is>
       </c>
       <c r="E588" s="20" t="n">
-        <v>222</v>
+        <v>162</v>
       </c>
     </row>
     <row r="589" ht="20" customHeight="1">
@@ -15753,7 +15753,7 @@
         </is>
       </c>
       <c r="E589" s="23" t="n">
-        <v>138</v>
+        <v>148</v>
       </c>
     </row>
     <row r="590" ht="20" customHeight="1">
@@ -15778,7 +15778,7 @@
         </is>
       </c>
       <c r="E590" s="20" t="n">
-        <v>229</v>
+        <v>161</v>
       </c>
     </row>
     <row r="591" ht="20" customHeight="1">
@@ -15803,7 +15803,7 @@
         </is>
       </c>
       <c r="E591" s="23" t="n">
-        <v>216</v>
+        <v>225</v>
       </c>
     </row>
     <row r="592" ht="20" customHeight="1">
@@ -15828,7 +15828,7 @@
         </is>
       </c>
       <c r="E592" s="20" t="n">
-        <v>140</v>
+        <v>202</v>
       </c>
     </row>
     <row r="593" ht="20" customHeight="1">
@@ -15853,7 +15853,7 @@
         </is>
       </c>
       <c r="E593" s="23" t="n">
-        <v>170</v>
+        <v>218</v>
       </c>
     </row>
     <row r="594" ht="20" customHeight="1">
@@ -15878,7 +15878,7 @@
         </is>
       </c>
       <c r="E594" s="20" t="n">
-        <v>132</v>
+        <v>184</v>
       </c>
     </row>
     <row r="595" ht="20" customHeight="1">
@@ -15903,7 +15903,7 @@
         </is>
       </c>
       <c r="E595" s="23" t="n">
-        <v>130</v>
+        <v>191</v>
       </c>
     </row>
     <row r="596" ht="20" customHeight="1">
@@ -15928,7 +15928,7 @@
         </is>
       </c>
       <c r="E596" s="20" t="n">
-        <v>205</v>
+        <v>187</v>
       </c>
     </row>
     <row r="597" ht="20" customHeight="1">
@@ -15953,7 +15953,7 @@
         </is>
       </c>
       <c r="E597" s="23" t="n">
-        <v>185</v>
+        <v>206</v>
       </c>
     </row>
     <row r="598" ht="20" customHeight="1">
@@ -15978,7 +15978,7 @@
         </is>
       </c>
       <c r="E598" s="20" t="n">
-        <v>125</v>
+        <v>180</v>
       </c>
     </row>
     <row r="599" ht="20" customHeight="1">
@@ -16003,7 +16003,7 @@
         </is>
       </c>
       <c r="E599" s="23" t="n">
-        <v>114</v>
+        <v>136</v>
       </c>
     </row>
     <row r="600" ht="20" customHeight="1">
@@ -16028,7 +16028,7 @@
         </is>
       </c>
       <c r="E600" s="20" t="n">
-        <v>204</v>
+        <v>216</v>
       </c>
     </row>
     <row r="601" ht="20" customHeight="1">
@@ -16053,7 +16053,7 @@
         </is>
       </c>
       <c r="E601" s="23" t="n">
-        <v>223</v>
+        <v>125</v>
       </c>
     </row>
     <row r="602" ht="20" customHeight="1">
@@ -16078,7 +16078,7 @@
         </is>
       </c>
       <c r="E602" s="20" t="n">
-        <v>166</v>
+        <v>199</v>
       </c>
     </row>
     <row r="603" ht="20" customHeight="1">
@@ -16103,7 +16103,7 @@
         </is>
       </c>
       <c r="E603" s="23" t="n">
-        <v>215</v>
+        <v>114</v>
       </c>
     </row>
     <row r="604" ht="20" customHeight="1">
@@ -16128,7 +16128,7 @@
         </is>
       </c>
       <c r="E604" s="20" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="605" ht="20" customHeight="1">
@@ -16153,7 +16153,7 @@
         </is>
       </c>
       <c r="E605" s="23" t="n">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="606" ht="20" customHeight="1">
@@ -16178,7 +16178,7 @@
         </is>
       </c>
       <c r="E606" s="20" t="n">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
     <row r="607" ht="20" customHeight="1">
@@ -16203,7 +16203,7 @@
         </is>
       </c>
       <c r="E607" s="23" t="n">
-        <v>221</v>
+        <v>190</v>
       </c>
     </row>
     <row r="608" ht="20" customHeight="1">
@@ -16228,7 +16228,7 @@
         </is>
       </c>
       <c r="E608" s="20" t="n">
-        <v>115</v>
+        <v>235</v>
       </c>
     </row>
     <row r="609" ht="20" customHeight="1">
@@ -16253,7 +16253,7 @@
         </is>
       </c>
       <c r="E609" s="23" t="n">
-        <v>212</v>
+        <v>225</v>
       </c>
     </row>
     <row r="610" ht="20" customHeight="1">
@@ -16278,7 +16278,7 @@
         </is>
       </c>
       <c r="E610" s="20" t="n">
-        <v>229</v>
+        <v>193</v>
       </c>
     </row>
     <row r="611" ht="20" customHeight="1">
@@ -16303,7 +16303,7 @@
         </is>
       </c>
       <c r="E611" s="23" t="n">
-        <v>115</v>
+        <v>189</v>
       </c>
     </row>
     <row r="612" ht="20" customHeight="1">
@@ -16328,7 +16328,7 @@
         </is>
       </c>
       <c r="E612" s="20" t="n">
-        <v>183</v>
+        <v>116</v>
       </c>
     </row>
     <row r="613" ht="20" customHeight="1">
@@ -16353,7 +16353,7 @@
         </is>
       </c>
       <c r="E613" s="23" t="n">
-        <v>234</v>
+        <v>188</v>
       </c>
     </row>
     <row r="614" ht="20" customHeight="1">
@@ -16378,7 +16378,7 @@
         </is>
       </c>
       <c r="E614" s="20" t="n">
-        <v>150</v>
+        <v>118</v>
       </c>
     </row>
     <row r="615" ht="20" customHeight="1">
@@ -16403,7 +16403,7 @@
         </is>
       </c>
       <c r="E615" s="23" t="n">
-        <v>230</v>
+        <v>130</v>
       </c>
     </row>
     <row r="616" ht="20" customHeight="1">
@@ -16428,7 +16428,7 @@
         </is>
       </c>
       <c r="E616" s="20" t="n">
-        <v>140</v>
+        <v>124</v>
       </c>
     </row>
     <row r="617" ht="20" customHeight="1">
@@ -16453,7 +16453,7 @@
         </is>
       </c>
       <c r="E617" s="23" t="n">
-        <v>113</v>
+        <v>146</v>
       </c>
     </row>
     <row r="618" ht="20" customHeight="1">
@@ -16478,7 +16478,7 @@
         </is>
       </c>
       <c r="E618" s="20" t="n">
-        <v>209</v>
+        <v>134</v>
       </c>
     </row>
     <row r="619" ht="20" customHeight="1">
@@ -16503,7 +16503,7 @@
         </is>
       </c>
       <c r="E619" s="23" t="n">
-        <v>173</v>
+        <v>233</v>
       </c>
     </row>
     <row r="620" ht="20" customHeight="1">
@@ -16528,7 +16528,7 @@
         </is>
       </c>
       <c r="E620" s="20" t="n">
-        <v>182</v>
+        <v>163</v>
       </c>
     </row>
     <row r="621" ht="20" customHeight="1">
@@ -16553,7 +16553,7 @@
         </is>
       </c>
       <c r="E621" s="23" t="n">
-        <v>144</v>
+        <v>237</v>
       </c>
     </row>
     <row r="622" ht="20" customHeight="1">
@@ -16578,7 +16578,7 @@
         </is>
       </c>
       <c r="E622" s="20" t="n">
-        <v>154</v>
+        <v>165</v>
       </c>
     </row>
     <row r="623" ht="20" customHeight="1">
@@ -16603,7 +16603,7 @@
         </is>
       </c>
       <c r="E623" s="23" t="n">
-        <v>200</v>
+        <v>227</v>
       </c>
     </row>
     <row r="624" ht="20" customHeight="1">
@@ -16628,7 +16628,7 @@
         </is>
       </c>
       <c r="E624" s="20" t="n">
-        <v>197</v>
+        <v>230</v>
       </c>
     </row>
     <row r="625" ht="20" customHeight="1">
@@ -16653,7 +16653,7 @@
         </is>
       </c>
       <c r="E625" s="23" t="n">
-        <v>165</v>
+        <v>238</v>
       </c>
     </row>
     <row r="626" ht="20" customHeight="1">
@@ -16678,7 +16678,7 @@
         </is>
       </c>
       <c r="E626" s="20" t="n">
-        <v>217</v>
+        <v>234</v>
       </c>
     </row>
     <row r="627" ht="20" customHeight="1">
@@ -16703,7 +16703,7 @@
         </is>
       </c>
       <c r="E627" s="23" t="n">
-        <v>211</v>
+        <v>226</v>
       </c>
     </row>
     <row r="628" ht="20" customHeight="1">
@@ -16728,7 +16728,7 @@
         </is>
       </c>
       <c r="E628" s="20" t="n">
-        <v>200</v>
+        <v>235</v>
       </c>
     </row>
     <row r="629" ht="20" customHeight="1">
@@ -16753,7 +16753,7 @@
         </is>
       </c>
       <c r="E629" s="23" t="n">
-        <v>112</v>
+        <v>190</v>
       </c>
     </row>
     <row r="630" ht="20" customHeight="1">
@@ -16778,7 +16778,7 @@
         </is>
       </c>
       <c r="E630" s="20" t="n">
-        <v>159</v>
+        <v>232</v>
       </c>
     </row>
     <row r="631" ht="20" customHeight="1">
@@ -16803,7 +16803,7 @@
         </is>
       </c>
       <c r="E631" s="23" t="n">
-        <v>136</v>
+        <v>201</v>
       </c>
     </row>
     <row r="632" ht="20" customHeight="1">
@@ -16828,7 +16828,7 @@
         </is>
       </c>
       <c r="E632" s="20" t="n">
-        <v>125</v>
+        <v>179</v>
       </c>
     </row>
     <row r="633" ht="20" customHeight="1">
@@ -16853,7 +16853,7 @@
         </is>
       </c>
       <c r="E633" s="23" t="n">
-        <v>178</v>
+        <v>224</v>
       </c>
     </row>
     <row r="634" ht="20" customHeight="1">
@@ -16878,7 +16878,7 @@
         </is>
       </c>
       <c r="E634" s="20" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="635" ht="20" customHeight="1">
@@ -16903,7 +16903,7 @@
         </is>
       </c>
       <c r="E635" s="23" t="n">
-        <v>153</v>
+        <v>190</v>
       </c>
     </row>
     <row r="636" ht="20" customHeight="1">
@@ -16928,7 +16928,7 @@
         </is>
       </c>
       <c r="E636" s="20" t="n">
-        <v>186</v>
+        <v>211</v>
       </c>
     </row>
     <row r="637" ht="20" customHeight="1">
@@ -16953,7 +16953,7 @@
         </is>
       </c>
       <c r="E637" s="23" t="n">
-        <v>118</v>
+        <v>235</v>
       </c>
     </row>
     <row r="638" ht="20" customHeight="1">
@@ -16978,7 +16978,7 @@
         </is>
       </c>
       <c r="E638" s="20" t="n">
-        <v>161</v>
+        <v>148</v>
       </c>
     </row>
     <row r="639" ht="20" customHeight="1">
@@ -17003,7 +17003,7 @@
         </is>
       </c>
       <c r="E639" s="23" t="n">
-        <v>185</v>
+        <v>165</v>
       </c>
     </row>
     <row r="640" ht="20" customHeight="1">
@@ -17028,7 +17028,7 @@
         </is>
       </c>
       <c r="E640" s="20" t="n">
-        <v>225</v>
+        <v>154</v>
       </c>
     </row>
     <row r="641" ht="20" customHeight="1">
@@ -17053,7 +17053,7 @@
         </is>
       </c>
       <c r="E641" s="23" t="n">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="642" ht="20" customHeight="1">
@@ -17078,7 +17078,7 @@
         </is>
       </c>
       <c r="E642" s="20" t="n">
-        <v>159</v>
+        <v>193</v>
       </c>
     </row>
     <row r="643" ht="20" customHeight="1">
@@ -17103,7 +17103,7 @@
         </is>
       </c>
       <c r="E643" s="23" t="n">
-        <v>191</v>
+        <v>132</v>
       </c>
     </row>
     <row r="644" ht="20" customHeight="1">
@@ -17128,7 +17128,7 @@
         </is>
       </c>
       <c r="E644" s="20" t="n">
-        <v>113</v>
+        <v>144</v>
       </c>
     </row>
     <row r="645" ht="20" customHeight="1">
@@ -17153,7 +17153,7 @@
         </is>
       </c>
       <c r="E645" s="23" t="n">
-        <v>155</v>
+        <v>119</v>
       </c>
     </row>
     <row r="646" ht="20" customHeight="1">
@@ -17178,7 +17178,7 @@
         </is>
       </c>
       <c r="E646" s="20" t="n">
-        <v>137</v>
+        <v>180</v>
       </c>
     </row>
     <row r="647" ht="20" customHeight="1">
@@ -17203,7 +17203,7 @@
         </is>
       </c>
       <c r="E647" s="23" t="n">
-        <v>214</v>
+        <v>208</v>
       </c>
     </row>
     <row r="648" ht="20" customHeight="1">
@@ -17228,7 +17228,7 @@
         </is>
       </c>
       <c r="E648" s="20" t="n">
-        <v>223</v>
+        <v>203</v>
       </c>
     </row>
     <row r="649" ht="20" customHeight="1">
@@ -17253,7 +17253,7 @@
         </is>
       </c>
       <c r="E649" s="23" t="n">
-        <v>196</v>
+        <v>175</v>
       </c>
     </row>
     <row r="650" ht="20" customHeight="1">
@@ -17278,7 +17278,7 @@
         </is>
       </c>
       <c r="E650" s="20" t="n">
-        <v>180</v>
+        <v>201</v>
       </c>
     </row>
     <row r="651" ht="20" customHeight="1">
@@ -17303,7 +17303,7 @@
         </is>
       </c>
       <c r="E651" s="23" t="n">
-        <v>185</v>
+        <v>122</v>
       </c>
     </row>
     <row r="652" ht="20" customHeight="1">
@@ -17328,7 +17328,7 @@
         </is>
       </c>
       <c r="E652" s="20" t="n">
-        <v>203</v>
+        <v>209</v>
       </c>
     </row>
     <row r="653" ht="20" customHeight="1">
@@ -17353,7 +17353,7 @@
         </is>
       </c>
       <c r="E653" s="23" t="n">
-        <v>194</v>
+        <v>212</v>
       </c>
     </row>
     <row r="654" ht="20" customHeight="1">
@@ -17378,7 +17378,7 @@
         </is>
       </c>
       <c r="E654" s="20" t="n">
-        <v>228</v>
+        <v>218</v>
       </c>
     </row>
     <row r="655" ht="20" customHeight="1">
@@ -17403,7 +17403,7 @@
         </is>
       </c>
       <c r="E655" s="23" t="n">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="656" ht="20" customHeight="1">
@@ -17428,7 +17428,7 @@
         </is>
       </c>
       <c r="E656" s="20" t="n">
-        <v>212</v>
+        <v>178</v>
       </c>
     </row>
     <row r="657" ht="20" customHeight="1">
@@ -17453,7 +17453,7 @@
         </is>
       </c>
       <c r="E657" s="23" t="n">
-        <v>171</v>
+        <v>219</v>
       </c>
     </row>
     <row r="658" ht="20" customHeight="1">
@@ -17478,7 +17478,7 @@
         </is>
       </c>
       <c r="E658" s="20" t="n">
-        <v>237</v>
+        <v>198</v>
       </c>
     </row>
     <row r="659" ht="20" customHeight="1">
@@ -17503,7 +17503,7 @@
         </is>
       </c>
       <c r="E659" s="23" t="n">
-        <v>204</v>
+        <v>228</v>
       </c>
     </row>
     <row r="660" ht="20" customHeight="1">
@@ -17528,7 +17528,7 @@
         </is>
       </c>
       <c r="E660" s="20" t="n">
-        <v>225</v>
+        <v>122</v>
       </c>
     </row>
     <row r="661" ht="20" customHeight="1">
@@ -17553,7 +17553,7 @@
         </is>
       </c>
       <c r="E661" s="23" t="n">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="662" ht="20" customHeight="1">
@@ -17578,7 +17578,7 @@
         </is>
       </c>
       <c r="E662" s="20" t="n">
-        <v>186</v>
+        <v>238</v>
       </c>
     </row>
     <row r="663" ht="20" customHeight="1">
@@ -17603,7 +17603,7 @@
         </is>
       </c>
       <c r="E663" s="23" t="n">
-        <v>134</v>
+        <v>153</v>
       </c>
     </row>
     <row r="664" ht="20" customHeight="1">
@@ -17628,7 +17628,7 @@
         </is>
       </c>
       <c r="E664" s="20" t="n">
-        <v>114</v>
+        <v>235</v>
       </c>
     </row>
     <row r="665" ht="20" customHeight="1">
@@ -17653,7 +17653,7 @@
         </is>
       </c>
       <c r="E665" s="23" t="n">
-        <v>230</v>
+        <v>194</v>
       </c>
     </row>
     <row r="666" ht="20" customHeight="1">
@@ -17678,7 +17678,7 @@
         </is>
       </c>
       <c r="E666" s="20" t="n">
-        <v>143</v>
+        <v>207</v>
       </c>
     </row>
     <row r="667" ht="20" customHeight="1">
@@ -17703,7 +17703,7 @@
         </is>
       </c>
       <c r="E667" s="23" t="n">
-        <v>132</v>
+        <v>212</v>
       </c>
     </row>
     <row r="668" ht="20" customHeight="1">
@@ -17728,7 +17728,7 @@
         </is>
       </c>
       <c r="E668" s="20" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="669" ht="20" customHeight="1">
@@ -17753,7 +17753,7 @@
         </is>
       </c>
       <c r="E669" s="23" t="n">
-        <v>229</v>
+        <v>141</v>
       </c>
     </row>
     <row r="670" ht="20" customHeight="1">
@@ -17778,7 +17778,7 @@
         </is>
       </c>
       <c r="E670" s="20" t="n">
-        <v>227</v>
+        <v>177</v>
       </c>
     </row>
     <row r="671" ht="20" customHeight="1">
@@ -17803,7 +17803,7 @@
         </is>
       </c>
       <c r="E671" s="23" t="n">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="672" ht="20" customHeight="1">
@@ -17828,7 +17828,7 @@
         </is>
       </c>
       <c r="E672" s="20" t="n">
-        <v>150</v>
+        <v>132</v>
       </c>
     </row>
     <row r="673" ht="20" customHeight="1">
@@ -17853,7 +17853,7 @@
         </is>
       </c>
       <c r="E673" s="23" t="n">
-        <v>191</v>
+        <v>220</v>
       </c>
     </row>
     <row r="674" ht="20" customHeight="1">
@@ -17878,7 +17878,7 @@
         </is>
       </c>
       <c r="E674" s="20" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="675" ht="20" customHeight="1">
@@ -17903,7 +17903,7 @@
         </is>
       </c>
       <c r="E675" s="23" t="n">
-        <v>204</v>
+        <v>155</v>
       </c>
     </row>
     <row r="676" ht="20" customHeight="1">
@@ -17928,7 +17928,7 @@
         </is>
       </c>
       <c r="E676" s="20" t="n">
-        <v>171</v>
+        <v>135</v>
       </c>
     </row>
     <row r="677" ht="20" customHeight="1">
@@ -17953,7 +17953,7 @@
         </is>
       </c>
       <c r="E677" s="23" t="n">
-        <v>198</v>
+        <v>138</v>
       </c>
     </row>
     <row r="678" ht="20" customHeight="1">
@@ -17978,7 +17978,7 @@
         </is>
       </c>
       <c r="E678" s="20" t="n">
-        <v>158</v>
+        <v>167</v>
       </c>
     </row>
     <row r="679" ht="20" customHeight="1">
@@ -18003,7 +18003,7 @@
         </is>
       </c>
       <c r="E679" s="23" t="n">
-        <v>201</v>
+        <v>143</v>
       </c>
     </row>
     <row r="680" ht="20" customHeight="1">
@@ -18053,7 +18053,7 @@
         </is>
       </c>
       <c r="E681" s="23" t="n">
-        <v>113</v>
+        <v>227</v>
       </c>
     </row>
     <row r="682" ht="20" customHeight="1">
@@ -18078,7 +18078,7 @@
         </is>
       </c>
       <c r="E682" s="20" t="n">
-        <v>152</v>
+        <v>238</v>
       </c>
     </row>
     <row r="683" ht="20" customHeight="1">
@@ -18103,7 +18103,7 @@
         </is>
       </c>
       <c r="E683" s="23" t="n">
-        <v>176</v>
+        <v>210</v>
       </c>
     </row>
     <row r="684" ht="20" customHeight="1">
@@ -18128,7 +18128,7 @@
         </is>
       </c>
       <c r="E684" s="20" t="n">
-        <v>129</v>
+        <v>197</v>
       </c>
     </row>
     <row r="685" ht="20" customHeight="1">
@@ -18153,7 +18153,7 @@
         </is>
       </c>
       <c r="E685" s="23" t="n">
-        <v>239</v>
+        <v>226</v>
       </c>
     </row>
     <row r="686" ht="20" customHeight="1">
@@ -18178,7 +18178,7 @@
         </is>
       </c>
       <c r="E686" s="20" t="n">
-        <v>183</v>
+        <v>210</v>
       </c>
     </row>
     <row r="687" ht="20" customHeight="1">
@@ -18203,7 +18203,7 @@
         </is>
       </c>
       <c r="E687" s="23" t="n">
-        <v>171</v>
+        <v>117</v>
       </c>
     </row>
     <row r="688" ht="20" customHeight="1">
@@ -18228,7 +18228,7 @@
         </is>
       </c>
       <c r="E688" s="20" t="n">
-        <v>141</v>
+        <v>165</v>
       </c>
     </row>
     <row r="689" ht="20" customHeight="1">
@@ -18253,7 +18253,7 @@
         </is>
       </c>
       <c r="E689" s="23" t="n">
-        <v>170</v>
+        <v>190</v>
       </c>
     </row>
     <row r="690" ht="20" customHeight="1">
@@ -18278,7 +18278,7 @@
         </is>
       </c>
       <c r="E690" s="20" t="n">
-        <v>155</v>
+        <v>184</v>
       </c>
     </row>
     <row r="691" ht="20" customHeight="1">
@@ -18303,7 +18303,7 @@
         </is>
       </c>
       <c r="E691" s="23" t="n">
-        <v>173</v>
+        <v>147</v>
       </c>
     </row>
     <row r="692" ht="20" customHeight="1">
@@ -18328,7 +18328,7 @@
         </is>
       </c>
       <c r="E692" s="20" t="n">
-        <v>190</v>
+        <v>149</v>
       </c>
     </row>
     <row r="693" ht="20" customHeight="1">
@@ -18353,7 +18353,7 @@
         </is>
       </c>
       <c r="E693" s="23" t="n">
-        <v>139</v>
+        <v>199</v>
       </c>
     </row>
     <row r="694" ht="20" customHeight="1">
@@ -18378,7 +18378,7 @@
         </is>
       </c>
       <c r="E694" s="20" t="n">
-        <v>162</v>
+        <v>185</v>
       </c>
     </row>
     <row r="695" ht="20" customHeight="1">
@@ -18403,7 +18403,7 @@
         </is>
       </c>
       <c r="E695" s="23" t="n">
-        <v>154</v>
+        <v>166</v>
       </c>
     </row>
     <row r="696" ht="20" customHeight="1">
@@ -18428,7 +18428,7 @@
         </is>
       </c>
       <c r="E696" s="20" t="n">
-        <v>132</v>
+        <v>204</v>
       </c>
     </row>
     <row r="697" ht="20" customHeight="1">
@@ -18453,7 +18453,7 @@
         </is>
       </c>
       <c r="E697" s="23" t="n">
-        <v>196</v>
+        <v>169</v>
       </c>
     </row>
     <row r="698" ht="20" customHeight="1">
@@ -18478,7 +18478,7 @@
         </is>
       </c>
       <c r="E698" s="20" t="n">
-        <v>114</v>
+        <v>188</v>
       </c>
     </row>
     <row r="699" ht="20" customHeight="1">
@@ -18503,7 +18503,7 @@
         </is>
       </c>
       <c r="E699" s="23" t="n">
-        <v>159</v>
+        <v>193</v>
       </c>
     </row>
     <row r="700" ht="20" customHeight="1">
@@ -18528,7 +18528,7 @@
         </is>
       </c>
       <c r="E700" s="20" t="n">
-        <v>195</v>
+        <v>223</v>
       </c>
     </row>
     <row r="701" ht="20" customHeight="1">
@@ -18553,7 +18553,7 @@
         </is>
       </c>
       <c r="E701" s="23" t="n">
-        <v>214</v>
+        <v>204</v>
       </c>
     </row>
     <row r="702" ht="20" customHeight="1">
@@ -18578,7 +18578,7 @@
         </is>
       </c>
       <c r="E702" s="20" t="n">
-        <v>234</v>
+        <v>126</v>
       </c>
     </row>
     <row r="703" ht="20" customHeight="1">
@@ -18603,7 +18603,7 @@
         </is>
       </c>
       <c r="E703" s="23" t="n">
-        <v>184</v>
+        <v>128</v>
       </c>
     </row>
     <row r="704" ht="20" customHeight="1">
@@ -18628,7 +18628,7 @@
         </is>
       </c>
       <c r="E704" s="20" t="n">
-        <v>213</v>
+        <v>152</v>
       </c>
     </row>
     <row r="705" ht="20" customHeight="1">
@@ -18653,7 +18653,7 @@
         </is>
       </c>
       <c r="E705" s="23" t="n">
-        <v>231</v>
+        <v>144</v>
       </c>
     </row>
     <row r="706" ht="20" customHeight="1">
@@ -18678,7 +18678,7 @@
         </is>
       </c>
       <c r="E706" s="20" t="n">
-        <v>234</v>
+        <v>149</v>
       </c>
     </row>
     <row r="707" ht="20" customHeight="1">
@@ -18703,7 +18703,7 @@
         </is>
       </c>
       <c r="E707" s="23" t="n">
-        <v>162</v>
+        <v>151</v>
       </c>
     </row>
     <row r="708" ht="20" customHeight="1">
@@ -18728,7 +18728,7 @@
         </is>
       </c>
       <c r="E708" s="20" t="n">
-        <v>234</v>
+        <v>119</v>
       </c>
     </row>
     <row r="709" ht="20" customHeight="1">
@@ -18753,7 +18753,7 @@
         </is>
       </c>
       <c r="E709" s="23" t="n">
-        <v>164</v>
+        <v>142</v>
       </c>
     </row>
     <row r="710" ht="20" customHeight="1">
@@ -18778,7 +18778,7 @@
         </is>
       </c>
       <c r="E710" s="20" t="n">
-        <v>144</v>
+        <v>237</v>
       </c>
     </row>
     <row r="711" ht="20" customHeight="1">
@@ -18803,7 +18803,7 @@
         </is>
       </c>
       <c r="E711" s="23" t="n">
-        <v>190</v>
+        <v>139</v>
       </c>
     </row>
     <row r="712" ht="20" customHeight="1">
@@ -18828,7 +18828,7 @@
         </is>
       </c>
       <c r="E712" s="20" t="n">
-        <v>236</v>
+        <v>148</v>
       </c>
     </row>
     <row r="713" ht="20" customHeight="1">
@@ -18853,7 +18853,7 @@
         </is>
       </c>
       <c r="E713" s="23" t="n">
-        <v>173</v>
+        <v>126</v>
       </c>
     </row>
     <row r="714" ht="20" customHeight="1">
@@ -18878,7 +18878,7 @@
         </is>
       </c>
       <c r="E714" s="20" t="n">
-        <v>123</v>
+        <v>167</v>
       </c>
     </row>
     <row r="715" ht="20" customHeight="1">
@@ -18903,7 +18903,7 @@
         </is>
       </c>
       <c r="E715" s="23" t="n">
-        <v>130</v>
+        <v>112</v>
       </c>
     </row>
     <row r="716" ht="20" customHeight="1">
@@ -18928,7 +18928,7 @@
         </is>
       </c>
       <c r="E716" s="20" t="n">
-        <v>236</v>
+        <v>208</v>
       </c>
     </row>
     <row r="717" ht="20" customHeight="1">
@@ -18953,7 +18953,7 @@
         </is>
       </c>
       <c r="E717" s="23" t="n">
-        <v>112</v>
+        <v>169</v>
       </c>
     </row>
     <row r="718" ht="20" customHeight="1">
@@ -18978,7 +18978,7 @@
         </is>
       </c>
       <c r="E718" s="20" t="n">
-        <v>218</v>
+        <v>198</v>
       </c>
     </row>
     <row r="719" ht="20" customHeight="1">
@@ -19028,7 +19028,7 @@
         </is>
       </c>
       <c r="E720" s="20" t="n">
-        <v>179</v>
+        <v>191</v>
       </c>
     </row>
     <row r="721" ht="20" customHeight="1">
@@ -19053,7 +19053,7 @@
         </is>
       </c>
       <c r="E721" s="23" t="n">
-        <v>192</v>
+        <v>154</v>
       </c>
     </row>
     <row r="722" ht="20" customHeight="1">
@@ -19078,7 +19078,7 @@
         </is>
       </c>
       <c r="E722" s="20" t="n">
-        <v>115</v>
+        <v>204</v>
       </c>
     </row>
     <row r="723" ht="20" customHeight="1">
@@ -19103,7 +19103,7 @@
         </is>
       </c>
       <c r="E723" s="23" t="n">
-        <v>183</v>
+        <v>217</v>
       </c>
     </row>
     <row r="724" ht="20" customHeight="1">
@@ -19128,7 +19128,7 @@
         </is>
       </c>
       <c r="E724" s="20" t="n">
-        <v>201</v>
+        <v>207</v>
       </c>
     </row>
     <row r="725" ht="20" customHeight="1">
@@ -19153,7 +19153,7 @@
         </is>
       </c>
       <c r="E725" s="23" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
     </row>
     <row r="726" ht="20" customHeight="1">
@@ -19178,7 +19178,7 @@
         </is>
       </c>
       <c r="E726" s="20" t="n">
-        <v>116</v>
+        <v>171</v>
       </c>
     </row>
     <row r="727" ht="20" customHeight="1">
@@ -19203,7 +19203,7 @@
         </is>
       </c>
       <c r="E727" s="23" t="n">
-        <v>156</v>
+        <v>136</v>
       </c>
     </row>
     <row r="728" ht="20" customHeight="1">
@@ -19228,7 +19228,7 @@
         </is>
       </c>
       <c r="E728" s="20" t="n">
-        <v>133</v>
+        <v>156</v>
       </c>
     </row>
     <row r="729" ht="20" customHeight="1">
@@ -19253,7 +19253,7 @@
         </is>
       </c>
       <c r="E729" s="23" t="n">
-        <v>185</v>
+        <v>155</v>
       </c>
     </row>
     <row r="730" ht="20" customHeight="1">
@@ -19278,7 +19278,7 @@
         </is>
       </c>
       <c r="E730" s="20" t="n">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
     <row r="731" ht="20" customHeight="1">
@@ -19303,7 +19303,7 @@
         </is>
       </c>
       <c r="E731" s="23" t="n">
-        <v>213</v>
+        <v>227</v>
       </c>
     </row>
     <row r="732" ht="20" customHeight="1">
@@ -19328,7 +19328,7 @@
         </is>
       </c>
       <c r="E732" s="20" t="n">
-        <v>153</v>
+        <v>168</v>
       </c>
     </row>
     <row r="733" ht="20" customHeight="1">
@@ -19353,7 +19353,7 @@
         </is>
       </c>
       <c r="E733" s="23" t="n">
-        <v>187</v>
+        <v>219</v>
       </c>
     </row>
     <row r="734" ht="20" customHeight="1">
@@ -19378,7 +19378,7 @@
         </is>
       </c>
       <c r="E734" s="20" t="n">
-        <v>126</v>
+        <v>199</v>
       </c>
     </row>
     <row r="735" ht="20" customHeight="1">
@@ -19403,7 +19403,7 @@
         </is>
       </c>
       <c r="E735" s="23" t="n">
-        <v>215</v>
+        <v>230</v>
       </c>
     </row>
     <row r="736" ht="20" customHeight="1">
@@ -19428,7 +19428,7 @@
         </is>
       </c>
       <c r="E736" s="20" t="n">
-        <v>165</v>
+        <v>129</v>
       </c>
     </row>
     <row r="737" ht="20" customHeight="1">
@@ -19453,7 +19453,7 @@
         </is>
       </c>
       <c r="E737" s="23" t="n">
-        <v>183</v>
+        <v>160</v>
       </c>
     </row>
     <row r="738" ht="20" customHeight="1">
@@ -19478,7 +19478,7 @@
         </is>
       </c>
       <c r="E738" s="20" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="739" ht="20" customHeight="1">
@@ -19503,7 +19503,7 @@
         </is>
       </c>
       <c r="E739" s="23" t="n">
-        <v>218</v>
+        <v>111</v>
       </c>
     </row>
     <row r="740" ht="20" customHeight="1">
@@ -19528,7 +19528,7 @@
         </is>
       </c>
       <c r="E740" s="20" t="n">
-        <v>224</v>
+        <v>209</v>
       </c>
     </row>
     <row r="741" ht="20" customHeight="1">
@@ -19553,7 +19553,7 @@
         </is>
       </c>
       <c r="E741" s="23" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="742" ht="20" customHeight="1">
@@ -19578,7 +19578,7 @@
         </is>
       </c>
       <c r="E742" s="20" t="n">
-        <v>138</v>
+        <v>183</v>
       </c>
     </row>
     <row r="743" ht="20" customHeight="1">
@@ -19603,7 +19603,7 @@
         </is>
       </c>
       <c r="E743" s="23" t="n">
-        <v>237</v>
+        <v>225</v>
       </c>
     </row>
     <row r="744" ht="20" customHeight="1">
@@ -19628,7 +19628,7 @@
         </is>
       </c>
       <c r="E744" s="20" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="745" ht="20" customHeight="1">
@@ -19653,7 +19653,7 @@
         </is>
       </c>
       <c r="E745" s="23" t="n">
-        <v>208</v>
+        <v>215</v>
       </c>
     </row>
     <row r="746" ht="20" customHeight="1">
@@ -19678,7 +19678,7 @@
         </is>
       </c>
       <c r="E746" s="20" t="n">
-        <v>240</v>
+        <v>207</v>
       </c>
     </row>
     <row r="747" ht="20" customHeight="1">
@@ -19703,7 +19703,7 @@
         </is>
       </c>
       <c r="E747" s="23" t="n">
-        <v>167</v>
+        <v>118</v>
       </c>
     </row>
     <row r="748" ht="20" customHeight="1">
@@ -19728,7 +19728,7 @@
         </is>
       </c>
       <c r="E748" s="20" t="n">
-        <v>195</v>
+        <v>228</v>
       </c>
     </row>
     <row r="749" ht="20" customHeight="1">
@@ -19753,7 +19753,7 @@
         </is>
       </c>
       <c r="E749" s="23" t="n">
-        <v>204</v>
+        <v>198</v>
       </c>
     </row>
     <row r="750" ht="20" customHeight="1">
@@ -19778,7 +19778,7 @@
         </is>
       </c>
       <c r="E750" s="20" t="n">
-        <v>121</v>
+        <v>171</v>
       </c>
     </row>
     <row r="751" ht="20" customHeight="1">
@@ -19803,7 +19803,7 @@
         </is>
       </c>
       <c r="E751" s="23" t="n">
-        <v>183</v>
+        <v>131</v>
       </c>
     </row>
     <row r="752" ht="20" customHeight="1">
@@ -19828,7 +19828,7 @@
         </is>
       </c>
       <c r="E752" s="20" t="n">
-        <v>201</v>
+        <v>234</v>
       </c>
     </row>
     <row r="753" ht="20" customHeight="1">
@@ -19853,7 +19853,7 @@
         </is>
       </c>
       <c r="E753" s="23" t="n">
-        <v>182</v>
+        <v>201</v>
       </c>
     </row>
     <row r="754" ht="20" customHeight="1">
@@ -19878,7 +19878,7 @@
         </is>
       </c>
       <c r="E754" s="20" t="n">
-        <v>228</v>
+        <v>140</v>
       </c>
     </row>
     <row r="755" ht="20" customHeight="1">
@@ -19903,7 +19903,7 @@
         </is>
       </c>
       <c r="E755" s="23" t="n">
-        <v>212</v>
+        <v>131</v>
       </c>
     </row>
     <row r="756" ht="20" customHeight="1">
@@ -19928,7 +19928,7 @@
         </is>
       </c>
       <c r="E756" s="20" t="n">
-        <v>167</v>
+        <v>141</v>
       </c>
     </row>
     <row r="757" ht="20" customHeight="1">
@@ -19953,7 +19953,7 @@
         </is>
       </c>
       <c r="E757" s="23" t="n">
-        <v>143</v>
+        <v>197</v>
       </c>
     </row>
     <row r="758" ht="20" customHeight="1">
@@ -19978,7 +19978,7 @@
         </is>
       </c>
       <c r="E758" s="20" t="n">
-        <v>158</v>
+        <v>194</v>
       </c>
     </row>
     <row r="759" ht="20" customHeight="1">
@@ -20003,7 +20003,7 @@
         </is>
       </c>
       <c r="E759" s="23" t="n">
-        <v>199</v>
+        <v>228</v>
       </c>
     </row>
     <row r="760" ht="20" customHeight="1">
@@ -20028,7 +20028,7 @@
         </is>
       </c>
       <c r="E760" s="20" t="n">
-        <v>232</v>
+        <v>210</v>
       </c>
     </row>
     <row r="761" ht="20" customHeight="1">
@@ -20053,7 +20053,7 @@
         </is>
       </c>
       <c r="E761" s="23" t="n">
-        <v>113</v>
+        <v>216</v>
       </c>
     </row>
     <row r="762" ht="20" customHeight="1">
@@ -20078,7 +20078,7 @@
         </is>
       </c>
       <c r="E762" s="20" t="n">
-        <v>158</v>
+        <v>153</v>
       </c>
     </row>
     <row r="763" ht="20" customHeight="1">
@@ -20103,7 +20103,7 @@
         </is>
       </c>
       <c r="E763" s="23" t="n">
-        <v>130</v>
+        <v>111</v>
       </c>
     </row>
     <row r="764" ht="20" customHeight="1">
@@ -20128,7 +20128,7 @@
         </is>
       </c>
       <c r="E764" s="20" t="n">
-        <v>122</v>
+        <v>208</v>
       </c>
     </row>
     <row r="765" ht="20" customHeight="1">
@@ -20153,7 +20153,7 @@
         </is>
       </c>
       <c r="E765" s="23" t="n">
-        <v>148</v>
+        <v>111</v>
       </c>
     </row>
     <row r="766" ht="20" customHeight="1">
@@ -20178,7 +20178,7 @@
         </is>
       </c>
       <c r="E766" s="20" t="n">
-        <v>160</v>
+        <v>129</v>
       </c>
     </row>
     <row r="767" ht="20" customHeight="1">
@@ -20203,7 +20203,7 @@
         </is>
       </c>
       <c r="E767" s="23" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="768" ht="20" customHeight="1">
@@ -20228,7 +20228,7 @@
         </is>
       </c>
       <c r="E768" s="20" t="n">
-        <v>113</v>
+        <v>206</v>
       </c>
     </row>
     <row r="769" ht="20" customHeight="1">
@@ -20253,7 +20253,7 @@
         </is>
       </c>
       <c r="E769" s="23" t="n">
-        <v>180</v>
+        <v>110</v>
       </c>
     </row>
     <row r="770" ht="20" customHeight="1">
@@ -20278,7 +20278,7 @@
         </is>
       </c>
       <c r="E770" s="20" t="n">
-        <v>112</v>
+        <v>218</v>
       </c>
     </row>
     <row r="771" ht="20" customHeight="1">
@@ -20303,7 +20303,7 @@
         </is>
       </c>
       <c r="E771" s="23" t="n">
-        <v>181</v>
+        <v>213</v>
       </c>
     </row>
     <row r="772" ht="20" customHeight="1">
@@ -20328,7 +20328,7 @@
         </is>
       </c>
       <c r="E772" s="20" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
     </row>
     <row r="773" ht="20" customHeight="1">
@@ -20353,7 +20353,7 @@
         </is>
       </c>
       <c r="E773" s="23" t="n">
-        <v>178</v>
+        <v>131</v>
       </c>
     </row>
     <row r="774" ht="20" customHeight="1">
@@ -20378,7 +20378,7 @@
         </is>
       </c>
       <c r="E774" s="20" t="n">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="775" ht="20" customHeight="1">
@@ -20403,7 +20403,7 @@
         </is>
       </c>
       <c r="E775" s="23" t="n">
-        <v>149</v>
+        <v>128</v>
       </c>
     </row>
     <row r="776" ht="20" customHeight="1">
@@ -20428,7 +20428,7 @@
         </is>
       </c>
       <c r="E776" s="20" t="n">
-        <v>239</v>
+        <v>146</v>
       </c>
     </row>
     <row r="777" ht="20" customHeight="1">
@@ -20453,7 +20453,7 @@
         </is>
       </c>
       <c r="E777" s="23" t="n">
-        <v>163</v>
+        <v>121</v>
       </c>
     </row>
     <row r="778" ht="20" customHeight="1">
@@ -20478,7 +20478,7 @@
         </is>
       </c>
       <c r="E778" s="20" t="n">
-        <v>146</v>
+        <v>154</v>
       </c>
     </row>
     <row r="779" ht="20" customHeight="1">
@@ -20503,7 +20503,7 @@
         </is>
       </c>
       <c r="E779" s="23" t="n">
-        <v>190</v>
+        <v>183</v>
       </c>
     </row>
     <row r="780" ht="20" customHeight="1">
@@ -20528,7 +20528,7 @@
         </is>
       </c>
       <c r="E780" s="20" t="n">
-        <v>239</v>
+        <v>174</v>
       </c>
     </row>
     <row r="781" ht="20" customHeight="1">
@@ -20553,7 +20553,7 @@
         </is>
       </c>
       <c r="E781" s="23" t="n">
-        <v>147</v>
+        <v>191</v>
       </c>
     </row>
     <row r="782" ht="20" customHeight="1">
@@ -20578,7 +20578,7 @@
         </is>
       </c>
       <c r="E782" s="20" t="n">
-        <v>129</v>
+        <v>173</v>
       </c>
     </row>
     <row r="783" ht="20" customHeight="1">
@@ -20603,7 +20603,7 @@
         </is>
       </c>
       <c r="E783" s="23" t="n">
-        <v>193</v>
+        <v>144</v>
       </c>
     </row>
     <row r="784" ht="20" customHeight="1">
@@ -20628,7 +20628,7 @@
         </is>
       </c>
       <c r="E784" s="20" t="n">
-        <v>175</v>
+        <v>231</v>
       </c>
     </row>
     <row r="785" ht="20" customHeight="1">
@@ -20653,7 +20653,7 @@
         </is>
       </c>
       <c r="E785" s="23" t="n">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="786" ht="20" customHeight="1">
@@ -20678,7 +20678,7 @@
         </is>
       </c>
       <c r="E786" s="20" t="n">
-        <v>126</v>
+        <v>118</v>
       </c>
     </row>
     <row r="787" ht="20" customHeight="1">
@@ -20703,7 +20703,7 @@
         </is>
       </c>
       <c r="E787" s="23" t="n">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="788" ht="20" customHeight="1">
@@ -20728,7 +20728,7 @@
         </is>
       </c>
       <c r="E788" s="20" t="n">
-        <v>168</v>
+        <v>228</v>
       </c>
     </row>
     <row r="789" ht="20" customHeight="1">
@@ -20753,7 +20753,7 @@
         </is>
       </c>
       <c r="E789" s="23" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="790" ht="20" customHeight="1">
@@ -20778,7 +20778,7 @@
         </is>
       </c>
       <c r="E790" s="20" t="n">
-        <v>112</v>
+        <v>132</v>
       </c>
     </row>
     <row r="791" ht="20" customHeight="1">
@@ -20803,7 +20803,7 @@
         </is>
       </c>
       <c r="E791" s="23" t="n">
-        <v>164</v>
+        <v>110</v>
       </c>
     </row>
     <row r="792" ht="20" customHeight="1">
@@ -20828,7 +20828,7 @@
         </is>
       </c>
       <c r="E792" s="20" t="n">
-        <v>197</v>
+        <v>179</v>
       </c>
     </row>
     <row r="793" ht="20" customHeight="1">
@@ -20853,7 +20853,7 @@
         </is>
       </c>
       <c r="E793" s="23" t="n">
-        <v>131</v>
+        <v>114</v>
       </c>
     </row>
     <row r="794" ht="20" customHeight="1">
@@ -20878,7 +20878,7 @@
         </is>
       </c>
       <c r="E794" s="20" t="n">
-        <v>195</v>
+        <v>225</v>
       </c>
     </row>
     <row r="795" ht="20" customHeight="1">
@@ -20903,7 +20903,7 @@
         </is>
       </c>
       <c r="E795" s="23" t="n">
-        <v>167</v>
+        <v>126</v>
       </c>
     </row>
     <row r="796" ht="20" customHeight="1">
@@ -20928,7 +20928,7 @@
         </is>
       </c>
       <c r="E796" s="20" t="n">
-        <v>132</v>
+        <v>236</v>
       </c>
     </row>
     <row r="797" ht="20" customHeight="1">
@@ -20953,7 +20953,7 @@
         </is>
       </c>
       <c r="E797" s="23" t="n">
-        <v>234</v>
+        <v>189</v>
       </c>
     </row>
     <row r="798" ht="20" customHeight="1">
@@ -20978,7 +20978,7 @@
         </is>
       </c>
       <c r="E798" s="20" t="n">
-        <v>222</v>
+        <v>112</v>
       </c>
     </row>
     <row r="799" ht="20" customHeight="1">
@@ -21003,7 +21003,7 @@
         </is>
       </c>
       <c r="E799" s="23" t="n">
-        <v>235</v>
+        <v>135</v>
       </c>
     </row>
     <row r="800" ht="20" customHeight="1">
@@ -21028,7 +21028,7 @@
         </is>
       </c>
       <c r="E800" s="20" t="n">
-        <v>174</v>
+        <v>215</v>
       </c>
     </row>
     <row r="801" ht="20" customHeight="1">
@@ -21053,7 +21053,7 @@
         </is>
       </c>
       <c r="E801" s="23" t="n">
-        <v>151</v>
+        <v>209</v>
       </c>
     </row>
   </sheetData>

--- a/Appium_E2E_Test_Report_Traverse.xlsx
+++ b/Appium_E2E_Test_Report_Traverse.xlsx
@@ -791,7 +791,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 07:36:11</t>
+          <t>2026-08-11 07:47:32</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="E2" s="20" t="n">
-        <v>161</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="E3" s="23" t="n">
-        <v>164</v>
+        <v>238</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="E4" s="20" t="n">
-        <v>213</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="E5" s="23" t="n">
-        <v>208</v>
+        <v>173</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="E6" s="20" t="n">
-        <v>202</v>
+        <v>217</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="E7" s="23" t="n">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -1228,7 +1228,7 @@
         </is>
       </c>
       <c r="E8" s="20" t="n">
-        <v>172</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="E9" s="23" t="n">
-        <v>116</v>
+        <v>217</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
@@ -1278,7 +1278,7 @@
         </is>
       </c>
       <c r="E10" s="20" t="n">
-        <v>223</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="E11" s="23" t="n">
-        <v>208</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
@@ -1328,7 +1328,7 @@
         </is>
       </c>
       <c r="E12" s="20" t="n">
-        <v>118</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="E13" s="23" t="n">
-        <v>218</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="E14" s="20" t="n">
-        <v>174</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="E15" s="23" t="n">
-        <v>122</v>
+        <v>208</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="E16" s="20" t="n">
-        <v>149</v>
+        <v>184</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="E17" s="23" t="n">
-        <v>175</v>
+        <v>135</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -1478,7 +1478,7 @@
         </is>
       </c>
       <c r="E18" s="20" t="n">
-        <v>121</v>
+        <v>151</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
@@ -1503,7 +1503,7 @@
         </is>
       </c>
       <c r="E19" s="23" t="n">
-        <v>179</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="E20" s="20" t="n">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="E21" s="23" t="n">
-        <v>188</v>
+        <v>204</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
@@ -1578,7 +1578,7 @@
         </is>
       </c>
       <c r="E22" s="20" t="n">
-        <v>126</v>
+        <v>158</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="E23" s="23" t="n">
-        <v>207</v>
+        <v>112</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
@@ -1628,7 +1628,7 @@
         </is>
       </c>
       <c r="E24" s="20" t="n">
-        <v>133</v>
+        <v>206</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="E25" s="23" t="n">
-        <v>205</v>
+        <v>189</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
@@ -1678,7 +1678,7 @@
         </is>
       </c>
       <c r="E26" s="20" t="n">
-        <v>172</v>
+        <v>190</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="E27" s="23" t="n">
-        <v>200</v>
+        <v>159</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="E28" s="20" t="n">
-        <v>214</v>
+        <v>139</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="E29" s="23" t="n">
-        <v>154</v>
+        <v>124</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="E30" s="20" t="n">
-        <v>159</v>
+        <v>229</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
@@ -1803,7 +1803,7 @@
         </is>
       </c>
       <c r="E31" s="23" t="n">
-        <v>145</v>
+        <v>215</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
@@ -1828,7 +1828,7 @@
         </is>
       </c>
       <c r="E32" s="20" t="n">
-        <v>208</v>
+        <v>143</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
@@ -1853,7 +1853,7 @@
         </is>
       </c>
       <c r="E33" s="23" t="n">
-        <v>213</v>
+        <v>142</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
@@ -1878,7 +1878,7 @@
         </is>
       </c>
       <c r="E34" s="20" t="n">
-        <v>210</v>
+        <v>149</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="E35" s="23" t="n">
-        <v>145</v>
+        <v>216</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="E36" s="20" t="n">
-        <v>136</v>
+        <v>200</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="E37" s="23" t="n">
-        <v>161</v>
+        <v>166</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
@@ -1978,7 +1978,7 @@
         </is>
       </c>
       <c r="E38" s="20" t="n">
-        <v>203</v>
+        <v>113</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="E39" s="23" t="n">
-        <v>204</v>
+        <v>154</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="E40" s="20" t="n">
-        <v>205</v>
+        <v>190</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="E41" s="23" t="n">
-        <v>232</v>
+        <v>118</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
@@ -2078,7 +2078,7 @@
         </is>
       </c>
       <c r="E42" s="20" t="n">
-        <v>187</v>
+        <v>214</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="E43" s="23" t="n">
-        <v>207</v>
+        <v>120</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="E44" s="20" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="E45" s="23" t="n">
-        <v>143</v>
+        <v>129</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
@@ -2178,7 +2178,7 @@
         </is>
       </c>
       <c r="E46" s="20" t="n">
-        <v>213</v>
+        <v>204</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
@@ -2203,7 +2203,7 @@
         </is>
       </c>
       <c r="E47" s="23" t="n">
-        <v>166</v>
+        <v>131</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="E48" s="20" t="n">
-        <v>143</v>
+        <v>124</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
@@ -2253,7 +2253,7 @@
         </is>
       </c>
       <c r="E49" s="23" t="n">
-        <v>233</v>
+        <v>238</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
@@ -2278,7 +2278,7 @@
         </is>
       </c>
       <c r="E50" s="20" t="n">
-        <v>196</v>
+        <v>160</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="E51" s="23" t="n">
-        <v>112</v>
+        <v>190</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
@@ -2328,7 +2328,7 @@
         </is>
       </c>
       <c r="E52" s="20" t="n">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
@@ -2353,7 +2353,7 @@
         </is>
       </c>
       <c r="E53" s="23" t="n">
-        <v>225</v>
+        <v>172</v>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="E54" s="20" t="n">
-        <v>199</v>
+        <v>133</v>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1">
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="E55" s="23" t="n">
-        <v>117</v>
+        <v>225</v>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1">
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="E56" s="20" t="n">
-        <v>120</v>
+        <v>166</v>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1">
@@ -2453,7 +2453,7 @@
         </is>
       </c>
       <c r="E57" s="23" t="n">
-        <v>139</v>
+        <v>113</v>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1">
@@ -2478,7 +2478,7 @@
         </is>
       </c>
       <c r="E58" s="20" t="n">
-        <v>214</v>
+        <v>125</v>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1">
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="E59" s="23" t="n">
-        <v>124</v>
+        <v>229</v>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1">
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="E60" s="20" t="n">
-        <v>148</v>
+        <v>121</v>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
@@ -2553,7 +2553,7 @@
         </is>
       </c>
       <c r="E61" s="23" t="n">
-        <v>180</v>
+        <v>143</v>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="E62" s="20" t="n">
-        <v>185</v>
+        <v>149</v>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="E63" s="23" t="n">
-        <v>126</v>
+        <v>221</v>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1">
@@ -2628,7 +2628,7 @@
         </is>
       </c>
       <c r="E64" s="20" t="n">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1">
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="E65" s="23" t="n">
-        <v>173</v>
+        <v>113</v>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1">
@@ -2678,7 +2678,7 @@
         </is>
       </c>
       <c r="E66" s="20" t="n">
-        <v>175</v>
+        <v>116</v>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="E67" s="23" t="n">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="E68" s="20" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="E69" s="23" t="n">
-        <v>217</v>
+        <v>226</v>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1">
@@ -2778,7 +2778,7 @@
         </is>
       </c>
       <c r="E70" s="20" t="n">
-        <v>191</v>
+        <v>139</v>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1">
@@ -2803,7 +2803,7 @@
         </is>
       </c>
       <c r="E71" s="23" t="n">
-        <v>184</v>
+        <v>140</v>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1">
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="E72" s="20" t="n">
-        <v>223</v>
+        <v>195</v>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1">
@@ -2853,7 +2853,7 @@
         </is>
       </c>
       <c r="E73" s="23" t="n">
-        <v>165</v>
+        <v>176</v>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
@@ -2878,7 +2878,7 @@
         </is>
       </c>
       <c r="E74" s="20" t="n">
-        <v>123</v>
+        <v>207</v>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="E75" s="23" t="n">
-        <v>128</v>
+        <v>171</v>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
@@ -2928,7 +2928,7 @@
         </is>
       </c>
       <c r="E76" s="20" t="n">
-        <v>137</v>
+        <v>234</v>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="E77" s="23" t="n">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1">
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="E78" s="20" t="n">
-        <v>152</v>
+        <v>237</v>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
@@ -3003,7 +3003,7 @@
         </is>
       </c>
       <c r="E79" s="23" t="n">
-        <v>118</v>
+        <v>236</v>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1">
@@ -3028,7 +3028,7 @@
         </is>
       </c>
       <c r="E80" s="20" t="n">
-        <v>215</v>
+        <v>238</v>
       </c>
     </row>
     <row r="81" ht="20" customHeight="1">
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="E81" s="23" t="n">
-        <v>238</v>
+        <v>226</v>
       </c>
     </row>
     <row r="82" ht="20" customHeight="1">
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="E82" s="20" t="n">
-        <v>176</v>
+        <v>239</v>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1">
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="E83" s="23" t="n">
-        <v>118</v>
+        <v>165</v>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1">
@@ -3128,7 +3128,7 @@
         </is>
       </c>
       <c r="E84" s="20" t="n">
-        <v>214</v>
+        <v>129</v>
       </c>
     </row>
     <row r="85" ht="20" customHeight="1">
@@ -3153,7 +3153,7 @@
         </is>
       </c>
       <c r="E85" s="23" t="n">
-        <v>237</v>
+        <v>159</v>
       </c>
     </row>
     <row r="86" ht="20" customHeight="1">
@@ -3178,7 +3178,7 @@
         </is>
       </c>
       <c r="E86" s="20" t="n">
-        <v>145</v>
+        <v>234</v>
       </c>
     </row>
     <row r="87" ht="20" customHeight="1">
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="E87" s="23" t="n">
-        <v>155</v>
+        <v>227</v>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1">
@@ -3228,7 +3228,7 @@
         </is>
       </c>
       <c r="E88" s="20" t="n">
-        <v>174</v>
+        <v>119</v>
       </c>
     </row>
     <row r="89" ht="20" customHeight="1">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="E89" s="23" t="n">
-        <v>117</v>
+        <v>204</v>
       </c>
     </row>
     <row r="90" ht="20" customHeight="1">
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="E90" s="20" t="n">
-        <v>224</v>
+        <v>214</v>
       </c>
     </row>
     <row r="91" ht="20" customHeight="1">
@@ -3303,7 +3303,7 @@
         </is>
       </c>
       <c r="E91" s="23" t="n">
-        <v>166</v>
+        <v>202</v>
       </c>
     </row>
     <row r="92" ht="20" customHeight="1">
@@ -3328,7 +3328,7 @@
         </is>
       </c>
       <c r="E92" s="20" t="n">
-        <v>134</v>
+        <v>173</v>
       </c>
     </row>
     <row r="93" ht="20" customHeight="1">
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="E93" s="23" t="n">
-        <v>190</v>
+        <v>182</v>
       </c>
     </row>
     <row r="94" ht="20" customHeight="1">
@@ -3378,7 +3378,7 @@
         </is>
       </c>
       <c r="E94" s="20" t="n">
-        <v>131</v>
+        <v>116</v>
       </c>
     </row>
     <row r="95" ht="20" customHeight="1">
@@ -3403,7 +3403,7 @@
         </is>
       </c>
       <c r="E95" s="23" t="n">
-        <v>213</v>
+        <v>146</v>
       </c>
     </row>
     <row r="96" ht="20" customHeight="1">
@@ -3428,7 +3428,7 @@
         </is>
       </c>
       <c r="E96" s="20" t="n">
-        <v>135</v>
+        <v>239</v>
       </c>
     </row>
     <row r="97" ht="20" customHeight="1">
@@ -3453,7 +3453,7 @@
         </is>
       </c>
       <c r="E97" s="23" t="n">
-        <v>181</v>
+        <v>188</v>
       </c>
     </row>
     <row r="98" ht="20" customHeight="1">
@@ -3478,7 +3478,7 @@
         </is>
       </c>
       <c r="E98" s="20" t="n">
-        <v>135</v>
+        <v>167</v>
       </c>
     </row>
     <row r="99" ht="20" customHeight="1">
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="E99" s="23" t="n">
-        <v>144</v>
+        <v>171</v>
       </c>
     </row>
     <row r="100" ht="20" customHeight="1">
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="E100" s="20" t="n">
-        <v>154</v>
+        <v>210</v>
       </c>
     </row>
     <row r="101" ht="20" customHeight="1">
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="E101" s="23" t="n">
-        <v>157</v>
+        <v>190</v>
       </c>
     </row>
     <row r="102" ht="20" customHeight="1">
@@ -3578,7 +3578,7 @@
         </is>
       </c>
       <c r="E102" s="20" t="n">
-        <v>164</v>
+        <v>198</v>
       </c>
     </row>
     <row r="103" ht="20" customHeight="1">
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="E103" s="23" t="n">
-        <v>130</v>
+        <v>191</v>
       </c>
     </row>
     <row r="104" ht="20" customHeight="1">
@@ -3628,7 +3628,7 @@
         </is>
       </c>
       <c r="E104" s="20" t="n">
-        <v>132</v>
+        <v>166</v>
       </c>
     </row>
     <row r="105" ht="20" customHeight="1">
@@ -3653,7 +3653,7 @@
         </is>
       </c>
       <c r="E105" s="23" t="n">
-        <v>118</v>
+        <v>182</v>
       </c>
     </row>
     <row r="106" ht="20" customHeight="1">
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="E106" s="20" t="n">
-        <v>167</v>
+        <v>141</v>
       </c>
     </row>
     <row r="107" ht="20" customHeight="1">
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="E107" s="23" t="n">
-        <v>222</v>
+        <v>167</v>
       </c>
     </row>
     <row r="108" ht="20" customHeight="1">
@@ -3728,7 +3728,7 @@
         </is>
       </c>
       <c r="E108" s="20" t="n">
-        <v>214</v>
+        <v>232</v>
       </c>
     </row>
     <row r="109" ht="20" customHeight="1">
@@ -3753,7 +3753,7 @@
         </is>
       </c>
       <c r="E109" s="23" t="n">
-        <v>238</v>
+        <v>192</v>
       </c>
     </row>
     <row r="110" ht="20" customHeight="1">
@@ -3778,7 +3778,7 @@
         </is>
       </c>
       <c r="E110" s="20" t="n">
-        <v>159</v>
+        <v>232</v>
       </c>
     </row>
     <row r="111" ht="20" customHeight="1">
@@ -3803,7 +3803,7 @@
         </is>
       </c>
       <c r="E111" s="23" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="112" ht="20" customHeight="1">
@@ -3828,7 +3828,7 @@
         </is>
       </c>
       <c r="E112" s="20" t="n">
-        <v>204</v>
+        <v>134</v>
       </c>
     </row>
     <row r="113" ht="20" customHeight="1">
@@ -3853,7 +3853,7 @@
         </is>
       </c>
       <c r="E113" s="23" t="n">
-        <v>151</v>
+        <v>177</v>
       </c>
     </row>
     <row r="114" ht="20" customHeight="1">
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="E114" s="20" t="n">
-        <v>172</v>
+        <v>148</v>
       </c>
     </row>
     <row r="115" ht="20" customHeight="1">
@@ -3903,7 +3903,7 @@
         </is>
       </c>
       <c r="E115" s="23" t="n">
-        <v>145</v>
+        <v>221</v>
       </c>
     </row>
     <row r="116" ht="20" customHeight="1">
@@ -3928,7 +3928,7 @@
         </is>
       </c>
       <c r="E116" s="20" t="n">
-        <v>121</v>
+        <v>176</v>
       </c>
     </row>
     <row r="117" ht="20" customHeight="1">
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="E117" s="23" t="n">
-        <v>220</v>
+        <v>194</v>
       </c>
     </row>
     <row r="118" ht="20" customHeight="1">
@@ -3978,7 +3978,7 @@
         </is>
       </c>
       <c r="E118" s="20" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="119" ht="20" customHeight="1">
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="E119" s="23" t="n">
-        <v>232</v>
+        <v>238</v>
       </c>
     </row>
     <row r="120" ht="20" customHeight="1">
@@ -4028,7 +4028,7 @@
         </is>
       </c>
       <c r="E120" s="20" t="n">
-        <v>125</v>
+        <v>133</v>
       </c>
     </row>
     <row r="121" ht="20" customHeight="1">
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="E121" s="23" t="n">
-        <v>155</v>
+        <v>138</v>
       </c>
     </row>
     <row r="122" ht="20" customHeight="1">
@@ -4078,7 +4078,7 @@
         </is>
       </c>
       <c r="E122" s="20" t="n">
-        <v>237</v>
+        <v>185</v>
       </c>
     </row>
     <row r="123" ht="20" customHeight="1">
@@ -4103,7 +4103,7 @@
         </is>
       </c>
       <c r="E123" s="23" t="n">
-        <v>218</v>
+        <v>149</v>
       </c>
     </row>
     <row r="124" ht="20" customHeight="1">
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="E124" s="20" t="n">
-        <v>232</v>
+        <v>145</v>
       </c>
     </row>
     <row r="125" ht="20" customHeight="1">
@@ -4153,7 +4153,7 @@
         </is>
       </c>
       <c r="E125" s="23" t="n">
-        <v>145</v>
+        <v>191</v>
       </c>
     </row>
     <row r="126" ht="20" customHeight="1">
@@ -4178,7 +4178,7 @@
         </is>
       </c>
       <c r="E126" s="20" t="n">
-        <v>170</v>
+        <v>239</v>
       </c>
     </row>
     <row r="127" ht="20" customHeight="1">
@@ -4203,7 +4203,7 @@
         </is>
       </c>
       <c r="E127" s="23" t="n">
-        <v>232</v>
+        <v>145</v>
       </c>
     </row>
     <row r="128" ht="20" customHeight="1">
@@ -4228,7 +4228,7 @@
         </is>
       </c>
       <c r="E128" s="20" t="n">
-        <v>212</v>
+        <v>144</v>
       </c>
     </row>
     <row r="129" ht="20" customHeight="1">
@@ -4253,7 +4253,7 @@
         </is>
       </c>
       <c r="E129" s="23" t="n">
-        <v>171</v>
+        <v>154</v>
       </c>
     </row>
     <row r="130" ht="20" customHeight="1">
@@ -4278,7 +4278,7 @@
         </is>
       </c>
       <c r="E130" s="20" t="n">
-        <v>129</v>
+        <v>229</v>
       </c>
     </row>
     <row r="131" ht="20" customHeight="1">
@@ -4303,7 +4303,7 @@
         </is>
       </c>
       <c r="E131" s="23" t="n">
-        <v>120</v>
+        <v>173</v>
       </c>
     </row>
     <row r="132" ht="20" customHeight="1">
@@ -4328,7 +4328,7 @@
         </is>
       </c>
       <c r="E132" s="20" t="n">
-        <v>124</v>
+        <v>162</v>
       </c>
     </row>
     <row r="133" ht="20" customHeight="1">
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="E133" s="23" t="n">
-        <v>180</v>
+        <v>191</v>
       </c>
     </row>
     <row r="134" ht="20" customHeight="1">
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="E134" s="20" t="n">
-        <v>234</v>
+        <v>175</v>
       </c>
     </row>
     <row r="135" ht="20" customHeight="1">
@@ -4403,7 +4403,7 @@
         </is>
       </c>
       <c r="E135" s="23" t="n">
-        <v>191</v>
+        <v>196</v>
       </c>
     </row>
     <row r="136" ht="20" customHeight="1">
@@ -4428,7 +4428,7 @@
         </is>
       </c>
       <c r="E136" s="20" t="n">
-        <v>127</v>
+        <v>160</v>
       </c>
     </row>
     <row r="137" ht="20" customHeight="1">
@@ -4453,7 +4453,7 @@
         </is>
       </c>
       <c r="E137" s="23" t="n">
-        <v>118</v>
+        <v>190</v>
       </c>
     </row>
     <row r="138" ht="20" customHeight="1">
@@ -4478,7 +4478,7 @@
         </is>
       </c>
       <c r="E138" s="20" t="n">
-        <v>136</v>
+        <v>195</v>
       </c>
     </row>
     <row r="139" ht="20" customHeight="1">
@@ -4503,7 +4503,7 @@
         </is>
       </c>
       <c r="E139" s="23" t="n">
-        <v>229</v>
+        <v>200</v>
       </c>
     </row>
     <row r="140" ht="20" customHeight="1">
@@ -4528,7 +4528,7 @@
         </is>
       </c>
       <c r="E140" s="20" t="n">
-        <v>161</v>
+        <v>135</v>
       </c>
     </row>
     <row r="141" ht="20" customHeight="1">
@@ -4553,7 +4553,7 @@
         </is>
       </c>
       <c r="E141" s="23" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="142" ht="20" customHeight="1">
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="E142" s="20" t="n">
-        <v>177</v>
+        <v>154</v>
       </c>
     </row>
     <row r="143" ht="20" customHeight="1">
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="E143" s="23" t="n">
-        <v>193</v>
+        <v>149</v>
       </c>
     </row>
     <row r="144" ht="20" customHeight="1">
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="E144" s="20" t="n">
-        <v>145</v>
+        <v>152</v>
       </c>
     </row>
     <row r="145" ht="20" customHeight="1">
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="E145" s="23" t="n">
-        <v>180</v>
+        <v>204</v>
       </c>
     </row>
     <row r="146" ht="20" customHeight="1">
@@ -4678,7 +4678,7 @@
         </is>
       </c>
       <c r="E146" s="20" t="n">
-        <v>173</v>
+        <v>185</v>
       </c>
     </row>
     <row r="147" ht="20" customHeight="1">
@@ -4703,7 +4703,7 @@
         </is>
       </c>
       <c r="E147" s="23" t="n">
-        <v>184</v>
+        <v>191</v>
       </c>
     </row>
     <row r="148" ht="20" customHeight="1">
@@ -4728,7 +4728,7 @@
         </is>
       </c>
       <c r="E148" s="20" t="n">
-        <v>143</v>
+        <v>200</v>
       </c>
     </row>
     <row r="149" ht="20" customHeight="1">
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c r="E149" s="23" t="n">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="150" ht="20" customHeight="1">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="E150" s="20" t="n">
-        <v>177</v>
+        <v>158</v>
       </c>
     </row>
     <row r="151" ht="20" customHeight="1">
@@ -4803,7 +4803,7 @@
         </is>
       </c>
       <c r="E151" s="23" t="n">
-        <v>118</v>
+        <v>149</v>
       </c>
     </row>
     <row r="152" ht="20" customHeight="1">
@@ -4828,7 +4828,7 @@
         </is>
       </c>
       <c r="E152" s="20" t="n">
-        <v>139</v>
+        <v>198</v>
       </c>
     </row>
     <row r="153" ht="20" customHeight="1">
@@ -4853,7 +4853,7 @@
         </is>
       </c>
       <c r="E153" s="23" t="n">
-        <v>194</v>
+        <v>221</v>
       </c>
     </row>
     <row r="154" ht="20" customHeight="1">
@@ -4878,7 +4878,7 @@
         </is>
       </c>
       <c r="E154" s="20" t="n">
-        <v>144</v>
+        <v>124</v>
       </c>
     </row>
     <row r="155" ht="20" customHeight="1">
@@ -4903,7 +4903,7 @@
         </is>
       </c>
       <c r="E155" s="23" t="n">
-        <v>143</v>
+        <v>214</v>
       </c>
     </row>
     <row r="156" ht="20" customHeight="1">
@@ -4928,7 +4928,7 @@
         </is>
       </c>
       <c r="E156" s="20" t="n">
-        <v>148</v>
+        <v>184</v>
       </c>
     </row>
     <row r="157" ht="20" customHeight="1">
@@ -4953,7 +4953,7 @@
         </is>
       </c>
       <c r="E157" s="23" t="n">
-        <v>124</v>
+        <v>239</v>
       </c>
     </row>
     <row r="158" ht="20" customHeight="1">
@@ -4978,7 +4978,7 @@
         </is>
       </c>
       <c r="E158" s="20" t="n">
-        <v>123</v>
+        <v>211</v>
       </c>
     </row>
     <row r="159" ht="20" customHeight="1">
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="E159" s="23" t="n">
-        <v>177</v>
+        <v>164</v>
       </c>
     </row>
     <row r="160" ht="20" customHeight="1">
@@ -5028,7 +5028,7 @@
         </is>
       </c>
       <c r="E160" s="20" t="n">
-        <v>229</v>
+        <v>214</v>
       </c>
     </row>
     <row r="161" ht="20" customHeight="1">
@@ -5053,7 +5053,7 @@
         </is>
       </c>
       <c r="E161" s="23" t="n">
-        <v>191</v>
+        <v>181</v>
       </c>
     </row>
     <row r="162" ht="20" customHeight="1">
@@ -5078,7 +5078,7 @@
         </is>
       </c>
       <c r="E162" s="20" t="n">
-        <v>164</v>
+        <v>186</v>
       </c>
     </row>
     <row r="163" ht="20" customHeight="1">
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="E163" s="23" t="n">
-        <v>117</v>
+        <v>199</v>
       </c>
     </row>
     <row r="164" ht="20" customHeight="1">
@@ -5128,7 +5128,7 @@
         </is>
       </c>
       <c r="E164" s="20" t="n">
-        <v>171</v>
+        <v>117</v>
       </c>
     </row>
     <row r="165" ht="20" customHeight="1">
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="E165" s="23" t="n">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="166" ht="20" customHeight="1">
@@ -5178,7 +5178,7 @@
         </is>
       </c>
       <c r="E166" s="20" t="n">
-        <v>160</v>
+        <v>141</v>
       </c>
     </row>
     <row r="167" ht="20" customHeight="1">
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="E167" s="23" t="n">
-        <v>152</v>
+        <v>237</v>
       </c>
     </row>
     <row r="168" ht="20" customHeight="1">
@@ -5228,7 +5228,7 @@
         </is>
       </c>
       <c r="E168" s="20" t="n">
-        <v>153</v>
+        <v>167</v>
       </c>
     </row>
     <row r="169" ht="20" customHeight="1">
@@ -5253,7 +5253,7 @@
         </is>
       </c>
       <c r="E169" s="23" t="n">
-        <v>195</v>
+        <v>129</v>
       </c>
     </row>
     <row r="170" ht="20" customHeight="1">
@@ -5278,7 +5278,7 @@
         </is>
       </c>
       <c r="E170" s="20" t="n">
-        <v>134</v>
+        <v>153</v>
       </c>
     </row>
     <row r="171" ht="20" customHeight="1">
@@ -5303,7 +5303,7 @@
         </is>
       </c>
       <c r="E171" s="23" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="172" ht="20" customHeight="1">
@@ -5328,7 +5328,7 @@
         </is>
       </c>
       <c r="E172" s="20" t="n">
-        <v>142</v>
+        <v>167</v>
       </c>
     </row>
     <row r="173" ht="20" customHeight="1">
@@ -5353,7 +5353,7 @@
         </is>
       </c>
       <c r="E173" s="23" t="n">
-        <v>182</v>
+        <v>234</v>
       </c>
     </row>
     <row r="174" ht="20" customHeight="1">
@@ -5378,7 +5378,7 @@
         </is>
       </c>
       <c r="E174" s="20" t="n">
-        <v>136</v>
+        <v>225</v>
       </c>
     </row>
     <row r="175" ht="20" customHeight="1">
@@ -5403,7 +5403,7 @@
         </is>
       </c>
       <c r="E175" s="23" t="n">
-        <v>184</v>
+        <v>218</v>
       </c>
     </row>
     <row r="176" ht="20" customHeight="1">
@@ -5428,7 +5428,7 @@
         </is>
       </c>
       <c r="E176" s="20" t="n">
-        <v>200</v>
+        <v>130</v>
       </c>
     </row>
     <row r="177" ht="20" customHeight="1">
@@ -5453,7 +5453,7 @@
         </is>
       </c>
       <c r="E177" s="23" t="n">
-        <v>119</v>
+        <v>233</v>
       </c>
     </row>
     <row r="178" ht="20" customHeight="1">
@@ -5478,7 +5478,7 @@
         </is>
       </c>
       <c r="E178" s="20" t="n">
-        <v>188</v>
+        <v>203</v>
       </c>
     </row>
     <row r="179" ht="20" customHeight="1">
@@ -5503,7 +5503,7 @@
         </is>
       </c>
       <c r="E179" s="23" t="n">
-        <v>235</v>
+        <v>127</v>
       </c>
     </row>
     <row r="180" ht="20" customHeight="1">
@@ -5528,7 +5528,7 @@
         </is>
       </c>
       <c r="E180" s="20" t="n">
-        <v>177</v>
+        <v>211</v>
       </c>
     </row>
     <row r="181" ht="20" customHeight="1">
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="E181" s="23" t="n">
-        <v>119</v>
+        <v>195</v>
       </c>
     </row>
     <row r="182" ht="20" customHeight="1">
@@ -5578,7 +5578,7 @@
         </is>
       </c>
       <c r="E182" s="20" t="n">
-        <v>143</v>
+        <v>194</v>
       </c>
     </row>
     <row r="183" ht="20" customHeight="1">
@@ -5603,7 +5603,7 @@
         </is>
       </c>
       <c r="E183" s="23" t="n">
-        <v>140</v>
+        <v>207</v>
       </c>
     </row>
     <row r="184" ht="20" customHeight="1">
@@ -5628,7 +5628,7 @@
         </is>
       </c>
       <c r="E184" s="20" t="n">
-        <v>120</v>
+        <v>148</v>
       </c>
     </row>
     <row r="185" ht="20" customHeight="1">
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="E185" s="23" t="n">
-        <v>129</v>
+        <v>158</v>
       </c>
     </row>
     <row r="186" ht="20" customHeight="1">
@@ -5678,7 +5678,7 @@
         </is>
       </c>
       <c r="E186" s="20" t="n">
-        <v>229</v>
+        <v>146</v>
       </c>
     </row>
     <row r="187" ht="20" customHeight="1">
@@ -5703,7 +5703,7 @@
         </is>
       </c>
       <c r="E187" s="23" t="n">
-        <v>131</v>
+        <v>151</v>
       </c>
     </row>
     <row r="188" ht="20" customHeight="1">
@@ -5728,7 +5728,7 @@
         </is>
       </c>
       <c r="E188" s="20" t="n">
-        <v>187</v>
+        <v>236</v>
       </c>
     </row>
     <row r="189" ht="20" customHeight="1">
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="E189" s="23" t="n">
-        <v>130</v>
+        <v>197</v>
       </c>
     </row>
     <row r="190" ht="20" customHeight="1">
@@ -5778,7 +5778,7 @@
         </is>
       </c>
       <c r="E190" s="20" t="n">
-        <v>219</v>
+        <v>117</v>
       </c>
     </row>
     <row r="191" ht="20" customHeight="1">
@@ -5803,7 +5803,7 @@
         </is>
       </c>
       <c r="E191" s="23" t="n">
-        <v>139</v>
+        <v>201</v>
       </c>
     </row>
     <row r="192" ht="20" customHeight="1">
@@ -5828,7 +5828,7 @@
         </is>
       </c>
       <c r="E192" s="20" t="n">
-        <v>122</v>
+        <v>175</v>
       </c>
     </row>
     <row r="193" ht="20" customHeight="1">
@@ -5853,7 +5853,7 @@
         </is>
       </c>
       <c r="E193" s="23" t="n">
-        <v>168</v>
+        <v>236</v>
       </c>
     </row>
     <row r="194" ht="20" customHeight="1">
@@ -5878,7 +5878,7 @@
         </is>
       </c>
       <c r="E194" s="20" t="n">
-        <v>143</v>
+        <v>219</v>
       </c>
     </row>
     <row r="195" ht="20" customHeight="1">
@@ -5903,7 +5903,7 @@
         </is>
       </c>
       <c r="E195" s="23" t="n">
-        <v>179</v>
+        <v>151</v>
       </c>
     </row>
     <row r="196" ht="20" customHeight="1">
@@ -5928,7 +5928,7 @@
         </is>
       </c>
       <c r="E196" s="20" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="197" ht="20" customHeight="1">
@@ -5953,7 +5953,7 @@
         </is>
       </c>
       <c r="E197" s="23" t="n">
-        <v>222</v>
+        <v>171</v>
       </c>
     </row>
     <row r="198" ht="20" customHeight="1">
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="E198" s="20" t="n">
-        <v>145</v>
+        <v>125</v>
       </c>
     </row>
     <row r="199" ht="20" customHeight="1">
@@ -6003,7 +6003,7 @@
         </is>
       </c>
       <c r="E199" s="23" t="n">
-        <v>176</v>
+        <v>228</v>
       </c>
     </row>
     <row r="200" ht="20" customHeight="1">
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="E200" s="20" t="n">
-        <v>118</v>
+        <v>172</v>
       </c>
     </row>
     <row r="201" ht="20" customHeight="1">
@@ -6053,7 +6053,7 @@
         </is>
       </c>
       <c r="E201" s="23" t="n">
-        <v>136</v>
+        <v>150</v>
       </c>
     </row>
     <row r="202" ht="20" customHeight="1">
@@ -6078,7 +6078,7 @@
         </is>
       </c>
       <c r="E202" s="20" t="n">
-        <v>181</v>
+        <v>157</v>
       </c>
     </row>
     <row r="203" ht="20" customHeight="1">
@@ -6103,7 +6103,7 @@
         </is>
       </c>
       <c r="E203" s="23" t="n">
-        <v>128</v>
+        <v>232</v>
       </c>
     </row>
     <row r="204" ht="20" customHeight="1">
@@ -6128,7 +6128,7 @@
         </is>
       </c>
       <c r="E204" s="20" t="n">
-        <v>228</v>
+        <v>117</v>
       </c>
     </row>
     <row r="205" ht="20" customHeight="1">
@@ -6153,7 +6153,7 @@
         </is>
       </c>
       <c r="E205" s="23" t="n">
-        <v>170</v>
+        <v>227</v>
       </c>
     </row>
     <row r="206" ht="20" customHeight="1">
@@ -6178,7 +6178,7 @@
         </is>
       </c>
       <c r="E206" s="20" t="n">
-        <v>175</v>
+        <v>223</v>
       </c>
     </row>
     <row r="207" ht="20" customHeight="1">
@@ -6203,7 +6203,7 @@
         </is>
       </c>
       <c r="E207" s="23" t="n">
-        <v>211</v>
+        <v>183</v>
       </c>
     </row>
     <row r="208" ht="20" customHeight="1">
@@ -6228,7 +6228,7 @@
         </is>
       </c>
       <c r="E208" s="20" t="n">
-        <v>120</v>
+        <v>149</v>
       </c>
     </row>
     <row r="209" ht="20" customHeight="1">
@@ -6253,7 +6253,7 @@
         </is>
       </c>
       <c r="E209" s="23" t="n">
-        <v>194</v>
+        <v>234</v>
       </c>
     </row>
     <row r="210" ht="20" customHeight="1">
@@ -6278,7 +6278,7 @@
         </is>
       </c>
       <c r="E210" s="20" t="n">
-        <v>234</v>
+        <v>157</v>
       </c>
     </row>
     <row r="211" ht="20" customHeight="1">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="E211" s="23" t="n">
-        <v>203</v>
+        <v>210</v>
       </c>
     </row>
     <row r="212" ht="20" customHeight="1">
@@ -6328,7 +6328,7 @@
         </is>
       </c>
       <c r="E212" s="20" t="n">
-        <v>186</v>
+        <v>119</v>
       </c>
     </row>
     <row r="213" ht="20" customHeight="1">
@@ -6353,7 +6353,7 @@
         </is>
       </c>
       <c r="E213" s="23" t="n">
-        <v>173</v>
+        <v>134</v>
       </c>
     </row>
     <row r="214" ht="20" customHeight="1">
@@ -6378,7 +6378,7 @@
         </is>
       </c>
       <c r="E214" s="20" t="n">
-        <v>170</v>
+        <v>144</v>
       </c>
     </row>
     <row r="215" ht="20" customHeight="1">
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="E215" s="23" t="n">
-        <v>131</v>
+        <v>152</v>
       </c>
     </row>
     <row r="216" ht="20" customHeight="1">
@@ -6428,7 +6428,7 @@
         </is>
       </c>
       <c r="E216" s="20" t="n">
-        <v>130</v>
+        <v>232</v>
       </c>
     </row>
     <row r="217" ht="20" customHeight="1">
@@ -6453,7 +6453,7 @@
         </is>
       </c>
       <c r="E217" s="23" t="n">
-        <v>212</v>
+        <v>217</v>
       </c>
     </row>
     <row r="218" ht="20" customHeight="1">
@@ -6478,7 +6478,7 @@
         </is>
       </c>
       <c r="E218" s="20" t="n">
-        <v>146</v>
+        <v>125</v>
       </c>
     </row>
     <row r="219" ht="20" customHeight="1">
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="E219" s="23" t="n">
-        <v>201</v>
+        <v>212</v>
       </c>
     </row>
     <row r="220" ht="20" customHeight="1">
@@ -6528,7 +6528,7 @@
         </is>
       </c>
       <c r="E220" s="20" t="n">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="221" ht="20" customHeight="1">
@@ -6553,7 +6553,7 @@
         </is>
       </c>
       <c r="E221" s="23" t="n">
-        <v>214</v>
+        <v>236</v>
       </c>
     </row>
     <row r="222" ht="20" customHeight="1">
@@ -6578,7 +6578,7 @@
         </is>
       </c>
       <c r="E222" s="20" t="n">
-        <v>142</v>
+        <v>153</v>
       </c>
     </row>
     <row r="223" ht="20" customHeight="1">
@@ -6603,7 +6603,7 @@
         </is>
       </c>
       <c r="E223" s="23" t="n">
-        <v>235</v>
+        <v>214</v>
       </c>
     </row>
     <row r="224" ht="20" customHeight="1">
@@ -6628,7 +6628,7 @@
         </is>
       </c>
       <c r="E224" s="20" t="n">
-        <v>231</v>
+        <v>136</v>
       </c>
     </row>
     <row r="225" ht="20" customHeight="1">
@@ -6653,7 +6653,7 @@
         </is>
       </c>
       <c r="E225" s="23" t="n">
-        <v>133</v>
+        <v>177</v>
       </c>
     </row>
     <row r="226" ht="20" customHeight="1">
@@ -6678,7 +6678,7 @@
         </is>
       </c>
       <c r="E226" s="20" t="n">
-        <v>159</v>
+        <v>134</v>
       </c>
     </row>
     <row r="227" ht="20" customHeight="1">
@@ -6703,7 +6703,7 @@
         </is>
       </c>
       <c r="E227" s="23" t="n">
-        <v>228</v>
+        <v>186</v>
       </c>
     </row>
     <row r="228" ht="20" customHeight="1">
@@ -6728,7 +6728,7 @@
         </is>
       </c>
       <c r="E228" s="20" t="n">
-        <v>213</v>
+        <v>174</v>
       </c>
     </row>
     <row r="229" ht="20" customHeight="1">
@@ -6753,7 +6753,7 @@
         </is>
       </c>
       <c r="E229" s="23" t="n">
-        <v>234</v>
+        <v>120</v>
       </c>
     </row>
     <row r="230" ht="20" customHeight="1">
@@ -6803,7 +6803,7 @@
         </is>
       </c>
       <c r="E231" s="23" t="n">
-        <v>197</v>
+        <v>127</v>
       </c>
     </row>
     <row r="232" ht="20" customHeight="1">
@@ -6828,7 +6828,7 @@
         </is>
       </c>
       <c r="E232" s="20" t="n">
-        <v>150</v>
+        <v>112</v>
       </c>
     </row>
     <row r="233" ht="20" customHeight="1">
@@ -6853,7 +6853,7 @@
         </is>
       </c>
       <c r="E233" s="23" t="n">
-        <v>111</v>
+        <v>160</v>
       </c>
     </row>
     <row r="234" ht="20" customHeight="1">
@@ -6878,7 +6878,7 @@
         </is>
       </c>
       <c r="E234" s="20" t="n">
-        <v>164</v>
+        <v>198</v>
       </c>
     </row>
     <row r="235" ht="20" customHeight="1">
@@ -6903,7 +6903,7 @@
         </is>
       </c>
       <c r="E235" s="23" t="n">
-        <v>230</v>
+        <v>166</v>
       </c>
     </row>
     <row r="236" ht="20" customHeight="1">
@@ -6928,7 +6928,7 @@
         </is>
       </c>
       <c r="E236" s="20" t="n">
-        <v>151</v>
+        <v>169</v>
       </c>
     </row>
     <row r="237" ht="20" customHeight="1">
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="E237" s="23" t="n">
-        <v>224</v>
+        <v>153</v>
       </c>
     </row>
     <row r="238" ht="20" customHeight="1">
@@ -6978,7 +6978,7 @@
         </is>
       </c>
       <c r="E238" s="20" t="n">
-        <v>215</v>
+        <v>135</v>
       </c>
     </row>
     <row r="239" ht="20" customHeight="1">
@@ -7003,7 +7003,7 @@
         </is>
       </c>
       <c r="E239" s="23" t="n">
-        <v>154</v>
+        <v>239</v>
       </c>
     </row>
     <row r="240" ht="20" customHeight="1">
@@ -7028,7 +7028,7 @@
         </is>
       </c>
       <c r="E240" s="20" t="n">
-        <v>145</v>
+        <v>161</v>
       </c>
     </row>
     <row r="241" ht="20" customHeight="1">
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="E241" s="23" t="n">
-        <v>146</v>
+        <v>122</v>
       </c>
     </row>
     <row r="242" ht="20" customHeight="1">
@@ -7078,7 +7078,7 @@
         </is>
       </c>
       <c r="E242" s="20" t="n">
-        <v>131</v>
+        <v>114</v>
       </c>
     </row>
     <row r="243" ht="20" customHeight="1">
@@ -7103,7 +7103,7 @@
         </is>
       </c>
       <c r="E243" s="23" t="n">
-        <v>199</v>
+        <v>171</v>
       </c>
     </row>
     <row r="244" ht="20" customHeight="1">
@@ -7128,7 +7128,7 @@
         </is>
       </c>
       <c r="E244" s="20" t="n">
-        <v>225</v>
+        <v>127</v>
       </c>
     </row>
     <row r="245" ht="20" customHeight="1">
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="E245" s="23" t="n">
-        <v>180</v>
+        <v>230</v>
       </c>
     </row>
     <row r="246" ht="20" customHeight="1">
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="E246" s="20" t="n">
-        <v>160</v>
+        <v>145</v>
       </c>
     </row>
     <row r="247" ht="20" customHeight="1">
@@ -7203,7 +7203,7 @@
         </is>
       </c>
       <c r="E247" s="23" t="n">
-        <v>165</v>
+        <v>233</v>
       </c>
     </row>
     <row r="248" ht="20" customHeight="1">
@@ -7228,7 +7228,7 @@
         </is>
       </c>
       <c r="E248" s="20" t="n">
-        <v>203</v>
+        <v>169</v>
       </c>
     </row>
     <row r="249" ht="20" customHeight="1">
@@ -7253,7 +7253,7 @@
         </is>
       </c>
       <c r="E249" s="23" t="n">
-        <v>175</v>
+        <v>147</v>
       </c>
     </row>
     <row r="250" ht="20" customHeight="1">
@@ -7278,7 +7278,7 @@
         </is>
       </c>
       <c r="E250" s="20" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="251" ht="20" customHeight="1">
@@ -7303,7 +7303,7 @@
         </is>
       </c>
       <c r="E251" s="23" t="n">
-        <v>139</v>
+        <v>128</v>
       </c>
     </row>
     <row r="252" ht="20" customHeight="1">
@@ -7328,7 +7328,7 @@
         </is>
       </c>
       <c r="E252" s="20" t="n">
-        <v>237</v>
+        <v>191</v>
       </c>
     </row>
     <row r="253" ht="20" customHeight="1">
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="E253" s="23" t="n">
-        <v>173</v>
+        <v>229</v>
       </c>
     </row>
     <row r="254" ht="20" customHeight="1">
@@ -7378,7 +7378,7 @@
         </is>
       </c>
       <c r="E254" s="20" t="n">
-        <v>129</v>
+        <v>230</v>
       </c>
     </row>
     <row r="255" ht="20" customHeight="1">
@@ -7403,7 +7403,7 @@
         </is>
       </c>
       <c r="E255" s="23" t="n">
-        <v>159</v>
+        <v>128</v>
       </c>
     </row>
     <row r="256" ht="20" customHeight="1">
@@ -7428,7 +7428,7 @@
         </is>
       </c>
       <c r="E256" s="20" t="n">
-        <v>212</v>
+        <v>138</v>
       </c>
     </row>
     <row r="257" ht="20" customHeight="1">
@@ -7453,7 +7453,7 @@
         </is>
       </c>
       <c r="E257" s="23" t="n">
-        <v>151</v>
+        <v>158</v>
       </c>
     </row>
     <row r="258" ht="20" customHeight="1">
@@ -7478,7 +7478,7 @@
         </is>
       </c>
       <c r="E258" s="20" t="n">
-        <v>198</v>
+        <v>111</v>
       </c>
     </row>
     <row r="259" ht="20" customHeight="1">
@@ -7503,7 +7503,7 @@
         </is>
       </c>
       <c r="E259" s="23" t="n">
-        <v>227</v>
+        <v>137</v>
       </c>
     </row>
     <row r="260" ht="20" customHeight="1">
@@ -7528,7 +7528,7 @@
         </is>
       </c>
       <c r="E260" s="20" t="n">
-        <v>209</v>
+        <v>126</v>
       </c>
     </row>
     <row r="261" ht="20" customHeight="1">
@@ -7553,7 +7553,7 @@
         </is>
       </c>
       <c r="E261" s="23" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="262" ht="20" customHeight="1">
@@ -7578,7 +7578,7 @@
         </is>
       </c>
       <c r="E262" s="20" t="n">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="263" ht="20" customHeight="1">
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="E263" s="23" t="n">
-        <v>226</v>
+        <v>143</v>
       </c>
     </row>
     <row r="264" ht="20" customHeight="1">
@@ -7628,7 +7628,7 @@
         </is>
       </c>
       <c r="E264" s="20" t="n">
-        <v>174</v>
+        <v>186</v>
       </c>
     </row>
     <row r="265" ht="20" customHeight="1">
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="E265" s="23" t="n">
-        <v>158</v>
+        <v>221</v>
       </c>
     </row>
     <row r="266" ht="20" customHeight="1">
@@ -7678,7 +7678,7 @@
         </is>
       </c>
       <c r="E266" s="20" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="267" ht="20" customHeight="1">
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="E267" s="23" t="n">
-        <v>114</v>
+        <v>239</v>
       </c>
     </row>
     <row r="268" ht="20" customHeight="1">
@@ -7728,7 +7728,7 @@
         </is>
       </c>
       <c r="E268" s="20" t="n">
-        <v>128</v>
+        <v>139</v>
       </c>
     </row>
     <row r="269" ht="20" customHeight="1">
@@ -7753,7 +7753,7 @@
         </is>
       </c>
       <c r="E269" s="23" t="n">
-        <v>235</v>
+        <v>142</v>
       </c>
     </row>
     <row r="270" ht="20" customHeight="1">
@@ -7778,7 +7778,7 @@
         </is>
       </c>
       <c r="E270" s="20" t="n">
-        <v>224</v>
+        <v>139</v>
       </c>
     </row>
     <row r="271" ht="20" customHeight="1">
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="E271" s="23" t="n">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="272" ht="20" customHeight="1">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="E272" s="20" t="n">
-        <v>215</v>
+        <v>200</v>
       </c>
     </row>
     <row r="273" ht="20" customHeight="1">
@@ -7853,7 +7853,7 @@
         </is>
       </c>
       <c r="E273" s="23" t="n">
-        <v>212</v>
+        <v>159</v>
       </c>
     </row>
     <row r="274" ht="20" customHeight="1">
@@ -7878,7 +7878,7 @@
         </is>
       </c>
       <c r="E274" s="20" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="275" ht="20" customHeight="1">
@@ -7903,7 +7903,7 @@
         </is>
       </c>
       <c r="E275" s="23" t="n">
-        <v>154</v>
+        <v>222</v>
       </c>
     </row>
     <row r="276" ht="20" customHeight="1">
@@ -7928,7 +7928,7 @@
         </is>
       </c>
       <c r="E276" s="20" t="n">
-        <v>118</v>
+        <v>173</v>
       </c>
     </row>
     <row r="277" ht="20" customHeight="1">
@@ -7953,7 +7953,7 @@
         </is>
       </c>
       <c r="E277" s="23" t="n">
-        <v>200</v>
+        <v>163</v>
       </c>
     </row>
     <row r="278" ht="20" customHeight="1">
@@ -7978,7 +7978,7 @@
         </is>
       </c>
       <c r="E278" s="20" t="n">
-        <v>182</v>
+        <v>194</v>
       </c>
     </row>
     <row r="279" ht="20" customHeight="1">
@@ -8003,7 +8003,7 @@
         </is>
       </c>
       <c r="E279" s="23" t="n">
-        <v>136</v>
+        <v>230</v>
       </c>
     </row>
     <row r="280" ht="20" customHeight="1">
@@ -8028,7 +8028,7 @@
         </is>
       </c>
       <c r="E280" s="20" t="n">
-        <v>130</v>
+        <v>138</v>
       </c>
     </row>
     <row r="281" ht="20" customHeight="1">
@@ -8053,7 +8053,7 @@
         </is>
       </c>
       <c r="E281" s="23" t="n">
-        <v>183</v>
+        <v>200</v>
       </c>
     </row>
     <row r="282" ht="20" customHeight="1">
@@ -8078,7 +8078,7 @@
         </is>
       </c>
       <c r="E282" s="20" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="283" ht="20" customHeight="1">
@@ -8103,7 +8103,7 @@
         </is>
       </c>
       <c r="E283" s="23" t="n">
-        <v>224</v>
+        <v>144</v>
       </c>
     </row>
     <row r="284" ht="20" customHeight="1">
@@ -8128,7 +8128,7 @@
         </is>
       </c>
       <c r="E284" s="20" t="n">
-        <v>179</v>
+        <v>162</v>
       </c>
     </row>
     <row r="285" ht="20" customHeight="1">
@@ -8153,7 +8153,7 @@
         </is>
       </c>
       <c r="E285" s="23" t="n">
-        <v>239</v>
+        <v>144</v>
       </c>
     </row>
     <row r="286" ht="20" customHeight="1">
@@ -8178,7 +8178,7 @@
         </is>
       </c>
       <c r="E286" s="20" t="n">
-        <v>128</v>
+        <v>204</v>
       </c>
     </row>
     <row r="287" ht="20" customHeight="1">
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="E287" s="23" t="n">
-        <v>239</v>
+        <v>191</v>
       </c>
     </row>
     <row r="288" ht="20" customHeight="1">
@@ -8228,7 +8228,7 @@
         </is>
       </c>
       <c r="E288" s="20" t="n">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="289" ht="20" customHeight="1">
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="E289" s="23" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="290" ht="20" customHeight="1">
@@ -8278,7 +8278,7 @@
         </is>
       </c>
       <c r="E290" s="20" t="n">
-        <v>113</v>
+        <v>162</v>
       </c>
     </row>
     <row r="291" ht="20" customHeight="1">
@@ -8303,7 +8303,7 @@
         </is>
       </c>
       <c r="E291" s="23" t="n">
-        <v>156</v>
+        <v>189</v>
       </c>
     </row>
     <row r="292" ht="20" customHeight="1">
@@ -8328,7 +8328,7 @@
         </is>
       </c>
       <c r="E292" s="20" t="n">
-        <v>111</v>
+        <v>231</v>
       </c>
     </row>
     <row r="293" ht="20" customHeight="1">
@@ -8353,7 +8353,7 @@
         </is>
       </c>
       <c r="E293" s="23" t="n">
-        <v>136</v>
+        <v>152</v>
       </c>
     </row>
     <row r="294" ht="20" customHeight="1">
@@ -8378,7 +8378,7 @@
         </is>
       </c>
       <c r="E294" s="20" t="n">
-        <v>216</v>
+        <v>157</v>
       </c>
     </row>
     <row r="295" ht="20" customHeight="1">
@@ -8403,7 +8403,7 @@
         </is>
       </c>
       <c r="E295" s="23" t="n">
-        <v>127</v>
+        <v>212</v>
       </c>
     </row>
     <row r="296" ht="20" customHeight="1">
@@ -8428,7 +8428,7 @@
         </is>
       </c>
       <c r="E296" s="20" t="n">
-        <v>229</v>
+        <v>177</v>
       </c>
     </row>
     <row r="297" ht="20" customHeight="1">
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="E297" s="23" t="n">
-        <v>160</v>
+        <v>227</v>
       </c>
     </row>
     <row r="298" ht="20" customHeight="1">
@@ -8478,7 +8478,7 @@
         </is>
       </c>
       <c r="E298" s="20" t="n">
-        <v>138</v>
+        <v>115</v>
       </c>
     </row>
     <row r="299" ht="20" customHeight="1">
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="E299" s="23" t="n">
-        <v>121</v>
+        <v>190</v>
       </c>
     </row>
     <row r="300" ht="20" customHeight="1">
@@ -8528,7 +8528,7 @@
         </is>
       </c>
       <c r="E300" s="20" t="n">
-        <v>201</v>
+        <v>166</v>
       </c>
     </row>
     <row r="301" ht="20" customHeight="1">
@@ -8553,7 +8553,7 @@
         </is>
       </c>
       <c r="E301" s="23" t="n">
-        <v>236</v>
+        <v>209</v>
       </c>
     </row>
     <row r="302" ht="20" customHeight="1">
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="E302" s="20" t="n">
-        <v>212</v>
+        <v>136</v>
       </c>
     </row>
     <row r="303" ht="20" customHeight="1">
@@ -8603,7 +8603,7 @@
         </is>
       </c>
       <c r="E303" s="23" t="n">
-        <v>127</v>
+        <v>216</v>
       </c>
     </row>
     <row r="304" ht="20" customHeight="1">
@@ -8628,7 +8628,7 @@
         </is>
       </c>
       <c r="E304" s="20" t="n">
-        <v>117</v>
+        <v>133</v>
       </c>
     </row>
     <row r="305" ht="20" customHeight="1">
@@ -8653,7 +8653,7 @@
         </is>
       </c>
       <c r="E305" s="23" t="n">
-        <v>231</v>
+        <v>176</v>
       </c>
     </row>
     <row r="306" ht="20" customHeight="1">
@@ -8678,7 +8678,7 @@
         </is>
       </c>
       <c r="E306" s="20" t="n">
-        <v>223</v>
+        <v>118</v>
       </c>
     </row>
     <row r="307" ht="20" customHeight="1">
@@ -8703,7 +8703,7 @@
         </is>
       </c>
       <c r="E307" s="23" t="n">
-        <v>113</v>
+        <v>156</v>
       </c>
     </row>
     <row r="308" ht="20" customHeight="1">
@@ -8728,7 +8728,7 @@
         </is>
       </c>
       <c r="E308" s="20" t="n">
-        <v>229</v>
+        <v>235</v>
       </c>
     </row>
     <row r="309" ht="20" customHeight="1">
@@ -8753,7 +8753,7 @@
         </is>
       </c>
       <c r="E309" s="23" t="n">
-        <v>178</v>
+        <v>127</v>
       </c>
     </row>
     <row r="310" ht="20" customHeight="1">
@@ -8778,7 +8778,7 @@
         </is>
       </c>
       <c r="E310" s="20" t="n">
-        <v>138</v>
+        <v>174</v>
       </c>
     </row>
     <row r="311" ht="20" customHeight="1">
@@ -8803,7 +8803,7 @@
         </is>
       </c>
       <c r="E311" s="23" t="n">
-        <v>117</v>
+        <v>168</v>
       </c>
     </row>
     <row r="312" ht="20" customHeight="1">
@@ -8828,7 +8828,7 @@
         </is>
       </c>
       <c r="E312" s="20" t="n">
-        <v>126</v>
+        <v>154</v>
       </c>
     </row>
     <row r="313" ht="20" customHeight="1">
@@ -8853,7 +8853,7 @@
         </is>
       </c>
       <c r="E313" s="23" t="n">
-        <v>167</v>
+        <v>115</v>
       </c>
     </row>
     <row r="314" ht="20" customHeight="1">
@@ -8878,7 +8878,7 @@
         </is>
       </c>
       <c r="E314" s="20" t="n">
-        <v>182</v>
+        <v>135</v>
       </c>
     </row>
     <row r="315" ht="20" customHeight="1">
@@ -8903,7 +8903,7 @@
         </is>
       </c>
       <c r="E315" s="23" t="n">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="316" ht="20" customHeight="1">
@@ -8928,7 +8928,7 @@
         </is>
       </c>
       <c r="E316" s="20" t="n">
-        <v>166</v>
+        <v>238</v>
       </c>
     </row>
     <row r="317" ht="20" customHeight="1">
@@ -8953,7 +8953,7 @@
         </is>
       </c>
       <c r="E317" s="23" t="n">
-        <v>189</v>
+        <v>154</v>
       </c>
     </row>
     <row r="318" ht="20" customHeight="1">
@@ -8978,7 +8978,7 @@
         </is>
       </c>
       <c r="E318" s="20" t="n">
-        <v>134</v>
+        <v>176</v>
       </c>
     </row>
     <row r="319" ht="20" customHeight="1">
@@ -9003,7 +9003,7 @@
         </is>
       </c>
       <c r="E319" s="23" t="n">
-        <v>238</v>
+        <v>231</v>
       </c>
     </row>
     <row r="320" ht="20" customHeight="1">
@@ -9028,7 +9028,7 @@
         </is>
       </c>
       <c r="E320" s="20" t="n">
-        <v>177</v>
+        <v>129</v>
       </c>
     </row>
     <row r="321" ht="20" customHeight="1">
@@ -9053,7 +9053,7 @@
         </is>
       </c>
       <c r="E321" s="23" t="n">
-        <v>232</v>
+        <v>182</v>
       </c>
     </row>
     <row r="322" ht="20" customHeight="1">
@@ -9078,7 +9078,7 @@
         </is>
       </c>
       <c r="E322" s="20" t="n">
-        <v>185</v>
+        <v>163</v>
       </c>
     </row>
     <row r="323" ht="20" customHeight="1">
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="E323" s="23" t="n">
-        <v>171</v>
+        <v>114</v>
       </c>
     </row>
     <row r="324" ht="20" customHeight="1">
@@ -9128,7 +9128,7 @@
         </is>
       </c>
       <c r="E324" s="20" t="n">
-        <v>110</v>
+        <v>125</v>
       </c>
     </row>
     <row r="325" ht="20" customHeight="1">
@@ -9153,7 +9153,7 @@
         </is>
       </c>
       <c r="E325" s="23" t="n">
-        <v>184</v>
+        <v>159</v>
       </c>
     </row>
     <row r="326" ht="20" customHeight="1">
@@ -9178,7 +9178,7 @@
         </is>
       </c>
       <c r="E326" s="20" t="n">
-        <v>157</v>
+        <v>152</v>
       </c>
     </row>
     <row r="327" ht="20" customHeight="1">
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="E327" s="23" t="n">
-        <v>149</v>
+        <v>111</v>
       </c>
     </row>
     <row r="328" ht="20" customHeight="1">
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="E328" s="20" t="n">
-        <v>151</v>
+        <v>220</v>
       </c>
     </row>
     <row r="329" ht="20" customHeight="1">
@@ -9253,7 +9253,7 @@
         </is>
       </c>
       <c r="E329" s="23" t="n">
-        <v>181</v>
+        <v>166</v>
       </c>
     </row>
     <row r="330" ht="20" customHeight="1">
@@ -9278,7 +9278,7 @@
         </is>
       </c>
       <c r="E330" s="20" t="n">
-        <v>211</v>
+        <v>111</v>
       </c>
     </row>
     <row r="331" ht="20" customHeight="1">
@@ -9303,7 +9303,7 @@
         </is>
       </c>
       <c r="E331" s="23" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
     </row>
     <row r="332" ht="20" customHeight="1">
@@ -9328,7 +9328,7 @@
         </is>
       </c>
       <c r="E332" s="20" t="n">
-        <v>212</v>
+        <v>176</v>
       </c>
     </row>
     <row r="333" ht="20" customHeight="1">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="E333" s="23" t="n">
-        <v>205</v>
+        <v>210</v>
       </c>
     </row>
     <row r="334" ht="20" customHeight="1">
@@ -9378,7 +9378,7 @@
         </is>
       </c>
       <c r="E334" s="20" t="n">
-        <v>148</v>
+        <v>176</v>
       </c>
     </row>
     <row r="335" ht="20" customHeight="1">
@@ -9403,7 +9403,7 @@
         </is>
       </c>
       <c r="E335" s="23" t="n">
-        <v>179</v>
+        <v>231</v>
       </c>
     </row>
     <row r="336" ht="20" customHeight="1">
@@ -9428,7 +9428,7 @@
         </is>
       </c>
       <c r="E336" s="20" t="n">
-        <v>136</v>
+        <v>232</v>
       </c>
     </row>
     <row r="337" ht="20" customHeight="1">
@@ -9453,7 +9453,7 @@
         </is>
       </c>
       <c r="E337" s="23" t="n">
-        <v>213</v>
+        <v>239</v>
       </c>
     </row>
     <row r="338" ht="20" customHeight="1">
@@ -9478,7 +9478,7 @@
         </is>
       </c>
       <c r="E338" s="20" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="339" ht="20" customHeight="1">
@@ -9503,7 +9503,7 @@
         </is>
       </c>
       <c r="E339" s="23" t="n">
-        <v>226</v>
+        <v>220</v>
       </c>
     </row>
     <row r="340" ht="20" customHeight="1">
@@ -9528,7 +9528,7 @@
         </is>
       </c>
       <c r="E340" s="20" t="n">
-        <v>116</v>
+        <v>148</v>
       </c>
     </row>
     <row r="341" ht="20" customHeight="1">
@@ -9553,7 +9553,7 @@
         </is>
       </c>
       <c r="E341" s="23" t="n">
-        <v>163</v>
+        <v>234</v>
       </c>
     </row>
     <row r="342" ht="20" customHeight="1">
@@ -9578,7 +9578,7 @@
         </is>
       </c>
       <c r="E342" s="20" t="n">
-        <v>193</v>
+        <v>197</v>
       </c>
     </row>
     <row r="343" ht="20" customHeight="1">
@@ -9603,7 +9603,7 @@
         </is>
       </c>
       <c r="E343" s="23" t="n">
-        <v>192</v>
+        <v>122</v>
       </c>
     </row>
     <row r="344" ht="20" customHeight="1">
@@ -9628,7 +9628,7 @@
         </is>
       </c>
       <c r="E344" s="20" t="n">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="345" ht="20" customHeight="1">
@@ -9653,7 +9653,7 @@
         </is>
       </c>
       <c r="E345" s="23" t="n">
-        <v>143</v>
+        <v>112</v>
       </c>
     </row>
     <row r="346" ht="20" customHeight="1">
@@ -9678,7 +9678,7 @@
         </is>
       </c>
       <c r="E346" s="20" t="n">
-        <v>130</v>
+        <v>215</v>
       </c>
     </row>
     <row r="347" ht="20" customHeight="1">
@@ -9703,7 +9703,7 @@
         </is>
       </c>
       <c r="E347" s="23" t="n">
-        <v>230</v>
+        <v>114</v>
       </c>
     </row>
     <row r="348" ht="20" customHeight="1">
@@ -9728,7 +9728,7 @@
         </is>
       </c>
       <c r="E348" s="20" t="n">
-        <v>146</v>
+        <v>137</v>
       </c>
     </row>
     <row r="349" ht="20" customHeight="1">
@@ -9753,7 +9753,7 @@
         </is>
       </c>
       <c r="E349" s="23" t="n">
-        <v>174</v>
+        <v>154</v>
       </c>
     </row>
     <row r="350" ht="20" customHeight="1">
@@ -9778,7 +9778,7 @@
         </is>
       </c>
       <c r="E350" s="20" t="n">
-        <v>116</v>
+        <v>131</v>
       </c>
     </row>
     <row r="351" ht="20" customHeight="1">
@@ -9803,7 +9803,7 @@
         </is>
       </c>
       <c r="E351" s="23" t="n">
-        <v>202</v>
+        <v>159</v>
       </c>
     </row>
     <row r="352" ht="20" customHeight="1">
@@ -9828,7 +9828,7 @@
         </is>
       </c>
       <c r="E352" s="20" t="n">
-        <v>149</v>
+        <v>211</v>
       </c>
     </row>
     <row r="353" ht="20" customHeight="1">
@@ -9853,7 +9853,7 @@
         </is>
       </c>
       <c r="E353" s="23" t="n">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="354" ht="20" customHeight="1">
@@ -9878,7 +9878,7 @@
         </is>
       </c>
       <c r="E354" s="20" t="n">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="355" ht="20" customHeight="1">
@@ -9903,7 +9903,7 @@
         </is>
       </c>
       <c r="E355" s="23" t="n">
-        <v>152</v>
+        <v>176</v>
       </c>
     </row>
     <row r="356" ht="20" customHeight="1">
@@ -9928,7 +9928,7 @@
         </is>
       </c>
       <c r="E356" s="20" t="n">
-        <v>128</v>
+        <v>176</v>
       </c>
     </row>
     <row r="357" ht="20" customHeight="1">
@@ -9953,7 +9953,7 @@
         </is>
       </c>
       <c r="E357" s="23" t="n">
-        <v>119</v>
+        <v>233</v>
       </c>
     </row>
     <row r="358" ht="20" customHeight="1">
@@ -9978,7 +9978,7 @@
         </is>
       </c>
       <c r="E358" s="20" t="n">
-        <v>155</v>
+        <v>134</v>
       </c>
     </row>
     <row r="359" ht="20" customHeight="1">
@@ -10003,7 +10003,7 @@
         </is>
       </c>
       <c r="E359" s="23" t="n">
-        <v>165</v>
+        <v>228</v>
       </c>
     </row>
     <row r="360" ht="20" customHeight="1">
@@ -10028,7 +10028,7 @@
         </is>
       </c>
       <c r="E360" s="20" t="n">
-        <v>175</v>
+        <v>143</v>
       </c>
     </row>
     <row r="361" ht="20" customHeight="1">
@@ -10053,7 +10053,7 @@
         </is>
       </c>
       <c r="E361" s="23" t="n">
-        <v>138</v>
+        <v>157</v>
       </c>
     </row>
     <row r="362" ht="20" customHeight="1">
@@ -10078,7 +10078,7 @@
         </is>
       </c>
       <c r="E362" s="20" t="n">
-        <v>196</v>
+        <v>222</v>
       </c>
     </row>
     <row r="363" ht="20" customHeight="1">
@@ -10103,7 +10103,7 @@
         </is>
       </c>
       <c r="E363" s="23" t="n">
-        <v>136</v>
+        <v>179</v>
       </c>
     </row>
     <row r="364" ht="20" customHeight="1">
@@ -10128,7 +10128,7 @@
         </is>
       </c>
       <c r="E364" s="20" t="n">
-        <v>206</v>
+        <v>129</v>
       </c>
     </row>
     <row r="365" ht="20" customHeight="1">
@@ -10153,7 +10153,7 @@
         </is>
       </c>
       <c r="E365" s="23" t="n">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="366" ht="20" customHeight="1">
@@ -10178,7 +10178,7 @@
         </is>
       </c>
       <c r="E366" s="20" t="n">
-        <v>223</v>
+        <v>114</v>
       </c>
     </row>
     <row r="367" ht="20" customHeight="1">
@@ -10203,7 +10203,7 @@
         </is>
       </c>
       <c r="E367" s="23" t="n">
-        <v>125</v>
+        <v>160</v>
       </c>
     </row>
     <row r="368" ht="20" customHeight="1">
@@ -10228,7 +10228,7 @@
         </is>
       </c>
       <c r="E368" s="20" t="n">
-        <v>231</v>
+        <v>163</v>
       </c>
     </row>
     <row r="369" ht="20" customHeight="1">
@@ -10253,7 +10253,7 @@
         </is>
       </c>
       <c r="E369" s="23" t="n">
-        <v>145</v>
+        <v>202</v>
       </c>
     </row>
     <row r="370" ht="20" customHeight="1">
@@ -10278,7 +10278,7 @@
         </is>
       </c>
       <c r="E370" s="20" t="n">
-        <v>129</v>
+        <v>136</v>
       </c>
     </row>
     <row r="371" ht="20" customHeight="1">
@@ -10303,7 +10303,7 @@
         </is>
       </c>
       <c r="E371" s="23" t="n">
-        <v>125</v>
+        <v>157</v>
       </c>
     </row>
     <row r="372" ht="20" customHeight="1">
@@ -10328,7 +10328,7 @@
         </is>
       </c>
       <c r="E372" s="20" t="n">
-        <v>110</v>
+        <v>168</v>
       </c>
     </row>
     <row r="373" ht="20" customHeight="1">
@@ -10353,7 +10353,7 @@
         </is>
       </c>
       <c r="E373" s="23" t="n">
-        <v>219</v>
+        <v>240</v>
       </c>
     </row>
     <row r="374" ht="20" customHeight="1">
@@ -10378,7 +10378,7 @@
         </is>
       </c>
       <c r="E374" s="20" t="n">
-        <v>121</v>
+        <v>135</v>
       </c>
     </row>
     <row r="375" ht="20" customHeight="1">
@@ -10403,7 +10403,7 @@
         </is>
       </c>
       <c r="E375" s="23" t="n">
-        <v>205</v>
+        <v>148</v>
       </c>
     </row>
     <row r="376" ht="20" customHeight="1">
@@ -10428,7 +10428,7 @@
         </is>
       </c>
       <c r="E376" s="20" t="n">
-        <v>207</v>
+        <v>223</v>
       </c>
     </row>
     <row r="377" ht="20" customHeight="1">
@@ -10453,7 +10453,7 @@
         </is>
       </c>
       <c r="E377" s="23" t="n">
-        <v>190</v>
+        <v>124</v>
       </c>
     </row>
     <row r="378" ht="20" customHeight="1">
@@ -10478,7 +10478,7 @@
         </is>
       </c>
       <c r="E378" s="20" t="n">
-        <v>172</v>
+        <v>194</v>
       </c>
     </row>
     <row r="379" ht="20" customHeight="1">
@@ -10503,7 +10503,7 @@
         </is>
       </c>
       <c r="E379" s="23" t="n">
-        <v>193</v>
+        <v>157</v>
       </c>
     </row>
     <row r="380" ht="20" customHeight="1">
@@ -10528,7 +10528,7 @@
         </is>
       </c>
       <c r="E380" s="20" t="n">
-        <v>231</v>
+        <v>216</v>
       </c>
     </row>
     <row r="381" ht="20" customHeight="1">
@@ -10553,7 +10553,7 @@
         </is>
       </c>
       <c r="E381" s="23" t="n">
-        <v>140</v>
+        <v>206</v>
       </c>
     </row>
     <row r="382" ht="20" customHeight="1">
@@ -10578,7 +10578,7 @@
         </is>
       </c>
       <c r="E382" s="20" t="n">
-        <v>202</v>
+        <v>176</v>
       </c>
     </row>
     <row r="383" ht="20" customHeight="1">
@@ -10603,7 +10603,7 @@
         </is>
       </c>
       <c r="E383" s="23" t="n">
-        <v>141</v>
+        <v>174</v>
       </c>
     </row>
     <row r="384" ht="20" customHeight="1">
@@ -10628,7 +10628,7 @@
         </is>
       </c>
       <c r="E384" s="20" t="n">
-        <v>209</v>
+        <v>239</v>
       </c>
     </row>
     <row r="385" ht="20" customHeight="1">
@@ -10653,7 +10653,7 @@
         </is>
       </c>
       <c r="E385" s="23" t="n">
-        <v>195</v>
+        <v>211</v>
       </c>
     </row>
     <row r="386" ht="20" customHeight="1">
@@ -10678,7 +10678,7 @@
         </is>
       </c>
       <c r="E386" s="20" t="n">
-        <v>178</v>
+        <v>206</v>
       </c>
     </row>
     <row r="387" ht="20" customHeight="1">
@@ -10703,7 +10703,7 @@
         </is>
       </c>
       <c r="E387" s="23" t="n">
-        <v>186</v>
+        <v>235</v>
       </c>
     </row>
     <row r="388" ht="20" customHeight="1">
@@ -10728,7 +10728,7 @@
         </is>
       </c>
       <c r="E388" s="20" t="n">
-        <v>240</v>
+        <v>215</v>
       </c>
     </row>
     <row r="389" ht="20" customHeight="1">
@@ -10753,7 +10753,7 @@
         </is>
       </c>
       <c r="E389" s="23" t="n">
-        <v>168</v>
+        <v>212</v>
       </c>
     </row>
     <row r="390" ht="20" customHeight="1">
@@ -10778,7 +10778,7 @@
         </is>
       </c>
       <c r="E390" s="20" t="n">
-        <v>207</v>
+        <v>202</v>
       </c>
     </row>
     <row r="391" ht="20" customHeight="1">
@@ -10803,7 +10803,7 @@
         </is>
       </c>
       <c r="E391" s="23" t="n">
-        <v>137</v>
+        <v>161</v>
       </c>
     </row>
     <row r="392" ht="20" customHeight="1">
@@ -10828,7 +10828,7 @@
         </is>
       </c>
       <c r="E392" s="20" t="n">
-        <v>176</v>
+        <v>185</v>
       </c>
     </row>
     <row r="393" ht="20" customHeight="1">
@@ -10853,7 +10853,7 @@
         </is>
       </c>
       <c r="E393" s="23" t="n">
-        <v>219</v>
+        <v>119</v>
       </c>
     </row>
     <row r="394" ht="20" customHeight="1">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="E394" s="20" t="n">
-        <v>174</v>
+        <v>165</v>
       </c>
     </row>
     <row r="395" ht="20" customHeight="1">
@@ -10903,7 +10903,7 @@
         </is>
       </c>
       <c r="E395" s="23" t="n">
-        <v>174</v>
+        <v>135</v>
       </c>
     </row>
     <row r="396" ht="20" customHeight="1">
@@ -10928,7 +10928,7 @@
         </is>
       </c>
       <c r="E396" s="20" t="n">
-        <v>154</v>
+        <v>203</v>
       </c>
     </row>
     <row r="397" ht="20" customHeight="1">
@@ -10953,7 +10953,7 @@
         </is>
       </c>
       <c r="E397" s="23" t="n">
-        <v>113</v>
+        <v>211</v>
       </c>
     </row>
     <row r="398" ht="20" customHeight="1">
@@ -10978,7 +10978,7 @@
         </is>
       </c>
       <c r="E398" s="20" t="n">
-        <v>169</v>
+        <v>240</v>
       </c>
     </row>
     <row r="399" ht="20" customHeight="1">
@@ -11003,7 +11003,7 @@
         </is>
       </c>
       <c r="E399" s="23" t="n">
-        <v>121</v>
+        <v>134</v>
       </c>
     </row>
     <row r="400" ht="20" customHeight="1">
@@ -11028,7 +11028,7 @@
         </is>
       </c>
       <c r="E400" s="20" t="n">
-        <v>208</v>
+        <v>229</v>
       </c>
     </row>
     <row r="401" ht="20" customHeight="1">
@@ -11053,7 +11053,7 @@
         </is>
       </c>
       <c r="E401" s="23" t="n">
-        <v>125</v>
+        <v>237</v>
       </c>
     </row>
     <row r="402" ht="20" customHeight="1">
@@ -11078,7 +11078,7 @@
         </is>
       </c>
       <c r="E402" s="20" t="n">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="403" ht="20" customHeight="1">
@@ -11103,7 +11103,7 @@
         </is>
       </c>
       <c r="E403" s="23" t="n">
-        <v>131</v>
+        <v>195</v>
       </c>
     </row>
     <row r="404" ht="20" customHeight="1">
@@ -11128,7 +11128,7 @@
         </is>
       </c>
       <c r="E404" s="20" t="n">
-        <v>147</v>
+        <v>152</v>
       </c>
     </row>
     <row r="405" ht="20" customHeight="1">
@@ -11153,7 +11153,7 @@
         </is>
       </c>
       <c r="E405" s="23" t="n">
-        <v>116</v>
+        <v>238</v>
       </c>
     </row>
     <row r="406" ht="20" customHeight="1">
@@ -11178,7 +11178,7 @@
         </is>
       </c>
       <c r="E406" s="20" t="n">
-        <v>167</v>
+        <v>132</v>
       </c>
     </row>
     <row r="407" ht="20" customHeight="1">
@@ -11203,7 +11203,7 @@
         </is>
       </c>
       <c r="E407" s="23" t="n">
-        <v>124</v>
+        <v>191</v>
       </c>
     </row>
     <row r="408" ht="20" customHeight="1">
@@ -11228,7 +11228,7 @@
         </is>
       </c>
       <c r="E408" s="20" t="n">
-        <v>130</v>
+        <v>141</v>
       </c>
     </row>
     <row r="409" ht="20" customHeight="1">
@@ -11278,7 +11278,7 @@
         </is>
       </c>
       <c r="E410" s="20" t="n">
-        <v>116</v>
+        <v>125</v>
       </c>
     </row>
     <row r="411" ht="20" customHeight="1">
@@ -11303,7 +11303,7 @@
         </is>
       </c>
       <c r="E411" s="23" t="n">
-        <v>113</v>
+        <v>240</v>
       </c>
     </row>
     <row r="412" ht="20" customHeight="1">
@@ -11328,7 +11328,7 @@
         </is>
       </c>
       <c r="E412" s="20" t="n">
-        <v>146</v>
+        <v>183</v>
       </c>
     </row>
     <row r="413" ht="20" customHeight="1">
@@ -11353,7 +11353,7 @@
         </is>
       </c>
       <c r="E413" s="23" t="n">
-        <v>170</v>
+        <v>158</v>
       </c>
     </row>
     <row r="414" ht="20" customHeight="1">
@@ -11378,7 +11378,7 @@
         </is>
       </c>
       <c r="E414" s="20" t="n">
-        <v>155</v>
+        <v>212</v>
       </c>
     </row>
     <row r="415" ht="20" customHeight="1">
@@ -11403,7 +11403,7 @@
         </is>
       </c>
       <c r="E415" s="23" t="n">
-        <v>155</v>
+        <v>221</v>
       </c>
     </row>
     <row r="416" ht="20" customHeight="1">
@@ -11428,7 +11428,7 @@
         </is>
       </c>
       <c r="E416" s="20" t="n">
-        <v>228</v>
+        <v>177</v>
       </c>
     </row>
     <row r="417" ht="20" customHeight="1">
@@ -11453,7 +11453,7 @@
         </is>
       </c>
       <c r="E417" s="23" t="n">
-        <v>234</v>
+        <v>180</v>
       </c>
     </row>
     <row r="418" ht="20" customHeight="1">
@@ -11478,7 +11478,7 @@
         </is>
       </c>
       <c r="E418" s="20" t="n">
-        <v>204</v>
+        <v>182</v>
       </c>
     </row>
     <row r="419" ht="20" customHeight="1">
@@ -11503,7 +11503,7 @@
         </is>
       </c>
       <c r="E419" s="23" t="n">
-        <v>213</v>
+        <v>220</v>
       </c>
     </row>
     <row r="420" ht="20" customHeight="1">
@@ -11528,7 +11528,7 @@
         </is>
       </c>
       <c r="E420" s="20" t="n">
-        <v>169</v>
+        <v>128</v>
       </c>
     </row>
     <row r="421" ht="20" customHeight="1">
@@ -11553,7 +11553,7 @@
         </is>
       </c>
       <c r="E421" s="23" t="n">
-        <v>148</v>
+        <v>210</v>
       </c>
     </row>
     <row r="422" ht="20" customHeight="1">
@@ -11578,7 +11578,7 @@
         </is>
       </c>
       <c r="E422" s="20" t="n">
-        <v>111</v>
+        <v>228</v>
       </c>
     </row>
     <row r="423" ht="20" customHeight="1">
@@ -11603,7 +11603,7 @@
         </is>
       </c>
       <c r="E423" s="23" t="n">
-        <v>120</v>
+        <v>139</v>
       </c>
     </row>
     <row r="424" ht="20" customHeight="1">
@@ -11628,7 +11628,7 @@
         </is>
       </c>
       <c r="E424" s="20" t="n">
-        <v>123</v>
+        <v>195</v>
       </c>
     </row>
     <row r="425" ht="20" customHeight="1">
@@ -11653,7 +11653,7 @@
         </is>
       </c>
       <c r="E425" s="23" t="n">
-        <v>119</v>
+        <v>198</v>
       </c>
     </row>
     <row r="426" ht="20" customHeight="1">
@@ -11678,7 +11678,7 @@
         </is>
       </c>
       <c r="E426" s="20" t="n">
-        <v>119</v>
+        <v>168</v>
       </c>
     </row>
     <row r="427" ht="20" customHeight="1">
@@ -11703,7 +11703,7 @@
         </is>
       </c>
       <c r="E427" s="23" t="n">
-        <v>207</v>
+        <v>219</v>
       </c>
     </row>
     <row r="428" ht="20" customHeight="1">
@@ -11728,7 +11728,7 @@
         </is>
       </c>
       <c r="E428" s="20" t="n">
-        <v>150</v>
+        <v>141</v>
       </c>
     </row>
     <row r="429" ht="20" customHeight="1">
@@ -11753,7 +11753,7 @@
         </is>
       </c>
       <c r="E429" s="23" t="n">
-        <v>181</v>
+        <v>185</v>
       </c>
     </row>
     <row r="430" ht="20" customHeight="1">
@@ -11778,7 +11778,7 @@
         </is>
       </c>
       <c r="E430" s="20" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="431" ht="20" customHeight="1">
@@ -11803,7 +11803,7 @@
         </is>
       </c>
       <c r="E431" s="23" t="n">
-        <v>162</v>
+        <v>181</v>
       </c>
     </row>
     <row r="432" ht="20" customHeight="1">
@@ -11828,7 +11828,7 @@
         </is>
       </c>
       <c r="E432" s="20" t="n">
-        <v>117</v>
+        <v>234</v>
       </c>
     </row>
     <row r="433" ht="20" customHeight="1">
@@ -11853,7 +11853,7 @@
         </is>
       </c>
       <c r="E433" s="23" t="n">
-        <v>232</v>
+        <v>183</v>
       </c>
     </row>
     <row r="434" ht="20" customHeight="1">
@@ -11878,7 +11878,7 @@
         </is>
       </c>
       <c r="E434" s="20" t="n">
-        <v>180</v>
+        <v>119</v>
       </c>
     </row>
     <row r="435" ht="20" customHeight="1">
@@ -11903,7 +11903,7 @@
         </is>
       </c>
       <c r="E435" s="23" t="n">
-        <v>136</v>
+        <v>170</v>
       </c>
     </row>
     <row r="436" ht="20" customHeight="1">
@@ -11928,7 +11928,7 @@
         </is>
       </c>
       <c r="E436" s="20" t="n">
-        <v>154</v>
+        <v>197</v>
       </c>
     </row>
     <row r="437" ht="20" customHeight="1">
@@ -11953,7 +11953,7 @@
         </is>
       </c>
       <c r="E437" s="23" t="n">
-        <v>222</v>
+        <v>176</v>
       </c>
     </row>
     <row r="438" ht="20" customHeight="1">
@@ -11978,7 +11978,7 @@
         </is>
       </c>
       <c r="E438" s="20" t="n">
-        <v>182</v>
+        <v>176</v>
       </c>
     </row>
     <row r="439" ht="20" customHeight="1">
@@ -12003,7 +12003,7 @@
         </is>
       </c>
       <c r="E439" s="23" t="n">
-        <v>179</v>
+        <v>190</v>
       </c>
     </row>
     <row r="440" ht="20" customHeight="1">
@@ -12028,7 +12028,7 @@
         </is>
       </c>
       <c r="E440" s="20" t="n">
-        <v>224</v>
+        <v>170</v>
       </c>
     </row>
     <row r="441" ht="20" customHeight="1">
@@ -12053,7 +12053,7 @@
         </is>
       </c>
       <c r="E441" s="23" t="n">
-        <v>194</v>
+        <v>130</v>
       </c>
     </row>
     <row r="442" ht="20" customHeight="1">
@@ -12078,7 +12078,7 @@
         </is>
       </c>
       <c r="E442" s="20" t="n">
-        <v>213</v>
+        <v>168</v>
       </c>
     </row>
     <row r="443" ht="20" customHeight="1">
@@ -12103,7 +12103,7 @@
         </is>
       </c>
       <c r="E443" s="23" t="n">
-        <v>120</v>
+        <v>228</v>
       </c>
     </row>
     <row r="444" ht="20" customHeight="1">
@@ -12128,7 +12128,7 @@
         </is>
       </c>
       <c r="E444" s="20" t="n">
-        <v>189</v>
+        <v>113</v>
       </c>
     </row>
     <row r="445" ht="20" customHeight="1">
@@ -12153,7 +12153,7 @@
         </is>
       </c>
       <c r="E445" s="23" t="n">
-        <v>141</v>
+        <v>182</v>
       </c>
     </row>
     <row r="446" ht="20" customHeight="1">
@@ -12178,7 +12178,7 @@
         </is>
       </c>
       <c r="E446" s="20" t="n">
-        <v>176</v>
+        <v>125</v>
       </c>
     </row>
     <row r="447" ht="20" customHeight="1">
@@ -12203,7 +12203,7 @@
         </is>
       </c>
       <c r="E447" s="23" t="n">
-        <v>137</v>
+        <v>163</v>
       </c>
     </row>
     <row r="448" ht="20" customHeight="1">
@@ -12228,7 +12228,7 @@
         </is>
       </c>
       <c r="E448" s="20" t="n">
-        <v>119</v>
+        <v>148</v>
       </c>
     </row>
     <row r="449" ht="20" customHeight="1">
@@ -12253,7 +12253,7 @@
         </is>
       </c>
       <c r="E449" s="23" t="n">
-        <v>189</v>
+        <v>111</v>
       </c>
     </row>
     <row r="450" ht="20" customHeight="1">
@@ -12278,7 +12278,7 @@
         </is>
       </c>
       <c r="E450" s="20" t="n">
-        <v>161</v>
+        <v>116</v>
       </c>
     </row>
     <row r="451" ht="20" customHeight="1">
@@ -12303,7 +12303,7 @@
         </is>
       </c>
       <c r="E451" s="23" t="n">
-        <v>132</v>
+        <v>192</v>
       </c>
     </row>
     <row r="452" ht="20" customHeight="1">
@@ -12328,7 +12328,7 @@
         </is>
       </c>
       <c r="E452" s="20" t="n">
-        <v>146</v>
+        <v>141</v>
       </c>
     </row>
     <row r="453" ht="20" customHeight="1">
@@ -12353,7 +12353,7 @@
         </is>
       </c>
       <c r="E453" s="23" t="n">
-        <v>119</v>
+        <v>236</v>
       </c>
     </row>
     <row r="454" ht="20" customHeight="1">
@@ -12378,7 +12378,7 @@
         </is>
       </c>
       <c r="E454" s="20" t="n">
-        <v>125</v>
+        <v>149</v>
       </c>
     </row>
     <row r="455" ht="20" customHeight="1">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="E455" s="23" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="456" ht="20" customHeight="1">
@@ -12428,7 +12428,7 @@
         </is>
       </c>
       <c r="E456" s="20" t="n">
-        <v>117</v>
+        <v>208</v>
       </c>
     </row>
     <row r="457" ht="20" customHeight="1">
@@ -12453,7 +12453,7 @@
         </is>
       </c>
       <c r="E457" s="23" t="n">
-        <v>214</v>
+        <v>236</v>
       </c>
     </row>
     <row r="458" ht="20" customHeight="1">
@@ -12478,7 +12478,7 @@
         </is>
       </c>
       <c r="E458" s="20" t="n">
-        <v>153</v>
+        <v>164</v>
       </c>
     </row>
     <row r="459" ht="20" customHeight="1">
@@ -12503,7 +12503,7 @@
         </is>
       </c>
       <c r="E459" s="23" t="n">
-        <v>132</v>
+        <v>123</v>
       </c>
     </row>
     <row r="460" ht="20" customHeight="1">
@@ -12528,7 +12528,7 @@
         </is>
       </c>
       <c r="E460" s="20" t="n">
-        <v>174</v>
+        <v>208</v>
       </c>
     </row>
     <row r="461" ht="20" customHeight="1">
@@ -12553,7 +12553,7 @@
         </is>
       </c>
       <c r="E461" s="23" t="n">
-        <v>189</v>
+        <v>133</v>
       </c>
     </row>
     <row r="462" ht="20" customHeight="1">
@@ -12578,7 +12578,7 @@
         </is>
       </c>
       <c r="E462" s="20" t="n">
-        <v>147</v>
+        <v>224</v>
       </c>
     </row>
     <row r="463" ht="20" customHeight="1">
@@ -12603,7 +12603,7 @@
         </is>
       </c>
       <c r="E463" s="23" t="n">
-        <v>206</v>
+        <v>238</v>
       </c>
     </row>
     <row r="464" ht="20" customHeight="1">
@@ -12628,7 +12628,7 @@
         </is>
       </c>
       <c r="E464" s="20" t="n">
-        <v>209</v>
+        <v>126</v>
       </c>
     </row>
     <row r="465" ht="20" customHeight="1">
@@ -12653,7 +12653,7 @@
         </is>
       </c>
       <c r="E465" s="23" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="466" ht="20" customHeight="1">
@@ -12678,7 +12678,7 @@
         </is>
       </c>
       <c r="E466" s="20" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="467" ht="20" customHeight="1">
@@ -12703,7 +12703,7 @@
         </is>
       </c>
       <c r="E467" s="23" t="n">
-        <v>142</v>
+        <v>120</v>
       </c>
     </row>
     <row r="468" ht="20" customHeight="1">
@@ -12728,7 +12728,7 @@
         </is>
       </c>
       <c r="E468" s="20" t="n">
-        <v>219</v>
+        <v>112</v>
       </c>
     </row>
     <row r="469" ht="20" customHeight="1">
@@ -12753,7 +12753,7 @@
         </is>
       </c>
       <c r="E469" s="23" t="n">
-        <v>175</v>
+        <v>234</v>
       </c>
     </row>
     <row r="470" ht="20" customHeight="1">
@@ -12778,7 +12778,7 @@
         </is>
       </c>
       <c r="E470" s="20" t="n">
-        <v>158</v>
+        <v>189</v>
       </c>
     </row>
     <row r="471" ht="20" customHeight="1">
@@ -12803,7 +12803,7 @@
         </is>
       </c>
       <c r="E471" s="23" t="n">
-        <v>216</v>
+        <v>120</v>
       </c>
     </row>
     <row r="472" ht="20" customHeight="1">
@@ -12828,7 +12828,7 @@
         </is>
       </c>
       <c r="E472" s="20" t="n">
-        <v>112</v>
+        <v>198</v>
       </c>
     </row>
     <row r="473" ht="20" customHeight="1">
@@ -12853,7 +12853,7 @@
         </is>
       </c>
       <c r="E473" s="23" t="n">
-        <v>218</v>
+        <v>197</v>
       </c>
     </row>
     <row r="474" ht="20" customHeight="1">
@@ -12878,7 +12878,7 @@
         </is>
       </c>
       <c r="E474" s="20" t="n">
-        <v>136</v>
+        <v>215</v>
       </c>
     </row>
     <row r="475" ht="20" customHeight="1">
@@ -12903,7 +12903,7 @@
         </is>
       </c>
       <c r="E475" s="23" t="n">
-        <v>196</v>
+        <v>210</v>
       </c>
     </row>
     <row r="476" ht="20" customHeight="1">
@@ -12928,7 +12928,7 @@
         </is>
       </c>
       <c r="E476" s="20" t="n">
-        <v>140</v>
+        <v>190</v>
       </c>
     </row>
     <row r="477" ht="20" customHeight="1">
@@ -12953,7 +12953,7 @@
         </is>
       </c>
       <c r="E477" s="23" t="n">
-        <v>146</v>
+        <v>200</v>
       </c>
     </row>
     <row r="478" ht="20" customHeight="1">
@@ -12978,7 +12978,7 @@
         </is>
       </c>
       <c r="E478" s="20" t="n">
-        <v>144</v>
+        <v>233</v>
       </c>
     </row>
     <row r="479" ht="20" customHeight="1">
@@ -13003,7 +13003,7 @@
         </is>
       </c>
       <c r="E479" s="23" t="n">
-        <v>118</v>
+        <v>205</v>
       </c>
     </row>
     <row r="480" ht="20" customHeight="1">
@@ -13028,7 +13028,7 @@
         </is>
       </c>
       <c r="E480" s="20" t="n">
-        <v>156</v>
+        <v>235</v>
       </c>
     </row>
     <row r="481" ht="20" customHeight="1">
@@ -13053,7 +13053,7 @@
         </is>
       </c>
       <c r="E481" s="23" t="n">
-        <v>119</v>
+        <v>198</v>
       </c>
     </row>
     <row r="482" ht="20" customHeight="1">
@@ -13078,7 +13078,7 @@
         </is>
       </c>
       <c r="E482" s="20" t="n">
-        <v>172</v>
+        <v>123</v>
       </c>
     </row>
     <row r="483" ht="20" customHeight="1">
@@ -13103,7 +13103,7 @@
         </is>
       </c>
       <c r="E483" s="23" t="n">
-        <v>136</v>
+        <v>185</v>
       </c>
     </row>
     <row r="484" ht="20" customHeight="1">
@@ -13128,7 +13128,7 @@
         </is>
       </c>
       <c r="E484" s="20" t="n">
-        <v>213</v>
+        <v>135</v>
       </c>
     </row>
     <row r="485" ht="20" customHeight="1">
@@ -13153,7 +13153,7 @@
         </is>
       </c>
       <c r="E485" s="23" t="n">
-        <v>163</v>
+        <v>216</v>
       </c>
     </row>
     <row r="486" ht="20" customHeight="1">
@@ -13178,7 +13178,7 @@
         </is>
       </c>
       <c r="E486" s="20" t="n">
-        <v>170</v>
+        <v>138</v>
       </c>
     </row>
     <row r="487" ht="20" customHeight="1">
@@ -13203,7 +13203,7 @@
         </is>
       </c>
       <c r="E487" s="23" t="n">
-        <v>124</v>
+        <v>113</v>
       </c>
     </row>
     <row r="488" ht="20" customHeight="1">
@@ -13228,7 +13228,7 @@
         </is>
       </c>
       <c r="E488" s="20" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="489" ht="20" customHeight="1">
@@ -13253,7 +13253,7 @@
         </is>
       </c>
       <c r="E489" s="23" t="n">
-        <v>165</v>
+        <v>189</v>
       </c>
     </row>
     <row r="490" ht="20" customHeight="1">
@@ -13278,7 +13278,7 @@
         </is>
       </c>
       <c r="E490" s="20" t="n">
-        <v>236</v>
+        <v>111</v>
       </c>
     </row>
     <row r="491" ht="20" customHeight="1">
@@ -13303,7 +13303,7 @@
         </is>
       </c>
       <c r="E491" s="23" t="n">
-        <v>210</v>
+        <v>171</v>
       </c>
     </row>
     <row r="492" ht="20" customHeight="1">
@@ -13328,7 +13328,7 @@
         </is>
       </c>
       <c r="E492" s="20" t="n">
-        <v>185</v>
+        <v>213</v>
       </c>
     </row>
     <row r="493" ht="20" customHeight="1">
@@ -13353,7 +13353,7 @@
         </is>
       </c>
       <c r="E493" s="23" t="n">
-        <v>112</v>
+        <v>205</v>
       </c>
     </row>
     <row r="494" ht="20" customHeight="1">
@@ -13378,7 +13378,7 @@
         </is>
       </c>
       <c r="E494" s="20" t="n">
-        <v>239</v>
+        <v>112</v>
       </c>
     </row>
     <row r="495" ht="20" customHeight="1">
@@ -13403,7 +13403,7 @@
         </is>
       </c>
       <c r="E495" s="23" t="n">
-        <v>182</v>
+        <v>224</v>
       </c>
     </row>
     <row r="496" ht="20" customHeight="1">
@@ -13428,7 +13428,7 @@
         </is>
       </c>
       <c r="E496" s="20" t="n">
-        <v>187</v>
+        <v>112</v>
       </c>
     </row>
     <row r="497" ht="20" customHeight="1">
@@ -13453,7 +13453,7 @@
         </is>
       </c>
       <c r="E497" s="23" t="n">
-        <v>156</v>
+        <v>140</v>
       </c>
     </row>
     <row r="498" ht="20" customHeight="1">
@@ -13478,7 +13478,7 @@
         </is>
       </c>
       <c r="E498" s="20" t="n">
-        <v>220</v>
+        <v>111</v>
       </c>
     </row>
     <row r="499" ht="20" customHeight="1">
@@ -13503,7 +13503,7 @@
         </is>
       </c>
       <c r="E499" s="23" t="n">
-        <v>156</v>
+        <v>161</v>
       </c>
     </row>
     <row r="500" ht="20" customHeight="1">
@@ -13528,7 +13528,7 @@
         </is>
       </c>
       <c r="E500" s="20" t="n">
-        <v>192</v>
+        <v>142</v>
       </c>
     </row>
     <row r="501" ht="20" customHeight="1">
@@ -13553,7 +13553,7 @@
         </is>
       </c>
       <c r="E501" s="23" t="n">
-        <v>237</v>
+        <v>216</v>
       </c>
     </row>
     <row r="502" ht="20" customHeight="1">
@@ -13578,7 +13578,7 @@
         </is>
       </c>
       <c r="E502" s="20" t="n">
-        <v>215</v>
+        <v>231</v>
       </c>
     </row>
     <row r="503" ht="20" customHeight="1">
@@ -13603,7 +13603,7 @@
         </is>
       </c>
       <c r="E503" s="23" t="n">
-        <v>115</v>
+        <v>190</v>
       </c>
     </row>
     <row r="504" ht="20" customHeight="1">
@@ -13628,7 +13628,7 @@
         </is>
       </c>
       <c r="E504" s="20" t="n">
-        <v>140</v>
+        <v>177</v>
       </c>
     </row>
     <row r="505" ht="20" customHeight="1">
@@ -13653,7 +13653,7 @@
         </is>
       </c>
       <c r="E505" s="23" t="n">
-        <v>229</v>
+        <v>204</v>
       </c>
     </row>
     <row r="506" ht="20" customHeight="1">
@@ -13678,7 +13678,7 @@
         </is>
       </c>
       <c r="E506" s="20" t="n">
-        <v>188</v>
+        <v>161</v>
       </c>
     </row>
     <row r="507" ht="20" customHeight="1">
@@ -13703,7 +13703,7 @@
         </is>
       </c>
       <c r="E507" s="23" t="n">
-        <v>219</v>
+        <v>139</v>
       </c>
     </row>
     <row r="508" ht="20" customHeight="1">
@@ -13728,7 +13728,7 @@
         </is>
       </c>
       <c r="E508" s="20" t="n">
-        <v>232</v>
+        <v>181</v>
       </c>
     </row>
     <row r="509" ht="20" customHeight="1">
@@ -13753,7 +13753,7 @@
         </is>
       </c>
       <c r="E509" s="23" t="n">
-        <v>184</v>
+        <v>171</v>
       </c>
     </row>
     <row r="510" ht="20" customHeight="1">
@@ -13778,7 +13778,7 @@
         </is>
       </c>
       <c r="E510" s="20" t="n">
-        <v>127</v>
+        <v>164</v>
       </c>
     </row>
     <row r="511" ht="20" customHeight="1">
@@ -13803,7 +13803,7 @@
         </is>
       </c>
       <c r="E511" s="23" t="n">
-        <v>190</v>
+        <v>143</v>
       </c>
     </row>
     <row r="512" ht="20" customHeight="1">
@@ -13828,7 +13828,7 @@
         </is>
       </c>
       <c r="E512" s="20" t="n">
-        <v>237</v>
+        <v>127</v>
       </c>
     </row>
     <row r="513" ht="20" customHeight="1">
@@ -13853,7 +13853,7 @@
         </is>
       </c>
       <c r="E513" s="23" t="n">
-        <v>126</v>
+        <v>151</v>
       </c>
     </row>
     <row r="514" ht="20" customHeight="1">
@@ -13878,7 +13878,7 @@
         </is>
       </c>
       <c r="E514" s="20" t="n">
-        <v>132</v>
+        <v>181</v>
       </c>
     </row>
     <row r="515" ht="20" customHeight="1">
@@ -13903,7 +13903,7 @@
         </is>
       </c>
       <c r="E515" s="23" t="n">
-        <v>122</v>
+        <v>136</v>
       </c>
     </row>
     <row r="516" ht="20" customHeight="1">
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="E516" s="20" t="n">
-        <v>147</v>
+        <v>223</v>
       </c>
     </row>
     <row r="517" ht="20" customHeight="1">
@@ -13953,7 +13953,7 @@
         </is>
       </c>
       <c r="E517" s="23" t="n">
-        <v>163</v>
+        <v>217</v>
       </c>
     </row>
     <row r="518" ht="20" customHeight="1">
@@ -13978,7 +13978,7 @@
         </is>
       </c>
       <c r="E518" s="20" t="n">
-        <v>236</v>
+        <v>179</v>
       </c>
     </row>
     <row r="519" ht="20" customHeight="1">
@@ -14003,7 +14003,7 @@
         </is>
       </c>
       <c r="E519" s="23" t="n">
-        <v>193</v>
+        <v>152</v>
       </c>
     </row>
     <row r="520" ht="20" customHeight="1">
@@ -14028,7 +14028,7 @@
         </is>
       </c>
       <c r="E520" s="20" t="n">
-        <v>152</v>
+        <v>127</v>
       </c>
     </row>
     <row r="521" ht="20" customHeight="1">
@@ -14053,7 +14053,7 @@
         </is>
       </c>
       <c r="E521" s="23" t="n">
-        <v>111</v>
+        <v>149</v>
       </c>
     </row>
     <row r="522" ht="20" customHeight="1">
@@ -14078,7 +14078,7 @@
         </is>
       </c>
       <c r="E522" s="20" t="n">
-        <v>210</v>
+        <v>183</v>
       </c>
     </row>
     <row r="523" ht="20" customHeight="1">
@@ -14103,7 +14103,7 @@
         </is>
       </c>
       <c r="E523" s="23" t="n">
-        <v>138</v>
+        <v>114</v>
       </c>
     </row>
     <row r="524" ht="20" customHeight="1">
@@ -14128,7 +14128,7 @@
         </is>
       </c>
       <c r="E524" s="20" t="n">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="525" ht="20" customHeight="1">
@@ -14153,7 +14153,7 @@
         </is>
       </c>
       <c r="E525" s="23" t="n">
-        <v>154</v>
+        <v>115</v>
       </c>
     </row>
     <row r="526" ht="20" customHeight="1">
@@ -14178,7 +14178,7 @@
         </is>
       </c>
       <c r="E526" s="20" t="n">
-        <v>235</v>
+        <v>202</v>
       </c>
     </row>
     <row r="527" ht="20" customHeight="1">
@@ -14203,7 +14203,7 @@
         </is>
       </c>
       <c r="E527" s="23" t="n">
-        <v>115</v>
+        <v>219</v>
       </c>
     </row>
     <row r="528" ht="20" customHeight="1">
@@ -14228,7 +14228,7 @@
         </is>
       </c>
       <c r="E528" s="20" t="n">
-        <v>129</v>
+        <v>214</v>
       </c>
     </row>
     <row r="529" ht="20" customHeight="1">
@@ -14253,7 +14253,7 @@
         </is>
       </c>
       <c r="E529" s="23" t="n">
-        <v>163</v>
+        <v>219</v>
       </c>
     </row>
     <row r="530" ht="20" customHeight="1">
@@ -14278,7 +14278,7 @@
         </is>
       </c>
       <c r="E530" s="20" t="n">
-        <v>140</v>
+        <v>171</v>
       </c>
     </row>
     <row r="531" ht="20" customHeight="1">
@@ -14303,7 +14303,7 @@
         </is>
       </c>
       <c r="E531" s="23" t="n">
-        <v>170</v>
+        <v>145</v>
       </c>
     </row>
     <row r="532" ht="20" customHeight="1">
@@ -14328,7 +14328,7 @@
         </is>
       </c>
       <c r="E532" s="20" t="n">
-        <v>228</v>
+        <v>195</v>
       </c>
     </row>
     <row r="533" ht="20" customHeight="1">
@@ -14353,7 +14353,7 @@
         </is>
       </c>
       <c r="E533" s="23" t="n">
-        <v>156</v>
+        <v>200</v>
       </c>
     </row>
     <row r="534" ht="20" customHeight="1">
@@ -14378,7 +14378,7 @@
         </is>
       </c>
       <c r="E534" s="20" t="n">
-        <v>193</v>
+        <v>160</v>
       </c>
     </row>
     <row r="535" ht="20" customHeight="1">
@@ -14403,7 +14403,7 @@
         </is>
       </c>
       <c r="E535" s="23" t="n">
-        <v>199</v>
+        <v>230</v>
       </c>
     </row>
     <row r="536" ht="20" customHeight="1">
@@ -14428,7 +14428,7 @@
         </is>
       </c>
       <c r="E536" s="20" t="n">
-        <v>113</v>
+        <v>162</v>
       </c>
     </row>
     <row r="537" ht="20" customHeight="1">
@@ -14453,7 +14453,7 @@
         </is>
       </c>
       <c r="E537" s="23" t="n">
-        <v>111</v>
+        <v>172</v>
       </c>
     </row>
     <row r="538" ht="20" customHeight="1">
@@ -14478,7 +14478,7 @@
         </is>
       </c>
       <c r="E538" s="20" t="n">
-        <v>237</v>
+        <v>182</v>
       </c>
     </row>
     <row r="539" ht="20" customHeight="1">
@@ -14503,7 +14503,7 @@
         </is>
       </c>
       <c r="E539" s="23" t="n">
-        <v>191</v>
+        <v>116</v>
       </c>
     </row>
     <row r="540" ht="20" customHeight="1">
@@ -14528,7 +14528,7 @@
         </is>
       </c>
       <c r="E540" s="20" t="n">
-        <v>151</v>
+        <v>112</v>
       </c>
     </row>
     <row r="541" ht="20" customHeight="1">
@@ -14553,7 +14553,7 @@
         </is>
       </c>
       <c r="E541" s="23" t="n">
-        <v>234</v>
+        <v>176</v>
       </c>
     </row>
     <row r="542" ht="20" customHeight="1">
@@ -14578,7 +14578,7 @@
         </is>
       </c>
       <c r="E542" s="20" t="n">
-        <v>173</v>
+        <v>115</v>
       </c>
     </row>
     <row r="543" ht="20" customHeight="1">
@@ -14603,7 +14603,7 @@
         </is>
       </c>
       <c r="E543" s="23" t="n">
-        <v>168</v>
+        <v>175</v>
       </c>
     </row>
     <row r="544" ht="20" customHeight="1">
@@ -14628,7 +14628,7 @@
         </is>
       </c>
       <c r="E544" s="20" t="n">
-        <v>112</v>
+        <v>155</v>
       </c>
     </row>
     <row r="545" ht="20" customHeight="1">
@@ -14653,7 +14653,7 @@
         </is>
       </c>
       <c r="E545" s="23" t="n">
-        <v>135</v>
+        <v>211</v>
       </c>
     </row>
     <row r="546" ht="20" customHeight="1">
@@ -14678,7 +14678,7 @@
         </is>
       </c>
       <c r="E546" s="20" t="n">
-        <v>119</v>
+        <v>169</v>
       </c>
     </row>
     <row r="547" ht="20" customHeight="1">
@@ -14703,7 +14703,7 @@
         </is>
       </c>
       <c r="E547" s="23" t="n">
-        <v>240</v>
+        <v>114</v>
       </c>
     </row>
     <row r="548" ht="20" customHeight="1">
@@ -14728,7 +14728,7 @@
         </is>
       </c>
       <c r="E548" s="20" t="n">
-        <v>215</v>
+        <v>159</v>
       </c>
     </row>
     <row r="549" ht="20" customHeight="1">
@@ -14753,7 +14753,7 @@
         </is>
       </c>
       <c r="E549" s="23" t="n">
-        <v>187</v>
+        <v>202</v>
       </c>
     </row>
     <row r="550" ht="20" customHeight="1">
@@ -14778,7 +14778,7 @@
         </is>
       </c>
       <c r="E550" s="20" t="n">
-        <v>121</v>
+        <v>239</v>
       </c>
     </row>
     <row r="551" ht="20" customHeight="1">
@@ -14803,7 +14803,7 @@
         </is>
       </c>
       <c r="E551" s="23" t="n">
-        <v>179</v>
+        <v>217</v>
       </c>
     </row>
     <row r="552" ht="20" customHeight="1">
@@ -14828,7 +14828,7 @@
         </is>
       </c>
       <c r="E552" s="20" t="n">
-        <v>229</v>
+        <v>122</v>
       </c>
     </row>
     <row r="553" ht="20" customHeight="1">
@@ -14853,7 +14853,7 @@
         </is>
       </c>
       <c r="E553" s="23" t="n">
-        <v>225</v>
+        <v>132</v>
       </c>
     </row>
     <row r="554" ht="20" customHeight="1">
@@ -14878,7 +14878,7 @@
         </is>
       </c>
       <c r="E554" s="20" t="n">
-        <v>240</v>
+        <v>153</v>
       </c>
     </row>
     <row r="555" ht="20" customHeight="1">
@@ -14903,7 +14903,7 @@
         </is>
       </c>
       <c r="E555" s="23" t="n">
-        <v>226</v>
+        <v>186</v>
       </c>
     </row>
     <row r="556" ht="20" customHeight="1">
@@ -14928,7 +14928,7 @@
         </is>
       </c>
       <c r="E556" s="20" t="n">
-        <v>134</v>
+        <v>234</v>
       </c>
     </row>
     <row r="557" ht="20" customHeight="1">
@@ -14953,7 +14953,7 @@
         </is>
       </c>
       <c r="E557" s="23" t="n">
-        <v>192</v>
+        <v>169</v>
       </c>
     </row>
     <row r="558" ht="20" customHeight="1">
@@ -14978,7 +14978,7 @@
         </is>
       </c>
       <c r="E558" s="20" t="n">
-        <v>213</v>
+        <v>190</v>
       </c>
     </row>
     <row r="559" ht="20" customHeight="1">
@@ -15003,7 +15003,7 @@
         </is>
       </c>
       <c r="E559" s="23" t="n">
-        <v>220</v>
+        <v>192</v>
       </c>
     </row>
     <row r="560" ht="20" customHeight="1">
@@ -15028,7 +15028,7 @@
         </is>
       </c>
       <c r="E560" s="20" t="n">
-        <v>166</v>
+        <v>191</v>
       </c>
     </row>
     <row r="561" ht="20" customHeight="1">
@@ -15053,7 +15053,7 @@
         </is>
       </c>
       <c r="E561" s="23" t="n">
-        <v>177</v>
+        <v>138</v>
       </c>
     </row>
     <row r="562" ht="20" customHeight="1">
@@ -15078,7 +15078,7 @@
         </is>
       </c>
       <c r="E562" s="20" t="n">
-        <v>136</v>
+        <v>205</v>
       </c>
     </row>
     <row r="563" ht="20" customHeight="1">
@@ -15103,7 +15103,7 @@
         </is>
       </c>
       <c r="E563" s="23" t="n">
-        <v>159</v>
+        <v>133</v>
       </c>
     </row>
     <row r="564" ht="20" customHeight="1">
@@ -15128,7 +15128,7 @@
         </is>
       </c>
       <c r="E564" s="20" t="n">
-        <v>149</v>
+        <v>120</v>
       </c>
     </row>
     <row r="565" ht="20" customHeight="1">
@@ -15153,7 +15153,7 @@
         </is>
       </c>
       <c r="E565" s="23" t="n">
-        <v>118</v>
+        <v>226</v>
       </c>
     </row>
     <row r="566" ht="20" customHeight="1">
@@ -15178,7 +15178,7 @@
         </is>
       </c>
       <c r="E566" s="20" t="n">
-        <v>147</v>
+        <v>162</v>
       </c>
     </row>
     <row r="567" ht="20" customHeight="1">
@@ -15203,7 +15203,7 @@
         </is>
       </c>
       <c r="E567" s="23" t="n">
-        <v>138</v>
+        <v>126</v>
       </c>
     </row>
     <row r="568" ht="20" customHeight="1">
@@ -15228,7 +15228,7 @@
         </is>
       </c>
       <c r="E568" s="20" t="n">
-        <v>202</v>
+        <v>161</v>
       </c>
     </row>
     <row r="569" ht="20" customHeight="1">
@@ -15253,7 +15253,7 @@
         </is>
       </c>
       <c r="E569" s="23" t="n">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="570" ht="20" customHeight="1">
@@ -15278,7 +15278,7 @@
         </is>
       </c>
       <c r="E570" s="20" t="n">
-        <v>112</v>
+        <v>211</v>
       </c>
     </row>
     <row r="571" ht="20" customHeight="1">
@@ -15303,7 +15303,7 @@
         </is>
       </c>
       <c r="E571" s="23" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="572" ht="20" customHeight="1">
@@ -15328,7 +15328,7 @@
         </is>
       </c>
       <c r="E572" s="20" t="n">
-        <v>113</v>
+        <v>147</v>
       </c>
     </row>
     <row r="573" ht="20" customHeight="1">
@@ -15353,7 +15353,7 @@
         </is>
       </c>
       <c r="E573" s="23" t="n">
-        <v>130</v>
+        <v>180</v>
       </c>
     </row>
     <row r="574" ht="20" customHeight="1">
@@ -15378,7 +15378,7 @@
         </is>
       </c>
       <c r="E574" s="20" t="n">
-        <v>145</v>
+        <v>132</v>
       </c>
     </row>
     <row r="575" ht="20" customHeight="1">
@@ -15403,7 +15403,7 @@
         </is>
       </c>
       <c r="E575" s="23" t="n">
-        <v>178</v>
+        <v>163</v>
       </c>
     </row>
     <row r="576" ht="20" customHeight="1">
@@ -15428,7 +15428,7 @@
         </is>
       </c>
       <c r="E576" s="20" t="n">
-        <v>128</v>
+        <v>117</v>
       </c>
     </row>
     <row r="577" ht="20" customHeight="1">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="E577" s="23" t="n">
-        <v>135</v>
+        <v>193</v>
       </c>
     </row>
     <row r="578" ht="20" customHeight="1">
@@ -15478,7 +15478,7 @@
         </is>
       </c>
       <c r="E578" s="20" t="n">
-        <v>169</v>
+        <v>201</v>
       </c>
     </row>
     <row r="579" ht="20" customHeight="1">
@@ -15503,7 +15503,7 @@
         </is>
       </c>
       <c r="E579" s="23" t="n">
-        <v>121</v>
+        <v>207</v>
       </c>
     </row>
     <row r="580" ht="20" customHeight="1">
@@ -15528,7 +15528,7 @@
         </is>
       </c>
       <c r="E580" s="20" t="n">
-        <v>209</v>
+        <v>159</v>
       </c>
     </row>
     <row r="581" ht="20" customHeight="1">
@@ -15553,7 +15553,7 @@
         </is>
       </c>
       <c r="E581" s="23" t="n">
-        <v>190</v>
+        <v>203</v>
       </c>
     </row>
     <row r="582" ht="20" customHeight="1">
@@ -15578,7 +15578,7 @@
         </is>
       </c>
       <c r="E582" s="20" t="n">
-        <v>214</v>
+        <v>126</v>
       </c>
     </row>
     <row r="583" ht="20" customHeight="1">
@@ -15603,7 +15603,7 @@
         </is>
       </c>
       <c r="E583" s="23" t="n">
-        <v>189</v>
+        <v>155</v>
       </c>
     </row>
     <row r="584" ht="20" customHeight="1">
@@ -15628,7 +15628,7 @@
         </is>
       </c>
       <c r="E584" s="20" t="n">
-        <v>219</v>
+        <v>141</v>
       </c>
     </row>
     <row r="585" ht="20" customHeight="1">
@@ -15653,7 +15653,7 @@
         </is>
       </c>
       <c r="E585" s="23" t="n">
-        <v>217</v>
+        <v>171</v>
       </c>
     </row>
     <row r="586" ht="20" customHeight="1">
@@ -15678,7 +15678,7 @@
         </is>
       </c>
       <c r="E586" s="20" t="n">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="587" ht="20" customHeight="1">
@@ -15703,7 +15703,7 @@
         </is>
       </c>
       <c r="E587" s="23" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="588" ht="20" customHeight="1">
@@ -15728,7 +15728,7 @@
         </is>
       </c>
       <c r="E588" s="20" t="n">
-        <v>162</v>
+        <v>139</v>
       </c>
     </row>
     <row r="589" ht="20" customHeight="1">
@@ -15753,7 +15753,7 @@
         </is>
       </c>
       <c r="E589" s="23" t="n">
-        <v>148</v>
+        <v>111</v>
       </c>
     </row>
     <row r="590" ht="20" customHeight="1">
@@ -15778,7 +15778,7 @@
         </is>
       </c>
       <c r="E590" s="20" t="n">
-        <v>161</v>
+        <v>181</v>
       </c>
     </row>
     <row r="591" ht="20" customHeight="1">
@@ -15803,7 +15803,7 @@
         </is>
       </c>
       <c r="E591" s="23" t="n">
-        <v>225</v>
+        <v>203</v>
       </c>
     </row>
     <row r="592" ht="20" customHeight="1">
@@ -15828,7 +15828,7 @@
         </is>
       </c>
       <c r="E592" s="20" t="n">
-        <v>202</v>
+        <v>115</v>
       </c>
     </row>
     <row r="593" ht="20" customHeight="1">
@@ -15853,7 +15853,7 @@
         </is>
       </c>
       <c r="E593" s="23" t="n">
-        <v>218</v>
+        <v>224</v>
       </c>
     </row>
     <row r="594" ht="20" customHeight="1">
@@ -15878,7 +15878,7 @@
         </is>
       </c>
       <c r="E594" s="20" t="n">
-        <v>184</v>
+        <v>111</v>
       </c>
     </row>
     <row r="595" ht="20" customHeight="1">
@@ -15903,7 +15903,7 @@
         </is>
       </c>
       <c r="E595" s="23" t="n">
-        <v>191</v>
+        <v>147</v>
       </c>
     </row>
     <row r="596" ht="20" customHeight="1">
@@ -15928,7 +15928,7 @@
         </is>
       </c>
       <c r="E596" s="20" t="n">
-        <v>187</v>
+        <v>168</v>
       </c>
     </row>
     <row r="597" ht="20" customHeight="1">
@@ -15953,7 +15953,7 @@
         </is>
       </c>
       <c r="E597" s="23" t="n">
-        <v>206</v>
+        <v>162</v>
       </c>
     </row>
     <row r="598" ht="20" customHeight="1">
@@ -15978,7 +15978,7 @@
         </is>
       </c>
       <c r="E598" s="20" t="n">
-        <v>180</v>
+        <v>215</v>
       </c>
     </row>
     <row r="599" ht="20" customHeight="1">
@@ -16003,7 +16003,7 @@
         </is>
       </c>
       <c r="E599" s="23" t="n">
-        <v>136</v>
+        <v>225</v>
       </c>
     </row>
     <row r="600" ht="20" customHeight="1">
@@ -16028,7 +16028,7 @@
         </is>
       </c>
       <c r="E600" s="20" t="n">
-        <v>216</v>
+        <v>160</v>
       </c>
     </row>
     <row r="601" ht="20" customHeight="1">
@@ -16053,7 +16053,7 @@
         </is>
       </c>
       <c r="E601" s="23" t="n">
-        <v>125</v>
+        <v>152</v>
       </c>
     </row>
     <row r="602" ht="20" customHeight="1">
@@ -16078,7 +16078,7 @@
         </is>
       </c>
       <c r="E602" s="20" t="n">
-        <v>199</v>
+        <v>239</v>
       </c>
     </row>
     <row r="603" ht="20" customHeight="1">
@@ -16103,7 +16103,7 @@
         </is>
       </c>
       <c r="E603" s="23" t="n">
-        <v>114</v>
+        <v>237</v>
       </c>
     </row>
     <row r="604" ht="20" customHeight="1">
@@ -16153,7 +16153,7 @@
         </is>
       </c>
       <c r="E605" s="23" t="n">
-        <v>144</v>
+        <v>196</v>
       </c>
     </row>
     <row r="606" ht="20" customHeight="1">
@@ -16178,7 +16178,7 @@
         </is>
       </c>
       <c r="E606" s="20" t="n">
-        <v>144</v>
+        <v>216</v>
       </c>
     </row>
     <row r="607" ht="20" customHeight="1">
@@ -16203,7 +16203,7 @@
         </is>
       </c>
       <c r="E607" s="23" t="n">
-        <v>190</v>
+        <v>220</v>
       </c>
     </row>
     <row r="608" ht="20" customHeight="1">
@@ -16228,7 +16228,7 @@
         </is>
       </c>
       <c r="E608" s="20" t="n">
-        <v>235</v>
+        <v>145</v>
       </c>
     </row>
     <row r="609" ht="20" customHeight="1">
@@ -16253,7 +16253,7 @@
         </is>
       </c>
       <c r="E609" s="23" t="n">
-        <v>225</v>
+        <v>178</v>
       </c>
     </row>
     <row r="610" ht="20" customHeight="1">
@@ -16278,7 +16278,7 @@
         </is>
       </c>
       <c r="E610" s="20" t="n">
-        <v>193</v>
+        <v>226</v>
       </c>
     </row>
     <row r="611" ht="20" customHeight="1">
@@ -16303,7 +16303,7 @@
         </is>
       </c>
       <c r="E611" s="23" t="n">
-        <v>189</v>
+        <v>120</v>
       </c>
     </row>
     <row r="612" ht="20" customHeight="1">
@@ -16328,7 +16328,7 @@
         </is>
       </c>
       <c r="E612" s="20" t="n">
-        <v>116</v>
+        <v>194</v>
       </c>
     </row>
     <row r="613" ht="20" customHeight="1">
@@ -16353,7 +16353,7 @@
         </is>
       </c>
       <c r="E613" s="23" t="n">
-        <v>188</v>
+        <v>182</v>
       </c>
     </row>
     <row r="614" ht="20" customHeight="1">
@@ -16378,7 +16378,7 @@
         </is>
       </c>
       <c r="E614" s="20" t="n">
-        <v>118</v>
+        <v>232</v>
       </c>
     </row>
     <row r="615" ht="20" customHeight="1">
@@ -16403,7 +16403,7 @@
         </is>
       </c>
       <c r="E615" s="23" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
     </row>
     <row r="616" ht="20" customHeight="1">
@@ -16428,7 +16428,7 @@
         </is>
       </c>
       <c r="E616" s="20" t="n">
-        <v>124</v>
+        <v>238</v>
       </c>
     </row>
     <row r="617" ht="20" customHeight="1">
@@ -16453,7 +16453,7 @@
         </is>
       </c>
       <c r="E617" s="23" t="n">
-        <v>146</v>
+        <v>219</v>
       </c>
     </row>
     <row r="618" ht="20" customHeight="1">
@@ -16478,7 +16478,7 @@
         </is>
       </c>
       <c r="E618" s="20" t="n">
-        <v>134</v>
+        <v>163</v>
       </c>
     </row>
     <row r="619" ht="20" customHeight="1">
@@ -16503,7 +16503,7 @@
         </is>
       </c>
       <c r="E619" s="23" t="n">
-        <v>233</v>
+        <v>130</v>
       </c>
     </row>
     <row r="620" ht="20" customHeight="1">
@@ -16528,7 +16528,7 @@
         </is>
       </c>
       <c r="E620" s="20" t="n">
-        <v>163</v>
+        <v>129</v>
       </c>
     </row>
     <row r="621" ht="20" customHeight="1">
@@ -16553,7 +16553,7 @@
         </is>
       </c>
       <c r="E621" s="23" t="n">
-        <v>237</v>
+        <v>193</v>
       </c>
     </row>
     <row r="622" ht="20" customHeight="1">
@@ -16578,7 +16578,7 @@
         </is>
       </c>
       <c r="E622" s="20" t="n">
-        <v>165</v>
+        <v>210</v>
       </c>
     </row>
     <row r="623" ht="20" customHeight="1">
@@ -16603,7 +16603,7 @@
         </is>
       </c>
       <c r="E623" s="23" t="n">
-        <v>227</v>
+        <v>120</v>
       </c>
     </row>
     <row r="624" ht="20" customHeight="1">
@@ -16628,7 +16628,7 @@
         </is>
       </c>
       <c r="E624" s="20" t="n">
-        <v>230</v>
+        <v>150</v>
       </c>
     </row>
     <row r="625" ht="20" customHeight="1">
@@ -16653,7 +16653,7 @@
         </is>
       </c>
       <c r="E625" s="23" t="n">
-        <v>238</v>
+        <v>139</v>
       </c>
     </row>
     <row r="626" ht="20" customHeight="1">
@@ -16678,7 +16678,7 @@
         </is>
       </c>
       <c r="E626" s="20" t="n">
-        <v>234</v>
+        <v>139</v>
       </c>
     </row>
     <row r="627" ht="20" customHeight="1">
@@ -16703,7 +16703,7 @@
         </is>
       </c>
       <c r="E627" s="23" t="n">
-        <v>226</v>
+        <v>211</v>
       </c>
     </row>
     <row r="628" ht="20" customHeight="1">
@@ -16728,7 +16728,7 @@
         </is>
       </c>
       <c r="E628" s="20" t="n">
-        <v>235</v>
+        <v>211</v>
       </c>
     </row>
     <row r="629" ht="20" customHeight="1">
@@ -16753,7 +16753,7 @@
         </is>
       </c>
       <c r="E629" s="23" t="n">
-        <v>190</v>
+        <v>127</v>
       </c>
     </row>
     <row r="630" ht="20" customHeight="1">
@@ -16778,7 +16778,7 @@
         </is>
       </c>
       <c r="E630" s="20" t="n">
-        <v>232</v>
+        <v>223</v>
       </c>
     </row>
     <row r="631" ht="20" customHeight="1">
@@ -16803,7 +16803,7 @@
         </is>
       </c>
       <c r="E631" s="23" t="n">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="632" ht="20" customHeight="1">
@@ -16828,7 +16828,7 @@
         </is>
       </c>
       <c r="E632" s="20" t="n">
-        <v>179</v>
+        <v>190</v>
       </c>
     </row>
     <row r="633" ht="20" customHeight="1">
@@ -16853,7 +16853,7 @@
         </is>
       </c>
       <c r="E633" s="23" t="n">
-        <v>224</v>
+        <v>140</v>
       </c>
     </row>
     <row r="634" ht="20" customHeight="1">
@@ -16878,7 +16878,7 @@
         </is>
       </c>
       <c r="E634" s="20" t="n">
-        <v>211</v>
+        <v>187</v>
       </c>
     </row>
     <row r="635" ht="20" customHeight="1">
@@ -16903,7 +16903,7 @@
         </is>
       </c>
       <c r="E635" s="23" t="n">
-        <v>190</v>
+        <v>204</v>
       </c>
     </row>
     <row r="636" ht="20" customHeight="1">
@@ -16928,7 +16928,7 @@
         </is>
       </c>
       <c r="E636" s="20" t="n">
-        <v>211</v>
+        <v>234</v>
       </c>
     </row>
     <row r="637" ht="20" customHeight="1">
@@ -16953,7 +16953,7 @@
         </is>
       </c>
       <c r="E637" s="23" t="n">
-        <v>235</v>
+        <v>164</v>
       </c>
     </row>
     <row r="638" ht="20" customHeight="1">
@@ -16978,7 +16978,7 @@
         </is>
       </c>
       <c r="E638" s="20" t="n">
-        <v>148</v>
+        <v>207</v>
       </c>
     </row>
     <row r="639" ht="20" customHeight="1">
@@ -17003,7 +17003,7 @@
         </is>
       </c>
       <c r="E639" s="23" t="n">
-        <v>165</v>
+        <v>198</v>
       </c>
     </row>
     <row r="640" ht="20" customHeight="1">
@@ -17028,7 +17028,7 @@
         </is>
       </c>
       <c r="E640" s="20" t="n">
-        <v>154</v>
+        <v>165</v>
       </c>
     </row>
     <row r="641" ht="20" customHeight="1">
@@ -17053,7 +17053,7 @@
         </is>
       </c>
       <c r="E641" s="23" t="n">
-        <v>168</v>
+        <v>229</v>
       </c>
     </row>
     <row r="642" ht="20" customHeight="1">
@@ -17078,7 +17078,7 @@
         </is>
       </c>
       <c r="E642" s="20" t="n">
-        <v>193</v>
+        <v>126</v>
       </c>
     </row>
     <row r="643" ht="20" customHeight="1">
@@ -17103,7 +17103,7 @@
         </is>
       </c>
       <c r="E643" s="23" t="n">
-        <v>132</v>
+        <v>204</v>
       </c>
     </row>
     <row r="644" ht="20" customHeight="1">
@@ -17128,7 +17128,7 @@
         </is>
       </c>
       <c r="E644" s="20" t="n">
-        <v>144</v>
+        <v>238</v>
       </c>
     </row>
     <row r="645" ht="20" customHeight="1">
@@ -17153,7 +17153,7 @@
         </is>
       </c>
       <c r="E645" s="23" t="n">
-        <v>119</v>
+        <v>127</v>
       </c>
     </row>
     <row r="646" ht="20" customHeight="1">
@@ -17178,7 +17178,7 @@
         </is>
       </c>
       <c r="E646" s="20" t="n">
-        <v>180</v>
+        <v>223</v>
       </c>
     </row>
     <row r="647" ht="20" customHeight="1">
@@ -17203,7 +17203,7 @@
         </is>
       </c>
       <c r="E647" s="23" t="n">
-        <v>208</v>
+        <v>148</v>
       </c>
     </row>
     <row r="648" ht="20" customHeight="1">
@@ -17228,7 +17228,7 @@
         </is>
       </c>
       <c r="E648" s="20" t="n">
-        <v>203</v>
+        <v>208</v>
       </c>
     </row>
     <row r="649" ht="20" customHeight="1">
@@ -17253,7 +17253,7 @@
         </is>
       </c>
       <c r="E649" s="23" t="n">
-        <v>175</v>
+        <v>112</v>
       </c>
     </row>
     <row r="650" ht="20" customHeight="1">
@@ -17278,7 +17278,7 @@
         </is>
       </c>
       <c r="E650" s="20" t="n">
-        <v>201</v>
+        <v>139</v>
       </c>
     </row>
     <row r="651" ht="20" customHeight="1">
@@ -17303,7 +17303,7 @@
         </is>
       </c>
       <c r="E651" s="23" t="n">
-        <v>122</v>
+        <v>175</v>
       </c>
     </row>
     <row r="652" ht="20" customHeight="1">
@@ -17328,7 +17328,7 @@
         </is>
       </c>
       <c r="E652" s="20" t="n">
-        <v>209</v>
+        <v>232</v>
       </c>
     </row>
     <row r="653" ht="20" customHeight="1">
@@ -17353,7 +17353,7 @@
         </is>
       </c>
       <c r="E653" s="23" t="n">
-        <v>212</v>
+        <v>168</v>
       </c>
     </row>
     <row r="654" ht="20" customHeight="1">
@@ -17378,7 +17378,7 @@
         </is>
       </c>
       <c r="E654" s="20" t="n">
-        <v>218</v>
+        <v>121</v>
       </c>
     </row>
     <row r="655" ht="20" customHeight="1">
@@ -17403,7 +17403,7 @@
         </is>
       </c>
       <c r="E655" s="23" t="n">
-        <v>168</v>
+        <v>173</v>
       </c>
     </row>
     <row r="656" ht="20" customHeight="1">
@@ -17428,7 +17428,7 @@
         </is>
       </c>
       <c r="E656" s="20" t="n">
-        <v>178</v>
+        <v>224</v>
       </c>
     </row>
     <row r="657" ht="20" customHeight="1">
@@ -17453,7 +17453,7 @@
         </is>
       </c>
       <c r="E657" s="23" t="n">
-        <v>219</v>
+        <v>122</v>
       </c>
     </row>
     <row r="658" ht="20" customHeight="1">
@@ -17478,7 +17478,7 @@
         </is>
       </c>
       <c r="E658" s="20" t="n">
-        <v>198</v>
+        <v>144</v>
       </c>
     </row>
     <row r="659" ht="20" customHeight="1">
@@ -17503,7 +17503,7 @@
         </is>
       </c>
       <c r="E659" s="23" t="n">
-        <v>228</v>
+        <v>148</v>
       </c>
     </row>
     <row r="660" ht="20" customHeight="1">
@@ -17528,7 +17528,7 @@
         </is>
       </c>
       <c r="E660" s="20" t="n">
-        <v>122</v>
+        <v>159</v>
       </c>
     </row>
     <row r="661" ht="20" customHeight="1">
@@ -17553,7 +17553,7 @@
         </is>
       </c>
       <c r="E661" s="23" t="n">
-        <v>198</v>
+        <v>211</v>
       </c>
     </row>
     <row r="662" ht="20" customHeight="1">
@@ -17578,7 +17578,7 @@
         </is>
       </c>
       <c r="E662" s="20" t="n">
-        <v>238</v>
+        <v>208</v>
       </c>
     </row>
     <row r="663" ht="20" customHeight="1">
@@ -17603,7 +17603,7 @@
         </is>
       </c>
       <c r="E663" s="23" t="n">
-        <v>153</v>
+        <v>196</v>
       </c>
     </row>
     <row r="664" ht="20" customHeight="1">
@@ -17628,7 +17628,7 @@
         </is>
       </c>
       <c r="E664" s="20" t="n">
-        <v>235</v>
+        <v>151</v>
       </c>
     </row>
     <row r="665" ht="20" customHeight="1">
@@ -17653,7 +17653,7 @@
         </is>
       </c>
       <c r="E665" s="23" t="n">
-        <v>194</v>
+        <v>149</v>
       </c>
     </row>
     <row r="666" ht="20" customHeight="1">
@@ -17678,7 +17678,7 @@
         </is>
       </c>
       <c r="E666" s="20" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="667" ht="20" customHeight="1">
@@ -17703,7 +17703,7 @@
         </is>
       </c>
       <c r="E667" s="23" t="n">
-        <v>212</v>
+        <v>182</v>
       </c>
     </row>
     <row r="668" ht="20" customHeight="1">
@@ -17728,7 +17728,7 @@
         </is>
       </c>
       <c r="E668" s="20" t="n">
-        <v>176</v>
+        <v>157</v>
       </c>
     </row>
     <row r="669" ht="20" customHeight="1">
@@ -17753,7 +17753,7 @@
         </is>
       </c>
       <c r="E669" s="23" t="n">
-        <v>141</v>
+        <v>126</v>
       </c>
     </row>
     <row r="670" ht="20" customHeight="1">
@@ -17778,7 +17778,7 @@
         </is>
       </c>
       <c r="E670" s="20" t="n">
-        <v>177</v>
+        <v>185</v>
       </c>
     </row>
     <row r="671" ht="20" customHeight="1">
@@ -17803,7 +17803,7 @@
         </is>
       </c>
       <c r="E671" s="23" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="672" ht="20" customHeight="1">
@@ -17828,7 +17828,7 @@
         </is>
       </c>
       <c r="E672" s="20" t="n">
-        <v>132</v>
+        <v>164</v>
       </c>
     </row>
     <row r="673" ht="20" customHeight="1">
@@ -17853,7 +17853,7 @@
         </is>
       </c>
       <c r="E673" s="23" t="n">
-        <v>220</v>
+        <v>142</v>
       </c>
     </row>
     <row r="674" ht="20" customHeight="1">
@@ -17878,7 +17878,7 @@
         </is>
       </c>
       <c r="E674" s="20" t="n">
-        <v>147</v>
+        <v>228</v>
       </c>
     </row>
     <row r="675" ht="20" customHeight="1">
@@ -17903,7 +17903,7 @@
         </is>
       </c>
       <c r="E675" s="23" t="n">
-        <v>155</v>
+        <v>185</v>
       </c>
     </row>
     <row r="676" ht="20" customHeight="1">
@@ -17928,7 +17928,7 @@
         </is>
       </c>
       <c r="E676" s="20" t="n">
-        <v>135</v>
+        <v>229</v>
       </c>
     </row>
     <row r="677" ht="20" customHeight="1">
@@ -17953,7 +17953,7 @@
         </is>
       </c>
       <c r="E677" s="23" t="n">
-        <v>138</v>
+        <v>145</v>
       </c>
     </row>
     <row r="678" ht="20" customHeight="1">
@@ -17978,7 +17978,7 @@
         </is>
       </c>
       <c r="E678" s="20" t="n">
-        <v>167</v>
+        <v>221</v>
       </c>
     </row>
     <row r="679" ht="20" customHeight="1">
@@ -18003,7 +18003,7 @@
         </is>
       </c>
       <c r="E679" s="23" t="n">
-        <v>143</v>
+        <v>229</v>
       </c>
     </row>
     <row r="680" ht="20" customHeight="1">
@@ -18028,7 +18028,7 @@
         </is>
       </c>
       <c r="E680" s="20" t="n">
-        <v>236</v>
+        <v>168</v>
       </c>
     </row>
     <row r="681" ht="20" customHeight="1">
@@ -18053,7 +18053,7 @@
         </is>
       </c>
       <c r="E681" s="23" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="682" ht="20" customHeight="1">
@@ -18078,7 +18078,7 @@
         </is>
       </c>
       <c r="E682" s="20" t="n">
-        <v>238</v>
+        <v>226</v>
       </c>
     </row>
     <row r="683" ht="20" customHeight="1">
@@ -18103,7 +18103,7 @@
         </is>
       </c>
       <c r="E683" s="23" t="n">
-        <v>210</v>
+        <v>181</v>
       </c>
     </row>
     <row r="684" ht="20" customHeight="1">
@@ -18128,7 +18128,7 @@
         </is>
       </c>
       <c r="E684" s="20" t="n">
-        <v>197</v>
+        <v>122</v>
       </c>
     </row>
     <row r="685" ht="20" customHeight="1">
@@ -18153,7 +18153,7 @@
         </is>
       </c>
       <c r="E685" s="23" t="n">
-        <v>226</v>
+        <v>214</v>
       </c>
     </row>
     <row r="686" ht="20" customHeight="1">
@@ -18178,7 +18178,7 @@
         </is>
       </c>
       <c r="E686" s="20" t="n">
-        <v>210</v>
+        <v>188</v>
       </c>
     </row>
     <row r="687" ht="20" customHeight="1">
@@ -18203,7 +18203,7 @@
         </is>
       </c>
       <c r="E687" s="23" t="n">
-        <v>117</v>
+        <v>136</v>
       </c>
     </row>
     <row r="688" ht="20" customHeight="1">
@@ -18228,7 +18228,7 @@
         </is>
       </c>
       <c r="E688" s="20" t="n">
-        <v>165</v>
+        <v>221</v>
       </c>
     </row>
     <row r="689" ht="20" customHeight="1">
@@ -18253,7 +18253,7 @@
         </is>
       </c>
       <c r="E689" s="23" t="n">
-        <v>190</v>
+        <v>229</v>
       </c>
     </row>
     <row r="690" ht="20" customHeight="1">
@@ -18278,7 +18278,7 @@
         </is>
       </c>
       <c r="E690" s="20" t="n">
-        <v>184</v>
+        <v>237</v>
       </c>
     </row>
     <row r="691" ht="20" customHeight="1">
@@ -18303,7 +18303,7 @@
         </is>
       </c>
       <c r="E691" s="23" t="n">
-        <v>147</v>
+        <v>227</v>
       </c>
     </row>
     <row r="692" ht="20" customHeight="1">
@@ -18328,7 +18328,7 @@
         </is>
       </c>
       <c r="E692" s="20" t="n">
-        <v>149</v>
+        <v>176</v>
       </c>
     </row>
     <row r="693" ht="20" customHeight="1">
@@ -18353,7 +18353,7 @@
         </is>
       </c>
       <c r="E693" s="23" t="n">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="694" ht="20" customHeight="1">
@@ -18378,7 +18378,7 @@
         </is>
       </c>
       <c r="E694" s="20" t="n">
-        <v>185</v>
+        <v>159</v>
       </c>
     </row>
     <row r="695" ht="20" customHeight="1">
@@ -18403,7 +18403,7 @@
         </is>
       </c>
       <c r="E695" s="23" t="n">
-        <v>166</v>
+        <v>114</v>
       </c>
     </row>
     <row r="696" ht="20" customHeight="1">
@@ -18428,7 +18428,7 @@
         </is>
       </c>
       <c r="E696" s="20" t="n">
-        <v>204</v>
+        <v>110</v>
       </c>
     </row>
     <row r="697" ht="20" customHeight="1">
@@ -18453,7 +18453,7 @@
         </is>
       </c>
       <c r="E697" s="23" t="n">
-        <v>169</v>
+        <v>201</v>
       </c>
     </row>
     <row r="698" ht="20" customHeight="1">
@@ -18478,7 +18478,7 @@
         </is>
       </c>
       <c r="E698" s="20" t="n">
-        <v>188</v>
+        <v>213</v>
       </c>
     </row>
     <row r="699" ht="20" customHeight="1">
@@ -18503,7 +18503,7 @@
         </is>
       </c>
       <c r="E699" s="23" t="n">
-        <v>193</v>
+        <v>204</v>
       </c>
     </row>
     <row r="700" ht="20" customHeight="1">
@@ -18528,7 +18528,7 @@
         </is>
       </c>
       <c r="E700" s="20" t="n">
-        <v>223</v>
+        <v>137</v>
       </c>
     </row>
     <row r="701" ht="20" customHeight="1">
@@ -18553,7 +18553,7 @@
         </is>
       </c>
       <c r="E701" s="23" t="n">
-        <v>204</v>
+        <v>152</v>
       </c>
     </row>
     <row r="702" ht="20" customHeight="1">
@@ -18578,7 +18578,7 @@
         </is>
       </c>
       <c r="E702" s="20" t="n">
-        <v>126</v>
+        <v>149</v>
       </c>
     </row>
     <row r="703" ht="20" customHeight="1">
@@ -18603,7 +18603,7 @@
         </is>
       </c>
       <c r="E703" s="23" t="n">
-        <v>128</v>
+        <v>196</v>
       </c>
     </row>
     <row r="704" ht="20" customHeight="1">
@@ -18628,7 +18628,7 @@
         </is>
       </c>
       <c r="E704" s="20" t="n">
-        <v>152</v>
+        <v>171</v>
       </c>
     </row>
     <row r="705" ht="20" customHeight="1">
@@ -18653,7 +18653,7 @@
         </is>
       </c>
       <c r="E705" s="23" t="n">
-        <v>144</v>
+        <v>134</v>
       </c>
     </row>
     <row r="706" ht="20" customHeight="1">
@@ -18678,7 +18678,7 @@
         </is>
       </c>
       <c r="E706" s="20" t="n">
-        <v>149</v>
+        <v>223</v>
       </c>
     </row>
     <row r="707" ht="20" customHeight="1">
@@ -18703,7 +18703,7 @@
         </is>
       </c>
       <c r="E707" s="23" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="708" ht="20" customHeight="1">
@@ -18728,7 +18728,7 @@
         </is>
       </c>
       <c r="E708" s="20" t="n">
-        <v>119</v>
+        <v>201</v>
       </c>
     </row>
     <row r="709" ht="20" customHeight="1">
@@ -18753,7 +18753,7 @@
         </is>
       </c>
       <c r="E709" s="23" t="n">
-        <v>142</v>
+        <v>230</v>
       </c>
     </row>
     <row r="710" ht="20" customHeight="1">
@@ -18778,7 +18778,7 @@
         </is>
       </c>
       <c r="E710" s="20" t="n">
-        <v>237</v>
+        <v>126</v>
       </c>
     </row>
     <row r="711" ht="20" customHeight="1">
@@ -18803,7 +18803,7 @@
         </is>
       </c>
       <c r="E711" s="23" t="n">
-        <v>139</v>
+        <v>186</v>
       </c>
     </row>
     <row r="712" ht="20" customHeight="1">
@@ -18828,7 +18828,7 @@
         </is>
       </c>
       <c r="E712" s="20" t="n">
-        <v>148</v>
+        <v>157</v>
       </c>
     </row>
     <row r="713" ht="20" customHeight="1">
@@ -18853,7 +18853,7 @@
         </is>
       </c>
       <c r="E713" s="23" t="n">
-        <v>126</v>
+        <v>142</v>
       </c>
     </row>
     <row r="714" ht="20" customHeight="1">
@@ -18878,7 +18878,7 @@
         </is>
       </c>
       <c r="E714" s="20" t="n">
-        <v>167</v>
+        <v>224</v>
       </c>
     </row>
     <row r="715" ht="20" customHeight="1">
@@ -18903,7 +18903,7 @@
         </is>
       </c>
       <c r="E715" s="23" t="n">
-        <v>112</v>
+        <v>224</v>
       </c>
     </row>
     <row r="716" ht="20" customHeight="1">
@@ -18928,7 +18928,7 @@
         </is>
       </c>
       <c r="E716" s="20" t="n">
-        <v>208</v>
+        <v>192</v>
       </c>
     </row>
     <row r="717" ht="20" customHeight="1">
@@ -18953,7 +18953,7 @@
         </is>
       </c>
       <c r="E717" s="23" t="n">
-        <v>169</v>
+        <v>112</v>
       </c>
     </row>
     <row r="718" ht="20" customHeight="1">
@@ -18978,7 +18978,7 @@
         </is>
       </c>
       <c r="E718" s="20" t="n">
-        <v>198</v>
+        <v>204</v>
       </c>
     </row>
     <row r="719" ht="20" customHeight="1">
@@ -19003,7 +19003,7 @@
         </is>
       </c>
       <c r="E719" s="23" t="n">
-        <v>127</v>
+        <v>219</v>
       </c>
     </row>
     <row r="720" ht="20" customHeight="1">
@@ -19028,7 +19028,7 @@
         </is>
       </c>
       <c r="E720" s="20" t="n">
-        <v>191</v>
+        <v>210</v>
       </c>
     </row>
     <row r="721" ht="20" customHeight="1">
@@ -19053,7 +19053,7 @@
         </is>
       </c>
       <c r="E721" s="23" t="n">
-        <v>154</v>
+        <v>235</v>
       </c>
     </row>
     <row r="722" ht="20" customHeight="1">
@@ -19078,7 +19078,7 @@
         </is>
       </c>
       <c r="E722" s="20" t="n">
-        <v>204</v>
+        <v>170</v>
       </c>
     </row>
     <row r="723" ht="20" customHeight="1">
@@ -19103,7 +19103,7 @@
         </is>
       </c>
       <c r="E723" s="23" t="n">
-        <v>217</v>
+        <v>211</v>
       </c>
     </row>
     <row r="724" ht="20" customHeight="1">
@@ -19128,7 +19128,7 @@
         </is>
       </c>
       <c r="E724" s="20" t="n">
-        <v>207</v>
+        <v>133</v>
       </c>
     </row>
     <row r="725" ht="20" customHeight="1">
@@ -19153,7 +19153,7 @@
         </is>
       </c>
       <c r="E725" s="23" t="n">
-        <v>123</v>
+        <v>233</v>
       </c>
     </row>
     <row r="726" ht="20" customHeight="1">
@@ -19178,7 +19178,7 @@
         </is>
       </c>
       <c r="E726" s="20" t="n">
-        <v>171</v>
+        <v>215</v>
       </c>
     </row>
     <row r="727" ht="20" customHeight="1">
@@ -19203,7 +19203,7 @@
         </is>
       </c>
       <c r="E727" s="23" t="n">
-        <v>136</v>
+        <v>198</v>
       </c>
     </row>
     <row r="728" ht="20" customHeight="1">
@@ -19228,7 +19228,7 @@
         </is>
       </c>
       <c r="E728" s="20" t="n">
-        <v>156</v>
+        <v>209</v>
       </c>
     </row>
     <row r="729" ht="20" customHeight="1">
@@ -19253,7 +19253,7 @@
         </is>
       </c>
       <c r="E729" s="23" t="n">
-        <v>155</v>
+        <v>147</v>
       </c>
     </row>
     <row r="730" ht="20" customHeight="1">
@@ -19278,7 +19278,7 @@
         </is>
       </c>
       <c r="E730" s="20" t="n">
-        <v>214</v>
+        <v>187</v>
       </c>
     </row>
     <row r="731" ht="20" customHeight="1">
@@ -19303,7 +19303,7 @@
         </is>
       </c>
       <c r="E731" s="23" t="n">
-        <v>227</v>
+        <v>165</v>
       </c>
     </row>
     <row r="732" ht="20" customHeight="1">
@@ -19328,7 +19328,7 @@
         </is>
       </c>
       <c r="E732" s="20" t="n">
-        <v>168</v>
+        <v>185</v>
       </c>
     </row>
     <row r="733" ht="20" customHeight="1">
@@ -19353,7 +19353,7 @@
         </is>
       </c>
       <c r="E733" s="23" t="n">
-        <v>219</v>
+        <v>181</v>
       </c>
     </row>
     <row r="734" ht="20" customHeight="1">
@@ -19378,7 +19378,7 @@
         </is>
       </c>
       <c r="E734" s="20" t="n">
-        <v>199</v>
+        <v>135</v>
       </c>
     </row>
     <row r="735" ht="20" customHeight="1">
@@ -19403,7 +19403,7 @@
         </is>
       </c>
       <c r="E735" s="23" t="n">
-        <v>230</v>
+        <v>133</v>
       </c>
     </row>
     <row r="736" ht="20" customHeight="1">
@@ -19428,7 +19428,7 @@
         </is>
       </c>
       <c r="E736" s="20" t="n">
-        <v>129</v>
+        <v>187</v>
       </c>
     </row>
     <row r="737" ht="20" customHeight="1">
@@ -19453,7 +19453,7 @@
         </is>
       </c>
       <c r="E737" s="23" t="n">
-        <v>160</v>
+        <v>216</v>
       </c>
     </row>
     <row r="738" ht="20" customHeight="1">
@@ -19478,7 +19478,7 @@
         </is>
       </c>
       <c r="E738" s="20" t="n">
-        <v>142</v>
+        <v>206</v>
       </c>
     </row>
     <row r="739" ht="20" customHeight="1">
@@ -19503,7 +19503,7 @@
         </is>
       </c>
       <c r="E739" s="23" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="740" ht="20" customHeight="1">
@@ -19528,7 +19528,7 @@
         </is>
       </c>
       <c r="E740" s="20" t="n">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="741" ht="20" customHeight="1">
@@ -19553,7 +19553,7 @@
         </is>
       </c>
       <c r="E741" s="23" t="n">
-        <v>117</v>
+        <v>224</v>
       </c>
     </row>
     <row r="742" ht="20" customHeight="1">
@@ -19578,7 +19578,7 @@
         </is>
       </c>
       <c r="E742" s="20" t="n">
-        <v>183</v>
+        <v>117</v>
       </c>
     </row>
     <row r="743" ht="20" customHeight="1">
@@ -19603,7 +19603,7 @@
         </is>
       </c>
       <c r="E743" s="23" t="n">
-        <v>225</v>
+        <v>216</v>
       </c>
     </row>
     <row r="744" ht="20" customHeight="1">
@@ -19628,7 +19628,7 @@
         </is>
       </c>
       <c r="E744" s="20" t="n">
-        <v>219</v>
+        <v>239</v>
       </c>
     </row>
     <row r="745" ht="20" customHeight="1">
@@ -19653,7 +19653,7 @@
         </is>
       </c>
       <c r="E745" s="23" t="n">
-        <v>215</v>
+        <v>123</v>
       </c>
     </row>
     <row r="746" ht="20" customHeight="1">
@@ -19678,7 +19678,7 @@
         </is>
       </c>
       <c r="E746" s="20" t="n">
-        <v>207</v>
+        <v>219</v>
       </c>
     </row>
     <row r="747" ht="20" customHeight="1">
@@ -19703,7 +19703,7 @@
         </is>
       </c>
       <c r="E747" s="23" t="n">
-        <v>118</v>
+        <v>229</v>
       </c>
     </row>
     <row r="748" ht="20" customHeight="1">
@@ -19728,7 +19728,7 @@
         </is>
       </c>
       <c r="E748" s="20" t="n">
-        <v>228</v>
+        <v>185</v>
       </c>
     </row>
     <row r="749" ht="20" customHeight="1">
@@ -19753,7 +19753,7 @@
         </is>
       </c>
       <c r="E749" s="23" t="n">
-        <v>198</v>
+        <v>148</v>
       </c>
     </row>
     <row r="750" ht="20" customHeight="1">
@@ -19778,7 +19778,7 @@
         </is>
       </c>
       <c r="E750" s="20" t="n">
-        <v>171</v>
+        <v>229</v>
       </c>
     </row>
     <row r="751" ht="20" customHeight="1">
@@ -19803,7 +19803,7 @@
         </is>
       </c>
       <c r="E751" s="23" t="n">
-        <v>131</v>
+        <v>231</v>
       </c>
     </row>
     <row r="752" ht="20" customHeight="1">
@@ -19828,7 +19828,7 @@
         </is>
       </c>
       <c r="E752" s="20" t="n">
-        <v>234</v>
+        <v>119</v>
       </c>
     </row>
     <row r="753" ht="20" customHeight="1">
@@ -19853,7 +19853,7 @@
         </is>
       </c>
       <c r="E753" s="23" t="n">
-        <v>201</v>
+        <v>174</v>
       </c>
     </row>
     <row r="754" ht="20" customHeight="1">
@@ -19878,7 +19878,7 @@
         </is>
       </c>
       <c r="E754" s="20" t="n">
-        <v>140</v>
+        <v>161</v>
       </c>
     </row>
     <row r="755" ht="20" customHeight="1">
@@ -19903,7 +19903,7 @@
         </is>
       </c>
       <c r="E755" s="23" t="n">
-        <v>131</v>
+        <v>187</v>
       </c>
     </row>
     <row r="756" ht="20" customHeight="1">
@@ -19928,7 +19928,7 @@
         </is>
       </c>
       <c r="E756" s="20" t="n">
-        <v>141</v>
+        <v>156</v>
       </c>
     </row>
     <row r="757" ht="20" customHeight="1">
@@ -19953,7 +19953,7 @@
         </is>
       </c>
       <c r="E757" s="23" t="n">
-        <v>197</v>
+        <v>134</v>
       </c>
     </row>
     <row r="758" ht="20" customHeight="1">
@@ -19978,7 +19978,7 @@
         </is>
       </c>
       <c r="E758" s="20" t="n">
-        <v>194</v>
+        <v>156</v>
       </c>
     </row>
     <row r="759" ht="20" customHeight="1">
@@ -20003,7 +20003,7 @@
         </is>
       </c>
       <c r="E759" s="23" t="n">
-        <v>228</v>
+        <v>176</v>
       </c>
     </row>
     <row r="760" ht="20" customHeight="1">
@@ -20028,7 +20028,7 @@
         </is>
       </c>
       <c r="E760" s="20" t="n">
-        <v>210</v>
+        <v>150</v>
       </c>
     </row>
     <row r="761" ht="20" customHeight="1">
@@ -20053,7 +20053,7 @@
         </is>
       </c>
       <c r="E761" s="23" t="n">
-        <v>216</v>
+        <v>161</v>
       </c>
     </row>
     <row r="762" ht="20" customHeight="1">
@@ -20078,7 +20078,7 @@
         </is>
       </c>
       <c r="E762" s="20" t="n">
-        <v>153</v>
+        <v>198</v>
       </c>
     </row>
     <row r="763" ht="20" customHeight="1">
@@ -20103,7 +20103,7 @@
         </is>
       </c>
       <c r="E763" s="23" t="n">
-        <v>111</v>
+        <v>226</v>
       </c>
     </row>
     <row r="764" ht="20" customHeight="1">
@@ -20128,7 +20128,7 @@
         </is>
       </c>
       <c r="E764" s="20" t="n">
-        <v>208</v>
+        <v>228</v>
       </c>
     </row>
     <row r="765" ht="20" customHeight="1">
@@ -20153,7 +20153,7 @@
         </is>
       </c>
       <c r="E765" s="23" t="n">
-        <v>111</v>
+        <v>178</v>
       </c>
     </row>
     <row r="766" ht="20" customHeight="1">
@@ -20178,7 +20178,7 @@
         </is>
       </c>
       <c r="E766" s="20" t="n">
-        <v>129</v>
+        <v>180</v>
       </c>
     </row>
     <row r="767" ht="20" customHeight="1">
@@ -20203,7 +20203,7 @@
         </is>
       </c>
       <c r="E767" s="23" t="n">
-        <v>121</v>
+        <v>139</v>
       </c>
     </row>
     <row r="768" ht="20" customHeight="1">
@@ -20228,7 +20228,7 @@
         </is>
       </c>
       <c r="E768" s="20" t="n">
-        <v>206</v>
+        <v>170</v>
       </c>
     </row>
     <row r="769" ht="20" customHeight="1">
@@ -20253,7 +20253,7 @@
         </is>
       </c>
       <c r="E769" s="23" t="n">
-        <v>110</v>
+        <v>188</v>
       </c>
     </row>
     <row r="770" ht="20" customHeight="1">
@@ -20278,7 +20278,7 @@
         </is>
       </c>
       <c r="E770" s="20" t="n">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="771" ht="20" customHeight="1">
@@ -20303,7 +20303,7 @@
         </is>
       </c>
       <c r="E771" s="23" t="n">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="772" ht="20" customHeight="1">
@@ -20328,7 +20328,7 @@
         </is>
       </c>
       <c r="E772" s="20" t="n">
-        <v>224</v>
+        <v>235</v>
       </c>
     </row>
     <row r="773" ht="20" customHeight="1">
@@ -20353,7 +20353,7 @@
         </is>
       </c>
       <c r="E773" s="23" t="n">
-        <v>131</v>
+        <v>161</v>
       </c>
     </row>
     <row r="774" ht="20" customHeight="1">
@@ -20378,7 +20378,7 @@
         </is>
       </c>
       <c r="E774" s="20" t="n">
-        <v>153</v>
+        <v>135</v>
       </c>
     </row>
     <row r="775" ht="20" customHeight="1">
@@ -20403,7 +20403,7 @@
         </is>
       </c>
       <c r="E775" s="23" t="n">
-        <v>128</v>
+        <v>231</v>
       </c>
     </row>
     <row r="776" ht="20" customHeight="1">
@@ -20428,7 +20428,7 @@
         </is>
       </c>
       <c r="E776" s="20" t="n">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="777" ht="20" customHeight="1">
@@ -20453,7 +20453,7 @@
         </is>
       </c>
       <c r="E777" s="23" t="n">
-        <v>121</v>
+        <v>134</v>
       </c>
     </row>
     <row r="778" ht="20" customHeight="1">
@@ -20478,7 +20478,7 @@
         </is>
       </c>
       <c r="E778" s="20" t="n">
-        <v>154</v>
+        <v>111</v>
       </c>
     </row>
     <row r="779" ht="20" customHeight="1">
@@ -20503,7 +20503,7 @@
         </is>
       </c>
       <c r="E779" s="23" t="n">
-        <v>183</v>
+        <v>113</v>
       </c>
     </row>
     <row r="780" ht="20" customHeight="1">
@@ -20528,7 +20528,7 @@
         </is>
       </c>
       <c r="E780" s="20" t="n">
-        <v>174</v>
+        <v>226</v>
       </c>
     </row>
     <row r="781" ht="20" customHeight="1">
@@ -20553,7 +20553,7 @@
         </is>
       </c>
       <c r="E781" s="23" t="n">
-        <v>191</v>
+        <v>149</v>
       </c>
     </row>
     <row r="782" ht="20" customHeight="1">
@@ -20578,7 +20578,7 @@
         </is>
       </c>
       <c r="E782" s="20" t="n">
-        <v>173</v>
+        <v>179</v>
       </c>
     </row>
     <row r="783" ht="20" customHeight="1">
@@ -20603,7 +20603,7 @@
         </is>
       </c>
       <c r="E783" s="23" t="n">
-        <v>144</v>
+        <v>202</v>
       </c>
     </row>
     <row r="784" ht="20" customHeight="1">
@@ -20628,7 +20628,7 @@
         </is>
       </c>
       <c r="E784" s="20" t="n">
-        <v>231</v>
+        <v>193</v>
       </c>
     </row>
     <row r="785" ht="20" customHeight="1">
@@ -20653,7 +20653,7 @@
         </is>
       </c>
       <c r="E785" s="23" t="n">
-        <v>152</v>
+        <v>240</v>
       </c>
     </row>
     <row r="786" ht="20" customHeight="1">
@@ -20678,7 +20678,7 @@
         </is>
       </c>
       <c r="E786" s="20" t="n">
-        <v>118</v>
+        <v>131</v>
       </c>
     </row>
     <row r="787" ht="20" customHeight="1">
@@ -20703,7 +20703,7 @@
         </is>
       </c>
       <c r="E787" s="23" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="788" ht="20" customHeight="1">
@@ -20728,7 +20728,7 @@
         </is>
       </c>
       <c r="E788" s="20" t="n">
-        <v>228</v>
+        <v>218</v>
       </c>
     </row>
     <row r="789" ht="20" customHeight="1">
@@ -20753,7 +20753,7 @@
         </is>
       </c>
       <c r="E789" s="23" t="n">
-        <v>123</v>
+        <v>161</v>
       </c>
     </row>
     <row r="790" ht="20" customHeight="1">
@@ -20778,7 +20778,7 @@
         </is>
       </c>
       <c r="E790" s="20" t="n">
-        <v>132</v>
+        <v>237</v>
       </c>
     </row>
     <row r="791" ht="20" customHeight="1">
@@ -20803,7 +20803,7 @@
         </is>
       </c>
       <c r="E791" s="23" t="n">
-        <v>110</v>
+        <v>166</v>
       </c>
     </row>
     <row r="792" ht="20" customHeight="1">
@@ -20828,7 +20828,7 @@
         </is>
       </c>
       <c r="E792" s="20" t="n">
-        <v>179</v>
+        <v>207</v>
       </c>
     </row>
     <row r="793" ht="20" customHeight="1">
@@ -20853,7 +20853,7 @@
         </is>
       </c>
       <c r="E793" s="23" t="n">
-        <v>114</v>
+        <v>201</v>
       </c>
     </row>
     <row r="794" ht="20" customHeight="1">
@@ -20878,7 +20878,7 @@
         </is>
       </c>
       <c r="E794" s="20" t="n">
-        <v>225</v>
+        <v>193</v>
       </c>
     </row>
     <row r="795" ht="20" customHeight="1">
@@ -20903,7 +20903,7 @@
         </is>
       </c>
       <c r="E795" s="23" t="n">
-        <v>126</v>
+        <v>155</v>
       </c>
     </row>
     <row r="796" ht="20" customHeight="1">
@@ -20928,7 +20928,7 @@
         </is>
       </c>
       <c r="E796" s="20" t="n">
-        <v>236</v>
+        <v>123</v>
       </c>
     </row>
     <row r="797" ht="20" customHeight="1">
@@ -20953,7 +20953,7 @@
         </is>
       </c>
       <c r="E797" s="23" t="n">
-        <v>189</v>
+        <v>129</v>
       </c>
     </row>
     <row r="798" ht="20" customHeight="1">
@@ -20978,7 +20978,7 @@
         </is>
       </c>
       <c r="E798" s="20" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="799" ht="20" customHeight="1">
@@ -21003,7 +21003,7 @@
         </is>
       </c>
       <c r="E799" s="23" t="n">
-        <v>135</v>
+        <v>194</v>
       </c>
     </row>
     <row r="800" ht="20" customHeight="1">
@@ -21028,7 +21028,7 @@
         </is>
       </c>
       <c r="E800" s="20" t="n">
-        <v>215</v>
+        <v>155</v>
       </c>
     </row>
     <row r="801" ht="20" customHeight="1">
@@ -21053,7 +21053,7 @@
         </is>
       </c>
       <c r="E801" s="23" t="n">
-        <v>209</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>

--- a/Appium_E2E_Test_Report_Traverse.xlsx
+++ b/Appium_E2E_Test_Report_Traverse.xlsx
@@ -791,7 +791,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 07:47:32</t>
+          <t>2026-08-11 07:50:06</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="E2" s="20" t="n">
-        <v>200</v>
+        <v>223</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="E3" s="23" t="n">
-        <v>238</v>
+        <v>208</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="E4" s="20" t="n">
-        <v>174</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="E5" s="23" t="n">
-        <v>173</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="E6" s="20" t="n">
-        <v>217</v>
+        <v>168</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="E7" s="23" t="n">
-        <v>131</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -1228,7 +1228,7 @@
         </is>
       </c>
       <c r="E8" s="20" t="n">
-        <v>166</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="E9" s="23" t="n">
-        <v>217</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
@@ -1278,7 +1278,7 @@
         </is>
       </c>
       <c r="E10" s="20" t="n">
-        <v>153</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="E11" s="23" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
@@ -1328,7 +1328,7 @@
         </is>
       </c>
       <c r="E12" s="20" t="n">
-        <v>159</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="E13" s="23" t="n">
-        <v>119</v>
+        <v>189</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="E14" s="20" t="n">
-        <v>110</v>
+        <v>165</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="E15" s="23" t="n">
-        <v>208</v>
+        <v>239</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="E16" s="20" t="n">
-        <v>184</v>
+        <v>205</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="E17" s="23" t="n">
-        <v>135</v>
+        <v>233</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -1478,7 +1478,7 @@
         </is>
       </c>
       <c r="E18" s="20" t="n">
-        <v>151</v>
+        <v>192</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
@@ -1503,7 +1503,7 @@
         </is>
       </c>
       <c r="E19" s="23" t="n">
-        <v>128</v>
+        <v>222</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="E20" s="20" t="n">
-        <v>162</v>
+        <v>136</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="E21" s="23" t="n">
-        <v>204</v>
+        <v>161</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
@@ -1578,7 +1578,7 @@
         </is>
       </c>
       <c r="E22" s="20" t="n">
-        <v>158</v>
+        <v>213</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="E23" s="23" t="n">
-        <v>112</v>
+        <v>217</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
@@ -1628,7 +1628,7 @@
         </is>
       </c>
       <c r="E24" s="20" t="n">
-        <v>206</v>
+        <v>121</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="E25" s="23" t="n">
-        <v>189</v>
+        <v>176</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
@@ -1678,7 +1678,7 @@
         </is>
       </c>
       <c r="E26" s="20" t="n">
-        <v>190</v>
+        <v>166</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="E27" s="23" t="n">
-        <v>159</v>
+        <v>237</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="E28" s="20" t="n">
-        <v>139</v>
+        <v>212</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="E29" s="23" t="n">
-        <v>124</v>
+        <v>209</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="E30" s="20" t="n">
-        <v>229</v>
+        <v>151</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
@@ -1803,7 +1803,7 @@
         </is>
       </c>
       <c r="E31" s="23" t="n">
-        <v>215</v>
+        <v>159</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
@@ -1828,7 +1828,7 @@
         </is>
       </c>
       <c r="E32" s="20" t="n">
-        <v>143</v>
+        <v>235</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
@@ -1853,7 +1853,7 @@
         </is>
       </c>
       <c r="E33" s="23" t="n">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
@@ -1878,7 +1878,7 @@
         </is>
       </c>
       <c r="E34" s="20" t="n">
-        <v>149</v>
+        <v>163</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="E35" s="23" t="n">
-        <v>216</v>
+        <v>208</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="E36" s="20" t="n">
-        <v>200</v>
+        <v>173</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="E37" s="23" t="n">
-        <v>166</v>
+        <v>214</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
@@ -1978,7 +1978,7 @@
         </is>
       </c>
       <c r="E38" s="20" t="n">
-        <v>113</v>
+        <v>222</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="E39" s="23" t="n">
-        <v>154</v>
+        <v>212</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="E40" s="20" t="n">
-        <v>190</v>
+        <v>121</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="E41" s="23" t="n">
-        <v>118</v>
+        <v>216</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
@@ -2078,7 +2078,7 @@
         </is>
       </c>
       <c r="E42" s="20" t="n">
-        <v>214</v>
+        <v>151</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="E44" s="20" t="n">
-        <v>153</v>
+        <v>139</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="E45" s="23" t="n">
-        <v>129</v>
+        <v>227</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
@@ -2178,7 +2178,7 @@
         </is>
       </c>
       <c r="E46" s="20" t="n">
-        <v>204</v>
+        <v>182</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
@@ -2203,7 +2203,7 @@
         </is>
       </c>
       <c r="E47" s="23" t="n">
-        <v>131</v>
+        <v>189</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="E48" s="20" t="n">
-        <v>124</v>
+        <v>182</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
@@ -2253,7 +2253,7 @@
         </is>
       </c>
       <c r="E49" s="23" t="n">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
@@ -2278,7 +2278,7 @@
         </is>
       </c>
       <c r="E50" s="20" t="n">
-        <v>160</v>
+        <v>218</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="E51" s="23" t="n">
-        <v>190</v>
+        <v>146</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
@@ -2328,7 +2328,7 @@
         </is>
       </c>
       <c r="E52" s="20" t="n">
-        <v>181</v>
+        <v>160</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
@@ -2353,7 +2353,7 @@
         </is>
       </c>
       <c r="E53" s="23" t="n">
-        <v>172</v>
+        <v>181</v>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="E54" s="20" t="n">
-        <v>133</v>
+        <v>183</v>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1">
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="E55" s="23" t="n">
-        <v>225</v>
+        <v>160</v>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1">
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="E56" s="20" t="n">
-        <v>166</v>
+        <v>219</v>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1">
@@ -2453,7 +2453,7 @@
         </is>
       </c>
       <c r="E57" s="23" t="n">
-        <v>113</v>
+        <v>131</v>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1">
@@ -2478,7 +2478,7 @@
         </is>
       </c>
       <c r="E58" s="20" t="n">
-        <v>125</v>
+        <v>146</v>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1">
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="E59" s="23" t="n">
-        <v>229</v>
+        <v>155</v>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1">
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="E60" s="20" t="n">
-        <v>121</v>
+        <v>220</v>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
@@ -2553,7 +2553,7 @@
         </is>
       </c>
       <c r="E61" s="23" t="n">
-        <v>143</v>
+        <v>200</v>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="E62" s="20" t="n">
-        <v>149</v>
+        <v>198</v>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="E63" s="23" t="n">
-        <v>221</v>
+        <v>204</v>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1">
@@ -2628,7 +2628,7 @@
         </is>
       </c>
       <c r="E64" s="20" t="n">
-        <v>162</v>
+        <v>184</v>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1">
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="E65" s="23" t="n">
-        <v>113</v>
+        <v>184</v>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1">
@@ -2678,7 +2678,7 @@
         </is>
       </c>
       <c r="E66" s="20" t="n">
-        <v>116</v>
+        <v>196</v>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="E67" s="23" t="n">
-        <v>184</v>
+        <v>140</v>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="E68" s="20" t="n">
-        <v>120</v>
+        <v>198</v>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="E69" s="23" t="n">
-        <v>226</v>
+        <v>168</v>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1">
@@ -2778,7 +2778,7 @@
         </is>
       </c>
       <c r="E70" s="20" t="n">
-        <v>139</v>
+        <v>236</v>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1">
@@ -2803,7 +2803,7 @@
         </is>
       </c>
       <c r="E71" s="23" t="n">
-        <v>140</v>
+        <v>189</v>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1">
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="E72" s="20" t="n">
-        <v>195</v>
+        <v>169</v>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1">
@@ -2853,7 +2853,7 @@
         </is>
       </c>
       <c r="E73" s="23" t="n">
-        <v>176</v>
+        <v>146</v>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
@@ -2878,7 +2878,7 @@
         </is>
       </c>
       <c r="E74" s="20" t="n">
-        <v>207</v>
+        <v>143</v>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="E75" s="23" t="n">
-        <v>171</v>
+        <v>155</v>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
@@ -2928,7 +2928,7 @@
         </is>
       </c>
       <c r="E76" s="20" t="n">
-        <v>234</v>
+        <v>133</v>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="E77" s="23" t="n">
-        <v>228</v>
+        <v>139</v>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1">
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="E78" s="20" t="n">
-        <v>237</v>
+        <v>173</v>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
@@ -3003,7 +3003,7 @@
         </is>
       </c>
       <c r="E79" s="23" t="n">
-        <v>236</v>
+        <v>220</v>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1">
@@ -3028,7 +3028,7 @@
         </is>
       </c>
       <c r="E80" s="20" t="n">
-        <v>238</v>
+        <v>176</v>
       </c>
     </row>
     <row r="81" ht="20" customHeight="1">
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="E81" s="23" t="n">
-        <v>226</v>
+        <v>160</v>
       </c>
     </row>
     <row r="82" ht="20" customHeight="1">
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="E82" s="20" t="n">
-        <v>239</v>
+        <v>206</v>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1">
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="E83" s="23" t="n">
-        <v>165</v>
+        <v>134</v>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1">
@@ -3128,7 +3128,7 @@
         </is>
       </c>
       <c r="E84" s="20" t="n">
-        <v>129</v>
+        <v>239</v>
       </c>
     </row>
     <row r="85" ht="20" customHeight="1">
@@ -3153,7 +3153,7 @@
         </is>
       </c>
       <c r="E85" s="23" t="n">
-        <v>159</v>
+        <v>151</v>
       </c>
     </row>
     <row r="86" ht="20" customHeight="1">
@@ -3178,7 +3178,7 @@
         </is>
       </c>
       <c r="E86" s="20" t="n">
-        <v>234</v>
+        <v>176</v>
       </c>
     </row>
     <row r="87" ht="20" customHeight="1">
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="E87" s="23" t="n">
-        <v>227</v>
+        <v>117</v>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1">
@@ -3228,7 +3228,7 @@
         </is>
       </c>
       <c r="E88" s="20" t="n">
-        <v>119</v>
+        <v>216</v>
       </c>
     </row>
     <row r="89" ht="20" customHeight="1">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="E89" s="23" t="n">
-        <v>204</v>
+        <v>236</v>
       </c>
     </row>
     <row r="90" ht="20" customHeight="1">
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="E90" s="20" t="n">
-        <v>214</v>
+        <v>167</v>
       </c>
     </row>
     <row r="91" ht="20" customHeight="1">
@@ -3303,7 +3303,7 @@
         </is>
       </c>
       <c r="E91" s="23" t="n">
-        <v>202</v>
+        <v>193</v>
       </c>
     </row>
     <row r="92" ht="20" customHeight="1">
@@ -3328,7 +3328,7 @@
         </is>
       </c>
       <c r="E92" s="20" t="n">
-        <v>173</v>
+        <v>198</v>
       </c>
     </row>
     <row r="93" ht="20" customHeight="1">
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="E93" s="23" t="n">
-        <v>182</v>
+        <v>206</v>
       </c>
     </row>
     <row r="94" ht="20" customHeight="1">
@@ -3378,7 +3378,7 @@
         </is>
       </c>
       <c r="E94" s="20" t="n">
-        <v>116</v>
+        <v>233</v>
       </c>
     </row>
     <row r="95" ht="20" customHeight="1">
@@ -3403,7 +3403,7 @@
         </is>
       </c>
       <c r="E95" s="23" t="n">
-        <v>146</v>
+        <v>205</v>
       </c>
     </row>
     <row r="96" ht="20" customHeight="1">
@@ -3428,7 +3428,7 @@
         </is>
       </c>
       <c r="E96" s="20" t="n">
-        <v>239</v>
+        <v>170</v>
       </c>
     </row>
     <row r="97" ht="20" customHeight="1">
@@ -3453,7 +3453,7 @@
         </is>
       </c>
       <c r="E97" s="23" t="n">
-        <v>188</v>
+        <v>204</v>
       </c>
     </row>
     <row r="98" ht="20" customHeight="1">
@@ -3478,7 +3478,7 @@
         </is>
       </c>
       <c r="E98" s="20" t="n">
-        <v>167</v>
+        <v>213</v>
       </c>
     </row>
     <row r="99" ht="20" customHeight="1">
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="E99" s="23" t="n">
-        <v>171</v>
+        <v>194</v>
       </c>
     </row>
     <row r="100" ht="20" customHeight="1">
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="E100" s="20" t="n">
-        <v>210</v>
+        <v>228</v>
       </c>
     </row>
     <row r="101" ht="20" customHeight="1">
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="E101" s="23" t="n">
-        <v>190</v>
+        <v>124</v>
       </c>
     </row>
     <row r="102" ht="20" customHeight="1">
@@ -3578,7 +3578,7 @@
         </is>
       </c>
       <c r="E102" s="20" t="n">
-        <v>198</v>
+        <v>207</v>
       </c>
     </row>
     <row r="103" ht="20" customHeight="1">
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="E103" s="23" t="n">
-        <v>191</v>
+        <v>175</v>
       </c>
     </row>
     <row r="104" ht="20" customHeight="1">
@@ -3628,7 +3628,7 @@
         </is>
       </c>
       <c r="E104" s="20" t="n">
-        <v>166</v>
+        <v>171</v>
       </c>
     </row>
     <row r="105" ht="20" customHeight="1">
@@ -3653,7 +3653,7 @@
         </is>
       </c>
       <c r="E105" s="23" t="n">
-        <v>182</v>
+        <v>154</v>
       </c>
     </row>
     <row r="106" ht="20" customHeight="1">
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="E106" s="20" t="n">
-        <v>141</v>
+        <v>200</v>
       </c>
     </row>
     <row r="107" ht="20" customHeight="1">
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="E107" s="23" t="n">
-        <v>167</v>
+        <v>139</v>
       </c>
     </row>
     <row r="108" ht="20" customHeight="1">
@@ -3728,7 +3728,7 @@
         </is>
       </c>
       <c r="E108" s="20" t="n">
-        <v>232</v>
+        <v>239</v>
       </c>
     </row>
     <row r="109" ht="20" customHeight="1">
@@ -3753,7 +3753,7 @@
         </is>
       </c>
       <c r="E109" s="23" t="n">
-        <v>192</v>
+        <v>185</v>
       </c>
     </row>
     <row r="110" ht="20" customHeight="1">
@@ -3778,7 +3778,7 @@
         </is>
       </c>
       <c r="E110" s="20" t="n">
-        <v>232</v>
+        <v>204</v>
       </c>
     </row>
     <row r="111" ht="20" customHeight="1">
@@ -3803,7 +3803,7 @@
         </is>
       </c>
       <c r="E111" s="23" t="n">
-        <v>167</v>
+        <v>222</v>
       </c>
     </row>
     <row r="112" ht="20" customHeight="1">
@@ -3828,7 +3828,7 @@
         </is>
       </c>
       <c r="E112" s="20" t="n">
-        <v>134</v>
+        <v>118</v>
       </c>
     </row>
     <row r="113" ht="20" customHeight="1">
@@ -3853,7 +3853,7 @@
         </is>
       </c>
       <c r="E113" s="23" t="n">
-        <v>177</v>
+        <v>239</v>
       </c>
     </row>
     <row r="114" ht="20" customHeight="1">
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="E114" s="20" t="n">
-        <v>148</v>
+        <v>217</v>
       </c>
     </row>
     <row r="115" ht="20" customHeight="1">
@@ -3903,7 +3903,7 @@
         </is>
       </c>
       <c r="E115" s="23" t="n">
-        <v>221</v>
+        <v>189</v>
       </c>
     </row>
     <row r="116" ht="20" customHeight="1">
@@ -3928,7 +3928,7 @@
         </is>
       </c>
       <c r="E116" s="20" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="117" ht="20" customHeight="1">
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="E117" s="23" t="n">
-        <v>194</v>
+        <v>152</v>
       </c>
     </row>
     <row r="118" ht="20" customHeight="1">
@@ -3978,7 +3978,7 @@
         </is>
       </c>
       <c r="E118" s="20" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
     </row>
     <row r="119" ht="20" customHeight="1">
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="E119" s="23" t="n">
-        <v>238</v>
+        <v>154</v>
       </c>
     </row>
     <row r="120" ht="20" customHeight="1">
@@ -4028,7 +4028,7 @@
         </is>
       </c>
       <c r="E120" s="20" t="n">
-        <v>133</v>
+        <v>142</v>
       </c>
     </row>
     <row r="121" ht="20" customHeight="1">
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="E121" s="23" t="n">
-        <v>138</v>
+        <v>156</v>
       </c>
     </row>
     <row r="122" ht="20" customHeight="1">
@@ -4078,7 +4078,7 @@
         </is>
       </c>
       <c r="E122" s="20" t="n">
-        <v>185</v>
+        <v>229</v>
       </c>
     </row>
     <row r="123" ht="20" customHeight="1">
@@ -4103,7 +4103,7 @@
         </is>
       </c>
       <c r="E123" s="23" t="n">
-        <v>149</v>
+        <v>179</v>
       </c>
     </row>
     <row r="124" ht="20" customHeight="1">
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="E124" s="20" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="125" ht="20" customHeight="1">
@@ -4153,7 +4153,7 @@
         </is>
       </c>
       <c r="E125" s="23" t="n">
-        <v>191</v>
+        <v>207</v>
       </c>
     </row>
     <row r="126" ht="20" customHeight="1">
@@ -4178,7 +4178,7 @@
         </is>
       </c>
       <c r="E126" s="20" t="n">
-        <v>239</v>
+        <v>231</v>
       </c>
     </row>
     <row r="127" ht="20" customHeight="1">
@@ -4203,7 +4203,7 @@
         </is>
       </c>
       <c r="E127" s="23" t="n">
-        <v>145</v>
+        <v>196</v>
       </c>
     </row>
     <row r="128" ht="20" customHeight="1">
@@ -4228,7 +4228,7 @@
         </is>
       </c>
       <c r="E128" s="20" t="n">
-        <v>144</v>
+        <v>203</v>
       </c>
     </row>
     <row r="129" ht="20" customHeight="1">
@@ -4253,7 +4253,7 @@
         </is>
       </c>
       <c r="E129" s="23" t="n">
-        <v>154</v>
+        <v>233</v>
       </c>
     </row>
     <row r="130" ht="20" customHeight="1">
@@ -4278,7 +4278,7 @@
         </is>
       </c>
       <c r="E130" s="20" t="n">
-        <v>229</v>
+        <v>171</v>
       </c>
     </row>
     <row r="131" ht="20" customHeight="1">
@@ -4303,7 +4303,7 @@
         </is>
       </c>
       <c r="E131" s="23" t="n">
-        <v>173</v>
+        <v>132</v>
       </c>
     </row>
     <row r="132" ht="20" customHeight="1">
@@ -4328,7 +4328,7 @@
         </is>
       </c>
       <c r="E132" s="20" t="n">
-        <v>162</v>
+        <v>151</v>
       </c>
     </row>
     <row r="133" ht="20" customHeight="1">
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="E133" s="23" t="n">
-        <v>191</v>
+        <v>115</v>
       </c>
     </row>
     <row r="134" ht="20" customHeight="1">
@@ -4403,7 +4403,7 @@
         </is>
       </c>
       <c r="E135" s="23" t="n">
-        <v>196</v>
+        <v>235</v>
       </c>
     </row>
     <row r="136" ht="20" customHeight="1">
@@ -4428,7 +4428,7 @@
         </is>
       </c>
       <c r="E136" s="20" t="n">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="137" ht="20" customHeight="1">
@@ -4453,7 +4453,7 @@
         </is>
       </c>
       <c r="E137" s="23" t="n">
-        <v>190</v>
+        <v>139</v>
       </c>
     </row>
     <row r="138" ht="20" customHeight="1">
@@ -4478,7 +4478,7 @@
         </is>
       </c>
       <c r="E138" s="20" t="n">
-        <v>195</v>
+        <v>203</v>
       </c>
     </row>
     <row r="139" ht="20" customHeight="1">
@@ -4503,7 +4503,7 @@
         </is>
       </c>
       <c r="E139" s="23" t="n">
-        <v>200</v>
+        <v>128</v>
       </c>
     </row>
     <row r="140" ht="20" customHeight="1">
@@ -4528,7 +4528,7 @@
         </is>
       </c>
       <c r="E140" s="20" t="n">
-        <v>135</v>
+        <v>147</v>
       </c>
     </row>
     <row r="141" ht="20" customHeight="1">
@@ -4553,7 +4553,7 @@
         </is>
       </c>
       <c r="E141" s="23" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="142" ht="20" customHeight="1">
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="E142" s="20" t="n">
-        <v>154</v>
+        <v>181</v>
       </c>
     </row>
     <row r="143" ht="20" customHeight="1">
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="E143" s="23" t="n">
-        <v>149</v>
+        <v>219</v>
       </c>
     </row>
     <row r="144" ht="20" customHeight="1">
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="E144" s="20" t="n">
-        <v>152</v>
+        <v>222</v>
       </c>
     </row>
     <row r="145" ht="20" customHeight="1">
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="E145" s="23" t="n">
-        <v>204</v>
+        <v>234</v>
       </c>
     </row>
     <row r="146" ht="20" customHeight="1">
@@ -4678,7 +4678,7 @@
         </is>
       </c>
       <c r="E146" s="20" t="n">
-        <v>185</v>
+        <v>209</v>
       </c>
     </row>
     <row r="147" ht="20" customHeight="1">
@@ -4703,7 +4703,7 @@
         </is>
       </c>
       <c r="E147" s="23" t="n">
-        <v>191</v>
+        <v>156</v>
       </c>
     </row>
     <row r="148" ht="20" customHeight="1">
@@ -4728,7 +4728,7 @@
         </is>
       </c>
       <c r="E148" s="20" t="n">
-        <v>200</v>
+        <v>223</v>
       </c>
     </row>
     <row r="149" ht="20" customHeight="1">
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c r="E149" s="23" t="n">
-        <v>160</v>
+        <v>117</v>
       </c>
     </row>
     <row r="150" ht="20" customHeight="1">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="E150" s="20" t="n">
-        <v>158</v>
+        <v>215</v>
       </c>
     </row>
     <row r="151" ht="20" customHeight="1">
@@ -4803,7 +4803,7 @@
         </is>
       </c>
       <c r="E151" s="23" t="n">
-        <v>149</v>
+        <v>226</v>
       </c>
     </row>
     <row r="152" ht="20" customHeight="1">
@@ -4828,7 +4828,7 @@
         </is>
       </c>
       <c r="E152" s="20" t="n">
-        <v>198</v>
+        <v>169</v>
       </c>
     </row>
     <row r="153" ht="20" customHeight="1">
@@ -4853,7 +4853,7 @@
         </is>
       </c>
       <c r="E153" s="23" t="n">
-        <v>221</v>
+        <v>197</v>
       </c>
     </row>
     <row r="154" ht="20" customHeight="1">
@@ -4878,7 +4878,7 @@
         </is>
       </c>
       <c r="E154" s="20" t="n">
-        <v>124</v>
+        <v>110</v>
       </c>
     </row>
     <row r="155" ht="20" customHeight="1">
@@ -4903,7 +4903,7 @@
         </is>
       </c>
       <c r="E155" s="23" t="n">
-        <v>214</v>
+        <v>205</v>
       </c>
     </row>
     <row r="156" ht="20" customHeight="1">
@@ -4928,7 +4928,7 @@
         </is>
       </c>
       <c r="E156" s="20" t="n">
-        <v>184</v>
+        <v>164</v>
       </c>
     </row>
     <row r="157" ht="20" customHeight="1">
@@ -4953,7 +4953,7 @@
         </is>
       </c>
       <c r="E157" s="23" t="n">
-        <v>239</v>
+        <v>214</v>
       </c>
     </row>
     <row r="158" ht="20" customHeight="1">
@@ -4978,7 +4978,7 @@
         </is>
       </c>
       <c r="E158" s="20" t="n">
-        <v>211</v>
+        <v>168</v>
       </c>
     </row>
     <row r="159" ht="20" customHeight="1">
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="E159" s="23" t="n">
-        <v>164</v>
+        <v>235</v>
       </c>
     </row>
     <row r="160" ht="20" customHeight="1">
@@ -5028,7 +5028,7 @@
         </is>
       </c>
       <c r="E160" s="20" t="n">
-        <v>214</v>
+        <v>234</v>
       </c>
     </row>
     <row r="161" ht="20" customHeight="1">
@@ -5053,7 +5053,7 @@
         </is>
       </c>
       <c r="E161" s="23" t="n">
-        <v>181</v>
+        <v>116</v>
       </c>
     </row>
     <row r="162" ht="20" customHeight="1">
@@ -5078,7 +5078,7 @@
         </is>
       </c>
       <c r="E162" s="20" t="n">
-        <v>186</v>
+        <v>182</v>
       </c>
     </row>
     <row r="163" ht="20" customHeight="1">
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="E163" s="23" t="n">
-        <v>199</v>
+        <v>165</v>
       </c>
     </row>
     <row r="164" ht="20" customHeight="1">
@@ -5128,7 +5128,7 @@
         </is>
       </c>
       <c r="E164" s="20" t="n">
-        <v>117</v>
+        <v>137</v>
       </c>
     </row>
     <row r="165" ht="20" customHeight="1">
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="E165" s="23" t="n">
-        <v>116</v>
+        <v>189</v>
       </c>
     </row>
     <row r="166" ht="20" customHeight="1">
@@ -5178,7 +5178,7 @@
         </is>
       </c>
       <c r="E166" s="20" t="n">
-        <v>141</v>
+        <v>227</v>
       </c>
     </row>
     <row r="167" ht="20" customHeight="1">
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="E167" s="23" t="n">
-        <v>237</v>
+        <v>210</v>
       </c>
     </row>
     <row r="168" ht="20" customHeight="1">
@@ -5228,7 +5228,7 @@
         </is>
       </c>
       <c r="E168" s="20" t="n">
-        <v>167</v>
+        <v>209</v>
       </c>
     </row>
     <row r="169" ht="20" customHeight="1">
@@ -5253,7 +5253,7 @@
         </is>
       </c>
       <c r="E169" s="23" t="n">
-        <v>129</v>
+        <v>148</v>
       </c>
     </row>
     <row r="170" ht="20" customHeight="1">
@@ -5278,7 +5278,7 @@
         </is>
       </c>
       <c r="E170" s="20" t="n">
-        <v>153</v>
+        <v>210</v>
       </c>
     </row>
     <row r="171" ht="20" customHeight="1">
@@ -5303,7 +5303,7 @@
         </is>
       </c>
       <c r="E171" s="23" t="n">
-        <v>197</v>
+        <v>224</v>
       </c>
     </row>
     <row r="172" ht="20" customHeight="1">
@@ -5328,7 +5328,7 @@
         </is>
       </c>
       <c r="E172" s="20" t="n">
-        <v>167</v>
+        <v>140</v>
       </c>
     </row>
     <row r="173" ht="20" customHeight="1">
@@ -5353,7 +5353,7 @@
         </is>
       </c>
       <c r="E173" s="23" t="n">
-        <v>234</v>
+        <v>226</v>
       </c>
     </row>
     <row r="174" ht="20" customHeight="1">
@@ -5378,7 +5378,7 @@
         </is>
       </c>
       <c r="E174" s="20" t="n">
-        <v>225</v>
+        <v>159</v>
       </c>
     </row>
     <row r="175" ht="20" customHeight="1">
@@ -5403,7 +5403,7 @@
         </is>
       </c>
       <c r="E175" s="23" t="n">
-        <v>218</v>
+        <v>112</v>
       </c>
     </row>
     <row r="176" ht="20" customHeight="1">
@@ -5428,7 +5428,7 @@
         </is>
       </c>
       <c r="E176" s="20" t="n">
-        <v>130</v>
+        <v>230</v>
       </c>
     </row>
     <row r="177" ht="20" customHeight="1">
@@ -5453,7 +5453,7 @@
         </is>
       </c>
       <c r="E177" s="23" t="n">
-        <v>233</v>
+        <v>155</v>
       </c>
     </row>
     <row r="178" ht="20" customHeight="1">
@@ -5478,7 +5478,7 @@
         </is>
       </c>
       <c r="E178" s="20" t="n">
-        <v>203</v>
+        <v>134</v>
       </c>
     </row>
     <row r="179" ht="20" customHeight="1">
@@ -5503,7 +5503,7 @@
         </is>
       </c>
       <c r="E179" s="23" t="n">
-        <v>127</v>
+        <v>158</v>
       </c>
     </row>
     <row r="180" ht="20" customHeight="1">
@@ -5528,7 +5528,7 @@
         </is>
       </c>
       <c r="E180" s="20" t="n">
-        <v>211</v>
+        <v>135</v>
       </c>
     </row>
     <row r="181" ht="20" customHeight="1">
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="E181" s="23" t="n">
-        <v>195</v>
+        <v>154</v>
       </c>
     </row>
     <row r="182" ht="20" customHeight="1">
@@ -5578,7 +5578,7 @@
         </is>
       </c>
       <c r="E182" s="20" t="n">
-        <v>194</v>
+        <v>219</v>
       </c>
     </row>
     <row r="183" ht="20" customHeight="1">
@@ -5603,7 +5603,7 @@
         </is>
       </c>
       <c r="E183" s="23" t="n">
-        <v>207</v>
+        <v>214</v>
       </c>
     </row>
     <row r="184" ht="20" customHeight="1">
@@ -5628,7 +5628,7 @@
         </is>
       </c>
       <c r="E184" s="20" t="n">
-        <v>148</v>
+        <v>186</v>
       </c>
     </row>
     <row r="185" ht="20" customHeight="1">
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="E185" s="23" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="186" ht="20" customHeight="1">
@@ -5678,7 +5678,7 @@
         </is>
       </c>
       <c r="E186" s="20" t="n">
-        <v>146</v>
+        <v>213</v>
       </c>
     </row>
     <row r="187" ht="20" customHeight="1">
@@ -5703,7 +5703,7 @@
         </is>
       </c>
       <c r="E187" s="23" t="n">
-        <v>151</v>
+        <v>194</v>
       </c>
     </row>
     <row r="188" ht="20" customHeight="1">
@@ -5728,7 +5728,7 @@
         </is>
       </c>
       <c r="E188" s="20" t="n">
-        <v>236</v>
+        <v>231</v>
       </c>
     </row>
     <row r="189" ht="20" customHeight="1">
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="E189" s="23" t="n">
-        <v>197</v>
+        <v>183</v>
       </c>
     </row>
     <row r="190" ht="20" customHeight="1">
@@ -5778,7 +5778,7 @@
         </is>
       </c>
       <c r="E190" s="20" t="n">
-        <v>117</v>
+        <v>233</v>
       </c>
     </row>
     <row r="191" ht="20" customHeight="1">
@@ -5803,7 +5803,7 @@
         </is>
       </c>
       <c r="E191" s="23" t="n">
-        <v>201</v>
+        <v>113</v>
       </c>
     </row>
     <row r="192" ht="20" customHeight="1">
@@ -5828,7 +5828,7 @@
         </is>
       </c>
       <c r="E192" s="20" t="n">
-        <v>175</v>
+        <v>141</v>
       </c>
     </row>
     <row r="193" ht="20" customHeight="1">
@@ -5853,7 +5853,7 @@
         </is>
       </c>
       <c r="E193" s="23" t="n">
-        <v>236</v>
+        <v>161</v>
       </c>
     </row>
     <row r="194" ht="20" customHeight="1">
@@ -5878,7 +5878,7 @@
         </is>
       </c>
       <c r="E194" s="20" t="n">
-        <v>219</v>
+        <v>160</v>
       </c>
     </row>
     <row r="195" ht="20" customHeight="1">
@@ -5903,7 +5903,7 @@
         </is>
       </c>
       <c r="E195" s="23" t="n">
-        <v>151</v>
+        <v>173</v>
       </c>
     </row>
     <row r="196" ht="20" customHeight="1">
@@ -5928,7 +5928,7 @@
         </is>
       </c>
       <c r="E196" s="20" t="n">
-        <v>177</v>
+        <v>129</v>
       </c>
     </row>
     <row r="197" ht="20" customHeight="1">
@@ -5953,7 +5953,7 @@
         </is>
       </c>
       <c r="E197" s="23" t="n">
-        <v>171</v>
+        <v>199</v>
       </c>
     </row>
     <row r="198" ht="20" customHeight="1">
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="E198" s="20" t="n">
-        <v>125</v>
+        <v>214</v>
       </c>
     </row>
     <row r="199" ht="20" customHeight="1">
@@ -6003,7 +6003,7 @@
         </is>
       </c>
       <c r="E199" s="23" t="n">
-        <v>228</v>
+        <v>220</v>
       </c>
     </row>
     <row r="200" ht="20" customHeight="1">
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="E200" s="20" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="201" ht="20" customHeight="1">
@@ -6053,7 +6053,7 @@
         </is>
       </c>
       <c r="E201" s="23" t="n">
-        <v>150</v>
+        <v>231</v>
       </c>
     </row>
     <row r="202" ht="20" customHeight="1">
@@ -6078,7 +6078,7 @@
         </is>
       </c>
       <c r="E202" s="20" t="n">
-        <v>157</v>
+        <v>130</v>
       </c>
     </row>
     <row r="203" ht="20" customHeight="1">
@@ -6103,7 +6103,7 @@
         </is>
       </c>
       <c r="E203" s="23" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
     </row>
     <row r="204" ht="20" customHeight="1">
@@ -6128,7 +6128,7 @@
         </is>
       </c>
       <c r="E204" s="20" t="n">
-        <v>117</v>
+        <v>173</v>
       </c>
     </row>
     <row r="205" ht="20" customHeight="1">
@@ -6153,7 +6153,7 @@
         </is>
       </c>
       <c r="E205" s="23" t="n">
-        <v>227</v>
+        <v>204</v>
       </c>
     </row>
     <row r="206" ht="20" customHeight="1">
@@ -6178,7 +6178,7 @@
         </is>
       </c>
       <c r="E206" s="20" t="n">
-        <v>223</v>
+        <v>152</v>
       </c>
     </row>
     <row r="207" ht="20" customHeight="1">
@@ -6203,7 +6203,7 @@
         </is>
       </c>
       <c r="E207" s="23" t="n">
-        <v>183</v>
+        <v>204</v>
       </c>
     </row>
     <row r="208" ht="20" customHeight="1">
@@ -6228,7 +6228,7 @@
         </is>
       </c>
       <c r="E208" s="20" t="n">
-        <v>149</v>
+        <v>197</v>
       </c>
     </row>
     <row r="209" ht="20" customHeight="1">
@@ -6253,7 +6253,7 @@
         </is>
       </c>
       <c r="E209" s="23" t="n">
-        <v>234</v>
+        <v>135</v>
       </c>
     </row>
     <row r="210" ht="20" customHeight="1">
@@ -6278,7 +6278,7 @@
         </is>
       </c>
       <c r="E210" s="20" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="211" ht="20" customHeight="1">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="E211" s="23" t="n">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="212" ht="20" customHeight="1">
@@ -6328,7 +6328,7 @@
         </is>
       </c>
       <c r="E212" s="20" t="n">
-        <v>119</v>
+        <v>209</v>
       </c>
     </row>
     <row r="213" ht="20" customHeight="1">
@@ -6353,7 +6353,7 @@
         </is>
       </c>
       <c r="E213" s="23" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="214" ht="20" customHeight="1">
@@ -6378,7 +6378,7 @@
         </is>
       </c>
       <c r="E214" s="20" t="n">
-        <v>144</v>
+        <v>136</v>
       </c>
     </row>
     <row r="215" ht="20" customHeight="1">
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="E215" s="23" t="n">
-        <v>152</v>
+        <v>143</v>
       </c>
     </row>
     <row r="216" ht="20" customHeight="1">
@@ -6428,7 +6428,7 @@
         </is>
       </c>
       <c r="E216" s="20" t="n">
-        <v>232</v>
+        <v>122</v>
       </c>
     </row>
     <row r="217" ht="20" customHeight="1">
@@ -6453,7 +6453,7 @@
         </is>
       </c>
       <c r="E217" s="23" t="n">
-        <v>217</v>
+        <v>209</v>
       </c>
     </row>
     <row r="218" ht="20" customHeight="1">
@@ -6478,7 +6478,7 @@
         </is>
       </c>
       <c r="E218" s="20" t="n">
-        <v>125</v>
+        <v>146</v>
       </c>
     </row>
     <row r="219" ht="20" customHeight="1">
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="E219" s="23" t="n">
-        <v>212</v>
+        <v>235</v>
       </c>
     </row>
     <row r="220" ht="20" customHeight="1">
@@ -6528,7 +6528,7 @@
         </is>
       </c>
       <c r="E220" s="20" t="n">
-        <v>226</v>
+        <v>171</v>
       </c>
     </row>
     <row r="221" ht="20" customHeight="1">
@@ -6553,7 +6553,7 @@
         </is>
       </c>
       <c r="E221" s="23" t="n">
-        <v>236</v>
+        <v>226</v>
       </c>
     </row>
     <row r="222" ht="20" customHeight="1">
@@ -6578,7 +6578,7 @@
         </is>
       </c>
       <c r="E222" s="20" t="n">
-        <v>153</v>
+        <v>213</v>
       </c>
     </row>
     <row r="223" ht="20" customHeight="1">
@@ -6603,7 +6603,7 @@
         </is>
       </c>
       <c r="E223" s="23" t="n">
-        <v>214</v>
+        <v>233</v>
       </c>
     </row>
     <row r="224" ht="20" customHeight="1">
@@ -6628,7 +6628,7 @@
         </is>
       </c>
       <c r="E224" s="20" t="n">
-        <v>136</v>
+        <v>194</v>
       </c>
     </row>
     <row r="225" ht="20" customHeight="1">
@@ -6653,7 +6653,7 @@
         </is>
       </c>
       <c r="E225" s="23" t="n">
-        <v>177</v>
+        <v>142</v>
       </c>
     </row>
     <row r="226" ht="20" customHeight="1">
@@ -6678,7 +6678,7 @@
         </is>
       </c>
       <c r="E226" s="20" t="n">
-        <v>134</v>
+        <v>209</v>
       </c>
     </row>
     <row r="227" ht="20" customHeight="1">
@@ -6703,7 +6703,7 @@
         </is>
       </c>
       <c r="E227" s="23" t="n">
-        <v>186</v>
+        <v>112</v>
       </c>
     </row>
     <row r="228" ht="20" customHeight="1">
@@ -6728,7 +6728,7 @@
         </is>
       </c>
       <c r="E228" s="20" t="n">
-        <v>174</v>
+        <v>134</v>
       </c>
     </row>
     <row r="229" ht="20" customHeight="1">
@@ -6753,7 +6753,7 @@
         </is>
       </c>
       <c r="E229" s="23" t="n">
-        <v>120</v>
+        <v>168</v>
       </c>
     </row>
     <row r="230" ht="20" customHeight="1">
@@ -6778,7 +6778,7 @@
         </is>
       </c>
       <c r="E230" s="20" t="n">
-        <v>175</v>
+        <v>191</v>
       </c>
     </row>
     <row r="231" ht="20" customHeight="1">
@@ -6803,7 +6803,7 @@
         </is>
       </c>
       <c r="E231" s="23" t="n">
-        <v>127</v>
+        <v>206</v>
       </c>
     </row>
     <row r="232" ht="20" customHeight="1">
@@ -6828,7 +6828,7 @@
         </is>
       </c>
       <c r="E232" s="20" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="233" ht="20" customHeight="1">
@@ -6853,7 +6853,7 @@
         </is>
       </c>
       <c r="E233" s="23" t="n">
-        <v>160</v>
+        <v>204</v>
       </c>
     </row>
     <row r="234" ht="20" customHeight="1">
@@ -6878,7 +6878,7 @@
         </is>
       </c>
       <c r="E234" s="20" t="n">
-        <v>198</v>
+        <v>194</v>
       </c>
     </row>
     <row r="235" ht="20" customHeight="1">
@@ -6903,7 +6903,7 @@
         </is>
       </c>
       <c r="E235" s="23" t="n">
-        <v>166</v>
+        <v>238</v>
       </c>
     </row>
     <row r="236" ht="20" customHeight="1">
@@ -6928,7 +6928,7 @@
         </is>
       </c>
       <c r="E236" s="20" t="n">
-        <v>169</v>
+        <v>141</v>
       </c>
     </row>
     <row r="237" ht="20" customHeight="1">
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="E237" s="23" t="n">
-        <v>153</v>
+        <v>143</v>
       </c>
     </row>
     <row r="238" ht="20" customHeight="1">
@@ -6978,7 +6978,7 @@
         </is>
       </c>
       <c r="E238" s="20" t="n">
-        <v>135</v>
+        <v>121</v>
       </c>
     </row>
     <row r="239" ht="20" customHeight="1">
@@ -7003,7 +7003,7 @@
         </is>
       </c>
       <c r="E239" s="23" t="n">
-        <v>239</v>
+        <v>168</v>
       </c>
     </row>
     <row r="240" ht="20" customHeight="1">
@@ -7028,7 +7028,7 @@
         </is>
       </c>
       <c r="E240" s="20" t="n">
-        <v>161</v>
+        <v>205</v>
       </c>
     </row>
     <row r="241" ht="20" customHeight="1">
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="E241" s="23" t="n">
-        <v>122</v>
+        <v>186</v>
       </c>
     </row>
     <row r="242" ht="20" customHeight="1">
@@ -7078,7 +7078,7 @@
         </is>
       </c>
       <c r="E242" s="20" t="n">
-        <v>114</v>
+        <v>215</v>
       </c>
     </row>
     <row r="243" ht="20" customHeight="1">
@@ -7103,7 +7103,7 @@
         </is>
       </c>
       <c r="E243" s="23" t="n">
-        <v>171</v>
+        <v>151</v>
       </c>
     </row>
     <row r="244" ht="20" customHeight="1">
@@ -7128,7 +7128,7 @@
         </is>
       </c>
       <c r="E244" s="20" t="n">
-        <v>127</v>
+        <v>173</v>
       </c>
     </row>
     <row r="245" ht="20" customHeight="1">
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="E245" s="23" t="n">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="246" ht="20" customHeight="1">
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="E246" s="20" t="n">
-        <v>145</v>
+        <v>236</v>
       </c>
     </row>
     <row r="247" ht="20" customHeight="1">
@@ -7203,7 +7203,7 @@
         </is>
       </c>
       <c r="E247" s="23" t="n">
-        <v>233</v>
+        <v>238</v>
       </c>
     </row>
     <row r="248" ht="20" customHeight="1">
@@ -7228,7 +7228,7 @@
         </is>
       </c>
       <c r="E248" s="20" t="n">
-        <v>169</v>
+        <v>124</v>
       </c>
     </row>
     <row r="249" ht="20" customHeight="1">
@@ -7253,7 +7253,7 @@
         </is>
       </c>
       <c r="E249" s="23" t="n">
-        <v>147</v>
+        <v>138</v>
       </c>
     </row>
     <row r="250" ht="20" customHeight="1">
@@ -7278,7 +7278,7 @@
         </is>
       </c>
       <c r="E250" s="20" t="n">
-        <v>116</v>
+        <v>167</v>
       </c>
     </row>
     <row r="251" ht="20" customHeight="1">
@@ -7303,7 +7303,7 @@
         </is>
       </c>
       <c r="E251" s="23" t="n">
-        <v>128</v>
+        <v>175</v>
       </c>
     </row>
     <row r="252" ht="20" customHeight="1">
@@ -7328,7 +7328,7 @@
         </is>
       </c>
       <c r="E252" s="20" t="n">
-        <v>191</v>
+        <v>152</v>
       </c>
     </row>
     <row r="253" ht="20" customHeight="1">
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="E253" s="23" t="n">
-        <v>229</v>
+        <v>153</v>
       </c>
     </row>
     <row r="254" ht="20" customHeight="1">
@@ -7378,7 +7378,7 @@
         </is>
       </c>
       <c r="E254" s="20" t="n">
-        <v>230</v>
+        <v>216</v>
       </c>
     </row>
     <row r="255" ht="20" customHeight="1">
@@ -7403,7 +7403,7 @@
         </is>
       </c>
       <c r="E255" s="23" t="n">
-        <v>128</v>
+        <v>223</v>
       </c>
     </row>
     <row r="256" ht="20" customHeight="1">
@@ -7428,7 +7428,7 @@
         </is>
       </c>
       <c r="E256" s="20" t="n">
-        <v>138</v>
+        <v>206</v>
       </c>
     </row>
     <row r="257" ht="20" customHeight="1">
@@ -7453,7 +7453,7 @@
         </is>
       </c>
       <c r="E257" s="23" t="n">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="258" ht="20" customHeight="1">
@@ -7478,7 +7478,7 @@
         </is>
       </c>
       <c r="E258" s="20" t="n">
-        <v>111</v>
+        <v>190</v>
       </c>
     </row>
     <row r="259" ht="20" customHeight="1">
@@ -7503,7 +7503,7 @@
         </is>
       </c>
       <c r="E259" s="23" t="n">
-        <v>137</v>
+        <v>239</v>
       </c>
     </row>
     <row r="260" ht="20" customHeight="1">
@@ -7528,7 +7528,7 @@
         </is>
       </c>
       <c r="E260" s="20" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="261" ht="20" customHeight="1">
@@ -7553,7 +7553,7 @@
         </is>
       </c>
       <c r="E261" s="23" t="n">
-        <v>130</v>
+        <v>173</v>
       </c>
     </row>
     <row r="262" ht="20" customHeight="1">
@@ -7578,7 +7578,7 @@
         </is>
       </c>
       <c r="E262" s="20" t="n">
-        <v>195</v>
+        <v>124</v>
       </c>
     </row>
     <row r="263" ht="20" customHeight="1">
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="E263" s="23" t="n">
-        <v>143</v>
+        <v>136</v>
       </c>
     </row>
     <row r="264" ht="20" customHeight="1">
@@ -7628,7 +7628,7 @@
         </is>
       </c>
       <c r="E264" s="20" t="n">
-        <v>186</v>
+        <v>143</v>
       </c>
     </row>
     <row r="265" ht="20" customHeight="1">
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="E265" s="23" t="n">
-        <v>221</v>
+        <v>136</v>
       </c>
     </row>
     <row r="266" ht="20" customHeight="1">
@@ -7678,7 +7678,7 @@
         </is>
       </c>
       <c r="E266" s="20" t="n">
-        <v>131</v>
+        <v>142</v>
       </c>
     </row>
     <row r="267" ht="20" customHeight="1">
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="E267" s="23" t="n">
-        <v>239</v>
+        <v>146</v>
       </c>
     </row>
     <row r="268" ht="20" customHeight="1">
@@ -7728,7 +7728,7 @@
         </is>
       </c>
       <c r="E268" s="20" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="269" ht="20" customHeight="1">
@@ -7753,7 +7753,7 @@
         </is>
       </c>
       <c r="E269" s="23" t="n">
-        <v>142</v>
+        <v>192</v>
       </c>
     </row>
     <row r="270" ht="20" customHeight="1">
@@ -7778,7 +7778,7 @@
         </is>
       </c>
       <c r="E270" s="20" t="n">
-        <v>139</v>
+        <v>235</v>
       </c>
     </row>
     <row r="271" ht="20" customHeight="1">
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="E271" s="23" t="n">
-        <v>127</v>
+        <v>166</v>
       </c>
     </row>
     <row r="272" ht="20" customHeight="1">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="E272" s="20" t="n">
-        <v>200</v>
+        <v>194</v>
       </c>
     </row>
     <row r="273" ht="20" customHeight="1">
@@ -7853,7 +7853,7 @@
         </is>
       </c>
       <c r="E273" s="23" t="n">
-        <v>159</v>
+        <v>229</v>
       </c>
     </row>
     <row r="274" ht="20" customHeight="1">
@@ -7878,7 +7878,7 @@
         </is>
       </c>
       <c r="E274" s="20" t="n">
-        <v>113</v>
+        <v>139</v>
       </c>
     </row>
     <row r="275" ht="20" customHeight="1">
@@ -7903,7 +7903,7 @@
         </is>
       </c>
       <c r="E275" s="23" t="n">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="276" ht="20" customHeight="1">
@@ -7928,7 +7928,7 @@
         </is>
       </c>
       <c r="E276" s="20" t="n">
-        <v>173</v>
+        <v>201</v>
       </c>
     </row>
     <row r="277" ht="20" customHeight="1">
@@ -7953,7 +7953,7 @@
         </is>
       </c>
       <c r="E277" s="23" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="278" ht="20" customHeight="1">
@@ -7978,7 +7978,7 @@
         </is>
       </c>
       <c r="E278" s="20" t="n">
-        <v>194</v>
+        <v>161</v>
       </c>
     </row>
     <row r="279" ht="20" customHeight="1">
@@ -8003,7 +8003,7 @@
         </is>
       </c>
       <c r="E279" s="23" t="n">
-        <v>230</v>
+        <v>141</v>
       </c>
     </row>
     <row r="280" ht="20" customHeight="1">
@@ -8028,7 +8028,7 @@
         </is>
       </c>
       <c r="E280" s="20" t="n">
-        <v>138</v>
+        <v>221</v>
       </c>
     </row>
     <row r="281" ht="20" customHeight="1">
@@ -8053,7 +8053,7 @@
         </is>
       </c>
       <c r="E281" s="23" t="n">
-        <v>200</v>
+        <v>191</v>
       </c>
     </row>
     <row r="282" ht="20" customHeight="1">
@@ -8078,7 +8078,7 @@
         </is>
       </c>
       <c r="E282" s="20" t="n">
-        <v>119</v>
+        <v>160</v>
       </c>
     </row>
     <row r="283" ht="20" customHeight="1">
@@ -8103,7 +8103,7 @@
         </is>
       </c>
       <c r="E283" s="23" t="n">
-        <v>144</v>
+        <v>202</v>
       </c>
     </row>
     <row r="284" ht="20" customHeight="1">
@@ -8128,7 +8128,7 @@
         </is>
       </c>
       <c r="E284" s="20" t="n">
-        <v>162</v>
+        <v>142</v>
       </c>
     </row>
     <row r="285" ht="20" customHeight="1">
@@ -8153,7 +8153,7 @@
         </is>
       </c>
       <c r="E285" s="23" t="n">
-        <v>144</v>
+        <v>206</v>
       </c>
     </row>
     <row r="286" ht="20" customHeight="1">
@@ -8178,7 +8178,7 @@
         </is>
       </c>
       <c r="E286" s="20" t="n">
-        <v>204</v>
+        <v>184</v>
       </c>
     </row>
     <row r="287" ht="20" customHeight="1">
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="E287" s="23" t="n">
-        <v>191</v>
+        <v>116</v>
       </c>
     </row>
     <row r="288" ht="20" customHeight="1">
@@ -8228,7 +8228,7 @@
         </is>
       </c>
       <c r="E288" s="20" t="n">
-        <v>130</v>
+        <v>164</v>
       </c>
     </row>
     <row r="289" ht="20" customHeight="1">
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="E289" s="23" t="n">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="290" ht="20" customHeight="1">
@@ -8278,7 +8278,7 @@
         </is>
       </c>
       <c r="E290" s="20" t="n">
-        <v>162</v>
+        <v>204</v>
       </c>
     </row>
     <row r="291" ht="20" customHeight="1">
@@ -8303,7 +8303,7 @@
         </is>
       </c>
       <c r="E291" s="23" t="n">
-        <v>189</v>
+        <v>157</v>
       </c>
     </row>
     <row r="292" ht="20" customHeight="1">
@@ -8328,7 +8328,7 @@
         </is>
       </c>
       <c r="E292" s="20" t="n">
-        <v>231</v>
+        <v>212</v>
       </c>
     </row>
     <row r="293" ht="20" customHeight="1">
@@ -8353,7 +8353,7 @@
         </is>
       </c>
       <c r="E293" s="23" t="n">
-        <v>152</v>
+        <v>110</v>
       </c>
     </row>
     <row r="294" ht="20" customHeight="1">
@@ -8378,7 +8378,7 @@
         </is>
       </c>
       <c r="E294" s="20" t="n">
-        <v>157</v>
+        <v>165</v>
       </c>
     </row>
     <row r="295" ht="20" customHeight="1">
@@ -8403,7 +8403,7 @@
         </is>
       </c>
       <c r="E295" s="23" t="n">
-        <v>212</v>
+        <v>156</v>
       </c>
     </row>
     <row r="296" ht="20" customHeight="1">
@@ -8428,7 +8428,7 @@
         </is>
       </c>
       <c r="E296" s="20" t="n">
-        <v>177</v>
+        <v>232</v>
       </c>
     </row>
     <row r="297" ht="20" customHeight="1">
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="E297" s="23" t="n">
-        <v>227</v>
+        <v>111</v>
       </c>
     </row>
     <row r="298" ht="20" customHeight="1">
@@ -8478,7 +8478,7 @@
         </is>
       </c>
       <c r="E298" s="20" t="n">
-        <v>115</v>
+        <v>237</v>
       </c>
     </row>
     <row r="299" ht="20" customHeight="1">
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="E299" s="23" t="n">
-        <v>190</v>
+        <v>225</v>
       </c>
     </row>
     <row r="300" ht="20" customHeight="1">
@@ -8528,7 +8528,7 @@
         </is>
       </c>
       <c r="E300" s="20" t="n">
-        <v>166</v>
+        <v>237</v>
       </c>
     </row>
     <row r="301" ht="20" customHeight="1">
@@ -8553,7 +8553,7 @@
         </is>
       </c>
       <c r="E301" s="23" t="n">
-        <v>209</v>
+        <v>114</v>
       </c>
     </row>
     <row r="302" ht="20" customHeight="1">
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="E302" s="20" t="n">
-        <v>136</v>
+        <v>161</v>
       </c>
     </row>
     <row r="303" ht="20" customHeight="1">
@@ -8603,7 +8603,7 @@
         </is>
       </c>
       <c r="E303" s="23" t="n">
-        <v>216</v>
+        <v>234</v>
       </c>
     </row>
     <row r="304" ht="20" customHeight="1">
@@ -8628,7 +8628,7 @@
         </is>
       </c>
       <c r="E304" s="20" t="n">
-        <v>133</v>
+        <v>203</v>
       </c>
     </row>
     <row r="305" ht="20" customHeight="1">
@@ -8653,7 +8653,7 @@
         </is>
       </c>
       <c r="E305" s="23" t="n">
-        <v>176</v>
+        <v>123</v>
       </c>
     </row>
     <row r="306" ht="20" customHeight="1">
@@ -8678,7 +8678,7 @@
         </is>
       </c>
       <c r="E306" s="20" t="n">
-        <v>118</v>
+        <v>219</v>
       </c>
     </row>
     <row r="307" ht="20" customHeight="1">
@@ -8703,7 +8703,7 @@
         </is>
       </c>
       <c r="E307" s="23" t="n">
-        <v>156</v>
+        <v>122</v>
       </c>
     </row>
     <row r="308" ht="20" customHeight="1">
@@ -8728,7 +8728,7 @@
         </is>
       </c>
       <c r="E308" s="20" t="n">
-        <v>235</v>
+        <v>206</v>
       </c>
     </row>
     <row r="309" ht="20" customHeight="1">
@@ -8753,7 +8753,7 @@
         </is>
       </c>
       <c r="E309" s="23" t="n">
-        <v>127</v>
+        <v>178</v>
       </c>
     </row>
     <row r="310" ht="20" customHeight="1">
@@ -8778,7 +8778,7 @@
         </is>
       </c>
       <c r="E310" s="20" t="n">
-        <v>174</v>
+        <v>219</v>
       </c>
     </row>
     <row r="311" ht="20" customHeight="1">
@@ -8803,7 +8803,7 @@
         </is>
       </c>
       <c r="E311" s="23" t="n">
-        <v>168</v>
+        <v>205</v>
       </c>
     </row>
     <row r="312" ht="20" customHeight="1">
@@ -8828,7 +8828,7 @@
         </is>
       </c>
       <c r="E312" s="20" t="n">
-        <v>154</v>
+        <v>234</v>
       </c>
     </row>
     <row r="313" ht="20" customHeight="1">
@@ -8853,7 +8853,7 @@
         </is>
       </c>
       <c r="E313" s="23" t="n">
-        <v>115</v>
+        <v>176</v>
       </c>
     </row>
     <row r="314" ht="20" customHeight="1">
@@ -8878,7 +8878,7 @@
         </is>
       </c>
       <c r="E314" s="20" t="n">
-        <v>135</v>
+        <v>217</v>
       </c>
     </row>
     <row r="315" ht="20" customHeight="1">
@@ -8903,7 +8903,7 @@
         </is>
       </c>
       <c r="E315" s="23" t="n">
-        <v>151</v>
+        <v>123</v>
       </c>
     </row>
     <row r="316" ht="20" customHeight="1">
@@ -8928,7 +8928,7 @@
         </is>
       </c>
       <c r="E316" s="20" t="n">
-        <v>238</v>
+        <v>169</v>
       </c>
     </row>
     <row r="317" ht="20" customHeight="1">
@@ -8953,7 +8953,7 @@
         </is>
       </c>
       <c r="E317" s="23" t="n">
-        <v>154</v>
+        <v>119</v>
       </c>
     </row>
     <row r="318" ht="20" customHeight="1">
@@ -8978,7 +8978,7 @@
         </is>
       </c>
       <c r="E318" s="20" t="n">
-        <v>176</v>
+        <v>187</v>
       </c>
     </row>
     <row r="319" ht="20" customHeight="1">
@@ -9003,7 +9003,7 @@
         </is>
       </c>
       <c r="E319" s="23" t="n">
-        <v>231</v>
+        <v>196</v>
       </c>
     </row>
     <row r="320" ht="20" customHeight="1">
@@ -9028,7 +9028,7 @@
         </is>
       </c>
       <c r="E320" s="20" t="n">
-        <v>129</v>
+        <v>158</v>
       </c>
     </row>
     <row r="321" ht="20" customHeight="1">
@@ -9053,7 +9053,7 @@
         </is>
       </c>
       <c r="E321" s="23" t="n">
-        <v>182</v>
+        <v>126</v>
       </c>
     </row>
     <row r="322" ht="20" customHeight="1">
@@ -9078,7 +9078,7 @@
         </is>
       </c>
       <c r="E322" s="20" t="n">
-        <v>163</v>
+        <v>118</v>
       </c>
     </row>
     <row r="323" ht="20" customHeight="1">
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="E323" s="23" t="n">
-        <v>114</v>
+        <v>211</v>
       </c>
     </row>
     <row r="324" ht="20" customHeight="1">
@@ -9128,7 +9128,7 @@
         </is>
       </c>
       <c r="E324" s="20" t="n">
-        <v>125</v>
+        <v>213</v>
       </c>
     </row>
     <row r="325" ht="20" customHeight="1">
@@ -9153,7 +9153,7 @@
         </is>
       </c>
       <c r="E325" s="23" t="n">
-        <v>159</v>
+        <v>198</v>
       </c>
     </row>
     <row r="326" ht="20" customHeight="1">
@@ -9178,7 +9178,7 @@
         </is>
       </c>
       <c r="E326" s="20" t="n">
-        <v>152</v>
+        <v>211</v>
       </c>
     </row>
     <row r="327" ht="20" customHeight="1">
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="E327" s="23" t="n">
-        <v>111</v>
+        <v>139</v>
       </c>
     </row>
     <row r="328" ht="20" customHeight="1">
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="E328" s="20" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="329" ht="20" customHeight="1">
@@ -9253,7 +9253,7 @@
         </is>
       </c>
       <c r="E329" s="23" t="n">
-        <v>166</v>
+        <v>197</v>
       </c>
     </row>
     <row r="330" ht="20" customHeight="1">
@@ -9278,7 +9278,7 @@
         </is>
       </c>
       <c r="E330" s="20" t="n">
-        <v>111</v>
+        <v>123</v>
       </c>
     </row>
     <row r="331" ht="20" customHeight="1">
@@ -9303,7 +9303,7 @@
         </is>
       </c>
       <c r="E331" s="23" t="n">
-        <v>160</v>
+        <v>231</v>
       </c>
     </row>
     <row r="332" ht="20" customHeight="1">
@@ -9328,7 +9328,7 @@
         </is>
       </c>
       <c r="E332" s="20" t="n">
-        <v>176</v>
+        <v>204</v>
       </c>
     </row>
     <row r="333" ht="20" customHeight="1">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="E333" s="23" t="n">
-        <v>210</v>
+        <v>143</v>
       </c>
     </row>
     <row r="334" ht="20" customHeight="1">
@@ -9378,7 +9378,7 @@
         </is>
       </c>
       <c r="E334" s="20" t="n">
-        <v>176</v>
+        <v>230</v>
       </c>
     </row>
     <row r="335" ht="20" customHeight="1">
@@ -9403,7 +9403,7 @@
         </is>
       </c>
       <c r="E335" s="23" t="n">
-        <v>231</v>
+        <v>128</v>
       </c>
     </row>
     <row r="336" ht="20" customHeight="1">
@@ -9428,7 +9428,7 @@
         </is>
       </c>
       <c r="E336" s="20" t="n">
-        <v>232</v>
+        <v>190</v>
       </c>
     </row>
     <row r="337" ht="20" customHeight="1">
@@ -9453,7 +9453,7 @@
         </is>
       </c>
       <c r="E337" s="23" t="n">
-        <v>239</v>
+        <v>231</v>
       </c>
     </row>
     <row r="338" ht="20" customHeight="1">
@@ -9478,7 +9478,7 @@
         </is>
       </c>
       <c r="E338" s="20" t="n">
-        <v>138</v>
+        <v>150</v>
       </c>
     </row>
     <row r="339" ht="20" customHeight="1">
@@ -9503,7 +9503,7 @@
         </is>
       </c>
       <c r="E339" s="23" t="n">
-        <v>220</v>
+        <v>157</v>
       </c>
     </row>
     <row r="340" ht="20" customHeight="1">
@@ -9528,7 +9528,7 @@
         </is>
       </c>
       <c r="E340" s="20" t="n">
-        <v>148</v>
+        <v>189</v>
       </c>
     </row>
     <row r="341" ht="20" customHeight="1">
@@ -9553,7 +9553,7 @@
         </is>
       </c>
       <c r="E341" s="23" t="n">
-        <v>234</v>
+        <v>221</v>
       </c>
     </row>
     <row r="342" ht="20" customHeight="1">
@@ -9578,7 +9578,7 @@
         </is>
       </c>
       <c r="E342" s="20" t="n">
-        <v>197</v>
+        <v>158</v>
       </c>
     </row>
     <row r="343" ht="20" customHeight="1">
@@ -9603,7 +9603,7 @@
         </is>
       </c>
       <c r="E343" s="23" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
     </row>
     <row r="344" ht="20" customHeight="1">
@@ -9628,7 +9628,7 @@
         </is>
       </c>
       <c r="E344" s="20" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="345" ht="20" customHeight="1">
@@ -9653,7 +9653,7 @@
         </is>
       </c>
       <c r="E345" s="23" t="n">
-        <v>112</v>
+        <v>141</v>
       </c>
     </row>
     <row r="346" ht="20" customHeight="1">
@@ -9678,7 +9678,7 @@
         </is>
       </c>
       <c r="E346" s="20" t="n">
-        <v>215</v>
+        <v>182</v>
       </c>
     </row>
     <row r="347" ht="20" customHeight="1">
@@ -9703,7 +9703,7 @@
         </is>
       </c>
       <c r="E347" s="23" t="n">
-        <v>114</v>
+        <v>125</v>
       </c>
     </row>
     <row r="348" ht="20" customHeight="1">
@@ -9728,7 +9728,7 @@
         </is>
       </c>
       <c r="E348" s="20" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
     </row>
     <row r="349" ht="20" customHeight="1">
@@ -9753,7 +9753,7 @@
         </is>
       </c>
       <c r="E349" s="23" t="n">
-        <v>154</v>
+        <v>215</v>
       </c>
     </row>
     <row r="350" ht="20" customHeight="1">
@@ -9778,7 +9778,7 @@
         </is>
       </c>
       <c r="E350" s="20" t="n">
-        <v>131</v>
+        <v>174</v>
       </c>
     </row>
     <row r="351" ht="20" customHeight="1">
@@ -9803,7 +9803,7 @@
         </is>
       </c>
       <c r="E351" s="23" t="n">
-        <v>159</v>
+        <v>220</v>
       </c>
     </row>
     <row r="352" ht="20" customHeight="1">
@@ -9828,7 +9828,7 @@
         </is>
       </c>
       <c r="E352" s="20" t="n">
-        <v>211</v>
+        <v>121</v>
       </c>
     </row>
     <row r="353" ht="20" customHeight="1">
@@ -9853,7 +9853,7 @@
         </is>
       </c>
       <c r="E353" s="23" t="n">
-        <v>198</v>
+        <v>231</v>
       </c>
     </row>
     <row r="354" ht="20" customHeight="1">
@@ -9878,7 +9878,7 @@
         </is>
       </c>
       <c r="E354" s="20" t="n">
-        <v>236</v>
+        <v>188</v>
       </c>
     </row>
     <row r="355" ht="20" customHeight="1">
@@ -9903,7 +9903,7 @@
         </is>
       </c>
       <c r="E355" s="23" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="356" ht="20" customHeight="1">
@@ -9928,7 +9928,7 @@
         </is>
       </c>
       <c r="E356" s="20" t="n">
-        <v>176</v>
+        <v>113</v>
       </c>
     </row>
     <row r="357" ht="20" customHeight="1">
@@ -9953,7 +9953,7 @@
         </is>
       </c>
       <c r="E357" s="23" t="n">
-        <v>233</v>
+        <v>157</v>
       </c>
     </row>
     <row r="358" ht="20" customHeight="1">
@@ -9978,7 +9978,7 @@
         </is>
       </c>
       <c r="E358" s="20" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="359" ht="20" customHeight="1">
@@ -10003,7 +10003,7 @@
         </is>
       </c>
       <c r="E359" s="23" t="n">
-        <v>228</v>
+        <v>136</v>
       </c>
     </row>
     <row r="360" ht="20" customHeight="1">
@@ -10028,7 +10028,7 @@
         </is>
       </c>
       <c r="E360" s="20" t="n">
-        <v>143</v>
+        <v>117</v>
       </c>
     </row>
     <row r="361" ht="20" customHeight="1">
@@ -10053,7 +10053,7 @@
         </is>
       </c>
       <c r="E361" s="23" t="n">
-        <v>157</v>
+        <v>128</v>
       </c>
     </row>
     <row r="362" ht="20" customHeight="1">
@@ -10078,7 +10078,7 @@
         </is>
       </c>
       <c r="E362" s="20" t="n">
-        <v>222</v>
+        <v>229</v>
       </c>
     </row>
     <row r="363" ht="20" customHeight="1">
@@ -10103,7 +10103,7 @@
         </is>
       </c>
       <c r="E363" s="23" t="n">
-        <v>179</v>
+        <v>136</v>
       </c>
     </row>
     <row r="364" ht="20" customHeight="1">
@@ -10128,7 +10128,7 @@
         </is>
       </c>
       <c r="E364" s="20" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
     </row>
     <row r="365" ht="20" customHeight="1">
@@ -10153,7 +10153,7 @@
         </is>
       </c>
       <c r="E365" s="23" t="n">
-        <v>237</v>
+        <v>182</v>
       </c>
     </row>
     <row r="366" ht="20" customHeight="1">
@@ -10178,7 +10178,7 @@
         </is>
       </c>
       <c r="E366" s="20" t="n">
-        <v>114</v>
+        <v>128</v>
       </c>
     </row>
     <row r="367" ht="20" customHeight="1">
@@ -10203,7 +10203,7 @@
         </is>
       </c>
       <c r="E367" s="23" t="n">
-        <v>160</v>
+        <v>181</v>
       </c>
     </row>
     <row r="368" ht="20" customHeight="1">
@@ -10228,7 +10228,7 @@
         </is>
       </c>
       <c r="E368" s="20" t="n">
-        <v>163</v>
+        <v>208</v>
       </c>
     </row>
     <row r="369" ht="20" customHeight="1">
@@ -10253,7 +10253,7 @@
         </is>
       </c>
       <c r="E369" s="23" t="n">
-        <v>202</v>
+        <v>194</v>
       </c>
     </row>
     <row r="370" ht="20" customHeight="1">
@@ -10278,7 +10278,7 @@
         </is>
       </c>
       <c r="E370" s="20" t="n">
-        <v>136</v>
+        <v>192</v>
       </c>
     </row>
     <row r="371" ht="20" customHeight="1">
@@ -10303,7 +10303,7 @@
         </is>
       </c>
       <c r="E371" s="23" t="n">
-        <v>157</v>
+        <v>111</v>
       </c>
     </row>
     <row r="372" ht="20" customHeight="1">
@@ -10328,7 +10328,7 @@
         </is>
       </c>
       <c r="E372" s="20" t="n">
-        <v>168</v>
+        <v>200</v>
       </c>
     </row>
     <row r="373" ht="20" customHeight="1">
@@ -10353,7 +10353,7 @@
         </is>
       </c>
       <c r="E373" s="23" t="n">
-        <v>240</v>
+        <v>226</v>
       </c>
     </row>
     <row r="374" ht="20" customHeight="1">
@@ -10378,7 +10378,7 @@
         </is>
       </c>
       <c r="E374" s="20" t="n">
-        <v>135</v>
+        <v>128</v>
       </c>
     </row>
     <row r="375" ht="20" customHeight="1">
@@ -10403,7 +10403,7 @@
         </is>
       </c>
       <c r="E375" s="23" t="n">
-        <v>148</v>
+        <v>221</v>
       </c>
     </row>
     <row r="376" ht="20" customHeight="1">
@@ -10428,7 +10428,7 @@
         </is>
       </c>
       <c r="E376" s="20" t="n">
-        <v>223</v>
+        <v>112</v>
       </c>
     </row>
     <row r="377" ht="20" customHeight="1">
@@ -10453,7 +10453,7 @@
         </is>
       </c>
       <c r="E377" s="23" t="n">
-        <v>124</v>
+        <v>156</v>
       </c>
     </row>
     <row r="378" ht="20" customHeight="1">
@@ -10478,7 +10478,7 @@
         </is>
       </c>
       <c r="E378" s="20" t="n">
-        <v>194</v>
+        <v>200</v>
       </c>
     </row>
     <row r="379" ht="20" customHeight="1">
@@ -10503,7 +10503,7 @@
         </is>
       </c>
       <c r="E379" s="23" t="n">
-        <v>157</v>
+        <v>228</v>
       </c>
     </row>
     <row r="380" ht="20" customHeight="1">
@@ -10528,7 +10528,7 @@
         </is>
       </c>
       <c r="E380" s="20" t="n">
-        <v>216</v>
+        <v>237</v>
       </c>
     </row>
     <row r="381" ht="20" customHeight="1">
@@ -10553,7 +10553,7 @@
         </is>
       </c>
       <c r="E381" s="23" t="n">
-        <v>206</v>
+        <v>157</v>
       </c>
     </row>
     <row r="382" ht="20" customHeight="1">
@@ -10578,7 +10578,7 @@
         </is>
       </c>
       <c r="E382" s="20" t="n">
-        <v>176</v>
+        <v>142</v>
       </c>
     </row>
     <row r="383" ht="20" customHeight="1">
@@ -10603,7 +10603,7 @@
         </is>
       </c>
       <c r="E383" s="23" t="n">
-        <v>174</v>
+        <v>167</v>
       </c>
     </row>
     <row r="384" ht="20" customHeight="1">
@@ -10628,7 +10628,7 @@
         </is>
       </c>
       <c r="E384" s="20" t="n">
-        <v>239</v>
+        <v>173</v>
       </c>
     </row>
     <row r="385" ht="20" customHeight="1">
@@ -10653,7 +10653,7 @@
         </is>
       </c>
       <c r="E385" s="23" t="n">
-        <v>211</v>
+        <v>126</v>
       </c>
     </row>
     <row r="386" ht="20" customHeight="1">
@@ -10678,7 +10678,7 @@
         </is>
       </c>
       <c r="E386" s="20" t="n">
-        <v>206</v>
+        <v>164</v>
       </c>
     </row>
     <row r="387" ht="20" customHeight="1">
@@ -10703,7 +10703,7 @@
         </is>
       </c>
       <c r="E387" s="23" t="n">
-        <v>235</v>
+        <v>183</v>
       </c>
     </row>
     <row r="388" ht="20" customHeight="1">
@@ -10728,7 +10728,7 @@
         </is>
       </c>
       <c r="E388" s="20" t="n">
-        <v>215</v>
+        <v>170</v>
       </c>
     </row>
     <row r="389" ht="20" customHeight="1">
@@ -10753,7 +10753,7 @@
         </is>
       </c>
       <c r="E389" s="23" t="n">
-        <v>212</v>
+        <v>225</v>
       </c>
     </row>
     <row r="390" ht="20" customHeight="1">
@@ -10778,7 +10778,7 @@
         </is>
       </c>
       <c r="E390" s="20" t="n">
-        <v>202</v>
+        <v>127</v>
       </c>
     </row>
     <row r="391" ht="20" customHeight="1">
@@ -10803,7 +10803,7 @@
         </is>
       </c>
       <c r="E391" s="23" t="n">
-        <v>161</v>
+        <v>205</v>
       </c>
     </row>
     <row r="392" ht="20" customHeight="1">
@@ -10828,7 +10828,7 @@
         </is>
       </c>
       <c r="E392" s="20" t="n">
-        <v>185</v>
+        <v>156</v>
       </c>
     </row>
     <row r="393" ht="20" customHeight="1">
@@ -10853,7 +10853,7 @@
         </is>
       </c>
       <c r="E393" s="23" t="n">
-        <v>119</v>
+        <v>161</v>
       </c>
     </row>
     <row r="394" ht="20" customHeight="1">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="E394" s="20" t="n">
-        <v>165</v>
+        <v>132</v>
       </c>
     </row>
     <row r="395" ht="20" customHeight="1">
@@ -10903,7 +10903,7 @@
         </is>
       </c>
       <c r="E395" s="23" t="n">
-        <v>135</v>
+        <v>238</v>
       </c>
     </row>
     <row r="396" ht="20" customHeight="1">
@@ -10928,7 +10928,7 @@
         </is>
       </c>
       <c r="E396" s="20" t="n">
-        <v>203</v>
+        <v>136</v>
       </c>
     </row>
     <row r="397" ht="20" customHeight="1">
@@ -10953,7 +10953,7 @@
         </is>
       </c>
       <c r="E397" s="23" t="n">
-        <v>211</v>
+        <v>218</v>
       </c>
     </row>
     <row r="398" ht="20" customHeight="1">
@@ -10978,7 +10978,7 @@
         </is>
       </c>
       <c r="E398" s="20" t="n">
-        <v>240</v>
+        <v>190</v>
       </c>
     </row>
     <row r="399" ht="20" customHeight="1">
@@ -11003,7 +11003,7 @@
         </is>
       </c>
       <c r="E399" s="23" t="n">
-        <v>134</v>
+        <v>173</v>
       </c>
     </row>
     <row r="400" ht="20" customHeight="1">
@@ -11028,7 +11028,7 @@
         </is>
       </c>
       <c r="E400" s="20" t="n">
-        <v>229</v>
+        <v>214</v>
       </c>
     </row>
     <row r="401" ht="20" customHeight="1">
@@ -11053,7 +11053,7 @@
         </is>
       </c>
       <c r="E401" s="23" t="n">
-        <v>237</v>
+        <v>187</v>
       </c>
     </row>
     <row r="402" ht="20" customHeight="1">
@@ -11078,7 +11078,7 @@
         </is>
       </c>
       <c r="E402" s="20" t="n">
-        <v>199</v>
+        <v>157</v>
       </c>
     </row>
     <row r="403" ht="20" customHeight="1">
@@ -11103,7 +11103,7 @@
         </is>
       </c>
       <c r="E403" s="23" t="n">
-        <v>195</v>
+        <v>213</v>
       </c>
     </row>
     <row r="404" ht="20" customHeight="1">
@@ -11128,7 +11128,7 @@
         </is>
       </c>
       <c r="E404" s="20" t="n">
-        <v>152</v>
+        <v>226</v>
       </c>
     </row>
     <row r="405" ht="20" customHeight="1">
@@ -11153,7 +11153,7 @@
         </is>
       </c>
       <c r="E405" s="23" t="n">
-        <v>238</v>
+        <v>233</v>
       </c>
     </row>
     <row r="406" ht="20" customHeight="1">
@@ -11178,7 +11178,7 @@
         </is>
       </c>
       <c r="E406" s="20" t="n">
-        <v>132</v>
+        <v>162</v>
       </c>
     </row>
     <row r="407" ht="20" customHeight="1">
@@ -11203,7 +11203,7 @@
         </is>
       </c>
       <c r="E407" s="23" t="n">
-        <v>191</v>
+        <v>159</v>
       </c>
     </row>
     <row r="408" ht="20" customHeight="1">
@@ -11228,7 +11228,7 @@
         </is>
       </c>
       <c r="E408" s="20" t="n">
-        <v>141</v>
+        <v>150</v>
       </c>
     </row>
     <row r="409" ht="20" customHeight="1">
@@ -11253,7 +11253,7 @@
         </is>
       </c>
       <c r="E409" s="23" t="n">
-        <v>190</v>
+        <v>135</v>
       </c>
     </row>
     <row r="410" ht="20" customHeight="1">
@@ -11278,7 +11278,7 @@
         </is>
       </c>
       <c r="E410" s="20" t="n">
-        <v>125</v>
+        <v>240</v>
       </c>
     </row>
     <row r="411" ht="20" customHeight="1">
@@ -11303,7 +11303,7 @@
         </is>
       </c>
       <c r="E411" s="23" t="n">
-        <v>240</v>
+        <v>224</v>
       </c>
     </row>
     <row r="412" ht="20" customHeight="1">
@@ -11353,7 +11353,7 @@
         </is>
       </c>
       <c r="E413" s="23" t="n">
-        <v>158</v>
+        <v>152</v>
       </c>
     </row>
     <row r="414" ht="20" customHeight="1">
@@ -11378,7 +11378,7 @@
         </is>
       </c>
       <c r="E414" s="20" t="n">
-        <v>212</v>
+        <v>207</v>
       </c>
     </row>
     <row r="415" ht="20" customHeight="1">
@@ -11403,7 +11403,7 @@
         </is>
       </c>
       <c r="E415" s="23" t="n">
-        <v>221</v>
+        <v>127</v>
       </c>
     </row>
     <row r="416" ht="20" customHeight="1">
@@ -11428,7 +11428,7 @@
         </is>
       </c>
       <c r="E416" s="20" t="n">
-        <v>177</v>
+        <v>232</v>
       </c>
     </row>
     <row r="417" ht="20" customHeight="1">
@@ -11453,7 +11453,7 @@
         </is>
       </c>
       <c r="E417" s="23" t="n">
-        <v>180</v>
+        <v>140</v>
       </c>
     </row>
     <row r="418" ht="20" customHeight="1">
@@ -11478,7 +11478,7 @@
         </is>
       </c>
       <c r="E418" s="20" t="n">
-        <v>182</v>
+        <v>212</v>
       </c>
     </row>
     <row r="419" ht="20" customHeight="1">
@@ -11503,7 +11503,7 @@
         </is>
       </c>
       <c r="E419" s="23" t="n">
-        <v>220</v>
+        <v>202</v>
       </c>
     </row>
     <row r="420" ht="20" customHeight="1">
@@ -11528,7 +11528,7 @@
         </is>
       </c>
       <c r="E420" s="20" t="n">
-        <v>128</v>
+        <v>166</v>
       </c>
     </row>
     <row r="421" ht="20" customHeight="1">
@@ -11553,7 +11553,7 @@
         </is>
       </c>
       <c r="E421" s="23" t="n">
-        <v>210</v>
+        <v>135</v>
       </c>
     </row>
     <row r="422" ht="20" customHeight="1">
@@ -11578,7 +11578,7 @@
         </is>
       </c>
       <c r="E422" s="20" t="n">
-        <v>228</v>
+        <v>151</v>
       </c>
     </row>
     <row r="423" ht="20" customHeight="1">
@@ -11603,7 +11603,7 @@
         </is>
       </c>
       <c r="E423" s="23" t="n">
-        <v>139</v>
+        <v>156</v>
       </c>
     </row>
     <row r="424" ht="20" customHeight="1">
@@ -11628,7 +11628,7 @@
         </is>
       </c>
       <c r="E424" s="20" t="n">
-        <v>195</v>
+        <v>238</v>
       </c>
     </row>
     <row r="425" ht="20" customHeight="1">
@@ -11653,7 +11653,7 @@
         </is>
       </c>
       <c r="E425" s="23" t="n">
-        <v>198</v>
+        <v>205</v>
       </c>
     </row>
     <row r="426" ht="20" customHeight="1">
@@ -11678,7 +11678,7 @@
         </is>
       </c>
       <c r="E426" s="20" t="n">
-        <v>168</v>
+        <v>137</v>
       </c>
     </row>
     <row r="427" ht="20" customHeight="1">
@@ -11703,7 +11703,7 @@
         </is>
       </c>
       <c r="E427" s="23" t="n">
-        <v>219</v>
+        <v>225</v>
       </c>
     </row>
     <row r="428" ht="20" customHeight="1">
@@ -11728,7 +11728,7 @@
         </is>
       </c>
       <c r="E428" s="20" t="n">
-        <v>141</v>
+        <v>190</v>
       </c>
     </row>
     <row r="429" ht="20" customHeight="1">
@@ -11753,7 +11753,7 @@
         </is>
       </c>
       <c r="E429" s="23" t="n">
-        <v>185</v>
+        <v>223</v>
       </c>
     </row>
     <row r="430" ht="20" customHeight="1">
@@ -11778,7 +11778,7 @@
         </is>
       </c>
       <c r="E430" s="20" t="n">
-        <v>176</v>
+        <v>224</v>
       </c>
     </row>
     <row r="431" ht="20" customHeight="1">
@@ -11803,7 +11803,7 @@
         </is>
       </c>
       <c r="E431" s="23" t="n">
-        <v>181</v>
+        <v>154</v>
       </c>
     </row>
     <row r="432" ht="20" customHeight="1">
@@ -11828,7 +11828,7 @@
         </is>
       </c>
       <c r="E432" s="20" t="n">
-        <v>234</v>
+        <v>161</v>
       </c>
     </row>
     <row r="433" ht="20" customHeight="1">
@@ -11853,7 +11853,7 @@
         </is>
       </c>
       <c r="E433" s="23" t="n">
-        <v>183</v>
+        <v>156</v>
       </c>
     </row>
     <row r="434" ht="20" customHeight="1">
@@ -11878,7 +11878,7 @@
         </is>
       </c>
       <c r="E434" s="20" t="n">
-        <v>119</v>
+        <v>149</v>
       </c>
     </row>
     <row r="435" ht="20" customHeight="1">
@@ -11903,7 +11903,7 @@
         </is>
       </c>
       <c r="E435" s="23" t="n">
-        <v>170</v>
+        <v>205</v>
       </c>
     </row>
     <row r="436" ht="20" customHeight="1">
@@ -11928,7 +11928,7 @@
         </is>
       </c>
       <c r="E436" s="20" t="n">
-        <v>197</v>
+        <v>208</v>
       </c>
     </row>
     <row r="437" ht="20" customHeight="1">
@@ -11953,7 +11953,7 @@
         </is>
       </c>
       <c r="E437" s="23" t="n">
-        <v>176</v>
+        <v>212</v>
       </c>
     </row>
     <row r="438" ht="20" customHeight="1">
@@ -11978,7 +11978,7 @@
         </is>
       </c>
       <c r="E438" s="20" t="n">
-        <v>176</v>
+        <v>156</v>
       </c>
     </row>
     <row r="439" ht="20" customHeight="1">
@@ -12003,7 +12003,7 @@
         </is>
       </c>
       <c r="E439" s="23" t="n">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="440" ht="20" customHeight="1">
@@ -12028,7 +12028,7 @@
         </is>
       </c>
       <c r="E440" s="20" t="n">
-        <v>170</v>
+        <v>184</v>
       </c>
     </row>
     <row r="441" ht="20" customHeight="1">
@@ -12053,7 +12053,7 @@
         </is>
       </c>
       <c r="E441" s="23" t="n">
-        <v>130</v>
+        <v>169</v>
       </c>
     </row>
     <row r="442" ht="20" customHeight="1">
@@ -12078,7 +12078,7 @@
         </is>
       </c>
       <c r="E442" s="20" t="n">
-        <v>168</v>
+        <v>203</v>
       </c>
     </row>
     <row r="443" ht="20" customHeight="1">
@@ -12103,7 +12103,7 @@
         </is>
       </c>
       <c r="E443" s="23" t="n">
-        <v>228</v>
+        <v>188</v>
       </c>
     </row>
     <row r="444" ht="20" customHeight="1">
@@ -12153,7 +12153,7 @@
         </is>
       </c>
       <c r="E445" s="23" t="n">
-        <v>182</v>
+        <v>123</v>
       </c>
     </row>
     <row r="446" ht="20" customHeight="1">
@@ -12178,7 +12178,7 @@
         </is>
       </c>
       <c r="E446" s="20" t="n">
-        <v>125</v>
+        <v>176</v>
       </c>
     </row>
     <row r="447" ht="20" customHeight="1">
@@ -12203,7 +12203,7 @@
         </is>
       </c>
       <c r="E447" s="23" t="n">
-        <v>163</v>
+        <v>129</v>
       </c>
     </row>
     <row r="448" ht="20" customHeight="1">
@@ -12228,7 +12228,7 @@
         </is>
       </c>
       <c r="E448" s="20" t="n">
-        <v>148</v>
+        <v>212</v>
       </c>
     </row>
     <row r="449" ht="20" customHeight="1">
@@ -12253,7 +12253,7 @@
         </is>
       </c>
       <c r="E449" s="23" t="n">
-        <v>111</v>
+        <v>235</v>
       </c>
     </row>
     <row r="450" ht="20" customHeight="1">
@@ -12278,7 +12278,7 @@
         </is>
       </c>
       <c r="E450" s="20" t="n">
-        <v>116</v>
+        <v>196</v>
       </c>
     </row>
     <row r="451" ht="20" customHeight="1">
@@ -12303,7 +12303,7 @@
         </is>
       </c>
       <c r="E451" s="23" t="n">
-        <v>192</v>
+        <v>239</v>
       </c>
     </row>
     <row r="452" ht="20" customHeight="1">
@@ -12328,7 +12328,7 @@
         </is>
       </c>
       <c r="E452" s="20" t="n">
-        <v>141</v>
+        <v>236</v>
       </c>
     </row>
     <row r="453" ht="20" customHeight="1">
@@ -12353,7 +12353,7 @@
         </is>
       </c>
       <c r="E453" s="23" t="n">
-        <v>236</v>
+        <v>171</v>
       </c>
     </row>
     <row r="454" ht="20" customHeight="1">
@@ -12378,7 +12378,7 @@
         </is>
       </c>
       <c r="E454" s="20" t="n">
-        <v>149</v>
+        <v>179</v>
       </c>
     </row>
     <row r="455" ht="20" customHeight="1">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="E455" s="23" t="n">
-        <v>229</v>
+        <v>160</v>
       </c>
     </row>
     <row r="456" ht="20" customHeight="1">
@@ -12428,7 +12428,7 @@
         </is>
       </c>
       <c r="E456" s="20" t="n">
-        <v>208</v>
+        <v>164</v>
       </c>
     </row>
     <row r="457" ht="20" customHeight="1">
@@ -12453,7 +12453,7 @@
         </is>
       </c>
       <c r="E457" s="23" t="n">
-        <v>236</v>
+        <v>191</v>
       </c>
     </row>
     <row r="458" ht="20" customHeight="1">
@@ -12478,7 +12478,7 @@
         </is>
       </c>
       <c r="E458" s="20" t="n">
-        <v>164</v>
+        <v>172</v>
       </c>
     </row>
     <row r="459" ht="20" customHeight="1">
@@ -12503,7 +12503,7 @@
         </is>
       </c>
       <c r="E459" s="23" t="n">
-        <v>123</v>
+        <v>235</v>
       </c>
     </row>
     <row r="460" ht="20" customHeight="1">
@@ -12528,7 +12528,7 @@
         </is>
       </c>
       <c r="E460" s="20" t="n">
-        <v>208</v>
+        <v>127</v>
       </c>
     </row>
     <row r="461" ht="20" customHeight="1">
@@ -12553,7 +12553,7 @@
         </is>
       </c>
       <c r="E461" s="23" t="n">
-        <v>133</v>
+        <v>220</v>
       </c>
     </row>
     <row r="462" ht="20" customHeight="1">
@@ -12578,7 +12578,7 @@
         </is>
       </c>
       <c r="E462" s="20" t="n">
-        <v>224</v>
+        <v>233</v>
       </c>
     </row>
     <row r="463" ht="20" customHeight="1">
@@ -12603,7 +12603,7 @@
         </is>
       </c>
       <c r="E463" s="23" t="n">
-        <v>238</v>
+        <v>116</v>
       </c>
     </row>
     <row r="464" ht="20" customHeight="1">
@@ -12628,7 +12628,7 @@
         </is>
       </c>
       <c r="E464" s="20" t="n">
-        <v>126</v>
+        <v>169</v>
       </c>
     </row>
     <row r="465" ht="20" customHeight="1">
@@ -12653,7 +12653,7 @@
         </is>
       </c>
       <c r="E465" s="23" t="n">
-        <v>164</v>
+        <v>230</v>
       </c>
     </row>
     <row r="466" ht="20" customHeight="1">
@@ -12678,7 +12678,7 @@
         </is>
       </c>
       <c r="E466" s="20" t="n">
-        <v>114</v>
+        <v>219</v>
       </c>
     </row>
     <row r="467" ht="20" customHeight="1">
@@ -12703,7 +12703,7 @@
         </is>
       </c>
       <c r="E467" s="23" t="n">
-        <v>120</v>
+        <v>195</v>
       </c>
     </row>
     <row r="468" ht="20" customHeight="1">
@@ -12728,7 +12728,7 @@
         </is>
       </c>
       <c r="E468" s="20" t="n">
-        <v>112</v>
+        <v>119</v>
       </c>
     </row>
     <row r="469" ht="20" customHeight="1">
@@ -12753,7 +12753,7 @@
         </is>
       </c>
       <c r="E469" s="23" t="n">
-        <v>234</v>
+        <v>191</v>
       </c>
     </row>
     <row r="470" ht="20" customHeight="1">
@@ -12778,7 +12778,7 @@
         </is>
       </c>
       <c r="E470" s="20" t="n">
-        <v>189</v>
+        <v>171</v>
       </c>
     </row>
     <row r="471" ht="20" customHeight="1">
@@ -12803,7 +12803,7 @@
         </is>
       </c>
       <c r="E471" s="23" t="n">
-        <v>120</v>
+        <v>202</v>
       </c>
     </row>
     <row r="472" ht="20" customHeight="1">
@@ -12828,7 +12828,7 @@
         </is>
       </c>
       <c r="E472" s="20" t="n">
-        <v>198</v>
+        <v>169</v>
       </c>
     </row>
     <row r="473" ht="20" customHeight="1">
@@ -12853,7 +12853,7 @@
         </is>
       </c>
       <c r="E473" s="23" t="n">
-        <v>197</v>
+        <v>147</v>
       </c>
     </row>
     <row r="474" ht="20" customHeight="1">
@@ -12878,7 +12878,7 @@
         </is>
       </c>
       <c r="E474" s="20" t="n">
-        <v>215</v>
+        <v>204</v>
       </c>
     </row>
     <row r="475" ht="20" customHeight="1">
@@ -12903,7 +12903,7 @@
         </is>
       </c>
       <c r="E475" s="23" t="n">
-        <v>210</v>
+        <v>116</v>
       </c>
     </row>
     <row r="476" ht="20" customHeight="1">
@@ -12928,7 +12928,7 @@
         </is>
       </c>
       <c r="E476" s="20" t="n">
-        <v>190</v>
+        <v>120</v>
       </c>
     </row>
     <row r="477" ht="20" customHeight="1">
@@ -12953,7 +12953,7 @@
         </is>
       </c>
       <c r="E477" s="23" t="n">
-        <v>200</v>
+        <v>235</v>
       </c>
     </row>
     <row r="478" ht="20" customHeight="1">
@@ -12978,7 +12978,7 @@
         </is>
       </c>
       <c r="E478" s="20" t="n">
-        <v>233</v>
+        <v>183</v>
       </c>
     </row>
     <row r="479" ht="20" customHeight="1">
@@ -13003,7 +13003,7 @@
         </is>
       </c>
       <c r="E479" s="23" t="n">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="480" ht="20" customHeight="1">
@@ -13028,7 +13028,7 @@
         </is>
       </c>
       <c r="E480" s="20" t="n">
-        <v>235</v>
+        <v>110</v>
       </c>
     </row>
     <row r="481" ht="20" customHeight="1">
@@ -13053,7 +13053,7 @@
         </is>
       </c>
       <c r="E481" s="23" t="n">
-        <v>198</v>
+        <v>223</v>
       </c>
     </row>
     <row r="482" ht="20" customHeight="1">
@@ -13078,7 +13078,7 @@
         </is>
       </c>
       <c r="E482" s="20" t="n">
-        <v>123</v>
+        <v>159</v>
       </c>
     </row>
     <row r="483" ht="20" customHeight="1">
@@ -13103,7 +13103,7 @@
         </is>
       </c>
       <c r="E483" s="23" t="n">
-        <v>185</v>
+        <v>166</v>
       </c>
     </row>
     <row r="484" ht="20" customHeight="1">
@@ -13128,7 +13128,7 @@
         </is>
       </c>
       <c r="E484" s="20" t="n">
-        <v>135</v>
+        <v>217</v>
       </c>
     </row>
     <row r="485" ht="20" customHeight="1">
@@ -13153,7 +13153,7 @@
         </is>
       </c>
       <c r="E485" s="23" t="n">
-        <v>216</v>
+        <v>118</v>
       </c>
     </row>
     <row r="486" ht="20" customHeight="1">
@@ -13178,7 +13178,7 @@
         </is>
       </c>
       <c r="E486" s="20" t="n">
-        <v>138</v>
+        <v>146</v>
       </c>
     </row>
     <row r="487" ht="20" customHeight="1">
@@ -13203,7 +13203,7 @@
         </is>
       </c>
       <c r="E487" s="23" t="n">
-        <v>113</v>
+        <v>155</v>
       </c>
     </row>
     <row r="488" ht="20" customHeight="1">
@@ -13228,7 +13228,7 @@
         </is>
       </c>
       <c r="E488" s="20" t="n">
-        <v>114</v>
+        <v>207</v>
       </c>
     </row>
     <row r="489" ht="20" customHeight="1">
@@ -13253,7 +13253,7 @@
         </is>
       </c>
       <c r="E489" s="23" t="n">
-        <v>189</v>
+        <v>112</v>
       </c>
     </row>
     <row r="490" ht="20" customHeight="1">
@@ -13278,7 +13278,7 @@
         </is>
       </c>
       <c r="E490" s="20" t="n">
-        <v>111</v>
+        <v>228</v>
       </c>
     </row>
     <row r="491" ht="20" customHeight="1">
@@ -13303,7 +13303,7 @@
         </is>
       </c>
       <c r="E491" s="23" t="n">
-        <v>171</v>
+        <v>198</v>
       </c>
     </row>
     <row r="492" ht="20" customHeight="1">
@@ -13328,7 +13328,7 @@
         </is>
       </c>
       <c r="E492" s="20" t="n">
-        <v>213</v>
+        <v>126</v>
       </c>
     </row>
     <row r="493" ht="20" customHeight="1">
@@ -13353,7 +13353,7 @@
         </is>
       </c>
       <c r="E493" s="23" t="n">
-        <v>205</v>
+        <v>201</v>
       </c>
     </row>
     <row r="494" ht="20" customHeight="1">
@@ -13378,7 +13378,7 @@
         </is>
       </c>
       <c r="E494" s="20" t="n">
-        <v>112</v>
+        <v>219</v>
       </c>
     </row>
     <row r="495" ht="20" customHeight="1">
@@ -13403,7 +13403,7 @@
         </is>
       </c>
       <c r="E495" s="23" t="n">
-        <v>224</v>
+        <v>237</v>
       </c>
     </row>
     <row r="496" ht="20" customHeight="1">
@@ -13428,7 +13428,7 @@
         </is>
       </c>
       <c r="E496" s="20" t="n">
-        <v>112</v>
+        <v>205</v>
       </c>
     </row>
     <row r="497" ht="20" customHeight="1">
@@ -13453,7 +13453,7 @@
         </is>
       </c>
       <c r="E497" s="23" t="n">
-        <v>140</v>
+        <v>236</v>
       </c>
     </row>
     <row r="498" ht="20" customHeight="1">
@@ -13478,7 +13478,7 @@
         </is>
       </c>
       <c r="E498" s="20" t="n">
-        <v>111</v>
+        <v>227</v>
       </c>
     </row>
     <row r="499" ht="20" customHeight="1">
@@ -13503,7 +13503,7 @@
         </is>
       </c>
       <c r="E499" s="23" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="500" ht="20" customHeight="1">
@@ -13528,7 +13528,7 @@
         </is>
       </c>
       <c r="E500" s="20" t="n">
-        <v>142</v>
+        <v>162</v>
       </c>
     </row>
     <row r="501" ht="20" customHeight="1">
@@ -13553,7 +13553,7 @@
         </is>
       </c>
       <c r="E501" s="23" t="n">
-        <v>216</v>
+        <v>221</v>
       </c>
     </row>
     <row r="502" ht="20" customHeight="1">
@@ -13578,7 +13578,7 @@
         </is>
       </c>
       <c r="E502" s="20" t="n">
-        <v>231</v>
+        <v>224</v>
       </c>
     </row>
     <row r="503" ht="20" customHeight="1">
@@ -13603,7 +13603,7 @@
         </is>
       </c>
       <c r="E503" s="23" t="n">
-        <v>190</v>
+        <v>143</v>
       </c>
     </row>
     <row r="504" ht="20" customHeight="1">
@@ -13628,7 +13628,7 @@
         </is>
       </c>
       <c r="E504" s="20" t="n">
-        <v>177</v>
+        <v>226</v>
       </c>
     </row>
     <row r="505" ht="20" customHeight="1">
@@ -13653,7 +13653,7 @@
         </is>
       </c>
       <c r="E505" s="23" t="n">
-        <v>204</v>
+        <v>155</v>
       </c>
     </row>
     <row r="506" ht="20" customHeight="1">
@@ -13678,7 +13678,7 @@
         </is>
       </c>
       <c r="E506" s="20" t="n">
-        <v>161</v>
+        <v>130</v>
       </c>
     </row>
     <row r="507" ht="20" customHeight="1">
@@ -13703,7 +13703,7 @@
         </is>
       </c>
       <c r="E507" s="23" t="n">
-        <v>139</v>
+        <v>238</v>
       </c>
     </row>
     <row r="508" ht="20" customHeight="1">
@@ -13728,7 +13728,7 @@
         </is>
       </c>
       <c r="E508" s="20" t="n">
-        <v>181</v>
+        <v>224</v>
       </c>
     </row>
     <row r="509" ht="20" customHeight="1">
@@ -13753,7 +13753,7 @@
         </is>
       </c>
       <c r="E509" s="23" t="n">
-        <v>171</v>
+        <v>148</v>
       </c>
     </row>
     <row r="510" ht="20" customHeight="1">
@@ -13778,7 +13778,7 @@
         </is>
       </c>
       <c r="E510" s="20" t="n">
-        <v>164</v>
+        <v>149</v>
       </c>
     </row>
     <row r="511" ht="20" customHeight="1">
@@ -13803,7 +13803,7 @@
         </is>
       </c>
       <c r="E511" s="23" t="n">
-        <v>143</v>
+        <v>182</v>
       </c>
     </row>
     <row r="512" ht="20" customHeight="1">
@@ -13828,7 +13828,7 @@
         </is>
       </c>
       <c r="E512" s="20" t="n">
-        <v>127</v>
+        <v>209</v>
       </c>
     </row>
     <row r="513" ht="20" customHeight="1">
@@ -13853,7 +13853,7 @@
         </is>
       </c>
       <c r="E513" s="23" t="n">
-        <v>151</v>
+        <v>227</v>
       </c>
     </row>
     <row r="514" ht="20" customHeight="1">
@@ -13878,7 +13878,7 @@
         </is>
       </c>
       <c r="E514" s="20" t="n">
-        <v>181</v>
+        <v>153</v>
       </c>
     </row>
     <row r="515" ht="20" customHeight="1">
@@ -13903,7 +13903,7 @@
         </is>
       </c>
       <c r="E515" s="23" t="n">
-        <v>136</v>
+        <v>180</v>
       </c>
     </row>
     <row r="516" ht="20" customHeight="1">
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="E516" s="20" t="n">
-        <v>223</v>
+        <v>112</v>
       </c>
     </row>
     <row r="517" ht="20" customHeight="1">
@@ -13953,7 +13953,7 @@
         </is>
       </c>
       <c r="E517" s="23" t="n">
-        <v>217</v>
+        <v>169</v>
       </c>
     </row>
     <row r="518" ht="20" customHeight="1">
@@ -13978,7 +13978,7 @@
         </is>
       </c>
       <c r="E518" s="20" t="n">
-        <v>179</v>
+        <v>146</v>
       </c>
     </row>
     <row r="519" ht="20" customHeight="1">
@@ -14003,7 +14003,7 @@
         </is>
       </c>
       <c r="E519" s="23" t="n">
-        <v>152</v>
+        <v>123</v>
       </c>
     </row>
     <row r="520" ht="20" customHeight="1">
@@ -14028,7 +14028,7 @@
         </is>
       </c>
       <c r="E520" s="20" t="n">
-        <v>127</v>
+        <v>174</v>
       </c>
     </row>
     <row r="521" ht="20" customHeight="1">
@@ -14053,7 +14053,7 @@
         </is>
       </c>
       <c r="E521" s="23" t="n">
-        <v>149</v>
+        <v>139</v>
       </c>
     </row>
     <row r="522" ht="20" customHeight="1">
@@ -14078,7 +14078,7 @@
         </is>
       </c>
       <c r="E522" s="20" t="n">
-        <v>183</v>
+        <v>139</v>
       </c>
     </row>
     <row r="523" ht="20" customHeight="1">
@@ -14103,7 +14103,7 @@
         </is>
       </c>
       <c r="E523" s="23" t="n">
-        <v>114</v>
+        <v>209</v>
       </c>
     </row>
     <row r="524" ht="20" customHeight="1">
@@ -14128,7 +14128,7 @@
         </is>
       </c>
       <c r="E524" s="20" t="n">
-        <v>113</v>
+        <v>175</v>
       </c>
     </row>
     <row r="525" ht="20" customHeight="1">
@@ -14153,7 +14153,7 @@
         </is>
       </c>
       <c r="E525" s="23" t="n">
-        <v>115</v>
+        <v>157</v>
       </c>
     </row>
     <row r="526" ht="20" customHeight="1">
@@ -14178,7 +14178,7 @@
         </is>
       </c>
       <c r="E526" s="20" t="n">
-        <v>202</v>
+        <v>163</v>
       </c>
     </row>
     <row r="527" ht="20" customHeight="1">
@@ -14203,7 +14203,7 @@
         </is>
       </c>
       <c r="E527" s="23" t="n">
-        <v>219</v>
+        <v>119</v>
       </c>
     </row>
     <row r="528" ht="20" customHeight="1">
@@ -14228,7 +14228,7 @@
         </is>
       </c>
       <c r="E528" s="20" t="n">
-        <v>214</v>
+        <v>239</v>
       </c>
     </row>
     <row r="529" ht="20" customHeight="1">
@@ -14253,7 +14253,7 @@
         </is>
       </c>
       <c r="E529" s="23" t="n">
-        <v>219</v>
+        <v>123</v>
       </c>
     </row>
     <row r="530" ht="20" customHeight="1">
@@ -14278,7 +14278,7 @@
         </is>
       </c>
       <c r="E530" s="20" t="n">
-        <v>171</v>
+        <v>194</v>
       </c>
     </row>
     <row r="531" ht="20" customHeight="1">
@@ -14303,7 +14303,7 @@
         </is>
       </c>
       <c r="E531" s="23" t="n">
-        <v>145</v>
+        <v>201</v>
       </c>
     </row>
     <row r="532" ht="20" customHeight="1">
@@ -14328,7 +14328,7 @@
         </is>
       </c>
       <c r="E532" s="20" t="n">
-        <v>195</v>
+        <v>161</v>
       </c>
     </row>
     <row r="533" ht="20" customHeight="1">
@@ -14353,7 +14353,7 @@
         </is>
       </c>
       <c r="E533" s="23" t="n">
-        <v>200</v>
+        <v>165</v>
       </c>
     </row>
     <row r="534" ht="20" customHeight="1">
@@ -14378,7 +14378,7 @@
         </is>
       </c>
       <c r="E534" s="20" t="n">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="535" ht="20" customHeight="1">
@@ -14403,7 +14403,7 @@
         </is>
       </c>
       <c r="E535" s="23" t="n">
-        <v>230</v>
+        <v>169</v>
       </c>
     </row>
     <row r="536" ht="20" customHeight="1">
@@ -14428,7 +14428,7 @@
         </is>
       </c>
       <c r="E536" s="20" t="n">
-        <v>162</v>
+        <v>146</v>
       </c>
     </row>
     <row r="537" ht="20" customHeight="1">
@@ -14453,7 +14453,7 @@
         </is>
       </c>
       <c r="E537" s="23" t="n">
-        <v>172</v>
+        <v>150</v>
       </c>
     </row>
     <row r="538" ht="20" customHeight="1">
@@ -14478,7 +14478,7 @@
         </is>
       </c>
       <c r="E538" s="20" t="n">
-        <v>182</v>
+        <v>141</v>
       </c>
     </row>
     <row r="539" ht="20" customHeight="1">
@@ -14503,7 +14503,7 @@
         </is>
       </c>
       <c r="E539" s="23" t="n">
-        <v>116</v>
+        <v>196</v>
       </c>
     </row>
     <row r="540" ht="20" customHeight="1">
@@ -14528,7 +14528,7 @@
         </is>
       </c>
       <c r="E540" s="20" t="n">
-        <v>112</v>
+        <v>171</v>
       </c>
     </row>
     <row r="541" ht="20" customHeight="1">
@@ -14553,7 +14553,7 @@
         </is>
       </c>
       <c r="E541" s="23" t="n">
-        <v>176</v>
+        <v>192</v>
       </c>
     </row>
     <row r="542" ht="20" customHeight="1">
@@ -14578,7 +14578,7 @@
         </is>
       </c>
       <c r="E542" s="20" t="n">
-        <v>115</v>
+        <v>136</v>
       </c>
     </row>
     <row r="543" ht="20" customHeight="1">
@@ -14603,7 +14603,7 @@
         </is>
       </c>
       <c r="E543" s="23" t="n">
-        <v>175</v>
+        <v>166</v>
       </c>
     </row>
     <row r="544" ht="20" customHeight="1">
@@ -14628,7 +14628,7 @@
         </is>
       </c>
       <c r="E544" s="20" t="n">
-        <v>155</v>
+        <v>194</v>
       </c>
     </row>
     <row r="545" ht="20" customHeight="1">
@@ -14653,7 +14653,7 @@
         </is>
       </c>
       <c r="E545" s="23" t="n">
-        <v>211</v>
+        <v>125</v>
       </c>
     </row>
     <row r="546" ht="20" customHeight="1">
@@ -14678,7 +14678,7 @@
         </is>
       </c>
       <c r="E546" s="20" t="n">
-        <v>169</v>
+        <v>221</v>
       </c>
     </row>
     <row r="547" ht="20" customHeight="1">
@@ -14703,7 +14703,7 @@
         </is>
       </c>
       <c r="E547" s="23" t="n">
-        <v>114</v>
+        <v>155</v>
       </c>
     </row>
     <row r="548" ht="20" customHeight="1">
@@ -14728,7 +14728,7 @@
         </is>
       </c>
       <c r="E548" s="20" t="n">
-        <v>159</v>
+        <v>141</v>
       </c>
     </row>
     <row r="549" ht="20" customHeight="1">
@@ -14753,7 +14753,7 @@
         </is>
       </c>
       <c r="E549" s="23" t="n">
-        <v>202</v>
+        <v>147</v>
       </c>
     </row>
     <row r="550" ht="20" customHeight="1">
@@ -14778,7 +14778,7 @@
         </is>
       </c>
       <c r="E550" s="20" t="n">
-        <v>239</v>
+        <v>181</v>
       </c>
     </row>
     <row r="551" ht="20" customHeight="1">
@@ -14803,7 +14803,7 @@
         </is>
       </c>
       <c r="E551" s="23" t="n">
-        <v>217</v>
+        <v>230</v>
       </c>
     </row>
     <row r="552" ht="20" customHeight="1">
@@ -14828,7 +14828,7 @@
         </is>
       </c>
       <c r="E552" s="20" t="n">
-        <v>122</v>
+        <v>196</v>
       </c>
     </row>
     <row r="553" ht="20" customHeight="1">
@@ -14853,7 +14853,7 @@
         </is>
       </c>
       <c r="E553" s="23" t="n">
-        <v>132</v>
+        <v>225</v>
       </c>
     </row>
     <row r="554" ht="20" customHeight="1">
@@ -14878,7 +14878,7 @@
         </is>
       </c>
       <c r="E554" s="20" t="n">
-        <v>153</v>
+        <v>238</v>
       </c>
     </row>
     <row r="555" ht="20" customHeight="1">
@@ -14903,7 +14903,7 @@
         </is>
       </c>
       <c r="E555" s="23" t="n">
-        <v>186</v>
+        <v>201</v>
       </c>
     </row>
     <row r="556" ht="20" customHeight="1">
@@ -14928,7 +14928,7 @@
         </is>
       </c>
       <c r="E556" s="20" t="n">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="557" ht="20" customHeight="1">
@@ -14953,7 +14953,7 @@
         </is>
       </c>
       <c r="E557" s="23" t="n">
-        <v>169</v>
+        <v>113</v>
       </c>
     </row>
     <row r="558" ht="20" customHeight="1">
@@ -14978,7 +14978,7 @@
         </is>
       </c>
       <c r="E558" s="20" t="n">
-        <v>190</v>
+        <v>184</v>
       </c>
     </row>
     <row r="559" ht="20" customHeight="1">
@@ -15003,7 +15003,7 @@
         </is>
       </c>
       <c r="E559" s="23" t="n">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="560" ht="20" customHeight="1">
@@ -15028,7 +15028,7 @@
         </is>
       </c>
       <c r="E560" s="20" t="n">
-        <v>191</v>
+        <v>225</v>
       </c>
     </row>
     <row r="561" ht="20" customHeight="1">
@@ -15053,7 +15053,7 @@
         </is>
       </c>
       <c r="E561" s="23" t="n">
-        <v>138</v>
+        <v>127</v>
       </c>
     </row>
     <row r="562" ht="20" customHeight="1">
@@ -15078,7 +15078,7 @@
         </is>
       </c>
       <c r="E562" s="20" t="n">
-        <v>205</v>
+        <v>147</v>
       </c>
     </row>
     <row r="563" ht="20" customHeight="1">
@@ -15103,7 +15103,7 @@
         </is>
       </c>
       <c r="E563" s="23" t="n">
-        <v>133</v>
+        <v>184</v>
       </c>
     </row>
     <row r="564" ht="20" customHeight="1">
@@ -15128,7 +15128,7 @@
         </is>
       </c>
       <c r="E564" s="20" t="n">
-        <v>120</v>
+        <v>237</v>
       </c>
     </row>
     <row r="565" ht="20" customHeight="1">
@@ -15153,7 +15153,7 @@
         </is>
       </c>
       <c r="E565" s="23" t="n">
-        <v>226</v>
+        <v>210</v>
       </c>
     </row>
     <row r="566" ht="20" customHeight="1">
@@ -15178,7 +15178,7 @@
         </is>
       </c>
       <c r="E566" s="20" t="n">
-        <v>162</v>
+        <v>126</v>
       </c>
     </row>
     <row r="567" ht="20" customHeight="1">
@@ -15203,7 +15203,7 @@
         </is>
       </c>
       <c r="E567" s="23" t="n">
-        <v>126</v>
+        <v>152</v>
       </c>
     </row>
     <row r="568" ht="20" customHeight="1">
@@ -15228,7 +15228,7 @@
         </is>
       </c>
       <c r="E568" s="20" t="n">
-        <v>161</v>
+        <v>212</v>
       </c>
     </row>
     <row r="569" ht="20" customHeight="1">
@@ -15253,7 +15253,7 @@
         </is>
       </c>
       <c r="E569" s="23" t="n">
-        <v>161</v>
+        <v>200</v>
       </c>
     </row>
     <row r="570" ht="20" customHeight="1">
@@ -15278,7 +15278,7 @@
         </is>
       </c>
       <c r="E570" s="20" t="n">
-        <v>211</v>
+        <v>119</v>
       </c>
     </row>
     <row r="571" ht="20" customHeight="1">
@@ -15303,7 +15303,7 @@
         </is>
       </c>
       <c r="E571" s="23" t="n">
-        <v>183</v>
+        <v>235</v>
       </c>
     </row>
     <row r="572" ht="20" customHeight="1">
@@ -15328,7 +15328,7 @@
         </is>
       </c>
       <c r="E572" s="20" t="n">
-        <v>147</v>
+        <v>128</v>
       </c>
     </row>
     <row r="573" ht="20" customHeight="1">
@@ -15353,7 +15353,7 @@
         </is>
       </c>
       <c r="E573" s="23" t="n">
-        <v>180</v>
+        <v>232</v>
       </c>
     </row>
     <row r="574" ht="20" customHeight="1">
@@ -15378,7 +15378,7 @@
         </is>
       </c>
       <c r="E574" s="20" t="n">
-        <v>132</v>
+        <v>156</v>
       </c>
     </row>
     <row r="575" ht="20" customHeight="1">
@@ -15403,7 +15403,7 @@
         </is>
       </c>
       <c r="E575" s="23" t="n">
-        <v>163</v>
+        <v>215</v>
       </c>
     </row>
     <row r="576" ht="20" customHeight="1">
@@ -15428,7 +15428,7 @@
         </is>
       </c>
       <c r="E576" s="20" t="n">
-        <v>117</v>
+        <v>176</v>
       </c>
     </row>
     <row r="577" ht="20" customHeight="1">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="E577" s="23" t="n">
-        <v>193</v>
+        <v>173</v>
       </c>
     </row>
     <row r="578" ht="20" customHeight="1">
@@ -15478,7 +15478,7 @@
         </is>
       </c>
       <c r="E578" s="20" t="n">
-        <v>201</v>
+        <v>225</v>
       </c>
     </row>
     <row r="579" ht="20" customHeight="1">
@@ -15503,7 +15503,7 @@
         </is>
       </c>
       <c r="E579" s="23" t="n">
-        <v>207</v>
+        <v>180</v>
       </c>
     </row>
     <row r="580" ht="20" customHeight="1">
@@ -15528,7 +15528,7 @@
         </is>
       </c>
       <c r="E580" s="20" t="n">
-        <v>159</v>
+        <v>210</v>
       </c>
     </row>
     <row r="581" ht="20" customHeight="1">
@@ -15553,7 +15553,7 @@
         </is>
       </c>
       <c r="E581" s="23" t="n">
-        <v>203</v>
+        <v>192</v>
       </c>
     </row>
     <row r="582" ht="20" customHeight="1">
@@ -15578,7 +15578,7 @@
         </is>
       </c>
       <c r="E582" s="20" t="n">
-        <v>126</v>
+        <v>167</v>
       </c>
     </row>
     <row r="583" ht="20" customHeight="1">
@@ -15603,7 +15603,7 @@
         </is>
       </c>
       <c r="E583" s="23" t="n">
-        <v>155</v>
+        <v>139</v>
       </c>
     </row>
     <row r="584" ht="20" customHeight="1">
@@ -15628,7 +15628,7 @@
         </is>
       </c>
       <c r="E584" s="20" t="n">
-        <v>141</v>
+        <v>171</v>
       </c>
     </row>
     <row r="585" ht="20" customHeight="1">
@@ -15653,7 +15653,7 @@
         </is>
       </c>
       <c r="E585" s="23" t="n">
-        <v>171</v>
+        <v>181</v>
       </c>
     </row>
     <row r="586" ht="20" customHeight="1">
@@ -15678,7 +15678,7 @@
         </is>
       </c>
       <c r="E586" s="20" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="587" ht="20" customHeight="1">
@@ -15703,7 +15703,7 @@
         </is>
       </c>
       <c r="E587" s="23" t="n">
-        <v>144</v>
+        <v>112</v>
       </c>
     </row>
     <row r="588" ht="20" customHeight="1">
@@ -15728,7 +15728,7 @@
         </is>
       </c>
       <c r="E588" s="20" t="n">
-        <v>139</v>
+        <v>202</v>
       </c>
     </row>
     <row r="589" ht="20" customHeight="1">
@@ -15753,7 +15753,7 @@
         </is>
       </c>
       <c r="E589" s="23" t="n">
-        <v>111</v>
+        <v>161</v>
       </c>
     </row>
     <row r="590" ht="20" customHeight="1">
@@ -15778,7 +15778,7 @@
         </is>
       </c>
       <c r="E590" s="20" t="n">
-        <v>181</v>
+        <v>138</v>
       </c>
     </row>
     <row r="591" ht="20" customHeight="1">
@@ -15803,7 +15803,7 @@
         </is>
       </c>
       <c r="E591" s="23" t="n">
-        <v>203</v>
+        <v>179</v>
       </c>
     </row>
     <row r="592" ht="20" customHeight="1">
@@ -15828,7 +15828,7 @@
         </is>
       </c>
       <c r="E592" s="20" t="n">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="593" ht="20" customHeight="1">
@@ -15853,7 +15853,7 @@
         </is>
       </c>
       <c r="E593" s="23" t="n">
-        <v>224</v>
+        <v>214</v>
       </c>
     </row>
     <row r="594" ht="20" customHeight="1">
@@ -15878,7 +15878,7 @@
         </is>
       </c>
       <c r="E594" s="20" t="n">
-        <v>111</v>
+        <v>126</v>
       </c>
     </row>
     <row r="595" ht="20" customHeight="1">
@@ -15928,7 +15928,7 @@
         </is>
       </c>
       <c r="E596" s="20" t="n">
-        <v>168</v>
+        <v>142</v>
       </c>
     </row>
     <row r="597" ht="20" customHeight="1">
@@ -15953,7 +15953,7 @@
         </is>
       </c>
       <c r="E597" s="23" t="n">
-        <v>162</v>
+        <v>189</v>
       </c>
     </row>
     <row r="598" ht="20" customHeight="1">
@@ -15978,7 +15978,7 @@
         </is>
       </c>
       <c r="E598" s="20" t="n">
-        <v>215</v>
+        <v>165</v>
       </c>
     </row>
     <row r="599" ht="20" customHeight="1">
@@ -16003,7 +16003,7 @@
         </is>
       </c>
       <c r="E599" s="23" t="n">
-        <v>225</v>
+        <v>119</v>
       </c>
     </row>
     <row r="600" ht="20" customHeight="1">
@@ -16028,7 +16028,7 @@
         </is>
       </c>
       <c r="E600" s="20" t="n">
-        <v>160</v>
+        <v>184</v>
       </c>
     </row>
     <row r="601" ht="20" customHeight="1">
@@ -16053,7 +16053,7 @@
         </is>
       </c>
       <c r="E601" s="23" t="n">
-        <v>152</v>
+        <v>144</v>
       </c>
     </row>
     <row r="602" ht="20" customHeight="1">
@@ -16078,7 +16078,7 @@
         </is>
       </c>
       <c r="E602" s="20" t="n">
-        <v>239</v>
+        <v>151</v>
       </c>
     </row>
     <row r="603" ht="20" customHeight="1">
@@ -16103,7 +16103,7 @@
         </is>
       </c>
       <c r="E603" s="23" t="n">
-        <v>237</v>
+        <v>114</v>
       </c>
     </row>
     <row r="604" ht="20" customHeight="1">
@@ -16128,7 +16128,7 @@
         </is>
       </c>
       <c r="E604" s="20" t="n">
-        <v>198</v>
+        <v>135</v>
       </c>
     </row>
     <row r="605" ht="20" customHeight="1">
@@ -16153,7 +16153,7 @@
         </is>
       </c>
       <c r="E605" s="23" t="n">
-        <v>196</v>
+        <v>168</v>
       </c>
     </row>
     <row r="606" ht="20" customHeight="1">
@@ -16178,7 +16178,7 @@
         </is>
       </c>
       <c r="E606" s="20" t="n">
-        <v>216</v>
+        <v>126</v>
       </c>
     </row>
     <row r="607" ht="20" customHeight="1">
@@ -16203,7 +16203,7 @@
         </is>
       </c>
       <c r="E607" s="23" t="n">
-        <v>220</v>
+        <v>174</v>
       </c>
     </row>
     <row r="608" ht="20" customHeight="1">
@@ -16228,7 +16228,7 @@
         </is>
       </c>
       <c r="E608" s="20" t="n">
-        <v>145</v>
+        <v>227</v>
       </c>
     </row>
     <row r="609" ht="20" customHeight="1">
@@ -16253,7 +16253,7 @@
         </is>
       </c>
       <c r="E609" s="23" t="n">
-        <v>178</v>
+        <v>167</v>
       </c>
     </row>
     <row r="610" ht="20" customHeight="1">
@@ -16278,7 +16278,7 @@
         </is>
       </c>
       <c r="E610" s="20" t="n">
-        <v>226</v>
+        <v>116</v>
       </c>
     </row>
     <row r="611" ht="20" customHeight="1">
@@ -16303,7 +16303,7 @@
         </is>
       </c>
       <c r="E611" s="23" t="n">
-        <v>120</v>
+        <v>235</v>
       </c>
     </row>
     <row r="612" ht="20" customHeight="1">
@@ -16328,7 +16328,7 @@
         </is>
       </c>
       <c r="E612" s="20" t="n">
-        <v>194</v>
+        <v>177</v>
       </c>
     </row>
     <row r="613" ht="20" customHeight="1">
@@ -16353,7 +16353,7 @@
         </is>
       </c>
       <c r="E613" s="23" t="n">
-        <v>182</v>
+        <v>212</v>
       </c>
     </row>
     <row r="614" ht="20" customHeight="1">
@@ -16378,7 +16378,7 @@
         </is>
       </c>
       <c r="E614" s="20" t="n">
-        <v>232</v>
+        <v>200</v>
       </c>
     </row>
     <row r="615" ht="20" customHeight="1">
@@ -16403,7 +16403,7 @@
         </is>
       </c>
       <c r="E615" s="23" t="n">
-        <v>137</v>
+        <v>201</v>
       </c>
     </row>
     <row r="616" ht="20" customHeight="1">
@@ -16428,7 +16428,7 @@
         </is>
       </c>
       <c r="E616" s="20" t="n">
-        <v>238</v>
+        <v>225</v>
       </c>
     </row>
     <row r="617" ht="20" customHeight="1">
@@ -16453,7 +16453,7 @@
         </is>
       </c>
       <c r="E617" s="23" t="n">
-        <v>219</v>
+        <v>169</v>
       </c>
     </row>
     <row r="618" ht="20" customHeight="1">
@@ -16478,7 +16478,7 @@
         </is>
       </c>
       <c r="E618" s="20" t="n">
-        <v>163</v>
+        <v>224</v>
       </c>
     </row>
     <row r="619" ht="20" customHeight="1">
@@ -16503,7 +16503,7 @@
         </is>
       </c>
       <c r="E619" s="23" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
     </row>
     <row r="620" ht="20" customHeight="1">
@@ -16528,7 +16528,7 @@
         </is>
       </c>
       <c r="E620" s="20" t="n">
-        <v>129</v>
+        <v>115</v>
       </c>
     </row>
     <row r="621" ht="20" customHeight="1">
@@ -16553,7 +16553,7 @@
         </is>
       </c>
       <c r="E621" s="23" t="n">
-        <v>193</v>
+        <v>122</v>
       </c>
     </row>
     <row r="622" ht="20" customHeight="1">
@@ -16578,7 +16578,7 @@
         </is>
       </c>
       <c r="E622" s="20" t="n">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="623" ht="20" customHeight="1">
@@ -16603,7 +16603,7 @@
         </is>
       </c>
       <c r="E623" s="23" t="n">
-        <v>120</v>
+        <v>183</v>
       </c>
     </row>
     <row r="624" ht="20" customHeight="1">
@@ -16628,7 +16628,7 @@
         </is>
       </c>
       <c r="E624" s="20" t="n">
-        <v>150</v>
+        <v>238</v>
       </c>
     </row>
     <row r="625" ht="20" customHeight="1">
@@ -16653,7 +16653,7 @@
         </is>
       </c>
       <c r="E625" s="23" t="n">
-        <v>139</v>
+        <v>130</v>
       </c>
     </row>
     <row r="626" ht="20" customHeight="1">
@@ -16678,7 +16678,7 @@
         </is>
       </c>
       <c r="E626" s="20" t="n">
-        <v>139</v>
+        <v>236</v>
       </c>
     </row>
     <row r="627" ht="20" customHeight="1">
@@ -16703,7 +16703,7 @@
         </is>
       </c>
       <c r="E627" s="23" t="n">
-        <v>211</v>
+        <v>227</v>
       </c>
     </row>
     <row r="628" ht="20" customHeight="1">
@@ -16728,7 +16728,7 @@
         </is>
       </c>
       <c r="E628" s="20" t="n">
-        <v>211</v>
+        <v>156</v>
       </c>
     </row>
     <row r="629" ht="20" customHeight="1">
@@ -16753,7 +16753,7 @@
         </is>
       </c>
       <c r="E629" s="23" t="n">
-        <v>127</v>
+        <v>181</v>
       </c>
     </row>
     <row r="630" ht="20" customHeight="1">
@@ -16778,7 +16778,7 @@
         </is>
       </c>
       <c r="E630" s="20" t="n">
-        <v>223</v>
+        <v>217</v>
       </c>
     </row>
     <row r="631" ht="20" customHeight="1">
@@ -16803,7 +16803,7 @@
         </is>
       </c>
       <c r="E631" s="23" t="n">
-        <v>209</v>
+        <v>175</v>
       </c>
     </row>
     <row r="632" ht="20" customHeight="1">
@@ -16828,7 +16828,7 @@
         </is>
       </c>
       <c r="E632" s="20" t="n">
-        <v>190</v>
+        <v>170</v>
       </c>
     </row>
     <row r="633" ht="20" customHeight="1">
@@ -16853,7 +16853,7 @@
         </is>
       </c>
       <c r="E633" s="23" t="n">
-        <v>140</v>
+        <v>163</v>
       </c>
     </row>
     <row r="634" ht="20" customHeight="1">
@@ -16878,7 +16878,7 @@
         </is>
       </c>
       <c r="E634" s="20" t="n">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="635" ht="20" customHeight="1">
@@ -16903,7 +16903,7 @@
         </is>
       </c>
       <c r="E635" s="23" t="n">
-        <v>204</v>
+        <v>128</v>
       </c>
     </row>
     <row r="636" ht="20" customHeight="1">
@@ -16928,7 +16928,7 @@
         </is>
       </c>
       <c r="E636" s="20" t="n">
-        <v>234</v>
+        <v>123</v>
       </c>
     </row>
     <row r="637" ht="20" customHeight="1">
@@ -16953,7 +16953,7 @@
         </is>
       </c>
       <c r="E637" s="23" t="n">
-        <v>164</v>
+        <v>237</v>
       </c>
     </row>
     <row r="638" ht="20" customHeight="1">
@@ -16978,7 +16978,7 @@
         </is>
       </c>
       <c r="E638" s="20" t="n">
-        <v>207</v>
+        <v>144</v>
       </c>
     </row>
     <row r="639" ht="20" customHeight="1">
@@ -17003,7 +17003,7 @@
         </is>
       </c>
       <c r="E639" s="23" t="n">
-        <v>198</v>
+        <v>188</v>
       </c>
     </row>
     <row r="640" ht="20" customHeight="1">
@@ -17028,7 +17028,7 @@
         </is>
       </c>
       <c r="E640" s="20" t="n">
-        <v>165</v>
+        <v>235</v>
       </c>
     </row>
     <row r="641" ht="20" customHeight="1">
@@ -17053,7 +17053,7 @@
         </is>
       </c>
       <c r="E641" s="23" t="n">
-        <v>229</v>
+        <v>138</v>
       </c>
     </row>
     <row r="642" ht="20" customHeight="1">
@@ -17078,7 +17078,7 @@
         </is>
       </c>
       <c r="E642" s="20" t="n">
-        <v>126</v>
+        <v>146</v>
       </c>
     </row>
     <row r="643" ht="20" customHeight="1">
@@ -17103,7 +17103,7 @@
         </is>
       </c>
       <c r="E643" s="23" t="n">
-        <v>204</v>
+        <v>209</v>
       </c>
     </row>
     <row r="644" ht="20" customHeight="1">
@@ -17128,7 +17128,7 @@
         </is>
       </c>
       <c r="E644" s="20" t="n">
-        <v>238</v>
+        <v>136</v>
       </c>
     </row>
     <row r="645" ht="20" customHeight="1">
@@ -17153,7 +17153,7 @@
         </is>
       </c>
       <c r="E645" s="23" t="n">
-        <v>127</v>
+        <v>204</v>
       </c>
     </row>
     <row r="646" ht="20" customHeight="1">
@@ -17178,7 +17178,7 @@
         </is>
       </c>
       <c r="E646" s="20" t="n">
-        <v>223</v>
+        <v>149</v>
       </c>
     </row>
     <row r="647" ht="20" customHeight="1">
@@ -17203,7 +17203,7 @@
         </is>
       </c>
       <c r="E647" s="23" t="n">
-        <v>148</v>
+        <v>163</v>
       </c>
     </row>
     <row r="648" ht="20" customHeight="1">
@@ -17228,7 +17228,7 @@
         </is>
       </c>
       <c r="E648" s="20" t="n">
-        <v>208</v>
+        <v>227</v>
       </c>
     </row>
     <row r="649" ht="20" customHeight="1">
@@ -17253,7 +17253,7 @@
         </is>
       </c>
       <c r="E649" s="23" t="n">
-        <v>112</v>
+        <v>210</v>
       </c>
     </row>
     <row r="650" ht="20" customHeight="1">
@@ -17278,7 +17278,7 @@
         </is>
       </c>
       <c r="E650" s="20" t="n">
-        <v>139</v>
+        <v>129</v>
       </c>
     </row>
     <row r="651" ht="20" customHeight="1">
@@ -17303,7 +17303,7 @@
         </is>
       </c>
       <c r="E651" s="23" t="n">
-        <v>175</v>
+        <v>132</v>
       </c>
     </row>
     <row r="652" ht="20" customHeight="1">
@@ -17328,7 +17328,7 @@
         </is>
       </c>
       <c r="E652" s="20" t="n">
-        <v>232</v>
+        <v>160</v>
       </c>
     </row>
     <row r="653" ht="20" customHeight="1">
@@ -17353,7 +17353,7 @@
         </is>
       </c>
       <c r="E653" s="23" t="n">
-        <v>168</v>
+        <v>182</v>
       </c>
     </row>
     <row r="654" ht="20" customHeight="1">
@@ -17378,7 +17378,7 @@
         </is>
       </c>
       <c r="E654" s="20" t="n">
-        <v>121</v>
+        <v>219</v>
       </c>
     </row>
     <row r="655" ht="20" customHeight="1">
@@ -17403,7 +17403,7 @@
         </is>
       </c>
       <c r="E655" s="23" t="n">
-        <v>173</v>
+        <v>214</v>
       </c>
     </row>
     <row r="656" ht="20" customHeight="1">
@@ -17428,7 +17428,7 @@
         </is>
       </c>
       <c r="E656" s="20" t="n">
-        <v>224</v>
+        <v>178</v>
       </c>
     </row>
     <row r="657" ht="20" customHeight="1">
@@ -17453,7 +17453,7 @@
         </is>
       </c>
       <c r="E657" s="23" t="n">
-        <v>122</v>
+        <v>222</v>
       </c>
     </row>
     <row r="658" ht="20" customHeight="1">
@@ -17478,7 +17478,7 @@
         </is>
       </c>
       <c r="E658" s="20" t="n">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="659" ht="20" customHeight="1">
@@ -17503,7 +17503,7 @@
         </is>
       </c>
       <c r="E659" s="23" t="n">
-        <v>148</v>
+        <v>154</v>
       </c>
     </row>
     <row r="660" ht="20" customHeight="1">
@@ -17528,7 +17528,7 @@
         </is>
       </c>
       <c r="E660" s="20" t="n">
-        <v>159</v>
+        <v>174</v>
       </c>
     </row>
     <row r="661" ht="20" customHeight="1">
@@ -17553,7 +17553,7 @@
         </is>
       </c>
       <c r="E661" s="23" t="n">
-        <v>211</v>
+        <v>128</v>
       </c>
     </row>
     <row r="662" ht="20" customHeight="1">
@@ -17578,7 +17578,7 @@
         </is>
       </c>
       <c r="E662" s="20" t="n">
-        <v>208</v>
+        <v>169</v>
       </c>
     </row>
     <row r="663" ht="20" customHeight="1">
@@ -17603,7 +17603,7 @@
         </is>
       </c>
       <c r="E663" s="23" t="n">
-        <v>196</v>
+        <v>133</v>
       </c>
     </row>
     <row r="664" ht="20" customHeight="1">
@@ -17628,7 +17628,7 @@
         </is>
       </c>
       <c r="E664" s="20" t="n">
-        <v>151</v>
+        <v>234</v>
       </c>
     </row>
     <row r="665" ht="20" customHeight="1">
@@ -17653,7 +17653,7 @@
         </is>
       </c>
       <c r="E665" s="23" t="n">
-        <v>149</v>
+        <v>211</v>
       </c>
     </row>
     <row r="666" ht="20" customHeight="1">
@@ -17678,7 +17678,7 @@
         </is>
       </c>
       <c r="E666" s="20" t="n">
-        <v>208</v>
+        <v>214</v>
       </c>
     </row>
     <row r="667" ht="20" customHeight="1">
@@ -17703,7 +17703,7 @@
         </is>
       </c>
       <c r="E667" s="23" t="n">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="668" ht="20" customHeight="1">
@@ -17728,7 +17728,7 @@
         </is>
       </c>
       <c r="E668" s="20" t="n">
-        <v>157</v>
+        <v>143</v>
       </c>
     </row>
     <row r="669" ht="20" customHeight="1">
@@ -17753,7 +17753,7 @@
         </is>
       </c>
       <c r="E669" s="23" t="n">
-        <v>126</v>
+        <v>232</v>
       </c>
     </row>
     <row r="670" ht="20" customHeight="1">
@@ -17778,7 +17778,7 @@
         </is>
       </c>
       <c r="E670" s="20" t="n">
-        <v>185</v>
+        <v>173</v>
       </c>
     </row>
     <row r="671" ht="20" customHeight="1">
@@ -17803,7 +17803,7 @@
         </is>
       </c>
       <c r="E671" s="23" t="n">
-        <v>207</v>
+        <v>224</v>
       </c>
     </row>
     <row r="672" ht="20" customHeight="1">
@@ -17828,7 +17828,7 @@
         </is>
       </c>
       <c r="E672" s="20" t="n">
-        <v>164</v>
+        <v>175</v>
       </c>
     </row>
     <row r="673" ht="20" customHeight="1">
@@ -17853,7 +17853,7 @@
         </is>
       </c>
       <c r="E673" s="23" t="n">
-        <v>142</v>
+        <v>201</v>
       </c>
     </row>
     <row r="674" ht="20" customHeight="1">
@@ -17878,7 +17878,7 @@
         </is>
       </c>
       <c r="E674" s="20" t="n">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="675" ht="20" customHeight="1">
@@ -17903,7 +17903,7 @@
         </is>
       </c>
       <c r="E675" s="23" t="n">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
     <row r="676" ht="20" customHeight="1">
@@ -17928,7 +17928,7 @@
         </is>
       </c>
       <c r="E676" s="20" t="n">
-        <v>229</v>
+        <v>202</v>
       </c>
     </row>
     <row r="677" ht="20" customHeight="1">
@@ -17953,7 +17953,7 @@
         </is>
       </c>
       <c r="E677" s="23" t="n">
-        <v>145</v>
+        <v>210</v>
       </c>
     </row>
     <row r="678" ht="20" customHeight="1">
@@ -17978,7 +17978,7 @@
         </is>
       </c>
       <c r="E678" s="20" t="n">
-        <v>221</v>
+        <v>228</v>
       </c>
     </row>
     <row r="679" ht="20" customHeight="1">
@@ -18003,7 +18003,7 @@
         </is>
       </c>
       <c r="E679" s="23" t="n">
-        <v>229</v>
+        <v>141</v>
       </c>
     </row>
     <row r="680" ht="20" customHeight="1">
@@ -18028,7 +18028,7 @@
         </is>
       </c>
       <c r="E680" s="20" t="n">
-        <v>168</v>
+        <v>123</v>
       </c>
     </row>
     <row r="681" ht="20" customHeight="1">
@@ -18053,7 +18053,7 @@
         </is>
       </c>
       <c r="E681" s="23" t="n">
-        <v>229</v>
+        <v>143</v>
       </c>
     </row>
     <row r="682" ht="20" customHeight="1">
@@ -18078,7 +18078,7 @@
         </is>
       </c>
       <c r="E682" s="20" t="n">
-        <v>226</v>
+        <v>193</v>
       </c>
     </row>
     <row r="683" ht="20" customHeight="1">
@@ -18103,7 +18103,7 @@
         </is>
       </c>
       <c r="E683" s="23" t="n">
-        <v>181</v>
+        <v>160</v>
       </c>
     </row>
     <row r="684" ht="20" customHeight="1">
@@ -18128,7 +18128,7 @@
         </is>
       </c>
       <c r="E684" s="20" t="n">
-        <v>122</v>
+        <v>112</v>
       </c>
     </row>
     <row r="685" ht="20" customHeight="1">
@@ -18153,7 +18153,7 @@
         </is>
       </c>
       <c r="E685" s="23" t="n">
-        <v>214</v>
+        <v>163</v>
       </c>
     </row>
     <row r="686" ht="20" customHeight="1">
@@ -18178,7 +18178,7 @@
         </is>
       </c>
       <c r="E686" s="20" t="n">
-        <v>188</v>
+        <v>181</v>
       </c>
     </row>
     <row r="687" ht="20" customHeight="1">
@@ -18203,7 +18203,7 @@
         </is>
       </c>
       <c r="E687" s="23" t="n">
-        <v>136</v>
+        <v>195</v>
       </c>
     </row>
     <row r="688" ht="20" customHeight="1">
@@ -18228,7 +18228,7 @@
         </is>
       </c>
       <c r="E688" s="20" t="n">
-        <v>221</v>
+        <v>127</v>
       </c>
     </row>
     <row r="689" ht="20" customHeight="1">
@@ -18253,7 +18253,7 @@
         </is>
       </c>
       <c r="E689" s="23" t="n">
-        <v>229</v>
+        <v>173</v>
       </c>
     </row>
     <row r="690" ht="20" customHeight="1">
@@ -18278,7 +18278,7 @@
         </is>
       </c>
       <c r="E690" s="20" t="n">
-        <v>237</v>
+        <v>216</v>
       </c>
     </row>
     <row r="691" ht="20" customHeight="1">
@@ -18303,7 +18303,7 @@
         </is>
       </c>
       <c r="E691" s="23" t="n">
-        <v>227</v>
+        <v>133</v>
       </c>
     </row>
     <row r="692" ht="20" customHeight="1">
@@ -18328,7 +18328,7 @@
         </is>
       </c>
       <c r="E692" s="20" t="n">
-        <v>176</v>
+        <v>229</v>
       </c>
     </row>
     <row r="693" ht="20" customHeight="1">
@@ -18353,7 +18353,7 @@
         </is>
       </c>
       <c r="E693" s="23" t="n">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="694" ht="20" customHeight="1">
@@ -18378,7 +18378,7 @@
         </is>
       </c>
       <c r="E694" s="20" t="n">
-        <v>159</v>
+        <v>211</v>
       </c>
     </row>
     <row r="695" ht="20" customHeight="1">
@@ -18403,7 +18403,7 @@
         </is>
       </c>
       <c r="E695" s="23" t="n">
-        <v>114</v>
+        <v>240</v>
       </c>
     </row>
     <row r="696" ht="20" customHeight="1">
@@ -18428,7 +18428,7 @@
         </is>
       </c>
       <c r="E696" s="20" t="n">
-        <v>110</v>
+        <v>122</v>
       </c>
     </row>
     <row r="697" ht="20" customHeight="1">
@@ -18453,7 +18453,7 @@
         </is>
       </c>
       <c r="E697" s="23" t="n">
-        <v>201</v>
+        <v>188</v>
       </c>
     </row>
     <row r="698" ht="20" customHeight="1">
@@ -18478,7 +18478,7 @@
         </is>
       </c>
       <c r="E698" s="20" t="n">
-        <v>213</v>
+        <v>235</v>
       </c>
     </row>
     <row r="699" ht="20" customHeight="1">
@@ -18503,7 +18503,7 @@
         </is>
       </c>
       <c r="E699" s="23" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="700" ht="20" customHeight="1">
@@ -18528,7 +18528,7 @@
         </is>
       </c>
       <c r="E700" s="20" t="n">
-        <v>137</v>
+        <v>192</v>
       </c>
     </row>
     <row r="701" ht="20" customHeight="1">
@@ -18553,7 +18553,7 @@
         </is>
       </c>
       <c r="E701" s="23" t="n">
-        <v>152</v>
+        <v>213</v>
       </c>
     </row>
     <row r="702" ht="20" customHeight="1">
@@ -18578,7 +18578,7 @@
         </is>
       </c>
       <c r="E702" s="20" t="n">
-        <v>149</v>
+        <v>141</v>
       </c>
     </row>
     <row r="703" ht="20" customHeight="1">
@@ -18603,7 +18603,7 @@
         </is>
       </c>
       <c r="E703" s="23" t="n">
-        <v>196</v>
+        <v>144</v>
       </c>
     </row>
     <row r="704" ht="20" customHeight="1">
@@ -18628,7 +18628,7 @@
         </is>
       </c>
       <c r="E704" s="20" t="n">
-        <v>171</v>
+        <v>230</v>
       </c>
     </row>
     <row r="705" ht="20" customHeight="1">
@@ -18653,7 +18653,7 @@
         </is>
       </c>
       <c r="E705" s="23" t="n">
-        <v>134</v>
+        <v>207</v>
       </c>
     </row>
     <row r="706" ht="20" customHeight="1">
@@ -18678,7 +18678,7 @@
         </is>
       </c>
       <c r="E706" s="20" t="n">
-        <v>223</v>
+        <v>160</v>
       </c>
     </row>
     <row r="707" ht="20" customHeight="1">
@@ -18703,7 +18703,7 @@
         </is>
       </c>
       <c r="E707" s="23" t="n">
-        <v>153</v>
+        <v>223</v>
       </c>
     </row>
     <row r="708" ht="20" customHeight="1">
@@ -18728,7 +18728,7 @@
         </is>
       </c>
       <c r="E708" s="20" t="n">
-        <v>201</v>
+        <v>152</v>
       </c>
     </row>
     <row r="709" ht="20" customHeight="1">
@@ -18753,7 +18753,7 @@
         </is>
       </c>
       <c r="E709" s="23" t="n">
-        <v>230</v>
+        <v>208</v>
       </c>
     </row>
     <row r="710" ht="20" customHeight="1">
@@ -18778,7 +18778,7 @@
         </is>
       </c>
       <c r="E710" s="20" t="n">
-        <v>126</v>
+        <v>181</v>
       </c>
     </row>
     <row r="711" ht="20" customHeight="1">
@@ -18803,7 +18803,7 @@
         </is>
       </c>
       <c r="E711" s="23" t="n">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="712" ht="20" customHeight="1">
@@ -18828,7 +18828,7 @@
         </is>
       </c>
       <c r="E712" s="20" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
     </row>
     <row r="713" ht="20" customHeight="1">
@@ -18853,7 +18853,7 @@
         </is>
       </c>
       <c r="E713" s="23" t="n">
-        <v>142</v>
+        <v>235</v>
       </c>
     </row>
     <row r="714" ht="20" customHeight="1">
@@ -18878,7 +18878,7 @@
         </is>
       </c>
       <c r="E714" s="20" t="n">
-        <v>224</v>
+        <v>130</v>
       </c>
     </row>
     <row r="715" ht="20" customHeight="1">
@@ -18903,7 +18903,7 @@
         </is>
       </c>
       <c r="E715" s="23" t="n">
-        <v>224</v>
+        <v>233</v>
       </c>
     </row>
     <row r="716" ht="20" customHeight="1">
@@ -18928,7 +18928,7 @@
         </is>
       </c>
       <c r="E716" s="20" t="n">
-        <v>192</v>
+        <v>112</v>
       </c>
     </row>
     <row r="717" ht="20" customHeight="1">
@@ -18953,7 +18953,7 @@
         </is>
       </c>
       <c r="E717" s="23" t="n">
-        <v>112</v>
+        <v>237</v>
       </c>
     </row>
     <row r="718" ht="20" customHeight="1">
@@ -18978,7 +18978,7 @@
         </is>
       </c>
       <c r="E718" s="20" t="n">
-        <v>204</v>
+        <v>216</v>
       </c>
     </row>
     <row r="719" ht="20" customHeight="1">
@@ -19003,7 +19003,7 @@
         </is>
       </c>
       <c r="E719" s="23" t="n">
-        <v>219</v>
+        <v>202</v>
       </c>
     </row>
     <row r="720" ht="20" customHeight="1">
@@ -19028,7 +19028,7 @@
         </is>
       </c>
       <c r="E720" s="20" t="n">
-        <v>210</v>
+        <v>194</v>
       </c>
     </row>
     <row r="721" ht="20" customHeight="1">
@@ -19053,7 +19053,7 @@
         </is>
       </c>
       <c r="E721" s="23" t="n">
-        <v>235</v>
+        <v>210</v>
       </c>
     </row>
     <row r="722" ht="20" customHeight="1">
@@ -19078,7 +19078,7 @@
         </is>
       </c>
       <c r="E722" s="20" t="n">
-        <v>170</v>
+        <v>178</v>
       </c>
     </row>
     <row r="723" ht="20" customHeight="1">
@@ -19103,7 +19103,7 @@
         </is>
       </c>
       <c r="E723" s="23" t="n">
-        <v>211</v>
+        <v>151</v>
       </c>
     </row>
     <row r="724" ht="20" customHeight="1">
@@ -19128,7 +19128,7 @@
         </is>
       </c>
       <c r="E724" s="20" t="n">
-        <v>133</v>
+        <v>117</v>
       </c>
     </row>
     <row r="725" ht="20" customHeight="1">
@@ -19153,7 +19153,7 @@
         </is>
       </c>
       <c r="E725" s="23" t="n">
-        <v>233</v>
+        <v>190</v>
       </c>
     </row>
     <row r="726" ht="20" customHeight="1">
@@ -19178,7 +19178,7 @@
         </is>
       </c>
       <c r="E726" s="20" t="n">
-        <v>215</v>
+        <v>181</v>
       </c>
     </row>
     <row r="727" ht="20" customHeight="1">
@@ -19203,7 +19203,7 @@
         </is>
       </c>
       <c r="E727" s="23" t="n">
-        <v>198</v>
+        <v>155</v>
       </c>
     </row>
     <row r="728" ht="20" customHeight="1">
@@ -19228,7 +19228,7 @@
         </is>
       </c>
       <c r="E728" s="20" t="n">
-        <v>209</v>
+        <v>200</v>
       </c>
     </row>
     <row r="729" ht="20" customHeight="1">
@@ -19253,7 +19253,7 @@
         </is>
       </c>
       <c r="E729" s="23" t="n">
-        <v>147</v>
+        <v>157</v>
       </c>
     </row>
     <row r="730" ht="20" customHeight="1">
@@ -19278,7 +19278,7 @@
         </is>
       </c>
       <c r="E730" s="20" t="n">
-        <v>187</v>
+        <v>232</v>
       </c>
     </row>
     <row r="731" ht="20" customHeight="1">
@@ -19303,7 +19303,7 @@
         </is>
       </c>
       <c r="E731" s="23" t="n">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="732" ht="20" customHeight="1">
@@ -19328,7 +19328,7 @@
         </is>
       </c>
       <c r="E732" s="20" t="n">
-        <v>185</v>
+        <v>120</v>
       </c>
     </row>
     <row r="733" ht="20" customHeight="1">
@@ -19353,7 +19353,7 @@
         </is>
       </c>
       <c r="E733" s="23" t="n">
-        <v>181</v>
+        <v>158</v>
       </c>
     </row>
     <row r="734" ht="20" customHeight="1">
@@ -19378,7 +19378,7 @@
         </is>
       </c>
       <c r="E734" s="20" t="n">
-        <v>135</v>
+        <v>151</v>
       </c>
     </row>
     <row r="735" ht="20" customHeight="1">
@@ -19403,7 +19403,7 @@
         </is>
       </c>
       <c r="E735" s="23" t="n">
-        <v>133</v>
+        <v>190</v>
       </c>
     </row>
     <row r="736" ht="20" customHeight="1">
@@ -19428,7 +19428,7 @@
         </is>
       </c>
       <c r="E736" s="20" t="n">
-        <v>187</v>
+        <v>197</v>
       </c>
     </row>
     <row r="737" ht="20" customHeight="1">
@@ -19453,7 +19453,7 @@
         </is>
       </c>
       <c r="E737" s="23" t="n">
-        <v>216</v>
+        <v>121</v>
       </c>
     </row>
     <row r="738" ht="20" customHeight="1">
@@ -19478,7 +19478,7 @@
         </is>
       </c>
       <c r="E738" s="20" t="n">
-        <v>206</v>
+        <v>148</v>
       </c>
     </row>
     <row r="739" ht="20" customHeight="1">
@@ -19503,7 +19503,7 @@
         </is>
       </c>
       <c r="E739" s="23" t="n">
-        <v>112</v>
+        <v>231</v>
       </c>
     </row>
     <row r="740" ht="20" customHeight="1">
@@ -19528,7 +19528,7 @@
         </is>
       </c>
       <c r="E740" s="20" t="n">
-        <v>215</v>
+        <v>192</v>
       </c>
     </row>
     <row r="741" ht="20" customHeight="1">
@@ -19553,7 +19553,7 @@
         </is>
       </c>
       <c r="E741" s="23" t="n">
-        <v>224</v>
+        <v>132</v>
       </c>
     </row>
     <row r="742" ht="20" customHeight="1">
@@ -19578,7 +19578,7 @@
         </is>
       </c>
       <c r="E742" s="20" t="n">
-        <v>117</v>
+        <v>216</v>
       </c>
     </row>
     <row r="743" ht="20" customHeight="1">
@@ -19603,7 +19603,7 @@
         </is>
       </c>
       <c r="E743" s="23" t="n">
-        <v>216</v>
+        <v>179</v>
       </c>
     </row>
     <row r="744" ht="20" customHeight="1">
@@ -19628,7 +19628,7 @@
         </is>
       </c>
       <c r="E744" s="20" t="n">
-        <v>239</v>
+        <v>200</v>
       </c>
     </row>
     <row r="745" ht="20" customHeight="1">
@@ -19653,7 +19653,7 @@
         </is>
       </c>
       <c r="E745" s="23" t="n">
-        <v>123</v>
+        <v>176</v>
       </c>
     </row>
     <row r="746" ht="20" customHeight="1">
@@ -19678,7 +19678,7 @@
         </is>
       </c>
       <c r="E746" s="20" t="n">
-        <v>219</v>
+        <v>127</v>
       </c>
     </row>
     <row r="747" ht="20" customHeight="1">
@@ -19703,7 +19703,7 @@
         </is>
       </c>
       <c r="E747" s="23" t="n">
-        <v>229</v>
+        <v>192</v>
       </c>
     </row>
     <row r="748" ht="20" customHeight="1">
@@ -19728,7 +19728,7 @@
         </is>
       </c>
       <c r="E748" s="20" t="n">
-        <v>185</v>
+        <v>126</v>
       </c>
     </row>
     <row r="749" ht="20" customHeight="1">
@@ -19753,7 +19753,7 @@
         </is>
       </c>
       <c r="E749" s="23" t="n">
-        <v>148</v>
+        <v>139</v>
       </c>
     </row>
     <row r="750" ht="20" customHeight="1">
@@ -19778,7 +19778,7 @@
         </is>
       </c>
       <c r="E750" s="20" t="n">
-        <v>229</v>
+        <v>143</v>
       </c>
     </row>
     <row r="751" ht="20" customHeight="1">
@@ -19803,7 +19803,7 @@
         </is>
       </c>
       <c r="E751" s="23" t="n">
-        <v>231</v>
+        <v>126</v>
       </c>
     </row>
     <row r="752" ht="20" customHeight="1">
@@ -19828,7 +19828,7 @@
         </is>
       </c>
       <c r="E752" s="20" t="n">
-        <v>119</v>
+        <v>195</v>
       </c>
     </row>
     <row r="753" ht="20" customHeight="1">
@@ -19853,7 +19853,7 @@
         </is>
       </c>
       <c r="E753" s="23" t="n">
-        <v>174</v>
+        <v>219</v>
       </c>
     </row>
     <row r="754" ht="20" customHeight="1">
@@ -19878,7 +19878,7 @@
         </is>
       </c>
       <c r="E754" s="20" t="n">
-        <v>161</v>
+        <v>137</v>
       </c>
     </row>
     <row r="755" ht="20" customHeight="1">
@@ -19903,7 +19903,7 @@
         </is>
       </c>
       <c r="E755" s="23" t="n">
-        <v>187</v>
+        <v>212</v>
       </c>
     </row>
     <row r="756" ht="20" customHeight="1">
@@ -19928,7 +19928,7 @@
         </is>
       </c>
       <c r="E756" s="20" t="n">
-        <v>156</v>
+        <v>119</v>
       </c>
     </row>
     <row r="757" ht="20" customHeight="1">
@@ -19953,7 +19953,7 @@
         </is>
       </c>
       <c r="E757" s="23" t="n">
-        <v>134</v>
+        <v>128</v>
       </c>
     </row>
     <row r="758" ht="20" customHeight="1">
@@ -19978,7 +19978,7 @@
         </is>
       </c>
       <c r="E758" s="20" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="759" ht="20" customHeight="1">
@@ -20003,7 +20003,7 @@
         </is>
       </c>
       <c r="E759" s="23" t="n">
-        <v>176</v>
+        <v>190</v>
       </c>
     </row>
     <row r="760" ht="20" customHeight="1">
@@ -20028,7 +20028,7 @@
         </is>
       </c>
       <c r="E760" s="20" t="n">
-        <v>150</v>
+        <v>181</v>
       </c>
     </row>
     <row r="761" ht="20" customHeight="1">
@@ -20053,7 +20053,7 @@
         </is>
       </c>
       <c r="E761" s="23" t="n">
-        <v>161</v>
+        <v>196</v>
       </c>
     </row>
     <row r="762" ht="20" customHeight="1">
@@ -20103,7 +20103,7 @@
         </is>
       </c>
       <c r="E763" s="23" t="n">
-        <v>226</v>
+        <v>173</v>
       </c>
     </row>
     <row r="764" ht="20" customHeight="1">
@@ -20128,7 +20128,7 @@
         </is>
       </c>
       <c r="E764" s="20" t="n">
-        <v>228</v>
+        <v>135</v>
       </c>
     </row>
     <row r="765" ht="20" customHeight="1">
@@ -20153,7 +20153,7 @@
         </is>
       </c>
       <c r="E765" s="23" t="n">
-        <v>178</v>
+        <v>155</v>
       </c>
     </row>
     <row r="766" ht="20" customHeight="1">
@@ -20178,7 +20178,7 @@
         </is>
       </c>
       <c r="E766" s="20" t="n">
-        <v>180</v>
+        <v>191</v>
       </c>
     </row>
     <row r="767" ht="20" customHeight="1">
@@ -20203,7 +20203,7 @@
         </is>
       </c>
       <c r="E767" s="23" t="n">
-        <v>139</v>
+        <v>179</v>
       </c>
     </row>
     <row r="768" ht="20" customHeight="1">
@@ -20228,7 +20228,7 @@
         </is>
       </c>
       <c r="E768" s="20" t="n">
-        <v>170</v>
+        <v>144</v>
       </c>
     </row>
     <row r="769" ht="20" customHeight="1">
@@ -20253,7 +20253,7 @@
         </is>
       </c>
       <c r="E769" s="23" t="n">
-        <v>188</v>
+        <v>204</v>
       </c>
     </row>
     <row r="770" ht="20" customHeight="1">
@@ -20278,7 +20278,7 @@
         </is>
       </c>
       <c r="E770" s="20" t="n">
-        <v>221</v>
+        <v>165</v>
       </c>
     </row>
     <row r="771" ht="20" customHeight="1">
@@ -20303,7 +20303,7 @@
         </is>
       </c>
       <c r="E771" s="23" t="n">
-        <v>216</v>
+        <v>127</v>
       </c>
     </row>
     <row r="772" ht="20" customHeight="1">
@@ -20328,7 +20328,7 @@
         </is>
       </c>
       <c r="E772" s="20" t="n">
-        <v>235</v>
+        <v>199</v>
       </c>
     </row>
     <row r="773" ht="20" customHeight="1">
@@ -20353,7 +20353,7 @@
         </is>
       </c>
       <c r="E773" s="23" t="n">
-        <v>161</v>
+        <v>237</v>
       </c>
     </row>
     <row r="774" ht="20" customHeight="1">
@@ -20378,7 +20378,7 @@
         </is>
       </c>
       <c r="E774" s="20" t="n">
-        <v>135</v>
+        <v>219</v>
       </c>
     </row>
     <row r="775" ht="20" customHeight="1">
@@ -20403,7 +20403,7 @@
         </is>
       </c>
       <c r="E775" s="23" t="n">
-        <v>231</v>
+        <v>153</v>
       </c>
     </row>
     <row r="776" ht="20" customHeight="1">
@@ -20428,7 +20428,7 @@
         </is>
       </c>
       <c r="E776" s="20" t="n">
-        <v>142</v>
+        <v>164</v>
       </c>
     </row>
     <row r="777" ht="20" customHeight="1">
@@ -20453,7 +20453,7 @@
         </is>
       </c>
       <c r="E777" s="23" t="n">
-        <v>134</v>
+        <v>166</v>
       </c>
     </row>
     <row r="778" ht="20" customHeight="1">
@@ -20478,7 +20478,7 @@
         </is>
       </c>
       <c r="E778" s="20" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="779" ht="20" customHeight="1">
@@ -20503,7 +20503,7 @@
         </is>
       </c>
       <c r="E779" s="23" t="n">
-        <v>113</v>
+        <v>183</v>
       </c>
     </row>
     <row r="780" ht="20" customHeight="1">
@@ -20528,7 +20528,7 @@
         </is>
       </c>
       <c r="E780" s="20" t="n">
-        <v>226</v>
+        <v>167</v>
       </c>
     </row>
     <row r="781" ht="20" customHeight="1">
@@ -20553,7 +20553,7 @@
         </is>
       </c>
       <c r="E781" s="23" t="n">
-        <v>149</v>
+        <v>118</v>
       </c>
     </row>
     <row r="782" ht="20" customHeight="1">
@@ -20578,7 +20578,7 @@
         </is>
       </c>
       <c r="E782" s="20" t="n">
-        <v>179</v>
+        <v>238</v>
       </c>
     </row>
     <row r="783" ht="20" customHeight="1">
@@ -20603,7 +20603,7 @@
         </is>
       </c>
       <c r="E783" s="23" t="n">
-        <v>202</v>
+        <v>182</v>
       </c>
     </row>
     <row r="784" ht="20" customHeight="1">
@@ -20628,7 +20628,7 @@
         </is>
       </c>
       <c r="E784" s="20" t="n">
-        <v>193</v>
+        <v>213</v>
       </c>
     </row>
     <row r="785" ht="20" customHeight="1">
@@ -20653,7 +20653,7 @@
         </is>
       </c>
       <c r="E785" s="23" t="n">
-        <v>240</v>
+        <v>168</v>
       </c>
     </row>
     <row r="786" ht="20" customHeight="1">
@@ -20678,7 +20678,7 @@
         </is>
       </c>
       <c r="E786" s="20" t="n">
-        <v>131</v>
+        <v>142</v>
       </c>
     </row>
     <row r="787" ht="20" customHeight="1">
@@ -20703,7 +20703,7 @@
         </is>
       </c>
       <c r="E787" s="23" t="n">
-        <v>206</v>
+        <v>120</v>
       </c>
     </row>
     <row r="788" ht="20" customHeight="1">
@@ -20728,7 +20728,7 @@
         </is>
       </c>
       <c r="E788" s="20" t="n">
-        <v>218</v>
+        <v>210</v>
       </c>
     </row>
     <row r="789" ht="20" customHeight="1">
@@ -20753,7 +20753,7 @@
         </is>
       </c>
       <c r="E789" s="23" t="n">
-        <v>161</v>
+        <v>187</v>
       </c>
     </row>
     <row r="790" ht="20" customHeight="1">
@@ -20778,7 +20778,7 @@
         </is>
       </c>
       <c r="E790" s="20" t="n">
-        <v>237</v>
+        <v>143</v>
       </c>
     </row>
     <row r="791" ht="20" customHeight="1">
@@ -20803,7 +20803,7 @@
         </is>
       </c>
       <c r="E791" s="23" t="n">
-        <v>166</v>
+        <v>188</v>
       </c>
     </row>
     <row r="792" ht="20" customHeight="1">
@@ -20828,7 +20828,7 @@
         </is>
       </c>
       <c r="E792" s="20" t="n">
-        <v>207</v>
+        <v>138</v>
       </c>
     </row>
     <row r="793" ht="20" customHeight="1">
@@ -20853,7 +20853,7 @@
         </is>
       </c>
       <c r="E793" s="23" t="n">
-        <v>201</v>
+        <v>113</v>
       </c>
     </row>
     <row r="794" ht="20" customHeight="1">
@@ -20878,7 +20878,7 @@
         </is>
       </c>
       <c r="E794" s="20" t="n">
-        <v>193</v>
+        <v>117</v>
       </c>
     </row>
     <row r="795" ht="20" customHeight="1">
@@ -20903,7 +20903,7 @@
         </is>
       </c>
       <c r="E795" s="23" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="796" ht="20" customHeight="1">
@@ -20928,7 +20928,7 @@
         </is>
       </c>
       <c r="E796" s="20" t="n">
-        <v>123</v>
+        <v>221</v>
       </c>
     </row>
     <row r="797" ht="20" customHeight="1">
@@ -20953,7 +20953,7 @@
         </is>
       </c>
       <c r="E797" s="23" t="n">
-        <v>129</v>
+        <v>110</v>
       </c>
     </row>
     <row r="798" ht="20" customHeight="1">
@@ -20978,7 +20978,7 @@
         </is>
       </c>
       <c r="E798" s="20" t="n">
-        <v>111</v>
+        <v>128</v>
       </c>
     </row>
     <row r="799" ht="20" customHeight="1">
@@ -21003,7 +21003,7 @@
         </is>
       </c>
       <c r="E799" s="23" t="n">
-        <v>194</v>
+        <v>172</v>
       </c>
     </row>
     <row r="800" ht="20" customHeight="1">
@@ -21028,7 +21028,7 @@
         </is>
       </c>
       <c r="E800" s="20" t="n">
-        <v>155</v>
+        <v>181</v>
       </c>
     </row>
     <row r="801" ht="20" customHeight="1">
@@ -21053,7 +21053,7 @@
         </is>
       </c>
       <c r="E801" s="23" t="n">
-        <v>139</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/Appium_E2E_Test_Report_Traverse.xlsx
+++ b/Appium_E2E_Test_Report_Traverse.xlsx
@@ -791,7 +791,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 07:50:06</t>
+          <t>2026-08-11 07:53:42</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="E2" s="20" t="n">
-        <v>223</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="E3" s="23" t="n">
-        <v>208</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="E4" s="20" t="n">
-        <v>141</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="E5" s="23" t="n">
-        <v>139</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="E6" s="20" t="n">
-        <v>168</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="E7" s="23" t="n">
-        <v>149</v>
+        <v>208</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -1228,7 +1228,7 @@
         </is>
       </c>
       <c r="E8" s="20" t="n">
-        <v>144</v>
+        <v>181</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="E9" s="23" t="n">
-        <v>129</v>
+        <v>214</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
@@ -1278,7 +1278,7 @@
         </is>
       </c>
       <c r="E10" s="20" t="n">
-        <v>140</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="E11" s="23" t="n">
-        <v>148</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
@@ -1328,7 +1328,7 @@
         </is>
       </c>
       <c r="E12" s="20" t="n">
-        <v>119</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="E13" s="23" t="n">
-        <v>189</v>
+        <v>207</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="E14" s="20" t="n">
-        <v>165</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="E15" s="23" t="n">
-        <v>239</v>
+        <v>213</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="E16" s="20" t="n">
-        <v>205</v>
+        <v>237</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="E17" s="23" t="n">
-        <v>233</v>
+        <v>190</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -1478,7 +1478,7 @@
         </is>
       </c>
       <c r="E18" s="20" t="n">
-        <v>192</v>
+        <v>235</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
@@ -1503,7 +1503,7 @@
         </is>
       </c>
       <c r="E19" s="23" t="n">
-        <v>222</v>
+        <v>200</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="E20" s="20" t="n">
-        <v>136</v>
+        <v>171</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="E21" s="23" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
@@ -1578,7 +1578,7 @@
         </is>
       </c>
       <c r="E22" s="20" t="n">
-        <v>213</v>
+        <v>136</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="E23" s="23" t="n">
-        <v>217</v>
+        <v>116</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
@@ -1628,7 +1628,7 @@
         </is>
       </c>
       <c r="E24" s="20" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="E25" s="23" t="n">
-        <v>176</v>
+        <v>157</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
@@ -1678,7 +1678,7 @@
         </is>
       </c>
       <c r="E26" s="20" t="n">
-        <v>166</v>
+        <v>204</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="E27" s="23" t="n">
-        <v>237</v>
+        <v>164</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="E28" s="20" t="n">
-        <v>212</v>
+        <v>122</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="E29" s="23" t="n">
-        <v>209</v>
+        <v>236</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="E30" s="20" t="n">
-        <v>151</v>
+        <v>116</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
@@ -1803,7 +1803,7 @@
         </is>
       </c>
       <c r="E31" s="23" t="n">
-        <v>159</v>
+        <v>192</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
@@ -1828,7 +1828,7 @@
         </is>
       </c>
       <c r="E32" s="20" t="n">
-        <v>235</v>
+        <v>120</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
@@ -1853,7 +1853,7 @@
         </is>
       </c>
       <c r="E33" s="23" t="n">
-        <v>161</v>
+        <v>170</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
@@ -1878,7 +1878,7 @@
         </is>
       </c>
       <c r="E34" s="20" t="n">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="E35" s="23" t="n">
-        <v>208</v>
+        <v>197</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="E36" s="20" t="n">
-        <v>173</v>
+        <v>162</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="E37" s="23" t="n">
-        <v>214</v>
+        <v>148</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
@@ -1978,7 +1978,7 @@
         </is>
       </c>
       <c r="E38" s="20" t="n">
-        <v>222</v>
+        <v>165</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="E39" s="23" t="n">
-        <v>212</v>
+        <v>172</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="E40" s="20" t="n">
-        <v>121</v>
+        <v>176</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="E41" s="23" t="n">
-        <v>216</v>
+        <v>117</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
@@ -2078,7 +2078,7 @@
         </is>
       </c>
       <c r="E42" s="20" t="n">
-        <v>151</v>
+        <v>121</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="E43" s="23" t="n">
-        <v>120</v>
+        <v>114</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="E44" s="20" t="n">
-        <v>139</v>
+        <v>198</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="E45" s="23" t="n">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
@@ -2178,7 +2178,7 @@
         </is>
       </c>
       <c r="E46" s="20" t="n">
-        <v>182</v>
+        <v>232</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
@@ -2203,7 +2203,7 @@
         </is>
       </c>
       <c r="E47" s="23" t="n">
-        <v>189</v>
+        <v>230</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="E48" s="20" t="n">
-        <v>182</v>
+        <v>171</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
@@ -2253,7 +2253,7 @@
         </is>
       </c>
       <c r="E49" s="23" t="n">
-        <v>237</v>
+        <v>138</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
@@ -2278,7 +2278,7 @@
         </is>
       </c>
       <c r="E50" s="20" t="n">
-        <v>218</v>
+        <v>179</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="E51" s="23" t="n">
-        <v>146</v>
+        <v>207</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
@@ -2328,7 +2328,7 @@
         </is>
       </c>
       <c r="E52" s="20" t="n">
-        <v>160</v>
+        <v>125</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
@@ -2353,7 +2353,7 @@
         </is>
       </c>
       <c r="E53" s="23" t="n">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="E54" s="20" t="n">
-        <v>183</v>
+        <v>159</v>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1">
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="E55" s="23" t="n">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1">
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="E56" s="20" t="n">
-        <v>219</v>
+        <v>192</v>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1">
@@ -2453,7 +2453,7 @@
         </is>
       </c>
       <c r="E57" s="23" t="n">
-        <v>131</v>
+        <v>116</v>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1">
@@ -2478,7 +2478,7 @@
         </is>
       </c>
       <c r="E58" s="20" t="n">
-        <v>146</v>
+        <v>154</v>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1">
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="E59" s="23" t="n">
-        <v>155</v>
+        <v>132</v>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1">
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="E60" s="20" t="n">
-        <v>220</v>
+        <v>166</v>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
@@ -2553,7 +2553,7 @@
         </is>
       </c>
       <c r="E61" s="23" t="n">
-        <v>200</v>
+        <v>211</v>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="E62" s="20" t="n">
-        <v>198</v>
+        <v>226</v>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="E63" s="23" t="n">
-        <v>204</v>
+        <v>193</v>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1">
@@ -2628,7 +2628,7 @@
         </is>
       </c>
       <c r="E64" s="20" t="n">
-        <v>184</v>
+        <v>196</v>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1">
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="E65" s="23" t="n">
-        <v>184</v>
+        <v>152</v>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1">
@@ -2678,7 +2678,7 @@
         </is>
       </c>
       <c r="E66" s="20" t="n">
-        <v>196</v>
+        <v>157</v>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="E67" s="23" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="E68" s="20" t="n">
-        <v>198</v>
+        <v>210</v>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="E69" s="23" t="n">
-        <v>168</v>
+        <v>231</v>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1">
@@ -2778,7 +2778,7 @@
         </is>
       </c>
       <c r="E70" s="20" t="n">
-        <v>236</v>
+        <v>170</v>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1">
@@ -2803,7 +2803,7 @@
         </is>
       </c>
       <c r="E71" s="23" t="n">
-        <v>189</v>
+        <v>197</v>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1">
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="E72" s="20" t="n">
-        <v>169</v>
+        <v>125</v>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1">
@@ -2853,7 +2853,7 @@
         </is>
       </c>
       <c r="E73" s="23" t="n">
-        <v>146</v>
+        <v>201</v>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
@@ -2878,7 +2878,7 @@
         </is>
       </c>
       <c r="E74" s="20" t="n">
-        <v>143</v>
+        <v>226</v>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="E75" s="23" t="n">
-        <v>155</v>
+        <v>229</v>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
@@ -2928,7 +2928,7 @@
         </is>
       </c>
       <c r="E76" s="20" t="n">
-        <v>133</v>
+        <v>207</v>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="E77" s="23" t="n">
-        <v>139</v>
+        <v>221</v>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1">
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="E78" s="20" t="n">
-        <v>173</v>
+        <v>111</v>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
@@ -3028,7 +3028,7 @@
         </is>
       </c>
       <c r="E80" s="20" t="n">
-        <v>176</v>
+        <v>121</v>
       </c>
     </row>
     <row r="81" ht="20" customHeight="1">
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="E81" s="23" t="n">
-        <v>160</v>
+        <v>198</v>
       </c>
     </row>
     <row r="82" ht="20" customHeight="1">
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="E82" s="20" t="n">
-        <v>206</v>
+        <v>136</v>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1">
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="E83" s="23" t="n">
-        <v>134</v>
+        <v>237</v>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1">
@@ -3128,7 +3128,7 @@
         </is>
       </c>
       <c r="E84" s="20" t="n">
-        <v>239</v>
+        <v>124</v>
       </c>
     </row>
     <row r="85" ht="20" customHeight="1">
@@ -3153,7 +3153,7 @@
         </is>
       </c>
       <c r="E85" s="23" t="n">
-        <v>151</v>
+        <v>162</v>
       </c>
     </row>
     <row r="86" ht="20" customHeight="1">
@@ -3178,7 +3178,7 @@
         </is>
       </c>
       <c r="E86" s="20" t="n">
-        <v>176</v>
+        <v>186</v>
       </c>
     </row>
     <row r="87" ht="20" customHeight="1">
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="E87" s="23" t="n">
-        <v>117</v>
+        <v>232</v>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1">
@@ -3228,7 +3228,7 @@
         </is>
       </c>
       <c r="E88" s="20" t="n">
-        <v>216</v>
+        <v>190</v>
       </c>
     </row>
     <row r="89" ht="20" customHeight="1">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="E89" s="23" t="n">
-        <v>236</v>
+        <v>190</v>
       </c>
     </row>
     <row r="90" ht="20" customHeight="1">
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="E90" s="20" t="n">
-        <v>167</v>
+        <v>209</v>
       </c>
     </row>
     <row r="91" ht="20" customHeight="1">
@@ -3303,7 +3303,7 @@
         </is>
       </c>
       <c r="E91" s="23" t="n">
-        <v>193</v>
+        <v>208</v>
       </c>
     </row>
     <row r="92" ht="20" customHeight="1">
@@ -3328,7 +3328,7 @@
         </is>
       </c>
       <c r="E92" s="20" t="n">
-        <v>198</v>
+        <v>166</v>
       </c>
     </row>
     <row r="93" ht="20" customHeight="1">
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="E93" s="23" t="n">
-        <v>206</v>
+        <v>129</v>
       </c>
     </row>
     <row r="94" ht="20" customHeight="1">
@@ -3378,7 +3378,7 @@
         </is>
       </c>
       <c r="E94" s="20" t="n">
-        <v>233</v>
+        <v>220</v>
       </c>
     </row>
     <row r="95" ht="20" customHeight="1">
@@ -3403,7 +3403,7 @@
         </is>
       </c>
       <c r="E95" s="23" t="n">
-        <v>205</v>
+        <v>150</v>
       </c>
     </row>
     <row r="96" ht="20" customHeight="1">
@@ -3428,7 +3428,7 @@
         </is>
       </c>
       <c r="E96" s="20" t="n">
-        <v>170</v>
+        <v>117</v>
       </c>
     </row>
     <row r="97" ht="20" customHeight="1">
@@ -3453,7 +3453,7 @@
         </is>
       </c>
       <c r="E97" s="23" t="n">
-        <v>204</v>
+        <v>130</v>
       </c>
     </row>
     <row r="98" ht="20" customHeight="1">
@@ -3478,7 +3478,7 @@
         </is>
       </c>
       <c r="E98" s="20" t="n">
-        <v>213</v>
+        <v>179</v>
       </c>
     </row>
     <row r="99" ht="20" customHeight="1">
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="E99" s="23" t="n">
-        <v>194</v>
+        <v>178</v>
       </c>
     </row>
     <row r="100" ht="20" customHeight="1">
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="E100" s="20" t="n">
-        <v>228</v>
+        <v>126</v>
       </c>
     </row>
     <row r="101" ht="20" customHeight="1">
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="E101" s="23" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="102" ht="20" customHeight="1">
@@ -3578,7 +3578,7 @@
         </is>
       </c>
       <c r="E102" s="20" t="n">
-        <v>207</v>
+        <v>126</v>
       </c>
     </row>
     <row r="103" ht="20" customHeight="1">
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="E103" s="23" t="n">
-        <v>175</v>
+        <v>125</v>
       </c>
     </row>
     <row r="104" ht="20" customHeight="1">
@@ -3628,7 +3628,7 @@
         </is>
       </c>
       <c r="E104" s="20" t="n">
-        <v>171</v>
+        <v>153</v>
       </c>
     </row>
     <row r="105" ht="20" customHeight="1">
@@ -3653,7 +3653,7 @@
         </is>
       </c>
       <c r="E105" s="23" t="n">
-        <v>154</v>
+        <v>198</v>
       </c>
     </row>
     <row r="106" ht="20" customHeight="1">
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="E106" s="20" t="n">
-        <v>200</v>
+        <v>116</v>
       </c>
     </row>
     <row r="107" ht="20" customHeight="1">
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="E107" s="23" t="n">
-        <v>139</v>
+        <v>120</v>
       </c>
     </row>
     <row r="108" ht="20" customHeight="1">
@@ -3728,7 +3728,7 @@
         </is>
       </c>
       <c r="E108" s="20" t="n">
-        <v>239</v>
+        <v>121</v>
       </c>
     </row>
     <row r="109" ht="20" customHeight="1">
@@ -3753,7 +3753,7 @@
         </is>
       </c>
       <c r="E109" s="23" t="n">
-        <v>185</v>
+        <v>130</v>
       </c>
     </row>
     <row r="110" ht="20" customHeight="1">
@@ -3778,7 +3778,7 @@
         </is>
       </c>
       <c r="E110" s="20" t="n">
-        <v>204</v>
+        <v>166</v>
       </c>
     </row>
     <row r="111" ht="20" customHeight="1">
@@ -3803,7 +3803,7 @@
         </is>
       </c>
       <c r="E111" s="23" t="n">
-        <v>222</v>
+        <v>120</v>
       </c>
     </row>
     <row r="112" ht="20" customHeight="1">
@@ -3828,7 +3828,7 @@
         </is>
       </c>
       <c r="E112" s="20" t="n">
-        <v>118</v>
+        <v>212</v>
       </c>
     </row>
     <row r="113" ht="20" customHeight="1">
@@ -3853,7 +3853,7 @@
         </is>
       </c>
       <c r="E113" s="23" t="n">
-        <v>239</v>
+        <v>228</v>
       </c>
     </row>
     <row r="114" ht="20" customHeight="1">
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="E114" s="20" t="n">
-        <v>217</v>
+        <v>227</v>
       </c>
     </row>
     <row r="115" ht="20" customHeight="1">
@@ -3903,7 +3903,7 @@
         </is>
       </c>
       <c r="E115" s="23" t="n">
-        <v>189</v>
+        <v>213</v>
       </c>
     </row>
     <row r="116" ht="20" customHeight="1">
@@ -3928,7 +3928,7 @@
         </is>
       </c>
       <c r="E116" s="20" t="n">
-        <v>178</v>
+        <v>110</v>
       </c>
     </row>
     <row r="117" ht="20" customHeight="1">
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="E117" s="23" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="118" ht="20" customHeight="1">
@@ -3978,7 +3978,7 @@
         </is>
       </c>
       <c r="E118" s="20" t="n">
-        <v>180</v>
+        <v>113</v>
       </c>
     </row>
     <row r="119" ht="20" customHeight="1">
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="E119" s="23" t="n">
-        <v>154</v>
+        <v>185</v>
       </c>
     </row>
     <row r="120" ht="20" customHeight="1">
@@ -4028,7 +4028,7 @@
         </is>
       </c>
       <c r="E120" s="20" t="n">
-        <v>142</v>
+        <v>152</v>
       </c>
     </row>
     <row r="121" ht="20" customHeight="1">
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="E121" s="23" t="n">
-        <v>156</v>
+        <v>200</v>
       </c>
     </row>
     <row r="122" ht="20" customHeight="1">
@@ -4078,7 +4078,7 @@
         </is>
       </c>
       <c r="E122" s="20" t="n">
-        <v>229</v>
+        <v>233</v>
       </c>
     </row>
     <row r="123" ht="20" customHeight="1">
@@ -4103,7 +4103,7 @@
         </is>
       </c>
       <c r="E123" s="23" t="n">
-        <v>179</v>
+        <v>140</v>
       </c>
     </row>
     <row r="124" ht="20" customHeight="1">
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="E124" s="20" t="n">
-        <v>144</v>
+        <v>207</v>
       </c>
     </row>
     <row r="125" ht="20" customHeight="1">
@@ -4153,7 +4153,7 @@
         </is>
       </c>
       <c r="E125" s="23" t="n">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="126" ht="20" customHeight="1">
@@ -4178,7 +4178,7 @@
         </is>
       </c>
       <c r="E126" s="20" t="n">
-        <v>231</v>
+        <v>203</v>
       </c>
     </row>
     <row r="127" ht="20" customHeight="1">
@@ -4203,7 +4203,7 @@
         </is>
       </c>
       <c r="E127" s="23" t="n">
-        <v>196</v>
+        <v>204</v>
       </c>
     </row>
     <row r="128" ht="20" customHeight="1">
@@ -4228,7 +4228,7 @@
         </is>
       </c>
       <c r="E128" s="20" t="n">
-        <v>203</v>
+        <v>235</v>
       </c>
     </row>
     <row r="129" ht="20" customHeight="1">
@@ -4253,7 +4253,7 @@
         </is>
       </c>
       <c r="E129" s="23" t="n">
-        <v>233</v>
+        <v>140</v>
       </c>
     </row>
     <row r="130" ht="20" customHeight="1">
@@ -4278,7 +4278,7 @@
         </is>
       </c>
       <c r="E130" s="20" t="n">
-        <v>171</v>
+        <v>143</v>
       </c>
     </row>
     <row r="131" ht="20" customHeight="1">
@@ -4303,7 +4303,7 @@
         </is>
       </c>
       <c r="E131" s="23" t="n">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="132" ht="20" customHeight="1">
@@ -4328,7 +4328,7 @@
         </is>
       </c>
       <c r="E132" s="20" t="n">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="133" ht="20" customHeight="1">
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="E133" s="23" t="n">
-        <v>115</v>
+        <v>239</v>
       </c>
     </row>
     <row r="134" ht="20" customHeight="1">
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="E134" s="20" t="n">
-        <v>175</v>
+        <v>125</v>
       </c>
     </row>
     <row r="135" ht="20" customHeight="1">
@@ -4403,7 +4403,7 @@
         </is>
       </c>
       <c r="E135" s="23" t="n">
-        <v>235</v>
+        <v>115</v>
       </c>
     </row>
     <row r="136" ht="20" customHeight="1">
@@ -4428,7 +4428,7 @@
         </is>
       </c>
       <c r="E136" s="20" t="n">
-        <v>169</v>
+        <v>176</v>
       </c>
     </row>
     <row r="137" ht="20" customHeight="1">
@@ -4453,7 +4453,7 @@
         </is>
       </c>
       <c r="E137" s="23" t="n">
-        <v>139</v>
+        <v>133</v>
       </c>
     </row>
     <row r="138" ht="20" customHeight="1">
@@ -4478,7 +4478,7 @@
         </is>
       </c>
       <c r="E138" s="20" t="n">
-        <v>203</v>
+        <v>176</v>
       </c>
     </row>
     <row r="139" ht="20" customHeight="1">
@@ -4503,7 +4503,7 @@
         </is>
       </c>
       <c r="E139" s="23" t="n">
-        <v>128</v>
+        <v>164</v>
       </c>
     </row>
     <row r="140" ht="20" customHeight="1">
@@ -4528,7 +4528,7 @@
         </is>
       </c>
       <c r="E140" s="20" t="n">
-        <v>147</v>
+        <v>236</v>
       </c>
     </row>
     <row r="141" ht="20" customHeight="1">
@@ -4553,7 +4553,7 @@
         </is>
       </c>
       <c r="E141" s="23" t="n">
-        <v>122</v>
+        <v>210</v>
       </c>
     </row>
     <row r="142" ht="20" customHeight="1">
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="E142" s="20" t="n">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="143" ht="20" customHeight="1">
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="E143" s="23" t="n">
-        <v>219</v>
+        <v>200</v>
       </c>
     </row>
     <row r="144" ht="20" customHeight="1">
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="E144" s="20" t="n">
-        <v>222</v>
+        <v>152</v>
       </c>
     </row>
     <row r="145" ht="20" customHeight="1">
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="E145" s="23" t="n">
-        <v>234</v>
+        <v>143</v>
       </c>
     </row>
     <row r="146" ht="20" customHeight="1">
@@ -4678,7 +4678,7 @@
         </is>
       </c>
       <c r="E146" s="20" t="n">
-        <v>209</v>
+        <v>196</v>
       </c>
     </row>
     <row r="147" ht="20" customHeight="1">
@@ -4703,7 +4703,7 @@
         </is>
       </c>
       <c r="E147" s="23" t="n">
-        <v>156</v>
+        <v>232</v>
       </c>
     </row>
     <row r="148" ht="20" customHeight="1">
@@ -4728,7 +4728,7 @@
         </is>
       </c>
       <c r="E148" s="20" t="n">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="149" ht="20" customHeight="1">
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c r="E149" s="23" t="n">
-        <v>117</v>
+        <v>199</v>
       </c>
     </row>
     <row r="150" ht="20" customHeight="1">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="E150" s="20" t="n">
-        <v>215</v>
+        <v>115</v>
       </c>
     </row>
     <row r="151" ht="20" customHeight="1">
@@ -4803,7 +4803,7 @@
         </is>
       </c>
       <c r="E151" s="23" t="n">
-        <v>226</v>
+        <v>183</v>
       </c>
     </row>
     <row r="152" ht="20" customHeight="1">
@@ -4828,7 +4828,7 @@
         </is>
       </c>
       <c r="E152" s="20" t="n">
-        <v>169</v>
+        <v>217</v>
       </c>
     </row>
     <row r="153" ht="20" customHeight="1">
@@ -4853,7 +4853,7 @@
         </is>
       </c>
       <c r="E153" s="23" t="n">
-        <v>197</v>
+        <v>186</v>
       </c>
     </row>
     <row r="154" ht="20" customHeight="1">
@@ -4878,7 +4878,7 @@
         </is>
       </c>
       <c r="E154" s="20" t="n">
-        <v>110</v>
+        <v>136</v>
       </c>
     </row>
     <row r="155" ht="20" customHeight="1">
@@ -4903,7 +4903,7 @@
         </is>
       </c>
       <c r="E155" s="23" t="n">
-        <v>205</v>
+        <v>189</v>
       </c>
     </row>
     <row r="156" ht="20" customHeight="1">
@@ -4928,7 +4928,7 @@
         </is>
       </c>
       <c r="E156" s="20" t="n">
-        <v>164</v>
+        <v>240</v>
       </c>
     </row>
     <row r="157" ht="20" customHeight="1">
@@ -4953,7 +4953,7 @@
         </is>
       </c>
       <c r="E157" s="23" t="n">
-        <v>214</v>
+        <v>145</v>
       </c>
     </row>
     <row r="158" ht="20" customHeight="1">
@@ -4978,7 +4978,7 @@
         </is>
       </c>
       <c r="E158" s="20" t="n">
-        <v>168</v>
+        <v>232</v>
       </c>
     </row>
     <row r="159" ht="20" customHeight="1">
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="E159" s="23" t="n">
-        <v>235</v>
+        <v>126</v>
       </c>
     </row>
     <row r="160" ht="20" customHeight="1">
@@ -5028,7 +5028,7 @@
         </is>
       </c>
       <c r="E160" s="20" t="n">
-        <v>234</v>
+        <v>151</v>
       </c>
     </row>
     <row r="161" ht="20" customHeight="1">
@@ -5053,7 +5053,7 @@
         </is>
       </c>
       <c r="E161" s="23" t="n">
-        <v>116</v>
+        <v>207</v>
       </c>
     </row>
     <row r="162" ht="20" customHeight="1">
@@ -5078,7 +5078,7 @@
         </is>
       </c>
       <c r="E162" s="20" t="n">
-        <v>182</v>
+        <v>175</v>
       </c>
     </row>
     <row r="163" ht="20" customHeight="1">
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="E163" s="23" t="n">
-        <v>165</v>
+        <v>229</v>
       </c>
     </row>
     <row r="164" ht="20" customHeight="1">
@@ -5128,7 +5128,7 @@
         </is>
       </c>
       <c r="E164" s="20" t="n">
-        <v>137</v>
+        <v>110</v>
       </c>
     </row>
     <row r="165" ht="20" customHeight="1">
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="E165" s="23" t="n">
-        <v>189</v>
+        <v>165</v>
       </c>
     </row>
     <row r="166" ht="20" customHeight="1">
@@ -5178,7 +5178,7 @@
         </is>
       </c>
       <c r="E166" s="20" t="n">
-        <v>227</v>
+        <v>186</v>
       </c>
     </row>
     <row r="167" ht="20" customHeight="1">
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="E167" s="23" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="168" ht="20" customHeight="1">
@@ -5228,7 +5228,7 @@
         </is>
       </c>
       <c r="E168" s="20" t="n">
-        <v>209</v>
+        <v>198</v>
       </c>
     </row>
     <row r="169" ht="20" customHeight="1">
@@ -5253,7 +5253,7 @@
         </is>
       </c>
       <c r="E169" s="23" t="n">
-        <v>148</v>
+        <v>205</v>
       </c>
     </row>
     <row r="170" ht="20" customHeight="1">
@@ -5278,7 +5278,7 @@
         </is>
       </c>
       <c r="E170" s="20" t="n">
-        <v>210</v>
+        <v>138</v>
       </c>
     </row>
     <row r="171" ht="20" customHeight="1">
@@ -5303,7 +5303,7 @@
         </is>
       </c>
       <c r="E171" s="23" t="n">
-        <v>224</v>
+        <v>211</v>
       </c>
     </row>
     <row r="172" ht="20" customHeight="1">
@@ -5328,7 +5328,7 @@
         </is>
       </c>
       <c r="E172" s="20" t="n">
-        <v>140</v>
+        <v>127</v>
       </c>
     </row>
     <row r="173" ht="20" customHeight="1">
@@ -5353,7 +5353,7 @@
         </is>
       </c>
       <c r="E173" s="23" t="n">
-        <v>226</v>
+        <v>235</v>
       </c>
     </row>
     <row r="174" ht="20" customHeight="1">
@@ -5378,7 +5378,7 @@
         </is>
       </c>
       <c r="E174" s="20" t="n">
-        <v>159</v>
+        <v>152</v>
       </c>
     </row>
     <row r="175" ht="20" customHeight="1">
@@ -5403,7 +5403,7 @@
         </is>
       </c>
       <c r="E175" s="23" t="n">
-        <v>112</v>
+        <v>200</v>
       </c>
     </row>
     <row r="176" ht="20" customHeight="1">
@@ -5428,7 +5428,7 @@
         </is>
       </c>
       <c r="E176" s="20" t="n">
-        <v>230</v>
+        <v>207</v>
       </c>
     </row>
     <row r="177" ht="20" customHeight="1">
@@ -5453,7 +5453,7 @@
         </is>
       </c>
       <c r="E177" s="23" t="n">
-        <v>155</v>
+        <v>124</v>
       </c>
     </row>
     <row r="178" ht="20" customHeight="1">
@@ -5478,7 +5478,7 @@
         </is>
       </c>
       <c r="E178" s="20" t="n">
-        <v>134</v>
+        <v>121</v>
       </c>
     </row>
     <row r="179" ht="20" customHeight="1">
@@ -5503,7 +5503,7 @@
         </is>
       </c>
       <c r="E179" s="23" t="n">
-        <v>158</v>
+        <v>207</v>
       </c>
     </row>
     <row r="180" ht="20" customHeight="1">
@@ -5528,7 +5528,7 @@
         </is>
       </c>
       <c r="E180" s="20" t="n">
-        <v>135</v>
+        <v>220</v>
       </c>
     </row>
     <row r="181" ht="20" customHeight="1">
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="E181" s="23" t="n">
-        <v>154</v>
+        <v>200</v>
       </c>
     </row>
     <row r="182" ht="20" customHeight="1">
@@ -5578,7 +5578,7 @@
         </is>
       </c>
       <c r="E182" s="20" t="n">
-        <v>219</v>
+        <v>194</v>
       </c>
     </row>
     <row r="183" ht="20" customHeight="1">
@@ -5603,7 +5603,7 @@
         </is>
       </c>
       <c r="E183" s="23" t="n">
-        <v>214</v>
+        <v>169</v>
       </c>
     </row>
     <row r="184" ht="20" customHeight="1">
@@ -5628,7 +5628,7 @@
         </is>
       </c>
       <c r="E184" s="20" t="n">
-        <v>186</v>
+        <v>231</v>
       </c>
     </row>
     <row r="185" ht="20" customHeight="1">
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="E185" s="23" t="n">
-        <v>160</v>
+        <v>129</v>
       </c>
     </row>
     <row r="186" ht="20" customHeight="1">
@@ -5678,7 +5678,7 @@
         </is>
       </c>
       <c r="E186" s="20" t="n">
-        <v>213</v>
+        <v>221</v>
       </c>
     </row>
     <row r="187" ht="20" customHeight="1">
@@ -5703,7 +5703,7 @@
         </is>
       </c>
       <c r="E187" s="23" t="n">
-        <v>194</v>
+        <v>206</v>
       </c>
     </row>
     <row r="188" ht="20" customHeight="1">
@@ -5728,7 +5728,7 @@
         </is>
       </c>
       <c r="E188" s="20" t="n">
-        <v>231</v>
+        <v>223</v>
       </c>
     </row>
     <row r="189" ht="20" customHeight="1">
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="E189" s="23" t="n">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="190" ht="20" customHeight="1">
@@ -5778,7 +5778,7 @@
         </is>
       </c>
       <c r="E190" s="20" t="n">
-        <v>233</v>
+        <v>157</v>
       </c>
     </row>
     <row r="191" ht="20" customHeight="1">
@@ -5803,7 +5803,7 @@
         </is>
       </c>
       <c r="E191" s="23" t="n">
-        <v>113</v>
+        <v>179</v>
       </c>
     </row>
     <row r="192" ht="20" customHeight="1">
@@ -5828,7 +5828,7 @@
         </is>
       </c>
       <c r="E192" s="20" t="n">
-        <v>141</v>
+        <v>232</v>
       </c>
     </row>
     <row r="193" ht="20" customHeight="1">
@@ -5853,7 +5853,7 @@
         </is>
       </c>
       <c r="E193" s="23" t="n">
-        <v>161</v>
+        <v>181</v>
       </c>
     </row>
     <row r="194" ht="20" customHeight="1">
@@ -5878,7 +5878,7 @@
         </is>
       </c>
       <c r="E194" s="20" t="n">
-        <v>160</v>
+        <v>217</v>
       </c>
     </row>
     <row r="195" ht="20" customHeight="1">
@@ -5903,7 +5903,7 @@
         </is>
       </c>
       <c r="E195" s="23" t="n">
-        <v>173</v>
+        <v>213</v>
       </c>
     </row>
     <row r="196" ht="20" customHeight="1">
@@ -5928,7 +5928,7 @@
         </is>
       </c>
       <c r="E196" s="20" t="n">
-        <v>129</v>
+        <v>216</v>
       </c>
     </row>
     <row r="197" ht="20" customHeight="1">
@@ -5953,7 +5953,7 @@
         </is>
       </c>
       <c r="E197" s="23" t="n">
-        <v>199</v>
+        <v>144</v>
       </c>
     </row>
     <row r="198" ht="20" customHeight="1">
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="E198" s="20" t="n">
-        <v>214</v>
+        <v>179</v>
       </c>
     </row>
     <row r="199" ht="20" customHeight="1">
@@ -6003,7 +6003,7 @@
         </is>
       </c>
       <c r="E199" s="23" t="n">
-        <v>220</v>
+        <v>169</v>
       </c>
     </row>
     <row r="200" ht="20" customHeight="1">
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="E200" s="20" t="n">
-        <v>171</v>
+        <v>140</v>
       </c>
     </row>
     <row r="201" ht="20" customHeight="1">
@@ -6053,7 +6053,7 @@
         </is>
       </c>
       <c r="E201" s="23" t="n">
-        <v>231</v>
+        <v>131</v>
       </c>
     </row>
     <row r="202" ht="20" customHeight="1">
@@ -6078,7 +6078,7 @@
         </is>
       </c>
       <c r="E202" s="20" t="n">
-        <v>130</v>
+        <v>215</v>
       </c>
     </row>
     <row r="203" ht="20" customHeight="1">
@@ -6103,7 +6103,7 @@
         </is>
       </c>
       <c r="E203" s="23" t="n">
-        <v>188</v>
+        <v>157</v>
       </c>
     </row>
     <row r="204" ht="20" customHeight="1">
@@ -6128,7 +6128,7 @@
         </is>
       </c>
       <c r="E204" s="20" t="n">
-        <v>173</v>
+        <v>133</v>
       </c>
     </row>
     <row r="205" ht="20" customHeight="1">
@@ -6153,7 +6153,7 @@
         </is>
       </c>
       <c r="E205" s="23" t="n">
-        <v>204</v>
+        <v>167</v>
       </c>
     </row>
     <row r="206" ht="20" customHeight="1">
@@ -6178,7 +6178,7 @@
         </is>
       </c>
       <c r="E206" s="20" t="n">
-        <v>152</v>
+        <v>187</v>
       </c>
     </row>
     <row r="207" ht="20" customHeight="1">
@@ -6203,7 +6203,7 @@
         </is>
       </c>
       <c r="E207" s="23" t="n">
-        <v>204</v>
+        <v>119</v>
       </c>
     </row>
     <row r="208" ht="20" customHeight="1">
@@ -6228,7 +6228,7 @@
         </is>
       </c>
       <c r="E208" s="20" t="n">
-        <v>197</v>
+        <v>236</v>
       </c>
     </row>
     <row r="209" ht="20" customHeight="1">
@@ -6253,7 +6253,7 @@
         </is>
       </c>
       <c r="E209" s="23" t="n">
-        <v>135</v>
+        <v>149</v>
       </c>
     </row>
     <row r="210" ht="20" customHeight="1">
@@ -6278,7 +6278,7 @@
         </is>
       </c>
       <c r="E210" s="20" t="n">
-        <v>155</v>
+        <v>197</v>
       </c>
     </row>
     <row r="211" ht="20" customHeight="1">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="E211" s="23" t="n">
-        <v>206</v>
+        <v>234</v>
       </c>
     </row>
     <row r="212" ht="20" customHeight="1">
@@ -6328,7 +6328,7 @@
         </is>
       </c>
       <c r="E212" s="20" t="n">
-        <v>209</v>
+        <v>164</v>
       </c>
     </row>
     <row r="213" ht="20" customHeight="1">
@@ -6353,7 +6353,7 @@
         </is>
       </c>
       <c r="E213" s="23" t="n">
-        <v>133</v>
+        <v>197</v>
       </c>
     </row>
     <row r="214" ht="20" customHeight="1">
@@ -6378,7 +6378,7 @@
         </is>
       </c>
       <c r="E214" s="20" t="n">
-        <v>136</v>
+        <v>158</v>
       </c>
     </row>
     <row r="215" ht="20" customHeight="1">
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="E215" s="23" t="n">
-        <v>143</v>
+        <v>132</v>
       </c>
     </row>
     <row r="216" ht="20" customHeight="1">
@@ -6428,7 +6428,7 @@
         </is>
       </c>
       <c r="E216" s="20" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="217" ht="20" customHeight="1">
@@ -6453,7 +6453,7 @@
         </is>
       </c>
       <c r="E217" s="23" t="n">
-        <v>209</v>
+        <v>191</v>
       </c>
     </row>
     <row r="218" ht="20" customHeight="1">
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="E219" s="23" t="n">
-        <v>235</v>
+        <v>135</v>
       </c>
     </row>
     <row r="220" ht="20" customHeight="1">
@@ -6528,7 +6528,7 @@
         </is>
       </c>
       <c r="E220" s="20" t="n">
-        <v>171</v>
+        <v>153</v>
       </c>
     </row>
     <row r="221" ht="20" customHeight="1">
@@ -6553,7 +6553,7 @@
         </is>
       </c>
       <c r="E221" s="23" t="n">
-        <v>226</v>
+        <v>194</v>
       </c>
     </row>
     <row r="222" ht="20" customHeight="1">
@@ -6578,7 +6578,7 @@
         </is>
       </c>
       <c r="E222" s="20" t="n">
-        <v>213</v>
+        <v>138</v>
       </c>
     </row>
     <row r="223" ht="20" customHeight="1">
@@ -6603,7 +6603,7 @@
         </is>
       </c>
       <c r="E223" s="23" t="n">
-        <v>233</v>
+        <v>188</v>
       </c>
     </row>
     <row r="224" ht="20" customHeight="1">
@@ -6628,7 +6628,7 @@
         </is>
       </c>
       <c r="E224" s="20" t="n">
-        <v>194</v>
+        <v>225</v>
       </c>
     </row>
     <row r="225" ht="20" customHeight="1">
@@ -6653,7 +6653,7 @@
         </is>
       </c>
       <c r="E225" s="23" t="n">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="226" ht="20" customHeight="1">
@@ -6678,7 +6678,7 @@
         </is>
       </c>
       <c r="E226" s="20" t="n">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="227" ht="20" customHeight="1">
@@ -6703,7 +6703,7 @@
         </is>
       </c>
       <c r="E227" s="23" t="n">
-        <v>112</v>
+        <v>200</v>
       </c>
     </row>
     <row r="228" ht="20" customHeight="1">
@@ -6728,7 +6728,7 @@
         </is>
       </c>
       <c r="E228" s="20" t="n">
-        <v>134</v>
+        <v>184</v>
       </c>
     </row>
     <row r="229" ht="20" customHeight="1">
@@ -6753,7 +6753,7 @@
         </is>
       </c>
       <c r="E229" s="23" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="230" ht="20" customHeight="1">
@@ -6778,7 +6778,7 @@
         </is>
       </c>
       <c r="E230" s="20" t="n">
-        <v>191</v>
+        <v>222</v>
       </c>
     </row>
     <row r="231" ht="20" customHeight="1">
@@ -6803,7 +6803,7 @@
         </is>
       </c>
       <c r="E231" s="23" t="n">
-        <v>206</v>
+        <v>119</v>
       </c>
     </row>
     <row r="232" ht="20" customHeight="1">
@@ -6828,7 +6828,7 @@
         </is>
       </c>
       <c r="E232" s="20" t="n">
-        <v>114</v>
+        <v>226</v>
       </c>
     </row>
     <row r="233" ht="20" customHeight="1">
@@ -6853,7 +6853,7 @@
         </is>
       </c>
       <c r="E233" s="23" t="n">
-        <v>204</v>
+        <v>149</v>
       </c>
     </row>
     <row r="234" ht="20" customHeight="1">
@@ -6878,7 +6878,7 @@
         </is>
       </c>
       <c r="E234" s="20" t="n">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="235" ht="20" customHeight="1">
@@ -6903,7 +6903,7 @@
         </is>
       </c>
       <c r="E235" s="23" t="n">
-        <v>238</v>
+        <v>223</v>
       </c>
     </row>
     <row r="236" ht="20" customHeight="1">
@@ -6928,7 +6928,7 @@
         </is>
       </c>
       <c r="E236" s="20" t="n">
-        <v>141</v>
+        <v>126</v>
       </c>
     </row>
     <row r="237" ht="20" customHeight="1">
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="E237" s="23" t="n">
-        <v>143</v>
+        <v>115</v>
       </c>
     </row>
     <row r="238" ht="20" customHeight="1">
@@ -6978,7 +6978,7 @@
         </is>
       </c>
       <c r="E238" s="20" t="n">
-        <v>121</v>
+        <v>185</v>
       </c>
     </row>
     <row r="239" ht="20" customHeight="1">
@@ -7003,7 +7003,7 @@
         </is>
       </c>
       <c r="E239" s="23" t="n">
-        <v>168</v>
+        <v>181</v>
       </c>
     </row>
     <row r="240" ht="20" customHeight="1">
@@ -7028,7 +7028,7 @@
         </is>
       </c>
       <c r="E240" s="20" t="n">
-        <v>205</v>
+        <v>151</v>
       </c>
     </row>
     <row r="241" ht="20" customHeight="1">
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="E241" s="23" t="n">
-        <v>186</v>
+        <v>130</v>
       </c>
     </row>
     <row r="242" ht="20" customHeight="1">
@@ -7078,7 +7078,7 @@
         </is>
       </c>
       <c r="E242" s="20" t="n">
-        <v>215</v>
+        <v>167</v>
       </c>
     </row>
     <row r="243" ht="20" customHeight="1">
@@ -7103,7 +7103,7 @@
         </is>
       </c>
       <c r="E243" s="23" t="n">
-        <v>151</v>
+        <v>139</v>
       </c>
     </row>
     <row r="244" ht="20" customHeight="1">
@@ -7128,7 +7128,7 @@
         </is>
       </c>
       <c r="E244" s="20" t="n">
-        <v>173</v>
+        <v>200</v>
       </c>
     </row>
     <row r="245" ht="20" customHeight="1">
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="E245" s="23" t="n">
-        <v>229</v>
+        <v>194</v>
       </c>
     </row>
     <row r="246" ht="20" customHeight="1">
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="E246" s="20" t="n">
-        <v>236</v>
+        <v>169</v>
       </c>
     </row>
     <row r="247" ht="20" customHeight="1">
@@ -7203,7 +7203,7 @@
         </is>
       </c>
       <c r="E247" s="23" t="n">
-        <v>238</v>
+        <v>139</v>
       </c>
     </row>
     <row r="248" ht="20" customHeight="1">
@@ -7228,7 +7228,7 @@
         </is>
       </c>
       <c r="E248" s="20" t="n">
-        <v>124</v>
+        <v>233</v>
       </c>
     </row>
     <row r="249" ht="20" customHeight="1">
@@ -7253,7 +7253,7 @@
         </is>
       </c>
       <c r="E249" s="23" t="n">
-        <v>138</v>
+        <v>185</v>
       </c>
     </row>
     <row r="250" ht="20" customHeight="1">
@@ -7278,7 +7278,7 @@
         </is>
       </c>
       <c r="E250" s="20" t="n">
-        <v>167</v>
+        <v>238</v>
       </c>
     </row>
     <row r="251" ht="20" customHeight="1">
@@ -7303,7 +7303,7 @@
         </is>
       </c>
       <c r="E251" s="23" t="n">
-        <v>175</v>
+        <v>193</v>
       </c>
     </row>
     <row r="252" ht="20" customHeight="1">
@@ -7328,7 +7328,7 @@
         </is>
       </c>
       <c r="E252" s="20" t="n">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="253" ht="20" customHeight="1">
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="E253" s="23" t="n">
-        <v>153</v>
+        <v>113</v>
       </c>
     </row>
     <row r="254" ht="20" customHeight="1">
@@ -7378,7 +7378,7 @@
         </is>
       </c>
       <c r="E254" s="20" t="n">
-        <v>216</v>
+        <v>222</v>
       </c>
     </row>
     <row r="255" ht="20" customHeight="1">
@@ -7403,7 +7403,7 @@
         </is>
       </c>
       <c r="E255" s="23" t="n">
-        <v>223</v>
+        <v>175</v>
       </c>
     </row>
     <row r="256" ht="20" customHeight="1">
@@ -7428,7 +7428,7 @@
         </is>
       </c>
       <c r="E256" s="20" t="n">
-        <v>206</v>
+        <v>174</v>
       </c>
     </row>
     <row r="257" ht="20" customHeight="1">
@@ -7453,7 +7453,7 @@
         </is>
       </c>
       <c r="E257" s="23" t="n">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="258" ht="20" customHeight="1">
@@ -7478,7 +7478,7 @@
         </is>
       </c>
       <c r="E258" s="20" t="n">
-        <v>190</v>
+        <v>116</v>
       </c>
     </row>
     <row r="259" ht="20" customHeight="1">
@@ -7503,7 +7503,7 @@
         </is>
       </c>
       <c r="E259" s="23" t="n">
-        <v>239</v>
+        <v>144</v>
       </c>
     </row>
     <row r="260" ht="20" customHeight="1">
@@ -7528,7 +7528,7 @@
         </is>
       </c>
       <c r="E260" s="20" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="261" ht="20" customHeight="1">
@@ -7553,7 +7553,7 @@
         </is>
       </c>
       <c r="E261" s="23" t="n">
-        <v>173</v>
+        <v>139</v>
       </c>
     </row>
     <row r="262" ht="20" customHeight="1">
@@ -7578,7 +7578,7 @@
         </is>
       </c>
       <c r="E262" s="20" t="n">
-        <v>124</v>
+        <v>139</v>
       </c>
     </row>
     <row r="263" ht="20" customHeight="1">
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="E263" s="23" t="n">
-        <v>136</v>
+        <v>115</v>
       </c>
     </row>
     <row r="264" ht="20" customHeight="1">
@@ -7628,7 +7628,7 @@
         </is>
       </c>
       <c r="E264" s="20" t="n">
-        <v>143</v>
+        <v>215</v>
       </c>
     </row>
     <row r="265" ht="20" customHeight="1">
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="E265" s="23" t="n">
-        <v>136</v>
+        <v>160</v>
       </c>
     </row>
     <row r="266" ht="20" customHeight="1">
@@ -7678,7 +7678,7 @@
         </is>
       </c>
       <c r="E266" s="20" t="n">
-        <v>142</v>
+        <v>168</v>
       </c>
     </row>
     <row r="267" ht="20" customHeight="1">
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="E267" s="23" t="n">
-        <v>146</v>
+        <v>124</v>
       </c>
     </row>
     <row r="268" ht="20" customHeight="1">
@@ -7728,7 +7728,7 @@
         </is>
       </c>
       <c r="E268" s="20" t="n">
-        <v>143</v>
+        <v>190</v>
       </c>
     </row>
     <row r="269" ht="20" customHeight="1">
@@ -7753,7 +7753,7 @@
         </is>
       </c>
       <c r="E269" s="23" t="n">
-        <v>192</v>
+        <v>175</v>
       </c>
     </row>
     <row r="270" ht="20" customHeight="1">
@@ -7778,7 +7778,7 @@
         </is>
       </c>
       <c r="E270" s="20" t="n">
-        <v>235</v>
+        <v>148</v>
       </c>
     </row>
     <row r="271" ht="20" customHeight="1">
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="E271" s="23" t="n">
-        <v>166</v>
+        <v>176</v>
       </c>
     </row>
     <row r="272" ht="20" customHeight="1">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="E272" s="20" t="n">
-        <v>194</v>
+        <v>111</v>
       </c>
     </row>
     <row r="273" ht="20" customHeight="1">
@@ -7853,7 +7853,7 @@
         </is>
       </c>
       <c r="E273" s="23" t="n">
-        <v>229</v>
+        <v>206</v>
       </c>
     </row>
     <row r="274" ht="20" customHeight="1">
@@ -7878,7 +7878,7 @@
         </is>
       </c>
       <c r="E274" s="20" t="n">
-        <v>139</v>
+        <v>205</v>
       </c>
     </row>
     <row r="275" ht="20" customHeight="1">
@@ -7903,7 +7903,7 @@
         </is>
       </c>
       <c r="E275" s="23" t="n">
-        <v>219</v>
+        <v>111</v>
       </c>
     </row>
     <row r="276" ht="20" customHeight="1">
@@ -7928,7 +7928,7 @@
         </is>
       </c>
       <c r="E276" s="20" t="n">
-        <v>201</v>
+        <v>228</v>
       </c>
     </row>
     <row r="277" ht="20" customHeight="1">
@@ -7953,7 +7953,7 @@
         </is>
       </c>
       <c r="E277" s="23" t="n">
-        <v>161</v>
+        <v>218</v>
       </c>
     </row>
     <row r="278" ht="20" customHeight="1">
@@ -7978,7 +7978,7 @@
         </is>
       </c>
       <c r="E278" s="20" t="n">
-        <v>161</v>
+        <v>233</v>
       </c>
     </row>
     <row r="279" ht="20" customHeight="1">
@@ -8003,7 +8003,7 @@
         </is>
       </c>
       <c r="E279" s="23" t="n">
-        <v>141</v>
+        <v>216</v>
       </c>
     </row>
     <row r="280" ht="20" customHeight="1">
@@ -8028,7 +8028,7 @@
         </is>
       </c>
       <c r="E280" s="20" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="281" ht="20" customHeight="1">
@@ -8053,7 +8053,7 @@
         </is>
       </c>
       <c r="E281" s="23" t="n">
-        <v>191</v>
+        <v>174</v>
       </c>
     </row>
     <row r="282" ht="20" customHeight="1">
@@ -8078,7 +8078,7 @@
         </is>
       </c>
       <c r="E282" s="20" t="n">
-        <v>160</v>
+        <v>236</v>
       </c>
     </row>
     <row r="283" ht="20" customHeight="1">
@@ -8103,7 +8103,7 @@
         </is>
       </c>
       <c r="E283" s="23" t="n">
-        <v>202</v>
+        <v>233</v>
       </c>
     </row>
     <row r="284" ht="20" customHeight="1">
@@ -8128,7 +8128,7 @@
         </is>
       </c>
       <c r="E284" s="20" t="n">
-        <v>142</v>
+        <v>202</v>
       </c>
     </row>
     <row r="285" ht="20" customHeight="1">
@@ -8153,7 +8153,7 @@
         </is>
       </c>
       <c r="E285" s="23" t="n">
-        <v>206</v>
+        <v>152</v>
       </c>
     </row>
     <row r="286" ht="20" customHeight="1">
@@ -8178,7 +8178,7 @@
         </is>
       </c>
       <c r="E286" s="20" t="n">
-        <v>184</v>
+        <v>119</v>
       </c>
     </row>
     <row r="287" ht="20" customHeight="1">
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="E287" s="23" t="n">
-        <v>116</v>
+        <v>212</v>
       </c>
     </row>
     <row r="288" ht="20" customHeight="1">
@@ -8228,7 +8228,7 @@
         </is>
       </c>
       <c r="E288" s="20" t="n">
-        <v>164</v>
+        <v>122</v>
       </c>
     </row>
     <row r="289" ht="20" customHeight="1">
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="E289" s="23" t="n">
-        <v>156</v>
+        <v>207</v>
       </c>
     </row>
     <row r="290" ht="20" customHeight="1">
@@ -8278,7 +8278,7 @@
         </is>
       </c>
       <c r="E290" s="20" t="n">
-        <v>204</v>
+        <v>178</v>
       </c>
     </row>
     <row r="291" ht="20" customHeight="1">
@@ -8303,7 +8303,7 @@
         </is>
       </c>
       <c r="E291" s="23" t="n">
-        <v>157</v>
+        <v>145</v>
       </c>
     </row>
     <row r="292" ht="20" customHeight="1">
@@ -8328,7 +8328,7 @@
         </is>
       </c>
       <c r="E292" s="20" t="n">
-        <v>212</v>
+        <v>123</v>
       </c>
     </row>
     <row r="293" ht="20" customHeight="1">
@@ -8353,7 +8353,7 @@
         </is>
       </c>
       <c r="E293" s="23" t="n">
-        <v>110</v>
+        <v>205</v>
       </c>
     </row>
     <row r="294" ht="20" customHeight="1">
@@ -8378,7 +8378,7 @@
         </is>
       </c>
       <c r="E294" s="20" t="n">
-        <v>165</v>
+        <v>189</v>
       </c>
     </row>
     <row r="295" ht="20" customHeight="1">
@@ -8403,7 +8403,7 @@
         </is>
       </c>
       <c r="E295" s="23" t="n">
-        <v>156</v>
+        <v>237</v>
       </c>
     </row>
     <row r="296" ht="20" customHeight="1">
@@ -8428,7 +8428,7 @@
         </is>
       </c>
       <c r="E296" s="20" t="n">
-        <v>232</v>
+        <v>166</v>
       </c>
     </row>
     <row r="297" ht="20" customHeight="1">
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="E297" s="23" t="n">
-        <v>111</v>
+        <v>237</v>
       </c>
     </row>
     <row r="298" ht="20" customHeight="1">
@@ -8478,7 +8478,7 @@
         </is>
       </c>
       <c r="E298" s="20" t="n">
-        <v>237</v>
+        <v>111</v>
       </c>
     </row>
     <row r="299" ht="20" customHeight="1">
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="E299" s="23" t="n">
-        <v>225</v>
+        <v>216</v>
       </c>
     </row>
     <row r="300" ht="20" customHeight="1">
@@ -8528,7 +8528,7 @@
         </is>
       </c>
       <c r="E300" s="20" t="n">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="301" ht="20" customHeight="1">
@@ -8553,7 +8553,7 @@
         </is>
       </c>
       <c r="E301" s="23" t="n">
-        <v>114</v>
+        <v>182</v>
       </c>
     </row>
     <row r="302" ht="20" customHeight="1">
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="E302" s="20" t="n">
-        <v>161</v>
+        <v>125</v>
       </c>
     </row>
     <row r="303" ht="20" customHeight="1">
@@ -8603,7 +8603,7 @@
         </is>
       </c>
       <c r="E303" s="23" t="n">
-        <v>234</v>
+        <v>218</v>
       </c>
     </row>
     <row r="304" ht="20" customHeight="1">
@@ -8628,7 +8628,7 @@
         </is>
       </c>
       <c r="E304" s="20" t="n">
-        <v>203</v>
+        <v>172</v>
       </c>
     </row>
     <row r="305" ht="20" customHeight="1">
@@ -8653,7 +8653,7 @@
         </is>
       </c>
       <c r="E305" s="23" t="n">
-        <v>123</v>
+        <v>170</v>
       </c>
     </row>
     <row r="306" ht="20" customHeight="1">
@@ -8678,7 +8678,7 @@
         </is>
       </c>
       <c r="E306" s="20" t="n">
-        <v>219</v>
+        <v>158</v>
       </c>
     </row>
     <row r="307" ht="20" customHeight="1">
@@ -8703,7 +8703,7 @@
         </is>
       </c>
       <c r="E307" s="23" t="n">
-        <v>122</v>
+        <v>182</v>
       </c>
     </row>
     <row r="308" ht="20" customHeight="1">
@@ -8728,7 +8728,7 @@
         </is>
       </c>
       <c r="E308" s="20" t="n">
-        <v>206</v>
+        <v>168</v>
       </c>
     </row>
     <row r="309" ht="20" customHeight="1">
@@ -8753,7 +8753,7 @@
         </is>
       </c>
       <c r="E309" s="23" t="n">
-        <v>178</v>
+        <v>127</v>
       </c>
     </row>
     <row r="310" ht="20" customHeight="1">
@@ -8778,7 +8778,7 @@
         </is>
       </c>
       <c r="E310" s="20" t="n">
-        <v>219</v>
+        <v>160</v>
       </c>
     </row>
     <row r="311" ht="20" customHeight="1">
@@ -8803,7 +8803,7 @@
         </is>
       </c>
       <c r="E311" s="23" t="n">
-        <v>205</v>
+        <v>156</v>
       </c>
     </row>
     <row r="312" ht="20" customHeight="1">
@@ -8828,7 +8828,7 @@
         </is>
       </c>
       <c r="E312" s="20" t="n">
-        <v>234</v>
+        <v>165</v>
       </c>
     </row>
     <row r="313" ht="20" customHeight="1">
@@ -8853,7 +8853,7 @@
         </is>
       </c>
       <c r="E313" s="23" t="n">
-        <v>176</v>
+        <v>191</v>
       </c>
     </row>
     <row r="314" ht="20" customHeight="1">
@@ -8878,7 +8878,7 @@
         </is>
       </c>
       <c r="E314" s="20" t="n">
-        <v>217</v>
+        <v>204</v>
       </c>
     </row>
     <row r="315" ht="20" customHeight="1">
@@ -8903,7 +8903,7 @@
         </is>
       </c>
       <c r="E315" s="23" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="316" ht="20" customHeight="1">
@@ -8928,7 +8928,7 @@
         </is>
       </c>
       <c r="E316" s="20" t="n">
-        <v>169</v>
+        <v>154</v>
       </c>
     </row>
     <row r="317" ht="20" customHeight="1">
@@ -8953,7 +8953,7 @@
         </is>
       </c>
       <c r="E317" s="23" t="n">
-        <v>119</v>
+        <v>215</v>
       </c>
     </row>
     <row r="318" ht="20" customHeight="1">
@@ -8978,7 +8978,7 @@
         </is>
       </c>
       <c r="E318" s="20" t="n">
-        <v>187</v>
+        <v>209</v>
       </c>
     </row>
     <row r="319" ht="20" customHeight="1">
@@ -9003,7 +9003,7 @@
         </is>
       </c>
       <c r="E319" s="23" t="n">
-        <v>196</v>
+        <v>208</v>
       </c>
     </row>
     <row r="320" ht="20" customHeight="1">
@@ -9028,7 +9028,7 @@
         </is>
       </c>
       <c r="E320" s="20" t="n">
-        <v>158</v>
+        <v>166</v>
       </c>
     </row>
     <row r="321" ht="20" customHeight="1">
@@ -9053,7 +9053,7 @@
         </is>
       </c>
       <c r="E321" s="23" t="n">
-        <v>126</v>
+        <v>221</v>
       </c>
     </row>
     <row r="322" ht="20" customHeight="1">
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="E323" s="23" t="n">
-        <v>211</v>
+        <v>136</v>
       </c>
     </row>
     <row r="324" ht="20" customHeight="1">
@@ -9128,7 +9128,7 @@
         </is>
       </c>
       <c r="E324" s="20" t="n">
-        <v>213</v>
+        <v>168</v>
       </c>
     </row>
     <row r="325" ht="20" customHeight="1">
@@ -9153,7 +9153,7 @@
         </is>
       </c>
       <c r="E325" s="23" t="n">
-        <v>198</v>
+        <v>120</v>
       </c>
     </row>
     <row r="326" ht="20" customHeight="1">
@@ -9178,7 +9178,7 @@
         </is>
       </c>
       <c r="E326" s="20" t="n">
-        <v>211</v>
+        <v>111</v>
       </c>
     </row>
     <row r="327" ht="20" customHeight="1">
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="E327" s="23" t="n">
-        <v>139</v>
+        <v>114</v>
       </c>
     </row>
     <row r="328" ht="20" customHeight="1">
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="E328" s="20" t="n">
-        <v>221</v>
+        <v>140</v>
       </c>
     </row>
     <row r="329" ht="20" customHeight="1">
@@ -9253,7 +9253,7 @@
         </is>
       </c>
       <c r="E329" s="23" t="n">
-        <v>197</v>
+        <v>217</v>
       </c>
     </row>
     <row r="330" ht="20" customHeight="1">
@@ -9278,7 +9278,7 @@
         </is>
       </c>
       <c r="E330" s="20" t="n">
-        <v>123</v>
+        <v>192</v>
       </c>
     </row>
     <row r="331" ht="20" customHeight="1">
@@ -9303,7 +9303,7 @@
         </is>
       </c>
       <c r="E331" s="23" t="n">
-        <v>231</v>
+        <v>223</v>
       </c>
     </row>
     <row r="332" ht="20" customHeight="1">
@@ -9328,7 +9328,7 @@
         </is>
       </c>
       <c r="E332" s="20" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="333" ht="20" customHeight="1">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="E333" s="23" t="n">
-        <v>143</v>
+        <v>201</v>
       </c>
     </row>
     <row r="334" ht="20" customHeight="1">
@@ -9378,7 +9378,7 @@
         </is>
       </c>
       <c r="E334" s="20" t="n">
-        <v>230</v>
+        <v>209</v>
       </c>
     </row>
     <row r="335" ht="20" customHeight="1">
@@ -9403,7 +9403,7 @@
         </is>
       </c>
       <c r="E335" s="23" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="336" ht="20" customHeight="1">
@@ -9428,7 +9428,7 @@
         </is>
       </c>
       <c r="E336" s="20" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="337" ht="20" customHeight="1">
@@ -9453,7 +9453,7 @@
         </is>
       </c>
       <c r="E337" s="23" t="n">
-        <v>231</v>
+        <v>207</v>
       </c>
     </row>
     <row r="338" ht="20" customHeight="1">
@@ -9478,7 +9478,7 @@
         </is>
       </c>
       <c r="E338" s="20" t="n">
-        <v>150</v>
+        <v>145</v>
       </c>
     </row>
     <row r="339" ht="20" customHeight="1">
@@ -9503,7 +9503,7 @@
         </is>
       </c>
       <c r="E339" s="23" t="n">
-        <v>157</v>
+        <v>204</v>
       </c>
     </row>
     <row r="340" ht="20" customHeight="1">
@@ -9528,7 +9528,7 @@
         </is>
       </c>
       <c r="E340" s="20" t="n">
-        <v>189</v>
+        <v>180</v>
       </c>
     </row>
     <row r="341" ht="20" customHeight="1">
@@ -9553,7 +9553,7 @@
         </is>
       </c>
       <c r="E341" s="23" t="n">
-        <v>221</v>
+        <v>201</v>
       </c>
     </row>
     <row r="342" ht="20" customHeight="1">
@@ -9578,7 +9578,7 @@
         </is>
       </c>
       <c r="E342" s="20" t="n">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="343" ht="20" customHeight="1">
@@ -9603,7 +9603,7 @@
         </is>
       </c>
       <c r="E343" s="23" t="n">
-        <v>129</v>
+        <v>196</v>
       </c>
     </row>
     <row r="344" ht="20" customHeight="1">
@@ -9628,7 +9628,7 @@
         </is>
       </c>
       <c r="E344" s="20" t="n">
-        <v>158</v>
+        <v>229</v>
       </c>
     </row>
     <row r="345" ht="20" customHeight="1">
@@ -9653,7 +9653,7 @@
         </is>
       </c>
       <c r="E345" s="23" t="n">
-        <v>141</v>
+        <v>160</v>
       </c>
     </row>
     <row r="346" ht="20" customHeight="1">
@@ -9678,7 +9678,7 @@
         </is>
       </c>
       <c r="E346" s="20" t="n">
-        <v>182</v>
+        <v>205</v>
       </c>
     </row>
     <row r="347" ht="20" customHeight="1">
@@ -9703,7 +9703,7 @@
         </is>
       </c>
       <c r="E347" s="23" t="n">
-        <v>125</v>
+        <v>118</v>
       </c>
     </row>
     <row r="348" ht="20" customHeight="1">
@@ -9728,7 +9728,7 @@
         </is>
       </c>
       <c r="E348" s="20" t="n">
-        <v>143</v>
+        <v>125</v>
       </c>
     </row>
     <row r="349" ht="20" customHeight="1">
@@ -9753,7 +9753,7 @@
         </is>
       </c>
       <c r="E349" s="23" t="n">
-        <v>215</v>
+        <v>189</v>
       </c>
     </row>
     <row r="350" ht="20" customHeight="1">
@@ -9803,7 +9803,7 @@
         </is>
       </c>
       <c r="E351" s="23" t="n">
-        <v>220</v>
+        <v>122</v>
       </c>
     </row>
     <row r="352" ht="20" customHeight="1">
@@ -9828,7 +9828,7 @@
         </is>
       </c>
       <c r="E352" s="20" t="n">
-        <v>121</v>
+        <v>138</v>
       </c>
     </row>
     <row r="353" ht="20" customHeight="1">
@@ -9853,7 +9853,7 @@
         </is>
       </c>
       <c r="E353" s="23" t="n">
-        <v>231</v>
+        <v>144</v>
       </c>
     </row>
     <row r="354" ht="20" customHeight="1">
@@ -9878,7 +9878,7 @@
         </is>
       </c>
       <c r="E354" s="20" t="n">
-        <v>188</v>
+        <v>128</v>
       </c>
     </row>
     <row r="355" ht="20" customHeight="1">
@@ -9903,7 +9903,7 @@
         </is>
       </c>
       <c r="E355" s="23" t="n">
-        <v>178</v>
+        <v>141</v>
       </c>
     </row>
     <row r="356" ht="20" customHeight="1">
@@ -9928,7 +9928,7 @@
         </is>
       </c>
       <c r="E356" s="20" t="n">
-        <v>113</v>
+        <v>188</v>
       </c>
     </row>
     <row r="357" ht="20" customHeight="1">
@@ -9953,7 +9953,7 @@
         </is>
       </c>
       <c r="E357" s="23" t="n">
-        <v>157</v>
+        <v>169</v>
       </c>
     </row>
     <row r="358" ht="20" customHeight="1">
@@ -9978,7 +9978,7 @@
         </is>
       </c>
       <c r="E358" s="20" t="n">
-        <v>135</v>
+        <v>231</v>
       </c>
     </row>
     <row r="359" ht="20" customHeight="1">
@@ -10003,7 +10003,7 @@
         </is>
       </c>
       <c r="E359" s="23" t="n">
-        <v>136</v>
+        <v>230</v>
       </c>
     </row>
     <row r="360" ht="20" customHeight="1">
@@ -10053,7 +10053,7 @@
         </is>
       </c>
       <c r="E361" s="23" t="n">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="362" ht="20" customHeight="1">
@@ -10078,7 +10078,7 @@
         </is>
       </c>
       <c r="E362" s="20" t="n">
-        <v>229</v>
+        <v>182</v>
       </c>
     </row>
     <row r="363" ht="20" customHeight="1">
@@ -10103,7 +10103,7 @@
         </is>
       </c>
       <c r="E363" s="23" t="n">
-        <v>136</v>
+        <v>125</v>
       </c>
     </row>
     <row r="364" ht="20" customHeight="1">
@@ -10128,7 +10128,7 @@
         </is>
       </c>
       <c r="E364" s="20" t="n">
-        <v>202</v>
+        <v>130</v>
       </c>
     </row>
     <row r="365" ht="20" customHeight="1">
@@ -10153,7 +10153,7 @@
         </is>
       </c>
       <c r="E365" s="23" t="n">
-        <v>182</v>
+        <v>205</v>
       </c>
     </row>
     <row r="366" ht="20" customHeight="1">
@@ -10178,7 +10178,7 @@
         </is>
       </c>
       <c r="E366" s="20" t="n">
-        <v>128</v>
+        <v>139</v>
       </c>
     </row>
     <row r="367" ht="20" customHeight="1">
@@ -10203,7 +10203,7 @@
         </is>
       </c>
       <c r="E367" s="23" t="n">
-        <v>181</v>
+        <v>208</v>
       </c>
     </row>
     <row r="368" ht="20" customHeight="1">
@@ -10228,7 +10228,7 @@
         </is>
       </c>
       <c r="E368" s="20" t="n">
-        <v>208</v>
+        <v>130</v>
       </c>
     </row>
     <row r="369" ht="20" customHeight="1">
@@ -10253,7 +10253,7 @@
         </is>
       </c>
       <c r="E369" s="23" t="n">
-        <v>194</v>
+        <v>222</v>
       </c>
     </row>
     <row r="370" ht="20" customHeight="1">
@@ -10278,7 +10278,7 @@
         </is>
       </c>
       <c r="E370" s="20" t="n">
-        <v>192</v>
+        <v>168</v>
       </c>
     </row>
     <row r="371" ht="20" customHeight="1">
@@ -10303,7 +10303,7 @@
         </is>
       </c>
       <c r="E371" s="23" t="n">
-        <v>111</v>
+        <v>158</v>
       </c>
     </row>
     <row r="372" ht="20" customHeight="1">
@@ -10353,7 +10353,7 @@
         </is>
       </c>
       <c r="E373" s="23" t="n">
-        <v>226</v>
+        <v>114</v>
       </c>
     </row>
     <row r="374" ht="20" customHeight="1">
@@ -10378,7 +10378,7 @@
         </is>
       </c>
       <c r="E374" s="20" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="375" ht="20" customHeight="1">
@@ -10403,7 +10403,7 @@
         </is>
       </c>
       <c r="E375" s="23" t="n">
-        <v>221</v>
+        <v>129</v>
       </c>
     </row>
     <row r="376" ht="20" customHeight="1">
@@ -10428,7 +10428,7 @@
         </is>
       </c>
       <c r="E376" s="20" t="n">
-        <v>112</v>
+        <v>169</v>
       </c>
     </row>
     <row r="377" ht="20" customHeight="1">
@@ -10453,7 +10453,7 @@
         </is>
       </c>
       <c r="E377" s="23" t="n">
-        <v>156</v>
+        <v>184</v>
       </c>
     </row>
     <row r="378" ht="20" customHeight="1">
@@ -10478,7 +10478,7 @@
         </is>
       </c>
       <c r="E378" s="20" t="n">
-        <v>200</v>
+        <v>146</v>
       </c>
     </row>
     <row r="379" ht="20" customHeight="1">
@@ -10503,7 +10503,7 @@
         </is>
       </c>
       <c r="E379" s="23" t="n">
-        <v>228</v>
+        <v>115</v>
       </c>
     </row>
     <row r="380" ht="20" customHeight="1">
@@ -10528,7 +10528,7 @@
         </is>
       </c>
       <c r="E380" s="20" t="n">
-        <v>237</v>
+        <v>151</v>
       </c>
     </row>
     <row r="381" ht="20" customHeight="1">
@@ -10553,7 +10553,7 @@
         </is>
       </c>
       <c r="E381" s="23" t="n">
-        <v>157</v>
+        <v>146</v>
       </c>
     </row>
     <row r="382" ht="20" customHeight="1">
@@ -10578,7 +10578,7 @@
         </is>
       </c>
       <c r="E382" s="20" t="n">
-        <v>142</v>
+        <v>112</v>
       </c>
     </row>
     <row r="383" ht="20" customHeight="1">
@@ -10603,7 +10603,7 @@
         </is>
       </c>
       <c r="E383" s="23" t="n">
-        <v>167</v>
+        <v>186</v>
       </c>
     </row>
     <row r="384" ht="20" customHeight="1">
@@ -10628,7 +10628,7 @@
         </is>
       </c>
       <c r="E384" s="20" t="n">
-        <v>173</v>
+        <v>114</v>
       </c>
     </row>
     <row r="385" ht="20" customHeight="1">
@@ -10653,7 +10653,7 @@
         </is>
       </c>
       <c r="E385" s="23" t="n">
-        <v>126</v>
+        <v>203</v>
       </c>
     </row>
     <row r="386" ht="20" customHeight="1">
@@ -10678,7 +10678,7 @@
         </is>
       </c>
       <c r="E386" s="20" t="n">
-        <v>164</v>
+        <v>190</v>
       </c>
     </row>
     <row r="387" ht="20" customHeight="1">
@@ -10703,7 +10703,7 @@
         </is>
       </c>
       <c r="E387" s="23" t="n">
-        <v>183</v>
+        <v>196</v>
       </c>
     </row>
     <row r="388" ht="20" customHeight="1">
@@ -10728,7 +10728,7 @@
         </is>
       </c>
       <c r="E388" s="20" t="n">
-        <v>170</v>
+        <v>234</v>
       </c>
     </row>
     <row r="389" ht="20" customHeight="1">
@@ -10753,7 +10753,7 @@
         </is>
       </c>
       <c r="E389" s="23" t="n">
-        <v>225</v>
+        <v>136</v>
       </c>
     </row>
     <row r="390" ht="20" customHeight="1">
@@ -10778,7 +10778,7 @@
         </is>
       </c>
       <c r="E390" s="20" t="n">
-        <v>127</v>
+        <v>181</v>
       </c>
     </row>
     <row r="391" ht="20" customHeight="1">
@@ -10803,7 +10803,7 @@
         </is>
       </c>
       <c r="E391" s="23" t="n">
-        <v>205</v>
+        <v>137</v>
       </c>
     </row>
     <row r="392" ht="20" customHeight="1">
@@ -10828,7 +10828,7 @@
         </is>
       </c>
       <c r="E392" s="20" t="n">
-        <v>156</v>
+        <v>186</v>
       </c>
     </row>
     <row r="393" ht="20" customHeight="1">
@@ -10853,7 +10853,7 @@
         </is>
       </c>
       <c r="E393" s="23" t="n">
-        <v>161</v>
+        <v>180</v>
       </c>
     </row>
     <row r="394" ht="20" customHeight="1">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="E394" s="20" t="n">
-        <v>132</v>
+        <v>189</v>
       </c>
     </row>
     <row r="395" ht="20" customHeight="1">
@@ -10903,7 +10903,7 @@
         </is>
       </c>
       <c r="E395" s="23" t="n">
-        <v>238</v>
+        <v>219</v>
       </c>
     </row>
     <row r="396" ht="20" customHeight="1">
@@ -10928,7 +10928,7 @@
         </is>
       </c>
       <c r="E396" s="20" t="n">
-        <v>136</v>
+        <v>234</v>
       </c>
     </row>
     <row r="397" ht="20" customHeight="1">
@@ -10953,7 +10953,7 @@
         </is>
       </c>
       <c r="E397" s="23" t="n">
-        <v>218</v>
+        <v>131</v>
       </c>
     </row>
     <row r="398" ht="20" customHeight="1">
@@ -10978,7 +10978,7 @@
         </is>
       </c>
       <c r="E398" s="20" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="399" ht="20" customHeight="1">
@@ -11003,7 +11003,7 @@
         </is>
       </c>
       <c r="E399" s="23" t="n">
-        <v>173</v>
+        <v>205</v>
       </c>
     </row>
     <row r="400" ht="20" customHeight="1">
@@ -11028,7 +11028,7 @@
         </is>
       </c>
       <c r="E400" s="20" t="n">
-        <v>214</v>
+        <v>228</v>
       </c>
     </row>
     <row r="401" ht="20" customHeight="1">
@@ -11053,7 +11053,7 @@
         </is>
       </c>
       <c r="E401" s="23" t="n">
-        <v>187</v>
+        <v>158</v>
       </c>
     </row>
     <row r="402" ht="20" customHeight="1">
@@ -11078,7 +11078,7 @@
         </is>
       </c>
       <c r="E402" s="20" t="n">
-        <v>157</v>
+        <v>183</v>
       </c>
     </row>
     <row r="403" ht="20" customHeight="1">
@@ -11103,7 +11103,7 @@
         </is>
       </c>
       <c r="E403" s="23" t="n">
-        <v>213</v>
+        <v>234</v>
       </c>
     </row>
     <row r="404" ht="20" customHeight="1">
@@ -11128,7 +11128,7 @@
         </is>
       </c>
       <c r="E404" s="20" t="n">
-        <v>226</v>
+        <v>199</v>
       </c>
     </row>
     <row r="405" ht="20" customHeight="1">
@@ -11153,7 +11153,7 @@
         </is>
       </c>
       <c r="E405" s="23" t="n">
-        <v>233</v>
+        <v>226</v>
       </c>
     </row>
     <row r="406" ht="20" customHeight="1">
@@ -11178,7 +11178,7 @@
         </is>
       </c>
       <c r="E406" s="20" t="n">
-        <v>162</v>
+        <v>121</v>
       </c>
     </row>
     <row r="407" ht="20" customHeight="1">
@@ -11203,7 +11203,7 @@
         </is>
       </c>
       <c r="E407" s="23" t="n">
-        <v>159</v>
+        <v>200</v>
       </c>
     </row>
     <row r="408" ht="20" customHeight="1">
@@ -11228,7 +11228,7 @@
         </is>
       </c>
       <c r="E408" s="20" t="n">
-        <v>150</v>
+        <v>232</v>
       </c>
     </row>
     <row r="409" ht="20" customHeight="1">
@@ -11253,7 +11253,7 @@
         </is>
       </c>
       <c r="E409" s="23" t="n">
-        <v>135</v>
+        <v>198</v>
       </c>
     </row>
     <row r="410" ht="20" customHeight="1">
@@ -11278,7 +11278,7 @@
         </is>
       </c>
       <c r="E410" s="20" t="n">
-        <v>240</v>
+        <v>116</v>
       </c>
     </row>
     <row r="411" ht="20" customHeight="1">
@@ -11303,7 +11303,7 @@
         </is>
       </c>
       <c r="E411" s="23" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="412" ht="20" customHeight="1">
@@ -11328,7 +11328,7 @@
         </is>
       </c>
       <c r="E412" s="20" t="n">
-        <v>183</v>
+        <v>203</v>
       </c>
     </row>
     <row r="413" ht="20" customHeight="1">
@@ -11353,7 +11353,7 @@
         </is>
       </c>
       <c r="E413" s="23" t="n">
-        <v>152</v>
+        <v>139</v>
       </c>
     </row>
     <row r="414" ht="20" customHeight="1">
@@ -11378,7 +11378,7 @@
         </is>
       </c>
       <c r="E414" s="20" t="n">
-        <v>207</v>
+        <v>165</v>
       </c>
     </row>
     <row r="415" ht="20" customHeight="1">
@@ -11403,7 +11403,7 @@
         </is>
       </c>
       <c r="E415" s="23" t="n">
-        <v>127</v>
+        <v>159</v>
       </c>
     </row>
     <row r="416" ht="20" customHeight="1">
@@ -11428,7 +11428,7 @@
         </is>
       </c>
       <c r="E416" s="20" t="n">
-        <v>232</v>
+        <v>213</v>
       </c>
     </row>
     <row r="417" ht="20" customHeight="1">
@@ -11453,7 +11453,7 @@
         </is>
       </c>
       <c r="E417" s="23" t="n">
-        <v>140</v>
+        <v>236</v>
       </c>
     </row>
     <row r="418" ht="20" customHeight="1">
@@ -11478,7 +11478,7 @@
         </is>
       </c>
       <c r="E418" s="20" t="n">
-        <v>212</v>
+        <v>124</v>
       </c>
     </row>
     <row r="419" ht="20" customHeight="1">
@@ -11503,7 +11503,7 @@
         </is>
       </c>
       <c r="E419" s="23" t="n">
-        <v>202</v>
+        <v>143</v>
       </c>
     </row>
     <row r="420" ht="20" customHeight="1">
@@ -11528,7 +11528,7 @@
         </is>
       </c>
       <c r="E420" s="20" t="n">
-        <v>166</v>
+        <v>189</v>
       </c>
     </row>
     <row r="421" ht="20" customHeight="1">
@@ -11553,7 +11553,7 @@
         </is>
       </c>
       <c r="E421" s="23" t="n">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="422" ht="20" customHeight="1">
@@ -11578,7 +11578,7 @@
         </is>
       </c>
       <c r="E422" s="20" t="n">
-        <v>151</v>
+        <v>185</v>
       </c>
     </row>
     <row r="423" ht="20" customHeight="1">
@@ -11603,7 +11603,7 @@
         </is>
       </c>
       <c r="E423" s="23" t="n">
-        <v>156</v>
+        <v>238</v>
       </c>
     </row>
     <row r="424" ht="20" customHeight="1">
@@ -11628,7 +11628,7 @@
         </is>
       </c>
       <c r="E424" s="20" t="n">
-        <v>238</v>
+        <v>218</v>
       </c>
     </row>
     <row r="425" ht="20" customHeight="1">
@@ -11653,7 +11653,7 @@
         </is>
       </c>
       <c r="E425" s="23" t="n">
-        <v>205</v>
+        <v>188</v>
       </c>
     </row>
     <row r="426" ht="20" customHeight="1">
@@ -11678,7 +11678,7 @@
         </is>
       </c>
       <c r="E426" s="20" t="n">
-        <v>137</v>
+        <v>200</v>
       </c>
     </row>
     <row r="427" ht="20" customHeight="1">
@@ -11703,7 +11703,7 @@
         </is>
       </c>
       <c r="E427" s="23" t="n">
-        <v>225</v>
+        <v>142</v>
       </c>
     </row>
     <row r="428" ht="20" customHeight="1">
@@ -11728,7 +11728,7 @@
         </is>
       </c>
       <c r="E428" s="20" t="n">
-        <v>190</v>
+        <v>119</v>
       </c>
     </row>
     <row r="429" ht="20" customHeight="1">
@@ -11753,7 +11753,7 @@
         </is>
       </c>
       <c r="E429" s="23" t="n">
-        <v>223</v>
+        <v>114</v>
       </c>
     </row>
     <row r="430" ht="20" customHeight="1">
@@ -11778,7 +11778,7 @@
         </is>
       </c>
       <c r="E430" s="20" t="n">
-        <v>224</v>
+        <v>187</v>
       </c>
     </row>
     <row r="431" ht="20" customHeight="1">
@@ -11803,7 +11803,7 @@
         </is>
       </c>
       <c r="E431" s="23" t="n">
-        <v>154</v>
+        <v>162</v>
       </c>
     </row>
     <row r="432" ht="20" customHeight="1">
@@ -11828,7 +11828,7 @@
         </is>
       </c>
       <c r="E432" s="20" t="n">
-        <v>161</v>
+        <v>220</v>
       </c>
     </row>
     <row r="433" ht="20" customHeight="1">
@@ -11853,7 +11853,7 @@
         </is>
       </c>
       <c r="E433" s="23" t="n">
-        <v>156</v>
+        <v>186</v>
       </c>
     </row>
     <row r="434" ht="20" customHeight="1">
@@ -11878,7 +11878,7 @@
         </is>
       </c>
       <c r="E434" s="20" t="n">
-        <v>149</v>
+        <v>168</v>
       </c>
     </row>
     <row r="435" ht="20" customHeight="1">
@@ -11903,7 +11903,7 @@
         </is>
       </c>
       <c r="E435" s="23" t="n">
-        <v>205</v>
+        <v>113</v>
       </c>
     </row>
     <row r="436" ht="20" customHeight="1">
@@ -11928,7 +11928,7 @@
         </is>
       </c>
       <c r="E436" s="20" t="n">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="437" ht="20" customHeight="1">
@@ -11953,7 +11953,7 @@
         </is>
       </c>
       <c r="E437" s="23" t="n">
-        <v>212</v>
+        <v>178</v>
       </c>
     </row>
     <row r="438" ht="20" customHeight="1">
@@ -11978,7 +11978,7 @@
         </is>
       </c>
       <c r="E438" s="20" t="n">
-        <v>156</v>
+        <v>186</v>
       </c>
     </row>
     <row r="439" ht="20" customHeight="1">
@@ -12003,7 +12003,7 @@
         </is>
       </c>
       <c r="E439" s="23" t="n">
-        <v>186</v>
+        <v>210</v>
       </c>
     </row>
     <row r="440" ht="20" customHeight="1">
@@ -12028,7 +12028,7 @@
         </is>
       </c>
       <c r="E440" s="20" t="n">
-        <v>184</v>
+        <v>174</v>
       </c>
     </row>
     <row r="441" ht="20" customHeight="1">
@@ -12053,7 +12053,7 @@
         </is>
       </c>
       <c r="E441" s="23" t="n">
-        <v>169</v>
+        <v>201</v>
       </c>
     </row>
     <row r="442" ht="20" customHeight="1">
@@ -12078,7 +12078,7 @@
         </is>
       </c>
       <c r="E442" s="20" t="n">
-        <v>203</v>
+        <v>182</v>
       </c>
     </row>
     <row r="443" ht="20" customHeight="1">
@@ -12103,7 +12103,7 @@
         </is>
       </c>
       <c r="E443" s="23" t="n">
-        <v>188</v>
+        <v>147</v>
       </c>
     </row>
     <row r="444" ht="20" customHeight="1">
@@ -12128,7 +12128,7 @@
         </is>
       </c>
       <c r="E444" s="20" t="n">
-        <v>113</v>
+        <v>134</v>
       </c>
     </row>
     <row r="445" ht="20" customHeight="1">
@@ -12153,7 +12153,7 @@
         </is>
       </c>
       <c r="E445" s="23" t="n">
-        <v>123</v>
+        <v>167</v>
       </c>
     </row>
     <row r="446" ht="20" customHeight="1">
@@ -12178,7 +12178,7 @@
         </is>
       </c>
       <c r="E446" s="20" t="n">
-        <v>176</v>
+        <v>192</v>
       </c>
     </row>
     <row r="447" ht="20" customHeight="1">
@@ -12203,7 +12203,7 @@
         </is>
       </c>
       <c r="E447" s="23" t="n">
-        <v>129</v>
+        <v>121</v>
       </c>
     </row>
     <row r="448" ht="20" customHeight="1">
@@ -12228,7 +12228,7 @@
         </is>
       </c>
       <c r="E448" s="20" t="n">
-        <v>212</v>
+        <v>235</v>
       </c>
     </row>
     <row r="449" ht="20" customHeight="1">
@@ -12253,7 +12253,7 @@
         </is>
       </c>
       <c r="E449" s="23" t="n">
-        <v>235</v>
+        <v>133</v>
       </c>
     </row>
     <row r="450" ht="20" customHeight="1">
@@ -12278,7 +12278,7 @@
         </is>
       </c>
       <c r="E450" s="20" t="n">
-        <v>196</v>
+        <v>165</v>
       </c>
     </row>
     <row r="451" ht="20" customHeight="1">
@@ -12303,7 +12303,7 @@
         </is>
       </c>
       <c r="E451" s="23" t="n">
-        <v>239</v>
+        <v>126</v>
       </c>
     </row>
     <row r="452" ht="20" customHeight="1">
@@ -12328,7 +12328,7 @@
         </is>
       </c>
       <c r="E452" s="20" t="n">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="453" ht="20" customHeight="1">
@@ -12353,7 +12353,7 @@
         </is>
       </c>
       <c r="E453" s="23" t="n">
-        <v>171</v>
+        <v>181</v>
       </c>
     </row>
     <row r="454" ht="20" customHeight="1">
@@ -12378,7 +12378,7 @@
         </is>
       </c>
       <c r="E454" s="20" t="n">
-        <v>179</v>
+        <v>112</v>
       </c>
     </row>
     <row r="455" ht="20" customHeight="1">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="E455" s="23" t="n">
-        <v>160</v>
+        <v>141</v>
       </c>
     </row>
     <row r="456" ht="20" customHeight="1">
@@ -12428,7 +12428,7 @@
         </is>
       </c>
       <c r="E456" s="20" t="n">
-        <v>164</v>
+        <v>215</v>
       </c>
     </row>
     <row r="457" ht="20" customHeight="1">
@@ -12453,7 +12453,7 @@
         </is>
       </c>
       <c r="E457" s="23" t="n">
-        <v>191</v>
+        <v>232</v>
       </c>
     </row>
     <row r="458" ht="20" customHeight="1">
@@ -12478,7 +12478,7 @@
         </is>
       </c>
       <c r="E458" s="20" t="n">
-        <v>172</v>
+        <v>187</v>
       </c>
     </row>
     <row r="459" ht="20" customHeight="1">
@@ -12503,7 +12503,7 @@
         </is>
       </c>
       <c r="E459" s="23" t="n">
-        <v>235</v>
+        <v>128</v>
       </c>
     </row>
     <row r="460" ht="20" customHeight="1">
@@ -12528,7 +12528,7 @@
         </is>
       </c>
       <c r="E460" s="20" t="n">
-        <v>127</v>
+        <v>113</v>
       </c>
     </row>
     <row r="461" ht="20" customHeight="1">
@@ -12553,7 +12553,7 @@
         </is>
       </c>
       <c r="E461" s="23" t="n">
-        <v>220</v>
+        <v>152</v>
       </c>
     </row>
     <row r="462" ht="20" customHeight="1">
@@ -12578,7 +12578,7 @@
         </is>
       </c>
       <c r="E462" s="20" t="n">
-        <v>233</v>
+        <v>142</v>
       </c>
     </row>
     <row r="463" ht="20" customHeight="1">
@@ -12603,7 +12603,7 @@
         </is>
       </c>
       <c r="E463" s="23" t="n">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="464" ht="20" customHeight="1">
@@ -12628,7 +12628,7 @@
         </is>
       </c>
       <c r="E464" s="20" t="n">
-        <v>169</v>
+        <v>154</v>
       </c>
     </row>
     <row r="465" ht="20" customHeight="1">
@@ -12653,7 +12653,7 @@
         </is>
       </c>
       <c r="E465" s="23" t="n">
-        <v>230</v>
+        <v>160</v>
       </c>
     </row>
     <row r="466" ht="20" customHeight="1">
@@ -12678,7 +12678,7 @@
         </is>
       </c>
       <c r="E466" s="20" t="n">
-        <v>219</v>
+        <v>156</v>
       </c>
     </row>
     <row r="467" ht="20" customHeight="1">
@@ -12703,7 +12703,7 @@
         </is>
       </c>
       <c r="E467" s="23" t="n">
-        <v>195</v>
+        <v>217</v>
       </c>
     </row>
     <row r="468" ht="20" customHeight="1">
@@ -12728,7 +12728,7 @@
         </is>
       </c>
       <c r="E468" s="20" t="n">
-        <v>119</v>
+        <v>141</v>
       </c>
     </row>
     <row r="469" ht="20" customHeight="1">
@@ -12753,7 +12753,7 @@
         </is>
       </c>
       <c r="E469" s="23" t="n">
-        <v>191</v>
+        <v>147</v>
       </c>
     </row>
     <row r="470" ht="20" customHeight="1">
@@ -12778,7 +12778,7 @@
         </is>
       </c>
       <c r="E470" s="20" t="n">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="471" ht="20" customHeight="1">
@@ -12803,7 +12803,7 @@
         </is>
       </c>
       <c r="E471" s="23" t="n">
-        <v>202</v>
+        <v>194</v>
       </c>
     </row>
     <row r="472" ht="20" customHeight="1">
@@ -12828,7 +12828,7 @@
         </is>
       </c>
       <c r="E472" s="20" t="n">
-        <v>169</v>
+        <v>119</v>
       </c>
     </row>
     <row r="473" ht="20" customHeight="1">
@@ -12853,7 +12853,7 @@
         </is>
       </c>
       <c r="E473" s="23" t="n">
-        <v>147</v>
+        <v>240</v>
       </c>
     </row>
     <row r="474" ht="20" customHeight="1">
@@ -12878,7 +12878,7 @@
         </is>
       </c>
       <c r="E474" s="20" t="n">
-        <v>204</v>
+        <v>159</v>
       </c>
     </row>
     <row r="475" ht="20" customHeight="1">
@@ -12903,7 +12903,7 @@
         </is>
       </c>
       <c r="E475" s="23" t="n">
-        <v>116</v>
+        <v>189</v>
       </c>
     </row>
     <row r="476" ht="20" customHeight="1">
@@ -12928,7 +12928,7 @@
         </is>
       </c>
       <c r="E476" s="20" t="n">
-        <v>120</v>
+        <v>164</v>
       </c>
     </row>
     <row r="477" ht="20" customHeight="1">
@@ -12953,7 +12953,7 @@
         </is>
       </c>
       <c r="E477" s="23" t="n">
-        <v>235</v>
+        <v>227</v>
       </c>
     </row>
     <row r="478" ht="20" customHeight="1">
@@ -12978,7 +12978,7 @@
         </is>
       </c>
       <c r="E478" s="20" t="n">
-        <v>183</v>
+        <v>139</v>
       </c>
     </row>
     <row r="479" ht="20" customHeight="1">
@@ -13003,7 +13003,7 @@
         </is>
       </c>
       <c r="E479" s="23" t="n">
-        <v>209</v>
+        <v>129</v>
       </c>
     </row>
     <row r="480" ht="20" customHeight="1">
@@ -13028,7 +13028,7 @@
         </is>
       </c>
       <c r="E480" s="20" t="n">
-        <v>110</v>
+        <v>237</v>
       </c>
     </row>
     <row r="481" ht="20" customHeight="1">
@@ -13053,7 +13053,7 @@
         </is>
       </c>
       <c r="E481" s="23" t="n">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="482" ht="20" customHeight="1">
@@ -13078,7 +13078,7 @@
         </is>
       </c>
       <c r="E482" s="20" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="483" ht="20" customHeight="1">
@@ -13103,7 +13103,7 @@
         </is>
       </c>
       <c r="E483" s="23" t="n">
-        <v>166</v>
+        <v>189</v>
       </c>
     </row>
     <row r="484" ht="20" customHeight="1">
@@ -13128,7 +13128,7 @@
         </is>
       </c>
       <c r="E484" s="20" t="n">
-        <v>217</v>
+        <v>134</v>
       </c>
     </row>
     <row r="485" ht="20" customHeight="1">
@@ -13153,7 +13153,7 @@
         </is>
       </c>
       <c r="E485" s="23" t="n">
-        <v>118</v>
+        <v>195</v>
       </c>
     </row>
     <row r="486" ht="20" customHeight="1">
@@ -13178,7 +13178,7 @@
         </is>
       </c>
       <c r="E486" s="20" t="n">
-        <v>146</v>
+        <v>159</v>
       </c>
     </row>
     <row r="487" ht="20" customHeight="1">
@@ -13203,7 +13203,7 @@
         </is>
       </c>
       <c r="E487" s="23" t="n">
-        <v>155</v>
+        <v>214</v>
       </c>
     </row>
     <row r="488" ht="20" customHeight="1">
@@ -13228,7 +13228,7 @@
         </is>
       </c>
       <c r="E488" s="20" t="n">
-        <v>207</v>
+        <v>225</v>
       </c>
     </row>
     <row r="489" ht="20" customHeight="1">
@@ -13253,7 +13253,7 @@
         </is>
       </c>
       <c r="E489" s="23" t="n">
-        <v>112</v>
+        <v>219</v>
       </c>
     </row>
     <row r="490" ht="20" customHeight="1">
@@ -13278,7 +13278,7 @@
         </is>
       </c>
       <c r="E490" s="20" t="n">
-        <v>228</v>
+        <v>120</v>
       </c>
     </row>
     <row r="491" ht="20" customHeight="1">
@@ -13303,7 +13303,7 @@
         </is>
       </c>
       <c r="E491" s="23" t="n">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="492" ht="20" customHeight="1">
@@ -13328,7 +13328,7 @@
         </is>
       </c>
       <c r="E492" s="20" t="n">
-        <v>126</v>
+        <v>146</v>
       </c>
     </row>
     <row r="493" ht="20" customHeight="1">
@@ -13353,7 +13353,7 @@
         </is>
       </c>
       <c r="E493" s="23" t="n">
-        <v>201</v>
+        <v>223</v>
       </c>
     </row>
     <row r="494" ht="20" customHeight="1">
@@ -13378,7 +13378,7 @@
         </is>
       </c>
       <c r="E494" s="20" t="n">
-        <v>219</v>
+        <v>183</v>
       </c>
     </row>
     <row r="495" ht="20" customHeight="1">
@@ -13403,7 +13403,7 @@
         </is>
       </c>
       <c r="E495" s="23" t="n">
-        <v>237</v>
+        <v>146</v>
       </c>
     </row>
     <row r="496" ht="20" customHeight="1">
@@ -13428,7 +13428,7 @@
         </is>
       </c>
       <c r="E496" s="20" t="n">
-        <v>205</v>
+        <v>194</v>
       </c>
     </row>
     <row r="497" ht="20" customHeight="1">
@@ -13453,7 +13453,7 @@
         </is>
       </c>
       <c r="E497" s="23" t="n">
-        <v>236</v>
+        <v>162</v>
       </c>
     </row>
     <row r="498" ht="20" customHeight="1">
@@ -13478,7 +13478,7 @@
         </is>
       </c>
       <c r="E498" s="20" t="n">
-        <v>227</v>
+        <v>155</v>
       </c>
     </row>
     <row r="499" ht="20" customHeight="1">
@@ -13503,7 +13503,7 @@
         </is>
       </c>
       <c r="E499" s="23" t="n">
-        <v>165</v>
+        <v>235</v>
       </c>
     </row>
     <row r="500" ht="20" customHeight="1">
@@ -13528,7 +13528,7 @@
         </is>
       </c>
       <c r="E500" s="20" t="n">
-        <v>162</v>
+        <v>186</v>
       </c>
     </row>
     <row r="501" ht="20" customHeight="1">
@@ -13553,7 +13553,7 @@
         </is>
       </c>
       <c r="E501" s="23" t="n">
-        <v>221</v>
+        <v>232</v>
       </c>
     </row>
     <row r="502" ht="20" customHeight="1">
@@ -13578,7 +13578,7 @@
         </is>
       </c>
       <c r="E502" s="20" t="n">
-        <v>224</v>
+        <v>181</v>
       </c>
     </row>
     <row r="503" ht="20" customHeight="1">
@@ -13603,7 +13603,7 @@
         </is>
       </c>
       <c r="E503" s="23" t="n">
-        <v>143</v>
+        <v>208</v>
       </c>
     </row>
     <row r="504" ht="20" customHeight="1">
@@ -13628,7 +13628,7 @@
         </is>
       </c>
       <c r="E504" s="20" t="n">
-        <v>226</v>
+        <v>203</v>
       </c>
     </row>
     <row r="505" ht="20" customHeight="1">
@@ -13653,7 +13653,7 @@
         </is>
       </c>
       <c r="E505" s="23" t="n">
-        <v>155</v>
+        <v>139</v>
       </c>
     </row>
     <row r="506" ht="20" customHeight="1">
@@ -13678,7 +13678,7 @@
         </is>
       </c>
       <c r="E506" s="20" t="n">
-        <v>130</v>
+        <v>190</v>
       </c>
     </row>
     <row r="507" ht="20" customHeight="1">
@@ -13703,7 +13703,7 @@
         </is>
       </c>
       <c r="E507" s="23" t="n">
-        <v>238</v>
+        <v>154</v>
       </c>
     </row>
     <row r="508" ht="20" customHeight="1">
@@ -13728,7 +13728,7 @@
         </is>
       </c>
       <c r="E508" s="20" t="n">
-        <v>224</v>
+        <v>152</v>
       </c>
     </row>
     <row r="509" ht="20" customHeight="1">
@@ -13753,7 +13753,7 @@
         </is>
       </c>
       <c r="E509" s="23" t="n">
-        <v>148</v>
+        <v>168</v>
       </c>
     </row>
     <row r="510" ht="20" customHeight="1">
@@ -13778,7 +13778,7 @@
         </is>
       </c>
       <c r="E510" s="20" t="n">
-        <v>149</v>
+        <v>239</v>
       </c>
     </row>
     <row r="511" ht="20" customHeight="1">
@@ -13803,7 +13803,7 @@
         </is>
       </c>
       <c r="E511" s="23" t="n">
-        <v>182</v>
+        <v>168</v>
       </c>
     </row>
     <row r="512" ht="20" customHeight="1">
@@ -13828,7 +13828,7 @@
         </is>
       </c>
       <c r="E512" s="20" t="n">
-        <v>209</v>
+        <v>110</v>
       </c>
     </row>
     <row r="513" ht="20" customHeight="1">
@@ -13853,7 +13853,7 @@
         </is>
       </c>
       <c r="E513" s="23" t="n">
-        <v>227</v>
+        <v>120</v>
       </c>
     </row>
     <row r="514" ht="20" customHeight="1">
@@ -13878,7 +13878,7 @@
         </is>
       </c>
       <c r="E514" s="20" t="n">
-        <v>153</v>
+        <v>175</v>
       </c>
     </row>
     <row r="515" ht="20" customHeight="1">
@@ -13903,7 +13903,7 @@
         </is>
       </c>
       <c r="E515" s="23" t="n">
-        <v>180</v>
+        <v>224</v>
       </c>
     </row>
     <row r="516" ht="20" customHeight="1">
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="E516" s="20" t="n">
-        <v>112</v>
+        <v>236</v>
       </c>
     </row>
     <row r="517" ht="20" customHeight="1">
@@ -13953,7 +13953,7 @@
         </is>
       </c>
       <c r="E517" s="23" t="n">
-        <v>169</v>
+        <v>125</v>
       </c>
     </row>
     <row r="518" ht="20" customHeight="1">
@@ -13978,7 +13978,7 @@
         </is>
       </c>
       <c r="E518" s="20" t="n">
-        <v>146</v>
+        <v>194</v>
       </c>
     </row>
     <row r="519" ht="20" customHeight="1">
@@ -14003,7 +14003,7 @@
         </is>
       </c>
       <c r="E519" s="23" t="n">
-        <v>123</v>
+        <v>175</v>
       </c>
     </row>
     <row r="520" ht="20" customHeight="1">
@@ -14028,7 +14028,7 @@
         </is>
       </c>
       <c r="E520" s="20" t="n">
-        <v>174</v>
+        <v>236</v>
       </c>
     </row>
     <row r="521" ht="20" customHeight="1">
@@ -14053,7 +14053,7 @@
         </is>
       </c>
       <c r="E521" s="23" t="n">
-        <v>139</v>
+        <v>158</v>
       </c>
     </row>
     <row r="522" ht="20" customHeight="1">
@@ -14078,7 +14078,7 @@
         </is>
       </c>
       <c r="E522" s="20" t="n">
-        <v>139</v>
+        <v>229</v>
       </c>
     </row>
     <row r="523" ht="20" customHeight="1">
@@ -14103,7 +14103,7 @@
         </is>
       </c>
       <c r="E523" s="23" t="n">
-        <v>209</v>
+        <v>155</v>
       </c>
     </row>
     <row r="524" ht="20" customHeight="1">
@@ -14128,7 +14128,7 @@
         </is>
       </c>
       <c r="E524" s="20" t="n">
-        <v>175</v>
+        <v>212</v>
       </c>
     </row>
     <row r="525" ht="20" customHeight="1">
@@ -14153,7 +14153,7 @@
         </is>
       </c>
       <c r="E525" s="23" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
     </row>
     <row r="526" ht="20" customHeight="1">
@@ -14178,7 +14178,7 @@
         </is>
       </c>
       <c r="E526" s="20" t="n">
-        <v>163</v>
+        <v>158</v>
       </c>
     </row>
     <row r="527" ht="20" customHeight="1">
@@ -14203,7 +14203,7 @@
         </is>
       </c>
       <c r="E527" s="23" t="n">
-        <v>119</v>
+        <v>183</v>
       </c>
     </row>
     <row r="528" ht="20" customHeight="1">
@@ -14228,7 +14228,7 @@
         </is>
       </c>
       <c r="E528" s="20" t="n">
-        <v>239</v>
+        <v>134</v>
       </c>
     </row>
     <row r="529" ht="20" customHeight="1">
@@ -14253,7 +14253,7 @@
         </is>
       </c>
       <c r="E529" s="23" t="n">
-        <v>123</v>
+        <v>151</v>
       </c>
     </row>
     <row r="530" ht="20" customHeight="1">
@@ -14278,7 +14278,7 @@
         </is>
       </c>
       <c r="E530" s="20" t="n">
-        <v>194</v>
+        <v>234</v>
       </c>
     </row>
     <row r="531" ht="20" customHeight="1">
@@ -14303,7 +14303,7 @@
         </is>
       </c>
       <c r="E531" s="23" t="n">
-        <v>201</v>
+        <v>220</v>
       </c>
     </row>
     <row r="532" ht="20" customHeight="1">
@@ -14328,7 +14328,7 @@
         </is>
       </c>
       <c r="E532" s="20" t="n">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="533" ht="20" customHeight="1">
@@ -14353,7 +14353,7 @@
         </is>
       </c>
       <c r="E533" s="23" t="n">
-        <v>165</v>
+        <v>119</v>
       </c>
     </row>
     <row r="534" ht="20" customHeight="1">
@@ -14378,7 +14378,7 @@
         </is>
       </c>
       <c r="E534" s="20" t="n">
-        <v>155</v>
+        <v>123</v>
       </c>
     </row>
     <row r="535" ht="20" customHeight="1">
@@ -14403,7 +14403,7 @@
         </is>
       </c>
       <c r="E535" s="23" t="n">
-        <v>169</v>
+        <v>121</v>
       </c>
     </row>
     <row r="536" ht="20" customHeight="1">
@@ -14428,7 +14428,7 @@
         </is>
       </c>
       <c r="E536" s="20" t="n">
-        <v>146</v>
+        <v>213</v>
       </c>
     </row>
     <row r="537" ht="20" customHeight="1">
@@ -14453,7 +14453,7 @@
         </is>
       </c>
       <c r="E537" s="23" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="538" ht="20" customHeight="1">
@@ -14478,7 +14478,7 @@
         </is>
       </c>
       <c r="E538" s="20" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
     </row>
     <row r="539" ht="20" customHeight="1">
@@ -14503,7 +14503,7 @@
         </is>
       </c>
       <c r="E539" s="23" t="n">
-        <v>196</v>
+        <v>228</v>
       </c>
     </row>
     <row r="540" ht="20" customHeight="1">
@@ -14528,7 +14528,7 @@
         </is>
       </c>
       <c r="E540" s="20" t="n">
-        <v>171</v>
+        <v>230</v>
       </c>
     </row>
     <row r="541" ht="20" customHeight="1">
@@ -14553,7 +14553,7 @@
         </is>
       </c>
       <c r="E541" s="23" t="n">
-        <v>192</v>
+        <v>146</v>
       </c>
     </row>
     <row r="542" ht="20" customHeight="1">
@@ -14578,7 +14578,7 @@
         </is>
       </c>
       <c r="E542" s="20" t="n">
-        <v>136</v>
+        <v>205</v>
       </c>
     </row>
     <row r="543" ht="20" customHeight="1">
@@ -14603,7 +14603,7 @@
         </is>
       </c>
       <c r="E543" s="23" t="n">
-        <v>166</v>
+        <v>148</v>
       </c>
     </row>
     <row r="544" ht="20" customHeight="1">
@@ -14628,7 +14628,7 @@
         </is>
       </c>
       <c r="E544" s="20" t="n">
-        <v>194</v>
+        <v>200</v>
       </c>
     </row>
     <row r="545" ht="20" customHeight="1">
@@ -14653,7 +14653,7 @@
         </is>
       </c>
       <c r="E545" s="23" t="n">
-        <v>125</v>
+        <v>198</v>
       </c>
     </row>
     <row r="546" ht="20" customHeight="1">
@@ -14678,7 +14678,7 @@
         </is>
       </c>
       <c r="E546" s="20" t="n">
-        <v>221</v>
+        <v>172</v>
       </c>
     </row>
     <row r="547" ht="20" customHeight="1">
@@ -14703,7 +14703,7 @@
         </is>
       </c>
       <c r="E547" s="23" t="n">
-        <v>155</v>
+        <v>148</v>
       </c>
     </row>
     <row r="548" ht="20" customHeight="1">
@@ -14728,7 +14728,7 @@
         </is>
       </c>
       <c r="E548" s="20" t="n">
-        <v>141</v>
+        <v>221</v>
       </c>
     </row>
     <row r="549" ht="20" customHeight="1">
@@ -14753,7 +14753,7 @@
         </is>
       </c>
       <c r="E549" s="23" t="n">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="550" ht="20" customHeight="1">
@@ -14778,7 +14778,7 @@
         </is>
       </c>
       <c r="E550" s="20" t="n">
-        <v>181</v>
+        <v>163</v>
       </c>
     </row>
     <row r="551" ht="20" customHeight="1">
@@ -14803,7 +14803,7 @@
         </is>
       </c>
       <c r="E551" s="23" t="n">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="552" ht="20" customHeight="1">
@@ -14828,7 +14828,7 @@
         </is>
       </c>
       <c r="E552" s="20" t="n">
-        <v>196</v>
+        <v>176</v>
       </c>
     </row>
     <row r="553" ht="20" customHeight="1">
@@ -14853,7 +14853,7 @@
         </is>
       </c>
       <c r="E553" s="23" t="n">
-        <v>225</v>
+        <v>180</v>
       </c>
     </row>
     <row r="554" ht="20" customHeight="1">
@@ -14878,7 +14878,7 @@
         </is>
       </c>
       <c r="E554" s="20" t="n">
-        <v>238</v>
+        <v>145</v>
       </c>
     </row>
     <row r="555" ht="20" customHeight="1">
@@ -14903,7 +14903,7 @@
         </is>
       </c>
       <c r="E555" s="23" t="n">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="556" ht="20" customHeight="1">
@@ -14928,7 +14928,7 @@
         </is>
       </c>
       <c r="E556" s="20" t="n">
-        <v>233</v>
+        <v>140</v>
       </c>
     </row>
     <row r="557" ht="20" customHeight="1">
@@ -14953,7 +14953,7 @@
         </is>
       </c>
       <c r="E557" s="23" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="558" ht="20" customHeight="1">
@@ -14978,7 +14978,7 @@
         </is>
       </c>
       <c r="E558" s="20" t="n">
-        <v>184</v>
+        <v>130</v>
       </c>
     </row>
     <row r="559" ht="20" customHeight="1">
@@ -15003,7 +15003,7 @@
         </is>
       </c>
       <c r="E559" s="23" t="n">
-        <v>189</v>
+        <v>167</v>
       </c>
     </row>
     <row r="560" ht="20" customHeight="1">
@@ -15028,7 +15028,7 @@
         </is>
       </c>
       <c r="E560" s="20" t="n">
-        <v>225</v>
+        <v>217</v>
       </c>
     </row>
     <row r="561" ht="20" customHeight="1">
@@ -15053,7 +15053,7 @@
         </is>
       </c>
       <c r="E561" s="23" t="n">
-        <v>127</v>
+        <v>160</v>
       </c>
     </row>
     <row r="562" ht="20" customHeight="1">
@@ -15078,7 +15078,7 @@
         </is>
       </c>
       <c r="E562" s="20" t="n">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="563" ht="20" customHeight="1">
@@ -15103,7 +15103,7 @@
         </is>
       </c>
       <c r="E563" s="23" t="n">
-        <v>184</v>
+        <v>134</v>
       </c>
     </row>
     <row r="564" ht="20" customHeight="1">
@@ -15128,7 +15128,7 @@
         </is>
       </c>
       <c r="E564" s="20" t="n">
-        <v>237</v>
+        <v>218</v>
       </c>
     </row>
     <row r="565" ht="20" customHeight="1">
@@ -15153,7 +15153,7 @@
         </is>
       </c>
       <c r="E565" s="23" t="n">
-        <v>210</v>
+        <v>198</v>
       </c>
     </row>
     <row r="566" ht="20" customHeight="1">
@@ -15178,7 +15178,7 @@
         </is>
       </c>
       <c r="E566" s="20" t="n">
-        <v>126</v>
+        <v>195</v>
       </c>
     </row>
     <row r="567" ht="20" customHeight="1">
@@ -15203,7 +15203,7 @@
         </is>
       </c>
       <c r="E567" s="23" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="568" ht="20" customHeight="1">
@@ -15228,7 +15228,7 @@
         </is>
       </c>
       <c r="E568" s="20" t="n">
-        <v>212</v>
+        <v>144</v>
       </c>
     </row>
     <row r="569" ht="20" customHeight="1">
@@ -15253,7 +15253,7 @@
         </is>
       </c>
       <c r="E569" s="23" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
     </row>
     <row r="570" ht="20" customHeight="1">
@@ -15278,7 +15278,7 @@
         </is>
       </c>
       <c r="E570" s="20" t="n">
-        <v>119</v>
+        <v>179</v>
       </c>
     </row>
     <row r="571" ht="20" customHeight="1">
@@ -15303,7 +15303,7 @@
         </is>
       </c>
       <c r="E571" s="23" t="n">
-        <v>235</v>
+        <v>239</v>
       </c>
     </row>
     <row r="572" ht="20" customHeight="1">
@@ -15328,7 +15328,7 @@
         </is>
       </c>
       <c r="E572" s="20" t="n">
-        <v>128</v>
+        <v>177</v>
       </c>
     </row>
     <row r="573" ht="20" customHeight="1">
@@ -15353,7 +15353,7 @@
         </is>
       </c>
       <c r="E573" s="23" t="n">
-        <v>232</v>
+        <v>183</v>
       </c>
     </row>
     <row r="574" ht="20" customHeight="1">
@@ -15378,7 +15378,7 @@
         </is>
       </c>
       <c r="E574" s="20" t="n">
-        <v>156</v>
+        <v>139</v>
       </c>
     </row>
     <row r="575" ht="20" customHeight="1">
@@ -15403,7 +15403,7 @@
         </is>
       </c>
       <c r="E575" s="23" t="n">
-        <v>215</v>
+        <v>168</v>
       </c>
     </row>
     <row r="576" ht="20" customHeight="1">
@@ -15428,7 +15428,7 @@
         </is>
       </c>
       <c r="E576" s="20" t="n">
-        <v>176</v>
+        <v>120</v>
       </c>
     </row>
     <row r="577" ht="20" customHeight="1">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="E577" s="23" t="n">
-        <v>173</v>
+        <v>233</v>
       </c>
     </row>
     <row r="578" ht="20" customHeight="1">
@@ -15478,7 +15478,7 @@
         </is>
       </c>
       <c r="E578" s="20" t="n">
-        <v>225</v>
+        <v>125</v>
       </c>
     </row>
     <row r="579" ht="20" customHeight="1">
@@ -15503,7 +15503,7 @@
         </is>
       </c>
       <c r="E579" s="23" t="n">
-        <v>180</v>
+        <v>138</v>
       </c>
     </row>
     <row r="580" ht="20" customHeight="1">
@@ -15528,7 +15528,7 @@
         </is>
       </c>
       <c r="E580" s="20" t="n">
-        <v>210</v>
+        <v>217</v>
       </c>
     </row>
     <row r="581" ht="20" customHeight="1">
@@ -15553,7 +15553,7 @@
         </is>
       </c>
       <c r="E581" s="23" t="n">
-        <v>192</v>
+        <v>179</v>
       </c>
     </row>
     <row r="582" ht="20" customHeight="1">
@@ -15578,7 +15578,7 @@
         </is>
       </c>
       <c r="E582" s="20" t="n">
-        <v>167</v>
+        <v>201</v>
       </c>
     </row>
     <row r="583" ht="20" customHeight="1">
@@ -15603,7 +15603,7 @@
         </is>
       </c>
       <c r="E583" s="23" t="n">
-        <v>139</v>
+        <v>157</v>
       </c>
     </row>
     <row r="584" ht="20" customHeight="1">
@@ -15628,7 +15628,7 @@
         </is>
       </c>
       <c r="E584" s="20" t="n">
-        <v>171</v>
+        <v>135</v>
       </c>
     </row>
     <row r="585" ht="20" customHeight="1">
@@ -15653,7 +15653,7 @@
         </is>
       </c>
       <c r="E585" s="23" t="n">
-        <v>181</v>
+        <v>230</v>
       </c>
     </row>
     <row r="586" ht="20" customHeight="1">
@@ -15678,7 +15678,7 @@
         </is>
       </c>
       <c r="E586" s="20" t="n">
-        <v>127</v>
+        <v>120</v>
       </c>
     </row>
     <row r="587" ht="20" customHeight="1">
@@ -15703,7 +15703,7 @@
         </is>
       </c>
       <c r="E587" s="23" t="n">
-        <v>112</v>
+        <v>178</v>
       </c>
     </row>
     <row r="588" ht="20" customHeight="1">
@@ -15728,7 +15728,7 @@
         </is>
       </c>
       <c r="E588" s="20" t="n">
-        <v>202</v>
+        <v>185</v>
       </c>
     </row>
     <row r="589" ht="20" customHeight="1">
@@ -15753,7 +15753,7 @@
         </is>
       </c>
       <c r="E589" s="23" t="n">
-        <v>161</v>
+        <v>149</v>
       </c>
     </row>
     <row r="590" ht="20" customHeight="1">
@@ -15778,7 +15778,7 @@
         </is>
       </c>
       <c r="E590" s="20" t="n">
-        <v>138</v>
+        <v>179</v>
       </c>
     </row>
     <row r="591" ht="20" customHeight="1">
@@ -15803,7 +15803,7 @@
         </is>
       </c>
       <c r="E591" s="23" t="n">
-        <v>179</v>
+        <v>219</v>
       </c>
     </row>
     <row r="592" ht="20" customHeight="1">
@@ -15828,7 +15828,7 @@
         </is>
       </c>
       <c r="E592" s="20" t="n">
-        <v>110</v>
+        <v>203</v>
       </c>
     </row>
     <row r="593" ht="20" customHeight="1">
@@ -15853,7 +15853,7 @@
         </is>
       </c>
       <c r="E593" s="23" t="n">
-        <v>214</v>
+        <v>111</v>
       </c>
     </row>
     <row r="594" ht="20" customHeight="1">
@@ -15878,7 +15878,7 @@
         </is>
       </c>
       <c r="E594" s="20" t="n">
-        <v>126</v>
+        <v>152</v>
       </c>
     </row>
     <row r="595" ht="20" customHeight="1">
@@ -15903,7 +15903,7 @@
         </is>
       </c>
       <c r="E595" s="23" t="n">
-        <v>147</v>
+        <v>156</v>
       </c>
     </row>
     <row r="596" ht="20" customHeight="1">
@@ -15928,7 +15928,7 @@
         </is>
       </c>
       <c r="E596" s="20" t="n">
-        <v>142</v>
+        <v>195</v>
       </c>
     </row>
     <row r="597" ht="20" customHeight="1">
@@ -15953,7 +15953,7 @@
         </is>
       </c>
       <c r="E597" s="23" t="n">
-        <v>189</v>
+        <v>151</v>
       </c>
     </row>
     <row r="598" ht="20" customHeight="1">
@@ -15978,7 +15978,7 @@
         </is>
       </c>
       <c r="E598" s="20" t="n">
-        <v>165</v>
+        <v>206</v>
       </c>
     </row>
     <row r="599" ht="20" customHeight="1">
@@ -16003,7 +16003,7 @@
         </is>
       </c>
       <c r="E599" s="23" t="n">
-        <v>119</v>
+        <v>186</v>
       </c>
     </row>
     <row r="600" ht="20" customHeight="1">
@@ -16028,7 +16028,7 @@
         </is>
       </c>
       <c r="E600" s="20" t="n">
-        <v>184</v>
+        <v>177</v>
       </c>
     </row>
     <row r="601" ht="20" customHeight="1">
@@ -16053,7 +16053,7 @@
         </is>
       </c>
       <c r="E601" s="23" t="n">
-        <v>144</v>
+        <v>119</v>
       </c>
     </row>
     <row r="602" ht="20" customHeight="1">
@@ -16078,7 +16078,7 @@
         </is>
       </c>
       <c r="E602" s="20" t="n">
-        <v>151</v>
+        <v>115</v>
       </c>
     </row>
     <row r="603" ht="20" customHeight="1">
@@ -16103,7 +16103,7 @@
         </is>
       </c>
       <c r="E603" s="23" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
     </row>
     <row r="604" ht="20" customHeight="1">
@@ -16128,7 +16128,7 @@
         </is>
       </c>
       <c r="E604" s="20" t="n">
-        <v>135</v>
+        <v>225</v>
       </c>
     </row>
     <row r="605" ht="20" customHeight="1">
@@ -16153,7 +16153,7 @@
         </is>
       </c>
       <c r="E605" s="23" t="n">
-        <v>168</v>
+        <v>116</v>
       </c>
     </row>
     <row r="606" ht="20" customHeight="1">
@@ -16178,7 +16178,7 @@
         </is>
       </c>
       <c r="E606" s="20" t="n">
-        <v>126</v>
+        <v>168</v>
       </c>
     </row>
     <row r="607" ht="20" customHeight="1">
@@ -16203,7 +16203,7 @@
         </is>
       </c>
       <c r="E607" s="23" t="n">
-        <v>174</v>
+        <v>130</v>
       </c>
     </row>
     <row r="608" ht="20" customHeight="1">
@@ -16228,7 +16228,7 @@
         </is>
       </c>
       <c r="E608" s="20" t="n">
-        <v>227</v>
+        <v>183</v>
       </c>
     </row>
     <row r="609" ht="20" customHeight="1">
@@ -16253,7 +16253,7 @@
         </is>
       </c>
       <c r="E609" s="23" t="n">
-        <v>167</v>
+        <v>156</v>
       </c>
     </row>
     <row r="610" ht="20" customHeight="1">
@@ -16278,7 +16278,7 @@
         </is>
       </c>
       <c r="E610" s="20" t="n">
-        <v>116</v>
+        <v>201</v>
       </c>
     </row>
     <row r="611" ht="20" customHeight="1">
@@ -16303,7 +16303,7 @@
         </is>
       </c>
       <c r="E611" s="23" t="n">
-        <v>235</v>
+        <v>163</v>
       </c>
     </row>
     <row r="612" ht="20" customHeight="1">
@@ -16328,7 +16328,7 @@
         </is>
       </c>
       <c r="E612" s="20" t="n">
-        <v>177</v>
+        <v>163</v>
       </c>
     </row>
     <row r="613" ht="20" customHeight="1">
@@ -16353,7 +16353,7 @@
         </is>
       </c>
       <c r="E613" s="23" t="n">
-        <v>212</v>
+        <v>149</v>
       </c>
     </row>
     <row r="614" ht="20" customHeight="1">
@@ -16378,7 +16378,7 @@
         </is>
       </c>
       <c r="E614" s="20" t="n">
-        <v>200</v>
+        <v>177</v>
       </c>
     </row>
     <row r="615" ht="20" customHeight="1">
@@ -16403,7 +16403,7 @@
         </is>
       </c>
       <c r="E615" s="23" t="n">
-        <v>201</v>
+        <v>183</v>
       </c>
     </row>
     <row r="616" ht="20" customHeight="1">
@@ -16428,7 +16428,7 @@
         </is>
       </c>
       <c r="E616" s="20" t="n">
-        <v>225</v>
+        <v>131</v>
       </c>
     </row>
     <row r="617" ht="20" customHeight="1">
@@ -16453,7 +16453,7 @@
         </is>
       </c>
       <c r="E617" s="23" t="n">
-        <v>169</v>
+        <v>207</v>
       </c>
     </row>
     <row r="618" ht="20" customHeight="1">
@@ -16478,7 +16478,7 @@
         </is>
       </c>
       <c r="E618" s="20" t="n">
-        <v>224</v>
+        <v>206</v>
       </c>
     </row>
     <row r="619" ht="20" customHeight="1">
@@ -16503,7 +16503,7 @@
         </is>
       </c>
       <c r="E619" s="23" t="n">
-        <v>120</v>
+        <v>208</v>
       </c>
     </row>
     <row r="620" ht="20" customHeight="1">
@@ -16528,7 +16528,7 @@
         </is>
       </c>
       <c r="E620" s="20" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="621" ht="20" customHeight="1">
@@ -16553,7 +16553,7 @@
         </is>
       </c>
       <c r="E621" s="23" t="n">
-        <v>122</v>
+        <v>215</v>
       </c>
     </row>
     <row r="622" ht="20" customHeight="1">
@@ -16578,7 +16578,7 @@
         </is>
       </c>
       <c r="E622" s="20" t="n">
-        <v>207</v>
+        <v>117</v>
       </c>
     </row>
     <row r="623" ht="20" customHeight="1">
@@ -16603,7 +16603,7 @@
         </is>
       </c>
       <c r="E623" s="23" t="n">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="624" ht="20" customHeight="1">
@@ -16628,7 +16628,7 @@
         </is>
       </c>
       <c r="E624" s="20" t="n">
-        <v>238</v>
+        <v>225</v>
       </c>
     </row>
     <row r="625" ht="20" customHeight="1">
@@ -16653,7 +16653,7 @@
         </is>
       </c>
       <c r="E625" s="23" t="n">
-        <v>130</v>
+        <v>233</v>
       </c>
     </row>
     <row r="626" ht="20" customHeight="1">
@@ -16678,7 +16678,7 @@
         </is>
       </c>
       <c r="E626" s="20" t="n">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="627" ht="20" customHeight="1">
@@ -16703,7 +16703,7 @@
         </is>
       </c>
       <c r="E627" s="23" t="n">
-        <v>227</v>
+        <v>110</v>
       </c>
     </row>
     <row r="628" ht="20" customHeight="1">
@@ -16728,7 +16728,7 @@
         </is>
       </c>
       <c r="E628" s="20" t="n">
-        <v>156</v>
+        <v>178</v>
       </c>
     </row>
     <row r="629" ht="20" customHeight="1">
@@ -16753,7 +16753,7 @@
         </is>
       </c>
       <c r="E629" s="23" t="n">
-        <v>181</v>
+        <v>122</v>
       </c>
     </row>
     <row r="630" ht="20" customHeight="1">
@@ -16778,7 +16778,7 @@
         </is>
       </c>
       <c r="E630" s="20" t="n">
-        <v>217</v>
+        <v>164</v>
       </c>
     </row>
     <row r="631" ht="20" customHeight="1">
@@ -16803,7 +16803,7 @@
         </is>
       </c>
       <c r="E631" s="23" t="n">
-        <v>175</v>
+        <v>121</v>
       </c>
     </row>
     <row r="632" ht="20" customHeight="1">
@@ -16828,7 +16828,7 @@
         </is>
       </c>
       <c r="E632" s="20" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
     </row>
     <row r="633" ht="20" customHeight="1">
@@ -16853,7 +16853,7 @@
         </is>
       </c>
       <c r="E633" s="23" t="n">
-        <v>163</v>
+        <v>184</v>
       </c>
     </row>
     <row r="634" ht="20" customHeight="1">
@@ -16878,7 +16878,7 @@
         </is>
       </c>
       <c r="E634" s="20" t="n">
-        <v>184</v>
+        <v>194</v>
       </c>
     </row>
     <row r="635" ht="20" customHeight="1">
@@ -16903,7 +16903,7 @@
         </is>
       </c>
       <c r="E635" s="23" t="n">
-        <v>128</v>
+        <v>222</v>
       </c>
     </row>
     <row r="636" ht="20" customHeight="1">
@@ -16928,7 +16928,7 @@
         </is>
       </c>
       <c r="E636" s="20" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="637" ht="20" customHeight="1">
@@ -16953,7 +16953,7 @@
         </is>
       </c>
       <c r="E637" s="23" t="n">
-        <v>237</v>
+        <v>225</v>
       </c>
     </row>
     <row r="638" ht="20" customHeight="1">
@@ -16978,7 +16978,7 @@
         </is>
       </c>
       <c r="E638" s="20" t="n">
-        <v>144</v>
+        <v>117</v>
       </c>
     </row>
     <row r="639" ht="20" customHeight="1">
@@ -17003,7 +17003,7 @@
         </is>
       </c>
       <c r="E639" s="23" t="n">
-        <v>188</v>
+        <v>231</v>
       </c>
     </row>
     <row r="640" ht="20" customHeight="1">
@@ -17028,7 +17028,7 @@
         </is>
       </c>
       <c r="E640" s="20" t="n">
-        <v>235</v>
+        <v>196</v>
       </c>
     </row>
     <row r="641" ht="20" customHeight="1">
@@ -17053,7 +17053,7 @@
         </is>
       </c>
       <c r="E641" s="23" t="n">
-        <v>138</v>
+        <v>168</v>
       </c>
     </row>
     <row r="642" ht="20" customHeight="1">
@@ -17078,7 +17078,7 @@
         </is>
       </c>
       <c r="E642" s="20" t="n">
-        <v>146</v>
+        <v>223</v>
       </c>
     </row>
     <row r="643" ht="20" customHeight="1">
@@ -17103,7 +17103,7 @@
         </is>
       </c>
       <c r="E643" s="23" t="n">
-        <v>209</v>
+        <v>158</v>
       </c>
     </row>
     <row r="644" ht="20" customHeight="1">
@@ -17128,7 +17128,7 @@
         </is>
       </c>
       <c r="E644" s="20" t="n">
-        <v>136</v>
+        <v>197</v>
       </c>
     </row>
     <row r="645" ht="20" customHeight="1">
@@ -17153,7 +17153,7 @@
         </is>
       </c>
       <c r="E645" s="23" t="n">
-        <v>204</v>
+        <v>197</v>
       </c>
     </row>
     <row r="646" ht="20" customHeight="1">
@@ -17178,7 +17178,7 @@
         </is>
       </c>
       <c r="E646" s="20" t="n">
-        <v>149</v>
+        <v>198</v>
       </c>
     </row>
     <row r="647" ht="20" customHeight="1">
@@ -17203,7 +17203,7 @@
         </is>
       </c>
       <c r="E647" s="23" t="n">
-        <v>163</v>
+        <v>199</v>
       </c>
     </row>
     <row r="648" ht="20" customHeight="1">
@@ -17228,7 +17228,7 @@
         </is>
       </c>
       <c r="E648" s="20" t="n">
-        <v>227</v>
+        <v>141</v>
       </c>
     </row>
     <row r="649" ht="20" customHeight="1">
@@ -17253,7 +17253,7 @@
         </is>
       </c>
       <c r="E649" s="23" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="650" ht="20" customHeight="1">
@@ -17278,7 +17278,7 @@
         </is>
       </c>
       <c r="E650" s="20" t="n">
-        <v>129</v>
+        <v>117</v>
       </c>
     </row>
     <row r="651" ht="20" customHeight="1">
@@ -17303,7 +17303,7 @@
         </is>
       </c>
       <c r="E651" s="23" t="n">
-        <v>132</v>
+        <v>155</v>
       </c>
     </row>
     <row r="652" ht="20" customHeight="1">
@@ -17328,7 +17328,7 @@
         </is>
       </c>
       <c r="E652" s="20" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
     </row>
     <row r="653" ht="20" customHeight="1">
@@ -17353,7 +17353,7 @@
         </is>
       </c>
       <c r="E653" s="23" t="n">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="654" ht="20" customHeight="1">
@@ -17378,7 +17378,7 @@
         </is>
       </c>
       <c r="E654" s="20" t="n">
-        <v>219</v>
+        <v>208</v>
       </c>
     </row>
     <row r="655" ht="20" customHeight="1">
@@ -17403,7 +17403,7 @@
         </is>
       </c>
       <c r="E655" s="23" t="n">
-        <v>214</v>
+        <v>184</v>
       </c>
     </row>
     <row r="656" ht="20" customHeight="1">
@@ -17428,7 +17428,7 @@
         </is>
       </c>
       <c r="E656" s="20" t="n">
-        <v>178</v>
+        <v>141</v>
       </c>
     </row>
     <row r="657" ht="20" customHeight="1">
@@ -17453,7 +17453,7 @@
         </is>
       </c>
       <c r="E657" s="23" t="n">
-        <v>222</v>
+        <v>127</v>
       </c>
     </row>
     <row r="658" ht="20" customHeight="1">
@@ -17478,7 +17478,7 @@
         </is>
       </c>
       <c r="E658" s="20" t="n">
-        <v>151</v>
+        <v>200</v>
       </c>
     </row>
     <row r="659" ht="20" customHeight="1">
@@ -17503,7 +17503,7 @@
         </is>
       </c>
       <c r="E659" s="23" t="n">
-        <v>154</v>
+        <v>206</v>
       </c>
     </row>
     <row r="660" ht="20" customHeight="1">
@@ -17528,7 +17528,7 @@
         </is>
       </c>
       <c r="E660" s="20" t="n">
-        <v>174</v>
+        <v>188</v>
       </c>
     </row>
     <row r="661" ht="20" customHeight="1">
@@ -17553,7 +17553,7 @@
         </is>
       </c>
       <c r="E661" s="23" t="n">
-        <v>128</v>
+        <v>202</v>
       </c>
     </row>
     <row r="662" ht="20" customHeight="1">
@@ -17578,7 +17578,7 @@
         </is>
       </c>
       <c r="E662" s="20" t="n">
-        <v>169</v>
+        <v>197</v>
       </c>
     </row>
     <row r="663" ht="20" customHeight="1">
@@ -17603,7 +17603,7 @@
         </is>
       </c>
       <c r="E663" s="23" t="n">
-        <v>133</v>
+        <v>233</v>
       </c>
     </row>
     <row r="664" ht="20" customHeight="1">
@@ -17628,7 +17628,7 @@
         </is>
       </c>
       <c r="E664" s="20" t="n">
-        <v>234</v>
+        <v>189</v>
       </c>
     </row>
     <row r="665" ht="20" customHeight="1">
@@ -17653,7 +17653,7 @@
         </is>
       </c>
       <c r="E665" s="23" t="n">
-        <v>211</v>
+        <v>176</v>
       </c>
     </row>
     <row r="666" ht="20" customHeight="1">
@@ -17678,7 +17678,7 @@
         </is>
       </c>
       <c r="E666" s="20" t="n">
-        <v>214</v>
+        <v>224</v>
       </c>
     </row>
     <row r="667" ht="20" customHeight="1">
@@ -17703,7 +17703,7 @@
         </is>
       </c>
       <c r="E667" s="23" t="n">
-        <v>187</v>
+        <v>135</v>
       </c>
     </row>
     <row r="668" ht="20" customHeight="1">
@@ -17728,7 +17728,7 @@
         </is>
       </c>
       <c r="E668" s="20" t="n">
-        <v>143</v>
+        <v>233</v>
       </c>
     </row>
     <row r="669" ht="20" customHeight="1">
@@ -17753,7 +17753,7 @@
         </is>
       </c>
       <c r="E669" s="23" t="n">
-        <v>232</v>
+        <v>118</v>
       </c>
     </row>
     <row r="670" ht="20" customHeight="1">
@@ -17778,7 +17778,7 @@
         </is>
       </c>
       <c r="E670" s="20" t="n">
-        <v>173</v>
+        <v>154</v>
       </c>
     </row>
     <row r="671" ht="20" customHeight="1">
@@ -17803,7 +17803,7 @@
         </is>
       </c>
       <c r="E671" s="23" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="672" ht="20" customHeight="1">
@@ -17828,7 +17828,7 @@
         </is>
       </c>
       <c r="E672" s="20" t="n">
-        <v>175</v>
+        <v>203</v>
       </c>
     </row>
     <row r="673" ht="20" customHeight="1">
@@ -17853,7 +17853,7 @@
         </is>
       </c>
       <c r="E673" s="23" t="n">
-        <v>201</v>
+        <v>145</v>
       </c>
     </row>
     <row r="674" ht="20" customHeight="1">
@@ -17878,7 +17878,7 @@
         </is>
       </c>
       <c r="E674" s="20" t="n">
-        <v>226</v>
+        <v>188</v>
       </c>
     </row>
     <row r="675" ht="20" customHeight="1">
@@ -17903,7 +17903,7 @@
         </is>
       </c>
       <c r="E675" s="23" t="n">
-        <v>182</v>
+        <v>175</v>
       </c>
     </row>
     <row r="676" ht="20" customHeight="1">
@@ -17928,7 +17928,7 @@
         </is>
       </c>
       <c r="E676" s="20" t="n">
-        <v>202</v>
+        <v>136</v>
       </c>
     </row>
     <row r="677" ht="20" customHeight="1">
@@ -17953,7 +17953,7 @@
         </is>
       </c>
       <c r="E677" s="23" t="n">
-        <v>210</v>
+        <v>127</v>
       </c>
     </row>
     <row r="678" ht="20" customHeight="1">
@@ -17978,7 +17978,7 @@
         </is>
       </c>
       <c r="E678" s="20" t="n">
-        <v>228</v>
+        <v>221</v>
       </c>
     </row>
     <row r="679" ht="20" customHeight="1">
@@ -18003,7 +18003,7 @@
         </is>
       </c>
       <c r="E679" s="23" t="n">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="680" ht="20" customHeight="1">
@@ -18028,7 +18028,7 @@
         </is>
       </c>
       <c r="E680" s="20" t="n">
-        <v>123</v>
+        <v>211</v>
       </c>
     </row>
     <row r="681" ht="20" customHeight="1">
@@ -18053,7 +18053,7 @@
         </is>
       </c>
       <c r="E681" s="23" t="n">
-        <v>143</v>
+        <v>216</v>
       </c>
     </row>
     <row r="682" ht="20" customHeight="1">
@@ -18078,7 +18078,7 @@
         </is>
       </c>
       <c r="E682" s="20" t="n">
-        <v>193</v>
+        <v>220</v>
       </c>
     </row>
     <row r="683" ht="20" customHeight="1">
@@ -18103,7 +18103,7 @@
         </is>
       </c>
       <c r="E683" s="23" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
     </row>
     <row r="684" ht="20" customHeight="1">
@@ -18128,7 +18128,7 @@
         </is>
       </c>
       <c r="E684" s="20" t="n">
-        <v>112</v>
+        <v>141</v>
       </c>
     </row>
     <row r="685" ht="20" customHeight="1">
@@ -18153,7 +18153,7 @@
         </is>
       </c>
       <c r="E685" s="23" t="n">
-        <v>163</v>
+        <v>139</v>
       </c>
     </row>
     <row r="686" ht="20" customHeight="1">
@@ -18178,7 +18178,7 @@
         </is>
       </c>
       <c r="E686" s="20" t="n">
-        <v>181</v>
+        <v>167</v>
       </c>
     </row>
     <row r="687" ht="20" customHeight="1">
@@ -18203,7 +18203,7 @@
         </is>
       </c>
       <c r="E687" s="23" t="n">
-        <v>195</v>
+        <v>234</v>
       </c>
     </row>
     <row r="688" ht="20" customHeight="1">
@@ -18228,7 +18228,7 @@
         </is>
       </c>
       <c r="E688" s="20" t="n">
-        <v>127</v>
+        <v>238</v>
       </c>
     </row>
     <row r="689" ht="20" customHeight="1">
@@ -18253,7 +18253,7 @@
         </is>
       </c>
       <c r="E689" s="23" t="n">
-        <v>173</v>
+        <v>130</v>
       </c>
     </row>
     <row r="690" ht="20" customHeight="1">
@@ -18278,7 +18278,7 @@
         </is>
       </c>
       <c r="E690" s="20" t="n">
-        <v>216</v>
+        <v>142</v>
       </c>
     </row>
     <row r="691" ht="20" customHeight="1">
@@ -18303,7 +18303,7 @@
         </is>
       </c>
       <c r="E691" s="23" t="n">
-        <v>133</v>
+        <v>145</v>
       </c>
     </row>
     <row r="692" ht="20" customHeight="1">
@@ -18328,7 +18328,7 @@
         </is>
       </c>
       <c r="E692" s="20" t="n">
-        <v>229</v>
+        <v>209</v>
       </c>
     </row>
     <row r="693" ht="20" customHeight="1">
@@ -18353,7 +18353,7 @@
         </is>
       </c>
       <c r="E693" s="23" t="n">
-        <v>194</v>
+        <v>142</v>
       </c>
     </row>
     <row r="694" ht="20" customHeight="1">
@@ -18378,7 +18378,7 @@
         </is>
       </c>
       <c r="E694" s="20" t="n">
-        <v>211</v>
+        <v>144</v>
       </c>
     </row>
     <row r="695" ht="20" customHeight="1">
@@ -18403,7 +18403,7 @@
         </is>
       </c>
       <c r="E695" s="23" t="n">
-        <v>240</v>
+        <v>181</v>
       </c>
     </row>
     <row r="696" ht="20" customHeight="1">
@@ -18428,7 +18428,7 @@
         </is>
       </c>
       <c r="E696" s="20" t="n">
-        <v>122</v>
+        <v>209</v>
       </c>
     </row>
     <row r="697" ht="20" customHeight="1">
@@ -18453,7 +18453,7 @@
         </is>
       </c>
       <c r="E697" s="23" t="n">
-        <v>188</v>
+        <v>121</v>
       </c>
     </row>
     <row r="698" ht="20" customHeight="1">
@@ -18478,7 +18478,7 @@
         </is>
       </c>
       <c r="E698" s="20" t="n">
-        <v>235</v>
+        <v>209</v>
       </c>
     </row>
     <row r="699" ht="20" customHeight="1">
@@ -18503,7 +18503,7 @@
         </is>
       </c>
       <c r="E699" s="23" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="700" ht="20" customHeight="1">
@@ -18528,7 +18528,7 @@
         </is>
       </c>
       <c r="E700" s="20" t="n">
-        <v>192</v>
+        <v>183</v>
       </c>
     </row>
     <row r="701" ht="20" customHeight="1">
@@ -18553,7 +18553,7 @@
         </is>
       </c>
       <c r="E701" s="23" t="n">
-        <v>213</v>
+        <v>119</v>
       </c>
     </row>
     <row r="702" ht="20" customHeight="1">
@@ -18578,7 +18578,7 @@
         </is>
       </c>
       <c r="E702" s="20" t="n">
-        <v>141</v>
+        <v>193</v>
       </c>
     </row>
     <row r="703" ht="20" customHeight="1">
@@ -18603,7 +18603,7 @@
         </is>
       </c>
       <c r="E703" s="23" t="n">
-        <v>144</v>
+        <v>149</v>
       </c>
     </row>
     <row r="704" ht="20" customHeight="1">
@@ -18628,7 +18628,7 @@
         </is>
       </c>
       <c r="E704" s="20" t="n">
-        <v>230</v>
+        <v>192</v>
       </c>
     </row>
     <row r="705" ht="20" customHeight="1">
@@ -18653,7 +18653,7 @@
         </is>
       </c>
       <c r="E705" s="23" t="n">
-        <v>207</v>
+        <v>240</v>
       </c>
     </row>
     <row r="706" ht="20" customHeight="1">
@@ -18678,7 +18678,7 @@
         </is>
       </c>
       <c r="E706" s="20" t="n">
-        <v>160</v>
+        <v>217</v>
       </c>
     </row>
     <row r="707" ht="20" customHeight="1">
@@ -18703,7 +18703,7 @@
         </is>
       </c>
       <c r="E707" s="23" t="n">
-        <v>223</v>
+        <v>192</v>
       </c>
     </row>
     <row r="708" ht="20" customHeight="1">
@@ -18728,7 +18728,7 @@
         </is>
       </c>
       <c r="E708" s="20" t="n">
-        <v>152</v>
+        <v>142</v>
       </c>
     </row>
     <row r="709" ht="20" customHeight="1">
@@ -18753,7 +18753,7 @@
         </is>
       </c>
       <c r="E709" s="23" t="n">
-        <v>208</v>
+        <v>117</v>
       </c>
     </row>
     <row r="710" ht="20" customHeight="1">
@@ -18778,7 +18778,7 @@
         </is>
       </c>
       <c r="E710" s="20" t="n">
-        <v>181</v>
+        <v>233</v>
       </c>
     </row>
     <row r="711" ht="20" customHeight="1">
@@ -18803,7 +18803,7 @@
         </is>
       </c>
       <c r="E711" s="23" t="n">
-        <v>190</v>
+        <v>202</v>
       </c>
     </row>
     <row r="712" ht="20" customHeight="1">
@@ -18828,7 +18828,7 @@
         </is>
       </c>
       <c r="E712" s="20" t="n">
-        <v>162</v>
+        <v>132</v>
       </c>
     </row>
     <row r="713" ht="20" customHeight="1">
@@ -18853,7 +18853,7 @@
         </is>
       </c>
       <c r="E713" s="23" t="n">
-        <v>235</v>
+        <v>214</v>
       </c>
     </row>
     <row r="714" ht="20" customHeight="1">
@@ -18878,7 +18878,7 @@
         </is>
       </c>
       <c r="E714" s="20" t="n">
-        <v>130</v>
+        <v>236</v>
       </c>
     </row>
     <row r="715" ht="20" customHeight="1">
@@ -18903,7 +18903,7 @@
         </is>
       </c>
       <c r="E715" s="23" t="n">
-        <v>233</v>
+        <v>186</v>
       </c>
     </row>
     <row r="716" ht="20" customHeight="1">
@@ -18928,7 +18928,7 @@
         </is>
       </c>
       <c r="E716" s="20" t="n">
-        <v>112</v>
+        <v>223</v>
       </c>
     </row>
     <row r="717" ht="20" customHeight="1">
@@ -18953,7 +18953,7 @@
         </is>
       </c>
       <c r="E717" s="23" t="n">
-        <v>237</v>
+        <v>214</v>
       </c>
     </row>
     <row r="718" ht="20" customHeight="1">
@@ -18978,7 +18978,7 @@
         </is>
       </c>
       <c r="E718" s="20" t="n">
-        <v>216</v>
+        <v>227</v>
       </c>
     </row>
     <row r="719" ht="20" customHeight="1">
@@ -19003,7 +19003,7 @@
         </is>
       </c>
       <c r="E719" s="23" t="n">
-        <v>202</v>
+        <v>159</v>
       </c>
     </row>
     <row r="720" ht="20" customHeight="1">
@@ -19028,7 +19028,7 @@
         </is>
       </c>
       <c r="E720" s="20" t="n">
-        <v>194</v>
+        <v>114</v>
       </c>
     </row>
     <row r="721" ht="20" customHeight="1">
@@ -19053,7 +19053,7 @@
         </is>
       </c>
       <c r="E721" s="23" t="n">
-        <v>210</v>
+        <v>152</v>
       </c>
     </row>
     <row r="722" ht="20" customHeight="1">
@@ -19078,7 +19078,7 @@
         </is>
       </c>
       <c r="E722" s="20" t="n">
-        <v>178</v>
+        <v>171</v>
       </c>
     </row>
     <row r="723" ht="20" customHeight="1">
@@ -19103,7 +19103,7 @@
         </is>
       </c>
       <c r="E723" s="23" t="n">
-        <v>151</v>
+        <v>125</v>
       </c>
     </row>
     <row r="724" ht="20" customHeight="1">
@@ -19128,7 +19128,7 @@
         </is>
       </c>
       <c r="E724" s="20" t="n">
-        <v>117</v>
+        <v>165</v>
       </c>
     </row>
     <row r="725" ht="20" customHeight="1">
@@ -19153,7 +19153,7 @@
         </is>
       </c>
       <c r="E725" s="23" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
     </row>
     <row r="726" ht="20" customHeight="1">
@@ -19178,7 +19178,7 @@
         </is>
       </c>
       <c r="E726" s="20" t="n">
-        <v>181</v>
+        <v>222</v>
       </c>
     </row>
     <row r="727" ht="20" customHeight="1">
@@ -19203,7 +19203,7 @@
         </is>
       </c>
       <c r="E727" s="23" t="n">
-        <v>155</v>
+        <v>193</v>
       </c>
     </row>
     <row r="728" ht="20" customHeight="1">
@@ -19228,7 +19228,7 @@
         </is>
       </c>
       <c r="E728" s="20" t="n">
-        <v>200</v>
+        <v>193</v>
       </c>
     </row>
     <row r="729" ht="20" customHeight="1">
@@ -19253,7 +19253,7 @@
         </is>
       </c>
       <c r="E729" s="23" t="n">
-        <v>157</v>
+        <v>218</v>
       </c>
     </row>
     <row r="730" ht="20" customHeight="1">
@@ -19278,7 +19278,7 @@
         </is>
       </c>
       <c r="E730" s="20" t="n">
-        <v>232</v>
+        <v>111</v>
       </c>
     </row>
     <row r="731" ht="20" customHeight="1">
@@ -19303,7 +19303,7 @@
         </is>
       </c>
       <c r="E731" s="23" t="n">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="732" ht="20" customHeight="1">
@@ -19328,7 +19328,7 @@
         </is>
       </c>
       <c r="E732" s="20" t="n">
-        <v>120</v>
+        <v>146</v>
       </c>
     </row>
     <row r="733" ht="20" customHeight="1">
@@ -19353,7 +19353,7 @@
         </is>
       </c>
       <c r="E733" s="23" t="n">
-        <v>158</v>
+        <v>204</v>
       </c>
     </row>
     <row r="734" ht="20" customHeight="1">
@@ -19378,7 +19378,7 @@
         </is>
       </c>
       <c r="E734" s="20" t="n">
-        <v>151</v>
+        <v>228</v>
       </c>
     </row>
     <row r="735" ht="20" customHeight="1">
@@ -19403,7 +19403,7 @@
         </is>
       </c>
       <c r="E735" s="23" t="n">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="736" ht="20" customHeight="1">
@@ -19428,7 +19428,7 @@
         </is>
       </c>
       <c r="E736" s="20" t="n">
-        <v>197</v>
+        <v>151</v>
       </c>
     </row>
     <row r="737" ht="20" customHeight="1">
@@ -19453,7 +19453,7 @@
         </is>
       </c>
       <c r="E737" s="23" t="n">
-        <v>121</v>
+        <v>111</v>
       </c>
     </row>
     <row r="738" ht="20" customHeight="1">
@@ -19478,7 +19478,7 @@
         </is>
       </c>
       <c r="E738" s="20" t="n">
-        <v>148</v>
+        <v>178</v>
       </c>
     </row>
     <row r="739" ht="20" customHeight="1">
@@ -19503,7 +19503,7 @@
         </is>
       </c>
       <c r="E739" s="23" t="n">
-        <v>231</v>
+        <v>143</v>
       </c>
     </row>
     <row r="740" ht="20" customHeight="1">
@@ -19528,7 +19528,7 @@
         </is>
       </c>
       <c r="E740" s="20" t="n">
-        <v>192</v>
+        <v>231</v>
       </c>
     </row>
     <row r="741" ht="20" customHeight="1">
@@ -19553,7 +19553,7 @@
         </is>
       </c>
       <c r="E741" s="23" t="n">
-        <v>132</v>
+        <v>184</v>
       </c>
     </row>
     <row r="742" ht="20" customHeight="1">
@@ -19578,7 +19578,7 @@
         </is>
       </c>
       <c r="E742" s="20" t="n">
-        <v>216</v>
+        <v>197</v>
       </c>
     </row>
     <row r="743" ht="20" customHeight="1">
@@ -19603,7 +19603,7 @@
         </is>
       </c>
       <c r="E743" s="23" t="n">
-        <v>179</v>
+        <v>236</v>
       </c>
     </row>
     <row r="744" ht="20" customHeight="1">
@@ -19628,7 +19628,7 @@
         </is>
       </c>
       <c r="E744" s="20" t="n">
-        <v>200</v>
+        <v>166</v>
       </c>
     </row>
     <row r="745" ht="20" customHeight="1">
@@ -19653,7 +19653,7 @@
         </is>
       </c>
       <c r="E745" s="23" t="n">
-        <v>176</v>
+        <v>165</v>
       </c>
     </row>
     <row r="746" ht="20" customHeight="1">
@@ -19678,7 +19678,7 @@
         </is>
       </c>
       <c r="E746" s="20" t="n">
-        <v>127</v>
+        <v>216</v>
       </c>
     </row>
     <row r="747" ht="20" customHeight="1">
@@ -19703,7 +19703,7 @@
         </is>
       </c>
       <c r="E747" s="23" t="n">
-        <v>192</v>
+        <v>225</v>
       </c>
     </row>
     <row r="748" ht="20" customHeight="1">
@@ -19728,7 +19728,7 @@
         </is>
       </c>
       <c r="E748" s="20" t="n">
-        <v>126</v>
+        <v>212</v>
       </c>
     </row>
     <row r="749" ht="20" customHeight="1">
@@ -19753,7 +19753,7 @@
         </is>
       </c>
       <c r="E749" s="23" t="n">
-        <v>139</v>
+        <v>196</v>
       </c>
     </row>
     <row r="750" ht="20" customHeight="1">
@@ -19778,7 +19778,7 @@
         </is>
       </c>
       <c r="E750" s="20" t="n">
-        <v>143</v>
+        <v>152</v>
       </c>
     </row>
     <row r="751" ht="20" customHeight="1">
@@ -19803,7 +19803,7 @@
         </is>
       </c>
       <c r="E751" s="23" t="n">
-        <v>126</v>
+        <v>190</v>
       </c>
     </row>
     <row r="752" ht="20" customHeight="1">
@@ -19828,7 +19828,7 @@
         </is>
       </c>
       <c r="E752" s="20" t="n">
-        <v>195</v>
+        <v>141</v>
       </c>
     </row>
     <row r="753" ht="20" customHeight="1">
@@ -19853,7 +19853,7 @@
         </is>
       </c>
       <c r="E753" s="23" t="n">
-        <v>219</v>
+        <v>160</v>
       </c>
     </row>
     <row r="754" ht="20" customHeight="1">
@@ -19878,7 +19878,7 @@
         </is>
       </c>
       <c r="E754" s="20" t="n">
-        <v>137</v>
+        <v>180</v>
       </c>
     </row>
     <row r="755" ht="20" customHeight="1">
@@ -19903,7 +19903,7 @@
         </is>
       </c>
       <c r="E755" s="23" t="n">
-        <v>212</v>
+        <v>145</v>
       </c>
     </row>
     <row r="756" ht="20" customHeight="1">
@@ -19928,7 +19928,7 @@
         </is>
       </c>
       <c r="E756" s="20" t="n">
-        <v>119</v>
+        <v>147</v>
       </c>
     </row>
     <row r="757" ht="20" customHeight="1">
@@ -19953,7 +19953,7 @@
         </is>
       </c>
       <c r="E757" s="23" t="n">
-        <v>128</v>
+        <v>217</v>
       </c>
     </row>
     <row r="758" ht="20" customHeight="1">
@@ -19978,7 +19978,7 @@
         </is>
       </c>
       <c r="E758" s="20" t="n">
-        <v>157</v>
+        <v>190</v>
       </c>
     </row>
     <row r="759" ht="20" customHeight="1">
@@ -20003,7 +20003,7 @@
         </is>
       </c>
       <c r="E759" s="23" t="n">
-        <v>190</v>
+        <v>211</v>
       </c>
     </row>
     <row r="760" ht="20" customHeight="1">
@@ -20028,7 +20028,7 @@
         </is>
       </c>
       <c r="E760" s="20" t="n">
-        <v>181</v>
+        <v>152</v>
       </c>
     </row>
     <row r="761" ht="20" customHeight="1">
@@ -20053,7 +20053,7 @@
         </is>
       </c>
       <c r="E761" s="23" t="n">
-        <v>196</v>
+        <v>200</v>
       </c>
     </row>
     <row r="762" ht="20" customHeight="1">
@@ -20078,7 +20078,7 @@
         </is>
       </c>
       <c r="E762" s="20" t="n">
-        <v>198</v>
+        <v>154</v>
       </c>
     </row>
     <row r="763" ht="20" customHeight="1">
@@ -20103,7 +20103,7 @@
         </is>
       </c>
       <c r="E763" s="23" t="n">
-        <v>173</v>
+        <v>127</v>
       </c>
     </row>
     <row r="764" ht="20" customHeight="1">
@@ -20128,7 +20128,7 @@
         </is>
       </c>
       <c r="E764" s="20" t="n">
-        <v>135</v>
+        <v>218</v>
       </c>
     </row>
     <row r="765" ht="20" customHeight="1">
@@ -20153,7 +20153,7 @@
         </is>
       </c>
       <c r="E765" s="23" t="n">
-        <v>155</v>
+        <v>201</v>
       </c>
     </row>
     <row r="766" ht="20" customHeight="1">
@@ -20178,7 +20178,7 @@
         </is>
       </c>
       <c r="E766" s="20" t="n">
-        <v>191</v>
+        <v>147</v>
       </c>
     </row>
     <row r="767" ht="20" customHeight="1">
@@ -20203,7 +20203,7 @@
         </is>
       </c>
       <c r="E767" s="23" t="n">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="768" ht="20" customHeight="1">
@@ -20228,7 +20228,7 @@
         </is>
       </c>
       <c r="E768" s="20" t="n">
-        <v>144</v>
+        <v>231</v>
       </c>
     </row>
     <row r="769" ht="20" customHeight="1">
@@ -20253,7 +20253,7 @@
         </is>
       </c>
       <c r="E769" s="23" t="n">
-        <v>204</v>
+        <v>148</v>
       </c>
     </row>
     <row r="770" ht="20" customHeight="1">
@@ -20278,7 +20278,7 @@
         </is>
       </c>
       <c r="E770" s="20" t="n">
-        <v>165</v>
+        <v>196</v>
       </c>
     </row>
     <row r="771" ht="20" customHeight="1">
@@ -20303,7 +20303,7 @@
         </is>
       </c>
       <c r="E771" s="23" t="n">
-        <v>127</v>
+        <v>143</v>
       </c>
     </row>
     <row r="772" ht="20" customHeight="1">
@@ -20328,7 +20328,7 @@
         </is>
       </c>
       <c r="E772" s="20" t="n">
-        <v>199</v>
+        <v>173</v>
       </c>
     </row>
     <row r="773" ht="20" customHeight="1">
@@ -20353,7 +20353,7 @@
         </is>
       </c>
       <c r="E773" s="23" t="n">
-        <v>237</v>
+        <v>139</v>
       </c>
     </row>
     <row r="774" ht="20" customHeight="1">
@@ -20378,7 +20378,7 @@
         </is>
       </c>
       <c r="E774" s="20" t="n">
-        <v>219</v>
+        <v>208</v>
       </c>
     </row>
     <row r="775" ht="20" customHeight="1">
@@ -20403,7 +20403,7 @@
         </is>
       </c>
       <c r="E775" s="23" t="n">
-        <v>153</v>
+        <v>178</v>
       </c>
     </row>
     <row r="776" ht="20" customHeight="1">
@@ -20428,7 +20428,7 @@
         </is>
       </c>
       <c r="E776" s="20" t="n">
-        <v>164</v>
+        <v>179</v>
       </c>
     </row>
     <row r="777" ht="20" customHeight="1">
@@ -20453,7 +20453,7 @@
         </is>
       </c>
       <c r="E777" s="23" t="n">
-        <v>166</v>
+        <v>224</v>
       </c>
     </row>
     <row r="778" ht="20" customHeight="1">
@@ -20478,7 +20478,7 @@
         </is>
       </c>
       <c r="E778" s="20" t="n">
-        <v>114</v>
+        <v>234</v>
       </c>
     </row>
     <row r="779" ht="20" customHeight="1">
@@ -20503,7 +20503,7 @@
         </is>
       </c>
       <c r="E779" s="23" t="n">
-        <v>183</v>
+        <v>229</v>
       </c>
     </row>
     <row r="780" ht="20" customHeight="1">
@@ -20528,7 +20528,7 @@
         </is>
       </c>
       <c r="E780" s="20" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="781" ht="20" customHeight="1">
@@ -20553,7 +20553,7 @@
         </is>
       </c>
       <c r="E781" s="23" t="n">
-        <v>118</v>
+        <v>226</v>
       </c>
     </row>
     <row r="782" ht="20" customHeight="1">
@@ -20578,7 +20578,7 @@
         </is>
       </c>
       <c r="E782" s="20" t="n">
-        <v>238</v>
+        <v>211</v>
       </c>
     </row>
     <row r="783" ht="20" customHeight="1">
@@ -20603,7 +20603,7 @@
         </is>
       </c>
       <c r="E783" s="23" t="n">
-        <v>182</v>
+        <v>141</v>
       </c>
     </row>
     <row r="784" ht="20" customHeight="1">
@@ -20628,7 +20628,7 @@
         </is>
       </c>
       <c r="E784" s="20" t="n">
-        <v>213</v>
+        <v>165</v>
       </c>
     </row>
     <row r="785" ht="20" customHeight="1">
@@ -20653,7 +20653,7 @@
         </is>
       </c>
       <c r="E785" s="23" t="n">
-        <v>168</v>
+        <v>118</v>
       </c>
     </row>
     <row r="786" ht="20" customHeight="1">
@@ -20678,7 +20678,7 @@
         </is>
       </c>
       <c r="E786" s="20" t="n">
-        <v>142</v>
+        <v>149</v>
       </c>
     </row>
     <row r="787" ht="20" customHeight="1">
@@ -20703,7 +20703,7 @@
         </is>
       </c>
       <c r="E787" s="23" t="n">
-        <v>120</v>
+        <v>193</v>
       </c>
     </row>
     <row r="788" ht="20" customHeight="1">
@@ -20728,7 +20728,7 @@
         </is>
       </c>
       <c r="E788" s="20" t="n">
-        <v>210</v>
+        <v>188</v>
       </c>
     </row>
     <row r="789" ht="20" customHeight="1">
@@ -20753,7 +20753,7 @@
         </is>
       </c>
       <c r="E789" s="23" t="n">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="790" ht="20" customHeight="1">
@@ -20803,7 +20803,7 @@
         </is>
       </c>
       <c r="E791" s="23" t="n">
-        <v>188</v>
+        <v>204</v>
       </c>
     </row>
     <row r="792" ht="20" customHeight="1">
@@ -20828,7 +20828,7 @@
         </is>
       </c>
       <c r="E792" s="20" t="n">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
     <row r="793" ht="20" customHeight="1">
@@ -20853,7 +20853,7 @@
         </is>
       </c>
       <c r="E793" s="23" t="n">
-        <v>113</v>
+        <v>194</v>
       </c>
     </row>
     <row r="794" ht="20" customHeight="1">
@@ -20878,7 +20878,7 @@
         </is>
       </c>
       <c r="E794" s="20" t="n">
-        <v>117</v>
+        <v>193</v>
       </c>
     </row>
     <row r="795" ht="20" customHeight="1">
@@ -20903,7 +20903,7 @@
         </is>
       </c>
       <c r="E795" s="23" t="n">
-        <v>153</v>
+        <v>175</v>
       </c>
     </row>
     <row r="796" ht="20" customHeight="1">
@@ -20928,7 +20928,7 @@
         </is>
       </c>
       <c r="E796" s="20" t="n">
-        <v>221</v>
+        <v>110</v>
       </c>
     </row>
     <row r="797" ht="20" customHeight="1">
@@ -20953,7 +20953,7 @@
         </is>
       </c>
       <c r="E797" s="23" t="n">
-        <v>110</v>
+        <v>171</v>
       </c>
     </row>
     <row r="798" ht="20" customHeight="1">
@@ -21003,7 +21003,7 @@
         </is>
       </c>
       <c r="E799" s="23" t="n">
-        <v>172</v>
+        <v>154</v>
       </c>
     </row>
     <row r="800" ht="20" customHeight="1">
@@ -21028,7 +21028,7 @@
         </is>
       </c>
       <c r="E800" s="20" t="n">
-        <v>181</v>
+        <v>215</v>
       </c>
     </row>
     <row r="801" ht="20" customHeight="1">
@@ -21053,7 +21053,7 @@
         </is>
       </c>
       <c r="E801" s="23" t="n">
-        <v>120</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>

--- a/Appium_E2E_Test_Report_Traverse.xlsx
+++ b/Appium_E2E_Test_Report_Traverse.xlsx
@@ -791,7 +791,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 07:53:42</t>
+          <t>2026-08-11 08:02:59</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="E2" s="20" t="n">
-        <v>136</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="E3" s="23" t="n">
-        <v>158</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="E4" s="20" t="n">
-        <v>127</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="E6" s="20" t="n">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="E7" s="23" t="n">
-        <v>208</v>
+        <v>177</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -1228,7 +1228,7 @@
         </is>
       </c>
       <c r="E8" s="20" t="n">
-        <v>181</v>
+        <v>208</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="E9" s="23" t="n">
-        <v>214</v>
+        <v>225</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
@@ -1278,7 +1278,7 @@
         </is>
       </c>
       <c r="E10" s="20" t="n">
-        <v>165</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="E11" s="23" t="n">
-        <v>130</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
@@ -1328,7 +1328,7 @@
         </is>
       </c>
       <c r="E12" s="20" t="n">
-        <v>173</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="E13" s="23" t="n">
-        <v>207</v>
+        <v>131</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="E14" s="20" t="n">
-        <v>171</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="E15" s="23" t="n">
-        <v>213</v>
+        <v>234</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="E16" s="20" t="n">
-        <v>237</v>
+        <v>151</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="E17" s="23" t="n">
-        <v>190</v>
+        <v>130</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -1478,7 +1478,7 @@
         </is>
       </c>
       <c r="E18" s="20" t="n">
-        <v>235</v>
+        <v>229</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
@@ -1503,7 +1503,7 @@
         </is>
       </c>
       <c r="E19" s="23" t="n">
-        <v>200</v>
+        <v>123</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="E20" s="20" t="n">
-        <v>171</v>
+        <v>211</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="E21" s="23" t="n">
-        <v>159</v>
+        <v>215</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
@@ -1578,7 +1578,7 @@
         </is>
       </c>
       <c r="E22" s="20" t="n">
-        <v>136</v>
+        <v>151</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="E23" s="23" t="n">
-        <v>116</v>
+        <v>156</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
@@ -1628,7 +1628,7 @@
         </is>
       </c>
       <c r="E24" s="20" t="n">
-        <v>120</v>
+        <v>196</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="E25" s="23" t="n">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
@@ -1678,7 +1678,7 @@
         </is>
       </c>
       <c r="E26" s="20" t="n">
-        <v>204</v>
+        <v>238</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="E27" s="23" t="n">
-        <v>164</v>
+        <v>177</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="E28" s="20" t="n">
-        <v>122</v>
+        <v>157</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="E29" s="23" t="n">
-        <v>236</v>
+        <v>198</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="E30" s="20" t="n">
-        <v>116</v>
+        <v>168</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
@@ -1803,7 +1803,7 @@
         </is>
       </c>
       <c r="E31" s="23" t="n">
-        <v>192</v>
+        <v>199</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
@@ -1828,7 +1828,7 @@
         </is>
       </c>
       <c r="E32" s="20" t="n">
-        <v>120</v>
+        <v>237</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
@@ -1853,7 +1853,7 @@
         </is>
       </c>
       <c r="E33" s="23" t="n">
-        <v>170</v>
+        <v>153</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
@@ -1878,7 +1878,7 @@
         </is>
       </c>
       <c r="E34" s="20" t="n">
-        <v>168</v>
+        <v>229</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="E35" s="23" t="n">
-        <v>197</v>
+        <v>208</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="E36" s="20" t="n">
-        <v>162</v>
+        <v>231</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="E37" s="23" t="n">
-        <v>148</v>
+        <v>124</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
@@ -1978,7 +1978,7 @@
         </is>
       </c>
       <c r="E38" s="20" t="n">
-        <v>165</v>
+        <v>158</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="E39" s="23" t="n">
-        <v>172</v>
+        <v>131</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="E40" s="20" t="n">
-        <v>176</v>
+        <v>228</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="E41" s="23" t="n">
-        <v>117</v>
+        <v>199</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
@@ -2078,7 +2078,7 @@
         </is>
       </c>
       <c r="E42" s="20" t="n">
-        <v>121</v>
+        <v>214</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="E43" s="23" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="E44" s="20" t="n">
-        <v>198</v>
+        <v>139</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="E45" s="23" t="n">
-        <v>237</v>
+        <v>110</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
@@ -2178,7 +2178,7 @@
         </is>
       </c>
       <c r="E46" s="20" t="n">
-        <v>232</v>
+        <v>153</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
@@ -2203,7 +2203,7 @@
         </is>
       </c>
       <c r="E47" s="23" t="n">
-        <v>230</v>
+        <v>139</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="E48" s="20" t="n">
-        <v>171</v>
+        <v>119</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
@@ -2253,7 +2253,7 @@
         </is>
       </c>
       <c r="E49" s="23" t="n">
-        <v>138</v>
+        <v>219</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
@@ -2278,7 +2278,7 @@
         </is>
       </c>
       <c r="E50" s="20" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="E51" s="23" t="n">
-        <v>207</v>
+        <v>176</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
@@ -2328,7 +2328,7 @@
         </is>
       </c>
       <c r="E52" s="20" t="n">
-        <v>125</v>
+        <v>229</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
@@ -2353,7 +2353,7 @@
         </is>
       </c>
       <c r="E53" s="23" t="n">
-        <v>195</v>
+        <v>139</v>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="E54" s="20" t="n">
-        <v>159</v>
+        <v>173</v>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1">
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="E56" s="20" t="n">
-        <v>192</v>
+        <v>223</v>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1">
@@ -2453,7 +2453,7 @@
         </is>
       </c>
       <c r="E57" s="23" t="n">
-        <v>116</v>
+        <v>189</v>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1">
@@ -2478,7 +2478,7 @@
         </is>
       </c>
       <c r="E58" s="20" t="n">
-        <v>154</v>
+        <v>214</v>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1">
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="E59" s="23" t="n">
-        <v>132</v>
+        <v>141</v>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1">
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="E60" s="20" t="n">
-        <v>166</v>
+        <v>113</v>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
@@ -2553,7 +2553,7 @@
         </is>
       </c>
       <c r="E61" s="23" t="n">
-        <v>211</v>
+        <v>144</v>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="E62" s="20" t="n">
-        <v>226</v>
+        <v>191</v>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="E63" s="23" t="n">
-        <v>193</v>
+        <v>126</v>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1">
@@ -2628,7 +2628,7 @@
         </is>
       </c>
       <c r="E64" s="20" t="n">
-        <v>196</v>
+        <v>126</v>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1">
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="E65" s="23" t="n">
-        <v>152</v>
+        <v>113</v>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1">
@@ -2678,7 +2678,7 @@
         </is>
       </c>
       <c r="E66" s="20" t="n">
-        <v>157</v>
+        <v>150</v>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="E67" s="23" t="n">
-        <v>139</v>
+        <v>227</v>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="E68" s="20" t="n">
-        <v>210</v>
+        <v>113</v>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="E69" s="23" t="n">
-        <v>231</v>
+        <v>210</v>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1">
@@ -2778,7 +2778,7 @@
         </is>
       </c>
       <c r="E70" s="20" t="n">
-        <v>170</v>
+        <v>198</v>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1">
@@ -2803,7 +2803,7 @@
         </is>
       </c>
       <c r="E71" s="23" t="n">
-        <v>197</v>
+        <v>123</v>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1">
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="E72" s="20" t="n">
-        <v>125</v>
+        <v>110</v>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1">
@@ -2853,7 +2853,7 @@
         </is>
       </c>
       <c r="E73" s="23" t="n">
-        <v>201</v>
+        <v>238</v>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
@@ -2878,7 +2878,7 @@
         </is>
       </c>
       <c r="E74" s="20" t="n">
-        <v>226</v>
+        <v>120</v>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="E75" s="23" t="n">
-        <v>229</v>
+        <v>118</v>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
@@ -2928,7 +2928,7 @@
         </is>
       </c>
       <c r="E76" s="20" t="n">
-        <v>207</v>
+        <v>173</v>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="E77" s="23" t="n">
-        <v>221</v>
+        <v>182</v>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1">
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="E78" s="20" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
@@ -3003,7 +3003,7 @@
         </is>
       </c>
       <c r="E79" s="23" t="n">
-        <v>220</v>
+        <v>149</v>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1">
@@ -3028,7 +3028,7 @@
         </is>
       </c>
       <c r="E80" s="20" t="n">
-        <v>121</v>
+        <v>175</v>
       </c>
     </row>
     <row r="81" ht="20" customHeight="1">
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="E81" s="23" t="n">
-        <v>198</v>
+        <v>172</v>
       </c>
     </row>
     <row r="82" ht="20" customHeight="1">
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="E82" s="20" t="n">
-        <v>136</v>
+        <v>116</v>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1">
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="E83" s="23" t="n">
-        <v>237</v>
+        <v>154</v>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1">
@@ -3128,7 +3128,7 @@
         </is>
       </c>
       <c r="E84" s="20" t="n">
-        <v>124</v>
+        <v>151</v>
       </c>
     </row>
     <row r="85" ht="20" customHeight="1">
@@ -3153,7 +3153,7 @@
         </is>
       </c>
       <c r="E85" s="23" t="n">
-        <v>162</v>
+        <v>211</v>
       </c>
     </row>
     <row r="86" ht="20" customHeight="1">
@@ -3178,7 +3178,7 @@
         </is>
       </c>
       <c r="E86" s="20" t="n">
-        <v>186</v>
+        <v>140</v>
       </c>
     </row>
     <row r="87" ht="20" customHeight="1">
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="E87" s="23" t="n">
-        <v>232</v>
+        <v>135</v>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1">
@@ -3228,7 +3228,7 @@
         </is>
       </c>
       <c r="E88" s="20" t="n">
-        <v>190</v>
+        <v>195</v>
       </c>
     </row>
     <row r="89" ht="20" customHeight="1">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="E89" s="23" t="n">
-        <v>190</v>
+        <v>147</v>
       </c>
     </row>
     <row r="90" ht="20" customHeight="1">
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="E90" s="20" t="n">
-        <v>209</v>
+        <v>111</v>
       </c>
     </row>
     <row r="91" ht="20" customHeight="1">
@@ -3303,7 +3303,7 @@
         </is>
       </c>
       <c r="E91" s="23" t="n">
-        <v>208</v>
+        <v>126</v>
       </c>
     </row>
     <row r="92" ht="20" customHeight="1">
@@ -3328,7 +3328,7 @@
         </is>
       </c>
       <c r="E92" s="20" t="n">
-        <v>166</v>
+        <v>236</v>
       </c>
     </row>
     <row r="93" ht="20" customHeight="1">
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="E93" s="23" t="n">
-        <v>129</v>
+        <v>219</v>
       </c>
     </row>
     <row r="94" ht="20" customHeight="1">
@@ -3378,7 +3378,7 @@
         </is>
       </c>
       <c r="E94" s="20" t="n">
-        <v>220</v>
+        <v>161</v>
       </c>
     </row>
     <row r="95" ht="20" customHeight="1">
@@ -3403,7 +3403,7 @@
         </is>
       </c>
       <c r="E95" s="23" t="n">
-        <v>150</v>
+        <v>145</v>
       </c>
     </row>
     <row r="96" ht="20" customHeight="1">
@@ -3428,7 +3428,7 @@
         </is>
       </c>
       <c r="E96" s="20" t="n">
-        <v>117</v>
+        <v>225</v>
       </c>
     </row>
     <row r="97" ht="20" customHeight="1">
@@ -3453,7 +3453,7 @@
         </is>
       </c>
       <c r="E97" s="23" t="n">
-        <v>130</v>
+        <v>182</v>
       </c>
     </row>
     <row r="98" ht="20" customHeight="1">
@@ -3478,7 +3478,7 @@
         </is>
       </c>
       <c r="E98" s="20" t="n">
-        <v>179</v>
+        <v>125</v>
       </c>
     </row>
     <row r="99" ht="20" customHeight="1">
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="E99" s="23" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="100" ht="20" customHeight="1">
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="E100" s="20" t="n">
-        <v>126</v>
+        <v>156</v>
       </c>
     </row>
     <row r="101" ht="20" customHeight="1">
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="E101" s="23" t="n">
-        <v>126</v>
+        <v>203</v>
       </c>
     </row>
     <row r="102" ht="20" customHeight="1">
@@ -3578,7 +3578,7 @@
         </is>
       </c>
       <c r="E102" s="20" t="n">
-        <v>126</v>
+        <v>191</v>
       </c>
     </row>
     <row r="103" ht="20" customHeight="1">
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="E103" s="23" t="n">
-        <v>125</v>
+        <v>217</v>
       </c>
     </row>
     <row r="104" ht="20" customHeight="1">
@@ -3628,7 +3628,7 @@
         </is>
       </c>
       <c r="E104" s="20" t="n">
-        <v>153</v>
+        <v>218</v>
       </c>
     </row>
     <row r="105" ht="20" customHeight="1">
@@ -3653,7 +3653,7 @@
         </is>
       </c>
       <c r="E105" s="23" t="n">
-        <v>198</v>
+        <v>187</v>
       </c>
     </row>
     <row r="106" ht="20" customHeight="1">
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="E106" s="20" t="n">
-        <v>116</v>
+        <v>236</v>
       </c>
     </row>
     <row r="107" ht="20" customHeight="1">
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="E107" s="23" t="n">
-        <v>120</v>
+        <v>134</v>
       </c>
     </row>
     <row r="108" ht="20" customHeight="1">
@@ -3728,7 +3728,7 @@
         </is>
       </c>
       <c r="E108" s="20" t="n">
-        <v>121</v>
+        <v>136</v>
       </c>
     </row>
     <row r="109" ht="20" customHeight="1">
@@ -3753,7 +3753,7 @@
         </is>
       </c>
       <c r="E109" s="23" t="n">
-        <v>130</v>
+        <v>220</v>
       </c>
     </row>
     <row r="110" ht="20" customHeight="1">
@@ -3778,7 +3778,7 @@
         </is>
       </c>
       <c r="E110" s="20" t="n">
-        <v>166</v>
+        <v>214</v>
       </c>
     </row>
     <row r="111" ht="20" customHeight="1">
@@ -3803,7 +3803,7 @@
         </is>
       </c>
       <c r="E111" s="23" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="112" ht="20" customHeight="1">
@@ -3828,7 +3828,7 @@
         </is>
       </c>
       <c r="E112" s="20" t="n">
-        <v>212</v>
+        <v>229</v>
       </c>
     </row>
     <row r="113" ht="20" customHeight="1">
@@ -3853,7 +3853,7 @@
         </is>
       </c>
       <c r="E113" s="23" t="n">
-        <v>228</v>
+        <v>138</v>
       </c>
     </row>
     <row r="114" ht="20" customHeight="1">
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="E114" s="20" t="n">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
     <row r="115" ht="20" customHeight="1">
@@ -3903,7 +3903,7 @@
         </is>
       </c>
       <c r="E115" s="23" t="n">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="116" ht="20" customHeight="1">
@@ -3928,7 +3928,7 @@
         </is>
       </c>
       <c r="E116" s="20" t="n">
-        <v>110</v>
+        <v>160</v>
       </c>
     </row>
     <row r="117" ht="20" customHeight="1">
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="E117" s="23" t="n">
-        <v>151</v>
+        <v>133</v>
       </c>
     </row>
     <row r="118" ht="20" customHeight="1">
@@ -3978,7 +3978,7 @@
         </is>
       </c>
       <c r="E118" s="20" t="n">
-        <v>113</v>
+        <v>239</v>
       </c>
     </row>
     <row r="119" ht="20" customHeight="1">
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="E119" s="23" t="n">
-        <v>185</v>
+        <v>179</v>
       </c>
     </row>
     <row r="120" ht="20" customHeight="1">
@@ -4028,7 +4028,7 @@
         </is>
       </c>
       <c r="E120" s="20" t="n">
-        <v>152</v>
+        <v>211</v>
       </c>
     </row>
     <row r="121" ht="20" customHeight="1">
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="E121" s="23" t="n">
-        <v>200</v>
+        <v>138</v>
       </c>
     </row>
     <row r="122" ht="20" customHeight="1">
@@ -4078,7 +4078,7 @@
         </is>
       </c>
       <c r="E122" s="20" t="n">
-        <v>233</v>
+        <v>207</v>
       </c>
     </row>
     <row r="123" ht="20" customHeight="1">
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="E124" s="20" t="n">
-        <v>207</v>
+        <v>114</v>
       </c>
     </row>
     <row r="125" ht="20" customHeight="1">
@@ -4153,7 +4153,7 @@
         </is>
       </c>
       <c r="E125" s="23" t="n">
-        <v>206</v>
+        <v>228</v>
       </c>
     </row>
     <row r="126" ht="20" customHeight="1">
@@ -4178,7 +4178,7 @@
         </is>
       </c>
       <c r="E126" s="20" t="n">
-        <v>203</v>
+        <v>135</v>
       </c>
     </row>
     <row r="127" ht="20" customHeight="1">
@@ -4203,7 +4203,7 @@
         </is>
       </c>
       <c r="E127" s="23" t="n">
-        <v>204</v>
+        <v>160</v>
       </c>
     </row>
     <row r="128" ht="20" customHeight="1">
@@ -4228,7 +4228,7 @@
         </is>
       </c>
       <c r="E128" s="20" t="n">
-        <v>235</v>
+        <v>226</v>
       </c>
     </row>
     <row r="129" ht="20" customHeight="1">
@@ -4253,7 +4253,7 @@
         </is>
       </c>
       <c r="E129" s="23" t="n">
-        <v>140</v>
+        <v>192</v>
       </c>
     </row>
     <row r="130" ht="20" customHeight="1">
@@ -4278,7 +4278,7 @@
         </is>
       </c>
       <c r="E130" s="20" t="n">
-        <v>143</v>
+        <v>214</v>
       </c>
     </row>
     <row r="131" ht="20" customHeight="1">
@@ -4303,7 +4303,7 @@
         </is>
       </c>
       <c r="E131" s="23" t="n">
-        <v>111</v>
+        <v>196</v>
       </c>
     </row>
     <row r="132" ht="20" customHeight="1">
@@ -4328,7 +4328,7 @@
         </is>
       </c>
       <c r="E132" s="20" t="n">
-        <v>147</v>
+        <v>123</v>
       </c>
     </row>
     <row r="133" ht="20" customHeight="1">
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="E133" s="23" t="n">
-        <v>239</v>
+        <v>123</v>
       </c>
     </row>
     <row r="134" ht="20" customHeight="1">
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="E134" s="20" t="n">
-        <v>125</v>
+        <v>178</v>
       </c>
     </row>
     <row r="135" ht="20" customHeight="1">
@@ -4403,7 +4403,7 @@
         </is>
       </c>
       <c r="E135" s="23" t="n">
-        <v>115</v>
+        <v>212</v>
       </c>
     </row>
     <row r="136" ht="20" customHeight="1">
@@ -4428,7 +4428,7 @@
         </is>
       </c>
       <c r="E136" s="20" t="n">
-        <v>176</v>
+        <v>159</v>
       </c>
     </row>
     <row r="137" ht="20" customHeight="1">
@@ -4453,7 +4453,7 @@
         </is>
       </c>
       <c r="E137" s="23" t="n">
-        <v>133</v>
+        <v>156</v>
       </c>
     </row>
     <row r="138" ht="20" customHeight="1">
@@ -4478,7 +4478,7 @@
         </is>
       </c>
       <c r="E138" s="20" t="n">
-        <v>176</v>
+        <v>210</v>
       </c>
     </row>
     <row r="139" ht="20" customHeight="1">
@@ -4503,7 +4503,7 @@
         </is>
       </c>
       <c r="E139" s="23" t="n">
-        <v>164</v>
+        <v>183</v>
       </c>
     </row>
     <row r="140" ht="20" customHeight="1">
@@ -4528,7 +4528,7 @@
         </is>
       </c>
       <c r="E140" s="20" t="n">
-        <v>236</v>
+        <v>131</v>
       </c>
     </row>
     <row r="141" ht="20" customHeight="1">
@@ -4553,7 +4553,7 @@
         </is>
       </c>
       <c r="E141" s="23" t="n">
-        <v>210</v>
+        <v>224</v>
       </c>
     </row>
     <row r="142" ht="20" customHeight="1">
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="E142" s="20" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="143" ht="20" customHeight="1">
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="E143" s="23" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="144" ht="20" customHeight="1">
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="E144" s="20" t="n">
-        <v>152</v>
+        <v>220</v>
       </c>
     </row>
     <row r="145" ht="20" customHeight="1">
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="E145" s="23" t="n">
-        <v>143</v>
+        <v>147</v>
       </c>
     </row>
     <row r="146" ht="20" customHeight="1">
@@ -4678,7 +4678,7 @@
         </is>
       </c>
       <c r="E146" s="20" t="n">
-        <v>196</v>
+        <v>211</v>
       </c>
     </row>
     <row r="147" ht="20" customHeight="1">
@@ -4703,7 +4703,7 @@
         </is>
       </c>
       <c r="E147" s="23" t="n">
-        <v>232</v>
+        <v>154</v>
       </c>
     </row>
     <row r="148" ht="20" customHeight="1">
@@ -4728,7 +4728,7 @@
         </is>
       </c>
       <c r="E148" s="20" t="n">
-        <v>227</v>
+        <v>201</v>
       </c>
     </row>
     <row r="149" ht="20" customHeight="1">
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c r="E149" s="23" t="n">
-        <v>199</v>
+        <v>216</v>
       </c>
     </row>
     <row r="150" ht="20" customHeight="1">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="E150" s="20" t="n">
-        <v>115</v>
+        <v>221</v>
       </c>
     </row>
     <row r="151" ht="20" customHeight="1">
@@ -4803,7 +4803,7 @@
         </is>
       </c>
       <c r="E151" s="23" t="n">
-        <v>183</v>
+        <v>147</v>
       </c>
     </row>
     <row r="152" ht="20" customHeight="1">
@@ -4828,7 +4828,7 @@
         </is>
       </c>
       <c r="E152" s="20" t="n">
-        <v>217</v>
+        <v>208</v>
       </c>
     </row>
     <row r="153" ht="20" customHeight="1">
@@ -4853,7 +4853,7 @@
         </is>
       </c>
       <c r="E153" s="23" t="n">
-        <v>186</v>
+        <v>160</v>
       </c>
     </row>
     <row r="154" ht="20" customHeight="1">
@@ -4878,7 +4878,7 @@
         </is>
       </c>
       <c r="E154" s="20" t="n">
-        <v>136</v>
+        <v>180</v>
       </c>
     </row>
     <row r="155" ht="20" customHeight="1">
@@ -4903,7 +4903,7 @@
         </is>
       </c>
       <c r="E155" s="23" t="n">
-        <v>189</v>
+        <v>206</v>
       </c>
     </row>
     <row r="156" ht="20" customHeight="1">
@@ -4928,7 +4928,7 @@
         </is>
       </c>
       <c r="E156" s="20" t="n">
-        <v>240</v>
+        <v>114</v>
       </c>
     </row>
     <row r="157" ht="20" customHeight="1">
@@ -4953,7 +4953,7 @@
         </is>
       </c>
       <c r="E157" s="23" t="n">
-        <v>145</v>
+        <v>121</v>
       </c>
     </row>
     <row r="158" ht="20" customHeight="1">
@@ -4978,7 +4978,7 @@
         </is>
       </c>
       <c r="E158" s="20" t="n">
-        <v>232</v>
+        <v>196</v>
       </c>
     </row>
     <row r="159" ht="20" customHeight="1">
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="E159" s="23" t="n">
-        <v>126</v>
+        <v>238</v>
       </c>
     </row>
     <row r="160" ht="20" customHeight="1">
@@ -5028,7 +5028,7 @@
         </is>
       </c>
       <c r="E160" s="20" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="161" ht="20" customHeight="1">
@@ -5053,7 +5053,7 @@
         </is>
       </c>
       <c r="E161" s="23" t="n">
-        <v>207</v>
+        <v>173</v>
       </c>
     </row>
     <row r="162" ht="20" customHeight="1">
@@ -5078,7 +5078,7 @@
         </is>
       </c>
       <c r="E162" s="20" t="n">
-        <v>175</v>
+        <v>164</v>
       </c>
     </row>
     <row r="163" ht="20" customHeight="1">
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="E163" s="23" t="n">
-        <v>229</v>
+        <v>179</v>
       </c>
     </row>
     <row r="164" ht="20" customHeight="1">
@@ -5128,7 +5128,7 @@
         </is>
       </c>
       <c r="E164" s="20" t="n">
-        <v>110</v>
+        <v>133</v>
       </c>
     </row>
     <row r="165" ht="20" customHeight="1">
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="E165" s="23" t="n">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="166" ht="20" customHeight="1">
@@ -5178,7 +5178,7 @@
         </is>
       </c>
       <c r="E166" s="20" t="n">
-        <v>186</v>
+        <v>216</v>
       </c>
     </row>
     <row r="167" ht="20" customHeight="1">
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="E167" s="23" t="n">
-        <v>209</v>
+        <v>180</v>
       </c>
     </row>
     <row r="168" ht="20" customHeight="1">
@@ -5228,7 +5228,7 @@
         </is>
       </c>
       <c r="E168" s="20" t="n">
-        <v>198</v>
+        <v>174</v>
       </c>
     </row>
     <row r="169" ht="20" customHeight="1">
@@ -5253,7 +5253,7 @@
         </is>
       </c>
       <c r="E169" s="23" t="n">
-        <v>205</v>
+        <v>185</v>
       </c>
     </row>
     <row r="170" ht="20" customHeight="1">
@@ -5278,7 +5278,7 @@
         </is>
       </c>
       <c r="E170" s="20" t="n">
-        <v>138</v>
+        <v>171</v>
       </c>
     </row>
     <row r="171" ht="20" customHeight="1">
@@ -5303,7 +5303,7 @@
         </is>
       </c>
       <c r="E171" s="23" t="n">
-        <v>211</v>
+        <v>118</v>
       </c>
     </row>
     <row r="172" ht="20" customHeight="1">
@@ -5328,7 +5328,7 @@
         </is>
       </c>
       <c r="E172" s="20" t="n">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="173" ht="20" customHeight="1">
@@ -5353,7 +5353,7 @@
         </is>
       </c>
       <c r="E173" s="23" t="n">
-        <v>235</v>
+        <v>170</v>
       </c>
     </row>
     <row r="174" ht="20" customHeight="1">
@@ -5378,7 +5378,7 @@
         </is>
       </c>
       <c r="E174" s="20" t="n">
-        <v>152</v>
+        <v>166</v>
       </c>
     </row>
     <row r="175" ht="20" customHeight="1">
@@ -5403,7 +5403,7 @@
         </is>
       </c>
       <c r="E175" s="23" t="n">
-        <v>200</v>
+        <v>174</v>
       </c>
     </row>
     <row r="176" ht="20" customHeight="1">
@@ -5428,7 +5428,7 @@
         </is>
       </c>
       <c r="E176" s="20" t="n">
-        <v>207</v>
+        <v>223</v>
       </c>
     </row>
     <row r="177" ht="20" customHeight="1">
@@ -5453,7 +5453,7 @@
         </is>
       </c>
       <c r="E177" s="23" t="n">
-        <v>124</v>
+        <v>133</v>
       </c>
     </row>
     <row r="178" ht="20" customHeight="1">
@@ -5478,7 +5478,7 @@
         </is>
       </c>
       <c r="E178" s="20" t="n">
-        <v>121</v>
+        <v>236</v>
       </c>
     </row>
     <row r="179" ht="20" customHeight="1">
@@ -5503,7 +5503,7 @@
         </is>
       </c>
       <c r="E179" s="23" t="n">
-        <v>207</v>
+        <v>140</v>
       </c>
     </row>
     <row r="180" ht="20" customHeight="1">
@@ -5528,7 +5528,7 @@
         </is>
       </c>
       <c r="E180" s="20" t="n">
-        <v>220</v>
+        <v>194</v>
       </c>
     </row>
     <row r="181" ht="20" customHeight="1">
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="E181" s="23" t="n">
-        <v>200</v>
+        <v>230</v>
       </c>
     </row>
     <row r="182" ht="20" customHeight="1">
@@ -5578,7 +5578,7 @@
         </is>
       </c>
       <c r="E182" s="20" t="n">
-        <v>194</v>
+        <v>129</v>
       </c>
     </row>
     <row r="183" ht="20" customHeight="1">
@@ -5603,7 +5603,7 @@
         </is>
       </c>
       <c r="E183" s="23" t="n">
-        <v>169</v>
+        <v>194</v>
       </c>
     </row>
     <row r="184" ht="20" customHeight="1">
@@ -5628,7 +5628,7 @@
         </is>
       </c>
       <c r="E184" s="20" t="n">
-        <v>231</v>
+        <v>201</v>
       </c>
     </row>
     <row r="185" ht="20" customHeight="1">
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="E185" s="23" t="n">
-        <v>129</v>
+        <v>221</v>
       </c>
     </row>
     <row r="186" ht="20" customHeight="1">
@@ -5678,7 +5678,7 @@
         </is>
       </c>
       <c r="E186" s="20" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="187" ht="20" customHeight="1">
@@ -5703,7 +5703,7 @@
         </is>
       </c>
       <c r="E187" s="23" t="n">
-        <v>206</v>
+        <v>230</v>
       </c>
     </row>
     <row r="188" ht="20" customHeight="1">
@@ -5728,7 +5728,7 @@
         </is>
       </c>
       <c r="E188" s="20" t="n">
-        <v>223</v>
+        <v>158</v>
       </c>
     </row>
     <row r="189" ht="20" customHeight="1">
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="E189" s="23" t="n">
-        <v>195</v>
+        <v>181</v>
       </c>
     </row>
     <row r="190" ht="20" customHeight="1">
@@ -5778,7 +5778,7 @@
         </is>
       </c>
       <c r="E190" s="20" t="n">
-        <v>157</v>
+        <v>192</v>
       </c>
     </row>
     <row r="191" ht="20" customHeight="1">
@@ -5803,7 +5803,7 @@
         </is>
       </c>
       <c r="E191" s="23" t="n">
-        <v>179</v>
+        <v>142</v>
       </c>
     </row>
     <row r="192" ht="20" customHeight="1">
@@ -5828,7 +5828,7 @@
         </is>
       </c>
       <c r="E192" s="20" t="n">
-        <v>232</v>
+        <v>148</v>
       </c>
     </row>
     <row r="193" ht="20" customHeight="1">
@@ -5853,7 +5853,7 @@
         </is>
       </c>
       <c r="E193" s="23" t="n">
-        <v>181</v>
+        <v>175</v>
       </c>
     </row>
     <row r="194" ht="20" customHeight="1">
@@ -5878,7 +5878,7 @@
         </is>
       </c>
       <c r="E194" s="20" t="n">
-        <v>217</v>
+        <v>225</v>
       </c>
     </row>
     <row r="195" ht="20" customHeight="1">
@@ -5903,7 +5903,7 @@
         </is>
       </c>
       <c r="E195" s="23" t="n">
-        <v>213</v>
+        <v>119</v>
       </c>
     </row>
     <row r="196" ht="20" customHeight="1">
@@ -5928,7 +5928,7 @@
         </is>
       </c>
       <c r="E196" s="20" t="n">
-        <v>216</v>
+        <v>182</v>
       </c>
     </row>
     <row r="197" ht="20" customHeight="1">
@@ -5953,7 +5953,7 @@
         </is>
       </c>
       <c r="E197" s="23" t="n">
-        <v>144</v>
+        <v>169</v>
       </c>
     </row>
     <row r="198" ht="20" customHeight="1">
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="E198" s="20" t="n">
-        <v>179</v>
+        <v>196</v>
       </c>
     </row>
     <row r="199" ht="20" customHeight="1">
@@ -6003,7 +6003,7 @@
         </is>
       </c>
       <c r="E199" s="23" t="n">
-        <v>169</v>
+        <v>114</v>
       </c>
     </row>
     <row r="200" ht="20" customHeight="1">
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="E200" s="20" t="n">
-        <v>140</v>
+        <v>176</v>
       </c>
     </row>
     <row r="201" ht="20" customHeight="1">
@@ -6053,7 +6053,7 @@
         </is>
       </c>
       <c r="E201" s="23" t="n">
-        <v>131</v>
+        <v>156</v>
       </c>
     </row>
     <row r="202" ht="20" customHeight="1">
@@ -6078,7 +6078,7 @@
         </is>
       </c>
       <c r="E202" s="20" t="n">
-        <v>215</v>
+        <v>200</v>
       </c>
     </row>
     <row r="203" ht="20" customHeight="1">
@@ -6103,7 +6103,7 @@
         </is>
       </c>
       <c r="E203" s="23" t="n">
-        <v>157</v>
+        <v>203</v>
       </c>
     </row>
     <row r="204" ht="20" customHeight="1">
@@ -6128,7 +6128,7 @@
         </is>
       </c>
       <c r="E204" s="20" t="n">
-        <v>133</v>
+        <v>169</v>
       </c>
     </row>
     <row r="205" ht="20" customHeight="1">
@@ -6153,7 +6153,7 @@
         </is>
       </c>
       <c r="E205" s="23" t="n">
-        <v>167</v>
+        <v>150</v>
       </c>
     </row>
     <row r="206" ht="20" customHeight="1">
@@ -6178,7 +6178,7 @@
         </is>
       </c>
       <c r="E206" s="20" t="n">
-        <v>187</v>
+        <v>134</v>
       </c>
     </row>
     <row r="207" ht="20" customHeight="1">
@@ -6203,7 +6203,7 @@
         </is>
       </c>
       <c r="E207" s="23" t="n">
-        <v>119</v>
+        <v>163</v>
       </c>
     </row>
     <row r="208" ht="20" customHeight="1">
@@ -6228,7 +6228,7 @@
         </is>
       </c>
       <c r="E208" s="20" t="n">
-        <v>236</v>
+        <v>224</v>
       </c>
     </row>
     <row r="209" ht="20" customHeight="1">
@@ -6253,7 +6253,7 @@
         </is>
       </c>
       <c r="E209" s="23" t="n">
-        <v>149</v>
+        <v>116</v>
       </c>
     </row>
     <row r="210" ht="20" customHeight="1">
@@ -6278,7 +6278,7 @@
         </is>
       </c>
       <c r="E210" s="20" t="n">
-        <v>197</v>
+        <v>168</v>
       </c>
     </row>
     <row r="211" ht="20" customHeight="1">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="E211" s="23" t="n">
-        <v>234</v>
+        <v>116</v>
       </c>
     </row>
     <row r="212" ht="20" customHeight="1">
@@ -6328,7 +6328,7 @@
         </is>
       </c>
       <c r="E212" s="20" t="n">
-        <v>164</v>
+        <v>230</v>
       </c>
     </row>
     <row r="213" ht="20" customHeight="1">
@@ -6353,7 +6353,7 @@
         </is>
       </c>
       <c r="E213" s="23" t="n">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="214" ht="20" customHeight="1">
@@ -6378,7 +6378,7 @@
         </is>
       </c>
       <c r="E214" s="20" t="n">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="215" ht="20" customHeight="1">
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="E215" s="23" t="n">
-        <v>132</v>
+        <v>141</v>
       </c>
     </row>
     <row r="216" ht="20" customHeight="1">
@@ -6428,7 +6428,7 @@
         </is>
       </c>
       <c r="E216" s="20" t="n">
-        <v>125</v>
+        <v>198</v>
       </c>
     </row>
     <row r="217" ht="20" customHeight="1">
@@ -6453,7 +6453,7 @@
         </is>
       </c>
       <c r="E217" s="23" t="n">
-        <v>191</v>
+        <v>173</v>
       </c>
     </row>
     <row r="218" ht="20" customHeight="1">
@@ -6478,7 +6478,7 @@
         </is>
       </c>
       <c r="E218" s="20" t="n">
-        <v>146</v>
+        <v>209</v>
       </c>
     </row>
     <row r="219" ht="20" customHeight="1">
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="E219" s="23" t="n">
-        <v>135</v>
+        <v>218</v>
       </c>
     </row>
     <row r="220" ht="20" customHeight="1">
@@ -6528,7 +6528,7 @@
         </is>
       </c>
       <c r="E220" s="20" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="221" ht="20" customHeight="1">
@@ -6553,7 +6553,7 @@
         </is>
       </c>
       <c r="E221" s="23" t="n">
-        <v>194</v>
+        <v>115</v>
       </c>
     </row>
     <row r="222" ht="20" customHeight="1">
@@ -6578,7 +6578,7 @@
         </is>
       </c>
       <c r="E222" s="20" t="n">
-        <v>138</v>
+        <v>110</v>
       </c>
     </row>
     <row r="223" ht="20" customHeight="1">
@@ -6603,7 +6603,7 @@
         </is>
       </c>
       <c r="E223" s="23" t="n">
-        <v>188</v>
+        <v>239</v>
       </c>
     </row>
     <row r="224" ht="20" customHeight="1">
@@ -6628,7 +6628,7 @@
         </is>
       </c>
       <c r="E224" s="20" t="n">
-        <v>225</v>
+        <v>126</v>
       </c>
     </row>
     <row r="225" ht="20" customHeight="1">
@@ -6653,7 +6653,7 @@
         </is>
       </c>
       <c r="E225" s="23" t="n">
-        <v>140</v>
+        <v>146</v>
       </c>
     </row>
     <row r="226" ht="20" customHeight="1">
@@ -6678,7 +6678,7 @@
         </is>
       </c>
       <c r="E226" s="20" t="n">
-        <v>212</v>
+        <v>190</v>
       </c>
     </row>
     <row r="227" ht="20" customHeight="1">
@@ -6703,7 +6703,7 @@
         </is>
       </c>
       <c r="E227" s="23" t="n">
-        <v>200</v>
+        <v>153</v>
       </c>
     </row>
     <row r="228" ht="20" customHeight="1">
@@ -6728,7 +6728,7 @@
         </is>
       </c>
       <c r="E228" s="20" t="n">
-        <v>184</v>
+        <v>155</v>
       </c>
     </row>
     <row r="229" ht="20" customHeight="1">
@@ -6753,7 +6753,7 @@
         </is>
       </c>
       <c r="E229" s="23" t="n">
-        <v>169</v>
+        <v>162</v>
       </c>
     </row>
     <row r="230" ht="20" customHeight="1">
@@ -6778,7 +6778,7 @@
         </is>
       </c>
       <c r="E230" s="20" t="n">
-        <v>222</v>
+        <v>110</v>
       </c>
     </row>
     <row r="231" ht="20" customHeight="1">
@@ -6803,7 +6803,7 @@
         </is>
       </c>
       <c r="E231" s="23" t="n">
-        <v>119</v>
+        <v>231</v>
       </c>
     </row>
     <row r="232" ht="20" customHeight="1">
@@ -6828,7 +6828,7 @@
         </is>
       </c>
       <c r="E232" s="20" t="n">
-        <v>226</v>
+        <v>146</v>
       </c>
     </row>
     <row r="233" ht="20" customHeight="1">
@@ -6853,7 +6853,7 @@
         </is>
       </c>
       <c r="E233" s="23" t="n">
-        <v>149</v>
+        <v>177</v>
       </c>
     </row>
     <row r="234" ht="20" customHeight="1">
@@ -6878,7 +6878,7 @@
         </is>
       </c>
       <c r="E234" s="20" t="n">
-        <v>192</v>
+        <v>125</v>
       </c>
     </row>
     <row r="235" ht="20" customHeight="1">
@@ -6903,7 +6903,7 @@
         </is>
       </c>
       <c r="E235" s="23" t="n">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="236" ht="20" customHeight="1">
@@ -6928,7 +6928,7 @@
         </is>
       </c>
       <c r="E236" s="20" t="n">
-        <v>126</v>
+        <v>133</v>
       </c>
     </row>
     <row r="237" ht="20" customHeight="1">
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="E237" s="23" t="n">
-        <v>115</v>
+        <v>168</v>
       </c>
     </row>
     <row r="238" ht="20" customHeight="1">
@@ -6978,7 +6978,7 @@
         </is>
       </c>
       <c r="E238" s="20" t="n">
-        <v>185</v>
+        <v>144</v>
       </c>
     </row>
     <row r="239" ht="20" customHeight="1">
@@ -7003,7 +7003,7 @@
         </is>
       </c>
       <c r="E239" s="23" t="n">
-        <v>181</v>
+        <v>146</v>
       </c>
     </row>
     <row r="240" ht="20" customHeight="1">
@@ -7028,7 +7028,7 @@
         </is>
       </c>
       <c r="E240" s="20" t="n">
-        <v>151</v>
+        <v>171</v>
       </c>
     </row>
     <row r="241" ht="20" customHeight="1">
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="E241" s="23" t="n">
-        <v>130</v>
+        <v>203</v>
       </c>
     </row>
     <row r="242" ht="20" customHeight="1">
@@ -7078,7 +7078,7 @@
         </is>
       </c>
       <c r="E242" s="20" t="n">
-        <v>167</v>
+        <v>156</v>
       </c>
     </row>
     <row r="243" ht="20" customHeight="1">
@@ -7103,7 +7103,7 @@
         </is>
       </c>
       <c r="E243" s="23" t="n">
-        <v>139</v>
+        <v>132</v>
       </c>
     </row>
     <row r="244" ht="20" customHeight="1">
@@ -7128,7 +7128,7 @@
         </is>
       </c>
       <c r="E244" s="20" t="n">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="245" ht="20" customHeight="1">
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="E245" s="23" t="n">
-        <v>194</v>
+        <v>189</v>
       </c>
     </row>
     <row r="246" ht="20" customHeight="1">
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="E246" s="20" t="n">
-        <v>169</v>
+        <v>148</v>
       </c>
     </row>
     <row r="247" ht="20" customHeight="1">
@@ -7203,7 +7203,7 @@
         </is>
       </c>
       <c r="E247" s="23" t="n">
-        <v>139</v>
+        <v>168</v>
       </c>
     </row>
     <row r="248" ht="20" customHeight="1">
@@ -7228,7 +7228,7 @@
         </is>
       </c>
       <c r="E248" s="20" t="n">
-        <v>233</v>
+        <v>171</v>
       </c>
     </row>
     <row r="249" ht="20" customHeight="1">
@@ -7253,7 +7253,7 @@
         </is>
       </c>
       <c r="E249" s="23" t="n">
-        <v>185</v>
+        <v>165</v>
       </c>
     </row>
     <row r="250" ht="20" customHeight="1">
@@ -7278,7 +7278,7 @@
         </is>
       </c>
       <c r="E250" s="20" t="n">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="251" ht="20" customHeight="1">
@@ -7303,7 +7303,7 @@
         </is>
       </c>
       <c r="E251" s="23" t="n">
-        <v>193</v>
+        <v>206</v>
       </c>
     </row>
     <row r="252" ht="20" customHeight="1">
@@ -7328,7 +7328,7 @@
         </is>
       </c>
       <c r="E252" s="20" t="n">
-        <v>149</v>
+        <v>198</v>
       </c>
     </row>
     <row r="253" ht="20" customHeight="1">
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="E253" s="23" t="n">
-        <v>113</v>
+        <v>167</v>
       </c>
     </row>
     <row r="254" ht="20" customHeight="1">
@@ -7378,7 +7378,7 @@
         </is>
       </c>
       <c r="E254" s="20" t="n">
-        <v>222</v>
+        <v>180</v>
       </c>
     </row>
     <row r="255" ht="20" customHeight="1">
@@ -7403,7 +7403,7 @@
         </is>
       </c>
       <c r="E255" s="23" t="n">
-        <v>175</v>
+        <v>143</v>
       </c>
     </row>
     <row r="256" ht="20" customHeight="1">
@@ -7428,7 +7428,7 @@
         </is>
       </c>
       <c r="E256" s="20" t="n">
-        <v>174</v>
+        <v>214</v>
       </c>
     </row>
     <row r="257" ht="20" customHeight="1">
@@ -7453,7 +7453,7 @@
         </is>
       </c>
       <c r="E257" s="23" t="n">
-        <v>159</v>
+        <v>208</v>
       </c>
     </row>
     <row r="258" ht="20" customHeight="1">
@@ -7478,7 +7478,7 @@
         </is>
       </c>
       <c r="E258" s="20" t="n">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="259" ht="20" customHeight="1">
@@ -7503,7 +7503,7 @@
         </is>
       </c>
       <c r="E259" s="23" t="n">
-        <v>144</v>
+        <v>172</v>
       </c>
     </row>
     <row r="260" ht="20" customHeight="1">
@@ -7528,7 +7528,7 @@
         </is>
       </c>
       <c r="E260" s="20" t="n">
-        <v>135</v>
+        <v>152</v>
       </c>
     </row>
     <row r="261" ht="20" customHeight="1">
@@ -7553,7 +7553,7 @@
         </is>
       </c>
       <c r="E261" s="23" t="n">
-        <v>139</v>
+        <v>168</v>
       </c>
     </row>
     <row r="262" ht="20" customHeight="1">
@@ -7578,7 +7578,7 @@
         </is>
       </c>
       <c r="E262" s="20" t="n">
-        <v>139</v>
+        <v>218</v>
       </c>
     </row>
     <row r="263" ht="20" customHeight="1">
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="E263" s="23" t="n">
-        <v>115</v>
+        <v>182</v>
       </c>
     </row>
     <row r="264" ht="20" customHeight="1">
@@ -7628,7 +7628,7 @@
         </is>
       </c>
       <c r="E264" s="20" t="n">
-        <v>215</v>
+        <v>125</v>
       </c>
     </row>
     <row r="265" ht="20" customHeight="1">
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="E265" s="23" t="n">
-        <v>160</v>
+        <v>174</v>
       </c>
     </row>
     <row r="266" ht="20" customHeight="1">
@@ -7678,7 +7678,7 @@
         </is>
       </c>
       <c r="E266" s="20" t="n">
-        <v>168</v>
+        <v>221</v>
       </c>
     </row>
     <row r="267" ht="20" customHeight="1">
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="E267" s="23" t="n">
-        <v>124</v>
+        <v>116</v>
       </c>
     </row>
     <row r="268" ht="20" customHeight="1">
@@ -7728,7 +7728,7 @@
         </is>
       </c>
       <c r="E268" s="20" t="n">
-        <v>190</v>
+        <v>167</v>
       </c>
     </row>
     <row r="269" ht="20" customHeight="1">
@@ -7753,7 +7753,7 @@
         </is>
       </c>
       <c r="E269" s="23" t="n">
-        <v>175</v>
+        <v>128</v>
       </c>
     </row>
     <row r="270" ht="20" customHeight="1">
@@ -7778,7 +7778,7 @@
         </is>
       </c>
       <c r="E270" s="20" t="n">
-        <v>148</v>
+        <v>188</v>
       </c>
     </row>
     <row r="271" ht="20" customHeight="1">
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="E271" s="23" t="n">
-        <v>176</v>
+        <v>146</v>
       </c>
     </row>
     <row r="272" ht="20" customHeight="1">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="E272" s="20" t="n">
-        <v>111</v>
+        <v>184</v>
       </c>
     </row>
     <row r="273" ht="20" customHeight="1">
@@ -7853,7 +7853,7 @@
         </is>
       </c>
       <c r="E273" s="23" t="n">
-        <v>206</v>
+        <v>172</v>
       </c>
     </row>
     <row r="274" ht="20" customHeight="1">
@@ -7878,7 +7878,7 @@
         </is>
       </c>
       <c r="E274" s="20" t="n">
-        <v>205</v>
+        <v>139</v>
       </c>
     </row>
     <row r="275" ht="20" customHeight="1">
@@ -7903,7 +7903,7 @@
         </is>
       </c>
       <c r="E275" s="23" t="n">
-        <v>111</v>
+        <v>131</v>
       </c>
     </row>
     <row r="276" ht="20" customHeight="1">
@@ -7928,7 +7928,7 @@
         </is>
       </c>
       <c r="E276" s="20" t="n">
-        <v>228</v>
+        <v>116</v>
       </c>
     </row>
     <row r="277" ht="20" customHeight="1">
@@ -7953,7 +7953,7 @@
         </is>
       </c>
       <c r="E277" s="23" t="n">
-        <v>218</v>
+        <v>189</v>
       </c>
     </row>
     <row r="278" ht="20" customHeight="1">
@@ -7978,7 +7978,7 @@
         </is>
       </c>
       <c r="E278" s="20" t="n">
-        <v>233</v>
+        <v>200</v>
       </c>
     </row>
     <row r="279" ht="20" customHeight="1">
@@ -8003,7 +8003,7 @@
         </is>
       </c>
       <c r="E279" s="23" t="n">
-        <v>216</v>
+        <v>190</v>
       </c>
     </row>
     <row r="280" ht="20" customHeight="1">
@@ -8028,7 +8028,7 @@
         </is>
       </c>
       <c r="E280" s="20" t="n">
-        <v>220</v>
+        <v>195</v>
       </c>
     </row>
     <row r="281" ht="20" customHeight="1">
@@ -8078,7 +8078,7 @@
         </is>
       </c>
       <c r="E282" s="20" t="n">
-        <v>236</v>
+        <v>168</v>
       </c>
     </row>
     <row r="283" ht="20" customHeight="1">
@@ -8103,7 +8103,7 @@
         </is>
       </c>
       <c r="E283" s="23" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="284" ht="20" customHeight="1">
@@ -8128,7 +8128,7 @@
         </is>
       </c>
       <c r="E284" s="20" t="n">
-        <v>202</v>
+        <v>210</v>
       </c>
     </row>
     <row r="285" ht="20" customHeight="1">
@@ -8153,7 +8153,7 @@
         </is>
       </c>
       <c r="E285" s="23" t="n">
-        <v>152</v>
+        <v>138</v>
       </c>
     </row>
     <row r="286" ht="20" customHeight="1">
@@ -8178,7 +8178,7 @@
         </is>
       </c>
       <c r="E286" s="20" t="n">
-        <v>119</v>
+        <v>186</v>
       </c>
     </row>
     <row r="287" ht="20" customHeight="1">
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="E287" s="23" t="n">
-        <v>212</v>
+        <v>194</v>
       </c>
     </row>
     <row r="288" ht="20" customHeight="1">
@@ -8228,7 +8228,7 @@
         </is>
       </c>
       <c r="E288" s="20" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="289" ht="20" customHeight="1">
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="E289" s="23" t="n">
-        <v>207</v>
+        <v>201</v>
       </c>
     </row>
     <row r="290" ht="20" customHeight="1">
@@ -8278,7 +8278,7 @@
         </is>
       </c>
       <c r="E290" s="20" t="n">
-        <v>178</v>
+        <v>112</v>
       </c>
     </row>
     <row r="291" ht="20" customHeight="1">
@@ -8303,7 +8303,7 @@
         </is>
       </c>
       <c r="E291" s="23" t="n">
-        <v>145</v>
+        <v>117</v>
       </c>
     </row>
     <row r="292" ht="20" customHeight="1">
@@ -8328,7 +8328,7 @@
         </is>
       </c>
       <c r="E292" s="20" t="n">
-        <v>123</v>
+        <v>227</v>
       </c>
     </row>
     <row r="293" ht="20" customHeight="1">
@@ -8353,7 +8353,7 @@
         </is>
       </c>
       <c r="E293" s="23" t="n">
-        <v>205</v>
+        <v>132</v>
       </c>
     </row>
     <row r="294" ht="20" customHeight="1">
@@ -8378,7 +8378,7 @@
         </is>
       </c>
       <c r="E294" s="20" t="n">
-        <v>189</v>
+        <v>132</v>
       </c>
     </row>
     <row r="295" ht="20" customHeight="1">
@@ -8403,7 +8403,7 @@
         </is>
       </c>
       <c r="E295" s="23" t="n">
-        <v>237</v>
+        <v>196</v>
       </c>
     </row>
     <row r="296" ht="20" customHeight="1">
@@ -8428,7 +8428,7 @@
         </is>
       </c>
       <c r="E296" s="20" t="n">
-        <v>166</v>
+        <v>223</v>
       </c>
     </row>
     <row r="297" ht="20" customHeight="1">
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="E297" s="23" t="n">
-        <v>237</v>
+        <v>154</v>
       </c>
     </row>
     <row r="298" ht="20" customHeight="1">
@@ -8478,7 +8478,7 @@
         </is>
       </c>
       <c r="E298" s="20" t="n">
-        <v>111</v>
+        <v>225</v>
       </c>
     </row>
     <row r="299" ht="20" customHeight="1">
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="E299" s="23" t="n">
-        <v>216</v>
+        <v>174</v>
       </c>
     </row>
     <row r="300" ht="20" customHeight="1">
@@ -8528,7 +8528,7 @@
         </is>
       </c>
       <c r="E300" s="20" t="n">
-        <v>227</v>
+        <v>135</v>
       </c>
     </row>
     <row r="301" ht="20" customHeight="1">
@@ -8553,7 +8553,7 @@
         </is>
       </c>
       <c r="E301" s="23" t="n">
-        <v>182</v>
+        <v>157</v>
       </c>
     </row>
     <row r="302" ht="20" customHeight="1">
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="E302" s="20" t="n">
-        <v>125</v>
+        <v>136</v>
       </c>
     </row>
     <row r="303" ht="20" customHeight="1">
@@ -8603,7 +8603,7 @@
         </is>
       </c>
       <c r="E303" s="23" t="n">
-        <v>218</v>
+        <v>125</v>
       </c>
     </row>
     <row r="304" ht="20" customHeight="1">
@@ -8628,7 +8628,7 @@
         </is>
       </c>
       <c r="E304" s="20" t="n">
-        <v>172</v>
+        <v>126</v>
       </c>
     </row>
     <row r="305" ht="20" customHeight="1">
@@ -8653,7 +8653,7 @@
         </is>
       </c>
       <c r="E305" s="23" t="n">
-        <v>170</v>
+        <v>118</v>
       </c>
     </row>
     <row r="306" ht="20" customHeight="1">
@@ -8678,7 +8678,7 @@
         </is>
       </c>
       <c r="E306" s="20" t="n">
-        <v>158</v>
+        <v>149</v>
       </c>
     </row>
     <row r="307" ht="20" customHeight="1">
@@ -8703,7 +8703,7 @@
         </is>
       </c>
       <c r="E307" s="23" t="n">
-        <v>182</v>
+        <v>141</v>
       </c>
     </row>
     <row r="308" ht="20" customHeight="1">
@@ -8728,7 +8728,7 @@
         </is>
       </c>
       <c r="E308" s="20" t="n">
-        <v>168</v>
+        <v>188</v>
       </c>
     </row>
     <row r="309" ht="20" customHeight="1">
@@ -8753,7 +8753,7 @@
         </is>
       </c>
       <c r="E309" s="23" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="310" ht="20" customHeight="1">
@@ -8778,7 +8778,7 @@
         </is>
       </c>
       <c r="E310" s="20" t="n">
-        <v>160</v>
+        <v>139</v>
       </c>
     </row>
     <row r="311" ht="20" customHeight="1">
@@ -8803,7 +8803,7 @@
         </is>
       </c>
       <c r="E311" s="23" t="n">
-        <v>156</v>
+        <v>117</v>
       </c>
     </row>
     <row r="312" ht="20" customHeight="1">
@@ -8828,7 +8828,7 @@
         </is>
       </c>
       <c r="E312" s="20" t="n">
-        <v>165</v>
+        <v>213</v>
       </c>
     </row>
     <row r="313" ht="20" customHeight="1">
@@ -8853,7 +8853,7 @@
         </is>
       </c>
       <c r="E313" s="23" t="n">
-        <v>191</v>
+        <v>141</v>
       </c>
     </row>
     <row r="314" ht="20" customHeight="1">
@@ -8878,7 +8878,7 @@
         </is>
       </c>
       <c r="E314" s="20" t="n">
-        <v>204</v>
+        <v>135</v>
       </c>
     </row>
     <row r="315" ht="20" customHeight="1">
@@ -8903,7 +8903,7 @@
         </is>
       </c>
       <c r="E315" s="23" t="n">
-        <v>120</v>
+        <v>186</v>
       </c>
     </row>
     <row r="316" ht="20" customHeight="1">
@@ -8928,7 +8928,7 @@
         </is>
       </c>
       <c r="E316" s="20" t="n">
-        <v>154</v>
+        <v>240</v>
       </c>
     </row>
     <row r="317" ht="20" customHeight="1">
@@ -8953,7 +8953,7 @@
         </is>
       </c>
       <c r="E317" s="23" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="318" ht="20" customHeight="1">
@@ -8978,7 +8978,7 @@
         </is>
       </c>
       <c r="E318" s="20" t="n">
-        <v>209</v>
+        <v>202</v>
       </c>
     </row>
     <row r="319" ht="20" customHeight="1">
@@ -9003,7 +9003,7 @@
         </is>
       </c>
       <c r="E319" s="23" t="n">
-        <v>208</v>
+        <v>134</v>
       </c>
     </row>
     <row r="320" ht="20" customHeight="1">
@@ -9028,7 +9028,7 @@
         </is>
       </c>
       <c r="E320" s="20" t="n">
-        <v>166</v>
+        <v>190</v>
       </c>
     </row>
     <row r="321" ht="20" customHeight="1">
@@ -9053,7 +9053,7 @@
         </is>
       </c>
       <c r="E321" s="23" t="n">
-        <v>221</v>
+        <v>140</v>
       </c>
     </row>
     <row r="322" ht="20" customHeight="1">
@@ -9078,7 +9078,7 @@
         </is>
       </c>
       <c r="E322" s="20" t="n">
-        <v>118</v>
+        <v>201</v>
       </c>
     </row>
     <row r="323" ht="20" customHeight="1">
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="E323" s="23" t="n">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="324" ht="20" customHeight="1">
@@ -9128,7 +9128,7 @@
         </is>
       </c>
       <c r="E324" s="20" t="n">
-        <v>168</v>
+        <v>121</v>
       </c>
     </row>
     <row r="325" ht="20" customHeight="1">
@@ -9153,7 +9153,7 @@
         </is>
       </c>
       <c r="E325" s="23" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
     </row>
     <row r="326" ht="20" customHeight="1">
@@ -9178,7 +9178,7 @@
         </is>
       </c>
       <c r="E326" s="20" t="n">
-        <v>111</v>
+        <v>147</v>
       </c>
     </row>
     <row r="327" ht="20" customHeight="1">
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="E327" s="23" t="n">
-        <v>114</v>
+        <v>129</v>
       </c>
     </row>
     <row r="328" ht="20" customHeight="1">
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="E328" s="20" t="n">
-        <v>140</v>
+        <v>189</v>
       </c>
     </row>
     <row r="329" ht="20" customHeight="1">
@@ -9253,7 +9253,7 @@
         </is>
       </c>
       <c r="E329" s="23" t="n">
-        <v>217</v>
+        <v>168</v>
       </c>
     </row>
     <row r="330" ht="20" customHeight="1">
@@ -9278,7 +9278,7 @@
         </is>
       </c>
       <c r="E330" s="20" t="n">
-        <v>192</v>
+        <v>217</v>
       </c>
     </row>
     <row r="331" ht="20" customHeight="1">
@@ -9303,7 +9303,7 @@
         </is>
       </c>
       <c r="E331" s="23" t="n">
-        <v>223</v>
+        <v>174</v>
       </c>
     </row>
     <row r="332" ht="20" customHeight="1">
@@ -9328,7 +9328,7 @@
         </is>
       </c>
       <c r="E332" s="20" t="n">
-        <v>201</v>
+        <v>136</v>
       </c>
     </row>
     <row r="333" ht="20" customHeight="1">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="E333" s="23" t="n">
-        <v>201</v>
+        <v>112</v>
       </c>
     </row>
     <row r="334" ht="20" customHeight="1">
@@ -9378,7 +9378,7 @@
         </is>
       </c>
       <c r="E334" s="20" t="n">
-        <v>209</v>
+        <v>167</v>
       </c>
     </row>
     <row r="335" ht="20" customHeight="1">
@@ -9403,7 +9403,7 @@
         </is>
       </c>
       <c r="E335" s="23" t="n">
-        <v>126</v>
+        <v>232</v>
       </c>
     </row>
     <row r="336" ht="20" customHeight="1">
@@ -9428,7 +9428,7 @@
         </is>
       </c>
       <c r="E336" s="20" t="n">
-        <v>189</v>
+        <v>179</v>
       </c>
     </row>
     <row r="337" ht="20" customHeight="1">
@@ -9453,7 +9453,7 @@
         </is>
       </c>
       <c r="E337" s="23" t="n">
-        <v>207</v>
+        <v>201</v>
       </c>
     </row>
     <row r="338" ht="20" customHeight="1">
@@ -9478,7 +9478,7 @@
         </is>
       </c>
       <c r="E338" s="20" t="n">
-        <v>145</v>
+        <v>112</v>
       </c>
     </row>
     <row r="339" ht="20" customHeight="1">
@@ -9503,7 +9503,7 @@
         </is>
       </c>
       <c r="E339" s="23" t="n">
-        <v>204</v>
+        <v>144</v>
       </c>
     </row>
     <row r="340" ht="20" customHeight="1">
@@ -9528,7 +9528,7 @@
         </is>
       </c>
       <c r="E340" s="20" t="n">
-        <v>180</v>
+        <v>110</v>
       </c>
     </row>
     <row r="341" ht="20" customHeight="1">
@@ -9553,7 +9553,7 @@
         </is>
       </c>
       <c r="E341" s="23" t="n">
-        <v>201</v>
+        <v>224</v>
       </c>
     </row>
     <row r="342" ht="20" customHeight="1">
@@ -9578,7 +9578,7 @@
         </is>
       </c>
       <c r="E342" s="20" t="n">
-        <v>155</v>
+        <v>111</v>
       </c>
     </row>
     <row r="343" ht="20" customHeight="1">
@@ -9603,7 +9603,7 @@
         </is>
       </c>
       <c r="E343" s="23" t="n">
-        <v>196</v>
+        <v>117</v>
       </c>
     </row>
     <row r="344" ht="20" customHeight="1">
@@ -9628,7 +9628,7 @@
         </is>
       </c>
       <c r="E344" s="20" t="n">
-        <v>229</v>
+        <v>225</v>
       </c>
     </row>
     <row r="345" ht="20" customHeight="1">
@@ -9653,7 +9653,7 @@
         </is>
       </c>
       <c r="E345" s="23" t="n">
-        <v>160</v>
+        <v>228</v>
       </c>
     </row>
     <row r="346" ht="20" customHeight="1">
@@ -9703,7 +9703,7 @@
         </is>
       </c>
       <c r="E347" s="23" t="n">
-        <v>118</v>
+        <v>178</v>
       </c>
     </row>
     <row r="348" ht="20" customHeight="1">
@@ -9728,7 +9728,7 @@
         </is>
       </c>
       <c r="E348" s="20" t="n">
-        <v>125</v>
+        <v>187</v>
       </c>
     </row>
     <row r="349" ht="20" customHeight="1">
@@ -9753,7 +9753,7 @@
         </is>
       </c>
       <c r="E349" s="23" t="n">
-        <v>189</v>
+        <v>154</v>
       </c>
     </row>
     <row r="350" ht="20" customHeight="1">
@@ -9778,7 +9778,7 @@
         </is>
       </c>
       <c r="E350" s="20" t="n">
-        <v>174</v>
+        <v>113</v>
       </c>
     </row>
     <row r="351" ht="20" customHeight="1">
@@ -9803,7 +9803,7 @@
         </is>
       </c>
       <c r="E351" s="23" t="n">
-        <v>122</v>
+        <v>144</v>
       </c>
     </row>
     <row r="352" ht="20" customHeight="1">
@@ -9828,7 +9828,7 @@
         </is>
       </c>
       <c r="E352" s="20" t="n">
-        <v>138</v>
+        <v>185</v>
       </c>
     </row>
     <row r="353" ht="20" customHeight="1">
@@ -9853,7 +9853,7 @@
         </is>
       </c>
       <c r="E353" s="23" t="n">
-        <v>144</v>
+        <v>123</v>
       </c>
     </row>
     <row r="354" ht="20" customHeight="1">
@@ -9878,7 +9878,7 @@
         </is>
       </c>
       <c r="E354" s="20" t="n">
-        <v>128</v>
+        <v>121</v>
       </c>
     </row>
     <row r="355" ht="20" customHeight="1">
@@ -9903,7 +9903,7 @@
         </is>
       </c>
       <c r="E355" s="23" t="n">
-        <v>141</v>
+        <v>119</v>
       </c>
     </row>
     <row r="356" ht="20" customHeight="1">
@@ -9928,7 +9928,7 @@
         </is>
       </c>
       <c r="E356" s="20" t="n">
-        <v>188</v>
+        <v>237</v>
       </c>
     </row>
     <row r="357" ht="20" customHeight="1">
@@ -9953,7 +9953,7 @@
         </is>
       </c>
       <c r="E357" s="23" t="n">
-        <v>169</v>
+        <v>163</v>
       </c>
     </row>
     <row r="358" ht="20" customHeight="1">
@@ -9978,7 +9978,7 @@
         </is>
       </c>
       <c r="E358" s="20" t="n">
-        <v>231</v>
+        <v>196</v>
       </c>
     </row>
     <row r="359" ht="20" customHeight="1">
@@ -10003,7 +10003,7 @@
         </is>
       </c>
       <c r="E359" s="23" t="n">
-        <v>230</v>
+        <v>125</v>
       </c>
     </row>
     <row r="360" ht="20" customHeight="1">
@@ -10028,7 +10028,7 @@
         </is>
       </c>
       <c r="E360" s="20" t="n">
-        <v>117</v>
+        <v>129</v>
       </c>
     </row>
     <row r="361" ht="20" customHeight="1">
@@ -10053,7 +10053,7 @@
         </is>
       </c>
       <c r="E361" s="23" t="n">
-        <v>135</v>
+        <v>225</v>
       </c>
     </row>
     <row r="362" ht="20" customHeight="1">
@@ -10078,7 +10078,7 @@
         </is>
       </c>
       <c r="E362" s="20" t="n">
-        <v>182</v>
+        <v>200</v>
       </c>
     </row>
     <row r="363" ht="20" customHeight="1">
@@ -10103,7 +10103,7 @@
         </is>
       </c>
       <c r="E363" s="23" t="n">
-        <v>125</v>
+        <v>235</v>
       </c>
     </row>
     <row r="364" ht="20" customHeight="1">
@@ -10128,7 +10128,7 @@
         </is>
       </c>
       <c r="E364" s="20" t="n">
-        <v>130</v>
+        <v>229</v>
       </c>
     </row>
     <row r="365" ht="20" customHeight="1">
@@ -10153,7 +10153,7 @@
         </is>
       </c>
       <c r="E365" s="23" t="n">
-        <v>205</v>
+        <v>116</v>
       </c>
     </row>
     <row r="366" ht="20" customHeight="1">
@@ -10178,7 +10178,7 @@
         </is>
       </c>
       <c r="E366" s="20" t="n">
-        <v>139</v>
+        <v>228</v>
       </c>
     </row>
     <row r="367" ht="20" customHeight="1">
@@ -10203,7 +10203,7 @@
         </is>
       </c>
       <c r="E367" s="23" t="n">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="368" ht="20" customHeight="1">
@@ -10228,7 +10228,7 @@
         </is>
       </c>
       <c r="E368" s="20" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
     </row>
     <row r="369" ht="20" customHeight="1">
@@ -10253,7 +10253,7 @@
         </is>
       </c>
       <c r="E369" s="23" t="n">
-        <v>222</v>
+        <v>157</v>
       </c>
     </row>
     <row r="370" ht="20" customHeight="1">
@@ -10278,7 +10278,7 @@
         </is>
       </c>
       <c r="E370" s="20" t="n">
-        <v>168</v>
+        <v>184</v>
       </c>
     </row>
     <row r="371" ht="20" customHeight="1">
@@ -10303,7 +10303,7 @@
         </is>
       </c>
       <c r="E371" s="23" t="n">
-        <v>158</v>
+        <v>183</v>
       </c>
     </row>
     <row r="372" ht="20" customHeight="1">
@@ -10328,7 +10328,7 @@
         </is>
       </c>
       <c r="E372" s="20" t="n">
-        <v>200</v>
+        <v>236</v>
       </c>
     </row>
     <row r="373" ht="20" customHeight="1">
@@ -10353,7 +10353,7 @@
         </is>
       </c>
       <c r="E373" s="23" t="n">
-        <v>114</v>
+        <v>124</v>
       </c>
     </row>
     <row r="374" ht="20" customHeight="1">
@@ -10378,7 +10378,7 @@
         </is>
       </c>
       <c r="E374" s="20" t="n">
-        <v>126</v>
+        <v>213</v>
       </c>
     </row>
     <row r="375" ht="20" customHeight="1">
@@ -10403,7 +10403,7 @@
         </is>
       </c>
       <c r="E375" s="23" t="n">
-        <v>129</v>
+        <v>221</v>
       </c>
     </row>
     <row r="376" ht="20" customHeight="1">
@@ -10428,7 +10428,7 @@
         </is>
       </c>
       <c r="E376" s="20" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="377" ht="20" customHeight="1">
@@ -10453,7 +10453,7 @@
         </is>
       </c>
       <c r="E377" s="23" t="n">
-        <v>184</v>
+        <v>162</v>
       </c>
     </row>
     <row r="378" ht="20" customHeight="1">
@@ -10478,7 +10478,7 @@
         </is>
       </c>
       <c r="E378" s="20" t="n">
-        <v>146</v>
+        <v>163</v>
       </c>
     </row>
     <row r="379" ht="20" customHeight="1">
@@ -10503,7 +10503,7 @@
         </is>
       </c>
       <c r="E379" s="23" t="n">
-        <v>115</v>
+        <v>148</v>
       </c>
     </row>
     <row r="380" ht="20" customHeight="1">
@@ -10528,7 +10528,7 @@
         </is>
       </c>
       <c r="E380" s="20" t="n">
-        <v>151</v>
+        <v>160</v>
       </c>
     </row>
     <row r="381" ht="20" customHeight="1">
@@ -10553,7 +10553,7 @@
         </is>
       </c>
       <c r="E381" s="23" t="n">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="382" ht="20" customHeight="1">
@@ -10578,7 +10578,7 @@
         </is>
       </c>
       <c r="E382" s="20" t="n">
-        <v>112</v>
+        <v>220</v>
       </c>
     </row>
     <row r="383" ht="20" customHeight="1">
@@ -10603,7 +10603,7 @@
         </is>
       </c>
       <c r="E383" s="23" t="n">
-        <v>186</v>
+        <v>221</v>
       </c>
     </row>
     <row r="384" ht="20" customHeight="1">
@@ -10628,7 +10628,7 @@
         </is>
       </c>
       <c r="E384" s="20" t="n">
-        <v>114</v>
+        <v>236</v>
       </c>
     </row>
     <row r="385" ht="20" customHeight="1">
@@ -10653,7 +10653,7 @@
         </is>
       </c>
       <c r="E385" s="23" t="n">
-        <v>203</v>
+        <v>220</v>
       </c>
     </row>
     <row r="386" ht="20" customHeight="1">
@@ -10678,7 +10678,7 @@
         </is>
       </c>
       <c r="E386" s="20" t="n">
-        <v>190</v>
+        <v>143</v>
       </c>
     </row>
     <row r="387" ht="20" customHeight="1">
@@ -10703,7 +10703,7 @@
         </is>
       </c>
       <c r="E387" s="23" t="n">
-        <v>196</v>
+        <v>179</v>
       </c>
     </row>
     <row r="388" ht="20" customHeight="1">
@@ -10728,7 +10728,7 @@
         </is>
       </c>
       <c r="E388" s="20" t="n">
-        <v>234</v>
+        <v>111</v>
       </c>
     </row>
     <row r="389" ht="20" customHeight="1">
@@ -10753,7 +10753,7 @@
         </is>
       </c>
       <c r="E389" s="23" t="n">
-        <v>136</v>
+        <v>126</v>
       </c>
     </row>
     <row r="390" ht="20" customHeight="1">
@@ -10778,7 +10778,7 @@
         </is>
       </c>
       <c r="E390" s="20" t="n">
-        <v>181</v>
+        <v>213</v>
       </c>
     </row>
     <row r="391" ht="20" customHeight="1">
@@ -10803,7 +10803,7 @@
         </is>
       </c>
       <c r="E391" s="23" t="n">
-        <v>137</v>
+        <v>158</v>
       </c>
     </row>
     <row r="392" ht="20" customHeight="1">
@@ -10828,7 +10828,7 @@
         </is>
       </c>
       <c r="E392" s="20" t="n">
-        <v>186</v>
+        <v>134</v>
       </c>
     </row>
     <row r="393" ht="20" customHeight="1">
@@ -10853,7 +10853,7 @@
         </is>
       </c>
       <c r="E393" s="23" t="n">
-        <v>180</v>
+        <v>216</v>
       </c>
     </row>
     <row r="394" ht="20" customHeight="1">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="E394" s="20" t="n">
-        <v>189</v>
+        <v>125</v>
       </c>
     </row>
     <row r="395" ht="20" customHeight="1">
@@ -10903,7 +10903,7 @@
         </is>
       </c>
       <c r="E395" s="23" t="n">
-        <v>219</v>
+        <v>186</v>
       </c>
     </row>
     <row r="396" ht="20" customHeight="1">
@@ -10928,7 +10928,7 @@
         </is>
       </c>
       <c r="E396" s="20" t="n">
-        <v>234</v>
+        <v>151</v>
       </c>
     </row>
     <row r="397" ht="20" customHeight="1">
@@ -10953,7 +10953,7 @@
         </is>
       </c>
       <c r="E397" s="23" t="n">
-        <v>131</v>
+        <v>229</v>
       </c>
     </row>
     <row r="398" ht="20" customHeight="1">
@@ -10978,7 +10978,7 @@
         </is>
       </c>
       <c r="E398" s="20" t="n">
-        <v>187</v>
+        <v>141</v>
       </c>
     </row>
     <row r="399" ht="20" customHeight="1">
@@ -11003,7 +11003,7 @@
         </is>
       </c>
       <c r="E399" s="23" t="n">
-        <v>205</v>
+        <v>212</v>
       </c>
     </row>
     <row r="400" ht="20" customHeight="1">
@@ -11028,7 +11028,7 @@
         </is>
       </c>
       <c r="E400" s="20" t="n">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="401" ht="20" customHeight="1">
@@ -11053,7 +11053,7 @@
         </is>
       </c>
       <c r="E401" s="23" t="n">
-        <v>158</v>
+        <v>238</v>
       </c>
     </row>
     <row r="402" ht="20" customHeight="1">
@@ -11103,7 +11103,7 @@
         </is>
       </c>
       <c r="E403" s="23" t="n">
-        <v>234</v>
+        <v>209</v>
       </c>
     </row>
     <row r="404" ht="20" customHeight="1">
@@ -11128,7 +11128,7 @@
         </is>
       </c>
       <c r="E404" s="20" t="n">
-        <v>199</v>
+        <v>146</v>
       </c>
     </row>
     <row r="405" ht="20" customHeight="1">
@@ -11153,7 +11153,7 @@
         </is>
       </c>
       <c r="E405" s="23" t="n">
-        <v>226</v>
+        <v>141</v>
       </c>
     </row>
     <row r="406" ht="20" customHeight="1">
@@ -11178,7 +11178,7 @@
         </is>
       </c>
       <c r="E406" s="20" t="n">
-        <v>121</v>
+        <v>157</v>
       </c>
     </row>
     <row r="407" ht="20" customHeight="1">
@@ -11203,7 +11203,7 @@
         </is>
       </c>
       <c r="E407" s="23" t="n">
-        <v>200</v>
+        <v>172</v>
       </c>
     </row>
     <row r="408" ht="20" customHeight="1">
@@ -11228,7 +11228,7 @@
         </is>
       </c>
       <c r="E408" s="20" t="n">
-        <v>232</v>
+        <v>150</v>
       </c>
     </row>
     <row r="409" ht="20" customHeight="1">
@@ -11253,7 +11253,7 @@
         </is>
       </c>
       <c r="E409" s="23" t="n">
-        <v>198</v>
+        <v>138</v>
       </c>
     </row>
     <row r="410" ht="20" customHeight="1">
@@ -11278,7 +11278,7 @@
         </is>
       </c>
       <c r="E410" s="20" t="n">
-        <v>116</v>
+        <v>203</v>
       </c>
     </row>
     <row r="411" ht="20" customHeight="1">
@@ -11303,7 +11303,7 @@
         </is>
       </c>
       <c r="E411" s="23" t="n">
-        <v>226</v>
+        <v>154</v>
       </c>
     </row>
     <row r="412" ht="20" customHeight="1">
@@ -11328,7 +11328,7 @@
         </is>
       </c>
       <c r="E412" s="20" t="n">
-        <v>203</v>
+        <v>163</v>
       </c>
     </row>
     <row r="413" ht="20" customHeight="1">
@@ -11353,7 +11353,7 @@
         </is>
       </c>
       <c r="E413" s="23" t="n">
-        <v>139</v>
+        <v>132</v>
       </c>
     </row>
     <row r="414" ht="20" customHeight="1">
@@ -11378,7 +11378,7 @@
         </is>
       </c>
       <c r="E414" s="20" t="n">
-        <v>165</v>
+        <v>219</v>
       </c>
     </row>
     <row r="415" ht="20" customHeight="1">
@@ -11403,7 +11403,7 @@
         </is>
       </c>
       <c r="E415" s="23" t="n">
-        <v>159</v>
+        <v>138</v>
       </c>
     </row>
     <row r="416" ht="20" customHeight="1">
@@ -11428,7 +11428,7 @@
         </is>
       </c>
       <c r="E416" s="20" t="n">
-        <v>213</v>
+        <v>193</v>
       </c>
     </row>
     <row r="417" ht="20" customHeight="1">
@@ -11453,7 +11453,7 @@
         </is>
       </c>
       <c r="E417" s="23" t="n">
-        <v>236</v>
+        <v>157</v>
       </c>
     </row>
     <row r="418" ht="20" customHeight="1">
@@ -11478,7 +11478,7 @@
         </is>
       </c>
       <c r="E418" s="20" t="n">
-        <v>124</v>
+        <v>225</v>
       </c>
     </row>
     <row r="419" ht="20" customHeight="1">
@@ -11503,7 +11503,7 @@
         </is>
       </c>
       <c r="E419" s="23" t="n">
-        <v>143</v>
+        <v>190</v>
       </c>
     </row>
     <row r="420" ht="20" customHeight="1">
@@ -11528,7 +11528,7 @@
         </is>
       </c>
       <c r="E420" s="20" t="n">
-        <v>189</v>
+        <v>173</v>
       </c>
     </row>
     <row r="421" ht="20" customHeight="1">
@@ -11553,7 +11553,7 @@
         </is>
       </c>
       <c r="E421" s="23" t="n">
-        <v>139</v>
+        <v>231</v>
       </c>
     </row>
     <row r="422" ht="20" customHeight="1">
@@ -11578,7 +11578,7 @@
         </is>
       </c>
       <c r="E422" s="20" t="n">
-        <v>185</v>
+        <v>201</v>
       </c>
     </row>
     <row r="423" ht="20" customHeight="1">
@@ -11603,7 +11603,7 @@
         </is>
       </c>
       <c r="E423" s="23" t="n">
-        <v>238</v>
+        <v>228</v>
       </c>
     </row>
     <row r="424" ht="20" customHeight="1">
@@ -11628,7 +11628,7 @@
         </is>
       </c>
       <c r="E424" s="20" t="n">
-        <v>218</v>
+        <v>225</v>
       </c>
     </row>
     <row r="425" ht="20" customHeight="1">
@@ -11653,7 +11653,7 @@
         </is>
       </c>
       <c r="E425" s="23" t="n">
-        <v>188</v>
+        <v>144</v>
       </c>
     </row>
     <row r="426" ht="20" customHeight="1">
@@ -11678,7 +11678,7 @@
         </is>
       </c>
       <c r="E426" s="20" t="n">
-        <v>200</v>
+        <v>228</v>
       </c>
     </row>
     <row r="427" ht="20" customHeight="1">
@@ -11703,7 +11703,7 @@
         </is>
       </c>
       <c r="E427" s="23" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="428" ht="20" customHeight="1">
@@ -11728,7 +11728,7 @@
         </is>
       </c>
       <c r="E428" s="20" t="n">
-        <v>119</v>
+        <v>211</v>
       </c>
     </row>
     <row r="429" ht="20" customHeight="1">
@@ -11753,7 +11753,7 @@
         </is>
       </c>
       <c r="E429" s="23" t="n">
-        <v>114</v>
+        <v>215</v>
       </c>
     </row>
     <row r="430" ht="20" customHeight="1">
@@ -11778,7 +11778,7 @@
         </is>
       </c>
       <c r="E430" s="20" t="n">
-        <v>187</v>
+        <v>122</v>
       </c>
     </row>
     <row r="431" ht="20" customHeight="1">
@@ -11803,7 +11803,7 @@
         </is>
       </c>
       <c r="E431" s="23" t="n">
-        <v>162</v>
+        <v>138</v>
       </c>
     </row>
     <row r="432" ht="20" customHeight="1">
@@ -11828,7 +11828,7 @@
         </is>
       </c>
       <c r="E432" s="20" t="n">
-        <v>220</v>
+        <v>136</v>
       </c>
     </row>
     <row r="433" ht="20" customHeight="1">
@@ -11853,7 +11853,7 @@
         </is>
       </c>
       <c r="E433" s="23" t="n">
-        <v>186</v>
+        <v>118</v>
       </c>
     </row>
     <row r="434" ht="20" customHeight="1">
@@ -11878,7 +11878,7 @@
         </is>
       </c>
       <c r="E434" s="20" t="n">
-        <v>168</v>
+        <v>204</v>
       </c>
     </row>
     <row r="435" ht="20" customHeight="1">
@@ -11903,7 +11903,7 @@
         </is>
       </c>
       <c r="E435" s="23" t="n">
-        <v>113</v>
+        <v>129</v>
       </c>
     </row>
     <row r="436" ht="20" customHeight="1">
@@ -11928,7 +11928,7 @@
         </is>
       </c>
       <c r="E436" s="20" t="n">
-        <v>211</v>
+        <v>152</v>
       </c>
     </row>
     <row r="437" ht="20" customHeight="1">
@@ -11953,7 +11953,7 @@
         </is>
       </c>
       <c r="E437" s="23" t="n">
-        <v>178</v>
+        <v>226</v>
       </c>
     </row>
     <row r="438" ht="20" customHeight="1">
@@ -11978,7 +11978,7 @@
         </is>
       </c>
       <c r="E438" s="20" t="n">
-        <v>186</v>
+        <v>194</v>
       </c>
     </row>
     <row r="439" ht="20" customHeight="1">
@@ -12003,7 +12003,7 @@
         </is>
       </c>
       <c r="E439" s="23" t="n">
-        <v>210</v>
+        <v>240</v>
       </c>
     </row>
     <row r="440" ht="20" customHeight="1">
@@ -12028,7 +12028,7 @@
         </is>
       </c>
       <c r="E440" s="20" t="n">
-        <v>174</v>
+        <v>166</v>
       </c>
     </row>
     <row r="441" ht="20" customHeight="1">
@@ -12053,7 +12053,7 @@
         </is>
       </c>
       <c r="E441" s="23" t="n">
-        <v>201</v>
+        <v>121</v>
       </c>
     </row>
     <row r="442" ht="20" customHeight="1">
@@ -12078,7 +12078,7 @@
         </is>
       </c>
       <c r="E442" s="20" t="n">
-        <v>182</v>
+        <v>205</v>
       </c>
     </row>
     <row r="443" ht="20" customHeight="1">
@@ -12103,7 +12103,7 @@
         </is>
       </c>
       <c r="E443" s="23" t="n">
-        <v>147</v>
+        <v>114</v>
       </c>
     </row>
     <row r="444" ht="20" customHeight="1">
@@ -12128,7 +12128,7 @@
         </is>
       </c>
       <c r="E444" s="20" t="n">
-        <v>134</v>
+        <v>155</v>
       </c>
     </row>
     <row r="445" ht="20" customHeight="1">
@@ -12153,7 +12153,7 @@
         </is>
       </c>
       <c r="E445" s="23" t="n">
-        <v>167</v>
+        <v>161</v>
       </c>
     </row>
     <row r="446" ht="20" customHeight="1">
@@ -12178,7 +12178,7 @@
         </is>
       </c>
       <c r="E446" s="20" t="n">
-        <v>192</v>
+        <v>136</v>
       </c>
     </row>
     <row r="447" ht="20" customHeight="1">
@@ -12203,7 +12203,7 @@
         </is>
       </c>
       <c r="E447" s="23" t="n">
-        <v>121</v>
+        <v>238</v>
       </c>
     </row>
     <row r="448" ht="20" customHeight="1">
@@ -12228,7 +12228,7 @@
         </is>
       </c>
       <c r="E448" s="20" t="n">
-        <v>235</v>
+        <v>116</v>
       </c>
     </row>
     <row r="449" ht="20" customHeight="1">
@@ -12253,7 +12253,7 @@
         </is>
       </c>
       <c r="E449" s="23" t="n">
-        <v>133</v>
+        <v>204</v>
       </c>
     </row>
     <row r="450" ht="20" customHeight="1">
@@ -12278,7 +12278,7 @@
         </is>
       </c>
       <c r="E450" s="20" t="n">
-        <v>165</v>
+        <v>224</v>
       </c>
     </row>
     <row r="451" ht="20" customHeight="1">
@@ -12303,7 +12303,7 @@
         </is>
       </c>
       <c r="E451" s="23" t="n">
-        <v>126</v>
+        <v>232</v>
       </c>
     </row>
     <row r="452" ht="20" customHeight="1">
@@ -12328,7 +12328,7 @@
         </is>
       </c>
       <c r="E452" s="20" t="n">
-        <v>239</v>
+        <v>198</v>
       </c>
     </row>
     <row r="453" ht="20" customHeight="1">
@@ -12353,7 +12353,7 @@
         </is>
       </c>
       <c r="E453" s="23" t="n">
-        <v>181</v>
+        <v>158</v>
       </c>
     </row>
     <row r="454" ht="20" customHeight="1">
@@ -12378,7 +12378,7 @@
         </is>
       </c>
       <c r="E454" s="20" t="n">
-        <v>112</v>
+        <v>137</v>
       </c>
     </row>
     <row r="455" ht="20" customHeight="1">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="E455" s="23" t="n">
-        <v>141</v>
+        <v>180</v>
       </c>
     </row>
     <row r="456" ht="20" customHeight="1">
@@ -12428,7 +12428,7 @@
         </is>
       </c>
       <c r="E456" s="20" t="n">
-        <v>215</v>
+        <v>158</v>
       </c>
     </row>
     <row r="457" ht="20" customHeight="1">
@@ -12453,7 +12453,7 @@
         </is>
       </c>
       <c r="E457" s="23" t="n">
-        <v>232</v>
+        <v>240</v>
       </c>
     </row>
     <row r="458" ht="20" customHeight="1">
@@ -12478,7 +12478,7 @@
         </is>
       </c>
       <c r="E458" s="20" t="n">
-        <v>187</v>
+        <v>217</v>
       </c>
     </row>
     <row r="459" ht="20" customHeight="1">
@@ -12503,7 +12503,7 @@
         </is>
       </c>
       <c r="E459" s="23" t="n">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="460" ht="20" customHeight="1">
@@ -12528,7 +12528,7 @@
         </is>
       </c>
       <c r="E460" s="20" t="n">
-        <v>113</v>
+        <v>193</v>
       </c>
     </row>
     <row r="461" ht="20" customHeight="1">
@@ -12553,7 +12553,7 @@
         </is>
       </c>
       <c r="E461" s="23" t="n">
-        <v>152</v>
+        <v>194</v>
       </c>
     </row>
     <row r="462" ht="20" customHeight="1">
@@ -12578,7 +12578,7 @@
         </is>
       </c>
       <c r="E462" s="20" t="n">
-        <v>142</v>
+        <v>237</v>
       </c>
     </row>
     <row r="463" ht="20" customHeight="1">
@@ -12603,7 +12603,7 @@
         </is>
       </c>
       <c r="E463" s="23" t="n">
-        <v>110</v>
+        <v>160</v>
       </c>
     </row>
     <row r="464" ht="20" customHeight="1">
@@ -12628,7 +12628,7 @@
         </is>
       </c>
       <c r="E464" s="20" t="n">
-        <v>154</v>
+        <v>199</v>
       </c>
     </row>
     <row r="465" ht="20" customHeight="1">
@@ -12653,7 +12653,7 @@
         </is>
       </c>
       <c r="E465" s="23" t="n">
-        <v>160</v>
+        <v>216</v>
       </c>
     </row>
     <row r="466" ht="20" customHeight="1">
@@ -12678,7 +12678,7 @@
         </is>
       </c>
       <c r="E466" s="20" t="n">
-        <v>156</v>
+        <v>202</v>
       </c>
     </row>
     <row r="467" ht="20" customHeight="1">
@@ -12703,7 +12703,7 @@
         </is>
       </c>
       <c r="E467" s="23" t="n">
-        <v>217</v>
+        <v>228</v>
       </c>
     </row>
     <row r="468" ht="20" customHeight="1">
@@ -12728,7 +12728,7 @@
         </is>
       </c>
       <c r="E468" s="20" t="n">
-        <v>141</v>
+        <v>180</v>
       </c>
     </row>
     <row r="469" ht="20" customHeight="1">
@@ -12753,7 +12753,7 @@
         </is>
       </c>
       <c r="E469" s="23" t="n">
-        <v>147</v>
+        <v>214</v>
       </c>
     </row>
     <row r="470" ht="20" customHeight="1">
@@ -12778,7 +12778,7 @@
         </is>
       </c>
       <c r="E470" s="20" t="n">
-        <v>168</v>
+        <v>131</v>
       </c>
     </row>
     <row r="471" ht="20" customHeight="1">
@@ -12803,7 +12803,7 @@
         </is>
       </c>
       <c r="E471" s="23" t="n">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="472" ht="20" customHeight="1">
@@ -12828,7 +12828,7 @@
         </is>
       </c>
       <c r="E472" s="20" t="n">
-        <v>119</v>
+        <v>237</v>
       </c>
     </row>
     <row r="473" ht="20" customHeight="1">
@@ -12853,7 +12853,7 @@
         </is>
       </c>
       <c r="E473" s="23" t="n">
-        <v>240</v>
+        <v>140</v>
       </c>
     </row>
     <row r="474" ht="20" customHeight="1">
@@ -12878,7 +12878,7 @@
         </is>
       </c>
       <c r="E474" s="20" t="n">
-        <v>159</v>
+        <v>183</v>
       </c>
     </row>
     <row r="475" ht="20" customHeight="1">
@@ -12903,7 +12903,7 @@
         </is>
       </c>
       <c r="E475" s="23" t="n">
-        <v>189</v>
+        <v>225</v>
       </c>
     </row>
     <row r="476" ht="20" customHeight="1">
@@ -12928,7 +12928,7 @@
         </is>
       </c>
       <c r="E476" s="20" t="n">
-        <v>164</v>
+        <v>234</v>
       </c>
     </row>
     <row r="477" ht="20" customHeight="1">
@@ -12953,7 +12953,7 @@
         </is>
       </c>
       <c r="E477" s="23" t="n">
-        <v>227</v>
+        <v>212</v>
       </c>
     </row>
     <row r="478" ht="20" customHeight="1">
@@ -12978,7 +12978,7 @@
         </is>
       </c>
       <c r="E478" s="20" t="n">
-        <v>139</v>
+        <v>153</v>
       </c>
     </row>
     <row r="479" ht="20" customHeight="1">
@@ -13003,7 +13003,7 @@
         </is>
       </c>
       <c r="E479" s="23" t="n">
-        <v>129</v>
+        <v>211</v>
       </c>
     </row>
     <row r="480" ht="20" customHeight="1">
@@ -13028,7 +13028,7 @@
         </is>
       </c>
       <c r="E480" s="20" t="n">
-        <v>237</v>
+        <v>116</v>
       </c>
     </row>
     <row r="481" ht="20" customHeight="1">
@@ -13078,7 +13078,7 @@
         </is>
       </c>
       <c r="E482" s="20" t="n">
-        <v>157</v>
+        <v>221</v>
       </c>
     </row>
     <row r="483" ht="20" customHeight="1">
@@ -13103,7 +13103,7 @@
         </is>
       </c>
       <c r="E483" s="23" t="n">
-        <v>189</v>
+        <v>111</v>
       </c>
     </row>
     <row r="484" ht="20" customHeight="1">
@@ -13128,7 +13128,7 @@
         </is>
       </c>
       <c r="E484" s="20" t="n">
-        <v>134</v>
+        <v>116</v>
       </c>
     </row>
     <row r="485" ht="20" customHeight="1">
@@ -13153,7 +13153,7 @@
         </is>
       </c>
       <c r="E485" s="23" t="n">
-        <v>195</v>
+        <v>137</v>
       </c>
     </row>
     <row r="486" ht="20" customHeight="1">
@@ -13178,7 +13178,7 @@
         </is>
       </c>
       <c r="E486" s="20" t="n">
-        <v>159</v>
+        <v>227</v>
       </c>
     </row>
     <row r="487" ht="20" customHeight="1">
@@ -13203,7 +13203,7 @@
         </is>
       </c>
       <c r="E487" s="23" t="n">
-        <v>214</v>
+        <v>195</v>
       </c>
     </row>
     <row r="488" ht="20" customHeight="1">
@@ -13228,7 +13228,7 @@
         </is>
       </c>
       <c r="E488" s="20" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
     </row>
     <row r="489" ht="20" customHeight="1">
@@ -13253,7 +13253,7 @@
         </is>
       </c>
       <c r="E489" s="23" t="n">
-        <v>219</v>
+        <v>161</v>
       </c>
     </row>
     <row r="490" ht="20" customHeight="1">
@@ -13278,7 +13278,7 @@
         </is>
       </c>
       <c r="E490" s="20" t="n">
-        <v>120</v>
+        <v>111</v>
       </c>
     </row>
     <row r="491" ht="20" customHeight="1">
@@ -13303,7 +13303,7 @@
         </is>
       </c>
       <c r="E491" s="23" t="n">
-        <v>195</v>
+        <v>172</v>
       </c>
     </row>
     <row r="492" ht="20" customHeight="1">
@@ -13328,7 +13328,7 @@
         </is>
       </c>
       <c r="E492" s="20" t="n">
-        <v>146</v>
+        <v>114</v>
       </c>
     </row>
     <row r="493" ht="20" customHeight="1">
@@ -13353,7 +13353,7 @@
         </is>
       </c>
       <c r="E493" s="23" t="n">
-        <v>223</v>
+        <v>184</v>
       </c>
     </row>
     <row r="494" ht="20" customHeight="1">
@@ -13378,7 +13378,7 @@
         </is>
       </c>
       <c r="E494" s="20" t="n">
-        <v>183</v>
+        <v>217</v>
       </c>
     </row>
     <row r="495" ht="20" customHeight="1">
@@ -13403,7 +13403,7 @@
         </is>
       </c>
       <c r="E495" s="23" t="n">
-        <v>146</v>
+        <v>217</v>
       </c>
     </row>
     <row r="496" ht="20" customHeight="1">
@@ -13428,7 +13428,7 @@
         </is>
       </c>
       <c r="E496" s="20" t="n">
-        <v>194</v>
+        <v>134</v>
       </c>
     </row>
     <row r="497" ht="20" customHeight="1">
@@ -13453,7 +13453,7 @@
         </is>
       </c>
       <c r="E497" s="23" t="n">
-        <v>162</v>
+        <v>177</v>
       </c>
     </row>
     <row r="498" ht="20" customHeight="1">
@@ -13478,7 +13478,7 @@
         </is>
       </c>
       <c r="E498" s="20" t="n">
-        <v>155</v>
+        <v>235</v>
       </c>
     </row>
     <row r="499" ht="20" customHeight="1">
@@ -13503,7 +13503,7 @@
         </is>
       </c>
       <c r="E499" s="23" t="n">
-        <v>235</v>
+        <v>137</v>
       </c>
     </row>
     <row r="500" ht="20" customHeight="1">
@@ -13528,7 +13528,7 @@
         </is>
       </c>
       <c r="E500" s="20" t="n">
-        <v>186</v>
+        <v>140</v>
       </c>
     </row>
     <row r="501" ht="20" customHeight="1">
@@ -13553,7 +13553,7 @@
         </is>
       </c>
       <c r="E501" s="23" t="n">
-        <v>232</v>
+        <v>220</v>
       </c>
     </row>
     <row r="502" ht="20" customHeight="1">
@@ -13578,7 +13578,7 @@
         </is>
       </c>
       <c r="E502" s="20" t="n">
-        <v>181</v>
+        <v>141</v>
       </c>
     </row>
     <row r="503" ht="20" customHeight="1">
@@ -13603,7 +13603,7 @@
         </is>
       </c>
       <c r="E503" s="23" t="n">
-        <v>208</v>
+        <v>118</v>
       </c>
     </row>
     <row r="504" ht="20" customHeight="1">
@@ -13628,7 +13628,7 @@
         </is>
       </c>
       <c r="E504" s="20" t="n">
-        <v>203</v>
+        <v>185</v>
       </c>
     </row>
     <row r="505" ht="20" customHeight="1">
@@ -13653,7 +13653,7 @@
         </is>
       </c>
       <c r="E505" s="23" t="n">
-        <v>139</v>
+        <v>207</v>
       </c>
     </row>
     <row r="506" ht="20" customHeight="1">
@@ -13678,7 +13678,7 @@
         </is>
       </c>
       <c r="E506" s="20" t="n">
-        <v>190</v>
+        <v>136</v>
       </c>
     </row>
     <row r="507" ht="20" customHeight="1">
@@ -13703,7 +13703,7 @@
         </is>
       </c>
       <c r="E507" s="23" t="n">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="508" ht="20" customHeight="1">
@@ -13728,7 +13728,7 @@
         </is>
       </c>
       <c r="E508" s="20" t="n">
-        <v>152</v>
+        <v>229</v>
       </c>
     </row>
     <row r="509" ht="20" customHeight="1">
@@ -13753,7 +13753,7 @@
         </is>
       </c>
       <c r="E509" s="23" t="n">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="510" ht="20" customHeight="1">
@@ -13778,7 +13778,7 @@
         </is>
       </c>
       <c r="E510" s="20" t="n">
-        <v>239</v>
+        <v>165</v>
       </c>
     </row>
     <row r="511" ht="20" customHeight="1">
@@ -13803,7 +13803,7 @@
         </is>
       </c>
       <c r="E511" s="23" t="n">
-        <v>168</v>
+        <v>131</v>
       </c>
     </row>
     <row r="512" ht="20" customHeight="1">
@@ -13828,7 +13828,7 @@
         </is>
       </c>
       <c r="E512" s="20" t="n">
-        <v>110</v>
+        <v>218</v>
       </c>
     </row>
     <row r="513" ht="20" customHeight="1">
@@ -13853,7 +13853,7 @@
         </is>
       </c>
       <c r="E513" s="23" t="n">
-        <v>120</v>
+        <v>202</v>
       </c>
     </row>
     <row r="514" ht="20" customHeight="1">
@@ -13878,7 +13878,7 @@
         </is>
       </c>
       <c r="E514" s="20" t="n">
-        <v>175</v>
+        <v>235</v>
       </c>
     </row>
     <row r="515" ht="20" customHeight="1">
@@ -13903,7 +13903,7 @@
         </is>
       </c>
       <c r="E515" s="23" t="n">
-        <v>224</v>
+        <v>178</v>
       </c>
     </row>
     <row r="516" ht="20" customHeight="1">
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="E516" s="20" t="n">
-        <v>236</v>
+        <v>162</v>
       </c>
     </row>
     <row r="517" ht="20" customHeight="1">
@@ -13953,7 +13953,7 @@
         </is>
       </c>
       <c r="E517" s="23" t="n">
-        <v>125</v>
+        <v>169</v>
       </c>
     </row>
     <row r="518" ht="20" customHeight="1">
@@ -13978,7 +13978,7 @@
         </is>
       </c>
       <c r="E518" s="20" t="n">
-        <v>194</v>
+        <v>127</v>
       </c>
     </row>
     <row r="519" ht="20" customHeight="1">
@@ -14003,7 +14003,7 @@
         </is>
       </c>
       <c r="E519" s="23" t="n">
-        <v>175</v>
+        <v>147</v>
       </c>
     </row>
     <row r="520" ht="20" customHeight="1">
@@ -14028,7 +14028,7 @@
         </is>
       </c>
       <c r="E520" s="20" t="n">
-        <v>236</v>
+        <v>124</v>
       </c>
     </row>
     <row r="521" ht="20" customHeight="1">
@@ -14053,7 +14053,7 @@
         </is>
       </c>
       <c r="E521" s="23" t="n">
-        <v>158</v>
+        <v>132</v>
       </c>
     </row>
     <row r="522" ht="20" customHeight="1">
@@ -14078,7 +14078,7 @@
         </is>
       </c>
       <c r="E522" s="20" t="n">
-        <v>229</v>
+        <v>221</v>
       </c>
     </row>
     <row r="523" ht="20" customHeight="1">
@@ -14103,7 +14103,7 @@
         </is>
       </c>
       <c r="E523" s="23" t="n">
-        <v>155</v>
+        <v>111</v>
       </c>
     </row>
     <row r="524" ht="20" customHeight="1">
@@ -14128,7 +14128,7 @@
         </is>
       </c>
       <c r="E524" s="20" t="n">
-        <v>212</v>
+        <v>217</v>
       </c>
     </row>
     <row r="525" ht="20" customHeight="1">
@@ -14153,7 +14153,7 @@
         </is>
       </c>
       <c r="E525" s="23" t="n">
-        <v>162</v>
+        <v>176</v>
       </c>
     </row>
     <row r="526" ht="20" customHeight="1">
@@ -14178,7 +14178,7 @@
         </is>
       </c>
       <c r="E526" s="20" t="n">
-        <v>158</v>
+        <v>217</v>
       </c>
     </row>
     <row r="527" ht="20" customHeight="1">
@@ -14203,7 +14203,7 @@
         </is>
       </c>
       <c r="E527" s="23" t="n">
-        <v>183</v>
+        <v>137</v>
       </c>
     </row>
     <row r="528" ht="20" customHeight="1">
@@ -14228,7 +14228,7 @@
         </is>
       </c>
       <c r="E528" s="20" t="n">
-        <v>134</v>
+        <v>205</v>
       </c>
     </row>
     <row r="529" ht="20" customHeight="1">
@@ -14253,7 +14253,7 @@
         </is>
       </c>
       <c r="E529" s="23" t="n">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="530" ht="20" customHeight="1">
@@ -14278,7 +14278,7 @@
         </is>
       </c>
       <c r="E530" s="20" t="n">
-        <v>234</v>
+        <v>147</v>
       </c>
     </row>
     <row r="531" ht="20" customHeight="1">
@@ -14303,7 +14303,7 @@
         </is>
       </c>
       <c r="E531" s="23" t="n">
-        <v>220</v>
+        <v>137</v>
       </c>
     </row>
     <row r="532" ht="20" customHeight="1">
@@ -14328,7 +14328,7 @@
         </is>
       </c>
       <c r="E532" s="20" t="n">
-        <v>127</v>
+        <v>161</v>
       </c>
     </row>
     <row r="533" ht="20" customHeight="1">
@@ -14353,7 +14353,7 @@
         </is>
       </c>
       <c r="E533" s="23" t="n">
-        <v>119</v>
+        <v>144</v>
       </c>
     </row>
     <row r="534" ht="20" customHeight="1">
@@ -14378,7 +14378,7 @@
         </is>
       </c>
       <c r="E534" s="20" t="n">
-        <v>123</v>
+        <v>159</v>
       </c>
     </row>
     <row r="535" ht="20" customHeight="1">
@@ -14403,7 +14403,7 @@
         </is>
       </c>
       <c r="E535" s="23" t="n">
-        <v>121</v>
+        <v>185</v>
       </c>
     </row>
     <row r="536" ht="20" customHeight="1">
@@ -14428,7 +14428,7 @@
         </is>
       </c>
       <c r="E536" s="20" t="n">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="537" ht="20" customHeight="1">
@@ -14453,7 +14453,7 @@
         </is>
       </c>
       <c r="E537" s="23" t="n">
-        <v>155</v>
+        <v>187</v>
       </c>
     </row>
     <row r="538" ht="20" customHeight="1">
@@ -14478,7 +14478,7 @@
         </is>
       </c>
       <c r="E538" s="20" t="n">
-        <v>147</v>
+        <v>164</v>
       </c>
     </row>
     <row r="539" ht="20" customHeight="1">
@@ -14503,7 +14503,7 @@
         </is>
       </c>
       <c r="E539" s="23" t="n">
-        <v>228</v>
+        <v>143</v>
       </c>
     </row>
     <row r="540" ht="20" customHeight="1">
@@ -14528,7 +14528,7 @@
         </is>
       </c>
       <c r="E540" s="20" t="n">
-        <v>230</v>
+        <v>194</v>
       </c>
     </row>
     <row r="541" ht="20" customHeight="1">
@@ -14553,7 +14553,7 @@
         </is>
       </c>
       <c r="E541" s="23" t="n">
-        <v>146</v>
+        <v>236</v>
       </c>
     </row>
     <row r="542" ht="20" customHeight="1">
@@ -14578,7 +14578,7 @@
         </is>
       </c>
       <c r="E542" s="20" t="n">
-        <v>205</v>
+        <v>200</v>
       </c>
     </row>
     <row r="543" ht="20" customHeight="1">
@@ -14603,7 +14603,7 @@
         </is>
       </c>
       <c r="E543" s="23" t="n">
-        <v>148</v>
+        <v>110</v>
       </c>
     </row>
     <row r="544" ht="20" customHeight="1">
@@ -14628,7 +14628,7 @@
         </is>
       </c>
       <c r="E544" s="20" t="n">
-        <v>200</v>
+        <v>178</v>
       </c>
     </row>
     <row r="545" ht="20" customHeight="1">
@@ -14653,7 +14653,7 @@
         </is>
       </c>
       <c r="E545" s="23" t="n">
-        <v>198</v>
+        <v>160</v>
       </c>
     </row>
     <row r="546" ht="20" customHeight="1">
@@ -14678,7 +14678,7 @@
         </is>
       </c>
       <c r="E546" s="20" t="n">
-        <v>172</v>
+        <v>206</v>
       </c>
     </row>
     <row r="547" ht="20" customHeight="1">
@@ -14703,7 +14703,7 @@
         </is>
       </c>
       <c r="E547" s="23" t="n">
-        <v>148</v>
+        <v>207</v>
       </c>
     </row>
     <row r="548" ht="20" customHeight="1">
@@ -14728,7 +14728,7 @@
         </is>
       </c>
       <c r="E548" s="20" t="n">
-        <v>221</v>
+        <v>143</v>
       </c>
     </row>
     <row r="549" ht="20" customHeight="1">
@@ -14753,7 +14753,7 @@
         </is>
       </c>
       <c r="E549" s="23" t="n">
-        <v>136</v>
+        <v>113</v>
       </c>
     </row>
     <row r="550" ht="20" customHeight="1">
@@ -14778,7 +14778,7 @@
         </is>
       </c>
       <c r="E550" s="20" t="n">
-        <v>163</v>
+        <v>121</v>
       </c>
     </row>
     <row r="551" ht="20" customHeight="1">
@@ -14803,7 +14803,7 @@
         </is>
       </c>
       <c r="E551" s="23" t="n">
-        <v>233</v>
+        <v>172</v>
       </c>
     </row>
     <row r="552" ht="20" customHeight="1">
@@ -14828,7 +14828,7 @@
         </is>
       </c>
       <c r="E552" s="20" t="n">
-        <v>176</v>
+        <v>131</v>
       </c>
     </row>
     <row r="553" ht="20" customHeight="1">
@@ -14853,7 +14853,7 @@
         </is>
       </c>
       <c r="E553" s="23" t="n">
-        <v>180</v>
+        <v>118</v>
       </c>
     </row>
     <row r="554" ht="20" customHeight="1">
@@ -14878,7 +14878,7 @@
         </is>
       </c>
       <c r="E554" s="20" t="n">
-        <v>145</v>
+        <v>193</v>
       </c>
     </row>
     <row r="555" ht="20" customHeight="1">
@@ -14903,7 +14903,7 @@
         </is>
       </c>
       <c r="E555" s="23" t="n">
-        <v>198</v>
+        <v>149</v>
       </c>
     </row>
     <row r="556" ht="20" customHeight="1">
@@ -14928,7 +14928,7 @@
         </is>
       </c>
       <c r="E556" s="20" t="n">
-        <v>140</v>
+        <v>167</v>
       </c>
     </row>
     <row r="557" ht="20" customHeight="1">
@@ -14953,7 +14953,7 @@
         </is>
       </c>
       <c r="E557" s="23" t="n">
-        <v>112</v>
+        <v>152</v>
       </c>
     </row>
     <row r="558" ht="20" customHeight="1">
@@ -14978,7 +14978,7 @@
         </is>
       </c>
       <c r="E558" s="20" t="n">
-        <v>130</v>
+        <v>161</v>
       </c>
     </row>
     <row r="559" ht="20" customHeight="1">
@@ -15003,7 +15003,7 @@
         </is>
       </c>
       <c r="E559" s="23" t="n">
-        <v>167</v>
+        <v>119</v>
       </c>
     </row>
     <row r="560" ht="20" customHeight="1">
@@ -15028,7 +15028,7 @@
         </is>
       </c>
       <c r="E560" s="20" t="n">
-        <v>217</v>
+        <v>153</v>
       </c>
     </row>
     <row r="561" ht="20" customHeight="1">
@@ -15053,7 +15053,7 @@
         </is>
       </c>
       <c r="E561" s="23" t="n">
-        <v>160</v>
+        <v>133</v>
       </c>
     </row>
     <row r="562" ht="20" customHeight="1">
@@ -15078,7 +15078,7 @@
         </is>
       </c>
       <c r="E562" s="20" t="n">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="563" ht="20" customHeight="1">
@@ -15103,7 +15103,7 @@
         </is>
       </c>
       <c r="E563" s="23" t="n">
-        <v>134</v>
+        <v>197</v>
       </c>
     </row>
     <row r="564" ht="20" customHeight="1">
@@ -15128,7 +15128,7 @@
         </is>
       </c>
       <c r="E564" s="20" t="n">
-        <v>218</v>
+        <v>140</v>
       </c>
     </row>
     <row r="565" ht="20" customHeight="1">
@@ -15153,7 +15153,7 @@
         </is>
       </c>
       <c r="E565" s="23" t="n">
-        <v>198</v>
+        <v>157</v>
       </c>
     </row>
     <row r="566" ht="20" customHeight="1">
@@ -15178,7 +15178,7 @@
         </is>
       </c>
       <c r="E566" s="20" t="n">
-        <v>195</v>
+        <v>126</v>
       </c>
     </row>
     <row r="567" ht="20" customHeight="1">
@@ -15203,7 +15203,7 @@
         </is>
       </c>
       <c r="E567" s="23" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="568" ht="20" customHeight="1">
@@ -15228,7 +15228,7 @@
         </is>
       </c>
       <c r="E568" s="20" t="n">
-        <v>144</v>
+        <v>173</v>
       </c>
     </row>
     <row r="569" ht="20" customHeight="1">
@@ -15253,7 +15253,7 @@
         </is>
       </c>
       <c r="E569" s="23" t="n">
-        <v>220</v>
+        <v>184</v>
       </c>
     </row>
     <row r="570" ht="20" customHeight="1">
@@ -15278,7 +15278,7 @@
         </is>
       </c>
       <c r="E570" s="20" t="n">
-        <v>179</v>
+        <v>121</v>
       </c>
     </row>
     <row r="571" ht="20" customHeight="1">
@@ -15303,7 +15303,7 @@
         </is>
       </c>
       <c r="E571" s="23" t="n">
-        <v>239</v>
+        <v>144</v>
       </c>
     </row>
     <row r="572" ht="20" customHeight="1">
@@ -15328,7 +15328,7 @@
         </is>
       </c>
       <c r="E572" s="20" t="n">
-        <v>177</v>
+        <v>164</v>
       </c>
     </row>
     <row r="573" ht="20" customHeight="1">
@@ -15353,7 +15353,7 @@
         </is>
       </c>
       <c r="E573" s="23" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="574" ht="20" customHeight="1">
@@ -15378,7 +15378,7 @@
         </is>
       </c>
       <c r="E574" s="20" t="n">
-        <v>139</v>
+        <v>150</v>
       </c>
     </row>
     <row r="575" ht="20" customHeight="1">
@@ -15403,7 +15403,7 @@
         </is>
       </c>
       <c r="E575" s="23" t="n">
-        <v>168</v>
+        <v>237</v>
       </c>
     </row>
     <row r="576" ht="20" customHeight="1">
@@ -15428,7 +15428,7 @@
         </is>
       </c>
       <c r="E576" s="20" t="n">
-        <v>120</v>
+        <v>190</v>
       </c>
     </row>
     <row r="577" ht="20" customHeight="1">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="E577" s="23" t="n">
-        <v>233</v>
+        <v>219</v>
       </c>
     </row>
     <row r="578" ht="20" customHeight="1">
@@ -15478,7 +15478,7 @@
         </is>
       </c>
       <c r="E578" s="20" t="n">
-        <v>125</v>
+        <v>116</v>
       </c>
     </row>
     <row r="579" ht="20" customHeight="1">
@@ -15503,7 +15503,7 @@
         </is>
       </c>
       <c r="E579" s="23" t="n">
-        <v>138</v>
+        <v>188</v>
       </c>
     </row>
     <row r="580" ht="20" customHeight="1">
@@ -15528,7 +15528,7 @@
         </is>
       </c>
       <c r="E580" s="20" t="n">
-        <v>217</v>
+        <v>179</v>
       </c>
     </row>
     <row r="581" ht="20" customHeight="1">
@@ -15553,7 +15553,7 @@
         </is>
       </c>
       <c r="E581" s="23" t="n">
-        <v>179</v>
+        <v>217</v>
       </c>
     </row>
     <row r="582" ht="20" customHeight="1">
@@ -15578,7 +15578,7 @@
         </is>
       </c>
       <c r="E582" s="20" t="n">
-        <v>201</v>
+        <v>236</v>
       </c>
     </row>
     <row r="583" ht="20" customHeight="1">
@@ -15603,7 +15603,7 @@
         </is>
       </c>
       <c r="E583" s="23" t="n">
-        <v>157</v>
+        <v>142</v>
       </c>
     </row>
     <row r="584" ht="20" customHeight="1">
@@ -15628,7 +15628,7 @@
         </is>
       </c>
       <c r="E584" s="20" t="n">
-        <v>135</v>
+        <v>126</v>
       </c>
     </row>
     <row r="585" ht="20" customHeight="1">
@@ -15653,7 +15653,7 @@
         </is>
       </c>
       <c r="E585" s="23" t="n">
-        <v>230</v>
+        <v>224</v>
       </c>
     </row>
     <row r="586" ht="20" customHeight="1">
@@ -15678,7 +15678,7 @@
         </is>
       </c>
       <c r="E586" s="20" t="n">
-        <v>120</v>
+        <v>199</v>
       </c>
     </row>
     <row r="587" ht="20" customHeight="1">
@@ -15703,7 +15703,7 @@
         </is>
       </c>
       <c r="E587" s="23" t="n">
-        <v>178</v>
+        <v>208</v>
       </c>
     </row>
     <row r="588" ht="20" customHeight="1">
@@ -15728,7 +15728,7 @@
         </is>
       </c>
       <c r="E588" s="20" t="n">
-        <v>185</v>
+        <v>119</v>
       </c>
     </row>
     <row r="589" ht="20" customHeight="1">
@@ -15753,7 +15753,7 @@
         </is>
       </c>
       <c r="E589" s="23" t="n">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="590" ht="20" customHeight="1">
@@ -15778,7 +15778,7 @@
         </is>
       </c>
       <c r="E590" s="20" t="n">
-        <v>179</v>
+        <v>187</v>
       </c>
     </row>
     <row r="591" ht="20" customHeight="1">
@@ -15803,7 +15803,7 @@
         </is>
       </c>
       <c r="E591" s="23" t="n">
-        <v>219</v>
+        <v>175</v>
       </c>
     </row>
     <row r="592" ht="20" customHeight="1">
@@ -15828,7 +15828,7 @@
         </is>
       </c>
       <c r="E592" s="20" t="n">
-        <v>203</v>
+        <v>213</v>
       </c>
     </row>
     <row r="593" ht="20" customHeight="1">
@@ -15853,7 +15853,7 @@
         </is>
       </c>
       <c r="E593" s="23" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="594" ht="20" customHeight="1">
@@ -15878,7 +15878,7 @@
         </is>
       </c>
       <c r="E594" s="20" t="n">
-        <v>152</v>
+        <v>222</v>
       </c>
     </row>
     <row r="595" ht="20" customHeight="1">
@@ -15903,7 +15903,7 @@
         </is>
       </c>
       <c r="E595" s="23" t="n">
-        <v>156</v>
+        <v>114</v>
       </c>
     </row>
     <row r="596" ht="20" customHeight="1">
@@ -15928,7 +15928,7 @@
         </is>
       </c>
       <c r="E596" s="20" t="n">
-        <v>195</v>
+        <v>148</v>
       </c>
     </row>
     <row r="597" ht="20" customHeight="1">
@@ -15953,7 +15953,7 @@
         </is>
       </c>
       <c r="E597" s="23" t="n">
-        <v>151</v>
+        <v>130</v>
       </c>
     </row>
     <row r="598" ht="20" customHeight="1">
@@ -15978,7 +15978,7 @@
         </is>
       </c>
       <c r="E598" s="20" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="599" ht="20" customHeight="1">
@@ -16003,7 +16003,7 @@
         </is>
       </c>
       <c r="E599" s="23" t="n">
-        <v>186</v>
+        <v>195</v>
       </c>
     </row>
     <row r="600" ht="20" customHeight="1">
@@ -16028,7 +16028,7 @@
         </is>
       </c>
       <c r="E600" s="20" t="n">
-        <v>177</v>
+        <v>191</v>
       </c>
     </row>
     <row r="601" ht="20" customHeight="1">
@@ -16053,7 +16053,7 @@
         </is>
       </c>
       <c r="E601" s="23" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="602" ht="20" customHeight="1">
@@ -16078,7 +16078,7 @@
         </is>
       </c>
       <c r="E602" s="20" t="n">
-        <v>115</v>
+        <v>185</v>
       </c>
     </row>
     <row r="603" ht="20" customHeight="1">
@@ -16103,7 +16103,7 @@
         </is>
       </c>
       <c r="E603" s="23" t="n">
-        <v>134</v>
+        <v>179</v>
       </c>
     </row>
     <row r="604" ht="20" customHeight="1">
@@ -16128,7 +16128,7 @@
         </is>
       </c>
       <c r="E604" s="20" t="n">
-        <v>225</v>
+        <v>162</v>
       </c>
     </row>
     <row r="605" ht="20" customHeight="1">
@@ -16153,7 +16153,7 @@
         </is>
       </c>
       <c r="E605" s="23" t="n">
-        <v>116</v>
+        <v>237</v>
       </c>
     </row>
     <row r="606" ht="20" customHeight="1">
@@ -16178,7 +16178,7 @@
         </is>
       </c>
       <c r="E606" s="20" t="n">
-        <v>168</v>
+        <v>207</v>
       </c>
     </row>
     <row r="607" ht="20" customHeight="1">
@@ -16203,7 +16203,7 @@
         </is>
       </c>
       <c r="E607" s="23" t="n">
-        <v>130</v>
+        <v>238</v>
       </c>
     </row>
     <row r="608" ht="20" customHeight="1">
@@ -16228,7 +16228,7 @@
         </is>
       </c>
       <c r="E608" s="20" t="n">
-        <v>183</v>
+        <v>176</v>
       </c>
     </row>
     <row r="609" ht="20" customHeight="1">
@@ -16253,7 +16253,7 @@
         </is>
       </c>
       <c r="E609" s="23" t="n">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="610" ht="20" customHeight="1">
@@ -16278,7 +16278,7 @@
         </is>
       </c>
       <c r="E610" s="20" t="n">
-        <v>201</v>
+        <v>210</v>
       </c>
     </row>
     <row r="611" ht="20" customHeight="1">
@@ -16303,7 +16303,7 @@
         </is>
       </c>
       <c r="E611" s="23" t="n">
-        <v>163</v>
+        <v>224</v>
       </c>
     </row>
     <row r="612" ht="20" customHeight="1">
@@ -16328,7 +16328,7 @@
         </is>
       </c>
       <c r="E612" s="20" t="n">
-        <v>163</v>
+        <v>126</v>
       </c>
     </row>
     <row r="613" ht="20" customHeight="1">
@@ -16353,7 +16353,7 @@
         </is>
       </c>
       <c r="E613" s="23" t="n">
-        <v>149</v>
+        <v>193</v>
       </c>
     </row>
     <row r="614" ht="20" customHeight="1">
@@ -16378,7 +16378,7 @@
         </is>
       </c>
       <c r="E614" s="20" t="n">
-        <v>177</v>
+        <v>224</v>
       </c>
     </row>
     <row r="615" ht="20" customHeight="1">
@@ -16403,7 +16403,7 @@
         </is>
       </c>
       <c r="E615" s="23" t="n">
-        <v>183</v>
+        <v>118</v>
       </c>
     </row>
     <row r="616" ht="20" customHeight="1">
@@ -16428,7 +16428,7 @@
         </is>
       </c>
       <c r="E616" s="20" t="n">
-        <v>131</v>
+        <v>150</v>
       </c>
     </row>
     <row r="617" ht="20" customHeight="1">
@@ -16453,7 +16453,7 @@
         </is>
       </c>
       <c r="E617" s="23" t="n">
-        <v>207</v>
+        <v>110</v>
       </c>
     </row>
     <row r="618" ht="20" customHeight="1">
@@ -16478,7 +16478,7 @@
         </is>
       </c>
       <c r="E618" s="20" t="n">
-        <v>206</v>
+        <v>151</v>
       </c>
     </row>
     <row r="619" ht="20" customHeight="1">
@@ -16503,7 +16503,7 @@
         </is>
       </c>
       <c r="E619" s="23" t="n">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="620" ht="20" customHeight="1">
@@ -16528,7 +16528,7 @@
         </is>
       </c>
       <c r="E620" s="20" t="n">
-        <v>119</v>
+        <v>155</v>
       </c>
     </row>
     <row r="621" ht="20" customHeight="1">
@@ -16553,7 +16553,7 @@
         </is>
       </c>
       <c r="E621" s="23" t="n">
-        <v>215</v>
+        <v>201</v>
       </c>
     </row>
     <row r="622" ht="20" customHeight="1">
@@ -16578,7 +16578,7 @@
         </is>
       </c>
       <c r="E622" s="20" t="n">
-        <v>117</v>
+        <v>183</v>
       </c>
     </row>
     <row r="623" ht="20" customHeight="1">
@@ -16603,7 +16603,7 @@
         </is>
       </c>
       <c r="E623" s="23" t="n">
-        <v>146</v>
+        <v>113</v>
       </c>
     </row>
     <row r="624" ht="20" customHeight="1">
@@ -16628,7 +16628,7 @@
         </is>
       </c>
       <c r="E624" s="20" t="n">
-        <v>225</v>
+        <v>152</v>
       </c>
     </row>
     <row r="625" ht="20" customHeight="1">
@@ -16653,7 +16653,7 @@
         </is>
       </c>
       <c r="E625" s="23" t="n">
-        <v>233</v>
+        <v>156</v>
       </c>
     </row>
     <row r="626" ht="20" customHeight="1">
@@ -16678,7 +16678,7 @@
         </is>
       </c>
       <c r="E626" s="20" t="n">
-        <v>235</v>
+        <v>192</v>
       </c>
     </row>
     <row r="627" ht="20" customHeight="1">
@@ -16703,7 +16703,7 @@
         </is>
       </c>
       <c r="E627" s="23" t="n">
-        <v>110</v>
+        <v>170</v>
       </c>
     </row>
     <row r="628" ht="20" customHeight="1">
@@ -16728,7 +16728,7 @@
         </is>
       </c>
       <c r="E628" s="20" t="n">
-        <v>178</v>
+        <v>112</v>
       </c>
     </row>
     <row r="629" ht="20" customHeight="1">
@@ -16753,7 +16753,7 @@
         </is>
       </c>
       <c r="E629" s="23" t="n">
-        <v>122</v>
+        <v>213</v>
       </c>
     </row>
     <row r="630" ht="20" customHeight="1">
@@ -16778,7 +16778,7 @@
         </is>
       </c>
       <c r="E630" s="20" t="n">
-        <v>164</v>
+        <v>113</v>
       </c>
     </row>
     <row r="631" ht="20" customHeight="1">
@@ -16803,7 +16803,7 @@
         </is>
       </c>
       <c r="E631" s="23" t="n">
-        <v>121</v>
+        <v>198</v>
       </c>
     </row>
     <row r="632" ht="20" customHeight="1">
@@ -16828,7 +16828,7 @@
         </is>
       </c>
       <c r="E632" s="20" t="n">
-        <v>175</v>
+        <v>163</v>
       </c>
     </row>
     <row r="633" ht="20" customHeight="1">
@@ -16853,7 +16853,7 @@
         </is>
       </c>
       <c r="E633" s="23" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="634" ht="20" customHeight="1">
@@ -16878,7 +16878,7 @@
         </is>
       </c>
       <c r="E634" s="20" t="n">
-        <v>194</v>
+        <v>113</v>
       </c>
     </row>
     <row r="635" ht="20" customHeight="1">
@@ -16903,7 +16903,7 @@
         </is>
       </c>
       <c r="E635" s="23" t="n">
-        <v>222</v>
+        <v>185</v>
       </c>
     </row>
     <row r="636" ht="20" customHeight="1">
@@ -16928,7 +16928,7 @@
         </is>
       </c>
       <c r="E636" s="20" t="n">
-        <v>125</v>
+        <v>144</v>
       </c>
     </row>
     <row r="637" ht="20" customHeight="1">
@@ -16953,7 +16953,7 @@
         </is>
       </c>
       <c r="E637" s="23" t="n">
-        <v>225</v>
+        <v>143</v>
       </c>
     </row>
     <row r="638" ht="20" customHeight="1">
@@ -16978,7 +16978,7 @@
         </is>
       </c>
       <c r="E638" s="20" t="n">
-        <v>117</v>
+        <v>152</v>
       </c>
     </row>
     <row r="639" ht="20" customHeight="1">
@@ -17003,7 +17003,7 @@
         </is>
       </c>
       <c r="E639" s="23" t="n">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="640" ht="20" customHeight="1">
@@ -17028,7 +17028,7 @@
         </is>
       </c>
       <c r="E640" s="20" t="n">
-        <v>196</v>
+        <v>147</v>
       </c>
     </row>
     <row r="641" ht="20" customHeight="1">
@@ -17053,7 +17053,7 @@
         </is>
       </c>
       <c r="E641" s="23" t="n">
-        <v>168</v>
+        <v>114</v>
       </c>
     </row>
     <row r="642" ht="20" customHeight="1">
@@ -17078,7 +17078,7 @@
         </is>
       </c>
       <c r="E642" s="20" t="n">
-        <v>223</v>
+        <v>235</v>
       </c>
     </row>
     <row r="643" ht="20" customHeight="1">
@@ -17103,7 +17103,7 @@
         </is>
       </c>
       <c r="E643" s="23" t="n">
-        <v>158</v>
+        <v>168</v>
       </c>
     </row>
     <row r="644" ht="20" customHeight="1">
@@ -17128,7 +17128,7 @@
         </is>
       </c>
       <c r="E644" s="20" t="n">
-        <v>197</v>
+        <v>190</v>
       </c>
     </row>
     <row r="645" ht="20" customHeight="1">
@@ -17153,7 +17153,7 @@
         </is>
       </c>
       <c r="E645" s="23" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="646" ht="20" customHeight="1">
@@ -17178,7 +17178,7 @@
         </is>
       </c>
       <c r="E646" s="20" t="n">
-        <v>198</v>
+        <v>178</v>
       </c>
     </row>
     <row r="647" ht="20" customHeight="1">
@@ -17203,7 +17203,7 @@
         </is>
       </c>
       <c r="E647" s="23" t="n">
-        <v>199</v>
+        <v>155</v>
       </c>
     </row>
     <row r="648" ht="20" customHeight="1">
@@ -17228,7 +17228,7 @@
         </is>
       </c>
       <c r="E648" s="20" t="n">
-        <v>141</v>
+        <v>174</v>
       </c>
     </row>
     <row r="649" ht="20" customHeight="1">
@@ -17253,7 +17253,7 @@
         </is>
       </c>
       <c r="E649" s="23" t="n">
-        <v>212</v>
+        <v>164</v>
       </c>
     </row>
     <row r="650" ht="20" customHeight="1">
@@ -17278,7 +17278,7 @@
         </is>
       </c>
       <c r="E650" s="20" t="n">
-        <v>117</v>
+        <v>218</v>
       </c>
     </row>
     <row r="651" ht="20" customHeight="1">
@@ -17303,7 +17303,7 @@
         </is>
       </c>
       <c r="E651" s="23" t="n">
-        <v>155</v>
+        <v>180</v>
       </c>
     </row>
     <row r="652" ht="20" customHeight="1">
@@ -17328,7 +17328,7 @@
         </is>
       </c>
       <c r="E652" s="20" t="n">
-        <v>165</v>
+        <v>120</v>
       </c>
     </row>
     <row r="653" ht="20" customHeight="1">
@@ -17353,7 +17353,7 @@
         </is>
       </c>
       <c r="E653" s="23" t="n">
-        <v>185</v>
+        <v>141</v>
       </c>
     </row>
     <row r="654" ht="20" customHeight="1">
@@ -17378,7 +17378,7 @@
         </is>
       </c>
       <c r="E654" s="20" t="n">
-        <v>208</v>
+        <v>137</v>
       </c>
     </row>
     <row r="655" ht="20" customHeight="1">
@@ -17403,7 +17403,7 @@
         </is>
       </c>
       <c r="E655" s="23" t="n">
-        <v>184</v>
+        <v>222</v>
       </c>
     </row>
     <row r="656" ht="20" customHeight="1">
@@ -17428,7 +17428,7 @@
         </is>
       </c>
       <c r="E656" s="20" t="n">
-        <v>141</v>
+        <v>195</v>
       </c>
     </row>
     <row r="657" ht="20" customHeight="1">
@@ -17453,7 +17453,7 @@
         </is>
       </c>
       <c r="E657" s="23" t="n">
-        <v>127</v>
+        <v>183</v>
       </c>
     </row>
     <row r="658" ht="20" customHeight="1">
@@ -17478,7 +17478,7 @@
         </is>
       </c>
       <c r="E658" s="20" t="n">
-        <v>200</v>
+        <v>221</v>
       </c>
     </row>
     <row r="659" ht="20" customHeight="1">
@@ -17503,7 +17503,7 @@
         </is>
       </c>
       <c r="E659" s="23" t="n">
-        <v>206</v>
+        <v>221</v>
       </c>
     </row>
     <row r="660" ht="20" customHeight="1">
@@ -17528,7 +17528,7 @@
         </is>
       </c>
       <c r="E660" s="20" t="n">
-        <v>188</v>
+        <v>153</v>
       </c>
     </row>
     <row r="661" ht="20" customHeight="1">
@@ -17553,7 +17553,7 @@
         </is>
       </c>
       <c r="E661" s="23" t="n">
-        <v>202</v>
+        <v>220</v>
       </c>
     </row>
     <row r="662" ht="20" customHeight="1">
@@ -17578,7 +17578,7 @@
         </is>
       </c>
       <c r="E662" s="20" t="n">
-        <v>197</v>
+        <v>120</v>
       </c>
     </row>
     <row r="663" ht="20" customHeight="1">
@@ -17603,7 +17603,7 @@
         </is>
       </c>
       <c r="E663" s="23" t="n">
-        <v>233</v>
+        <v>172</v>
       </c>
     </row>
     <row r="664" ht="20" customHeight="1">
@@ -17628,7 +17628,7 @@
         </is>
       </c>
       <c r="E664" s="20" t="n">
-        <v>189</v>
+        <v>124</v>
       </c>
     </row>
     <row r="665" ht="20" customHeight="1">
@@ -17653,7 +17653,7 @@
         </is>
       </c>
       <c r="E665" s="23" t="n">
-        <v>176</v>
+        <v>193</v>
       </c>
     </row>
     <row r="666" ht="20" customHeight="1">
@@ -17678,7 +17678,7 @@
         </is>
       </c>
       <c r="E666" s="20" t="n">
-        <v>224</v>
+        <v>176</v>
       </c>
     </row>
     <row r="667" ht="20" customHeight="1">
@@ -17703,7 +17703,7 @@
         </is>
       </c>
       <c r="E667" s="23" t="n">
-        <v>135</v>
+        <v>238</v>
       </c>
     </row>
     <row r="668" ht="20" customHeight="1">
@@ -17728,7 +17728,7 @@
         </is>
       </c>
       <c r="E668" s="20" t="n">
-        <v>233</v>
+        <v>197</v>
       </c>
     </row>
     <row r="669" ht="20" customHeight="1">
@@ -17753,7 +17753,7 @@
         </is>
       </c>
       <c r="E669" s="23" t="n">
-        <v>118</v>
+        <v>151</v>
       </c>
     </row>
     <row r="670" ht="20" customHeight="1">
@@ -17778,7 +17778,7 @@
         </is>
       </c>
       <c r="E670" s="20" t="n">
-        <v>154</v>
+        <v>145</v>
       </c>
     </row>
     <row r="671" ht="20" customHeight="1">
@@ -17803,7 +17803,7 @@
         </is>
       </c>
       <c r="E671" s="23" t="n">
-        <v>225</v>
+        <v>219</v>
       </c>
     </row>
     <row r="672" ht="20" customHeight="1">
@@ -17828,7 +17828,7 @@
         </is>
       </c>
       <c r="E672" s="20" t="n">
-        <v>203</v>
+        <v>147</v>
       </c>
     </row>
     <row r="673" ht="20" customHeight="1">
@@ -17853,7 +17853,7 @@
         </is>
       </c>
       <c r="E673" s="23" t="n">
-        <v>145</v>
+        <v>110</v>
       </c>
     </row>
     <row r="674" ht="20" customHeight="1">
@@ -17878,7 +17878,7 @@
         </is>
       </c>
       <c r="E674" s="20" t="n">
-        <v>188</v>
+        <v>120</v>
       </c>
     </row>
     <row r="675" ht="20" customHeight="1">
@@ -17903,7 +17903,7 @@
         </is>
       </c>
       <c r="E675" s="23" t="n">
-        <v>175</v>
+        <v>231</v>
       </c>
     </row>
     <row r="676" ht="20" customHeight="1">
@@ -17928,7 +17928,7 @@
         </is>
       </c>
       <c r="E676" s="20" t="n">
-        <v>136</v>
+        <v>203</v>
       </c>
     </row>
     <row r="677" ht="20" customHeight="1">
@@ -17953,7 +17953,7 @@
         </is>
       </c>
       <c r="E677" s="23" t="n">
-        <v>127</v>
+        <v>136</v>
       </c>
     </row>
     <row r="678" ht="20" customHeight="1">
@@ -17978,7 +17978,7 @@
         </is>
       </c>
       <c r="E678" s="20" t="n">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="679" ht="20" customHeight="1">
@@ -18003,7 +18003,7 @@
         </is>
       </c>
       <c r="E679" s="23" t="n">
-        <v>137</v>
+        <v>182</v>
       </c>
     </row>
     <row r="680" ht="20" customHeight="1">
@@ -18028,7 +18028,7 @@
         </is>
       </c>
       <c r="E680" s="20" t="n">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="681" ht="20" customHeight="1">
@@ -18053,7 +18053,7 @@
         </is>
       </c>
       <c r="E681" s="23" t="n">
-        <v>216</v>
+        <v>124</v>
       </c>
     </row>
     <row r="682" ht="20" customHeight="1">
@@ -18078,7 +18078,7 @@
         </is>
       </c>
       <c r="E682" s="20" t="n">
-        <v>220</v>
+        <v>190</v>
       </c>
     </row>
     <row r="683" ht="20" customHeight="1">
@@ -18103,7 +18103,7 @@
         </is>
       </c>
       <c r="E683" s="23" t="n">
-        <v>200</v>
+        <v>206</v>
       </c>
     </row>
     <row r="684" ht="20" customHeight="1">
@@ -18128,7 +18128,7 @@
         </is>
       </c>
       <c r="E684" s="20" t="n">
-        <v>141</v>
+        <v>224</v>
       </c>
     </row>
     <row r="685" ht="20" customHeight="1">
@@ -18153,7 +18153,7 @@
         </is>
       </c>
       <c r="E685" s="23" t="n">
-        <v>139</v>
+        <v>150</v>
       </c>
     </row>
     <row r="686" ht="20" customHeight="1">
@@ -18178,7 +18178,7 @@
         </is>
       </c>
       <c r="E686" s="20" t="n">
-        <v>167</v>
+        <v>143</v>
       </c>
     </row>
     <row r="687" ht="20" customHeight="1">
@@ -18203,7 +18203,7 @@
         </is>
       </c>
       <c r="E687" s="23" t="n">
-        <v>234</v>
+        <v>150</v>
       </c>
     </row>
     <row r="688" ht="20" customHeight="1">
@@ -18228,7 +18228,7 @@
         </is>
       </c>
       <c r="E688" s="20" t="n">
-        <v>238</v>
+        <v>165</v>
       </c>
     </row>
     <row r="689" ht="20" customHeight="1">
@@ -18253,7 +18253,7 @@
         </is>
       </c>
       <c r="E689" s="23" t="n">
-        <v>130</v>
+        <v>230</v>
       </c>
     </row>
     <row r="690" ht="20" customHeight="1">
@@ -18278,7 +18278,7 @@
         </is>
       </c>
       <c r="E690" s="20" t="n">
-        <v>142</v>
+        <v>204</v>
       </c>
     </row>
     <row r="691" ht="20" customHeight="1">
@@ -18303,7 +18303,7 @@
         </is>
       </c>
       <c r="E691" s="23" t="n">
-        <v>145</v>
+        <v>159</v>
       </c>
     </row>
     <row r="692" ht="20" customHeight="1">
@@ -18328,7 +18328,7 @@
         </is>
       </c>
       <c r="E692" s="20" t="n">
-        <v>209</v>
+        <v>147</v>
       </c>
     </row>
     <row r="693" ht="20" customHeight="1">
@@ -18353,7 +18353,7 @@
         </is>
       </c>
       <c r="E693" s="23" t="n">
-        <v>142</v>
+        <v>154</v>
       </c>
     </row>
     <row r="694" ht="20" customHeight="1">
@@ -18378,7 +18378,7 @@
         </is>
       </c>
       <c r="E694" s="20" t="n">
-        <v>144</v>
+        <v>131</v>
       </c>
     </row>
     <row r="695" ht="20" customHeight="1">
@@ -18403,7 +18403,7 @@
         </is>
       </c>
       <c r="E695" s="23" t="n">
-        <v>181</v>
+        <v>111</v>
       </c>
     </row>
     <row r="696" ht="20" customHeight="1">
@@ -18428,7 +18428,7 @@
         </is>
       </c>
       <c r="E696" s="20" t="n">
-        <v>209</v>
+        <v>227</v>
       </c>
     </row>
     <row r="697" ht="20" customHeight="1">
@@ -18453,7 +18453,7 @@
         </is>
       </c>
       <c r="E697" s="23" t="n">
-        <v>121</v>
+        <v>165</v>
       </c>
     </row>
     <row r="698" ht="20" customHeight="1">
@@ -18478,7 +18478,7 @@
         </is>
       </c>
       <c r="E698" s="20" t="n">
-        <v>209</v>
+        <v>169</v>
       </c>
     </row>
     <row r="699" ht="20" customHeight="1">
@@ -18503,7 +18503,7 @@
         </is>
       </c>
       <c r="E699" s="23" t="n">
-        <v>208</v>
+        <v>224</v>
       </c>
     </row>
     <row r="700" ht="20" customHeight="1">
@@ -18528,7 +18528,7 @@
         </is>
       </c>
       <c r="E700" s="20" t="n">
-        <v>183</v>
+        <v>197</v>
       </c>
     </row>
     <row r="701" ht="20" customHeight="1">
@@ -18553,7 +18553,7 @@
         </is>
       </c>
       <c r="E701" s="23" t="n">
-        <v>119</v>
+        <v>190</v>
       </c>
     </row>
     <row r="702" ht="20" customHeight="1">
@@ -18578,7 +18578,7 @@
         </is>
       </c>
       <c r="E702" s="20" t="n">
-        <v>193</v>
+        <v>167</v>
       </c>
     </row>
     <row r="703" ht="20" customHeight="1">
@@ -18603,7 +18603,7 @@
         </is>
       </c>
       <c r="E703" s="23" t="n">
-        <v>149</v>
+        <v>178</v>
       </c>
     </row>
     <row r="704" ht="20" customHeight="1">
@@ -18628,7 +18628,7 @@
         </is>
       </c>
       <c r="E704" s="20" t="n">
-        <v>192</v>
+        <v>233</v>
       </c>
     </row>
     <row r="705" ht="20" customHeight="1">
@@ -18653,7 +18653,7 @@
         </is>
       </c>
       <c r="E705" s="23" t="n">
-        <v>240</v>
+        <v>233</v>
       </c>
     </row>
     <row r="706" ht="20" customHeight="1">
@@ -18678,7 +18678,7 @@
         </is>
       </c>
       <c r="E706" s="20" t="n">
-        <v>217</v>
+        <v>178</v>
       </c>
     </row>
     <row r="707" ht="20" customHeight="1">
@@ -18703,7 +18703,7 @@
         </is>
       </c>
       <c r="E707" s="23" t="n">
-        <v>192</v>
+        <v>135</v>
       </c>
     </row>
     <row r="708" ht="20" customHeight="1">
@@ -18728,7 +18728,7 @@
         </is>
       </c>
       <c r="E708" s="20" t="n">
-        <v>142</v>
+        <v>197</v>
       </c>
     </row>
     <row r="709" ht="20" customHeight="1">
@@ -18753,7 +18753,7 @@
         </is>
       </c>
       <c r="E709" s="23" t="n">
-        <v>117</v>
+        <v>144</v>
       </c>
     </row>
     <row r="710" ht="20" customHeight="1">
@@ -18778,7 +18778,7 @@
         </is>
       </c>
       <c r="E710" s="20" t="n">
-        <v>233</v>
+        <v>200</v>
       </c>
     </row>
     <row r="711" ht="20" customHeight="1">
@@ -18803,7 +18803,7 @@
         </is>
       </c>
       <c r="E711" s="23" t="n">
-        <v>202</v>
+        <v>163</v>
       </c>
     </row>
     <row r="712" ht="20" customHeight="1">
@@ -18828,7 +18828,7 @@
         </is>
       </c>
       <c r="E712" s="20" t="n">
-        <v>132</v>
+        <v>232</v>
       </c>
     </row>
     <row r="713" ht="20" customHeight="1">
@@ -18853,7 +18853,7 @@
         </is>
       </c>
       <c r="E713" s="23" t="n">
-        <v>214</v>
+        <v>231</v>
       </c>
     </row>
     <row r="714" ht="20" customHeight="1">
@@ -18878,7 +18878,7 @@
         </is>
       </c>
       <c r="E714" s="20" t="n">
-        <v>236</v>
+        <v>230</v>
       </c>
     </row>
     <row r="715" ht="20" customHeight="1">
@@ -18903,7 +18903,7 @@
         </is>
       </c>
       <c r="E715" s="23" t="n">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="716" ht="20" customHeight="1">
@@ -18928,7 +18928,7 @@
         </is>
       </c>
       <c r="E716" s="20" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="717" ht="20" customHeight="1">
@@ -18953,7 +18953,7 @@
         </is>
       </c>
       <c r="E717" s="23" t="n">
-        <v>214</v>
+        <v>114</v>
       </c>
     </row>
     <row r="718" ht="20" customHeight="1">
@@ -18978,7 +18978,7 @@
         </is>
       </c>
       <c r="E718" s="20" t="n">
-        <v>227</v>
+        <v>114</v>
       </c>
     </row>
     <row r="719" ht="20" customHeight="1">
@@ -19003,7 +19003,7 @@
         </is>
       </c>
       <c r="E719" s="23" t="n">
-        <v>159</v>
+        <v>231</v>
       </c>
     </row>
     <row r="720" ht="20" customHeight="1">
@@ -19028,7 +19028,7 @@
         </is>
       </c>
       <c r="E720" s="20" t="n">
-        <v>114</v>
+        <v>180</v>
       </c>
     </row>
     <row r="721" ht="20" customHeight="1">
@@ -19053,7 +19053,7 @@
         </is>
       </c>
       <c r="E721" s="23" t="n">
-        <v>152</v>
+        <v>201</v>
       </c>
     </row>
     <row r="722" ht="20" customHeight="1">
@@ -19078,7 +19078,7 @@
         </is>
       </c>
       <c r="E722" s="20" t="n">
-        <v>171</v>
+        <v>208</v>
       </c>
     </row>
     <row r="723" ht="20" customHeight="1">
@@ -19103,7 +19103,7 @@
         </is>
       </c>
       <c r="E723" s="23" t="n">
-        <v>125</v>
+        <v>149</v>
       </c>
     </row>
     <row r="724" ht="20" customHeight="1">
@@ -19128,7 +19128,7 @@
         </is>
       </c>
       <c r="E724" s="20" t="n">
-        <v>165</v>
+        <v>147</v>
       </c>
     </row>
     <row r="725" ht="20" customHeight="1">
@@ -19153,7 +19153,7 @@
         </is>
       </c>
       <c r="E725" s="23" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="726" ht="20" customHeight="1">
@@ -19178,7 +19178,7 @@
         </is>
       </c>
       <c r="E726" s="20" t="n">
-        <v>222</v>
+        <v>150</v>
       </c>
     </row>
     <row r="727" ht="20" customHeight="1">
@@ -19203,7 +19203,7 @@
         </is>
       </c>
       <c r="E727" s="23" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="728" ht="20" customHeight="1">
@@ -19228,7 +19228,7 @@
         </is>
       </c>
       <c r="E728" s="20" t="n">
-        <v>193</v>
+        <v>222</v>
       </c>
     </row>
     <row r="729" ht="20" customHeight="1">
@@ -19253,7 +19253,7 @@
         </is>
       </c>
       <c r="E729" s="23" t="n">
-        <v>218</v>
+        <v>135</v>
       </c>
     </row>
     <row r="730" ht="20" customHeight="1">
@@ -19278,7 +19278,7 @@
         </is>
       </c>
       <c r="E730" s="20" t="n">
-        <v>111</v>
+        <v>222</v>
       </c>
     </row>
     <row r="731" ht="20" customHeight="1">
@@ -19303,7 +19303,7 @@
         </is>
       </c>
       <c r="E731" s="23" t="n">
-        <v>172</v>
+        <v>113</v>
       </c>
     </row>
     <row r="732" ht="20" customHeight="1">
@@ -19328,7 +19328,7 @@
         </is>
       </c>
       <c r="E732" s="20" t="n">
-        <v>146</v>
+        <v>219</v>
       </c>
     </row>
     <row r="733" ht="20" customHeight="1">
@@ -19353,7 +19353,7 @@
         </is>
       </c>
       <c r="E733" s="23" t="n">
-        <v>204</v>
+        <v>167</v>
       </c>
     </row>
     <row r="734" ht="20" customHeight="1">
@@ -19378,7 +19378,7 @@
         </is>
       </c>
       <c r="E734" s="20" t="n">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="735" ht="20" customHeight="1">
@@ -19403,7 +19403,7 @@
         </is>
       </c>
       <c r="E735" s="23" t="n">
-        <v>172</v>
+        <v>204</v>
       </c>
     </row>
     <row r="736" ht="20" customHeight="1">
@@ -19428,7 +19428,7 @@
         </is>
       </c>
       <c r="E736" s="20" t="n">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="737" ht="20" customHeight="1">
@@ -19453,7 +19453,7 @@
         </is>
       </c>
       <c r="E737" s="23" t="n">
-        <v>111</v>
+        <v>217</v>
       </c>
     </row>
     <row r="738" ht="20" customHeight="1">
@@ -19478,7 +19478,7 @@
         </is>
       </c>
       <c r="E738" s="20" t="n">
-        <v>178</v>
+        <v>225</v>
       </c>
     </row>
     <row r="739" ht="20" customHeight="1">
@@ -19503,7 +19503,7 @@
         </is>
       </c>
       <c r="E739" s="23" t="n">
-        <v>143</v>
+        <v>181</v>
       </c>
     </row>
     <row r="740" ht="20" customHeight="1">
@@ -19528,7 +19528,7 @@
         </is>
       </c>
       <c r="E740" s="20" t="n">
-        <v>231</v>
+        <v>226</v>
       </c>
     </row>
     <row r="741" ht="20" customHeight="1">
@@ -19553,7 +19553,7 @@
         </is>
       </c>
       <c r="E741" s="23" t="n">
-        <v>184</v>
+        <v>163</v>
       </c>
     </row>
     <row r="742" ht="20" customHeight="1">
@@ -19578,7 +19578,7 @@
         </is>
       </c>
       <c r="E742" s="20" t="n">
-        <v>197</v>
+        <v>159</v>
       </c>
     </row>
     <row r="743" ht="20" customHeight="1">
@@ -19603,7 +19603,7 @@
         </is>
       </c>
       <c r="E743" s="23" t="n">
-        <v>236</v>
+        <v>197</v>
       </c>
     </row>
     <row r="744" ht="20" customHeight="1">
@@ -19628,7 +19628,7 @@
         </is>
       </c>
       <c r="E744" s="20" t="n">
-        <v>166</v>
+        <v>127</v>
       </c>
     </row>
     <row r="745" ht="20" customHeight="1">
@@ -19653,7 +19653,7 @@
         </is>
       </c>
       <c r="E745" s="23" t="n">
-        <v>165</v>
+        <v>240</v>
       </c>
     </row>
     <row r="746" ht="20" customHeight="1">
@@ -19678,7 +19678,7 @@
         </is>
       </c>
       <c r="E746" s="20" t="n">
-        <v>216</v>
+        <v>233</v>
       </c>
     </row>
     <row r="747" ht="20" customHeight="1">
@@ -19703,7 +19703,7 @@
         </is>
       </c>
       <c r="E747" s="23" t="n">
-        <v>225</v>
+        <v>148</v>
       </c>
     </row>
     <row r="748" ht="20" customHeight="1">
@@ -19728,7 +19728,7 @@
         </is>
       </c>
       <c r="E748" s="20" t="n">
-        <v>212</v>
+        <v>192</v>
       </c>
     </row>
     <row r="749" ht="20" customHeight="1">
@@ -19753,7 +19753,7 @@
         </is>
       </c>
       <c r="E749" s="23" t="n">
-        <v>196</v>
+        <v>214</v>
       </c>
     </row>
     <row r="750" ht="20" customHeight="1">
@@ -19778,7 +19778,7 @@
         </is>
       </c>
       <c r="E750" s="20" t="n">
-        <v>152</v>
+        <v>157</v>
       </c>
     </row>
     <row r="751" ht="20" customHeight="1">
@@ -19803,7 +19803,7 @@
         </is>
       </c>
       <c r="E751" s="23" t="n">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="752" ht="20" customHeight="1">
@@ -19828,7 +19828,7 @@
         </is>
       </c>
       <c r="E752" s="20" t="n">
-        <v>141</v>
+        <v>232</v>
       </c>
     </row>
     <row r="753" ht="20" customHeight="1">
@@ -19853,7 +19853,7 @@
         </is>
       </c>
       <c r="E753" s="23" t="n">
-        <v>160</v>
+        <v>174</v>
       </c>
     </row>
     <row r="754" ht="20" customHeight="1">
@@ -19878,7 +19878,7 @@
         </is>
       </c>
       <c r="E754" s="20" t="n">
-        <v>180</v>
+        <v>225</v>
       </c>
     </row>
     <row r="755" ht="20" customHeight="1">
@@ -19903,7 +19903,7 @@
         </is>
       </c>
       <c r="E755" s="23" t="n">
-        <v>145</v>
+        <v>229</v>
       </c>
     </row>
     <row r="756" ht="20" customHeight="1">
@@ -19928,7 +19928,7 @@
         </is>
       </c>
       <c r="E756" s="20" t="n">
-        <v>147</v>
+        <v>175</v>
       </c>
     </row>
     <row r="757" ht="20" customHeight="1">
@@ -19953,7 +19953,7 @@
         </is>
       </c>
       <c r="E757" s="23" t="n">
-        <v>217</v>
+        <v>157</v>
       </c>
     </row>
     <row r="758" ht="20" customHeight="1">
@@ -19978,7 +19978,7 @@
         </is>
       </c>
       <c r="E758" s="20" t="n">
-        <v>190</v>
+        <v>166</v>
       </c>
     </row>
     <row r="759" ht="20" customHeight="1">
@@ -20003,7 +20003,7 @@
         </is>
       </c>
       <c r="E759" s="23" t="n">
-        <v>211</v>
+        <v>145</v>
       </c>
     </row>
     <row r="760" ht="20" customHeight="1">
@@ -20028,7 +20028,7 @@
         </is>
       </c>
       <c r="E760" s="20" t="n">
-        <v>152</v>
+        <v>137</v>
       </c>
     </row>
     <row r="761" ht="20" customHeight="1">
@@ -20053,7 +20053,7 @@
         </is>
       </c>
       <c r="E761" s="23" t="n">
-        <v>200</v>
+        <v>207</v>
       </c>
     </row>
     <row r="762" ht="20" customHeight="1">
@@ -20078,7 +20078,7 @@
         </is>
       </c>
       <c r="E762" s="20" t="n">
-        <v>154</v>
+        <v>219</v>
       </c>
     </row>
     <row r="763" ht="20" customHeight="1">
@@ -20103,7 +20103,7 @@
         </is>
       </c>
       <c r="E763" s="23" t="n">
-        <v>127</v>
+        <v>142</v>
       </c>
     </row>
     <row r="764" ht="20" customHeight="1">
@@ -20128,7 +20128,7 @@
         </is>
       </c>
       <c r="E764" s="20" t="n">
-        <v>218</v>
+        <v>159</v>
       </c>
     </row>
     <row r="765" ht="20" customHeight="1">
@@ -20153,7 +20153,7 @@
         </is>
       </c>
       <c r="E765" s="23" t="n">
-        <v>201</v>
+        <v>220</v>
       </c>
     </row>
     <row r="766" ht="20" customHeight="1">
@@ -20178,7 +20178,7 @@
         </is>
       </c>
       <c r="E766" s="20" t="n">
-        <v>147</v>
+        <v>216</v>
       </c>
     </row>
     <row r="767" ht="20" customHeight="1">
@@ -20203,7 +20203,7 @@
         </is>
       </c>
       <c r="E767" s="23" t="n">
-        <v>176</v>
+        <v>240</v>
       </c>
     </row>
     <row r="768" ht="20" customHeight="1">
@@ -20228,7 +20228,7 @@
         </is>
       </c>
       <c r="E768" s="20" t="n">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="769" ht="20" customHeight="1">
@@ -20253,7 +20253,7 @@
         </is>
       </c>
       <c r="E769" s="23" t="n">
-        <v>148</v>
+        <v>169</v>
       </c>
     </row>
     <row r="770" ht="20" customHeight="1">
@@ -20278,7 +20278,7 @@
         </is>
       </c>
       <c r="E770" s="20" t="n">
-        <v>196</v>
+        <v>164</v>
       </c>
     </row>
     <row r="771" ht="20" customHeight="1">
@@ -20303,7 +20303,7 @@
         </is>
       </c>
       <c r="E771" s="23" t="n">
-        <v>143</v>
+        <v>126</v>
       </c>
     </row>
     <row r="772" ht="20" customHeight="1">
@@ -20328,7 +20328,7 @@
         </is>
       </c>
       <c r="E772" s="20" t="n">
-        <v>173</v>
+        <v>113</v>
       </c>
     </row>
     <row r="773" ht="20" customHeight="1">
@@ -20353,7 +20353,7 @@
         </is>
       </c>
       <c r="E773" s="23" t="n">
-        <v>139</v>
+        <v>172</v>
       </c>
     </row>
     <row r="774" ht="20" customHeight="1">
@@ -20378,7 +20378,7 @@
         </is>
       </c>
       <c r="E774" s="20" t="n">
-        <v>208</v>
+        <v>169</v>
       </c>
     </row>
     <row r="775" ht="20" customHeight="1">
@@ -20403,7 +20403,7 @@
         </is>
       </c>
       <c r="E775" s="23" t="n">
-        <v>178</v>
+        <v>126</v>
       </c>
     </row>
     <row r="776" ht="20" customHeight="1">
@@ -20428,7 +20428,7 @@
         </is>
       </c>
       <c r="E776" s="20" t="n">
-        <v>179</v>
+        <v>224</v>
       </c>
     </row>
     <row r="777" ht="20" customHeight="1">
@@ -20453,7 +20453,7 @@
         </is>
       </c>
       <c r="E777" s="23" t="n">
-        <v>224</v>
+        <v>214</v>
       </c>
     </row>
     <row r="778" ht="20" customHeight="1">
@@ -20478,7 +20478,7 @@
         </is>
       </c>
       <c r="E778" s="20" t="n">
-        <v>234</v>
+        <v>138</v>
       </c>
     </row>
     <row r="779" ht="20" customHeight="1">
@@ -20503,7 +20503,7 @@
         </is>
       </c>
       <c r="E779" s="23" t="n">
-        <v>229</v>
+        <v>145</v>
       </c>
     </row>
     <row r="780" ht="20" customHeight="1">
@@ -20528,7 +20528,7 @@
         </is>
       </c>
       <c r="E780" s="20" t="n">
-        <v>165</v>
+        <v>226</v>
       </c>
     </row>
     <row r="781" ht="20" customHeight="1">
@@ -20553,7 +20553,7 @@
         </is>
       </c>
       <c r="E781" s="23" t="n">
-        <v>226</v>
+        <v>232</v>
       </c>
     </row>
     <row r="782" ht="20" customHeight="1">
@@ -20578,7 +20578,7 @@
         </is>
       </c>
       <c r="E782" s="20" t="n">
-        <v>211</v>
+        <v>167</v>
       </c>
     </row>
     <row r="783" ht="20" customHeight="1">
@@ -20603,7 +20603,7 @@
         </is>
       </c>
       <c r="E783" s="23" t="n">
-        <v>141</v>
+        <v>220</v>
       </c>
     </row>
     <row r="784" ht="20" customHeight="1">
@@ -20628,7 +20628,7 @@
         </is>
       </c>
       <c r="E784" s="20" t="n">
-        <v>165</v>
+        <v>129</v>
       </c>
     </row>
     <row r="785" ht="20" customHeight="1">
@@ -20653,7 +20653,7 @@
         </is>
       </c>
       <c r="E785" s="23" t="n">
-        <v>118</v>
+        <v>201</v>
       </c>
     </row>
     <row r="786" ht="20" customHeight="1">
@@ -20678,7 +20678,7 @@
         </is>
       </c>
       <c r="E786" s="20" t="n">
-        <v>149</v>
+        <v>219</v>
       </c>
     </row>
     <row r="787" ht="20" customHeight="1">
@@ -20703,7 +20703,7 @@
         </is>
       </c>
       <c r="E787" s="23" t="n">
-        <v>193</v>
+        <v>175</v>
       </c>
     </row>
     <row r="788" ht="20" customHeight="1">
@@ -20728,7 +20728,7 @@
         </is>
       </c>
       <c r="E788" s="20" t="n">
-        <v>188</v>
+        <v>116</v>
       </c>
     </row>
     <row r="789" ht="20" customHeight="1">
@@ -20753,7 +20753,7 @@
         </is>
       </c>
       <c r="E789" s="23" t="n">
-        <v>192</v>
+        <v>153</v>
       </c>
     </row>
     <row r="790" ht="20" customHeight="1">
@@ -20778,7 +20778,7 @@
         </is>
       </c>
       <c r="E790" s="20" t="n">
-        <v>143</v>
+        <v>169</v>
       </c>
     </row>
     <row r="791" ht="20" customHeight="1">
@@ -20828,7 +20828,7 @@
         </is>
       </c>
       <c r="E792" s="20" t="n">
-        <v>132</v>
+        <v>180</v>
       </c>
     </row>
     <row r="793" ht="20" customHeight="1">
@@ -20853,7 +20853,7 @@
         </is>
       </c>
       <c r="E793" s="23" t="n">
-        <v>194</v>
+        <v>111</v>
       </c>
     </row>
     <row r="794" ht="20" customHeight="1">
@@ -20878,7 +20878,7 @@
         </is>
       </c>
       <c r="E794" s="20" t="n">
-        <v>193</v>
+        <v>121</v>
       </c>
     </row>
     <row r="795" ht="20" customHeight="1">
@@ -20903,7 +20903,7 @@
         </is>
       </c>
       <c r="E795" s="23" t="n">
-        <v>175</v>
+        <v>135</v>
       </c>
     </row>
     <row r="796" ht="20" customHeight="1">
@@ -20928,7 +20928,7 @@
         </is>
       </c>
       <c r="E796" s="20" t="n">
-        <v>110</v>
+        <v>118</v>
       </c>
     </row>
     <row r="797" ht="20" customHeight="1">
@@ -20953,7 +20953,7 @@
         </is>
       </c>
       <c r="E797" s="23" t="n">
-        <v>171</v>
+        <v>231</v>
       </c>
     </row>
     <row r="798" ht="20" customHeight="1">
@@ -20978,7 +20978,7 @@
         </is>
       </c>
       <c r="E798" s="20" t="n">
-        <v>128</v>
+        <v>174</v>
       </c>
     </row>
     <row r="799" ht="20" customHeight="1">
@@ -21003,7 +21003,7 @@
         </is>
       </c>
       <c r="E799" s="23" t="n">
-        <v>154</v>
+        <v>145</v>
       </c>
     </row>
     <row r="800" ht="20" customHeight="1">
@@ -21028,7 +21028,7 @@
         </is>
       </c>
       <c r="E800" s="20" t="n">
-        <v>215</v>
+        <v>209</v>
       </c>
     </row>
     <row r="801" ht="20" customHeight="1">
@@ -21053,7 +21053,7 @@
         </is>
       </c>
       <c r="E801" s="23" t="n">
-        <v>139</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>

--- a/Appium_E2E_Test_Report_Traverse.xlsx
+++ b/Appium_E2E_Test_Report_Traverse.xlsx
@@ -791,7 +791,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 08:02:59</t>
+          <t>2026-08-11 08:18:49</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="E2" s="20" t="n">
-        <v>182</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="E3" s="23" t="n">
-        <v>170</v>
+        <v>191</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="E4" s="20" t="n">
-        <v>213</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="E5" s="23" t="n">
-        <v>163</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="E6" s="20" t="n">
-        <v>189</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="E7" s="23" t="n">
-        <v>177</v>
+        <v>222</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -1228,7 +1228,7 @@
         </is>
       </c>
       <c r="E8" s="20" t="n">
-        <v>208</v>
+        <v>236</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="E9" s="23" t="n">
-        <v>225</v>
+        <v>160</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
@@ -1278,7 +1278,7 @@
         </is>
       </c>
       <c r="E10" s="20" t="n">
-        <v>206</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="E11" s="23" t="n">
-        <v>171</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
@@ -1328,7 +1328,7 @@
         </is>
       </c>
       <c r="E12" s="20" t="n">
-        <v>154</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="E13" s="23" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="E14" s="20" t="n">
-        <v>117</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="E15" s="23" t="n">
-        <v>234</v>
+        <v>179</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="E16" s="20" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="E17" s="23" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -1478,7 +1478,7 @@
         </is>
       </c>
       <c r="E18" s="20" t="n">
-        <v>229</v>
+        <v>184</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
@@ -1503,7 +1503,7 @@
         </is>
       </c>
       <c r="E19" s="23" t="n">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="E20" s="20" t="n">
-        <v>211</v>
+        <v>135</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="E21" s="23" t="n">
-        <v>215</v>
+        <v>206</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
@@ -1578,7 +1578,7 @@
         </is>
       </c>
       <c r="E22" s="20" t="n">
-        <v>151</v>
+        <v>111</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="E23" s="23" t="n">
-        <v>156</v>
+        <v>224</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
@@ -1628,7 +1628,7 @@
         </is>
       </c>
       <c r="E24" s="20" t="n">
-        <v>196</v>
+        <v>200</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="E25" s="23" t="n">
-        <v>163</v>
+        <v>182</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
@@ -1678,7 +1678,7 @@
         </is>
       </c>
       <c r="E26" s="20" t="n">
-        <v>238</v>
+        <v>167</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="E27" s="23" t="n">
-        <v>177</v>
+        <v>145</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="E28" s="20" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="E29" s="23" t="n">
-        <v>198</v>
+        <v>184</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="E30" s="20" t="n">
-        <v>168</v>
+        <v>238</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
@@ -1803,7 +1803,7 @@
         </is>
       </c>
       <c r="E31" s="23" t="n">
-        <v>199</v>
+        <v>206</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
@@ -1828,7 +1828,7 @@
         </is>
       </c>
       <c r="E32" s="20" t="n">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
@@ -1853,7 +1853,7 @@
         </is>
       </c>
       <c r="E33" s="23" t="n">
-        <v>153</v>
+        <v>175</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
@@ -1878,7 +1878,7 @@
         </is>
       </c>
       <c r="E34" s="20" t="n">
-        <v>229</v>
+        <v>174</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="E35" s="23" t="n">
-        <v>208</v>
+        <v>153</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="E36" s="20" t="n">
-        <v>231</v>
+        <v>146</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="E37" s="23" t="n">
-        <v>124</v>
+        <v>212</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
@@ -1978,7 +1978,7 @@
         </is>
       </c>
       <c r="E38" s="20" t="n">
-        <v>158</v>
+        <v>232</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="E39" s="23" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="E40" s="20" t="n">
-        <v>228</v>
+        <v>202</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="E41" s="23" t="n">
-        <v>199</v>
+        <v>116</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
@@ -2078,7 +2078,7 @@
         </is>
       </c>
       <c r="E42" s="20" t="n">
-        <v>214</v>
+        <v>163</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="E43" s="23" t="n">
-        <v>121</v>
+        <v>220</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="E44" s="20" t="n">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="E45" s="23" t="n">
-        <v>110</v>
+        <v>146</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
@@ -2178,7 +2178,7 @@
         </is>
       </c>
       <c r="E46" s="20" t="n">
-        <v>153</v>
+        <v>201</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
@@ -2203,7 +2203,7 @@
         </is>
       </c>
       <c r="E47" s="23" t="n">
-        <v>139</v>
+        <v>223</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="E48" s="20" t="n">
-        <v>119</v>
+        <v>190</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
@@ -2253,7 +2253,7 @@
         </is>
       </c>
       <c r="E49" s="23" t="n">
-        <v>219</v>
+        <v>165</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
@@ -2278,7 +2278,7 @@
         </is>
       </c>
       <c r="E50" s="20" t="n">
-        <v>181</v>
+        <v>167</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="E51" s="23" t="n">
-        <v>176</v>
+        <v>127</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
@@ -2328,7 +2328,7 @@
         </is>
       </c>
       <c r="E52" s="20" t="n">
-        <v>229</v>
+        <v>157</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
@@ -2353,7 +2353,7 @@
         </is>
       </c>
       <c r="E53" s="23" t="n">
-        <v>139</v>
+        <v>126</v>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="E54" s="20" t="n">
-        <v>173</v>
+        <v>160</v>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1">
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="E55" s="23" t="n">
-        <v>157</v>
+        <v>207</v>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1">
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="E56" s="20" t="n">
-        <v>223</v>
+        <v>127</v>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1">
@@ -2453,7 +2453,7 @@
         </is>
       </c>
       <c r="E57" s="23" t="n">
-        <v>189</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1">
@@ -2478,7 +2478,7 @@
         </is>
       </c>
       <c r="E58" s="20" t="n">
-        <v>214</v>
+        <v>177</v>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1">
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="E59" s="23" t="n">
-        <v>141</v>
+        <v>190</v>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1">
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="E60" s="20" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
@@ -2553,7 +2553,7 @@
         </is>
       </c>
       <c r="E61" s="23" t="n">
-        <v>144</v>
+        <v>209</v>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="E62" s="20" t="n">
-        <v>191</v>
+        <v>238</v>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="E63" s="23" t="n">
-        <v>126</v>
+        <v>223</v>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1">
@@ -2628,7 +2628,7 @@
         </is>
       </c>
       <c r="E64" s="20" t="n">
-        <v>126</v>
+        <v>112</v>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1">
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="E65" s="23" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1">
@@ -2678,7 +2678,7 @@
         </is>
       </c>
       <c r="E66" s="20" t="n">
-        <v>150</v>
+        <v>221</v>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="E67" s="23" t="n">
-        <v>227</v>
+        <v>156</v>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="E68" s="20" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="E69" s="23" t="n">
-        <v>210</v>
+        <v>199</v>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1">
@@ -2778,7 +2778,7 @@
         </is>
       </c>
       <c r="E70" s="20" t="n">
-        <v>198</v>
+        <v>176</v>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1">
@@ -2803,7 +2803,7 @@
         </is>
       </c>
       <c r="E71" s="23" t="n">
-        <v>123</v>
+        <v>159</v>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1">
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="E72" s="20" t="n">
-        <v>110</v>
+        <v>138</v>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1">
@@ -2853,7 +2853,7 @@
         </is>
       </c>
       <c r="E73" s="23" t="n">
-        <v>238</v>
+        <v>178</v>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
@@ -2878,7 +2878,7 @@
         </is>
       </c>
       <c r="E74" s="20" t="n">
-        <v>120</v>
+        <v>139</v>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="E75" s="23" t="n">
-        <v>118</v>
+        <v>240</v>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
@@ -2928,7 +2928,7 @@
         </is>
       </c>
       <c r="E76" s="20" t="n">
-        <v>173</v>
+        <v>187</v>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="E77" s="23" t="n">
-        <v>182</v>
+        <v>229</v>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1">
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="E78" s="20" t="n">
-        <v>116</v>
+        <v>150</v>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
@@ -3003,7 +3003,7 @@
         </is>
       </c>
       <c r="E79" s="23" t="n">
-        <v>149</v>
+        <v>116</v>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1">
@@ -3028,7 +3028,7 @@
         </is>
       </c>
       <c r="E80" s="20" t="n">
-        <v>175</v>
+        <v>239</v>
       </c>
     </row>
     <row r="81" ht="20" customHeight="1">
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="E81" s="23" t="n">
-        <v>172</v>
+        <v>229</v>
       </c>
     </row>
     <row r="82" ht="20" customHeight="1">
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="E82" s="20" t="n">
-        <v>116</v>
+        <v>164</v>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1">
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="E83" s="23" t="n">
-        <v>154</v>
+        <v>211</v>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1">
@@ -3128,7 +3128,7 @@
         </is>
       </c>
       <c r="E84" s="20" t="n">
-        <v>151</v>
+        <v>203</v>
       </c>
     </row>
     <row r="85" ht="20" customHeight="1">
@@ -3153,7 +3153,7 @@
         </is>
       </c>
       <c r="E85" s="23" t="n">
-        <v>211</v>
+        <v>171</v>
       </c>
     </row>
     <row r="86" ht="20" customHeight="1">
@@ -3178,7 +3178,7 @@
         </is>
       </c>
       <c r="E86" s="20" t="n">
-        <v>140</v>
+        <v>215</v>
       </c>
     </row>
     <row r="87" ht="20" customHeight="1">
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="E87" s="23" t="n">
-        <v>135</v>
+        <v>187</v>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1">
@@ -3228,7 +3228,7 @@
         </is>
       </c>
       <c r="E88" s="20" t="n">
-        <v>195</v>
+        <v>224</v>
       </c>
     </row>
     <row r="89" ht="20" customHeight="1">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="E89" s="23" t="n">
-        <v>147</v>
+        <v>118</v>
       </c>
     </row>
     <row r="90" ht="20" customHeight="1">
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="E90" s="20" t="n">
-        <v>111</v>
+        <v>224</v>
       </c>
     </row>
     <row r="91" ht="20" customHeight="1">
@@ -3303,7 +3303,7 @@
         </is>
       </c>
       <c r="E91" s="23" t="n">
-        <v>126</v>
+        <v>153</v>
       </c>
     </row>
     <row r="92" ht="20" customHeight="1">
@@ -3328,7 +3328,7 @@
         </is>
       </c>
       <c r="E92" s="20" t="n">
-        <v>236</v>
+        <v>204</v>
       </c>
     </row>
     <row r="93" ht="20" customHeight="1">
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="E93" s="23" t="n">
-        <v>219</v>
+        <v>128</v>
       </c>
     </row>
     <row r="94" ht="20" customHeight="1">
@@ -3378,7 +3378,7 @@
         </is>
       </c>
       <c r="E94" s="20" t="n">
-        <v>161</v>
+        <v>206</v>
       </c>
     </row>
     <row r="95" ht="20" customHeight="1">
@@ -3403,7 +3403,7 @@
         </is>
       </c>
       <c r="E95" s="23" t="n">
-        <v>145</v>
+        <v>157</v>
       </c>
     </row>
     <row r="96" ht="20" customHeight="1">
@@ -3428,7 +3428,7 @@
         </is>
       </c>
       <c r="E96" s="20" t="n">
-        <v>225</v>
+        <v>120</v>
       </c>
     </row>
     <row r="97" ht="20" customHeight="1">
@@ -3453,7 +3453,7 @@
         </is>
       </c>
       <c r="E97" s="23" t="n">
-        <v>182</v>
+        <v>113</v>
       </c>
     </row>
     <row r="98" ht="20" customHeight="1">
@@ -3478,7 +3478,7 @@
         </is>
       </c>
       <c r="E98" s="20" t="n">
-        <v>125</v>
+        <v>139</v>
       </c>
     </row>
     <row r="99" ht="20" customHeight="1">
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="E99" s="23" t="n">
-        <v>179</v>
+        <v>193</v>
       </c>
     </row>
     <row r="100" ht="20" customHeight="1">
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="E100" s="20" t="n">
-        <v>156</v>
+        <v>221</v>
       </c>
     </row>
     <row r="101" ht="20" customHeight="1">
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="E101" s="23" t="n">
-        <v>203</v>
+        <v>126</v>
       </c>
     </row>
     <row r="102" ht="20" customHeight="1">
@@ -3578,7 +3578,7 @@
         </is>
       </c>
       <c r="E102" s="20" t="n">
-        <v>191</v>
+        <v>181</v>
       </c>
     </row>
     <row r="103" ht="20" customHeight="1">
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="E103" s="23" t="n">
-        <v>217</v>
+        <v>237</v>
       </c>
     </row>
     <row r="104" ht="20" customHeight="1">
@@ -3628,7 +3628,7 @@
         </is>
       </c>
       <c r="E104" s="20" t="n">
-        <v>218</v>
+        <v>171</v>
       </c>
     </row>
     <row r="105" ht="20" customHeight="1">
@@ -3653,7 +3653,7 @@
         </is>
       </c>
       <c r="E105" s="23" t="n">
-        <v>187</v>
+        <v>131</v>
       </c>
     </row>
     <row r="106" ht="20" customHeight="1">
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="E106" s="20" t="n">
-        <v>236</v>
+        <v>112</v>
       </c>
     </row>
     <row r="107" ht="20" customHeight="1">
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="E107" s="23" t="n">
-        <v>134</v>
+        <v>168</v>
       </c>
     </row>
     <row r="108" ht="20" customHeight="1">
@@ -3728,7 +3728,7 @@
         </is>
       </c>
       <c r="E108" s="20" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="109" ht="20" customHeight="1">
@@ -3753,7 +3753,7 @@
         </is>
       </c>
       <c r="E109" s="23" t="n">
-        <v>220</v>
+        <v>213</v>
       </c>
     </row>
     <row r="110" ht="20" customHeight="1">
@@ -3778,7 +3778,7 @@
         </is>
       </c>
       <c r="E110" s="20" t="n">
-        <v>214</v>
+        <v>186</v>
       </c>
     </row>
     <row r="111" ht="20" customHeight="1">
@@ -3803,7 +3803,7 @@
         </is>
       </c>
       <c r="E111" s="23" t="n">
-        <v>125</v>
+        <v>227</v>
       </c>
     </row>
     <row r="112" ht="20" customHeight="1">
@@ -3828,7 +3828,7 @@
         </is>
       </c>
       <c r="E112" s="20" t="n">
-        <v>229</v>
+        <v>195</v>
       </c>
     </row>
     <row r="113" ht="20" customHeight="1">
@@ -3853,7 +3853,7 @@
         </is>
       </c>
       <c r="E113" s="23" t="n">
-        <v>138</v>
+        <v>118</v>
       </c>
     </row>
     <row r="114" ht="20" customHeight="1">
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="E114" s="20" t="n">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="115" ht="20" customHeight="1">
@@ -3903,7 +3903,7 @@
         </is>
       </c>
       <c r="E115" s="23" t="n">
-        <v>210</v>
+        <v>160</v>
       </c>
     </row>
     <row r="116" ht="20" customHeight="1">
@@ -3928,7 +3928,7 @@
         </is>
       </c>
       <c r="E116" s="20" t="n">
-        <v>160</v>
+        <v>227</v>
       </c>
     </row>
     <row r="117" ht="20" customHeight="1">
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="E117" s="23" t="n">
-        <v>133</v>
+        <v>208</v>
       </c>
     </row>
     <row r="118" ht="20" customHeight="1">
@@ -3978,7 +3978,7 @@
         </is>
       </c>
       <c r="E118" s="20" t="n">
-        <v>239</v>
+        <v>153</v>
       </c>
     </row>
     <row r="119" ht="20" customHeight="1">
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="E119" s="23" t="n">
-        <v>179</v>
+        <v>139</v>
       </c>
     </row>
     <row r="120" ht="20" customHeight="1">
@@ -4028,7 +4028,7 @@
         </is>
       </c>
       <c r="E120" s="20" t="n">
-        <v>211</v>
+        <v>229</v>
       </c>
     </row>
     <row r="121" ht="20" customHeight="1">
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="E121" s="23" t="n">
-        <v>138</v>
+        <v>188</v>
       </c>
     </row>
     <row r="122" ht="20" customHeight="1">
@@ -4078,7 +4078,7 @@
         </is>
       </c>
       <c r="E122" s="20" t="n">
-        <v>207</v>
+        <v>146</v>
       </c>
     </row>
     <row r="123" ht="20" customHeight="1">
@@ -4103,7 +4103,7 @@
         </is>
       </c>
       <c r="E123" s="23" t="n">
-        <v>140</v>
+        <v>154</v>
       </c>
     </row>
     <row r="124" ht="20" customHeight="1">
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="E124" s="20" t="n">
-        <v>114</v>
+        <v>210</v>
       </c>
     </row>
     <row r="125" ht="20" customHeight="1">
@@ -4153,7 +4153,7 @@
         </is>
       </c>
       <c r="E125" s="23" t="n">
-        <v>228</v>
+        <v>180</v>
       </c>
     </row>
     <row r="126" ht="20" customHeight="1">
@@ -4178,7 +4178,7 @@
         </is>
       </c>
       <c r="E126" s="20" t="n">
-        <v>135</v>
+        <v>126</v>
       </c>
     </row>
     <row r="127" ht="20" customHeight="1">
@@ -4203,7 +4203,7 @@
         </is>
       </c>
       <c r="E127" s="23" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="128" ht="20" customHeight="1">
@@ -4228,7 +4228,7 @@
         </is>
       </c>
       <c r="E128" s="20" t="n">
-        <v>226</v>
+        <v>173</v>
       </c>
     </row>
     <row r="129" ht="20" customHeight="1">
@@ -4253,7 +4253,7 @@
         </is>
       </c>
       <c r="E129" s="23" t="n">
-        <v>192</v>
+        <v>200</v>
       </c>
     </row>
     <row r="130" ht="20" customHeight="1">
@@ -4278,7 +4278,7 @@
         </is>
       </c>
       <c r="E130" s="20" t="n">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="131" ht="20" customHeight="1">
@@ -4303,7 +4303,7 @@
         </is>
       </c>
       <c r="E131" s="23" t="n">
-        <v>196</v>
+        <v>142</v>
       </c>
     </row>
     <row r="132" ht="20" customHeight="1">
@@ -4328,7 +4328,7 @@
         </is>
       </c>
       <c r="E132" s="20" t="n">
-        <v>123</v>
+        <v>212</v>
       </c>
     </row>
     <row r="133" ht="20" customHeight="1">
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="E133" s="23" t="n">
-        <v>123</v>
+        <v>184</v>
       </c>
     </row>
     <row r="134" ht="20" customHeight="1">
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="E134" s="20" t="n">
-        <v>178</v>
+        <v>167</v>
       </c>
     </row>
     <row r="135" ht="20" customHeight="1">
@@ -4403,7 +4403,7 @@
         </is>
       </c>
       <c r="E135" s="23" t="n">
-        <v>212</v>
+        <v>204</v>
       </c>
     </row>
     <row r="136" ht="20" customHeight="1">
@@ -4428,7 +4428,7 @@
         </is>
       </c>
       <c r="E136" s="20" t="n">
-        <v>159</v>
+        <v>195</v>
       </c>
     </row>
     <row r="137" ht="20" customHeight="1">
@@ -4453,7 +4453,7 @@
         </is>
       </c>
       <c r="E137" s="23" t="n">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="138" ht="20" customHeight="1">
@@ -4478,7 +4478,7 @@
         </is>
       </c>
       <c r="E138" s="20" t="n">
-        <v>210</v>
+        <v>136</v>
       </c>
     </row>
     <row r="139" ht="20" customHeight="1">
@@ -4503,7 +4503,7 @@
         </is>
       </c>
       <c r="E139" s="23" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="140" ht="20" customHeight="1">
@@ -4528,7 +4528,7 @@
         </is>
       </c>
       <c r="E140" s="20" t="n">
-        <v>131</v>
+        <v>115</v>
       </c>
     </row>
     <row r="141" ht="20" customHeight="1">
@@ -4553,7 +4553,7 @@
         </is>
       </c>
       <c r="E141" s="23" t="n">
-        <v>224</v>
+        <v>199</v>
       </c>
     </row>
     <row r="142" ht="20" customHeight="1">
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="E142" s="20" t="n">
-        <v>178</v>
+        <v>154</v>
       </c>
     </row>
     <row r="143" ht="20" customHeight="1">
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="E143" s="23" t="n">
-        <v>202</v>
+        <v>185</v>
       </c>
     </row>
     <row r="144" ht="20" customHeight="1">
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="E144" s="20" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="145" ht="20" customHeight="1">
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="E145" s="23" t="n">
-        <v>147</v>
+        <v>124</v>
       </c>
     </row>
     <row r="146" ht="20" customHeight="1">
@@ -4678,7 +4678,7 @@
         </is>
       </c>
       <c r="E146" s="20" t="n">
-        <v>211</v>
+        <v>229</v>
       </c>
     </row>
     <row r="147" ht="20" customHeight="1">
@@ -4703,7 +4703,7 @@
         </is>
       </c>
       <c r="E147" s="23" t="n">
-        <v>154</v>
+        <v>194</v>
       </c>
     </row>
     <row r="148" ht="20" customHeight="1">
@@ -4728,7 +4728,7 @@
         </is>
       </c>
       <c r="E148" s="20" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="149" ht="20" customHeight="1">
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c r="E149" s="23" t="n">
-        <v>216</v>
+        <v>228</v>
       </c>
     </row>
     <row r="150" ht="20" customHeight="1">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="E150" s="20" t="n">
-        <v>221</v>
+        <v>230</v>
       </c>
     </row>
     <row r="151" ht="20" customHeight="1">
@@ -4803,7 +4803,7 @@
         </is>
       </c>
       <c r="E151" s="23" t="n">
-        <v>147</v>
+        <v>177</v>
       </c>
     </row>
     <row r="152" ht="20" customHeight="1">
@@ -4828,7 +4828,7 @@
         </is>
       </c>
       <c r="E152" s="20" t="n">
-        <v>208</v>
+        <v>225</v>
       </c>
     </row>
     <row r="153" ht="20" customHeight="1">
@@ -4853,7 +4853,7 @@
         </is>
       </c>
       <c r="E153" s="23" t="n">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="154" ht="20" customHeight="1">
@@ -4878,7 +4878,7 @@
         </is>
       </c>
       <c r="E154" s="20" t="n">
-        <v>180</v>
+        <v>142</v>
       </c>
     </row>
     <row r="155" ht="20" customHeight="1">
@@ -4903,7 +4903,7 @@
         </is>
       </c>
       <c r="E155" s="23" t="n">
-        <v>206</v>
+        <v>219</v>
       </c>
     </row>
     <row r="156" ht="20" customHeight="1">
@@ -4928,7 +4928,7 @@
         </is>
       </c>
       <c r="E156" s="20" t="n">
-        <v>114</v>
+        <v>190</v>
       </c>
     </row>
     <row r="157" ht="20" customHeight="1">
@@ -4953,7 +4953,7 @@
         </is>
       </c>
       <c r="E157" s="23" t="n">
-        <v>121</v>
+        <v>226</v>
       </c>
     </row>
     <row r="158" ht="20" customHeight="1">
@@ -4978,7 +4978,7 @@
         </is>
       </c>
       <c r="E158" s="20" t="n">
-        <v>196</v>
+        <v>124</v>
       </c>
     </row>
     <row r="159" ht="20" customHeight="1">
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="E159" s="23" t="n">
-        <v>238</v>
+        <v>171</v>
       </c>
     </row>
     <row r="160" ht="20" customHeight="1">
@@ -5028,7 +5028,7 @@
         </is>
       </c>
       <c r="E160" s="20" t="n">
-        <v>157</v>
+        <v>179</v>
       </c>
     </row>
     <row r="161" ht="20" customHeight="1">
@@ -5053,7 +5053,7 @@
         </is>
       </c>
       <c r="E161" s="23" t="n">
-        <v>173</v>
+        <v>149</v>
       </c>
     </row>
     <row r="162" ht="20" customHeight="1">
@@ -5078,7 +5078,7 @@
         </is>
       </c>
       <c r="E162" s="20" t="n">
-        <v>164</v>
+        <v>227</v>
       </c>
     </row>
     <row r="163" ht="20" customHeight="1">
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="E163" s="23" t="n">
-        <v>179</v>
+        <v>143</v>
       </c>
     </row>
     <row r="164" ht="20" customHeight="1">
@@ -5128,7 +5128,7 @@
         </is>
       </c>
       <c r="E164" s="20" t="n">
-        <v>133</v>
+        <v>155</v>
       </c>
     </row>
     <row r="165" ht="20" customHeight="1">
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="E165" s="23" t="n">
-        <v>174</v>
+        <v>208</v>
       </c>
     </row>
     <row r="166" ht="20" customHeight="1">
@@ -5178,7 +5178,7 @@
         </is>
       </c>
       <c r="E166" s="20" t="n">
-        <v>216</v>
+        <v>194</v>
       </c>
     </row>
     <row r="167" ht="20" customHeight="1">
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="E167" s="23" t="n">
-        <v>180</v>
+        <v>141</v>
       </c>
     </row>
     <row r="168" ht="20" customHeight="1">
@@ -5228,7 +5228,7 @@
         </is>
       </c>
       <c r="E168" s="20" t="n">
-        <v>174</v>
+        <v>146</v>
       </c>
     </row>
     <row r="169" ht="20" customHeight="1">
@@ -5253,7 +5253,7 @@
         </is>
       </c>
       <c r="E169" s="23" t="n">
-        <v>185</v>
+        <v>121</v>
       </c>
     </row>
     <row r="170" ht="20" customHeight="1">
@@ -5278,7 +5278,7 @@
         </is>
       </c>
       <c r="E170" s="20" t="n">
-        <v>171</v>
+        <v>213</v>
       </c>
     </row>
     <row r="171" ht="20" customHeight="1">
@@ -5303,7 +5303,7 @@
         </is>
       </c>
       <c r="E171" s="23" t="n">
-        <v>118</v>
+        <v>208</v>
       </c>
     </row>
     <row r="172" ht="20" customHeight="1">
@@ -5328,7 +5328,7 @@
         </is>
       </c>
       <c r="E172" s="20" t="n">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="173" ht="20" customHeight="1">
@@ -5353,7 +5353,7 @@
         </is>
       </c>
       <c r="E173" s="23" t="n">
-        <v>170</v>
+        <v>231</v>
       </c>
     </row>
     <row r="174" ht="20" customHeight="1">
@@ -5378,7 +5378,7 @@
         </is>
       </c>
       <c r="E174" s="20" t="n">
-        <v>166</v>
+        <v>196</v>
       </c>
     </row>
     <row r="175" ht="20" customHeight="1">
@@ -5403,7 +5403,7 @@
         </is>
       </c>
       <c r="E175" s="23" t="n">
-        <v>174</v>
+        <v>126</v>
       </c>
     </row>
     <row r="176" ht="20" customHeight="1">
@@ -5428,7 +5428,7 @@
         </is>
       </c>
       <c r="E176" s="20" t="n">
-        <v>223</v>
+        <v>133</v>
       </c>
     </row>
     <row r="177" ht="20" customHeight="1">
@@ -5453,7 +5453,7 @@
         </is>
       </c>
       <c r="E177" s="23" t="n">
-        <v>133</v>
+        <v>232</v>
       </c>
     </row>
     <row r="178" ht="20" customHeight="1">
@@ -5478,7 +5478,7 @@
         </is>
       </c>
       <c r="E178" s="20" t="n">
-        <v>236</v>
+        <v>163</v>
       </c>
     </row>
     <row r="179" ht="20" customHeight="1">
@@ -5503,7 +5503,7 @@
         </is>
       </c>
       <c r="E179" s="23" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="180" ht="20" customHeight="1">
@@ -5528,7 +5528,7 @@
         </is>
       </c>
       <c r="E180" s="20" t="n">
-        <v>194</v>
+        <v>202</v>
       </c>
     </row>
     <row r="181" ht="20" customHeight="1">
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="E181" s="23" t="n">
-        <v>230</v>
+        <v>113</v>
       </c>
     </row>
     <row r="182" ht="20" customHeight="1">
@@ -5578,7 +5578,7 @@
         </is>
       </c>
       <c r="E182" s="20" t="n">
-        <v>129</v>
+        <v>217</v>
       </c>
     </row>
     <row r="183" ht="20" customHeight="1">
@@ -5603,7 +5603,7 @@
         </is>
       </c>
       <c r="E183" s="23" t="n">
-        <v>194</v>
+        <v>149</v>
       </c>
     </row>
     <row r="184" ht="20" customHeight="1">
@@ -5628,7 +5628,7 @@
         </is>
       </c>
       <c r="E184" s="20" t="n">
-        <v>201</v>
+        <v>224</v>
       </c>
     </row>
     <row r="185" ht="20" customHeight="1">
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="E185" s="23" t="n">
-        <v>221</v>
+        <v>130</v>
       </c>
     </row>
     <row r="186" ht="20" customHeight="1">
@@ -5678,7 +5678,7 @@
         </is>
       </c>
       <c r="E186" s="20" t="n">
-        <v>223</v>
+        <v>126</v>
       </c>
     </row>
     <row r="187" ht="20" customHeight="1">
@@ -5703,7 +5703,7 @@
         </is>
       </c>
       <c r="E187" s="23" t="n">
-        <v>230</v>
+        <v>138</v>
       </c>
     </row>
     <row r="188" ht="20" customHeight="1">
@@ -5728,7 +5728,7 @@
         </is>
       </c>
       <c r="E188" s="20" t="n">
-        <v>158</v>
+        <v>151</v>
       </c>
     </row>
     <row r="189" ht="20" customHeight="1">
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="E189" s="23" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="190" ht="20" customHeight="1">
@@ -5778,7 +5778,7 @@
         </is>
       </c>
       <c r="E190" s="20" t="n">
-        <v>192</v>
+        <v>157</v>
       </c>
     </row>
     <row r="191" ht="20" customHeight="1">
@@ -5803,7 +5803,7 @@
         </is>
       </c>
       <c r="E191" s="23" t="n">
-        <v>142</v>
+        <v>174</v>
       </c>
     </row>
     <row r="192" ht="20" customHeight="1">
@@ -5828,7 +5828,7 @@
         </is>
       </c>
       <c r="E192" s="20" t="n">
-        <v>148</v>
+        <v>158</v>
       </c>
     </row>
     <row r="193" ht="20" customHeight="1">
@@ -5853,7 +5853,7 @@
         </is>
       </c>
       <c r="E193" s="23" t="n">
-        <v>175</v>
+        <v>156</v>
       </c>
     </row>
     <row r="194" ht="20" customHeight="1">
@@ -5878,7 +5878,7 @@
         </is>
       </c>
       <c r="E194" s="20" t="n">
-        <v>225</v>
+        <v>162</v>
       </c>
     </row>
     <row r="195" ht="20" customHeight="1">
@@ -5903,7 +5903,7 @@
         </is>
       </c>
       <c r="E195" s="23" t="n">
-        <v>119</v>
+        <v>127</v>
       </c>
     </row>
     <row r="196" ht="20" customHeight="1">
@@ -5928,7 +5928,7 @@
         </is>
       </c>
       <c r="E196" s="20" t="n">
-        <v>182</v>
+        <v>112</v>
       </c>
     </row>
     <row r="197" ht="20" customHeight="1">
@@ -5953,7 +5953,7 @@
         </is>
       </c>
       <c r="E197" s="23" t="n">
-        <v>169</v>
+        <v>204</v>
       </c>
     </row>
     <row r="198" ht="20" customHeight="1">
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="E198" s="20" t="n">
-        <v>196</v>
+        <v>232</v>
       </c>
     </row>
     <row r="199" ht="20" customHeight="1">
@@ -6003,7 +6003,7 @@
         </is>
       </c>
       <c r="E199" s="23" t="n">
-        <v>114</v>
+        <v>222</v>
       </c>
     </row>
     <row r="200" ht="20" customHeight="1">
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="E200" s="20" t="n">
-        <v>176</v>
+        <v>149</v>
       </c>
     </row>
     <row r="201" ht="20" customHeight="1">
@@ -6053,7 +6053,7 @@
         </is>
       </c>
       <c r="E201" s="23" t="n">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="202" ht="20" customHeight="1">
@@ -6078,7 +6078,7 @@
         </is>
       </c>
       <c r="E202" s="20" t="n">
-        <v>200</v>
+        <v>123</v>
       </c>
     </row>
     <row r="203" ht="20" customHeight="1">
@@ -6103,7 +6103,7 @@
         </is>
       </c>
       <c r="E203" s="23" t="n">
-        <v>203</v>
+        <v>180</v>
       </c>
     </row>
     <row r="204" ht="20" customHeight="1">
@@ -6128,7 +6128,7 @@
         </is>
       </c>
       <c r="E204" s="20" t="n">
-        <v>169</v>
+        <v>187</v>
       </c>
     </row>
     <row r="205" ht="20" customHeight="1">
@@ -6153,7 +6153,7 @@
         </is>
       </c>
       <c r="E205" s="23" t="n">
-        <v>150</v>
+        <v>134</v>
       </c>
     </row>
     <row r="206" ht="20" customHeight="1">
@@ -6178,7 +6178,7 @@
         </is>
       </c>
       <c r="E206" s="20" t="n">
-        <v>134</v>
+        <v>121</v>
       </c>
     </row>
     <row r="207" ht="20" customHeight="1">
@@ -6203,7 +6203,7 @@
         </is>
       </c>
       <c r="E207" s="23" t="n">
-        <v>163</v>
+        <v>139</v>
       </c>
     </row>
     <row r="208" ht="20" customHeight="1">
@@ -6228,7 +6228,7 @@
         </is>
       </c>
       <c r="E208" s="20" t="n">
-        <v>224</v>
+        <v>220</v>
       </c>
     </row>
     <row r="209" ht="20" customHeight="1">
@@ -6253,7 +6253,7 @@
         </is>
       </c>
       <c r="E209" s="23" t="n">
-        <v>116</v>
+        <v>147</v>
       </c>
     </row>
     <row r="210" ht="20" customHeight="1">
@@ -6278,7 +6278,7 @@
         </is>
       </c>
       <c r="E210" s="20" t="n">
-        <v>168</v>
+        <v>118</v>
       </c>
     </row>
     <row r="211" ht="20" customHeight="1">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="E211" s="23" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="212" ht="20" customHeight="1">
@@ -6328,7 +6328,7 @@
         </is>
       </c>
       <c r="E212" s="20" t="n">
-        <v>230</v>
+        <v>181</v>
       </c>
     </row>
     <row r="213" ht="20" customHeight="1">
@@ -6353,7 +6353,7 @@
         </is>
       </c>
       <c r="E213" s="23" t="n">
-        <v>195</v>
+        <v>237</v>
       </c>
     </row>
     <row r="214" ht="20" customHeight="1">
@@ -6378,7 +6378,7 @@
         </is>
       </c>
       <c r="E214" s="20" t="n">
-        <v>154</v>
+        <v>165</v>
       </c>
     </row>
     <row r="215" ht="20" customHeight="1">
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="E215" s="23" t="n">
-        <v>141</v>
+        <v>194</v>
       </c>
     </row>
     <row r="216" ht="20" customHeight="1">
@@ -6428,7 +6428,7 @@
         </is>
       </c>
       <c r="E216" s="20" t="n">
-        <v>198</v>
+        <v>166</v>
       </c>
     </row>
     <row r="217" ht="20" customHeight="1">
@@ -6453,7 +6453,7 @@
         </is>
       </c>
       <c r="E217" s="23" t="n">
-        <v>173</v>
+        <v>124</v>
       </c>
     </row>
     <row r="218" ht="20" customHeight="1">
@@ -6478,7 +6478,7 @@
         </is>
       </c>
       <c r="E218" s="20" t="n">
-        <v>209</v>
+        <v>240</v>
       </c>
     </row>
     <row r="219" ht="20" customHeight="1">
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="E219" s="23" t="n">
-        <v>218</v>
+        <v>146</v>
       </c>
     </row>
     <row r="220" ht="20" customHeight="1">
@@ -6528,7 +6528,7 @@
         </is>
       </c>
       <c r="E220" s="20" t="n">
-        <v>154</v>
+        <v>211</v>
       </c>
     </row>
     <row r="221" ht="20" customHeight="1">
@@ -6553,7 +6553,7 @@
         </is>
       </c>
       <c r="E221" s="23" t="n">
-        <v>115</v>
+        <v>160</v>
       </c>
     </row>
     <row r="222" ht="20" customHeight="1">
@@ -6578,7 +6578,7 @@
         </is>
       </c>
       <c r="E222" s="20" t="n">
-        <v>110</v>
+        <v>175</v>
       </c>
     </row>
     <row r="223" ht="20" customHeight="1">
@@ -6603,7 +6603,7 @@
         </is>
       </c>
       <c r="E223" s="23" t="n">
-        <v>239</v>
+        <v>122</v>
       </c>
     </row>
     <row r="224" ht="20" customHeight="1">
@@ -6628,7 +6628,7 @@
         </is>
       </c>
       <c r="E224" s="20" t="n">
-        <v>126</v>
+        <v>171</v>
       </c>
     </row>
     <row r="225" ht="20" customHeight="1">
@@ -6653,7 +6653,7 @@
         </is>
       </c>
       <c r="E225" s="23" t="n">
-        <v>146</v>
+        <v>219</v>
       </c>
     </row>
     <row r="226" ht="20" customHeight="1">
@@ -6678,7 +6678,7 @@
         </is>
       </c>
       <c r="E226" s="20" t="n">
-        <v>190</v>
+        <v>127</v>
       </c>
     </row>
     <row r="227" ht="20" customHeight="1">
@@ -6703,7 +6703,7 @@
         </is>
       </c>
       <c r="E227" s="23" t="n">
-        <v>153</v>
+        <v>172</v>
       </c>
     </row>
     <row r="228" ht="20" customHeight="1">
@@ -6728,7 +6728,7 @@
         </is>
       </c>
       <c r="E228" s="20" t="n">
-        <v>155</v>
+        <v>179</v>
       </c>
     </row>
     <row r="229" ht="20" customHeight="1">
@@ -6753,7 +6753,7 @@
         </is>
       </c>
       <c r="E229" s="23" t="n">
-        <v>162</v>
+        <v>238</v>
       </c>
     </row>
     <row r="230" ht="20" customHeight="1">
@@ -6778,7 +6778,7 @@
         </is>
       </c>
       <c r="E230" s="20" t="n">
-        <v>110</v>
+        <v>139</v>
       </c>
     </row>
     <row r="231" ht="20" customHeight="1">
@@ -6803,7 +6803,7 @@
         </is>
       </c>
       <c r="E231" s="23" t="n">
-        <v>231</v>
+        <v>136</v>
       </c>
     </row>
     <row r="232" ht="20" customHeight="1">
@@ -6828,7 +6828,7 @@
         </is>
       </c>
       <c r="E232" s="20" t="n">
-        <v>146</v>
+        <v>235</v>
       </c>
     </row>
     <row r="233" ht="20" customHeight="1">
@@ -6853,7 +6853,7 @@
         </is>
       </c>
       <c r="E233" s="23" t="n">
-        <v>177</v>
+        <v>215</v>
       </c>
     </row>
     <row r="234" ht="20" customHeight="1">
@@ -6878,7 +6878,7 @@
         </is>
       </c>
       <c r="E234" s="20" t="n">
-        <v>125</v>
+        <v>195</v>
       </c>
     </row>
     <row r="235" ht="20" customHeight="1">
@@ -6903,7 +6903,7 @@
         </is>
       </c>
       <c r="E235" s="23" t="n">
-        <v>225</v>
+        <v>151</v>
       </c>
     </row>
     <row r="236" ht="20" customHeight="1">
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="E237" s="23" t="n">
-        <v>168</v>
+        <v>115</v>
       </c>
     </row>
     <row r="238" ht="20" customHeight="1">
@@ -6978,7 +6978,7 @@
         </is>
       </c>
       <c r="E238" s="20" t="n">
-        <v>144</v>
+        <v>221</v>
       </c>
     </row>
     <row r="239" ht="20" customHeight="1">
@@ -7003,7 +7003,7 @@
         </is>
       </c>
       <c r="E239" s="23" t="n">
-        <v>146</v>
+        <v>193</v>
       </c>
     </row>
     <row r="240" ht="20" customHeight="1">
@@ -7028,7 +7028,7 @@
         </is>
       </c>
       <c r="E240" s="20" t="n">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="241" ht="20" customHeight="1">
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="E241" s="23" t="n">
-        <v>203</v>
+        <v>211</v>
       </c>
     </row>
     <row r="242" ht="20" customHeight="1">
@@ -7078,7 +7078,7 @@
         </is>
       </c>
       <c r="E242" s="20" t="n">
-        <v>156</v>
+        <v>218</v>
       </c>
     </row>
     <row r="243" ht="20" customHeight="1">
@@ -7103,7 +7103,7 @@
         </is>
       </c>
       <c r="E243" s="23" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="244" ht="20" customHeight="1">
@@ -7128,7 +7128,7 @@
         </is>
       </c>
       <c r="E244" s="20" t="n">
-        <v>203</v>
+        <v>229</v>
       </c>
     </row>
     <row r="245" ht="20" customHeight="1">
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="E245" s="23" t="n">
-        <v>189</v>
+        <v>175</v>
       </c>
     </row>
     <row r="246" ht="20" customHeight="1">
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="E246" s="20" t="n">
-        <v>148</v>
+        <v>179</v>
       </c>
     </row>
     <row r="247" ht="20" customHeight="1">
@@ -7228,7 +7228,7 @@
         </is>
       </c>
       <c r="E248" s="20" t="n">
-        <v>171</v>
+        <v>164</v>
       </c>
     </row>
     <row r="249" ht="20" customHeight="1">
@@ -7253,7 +7253,7 @@
         </is>
       </c>
       <c r="E249" s="23" t="n">
-        <v>165</v>
+        <v>119</v>
       </c>
     </row>
     <row r="250" ht="20" customHeight="1">
@@ -7278,7 +7278,7 @@
         </is>
       </c>
       <c r="E250" s="20" t="n">
-        <v>237</v>
+        <v>226</v>
       </c>
     </row>
     <row r="251" ht="20" customHeight="1">
@@ -7303,7 +7303,7 @@
         </is>
       </c>
       <c r="E251" s="23" t="n">
-        <v>206</v>
+        <v>230</v>
       </c>
     </row>
     <row r="252" ht="20" customHeight="1">
@@ -7328,7 +7328,7 @@
         </is>
       </c>
       <c r="E252" s="20" t="n">
-        <v>198</v>
+        <v>154</v>
       </c>
     </row>
     <row r="253" ht="20" customHeight="1">
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="E253" s="23" t="n">
-        <v>167</v>
+        <v>139</v>
       </c>
     </row>
     <row r="254" ht="20" customHeight="1">
@@ -7378,7 +7378,7 @@
         </is>
       </c>
       <c r="E254" s="20" t="n">
-        <v>180</v>
+        <v>135</v>
       </c>
     </row>
     <row r="255" ht="20" customHeight="1">
@@ -7403,7 +7403,7 @@
         </is>
       </c>
       <c r="E255" s="23" t="n">
-        <v>143</v>
+        <v>219</v>
       </c>
     </row>
     <row r="256" ht="20" customHeight="1">
@@ -7428,7 +7428,7 @@
         </is>
       </c>
       <c r="E256" s="20" t="n">
-        <v>214</v>
+        <v>199</v>
       </c>
     </row>
     <row r="257" ht="20" customHeight="1">
@@ -7453,7 +7453,7 @@
         </is>
       </c>
       <c r="E257" s="23" t="n">
-        <v>208</v>
+        <v>191</v>
       </c>
     </row>
     <row r="258" ht="20" customHeight="1">
@@ -7478,7 +7478,7 @@
         </is>
       </c>
       <c r="E258" s="20" t="n">
-        <v>111</v>
+        <v>191</v>
       </c>
     </row>
     <row r="259" ht="20" customHeight="1">
@@ -7503,7 +7503,7 @@
         </is>
       </c>
       <c r="E259" s="23" t="n">
-        <v>172</v>
+        <v>183</v>
       </c>
     </row>
     <row r="260" ht="20" customHeight="1">
@@ -7528,7 +7528,7 @@
         </is>
       </c>
       <c r="E260" s="20" t="n">
-        <v>152</v>
+        <v>181</v>
       </c>
     </row>
     <row r="261" ht="20" customHeight="1">
@@ -7553,7 +7553,7 @@
         </is>
       </c>
       <c r="E261" s="23" t="n">
-        <v>168</v>
+        <v>175</v>
       </c>
     </row>
     <row r="262" ht="20" customHeight="1">
@@ -7578,7 +7578,7 @@
         </is>
       </c>
       <c r="E262" s="20" t="n">
-        <v>218</v>
+        <v>120</v>
       </c>
     </row>
     <row r="263" ht="20" customHeight="1">
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="E263" s="23" t="n">
-        <v>182</v>
+        <v>130</v>
       </c>
     </row>
     <row r="264" ht="20" customHeight="1">
@@ -7628,7 +7628,7 @@
         </is>
       </c>
       <c r="E264" s="20" t="n">
-        <v>125</v>
+        <v>238</v>
       </c>
     </row>
     <row r="265" ht="20" customHeight="1">
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="E265" s="23" t="n">
-        <v>174</v>
+        <v>180</v>
       </c>
     </row>
     <row r="266" ht="20" customHeight="1">
@@ -7678,7 +7678,7 @@
         </is>
       </c>
       <c r="E266" s="20" t="n">
-        <v>221</v>
+        <v>184</v>
       </c>
     </row>
     <row r="267" ht="20" customHeight="1">
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="E267" s="23" t="n">
-        <v>116</v>
+        <v>205</v>
       </c>
     </row>
     <row r="268" ht="20" customHeight="1">
@@ -7728,7 +7728,7 @@
         </is>
       </c>
       <c r="E268" s="20" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="269" ht="20" customHeight="1">
@@ -7753,7 +7753,7 @@
         </is>
       </c>
       <c r="E269" s="23" t="n">
-        <v>128</v>
+        <v>161</v>
       </c>
     </row>
     <row r="270" ht="20" customHeight="1">
@@ -7778,7 +7778,7 @@
         </is>
       </c>
       <c r="E270" s="20" t="n">
-        <v>188</v>
+        <v>166</v>
       </c>
     </row>
     <row r="271" ht="20" customHeight="1">
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="E271" s="23" t="n">
-        <v>146</v>
+        <v>155</v>
       </c>
     </row>
     <row r="272" ht="20" customHeight="1">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="E272" s="20" t="n">
-        <v>184</v>
+        <v>202</v>
       </c>
     </row>
     <row r="273" ht="20" customHeight="1">
@@ -7853,7 +7853,7 @@
         </is>
       </c>
       <c r="E273" s="23" t="n">
-        <v>172</v>
+        <v>227</v>
       </c>
     </row>
     <row r="274" ht="20" customHeight="1">
@@ -7878,7 +7878,7 @@
         </is>
       </c>
       <c r="E274" s="20" t="n">
-        <v>139</v>
+        <v>114</v>
       </c>
     </row>
     <row r="275" ht="20" customHeight="1">
@@ -7903,7 +7903,7 @@
         </is>
       </c>
       <c r="E275" s="23" t="n">
-        <v>131</v>
+        <v>205</v>
       </c>
     </row>
     <row r="276" ht="20" customHeight="1">
@@ -7928,7 +7928,7 @@
         </is>
       </c>
       <c r="E276" s="20" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="277" ht="20" customHeight="1">
@@ -7953,7 +7953,7 @@
         </is>
       </c>
       <c r="E277" s="23" t="n">
-        <v>189</v>
+        <v>175</v>
       </c>
     </row>
     <row r="278" ht="20" customHeight="1">
@@ -7978,7 +7978,7 @@
         </is>
       </c>
       <c r="E278" s="20" t="n">
-        <v>200</v>
+        <v>179</v>
       </c>
     </row>
     <row r="279" ht="20" customHeight="1">
@@ -8003,7 +8003,7 @@
         </is>
       </c>
       <c r="E279" s="23" t="n">
-        <v>190</v>
+        <v>232</v>
       </c>
     </row>
     <row r="280" ht="20" customHeight="1">
@@ -8028,7 +8028,7 @@
         </is>
       </c>
       <c r="E280" s="20" t="n">
-        <v>195</v>
+        <v>123</v>
       </c>
     </row>
     <row r="281" ht="20" customHeight="1">
@@ -8053,7 +8053,7 @@
         </is>
       </c>
       <c r="E281" s="23" t="n">
-        <v>174</v>
+        <v>232</v>
       </c>
     </row>
     <row r="282" ht="20" customHeight="1">
@@ -8078,7 +8078,7 @@
         </is>
       </c>
       <c r="E282" s="20" t="n">
-        <v>168</v>
+        <v>133</v>
       </c>
     </row>
     <row r="283" ht="20" customHeight="1">
@@ -8103,7 +8103,7 @@
         </is>
       </c>
       <c r="E283" s="23" t="n">
-        <v>232</v>
+        <v>120</v>
       </c>
     </row>
     <row r="284" ht="20" customHeight="1">
@@ -8128,7 +8128,7 @@
         </is>
       </c>
       <c r="E284" s="20" t="n">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="285" ht="20" customHeight="1">
@@ -8153,7 +8153,7 @@
         </is>
       </c>
       <c r="E285" s="23" t="n">
-        <v>138</v>
+        <v>128</v>
       </c>
     </row>
     <row r="286" ht="20" customHeight="1">
@@ -8178,7 +8178,7 @@
         </is>
       </c>
       <c r="E286" s="20" t="n">
-        <v>186</v>
+        <v>179</v>
       </c>
     </row>
     <row r="287" ht="20" customHeight="1">
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="E287" s="23" t="n">
-        <v>194</v>
+        <v>226</v>
       </c>
     </row>
     <row r="288" ht="20" customHeight="1">
@@ -8228,7 +8228,7 @@
         </is>
       </c>
       <c r="E288" s="20" t="n">
-        <v>113</v>
+        <v>161</v>
       </c>
     </row>
     <row r="289" ht="20" customHeight="1">
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="E289" s="23" t="n">
-        <v>201</v>
+        <v>210</v>
       </c>
     </row>
     <row r="290" ht="20" customHeight="1">
@@ -8278,7 +8278,7 @@
         </is>
       </c>
       <c r="E290" s="20" t="n">
-        <v>112</v>
+        <v>157</v>
       </c>
     </row>
     <row r="291" ht="20" customHeight="1">
@@ -8303,7 +8303,7 @@
         </is>
       </c>
       <c r="E291" s="23" t="n">
-        <v>117</v>
+        <v>151</v>
       </c>
     </row>
     <row r="292" ht="20" customHeight="1">
@@ -8328,7 +8328,7 @@
         </is>
       </c>
       <c r="E292" s="20" t="n">
-        <v>227</v>
+        <v>125</v>
       </c>
     </row>
     <row r="293" ht="20" customHeight="1">
@@ -8353,7 +8353,7 @@
         </is>
       </c>
       <c r="E293" s="23" t="n">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="294" ht="20" customHeight="1">
@@ -8378,7 +8378,7 @@
         </is>
       </c>
       <c r="E294" s="20" t="n">
-        <v>132</v>
+        <v>215</v>
       </c>
     </row>
     <row r="295" ht="20" customHeight="1">
@@ -8403,7 +8403,7 @@
         </is>
       </c>
       <c r="E295" s="23" t="n">
-        <v>196</v>
+        <v>231</v>
       </c>
     </row>
     <row r="296" ht="20" customHeight="1">
@@ -8428,7 +8428,7 @@
         </is>
       </c>
       <c r="E296" s="20" t="n">
-        <v>223</v>
+        <v>149</v>
       </c>
     </row>
     <row r="297" ht="20" customHeight="1">
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="E297" s="23" t="n">
-        <v>154</v>
+        <v>225</v>
       </c>
     </row>
     <row r="298" ht="20" customHeight="1">
@@ -8478,7 +8478,7 @@
         </is>
       </c>
       <c r="E298" s="20" t="n">
-        <v>225</v>
+        <v>237</v>
       </c>
     </row>
     <row r="299" ht="20" customHeight="1">
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="E299" s="23" t="n">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="300" ht="20" customHeight="1">
@@ -8528,7 +8528,7 @@
         </is>
       </c>
       <c r="E300" s="20" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="301" ht="20" customHeight="1">
@@ -8553,7 +8553,7 @@
         </is>
       </c>
       <c r="E301" s="23" t="n">
-        <v>157</v>
+        <v>122</v>
       </c>
     </row>
     <row r="302" ht="20" customHeight="1">
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="E302" s="20" t="n">
-        <v>136</v>
+        <v>116</v>
       </c>
     </row>
     <row r="303" ht="20" customHeight="1">
@@ -8603,7 +8603,7 @@
         </is>
       </c>
       <c r="E303" s="23" t="n">
-        <v>125</v>
+        <v>160</v>
       </c>
     </row>
     <row r="304" ht="20" customHeight="1">
@@ -8628,7 +8628,7 @@
         </is>
       </c>
       <c r="E304" s="20" t="n">
-        <v>126</v>
+        <v>202</v>
       </c>
     </row>
     <row r="305" ht="20" customHeight="1">
@@ -8653,7 +8653,7 @@
         </is>
       </c>
       <c r="E305" s="23" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="306" ht="20" customHeight="1">
@@ -8678,7 +8678,7 @@
         </is>
       </c>
       <c r="E306" s="20" t="n">
-        <v>149</v>
+        <v>213</v>
       </c>
     </row>
     <row r="307" ht="20" customHeight="1">
@@ -8703,7 +8703,7 @@
         </is>
       </c>
       <c r="E307" s="23" t="n">
-        <v>141</v>
+        <v>179</v>
       </c>
     </row>
     <row r="308" ht="20" customHeight="1">
@@ -8728,7 +8728,7 @@
         </is>
       </c>
       <c r="E308" s="20" t="n">
-        <v>188</v>
+        <v>113</v>
       </c>
     </row>
     <row r="309" ht="20" customHeight="1">
@@ -8753,7 +8753,7 @@
         </is>
       </c>
       <c r="E309" s="23" t="n">
-        <v>124</v>
+        <v>183</v>
       </c>
     </row>
     <row r="310" ht="20" customHeight="1">
@@ -8778,7 +8778,7 @@
         </is>
       </c>
       <c r="E310" s="20" t="n">
-        <v>139</v>
+        <v>169</v>
       </c>
     </row>
     <row r="311" ht="20" customHeight="1">
@@ -8803,7 +8803,7 @@
         </is>
       </c>
       <c r="E311" s="23" t="n">
-        <v>117</v>
+        <v>155</v>
       </c>
     </row>
     <row r="312" ht="20" customHeight="1">
@@ -8828,7 +8828,7 @@
         </is>
       </c>
       <c r="E312" s="20" t="n">
-        <v>213</v>
+        <v>190</v>
       </c>
     </row>
     <row r="313" ht="20" customHeight="1">
@@ -8853,7 +8853,7 @@
         </is>
       </c>
       <c r="E313" s="23" t="n">
-        <v>141</v>
+        <v>135</v>
       </c>
     </row>
     <row r="314" ht="20" customHeight="1">
@@ -8878,7 +8878,7 @@
         </is>
       </c>
       <c r="E314" s="20" t="n">
-        <v>135</v>
+        <v>188</v>
       </c>
     </row>
     <row r="315" ht="20" customHeight="1">
@@ -8903,7 +8903,7 @@
         </is>
       </c>
       <c r="E315" s="23" t="n">
-        <v>186</v>
+        <v>123</v>
       </c>
     </row>
     <row r="316" ht="20" customHeight="1">
@@ -8928,7 +8928,7 @@
         </is>
       </c>
       <c r="E316" s="20" t="n">
-        <v>240</v>
+        <v>194</v>
       </c>
     </row>
     <row r="317" ht="20" customHeight="1">
@@ -8953,7 +8953,7 @@
         </is>
       </c>
       <c r="E317" s="23" t="n">
-        <v>216</v>
+        <v>122</v>
       </c>
     </row>
     <row r="318" ht="20" customHeight="1">
@@ -8978,7 +8978,7 @@
         </is>
       </c>
       <c r="E318" s="20" t="n">
-        <v>202</v>
+        <v>157</v>
       </c>
     </row>
     <row r="319" ht="20" customHeight="1">
@@ -9003,7 +9003,7 @@
         </is>
       </c>
       <c r="E319" s="23" t="n">
-        <v>134</v>
+        <v>234</v>
       </c>
     </row>
     <row r="320" ht="20" customHeight="1">
@@ -9028,7 +9028,7 @@
         </is>
       </c>
       <c r="E320" s="20" t="n">
-        <v>190</v>
+        <v>226</v>
       </c>
     </row>
     <row r="321" ht="20" customHeight="1">
@@ -9053,7 +9053,7 @@
         </is>
       </c>
       <c r="E321" s="23" t="n">
-        <v>140</v>
+        <v>129</v>
       </c>
     </row>
     <row r="322" ht="20" customHeight="1">
@@ -9078,7 +9078,7 @@
         </is>
       </c>
       <c r="E322" s="20" t="n">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="323" ht="20" customHeight="1">
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="E323" s="23" t="n">
-        <v>181</v>
+        <v>228</v>
       </c>
     </row>
     <row r="324" ht="20" customHeight="1">
@@ -9128,7 +9128,7 @@
         </is>
       </c>
       <c r="E324" s="20" t="n">
-        <v>121</v>
+        <v>178</v>
       </c>
     </row>
     <row r="325" ht="20" customHeight="1">
@@ -9153,7 +9153,7 @@
         </is>
       </c>
       <c r="E325" s="23" t="n">
-        <v>160</v>
+        <v>226</v>
       </c>
     </row>
     <row r="326" ht="20" customHeight="1">
@@ -9178,7 +9178,7 @@
         </is>
       </c>
       <c r="E326" s="20" t="n">
-        <v>147</v>
+        <v>201</v>
       </c>
     </row>
     <row r="327" ht="20" customHeight="1">
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="E327" s="23" t="n">
-        <v>129</v>
+        <v>169</v>
       </c>
     </row>
     <row r="328" ht="20" customHeight="1">
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="E328" s="20" t="n">
-        <v>189</v>
+        <v>223</v>
       </c>
     </row>
     <row r="329" ht="20" customHeight="1">
@@ -9253,7 +9253,7 @@
         </is>
       </c>
       <c r="E329" s="23" t="n">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="330" ht="20" customHeight="1">
@@ -9278,7 +9278,7 @@
         </is>
       </c>
       <c r="E330" s="20" t="n">
-        <v>217</v>
+        <v>117</v>
       </c>
     </row>
     <row r="331" ht="20" customHeight="1">
@@ -9303,7 +9303,7 @@
         </is>
       </c>
       <c r="E331" s="23" t="n">
-        <v>174</v>
+        <v>157</v>
       </c>
     </row>
     <row r="332" ht="20" customHeight="1">
@@ -9328,7 +9328,7 @@
         </is>
       </c>
       <c r="E332" s="20" t="n">
-        <v>136</v>
+        <v>154</v>
       </c>
     </row>
     <row r="333" ht="20" customHeight="1">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="E333" s="23" t="n">
-        <v>112</v>
+        <v>184</v>
       </c>
     </row>
     <row r="334" ht="20" customHeight="1">
@@ -9378,7 +9378,7 @@
         </is>
       </c>
       <c r="E334" s="20" t="n">
-        <v>167</v>
+        <v>240</v>
       </c>
     </row>
     <row r="335" ht="20" customHeight="1">
@@ -9403,7 +9403,7 @@
         </is>
       </c>
       <c r="E335" s="23" t="n">
-        <v>232</v>
+        <v>141</v>
       </c>
     </row>
     <row r="336" ht="20" customHeight="1">
@@ -9428,7 +9428,7 @@
         </is>
       </c>
       <c r="E336" s="20" t="n">
-        <v>179</v>
+        <v>199</v>
       </c>
     </row>
     <row r="337" ht="20" customHeight="1">
@@ -9453,7 +9453,7 @@
         </is>
       </c>
       <c r="E337" s="23" t="n">
-        <v>201</v>
+        <v>232</v>
       </c>
     </row>
     <row r="338" ht="20" customHeight="1">
@@ -9478,7 +9478,7 @@
         </is>
       </c>
       <c r="E338" s="20" t="n">
-        <v>112</v>
+        <v>157</v>
       </c>
     </row>
     <row r="339" ht="20" customHeight="1">
@@ -9503,7 +9503,7 @@
         </is>
       </c>
       <c r="E339" s="23" t="n">
-        <v>144</v>
+        <v>192</v>
       </c>
     </row>
     <row r="340" ht="20" customHeight="1">
@@ -9528,7 +9528,7 @@
         </is>
       </c>
       <c r="E340" s="20" t="n">
-        <v>110</v>
+        <v>191</v>
       </c>
     </row>
     <row r="341" ht="20" customHeight="1">
@@ -9553,7 +9553,7 @@
         </is>
       </c>
       <c r="E341" s="23" t="n">
-        <v>224</v>
+        <v>163</v>
       </c>
     </row>
     <row r="342" ht="20" customHeight="1">
@@ -9578,7 +9578,7 @@
         </is>
       </c>
       <c r="E342" s="20" t="n">
-        <v>111</v>
+        <v>234</v>
       </c>
     </row>
     <row r="343" ht="20" customHeight="1">
@@ -9603,7 +9603,7 @@
         </is>
       </c>
       <c r="E343" s="23" t="n">
-        <v>117</v>
+        <v>224</v>
       </c>
     </row>
     <row r="344" ht="20" customHeight="1">
@@ -9628,7 +9628,7 @@
         </is>
       </c>
       <c r="E344" s="20" t="n">
-        <v>225</v>
+        <v>205</v>
       </c>
     </row>
     <row r="345" ht="20" customHeight="1">
@@ -9653,7 +9653,7 @@
         </is>
       </c>
       <c r="E345" s="23" t="n">
-        <v>228</v>
+        <v>215</v>
       </c>
     </row>
     <row r="346" ht="20" customHeight="1">
@@ -9678,7 +9678,7 @@
         </is>
       </c>
       <c r="E346" s="20" t="n">
-        <v>205</v>
+        <v>237</v>
       </c>
     </row>
     <row r="347" ht="20" customHeight="1">
@@ -9703,7 +9703,7 @@
         </is>
       </c>
       <c r="E347" s="23" t="n">
-        <v>178</v>
+        <v>171</v>
       </c>
     </row>
     <row r="348" ht="20" customHeight="1">
@@ -9728,7 +9728,7 @@
         </is>
       </c>
       <c r="E348" s="20" t="n">
-        <v>187</v>
+        <v>237</v>
       </c>
     </row>
     <row r="349" ht="20" customHeight="1">
@@ -9753,7 +9753,7 @@
         </is>
       </c>
       <c r="E349" s="23" t="n">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
     <row r="350" ht="20" customHeight="1">
@@ -9778,7 +9778,7 @@
         </is>
       </c>
       <c r="E350" s="20" t="n">
-        <v>113</v>
+        <v>201</v>
       </c>
     </row>
     <row r="351" ht="20" customHeight="1">
@@ -9803,7 +9803,7 @@
         </is>
       </c>
       <c r="E351" s="23" t="n">
-        <v>144</v>
+        <v>176</v>
       </c>
     </row>
     <row r="352" ht="20" customHeight="1">
@@ -9828,7 +9828,7 @@
         </is>
       </c>
       <c r="E352" s="20" t="n">
-        <v>185</v>
+        <v>202</v>
       </c>
     </row>
     <row r="353" ht="20" customHeight="1">
@@ -9853,7 +9853,7 @@
         </is>
       </c>
       <c r="E353" s="23" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="354" ht="20" customHeight="1">
@@ -9878,7 +9878,7 @@
         </is>
       </c>
       <c r="E354" s="20" t="n">
-        <v>121</v>
+        <v>199</v>
       </c>
     </row>
     <row r="355" ht="20" customHeight="1">
@@ -9903,7 +9903,7 @@
         </is>
       </c>
       <c r="E355" s="23" t="n">
-        <v>119</v>
+        <v>177</v>
       </c>
     </row>
     <row r="356" ht="20" customHeight="1">
@@ -9928,7 +9928,7 @@
         </is>
       </c>
       <c r="E356" s="20" t="n">
-        <v>237</v>
+        <v>222</v>
       </c>
     </row>
     <row r="357" ht="20" customHeight="1">
@@ -9953,7 +9953,7 @@
         </is>
       </c>
       <c r="E357" s="23" t="n">
-        <v>163</v>
+        <v>220</v>
       </c>
     </row>
     <row r="358" ht="20" customHeight="1">
@@ -9978,7 +9978,7 @@
         </is>
       </c>
       <c r="E358" s="20" t="n">
-        <v>196</v>
+        <v>130</v>
       </c>
     </row>
     <row r="359" ht="20" customHeight="1">
@@ -10003,7 +10003,7 @@
         </is>
       </c>
       <c r="E359" s="23" t="n">
-        <v>125</v>
+        <v>136</v>
       </c>
     </row>
     <row r="360" ht="20" customHeight="1">
@@ -10028,7 +10028,7 @@
         </is>
       </c>
       <c r="E360" s="20" t="n">
-        <v>129</v>
+        <v>188</v>
       </c>
     </row>
     <row r="361" ht="20" customHeight="1">
@@ -10053,7 +10053,7 @@
         </is>
       </c>
       <c r="E361" s="23" t="n">
-        <v>225</v>
+        <v>167</v>
       </c>
     </row>
     <row r="362" ht="20" customHeight="1">
@@ -10078,7 +10078,7 @@
         </is>
       </c>
       <c r="E362" s="20" t="n">
-        <v>200</v>
+        <v>118</v>
       </c>
     </row>
     <row r="363" ht="20" customHeight="1">
@@ -10103,7 +10103,7 @@
         </is>
       </c>
       <c r="E363" s="23" t="n">
-        <v>235</v>
+        <v>185</v>
       </c>
     </row>
     <row r="364" ht="20" customHeight="1">
@@ -10128,7 +10128,7 @@
         </is>
       </c>
       <c r="E364" s="20" t="n">
-        <v>229</v>
+        <v>124</v>
       </c>
     </row>
     <row r="365" ht="20" customHeight="1">
@@ -10153,7 +10153,7 @@
         </is>
       </c>
       <c r="E365" s="23" t="n">
-        <v>116</v>
+        <v>129</v>
       </c>
     </row>
     <row r="366" ht="20" customHeight="1">
@@ -10178,7 +10178,7 @@
         </is>
       </c>
       <c r="E366" s="20" t="n">
-        <v>228</v>
+        <v>203</v>
       </c>
     </row>
     <row r="367" ht="20" customHeight="1">
@@ -10203,7 +10203,7 @@
         </is>
       </c>
       <c r="E367" s="23" t="n">
-        <v>205</v>
+        <v>210</v>
       </c>
     </row>
     <row r="368" ht="20" customHeight="1">
@@ -10228,7 +10228,7 @@
         </is>
       </c>
       <c r="E368" s="20" t="n">
-        <v>120</v>
+        <v>205</v>
       </c>
     </row>
     <row r="369" ht="20" customHeight="1">
@@ -10253,7 +10253,7 @@
         </is>
       </c>
       <c r="E369" s="23" t="n">
-        <v>157</v>
+        <v>216</v>
       </c>
     </row>
     <row r="370" ht="20" customHeight="1">
@@ -10278,7 +10278,7 @@
         </is>
       </c>
       <c r="E370" s="20" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="371" ht="20" customHeight="1">
@@ -10303,7 +10303,7 @@
         </is>
       </c>
       <c r="E371" s="23" t="n">
-        <v>183</v>
+        <v>203</v>
       </c>
     </row>
     <row r="372" ht="20" customHeight="1">
@@ -10328,7 +10328,7 @@
         </is>
       </c>
       <c r="E372" s="20" t="n">
-        <v>236</v>
+        <v>194</v>
       </c>
     </row>
     <row r="373" ht="20" customHeight="1">
@@ -10353,7 +10353,7 @@
         </is>
       </c>
       <c r="E373" s="23" t="n">
-        <v>124</v>
+        <v>235</v>
       </c>
     </row>
     <row r="374" ht="20" customHeight="1">
@@ -10378,7 +10378,7 @@
         </is>
       </c>
       <c r="E374" s="20" t="n">
-        <v>213</v>
+        <v>199</v>
       </c>
     </row>
     <row r="375" ht="20" customHeight="1">
@@ -10403,7 +10403,7 @@
         </is>
       </c>
       <c r="E375" s="23" t="n">
-        <v>221</v>
+        <v>132</v>
       </c>
     </row>
     <row r="376" ht="20" customHeight="1">
@@ -10428,7 +10428,7 @@
         </is>
       </c>
       <c r="E376" s="20" t="n">
-        <v>168</v>
+        <v>122</v>
       </c>
     </row>
     <row r="377" ht="20" customHeight="1">
@@ -10453,7 +10453,7 @@
         </is>
       </c>
       <c r="E377" s="23" t="n">
-        <v>162</v>
+        <v>184</v>
       </c>
     </row>
     <row r="378" ht="20" customHeight="1">
@@ -10478,7 +10478,7 @@
         </is>
       </c>
       <c r="E378" s="20" t="n">
-        <v>163</v>
+        <v>212</v>
       </c>
     </row>
     <row r="379" ht="20" customHeight="1">
@@ -10503,7 +10503,7 @@
         </is>
       </c>
       <c r="E379" s="23" t="n">
-        <v>148</v>
+        <v>165</v>
       </c>
     </row>
     <row r="380" ht="20" customHeight="1">
@@ -10528,7 +10528,7 @@
         </is>
       </c>
       <c r="E380" s="20" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="381" ht="20" customHeight="1">
@@ -10553,7 +10553,7 @@
         </is>
       </c>
       <c r="E381" s="23" t="n">
-        <v>150</v>
+        <v>129</v>
       </c>
     </row>
     <row r="382" ht="20" customHeight="1">
@@ -10578,7 +10578,7 @@
         </is>
       </c>
       <c r="E382" s="20" t="n">
-        <v>220</v>
+        <v>148</v>
       </c>
     </row>
     <row r="383" ht="20" customHeight="1">
@@ -10603,7 +10603,7 @@
         </is>
       </c>
       <c r="E383" s="23" t="n">
-        <v>221</v>
+        <v>225</v>
       </c>
     </row>
     <row r="384" ht="20" customHeight="1">
@@ -10628,7 +10628,7 @@
         </is>
       </c>
       <c r="E384" s="20" t="n">
-        <v>236</v>
+        <v>125</v>
       </c>
     </row>
     <row r="385" ht="20" customHeight="1">
@@ -10653,7 +10653,7 @@
         </is>
       </c>
       <c r="E385" s="23" t="n">
-        <v>220</v>
+        <v>189</v>
       </c>
     </row>
     <row r="386" ht="20" customHeight="1">
@@ -10678,7 +10678,7 @@
         </is>
       </c>
       <c r="E386" s="20" t="n">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="387" ht="20" customHeight="1">
@@ -10703,7 +10703,7 @@
         </is>
       </c>
       <c r="E387" s="23" t="n">
-        <v>179</v>
+        <v>169</v>
       </c>
     </row>
     <row r="388" ht="20" customHeight="1">
@@ -10728,7 +10728,7 @@
         </is>
       </c>
       <c r="E388" s="20" t="n">
-        <v>111</v>
+        <v>230</v>
       </c>
     </row>
     <row r="389" ht="20" customHeight="1">
@@ -10753,7 +10753,7 @@
         </is>
       </c>
       <c r="E389" s="23" t="n">
-        <v>126</v>
+        <v>179</v>
       </c>
     </row>
     <row r="390" ht="20" customHeight="1">
@@ -10778,7 +10778,7 @@
         </is>
       </c>
       <c r="E390" s="20" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="391" ht="20" customHeight="1">
@@ -10803,7 +10803,7 @@
         </is>
       </c>
       <c r="E391" s="23" t="n">
-        <v>158</v>
+        <v>165</v>
       </c>
     </row>
     <row r="392" ht="20" customHeight="1">
@@ -10828,7 +10828,7 @@
         </is>
       </c>
       <c r="E392" s="20" t="n">
-        <v>134</v>
+        <v>122</v>
       </c>
     </row>
     <row r="393" ht="20" customHeight="1">
@@ -10853,7 +10853,7 @@
         </is>
       </c>
       <c r="E393" s="23" t="n">
-        <v>216</v>
+        <v>240</v>
       </c>
     </row>
     <row r="394" ht="20" customHeight="1">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="E394" s="20" t="n">
-        <v>125</v>
+        <v>174</v>
       </c>
     </row>
     <row r="395" ht="20" customHeight="1">
@@ -10903,7 +10903,7 @@
         </is>
       </c>
       <c r="E395" s="23" t="n">
-        <v>186</v>
+        <v>238</v>
       </c>
     </row>
     <row r="396" ht="20" customHeight="1">
@@ -10928,7 +10928,7 @@
         </is>
       </c>
       <c r="E396" s="20" t="n">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="397" ht="20" customHeight="1">
@@ -10953,7 +10953,7 @@
         </is>
       </c>
       <c r="E397" s="23" t="n">
-        <v>229</v>
+        <v>133</v>
       </c>
     </row>
     <row r="398" ht="20" customHeight="1">
@@ -10978,7 +10978,7 @@
         </is>
       </c>
       <c r="E398" s="20" t="n">
-        <v>141</v>
+        <v>221</v>
       </c>
     </row>
     <row r="399" ht="20" customHeight="1">
@@ -11003,7 +11003,7 @@
         </is>
       </c>
       <c r="E399" s="23" t="n">
-        <v>212</v>
+        <v>228</v>
       </c>
     </row>
     <row r="400" ht="20" customHeight="1">
@@ -11028,7 +11028,7 @@
         </is>
       </c>
       <c r="E400" s="20" t="n">
-        <v>231</v>
+        <v>218</v>
       </c>
     </row>
     <row r="401" ht="20" customHeight="1">
@@ -11053,7 +11053,7 @@
         </is>
       </c>
       <c r="E401" s="23" t="n">
-        <v>238</v>
+        <v>184</v>
       </c>
     </row>
     <row r="402" ht="20" customHeight="1">
@@ -11078,7 +11078,7 @@
         </is>
       </c>
       <c r="E402" s="20" t="n">
-        <v>183</v>
+        <v>130</v>
       </c>
     </row>
     <row r="403" ht="20" customHeight="1">
@@ -11103,7 +11103,7 @@
         </is>
       </c>
       <c r="E403" s="23" t="n">
-        <v>209</v>
+        <v>146</v>
       </c>
     </row>
     <row r="404" ht="20" customHeight="1">
@@ -11128,7 +11128,7 @@
         </is>
       </c>
       <c r="E404" s="20" t="n">
-        <v>146</v>
+        <v>112</v>
       </c>
     </row>
     <row r="405" ht="20" customHeight="1">
@@ -11153,7 +11153,7 @@
         </is>
       </c>
       <c r="E405" s="23" t="n">
-        <v>141</v>
+        <v>199</v>
       </c>
     </row>
     <row r="406" ht="20" customHeight="1">
@@ -11178,7 +11178,7 @@
         </is>
       </c>
       <c r="E406" s="20" t="n">
-        <v>157</v>
+        <v>178</v>
       </c>
     </row>
     <row r="407" ht="20" customHeight="1">
@@ -11203,7 +11203,7 @@
         </is>
       </c>
       <c r="E407" s="23" t="n">
-        <v>172</v>
+        <v>218</v>
       </c>
     </row>
     <row r="408" ht="20" customHeight="1">
@@ -11228,7 +11228,7 @@
         </is>
       </c>
       <c r="E408" s="20" t="n">
-        <v>150</v>
+        <v>132</v>
       </c>
     </row>
     <row r="409" ht="20" customHeight="1">
@@ -11253,7 +11253,7 @@
         </is>
       </c>
       <c r="E409" s="23" t="n">
-        <v>138</v>
+        <v>121</v>
       </c>
     </row>
     <row r="410" ht="20" customHeight="1">
@@ -11278,7 +11278,7 @@
         </is>
       </c>
       <c r="E410" s="20" t="n">
-        <v>203</v>
+        <v>145</v>
       </c>
     </row>
     <row r="411" ht="20" customHeight="1">
@@ -11303,7 +11303,7 @@
         </is>
       </c>
       <c r="E411" s="23" t="n">
-        <v>154</v>
+        <v>227</v>
       </c>
     </row>
     <row r="412" ht="20" customHeight="1">
@@ -11328,7 +11328,7 @@
         </is>
       </c>
       <c r="E412" s="20" t="n">
-        <v>163</v>
+        <v>157</v>
       </c>
     </row>
     <row r="413" ht="20" customHeight="1">
@@ -11353,7 +11353,7 @@
         </is>
       </c>
       <c r="E413" s="23" t="n">
-        <v>132</v>
+        <v>193</v>
       </c>
     </row>
     <row r="414" ht="20" customHeight="1">
@@ -11378,7 +11378,7 @@
         </is>
       </c>
       <c r="E414" s="20" t="n">
-        <v>219</v>
+        <v>195</v>
       </c>
     </row>
     <row r="415" ht="20" customHeight="1">
@@ -11403,7 +11403,7 @@
         </is>
       </c>
       <c r="E415" s="23" t="n">
-        <v>138</v>
+        <v>143</v>
       </c>
     </row>
     <row r="416" ht="20" customHeight="1">
@@ -11428,7 +11428,7 @@
         </is>
       </c>
       <c r="E416" s="20" t="n">
-        <v>193</v>
+        <v>128</v>
       </c>
     </row>
     <row r="417" ht="20" customHeight="1">
@@ -11453,7 +11453,7 @@
         </is>
       </c>
       <c r="E417" s="23" t="n">
-        <v>157</v>
+        <v>169</v>
       </c>
     </row>
     <row r="418" ht="20" customHeight="1">
@@ -11478,7 +11478,7 @@
         </is>
       </c>
       <c r="E418" s="20" t="n">
-        <v>225</v>
+        <v>124</v>
       </c>
     </row>
     <row r="419" ht="20" customHeight="1">
@@ -11503,7 +11503,7 @@
         </is>
       </c>
       <c r="E419" s="23" t="n">
-        <v>190</v>
+        <v>227</v>
       </c>
     </row>
     <row r="420" ht="20" customHeight="1">
@@ -11528,7 +11528,7 @@
         </is>
       </c>
       <c r="E420" s="20" t="n">
-        <v>173</v>
+        <v>134</v>
       </c>
     </row>
     <row r="421" ht="20" customHeight="1">
@@ -11553,7 +11553,7 @@
         </is>
       </c>
       <c r="E421" s="23" t="n">
-        <v>231</v>
+        <v>146</v>
       </c>
     </row>
     <row r="422" ht="20" customHeight="1">
@@ -11578,7 +11578,7 @@
         </is>
       </c>
       <c r="E422" s="20" t="n">
-        <v>201</v>
+        <v>128</v>
       </c>
     </row>
     <row r="423" ht="20" customHeight="1">
@@ -11603,7 +11603,7 @@
         </is>
       </c>
       <c r="E423" s="23" t="n">
-        <v>228</v>
+        <v>187</v>
       </c>
     </row>
     <row r="424" ht="20" customHeight="1">
@@ -11628,7 +11628,7 @@
         </is>
       </c>
       <c r="E424" s="20" t="n">
-        <v>225</v>
+        <v>163</v>
       </c>
     </row>
     <row r="425" ht="20" customHeight="1">
@@ -11653,7 +11653,7 @@
         </is>
       </c>
       <c r="E425" s="23" t="n">
-        <v>144</v>
+        <v>121</v>
       </c>
     </row>
     <row r="426" ht="20" customHeight="1">
@@ -11678,7 +11678,7 @@
         </is>
       </c>
       <c r="E426" s="20" t="n">
-        <v>228</v>
+        <v>160</v>
       </c>
     </row>
     <row r="427" ht="20" customHeight="1">
@@ -11703,7 +11703,7 @@
         </is>
       </c>
       <c r="E427" s="23" t="n">
-        <v>141</v>
+        <v>151</v>
       </c>
     </row>
     <row r="428" ht="20" customHeight="1">
@@ -11728,7 +11728,7 @@
         </is>
       </c>
       <c r="E428" s="20" t="n">
-        <v>211</v>
+        <v>195</v>
       </c>
     </row>
     <row r="429" ht="20" customHeight="1">
@@ -11753,7 +11753,7 @@
         </is>
       </c>
       <c r="E429" s="23" t="n">
-        <v>215</v>
+        <v>137</v>
       </c>
     </row>
     <row r="430" ht="20" customHeight="1">
@@ -11778,7 +11778,7 @@
         </is>
       </c>
       <c r="E430" s="20" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="431" ht="20" customHeight="1">
@@ -11803,7 +11803,7 @@
         </is>
       </c>
       <c r="E431" s="23" t="n">
-        <v>138</v>
+        <v>171</v>
       </c>
     </row>
     <row r="432" ht="20" customHeight="1">
@@ -11828,7 +11828,7 @@
         </is>
       </c>
       <c r="E432" s="20" t="n">
-        <v>136</v>
+        <v>199</v>
       </c>
     </row>
     <row r="433" ht="20" customHeight="1">
@@ -11853,7 +11853,7 @@
         </is>
       </c>
       <c r="E433" s="23" t="n">
-        <v>118</v>
+        <v>200</v>
       </c>
     </row>
     <row r="434" ht="20" customHeight="1">
@@ -11878,7 +11878,7 @@
         </is>
       </c>
       <c r="E434" s="20" t="n">
-        <v>204</v>
+        <v>117</v>
       </c>
     </row>
     <row r="435" ht="20" customHeight="1">
@@ -11903,7 +11903,7 @@
         </is>
       </c>
       <c r="E435" s="23" t="n">
-        <v>129</v>
+        <v>237</v>
       </c>
     </row>
     <row r="436" ht="20" customHeight="1">
@@ -11928,7 +11928,7 @@
         </is>
       </c>
       <c r="E436" s="20" t="n">
-        <v>152</v>
+        <v>110</v>
       </c>
     </row>
     <row r="437" ht="20" customHeight="1">
@@ -11953,7 +11953,7 @@
         </is>
       </c>
       <c r="E437" s="23" t="n">
-        <v>226</v>
+        <v>161</v>
       </c>
     </row>
     <row r="438" ht="20" customHeight="1">
@@ -11978,7 +11978,7 @@
         </is>
       </c>
       <c r="E438" s="20" t="n">
-        <v>194</v>
+        <v>172</v>
       </c>
     </row>
     <row r="439" ht="20" customHeight="1">
@@ -12003,7 +12003,7 @@
         </is>
       </c>
       <c r="E439" s="23" t="n">
-        <v>240</v>
+        <v>223</v>
       </c>
     </row>
     <row r="440" ht="20" customHeight="1">
@@ -12028,7 +12028,7 @@
         </is>
       </c>
       <c r="E440" s="20" t="n">
-        <v>166</v>
+        <v>192</v>
       </c>
     </row>
     <row r="441" ht="20" customHeight="1">
@@ -12053,7 +12053,7 @@
         </is>
       </c>
       <c r="E441" s="23" t="n">
-        <v>121</v>
+        <v>170</v>
       </c>
     </row>
     <row r="442" ht="20" customHeight="1">
@@ -12078,7 +12078,7 @@
         </is>
       </c>
       <c r="E442" s="20" t="n">
-        <v>205</v>
+        <v>115</v>
       </c>
     </row>
     <row r="443" ht="20" customHeight="1">
@@ -12103,7 +12103,7 @@
         </is>
       </c>
       <c r="E443" s="23" t="n">
-        <v>114</v>
+        <v>138</v>
       </c>
     </row>
     <row r="444" ht="20" customHeight="1">
@@ -12128,7 +12128,7 @@
         </is>
       </c>
       <c r="E444" s="20" t="n">
-        <v>155</v>
+        <v>227</v>
       </c>
     </row>
     <row r="445" ht="20" customHeight="1">
@@ -12153,7 +12153,7 @@
         </is>
       </c>
       <c r="E445" s="23" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="446" ht="20" customHeight="1">
@@ -12178,7 +12178,7 @@
         </is>
       </c>
       <c r="E446" s="20" t="n">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="447" ht="20" customHeight="1">
@@ -12203,7 +12203,7 @@
         </is>
       </c>
       <c r="E447" s="23" t="n">
-        <v>238</v>
+        <v>161</v>
       </c>
     </row>
     <row r="448" ht="20" customHeight="1">
@@ -12228,7 +12228,7 @@
         </is>
       </c>
       <c r="E448" s="20" t="n">
-        <v>116</v>
+        <v>189</v>
       </c>
     </row>
     <row r="449" ht="20" customHeight="1">
@@ -12253,7 +12253,7 @@
         </is>
       </c>
       <c r="E449" s="23" t="n">
-        <v>204</v>
+        <v>110</v>
       </c>
     </row>
     <row r="450" ht="20" customHeight="1">
@@ -12278,7 +12278,7 @@
         </is>
       </c>
       <c r="E450" s="20" t="n">
-        <v>224</v>
+        <v>211</v>
       </c>
     </row>
     <row r="451" ht="20" customHeight="1">
@@ -12303,7 +12303,7 @@
         </is>
       </c>
       <c r="E451" s="23" t="n">
-        <v>232</v>
+        <v>138</v>
       </c>
     </row>
     <row r="452" ht="20" customHeight="1">
@@ -12328,7 +12328,7 @@
         </is>
       </c>
       <c r="E452" s="20" t="n">
-        <v>198</v>
+        <v>233</v>
       </c>
     </row>
     <row r="453" ht="20" customHeight="1">
@@ -12353,7 +12353,7 @@
         </is>
       </c>
       <c r="E453" s="23" t="n">
-        <v>158</v>
+        <v>235</v>
       </c>
     </row>
     <row r="454" ht="20" customHeight="1">
@@ -12378,7 +12378,7 @@
         </is>
       </c>
       <c r="E454" s="20" t="n">
-        <v>137</v>
+        <v>154</v>
       </c>
     </row>
     <row r="455" ht="20" customHeight="1">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="E455" s="23" t="n">
-        <v>180</v>
+        <v>189</v>
       </c>
     </row>
     <row r="456" ht="20" customHeight="1">
@@ -12428,7 +12428,7 @@
         </is>
       </c>
       <c r="E456" s="20" t="n">
-        <v>158</v>
+        <v>212</v>
       </c>
     </row>
     <row r="457" ht="20" customHeight="1">
@@ -12453,7 +12453,7 @@
         </is>
       </c>
       <c r="E457" s="23" t="n">
-        <v>240</v>
+        <v>117</v>
       </c>
     </row>
     <row r="458" ht="20" customHeight="1">
@@ -12478,7 +12478,7 @@
         </is>
       </c>
       <c r="E458" s="20" t="n">
-        <v>217</v>
+        <v>192</v>
       </c>
     </row>
     <row r="459" ht="20" customHeight="1">
@@ -12503,7 +12503,7 @@
         </is>
       </c>
       <c r="E459" s="23" t="n">
-        <v>135</v>
+        <v>231</v>
       </c>
     </row>
     <row r="460" ht="20" customHeight="1">
@@ -12528,7 +12528,7 @@
         </is>
       </c>
       <c r="E460" s="20" t="n">
-        <v>193</v>
+        <v>210</v>
       </c>
     </row>
     <row r="461" ht="20" customHeight="1">
@@ -12553,7 +12553,7 @@
         </is>
       </c>
       <c r="E461" s="23" t="n">
-        <v>194</v>
+        <v>215</v>
       </c>
     </row>
     <row r="462" ht="20" customHeight="1">
@@ -12578,7 +12578,7 @@
         </is>
       </c>
       <c r="E462" s="20" t="n">
-        <v>237</v>
+        <v>193</v>
       </c>
     </row>
     <row r="463" ht="20" customHeight="1">
@@ -12603,7 +12603,7 @@
         </is>
       </c>
       <c r="E463" s="23" t="n">
-        <v>160</v>
+        <v>129</v>
       </c>
     </row>
     <row r="464" ht="20" customHeight="1">
@@ -12628,7 +12628,7 @@
         </is>
       </c>
       <c r="E464" s="20" t="n">
-        <v>199</v>
+        <v>239</v>
       </c>
     </row>
     <row r="465" ht="20" customHeight="1">
@@ -12653,7 +12653,7 @@
         </is>
       </c>
       <c r="E465" s="23" t="n">
-        <v>216</v>
+        <v>111</v>
       </c>
     </row>
     <row r="466" ht="20" customHeight="1">
@@ -12678,7 +12678,7 @@
         </is>
       </c>
       <c r="E466" s="20" t="n">
-        <v>202</v>
+        <v>173</v>
       </c>
     </row>
     <row r="467" ht="20" customHeight="1">
@@ -12703,7 +12703,7 @@
         </is>
       </c>
       <c r="E467" s="23" t="n">
-        <v>228</v>
+        <v>218</v>
       </c>
     </row>
     <row r="468" ht="20" customHeight="1">
@@ -12728,7 +12728,7 @@
         </is>
       </c>
       <c r="E468" s="20" t="n">
-        <v>180</v>
+        <v>238</v>
       </c>
     </row>
     <row r="469" ht="20" customHeight="1">
@@ -12753,7 +12753,7 @@
         </is>
       </c>
       <c r="E469" s="23" t="n">
-        <v>214</v>
+        <v>235</v>
       </c>
     </row>
     <row r="470" ht="20" customHeight="1">
@@ -12778,7 +12778,7 @@
         </is>
       </c>
       <c r="E470" s="20" t="n">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="471" ht="20" customHeight="1">
@@ -12803,7 +12803,7 @@
         </is>
       </c>
       <c r="E471" s="23" t="n">
-        <v>192</v>
+        <v>210</v>
       </c>
     </row>
     <row r="472" ht="20" customHeight="1">
@@ -12828,7 +12828,7 @@
         </is>
       </c>
       <c r="E472" s="20" t="n">
-        <v>237</v>
+        <v>212</v>
       </c>
     </row>
     <row r="473" ht="20" customHeight="1">
@@ -12853,7 +12853,7 @@
         </is>
       </c>
       <c r="E473" s="23" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="474" ht="20" customHeight="1">
@@ -12878,7 +12878,7 @@
         </is>
       </c>
       <c r="E474" s="20" t="n">
-        <v>183</v>
+        <v>110</v>
       </c>
     </row>
     <row r="475" ht="20" customHeight="1">
@@ -12903,7 +12903,7 @@
         </is>
       </c>
       <c r="E475" s="23" t="n">
-        <v>225</v>
+        <v>174</v>
       </c>
     </row>
     <row r="476" ht="20" customHeight="1">
@@ -12928,7 +12928,7 @@
         </is>
       </c>
       <c r="E476" s="20" t="n">
-        <v>234</v>
+        <v>182</v>
       </c>
     </row>
     <row r="477" ht="20" customHeight="1">
@@ -12953,7 +12953,7 @@
         </is>
       </c>
       <c r="E477" s="23" t="n">
-        <v>212</v>
+        <v>114</v>
       </c>
     </row>
     <row r="478" ht="20" customHeight="1">
@@ -12978,7 +12978,7 @@
         </is>
       </c>
       <c r="E478" s="20" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="479" ht="20" customHeight="1">
@@ -13003,7 +13003,7 @@
         </is>
       </c>
       <c r="E479" s="23" t="n">
-        <v>211</v>
+        <v>229</v>
       </c>
     </row>
     <row r="480" ht="20" customHeight="1">
@@ -13028,7 +13028,7 @@
         </is>
       </c>
       <c r="E480" s="20" t="n">
-        <v>116</v>
+        <v>224</v>
       </c>
     </row>
     <row r="481" ht="20" customHeight="1">
@@ -13053,7 +13053,7 @@
         </is>
       </c>
       <c r="E481" s="23" t="n">
-        <v>232</v>
+        <v>159</v>
       </c>
     </row>
     <row r="482" ht="20" customHeight="1">
@@ -13078,7 +13078,7 @@
         </is>
       </c>
       <c r="E482" s="20" t="n">
-        <v>221</v>
+        <v>111</v>
       </c>
     </row>
     <row r="483" ht="20" customHeight="1">
@@ -13103,7 +13103,7 @@
         </is>
       </c>
       <c r="E483" s="23" t="n">
-        <v>111</v>
+        <v>142</v>
       </c>
     </row>
     <row r="484" ht="20" customHeight="1">
@@ -13128,7 +13128,7 @@
         </is>
       </c>
       <c r="E484" s="20" t="n">
-        <v>116</v>
+        <v>157</v>
       </c>
     </row>
     <row r="485" ht="20" customHeight="1">
@@ -13153,7 +13153,7 @@
         </is>
       </c>
       <c r="E485" s="23" t="n">
-        <v>137</v>
+        <v>240</v>
       </c>
     </row>
     <row r="486" ht="20" customHeight="1">
@@ -13178,7 +13178,7 @@
         </is>
       </c>
       <c r="E486" s="20" t="n">
-        <v>227</v>
+        <v>205</v>
       </c>
     </row>
     <row r="487" ht="20" customHeight="1">
@@ -13203,7 +13203,7 @@
         </is>
       </c>
       <c r="E487" s="23" t="n">
-        <v>195</v>
+        <v>240</v>
       </c>
     </row>
     <row r="488" ht="20" customHeight="1">
@@ -13228,7 +13228,7 @@
         </is>
       </c>
       <c r="E488" s="20" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
     </row>
     <row r="489" ht="20" customHeight="1">
@@ -13253,7 +13253,7 @@
         </is>
       </c>
       <c r="E489" s="23" t="n">
-        <v>161</v>
+        <v>175</v>
       </c>
     </row>
     <row r="490" ht="20" customHeight="1">
@@ -13278,7 +13278,7 @@
         </is>
       </c>
       <c r="E490" s="20" t="n">
-        <v>111</v>
+        <v>177</v>
       </c>
     </row>
     <row r="491" ht="20" customHeight="1">
@@ -13303,7 +13303,7 @@
         </is>
       </c>
       <c r="E491" s="23" t="n">
-        <v>172</v>
+        <v>149</v>
       </c>
     </row>
     <row r="492" ht="20" customHeight="1">
@@ -13328,7 +13328,7 @@
         </is>
       </c>
       <c r="E492" s="20" t="n">
-        <v>114</v>
+        <v>240</v>
       </c>
     </row>
     <row r="493" ht="20" customHeight="1">
@@ -13353,7 +13353,7 @@
         </is>
       </c>
       <c r="E493" s="23" t="n">
-        <v>184</v>
+        <v>216</v>
       </c>
     </row>
     <row r="494" ht="20" customHeight="1">
@@ -13378,7 +13378,7 @@
         </is>
       </c>
       <c r="E494" s="20" t="n">
-        <v>217</v>
+        <v>112</v>
       </c>
     </row>
     <row r="495" ht="20" customHeight="1">
@@ -13403,7 +13403,7 @@
         </is>
       </c>
       <c r="E495" s="23" t="n">
-        <v>217</v>
+        <v>127</v>
       </c>
     </row>
     <row r="496" ht="20" customHeight="1">
@@ -13428,7 +13428,7 @@
         </is>
       </c>
       <c r="E496" s="20" t="n">
-        <v>134</v>
+        <v>152</v>
       </c>
     </row>
     <row r="497" ht="20" customHeight="1">
@@ -13453,7 +13453,7 @@
         </is>
       </c>
       <c r="E497" s="23" t="n">
-        <v>177</v>
+        <v>193</v>
       </c>
     </row>
     <row r="498" ht="20" customHeight="1">
@@ -13478,7 +13478,7 @@
         </is>
       </c>
       <c r="E498" s="20" t="n">
-        <v>235</v>
+        <v>165</v>
       </c>
     </row>
     <row r="499" ht="20" customHeight="1">
@@ -13503,7 +13503,7 @@
         </is>
       </c>
       <c r="E499" s="23" t="n">
-        <v>137</v>
+        <v>231</v>
       </c>
     </row>
     <row r="500" ht="20" customHeight="1">
@@ -13528,7 +13528,7 @@
         </is>
       </c>
       <c r="E500" s="20" t="n">
-        <v>140</v>
+        <v>166</v>
       </c>
     </row>
     <row r="501" ht="20" customHeight="1">
@@ -13553,7 +13553,7 @@
         </is>
       </c>
       <c r="E501" s="23" t="n">
-        <v>220</v>
+        <v>144</v>
       </c>
     </row>
     <row r="502" ht="20" customHeight="1">
@@ -13578,7 +13578,7 @@
         </is>
       </c>
       <c r="E502" s="20" t="n">
-        <v>141</v>
+        <v>238</v>
       </c>
     </row>
     <row r="503" ht="20" customHeight="1">
@@ -13603,7 +13603,7 @@
         </is>
       </c>
       <c r="E503" s="23" t="n">
-        <v>118</v>
+        <v>187</v>
       </c>
     </row>
     <row r="504" ht="20" customHeight="1">
@@ -13628,7 +13628,7 @@
         </is>
       </c>
       <c r="E504" s="20" t="n">
-        <v>185</v>
+        <v>127</v>
       </c>
     </row>
     <row r="505" ht="20" customHeight="1">
@@ -13653,7 +13653,7 @@
         </is>
       </c>
       <c r="E505" s="23" t="n">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="506" ht="20" customHeight="1">
@@ -13678,7 +13678,7 @@
         </is>
       </c>
       <c r="E506" s="20" t="n">
-        <v>136</v>
+        <v>143</v>
       </c>
     </row>
     <row r="507" ht="20" customHeight="1">
@@ -13703,7 +13703,7 @@
         </is>
       </c>
       <c r="E507" s="23" t="n">
-        <v>136</v>
+        <v>223</v>
       </c>
     </row>
     <row r="508" ht="20" customHeight="1">
@@ -13728,7 +13728,7 @@
         </is>
       </c>
       <c r="E508" s="20" t="n">
-        <v>229</v>
+        <v>111</v>
       </c>
     </row>
     <row r="509" ht="20" customHeight="1">
@@ -13753,7 +13753,7 @@
         </is>
       </c>
       <c r="E509" s="23" t="n">
-        <v>171</v>
+        <v>195</v>
       </c>
     </row>
     <row r="510" ht="20" customHeight="1">
@@ -13778,7 +13778,7 @@
         </is>
       </c>
       <c r="E510" s="20" t="n">
-        <v>165</v>
+        <v>191</v>
       </c>
     </row>
     <row r="511" ht="20" customHeight="1">
@@ -13803,7 +13803,7 @@
         </is>
       </c>
       <c r="E511" s="23" t="n">
-        <v>131</v>
+        <v>209</v>
       </c>
     </row>
     <row r="512" ht="20" customHeight="1">
@@ -13828,7 +13828,7 @@
         </is>
       </c>
       <c r="E512" s="20" t="n">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="513" ht="20" customHeight="1">
@@ -13853,7 +13853,7 @@
         </is>
       </c>
       <c r="E513" s="23" t="n">
-        <v>202</v>
+        <v>182</v>
       </c>
     </row>
     <row r="514" ht="20" customHeight="1">
@@ -13878,7 +13878,7 @@
         </is>
       </c>
       <c r="E514" s="20" t="n">
-        <v>235</v>
+        <v>168</v>
       </c>
     </row>
     <row r="515" ht="20" customHeight="1">
@@ -13903,7 +13903,7 @@
         </is>
       </c>
       <c r="E515" s="23" t="n">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="516" ht="20" customHeight="1">
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="E516" s="20" t="n">
-        <v>162</v>
+        <v>128</v>
       </c>
     </row>
     <row r="517" ht="20" customHeight="1">
@@ -13953,7 +13953,7 @@
         </is>
       </c>
       <c r="E517" s="23" t="n">
-        <v>169</v>
+        <v>229</v>
       </c>
     </row>
     <row r="518" ht="20" customHeight="1">
@@ -13978,7 +13978,7 @@
         </is>
       </c>
       <c r="E518" s="20" t="n">
-        <v>127</v>
+        <v>118</v>
       </c>
     </row>
     <row r="519" ht="20" customHeight="1">
@@ -14003,7 +14003,7 @@
         </is>
       </c>
       <c r="E519" s="23" t="n">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="520" ht="20" customHeight="1">
@@ -14028,7 +14028,7 @@
         </is>
       </c>
       <c r="E520" s="20" t="n">
-        <v>124</v>
+        <v>209</v>
       </c>
     </row>
     <row r="521" ht="20" customHeight="1">
@@ -14053,7 +14053,7 @@
         </is>
       </c>
       <c r="E521" s="23" t="n">
-        <v>132</v>
+        <v>237</v>
       </c>
     </row>
     <row r="522" ht="20" customHeight="1">
@@ -14078,7 +14078,7 @@
         </is>
       </c>
       <c r="E522" s="20" t="n">
-        <v>221</v>
+        <v>157</v>
       </c>
     </row>
     <row r="523" ht="20" customHeight="1">
@@ -14103,7 +14103,7 @@
         </is>
       </c>
       <c r="E523" s="23" t="n">
-        <v>111</v>
+        <v>180</v>
       </c>
     </row>
     <row r="524" ht="20" customHeight="1">
@@ -14128,7 +14128,7 @@
         </is>
       </c>
       <c r="E524" s="20" t="n">
-        <v>217</v>
+        <v>164</v>
       </c>
     </row>
     <row r="525" ht="20" customHeight="1">
@@ -14153,7 +14153,7 @@
         </is>
       </c>
       <c r="E525" s="23" t="n">
-        <v>176</v>
+        <v>166</v>
       </c>
     </row>
     <row r="526" ht="20" customHeight="1">
@@ -14178,7 +14178,7 @@
         </is>
       </c>
       <c r="E526" s="20" t="n">
-        <v>217</v>
+        <v>235</v>
       </c>
     </row>
     <row r="527" ht="20" customHeight="1">
@@ -14203,7 +14203,7 @@
         </is>
       </c>
       <c r="E527" s="23" t="n">
-        <v>137</v>
+        <v>219</v>
       </c>
     </row>
     <row r="528" ht="20" customHeight="1">
@@ -14228,7 +14228,7 @@
         </is>
       </c>
       <c r="E528" s="20" t="n">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="529" ht="20" customHeight="1">
@@ -14253,7 +14253,7 @@
         </is>
       </c>
       <c r="E529" s="23" t="n">
-        <v>156</v>
+        <v>217</v>
       </c>
     </row>
     <row r="530" ht="20" customHeight="1">
@@ -14278,7 +14278,7 @@
         </is>
       </c>
       <c r="E530" s="20" t="n">
-        <v>147</v>
+        <v>141</v>
       </c>
     </row>
     <row r="531" ht="20" customHeight="1">
@@ -14303,7 +14303,7 @@
         </is>
       </c>
       <c r="E531" s="23" t="n">
-        <v>137</v>
+        <v>236</v>
       </c>
     </row>
     <row r="532" ht="20" customHeight="1">
@@ -14328,7 +14328,7 @@
         </is>
       </c>
       <c r="E532" s="20" t="n">
-        <v>161</v>
+        <v>222</v>
       </c>
     </row>
     <row r="533" ht="20" customHeight="1">
@@ -14353,7 +14353,7 @@
         </is>
       </c>
       <c r="E533" s="23" t="n">
-        <v>144</v>
+        <v>189</v>
       </c>
     </row>
     <row r="534" ht="20" customHeight="1">
@@ -14378,7 +14378,7 @@
         </is>
       </c>
       <c r="E534" s="20" t="n">
-        <v>159</v>
+        <v>197</v>
       </c>
     </row>
     <row r="535" ht="20" customHeight="1">
@@ -14403,7 +14403,7 @@
         </is>
       </c>
       <c r="E535" s="23" t="n">
-        <v>185</v>
+        <v>179</v>
       </c>
     </row>
     <row r="536" ht="20" customHeight="1">
@@ -14428,7 +14428,7 @@
         </is>
       </c>
       <c r="E536" s="20" t="n">
-        <v>230</v>
+        <v>136</v>
       </c>
     </row>
     <row r="537" ht="20" customHeight="1">
@@ -14453,7 +14453,7 @@
         </is>
       </c>
       <c r="E537" s="23" t="n">
-        <v>187</v>
+        <v>167</v>
       </c>
     </row>
     <row r="538" ht="20" customHeight="1">
@@ -14478,7 +14478,7 @@
         </is>
       </c>
       <c r="E538" s="20" t="n">
-        <v>164</v>
+        <v>227</v>
       </c>
     </row>
     <row r="539" ht="20" customHeight="1">
@@ -14503,7 +14503,7 @@
         </is>
       </c>
       <c r="E539" s="23" t="n">
-        <v>143</v>
+        <v>186</v>
       </c>
     </row>
     <row r="540" ht="20" customHeight="1">
@@ -14528,7 +14528,7 @@
         </is>
       </c>
       <c r="E540" s="20" t="n">
-        <v>194</v>
+        <v>177</v>
       </c>
     </row>
     <row r="541" ht="20" customHeight="1">
@@ -14553,7 +14553,7 @@
         </is>
       </c>
       <c r="E541" s="23" t="n">
-        <v>236</v>
+        <v>228</v>
       </c>
     </row>
     <row r="542" ht="20" customHeight="1">
@@ -14578,7 +14578,7 @@
         </is>
       </c>
       <c r="E542" s="20" t="n">
-        <v>200</v>
+        <v>162</v>
       </c>
     </row>
     <row r="543" ht="20" customHeight="1">
@@ -14603,7 +14603,7 @@
         </is>
       </c>
       <c r="E543" s="23" t="n">
-        <v>110</v>
+        <v>124</v>
       </c>
     </row>
     <row r="544" ht="20" customHeight="1">
@@ -14628,7 +14628,7 @@
         </is>
       </c>
       <c r="E544" s="20" t="n">
-        <v>178</v>
+        <v>110</v>
       </c>
     </row>
     <row r="545" ht="20" customHeight="1">
@@ -14653,7 +14653,7 @@
         </is>
       </c>
       <c r="E545" s="23" t="n">
-        <v>160</v>
+        <v>144</v>
       </c>
     </row>
     <row r="546" ht="20" customHeight="1">
@@ -14678,7 +14678,7 @@
         </is>
       </c>
       <c r="E546" s="20" t="n">
-        <v>206</v>
+        <v>223</v>
       </c>
     </row>
     <row r="547" ht="20" customHeight="1">
@@ -14703,7 +14703,7 @@
         </is>
       </c>
       <c r="E547" s="23" t="n">
-        <v>207</v>
+        <v>236</v>
       </c>
     </row>
     <row r="548" ht="20" customHeight="1">
@@ -14728,7 +14728,7 @@
         </is>
       </c>
       <c r="E548" s="20" t="n">
-        <v>143</v>
+        <v>237</v>
       </c>
     </row>
     <row r="549" ht="20" customHeight="1">
@@ -14753,7 +14753,7 @@
         </is>
       </c>
       <c r="E549" s="23" t="n">
-        <v>113</v>
+        <v>238</v>
       </c>
     </row>
     <row r="550" ht="20" customHeight="1">
@@ -14778,7 +14778,7 @@
         </is>
       </c>
       <c r="E550" s="20" t="n">
-        <v>121</v>
+        <v>227</v>
       </c>
     </row>
     <row r="551" ht="20" customHeight="1">
@@ -14803,7 +14803,7 @@
         </is>
       </c>
       <c r="E551" s="23" t="n">
-        <v>172</v>
+        <v>194</v>
       </c>
     </row>
     <row r="552" ht="20" customHeight="1">
@@ -14828,7 +14828,7 @@
         </is>
       </c>
       <c r="E552" s="20" t="n">
-        <v>131</v>
+        <v>119</v>
       </c>
     </row>
     <row r="553" ht="20" customHeight="1">
@@ -14853,7 +14853,7 @@
         </is>
       </c>
       <c r="E553" s="23" t="n">
-        <v>118</v>
+        <v>182</v>
       </c>
     </row>
     <row r="554" ht="20" customHeight="1">
@@ -14878,7 +14878,7 @@
         </is>
       </c>
       <c r="E554" s="20" t="n">
-        <v>193</v>
+        <v>218</v>
       </c>
     </row>
     <row r="555" ht="20" customHeight="1">
@@ -14903,7 +14903,7 @@
         </is>
       </c>
       <c r="E555" s="23" t="n">
-        <v>149</v>
+        <v>134</v>
       </c>
     </row>
     <row r="556" ht="20" customHeight="1">
@@ -14928,7 +14928,7 @@
         </is>
       </c>
       <c r="E556" s="20" t="n">
-        <v>167</v>
+        <v>221</v>
       </c>
     </row>
     <row r="557" ht="20" customHeight="1">
@@ -14953,7 +14953,7 @@
         </is>
       </c>
       <c r="E557" s="23" t="n">
-        <v>152</v>
+        <v>220</v>
       </c>
     </row>
     <row r="558" ht="20" customHeight="1">
@@ -14978,7 +14978,7 @@
         </is>
       </c>
       <c r="E558" s="20" t="n">
-        <v>161</v>
+        <v>149</v>
       </c>
     </row>
     <row r="559" ht="20" customHeight="1">
@@ -15003,7 +15003,7 @@
         </is>
       </c>
       <c r="E559" s="23" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="560" ht="20" customHeight="1">
@@ -15028,7 +15028,7 @@
         </is>
       </c>
       <c r="E560" s="20" t="n">
-        <v>153</v>
+        <v>216</v>
       </c>
     </row>
     <row r="561" ht="20" customHeight="1">
@@ -15053,7 +15053,7 @@
         </is>
       </c>
       <c r="E561" s="23" t="n">
-        <v>133</v>
+        <v>192</v>
       </c>
     </row>
     <row r="562" ht="20" customHeight="1">
@@ -15078,7 +15078,7 @@
         </is>
       </c>
       <c r="E562" s="20" t="n">
-        <v>181</v>
+        <v>120</v>
       </c>
     </row>
     <row r="563" ht="20" customHeight="1">
@@ -15103,7 +15103,7 @@
         </is>
       </c>
       <c r="E563" s="23" t="n">
-        <v>197</v>
+        <v>203</v>
       </c>
     </row>
     <row r="564" ht="20" customHeight="1">
@@ -15128,7 +15128,7 @@
         </is>
       </c>
       <c r="E564" s="20" t="n">
-        <v>140</v>
+        <v>166</v>
       </c>
     </row>
     <row r="565" ht="20" customHeight="1">
@@ -15153,7 +15153,7 @@
         </is>
       </c>
       <c r="E565" s="23" t="n">
-        <v>157</v>
+        <v>121</v>
       </c>
     </row>
     <row r="566" ht="20" customHeight="1">
@@ -15178,7 +15178,7 @@
         </is>
       </c>
       <c r="E566" s="20" t="n">
-        <v>126</v>
+        <v>170</v>
       </c>
     </row>
     <row r="567" ht="20" customHeight="1">
@@ -15203,7 +15203,7 @@
         </is>
       </c>
       <c r="E567" s="23" t="n">
-        <v>154</v>
+        <v>201</v>
       </c>
     </row>
     <row r="568" ht="20" customHeight="1">
@@ -15228,7 +15228,7 @@
         </is>
       </c>
       <c r="E568" s="20" t="n">
-        <v>173</v>
+        <v>119</v>
       </c>
     </row>
     <row r="569" ht="20" customHeight="1">
@@ -15253,7 +15253,7 @@
         </is>
       </c>
       <c r="E569" s="23" t="n">
-        <v>184</v>
+        <v>153</v>
       </c>
     </row>
     <row r="570" ht="20" customHeight="1">
@@ -15278,7 +15278,7 @@
         </is>
       </c>
       <c r="E570" s="20" t="n">
-        <v>121</v>
+        <v>236</v>
       </c>
     </row>
     <row r="571" ht="20" customHeight="1">
@@ -15303,7 +15303,7 @@
         </is>
       </c>
       <c r="E571" s="23" t="n">
-        <v>144</v>
+        <v>221</v>
       </c>
     </row>
     <row r="572" ht="20" customHeight="1">
@@ -15328,7 +15328,7 @@
         </is>
       </c>
       <c r="E572" s="20" t="n">
-        <v>164</v>
+        <v>224</v>
       </c>
     </row>
     <row r="573" ht="20" customHeight="1">
@@ -15353,7 +15353,7 @@
         </is>
       </c>
       <c r="E573" s="23" t="n">
-        <v>185</v>
+        <v>226</v>
       </c>
     </row>
     <row r="574" ht="20" customHeight="1">
@@ -15378,7 +15378,7 @@
         </is>
       </c>
       <c r="E574" s="20" t="n">
-        <v>150</v>
+        <v>129</v>
       </c>
     </row>
     <row r="575" ht="20" customHeight="1">
@@ -15403,7 +15403,7 @@
         </is>
       </c>
       <c r="E575" s="23" t="n">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="576" ht="20" customHeight="1">
@@ -15428,7 +15428,7 @@
         </is>
       </c>
       <c r="E576" s="20" t="n">
-        <v>190</v>
+        <v>123</v>
       </c>
     </row>
     <row r="577" ht="20" customHeight="1">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="E577" s="23" t="n">
-        <v>219</v>
+        <v>186</v>
       </c>
     </row>
     <row r="578" ht="20" customHeight="1">
@@ -15478,7 +15478,7 @@
         </is>
       </c>
       <c r="E578" s="20" t="n">
-        <v>116</v>
+        <v>145</v>
       </c>
     </row>
     <row r="579" ht="20" customHeight="1">
@@ -15503,7 +15503,7 @@
         </is>
       </c>
       <c r="E579" s="23" t="n">
-        <v>188</v>
+        <v>229</v>
       </c>
     </row>
     <row r="580" ht="20" customHeight="1">
@@ -15528,7 +15528,7 @@
         </is>
       </c>
       <c r="E580" s="20" t="n">
-        <v>179</v>
+        <v>217</v>
       </c>
     </row>
     <row r="581" ht="20" customHeight="1">
@@ -15553,7 +15553,7 @@
         </is>
       </c>
       <c r="E581" s="23" t="n">
-        <v>217</v>
+        <v>146</v>
       </c>
     </row>
     <row r="582" ht="20" customHeight="1">
@@ -15578,7 +15578,7 @@
         </is>
       </c>
       <c r="E582" s="20" t="n">
-        <v>236</v>
+        <v>134</v>
       </c>
     </row>
     <row r="583" ht="20" customHeight="1">
@@ -15603,7 +15603,7 @@
         </is>
       </c>
       <c r="E583" s="23" t="n">
-        <v>142</v>
+        <v>156</v>
       </c>
     </row>
     <row r="584" ht="20" customHeight="1">
@@ -15628,7 +15628,7 @@
         </is>
       </c>
       <c r="E584" s="20" t="n">
-        <v>126</v>
+        <v>192</v>
       </c>
     </row>
     <row r="585" ht="20" customHeight="1">
@@ -15653,7 +15653,7 @@
         </is>
       </c>
       <c r="E585" s="23" t="n">
-        <v>224</v>
+        <v>147</v>
       </c>
     </row>
     <row r="586" ht="20" customHeight="1">
@@ -15678,7 +15678,7 @@
         </is>
       </c>
       <c r="E586" s="20" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="587" ht="20" customHeight="1">
@@ -15703,7 +15703,7 @@
         </is>
       </c>
       <c r="E587" s="23" t="n">
-        <v>208</v>
+        <v>136</v>
       </c>
     </row>
     <row r="588" ht="20" customHeight="1">
@@ -15728,7 +15728,7 @@
         </is>
       </c>
       <c r="E588" s="20" t="n">
-        <v>119</v>
+        <v>142</v>
       </c>
     </row>
     <row r="589" ht="20" customHeight="1">
@@ -15753,7 +15753,7 @@
         </is>
       </c>
       <c r="E589" s="23" t="n">
-        <v>146</v>
+        <v>203</v>
       </c>
     </row>
     <row r="590" ht="20" customHeight="1">
@@ -15778,7 +15778,7 @@
         </is>
       </c>
       <c r="E590" s="20" t="n">
-        <v>187</v>
+        <v>211</v>
       </c>
     </row>
     <row r="591" ht="20" customHeight="1">
@@ -15803,7 +15803,7 @@
         </is>
       </c>
       <c r="E591" s="23" t="n">
-        <v>175</v>
+        <v>217</v>
       </c>
     </row>
     <row r="592" ht="20" customHeight="1">
@@ -15828,7 +15828,7 @@
         </is>
       </c>
       <c r="E592" s="20" t="n">
-        <v>213</v>
+        <v>172</v>
       </c>
     </row>
     <row r="593" ht="20" customHeight="1">
@@ -15853,7 +15853,7 @@
         </is>
       </c>
       <c r="E593" s="23" t="n">
-        <v>116</v>
+        <v>160</v>
       </c>
     </row>
     <row r="594" ht="20" customHeight="1">
@@ -15878,7 +15878,7 @@
         </is>
       </c>
       <c r="E594" s="20" t="n">
-        <v>222</v>
+        <v>172</v>
       </c>
     </row>
     <row r="595" ht="20" customHeight="1">
@@ -15903,7 +15903,7 @@
         </is>
       </c>
       <c r="E595" s="23" t="n">
-        <v>114</v>
+        <v>154</v>
       </c>
     </row>
     <row r="596" ht="20" customHeight="1">
@@ -15928,7 +15928,7 @@
         </is>
       </c>
       <c r="E596" s="20" t="n">
-        <v>148</v>
+        <v>182</v>
       </c>
     </row>
     <row r="597" ht="20" customHeight="1">
@@ -15953,7 +15953,7 @@
         </is>
       </c>
       <c r="E597" s="23" t="n">
-        <v>130</v>
+        <v>219</v>
       </c>
     </row>
     <row r="598" ht="20" customHeight="1">
@@ -15978,7 +15978,7 @@
         </is>
       </c>
       <c r="E598" s="20" t="n">
-        <v>204</v>
+        <v>167</v>
       </c>
     </row>
     <row r="599" ht="20" customHeight="1">
@@ -16003,7 +16003,7 @@
         </is>
       </c>
       <c r="E599" s="23" t="n">
-        <v>195</v>
+        <v>163</v>
       </c>
     </row>
     <row r="600" ht="20" customHeight="1">
@@ -16028,7 +16028,7 @@
         </is>
       </c>
       <c r="E600" s="20" t="n">
-        <v>191</v>
+        <v>226</v>
       </c>
     </row>
     <row r="601" ht="20" customHeight="1">
@@ -16053,7 +16053,7 @@
         </is>
       </c>
       <c r="E601" s="23" t="n">
-        <v>123</v>
+        <v>189</v>
       </c>
     </row>
     <row r="602" ht="20" customHeight="1">
@@ -16078,7 +16078,7 @@
         </is>
       </c>
       <c r="E602" s="20" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="603" ht="20" customHeight="1">
@@ -16103,7 +16103,7 @@
         </is>
       </c>
       <c r="E603" s="23" t="n">
-        <v>179</v>
+        <v>203</v>
       </c>
     </row>
     <row r="604" ht="20" customHeight="1">
@@ -16128,7 +16128,7 @@
         </is>
       </c>
       <c r="E604" s="20" t="n">
-        <v>162</v>
+        <v>146</v>
       </c>
     </row>
     <row r="605" ht="20" customHeight="1">
@@ -16153,7 +16153,7 @@
         </is>
       </c>
       <c r="E605" s="23" t="n">
-        <v>237</v>
+        <v>210</v>
       </c>
     </row>
     <row r="606" ht="20" customHeight="1">
@@ -16178,7 +16178,7 @@
         </is>
       </c>
       <c r="E606" s="20" t="n">
-        <v>207</v>
+        <v>186</v>
       </c>
     </row>
     <row r="607" ht="20" customHeight="1">
@@ -16203,7 +16203,7 @@
         </is>
       </c>
       <c r="E607" s="23" t="n">
-        <v>238</v>
+        <v>169</v>
       </c>
     </row>
     <row r="608" ht="20" customHeight="1">
@@ -16228,7 +16228,7 @@
         </is>
       </c>
       <c r="E608" s="20" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="609" ht="20" customHeight="1">
@@ -16253,7 +16253,7 @@
         </is>
       </c>
       <c r="E609" s="23" t="n">
-        <v>160</v>
+        <v>238</v>
       </c>
     </row>
     <row r="610" ht="20" customHeight="1">
@@ -16278,7 +16278,7 @@
         </is>
       </c>
       <c r="E610" s="20" t="n">
-        <v>210</v>
+        <v>173</v>
       </c>
     </row>
     <row r="611" ht="20" customHeight="1">
@@ -16303,7 +16303,7 @@
         </is>
       </c>
       <c r="E611" s="23" t="n">
-        <v>224</v>
+        <v>115</v>
       </c>
     </row>
     <row r="612" ht="20" customHeight="1">
@@ -16328,7 +16328,7 @@
         </is>
       </c>
       <c r="E612" s="20" t="n">
-        <v>126</v>
+        <v>236</v>
       </c>
     </row>
     <row r="613" ht="20" customHeight="1">
@@ -16353,7 +16353,7 @@
         </is>
       </c>
       <c r="E613" s="23" t="n">
-        <v>193</v>
+        <v>236</v>
       </c>
     </row>
     <row r="614" ht="20" customHeight="1">
@@ -16378,7 +16378,7 @@
         </is>
       </c>
       <c r="E614" s="20" t="n">
-        <v>224</v>
+        <v>234</v>
       </c>
     </row>
     <row r="615" ht="20" customHeight="1">
@@ -16403,7 +16403,7 @@
         </is>
       </c>
       <c r="E615" s="23" t="n">
-        <v>118</v>
+        <v>159</v>
       </c>
     </row>
     <row r="616" ht="20" customHeight="1">
@@ -16428,7 +16428,7 @@
         </is>
       </c>
       <c r="E616" s="20" t="n">
-        <v>150</v>
+        <v>173</v>
       </c>
     </row>
     <row r="617" ht="20" customHeight="1">
@@ -16453,7 +16453,7 @@
         </is>
       </c>
       <c r="E617" s="23" t="n">
-        <v>110</v>
+        <v>219</v>
       </c>
     </row>
     <row r="618" ht="20" customHeight="1">
@@ -16478,7 +16478,7 @@
         </is>
       </c>
       <c r="E618" s="20" t="n">
-        <v>151</v>
+        <v>202</v>
       </c>
     </row>
     <row r="619" ht="20" customHeight="1">
@@ -16503,7 +16503,7 @@
         </is>
       </c>
       <c r="E619" s="23" t="n">
-        <v>207</v>
+        <v>157</v>
       </c>
     </row>
     <row r="620" ht="20" customHeight="1">
@@ -16528,7 +16528,7 @@
         </is>
       </c>
       <c r="E620" s="20" t="n">
-        <v>155</v>
+        <v>217</v>
       </c>
     </row>
     <row r="621" ht="20" customHeight="1">
@@ -16553,7 +16553,7 @@
         </is>
       </c>
       <c r="E621" s="23" t="n">
-        <v>201</v>
+        <v>127</v>
       </c>
     </row>
     <row r="622" ht="20" customHeight="1">
@@ -16578,7 +16578,7 @@
         </is>
       </c>
       <c r="E622" s="20" t="n">
-        <v>183</v>
+        <v>119</v>
       </c>
     </row>
     <row r="623" ht="20" customHeight="1">
@@ -16603,7 +16603,7 @@
         </is>
       </c>
       <c r="E623" s="23" t="n">
-        <v>113</v>
+        <v>128</v>
       </c>
     </row>
     <row r="624" ht="20" customHeight="1">
@@ -16628,7 +16628,7 @@
         </is>
       </c>
       <c r="E624" s="20" t="n">
-        <v>152</v>
+        <v>157</v>
       </c>
     </row>
     <row r="625" ht="20" customHeight="1">
@@ -16653,7 +16653,7 @@
         </is>
       </c>
       <c r="E625" s="23" t="n">
-        <v>156</v>
+        <v>136</v>
       </c>
     </row>
     <row r="626" ht="20" customHeight="1">
@@ -16678,7 +16678,7 @@
         </is>
       </c>
       <c r="E626" s="20" t="n">
-        <v>192</v>
+        <v>141</v>
       </c>
     </row>
     <row r="627" ht="20" customHeight="1">
@@ -16703,7 +16703,7 @@
         </is>
       </c>
       <c r="E627" s="23" t="n">
-        <v>170</v>
+        <v>217</v>
       </c>
     </row>
     <row r="628" ht="20" customHeight="1">
@@ -16728,7 +16728,7 @@
         </is>
       </c>
       <c r="E628" s="20" t="n">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="629" ht="20" customHeight="1">
@@ -16753,7 +16753,7 @@
         </is>
       </c>
       <c r="E629" s="23" t="n">
-        <v>213</v>
+        <v>205</v>
       </c>
     </row>
     <row r="630" ht="20" customHeight="1">
@@ -16778,7 +16778,7 @@
         </is>
       </c>
       <c r="E630" s="20" t="n">
-        <v>113</v>
+        <v>139</v>
       </c>
     </row>
     <row r="631" ht="20" customHeight="1">
@@ -16803,7 +16803,7 @@
         </is>
       </c>
       <c r="E631" s="23" t="n">
-        <v>198</v>
+        <v>224</v>
       </c>
     </row>
     <row r="632" ht="20" customHeight="1">
@@ -16828,7 +16828,7 @@
         </is>
       </c>
       <c r="E632" s="20" t="n">
-        <v>163</v>
+        <v>187</v>
       </c>
     </row>
     <row r="633" ht="20" customHeight="1">
@@ -16853,7 +16853,7 @@
         </is>
       </c>
       <c r="E633" s="23" t="n">
-        <v>186</v>
+        <v>191</v>
       </c>
     </row>
     <row r="634" ht="20" customHeight="1">
@@ -16878,7 +16878,7 @@
         </is>
       </c>
       <c r="E634" s="20" t="n">
-        <v>113</v>
+        <v>212</v>
       </c>
     </row>
     <row r="635" ht="20" customHeight="1">
@@ -16903,7 +16903,7 @@
         </is>
       </c>
       <c r="E635" s="23" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="636" ht="20" customHeight="1">
@@ -16928,7 +16928,7 @@
         </is>
       </c>
       <c r="E636" s="20" t="n">
-        <v>144</v>
+        <v>207</v>
       </c>
     </row>
     <row r="637" ht="20" customHeight="1">
@@ -16953,7 +16953,7 @@
         </is>
       </c>
       <c r="E637" s="23" t="n">
-        <v>143</v>
+        <v>117</v>
       </c>
     </row>
     <row r="638" ht="20" customHeight="1">
@@ -16978,7 +16978,7 @@
         </is>
       </c>
       <c r="E638" s="20" t="n">
-        <v>152</v>
+        <v>115</v>
       </c>
     </row>
     <row r="639" ht="20" customHeight="1">
@@ -17003,7 +17003,7 @@
         </is>
       </c>
       <c r="E639" s="23" t="n">
-        <v>230</v>
+        <v>141</v>
       </c>
     </row>
     <row r="640" ht="20" customHeight="1">
@@ -17028,7 +17028,7 @@
         </is>
       </c>
       <c r="E640" s="20" t="n">
-        <v>147</v>
+        <v>202</v>
       </c>
     </row>
     <row r="641" ht="20" customHeight="1">
@@ -17053,7 +17053,7 @@
         </is>
       </c>
       <c r="E641" s="23" t="n">
-        <v>114</v>
+        <v>150</v>
       </c>
     </row>
     <row r="642" ht="20" customHeight="1">
@@ -17078,7 +17078,7 @@
         </is>
       </c>
       <c r="E642" s="20" t="n">
-        <v>235</v>
+        <v>230</v>
       </c>
     </row>
     <row r="643" ht="20" customHeight="1">
@@ -17103,7 +17103,7 @@
         </is>
       </c>
       <c r="E643" s="23" t="n">
-        <v>168</v>
+        <v>145</v>
       </c>
     </row>
     <row r="644" ht="20" customHeight="1">
@@ -17128,7 +17128,7 @@
         </is>
       </c>
       <c r="E644" s="20" t="n">
-        <v>190</v>
+        <v>144</v>
       </c>
     </row>
     <row r="645" ht="20" customHeight="1">
@@ -17153,7 +17153,7 @@
         </is>
       </c>
       <c r="E645" s="23" t="n">
-        <v>199</v>
+        <v>231</v>
       </c>
     </row>
     <row r="646" ht="20" customHeight="1">
@@ -17178,7 +17178,7 @@
         </is>
       </c>
       <c r="E646" s="20" t="n">
-        <v>178</v>
+        <v>171</v>
       </c>
     </row>
     <row r="647" ht="20" customHeight="1">
@@ -17203,7 +17203,7 @@
         </is>
       </c>
       <c r="E647" s="23" t="n">
-        <v>155</v>
+        <v>116</v>
       </c>
     </row>
     <row r="648" ht="20" customHeight="1">
@@ -17228,7 +17228,7 @@
         </is>
       </c>
       <c r="E648" s="20" t="n">
-        <v>174</v>
+        <v>224</v>
       </c>
     </row>
     <row r="649" ht="20" customHeight="1">
@@ -17253,7 +17253,7 @@
         </is>
       </c>
       <c r="E649" s="23" t="n">
-        <v>164</v>
+        <v>214</v>
       </c>
     </row>
     <row r="650" ht="20" customHeight="1">
@@ -17278,7 +17278,7 @@
         </is>
       </c>
       <c r="E650" s="20" t="n">
-        <v>218</v>
+        <v>233</v>
       </c>
     </row>
     <row r="651" ht="20" customHeight="1">
@@ -17303,7 +17303,7 @@
         </is>
       </c>
       <c r="E651" s="23" t="n">
-        <v>180</v>
+        <v>138</v>
       </c>
     </row>
     <row r="652" ht="20" customHeight="1">
@@ -17328,7 +17328,7 @@
         </is>
       </c>
       <c r="E652" s="20" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="653" ht="20" customHeight="1">
@@ -17353,7 +17353,7 @@
         </is>
       </c>
       <c r="E653" s="23" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
     </row>
     <row r="654" ht="20" customHeight="1">
@@ -17378,7 +17378,7 @@
         </is>
       </c>
       <c r="E654" s="20" t="n">
-        <v>137</v>
+        <v>238</v>
       </c>
     </row>
     <row r="655" ht="20" customHeight="1">
@@ -17403,7 +17403,7 @@
         </is>
       </c>
       <c r="E655" s="23" t="n">
-        <v>222</v>
+        <v>157</v>
       </c>
     </row>
     <row r="656" ht="20" customHeight="1">
@@ -17428,7 +17428,7 @@
         </is>
       </c>
       <c r="E656" s="20" t="n">
-        <v>195</v>
+        <v>156</v>
       </c>
     </row>
     <row r="657" ht="20" customHeight="1">
@@ -17453,7 +17453,7 @@
         </is>
       </c>
       <c r="E657" s="23" t="n">
-        <v>183</v>
+        <v>225</v>
       </c>
     </row>
     <row r="658" ht="20" customHeight="1">
@@ -17478,7 +17478,7 @@
         </is>
       </c>
       <c r="E658" s="20" t="n">
-        <v>221</v>
+        <v>119</v>
       </c>
     </row>
     <row r="659" ht="20" customHeight="1">
@@ -17503,7 +17503,7 @@
         </is>
       </c>
       <c r="E659" s="23" t="n">
-        <v>221</v>
+        <v>137</v>
       </c>
     </row>
     <row r="660" ht="20" customHeight="1">
@@ -17553,7 +17553,7 @@
         </is>
       </c>
       <c r="E661" s="23" t="n">
-        <v>220</v>
+        <v>236</v>
       </c>
     </row>
     <row r="662" ht="20" customHeight="1">
@@ -17578,7 +17578,7 @@
         </is>
       </c>
       <c r="E662" s="20" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
     </row>
     <row r="663" ht="20" customHeight="1">
@@ -17603,7 +17603,7 @@
         </is>
       </c>
       <c r="E663" s="23" t="n">
-        <v>172</v>
+        <v>137</v>
       </c>
     </row>
     <row r="664" ht="20" customHeight="1">
@@ -17628,7 +17628,7 @@
         </is>
       </c>
       <c r="E664" s="20" t="n">
-        <v>124</v>
+        <v>158</v>
       </c>
     </row>
     <row r="665" ht="20" customHeight="1">
@@ -17653,7 +17653,7 @@
         </is>
       </c>
       <c r="E665" s="23" t="n">
-        <v>193</v>
+        <v>121</v>
       </c>
     </row>
     <row r="666" ht="20" customHeight="1">
@@ -17678,7 +17678,7 @@
         </is>
       </c>
       <c r="E666" s="20" t="n">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="667" ht="20" customHeight="1">
@@ -17703,7 +17703,7 @@
         </is>
       </c>
       <c r="E667" s="23" t="n">
-        <v>238</v>
+        <v>111</v>
       </c>
     </row>
     <row r="668" ht="20" customHeight="1">
@@ -17728,7 +17728,7 @@
         </is>
       </c>
       <c r="E668" s="20" t="n">
-        <v>197</v>
+        <v>187</v>
       </c>
     </row>
     <row r="669" ht="20" customHeight="1">
@@ -17753,7 +17753,7 @@
         </is>
       </c>
       <c r="E669" s="23" t="n">
-        <v>151</v>
+        <v>187</v>
       </c>
     </row>
     <row r="670" ht="20" customHeight="1">
@@ -17778,7 +17778,7 @@
         </is>
       </c>
       <c r="E670" s="20" t="n">
-        <v>145</v>
+        <v>202</v>
       </c>
     </row>
     <row r="671" ht="20" customHeight="1">
@@ -17803,7 +17803,7 @@
         </is>
       </c>
       <c r="E671" s="23" t="n">
-        <v>219</v>
+        <v>173</v>
       </c>
     </row>
     <row r="672" ht="20" customHeight="1">
@@ -17828,7 +17828,7 @@
         </is>
       </c>
       <c r="E672" s="20" t="n">
-        <v>147</v>
+        <v>232</v>
       </c>
     </row>
     <row r="673" ht="20" customHeight="1">
@@ -17853,7 +17853,7 @@
         </is>
       </c>
       <c r="E673" s="23" t="n">
-        <v>110</v>
+        <v>225</v>
       </c>
     </row>
     <row r="674" ht="20" customHeight="1">
@@ -17878,7 +17878,7 @@
         </is>
       </c>
       <c r="E674" s="20" t="n">
-        <v>120</v>
+        <v>201</v>
       </c>
     </row>
     <row r="675" ht="20" customHeight="1">
@@ -17903,7 +17903,7 @@
         </is>
       </c>
       <c r="E675" s="23" t="n">
-        <v>231</v>
+        <v>130</v>
       </c>
     </row>
     <row r="676" ht="20" customHeight="1">
@@ -17928,7 +17928,7 @@
         </is>
       </c>
       <c r="E676" s="20" t="n">
-        <v>203</v>
+        <v>146</v>
       </c>
     </row>
     <row r="677" ht="20" customHeight="1">
@@ -17953,7 +17953,7 @@
         </is>
       </c>
       <c r="E677" s="23" t="n">
-        <v>136</v>
+        <v>174</v>
       </c>
     </row>
     <row r="678" ht="20" customHeight="1">
@@ -17978,7 +17978,7 @@
         </is>
       </c>
       <c r="E678" s="20" t="n">
-        <v>218</v>
+        <v>183</v>
       </c>
     </row>
     <row r="679" ht="20" customHeight="1">
@@ -18003,7 +18003,7 @@
         </is>
       </c>
       <c r="E679" s="23" t="n">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="680" ht="20" customHeight="1">
@@ -18028,7 +18028,7 @@
         </is>
       </c>
       <c r="E680" s="20" t="n">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="681" ht="20" customHeight="1">
@@ -18053,7 +18053,7 @@
         </is>
       </c>
       <c r="E681" s="23" t="n">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="682" ht="20" customHeight="1">
@@ -18078,7 +18078,7 @@
         </is>
       </c>
       <c r="E682" s="20" t="n">
-        <v>190</v>
+        <v>238</v>
       </c>
     </row>
     <row r="683" ht="20" customHeight="1">
@@ -18103,7 +18103,7 @@
         </is>
       </c>
       <c r="E683" s="23" t="n">
-        <v>206</v>
+        <v>162</v>
       </c>
     </row>
     <row r="684" ht="20" customHeight="1">
@@ -18128,7 +18128,7 @@
         </is>
       </c>
       <c r="E684" s="20" t="n">
-        <v>224</v>
+        <v>220</v>
       </c>
     </row>
     <row r="685" ht="20" customHeight="1">
@@ -18153,7 +18153,7 @@
         </is>
       </c>
       <c r="E685" s="23" t="n">
-        <v>150</v>
+        <v>122</v>
       </c>
     </row>
     <row r="686" ht="20" customHeight="1">
@@ -18178,7 +18178,7 @@
         </is>
       </c>
       <c r="E686" s="20" t="n">
-        <v>143</v>
+        <v>172</v>
       </c>
     </row>
     <row r="687" ht="20" customHeight="1">
@@ -18203,7 +18203,7 @@
         </is>
       </c>
       <c r="E687" s="23" t="n">
-        <v>150</v>
+        <v>128</v>
       </c>
     </row>
     <row r="688" ht="20" customHeight="1">
@@ -18228,7 +18228,7 @@
         </is>
       </c>
       <c r="E688" s="20" t="n">
-        <v>165</v>
+        <v>186</v>
       </c>
     </row>
     <row r="689" ht="20" customHeight="1">
@@ -18253,7 +18253,7 @@
         </is>
       </c>
       <c r="E689" s="23" t="n">
-        <v>230</v>
+        <v>222</v>
       </c>
     </row>
     <row r="690" ht="20" customHeight="1">
@@ -18278,7 +18278,7 @@
         </is>
       </c>
       <c r="E690" s="20" t="n">
-        <v>204</v>
+        <v>222</v>
       </c>
     </row>
     <row r="691" ht="20" customHeight="1">
@@ -18303,7 +18303,7 @@
         </is>
       </c>
       <c r="E691" s="23" t="n">
-        <v>159</v>
+        <v>218</v>
       </c>
     </row>
     <row r="692" ht="20" customHeight="1">
@@ -18328,7 +18328,7 @@
         </is>
       </c>
       <c r="E692" s="20" t="n">
-        <v>147</v>
+        <v>114</v>
       </c>
     </row>
     <row r="693" ht="20" customHeight="1">
@@ -18353,7 +18353,7 @@
         </is>
       </c>
       <c r="E693" s="23" t="n">
-        <v>154</v>
+        <v>220</v>
       </c>
     </row>
     <row r="694" ht="20" customHeight="1">
@@ -18378,7 +18378,7 @@
         </is>
       </c>
       <c r="E694" s="20" t="n">
-        <v>131</v>
+        <v>230</v>
       </c>
     </row>
     <row r="695" ht="20" customHeight="1">
@@ -18403,7 +18403,7 @@
         </is>
       </c>
       <c r="E695" s="23" t="n">
-        <v>111</v>
+        <v>231</v>
       </c>
     </row>
     <row r="696" ht="20" customHeight="1">
@@ -18428,7 +18428,7 @@
         </is>
       </c>
       <c r="E696" s="20" t="n">
-        <v>227</v>
+        <v>198</v>
       </c>
     </row>
     <row r="697" ht="20" customHeight="1">
@@ -18453,7 +18453,7 @@
         </is>
       </c>
       <c r="E697" s="23" t="n">
-        <v>165</v>
+        <v>176</v>
       </c>
     </row>
     <row r="698" ht="20" customHeight="1">
@@ -18478,7 +18478,7 @@
         </is>
       </c>
       <c r="E698" s="20" t="n">
-        <v>169</v>
+        <v>215</v>
       </c>
     </row>
     <row r="699" ht="20" customHeight="1">
@@ -18503,7 +18503,7 @@
         </is>
       </c>
       <c r="E699" s="23" t="n">
-        <v>224</v>
+        <v>157</v>
       </c>
     </row>
     <row r="700" ht="20" customHeight="1">
@@ -18528,7 +18528,7 @@
         </is>
       </c>
       <c r="E700" s="20" t="n">
-        <v>197</v>
+        <v>179</v>
       </c>
     </row>
     <row r="701" ht="20" customHeight="1">
@@ -18553,7 +18553,7 @@
         </is>
       </c>
       <c r="E701" s="23" t="n">
-        <v>190</v>
+        <v>233</v>
       </c>
     </row>
     <row r="702" ht="20" customHeight="1">
@@ -18578,7 +18578,7 @@
         </is>
       </c>
       <c r="E702" s="20" t="n">
-        <v>167</v>
+        <v>138</v>
       </c>
     </row>
     <row r="703" ht="20" customHeight="1">
@@ -18603,7 +18603,7 @@
         </is>
       </c>
       <c r="E703" s="23" t="n">
-        <v>178</v>
+        <v>222</v>
       </c>
     </row>
     <row r="704" ht="20" customHeight="1">
@@ -18628,7 +18628,7 @@
         </is>
       </c>
       <c r="E704" s="20" t="n">
-        <v>233</v>
+        <v>192</v>
       </c>
     </row>
     <row r="705" ht="20" customHeight="1">
@@ -18653,7 +18653,7 @@
         </is>
       </c>
       <c r="E705" s="23" t="n">
-        <v>233</v>
+        <v>209</v>
       </c>
     </row>
     <row r="706" ht="20" customHeight="1">
@@ -18678,7 +18678,7 @@
         </is>
       </c>
       <c r="E706" s="20" t="n">
-        <v>178</v>
+        <v>188</v>
       </c>
     </row>
     <row r="707" ht="20" customHeight="1">
@@ -18703,7 +18703,7 @@
         </is>
       </c>
       <c r="E707" s="23" t="n">
-        <v>135</v>
+        <v>125</v>
       </c>
     </row>
     <row r="708" ht="20" customHeight="1">
@@ -18728,7 +18728,7 @@
         </is>
       </c>
       <c r="E708" s="20" t="n">
-        <v>197</v>
+        <v>128</v>
       </c>
     </row>
     <row r="709" ht="20" customHeight="1">
@@ -18753,7 +18753,7 @@
         </is>
       </c>
       <c r="E709" s="23" t="n">
-        <v>144</v>
+        <v>189</v>
       </c>
     </row>
     <row r="710" ht="20" customHeight="1">
@@ -18778,7 +18778,7 @@
         </is>
       </c>
       <c r="E710" s="20" t="n">
-        <v>200</v>
+        <v>137</v>
       </c>
     </row>
     <row r="711" ht="20" customHeight="1">
@@ -18803,7 +18803,7 @@
         </is>
       </c>
       <c r="E711" s="23" t="n">
-        <v>163</v>
+        <v>224</v>
       </c>
     </row>
     <row r="712" ht="20" customHeight="1">
@@ -18828,7 +18828,7 @@
         </is>
       </c>
       <c r="E712" s="20" t="n">
-        <v>232</v>
+        <v>110</v>
       </c>
     </row>
     <row r="713" ht="20" customHeight="1">
@@ -18853,7 +18853,7 @@
         </is>
       </c>
       <c r="E713" s="23" t="n">
-        <v>231</v>
+        <v>200</v>
       </c>
     </row>
     <row r="714" ht="20" customHeight="1">
@@ -18878,7 +18878,7 @@
         </is>
       </c>
       <c r="E714" s="20" t="n">
-        <v>230</v>
+        <v>147</v>
       </c>
     </row>
     <row r="715" ht="20" customHeight="1">
@@ -18903,7 +18903,7 @@
         </is>
       </c>
       <c r="E715" s="23" t="n">
-        <v>190</v>
+        <v>126</v>
       </c>
     </row>
     <row r="716" ht="20" customHeight="1">
@@ -18928,7 +18928,7 @@
         </is>
       </c>
       <c r="E716" s="20" t="n">
-        <v>222</v>
+        <v>169</v>
       </c>
     </row>
     <row r="717" ht="20" customHeight="1">
@@ -18953,7 +18953,7 @@
         </is>
       </c>
       <c r="E717" s="23" t="n">
-        <v>114</v>
+        <v>158</v>
       </c>
     </row>
     <row r="718" ht="20" customHeight="1">
@@ -18978,7 +18978,7 @@
         </is>
       </c>
       <c r="E718" s="20" t="n">
-        <v>114</v>
+        <v>214</v>
       </c>
     </row>
     <row r="719" ht="20" customHeight="1">
@@ -19003,7 +19003,7 @@
         </is>
       </c>
       <c r="E719" s="23" t="n">
-        <v>231</v>
+        <v>200</v>
       </c>
     </row>
     <row r="720" ht="20" customHeight="1">
@@ -19028,7 +19028,7 @@
         </is>
       </c>
       <c r="E720" s="20" t="n">
-        <v>180</v>
+        <v>142</v>
       </c>
     </row>
     <row r="721" ht="20" customHeight="1">
@@ -19053,7 +19053,7 @@
         </is>
       </c>
       <c r="E721" s="23" t="n">
-        <v>201</v>
+        <v>211</v>
       </c>
     </row>
     <row r="722" ht="20" customHeight="1">
@@ -19078,7 +19078,7 @@
         </is>
       </c>
       <c r="E722" s="20" t="n">
-        <v>208</v>
+        <v>165</v>
       </c>
     </row>
     <row r="723" ht="20" customHeight="1">
@@ -19103,7 +19103,7 @@
         </is>
       </c>
       <c r="E723" s="23" t="n">
-        <v>149</v>
+        <v>122</v>
       </c>
     </row>
     <row r="724" ht="20" customHeight="1">
@@ -19128,7 +19128,7 @@
         </is>
       </c>
       <c r="E724" s="20" t="n">
-        <v>147</v>
+        <v>163</v>
       </c>
     </row>
     <row r="725" ht="20" customHeight="1">
@@ -19153,7 +19153,7 @@
         </is>
       </c>
       <c r="E725" s="23" t="n">
-        <v>150</v>
+        <v>111</v>
       </c>
     </row>
     <row r="726" ht="20" customHeight="1">
@@ -19178,7 +19178,7 @@
         </is>
       </c>
       <c r="E726" s="20" t="n">
-        <v>150</v>
+        <v>167</v>
       </c>
     </row>
     <row r="727" ht="20" customHeight="1">
@@ -19203,7 +19203,7 @@
         </is>
       </c>
       <c r="E727" s="23" t="n">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="728" ht="20" customHeight="1">
@@ -19228,7 +19228,7 @@
         </is>
       </c>
       <c r="E728" s="20" t="n">
-        <v>222</v>
+        <v>198</v>
       </c>
     </row>
     <row r="729" ht="20" customHeight="1">
@@ -19253,7 +19253,7 @@
         </is>
       </c>
       <c r="E729" s="23" t="n">
-        <v>135</v>
+        <v>209</v>
       </c>
     </row>
     <row r="730" ht="20" customHeight="1">
@@ -19278,7 +19278,7 @@
         </is>
       </c>
       <c r="E730" s="20" t="n">
-        <v>222</v>
+        <v>178</v>
       </c>
     </row>
     <row r="731" ht="20" customHeight="1">
@@ -19303,7 +19303,7 @@
         </is>
       </c>
       <c r="E731" s="23" t="n">
-        <v>113</v>
+        <v>198</v>
       </c>
     </row>
     <row r="732" ht="20" customHeight="1">
@@ -19328,7 +19328,7 @@
         </is>
       </c>
       <c r="E732" s="20" t="n">
-        <v>219</v>
+        <v>177</v>
       </c>
     </row>
     <row r="733" ht="20" customHeight="1">
@@ -19353,7 +19353,7 @@
         </is>
       </c>
       <c r="E733" s="23" t="n">
-        <v>167</v>
+        <v>197</v>
       </c>
     </row>
     <row r="734" ht="20" customHeight="1">
@@ -19378,7 +19378,7 @@
         </is>
       </c>
       <c r="E734" s="20" t="n">
-        <v>224</v>
+        <v>115</v>
       </c>
     </row>
     <row r="735" ht="20" customHeight="1">
@@ -19403,7 +19403,7 @@
         </is>
       </c>
       <c r="E735" s="23" t="n">
-        <v>204</v>
+        <v>186</v>
       </c>
     </row>
     <row r="736" ht="20" customHeight="1">
@@ -19428,7 +19428,7 @@
         </is>
       </c>
       <c r="E736" s="20" t="n">
-        <v>147</v>
+        <v>223</v>
       </c>
     </row>
     <row r="737" ht="20" customHeight="1">
@@ -19453,7 +19453,7 @@
         </is>
       </c>
       <c r="E737" s="23" t="n">
-        <v>217</v>
+        <v>140</v>
       </c>
     </row>
     <row r="738" ht="20" customHeight="1">
@@ -19478,7 +19478,7 @@
         </is>
       </c>
       <c r="E738" s="20" t="n">
-        <v>225</v>
+        <v>232</v>
       </c>
     </row>
     <row r="739" ht="20" customHeight="1">
@@ -19503,7 +19503,7 @@
         </is>
       </c>
       <c r="E739" s="23" t="n">
-        <v>181</v>
+        <v>149</v>
       </c>
     </row>
     <row r="740" ht="20" customHeight="1">
@@ -19528,7 +19528,7 @@
         </is>
       </c>
       <c r="E740" s="20" t="n">
-        <v>226</v>
+        <v>205</v>
       </c>
     </row>
     <row r="741" ht="20" customHeight="1">
@@ -19553,7 +19553,7 @@
         </is>
       </c>
       <c r="E741" s="23" t="n">
-        <v>163</v>
+        <v>152</v>
       </c>
     </row>
     <row r="742" ht="20" customHeight="1">
@@ -19578,7 +19578,7 @@
         </is>
       </c>
       <c r="E742" s="20" t="n">
-        <v>159</v>
+        <v>220</v>
       </c>
     </row>
     <row r="743" ht="20" customHeight="1">
@@ -19603,7 +19603,7 @@
         </is>
       </c>
       <c r="E743" s="23" t="n">
-        <v>197</v>
+        <v>139</v>
       </c>
     </row>
     <row r="744" ht="20" customHeight="1">
@@ -19628,7 +19628,7 @@
         </is>
       </c>
       <c r="E744" s="20" t="n">
-        <v>127</v>
+        <v>206</v>
       </c>
     </row>
     <row r="745" ht="20" customHeight="1">
@@ -19653,7 +19653,7 @@
         </is>
       </c>
       <c r="E745" s="23" t="n">
-        <v>240</v>
+        <v>160</v>
       </c>
     </row>
     <row r="746" ht="20" customHeight="1">
@@ -19678,7 +19678,7 @@
         </is>
       </c>
       <c r="E746" s="20" t="n">
-        <v>233</v>
+        <v>153</v>
       </c>
     </row>
     <row r="747" ht="20" customHeight="1">
@@ -19703,7 +19703,7 @@
         </is>
       </c>
       <c r="E747" s="23" t="n">
-        <v>148</v>
+        <v>115</v>
       </c>
     </row>
     <row r="748" ht="20" customHeight="1">
@@ -19728,7 +19728,7 @@
         </is>
       </c>
       <c r="E748" s="20" t="n">
-        <v>192</v>
+        <v>202</v>
       </c>
     </row>
     <row r="749" ht="20" customHeight="1">
@@ -19753,7 +19753,7 @@
         </is>
       </c>
       <c r="E749" s="23" t="n">
-        <v>214</v>
+        <v>154</v>
       </c>
     </row>
     <row r="750" ht="20" customHeight="1">
@@ -19778,7 +19778,7 @@
         </is>
       </c>
       <c r="E750" s="20" t="n">
-        <v>157</v>
+        <v>112</v>
       </c>
     </row>
     <row r="751" ht="20" customHeight="1">
@@ -19803,7 +19803,7 @@
         </is>
       </c>
       <c r="E751" s="23" t="n">
-        <v>194</v>
+        <v>142</v>
       </c>
     </row>
     <row r="752" ht="20" customHeight="1">
@@ -19828,7 +19828,7 @@
         </is>
       </c>
       <c r="E752" s="20" t="n">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="753" ht="20" customHeight="1">
@@ -19853,7 +19853,7 @@
         </is>
       </c>
       <c r="E753" s="23" t="n">
-        <v>174</v>
+        <v>123</v>
       </c>
     </row>
     <row r="754" ht="20" customHeight="1">
@@ -19878,7 +19878,7 @@
         </is>
       </c>
       <c r="E754" s="20" t="n">
-        <v>225</v>
+        <v>152</v>
       </c>
     </row>
     <row r="755" ht="20" customHeight="1">
@@ -19903,7 +19903,7 @@
         </is>
       </c>
       <c r="E755" s="23" t="n">
-        <v>229</v>
+        <v>164</v>
       </c>
     </row>
     <row r="756" ht="20" customHeight="1">
@@ -19928,7 +19928,7 @@
         </is>
       </c>
       <c r="E756" s="20" t="n">
-        <v>175</v>
+        <v>216</v>
       </c>
     </row>
     <row r="757" ht="20" customHeight="1">
@@ -19953,7 +19953,7 @@
         </is>
       </c>
       <c r="E757" s="23" t="n">
-        <v>157</v>
+        <v>200</v>
       </c>
     </row>
     <row r="758" ht="20" customHeight="1">
@@ -19978,7 +19978,7 @@
         </is>
       </c>
       <c r="E758" s="20" t="n">
-        <v>166</v>
+        <v>209</v>
       </c>
     </row>
     <row r="759" ht="20" customHeight="1">
@@ -20003,7 +20003,7 @@
         </is>
       </c>
       <c r="E759" s="23" t="n">
-        <v>145</v>
+        <v>185</v>
       </c>
     </row>
     <row r="760" ht="20" customHeight="1">
@@ -20028,7 +20028,7 @@
         </is>
       </c>
       <c r="E760" s="20" t="n">
-        <v>137</v>
+        <v>224</v>
       </c>
     </row>
     <row r="761" ht="20" customHeight="1">
@@ -20053,7 +20053,7 @@
         </is>
       </c>
       <c r="E761" s="23" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="762" ht="20" customHeight="1">
@@ -20078,7 +20078,7 @@
         </is>
       </c>
       <c r="E762" s="20" t="n">
-        <v>219</v>
+        <v>158</v>
       </c>
     </row>
     <row r="763" ht="20" customHeight="1">
@@ -20103,7 +20103,7 @@
         </is>
       </c>
       <c r="E763" s="23" t="n">
-        <v>142</v>
+        <v>154</v>
       </c>
     </row>
     <row r="764" ht="20" customHeight="1">
@@ -20128,7 +20128,7 @@
         </is>
       </c>
       <c r="E764" s="20" t="n">
-        <v>159</v>
+        <v>134</v>
       </c>
     </row>
     <row r="765" ht="20" customHeight="1">
@@ -20178,7 +20178,7 @@
         </is>
       </c>
       <c r="E766" s="20" t="n">
-        <v>216</v>
+        <v>183</v>
       </c>
     </row>
     <row r="767" ht="20" customHeight="1">
@@ -20203,7 +20203,7 @@
         </is>
       </c>
       <c r="E767" s="23" t="n">
-        <v>240</v>
+        <v>130</v>
       </c>
     </row>
     <row r="768" ht="20" customHeight="1">
@@ -20228,7 +20228,7 @@
         </is>
       </c>
       <c r="E768" s="20" t="n">
-        <v>233</v>
+        <v>120</v>
       </c>
     </row>
     <row r="769" ht="20" customHeight="1">
@@ -20253,7 +20253,7 @@
         </is>
       </c>
       <c r="E769" s="23" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="770" ht="20" customHeight="1">
@@ -20278,7 +20278,7 @@
         </is>
       </c>
       <c r="E770" s="20" t="n">
-        <v>164</v>
+        <v>178</v>
       </c>
     </row>
     <row r="771" ht="20" customHeight="1">
@@ -20303,7 +20303,7 @@
         </is>
       </c>
       <c r="E771" s="23" t="n">
-        <v>126</v>
+        <v>219</v>
       </c>
     </row>
     <row r="772" ht="20" customHeight="1">
@@ -20328,7 +20328,7 @@
         </is>
       </c>
       <c r="E772" s="20" t="n">
-        <v>113</v>
+        <v>182</v>
       </c>
     </row>
     <row r="773" ht="20" customHeight="1">
@@ -20353,7 +20353,7 @@
         </is>
       </c>
       <c r="E773" s="23" t="n">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="774" ht="20" customHeight="1">
@@ -20378,7 +20378,7 @@
         </is>
       </c>
       <c r="E774" s="20" t="n">
-        <v>169</v>
+        <v>139</v>
       </c>
     </row>
     <row r="775" ht="20" customHeight="1">
@@ -20403,7 +20403,7 @@
         </is>
       </c>
       <c r="E775" s="23" t="n">
-        <v>126</v>
+        <v>178</v>
       </c>
     </row>
     <row r="776" ht="20" customHeight="1">
@@ -20428,7 +20428,7 @@
         </is>
       </c>
       <c r="E776" s="20" t="n">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="777" ht="20" customHeight="1">
@@ -20453,7 +20453,7 @@
         </is>
       </c>
       <c r="E777" s="23" t="n">
-        <v>214</v>
+        <v>200</v>
       </c>
     </row>
     <row r="778" ht="20" customHeight="1">
@@ -20478,7 +20478,7 @@
         </is>
       </c>
       <c r="E778" s="20" t="n">
-        <v>138</v>
+        <v>167</v>
       </c>
     </row>
     <row r="779" ht="20" customHeight="1">
@@ -20503,7 +20503,7 @@
         </is>
       </c>
       <c r="E779" s="23" t="n">
-        <v>145</v>
+        <v>197</v>
       </c>
     </row>
     <row r="780" ht="20" customHeight="1">
@@ -20528,7 +20528,7 @@
         </is>
       </c>
       <c r="E780" s="20" t="n">
-        <v>226</v>
+        <v>231</v>
       </c>
     </row>
     <row r="781" ht="20" customHeight="1">
@@ -20553,7 +20553,7 @@
         </is>
       </c>
       <c r="E781" s="23" t="n">
-        <v>232</v>
+        <v>149</v>
       </c>
     </row>
     <row r="782" ht="20" customHeight="1">
@@ -20578,7 +20578,7 @@
         </is>
       </c>
       <c r="E782" s="20" t="n">
-        <v>167</v>
+        <v>232</v>
       </c>
     </row>
     <row r="783" ht="20" customHeight="1">
@@ -20603,7 +20603,7 @@
         </is>
       </c>
       <c r="E783" s="23" t="n">
-        <v>220</v>
+        <v>148</v>
       </c>
     </row>
     <row r="784" ht="20" customHeight="1">
@@ -20628,7 +20628,7 @@
         </is>
       </c>
       <c r="E784" s="20" t="n">
-        <v>129</v>
+        <v>112</v>
       </c>
     </row>
     <row r="785" ht="20" customHeight="1">
@@ -20653,7 +20653,7 @@
         </is>
       </c>
       <c r="E785" s="23" t="n">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="786" ht="20" customHeight="1">
@@ -20678,7 +20678,7 @@
         </is>
       </c>
       <c r="E786" s="20" t="n">
-        <v>219</v>
+        <v>195</v>
       </c>
     </row>
     <row r="787" ht="20" customHeight="1">
@@ -20703,7 +20703,7 @@
         </is>
       </c>
       <c r="E787" s="23" t="n">
-        <v>175</v>
+        <v>214</v>
       </c>
     </row>
     <row r="788" ht="20" customHeight="1">
@@ -20728,7 +20728,7 @@
         </is>
       </c>
       <c r="E788" s="20" t="n">
-        <v>116</v>
+        <v>123</v>
       </c>
     </row>
     <row r="789" ht="20" customHeight="1">
@@ -20753,7 +20753,7 @@
         </is>
       </c>
       <c r="E789" s="23" t="n">
-        <v>153</v>
+        <v>214</v>
       </c>
     </row>
     <row r="790" ht="20" customHeight="1">
@@ -20778,7 +20778,7 @@
         </is>
       </c>
       <c r="E790" s="20" t="n">
-        <v>169</v>
+        <v>119</v>
       </c>
     </row>
     <row r="791" ht="20" customHeight="1">
@@ -20803,7 +20803,7 @@
         </is>
       </c>
       <c r="E791" s="23" t="n">
-        <v>204</v>
+        <v>158</v>
       </c>
     </row>
     <row r="792" ht="20" customHeight="1">
@@ -20828,7 +20828,7 @@
         </is>
       </c>
       <c r="E792" s="20" t="n">
-        <v>180</v>
+        <v>198</v>
       </c>
     </row>
     <row r="793" ht="20" customHeight="1">
@@ -20853,7 +20853,7 @@
         </is>
       </c>
       <c r="E793" s="23" t="n">
-        <v>111</v>
+        <v>162</v>
       </c>
     </row>
     <row r="794" ht="20" customHeight="1">
@@ -20878,7 +20878,7 @@
         </is>
       </c>
       <c r="E794" s="20" t="n">
-        <v>121</v>
+        <v>223</v>
       </c>
     </row>
     <row r="795" ht="20" customHeight="1">
@@ -20903,7 +20903,7 @@
         </is>
       </c>
       <c r="E795" s="23" t="n">
-        <v>135</v>
+        <v>124</v>
       </c>
     </row>
     <row r="796" ht="20" customHeight="1">
@@ -20928,7 +20928,7 @@
         </is>
       </c>
       <c r="E796" s="20" t="n">
-        <v>118</v>
+        <v>153</v>
       </c>
     </row>
     <row r="797" ht="20" customHeight="1">
@@ -20953,7 +20953,7 @@
         </is>
       </c>
       <c r="E797" s="23" t="n">
-        <v>231</v>
+        <v>186</v>
       </c>
     </row>
     <row r="798" ht="20" customHeight="1">
@@ -20978,7 +20978,7 @@
         </is>
       </c>
       <c r="E798" s="20" t="n">
-        <v>174</v>
+        <v>213</v>
       </c>
     </row>
     <row r="799" ht="20" customHeight="1">
@@ -21003,7 +21003,7 @@
         </is>
       </c>
       <c r="E799" s="23" t="n">
-        <v>145</v>
+        <v>179</v>
       </c>
     </row>
     <row r="800" ht="20" customHeight="1">
@@ -21028,7 +21028,7 @@
         </is>
       </c>
       <c r="E800" s="20" t="n">
-        <v>209</v>
+        <v>128</v>
       </c>
     </row>
     <row r="801" ht="20" customHeight="1">
@@ -21053,7 +21053,7 @@
         </is>
       </c>
       <c r="E801" s="23" t="n">
-        <v>160</v>
+        <v>223</v>
       </c>
     </row>
   </sheetData>

--- a/Appium_E2E_Test_Report_Traverse.xlsx
+++ b/Appium_E2E_Test_Report_Traverse.xlsx
@@ -791,7 +791,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 08:18:49</t>
+          <t>2026-08-11 08:35:25</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="E2" s="20" t="n">
-        <v>166</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="E3" s="23" t="n">
-        <v>191</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="E4" s="20" t="n">
-        <v>135</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="E5" s="23" t="n">
-        <v>121</v>
+        <v>184</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="E6" s="20" t="n">
-        <v>136</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="E7" s="23" t="n">
-        <v>222</v>
+        <v>212</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -1228,7 +1228,7 @@
         </is>
       </c>
       <c r="E8" s="20" t="n">
-        <v>236</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="E9" s="23" t="n">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
@@ -1278,7 +1278,7 @@
         </is>
       </c>
       <c r="E10" s="20" t="n">
-        <v>137</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="E11" s="23" t="n">
-        <v>231</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
@@ -1328,7 +1328,7 @@
         </is>
       </c>
       <c r="E12" s="20" t="n">
-        <v>121</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="E13" s="23" t="n">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="E14" s="20" t="n">
-        <v>159</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="E15" s="23" t="n">
-        <v>179</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="E16" s="20" t="n">
-        <v>150</v>
+        <v>182</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="E17" s="23" t="n">
-        <v>135</v>
+        <v>161</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -1478,7 +1478,7 @@
         </is>
       </c>
       <c r="E18" s="20" t="n">
-        <v>184</v>
+        <v>207</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
@@ -1503,7 +1503,7 @@
         </is>
       </c>
       <c r="E19" s="23" t="n">
-        <v>118</v>
+        <v>216</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="E20" s="20" t="n">
-        <v>135</v>
+        <v>112</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="E21" s="23" t="n">
-        <v>206</v>
+        <v>164</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
@@ -1578,7 +1578,7 @@
         </is>
       </c>
       <c r="E22" s="20" t="n">
-        <v>111</v>
+        <v>156</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="E23" s="23" t="n">
-        <v>224</v>
+        <v>142</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
@@ -1628,7 +1628,7 @@
         </is>
       </c>
       <c r="E24" s="20" t="n">
-        <v>200</v>
+        <v>238</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="E25" s="23" t="n">
-        <v>182</v>
+        <v>211</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
@@ -1678,7 +1678,7 @@
         </is>
       </c>
       <c r="E26" s="20" t="n">
-        <v>167</v>
+        <v>202</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="E27" s="23" t="n">
-        <v>145</v>
+        <v>195</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="E28" s="20" t="n">
-        <v>156</v>
+        <v>128</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="E29" s="23" t="n">
-        <v>184</v>
+        <v>233</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="E30" s="20" t="n">
-        <v>238</v>
+        <v>189</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
@@ -1803,7 +1803,7 @@
         </is>
       </c>
       <c r="E31" s="23" t="n">
-        <v>206</v>
+        <v>186</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
@@ -1828,7 +1828,7 @@
         </is>
       </c>
       <c r="E32" s="20" t="n">
-        <v>236</v>
+        <v>150</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
@@ -1853,7 +1853,7 @@
         </is>
       </c>
       <c r="E33" s="23" t="n">
-        <v>175</v>
+        <v>161</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
@@ -1878,7 +1878,7 @@
         </is>
       </c>
       <c r="E34" s="20" t="n">
-        <v>174</v>
+        <v>219</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="E35" s="23" t="n">
-        <v>153</v>
+        <v>174</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="E36" s="20" t="n">
-        <v>146</v>
+        <v>180</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="E37" s="23" t="n">
-        <v>212</v>
+        <v>139</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
@@ -1978,7 +1978,7 @@
         </is>
       </c>
       <c r="E38" s="20" t="n">
-        <v>232</v>
+        <v>214</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="E39" s="23" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="E40" s="20" t="n">
-        <v>202</v>
+        <v>176</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="E41" s="23" t="n">
-        <v>116</v>
+        <v>151</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
@@ -2078,7 +2078,7 @@
         </is>
       </c>
       <c r="E42" s="20" t="n">
-        <v>163</v>
+        <v>118</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="E43" s="23" t="n">
-        <v>220</v>
+        <v>129</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="E44" s="20" t="n">
-        <v>135</v>
+        <v>115</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="E45" s="23" t="n">
-        <v>146</v>
+        <v>215</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
@@ -2178,7 +2178,7 @@
         </is>
       </c>
       <c r="E46" s="20" t="n">
-        <v>201</v>
+        <v>232</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
@@ -2203,7 +2203,7 @@
         </is>
       </c>
       <c r="E47" s="23" t="n">
-        <v>223</v>
+        <v>120</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="E48" s="20" t="n">
-        <v>190</v>
+        <v>110</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
@@ -2253,7 +2253,7 @@
         </is>
       </c>
       <c r="E49" s="23" t="n">
-        <v>165</v>
+        <v>118</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
@@ -2278,7 +2278,7 @@
         </is>
       </c>
       <c r="E50" s="20" t="n">
-        <v>167</v>
+        <v>189</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="E51" s="23" t="n">
-        <v>127</v>
+        <v>216</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
@@ -2328,7 +2328,7 @@
         </is>
       </c>
       <c r="E52" s="20" t="n">
-        <v>157</v>
+        <v>167</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
@@ -2353,7 +2353,7 @@
         </is>
       </c>
       <c r="E53" s="23" t="n">
-        <v>126</v>
+        <v>234</v>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="E54" s="20" t="n">
-        <v>160</v>
+        <v>129</v>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1">
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="E55" s="23" t="n">
-        <v>207</v>
+        <v>173</v>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1">
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="E56" s="20" t="n">
-        <v>127</v>
+        <v>163</v>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1">
@@ -2453,7 +2453,7 @@
         </is>
       </c>
       <c r="E57" s="23" t="n">
-        <v>202</v>
+        <v>194</v>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1">
@@ -2478,7 +2478,7 @@
         </is>
       </c>
       <c r="E58" s="20" t="n">
-        <v>177</v>
+        <v>196</v>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1">
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="E59" s="23" t="n">
-        <v>190</v>
+        <v>128</v>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1">
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="E60" s="20" t="n">
-        <v>111</v>
+        <v>122</v>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
@@ -2553,7 +2553,7 @@
         </is>
       </c>
       <c r="E61" s="23" t="n">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="E62" s="20" t="n">
-        <v>238</v>
+        <v>221</v>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="E63" s="23" t="n">
-        <v>223</v>
+        <v>169</v>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1">
@@ -2628,7 +2628,7 @@
         </is>
       </c>
       <c r="E64" s="20" t="n">
-        <v>112</v>
+        <v>197</v>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1">
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="E65" s="23" t="n">
-        <v>114</v>
+        <v>141</v>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1">
@@ -2678,7 +2678,7 @@
         </is>
       </c>
       <c r="E66" s="20" t="n">
-        <v>221</v>
+        <v>162</v>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="E67" s="23" t="n">
-        <v>156</v>
+        <v>116</v>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="E68" s="20" t="n">
-        <v>118</v>
+        <v>146</v>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="E69" s="23" t="n">
-        <v>199</v>
+        <v>144</v>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1">
@@ -2778,7 +2778,7 @@
         </is>
       </c>
       <c r="E70" s="20" t="n">
-        <v>176</v>
+        <v>231</v>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1">
@@ -2803,7 +2803,7 @@
         </is>
       </c>
       <c r="E71" s="23" t="n">
-        <v>159</v>
+        <v>183</v>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1">
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="E72" s="20" t="n">
-        <v>138</v>
+        <v>128</v>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1">
@@ -2853,7 +2853,7 @@
         </is>
       </c>
       <c r="E73" s="23" t="n">
-        <v>178</v>
+        <v>115</v>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
@@ -2878,7 +2878,7 @@
         </is>
       </c>
       <c r="E74" s="20" t="n">
-        <v>139</v>
+        <v>111</v>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="E75" s="23" t="n">
-        <v>240</v>
+        <v>217</v>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
@@ -2928,7 +2928,7 @@
         </is>
       </c>
       <c r="E76" s="20" t="n">
-        <v>187</v>
+        <v>136</v>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="E77" s="23" t="n">
-        <v>229</v>
+        <v>199</v>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1">
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="E78" s="20" t="n">
-        <v>150</v>
+        <v>167</v>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
@@ -3003,7 +3003,7 @@
         </is>
       </c>
       <c r="E79" s="23" t="n">
-        <v>116</v>
+        <v>174</v>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1">
@@ -3028,7 +3028,7 @@
         </is>
       </c>
       <c r="E80" s="20" t="n">
-        <v>239</v>
+        <v>149</v>
       </c>
     </row>
     <row r="81" ht="20" customHeight="1">
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="E81" s="23" t="n">
-        <v>229</v>
+        <v>235</v>
       </c>
     </row>
     <row r="82" ht="20" customHeight="1">
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="E82" s="20" t="n">
-        <v>164</v>
+        <v>211</v>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1">
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="E83" s="23" t="n">
-        <v>211</v>
+        <v>112</v>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1">
@@ -3128,7 +3128,7 @@
         </is>
       </c>
       <c r="E84" s="20" t="n">
-        <v>203</v>
+        <v>156</v>
       </c>
     </row>
     <row r="85" ht="20" customHeight="1">
@@ -3153,7 +3153,7 @@
         </is>
       </c>
       <c r="E85" s="23" t="n">
-        <v>171</v>
+        <v>155</v>
       </c>
     </row>
     <row r="86" ht="20" customHeight="1">
@@ -3178,7 +3178,7 @@
         </is>
       </c>
       <c r="E86" s="20" t="n">
-        <v>215</v>
+        <v>167</v>
       </c>
     </row>
     <row r="87" ht="20" customHeight="1">
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="E87" s="23" t="n">
-        <v>187</v>
+        <v>156</v>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1">
@@ -3228,7 +3228,7 @@
         </is>
       </c>
       <c r="E88" s="20" t="n">
-        <v>224</v>
+        <v>184</v>
       </c>
     </row>
     <row r="89" ht="20" customHeight="1">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="E89" s="23" t="n">
-        <v>118</v>
+        <v>187</v>
       </c>
     </row>
     <row r="90" ht="20" customHeight="1">
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="E90" s="20" t="n">
-        <v>224</v>
+        <v>130</v>
       </c>
     </row>
     <row r="91" ht="20" customHeight="1">
@@ -3303,7 +3303,7 @@
         </is>
       </c>
       <c r="E91" s="23" t="n">
-        <v>153</v>
+        <v>133</v>
       </c>
     </row>
     <row r="92" ht="20" customHeight="1">
@@ -3328,7 +3328,7 @@
         </is>
       </c>
       <c r="E92" s="20" t="n">
-        <v>204</v>
+        <v>183</v>
       </c>
     </row>
     <row r="93" ht="20" customHeight="1">
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="E93" s="23" t="n">
-        <v>128</v>
+        <v>214</v>
       </c>
     </row>
     <row r="94" ht="20" customHeight="1">
@@ -3378,7 +3378,7 @@
         </is>
       </c>
       <c r="E94" s="20" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="95" ht="20" customHeight="1">
@@ -3403,7 +3403,7 @@
         </is>
       </c>
       <c r="E95" s="23" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="96" ht="20" customHeight="1">
@@ -3428,7 +3428,7 @@
         </is>
       </c>
       <c r="E96" s="20" t="n">
-        <v>120</v>
+        <v>230</v>
       </c>
     </row>
     <row r="97" ht="20" customHeight="1">
@@ -3453,7 +3453,7 @@
         </is>
       </c>
       <c r="E97" s="23" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="98" ht="20" customHeight="1">
@@ -3478,7 +3478,7 @@
         </is>
       </c>
       <c r="E98" s="20" t="n">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="99" ht="20" customHeight="1">
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="E99" s="23" t="n">
-        <v>193</v>
+        <v>118</v>
       </c>
     </row>
     <row r="100" ht="20" customHeight="1">
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="E100" s="20" t="n">
-        <v>221</v>
+        <v>168</v>
       </c>
     </row>
     <row r="101" ht="20" customHeight="1">
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="E101" s="23" t="n">
-        <v>126</v>
+        <v>215</v>
       </c>
     </row>
     <row r="102" ht="20" customHeight="1">
@@ -3578,7 +3578,7 @@
         </is>
       </c>
       <c r="E102" s="20" t="n">
-        <v>181</v>
+        <v>152</v>
       </c>
     </row>
     <row r="103" ht="20" customHeight="1">
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="E103" s="23" t="n">
-        <v>237</v>
+        <v>116</v>
       </c>
     </row>
     <row r="104" ht="20" customHeight="1">
@@ -3628,7 +3628,7 @@
         </is>
       </c>
       <c r="E104" s="20" t="n">
-        <v>171</v>
+        <v>199</v>
       </c>
     </row>
     <row r="105" ht="20" customHeight="1">
@@ -3653,7 +3653,7 @@
         </is>
       </c>
       <c r="E105" s="23" t="n">
-        <v>131</v>
+        <v>164</v>
       </c>
     </row>
     <row r="106" ht="20" customHeight="1">
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="E106" s="20" t="n">
-        <v>112</v>
+        <v>139</v>
       </c>
     </row>
     <row r="107" ht="20" customHeight="1">
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="E107" s="23" t="n">
-        <v>168</v>
+        <v>179</v>
       </c>
     </row>
     <row r="108" ht="20" customHeight="1">
@@ -3728,7 +3728,7 @@
         </is>
       </c>
       <c r="E108" s="20" t="n">
-        <v>137</v>
+        <v>142</v>
       </c>
     </row>
     <row r="109" ht="20" customHeight="1">
@@ -3753,7 +3753,7 @@
         </is>
       </c>
       <c r="E109" s="23" t="n">
-        <v>213</v>
+        <v>136</v>
       </c>
     </row>
     <row r="110" ht="20" customHeight="1">
@@ -3778,7 +3778,7 @@
         </is>
       </c>
       <c r="E110" s="20" t="n">
-        <v>186</v>
+        <v>180</v>
       </c>
     </row>
     <row r="111" ht="20" customHeight="1">
@@ -3803,7 +3803,7 @@
         </is>
       </c>
       <c r="E111" s="23" t="n">
-        <v>227</v>
+        <v>141</v>
       </c>
     </row>
     <row r="112" ht="20" customHeight="1">
@@ -3828,7 +3828,7 @@
         </is>
       </c>
       <c r="E112" s="20" t="n">
-        <v>195</v>
+        <v>209</v>
       </c>
     </row>
     <row r="113" ht="20" customHeight="1">
@@ -3853,7 +3853,7 @@
         </is>
       </c>
       <c r="E113" s="23" t="n">
-        <v>118</v>
+        <v>232</v>
       </c>
     </row>
     <row r="114" ht="20" customHeight="1">
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="E114" s="20" t="n">
-        <v>227</v>
+        <v>169</v>
       </c>
     </row>
     <row r="115" ht="20" customHeight="1">
@@ -3903,7 +3903,7 @@
         </is>
       </c>
       <c r="E115" s="23" t="n">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="116" ht="20" customHeight="1">
@@ -3928,7 +3928,7 @@
         </is>
       </c>
       <c r="E116" s="20" t="n">
-        <v>227</v>
+        <v>238</v>
       </c>
     </row>
     <row r="117" ht="20" customHeight="1">
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="E117" s="23" t="n">
-        <v>208</v>
+        <v>186</v>
       </c>
     </row>
     <row r="118" ht="20" customHeight="1">
@@ -3978,7 +3978,7 @@
         </is>
       </c>
       <c r="E118" s="20" t="n">
-        <v>153</v>
+        <v>132</v>
       </c>
     </row>
     <row r="119" ht="20" customHeight="1">
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="E119" s="23" t="n">
-        <v>139</v>
+        <v>127</v>
       </c>
     </row>
     <row r="120" ht="20" customHeight="1">
@@ -4028,7 +4028,7 @@
         </is>
       </c>
       <c r="E120" s="20" t="n">
-        <v>229</v>
+        <v>216</v>
       </c>
     </row>
     <row r="121" ht="20" customHeight="1">
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="E121" s="23" t="n">
-        <v>188</v>
+        <v>135</v>
       </c>
     </row>
     <row r="122" ht="20" customHeight="1">
@@ -4078,7 +4078,7 @@
         </is>
       </c>
       <c r="E122" s="20" t="n">
-        <v>146</v>
+        <v>236</v>
       </c>
     </row>
     <row r="123" ht="20" customHeight="1">
@@ -4103,7 +4103,7 @@
         </is>
       </c>
       <c r="E123" s="23" t="n">
-        <v>154</v>
+        <v>188</v>
       </c>
     </row>
     <row r="124" ht="20" customHeight="1">
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="E124" s="20" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="125" ht="20" customHeight="1">
@@ -4153,7 +4153,7 @@
         </is>
       </c>
       <c r="E125" s="23" t="n">
-        <v>180</v>
+        <v>146</v>
       </c>
     </row>
     <row r="126" ht="20" customHeight="1">
@@ -4178,7 +4178,7 @@
         </is>
       </c>
       <c r="E126" s="20" t="n">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="127" ht="20" customHeight="1">
@@ -4203,7 +4203,7 @@
         </is>
       </c>
       <c r="E127" s="23" t="n">
-        <v>158</v>
+        <v>184</v>
       </c>
     </row>
     <row r="128" ht="20" customHeight="1">
@@ -4228,7 +4228,7 @@
         </is>
       </c>
       <c r="E128" s="20" t="n">
-        <v>173</v>
+        <v>224</v>
       </c>
     </row>
     <row r="129" ht="20" customHeight="1">
@@ -4253,7 +4253,7 @@
         </is>
       </c>
       <c r="E129" s="23" t="n">
-        <v>200</v>
+        <v>140</v>
       </c>
     </row>
     <row r="130" ht="20" customHeight="1">
@@ -4278,7 +4278,7 @@
         </is>
       </c>
       <c r="E130" s="20" t="n">
-        <v>210</v>
+        <v>137</v>
       </c>
     </row>
     <row r="131" ht="20" customHeight="1">
@@ -4303,7 +4303,7 @@
         </is>
       </c>
       <c r="E131" s="23" t="n">
-        <v>142</v>
+        <v>111</v>
       </c>
     </row>
     <row r="132" ht="20" customHeight="1">
@@ -4328,7 +4328,7 @@
         </is>
       </c>
       <c r="E132" s="20" t="n">
-        <v>212</v>
+        <v>140</v>
       </c>
     </row>
     <row r="133" ht="20" customHeight="1">
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="E133" s="23" t="n">
-        <v>184</v>
+        <v>169</v>
       </c>
     </row>
     <row r="134" ht="20" customHeight="1">
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="E134" s="20" t="n">
-        <v>167</v>
+        <v>131</v>
       </c>
     </row>
     <row r="135" ht="20" customHeight="1">
@@ -4403,7 +4403,7 @@
         </is>
       </c>
       <c r="E135" s="23" t="n">
-        <v>204</v>
+        <v>140</v>
       </c>
     </row>
     <row r="136" ht="20" customHeight="1">
@@ -4428,7 +4428,7 @@
         </is>
       </c>
       <c r="E136" s="20" t="n">
-        <v>195</v>
+        <v>148</v>
       </c>
     </row>
     <row r="137" ht="20" customHeight="1">
@@ -4453,7 +4453,7 @@
         </is>
       </c>
       <c r="E137" s="23" t="n">
-        <v>153</v>
+        <v>183</v>
       </c>
     </row>
     <row r="138" ht="20" customHeight="1">
@@ -4478,7 +4478,7 @@
         </is>
       </c>
       <c r="E138" s="20" t="n">
-        <v>136</v>
+        <v>121</v>
       </c>
     </row>
     <row r="139" ht="20" customHeight="1">
@@ -4503,7 +4503,7 @@
         </is>
       </c>
       <c r="E139" s="23" t="n">
-        <v>185</v>
+        <v>239</v>
       </c>
     </row>
     <row r="140" ht="20" customHeight="1">
@@ -4528,7 +4528,7 @@
         </is>
       </c>
       <c r="E140" s="20" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="141" ht="20" customHeight="1">
@@ -4553,7 +4553,7 @@
         </is>
       </c>
       <c r="E141" s="23" t="n">
-        <v>199</v>
+        <v>128</v>
       </c>
     </row>
     <row r="142" ht="20" customHeight="1">
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="E142" s="20" t="n">
-        <v>154</v>
+        <v>138</v>
       </c>
     </row>
     <row r="143" ht="20" customHeight="1">
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="E143" s="23" t="n">
-        <v>185</v>
+        <v>240</v>
       </c>
     </row>
     <row r="144" ht="20" customHeight="1">
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="E144" s="20" t="n">
-        <v>221</v>
+        <v>116</v>
       </c>
     </row>
     <row r="145" ht="20" customHeight="1">
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="E145" s="23" t="n">
-        <v>124</v>
+        <v>175</v>
       </c>
     </row>
     <row r="146" ht="20" customHeight="1">
@@ -4678,7 +4678,7 @@
         </is>
       </c>
       <c r="E146" s="20" t="n">
-        <v>229</v>
+        <v>161</v>
       </c>
     </row>
     <row r="147" ht="20" customHeight="1">
@@ -4703,7 +4703,7 @@
         </is>
       </c>
       <c r="E147" s="23" t="n">
-        <v>194</v>
+        <v>238</v>
       </c>
     </row>
     <row r="148" ht="20" customHeight="1">
@@ -4728,7 +4728,7 @@
         </is>
       </c>
       <c r="E148" s="20" t="n">
-        <v>203</v>
+        <v>120</v>
       </c>
     </row>
     <row r="149" ht="20" customHeight="1">
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c r="E149" s="23" t="n">
-        <v>228</v>
+        <v>138</v>
       </c>
     </row>
     <row r="150" ht="20" customHeight="1">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="E150" s="20" t="n">
-        <v>230</v>
+        <v>169</v>
       </c>
     </row>
     <row r="151" ht="20" customHeight="1">
@@ -4803,7 +4803,7 @@
         </is>
       </c>
       <c r="E151" s="23" t="n">
-        <v>177</v>
+        <v>134</v>
       </c>
     </row>
     <row r="152" ht="20" customHeight="1">
@@ -4828,7 +4828,7 @@
         </is>
       </c>
       <c r="E152" s="20" t="n">
-        <v>225</v>
+        <v>138</v>
       </c>
     </row>
     <row r="153" ht="20" customHeight="1">
@@ -4853,7 +4853,7 @@
         </is>
       </c>
       <c r="E153" s="23" t="n">
-        <v>157</v>
+        <v>211</v>
       </c>
     </row>
     <row r="154" ht="20" customHeight="1">
@@ -4878,7 +4878,7 @@
         </is>
       </c>
       <c r="E154" s="20" t="n">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="155" ht="20" customHeight="1">
@@ -4903,7 +4903,7 @@
         </is>
       </c>
       <c r="E155" s="23" t="n">
-        <v>219</v>
+        <v>184</v>
       </c>
     </row>
     <row r="156" ht="20" customHeight="1">
@@ -4928,7 +4928,7 @@
         </is>
       </c>
       <c r="E156" s="20" t="n">
-        <v>190</v>
+        <v>127</v>
       </c>
     </row>
     <row r="157" ht="20" customHeight="1">
@@ -4953,7 +4953,7 @@
         </is>
       </c>
       <c r="E157" s="23" t="n">
-        <v>226</v>
+        <v>214</v>
       </c>
     </row>
     <row r="158" ht="20" customHeight="1">
@@ -4978,7 +4978,7 @@
         </is>
       </c>
       <c r="E158" s="20" t="n">
-        <v>124</v>
+        <v>142</v>
       </c>
     </row>
     <row r="159" ht="20" customHeight="1">
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="E159" s="23" t="n">
-        <v>171</v>
+        <v>132</v>
       </c>
     </row>
     <row r="160" ht="20" customHeight="1">
@@ -5028,7 +5028,7 @@
         </is>
       </c>
       <c r="E160" s="20" t="n">
-        <v>179</v>
+        <v>152</v>
       </c>
     </row>
     <row r="161" ht="20" customHeight="1">
@@ -5053,7 +5053,7 @@
         </is>
       </c>
       <c r="E161" s="23" t="n">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="162" ht="20" customHeight="1">
@@ -5078,7 +5078,7 @@
         </is>
       </c>
       <c r="E162" s="20" t="n">
-        <v>227</v>
+        <v>220</v>
       </c>
     </row>
     <row r="163" ht="20" customHeight="1">
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="E163" s="23" t="n">
-        <v>143</v>
+        <v>118</v>
       </c>
     </row>
     <row r="164" ht="20" customHeight="1">
@@ -5128,7 +5128,7 @@
         </is>
       </c>
       <c r="E164" s="20" t="n">
-        <v>155</v>
+        <v>218</v>
       </c>
     </row>
     <row r="165" ht="20" customHeight="1">
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="E165" s="23" t="n">
-        <v>208</v>
+        <v>178</v>
       </c>
     </row>
     <row r="166" ht="20" customHeight="1">
@@ -5178,7 +5178,7 @@
         </is>
       </c>
       <c r="E166" s="20" t="n">
-        <v>194</v>
+        <v>133</v>
       </c>
     </row>
     <row r="167" ht="20" customHeight="1">
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="E167" s="23" t="n">
-        <v>141</v>
+        <v>158</v>
       </c>
     </row>
     <row r="168" ht="20" customHeight="1">
@@ -5228,7 +5228,7 @@
         </is>
       </c>
       <c r="E168" s="20" t="n">
-        <v>146</v>
+        <v>224</v>
       </c>
     </row>
     <row r="169" ht="20" customHeight="1">
@@ -5253,7 +5253,7 @@
         </is>
       </c>
       <c r="E169" s="23" t="n">
-        <v>121</v>
+        <v>158</v>
       </c>
     </row>
     <row r="170" ht="20" customHeight="1">
@@ -5278,7 +5278,7 @@
         </is>
       </c>
       <c r="E170" s="20" t="n">
-        <v>213</v>
+        <v>184</v>
       </c>
     </row>
     <row r="171" ht="20" customHeight="1">
@@ -5303,7 +5303,7 @@
         </is>
       </c>
       <c r="E171" s="23" t="n">
-        <v>208</v>
+        <v>173</v>
       </c>
     </row>
     <row r="172" ht="20" customHeight="1">
@@ -5328,7 +5328,7 @@
         </is>
       </c>
       <c r="E172" s="20" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="173" ht="20" customHeight="1">
@@ -5353,7 +5353,7 @@
         </is>
       </c>
       <c r="E173" s="23" t="n">
-        <v>231</v>
+        <v>170</v>
       </c>
     </row>
     <row r="174" ht="20" customHeight="1">
@@ -5403,7 +5403,7 @@
         </is>
       </c>
       <c r="E175" s="23" t="n">
-        <v>126</v>
+        <v>175</v>
       </c>
     </row>
     <row r="176" ht="20" customHeight="1">
@@ -5428,7 +5428,7 @@
         </is>
       </c>
       <c r="E176" s="20" t="n">
-        <v>133</v>
+        <v>191</v>
       </c>
     </row>
     <row r="177" ht="20" customHeight="1">
@@ -5453,7 +5453,7 @@
         </is>
       </c>
       <c r="E177" s="23" t="n">
-        <v>232</v>
+        <v>133</v>
       </c>
     </row>
     <row r="178" ht="20" customHeight="1">
@@ -5478,7 +5478,7 @@
         </is>
       </c>
       <c r="E178" s="20" t="n">
-        <v>163</v>
+        <v>129</v>
       </c>
     </row>
     <row r="179" ht="20" customHeight="1">
@@ -5503,7 +5503,7 @@
         </is>
       </c>
       <c r="E179" s="23" t="n">
-        <v>141</v>
+        <v>178</v>
       </c>
     </row>
     <row r="180" ht="20" customHeight="1">
@@ -5528,7 +5528,7 @@
         </is>
       </c>
       <c r="E180" s="20" t="n">
-        <v>202</v>
+        <v>236</v>
       </c>
     </row>
     <row r="181" ht="20" customHeight="1">
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="E181" s="23" t="n">
-        <v>113</v>
+        <v>163</v>
       </c>
     </row>
     <row r="182" ht="20" customHeight="1">
@@ -5578,7 +5578,7 @@
         </is>
       </c>
       <c r="E182" s="20" t="n">
-        <v>217</v>
+        <v>210</v>
       </c>
     </row>
     <row r="183" ht="20" customHeight="1">
@@ -5603,7 +5603,7 @@
         </is>
       </c>
       <c r="E183" s="23" t="n">
-        <v>149</v>
+        <v>165</v>
       </c>
     </row>
     <row r="184" ht="20" customHeight="1">
@@ -5628,7 +5628,7 @@
         </is>
       </c>
       <c r="E184" s="20" t="n">
-        <v>224</v>
+        <v>232</v>
       </c>
     </row>
     <row r="185" ht="20" customHeight="1">
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="E185" s="23" t="n">
-        <v>130</v>
+        <v>161</v>
       </c>
     </row>
     <row r="186" ht="20" customHeight="1">
@@ -5678,7 +5678,7 @@
         </is>
       </c>
       <c r="E186" s="20" t="n">
-        <v>126</v>
+        <v>219</v>
       </c>
     </row>
     <row r="187" ht="20" customHeight="1">
@@ -5703,7 +5703,7 @@
         </is>
       </c>
       <c r="E187" s="23" t="n">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
     <row r="188" ht="20" customHeight="1">
@@ -5728,7 +5728,7 @@
         </is>
       </c>
       <c r="E188" s="20" t="n">
-        <v>151</v>
+        <v>197</v>
       </c>
     </row>
     <row r="189" ht="20" customHeight="1">
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="E189" s="23" t="n">
-        <v>180</v>
+        <v>173</v>
       </c>
     </row>
     <row r="190" ht="20" customHeight="1">
@@ -5778,7 +5778,7 @@
         </is>
       </c>
       <c r="E190" s="20" t="n">
-        <v>157</v>
+        <v>141</v>
       </c>
     </row>
     <row r="191" ht="20" customHeight="1">
@@ -5803,7 +5803,7 @@
         </is>
       </c>
       <c r="E191" s="23" t="n">
-        <v>174</v>
+        <v>179</v>
       </c>
     </row>
     <row r="192" ht="20" customHeight="1">
@@ -5828,7 +5828,7 @@
         </is>
       </c>
       <c r="E192" s="20" t="n">
-        <v>158</v>
+        <v>177</v>
       </c>
     </row>
     <row r="193" ht="20" customHeight="1">
@@ -5853,7 +5853,7 @@
         </is>
       </c>
       <c r="E193" s="23" t="n">
-        <v>156</v>
+        <v>129</v>
       </c>
     </row>
     <row r="194" ht="20" customHeight="1">
@@ -5878,7 +5878,7 @@
         </is>
       </c>
       <c r="E194" s="20" t="n">
-        <v>162</v>
+        <v>230</v>
       </c>
     </row>
     <row r="195" ht="20" customHeight="1">
@@ -5903,7 +5903,7 @@
         </is>
       </c>
       <c r="E195" s="23" t="n">
-        <v>127</v>
+        <v>148</v>
       </c>
     </row>
     <row r="196" ht="20" customHeight="1">
@@ -5928,7 +5928,7 @@
         </is>
       </c>
       <c r="E196" s="20" t="n">
-        <v>112</v>
+        <v>125</v>
       </c>
     </row>
     <row r="197" ht="20" customHeight="1">
@@ -5953,7 +5953,7 @@
         </is>
       </c>
       <c r="E197" s="23" t="n">
-        <v>204</v>
+        <v>140</v>
       </c>
     </row>
     <row r="198" ht="20" customHeight="1">
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="E198" s="20" t="n">
-        <v>232</v>
+        <v>179</v>
       </c>
     </row>
     <row r="199" ht="20" customHeight="1">
@@ -6003,7 +6003,7 @@
         </is>
       </c>
       <c r="E199" s="23" t="n">
-        <v>222</v>
+        <v>159</v>
       </c>
     </row>
     <row r="200" ht="20" customHeight="1">
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="E200" s="20" t="n">
-        <v>149</v>
+        <v>141</v>
       </c>
     </row>
     <row r="201" ht="20" customHeight="1">
@@ -6053,7 +6053,7 @@
         </is>
       </c>
       <c r="E201" s="23" t="n">
-        <v>152</v>
+        <v>179</v>
       </c>
     </row>
     <row r="202" ht="20" customHeight="1">
@@ -6078,7 +6078,7 @@
         </is>
       </c>
       <c r="E202" s="20" t="n">
-        <v>123</v>
+        <v>181</v>
       </c>
     </row>
     <row r="203" ht="20" customHeight="1">
@@ -6103,7 +6103,7 @@
         </is>
       </c>
       <c r="E203" s="23" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
     </row>
     <row r="204" ht="20" customHeight="1">
@@ -6128,7 +6128,7 @@
         </is>
       </c>
       <c r="E204" s="20" t="n">
-        <v>187</v>
+        <v>182</v>
       </c>
     </row>
     <row r="205" ht="20" customHeight="1">
@@ -6153,7 +6153,7 @@
         </is>
       </c>
       <c r="E205" s="23" t="n">
-        <v>134</v>
+        <v>192</v>
       </c>
     </row>
     <row r="206" ht="20" customHeight="1">
@@ -6178,7 +6178,7 @@
         </is>
       </c>
       <c r="E206" s="20" t="n">
-        <v>121</v>
+        <v>216</v>
       </c>
     </row>
     <row r="207" ht="20" customHeight="1">
@@ -6203,7 +6203,7 @@
         </is>
       </c>
       <c r="E207" s="23" t="n">
-        <v>139</v>
+        <v>175</v>
       </c>
     </row>
     <row r="208" ht="20" customHeight="1">
@@ -6228,7 +6228,7 @@
         </is>
       </c>
       <c r="E208" s="20" t="n">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="209" ht="20" customHeight="1">
@@ -6253,7 +6253,7 @@
         </is>
       </c>
       <c r="E209" s="23" t="n">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="210" ht="20" customHeight="1">
@@ -6278,7 +6278,7 @@
         </is>
       </c>
       <c r="E210" s="20" t="n">
-        <v>118</v>
+        <v>221</v>
       </c>
     </row>
     <row r="211" ht="20" customHeight="1">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="E211" s="23" t="n">
-        <v>119</v>
+        <v>148</v>
       </c>
     </row>
     <row r="212" ht="20" customHeight="1">
@@ -6328,7 +6328,7 @@
         </is>
       </c>
       <c r="E212" s="20" t="n">
-        <v>181</v>
+        <v>156</v>
       </c>
     </row>
     <row r="213" ht="20" customHeight="1">
@@ -6353,7 +6353,7 @@
         </is>
       </c>
       <c r="E213" s="23" t="n">
-        <v>237</v>
+        <v>189</v>
       </c>
     </row>
     <row r="214" ht="20" customHeight="1">
@@ -6378,7 +6378,7 @@
         </is>
       </c>
       <c r="E214" s="20" t="n">
-        <v>165</v>
+        <v>240</v>
       </c>
     </row>
     <row r="215" ht="20" customHeight="1">
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="E215" s="23" t="n">
-        <v>194</v>
+        <v>145</v>
       </c>
     </row>
     <row r="216" ht="20" customHeight="1">
@@ -6428,7 +6428,7 @@
         </is>
       </c>
       <c r="E216" s="20" t="n">
-        <v>166</v>
+        <v>135</v>
       </c>
     </row>
     <row r="217" ht="20" customHeight="1">
@@ -6453,7 +6453,7 @@
         </is>
       </c>
       <c r="E217" s="23" t="n">
-        <v>124</v>
+        <v>216</v>
       </c>
     </row>
     <row r="218" ht="20" customHeight="1">
@@ -6478,7 +6478,7 @@
         </is>
       </c>
       <c r="E218" s="20" t="n">
-        <v>240</v>
+        <v>169</v>
       </c>
     </row>
     <row r="219" ht="20" customHeight="1">
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="E219" s="23" t="n">
-        <v>146</v>
+        <v>196</v>
       </c>
     </row>
     <row r="220" ht="20" customHeight="1">
@@ -6528,7 +6528,7 @@
         </is>
       </c>
       <c r="E220" s="20" t="n">
-        <v>211</v>
+        <v>227</v>
       </c>
     </row>
     <row r="221" ht="20" customHeight="1">
@@ -6553,7 +6553,7 @@
         </is>
       </c>
       <c r="E221" s="23" t="n">
-        <v>160</v>
+        <v>114</v>
       </c>
     </row>
     <row r="222" ht="20" customHeight="1">
@@ -6603,7 +6603,7 @@
         </is>
       </c>
       <c r="E223" s="23" t="n">
-        <v>122</v>
+        <v>166</v>
       </c>
     </row>
     <row r="224" ht="20" customHeight="1">
@@ -6628,7 +6628,7 @@
         </is>
       </c>
       <c r="E224" s="20" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="225" ht="20" customHeight="1">
@@ -6653,7 +6653,7 @@
         </is>
       </c>
       <c r="E225" s="23" t="n">
-        <v>219</v>
+        <v>132</v>
       </c>
     </row>
     <row r="226" ht="20" customHeight="1">
@@ -6678,7 +6678,7 @@
         </is>
       </c>
       <c r="E226" s="20" t="n">
-        <v>127</v>
+        <v>191</v>
       </c>
     </row>
     <row r="227" ht="20" customHeight="1">
@@ -6703,7 +6703,7 @@
         </is>
       </c>
       <c r="E227" s="23" t="n">
-        <v>172</v>
+        <v>138</v>
       </c>
     </row>
     <row r="228" ht="20" customHeight="1">
@@ -6728,7 +6728,7 @@
         </is>
       </c>
       <c r="E228" s="20" t="n">
-        <v>179</v>
+        <v>172</v>
       </c>
     </row>
     <row r="229" ht="20" customHeight="1">
@@ -6753,7 +6753,7 @@
         </is>
       </c>
       <c r="E229" s="23" t="n">
-        <v>238</v>
+        <v>123</v>
       </c>
     </row>
     <row r="230" ht="20" customHeight="1">
@@ -6778,7 +6778,7 @@
         </is>
       </c>
       <c r="E230" s="20" t="n">
-        <v>139</v>
+        <v>181</v>
       </c>
     </row>
     <row r="231" ht="20" customHeight="1">
@@ -6803,7 +6803,7 @@
         </is>
       </c>
       <c r="E231" s="23" t="n">
-        <v>136</v>
+        <v>178</v>
       </c>
     </row>
     <row r="232" ht="20" customHeight="1">
@@ -6828,7 +6828,7 @@
         </is>
       </c>
       <c r="E232" s="20" t="n">
-        <v>235</v>
+        <v>222</v>
       </c>
     </row>
     <row r="233" ht="20" customHeight="1">
@@ -6853,7 +6853,7 @@
         </is>
       </c>
       <c r="E233" s="23" t="n">
-        <v>215</v>
+        <v>180</v>
       </c>
     </row>
     <row r="234" ht="20" customHeight="1">
@@ -6878,7 +6878,7 @@
         </is>
       </c>
       <c r="E234" s="20" t="n">
-        <v>195</v>
+        <v>138</v>
       </c>
     </row>
     <row r="235" ht="20" customHeight="1">
@@ -6903,7 +6903,7 @@
         </is>
       </c>
       <c r="E235" s="23" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="236" ht="20" customHeight="1">
@@ -6928,7 +6928,7 @@
         </is>
       </c>
       <c r="E236" s="20" t="n">
-        <v>133</v>
+        <v>206</v>
       </c>
     </row>
     <row r="237" ht="20" customHeight="1">
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="E237" s="23" t="n">
-        <v>115</v>
+        <v>156</v>
       </c>
     </row>
     <row r="238" ht="20" customHeight="1">
@@ -6978,7 +6978,7 @@
         </is>
       </c>
       <c r="E238" s="20" t="n">
-        <v>221</v>
+        <v>238</v>
       </c>
     </row>
     <row r="239" ht="20" customHeight="1">
@@ -7003,7 +7003,7 @@
         </is>
       </c>
       <c r="E239" s="23" t="n">
-        <v>193</v>
+        <v>232</v>
       </c>
     </row>
     <row r="240" ht="20" customHeight="1">
@@ -7028,7 +7028,7 @@
         </is>
       </c>
       <c r="E240" s="20" t="n">
-        <v>186</v>
+        <v>126</v>
       </c>
     </row>
     <row r="241" ht="20" customHeight="1">
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="E241" s="23" t="n">
-        <v>211</v>
+        <v>204</v>
       </c>
     </row>
     <row r="242" ht="20" customHeight="1">
@@ -7078,7 +7078,7 @@
         </is>
       </c>
       <c r="E242" s="20" t="n">
-        <v>218</v>
+        <v>149</v>
       </c>
     </row>
     <row r="243" ht="20" customHeight="1">
@@ -7103,7 +7103,7 @@
         </is>
       </c>
       <c r="E243" s="23" t="n">
-        <v>133</v>
+        <v>159</v>
       </c>
     </row>
     <row r="244" ht="20" customHeight="1">
@@ -7128,7 +7128,7 @@
         </is>
       </c>
       <c r="E244" s="20" t="n">
-        <v>229</v>
+        <v>149</v>
       </c>
     </row>
     <row r="245" ht="20" customHeight="1">
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="E245" s="23" t="n">
-        <v>175</v>
+        <v>162</v>
       </c>
     </row>
     <row r="246" ht="20" customHeight="1">
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="E246" s="20" t="n">
-        <v>179</v>
+        <v>151</v>
       </c>
     </row>
     <row r="247" ht="20" customHeight="1">
@@ -7203,7 +7203,7 @@
         </is>
       </c>
       <c r="E247" s="23" t="n">
-        <v>168</v>
+        <v>173</v>
       </c>
     </row>
     <row r="248" ht="20" customHeight="1">
@@ -7228,7 +7228,7 @@
         </is>
       </c>
       <c r="E248" s="20" t="n">
-        <v>164</v>
+        <v>238</v>
       </c>
     </row>
     <row r="249" ht="20" customHeight="1">
@@ -7253,7 +7253,7 @@
         </is>
       </c>
       <c r="E249" s="23" t="n">
-        <v>119</v>
+        <v>212</v>
       </c>
     </row>
     <row r="250" ht="20" customHeight="1">
@@ -7278,7 +7278,7 @@
         </is>
       </c>
       <c r="E250" s="20" t="n">
-        <v>226</v>
+        <v>153</v>
       </c>
     </row>
     <row r="251" ht="20" customHeight="1">
@@ -7303,7 +7303,7 @@
         </is>
       </c>
       <c r="E251" s="23" t="n">
-        <v>230</v>
+        <v>157</v>
       </c>
     </row>
     <row r="252" ht="20" customHeight="1">
@@ -7328,7 +7328,7 @@
         </is>
       </c>
       <c r="E252" s="20" t="n">
-        <v>154</v>
+        <v>236</v>
       </c>
     </row>
     <row r="253" ht="20" customHeight="1">
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="E253" s="23" t="n">
-        <v>139</v>
+        <v>209</v>
       </c>
     </row>
     <row r="254" ht="20" customHeight="1">
@@ -7378,7 +7378,7 @@
         </is>
       </c>
       <c r="E254" s="20" t="n">
-        <v>135</v>
+        <v>153</v>
       </c>
     </row>
     <row r="255" ht="20" customHeight="1">
@@ -7403,7 +7403,7 @@
         </is>
       </c>
       <c r="E255" s="23" t="n">
-        <v>219</v>
+        <v>142</v>
       </c>
     </row>
     <row r="256" ht="20" customHeight="1">
@@ -7428,7 +7428,7 @@
         </is>
       </c>
       <c r="E256" s="20" t="n">
-        <v>199</v>
+        <v>146</v>
       </c>
     </row>
     <row r="257" ht="20" customHeight="1">
@@ -7453,7 +7453,7 @@
         </is>
       </c>
       <c r="E257" s="23" t="n">
-        <v>191</v>
+        <v>218</v>
       </c>
     </row>
     <row r="258" ht="20" customHeight="1">
@@ -7478,7 +7478,7 @@
         </is>
       </c>
       <c r="E258" s="20" t="n">
-        <v>191</v>
+        <v>148</v>
       </c>
     </row>
     <row r="259" ht="20" customHeight="1">
@@ -7503,7 +7503,7 @@
         </is>
       </c>
       <c r="E259" s="23" t="n">
-        <v>183</v>
+        <v>162</v>
       </c>
     </row>
     <row r="260" ht="20" customHeight="1">
@@ -7528,7 +7528,7 @@
         </is>
       </c>
       <c r="E260" s="20" t="n">
-        <v>181</v>
+        <v>202</v>
       </c>
     </row>
     <row r="261" ht="20" customHeight="1">
@@ -7553,7 +7553,7 @@
         </is>
       </c>
       <c r="E261" s="23" t="n">
-        <v>175</v>
+        <v>227</v>
       </c>
     </row>
     <row r="262" ht="20" customHeight="1">
@@ -7578,7 +7578,7 @@
         </is>
       </c>
       <c r="E262" s="20" t="n">
-        <v>120</v>
+        <v>152</v>
       </c>
     </row>
     <row r="263" ht="20" customHeight="1">
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="E263" s="23" t="n">
-        <v>130</v>
+        <v>197</v>
       </c>
     </row>
     <row r="264" ht="20" customHeight="1">
@@ -7628,7 +7628,7 @@
         </is>
       </c>
       <c r="E264" s="20" t="n">
-        <v>238</v>
+        <v>193</v>
       </c>
     </row>
     <row r="265" ht="20" customHeight="1">
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="E265" s="23" t="n">
-        <v>180</v>
+        <v>232</v>
       </c>
     </row>
     <row r="266" ht="20" customHeight="1">
@@ -7678,7 +7678,7 @@
         </is>
       </c>
       <c r="E266" s="20" t="n">
-        <v>184</v>
+        <v>130</v>
       </c>
     </row>
     <row r="267" ht="20" customHeight="1">
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="E267" s="23" t="n">
-        <v>205</v>
+        <v>240</v>
       </c>
     </row>
     <row r="268" ht="20" customHeight="1">
@@ -7728,7 +7728,7 @@
         </is>
       </c>
       <c r="E268" s="20" t="n">
-        <v>164</v>
+        <v>133</v>
       </c>
     </row>
     <row r="269" ht="20" customHeight="1">
@@ -7753,7 +7753,7 @@
         </is>
       </c>
       <c r="E269" s="23" t="n">
-        <v>161</v>
+        <v>194</v>
       </c>
     </row>
     <row r="270" ht="20" customHeight="1">
@@ -7778,7 +7778,7 @@
         </is>
       </c>
       <c r="E270" s="20" t="n">
-        <v>166</v>
+        <v>157</v>
       </c>
     </row>
     <row r="271" ht="20" customHeight="1">
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="E271" s="23" t="n">
-        <v>155</v>
+        <v>183</v>
       </c>
     </row>
     <row r="272" ht="20" customHeight="1">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="E272" s="20" t="n">
-        <v>202</v>
+        <v>144</v>
       </c>
     </row>
     <row r="273" ht="20" customHeight="1">
@@ -7853,7 +7853,7 @@
         </is>
       </c>
       <c r="E273" s="23" t="n">
-        <v>227</v>
+        <v>165</v>
       </c>
     </row>
     <row r="274" ht="20" customHeight="1">
@@ -7878,7 +7878,7 @@
         </is>
       </c>
       <c r="E274" s="20" t="n">
-        <v>114</v>
+        <v>123</v>
       </c>
     </row>
     <row r="275" ht="20" customHeight="1">
@@ -7903,7 +7903,7 @@
         </is>
       </c>
       <c r="E275" s="23" t="n">
-        <v>205</v>
+        <v>135</v>
       </c>
     </row>
     <row r="276" ht="20" customHeight="1">
@@ -7928,7 +7928,7 @@
         </is>
       </c>
       <c r="E276" s="20" t="n">
-        <v>120</v>
+        <v>168</v>
       </c>
     </row>
     <row r="277" ht="20" customHeight="1">
@@ -7953,7 +7953,7 @@
         </is>
       </c>
       <c r="E277" s="23" t="n">
-        <v>175</v>
+        <v>211</v>
       </c>
     </row>
     <row r="278" ht="20" customHeight="1">
@@ -7978,7 +7978,7 @@
         </is>
       </c>
       <c r="E278" s="20" t="n">
-        <v>179</v>
+        <v>170</v>
       </c>
     </row>
     <row r="279" ht="20" customHeight="1">
@@ -8003,7 +8003,7 @@
         </is>
       </c>
       <c r="E279" s="23" t="n">
-        <v>232</v>
+        <v>168</v>
       </c>
     </row>
     <row r="280" ht="20" customHeight="1">
@@ -8028,7 +8028,7 @@
         </is>
       </c>
       <c r="E280" s="20" t="n">
-        <v>123</v>
+        <v>217</v>
       </c>
     </row>
     <row r="281" ht="20" customHeight="1">
@@ -8053,7 +8053,7 @@
         </is>
       </c>
       <c r="E281" s="23" t="n">
-        <v>232</v>
+        <v>162</v>
       </c>
     </row>
     <row r="282" ht="20" customHeight="1">
@@ -8078,7 +8078,7 @@
         </is>
       </c>
       <c r="E282" s="20" t="n">
-        <v>133</v>
+        <v>118</v>
       </c>
     </row>
     <row r="283" ht="20" customHeight="1">
@@ -8103,7 +8103,7 @@
         </is>
       </c>
       <c r="E283" s="23" t="n">
-        <v>120</v>
+        <v>200</v>
       </c>
     </row>
     <row r="284" ht="20" customHeight="1">
@@ -8128,7 +8128,7 @@
         </is>
       </c>
       <c r="E284" s="20" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="285" ht="20" customHeight="1">
@@ -8153,7 +8153,7 @@
         </is>
       </c>
       <c r="E285" s="23" t="n">
-        <v>128</v>
+        <v>199</v>
       </c>
     </row>
     <row r="286" ht="20" customHeight="1">
@@ -8178,7 +8178,7 @@
         </is>
       </c>
       <c r="E286" s="20" t="n">
-        <v>179</v>
+        <v>171</v>
       </c>
     </row>
     <row r="287" ht="20" customHeight="1">
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="E287" s="23" t="n">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="288" ht="20" customHeight="1">
@@ -8228,7 +8228,7 @@
         </is>
       </c>
       <c r="E288" s="20" t="n">
-        <v>161</v>
+        <v>114</v>
       </c>
     </row>
     <row r="289" ht="20" customHeight="1">
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="E289" s="23" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
     </row>
     <row r="290" ht="20" customHeight="1">
@@ -8278,7 +8278,7 @@
         </is>
       </c>
       <c r="E290" s="20" t="n">
-        <v>157</v>
+        <v>196</v>
       </c>
     </row>
     <row r="291" ht="20" customHeight="1">
@@ -8303,7 +8303,7 @@
         </is>
       </c>
       <c r="E291" s="23" t="n">
-        <v>151</v>
+        <v>166</v>
       </c>
     </row>
     <row r="292" ht="20" customHeight="1">
@@ -8328,7 +8328,7 @@
         </is>
       </c>
       <c r="E292" s="20" t="n">
-        <v>125</v>
+        <v>175</v>
       </c>
     </row>
     <row r="293" ht="20" customHeight="1">
@@ -8353,7 +8353,7 @@
         </is>
       </c>
       <c r="E293" s="23" t="n">
-        <v>124</v>
+        <v>215</v>
       </c>
     </row>
     <row r="294" ht="20" customHeight="1">
@@ -8378,7 +8378,7 @@
         </is>
       </c>
       <c r="E294" s="20" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="295" ht="20" customHeight="1">
@@ -8403,7 +8403,7 @@
         </is>
       </c>
       <c r="E295" s="23" t="n">
-        <v>231</v>
+        <v>239</v>
       </c>
     </row>
     <row r="296" ht="20" customHeight="1">
@@ -8428,7 +8428,7 @@
         </is>
       </c>
       <c r="E296" s="20" t="n">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="297" ht="20" customHeight="1">
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="E297" s="23" t="n">
-        <v>225</v>
+        <v>193</v>
       </c>
     </row>
     <row r="298" ht="20" customHeight="1">
@@ -8478,7 +8478,7 @@
         </is>
       </c>
       <c r="E298" s="20" t="n">
-        <v>237</v>
+        <v>209</v>
       </c>
     </row>
     <row r="299" ht="20" customHeight="1">
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="E299" s="23" t="n">
-        <v>172</v>
+        <v>203</v>
       </c>
     </row>
     <row r="300" ht="20" customHeight="1">
@@ -8528,7 +8528,7 @@
         </is>
       </c>
       <c r="E300" s="20" t="n">
-        <v>133</v>
+        <v>111</v>
       </c>
     </row>
     <row r="301" ht="20" customHeight="1">
@@ -8553,7 +8553,7 @@
         </is>
       </c>
       <c r="E301" s="23" t="n">
-        <v>122</v>
+        <v>139</v>
       </c>
     </row>
     <row r="302" ht="20" customHeight="1">
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="E302" s="20" t="n">
-        <v>116</v>
+        <v>237</v>
       </c>
     </row>
     <row r="303" ht="20" customHeight="1">
@@ -8603,7 +8603,7 @@
         </is>
       </c>
       <c r="E303" s="23" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="304" ht="20" customHeight="1">
@@ -8628,7 +8628,7 @@
         </is>
       </c>
       <c r="E304" s="20" t="n">
-        <v>202</v>
+        <v>235</v>
       </c>
     </row>
     <row r="305" ht="20" customHeight="1">
@@ -8653,7 +8653,7 @@
         </is>
       </c>
       <c r="E305" s="23" t="n">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="306" ht="20" customHeight="1">
@@ -8678,7 +8678,7 @@
         </is>
       </c>
       <c r="E306" s="20" t="n">
-        <v>213</v>
+        <v>123</v>
       </c>
     </row>
     <row r="307" ht="20" customHeight="1">
@@ -8703,7 +8703,7 @@
         </is>
       </c>
       <c r="E307" s="23" t="n">
-        <v>179</v>
+        <v>192</v>
       </c>
     </row>
     <row r="308" ht="20" customHeight="1">
@@ -8728,7 +8728,7 @@
         </is>
       </c>
       <c r="E308" s="20" t="n">
-        <v>113</v>
+        <v>188</v>
       </c>
     </row>
     <row r="309" ht="20" customHeight="1">
@@ -8753,7 +8753,7 @@
         </is>
       </c>
       <c r="E309" s="23" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="310" ht="20" customHeight="1">
@@ -8778,7 +8778,7 @@
         </is>
       </c>
       <c r="E310" s="20" t="n">
-        <v>169</v>
+        <v>227</v>
       </c>
     </row>
     <row r="311" ht="20" customHeight="1">
@@ -8803,7 +8803,7 @@
         </is>
       </c>
       <c r="E311" s="23" t="n">
-        <v>155</v>
+        <v>169</v>
       </c>
     </row>
     <row r="312" ht="20" customHeight="1">
@@ -8828,7 +8828,7 @@
         </is>
       </c>
       <c r="E312" s="20" t="n">
-        <v>190</v>
+        <v>115</v>
       </c>
     </row>
     <row r="313" ht="20" customHeight="1">
@@ -8853,7 +8853,7 @@
         </is>
       </c>
       <c r="E313" s="23" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="314" ht="20" customHeight="1">
@@ -8878,7 +8878,7 @@
         </is>
       </c>
       <c r="E314" s="20" t="n">
-        <v>188</v>
+        <v>135</v>
       </c>
     </row>
     <row r="315" ht="20" customHeight="1">
@@ -8903,7 +8903,7 @@
         </is>
       </c>
       <c r="E315" s="23" t="n">
-        <v>123</v>
+        <v>203</v>
       </c>
     </row>
     <row r="316" ht="20" customHeight="1">
@@ -8928,7 +8928,7 @@
         </is>
       </c>
       <c r="E316" s="20" t="n">
-        <v>194</v>
+        <v>118</v>
       </c>
     </row>
     <row r="317" ht="20" customHeight="1">
@@ -8953,7 +8953,7 @@
         </is>
       </c>
       <c r="E317" s="23" t="n">
-        <v>122</v>
+        <v>171</v>
       </c>
     </row>
     <row r="318" ht="20" customHeight="1">
@@ -8978,7 +8978,7 @@
         </is>
       </c>
       <c r="E318" s="20" t="n">
-        <v>157</v>
+        <v>179</v>
       </c>
     </row>
     <row r="319" ht="20" customHeight="1">
@@ -9003,7 +9003,7 @@
         </is>
       </c>
       <c r="E319" s="23" t="n">
-        <v>234</v>
+        <v>145</v>
       </c>
     </row>
     <row r="320" ht="20" customHeight="1">
@@ -9028,7 +9028,7 @@
         </is>
       </c>
       <c r="E320" s="20" t="n">
-        <v>226</v>
+        <v>165</v>
       </c>
     </row>
     <row r="321" ht="20" customHeight="1">
@@ -9053,7 +9053,7 @@
         </is>
       </c>
       <c r="E321" s="23" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="322" ht="20" customHeight="1">
@@ -9078,7 +9078,7 @@
         </is>
       </c>
       <c r="E322" s="20" t="n">
-        <v>204</v>
+        <v>236</v>
       </c>
     </row>
     <row r="323" ht="20" customHeight="1">
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="E323" s="23" t="n">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="324" ht="20" customHeight="1">
@@ -9128,7 +9128,7 @@
         </is>
       </c>
       <c r="E324" s="20" t="n">
-        <v>178</v>
+        <v>160</v>
       </c>
     </row>
     <row r="325" ht="20" customHeight="1">
@@ -9153,7 +9153,7 @@
         </is>
       </c>
       <c r="E325" s="23" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="326" ht="20" customHeight="1">
@@ -9178,7 +9178,7 @@
         </is>
       </c>
       <c r="E326" s="20" t="n">
-        <v>201</v>
+        <v>154</v>
       </c>
     </row>
     <row r="327" ht="20" customHeight="1">
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="E327" s="23" t="n">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="328" ht="20" customHeight="1">
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="E328" s="20" t="n">
-        <v>223</v>
+        <v>186</v>
       </c>
     </row>
     <row r="329" ht="20" customHeight="1">
@@ -9253,7 +9253,7 @@
         </is>
       </c>
       <c r="E329" s="23" t="n">
-        <v>166</v>
+        <v>123</v>
       </c>
     </row>
     <row r="330" ht="20" customHeight="1">
@@ -9278,7 +9278,7 @@
         </is>
       </c>
       <c r="E330" s="20" t="n">
-        <v>117</v>
+        <v>159</v>
       </c>
     </row>
     <row r="331" ht="20" customHeight="1">
@@ -9303,7 +9303,7 @@
         </is>
       </c>
       <c r="E331" s="23" t="n">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="332" ht="20" customHeight="1">
@@ -9328,7 +9328,7 @@
         </is>
       </c>
       <c r="E332" s="20" t="n">
-        <v>154</v>
+        <v>135</v>
       </c>
     </row>
     <row r="333" ht="20" customHeight="1">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="E333" s="23" t="n">
-        <v>184</v>
+        <v>220</v>
       </c>
     </row>
     <row r="334" ht="20" customHeight="1">
@@ -9378,7 +9378,7 @@
         </is>
       </c>
       <c r="E334" s="20" t="n">
-        <v>240</v>
+        <v>233</v>
       </c>
     </row>
     <row r="335" ht="20" customHeight="1">
@@ -9403,7 +9403,7 @@
         </is>
       </c>
       <c r="E335" s="23" t="n">
-        <v>141</v>
+        <v>223</v>
       </c>
     </row>
     <row r="336" ht="20" customHeight="1">
@@ -9428,7 +9428,7 @@
         </is>
       </c>
       <c r="E336" s="20" t="n">
-        <v>199</v>
+        <v>190</v>
       </c>
     </row>
     <row r="337" ht="20" customHeight="1">
@@ -9453,7 +9453,7 @@
         </is>
       </c>
       <c r="E337" s="23" t="n">
-        <v>232</v>
+        <v>211</v>
       </c>
     </row>
     <row r="338" ht="20" customHeight="1">
@@ -9478,7 +9478,7 @@
         </is>
       </c>
       <c r="E338" s="20" t="n">
-        <v>157</v>
+        <v>116</v>
       </c>
     </row>
     <row r="339" ht="20" customHeight="1">
@@ -9503,7 +9503,7 @@
         </is>
       </c>
       <c r="E339" s="23" t="n">
-        <v>192</v>
+        <v>182</v>
       </c>
     </row>
     <row r="340" ht="20" customHeight="1">
@@ -9528,7 +9528,7 @@
         </is>
       </c>
       <c r="E340" s="20" t="n">
-        <v>191</v>
+        <v>202</v>
       </c>
     </row>
     <row r="341" ht="20" customHeight="1">
@@ -9553,7 +9553,7 @@
         </is>
       </c>
       <c r="E341" s="23" t="n">
-        <v>163</v>
+        <v>240</v>
       </c>
     </row>
     <row r="342" ht="20" customHeight="1">
@@ -9578,7 +9578,7 @@
         </is>
       </c>
       <c r="E342" s="20" t="n">
-        <v>234</v>
+        <v>134</v>
       </c>
     </row>
     <row r="343" ht="20" customHeight="1">
@@ -9603,7 +9603,7 @@
         </is>
       </c>
       <c r="E343" s="23" t="n">
-        <v>224</v>
+        <v>177</v>
       </c>
     </row>
     <row r="344" ht="20" customHeight="1">
@@ -9628,7 +9628,7 @@
         </is>
       </c>
       <c r="E344" s="20" t="n">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="345" ht="20" customHeight="1">
@@ -9653,7 +9653,7 @@
         </is>
       </c>
       <c r="E345" s="23" t="n">
-        <v>215</v>
+        <v>200</v>
       </c>
     </row>
     <row r="346" ht="20" customHeight="1">
@@ -9678,7 +9678,7 @@
         </is>
       </c>
       <c r="E346" s="20" t="n">
-        <v>237</v>
+        <v>119</v>
       </c>
     </row>
     <row r="347" ht="20" customHeight="1">
@@ -9703,7 +9703,7 @@
         </is>
       </c>
       <c r="E347" s="23" t="n">
-        <v>171</v>
+        <v>155</v>
       </c>
     </row>
     <row r="348" ht="20" customHeight="1">
@@ -9728,7 +9728,7 @@
         </is>
       </c>
       <c r="E348" s="20" t="n">
-        <v>237</v>
+        <v>144</v>
       </c>
     </row>
     <row r="349" ht="20" customHeight="1">
@@ -9753,7 +9753,7 @@
         </is>
       </c>
       <c r="E349" s="23" t="n">
-        <v>146</v>
+        <v>132</v>
       </c>
     </row>
     <row r="350" ht="20" customHeight="1">
@@ -9778,7 +9778,7 @@
         </is>
       </c>
       <c r="E350" s="20" t="n">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="351" ht="20" customHeight="1">
@@ -9803,7 +9803,7 @@
         </is>
       </c>
       <c r="E351" s="23" t="n">
-        <v>176</v>
+        <v>166</v>
       </c>
     </row>
     <row r="352" ht="20" customHeight="1">
@@ -9828,7 +9828,7 @@
         </is>
       </c>
       <c r="E352" s="20" t="n">
-        <v>202</v>
+        <v>211</v>
       </c>
     </row>
     <row r="353" ht="20" customHeight="1">
@@ -9853,7 +9853,7 @@
         </is>
       </c>
       <c r="E353" s="23" t="n">
-        <v>128</v>
+        <v>167</v>
       </c>
     </row>
     <row r="354" ht="20" customHeight="1">
@@ -9878,7 +9878,7 @@
         </is>
       </c>
       <c r="E354" s="20" t="n">
-        <v>199</v>
+        <v>204</v>
       </c>
     </row>
     <row r="355" ht="20" customHeight="1">
@@ -9903,7 +9903,7 @@
         </is>
       </c>
       <c r="E355" s="23" t="n">
-        <v>177</v>
+        <v>152</v>
       </c>
     </row>
     <row r="356" ht="20" customHeight="1">
@@ -9928,7 +9928,7 @@
         </is>
       </c>
       <c r="E356" s="20" t="n">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="357" ht="20" customHeight="1">
@@ -9953,7 +9953,7 @@
         </is>
       </c>
       <c r="E357" s="23" t="n">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="358" ht="20" customHeight="1">
@@ -9978,7 +9978,7 @@
         </is>
       </c>
       <c r="E358" s="20" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="359" ht="20" customHeight="1">
@@ -10003,7 +10003,7 @@
         </is>
       </c>
       <c r="E359" s="23" t="n">
-        <v>136</v>
+        <v>184</v>
       </c>
     </row>
     <row r="360" ht="20" customHeight="1">
@@ -10028,7 +10028,7 @@
         </is>
       </c>
       <c r="E360" s="20" t="n">
-        <v>188</v>
+        <v>165</v>
       </c>
     </row>
     <row r="361" ht="20" customHeight="1">
@@ -10053,7 +10053,7 @@
         </is>
       </c>
       <c r="E361" s="23" t="n">
-        <v>167</v>
+        <v>190</v>
       </c>
     </row>
     <row r="362" ht="20" customHeight="1">
@@ -10078,7 +10078,7 @@
         </is>
       </c>
       <c r="E362" s="20" t="n">
-        <v>118</v>
+        <v>194</v>
       </c>
     </row>
     <row r="363" ht="20" customHeight="1">
@@ -10103,7 +10103,7 @@
         </is>
       </c>
       <c r="E363" s="23" t="n">
-        <v>185</v>
+        <v>226</v>
       </c>
     </row>
     <row r="364" ht="20" customHeight="1">
@@ -10128,7 +10128,7 @@
         </is>
       </c>
       <c r="E364" s="20" t="n">
-        <v>124</v>
+        <v>233</v>
       </c>
     </row>
     <row r="365" ht="20" customHeight="1">
@@ -10153,7 +10153,7 @@
         </is>
       </c>
       <c r="E365" s="23" t="n">
-        <v>129</v>
+        <v>114</v>
       </c>
     </row>
     <row r="366" ht="20" customHeight="1">
@@ -10178,7 +10178,7 @@
         </is>
       </c>
       <c r="E366" s="20" t="n">
-        <v>203</v>
+        <v>172</v>
       </c>
     </row>
     <row r="367" ht="20" customHeight="1">
@@ -10203,7 +10203,7 @@
         </is>
       </c>
       <c r="E367" s="23" t="n">
-        <v>210</v>
+        <v>173</v>
       </c>
     </row>
     <row r="368" ht="20" customHeight="1">
@@ -10228,7 +10228,7 @@
         </is>
       </c>
       <c r="E368" s="20" t="n">
-        <v>205</v>
+        <v>181</v>
       </c>
     </row>
     <row r="369" ht="20" customHeight="1">
@@ -10253,7 +10253,7 @@
         </is>
       </c>
       <c r="E369" s="23" t="n">
-        <v>216</v>
+        <v>179</v>
       </c>
     </row>
     <row r="370" ht="20" customHeight="1">
@@ -10278,7 +10278,7 @@
         </is>
       </c>
       <c r="E370" s="20" t="n">
-        <v>185</v>
+        <v>204</v>
       </c>
     </row>
     <row r="371" ht="20" customHeight="1">
@@ -10303,7 +10303,7 @@
         </is>
       </c>
       <c r="E371" s="23" t="n">
-        <v>203</v>
+        <v>187</v>
       </c>
     </row>
     <row r="372" ht="20" customHeight="1">
@@ -10328,7 +10328,7 @@
         </is>
       </c>
       <c r="E372" s="20" t="n">
-        <v>194</v>
+        <v>217</v>
       </c>
     </row>
     <row r="373" ht="20" customHeight="1">
@@ -10353,7 +10353,7 @@
         </is>
       </c>
       <c r="E373" s="23" t="n">
-        <v>235</v>
+        <v>129</v>
       </c>
     </row>
     <row r="374" ht="20" customHeight="1">
@@ -10378,7 +10378,7 @@
         </is>
       </c>
       <c r="E374" s="20" t="n">
-        <v>199</v>
+        <v>234</v>
       </c>
     </row>
     <row r="375" ht="20" customHeight="1">
@@ -10403,7 +10403,7 @@
         </is>
       </c>
       <c r="E375" s="23" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="376" ht="20" customHeight="1">
@@ -10428,7 +10428,7 @@
         </is>
       </c>
       <c r="E376" s="20" t="n">
-        <v>122</v>
+        <v>210</v>
       </c>
     </row>
     <row r="377" ht="20" customHeight="1">
@@ -10453,7 +10453,7 @@
         </is>
       </c>
       <c r="E377" s="23" t="n">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="378" ht="20" customHeight="1">
@@ -10478,7 +10478,7 @@
         </is>
       </c>
       <c r="E378" s="20" t="n">
-        <v>212</v>
+        <v>123</v>
       </c>
     </row>
     <row r="379" ht="20" customHeight="1">
@@ -10503,7 +10503,7 @@
         </is>
       </c>
       <c r="E379" s="23" t="n">
-        <v>165</v>
+        <v>159</v>
       </c>
     </row>
     <row r="380" ht="20" customHeight="1">
@@ -10528,7 +10528,7 @@
         </is>
       </c>
       <c r="E380" s="20" t="n">
-        <v>164</v>
+        <v>188</v>
       </c>
     </row>
     <row r="381" ht="20" customHeight="1">
@@ -10553,7 +10553,7 @@
         </is>
       </c>
       <c r="E381" s="23" t="n">
-        <v>129</v>
+        <v>210</v>
       </c>
     </row>
     <row r="382" ht="20" customHeight="1">
@@ -10578,7 +10578,7 @@
         </is>
       </c>
       <c r="E382" s="20" t="n">
-        <v>148</v>
+        <v>203</v>
       </c>
     </row>
     <row r="383" ht="20" customHeight="1">
@@ -10603,7 +10603,7 @@
         </is>
       </c>
       <c r="E383" s="23" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="384" ht="20" customHeight="1">
@@ -10628,7 +10628,7 @@
         </is>
       </c>
       <c r="E384" s="20" t="n">
-        <v>125</v>
+        <v>190</v>
       </c>
     </row>
     <row r="385" ht="20" customHeight="1">
@@ -10653,7 +10653,7 @@
         </is>
       </c>
       <c r="E385" s="23" t="n">
-        <v>189</v>
+        <v>177</v>
       </c>
     </row>
     <row r="386" ht="20" customHeight="1">
@@ -10678,7 +10678,7 @@
         </is>
       </c>
       <c r="E386" s="20" t="n">
-        <v>131</v>
+        <v>182</v>
       </c>
     </row>
     <row r="387" ht="20" customHeight="1">
@@ -10703,7 +10703,7 @@
         </is>
       </c>
       <c r="E387" s="23" t="n">
-        <v>169</v>
+        <v>235</v>
       </c>
     </row>
     <row r="388" ht="20" customHeight="1">
@@ -10728,7 +10728,7 @@
         </is>
       </c>
       <c r="E388" s="20" t="n">
-        <v>230</v>
+        <v>152</v>
       </c>
     </row>
     <row r="389" ht="20" customHeight="1">
@@ -10753,7 +10753,7 @@
         </is>
       </c>
       <c r="E389" s="23" t="n">
-        <v>179</v>
+        <v>185</v>
       </c>
     </row>
     <row r="390" ht="20" customHeight="1">
@@ -10778,7 +10778,7 @@
         </is>
       </c>
       <c r="E390" s="20" t="n">
-        <v>211</v>
+        <v>139</v>
       </c>
     </row>
     <row r="391" ht="20" customHeight="1">
@@ -10803,7 +10803,7 @@
         </is>
       </c>
       <c r="E391" s="23" t="n">
-        <v>165</v>
+        <v>239</v>
       </c>
     </row>
     <row r="392" ht="20" customHeight="1">
@@ -10828,7 +10828,7 @@
         </is>
       </c>
       <c r="E392" s="20" t="n">
-        <v>122</v>
+        <v>183</v>
       </c>
     </row>
     <row r="393" ht="20" customHeight="1">
@@ -10853,7 +10853,7 @@
         </is>
       </c>
       <c r="E393" s="23" t="n">
-        <v>240</v>
+        <v>216</v>
       </c>
     </row>
     <row r="394" ht="20" customHeight="1">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="E394" s="20" t="n">
-        <v>174</v>
+        <v>135</v>
       </c>
     </row>
     <row r="395" ht="20" customHeight="1">
@@ -10903,7 +10903,7 @@
         </is>
       </c>
       <c r="E395" s="23" t="n">
-        <v>238</v>
+        <v>139</v>
       </c>
     </row>
     <row r="396" ht="20" customHeight="1">
@@ -10928,7 +10928,7 @@
         </is>
       </c>
       <c r="E396" s="20" t="n">
-        <v>154</v>
+        <v>173</v>
       </c>
     </row>
     <row r="397" ht="20" customHeight="1">
@@ -10953,7 +10953,7 @@
         </is>
       </c>
       <c r="E397" s="23" t="n">
-        <v>133</v>
+        <v>117</v>
       </c>
     </row>
     <row r="398" ht="20" customHeight="1">
@@ -10978,7 +10978,7 @@
         </is>
       </c>
       <c r="E398" s="20" t="n">
-        <v>221</v>
+        <v>169</v>
       </c>
     </row>
     <row r="399" ht="20" customHeight="1">
@@ -11003,7 +11003,7 @@
         </is>
       </c>
       <c r="E399" s="23" t="n">
-        <v>228</v>
+        <v>171</v>
       </c>
     </row>
     <row r="400" ht="20" customHeight="1">
@@ -11028,7 +11028,7 @@
         </is>
       </c>
       <c r="E400" s="20" t="n">
-        <v>218</v>
+        <v>205</v>
       </c>
     </row>
     <row r="401" ht="20" customHeight="1">
@@ -11053,7 +11053,7 @@
         </is>
       </c>
       <c r="E401" s="23" t="n">
-        <v>184</v>
+        <v>151</v>
       </c>
     </row>
     <row r="402" ht="20" customHeight="1">
@@ -11078,7 +11078,7 @@
         </is>
       </c>
       <c r="E402" s="20" t="n">
-        <v>130</v>
+        <v>155</v>
       </c>
     </row>
     <row r="403" ht="20" customHeight="1">
@@ -11103,7 +11103,7 @@
         </is>
       </c>
       <c r="E403" s="23" t="n">
-        <v>146</v>
+        <v>229</v>
       </c>
     </row>
     <row r="404" ht="20" customHeight="1">
@@ -11128,7 +11128,7 @@
         </is>
       </c>
       <c r="E404" s="20" t="n">
-        <v>112</v>
+        <v>213</v>
       </c>
     </row>
     <row r="405" ht="20" customHeight="1">
@@ -11153,7 +11153,7 @@
         </is>
       </c>
       <c r="E405" s="23" t="n">
-        <v>199</v>
+        <v>217</v>
       </c>
     </row>
     <row r="406" ht="20" customHeight="1">
@@ -11178,7 +11178,7 @@
         </is>
       </c>
       <c r="E406" s="20" t="n">
-        <v>178</v>
+        <v>197</v>
       </c>
     </row>
     <row r="407" ht="20" customHeight="1">
@@ -11203,7 +11203,7 @@
         </is>
       </c>
       <c r="E407" s="23" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="408" ht="20" customHeight="1">
@@ -11228,7 +11228,7 @@
         </is>
       </c>
       <c r="E408" s="20" t="n">
-        <v>132</v>
+        <v>191</v>
       </c>
     </row>
     <row r="409" ht="20" customHeight="1">
@@ -11253,7 +11253,7 @@
         </is>
       </c>
       <c r="E409" s="23" t="n">
-        <v>121</v>
+        <v>201</v>
       </c>
     </row>
     <row r="410" ht="20" customHeight="1">
@@ -11278,7 +11278,7 @@
         </is>
       </c>
       <c r="E410" s="20" t="n">
-        <v>145</v>
+        <v>157</v>
       </c>
     </row>
     <row r="411" ht="20" customHeight="1">
@@ -11303,7 +11303,7 @@
         </is>
       </c>
       <c r="E411" s="23" t="n">
-        <v>227</v>
+        <v>155</v>
       </c>
     </row>
     <row r="412" ht="20" customHeight="1">
@@ -11328,7 +11328,7 @@
         </is>
       </c>
       <c r="E412" s="20" t="n">
-        <v>157</v>
+        <v>178</v>
       </c>
     </row>
     <row r="413" ht="20" customHeight="1">
@@ -11353,7 +11353,7 @@
         </is>
       </c>
       <c r="E413" s="23" t="n">
-        <v>193</v>
+        <v>124</v>
       </c>
     </row>
     <row r="414" ht="20" customHeight="1">
@@ -11378,7 +11378,7 @@
         </is>
       </c>
       <c r="E414" s="20" t="n">
-        <v>195</v>
+        <v>118</v>
       </c>
     </row>
     <row r="415" ht="20" customHeight="1">
@@ -11403,7 +11403,7 @@
         </is>
       </c>
       <c r="E415" s="23" t="n">
-        <v>143</v>
+        <v>207</v>
       </c>
     </row>
     <row r="416" ht="20" customHeight="1">
@@ -11428,7 +11428,7 @@
         </is>
       </c>
       <c r="E416" s="20" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
     </row>
     <row r="417" ht="20" customHeight="1">
@@ -11453,7 +11453,7 @@
         </is>
       </c>
       <c r="E417" s="23" t="n">
-        <v>169</v>
+        <v>207</v>
       </c>
     </row>
     <row r="418" ht="20" customHeight="1">
@@ -11478,7 +11478,7 @@
         </is>
       </c>
       <c r="E418" s="20" t="n">
-        <v>124</v>
+        <v>132</v>
       </c>
     </row>
     <row r="419" ht="20" customHeight="1">
@@ -11503,7 +11503,7 @@
         </is>
       </c>
       <c r="E419" s="23" t="n">
-        <v>227</v>
+        <v>214</v>
       </c>
     </row>
     <row r="420" ht="20" customHeight="1">
@@ -11528,7 +11528,7 @@
         </is>
       </c>
       <c r="E420" s="20" t="n">
-        <v>134</v>
+        <v>213</v>
       </c>
     </row>
     <row r="421" ht="20" customHeight="1">
@@ -11553,7 +11553,7 @@
         </is>
       </c>
       <c r="E421" s="23" t="n">
-        <v>146</v>
+        <v>135</v>
       </c>
     </row>
     <row r="422" ht="20" customHeight="1">
@@ -11578,7 +11578,7 @@
         </is>
       </c>
       <c r="E422" s="20" t="n">
-        <v>128</v>
+        <v>238</v>
       </c>
     </row>
     <row r="423" ht="20" customHeight="1">
@@ -11603,7 +11603,7 @@
         </is>
       </c>
       <c r="E423" s="23" t="n">
-        <v>187</v>
+        <v>219</v>
       </c>
     </row>
     <row r="424" ht="20" customHeight="1">
@@ -11628,7 +11628,7 @@
         </is>
       </c>
       <c r="E424" s="20" t="n">
-        <v>163</v>
+        <v>204</v>
       </c>
     </row>
     <row r="425" ht="20" customHeight="1">
@@ -11653,7 +11653,7 @@
         </is>
       </c>
       <c r="E425" s="23" t="n">
-        <v>121</v>
+        <v>216</v>
       </c>
     </row>
     <row r="426" ht="20" customHeight="1">
@@ -11678,7 +11678,7 @@
         </is>
       </c>
       <c r="E426" s="20" t="n">
-        <v>160</v>
+        <v>137</v>
       </c>
     </row>
     <row r="427" ht="20" customHeight="1">
@@ -11703,7 +11703,7 @@
         </is>
       </c>
       <c r="E427" s="23" t="n">
-        <v>151</v>
+        <v>135</v>
       </c>
     </row>
     <row r="428" ht="20" customHeight="1">
@@ -11728,7 +11728,7 @@
         </is>
       </c>
       <c r="E428" s="20" t="n">
-        <v>195</v>
+        <v>235</v>
       </c>
     </row>
     <row r="429" ht="20" customHeight="1">
@@ -11753,7 +11753,7 @@
         </is>
       </c>
       <c r="E429" s="23" t="n">
-        <v>137</v>
+        <v>114</v>
       </c>
     </row>
     <row r="430" ht="20" customHeight="1">
@@ -11778,7 +11778,7 @@
         </is>
       </c>
       <c r="E430" s="20" t="n">
-        <v>125</v>
+        <v>206</v>
       </c>
     </row>
     <row r="431" ht="20" customHeight="1">
@@ -11803,7 +11803,7 @@
         </is>
       </c>
       <c r="E431" s="23" t="n">
-        <v>171</v>
+        <v>141</v>
       </c>
     </row>
     <row r="432" ht="20" customHeight="1">
@@ -11828,7 +11828,7 @@
         </is>
       </c>
       <c r="E432" s="20" t="n">
-        <v>199</v>
+        <v>176</v>
       </c>
     </row>
     <row r="433" ht="20" customHeight="1">
@@ -11853,7 +11853,7 @@
         </is>
       </c>
       <c r="E433" s="23" t="n">
-        <v>200</v>
+        <v>233</v>
       </c>
     </row>
     <row r="434" ht="20" customHeight="1">
@@ -11878,7 +11878,7 @@
         </is>
       </c>
       <c r="E434" s="20" t="n">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="435" ht="20" customHeight="1">
@@ -11903,7 +11903,7 @@
         </is>
       </c>
       <c r="E435" s="23" t="n">
-        <v>237</v>
+        <v>215</v>
       </c>
     </row>
     <row r="436" ht="20" customHeight="1">
@@ -11928,7 +11928,7 @@
         </is>
       </c>
       <c r="E436" s="20" t="n">
-        <v>110</v>
+        <v>154</v>
       </c>
     </row>
     <row r="437" ht="20" customHeight="1">
@@ -11953,7 +11953,7 @@
         </is>
       </c>
       <c r="E437" s="23" t="n">
-        <v>161</v>
+        <v>168</v>
       </c>
     </row>
     <row r="438" ht="20" customHeight="1">
@@ -11978,7 +11978,7 @@
         </is>
       </c>
       <c r="E438" s="20" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="439" ht="20" customHeight="1">
@@ -12003,7 +12003,7 @@
         </is>
       </c>
       <c r="E439" s="23" t="n">
-        <v>223</v>
+        <v>144</v>
       </c>
     </row>
     <row r="440" ht="20" customHeight="1">
@@ -12028,7 +12028,7 @@
         </is>
       </c>
       <c r="E440" s="20" t="n">
-        <v>192</v>
+        <v>146</v>
       </c>
     </row>
     <row r="441" ht="20" customHeight="1">
@@ -12053,7 +12053,7 @@
         </is>
       </c>
       <c r="E441" s="23" t="n">
-        <v>170</v>
+        <v>223</v>
       </c>
     </row>
     <row r="442" ht="20" customHeight="1">
@@ -12078,7 +12078,7 @@
         </is>
       </c>
       <c r="E442" s="20" t="n">
-        <v>115</v>
+        <v>186</v>
       </c>
     </row>
     <row r="443" ht="20" customHeight="1">
@@ -12103,7 +12103,7 @@
         </is>
       </c>
       <c r="E443" s="23" t="n">
-        <v>138</v>
+        <v>222</v>
       </c>
     </row>
     <row r="444" ht="20" customHeight="1">
@@ -12128,7 +12128,7 @@
         </is>
       </c>
       <c r="E444" s="20" t="n">
-        <v>227</v>
+        <v>208</v>
       </c>
     </row>
     <row r="445" ht="20" customHeight="1">
@@ -12153,7 +12153,7 @@
         </is>
       </c>
       <c r="E445" s="23" t="n">
-        <v>159</v>
+        <v>141</v>
       </c>
     </row>
     <row r="446" ht="20" customHeight="1">
@@ -12178,7 +12178,7 @@
         </is>
       </c>
       <c r="E446" s="20" t="n">
-        <v>181</v>
+        <v>123</v>
       </c>
     </row>
     <row r="447" ht="20" customHeight="1">
@@ -12203,7 +12203,7 @@
         </is>
       </c>
       <c r="E447" s="23" t="n">
-        <v>161</v>
+        <v>190</v>
       </c>
     </row>
     <row r="448" ht="20" customHeight="1">
@@ -12228,7 +12228,7 @@
         </is>
       </c>
       <c r="E448" s="20" t="n">
-        <v>189</v>
+        <v>227</v>
       </c>
     </row>
     <row r="449" ht="20" customHeight="1">
@@ -12253,7 +12253,7 @@
         </is>
       </c>
       <c r="E449" s="23" t="n">
-        <v>110</v>
+        <v>194</v>
       </c>
     </row>
     <row r="450" ht="20" customHeight="1">
@@ -12278,7 +12278,7 @@
         </is>
       </c>
       <c r="E450" s="20" t="n">
-        <v>211</v>
+        <v>199</v>
       </c>
     </row>
     <row r="451" ht="20" customHeight="1">
@@ -12303,7 +12303,7 @@
         </is>
       </c>
       <c r="E451" s="23" t="n">
-        <v>138</v>
+        <v>173</v>
       </c>
     </row>
     <row r="452" ht="20" customHeight="1">
@@ -12328,7 +12328,7 @@
         </is>
       </c>
       <c r="E452" s="20" t="n">
-        <v>233</v>
+        <v>189</v>
       </c>
     </row>
     <row r="453" ht="20" customHeight="1">
@@ -12353,7 +12353,7 @@
         </is>
       </c>
       <c r="E453" s="23" t="n">
-        <v>235</v>
+        <v>210</v>
       </c>
     </row>
     <row r="454" ht="20" customHeight="1">
@@ -12378,7 +12378,7 @@
         </is>
       </c>
       <c r="E454" s="20" t="n">
-        <v>154</v>
+        <v>227</v>
       </c>
     </row>
     <row r="455" ht="20" customHeight="1">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="E455" s="23" t="n">
-        <v>189</v>
+        <v>162</v>
       </c>
     </row>
     <row r="456" ht="20" customHeight="1">
@@ -12428,7 +12428,7 @@
         </is>
       </c>
       <c r="E456" s="20" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="457" ht="20" customHeight="1">
@@ -12453,7 +12453,7 @@
         </is>
       </c>
       <c r="E457" s="23" t="n">
-        <v>117</v>
+        <v>177</v>
       </c>
     </row>
     <row r="458" ht="20" customHeight="1">
@@ -12478,7 +12478,7 @@
         </is>
       </c>
       <c r="E458" s="20" t="n">
-        <v>192</v>
+        <v>211</v>
       </c>
     </row>
     <row r="459" ht="20" customHeight="1">
@@ -12503,7 +12503,7 @@
         </is>
       </c>
       <c r="E459" s="23" t="n">
-        <v>231</v>
+        <v>224</v>
       </c>
     </row>
     <row r="460" ht="20" customHeight="1">
@@ -12528,7 +12528,7 @@
         </is>
       </c>
       <c r="E460" s="20" t="n">
-        <v>210</v>
+        <v>238</v>
       </c>
     </row>
     <row r="461" ht="20" customHeight="1">
@@ -12553,7 +12553,7 @@
         </is>
       </c>
       <c r="E461" s="23" t="n">
-        <v>215</v>
+        <v>115</v>
       </c>
     </row>
     <row r="462" ht="20" customHeight="1">
@@ -12578,7 +12578,7 @@
         </is>
       </c>
       <c r="E462" s="20" t="n">
-        <v>193</v>
+        <v>121</v>
       </c>
     </row>
     <row r="463" ht="20" customHeight="1">
@@ -12603,7 +12603,7 @@
         </is>
       </c>
       <c r="E463" s="23" t="n">
-        <v>129</v>
+        <v>169</v>
       </c>
     </row>
     <row r="464" ht="20" customHeight="1">
@@ -12628,7 +12628,7 @@
         </is>
       </c>
       <c r="E464" s="20" t="n">
-        <v>239</v>
+        <v>210</v>
       </c>
     </row>
     <row r="465" ht="20" customHeight="1">
@@ -12653,7 +12653,7 @@
         </is>
       </c>
       <c r="E465" s="23" t="n">
-        <v>111</v>
+        <v>227</v>
       </c>
     </row>
     <row r="466" ht="20" customHeight="1">
@@ -12678,7 +12678,7 @@
         </is>
       </c>
       <c r="E466" s="20" t="n">
-        <v>173</v>
+        <v>204</v>
       </c>
     </row>
     <row r="467" ht="20" customHeight="1">
@@ -12703,7 +12703,7 @@
         </is>
       </c>
       <c r="E467" s="23" t="n">
-        <v>218</v>
+        <v>193</v>
       </c>
     </row>
     <row r="468" ht="20" customHeight="1">
@@ -12728,7 +12728,7 @@
         </is>
       </c>
       <c r="E468" s="20" t="n">
-        <v>238</v>
+        <v>165</v>
       </c>
     </row>
     <row r="469" ht="20" customHeight="1">
@@ -12753,7 +12753,7 @@
         </is>
       </c>
       <c r="E469" s="23" t="n">
-        <v>235</v>
+        <v>163</v>
       </c>
     </row>
     <row r="470" ht="20" customHeight="1">
@@ -12778,7 +12778,7 @@
         </is>
       </c>
       <c r="E470" s="20" t="n">
-        <v>126</v>
+        <v>223</v>
       </c>
     </row>
     <row r="471" ht="20" customHeight="1">
@@ -12803,7 +12803,7 @@
         </is>
       </c>
       <c r="E471" s="23" t="n">
-        <v>210</v>
+        <v>157</v>
       </c>
     </row>
     <row r="472" ht="20" customHeight="1">
@@ -12828,7 +12828,7 @@
         </is>
       </c>
       <c r="E472" s="20" t="n">
-        <v>212</v>
+        <v>239</v>
       </c>
     </row>
     <row r="473" ht="20" customHeight="1">
@@ -12853,7 +12853,7 @@
         </is>
       </c>
       <c r="E473" s="23" t="n">
-        <v>139</v>
+        <v>163</v>
       </c>
     </row>
     <row r="474" ht="20" customHeight="1">
@@ -12878,7 +12878,7 @@
         </is>
       </c>
       <c r="E474" s="20" t="n">
-        <v>110</v>
+        <v>184</v>
       </c>
     </row>
     <row r="475" ht="20" customHeight="1">
@@ -12903,7 +12903,7 @@
         </is>
       </c>
       <c r="E475" s="23" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="476" ht="20" customHeight="1">
@@ -12928,7 +12928,7 @@
         </is>
       </c>
       <c r="E476" s="20" t="n">
-        <v>182</v>
+        <v>120</v>
       </c>
     </row>
     <row r="477" ht="20" customHeight="1">
@@ -12953,7 +12953,7 @@
         </is>
       </c>
       <c r="E477" s="23" t="n">
-        <v>114</v>
+        <v>223</v>
       </c>
     </row>
     <row r="478" ht="20" customHeight="1">
@@ -12978,7 +12978,7 @@
         </is>
       </c>
       <c r="E478" s="20" t="n">
-        <v>151</v>
+        <v>133</v>
       </c>
     </row>
     <row r="479" ht="20" customHeight="1">
@@ -13003,7 +13003,7 @@
         </is>
       </c>
       <c r="E479" s="23" t="n">
-        <v>229</v>
+        <v>161</v>
       </c>
     </row>
     <row r="480" ht="20" customHeight="1">
@@ -13028,7 +13028,7 @@
         </is>
       </c>
       <c r="E480" s="20" t="n">
-        <v>224</v>
+        <v>186</v>
       </c>
     </row>
     <row r="481" ht="20" customHeight="1">
@@ -13053,7 +13053,7 @@
         </is>
       </c>
       <c r="E481" s="23" t="n">
-        <v>159</v>
+        <v>193</v>
       </c>
     </row>
     <row r="482" ht="20" customHeight="1">
@@ -13078,7 +13078,7 @@
         </is>
       </c>
       <c r="E482" s="20" t="n">
-        <v>111</v>
+        <v>137</v>
       </c>
     </row>
     <row r="483" ht="20" customHeight="1">
@@ -13103,7 +13103,7 @@
         </is>
       </c>
       <c r="E483" s="23" t="n">
-        <v>142</v>
+        <v>167</v>
       </c>
     </row>
     <row r="484" ht="20" customHeight="1">
@@ -13128,7 +13128,7 @@
         </is>
       </c>
       <c r="E484" s="20" t="n">
-        <v>157</v>
+        <v>151</v>
       </c>
     </row>
     <row r="485" ht="20" customHeight="1">
@@ -13153,7 +13153,7 @@
         </is>
       </c>
       <c r="E485" s="23" t="n">
-        <v>240</v>
+        <v>215</v>
       </c>
     </row>
     <row r="486" ht="20" customHeight="1">
@@ -13178,7 +13178,7 @@
         </is>
       </c>
       <c r="E486" s="20" t="n">
-        <v>205</v>
+        <v>154</v>
       </c>
     </row>
     <row r="487" ht="20" customHeight="1">
@@ -13203,7 +13203,7 @@
         </is>
       </c>
       <c r="E487" s="23" t="n">
-        <v>240</v>
+        <v>201</v>
       </c>
     </row>
     <row r="488" ht="20" customHeight="1">
@@ -13228,7 +13228,7 @@
         </is>
       </c>
       <c r="E488" s="20" t="n">
-        <v>225</v>
+        <v>233</v>
       </c>
     </row>
     <row r="489" ht="20" customHeight="1">
@@ -13253,7 +13253,7 @@
         </is>
       </c>
       <c r="E489" s="23" t="n">
-        <v>175</v>
+        <v>239</v>
       </c>
     </row>
     <row r="490" ht="20" customHeight="1">
@@ -13278,7 +13278,7 @@
         </is>
       </c>
       <c r="E490" s="20" t="n">
-        <v>177</v>
+        <v>187</v>
       </c>
     </row>
     <row r="491" ht="20" customHeight="1">
@@ -13303,7 +13303,7 @@
         </is>
       </c>
       <c r="E491" s="23" t="n">
-        <v>149</v>
+        <v>200</v>
       </c>
     </row>
     <row r="492" ht="20" customHeight="1">
@@ -13328,7 +13328,7 @@
         </is>
       </c>
       <c r="E492" s="20" t="n">
-        <v>240</v>
+        <v>150</v>
       </c>
     </row>
     <row r="493" ht="20" customHeight="1">
@@ -13353,7 +13353,7 @@
         </is>
       </c>
       <c r="E493" s="23" t="n">
-        <v>216</v>
+        <v>186</v>
       </c>
     </row>
     <row r="494" ht="20" customHeight="1">
@@ -13378,7 +13378,7 @@
         </is>
       </c>
       <c r="E494" s="20" t="n">
-        <v>112</v>
+        <v>129</v>
       </c>
     </row>
     <row r="495" ht="20" customHeight="1">
@@ -13403,7 +13403,7 @@
         </is>
       </c>
       <c r="E495" s="23" t="n">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="496" ht="20" customHeight="1">
@@ -13428,7 +13428,7 @@
         </is>
       </c>
       <c r="E496" s="20" t="n">
-        <v>152</v>
+        <v>215</v>
       </c>
     </row>
     <row r="497" ht="20" customHeight="1">
@@ -13453,7 +13453,7 @@
         </is>
       </c>
       <c r="E497" s="23" t="n">
-        <v>193</v>
+        <v>132</v>
       </c>
     </row>
     <row r="498" ht="20" customHeight="1">
@@ -13478,7 +13478,7 @@
         </is>
       </c>
       <c r="E498" s="20" t="n">
-        <v>165</v>
+        <v>144</v>
       </c>
     </row>
     <row r="499" ht="20" customHeight="1">
@@ -13503,7 +13503,7 @@
         </is>
       </c>
       <c r="E499" s="23" t="n">
-        <v>231</v>
+        <v>119</v>
       </c>
     </row>
     <row r="500" ht="20" customHeight="1">
@@ -13528,7 +13528,7 @@
         </is>
       </c>
       <c r="E500" s="20" t="n">
-        <v>166</v>
+        <v>112</v>
       </c>
     </row>
     <row r="501" ht="20" customHeight="1">
@@ -13553,7 +13553,7 @@
         </is>
       </c>
       <c r="E501" s="23" t="n">
-        <v>144</v>
+        <v>114</v>
       </c>
     </row>
     <row r="502" ht="20" customHeight="1">
@@ -13603,7 +13603,7 @@
         </is>
       </c>
       <c r="E503" s="23" t="n">
-        <v>187</v>
+        <v>141</v>
       </c>
     </row>
     <row r="504" ht="20" customHeight="1">
@@ -13628,7 +13628,7 @@
         </is>
       </c>
       <c r="E504" s="20" t="n">
-        <v>127</v>
+        <v>240</v>
       </c>
     </row>
     <row r="505" ht="20" customHeight="1">
@@ -13653,7 +13653,7 @@
         </is>
       </c>
       <c r="E505" s="23" t="n">
-        <v>204</v>
+        <v>193</v>
       </c>
     </row>
     <row r="506" ht="20" customHeight="1">
@@ -13678,7 +13678,7 @@
         </is>
       </c>
       <c r="E506" s="20" t="n">
-        <v>143</v>
+        <v>207</v>
       </c>
     </row>
     <row r="507" ht="20" customHeight="1">
@@ -13703,7 +13703,7 @@
         </is>
       </c>
       <c r="E507" s="23" t="n">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="508" ht="20" customHeight="1">
@@ -13728,7 +13728,7 @@
         </is>
       </c>
       <c r="E508" s="20" t="n">
-        <v>111</v>
+        <v>177</v>
       </c>
     </row>
     <row r="509" ht="20" customHeight="1">
@@ -13753,7 +13753,7 @@
         </is>
       </c>
       <c r="E509" s="23" t="n">
-        <v>195</v>
+        <v>110</v>
       </c>
     </row>
     <row r="510" ht="20" customHeight="1">
@@ -13778,7 +13778,7 @@
         </is>
       </c>
       <c r="E510" s="20" t="n">
-        <v>191</v>
+        <v>224</v>
       </c>
     </row>
     <row r="511" ht="20" customHeight="1">
@@ -13803,7 +13803,7 @@
         </is>
       </c>
       <c r="E511" s="23" t="n">
-        <v>209</v>
+        <v>147</v>
       </c>
     </row>
     <row r="512" ht="20" customHeight="1">
@@ -13828,7 +13828,7 @@
         </is>
       </c>
       <c r="E512" s="20" t="n">
-        <v>222</v>
+        <v>191</v>
       </c>
     </row>
     <row r="513" ht="20" customHeight="1">
@@ -13853,7 +13853,7 @@
         </is>
       </c>
       <c r="E513" s="23" t="n">
-        <v>182</v>
+        <v>234</v>
       </c>
     </row>
     <row r="514" ht="20" customHeight="1">
@@ -13878,7 +13878,7 @@
         </is>
       </c>
       <c r="E514" s="20" t="n">
-        <v>168</v>
+        <v>230</v>
       </c>
     </row>
     <row r="515" ht="20" customHeight="1">
@@ -13903,7 +13903,7 @@
         </is>
       </c>
       <c r="E515" s="23" t="n">
-        <v>176</v>
+        <v>183</v>
       </c>
     </row>
     <row r="516" ht="20" customHeight="1">
@@ -13953,7 +13953,7 @@
         </is>
       </c>
       <c r="E517" s="23" t="n">
-        <v>229</v>
+        <v>179</v>
       </c>
     </row>
     <row r="518" ht="20" customHeight="1">
@@ -13978,7 +13978,7 @@
         </is>
       </c>
       <c r="E518" s="20" t="n">
-        <v>118</v>
+        <v>137</v>
       </c>
     </row>
     <row r="519" ht="20" customHeight="1">
@@ -14003,7 +14003,7 @@
         </is>
       </c>
       <c r="E519" s="23" t="n">
-        <v>153</v>
+        <v>142</v>
       </c>
     </row>
     <row r="520" ht="20" customHeight="1">
@@ -14028,7 +14028,7 @@
         </is>
       </c>
       <c r="E520" s="20" t="n">
-        <v>209</v>
+        <v>122</v>
       </c>
     </row>
     <row r="521" ht="20" customHeight="1">
@@ -14053,7 +14053,7 @@
         </is>
       </c>
       <c r="E521" s="23" t="n">
-        <v>237</v>
+        <v>110</v>
       </c>
     </row>
     <row r="522" ht="20" customHeight="1">
@@ -14078,7 +14078,7 @@
         </is>
       </c>
       <c r="E522" s="20" t="n">
-        <v>157</v>
+        <v>128</v>
       </c>
     </row>
     <row r="523" ht="20" customHeight="1">
@@ -14103,7 +14103,7 @@
         </is>
       </c>
       <c r="E523" s="23" t="n">
-        <v>180</v>
+        <v>193</v>
       </c>
     </row>
     <row r="524" ht="20" customHeight="1">
@@ -14128,7 +14128,7 @@
         </is>
       </c>
       <c r="E524" s="20" t="n">
-        <v>164</v>
+        <v>119</v>
       </c>
     </row>
     <row r="525" ht="20" customHeight="1">
@@ -14153,7 +14153,7 @@
         </is>
       </c>
       <c r="E525" s="23" t="n">
-        <v>166</v>
+        <v>212</v>
       </c>
     </row>
     <row r="526" ht="20" customHeight="1">
@@ -14178,7 +14178,7 @@
         </is>
       </c>
       <c r="E526" s="20" t="n">
-        <v>235</v>
+        <v>211</v>
       </c>
     </row>
     <row r="527" ht="20" customHeight="1">
@@ -14203,7 +14203,7 @@
         </is>
       </c>
       <c r="E527" s="23" t="n">
-        <v>219</v>
+        <v>125</v>
       </c>
     </row>
     <row r="528" ht="20" customHeight="1">
@@ -14228,7 +14228,7 @@
         </is>
       </c>
       <c r="E528" s="20" t="n">
-        <v>195</v>
+        <v>125</v>
       </c>
     </row>
     <row r="529" ht="20" customHeight="1">
@@ -14253,7 +14253,7 @@
         </is>
       </c>
       <c r="E529" s="23" t="n">
-        <v>217</v>
+        <v>184</v>
       </c>
     </row>
     <row r="530" ht="20" customHeight="1">
@@ -14278,7 +14278,7 @@
         </is>
       </c>
       <c r="E530" s="20" t="n">
-        <v>141</v>
+        <v>135</v>
       </c>
     </row>
     <row r="531" ht="20" customHeight="1">
@@ -14303,7 +14303,7 @@
         </is>
       </c>
       <c r="E531" s="23" t="n">
-        <v>236</v>
+        <v>188</v>
       </c>
     </row>
     <row r="532" ht="20" customHeight="1">
@@ -14328,7 +14328,7 @@
         </is>
       </c>
       <c r="E532" s="20" t="n">
-        <v>222</v>
+        <v>174</v>
       </c>
     </row>
     <row r="533" ht="20" customHeight="1">
@@ -14353,7 +14353,7 @@
         </is>
       </c>
       <c r="E533" s="23" t="n">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="534" ht="20" customHeight="1">
@@ -14378,7 +14378,7 @@
         </is>
       </c>
       <c r="E534" s="20" t="n">
-        <v>197</v>
+        <v>229</v>
       </c>
     </row>
     <row r="535" ht="20" customHeight="1">
@@ -14403,7 +14403,7 @@
         </is>
       </c>
       <c r="E535" s="23" t="n">
-        <v>179</v>
+        <v>189</v>
       </c>
     </row>
     <row r="536" ht="20" customHeight="1">
@@ -14428,7 +14428,7 @@
         </is>
       </c>
       <c r="E536" s="20" t="n">
-        <v>136</v>
+        <v>196</v>
       </c>
     </row>
     <row r="537" ht="20" customHeight="1">
@@ -14453,7 +14453,7 @@
         </is>
       </c>
       <c r="E537" s="23" t="n">
-        <v>167</v>
+        <v>222</v>
       </c>
     </row>
     <row r="538" ht="20" customHeight="1">
@@ -14478,7 +14478,7 @@
         </is>
       </c>
       <c r="E538" s="20" t="n">
-        <v>227</v>
+        <v>178</v>
       </c>
     </row>
     <row r="539" ht="20" customHeight="1">
@@ -14503,7 +14503,7 @@
         </is>
       </c>
       <c r="E539" s="23" t="n">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="540" ht="20" customHeight="1">
@@ -14528,7 +14528,7 @@
         </is>
       </c>
       <c r="E540" s="20" t="n">
-        <v>177</v>
+        <v>185</v>
       </c>
     </row>
     <row r="541" ht="20" customHeight="1">
@@ -14553,7 +14553,7 @@
         </is>
       </c>
       <c r="E541" s="23" t="n">
-        <v>228</v>
+        <v>154</v>
       </c>
     </row>
     <row r="542" ht="20" customHeight="1">
@@ -14578,7 +14578,7 @@
         </is>
       </c>
       <c r="E542" s="20" t="n">
-        <v>162</v>
+        <v>178</v>
       </c>
     </row>
     <row r="543" ht="20" customHeight="1">
@@ -14603,7 +14603,7 @@
         </is>
       </c>
       <c r="E543" s="23" t="n">
-        <v>124</v>
+        <v>233</v>
       </c>
     </row>
     <row r="544" ht="20" customHeight="1">
@@ -14628,7 +14628,7 @@
         </is>
       </c>
       <c r="E544" s="20" t="n">
-        <v>110</v>
+        <v>137</v>
       </c>
     </row>
     <row r="545" ht="20" customHeight="1">
@@ -14653,7 +14653,7 @@
         </is>
       </c>
       <c r="E545" s="23" t="n">
-        <v>144</v>
+        <v>185</v>
       </c>
     </row>
     <row r="546" ht="20" customHeight="1">
@@ -14678,7 +14678,7 @@
         </is>
       </c>
       <c r="E546" s="20" t="n">
-        <v>223</v>
+        <v>136</v>
       </c>
     </row>
     <row r="547" ht="20" customHeight="1">
@@ -14703,7 +14703,7 @@
         </is>
       </c>
       <c r="E547" s="23" t="n">
-        <v>236</v>
+        <v>165</v>
       </c>
     </row>
     <row r="548" ht="20" customHeight="1">
@@ -14728,7 +14728,7 @@
         </is>
       </c>
       <c r="E548" s="20" t="n">
-        <v>237</v>
+        <v>115</v>
       </c>
     </row>
     <row r="549" ht="20" customHeight="1">
@@ -14753,7 +14753,7 @@
         </is>
       </c>
       <c r="E549" s="23" t="n">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="550" ht="20" customHeight="1">
@@ -14778,7 +14778,7 @@
         </is>
       </c>
       <c r="E550" s="20" t="n">
-        <v>227</v>
+        <v>213</v>
       </c>
     </row>
     <row r="551" ht="20" customHeight="1">
@@ -14803,7 +14803,7 @@
         </is>
       </c>
       <c r="E551" s="23" t="n">
-        <v>194</v>
+        <v>130</v>
       </c>
     </row>
     <row r="552" ht="20" customHeight="1">
@@ -14828,7 +14828,7 @@
         </is>
       </c>
       <c r="E552" s="20" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="553" ht="20" customHeight="1">
@@ -14853,7 +14853,7 @@
         </is>
       </c>
       <c r="E553" s="23" t="n">
-        <v>182</v>
+        <v>208</v>
       </c>
     </row>
     <row r="554" ht="20" customHeight="1">
@@ -14878,7 +14878,7 @@
         </is>
       </c>
       <c r="E554" s="20" t="n">
-        <v>218</v>
+        <v>157</v>
       </c>
     </row>
     <row r="555" ht="20" customHeight="1">
@@ -14903,7 +14903,7 @@
         </is>
       </c>
       <c r="E555" s="23" t="n">
-        <v>134</v>
+        <v>206</v>
       </c>
     </row>
     <row r="556" ht="20" customHeight="1">
@@ -14928,7 +14928,7 @@
         </is>
       </c>
       <c r="E556" s="20" t="n">
-        <v>221</v>
+        <v>121</v>
       </c>
     </row>
     <row r="557" ht="20" customHeight="1">
@@ -14953,7 +14953,7 @@
         </is>
       </c>
       <c r="E557" s="23" t="n">
-        <v>220</v>
+        <v>139</v>
       </c>
     </row>
     <row r="558" ht="20" customHeight="1">
@@ -14978,7 +14978,7 @@
         </is>
       </c>
       <c r="E558" s="20" t="n">
-        <v>149</v>
+        <v>174</v>
       </c>
     </row>
     <row r="559" ht="20" customHeight="1">
@@ -15003,7 +15003,7 @@
         </is>
       </c>
       <c r="E559" s="23" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="560" ht="20" customHeight="1">
@@ -15028,7 +15028,7 @@
         </is>
       </c>
       <c r="E560" s="20" t="n">
-        <v>216</v>
+        <v>204</v>
       </c>
     </row>
     <row r="561" ht="20" customHeight="1">
@@ -15053,7 +15053,7 @@
         </is>
       </c>
       <c r="E561" s="23" t="n">
-        <v>192</v>
+        <v>224</v>
       </c>
     </row>
     <row r="562" ht="20" customHeight="1">
@@ -15078,7 +15078,7 @@
         </is>
       </c>
       <c r="E562" s="20" t="n">
-        <v>120</v>
+        <v>155</v>
       </c>
     </row>
     <row r="563" ht="20" customHeight="1">
@@ -15103,7 +15103,7 @@
         </is>
       </c>
       <c r="E563" s="23" t="n">
-        <v>203</v>
+        <v>128</v>
       </c>
     </row>
     <row r="564" ht="20" customHeight="1">
@@ -15128,7 +15128,7 @@
         </is>
       </c>
       <c r="E564" s="20" t="n">
-        <v>166</v>
+        <v>161</v>
       </c>
     </row>
     <row r="565" ht="20" customHeight="1">
@@ -15153,7 +15153,7 @@
         </is>
       </c>
       <c r="E565" s="23" t="n">
-        <v>121</v>
+        <v>227</v>
       </c>
     </row>
     <row r="566" ht="20" customHeight="1">
@@ -15178,7 +15178,7 @@
         </is>
       </c>
       <c r="E566" s="20" t="n">
-        <v>170</v>
+        <v>184</v>
       </c>
     </row>
     <row r="567" ht="20" customHeight="1">
@@ -15203,7 +15203,7 @@
         </is>
       </c>
       <c r="E567" s="23" t="n">
-        <v>201</v>
+        <v>238</v>
       </c>
     </row>
     <row r="568" ht="20" customHeight="1">
@@ -15228,7 +15228,7 @@
         </is>
       </c>
       <c r="E568" s="20" t="n">
-        <v>119</v>
+        <v>132</v>
       </c>
     </row>
     <row r="569" ht="20" customHeight="1">
@@ -15253,7 +15253,7 @@
         </is>
       </c>
       <c r="E569" s="23" t="n">
-        <v>153</v>
+        <v>202</v>
       </c>
     </row>
     <row r="570" ht="20" customHeight="1">
@@ -15278,7 +15278,7 @@
         </is>
       </c>
       <c r="E570" s="20" t="n">
-        <v>236</v>
+        <v>158</v>
       </c>
     </row>
     <row r="571" ht="20" customHeight="1">
@@ -15303,7 +15303,7 @@
         </is>
       </c>
       <c r="E571" s="23" t="n">
-        <v>221</v>
+        <v>174</v>
       </c>
     </row>
     <row r="572" ht="20" customHeight="1">
@@ -15328,7 +15328,7 @@
         </is>
       </c>
       <c r="E572" s="20" t="n">
-        <v>224</v>
+        <v>237</v>
       </c>
     </row>
     <row r="573" ht="20" customHeight="1">
@@ -15353,7 +15353,7 @@
         </is>
       </c>
       <c r="E573" s="23" t="n">
-        <v>226</v>
+        <v>164</v>
       </c>
     </row>
     <row r="574" ht="20" customHeight="1">
@@ -15378,7 +15378,7 @@
         </is>
       </c>
       <c r="E574" s="20" t="n">
-        <v>129</v>
+        <v>164</v>
       </c>
     </row>
     <row r="575" ht="20" customHeight="1">
@@ -15403,7 +15403,7 @@
         </is>
       </c>
       <c r="E575" s="23" t="n">
-        <v>239</v>
+        <v>230</v>
       </c>
     </row>
     <row r="576" ht="20" customHeight="1">
@@ -15428,7 +15428,7 @@
         </is>
       </c>
       <c r="E576" s="20" t="n">
-        <v>123</v>
+        <v>147</v>
       </c>
     </row>
     <row r="577" ht="20" customHeight="1">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="E577" s="23" t="n">
-        <v>186</v>
+        <v>199</v>
       </c>
     </row>
     <row r="578" ht="20" customHeight="1">
@@ -15478,7 +15478,7 @@
         </is>
       </c>
       <c r="E578" s="20" t="n">
-        <v>145</v>
+        <v>200</v>
       </c>
     </row>
     <row r="579" ht="20" customHeight="1">
@@ -15503,7 +15503,7 @@
         </is>
       </c>
       <c r="E579" s="23" t="n">
-        <v>229</v>
+        <v>144</v>
       </c>
     </row>
     <row r="580" ht="20" customHeight="1">
@@ -15528,7 +15528,7 @@
         </is>
       </c>
       <c r="E580" s="20" t="n">
-        <v>217</v>
+        <v>143</v>
       </c>
     </row>
     <row r="581" ht="20" customHeight="1">
@@ -15578,7 +15578,7 @@
         </is>
       </c>
       <c r="E582" s="20" t="n">
-        <v>134</v>
+        <v>110</v>
       </c>
     </row>
     <row r="583" ht="20" customHeight="1">
@@ -15603,7 +15603,7 @@
         </is>
       </c>
       <c r="E583" s="23" t="n">
-        <v>156</v>
+        <v>232</v>
       </c>
     </row>
     <row r="584" ht="20" customHeight="1">
@@ -15628,7 +15628,7 @@
         </is>
       </c>
       <c r="E584" s="20" t="n">
-        <v>192</v>
+        <v>200</v>
       </c>
     </row>
     <row r="585" ht="20" customHeight="1">
@@ -15653,7 +15653,7 @@
         </is>
       </c>
       <c r="E585" s="23" t="n">
-        <v>147</v>
+        <v>194</v>
       </c>
     </row>
     <row r="586" ht="20" customHeight="1">
@@ -15678,7 +15678,7 @@
         </is>
       </c>
       <c r="E586" s="20" t="n">
-        <v>200</v>
+        <v>238</v>
       </c>
     </row>
     <row r="587" ht="20" customHeight="1">
@@ -15703,7 +15703,7 @@
         </is>
       </c>
       <c r="E587" s="23" t="n">
-        <v>136</v>
+        <v>234</v>
       </c>
     </row>
     <row r="588" ht="20" customHeight="1">
@@ -15728,7 +15728,7 @@
         </is>
       </c>
       <c r="E588" s="20" t="n">
-        <v>142</v>
+        <v>191</v>
       </c>
     </row>
     <row r="589" ht="20" customHeight="1">
@@ -15753,7 +15753,7 @@
         </is>
       </c>
       <c r="E589" s="23" t="n">
-        <v>203</v>
+        <v>116</v>
       </c>
     </row>
     <row r="590" ht="20" customHeight="1">
@@ -15778,7 +15778,7 @@
         </is>
       </c>
       <c r="E590" s="20" t="n">
-        <v>211</v>
+        <v>156</v>
       </c>
     </row>
     <row r="591" ht="20" customHeight="1">
@@ -15803,7 +15803,7 @@
         </is>
       </c>
       <c r="E591" s="23" t="n">
-        <v>217</v>
+        <v>185</v>
       </c>
     </row>
     <row r="592" ht="20" customHeight="1">
@@ -15828,7 +15828,7 @@
         </is>
       </c>
       <c r="E592" s="20" t="n">
-        <v>172</v>
+        <v>160</v>
       </c>
     </row>
     <row r="593" ht="20" customHeight="1">
@@ -15853,7 +15853,7 @@
         </is>
       </c>
       <c r="E593" s="23" t="n">
-        <v>160</v>
+        <v>148</v>
       </c>
     </row>
     <row r="594" ht="20" customHeight="1">
@@ -15878,7 +15878,7 @@
         </is>
       </c>
       <c r="E594" s="20" t="n">
-        <v>172</v>
+        <v>122</v>
       </c>
     </row>
     <row r="595" ht="20" customHeight="1">
@@ -15903,7 +15903,7 @@
         </is>
       </c>
       <c r="E595" s="23" t="n">
-        <v>154</v>
+        <v>221</v>
       </c>
     </row>
     <row r="596" ht="20" customHeight="1">
@@ -15928,7 +15928,7 @@
         </is>
       </c>
       <c r="E596" s="20" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="597" ht="20" customHeight="1">
@@ -15953,7 +15953,7 @@
         </is>
       </c>
       <c r="E597" s="23" t="n">
-        <v>219</v>
+        <v>229</v>
       </c>
     </row>
     <row r="598" ht="20" customHeight="1">
@@ -15978,7 +15978,7 @@
         </is>
       </c>
       <c r="E598" s="20" t="n">
-        <v>167</v>
+        <v>149</v>
       </c>
     </row>
     <row r="599" ht="20" customHeight="1">
@@ -16003,7 +16003,7 @@
         </is>
       </c>
       <c r="E599" s="23" t="n">
-        <v>163</v>
+        <v>123</v>
       </c>
     </row>
     <row r="600" ht="20" customHeight="1">
@@ -16028,7 +16028,7 @@
         </is>
       </c>
       <c r="E600" s="20" t="n">
-        <v>226</v>
+        <v>183</v>
       </c>
     </row>
     <row r="601" ht="20" customHeight="1">
@@ -16053,7 +16053,7 @@
         </is>
       </c>
       <c r="E601" s="23" t="n">
-        <v>189</v>
+        <v>132</v>
       </c>
     </row>
     <row r="602" ht="20" customHeight="1">
@@ -16078,7 +16078,7 @@
         </is>
       </c>
       <c r="E602" s="20" t="n">
-        <v>183</v>
+        <v>156</v>
       </c>
     </row>
     <row r="603" ht="20" customHeight="1">
@@ -16103,7 +16103,7 @@
         </is>
       </c>
       <c r="E603" s="23" t="n">
-        <v>203</v>
+        <v>222</v>
       </c>
     </row>
     <row r="604" ht="20" customHeight="1">
@@ -16128,7 +16128,7 @@
         </is>
       </c>
       <c r="E604" s="20" t="n">
-        <v>146</v>
+        <v>218</v>
       </c>
     </row>
     <row r="605" ht="20" customHeight="1">
@@ -16153,7 +16153,7 @@
         </is>
       </c>
       <c r="E605" s="23" t="n">
-        <v>210</v>
+        <v>144</v>
       </c>
     </row>
     <row r="606" ht="20" customHeight="1">
@@ -16178,7 +16178,7 @@
         </is>
       </c>
       <c r="E606" s="20" t="n">
-        <v>186</v>
+        <v>233</v>
       </c>
     </row>
     <row r="607" ht="20" customHeight="1">
@@ -16203,7 +16203,7 @@
         </is>
       </c>
       <c r="E607" s="23" t="n">
-        <v>169</v>
+        <v>182</v>
       </c>
     </row>
     <row r="608" ht="20" customHeight="1">
@@ -16228,7 +16228,7 @@
         </is>
       </c>
       <c r="E608" s="20" t="n">
-        <v>174</v>
+        <v>225</v>
       </c>
     </row>
     <row r="609" ht="20" customHeight="1">
@@ -16253,7 +16253,7 @@
         </is>
       </c>
       <c r="E609" s="23" t="n">
-        <v>238</v>
+        <v>173</v>
       </c>
     </row>
     <row r="610" ht="20" customHeight="1">
@@ -16278,7 +16278,7 @@
         </is>
       </c>
       <c r="E610" s="20" t="n">
-        <v>173</v>
+        <v>128</v>
       </c>
     </row>
     <row r="611" ht="20" customHeight="1">
@@ -16303,7 +16303,7 @@
         </is>
       </c>
       <c r="E611" s="23" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="612" ht="20" customHeight="1">
@@ -16328,7 +16328,7 @@
         </is>
       </c>
       <c r="E612" s="20" t="n">
-        <v>236</v>
+        <v>141</v>
       </c>
     </row>
     <row r="613" ht="20" customHeight="1">
@@ -16353,7 +16353,7 @@
         </is>
       </c>
       <c r="E613" s="23" t="n">
-        <v>236</v>
+        <v>224</v>
       </c>
     </row>
     <row r="614" ht="20" customHeight="1">
@@ -16378,7 +16378,7 @@
         </is>
       </c>
       <c r="E614" s="20" t="n">
-        <v>234</v>
+        <v>123</v>
       </c>
     </row>
     <row r="615" ht="20" customHeight="1">
@@ -16403,7 +16403,7 @@
         </is>
       </c>
       <c r="E615" s="23" t="n">
-        <v>159</v>
+        <v>228</v>
       </c>
     </row>
     <row r="616" ht="20" customHeight="1">
@@ -16428,7 +16428,7 @@
         </is>
       </c>
       <c r="E616" s="20" t="n">
-        <v>173</v>
+        <v>125</v>
       </c>
     </row>
     <row r="617" ht="20" customHeight="1">
@@ -16453,7 +16453,7 @@
         </is>
       </c>
       <c r="E617" s="23" t="n">
-        <v>219</v>
+        <v>239</v>
       </c>
     </row>
     <row r="618" ht="20" customHeight="1">
@@ -16478,7 +16478,7 @@
         </is>
       </c>
       <c r="E618" s="20" t="n">
-        <v>202</v>
+        <v>131</v>
       </c>
     </row>
     <row r="619" ht="20" customHeight="1">
@@ -16503,7 +16503,7 @@
         </is>
       </c>
       <c r="E619" s="23" t="n">
-        <v>157</v>
+        <v>180</v>
       </c>
     </row>
     <row r="620" ht="20" customHeight="1">
@@ -16528,7 +16528,7 @@
         </is>
       </c>
       <c r="E620" s="20" t="n">
-        <v>217</v>
+        <v>240</v>
       </c>
     </row>
     <row r="621" ht="20" customHeight="1">
@@ -16553,7 +16553,7 @@
         </is>
       </c>
       <c r="E621" s="23" t="n">
-        <v>127</v>
+        <v>228</v>
       </c>
     </row>
     <row r="622" ht="20" customHeight="1">
@@ -16578,7 +16578,7 @@
         </is>
       </c>
       <c r="E622" s="20" t="n">
-        <v>119</v>
+        <v>148</v>
       </c>
     </row>
     <row r="623" ht="20" customHeight="1">
@@ -16603,7 +16603,7 @@
         </is>
       </c>
       <c r="E623" s="23" t="n">
-        <v>128</v>
+        <v>157</v>
       </c>
     </row>
     <row r="624" ht="20" customHeight="1">
@@ -16628,7 +16628,7 @@
         </is>
       </c>
       <c r="E624" s="20" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="625" ht="20" customHeight="1">
@@ -16653,7 +16653,7 @@
         </is>
       </c>
       <c r="E625" s="23" t="n">
-        <v>136</v>
+        <v>220</v>
       </c>
     </row>
     <row r="626" ht="20" customHeight="1">
@@ -16678,7 +16678,7 @@
         </is>
       </c>
       <c r="E626" s="20" t="n">
-        <v>141</v>
+        <v>183</v>
       </c>
     </row>
     <row r="627" ht="20" customHeight="1">
@@ -16703,7 +16703,7 @@
         </is>
       </c>
       <c r="E627" s="23" t="n">
-        <v>217</v>
+        <v>189</v>
       </c>
     </row>
     <row r="628" ht="20" customHeight="1">
@@ -16728,7 +16728,7 @@
         </is>
       </c>
       <c r="E628" s="20" t="n">
-        <v>172</v>
+        <v>240</v>
       </c>
     </row>
     <row r="629" ht="20" customHeight="1">
@@ -16753,7 +16753,7 @@
         </is>
       </c>
       <c r="E629" s="23" t="n">
-        <v>205</v>
+        <v>217</v>
       </c>
     </row>
     <row r="630" ht="20" customHeight="1">
@@ -16778,7 +16778,7 @@
         </is>
       </c>
       <c r="E630" s="20" t="n">
-        <v>139</v>
+        <v>215</v>
       </c>
     </row>
     <row r="631" ht="20" customHeight="1">
@@ -16803,7 +16803,7 @@
         </is>
       </c>
       <c r="E631" s="23" t="n">
-        <v>224</v>
+        <v>175</v>
       </c>
     </row>
     <row r="632" ht="20" customHeight="1">
@@ -16828,7 +16828,7 @@
         </is>
       </c>
       <c r="E632" s="20" t="n">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="633" ht="20" customHeight="1">
@@ -16853,7 +16853,7 @@
         </is>
       </c>
       <c r="E633" s="23" t="n">
-        <v>191</v>
+        <v>172</v>
       </c>
     </row>
     <row r="634" ht="20" customHeight="1">
@@ -16878,7 +16878,7 @@
         </is>
       </c>
       <c r="E634" s="20" t="n">
-        <v>212</v>
+        <v>221</v>
       </c>
     </row>
     <row r="635" ht="20" customHeight="1">
@@ -16903,7 +16903,7 @@
         </is>
       </c>
       <c r="E635" s="23" t="n">
-        <v>186</v>
+        <v>198</v>
       </c>
     </row>
     <row r="636" ht="20" customHeight="1">
@@ -16928,7 +16928,7 @@
         </is>
       </c>
       <c r="E636" s="20" t="n">
-        <v>207</v>
+        <v>113</v>
       </c>
     </row>
     <row r="637" ht="20" customHeight="1">
@@ -16953,7 +16953,7 @@
         </is>
       </c>
       <c r="E637" s="23" t="n">
-        <v>117</v>
+        <v>219</v>
       </c>
     </row>
     <row r="638" ht="20" customHeight="1">
@@ -16978,7 +16978,7 @@
         </is>
       </c>
       <c r="E638" s="20" t="n">
-        <v>115</v>
+        <v>147</v>
       </c>
     </row>
     <row r="639" ht="20" customHeight="1">
@@ -17003,7 +17003,7 @@
         </is>
       </c>
       <c r="E639" s="23" t="n">
-        <v>141</v>
+        <v>220</v>
       </c>
     </row>
     <row r="640" ht="20" customHeight="1">
@@ -17028,7 +17028,7 @@
         </is>
       </c>
       <c r="E640" s="20" t="n">
-        <v>202</v>
+        <v>175</v>
       </c>
     </row>
     <row r="641" ht="20" customHeight="1">
@@ -17053,7 +17053,7 @@
         </is>
       </c>
       <c r="E641" s="23" t="n">
-        <v>150</v>
+        <v>124</v>
       </c>
     </row>
     <row r="642" ht="20" customHeight="1">
@@ -17078,7 +17078,7 @@
         </is>
       </c>
       <c r="E642" s="20" t="n">
-        <v>230</v>
+        <v>221</v>
       </c>
     </row>
     <row r="643" ht="20" customHeight="1">
@@ -17103,7 +17103,7 @@
         </is>
       </c>
       <c r="E643" s="23" t="n">
-        <v>145</v>
+        <v>169</v>
       </c>
     </row>
     <row r="644" ht="20" customHeight="1">
@@ -17128,7 +17128,7 @@
         </is>
       </c>
       <c r="E644" s="20" t="n">
-        <v>144</v>
+        <v>158</v>
       </c>
     </row>
     <row r="645" ht="20" customHeight="1">
@@ -17153,7 +17153,7 @@
         </is>
       </c>
       <c r="E645" s="23" t="n">
-        <v>231</v>
+        <v>133</v>
       </c>
     </row>
     <row r="646" ht="20" customHeight="1">
@@ -17178,7 +17178,7 @@
         </is>
       </c>
       <c r="E646" s="20" t="n">
-        <v>171</v>
+        <v>154</v>
       </c>
     </row>
     <row r="647" ht="20" customHeight="1">
@@ -17203,7 +17203,7 @@
         </is>
       </c>
       <c r="E647" s="23" t="n">
-        <v>116</v>
+        <v>219</v>
       </c>
     </row>
     <row r="648" ht="20" customHeight="1">
@@ -17228,7 +17228,7 @@
         </is>
       </c>
       <c r="E648" s="20" t="n">
-        <v>224</v>
+        <v>234</v>
       </c>
     </row>
     <row r="649" ht="20" customHeight="1">
@@ -17253,7 +17253,7 @@
         </is>
       </c>
       <c r="E649" s="23" t="n">
-        <v>214</v>
+        <v>173</v>
       </c>
     </row>
     <row r="650" ht="20" customHeight="1">
@@ -17278,7 +17278,7 @@
         </is>
       </c>
       <c r="E650" s="20" t="n">
-        <v>233</v>
+        <v>192</v>
       </c>
     </row>
     <row r="651" ht="20" customHeight="1">
@@ -17303,7 +17303,7 @@
         </is>
       </c>
       <c r="E651" s="23" t="n">
-        <v>138</v>
+        <v>127</v>
       </c>
     </row>
     <row r="652" ht="20" customHeight="1">
@@ -17328,7 +17328,7 @@
         </is>
       </c>
       <c r="E652" s="20" t="n">
-        <v>125</v>
+        <v>225</v>
       </c>
     </row>
     <row r="653" ht="20" customHeight="1">
@@ -17353,7 +17353,7 @@
         </is>
       </c>
       <c r="E653" s="23" t="n">
-        <v>147</v>
+        <v>231</v>
       </c>
     </row>
     <row r="654" ht="20" customHeight="1">
@@ -17378,7 +17378,7 @@
         </is>
       </c>
       <c r="E654" s="20" t="n">
-        <v>238</v>
+        <v>194</v>
       </c>
     </row>
     <row r="655" ht="20" customHeight="1">
@@ -17403,7 +17403,7 @@
         </is>
       </c>
       <c r="E655" s="23" t="n">
-        <v>157</v>
+        <v>174</v>
       </c>
     </row>
     <row r="656" ht="20" customHeight="1">
@@ -17428,7 +17428,7 @@
         </is>
       </c>
       <c r="E656" s="20" t="n">
-        <v>156</v>
+        <v>189</v>
       </c>
     </row>
     <row r="657" ht="20" customHeight="1">
@@ -17453,7 +17453,7 @@
         </is>
       </c>
       <c r="E657" s="23" t="n">
-        <v>225</v>
+        <v>194</v>
       </c>
     </row>
     <row r="658" ht="20" customHeight="1">
@@ -17478,7 +17478,7 @@
         </is>
       </c>
       <c r="E658" s="20" t="n">
-        <v>119</v>
+        <v>207</v>
       </c>
     </row>
     <row r="659" ht="20" customHeight="1">
@@ -17503,7 +17503,7 @@
         </is>
       </c>
       <c r="E659" s="23" t="n">
-        <v>137</v>
+        <v>178</v>
       </c>
     </row>
     <row r="660" ht="20" customHeight="1">
@@ -17528,7 +17528,7 @@
         </is>
       </c>
       <c r="E660" s="20" t="n">
-        <v>153</v>
+        <v>176</v>
       </c>
     </row>
     <row r="661" ht="20" customHeight="1">
@@ -17553,7 +17553,7 @@
         </is>
       </c>
       <c r="E661" s="23" t="n">
-        <v>236</v>
+        <v>147</v>
       </c>
     </row>
     <row r="662" ht="20" customHeight="1">
@@ -17578,7 +17578,7 @@
         </is>
       </c>
       <c r="E662" s="20" t="n">
-        <v>140</v>
+        <v>152</v>
       </c>
     </row>
     <row r="663" ht="20" customHeight="1">
@@ -17603,7 +17603,7 @@
         </is>
       </c>
       <c r="E663" s="23" t="n">
-        <v>137</v>
+        <v>176</v>
       </c>
     </row>
     <row r="664" ht="20" customHeight="1">
@@ -17628,7 +17628,7 @@
         </is>
       </c>
       <c r="E664" s="20" t="n">
-        <v>158</v>
+        <v>123</v>
       </c>
     </row>
     <row r="665" ht="20" customHeight="1">
@@ -17653,7 +17653,7 @@
         </is>
       </c>
       <c r="E665" s="23" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="666" ht="20" customHeight="1">
@@ -17678,7 +17678,7 @@
         </is>
       </c>
       <c r="E666" s="20" t="n">
-        <v>170</v>
+        <v>205</v>
       </c>
     </row>
     <row r="667" ht="20" customHeight="1">
@@ -17703,7 +17703,7 @@
         </is>
       </c>
       <c r="E667" s="23" t="n">
-        <v>111</v>
+        <v>144</v>
       </c>
     </row>
     <row r="668" ht="20" customHeight="1">
@@ -17728,7 +17728,7 @@
         </is>
       </c>
       <c r="E668" s="20" t="n">
-        <v>187</v>
+        <v>228</v>
       </c>
     </row>
     <row r="669" ht="20" customHeight="1">
@@ -17753,7 +17753,7 @@
         </is>
       </c>
       <c r="E669" s="23" t="n">
-        <v>187</v>
+        <v>128</v>
       </c>
     </row>
     <row r="670" ht="20" customHeight="1">
@@ -17778,7 +17778,7 @@
         </is>
       </c>
       <c r="E670" s="20" t="n">
-        <v>202</v>
+        <v>218</v>
       </c>
     </row>
     <row r="671" ht="20" customHeight="1">
@@ -17803,7 +17803,7 @@
         </is>
       </c>
       <c r="E671" s="23" t="n">
-        <v>173</v>
+        <v>126</v>
       </c>
     </row>
     <row r="672" ht="20" customHeight="1">
@@ -17828,7 +17828,7 @@
         </is>
       </c>
       <c r="E672" s="20" t="n">
-        <v>232</v>
+        <v>185</v>
       </c>
     </row>
     <row r="673" ht="20" customHeight="1">
@@ -17853,7 +17853,7 @@
         </is>
       </c>
       <c r="E673" s="23" t="n">
-        <v>225</v>
+        <v>151</v>
       </c>
     </row>
     <row r="674" ht="20" customHeight="1">
@@ -17878,7 +17878,7 @@
         </is>
       </c>
       <c r="E674" s="20" t="n">
-        <v>201</v>
+        <v>239</v>
       </c>
     </row>
     <row r="675" ht="20" customHeight="1">
@@ -17903,7 +17903,7 @@
         </is>
       </c>
       <c r="E675" s="23" t="n">
-        <v>130</v>
+        <v>210</v>
       </c>
     </row>
     <row r="676" ht="20" customHeight="1">
@@ -17928,7 +17928,7 @@
         </is>
       </c>
       <c r="E676" s="20" t="n">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
     <row r="677" ht="20" customHeight="1">
@@ -17953,7 +17953,7 @@
         </is>
       </c>
       <c r="E677" s="23" t="n">
-        <v>174</v>
+        <v>142</v>
       </c>
     </row>
     <row r="678" ht="20" customHeight="1">
@@ -17978,7 +17978,7 @@
         </is>
       </c>
       <c r="E678" s="20" t="n">
-        <v>183</v>
+        <v>162</v>
       </c>
     </row>
     <row r="679" ht="20" customHeight="1">
@@ -18003,7 +18003,7 @@
         </is>
       </c>
       <c r="E679" s="23" t="n">
-        <v>187</v>
+        <v>236</v>
       </c>
     </row>
     <row r="680" ht="20" customHeight="1">
@@ -18028,7 +18028,7 @@
         </is>
       </c>
       <c r="E680" s="20" t="n">
-        <v>213</v>
+        <v>168</v>
       </c>
     </row>
     <row r="681" ht="20" customHeight="1">
@@ -18053,7 +18053,7 @@
         </is>
       </c>
       <c r="E681" s="23" t="n">
-        <v>120</v>
+        <v>208</v>
       </c>
     </row>
     <row r="682" ht="20" customHeight="1">
@@ -18078,7 +18078,7 @@
         </is>
       </c>
       <c r="E682" s="20" t="n">
-        <v>238</v>
+        <v>192</v>
       </c>
     </row>
     <row r="683" ht="20" customHeight="1">
@@ -18103,7 +18103,7 @@
         </is>
       </c>
       <c r="E683" s="23" t="n">
-        <v>162</v>
+        <v>135</v>
       </c>
     </row>
     <row r="684" ht="20" customHeight="1">
@@ -18128,7 +18128,7 @@
         </is>
       </c>
       <c r="E684" s="20" t="n">
-        <v>220</v>
+        <v>115</v>
       </c>
     </row>
     <row r="685" ht="20" customHeight="1">
@@ -18178,7 +18178,7 @@
         </is>
       </c>
       <c r="E686" s="20" t="n">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="687" ht="20" customHeight="1">
@@ -18203,7 +18203,7 @@
         </is>
       </c>
       <c r="E687" s="23" t="n">
-        <v>128</v>
+        <v>182</v>
       </c>
     </row>
     <row r="688" ht="20" customHeight="1">
@@ -18228,7 +18228,7 @@
         </is>
       </c>
       <c r="E688" s="20" t="n">
-        <v>186</v>
+        <v>210</v>
       </c>
     </row>
     <row r="689" ht="20" customHeight="1">
@@ -18253,7 +18253,7 @@
         </is>
       </c>
       <c r="E689" s="23" t="n">
-        <v>222</v>
+        <v>203</v>
       </c>
     </row>
     <row r="690" ht="20" customHeight="1">
@@ -18278,7 +18278,7 @@
         </is>
       </c>
       <c r="E690" s="20" t="n">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="691" ht="20" customHeight="1">
@@ -18303,7 +18303,7 @@
         </is>
       </c>
       <c r="E691" s="23" t="n">
-        <v>218</v>
+        <v>149</v>
       </c>
     </row>
     <row r="692" ht="20" customHeight="1">
@@ -18328,7 +18328,7 @@
         </is>
       </c>
       <c r="E692" s="20" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="693" ht="20" customHeight="1">
@@ -18353,7 +18353,7 @@
         </is>
       </c>
       <c r="E693" s="23" t="n">
-        <v>220</v>
+        <v>228</v>
       </c>
     </row>
     <row r="694" ht="20" customHeight="1">
@@ -18378,7 +18378,7 @@
         </is>
       </c>
       <c r="E694" s="20" t="n">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="695" ht="20" customHeight="1">
@@ -18403,7 +18403,7 @@
         </is>
       </c>
       <c r="E695" s="23" t="n">
-        <v>231</v>
+        <v>237</v>
       </c>
     </row>
     <row r="696" ht="20" customHeight="1">
@@ -18428,7 +18428,7 @@
         </is>
       </c>
       <c r="E696" s="20" t="n">
-        <v>198</v>
+        <v>212</v>
       </c>
     </row>
     <row r="697" ht="20" customHeight="1">
@@ -18453,7 +18453,7 @@
         </is>
       </c>
       <c r="E697" s="23" t="n">
-        <v>176</v>
+        <v>152</v>
       </c>
     </row>
     <row r="698" ht="20" customHeight="1">
@@ -18478,7 +18478,7 @@
         </is>
       </c>
       <c r="E698" s="20" t="n">
-        <v>215</v>
+        <v>200</v>
       </c>
     </row>
     <row r="699" ht="20" customHeight="1">
@@ -18503,7 +18503,7 @@
         </is>
       </c>
       <c r="E699" s="23" t="n">
-        <v>157</v>
+        <v>228</v>
       </c>
     </row>
     <row r="700" ht="20" customHeight="1">
@@ -18528,7 +18528,7 @@
         </is>
       </c>
       <c r="E700" s="20" t="n">
-        <v>179</v>
+        <v>204</v>
       </c>
     </row>
     <row r="701" ht="20" customHeight="1">
@@ -18553,7 +18553,7 @@
         </is>
       </c>
       <c r="E701" s="23" t="n">
-        <v>233</v>
+        <v>221</v>
       </c>
     </row>
     <row r="702" ht="20" customHeight="1">
@@ -18578,7 +18578,7 @@
         </is>
       </c>
       <c r="E702" s="20" t="n">
-        <v>138</v>
+        <v>216</v>
       </c>
     </row>
     <row r="703" ht="20" customHeight="1">
@@ -18603,7 +18603,7 @@
         </is>
       </c>
       <c r="E703" s="23" t="n">
-        <v>222</v>
+        <v>137</v>
       </c>
     </row>
     <row r="704" ht="20" customHeight="1">
@@ -18628,7 +18628,7 @@
         </is>
       </c>
       <c r="E704" s="20" t="n">
-        <v>192</v>
+        <v>114</v>
       </c>
     </row>
     <row r="705" ht="20" customHeight="1">
@@ -18653,7 +18653,7 @@
         </is>
       </c>
       <c r="E705" s="23" t="n">
-        <v>209</v>
+        <v>145</v>
       </c>
     </row>
     <row r="706" ht="20" customHeight="1">
@@ -18678,7 +18678,7 @@
         </is>
       </c>
       <c r="E706" s="20" t="n">
-        <v>188</v>
+        <v>172</v>
       </c>
     </row>
     <row r="707" ht="20" customHeight="1">
@@ -18703,7 +18703,7 @@
         </is>
       </c>
       <c r="E707" s="23" t="n">
-        <v>125</v>
+        <v>142</v>
       </c>
     </row>
     <row r="708" ht="20" customHeight="1">
@@ -18728,7 +18728,7 @@
         </is>
       </c>
       <c r="E708" s="20" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="709" ht="20" customHeight="1">
@@ -18753,7 +18753,7 @@
         </is>
       </c>
       <c r="E709" s="23" t="n">
-        <v>189</v>
+        <v>119</v>
       </c>
     </row>
     <row r="710" ht="20" customHeight="1">
@@ -18778,7 +18778,7 @@
         </is>
       </c>
       <c r="E710" s="20" t="n">
-        <v>137</v>
+        <v>145</v>
       </c>
     </row>
     <row r="711" ht="20" customHeight="1">
@@ -18803,7 +18803,7 @@
         </is>
       </c>
       <c r="E711" s="23" t="n">
-        <v>224</v>
+        <v>217</v>
       </c>
     </row>
     <row r="712" ht="20" customHeight="1">
@@ -18828,7 +18828,7 @@
         </is>
       </c>
       <c r="E712" s="20" t="n">
-        <v>110</v>
+        <v>237</v>
       </c>
     </row>
     <row r="713" ht="20" customHeight="1">
@@ -18853,7 +18853,7 @@
         </is>
       </c>
       <c r="E713" s="23" t="n">
-        <v>200</v>
+        <v>213</v>
       </c>
     </row>
     <row r="714" ht="20" customHeight="1">
@@ -18878,7 +18878,7 @@
         </is>
       </c>
       <c r="E714" s="20" t="n">
-        <v>147</v>
+        <v>111</v>
       </c>
     </row>
     <row r="715" ht="20" customHeight="1">
@@ -18903,7 +18903,7 @@
         </is>
       </c>
       <c r="E715" s="23" t="n">
-        <v>126</v>
+        <v>163</v>
       </c>
     </row>
     <row r="716" ht="20" customHeight="1">
@@ -18928,7 +18928,7 @@
         </is>
       </c>
       <c r="E716" s="20" t="n">
-        <v>169</v>
+        <v>220</v>
       </c>
     </row>
     <row r="717" ht="20" customHeight="1">
@@ -18953,7 +18953,7 @@
         </is>
       </c>
       <c r="E717" s="23" t="n">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="718" ht="20" customHeight="1">
@@ -18978,7 +18978,7 @@
         </is>
       </c>
       <c r="E718" s="20" t="n">
-        <v>214</v>
+        <v>111</v>
       </c>
     </row>
     <row r="719" ht="20" customHeight="1">
@@ -19003,7 +19003,7 @@
         </is>
       </c>
       <c r="E719" s="23" t="n">
-        <v>200</v>
+        <v>204</v>
       </c>
     </row>
     <row r="720" ht="20" customHeight="1">
@@ -19028,7 +19028,7 @@
         </is>
       </c>
       <c r="E720" s="20" t="n">
-        <v>142</v>
+        <v>160</v>
       </c>
     </row>
     <row r="721" ht="20" customHeight="1">
@@ -19053,7 +19053,7 @@
         </is>
       </c>
       <c r="E721" s="23" t="n">
-        <v>211</v>
+        <v>227</v>
       </c>
     </row>
     <row r="722" ht="20" customHeight="1">
@@ -19078,7 +19078,7 @@
         </is>
       </c>
       <c r="E722" s="20" t="n">
-        <v>165</v>
+        <v>236</v>
       </c>
     </row>
     <row r="723" ht="20" customHeight="1">
@@ -19103,7 +19103,7 @@
         </is>
       </c>
       <c r="E723" s="23" t="n">
-        <v>122</v>
+        <v>215</v>
       </c>
     </row>
     <row r="724" ht="20" customHeight="1">
@@ -19128,7 +19128,7 @@
         </is>
       </c>
       <c r="E724" s="20" t="n">
-        <v>163</v>
+        <v>184</v>
       </c>
     </row>
     <row r="725" ht="20" customHeight="1">
@@ -19153,7 +19153,7 @@
         </is>
       </c>
       <c r="E725" s="23" t="n">
-        <v>111</v>
+        <v>175</v>
       </c>
     </row>
     <row r="726" ht="20" customHeight="1">
@@ -19178,7 +19178,7 @@
         </is>
       </c>
       <c r="E726" s="20" t="n">
-        <v>167</v>
+        <v>139</v>
       </c>
     </row>
     <row r="727" ht="20" customHeight="1">
@@ -19203,7 +19203,7 @@
         </is>
       </c>
       <c r="E727" s="23" t="n">
-        <v>191</v>
+        <v>233</v>
       </c>
     </row>
     <row r="728" ht="20" customHeight="1">
@@ -19228,7 +19228,7 @@
         </is>
       </c>
       <c r="E728" s="20" t="n">
-        <v>198</v>
+        <v>124</v>
       </c>
     </row>
     <row r="729" ht="20" customHeight="1">
@@ -19253,7 +19253,7 @@
         </is>
       </c>
       <c r="E729" s="23" t="n">
-        <v>209</v>
+        <v>153</v>
       </c>
     </row>
     <row r="730" ht="20" customHeight="1">
@@ -19278,7 +19278,7 @@
         </is>
       </c>
       <c r="E730" s="20" t="n">
-        <v>178</v>
+        <v>165</v>
       </c>
     </row>
     <row r="731" ht="20" customHeight="1">
@@ -19303,7 +19303,7 @@
         </is>
       </c>
       <c r="E731" s="23" t="n">
-        <v>198</v>
+        <v>167</v>
       </c>
     </row>
     <row r="732" ht="20" customHeight="1">
@@ -19353,7 +19353,7 @@
         </is>
       </c>
       <c r="E733" s="23" t="n">
-        <v>197</v>
+        <v>180</v>
       </c>
     </row>
     <row r="734" ht="20" customHeight="1">
@@ -19378,7 +19378,7 @@
         </is>
       </c>
       <c r="E734" s="20" t="n">
-        <v>115</v>
+        <v>212</v>
       </c>
     </row>
     <row r="735" ht="20" customHeight="1">
@@ -19403,7 +19403,7 @@
         </is>
       </c>
       <c r="E735" s="23" t="n">
-        <v>186</v>
+        <v>217</v>
       </c>
     </row>
     <row r="736" ht="20" customHeight="1">
@@ -19428,7 +19428,7 @@
         </is>
       </c>
       <c r="E736" s="20" t="n">
-        <v>223</v>
+        <v>202</v>
       </c>
     </row>
     <row r="737" ht="20" customHeight="1">
@@ -19453,7 +19453,7 @@
         </is>
       </c>
       <c r="E737" s="23" t="n">
-        <v>140</v>
+        <v>213</v>
       </c>
     </row>
     <row r="738" ht="20" customHeight="1">
@@ -19478,7 +19478,7 @@
         </is>
       </c>
       <c r="E738" s="20" t="n">
-        <v>232</v>
+        <v>121</v>
       </c>
     </row>
     <row r="739" ht="20" customHeight="1">
@@ -19503,7 +19503,7 @@
         </is>
       </c>
       <c r="E739" s="23" t="n">
-        <v>149</v>
+        <v>199</v>
       </c>
     </row>
     <row r="740" ht="20" customHeight="1">
@@ -19528,7 +19528,7 @@
         </is>
       </c>
       <c r="E740" s="20" t="n">
-        <v>205</v>
+        <v>132</v>
       </c>
     </row>
     <row r="741" ht="20" customHeight="1">
@@ -19553,7 +19553,7 @@
         </is>
       </c>
       <c r="E741" s="23" t="n">
-        <v>152</v>
+        <v>116</v>
       </c>
     </row>
     <row r="742" ht="20" customHeight="1">
@@ -19578,7 +19578,7 @@
         </is>
       </c>
       <c r="E742" s="20" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
     </row>
     <row r="743" ht="20" customHeight="1">
@@ -19603,7 +19603,7 @@
         </is>
       </c>
       <c r="E743" s="23" t="n">
-        <v>139</v>
+        <v>222</v>
       </c>
     </row>
     <row r="744" ht="20" customHeight="1">
@@ -19653,7 +19653,7 @@
         </is>
       </c>
       <c r="E745" s="23" t="n">
-        <v>160</v>
+        <v>191</v>
       </c>
     </row>
     <row r="746" ht="20" customHeight="1">
@@ -19678,7 +19678,7 @@
         </is>
       </c>
       <c r="E746" s="20" t="n">
-        <v>153</v>
+        <v>140</v>
       </c>
     </row>
     <row r="747" ht="20" customHeight="1">
@@ -19703,7 +19703,7 @@
         </is>
       </c>
       <c r="E747" s="23" t="n">
-        <v>115</v>
+        <v>207</v>
       </c>
     </row>
     <row r="748" ht="20" customHeight="1">
@@ -19728,7 +19728,7 @@
         </is>
       </c>
       <c r="E748" s="20" t="n">
-        <v>202</v>
+        <v>195</v>
       </c>
     </row>
     <row r="749" ht="20" customHeight="1">
@@ -19753,7 +19753,7 @@
         </is>
       </c>
       <c r="E749" s="23" t="n">
-        <v>154</v>
+        <v>199</v>
       </c>
     </row>
     <row r="750" ht="20" customHeight="1">
@@ -19778,7 +19778,7 @@
         </is>
       </c>
       <c r="E750" s="20" t="n">
-        <v>112</v>
+        <v>228</v>
       </c>
     </row>
     <row r="751" ht="20" customHeight="1">
@@ -19803,7 +19803,7 @@
         </is>
       </c>
       <c r="E751" s="23" t="n">
-        <v>142</v>
+        <v>184</v>
       </c>
     </row>
     <row r="752" ht="20" customHeight="1">
@@ -19828,7 +19828,7 @@
         </is>
       </c>
       <c r="E752" s="20" t="n">
-        <v>228</v>
+        <v>209</v>
       </c>
     </row>
     <row r="753" ht="20" customHeight="1">
@@ -19853,7 +19853,7 @@
         </is>
       </c>
       <c r="E753" s="23" t="n">
-        <v>123</v>
+        <v>140</v>
       </c>
     </row>
     <row r="754" ht="20" customHeight="1">
@@ -19878,7 +19878,7 @@
         </is>
       </c>
       <c r="E754" s="20" t="n">
-        <v>152</v>
+        <v>185</v>
       </c>
     </row>
     <row r="755" ht="20" customHeight="1">
@@ -19903,7 +19903,7 @@
         </is>
       </c>
       <c r="E755" s="23" t="n">
-        <v>164</v>
+        <v>210</v>
       </c>
     </row>
     <row r="756" ht="20" customHeight="1">
@@ -19928,7 +19928,7 @@
         </is>
       </c>
       <c r="E756" s="20" t="n">
-        <v>216</v>
+        <v>131</v>
       </c>
     </row>
     <row r="757" ht="20" customHeight="1">
@@ -19953,7 +19953,7 @@
         </is>
       </c>
       <c r="E757" s="23" t="n">
-        <v>200</v>
+        <v>193</v>
       </c>
     </row>
     <row r="758" ht="20" customHeight="1">
@@ -19978,7 +19978,7 @@
         </is>
       </c>
       <c r="E758" s="20" t="n">
-        <v>209</v>
+        <v>137</v>
       </c>
     </row>
     <row r="759" ht="20" customHeight="1">
@@ -20003,7 +20003,7 @@
         </is>
       </c>
       <c r="E759" s="23" t="n">
-        <v>185</v>
+        <v>200</v>
       </c>
     </row>
     <row r="760" ht="20" customHeight="1">
@@ -20028,7 +20028,7 @@
         </is>
       </c>
       <c r="E760" s="20" t="n">
-        <v>224</v>
+        <v>206</v>
       </c>
     </row>
     <row r="761" ht="20" customHeight="1">
@@ -20053,7 +20053,7 @@
         </is>
       </c>
       <c r="E761" s="23" t="n">
-        <v>208</v>
+        <v>117</v>
       </c>
     </row>
     <row r="762" ht="20" customHeight="1">
@@ -20078,7 +20078,7 @@
         </is>
       </c>
       <c r="E762" s="20" t="n">
-        <v>158</v>
+        <v>234</v>
       </c>
     </row>
     <row r="763" ht="20" customHeight="1">
@@ -20103,7 +20103,7 @@
         </is>
       </c>
       <c r="E763" s="23" t="n">
-        <v>154</v>
+        <v>118</v>
       </c>
     </row>
     <row r="764" ht="20" customHeight="1">
@@ -20128,7 +20128,7 @@
         </is>
       </c>
       <c r="E764" s="20" t="n">
-        <v>134</v>
+        <v>217</v>
       </c>
     </row>
     <row r="765" ht="20" customHeight="1">
@@ -20153,7 +20153,7 @@
         </is>
       </c>
       <c r="E765" s="23" t="n">
-        <v>220</v>
+        <v>226</v>
       </c>
     </row>
     <row r="766" ht="20" customHeight="1">
@@ -20178,7 +20178,7 @@
         </is>
       </c>
       <c r="E766" s="20" t="n">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="767" ht="20" customHeight="1">
@@ -20203,7 +20203,7 @@
         </is>
       </c>
       <c r="E767" s="23" t="n">
-        <v>130</v>
+        <v>167</v>
       </c>
     </row>
     <row r="768" ht="20" customHeight="1">
@@ -20228,7 +20228,7 @@
         </is>
       </c>
       <c r="E768" s="20" t="n">
-        <v>120</v>
+        <v>235</v>
       </c>
     </row>
     <row r="769" ht="20" customHeight="1">
@@ -20253,7 +20253,7 @@
         </is>
       </c>
       <c r="E769" s="23" t="n">
-        <v>170</v>
+        <v>223</v>
       </c>
     </row>
     <row r="770" ht="20" customHeight="1">
@@ -20278,7 +20278,7 @@
         </is>
       </c>
       <c r="E770" s="20" t="n">
-        <v>178</v>
+        <v>143</v>
       </c>
     </row>
     <row r="771" ht="20" customHeight="1">
@@ -20303,7 +20303,7 @@
         </is>
       </c>
       <c r="E771" s="23" t="n">
-        <v>219</v>
+        <v>167</v>
       </c>
     </row>
     <row r="772" ht="20" customHeight="1">
@@ -20328,7 +20328,7 @@
         </is>
       </c>
       <c r="E772" s="20" t="n">
-        <v>182</v>
+        <v>192</v>
       </c>
     </row>
     <row r="773" ht="20" customHeight="1">
@@ -20353,7 +20353,7 @@
         </is>
       </c>
       <c r="E773" s="23" t="n">
-        <v>175</v>
+        <v>212</v>
       </c>
     </row>
     <row r="774" ht="20" customHeight="1">
@@ -20378,7 +20378,7 @@
         </is>
       </c>
       <c r="E774" s="20" t="n">
-        <v>139</v>
+        <v>165</v>
       </c>
     </row>
     <row r="775" ht="20" customHeight="1">
@@ -20403,7 +20403,7 @@
         </is>
       </c>
       <c r="E775" s="23" t="n">
-        <v>178</v>
+        <v>215</v>
       </c>
     </row>
     <row r="776" ht="20" customHeight="1">
@@ -20428,7 +20428,7 @@
         </is>
       </c>
       <c r="E776" s="20" t="n">
-        <v>222</v>
+        <v>117</v>
       </c>
     </row>
     <row r="777" ht="20" customHeight="1">
@@ -20453,7 +20453,7 @@
         </is>
       </c>
       <c r="E777" s="23" t="n">
-        <v>200</v>
+        <v>174</v>
       </c>
     </row>
     <row r="778" ht="20" customHeight="1">
@@ -20478,7 +20478,7 @@
         </is>
       </c>
       <c r="E778" s="20" t="n">
-        <v>167</v>
+        <v>119</v>
       </c>
     </row>
     <row r="779" ht="20" customHeight="1">
@@ -20503,7 +20503,7 @@
         </is>
       </c>
       <c r="E779" s="23" t="n">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="780" ht="20" customHeight="1">
@@ -20528,7 +20528,7 @@
         </is>
       </c>
       <c r="E780" s="20" t="n">
-        <v>231</v>
+        <v>200</v>
       </c>
     </row>
     <row r="781" ht="20" customHeight="1">
@@ -20553,7 +20553,7 @@
         </is>
       </c>
       <c r="E781" s="23" t="n">
-        <v>149</v>
+        <v>131</v>
       </c>
     </row>
     <row r="782" ht="20" customHeight="1">
@@ -20578,7 +20578,7 @@
         </is>
       </c>
       <c r="E782" s="20" t="n">
-        <v>232</v>
+        <v>112</v>
       </c>
     </row>
     <row r="783" ht="20" customHeight="1">
@@ -20603,7 +20603,7 @@
         </is>
       </c>
       <c r="E783" s="23" t="n">
-        <v>148</v>
+        <v>121</v>
       </c>
     </row>
     <row r="784" ht="20" customHeight="1">
@@ -20628,7 +20628,7 @@
         </is>
       </c>
       <c r="E784" s="20" t="n">
-        <v>112</v>
+        <v>184</v>
       </c>
     </row>
     <row r="785" ht="20" customHeight="1">
@@ -20653,7 +20653,7 @@
         </is>
       </c>
       <c r="E785" s="23" t="n">
-        <v>198</v>
+        <v>118</v>
       </c>
     </row>
     <row r="786" ht="20" customHeight="1">
@@ -20678,7 +20678,7 @@
         </is>
       </c>
       <c r="E786" s="20" t="n">
-        <v>195</v>
+        <v>213</v>
       </c>
     </row>
     <row r="787" ht="20" customHeight="1">
@@ -20703,7 +20703,7 @@
         </is>
       </c>
       <c r="E787" s="23" t="n">
-        <v>214</v>
+        <v>116</v>
       </c>
     </row>
     <row r="788" ht="20" customHeight="1">
@@ -20728,7 +20728,7 @@
         </is>
       </c>
       <c r="E788" s="20" t="n">
-        <v>123</v>
+        <v>154</v>
       </c>
     </row>
     <row r="789" ht="20" customHeight="1">
@@ -20753,7 +20753,7 @@
         </is>
       </c>
       <c r="E789" s="23" t="n">
-        <v>214</v>
+        <v>145</v>
       </c>
     </row>
     <row r="790" ht="20" customHeight="1">
@@ -20778,7 +20778,7 @@
         </is>
       </c>
       <c r="E790" s="20" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="791" ht="20" customHeight="1">
@@ -20803,7 +20803,7 @@
         </is>
       </c>
       <c r="E791" s="23" t="n">
-        <v>158</v>
+        <v>181</v>
       </c>
     </row>
     <row r="792" ht="20" customHeight="1">
@@ -20828,7 +20828,7 @@
         </is>
       </c>
       <c r="E792" s="20" t="n">
-        <v>198</v>
+        <v>155</v>
       </c>
     </row>
     <row r="793" ht="20" customHeight="1">
@@ -20853,7 +20853,7 @@
         </is>
       </c>
       <c r="E793" s="23" t="n">
-        <v>162</v>
+        <v>207</v>
       </c>
     </row>
     <row r="794" ht="20" customHeight="1">
@@ -20878,7 +20878,7 @@
         </is>
       </c>
       <c r="E794" s="20" t="n">
-        <v>223</v>
+        <v>120</v>
       </c>
     </row>
     <row r="795" ht="20" customHeight="1">
@@ -20903,7 +20903,7 @@
         </is>
       </c>
       <c r="E795" s="23" t="n">
-        <v>124</v>
+        <v>113</v>
       </c>
     </row>
     <row r="796" ht="20" customHeight="1">
@@ -20928,7 +20928,7 @@
         </is>
       </c>
       <c r="E796" s="20" t="n">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="797" ht="20" customHeight="1">
@@ -20953,7 +20953,7 @@
         </is>
       </c>
       <c r="E797" s="23" t="n">
-        <v>186</v>
+        <v>115</v>
       </c>
     </row>
     <row r="798" ht="20" customHeight="1">
@@ -20978,7 +20978,7 @@
         </is>
       </c>
       <c r="E798" s="20" t="n">
-        <v>213</v>
+        <v>155</v>
       </c>
     </row>
     <row r="799" ht="20" customHeight="1">
@@ -21003,7 +21003,7 @@
         </is>
       </c>
       <c r="E799" s="23" t="n">
-        <v>179</v>
+        <v>138</v>
       </c>
     </row>
     <row r="800" ht="20" customHeight="1">
@@ -21028,7 +21028,7 @@
         </is>
       </c>
       <c r="E800" s="20" t="n">
-        <v>128</v>
+        <v>224</v>
       </c>
     </row>
     <row r="801" ht="20" customHeight="1">
@@ -21053,7 +21053,7 @@
         </is>
       </c>
       <c r="E801" s="23" t="n">
-        <v>223</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>

--- a/Appium_E2E_Test_Report_Traverse.xlsx
+++ b/Appium_E2E_Test_Report_Traverse.xlsx
@@ -791,7 +791,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 08:35:25</t>
+          <t>2026-08-11 08:49:49</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="E2" s="20" t="n">
-        <v>112</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="E3" s="23" t="n">
-        <v>210</v>
+        <v>191</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="E4" s="20" t="n">
-        <v>158</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="E5" s="23" t="n">
-        <v>184</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="E6" s="20" t="n">
-        <v>151</v>
+        <v>158</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="E7" s="23" t="n">
-        <v>212</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -1228,7 +1228,7 @@
         </is>
       </c>
       <c r="E8" s="20" t="n">
-        <v>143</v>
+        <v>165</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="E9" s="23" t="n">
-        <v>163</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
@@ -1278,7 +1278,7 @@
         </is>
       </c>
       <c r="E10" s="20" t="n">
-        <v>167</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="E11" s="23" t="n">
-        <v>129</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
@@ -1328,7 +1328,7 @@
         </is>
       </c>
       <c r="E12" s="20" t="n">
-        <v>207</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="E13" s="23" t="n">
-        <v>144</v>
+        <v>225</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="E14" s="20" t="n">
-        <v>110</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="E15" s="23" t="n">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="E16" s="20" t="n">
-        <v>182</v>
+        <v>176</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="E17" s="23" t="n">
-        <v>161</v>
+        <v>228</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -1478,7 +1478,7 @@
         </is>
       </c>
       <c r="E18" s="20" t="n">
-        <v>207</v>
+        <v>188</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
@@ -1503,7 +1503,7 @@
         </is>
       </c>
       <c r="E19" s="23" t="n">
-        <v>216</v>
+        <v>140</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="E20" s="20" t="n">
-        <v>112</v>
+        <v>227</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="E21" s="23" t="n">
-        <v>164</v>
+        <v>147</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
@@ -1578,7 +1578,7 @@
         </is>
       </c>
       <c r="E22" s="20" t="n">
-        <v>156</v>
+        <v>139</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="E23" s="23" t="n">
-        <v>142</v>
+        <v>128</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
@@ -1628,7 +1628,7 @@
         </is>
       </c>
       <c r="E24" s="20" t="n">
-        <v>238</v>
+        <v>158</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="E25" s="23" t="n">
-        <v>211</v>
+        <v>220</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
@@ -1678,7 +1678,7 @@
         </is>
       </c>
       <c r="E26" s="20" t="n">
-        <v>202</v>
+        <v>165</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="E27" s="23" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="E28" s="20" t="n">
-        <v>128</v>
+        <v>170</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="E29" s="23" t="n">
-        <v>233</v>
+        <v>150</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="E30" s="20" t="n">
-        <v>189</v>
+        <v>180</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
@@ -1803,7 +1803,7 @@
         </is>
       </c>
       <c r="E31" s="23" t="n">
-        <v>186</v>
+        <v>206</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
@@ -1828,7 +1828,7 @@
         </is>
       </c>
       <c r="E32" s="20" t="n">
-        <v>150</v>
+        <v>172</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
@@ -1853,7 +1853,7 @@
         </is>
       </c>
       <c r="E33" s="23" t="n">
-        <v>161</v>
+        <v>184</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
@@ -1878,7 +1878,7 @@
         </is>
       </c>
       <c r="E34" s="20" t="n">
-        <v>219</v>
+        <v>140</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="E35" s="23" t="n">
-        <v>174</v>
+        <v>133</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="E36" s="20" t="n">
-        <v>180</v>
+        <v>186</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="E37" s="23" t="n">
-        <v>139</v>
+        <v>128</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
@@ -1978,7 +1978,7 @@
         </is>
       </c>
       <c r="E38" s="20" t="n">
-        <v>214</v>
+        <v>113</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="E39" s="23" t="n">
-        <v>135</v>
+        <v>207</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="E40" s="20" t="n">
-        <v>176</v>
+        <v>215</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="E41" s="23" t="n">
-        <v>151</v>
+        <v>225</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
@@ -2078,7 +2078,7 @@
         </is>
       </c>
       <c r="E42" s="20" t="n">
-        <v>118</v>
+        <v>143</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="E43" s="23" t="n">
-        <v>129</v>
+        <v>139</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="E44" s="20" t="n">
-        <v>115</v>
+        <v>160</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="E45" s="23" t="n">
-        <v>215</v>
+        <v>200</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
@@ -2203,7 +2203,7 @@
         </is>
       </c>
       <c r="E47" s="23" t="n">
-        <v>120</v>
+        <v>179</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="E48" s="20" t="n">
-        <v>110</v>
+        <v>218</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
@@ -2253,7 +2253,7 @@
         </is>
       </c>
       <c r="E49" s="23" t="n">
-        <v>118</v>
+        <v>184</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
@@ -2278,7 +2278,7 @@
         </is>
       </c>
       <c r="E50" s="20" t="n">
-        <v>189</v>
+        <v>164</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="E51" s="23" t="n">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
@@ -2328,7 +2328,7 @@
         </is>
       </c>
       <c r="E52" s="20" t="n">
-        <v>167</v>
+        <v>218</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
@@ -2353,7 +2353,7 @@
         </is>
       </c>
       <c r="E53" s="23" t="n">
-        <v>234</v>
+        <v>117</v>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="E54" s="20" t="n">
-        <v>129</v>
+        <v>147</v>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1">
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="E55" s="23" t="n">
-        <v>173</v>
+        <v>134</v>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1">
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="E56" s="20" t="n">
-        <v>163</v>
+        <v>236</v>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1">
@@ -2453,7 +2453,7 @@
         </is>
       </c>
       <c r="E57" s="23" t="n">
-        <v>194</v>
+        <v>144</v>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1">
@@ -2478,7 +2478,7 @@
         </is>
       </c>
       <c r="E58" s="20" t="n">
-        <v>196</v>
+        <v>150</v>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1">
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="E59" s="23" t="n">
-        <v>128</v>
+        <v>181</v>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1">
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="E60" s="20" t="n">
-        <v>122</v>
+        <v>164</v>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
@@ -2553,7 +2553,7 @@
         </is>
       </c>
       <c r="E61" s="23" t="n">
-        <v>212</v>
+        <v>121</v>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="E62" s="20" t="n">
-        <v>221</v>
+        <v>159</v>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="E63" s="23" t="n">
-        <v>169</v>
+        <v>134</v>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1">
@@ -2628,7 +2628,7 @@
         </is>
       </c>
       <c r="E64" s="20" t="n">
-        <v>197</v>
+        <v>155</v>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1">
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="E65" s="23" t="n">
-        <v>141</v>
+        <v>204</v>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1">
@@ -2678,7 +2678,7 @@
         </is>
       </c>
       <c r="E66" s="20" t="n">
-        <v>162</v>
+        <v>187</v>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="E67" s="23" t="n">
-        <v>116</v>
+        <v>234</v>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="E68" s="20" t="n">
-        <v>146</v>
+        <v>132</v>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="E69" s="23" t="n">
-        <v>144</v>
+        <v>150</v>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1">
@@ -2778,7 +2778,7 @@
         </is>
       </c>
       <c r="E70" s="20" t="n">
-        <v>231</v>
+        <v>126</v>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1">
@@ -2803,7 +2803,7 @@
         </is>
       </c>
       <c r="E71" s="23" t="n">
-        <v>183</v>
+        <v>216</v>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1">
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="E72" s="20" t="n">
-        <v>128</v>
+        <v>199</v>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1">
@@ -2853,7 +2853,7 @@
         </is>
       </c>
       <c r="E73" s="23" t="n">
-        <v>115</v>
+        <v>165</v>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
@@ -2878,7 +2878,7 @@
         </is>
       </c>
       <c r="E74" s="20" t="n">
-        <v>111</v>
+        <v>203</v>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="E75" s="23" t="n">
-        <v>217</v>
+        <v>121</v>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
@@ -2928,7 +2928,7 @@
         </is>
       </c>
       <c r="E76" s="20" t="n">
-        <v>136</v>
+        <v>217</v>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="E77" s="23" t="n">
-        <v>199</v>
+        <v>229</v>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1">
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="E78" s="20" t="n">
-        <v>167</v>
+        <v>157</v>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
@@ -3003,7 +3003,7 @@
         </is>
       </c>
       <c r="E79" s="23" t="n">
-        <v>174</v>
+        <v>120</v>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1">
@@ -3028,7 +3028,7 @@
         </is>
       </c>
       <c r="E80" s="20" t="n">
-        <v>149</v>
+        <v>230</v>
       </c>
     </row>
     <row r="81" ht="20" customHeight="1">
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="E81" s="23" t="n">
-        <v>235</v>
+        <v>140</v>
       </c>
     </row>
     <row r="82" ht="20" customHeight="1">
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="E82" s="20" t="n">
-        <v>211</v>
+        <v>170</v>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1">
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="E83" s="23" t="n">
-        <v>112</v>
+        <v>193</v>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1">
@@ -3128,7 +3128,7 @@
         </is>
       </c>
       <c r="E84" s="20" t="n">
-        <v>156</v>
+        <v>226</v>
       </c>
     </row>
     <row r="85" ht="20" customHeight="1">
@@ -3153,7 +3153,7 @@
         </is>
       </c>
       <c r="E85" s="23" t="n">
-        <v>155</v>
+        <v>222</v>
       </c>
     </row>
     <row r="86" ht="20" customHeight="1">
@@ -3178,7 +3178,7 @@
         </is>
       </c>
       <c r="E86" s="20" t="n">
-        <v>167</v>
+        <v>181</v>
       </c>
     </row>
     <row r="87" ht="20" customHeight="1">
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="E87" s="23" t="n">
-        <v>156</v>
+        <v>147</v>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1">
@@ -3228,7 +3228,7 @@
         </is>
       </c>
       <c r="E88" s="20" t="n">
-        <v>184</v>
+        <v>174</v>
       </c>
     </row>
     <row r="89" ht="20" customHeight="1">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="E89" s="23" t="n">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="90" ht="20" customHeight="1">
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="E90" s="20" t="n">
-        <v>130</v>
+        <v>179</v>
       </c>
     </row>
     <row r="91" ht="20" customHeight="1">
@@ -3303,7 +3303,7 @@
         </is>
       </c>
       <c r="E91" s="23" t="n">
-        <v>133</v>
+        <v>228</v>
       </c>
     </row>
     <row r="92" ht="20" customHeight="1">
@@ -3328,7 +3328,7 @@
         </is>
       </c>
       <c r="E92" s="20" t="n">
-        <v>183</v>
+        <v>202</v>
       </c>
     </row>
     <row r="93" ht="20" customHeight="1">
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="E93" s="23" t="n">
-        <v>214</v>
+        <v>154</v>
       </c>
     </row>
     <row r="94" ht="20" customHeight="1">
@@ -3378,7 +3378,7 @@
         </is>
       </c>
       <c r="E94" s="20" t="n">
-        <v>205</v>
+        <v>164</v>
       </c>
     </row>
     <row r="95" ht="20" customHeight="1">
@@ -3403,7 +3403,7 @@
         </is>
       </c>
       <c r="E95" s="23" t="n">
-        <v>156</v>
+        <v>186</v>
       </c>
     </row>
     <row r="96" ht="20" customHeight="1">
@@ -3428,7 +3428,7 @@
         </is>
       </c>
       <c r="E96" s="20" t="n">
-        <v>230</v>
+        <v>134</v>
       </c>
     </row>
     <row r="97" ht="20" customHeight="1">
@@ -3453,7 +3453,7 @@
         </is>
       </c>
       <c r="E97" s="23" t="n">
-        <v>114</v>
+        <v>195</v>
       </c>
     </row>
     <row r="98" ht="20" customHeight="1">
@@ -3478,7 +3478,7 @@
         </is>
       </c>
       <c r="E98" s="20" t="n">
-        <v>142</v>
+        <v>182</v>
       </c>
     </row>
     <row r="99" ht="20" customHeight="1">
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="E99" s="23" t="n">
-        <v>118</v>
+        <v>192</v>
       </c>
     </row>
     <row r="100" ht="20" customHeight="1">
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="E100" s="20" t="n">
-        <v>168</v>
+        <v>212</v>
       </c>
     </row>
     <row r="101" ht="20" customHeight="1">
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="E101" s="23" t="n">
-        <v>215</v>
+        <v>144</v>
       </c>
     </row>
     <row r="102" ht="20" customHeight="1">
@@ -3578,7 +3578,7 @@
         </is>
       </c>
       <c r="E102" s="20" t="n">
-        <v>152</v>
+        <v>227</v>
       </c>
     </row>
     <row r="103" ht="20" customHeight="1">
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="E103" s="23" t="n">
-        <v>116</v>
+        <v>123</v>
       </c>
     </row>
     <row r="104" ht="20" customHeight="1">
@@ -3628,7 +3628,7 @@
         </is>
       </c>
       <c r="E104" s="20" t="n">
-        <v>199</v>
+        <v>144</v>
       </c>
     </row>
     <row r="105" ht="20" customHeight="1">
@@ -3653,7 +3653,7 @@
         </is>
       </c>
       <c r="E105" s="23" t="n">
-        <v>164</v>
+        <v>176</v>
       </c>
     </row>
     <row r="106" ht="20" customHeight="1">
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="E106" s="20" t="n">
-        <v>139</v>
+        <v>111</v>
       </c>
     </row>
     <row r="107" ht="20" customHeight="1">
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="E107" s="23" t="n">
-        <v>179</v>
+        <v>158</v>
       </c>
     </row>
     <row r="108" ht="20" customHeight="1">
@@ -3728,7 +3728,7 @@
         </is>
       </c>
       <c r="E108" s="20" t="n">
-        <v>142</v>
+        <v>150</v>
       </c>
     </row>
     <row r="109" ht="20" customHeight="1">
@@ -3753,7 +3753,7 @@
         </is>
       </c>
       <c r="E109" s="23" t="n">
-        <v>136</v>
+        <v>164</v>
       </c>
     </row>
     <row r="110" ht="20" customHeight="1">
@@ -3778,7 +3778,7 @@
         </is>
       </c>
       <c r="E110" s="20" t="n">
-        <v>180</v>
+        <v>194</v>
       </c>
     </row>
     <row r="111" ht="20" customHeight="1">
@@ -3803,7 +3803,7 @@
         </is>
       </c>
       <c r="E111" s="23" t="n">
-        <v>141</v>
+        <v>181</v>
       </c>
     </row>
     <row r="112" ht="20" customHeight="1">
@@ -3828,7 +3828,7 @@
         </is>
       </c>
       <c r="E112" s="20" t="n">
-        <v>209</v>
+        <v>225</v>
       </c>
     </row>
     <row r="113" ht="20" customHeight="1">
@@ -3853,7 +3853,7 @@
         </is>
       </c>
       <c r="E113" s="23" t="n">
-        <v>232</v>
+        <v>172</v>
       </c>
     </row>
     <row r="114" ht="20" customHeight="1">
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="E114" s="20" t="n">
-        <v>169</v>
+        <v>162</v>
       </c>
     </row>
     <row r="115" ht="20" customHeight="1">
@@ -3903,7 +3903,7 @@
         </is>
       </c>
       <c r="E115" s="23" t="n">
-        <v>157</v>
+        <v>210</v>
       </c>
     </row>
     <row r="116" ht="20" customHeight="1">
@@ -3928,7 +3928,7 @@
         </is>
       </c>
       <c r="E116" s="20" t="n">
-        <v>238</v>
+        <v>129</v>
       </c>
     </row>
     <row r="117" ht="20" customHeight="1">
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="E117" s="23" t="n">
-        <v>186</v>
+        <v>196</v>
       </c>
     </row>
     <row r="118" ht="20" customHeight="1">
@@ -3978,7 +3978,7 @@
         </is>
       </c>
       <c r="E118" s="20" t="n">
-        <v>132</v>
+        <v>110</v>
       </c>
     </row>
     <row r="119" ht="20" customHeight="1">
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="E119" s="23" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="120" ht="20" customHeight="1">
@@ -4028,7 +4028,7 @@
         </is>
       </c>
       <c r="E120" s="20" t="n">
-        <v>216</v>
+        <v>173</v>
       </c>
     </row>
     <row r="121" ht="20" customHeight="1">
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="E121" s="23" t="n">
-        <v>135</v>
+        <v>153</v>
       </c>
     </row>
     <row r="122" ht="20" customHeight="1">
@@ -4078,7 +4078,7 @@
         </is>
       </c>
       <c r="E122" s="20" t="n">
-        <v>236</v>
+        <v>228</v>
       </c>
     </row>
     <row r="123" ht="20" customHeight="1">
@@ -4103,7 +4103,7 @@
         </is>
       </c>
       <c r="E123" s="23" t="n">
-        <v>188</v>
+        <v>200</v>
       </c>
     </row>
     <row r="124" ht="20" customHeight="1">
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="E124" s="20" t="n">
-        <v>209</v>
+        <v>182</v>
       </c>
     </row>
     <row r="125" ht="20" customHeight="1">
@@ -4153,7 +4153,7 @@
         </is>
       </c>
       <c r="E125" s="23" t="n">
-        <v>146</v>
+        <v>211</v>
       </c>
     </row>
     <row r="126" ht="20" customHeight="1">
@@ -4178,7 +4178,7 @@
         </is>
       </c>
       <c r="E126" s="20" t="n">
-        <v>121</v>
+        <v>161</v>
       </c>
     </row>
     <row r="127" ht="20" customHeight="1">
@@ -4203,7 +4203,7 @@
         </is>
       </c>
       <c r="E127" s="23" t="n">
-        <v>184</v>
+        <v>159</v>
       </c>
     </row>
     <row r="128" ht="20" customHeight="1">
@@ -4228,7 +4228,7 @@
         </is>
       </c>
       <c r="E128" s="20" t="n">
-        <v>224</v>
+        <v>125</v>
       </c>
     </row>
     <row r="129" ht="20" customHeight="1">
@@ -4253,7 +4253,7 @@
         </is>
       </c>
       <c r="E129" s="23" t="n">
-        <v>140</v>
+        <v>134</v>
       </c>
     </row>
     <row r="130" ht="20" customHeight="1">
@@ -4278,7 +4278,7 @@
         </is>
       </c>
       <c r="E130" s="20" t="n">
-        <v>137</v>
+        <v>233</v>
       </c>
     </row>
     <row r="131" ht="20" customHeight="1">
@@ -4303,7 +4303,7 @@
         </is>
       </c>
       <c r="E131" s="23" t="n">
-        <v>111</v>
+        <v>156</v>
       </c>
     </row>
     <row r="132" ht="20" customHeight="1">
@@ -4328,7 +4328,7 @@
         </is>
       </c>
       <c r="E132" s="20" t="n">
-        <v>140</v>
+        <v>217</v>
       </c>
     </row>
     <row r="133" ht="20" customHeight="1">
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="E133" s="23" t="n">
-        <v>169</v>
+        <v>200</v>
       </c>
     </row>
     <row r="134" ht="20" customHeight="1">
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="E134" s="20" t="n">
-        <v>131</v>
+        <v>188</v>
       </c>
     </row>
     <row r="135" ht="20" customHeight="1">
@@ -4403,7 +4403,7 @@
         </is>
       </c>
       <c r="E135" s="23" t="n">
-        <v>140</v>
+        <v>202</v>
       </c>
     </row>
     <row r="136" ht="20" customHeight="1">
@@ -4428,7 +4428,7 @@
         </is>
       </c>
       <c r="E136" s="20" t="n">
-        <v>148</v>
+        <v>187</v>
       </c>
     </row>
     <row r="137" ht="20" customHeight="1">
@@ -4453,7 +4453,7 @@
         </is>
       </c>
       <c r="E137" s="23" t="n">
-        <v>183</v>
+        <v>193</v>
       </c>
     </row>
     <row r="138" ht="20" customHeight="1">
@@ -4478,7 +4478,7 @@
         </is>
       </c>
       <c r="E138" s="20" t="n">
-        <v>121</v>
+        <v>191</v>
       </c>
     </row>
     <row r="139" ht="20" customHeight="1">
@@ -4503,7 +4503,7 @@
         </is>
       </c>
       <c r="E139" s="23" t="n">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="140" ht="20" customHeight="1">
@@ -4528,7 +4528,7 @@
         </is>
       </c>
       <c r="E140" s="20" t="n">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="141" ht="20" customHeight="1">
@@ -4553,7 +4553,7 @@
         </is>
       </c>
       <c r="E141" s="23" t="n">
-        <v>128</v>
+        <v>198</v>
       </c>
     </row>
     <row r="142" ht="20" customHeight="1">
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="E142" s="20" t="n">
-        <v>138</v>
+        <v>194</v>
       </c>
     </row>
     <row r="143" ht="20" customHeight="1">
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="E143" s="23" t="n">
-        <v>240</v>
+        <v>197</v>
       </c>
     </row>
     <row r="144" ht="20" customHeight="1">
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="E144" s="20" t="n">
-        <v>116</v>
+        <v>218</v>
       </c>
     </row>
     <row r="145" ht="20" customHeight="1">
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="E145" s="23" t="n">
-        <v>175</v>
+        <v>225</v>
       </c>
     </row>
     <row r="146" ht="20" customHeight="1">
@@ -4678,7 +4678,7 @@
         </is>
       </c>
       <c r="E146" s="20" t="n">
-        <v>161</v>
+        <v>145</v>
       </c>
     </row>
     <row r="147" ht="20" customHeight="1">
@@ -4703,7 +4703,7 @@
         </is>
       </c>
       <c r="E147" s="23" t="n">
-        <v>238</v>
+        <v>213</v>
       </c>
     </row>
     <row r="148" ht="20" customHeight="1">
@@ -4728,7 +4728,7 @@
         </is>
       </c>
       <c r="E148" s="20" t="n">
-        <v>120</v>
+        <v>134</v>
       </c>
     </row>
     <row r="149" ht="20" customHeight="1">
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c r="E149" s="23" t="n">
-        <v>138</v>
+        <v>221</v>
       </c>
     </row>
     <row r="150" ht="20" customHeight="1">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="E150" s="20" t="n">
-        <v>169</v>
+        <v>145</v>
       </c>
     </row>
     <row r="151" ht="20" customHeight="1">
@@ -4803,7 +4803,7 @@
         </is>
       </c>
       <c r="E151" s="23" t="n">
-        <v>134</v>
+        <v>141</v>
       </c>
     </row>
     <row r="152" ht="20" customHeight="1">
@@ -4828,7 +4828,7 @@
         </is>
       </c>
       <c r="E152" s="20" t="n">
-        <v>138</v>
+        <v>214</v>
       </c>
     </row>
     <row r="153" ht="20" customHeight="1">
@@ -4853,7 +4853,7 @@
         </is>
       </c>
       <c r="E153" s="23" t="n">
-        <v>211</v>
+        <v>135</v>
       </c>
     </row>
     <row r="154" ht="20" customHeight="1">
@@ -4878,7 +4878,7 @@
         </is>
       </c>
       <c r="E154" s="20" t="n">
-        <v>140</v>
+        <v>190</v>
       </c>
     </row>
     <row r="155" ht="20" customHeight="1">
@@ -4903,7 +4903,7 @@
         </is>
       </c>
       <c r="E155" s="23" t="n">
-        <v>184</v>
+        <v>224</v>
       </c>
     </row>
     <row r="156" ht="20" customHeight="1">
@@ -4928,7 +4928,7 @@
         </is>
       </c>
       <c r="E156" s="20" t="n">
-        <v>127</v>
+        <v>176</v>
       </c>
     </row>
     <row r="157" ht="20" customHeight="1">
@@ -4953,7 +4953,7 @@
         </is>
       </c>
       <c r="E157" s="23" t="n">
-        <v>214</v>
+        <v>240</v>
       </c>
     </row>
     <row r="158" ht="20" customHeight="1">
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="E159" s="23" t="n">
-        <v>132</v>
+        <v>159</v>
       </c>
     </row>
     <row r="160" ht="20" customHeight="1">
@@ -5028,7 +5028,7 @@
         </is>
       </c>
       <c r="E160" s="20" t="n">
-        <v>152</v>
+        <v>143</v>
       </c>
     </row>
     <row r="161" ht="20" customHeight="1">
@@ -5053,7 +5053,7 @@
         </is>
       </c>
       <c r="E161" s="23" t="n">
-        <v>146</v>
+        <v>137</v>
       </c>
     </row>
     <row r="162" ht="20" customHeight="1">
@@ -5078,7 +5078,7 @@
         </is>
       </c>
       <c r="E162" s="20" t="n">
-        <v>220</v>
+        <v>229</v>
       </c>
     </row>
     <row r="163" ht="20" customHeight="1">
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="E163" s="23" t="n">
-        <v>118</v>
+        <v>233</v>
       </c>
     </row>
     <row r="164" ht="20" customHeight="1">
@@ -5128,7 +5128,7 @@
         </is>
       </c>
       <c r="E164" s="20" t="n">
-        <v>218</v>
+        <v>156</v>
       </c>
     </row>
     <row r="165" ht="20" customHeight="1">
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="E165" s="23" t="n">
-        <v>178</v>
+        <v>202</v>
       </c>
     </row>
     <row r="166" ht="20" customHeight="1">
@@ -5178,7 +5178,7 @@
         </is>
       </c>
       <c r="E166" s="20" t="n">
-        <v>133</v>
+        <v>165</v>
       </c>
     </row>
     <row r="167" ht="20" customHeight="1">
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="E167" s="23" t="n">
-        <v>158</v>
+        <v>226</v>
       </c>
     </row>
     <row r="168" ht="20" customHeight="1">
@@ -5228,7 +5228,7 @@
         </is>
       </c>
       <c r="E168" s="20" t="n">
-        <v>224</v>
+        <v>169</v>
       </c>
     </row>
     <row r="169" ht="20" customHeight="1">
@@ -5253,7 +5253,7 @@
         </is>
       </c>
       <c r="E169" s="23" t="n">
-        <v>158</v>
+        <v>232</v>
       </c>
     </row>
     <row r="170" ht="20" customHeight="1">
@@ -5278,7 +5278,7 @@
         </is>
       </c>
       <c r="E170" s="20" t="n">
-        <v>184</v>
+        <v>239</v>
       </c>
     </row>
     <row r="171" ht="20" customHeight="1">
@@ -5303,7 +5303,7 @@
         </is>
       </c>
       <c r="E171" s="23" t="n">
-        <v>173</v>
+        <v>188</v>
       </c>
     </row>
     <row r="172" ht="20" customHeight="1">
@@ -5328,7 +5328,7 @@
         </is>
       </c>
       <c r="E172" s="20" t="n">
-        <v>113</v>
+        <v>195</v>
       </c>
     </row>
     <row r="173" ht="20" customHeight="1">
@@ -5353,7 +5353,7 @@
         </is>
       </c>
       <c r="E173" s="23" t="n">
-        <v>170</v>
+        <v>184</v>
       </c>
     </row>
     <row r="174" ht="20" customHeight="1">
@@ -5378,7 +5378,7 @@
         </is>
       </c>
       <c r="E174" s="20" t="n">
-        <v>196</v>
+        <v>139</v>
       </c>
     </row>
     <row r="175" ht="20" customHeight="1">
@@ -5403,7 +5403,7 @@
         </is>
       </c>
       <c r="E175" s="23" t="n">
-        <v>175</v>
+        <v>240</v>
       </c>
     </row>
     <row r="176" ht="20" customHeight="1">
@@ -5428,7 +5428,7 @@
         </is>
       </c>
       <c r="E176" s="20" t="n">
-        <v>191</v>
+        <v>137</v>
       </c>
     </row>
     <row r="177" ht="20" customHeight="1">
@@ -5453,7 +5453,7 @@
         </is>
       </c>
       <c r="E177" s="23" t="n">
-        <v>133</v>
+        <v>175</v>
       </c>
     </row>
     <row r="178" ht="20" customHeight="1">
@@ -5478,7 +5478,7 @@
         </is>
       </c>
       <c r="E178" s="20" t="n">
-        <v>129</v>
+        <v>212</v>
       </c>
     </row>
     <row r="179" ht="20" customHeight="1">
@@ -5503,7 +5503,7 @@
         </is>
       </c>
       <c r="E179" s="23" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="180" ht="20" customHeight="1">
@@ -5528,7 +5528,7 @@
         </is>
       </c>
       <c r="E180" s="20" t="n">
-        <v>236</v>
+        <v>200</v>
       </c>
     </row>
     <row r="181" ht="20" customHeight="1">
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="E181" s="23" t="n">
-        <v>163</v>
+        <v>205</v>
       </c>
     </row>
     <row r="182" ht="20" customHeight="1">
@@ -5578,7 +5578,7 @@
         </is>
       </c>
       <c r="E182" s="20" t="n">
-        <v>210</v>
+        <v>170</v>
       </c>
     </row>
     <row r="183" ht="20" customHeight="1">
@@ -5603,7 +5603,7 @@
         </is>
       </c>
       <c r="E183" s="23" t="n">
-        <v>165</v>
+        <v>185</v>
       </c>
     </row>
     <row r="184" ht="20" customHeight="1">
@@ -5628,7 +5628,7 @@
         </is>
       </c>
       <c r="E184" s="20" t="n">
-        <v>232</v>
+        <v>159</v>
       </c>
     </row>
     <row r="185" ht="20" customHeight="1">
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="E185" s="23" t="n">
-        <v>161</v>
+        <v>120</v>
       </c>
     </row>
     <row r="186" ht="20" customHeight="1">
@@ -5678,7 +5678,7 @@
         </is>
       </c>
       <c r="E186" s="20" t="n">
-        <v>219</v>
+        <v>135</v>
       </c>
     </row>
     <row r="187" ht="20" customHeight="1">
@@ -5703,7 +5703,7 @@
         </is>
       </c>
       <c r="E187" s="23" t="n">
-        <v>132</v>
+        <v>161</v>
       </c>
     </row>
     <row r="188" ht="20" customHeight="1">
@@ -5728,7 +5728,7 @@
         </is>
       </c>
       <c r="E188" s="20" t="n">
-        <v>197</v>
+        <v>175</v>
       </c>
     </row>
     <row r="189" ht="20" customHeight="1">
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="E189" s="23" t="n">
-        <v>173</v>
+        <v>162</v>
       </c>
     </row>
     <row r="190" ht="20" customHeight="1">
@@ -5778,7 +5778,7 @@
         </is>
       </c>
       <c r="E190" s="20" t="n">
-        <v>141</v>
+        <v>151</v>
       </c>
     </row>
     <row r="191" ht="20" customHeight="1">
@@ -5803,7 +5803,7 @@
         </is>
       </c>
       <c r="E191" s="23" t="n">
-        <v>179</v>
+        <v>232</v>
       </c>
     </row>
     <row r="192" ht="20" customHeight="1">
@@ -5828,7 +5828,7 @@
         </is>
       </c>
       <c r="E192" s="20" t="n">
-        <v>177</v>
+        <v>169</v>
       </c>
     </row>
     <row r="193" ht="20" customHeight="1">
@@ -5853,7 +5853,7 @@
         </is>
       </c>
       <c r="E193" s="23" t="n">
-        <v>129</v>
+        <v>162</v>
       </c>
     </row>
     <row r="194" ht="20" customHeight="1">
@@ -5878,7 +5878,7 @@
         </is>
       </c>
       <c r="E194" s="20" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
     </row>
     <row r="195" ht="20" customHeight="1">
@@ -5903,7 +5903,7 @@
         </is>
       </c>
       <c r="E195" s="23" t="n">
-        <v>148</v>
+        <v>175</v>
       </c>
     </row>
     <row r="196" ht="20" customHeight="1">
@@ -5928,7 +5928,7 @@
         </is>
       </c>
       <c r="E196" s="20" t="n">
-        <v>125</v>
+        <v>197</v>
       </c>
     </row>
     <row r="197" ht="20" customHeight="1">
@@ -5953,7 +5953,7 @@
         </is>
       </c>
       <c r="E197" s="23" t="n">
-        <v>140</v>
+        <v>168</v>
       </c>
     </row>
     <row r="198" ht="20" customHeight="1">
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="E198" s="20" t="n">
-        <v>179</v>
+        <v>229</v>
       </c>
     </row>
     <row r="199" ht="20" customHeight="1">
@@ -6003,7 +6003,7 @@
         </is>
       </c>
       <c r="E199" s="23" t="n">
-        <v>159</v>
+        <v>227</v>
       </c>
     </row>
     <row r="200" ht="20" customHeight="1">
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="E200" s="20" t="n">
-        <v>141</v>
+        <v>225</v>
       </c>
     </row>
     <row r="201" ht="20" customHeight="1">
@@ -6053,7 +6053,7 @@
         </is>
       </c>
       <c r="E201" s="23" t="n">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="202" ht="20" customHeight="1">
@@ -6078,7 +6078,7 @@
         </is>
       </c>
       <c r="E202" s="20" t="n">
-        <v>181</v>
+        <v>237</v>
       </c>
     </row>
     <row r="203" ht="20" customHeight="1">
@@ -6103,7 +6103,7 @@
         </is>
       </c>
       <c r="E203" s="23" t="n">
-        <v>153</v>
+        <v>162</v>
       </c>
     </row>
     <row r="204" ht="20" customHeight="1">
@@ -6128,7 +6128,7 @@
         </is>
       </c>
       <c r="E204" s="20" t="n">
-        <v>182</v>
+        <v>176</v>
       </c>
     </row>
     <row r="205" ht="20" customHeight="1">
@@ -6153,7 +6153,7 @@
         </is>
       </c>
       <c r="E205" s="23" t="n">
-        <v>192</v>
+        <v>223</v>
       </c>
     </row>
     <row r="206" ht="20" customHeight="1">
@@ -6178,7 +6178,7 @@
         </is>
       </c>
       <c r="E206" s="20" t="n">
-        <v>216</v>
+        <v>175</v>
       </c>
     </row>
     <row r="207" ht="20" customHeight="1">
@@ -6203,7 +6203,7 @@
         </is>
       </c>
       <c r="E207" s="23" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="208" ht="20" customHeight="1">
@@ -6228,7 +6228,7 @@
         </is>
       </c>
       <c r="E208" s="20" t="n">
-        <v>215</v>
+        <v>196</v>
       </c>
     </row>
     <row r="209" ht="20" customHeight="1">
@@ -6253,7 +6253,7 @@
         </is>
       </c>
       <c r="E209" s="23" t="n">
-        <v>137</v>
+        <v>119</v>
       </c>
     </row>
     <row r="210" ht="20" customHeight="1">
@@ -6278,7 +6278,7 @@
         </is>
       </c>
       <c r="E210" s="20" t="n">
-        <v>221</v>
+        <v>177</v>
       </c>
     </row>
     <row r="211" ht="20" customHeight="1">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="E211" s="23" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="212" ht="20" customHeight="1">
@@ -6328,7 +6328,7 @@
         </is>
       </c>
       <c r="E212" s="20" t="n">
-        <v>156</v>
+        <v>178</v>
       </c>
     </row>
     <row r="213" ht="20" customHeight="1">
@@ -6353,7 +6353,7 @@
         </is>
       </c>
       <c r="E213" s="23" t="n">
-        <v>189</v>
+        <v>156</v>
       </c>
     </row>
     <row r="214" ht="20" customHeight="1">
@@ -6378,7 +6378,7 @@
         </is>
       </c>
       <c r="E214" s="20" t="n">
-        <v>240</v>
+        <v>159</v>
       </c>
     </row>
     <row r="215" ht="20" customHeight="1">
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="E215" s="23" t="n">
-        <v>145</v>
+        <v>236</v>
       </c>
     </row>
     <row r="216" ht="20" customHeight="1">
@@ -6428,7 +6428,7 @@
         </is>
       </c>
       <c r="E216" s="20" t="n">
-        <v>135</v>
+        <v>126</v>
       </c>
     </row>
     <row r="217" ht="20" customHeight="1">
@@ -6453,7 +6453,7 @@
         </is>
       </c>
       <c r="E217" s="23" t="n">
-        <v>216</v>
+        <v>144</v>
       </c>
     </row>
     <row r="218" ht="20" customHeight="1">
@@ -6478,7 +6478,7 @@
         </is>
       </c>
       <c r="E218" s="20" t="n">
-        <v>169</v>
+        <v>205</v>
       </c>
     </row>
     <row r="219" ht="20" customHeight="1">
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="E219" s="23" t="n">
-        <v>196</v>
+        <v>236</v>
       </c>
     </row>
     <row r="220" ht="20" customHeight="1">
@@ -6528,7 +6528,7 @@
         </is>
       </c>
       <c r="E220" s="20" t="n">
-        <v>227</v>
+        <v>194</v>
       </c>
     </row>
     <row r="221" ht="20" customHeight="1">
@@ -6553,7 +6553,7 @@
         </is>
       </c>
       <c r="E221" s="23" t="n">
-        <v>114</v>
+        <v>196</v>
       </c>
     </row>
     <row r="222" ht="20" customHeight="1">
@@ -6578,7 +6578,7 @@
         </is>
       </c>
       <c r="E222" s="20" t="n">
-        <v>175</v>
+        <v>114</v>
       </c>
     </row>
     <row r="223" ht="20" customHeight="1">
@@ -6603,7 +6603,7 @@
         </is>
       </c>
       <c r="E223" s="23" t="n">
-        <v>166</v>
+        <v>158</v>
       </c>
     </row>
     <row r="224" ht="20" customHeight="1">
@@ -6628,7 +6628,7 @@
         </is>
       </c>
       <c r="E224" s="20" t="n">
-        <v>173</v>
+        <v>179</v>
       </c>
     </row>
     <row r="225" ht="20" customHeight="1">
@@ -6653,7 +6653,7 @@
         </is>
       </c>
       <c r="E225" s="23" t="n">
-        <v>132</v>
+        <v>238</v>
       </c>
     </row>
     <row r="226" ht="20" customHeight="1">
@@ -6678,7 +6678,7 @@
         </is>
       </c>
       <c r="E226" s="20" t="n">
-        <v>191</v>
+        <v>130</v>
       </c>
     </row>
     <row r="227" ht="20" customHeight="1">
@@ -6703,7 +6703,7 @@
         </is>
       </c>
       <c r="E227" s="23" t="n">
-        <v>138</v>
+        <v>189</v>
       </c>
     </row>
     <row r="228" ht="20" customHeight="1">
@@ -6728,7 +6728,7 @@
         </is>
       </c>
       <c r="E228" s="20" t="n">
-        <v>172</v>
+        <v>187</v>
       </c>
     </row>
     <row r="229" ht="20" customHeight="1">
@@ -6753,7 +6753,7 @@
         </is>
       </c>
       <c r="E229" s="23" t="n">
-        <v>123</v>
+        <v>213</v>
       </c>
     </row>
     <row r="230" ht="20" customHeight="1">
@@ -6778,7 +6778,7 @@
         </is>
       </c>
       <c r="E230" s="20" t="n">
-        <v>181</v>
+        <v>121</v>
       </c>
     </row>
     <row r="231" ht="20" customHeight="1">
@@ -6803,7 +6803,7 @@
         </is>
       </c>
       <c r="E231" s="23" t="n">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="232" ht="20" customHeight="1">
@@ -6828,7 +6828,7 @@
         </is>
       </c>
       <c r="E232" s="20" t="n">
-        <v>222</v>
+        <v>121</v>
       </c>
     </row>
     <row r="233" ht="20" customHeight="1">
@@ -6853,7 +6853,7 @@
         </is>
       </c>
       <c r="E233" s="23" t="n">
-        <v>180</v>
+        <v>135</v>
       </c>
     </row>
     <row r="234" ht="20" customHeight="1">
@@ -6878,7 +6878,7 @@
         </is>
       </c>
       <c r="E234" s="20" t="n">
-        <v>138</v>
+        <v>235</v>
       </c>
     </row>
     <row r="235" ht="20" customHeight="1">
@@ -6903,7 +6903,7 @@
         </is>
       </c>
       <c r="E235" s="23" t="n">
-        <v>153</v>
+        <v>161</v>
       </c>
     </row>
     <row r="236" ht="20" customHeight="1">
@@ -6928,7 +6928,7 @@
         </is>
       </c>
       <c r="E236" s="20" t="n">
-        <v>206</v>
+        <v>143</v>
       </c>
     </row>
     <row r="237" ht="20" customHeight="1">
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="E237" s="23" t="n">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="238" ht="20" customHeight="1">
@@ -6978,7 +6978,7 @@
         </is>
       </c>
       <c r="E238" s="20" t="n">
-        <v>238</v>
+        <v>137</v>
       </c>
     </row>
     <row r="239" ht="20" customHeight="1">
@@ -7003,7 +7003,7 @@
         </is>
       </c>
       <c r="E239" s="23" t="n">
-        <v>232</v>
+        <v>163</v>
       </c>
     </row>
     <row r="240" ht="20" customHeight="1">
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="E241" s="23" t="n">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="242" ht="20" customHeight="1">
@@ -7078,7 +7078,7 @@
         </is>
       </c>
       <c r="E242" s="20" t="n">
-        <v>149</v>
+        <v>213</v>
       </c>
     </row>
     <row r="243" ht="20" customHeight="1">
@@ -7103,7 +7103,7 @@
         </is>
       </c>
       <c r="E243" s="23" t="n">
-        <v>159</v>
+        <v>173</v>
       </c>
     </row>
     <row r="244" ht="20" customHeight="1">
@@ -7128,7 +7128,7 @@
         </is>
       </c>
       <c r="E244" s="20" t="n">
-        <v>149</v>
+        <v>131</v>
       </c>
     </row>
     <row r="245" ht="20" customHeight="1">
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="E245" s="23" t="n">
-        <v>162</v>
+        <v>206</v>
       </c>
     </row>
     <row r="246" ht="20" customHeight="1">
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="E246" s="20" t="n">
-        <v>151</v>
+        <v>160</v>
       </c>
     </row>
     <row r="247" ht="20" customHeight="1">
@@ -7203,7 +7203,7 @@
         </is>
       </c>
       <c r="E247" s="23" t="n">
-        <v>173</v>
+        <v>238</v>
       </c>
     </row>
     <row r="248" ht="20" customHeight="1">
@@ -7228,7 +7228,7 @@
         </is>
       </c>
       <c r="E248" s="20" t="n">
-        <v>238</v>
+        <v>147</v>
       </c>
     </row>
     <row r="249" ht="20" customHeight="1">
@@ -7253,7 +7253,7 @@
         </is>
       </c>
       <c r="E249" s="23" t="n">
-        <v>212</v>
+        <v>230</v>
       </c>
     </row>
     <row r="250" ht="20" customHeight="1">
@@ -7278,7 +7278,7 @@
         </is>
       </c>
       <c r="E250" s="20" t="n">
-        <v>153</v>
+        <v>160</v>
       </c>
     </row>
     <row r="251" ht="20" customHeight="1">
@@ -7303,7 +7303,7 @@
         </is>
       </c>
       <c r="E251" s="23" t="n">
-        <v>157</v>
+        <v>227</v>
       </c>
     </row>
     <row r="252" ht="20" customHeight="1">
@@ -7328,7 +7328,7 @@
         </is>
       </c>
       <c r="E252" s="20" t="n">
-        <v>236</v>
+        <v>115</v>
       </c>
     </row>
     <row r="253" ht="20" customHeight="1">
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="E253" s="23" t="n">
-        <v>209</v>
+        <v>222</v>
       </c>
     </row>
     <row r="254" ht="20" customHeight="1">
@@ -7378,7 +7378,7 @@
         </is>
       </c>
       <c r="E254" s="20" t="n">
-        <v>153</v>
+        <v>173</v>
       </c>
     </row>
     <row r="255" ht="20" customHeight="1">
@@ -7403,7 +7403,7 @@
         </is>
       </c>
       <c r="E255" s="23" t="n">
-        <v>142</v>
+        <v>235</v>
       </c>
     </row>
     <row r="256" ht="20" customHeight="1">
@@ -7428,7 +7428,7 @@
         </is>
       </c>
       <c r="E256" s="20" t="n">
-        <v>146</v>
+        <v>132</v>
       </c>
     </row>
     <row r="257" ht="20" customHeight="1">
@@ -7453,7 +7453,7 @@
         </is>
       </c>
       <c r="E257" s="23" t="n">
-        <v>218</v>
+        <v>118</v>
       </c>
     </row>
     <row r="258" ht="20" customHeight="1">
@@ -7478,7 +7478,7 @@
         </is>
       </c>
       <c r="E258" s="20" t="n">
-        <v>148</v>
+        <v>192</v>
       </c>
     </row>
     <row r="259" ht="20" customHeight="1">
@@ -7503,7 +7503,7 @@
         </is>
       </c>
       <c r="E259" s="23" t="n">
-        <v>162</v>
+        <v>124</v>
       </c>
     </row>
     <row r="260" ht="20" customHeight="1">
@@ -7528,7 +7528,7 @@
         </is>
       </c>
       <c r="E260" s="20" t="n">
-        <v>202</v>
+        <v>175</v>
       </c>
     </row>
     <row r="261" ht="20" customHeight="1">
@@ -7553,7 +7553,7 @@
         </is>
       </c>
       <c r="E261" s="23" t="n">
-        <v>227</v>
+        <v>167</v>
       </c>
     </row>
     <row r="262" ht="20" customHeight="1">
@@ -7578,7 +7578,7 @@
         </is>
       </c>
       <c r="E262" s="20" t="n">
-        <v>152</v>
+        <v>143</v>
       </c>
     </row>
     <row r="263" ht="20" customHeight="1">
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="E263" s="23" t="n">
-        <v>197</v>
+        <v>221</v>
       </c>
     </row>
     <row r="264" ht="20" customHeight="1">
@@ -7628,7 +7628,7 @@
         </is>
       </c>
       <c r="E264" s="20" t="n">
-        <v>193</v>
+        <v>121</v>
       </c>
     </row>
     <row r="265" ht="20" customHeight="1">
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="E265" s="23" t="n">
-        <v>232</v>
+        <v>134</v>
       </c>
     </row>
     <row r="266" ht="20" customHeight="1">
@@ -7678,7 +7678,7 @@
         </is>
       </c>
       <c r="E266" s="20" t="n">
-        <v>130</v>
+        <v>164</v>
       </c>
     </row>
     <row r="267" ht="20" customHeight="1">
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="E267" s="23" t="n">
-        <v>240</v>
+        <v>220</v>
       </c>
     </row>
     <row r="268" ht="20" customHeight="1">
@@ -7728,7 +7728,7 @@
         </is>
       </c>
       <c r="E268" s="20" t="n">
-        <v>133</v>
+        <v>125</v>
       </c>
     </row>
     <row r="269" ht="20" customHeight="1">
@@ -7753,7 +7753,7 @@
         </is>
       </c>
       <c r="E269" s="23" t="n">
-        <v>194</v>
+        <v>185</v>
       </c>
     </row>
     <row r="270" ht="20" customHeight="1">
@@ -7778,7 +7778,7 @@
         </is>
       </c>
       <c r="E270" s="20" t="n">
-        <v>157</v>
+        <v>190</v>
       </c>
     </row>
     <row r="271" ht="20" customHeight="1">
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="E271" s="23" t="n">
-        <v>183</v>
+        <v>113</v>
       </c>
     </row>
     <row r="272" ht="20" customHeight="1">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="E272" s="20" t="n">
-        <v>144</v>
+        <v>154</v>
       </c>
     </row>
     <row r="273" ht="20" customHeight="1">
@@ -7853,7 +7853,7 @@
         </is>
       </c>
       <c r="E273" s="23" t="n">
-        <v>165</v>
+        <v>128</v>
       </c>
     </row>
     <row r="274" ht="20" customHeight="1">
@@ -7878,7 +7878,7 @@
         </is>
       </c>
       <c r="E274" s="20" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="275" ht="20" customHeight="1">
@@ -7903,7 +7903,7 @@
         </is>
       </c>
       <c r="E275" s="23" t="n">
-        <v>135</v>
+        <v>207</v>
       </c>
     </row>
     <row r="276" ht="20" customHeight="1">
@@ -7928,7 +7928,7 @@
         </is>
       </c>
       <c r="E276" s="20" t="n">
-        <v>168</v>
+        <v>189</v>
       </c>
     </row>
     <row r="277" ht="20" customHeight="1">
@@ -7953,7 +7953,7 @@
         </is>
       </c>
       <c r="E277" s="23" t="n">
-        <v>211</v>
+        <v>232</v>
       </c>
     </row>
     <row r="278" ht="20" customHeight="1">
@@ -7978,7 +7978,7 @@
         </is>
       </c>
       <c r="E278" s="20" t="n">
-        <v>170</v>
+        <v>200</v>
       </c>
     </row>
     <row r="279" ht="20" customHeight="1">
@@ -8003,7 +8003,7 @@
         </is>
       </c>
       <c r="E279" s="23" t="n">
-        <v>168</v>
+        <v>198</v>
       </c>
     </row>
     <row r="280" ht="20" customHeight="1">
@@ -8028,7 +8028,7 @@
         </is>
       </c>
       <c r="E280" s="20" t="n">
-        <v>217</v>
+        <v>116</v>
       </c>
     </row>
     <row r="281" ht="20" customHeight="1">
@@ -8053,7 +8053,7 @@
         </is>
       </c>
       <c r="E281" s="23" t="n">
-        <v>162</v>
+        <v>113</v>
       </c>
     </row>
     <row r="282" ht="20" customHeight="1">
@@ -8078,7 +8078,7 @@
         </is>
       </c>
       <c r="E282" s="20" t="n">
-        <v>118</v>
+        <v>181</v>
       </c>
     </row>
     <row r="283" ht="20" customHeight="1">
@@ -8103,7 +8103,7 @@
         </is>
       </c>
       <c r="E283" s="23" t="n">
-        <v>200</v>
+        <v>172</v>
       </c>
     </row>
     <row r="284" ht="20" customHeight="1">
@@ -8128,7 +8128,7 @@
         </is>
       </c>
       <c r="E284" s="20" t="n">
-        <v>208</v>
+        <v>189</v>
       </c>
     </row>
     <row r="285" ht="20" customHeight="1">
@@ -8153,7 +8153,7 @@
         </is>
       </c>
       <c r="E285" s="23" t="n">
-        <v>199</v>
+        <v>174</v>
       </c>
     </row>
     <row r="286" ht="20" customHeight="1">
@@ -8178,7 +8178,7 @@
         </is>
       </c>
       <c r="E286" s="20" t="n">
-        <v>171</v>
+        <v>126</v>
       </c>
     </row>
     <row r="287" ht="20" customHeight="1">
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="E287" s="23" t="n">
-        <v>229</v>
+        <v>239</v>
       </c>
     </row>
     <row r="288" ht="20" customHeight="1">
@@ -8228,7 +8228,7 @@
         </is>
       </c>
       <c r="E288" s="20" t="n">
-        <v>114</v>
+        <v>235</v>
       </c>
     </row>
     <row r="289" ht="20" customHeight="1">
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="E289" s="23" t="n">
-        <v>200</v>
+        <v>187</v>
       </c>
     </row>
     <row r="290" ht="20" customHeight="1">
@@ -8278,7 +8278,7 @@
         </is>
       </c>
       <c r="E290" s="20" t="n">
-        <v>196</v>
+        <v>166</v>
       </c>
     </row>
     <row r="291" ht="20" customHeight="1">
@@ -8303,7 +8303,7 @@
         </is>
       </c>
       <c r="E291" s="23" t="n">
-        <v>166</v>
+        <v>135</v>
       </c>
     </row>
     <row r="292" ht="20" customHeight="1">
@@ -8328,7 +8328,7 @@
         </is>
       </c>
       <c r="E292" s="20" t="n">
-        <v>175</v>
+        <v>229</v>
       </c>
     </row>
     <row r="293" ht="20" customHeight="1">
@@ -8353,7 +8353,7 @@
         </is>
       </c>
       <c r="E293" s="23" t="n">
-        <v>215</v>
+        <v>191</v>
       </c>
     </row>
     <row r="294" ht="20" customHeight="1">
@@ -8378,7 +8378,7 @@
         </is>
       </c>
       <c r="E294" s="20" t="n">
-        <v>214</v>
+        <v>142</v>
       </c>
     </row>
     <row r="295" ht="20" customHeight="1">
@@ -8403,7 +8403,7 @@
         </is>
       </c>
       <c r="E295" s="23" t="n">
-        <v>239</v>
+        <v>217</v>
       </c>
     </row>
     <row r="296" ht="20" customHeight="1">
@@ -8428,7 +8428,7 @@
         </is>
       </c>
       <c r="E296" s="20" t="n">
-        <v>145</v>
+        <v>181</v>
       </c>
     </row>
     <row r="297" ht="20" customHeight="1">
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="E297" s="23" t="n">
-        <v>193</v>
+        <v>120</v>
       </c>
     </row>
     <row r="298" ht="20" customHeight="1">
@@ -8478,7 +8478,7 @@
         </is>
       </c>
       <c r="E298" s="20" t="n">
-        <v>209</v>
+        <v>140</v>
       </c>
     </row>
     <row r="299" ht="20" customHeight="1">
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="E299" s="23" t="n">
-        <v>203</v>
+        <v>126</v>
       </c>
     </row>
     <row r="300" ht="20" customHeight="1">
@@ -8528,7 +8528,7 @@
         </is>
       </c>
       <c r="E300" s="20" t="n">
-        <v>111</v>
+        <v>208</v>
       </c>
     </row>
     <row r="301" ht="20" customHeight="1">
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="E302" s="20" t="n">
-        <v>237</v>
+        <v>210</v>
       </c>
     </row>
     <row r="303" ht="20" customHeight="1">
@@ -8603,7 +8603,7 @@
         </is>
       </c>
       <c r="E303" s="23" t="n">
-        <v>164</v>
+        <v>128</v>
       </c>
     </row>
     <row r="304" ht="20" customHeight="1">
@@ -8628,7 +8628,7 @@
         </is>
       </c>
       <c r="E304" s="20" t="n">
-        <v>235</v>
+        <v>168</v>
       </c>
     </row>
     <row r="305" ht="20" customHeight="1">
@@ -8653,7 +8653,7 @@
         </is>
       </c>
       <c r="E305" s="23" t="n">
-        <v>119</v>
+        <v>110</v>
       </c>
     </row>
     <row r="306" ht="20" customHeight="1">
@@ -8678,7 +8678,7 @@
         </is>
       </c>
       <c r="E306" s="20" t="n">
-        <v>123</v>
+        <v>221</v>
       </c>
     </row>
     <row r="307" ht="20" customHeight="1">
@@ -8703,7 +8703,7 @@
         </is>
       </c>
       <c r="E307" s="23" t="n">
-        <v>192</v>
+        <v>137</v>
       </c>
     </row>
     <row r="308" ht="20" customHeight="1">
@@ -8728,7 +8728,7 @@
         </is>
       </c>
       <c r="E308" s="20" t="n">
-        <v>188</v>
+        <v>239</v>
       </c>
     </row>
     <row r="309" ht="20" customHeight="1">
@@ -8753,7 +8753,7 @@
         </is>
       </c>
       <c r="E309" s="23" t="n">
-        <v>182</v>
+        <v>119</v>
       </c>
     </row>
     <row r="310" ht="20" customHeight="1">
@@ -8778,7 +8778,7 @@
         </is>
       </c>
       <c r="E310" s="20" t="n">
-        <v>227</v>
+        <v>183</v>
       </c>
     </row>
     <row r="311" ht="20" customHeight="1">
@@ -8803,7 +8803,7 @@
         </is>
       </c>
       <c r="E311" s="23" t="n">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="312" ht="20" customHeight="1">
@@ -8828,7 +8828,7 @@
         </is>
       </c>
       <c r="E312" s="20" t="n">
-        <v>115</v>
+        <v>202</v>
       </c>
     </row>
     <row r="313" ht="20" customHeight="1">
@@ -8853,7 +8853,7 @@
         </is>
       </c>
       <c r="E313" s="23" t="n">
-        <v>133</v>
+        <v>120</v>
       </c>
     </row>
     <row r="314" ht="20" customHeight="1">
@@ -8878,7 +8878,7 @@
         </is>
       </c>
       <c r="E314" s="20" t="n">
-        <v>135</v>
+        <v>181</v>
       </c>
     </row>
     <row r="315" ht="20" customHeight="1">
@@ -8903,7 +8903,7 @@
         </is>
       </c>
       <c r="E315" s="23" t="n">
-        <v>203</v>
+        <v>130</v>
       </c>
     </row>
     <row r="316" ht="20" customHeight="1">
@@ -8928,7 +8928,7 @@
         </is>
       </c>
       <c r="E316" s="20" t="n">
-        <v>118</v>
+        <v>186</v>
       </c>
     </row>
     <row r="317" ht="20" customHeight="1">
@@ -8953,7 +8953,7 @@
         </is>
       </c>
       <c r="E317" s="23" t="n">
-        <v>171</v>
+        <v>136</v>
       </c>
     </row>
     <row r="318" ht="20" customHeight="1">
@@ -8978,7 +8978,7 @@
         </is>
       </c>
       <c r="E318" s="20" t="n">
-        <v>179</v>
+        <v>187</v>
       </c>
     </row>
     <row r="319" ht="20" customHeight="1">
@@ -9003,7 +9003,7 @@
         </is>
       </c>
       <c r="E319" s="23" t="n">
-        <v>145</v>
+        <v>122</v>
       </c>
     </row>
     <row r="320" ht="20" customHeight="1">
@@ -9028,7 +9028,7 @@
         </is>
       </c>
       <c r="E320" s="20" t="n">
-        <v>165</v>
+        <v>191</v>
       </c>
     </row>
     <row r="321" ht="20" customHeight="1">
@@ -9053,7 +9053,7 @@
         </is>
       </c>
       <c r="E321" s="23" t="n">
-        <v>132</v>
+        <v>171</v>
       </c>
     </row>
     <row r="322" ht="20" customHeight="1">
@@ -9078,7 +9078,7 @@
         </is>
       </c>
       <c r="E322" s="20" t="n">
-        <v>236</v>
+        <v>184</v>
       </c>
     </row>
     <row r="323" ht="20" customHeight="1">
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="E323" s="23" t="n">
-        <v>231</v>
+        <v>178</v>
       </c>
     </row>
     <row r="324" ht="20" customHeight="1">
@@ -9128,7 +9128,7 @@
         </is>
       </c>
       <c r="E324" s="20" t="n">
-        <v>160</v>
+        <v>207</v>
       </c>
     </row>
     <row r="325" ht="20" customHeight="1">
@@ -9153,7 +9153,7 @@
         </is>
       </c>
       <c r="E325" s="23" t="n">
-        <v>227</v>
+        <v>238</v>
       </c>
     </row>
     <row r="326" ht="20" customHeight="1">
@@ -9178,7 +9178,7 @@
         </is>
       </c>
       <c r="E326" s="20" t="n">
-        <v>154</v>
+        <v>231</v>
       </c>
     </row>
     <row r="327" ht="20" customHeight="1">
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="E327" s="23" t="n">
-        <v>165</v>
+        <v>178</v>
       </c>
     </row>
     <row r="328" ht="20" customHeight="1">
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="E328" s="20" t="n">
-        <v>186</v>
+        <v>143</v>
       </c>
     </row>
     <row r="329" ht="20" customHeight="1">
@@ -9253,7 +9253,7 @@
         </is>
       </c>
       <c r="E329" s="23" t="n">
-        <v>123</v>
+        <v>164</v>
       </c>
     </row>
     <row r="330" ht="20" customHeight="1">
@@ -9278,7 +9278,7 @@
         </is>
       </c>
       <c r="E330" s="20" t="n">
-        <v>159</v>
+        <v>149</v>
       </c>
     </row>
     <row r="331" ht="20" customHeight="1">
@@ -9303,7 +9303,7 @@
         </is>
       </c>
       <c r="E331" s="23" t="n">
-        <v>172</v>
+        <v>123</v>
       </c>
     </row>
     <row r="332" ht="20" customHeight="1">
@@ -9328,7 +9328,7 @@
         </is>
       </c>
       <c r="E332" s="20" t="n">
-        <v>135</v>
+        <v>120</v>
       </c>
     </row>
     <row r="333" ht="20" customHeight="1">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="E333" s="23" t="n">
-        <v>220</v>
+        <v>165</v>
       </c>
     </row>
     <row r="334" ht="20" customHeight="1">
@@ -9378,7 +9378,7 @@
         </is>
       </c>
       <c r="E334" s="20" t="n">
-        <v>233</v>
+        <v>240</v>
       </c>
     </row>
     <row r="335" ht="20" customHeight="1">
@@ -9403,7 +9403,7 @@
         </is>
       </c>
       <c r="E335" s="23" t="n">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="336" ht="20" customHeight="1">
@@ -9428,7 +9428,7 @@
         </is>
       </c>
       <c r="E336" s="20" t="n">
-        <v>190</v>
+        <v>195</v>
       </c>
     </row>
     <row r="337" ht="20" customHeight="1">
@@ -9453,7 +9453,7 @@
         </is>
       </c>
       <c r="E337" s="23" t="n">
-        <v>211</v>
+        <v>112</v>
       </c>
     </row>
     <row r="338" ht="20" customHeight="1">
@@ -9478,7 +9478,7 @@
         </is>
       </c>
       <c r="E338" s="20" t="n">
-        <v>116</v>
+        <v>126</v>
       </c>
     </row>
     <row r="339" ht="20" customHeight="1">
@@ -9503,7 +9503,7 @@
         </is>
       </c>
       <c r="E339" s="23" t="n">
-        <v>182</v>
+        <v>214</v>
       </c>
     </row>
     <row r="340" ht="20" customHeight="1">
@@ -9528,7 +9528,7 @@
         </is>
       </c>
       <c r="E340" s="20" t="n">
-        <v>202</v>
+        <v>206</v>
       </c>
     </row>
     <row r="341" ht="20" customHeight="1">
@@ -9553,7 +9553,7 @@
         </is>
       </c>
       <c r="E341" s="23" t="n">
-        <v>240</v>
+        <v>213</v>
       </c>
     </row>
     <row r="342" ht="20" customHeight="1">
@@ -9578,7 +9578,7 @@
         </is>
       </c>
       <c r="E342" s="20" t="n">
-        <v>134</v>
+        <v>127</v>
       </c>
     </row>
     <row r="343" ht="20" customHeight="1">
@@ -9603,7 +9603,7 @@
         </is>
       </c>
       <c r="E343" s="23" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="344" ht="20" customHeight="1">
@@ -9628,7 +9628,7 @@
         </is>
       </c>
       <c r="E344" s="20" t="n">
-        <v>193</v>
+        <v>119</v>
       </c>
     </row>
     <row r="345" ht="20" customHeight="1">
@@ -9653,7 +9653,7 @@
         </is>
       </c>
       <c r="E345" s="23" t="n">
-        <v>200</v>
+        <v>163</v>
       </c>
     </row>
     <row r="346" ht="20" customHeight="1">
@@ -9678,7 +9678,7 @@
         </is>
       </c>
       <c r="E346" s="20" t="n">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="347" ht="20" customHeight="1">
@@ -9703,7 +9703,7 @@
         </is>
       </c>
       <c r="E347" s="23" t="n">
-        <v>155</v>
+        <v>136</v>
       </c>
     </row>
     <row r="348" ht="20" customHeight="1">
@@ -9728,7 +9728,7 @@
         </is>
       </c>
       <c r="E348" s="20" t="n">
-        <v>144</v>
+        <v>160</v>
       </c>
     </row>
     <row r="349" ht="20" customHeight="1">
@@ -9753,7 +9753,7 @@
         </is>
       </c>
       <c r="E349" s="23" t="n">
-        <v>132</v>
+        <v>206</v>
       </c>
     </row>
     <row r="350" ht="20" customHeight="1">
@@ -9778,7 +9778,7 @@
         </is>
       </c>
       <c r="E350" s="20" t="n">
-        <v>209</v>
+        <v>173</v>
       </c>
     </row>
     <row r="351" ht="20" customHeight="1">
@@ -9803,7 +9803,7 @@
         </is>
       </c>
       <c r="E351" s="23" t="n">
-        <v>166</v>
+        <v>232</v>
       </c>
     </row>
     <row r="352" ht="20" customHeight="1">
@@ -9828,7 +9828,7 @@
         </is>
       </c>
       <c r="E352" s="20" t="n">
-        <v>211</v>
+        <v>191</v>
       </c>
     </row>
     <row r="353" ht="20" customHeight="1">
@@ -9853,7 +9853,7 @@
         </is>
       </c>
       <c r="E353" s="23" t="n">
-        <v>167</v>
+        <v>125</v>
       </c>
     </row>
     <row r="354" ht="20" customHeight="1">
@@ -9878,7 +9878,7 @@
         </is>
       </c>
       <c r="E354" s="20" t="n">
-        <v>204</v>
+        <v>167</v>
       </c>
     </row>
     <row r="355" ht="20" customHeight="1">
@@ -9903,7 +9903,7 @@
         </is>
       </c>
       <c r="E355" s="23" t="n">
-        <v>152</v>
+        <v>176</v>
       </c>
     </row>
     <row r="356" ht="20" customHeight="1">
@@ -9928,7 +9928,7 @@
         </is>
       </c>
       <c r="E356" s="20" t="n">
-        <v>225</v>
+        <v>199</v>
       </c>
     </row>
     <row r="357" ht="20" customHeight="1">
@@ -9953,7 +9953,7 @@
         </is>
       </c>
       <c r="E357" s="23" t="n">
-        <v>224</v>
+        <v>182</v>
       </c>
     </row>
     <row r="358" ht="20" customHeight="1">
@@ -9978,7 +9978,7 @@
         </is>
       </c>
       <c r="E358" s="20" t="n">
-        <v>134</v>
+        <v>186</v>
       </c>
     </row>
     <row r="359" ht="20" customHeight="1">
@@ -10003,7 +10003,7 @@
         </is>
       </c>
       <c r="E359" s="23" t="n">
-        <v>184</v>
+        <v>209</v>
       </c>
     </row>
     <row r="360" ht="20" customHeight="1">
@@ -10028,7 +10028,7 @@
         </is>
       </c>
       <c r="E360" s="20" t="n">
-        <v>165</v>
+        <v>226</v>
       </c>
     </row>
     <row r="361" ht="20" customHeight="1">
@@ -10053,7 +10053,7 @@
         </is>
       </c>
       <c r="E361" s="23" t="n">
-        <v>190</v>
+        <v>197</v>
       </c>
     </row>
     <row r="362" ht="20" customHeight="1">
@@ -10078,7 +10078,7 @@
         </is>
       </c>
       <c r="E362" s="20" t="n">
-        <v>194</v>
+        <v>112</v>
       </c>
     </row>
     <row r="363" ht="20" customHeight="1">
@@ -10103,7 +10103,7 @@
         </is>
       </c>
       <c r="E363" s="23" t="n">
-        <v>226</v>
+        <v>233</v>
       </c>
     </row>
     <row r="364" ht="20" customHeight="1">
@@ -10128,7 +10128,7 @@
         </is>
       </c>
       <c r="E364" s="20" t="n">
-        <v>233</v>
+        <v>201</v>
       </c>
     </row>
     <row r="365" ht="20" customHeight="1">
@@ -10153,7 +10153,7 @@
         </is>
       </c>
       <c r="E365" s="23" t="n">
-        <v>114</v>
+        <v>194</v>
       </c>
     </row>
     <row r="366" ht="20" customHeight="1">
@@ -10178,7 +10178,7 @@
         </is>
       </c>
       <c r="E366" s="20" t="n">
-        <v>172</v>
+        <v>143</v>
       </c>
     </row>
     <row r="367" ht="20" customHeight="1">
@@ -10203,7 +10203,7 @@
         </is>
       </c>
       <c r="E367" s="23" t="n">
-        <v>173</v>
+        <v>125</v>
       </c>
     </row>
     <row r="368" ht="20" customHeight="1">
@@ -10228,7 +10228,7 @@
         </is>
       </c>
       <c r="E368" s="20" t="n">
-        <v>181</v>
+        <v>169</v>
       </c>
     </row>
     <row r="369" ht="20" customHeight="1">
@@ -10253,7 +10253,7 @@
         </is>
       </c>
       <c r="E369" s="23" t="n">
-        <v>179</v>
+        <v>191</v>
       </c>
     </row>
     <row r="370" ht="20" customHeight="1">
@@ -10278,7 +10278,7 @@
         </is>
       </c>
       <c r="E370" s="20" t="n">
-        <v>204</v>
+        <v>162</v>
       </c>
     </row>
     <row r="371" ht="20" customHeight="1">
@@ -10303,7 +10303,7 @@
         </is>
       </c>
       <c r="E371" s="23" t="n">
-        <v>187</v>
+        <v>116</v>
       </c>
     </row>
     <row r="372" ht="20" customHeight="1">
@@ -10328,7 +10328,7 @@
         </is>
       </c>
       <c r="E372" s="20" t="n">
-        <v>217</v>
+        <v>228</v>
       </c>
     </row>
     <row r="373" ht="20" customHeight="1">
@@ -10353,7 +10353,7 @@
         </is>
       </c>
       <c r="E373" s="23" t="n">
-        <v>129</v>
+        <v>228</v>
       </c>
     </row>
     <row r="374" ht="20" customHeight="1">
@@ -10378,7 +10378,7 @@
         </is>
       </c>
       <c r="E374" s="20" t="n">
-        <v>234</v>
+        <v>224</v>
       </c>
     </row>
     <row r="375" ht="20" customHeight="1">
@@ -10403,7 +10403,7 @@
         </is>
       </c>
       <c r="E375" s="23" t="n">
-        <v>126</v>
+        <v>222</v>
       </c>
     </row>
     <row r="376" ht="20" customHeight="1">
@@ -10428,7 +10428,7 @@
         </is>
       </c>
       <c r="E376" s="20" t="n">
-        <v>210</v>
+        <v>188</v>
       </c>
     </row>
     <row r="377" ht="20" customHeight="1">
@@ -10453,7 +10453,7 @@
         </is>
       </c>
       <c r="E377" s="23" t="n">
-        <v>204</v>
+        <v>238</v>
       </c>
     </row>
     <row r="378" ht="20" customHeight="1">
@@ -10478,7 +10478,7 @@
         </is>
       </c>
       <c r="E378" s="20" t="n">
-        <v>123</v>
+        <v>166</v>
       </c>
     </row>
     <row r="379" ht="20" customHeight="1">
@@ -10503,7 +10503,7 @@
         </is>
       </c>
       <c r="E379" s="23" t="n">
-        <v>159</v>
+        <v>186</v>
       </c>
     </row>
     <row r="380" ht="20" customHeight="1">
@@ -10528,7 +10528,7 @@
         </is>
       </c>
       <c r="E380" s="20" t="n">
-        <v>188</v>
+        <v>218</v>
       </c>
     </row>
     <row r="381" ht="20" customHeight="1">
@@ -10553,7 +10553,7 @@
         </is>
       </c>
       <c r="E381" s="23" t="n">
-        <v>210</v>
+        <v>184</v>
       </c>
     </row>
     <row r="382" ht="20" customHeight="1">
@@ -10578,7 +10578,7 @@
         </is>
       </c>
       <c r="E382" s="20" t="n">
-        <v>203</v>
+        <v>225</v>
       </c>
     </row>
     <row r="383" ht="20" customHeight="1">
@@ -10603,7 +10603,7 @@
         </is>
       </c>
       <c r="E383" s="23" t="n">
-        <v>227</v>
+        <v>161</v>
       </c>
     </row>
     <row r="384" ht="20" customHeight="1">
@@ -10628,7 +10628,7 @@
         </is>
       </c>
       <c r="E384" s="20" t="n">
-        <v>190</v>
+        <v>161</v>
       </c>
     </row>
     <row r="385" ht="20" customHeight="1">
@@ -10653,7 +10653,7 @@
         </is>
       </c>
       <c r="E385" s="23" t="n">
-        <v>177</v>
+        <v>220</v>
       </c>
     </row>
     <row r="386" ht="20" customHeight="1">
@@ -10678,7 +10678,7 @@
         </is>
       </c>
       <c r="E386" s="20" t="n">
-        <v>182</v>
+        <v>117</v>
       </c>
     </row>
     <row r="387" ht="20" customHeight="1">
@@ -10703,7 +10703,7 @@
         </is>
       </c>
       <c r="E387" s="23" t="n">
-        <v>235</v>
+        <v>231</v>
       </c>
     </row>
     <row r="388" ht="20" customHeight="1">
@@ -10728,7 +10728,7 @@
         </is>
       </c>
       <c r="E388" s="20" t="n">
-        <v>152</v>
+        <v>197</v>
       </c>
     </row>
     <row r="389" ht="20" customHeight="1">
@@ -10753,7 +10753,7 @@
         </is>
       </c>
       <c r="E389" s="23" t="n">
-        <v>185</v>
+        <v>221</v>
       </c>
     </row>
     <row r="390" ht="20" customHeight="1">
@@ -10778,7 +10778,7 @@
         </is>
       </c>
       <c r="E390" s="20" t="n">
-        <v>139</v>
+        <v>230</v>
       </c>
     </row>
     <row r="391" ht="20" customHeight="1">
@@ -10803,7 +10803,7 @@
         </is>
       </c>
       <c r="E391" s="23" t="n">
-        <v>239</v>
+        <v>133</v>
       </c>
     </row>
     <row r="392" ht="20" customHeight="1">
@@ -10828,7 +10828,7 @@
         </is>
       </c>
       <c r="E392" s="20" t="n">
-        <v>183</v>
+        <v>222</v>
       </c>
     </row>
     <row r="393" ht="20" customHeight="1">
@@ -10853,7 +10853,7 @@
         </is>
       </c>
       <c r="E393" s="23" t="n">
-        <v>216</v>
+        <v>126</v>
       </c>
     </row>
     <row r="394" ht="20" customHeight="1">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="E394" s="20" t="n">
-        <v>135</v>
+        <v>212</v>
       </c>
     </row>
     <row r="395" ht="20" customHeight="1">
@@ -10903,7 +10903,7 @@
         </is>
       </c>
       <c r="E395" s="23" t="n">
-        <v>139</v>
+        <v>207</v>
       </c>
     </row>
     <row r="396" ht="20" customHeight="1">
@@ -10928,7 +10928,7 @@
         </is>
       </c>
       <c r="E396" s="20" t="n">
-        <v>173</v>
+        <v>164</v>
       </c>
     </row>
     <row r="397" ht="20" customHeight="1">
@@ -10953,7 +10953,7 @@
         </is>
       </c>
       <c r="E397" s="23" t="n">
-        <v>117</v>
+        <v>225</v>
       </c>
     </row>
     <row r="398" ht="20" customHeight="1">
@@ -10978,7 +10978,7 @@
         </is>
       </c>
       <c r="E398" s="20" t="n">
-        <v>169</v>
+        <v>149</v>
       </c>
     </row>
     <row r="399" ht="20" customHeight="1">
@@ -11003,7 +11003,7 @@
         </is>
       </c>
       <c r="E399" s="23" t="n">
-        <v>171</v>
+        <v>196</v>
       </c>
     </row>
     <row r="400" ht="20" customHeight="1">
@@ -11028,7 +11028,7 @@
         </is>
       </c>
       <c r="E400" s="20" t="n">
-        <v>205</v>
+        <v>216</v>
       </c>
     </row>
     <row r="401" ht="20" customHeight="1">
@@ -11053,7 +11053,7 @@
         </is>
       </c>
       <c r="E401" s="23" t="n">
-        <v>151</v>
+        <v>208</v>
       </c>
     </row>
     <row r="402" ht="20" customHeight="1">
@@ -11078,7 +11078,7 @@
         </is>
       </c>
       <c r="E402" s="20" t="n">
-        <v>155</v>
+        <v>165</v>
       </c>
     </row>
     <row r="403" ht="20" customHeight="1">
@@ -11103,7 +11103,7 @@
         </is>
       </c>
       <c r="E403" s="23" t="n">
-        <v>229</v>
+        <v>208</v>
       </c>
     </row>
     <row r="404" ht="20" customHeight="1">
@@ -11128,7 +11128,7 @@
         </is>
       </c>
       <c r="E404" s="20" t="n">
-        <v>213</v>
+        <v>141</v>
       </c>
     </row>
     <row r="405" ht="20" customHeight="1">
@@ -11153,7 +11153,7 @@
         </is>
       </c>
       <c r="E405" s="23" t="n">
-        <v>217</v>
+        <v>124</v>
       </c>
     </row>
     <row r="406" ht="20" customHeight="1">
@@ -11178,7 +11178,7 @@
         </is>
       </c>
       <c r="E406" s="20" t="n">
-        <v>197</v>
+        <v>185</v>
       </c>
     </row>
     <row r="407" ht="20" customHeight="1">
@@ -11203,7 +11203,7 @@
         </is>
       </c>
       <c r="E407" s="23" t="n">
-        <v>219</v>
+        <v>239</v>
       </c>
     </row>
     <row r="408" ht="20" customHeight="1">
@@ -11228,7 +11228,7 @@
         </is>
       </c>
       <c r="E408" s="20" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="409" ht="20" customHeight="1">
@@ -11253,7 +11253,7 @@
         </is>
       </c>
       <c r="E409" s="23" t="n">
-        <v>201</v>
+        <v>183</v>
       </c>
     </row>
     <row r="410" ht="20" customHeight="1">
@@ -11278,7 +11278,7 @@
         </is>
       </c>
       <c r="E410" s="20" t="n">
-        <v>157</v>
+        <v>112</v>
       </c>
     </row>
     <row r="411" ht="20" customHeight="1">
@@ -11303,7 +11303,7 @@
         </is>
       </c>
       <c r="E411" s="23" t="n">
-        <v>155</v>
+        <v>138</v>
       </c>
     </row>
     <row r="412" ht="20" customHeight="1">
@@ -11328,7 +11328,7 @@
         </is>
       </c>
       <c r="E412" s="20" t="n">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="413" ht="20" customHeight="1">
@@ -11353,7 +11353,7 @@
         </is>
       </c>
       <c r="E413" s="23" t="n">
-        <v>124</v>
+        <v>207</v>
       </c>
     </row>
     <row r="414" ht="20" customHeight="1">
@@ -11378,7 +11378,7 @@
         </is>
       </c>
       <c r="E414" s="20" t="n">
-        <v>118</v>
+        <v>198</v>
       </c>
     </row>
     <row r="415" ht="20" customHeight="1">
@@ -11403,7 +11403,7 @@
         </is>
       </c>
       <c r="E415" s="23" t="n">
-        <v>207</v>
+        <v>192</v>
       </c>
     </row>
     <row r="416" ht="20" customHeight="1">
@@ -11428,7 +11428,7 @@
         </is>
       </c>
       <c r="E416" s="20" t="n">
-        <v>134</v>
+        <v>198</v>
       </c>
     </row>
     <row r="417" ht="20" customHeight="1">
@@ -11453,7 +11453,7 @@
         </is>
       </c>
       <c r="E417" s="23" t="n">
-        <v>207</v>
+        <v>144</v>
       </c>
     </row>
     <row r="418" ht="20" customHeight="1">
@@ -11478,7 +11478,7 @@
         </is>
       </c>
       <c r="E418" s="20" t="n">
-        <v>132</v>
+        <v>164</v>
       </c>
     </row>
     <row r="419" ht="20" customHeight="1">
@@ -11503,7 +11503,7 @@
         </is>
       </c>
       <c r="E419" s="23" t="n">
-        <v>214</v>
+        <v>125</v>
       </c>
     </row>
     <row r="420" ht="20" customHeight="1">
@@ -11528,7 +11528,7 @@
         </is>
       </c>
       <c r="E420" s="20" t="n">
-        <v>213</v>
+        <v>198</v>
       </c>
     </row>
     <row r="421" ht="20" customHeight="1">
@@ -11553,7 +11553,7 @@
         </is>
       </c>
       <c r="E421" s="23" t="n">
-        <v>135</v>
+        <v>237</v>
       </c>
     </row>
     <row r="422" ht="20" customHeight="1">
@@ -11578,7 +11578,7 @@
         </is>
       </c>
       <c r="E422" s="20" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="423" ht="20" customHeight="1">
@@ -11603,7 +11603,7 @@
         </is>
       </c>
       <c r="E423" s="23" t="n">
-        <v>219</v>
+        <v>230</v>
       </c>
     </row>
     <row r="424" ht="20" customHeight="1">
@@ -11628,7 +11628,7 @@
         </is>
       </c>
       <c r="E424" s="20" t="n">
-        <v>204</v>
+        <v>218</v>
       </c>
     </row>
     <row r="425" ht="20" customHeight="1">
@@ -11653,7 +11653,7 @@
         </is>
       </c>
       <c r="E425" s="23" t="n">
-        <v>216</v>
+        <v>139</v>
       </c>
     </row>
     <row r="426" ht="20" customHeight="1">
@@ -11678,7 +11678,7 @@
         </is>
       </c>
       <c r="E426" s="20" t="n">
-        <v>137</v>
+        <v>158</v>
       </c>
     </row>
     <row r="427" ht="20" customHeight="1">
@@ -11703,7 +11703,7 @@
         </is>
       </c>
       <c r="E427" s="23" t="n">
-        <v>135</v>
+        <v>146</v>
       </c>
     </row>
     <row r="428" ht="20" customHeight="1">
@@ -11728,7 +11728,7 @@
         </is>
       </c>
       <c r="E428" s="20" t="n">
-        <v>235</v>
+        <v>120</v>
       </c>
     </row>
     <row r="429" ht="20" customHeight="1">
@@ -11753,7 +11753,7 @@
         </is>
       </c>
       <c r="E429" s="23" t="n">
-        <v>114</v>
+        <v>225</v>
       </c>
     </row>
     <row r="430" ht="20" customHeight="1">
@@ -11778,7 +11778,7 @@
         </is>
       </c>
       <c r="E430" s="20" t="n">
-        <v>206</v>
+        <v>157</v>
       </c>
     </row>
     <row r="431" ht="20" customHeight="1">
@@ -11803,7 +11803,7 @@
         </is>
       </c>
       <c r="E431" s="23" t="n">
-        <v>141</v>
+        <v>230</v>
       </c>
     </row>
     <row r="432" ht="20" customHeight="1">
@@ -11828,7 +11828,7 @@
         </is>
       </c>
       <c r="E432" s="20" t="n">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="433" ht="20" customHeight="1">
@@ -11853,7 +11853,7 @@
         </is>
       </c>
       <c r="E433" s="23" t="n">
-        <v>233</v>
+        <v>217</v>
       </c>
     </row>
     <row r="434" ht="20" customHeight="1">
@@ -11878,7 +11878,7 @@
         </is>
       </c>
       <c r="E434" s="20" t="n">
-        <v>128</v>
+        <v>166</v>
       </c>
     </row>
     <row r="435" ht="20" customHeight="1">
@@ -11903,7 +11903,7 @@
         </is>
       </c>
       <c r="E435" s="23" t="n">
-        <v>215</v>
+        <v>133</v>
       </c>
     </row>
     <row r="436" ht="20" customHeight="1">
@@ -11928,7 +11928,7 @@
         </is>
       </c>
       <c r="E436" s="20" t="n">
-        <v>154</v>
+        <v>118</v>
       </c>
     </row>
     <row r="437" ht="20" customHeight="1">
@@ -11953,7 +11953,7 @@
         </is>
       </c>
       <c r="E437" s="23" t="n">
-        <v>168</v>
+        <v>156</v>
       </c>
     </row>
     <row r="438" ht="20" customHeight="1">
@@ -11978,7 +11978,7 @@
         </is>
       </c>
       <c r="E438" s="20" t="n">
-        <v>173</v>
+        <v>238</v>
       </c>
     </row>
     <row r="439" ht="20" customHeight="1">
@@ -12003,7 +12003,7 @@
         </is>
       </c>
       <c r="E439" s="23" t="n">
-        <v>144</v>
+        <v>239</v>
       </c>
     </row>
     <row r="440" ht="20" customHeight="1">
@@ -12028,7 +12028,7 @@
         </is>
       </c>
       <c r="E440" s="20" t="n">
-        <v>146</v>
+        <v>200</v>
       </c>
     </row>
     <row r="441" ht="20" customHeight="1">
@@ -12053,7 +12053,7 @@
         </is>
       </c>
       <c r="E441" s="23" t="n">
-        <v>223</v>
+        <v>125</v>
       </c>
     </row>
     <row r="442" ht="20" customHeight="1">
@@ -12078,7 +12078,7 @@
         </is>
       </c>
       <c r="E442" s="20" t="n">
-        <v>186</v>
+        <v>225</v>
       </c>
     </row>
     <row r="443" ht="20" customHeight="1">
@@ -12103,7 +12103,7 @@
         </is>
       </c>
       <c r="E443" s="23" t="n">
-        <v>222</v>
+        <v>110</v>
       </c>
     </row>
     <row r="444" ht="20" customHeight="1">
@@ -12128,7 +12128,7 @@
         </is>
       </c>
       <c r="E444" s="20" t="n">
-        <v>208</v>
+        <v>123</v>
       </c>
     </row>
     <row r="445" ht="20" customHeight="1">
@@ -12153,7 +12153,7 @@
         </is>
       </c>
       <c r="E445" s="23" t="n">
-        <v>141</v>
+        <v>206</v>
       </c>
     </row>
     <row r="446" ht="20" customHeight="1">
@@ -12178,7 +12178,7 @@
         </is>
       </c>
       <c r="E446" s="20" t="n">
-        <v>123</v>
+        <v>175</v>
       </c>
     </row>
     <row r="447" ht="20" customHeight="1">
@@ -12203,7 +12203,7 @@
         </is>
       </c>
       <c r="E447" s="23" t="n">
-        <v>190</v>
+        <v>204</v>
       </c>
     </row>
     <row r="448" ht="20" customHeight="1">
@@ -12228,7 +12228,7 @@
         </is>
       </c>
       <c r="E448" s="20" t="n">
-        <v>227</v>
+        <v>195</v>
       </c>
     </row>
     <row r="449" ht="20" customHeight="1">
@@ -12253,7 +12253,7 @@
         </is>
       </c>
       <c r="E449" s="23" t="n">
-        <v>194</v>
+        <v>137</v>
       </c>
     </row>
     <row r="450" ht="20" customHeight="1">
@@ -12278,7 +12278,7 @@
         </is>
       </c>
       <c r="E450" s="20" t="n">
-        <v>199</v>
+        <v>150</v>
       </c>
     </row>
     <row r="451" ht="20" customHeight="1">
@@ -12303,7 +12303,7 @@
         </is>
       </c>
       <c r="E451" s="23" t="n">
-        <v>173</v>
+        <v>219</v>
       </c>
     </row>
     <row r="452" ht="20" customHeight="1">
@@ -12328,7 +12328,7 @@
         </is>
       </c>
       <c r="E452" s="20" t="n">
-        <v>189</v>
+        <v>179</v>
       </c>
     </row>
     <row r="453" ht="20" customHeight="1">
@@ -12353,7 +12353,7 @@
         </is>
       </c>
       <c r="E453" s="23" t="n">
-        <v>210</v>
+        <v>153</v>
       </c>
     </row>
     <row r="454" ht="20" customHeight="1">
@@ -12378,7 +12378,7 @@
         </is>
       </c>
       <c r="E454" s="20" t="n">
-        <v>227</v>
+        <v>156</v>
       </c>
     </row>
     <row r="455" ht="20" customHeight="1">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="E455" s="23" t="n">
-        <v>162</v>
+        <v>213</v>
       </c>
     </row>
     <row r="456" ht="20" customHeight="1">
@@ -12428,7 +12428,7 @@
         </is>
       </c>
       <c r="E456" s="20" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="457" ht="20" customHeight="1">
@@ -12453,7 +12453,7 @@
         </is>
       </c>
       <c r="E457" s="23" t="n">
-        <v>177</v>
+        <v>190</v>
       </c>
     </row>
     <row r="458" ht="20" customHeight="1">
@@ -12478,7 +12478,7 @@
         </is>
       </c>
       <c r="E458" s="20" t="n">
-        <v>211</v>
+        <v>226</v>
       </c>
     </row>
     <row r="459" ht="20" customHeight="1">
@@ -12503,7 +12503,7 @@
         </is>
       </c>
       <c r="E459" s="23" t="n">
-        <v>224</v>
+        <v>174</v>
       </c>
     </row>
     <row r="460" ht="20" customHeight="1">
@@ -12528,7 +12528,7 @@
         </is>
       </c>
       <c r="E460" s="20" t="n">
-        <v>238</v>
+        <v>189</v>
       </c>
     </row>
     <row r="461" ht="20" customHeight="1">
@@ -12553,7 +12553,7 @@
         </is>
       </c>
       <c r="E461" s="23" t="n">
-        <v>115</v>
+        <v>193</v>
       </c>
     </row>
     <row r="462" ht="20" customHeight="1">
@@ -12578,7 +12578,7 @@
         </is>
       </c>
       <c r="E462" s="20" t="n">
-        <v>121</v>
+        <v>167</v>
       </c>
     </row>
     <row r="463" ht="20" customHeight="1">
@@ -12603,7 +12603,7 @@
         </is>
       </c>
       <c r="E463" s="23" t="n">
-        <v>169</v>
+        <v>189</v>
       </c>
     </row>
     <row r="464" ht="20" customHeight="1">
@@ -12628,7 +12628,7 @@
         </is>
       </c>
       <c r="E464" s="20" t="n">
-        <v>210</v>
+        <v>172</v>
       </c>
     </row>
     <row r="465" ht="20" customHeight="1">
@@ -12653,7 +12653,7 @@
         </is>
       </c>
       <c r="E465" s="23" t="n">
-        <v>227</v>
+        <v>139</v>
       </c>
     </row>
     <row r="466" ht="20" customHeight="1">
@@ -12678,7 +12678,7 @@
         </is>
       </c>
       <c r="E466" s="20" t="n">
-        <v>204</v>
+        <v>217</v>
       </c>
     </row>
     <row r="467" ht="20" customHeight="1">
@@ -12703,7 +12703,7 @@
         </is>
       </c>
       <c r="E467" s="23" t="n">
-        <v>193</v>
+        <v>184</v>
       </c>
     </row>
     <row r="468" ht="20" customHeight="1">
@@ -12728,7 +12728,7 @@
         </is>
       </c>
       <c r="E468" s="20" t="n">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="469" ht="20" customHeight="1">
@@ -12753,7 +12753,7 @@
         </is>
       </c>
       <c r="E469" s="23" t="n">
-        <v>163</v>
+        <v>112</v>
       </c>
     </row>
     <row r="470" ht="20" customHeight="1">
@@ -12778,7 +12778,7 @@
         </is>
       </c>
       <c r="E470" s="20" t="n">
-        <v>223</v>
+        <v>206</v>
       </c>
     </row>
     <row r="471" ht="20" customHeight="1">
@@ -12803,7 +12803,7 @@
         </is>
       </c>
       <c r="E471" s="23" t="n">
-        <v>157</v>
+        <v>173</v>
       </c>
     </row>
     <row r="472" ht="20" customHeight="1">
@@ -12828,7 +12828,7 @@
         </is>
       </c>
       <c r="E472" s="20" t="n">
-        <v>239</v>
+        <v>216</v>
       </c>
     </row>
     <row r="473" ht="20" customHeight="1">
@@ -12853,7 +12853,7 @@
         </is>
       </c>
       <c r="E473" s="23" t="n">
-        <v>163</v>
+        <v>181</v>
       </c>
     </row>
     <row r="474" ht="20" customHeight="1">
@@ -12878,7 +12878,7 @@
         </is>
       </c>
       <c r="E474" s="20" t="n">
-        <v>184</v>
+        <v>226</v>
       </c>
     </row>
     <row r="475" ht="20" customHeight="1">
@@ -12903,7 +12903,7 @@
         </is>
       </c>
       <c r="E475" s="23" t="n">
-        <v>173</v>
+        <v>118</v>
       </c>
     </row>
     <row r="476" ht="20" customHeight="1">
@@ -12928,7 +12928,7 @@
         </is>
       </c>
       <c r="E476" s="20" t="n">
-        <v>120</v>
+        <v>156</v>
       </c>
     </row>
     <row r="477" ht="20" customHeight="1">
@@ -12953,7 +12953,7 @@
         </is>
       </c>
       <c r="E477" s="23" t="n">
-        <v>223</v>
+        <v>128</v>
       </c>
     </row>
     <row r="478" ht="20" customHeight="1">
@@ -12978,7 +12978,7 @@
         </is>
       </c>
       <c r="E478" s="20" t="n">
-        <v>133</v>
+        <v>201</v>
       </c>
     </row>
     <row r="479" ht="20" customHeight="1">
@@ -13003,7 +13003,7 @@
         </is>
       </c>
       <c r="E479" s="23" t="n">
-        <v>161</v>
+        <v>199</v>
       </c>
     </row>
     <row r="480" ht="20" customHeight="1">
@@ -13028,7 +13028,7 @@
         </is>
       </c>
       <c r="E480" s="20" t="n">
-        <v>186</v>
+        <v>232</v>
       </c>
     </row>
     <row r="481" ht="20" customHeight="1">
@@ -13053,7 +13053,7 @@
         </is>
       </c>
       <c r="E481" s="23" t="n">
-        <v>193</v>
+        <v>161</v>
       </c>
     </row>
     <row r="482" ht="20" customHeight="1">
@@ -13078,7 +13078,7 @@
         </is>
       </c>
       <c r="E482" s="20" t="n">
-        <v>137</v>
+        <v>160</v>
       </c>
     </row>
     <row r="483" ht="20" customHeight="1">
@@ -13103,7 +13103,7 @@
         </is>
       </c>
       <c r="E483" s="23" t="n">
-        <v>167</v>
+        <v>213</v>
       </c>
     </row>
     <row r="484" ht="20" customHeight="1">
@@ -13128,7 +13128,7 @@
         </is>
       </c>
       <c r="E484" s="20" t="n">
-        <v>151</v>
+        <v>120</v>
       </c>
     </row>
     <row r="485" ht="20" customHeight="1">
@@ -13153,7 +13153,7 @@
         </is>
       </c>
       <c r="E485" s="23" t="n">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="486" ht="20" customHeight="1">
@@ -13178,7 +13178,7 @@
         </is>
       </c>
       <c r="E486" s="20" t="n">
-        <v>154</v>
+        <v>209</v>
       </c>
     </row>
     <row r="487" ht="20" customHeight="1">
@@ -13203,7 +13203,7 @@
         </is>
       </c>
       <c r="E487" s="23" t="n">
-        <v>201</v>
+        <v>133</v>
       </c>
     </row>
     <row r="488" ht="20" customHeight="1">
@@ -13228,7 +13228,7 @@
         </is>
       </c>
       <c r="E488" s="20" t="n">
-        <v>233</v>
+        <v>190</v>
       </c>
     </row>
     <row r="489" ht="20" customHeight="1">
@@ -13253,7 +13253,7 @@
         </is>
       </c>
       <c r="E489" s="23" t="n">
-        <v>239</v>
+        <v>171</v>
       </c>
     </row>
     <row r="490" ht="20" customHeight="1">
@@ -13278,7 +13278,7 @@
         </is>
       </c>
       <c r="E490" s="20" t="n">
-        <v>187</v>
+        <v>234</v>
       </c>
     </row>
     <row r="491" ht="20" customHeight="1">
@@ -13303,7 +13303,7 @@
         </is>
       </c>
       <c r="E491" s="23" t="n">
-        <v>200</v>
+        <v>222</v>
       </c>
     </row>
     <row r="492" ht="20" customHeight="1">
@@ -13328,7 +13328,7 @@
         </is>
       </c>
       <c r="E492" s="20" t="n">
-        <v>150</v>
+        <v>230</v>
       </c>
     </row>
     <row r="493" ht="20" customHeight="1">
@@ -13353,7 +13353,7 @@
         </is>
       </c>
       <c r="E493" s="23" t="n">
-        <v>186</v>
+        <v>133</v>
       </c>
     </row>
     <row r="494" ht="20" customHeight="1">
@@ -13378,7 +13378,7 @@
         </is>
       </c>
       <c r="E494" s="20" t="n">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="495" ht="20" customHeight="1">
@@ -13403,7 +13403,7 @@
         </is>
       </c>
       <c r="E495" s="23" t="n">
-        <v>123</v>
+        <v>230</v>
       </c>
     </row>
     <row r="496" ht="20" customHeight="1">
@@ -13428,7 +13428,7 @@
         </is>
       </c>
       <c r="E496" s="20" t="n">
-        <v>215</v>
+        <v>143</v>
       </c>
     </row>
     <row r="497" ht="20" customHeight="1">
@@ -13453,7 +13453,7 @@
         </is>
       </c>
       <c r="E497" s="23" t="n">
-        <v>132</v>
+        <v>197</v>
       </c>
     </row>
     <row r="498" ht="20" customHeight="1">
@@ -13478,7 +13478,7 @@
         </is>
       </c>
       <c r="E498" s="20" t="n">
-        <v>144</v>
+        <v>216</v>
       </c>
     </row>
     <row r="499" ht="20" customHeight="1">
@@ -13503,7 +13503,7 @@
         </is>
       </c>
       <c r="E499" s="23" t="n">
-        <v>119</v>
+        <v>153</v>
       </c>
     </row>
     <row r="500" ht="20" customHeight="1">
@@ -13528,7 +13528,7 @@
         </is>
       </c>
       <c r="E500" s="20" t="n">
-        <v>112</v>
+        <v>196</v>
       </c>
     </row>
     <row r="501" ht="20" customHeight="1">
@@ -13553,7 +13553,7 @@
         </is>
       </c>
       <c r="E501" s="23" t="n">
-        <v>114</v>
+        <v>154</v>
       </c>
     </row>
     <row r="502" ht="20" customHeight="1">
@@ -13578,7 +13578,7 @@
         </is>
       </c>
       <c r="E502" s="20" t="n">
-        <v>238</v>
+        <v>178</v>
       </c>
     </row>
     <row r="503" ht="20" customHeight="1">
@@ -13603,7 +13603,7 @@
         </is>
       </c>
       <c r="E503" s="23" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="504" ht="20" customHeight="1">
@@ -13628,7 +13628,7 @@
         </is>
       </c>
       <c r="E504" s="20" t="n">
-        <v>240</v>
+        <v>141</v>
       </c>
     </row>
     <row r="505" ht="20" customHeight="1">
@@ -13653,7 +13653,7 @@
         </is>
       </c>
       <c r="E505" s="23" t="n">
-        <v>193</v>
+        <v>211</v>
       </c>
     </row>
     <row r="506" ht="20" customHeight="1">
@@ -13678,7 +13678,7 @@
         </is>
       </c>
       <c r="E506" s="20" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="507" ht="20" customHeight="1">
@@ -13703,7 +13703,7 @@
         </is>
       </c>
       <c r="E507" s="23" t="n">
-        <v>226</v>
+        <v>170</v>
       </c>
     </row>
     <row r="508" ht="20" customHeight="1">
@@ -13728,7 +13728,7 @@
         </is>
       </c>
       <c r="E508" s="20" t="n">
-        <v>177</v>
+        <v>221</v>
       </c>
     </row>
     <row r="509" ht="20" customHeight="1">
@@ -13753,7 +13753,7 @@
         </is>
       </c>
       <c r="E509" s="23" t="n">
-        <v>110</v>
+        <v>224</v>
       </c>
     </row>
     <row r="510" ht="20" customHeight="1">
@@ -13778,7 +13778,7 @@
         </is>
       </c>
       <c r="E510" s="20" t="n">
-        <v>224</v>
+        <v>189</v>
       </c>
     </row>
     <row r="511" ht="20" customHeight="1">
@@ -13803,7 +13803,7 @@
         </is>
       </c>
       <c r="E511" s="23" t="n">
-        <v>147</v>
+        <v>222</v>
       </c>
     </row>
     <row r="512" ht="20" customHeight="1">
@@ -13828,7 +13828,7 @@
         </is>
       </c>
       <c r="E512" s="20" t="n">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="513" ht="20" customHeight="1">
@@ -13853,7 +13853,7 @@
         </is>
       </c>
       <c r="E513" s="23" t="n">
-        <v>234</v>
+        <v>157</v>
       </c>
     </row>
     <row r="514" ht="20" customHeight="1">
@@ -13878,7 +13878,7 @@
         </is>
       </c>
       <c r="E514" s="20" t="n">
-        <v>230</v>
+        <v>197</v>
       </c>
     </row>
     <row r="515" ht="20" customHeight="1">
@@ -13903,7 +13903,7 @@
         </is>
       </c>
       <c r="E515" s="23" t="n">
-        <v>183</v>
+        <v>127</v>
       </c>
     </row>
     <row r="516" ht="20" customHeight="1">
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="E516" s="20" t="n">
-        <v>128</v>
+        <v>228</v>
       </c>
     </row>
     <row r="517" ht="20" customHeight="1">
@@ -13953,7 +13953,7 @@
         </is>
       </c>
       <c r="E517" s="23" t="n">
-        <v>179</v>
+        <v>113</v>
       </c>
     </row>
     <row r="518" ht="20" customHeight="1">
@@ -13978,7 +13978,7 @@
         </is>
       </c>
       <c r="E518" s="20" t="n">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="519" ht="20" customHeight="1">
@@ -14003,7 +14003,7 @@
         </is>
       </c>
       <c r="E519" s="23" t="n">
-        <v>142</v>
+        <v>176</v>
       </c>
     </row>
     <row r="520" ht="20" customHeight="1">
@@ -14028,7 +14028,7 @@
         </is>
       </c>
       <c r="E520" s="20" t="n">
-        <v>122</v>
+        <v>187</v>
       </c>
     </row>
     <row r="521" ht="20" customHeight="1">
@@ -14053,7 +14053,7 @@
         </is>
       </c>
       <c r="E521" s="23" t="n">
-        <v>110</v>
+        <v>226</v>
       </c>
     </row>
     <row r="522" ht="20" customHeight="1">
@@ -14078,7 +14078,7 @@
         </is>
       </c>
       <c r="E522" s="20" t="n">
-        <v>128</v>
+        <v>179</v>
       </c>
     </row>
     <row r="523" ht="20" customHeight="1">
@@ -14103,7 +14103,7 @@
         </is>
       </c>
       <c r="E523" s="23" t="n">
-        <v>193</v>
+        <v>144</v>
       </c>
     </row>
     <row r="524" ht="20" customHeight="1">
@@ -14128,7 +14128,7 @@
         </is>
       </c>
       <c r="E524" s="20" t="n">
-        <v>119</v>
+        <v>129</v>
       </c>
     </row>
     <row r="525" ht="20" customHeight="1">
@@ -14153,7 +14153,7 @@
         </is>
       </c>
       <c r="E525" s="23" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="526" ht="20" customHeight="1">
@@ -14178,7 +14178,7 @@
         </is>
       </c>
       <c r="E526" s="20" t="n">
-        <v>211</v>
+        <v>120</v>
       </c>
     </row>
     <row r="527" ht="20" customHeight="1">
@@ -14203,7 +14203,7 @@
         </is>
       </c>
       <c r="E527" s="23" t="n">
-        <v>125</v>
+        <v>225</v>
       </c>
     </row>
     <row r="528" ht="20" customHeight="1">
@@ -14228,7 +14228,7 @@
         </is>
       </c>
       <c r="E528" s="20" t="n">
-        <v>125</v>
+        <v>199</v>
       </c>
     </row>
     <row r="529" ht="20" customHeight="1">
@@ -14253,7 +14253,7 @@
         </is>
       </c>
       <c r="E529" s="23" t="n">
-        <v>184</v>
+        <v>141</v>
       </c>
     </row>
     <row r="530" ht="20" customHeight="1">
@@ -14278,7 +14278,7 @@
         </is>
       </c>
       <c r="E530" s="20" t="n">
-        <v>135</v>
+        <v>147</v>
       </c>
     </row>
     <row r="531" ht="20" customHeight="1">
@@ -14303,7 +14303,7 @@
         </is>
       </c>
       <c r="E531" s="23" t="n">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="532" ht="20" customHeight="1">
@@ -14328,7 +14328,7 @@
         </is>
       </c>
       <c r="E532" s="20" t="n">
-        <v>174</v>
+        <v>142</v>
       </c>
     </row>
     <row r="533" ht="20" customHeight="1">
@@ -14353,7 +14353,7 @@
         </is>
       </c>
       <c r="E533" s="23" t="n">
-        <v>186</v>
+        <v>175</v>
       </c>
     </row>
     <row r="534" ht="20" customHeight="1">
@@ -14378,7 +14378,7 @@
         </is>
       </c>
       <c r="E534" s="20" t="n">
-        <v>229</v>
+        <v>114</v>
       </c>
     </row>
     <row r="535" ht="20" customHeight="1">
@@ -14403,7 +14403,7 @@
         </is>
       </c>
       <c r="E535" s="23" t="n">
-        <v>189</v>
+        <v>139</v>
       </c>
     </row>
     <row r="536" ht="20" customHeight="1">
@@ -14428,7 +14428,7 @@
         </is>
       </c>
       <c r="E536" s="20" t="n">
-        <v>196</v>
+        <v>172</v>
       </c>
     </row>
     <row r="537" ht="20" customHeight="1">
@@ -14453,7 +14453,7 @@
         </is>
       </c>
       <c r="E537" s="23" t="n">
-        <v>222</v>
+        <v>142</v>
       </c>
     </row>
     <row r="538" ht="20" customHeight="1">
@@ -14478,7 +14478,7 @@
         </is>
       </c>
       <c r="E538" s="20" t="n">
-        <v>178</v>
+        <v>162</v>
       </c>
     </row>
     <row r="539" ht="20" customHeight="1">
@@ -14503,7 +14503,7 @@
         </is>
       </c>
       <c r="E539" s="23" t="n">
-        <v>190</v>
+        <v>170</v>
       </c>
     </row>
     <row r="540" ht="20" customHeight="1">
@@ -14528,7 +14528,7 @@
         </is>
       </c>
       <c r="E540" s="20" t="n">
-        <v>185</v>
+        <v>154</v>
       </c>
     </row>
     <row r="541" ht="20" customHeight="1">
@@ -14553,7 +14553,7 @@
         </is>
       </c>
       <c r="E541" s="23" t="n">
-        <v>154</v>
+        <v>160</v>
       </c>
     </row>
     <row r="542" ht="20" customHeight="1">
@@ -14578,7 +14578,7 @@
         </is>
       </c>
       <c r="E542" s="20" t="n">
-        <v>178</v>
+        <v>156</v>
       </c>
     </row>
     <row r="543" ht="20" customHeight="1">
@@ -14603,7 +14603,7 @@
         </is>
       </c>
       <c r="E543" s="23" t="n">
-        <v>233</v>
+        <v>155</v>
       </c>
     </row>
     <row r="544" ht="20" customHeight="1">
@@ -14628,7 +14628,7 @@
         </is>
       </c>
       <c r="E544" s="20" t="n">
-        <v>137</v>
+        <v>168</v>
       </c>
     </row>
     <row r="545" ht="20" customHeight="1">
@@ -14653,7 +14653,7 @@
         </is>
       </c>
       <c r="E545" s="23" t="n">
-        <v>185</v>
+        <v>114</v>
       </c>
     </row>
     <row r="546" ht="20" customHeight="1">
@@ -14678,7 +14678,7 @@
         </is>
       </c>
       <c r="E546" s="20" t="n">
-        <v>136</v>
+        <v>211</v>
       </c>
     </row>
     <row r="547" ht="20" customHeight="1">
@@ -14703,7 +14703,7 @@
         </is>
       </c>
       <c r="E547" s="23" t="n">
-        <v>165</v>
+        <v>216</v>
       </c>
     </row>
     <row r="548" ht="20" customHeight="1">
@@ -14728,7 +14728,7 @@
         </is>
       </c>
       <c r="E548" s="20" t="n">
-        <v>115</v>
+        <v>213</v>
       </c>
     </row>
     <row r="549" ht="20" customHeight="1">
@@ -14753,7 +14753,7 @@
         </is>
       </c>
       <c r="E549" s="23" t="n">
-        <v>235</v>
+        <v>116</v>
       </c>
     </row>
     <row r="550" ht="20" customHeight="1">
@@ -14778,7 +14778,7 @@
         </is>
       </c>
       <c r="E550" s="20" t="n">
-        <v>213</v>
+        <v>204</v>
       </c>
     </row>
     <row r="551" ht="20" customHeight="1">
@@ -14803,7 +14803,7 @@
         </is>
       </c>
       <c r="E551" s="23" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
     </row>
     <row r="552" ht="20" customHeight="1">
@@ -14828,7 +14828,7 @@
         </is>
       </c>
       <c r="E552" s="20" t="n">
-        <v>122</v>
+        <v>140</v>
       </c>
     </row>
     <row r="553" ht="20" customHeight="1">
@@ -14853,7 +14853,7 @@
         </is>
       </c>
       <c r="E553" s="23" t="n">
-        <v>208</v>
+        <v>149</v>
       </c>
     </row>
     <row r="554" ht="20" customHeight="1">
@@ -14878,7 +14878,7 @@
         </is>
       </c>
       <c r="E554" s="20" t="n">
-        <v>157</v>
+        <v>168</v>
       </c>
     </row>
     <row r="555" ht="20" customHeight="1">
@@ -14903,7 +14903,7 @@
         </is>
       </c>
       <c r="E555" s="23" t="n">
-        <v>206</v>
+        <v>197</v>
       </c>
     </row>
     <row r="556" ht="20" customHeight="1">
@@ -14928,7 +14928,7 @@
         </is>
       </c>
       <c r="E556" s="20" t="n">
-        <v>121</v>
+        <v>225</v>
       </c>
     </row>
     <row r="557" ht="20" customHeight="1">
@@ -14953,7 +14953,7 @@
         </is>
       </c>
       <c r="E557" s="23" t="n">
-        <v>139</v>
+        <v>160</v>
       </c>
     </row>
     <row r="558" ht="20" customHeight="1">
@@ -14978,7 +14978,7 @@
         </is>
       </c>
       <c r="E558" s="20" t="n">
-        <v>174</v>
+        <v>153</v>
       </c>
     </row>
     <row r="559" ht="20" customHeight="1">
@@ -15003,7 +15003,7 @@
         </is>
       </c>
       <c r="E559" s="23" t="n">
-        <v>124</v>
+        <v>167</v>
       </c>
     </row>
     <row r="560" ht="20" customHeight="1">
@@ -15028,7 +15028,7 @@
         </is>
       </c>
       <c r="E560" s="20" t="n">
-        <v>204</v>
+        <v>223</v>
       </c>
     </row>
     <row r="561" ht="20" customHeight="1">
@@ -15053,7 +15053,7 @@
         </is>
       </c>
       <c r="E561" s="23" t="n">
-        <v>224</v>
+        <v>232</v>
       </c>
     </row>
     <row r="562" ht="20" customHeight="1">
@@ -15078,7 +15078,7 @@
         </is>
       </c>
       <c r="E562" s="20" t="n">
-        <v>155</v>
+        <v>194</v>
       </c>
     </row>
     <row r="563" ht="20" customHeight="1">
@@ -15103,7 +15103,7 @@
         </is>
       </c>
       <c r="E563" s="23" t="n">
-        <v>128</v>
+        <v>119</v>
       </c>
     </row>
     <row r="564" ht="20" customHeight="1">
@@ -15128,7 +15128,7 @@
         </is>
       </c>
       <c r="E564" s="20" t="n">
-        <v>161</v>
+        <v>183</v>
       </c>
     </row>
     <row r="565" ht="20" customHeight="1">
@@ -15153,7 +15153,7 @@
         </is>
       </c>
       <c r="E565" s="23" t="n">
-        <v>227</v>
+        <v>136</v>
       </c>
     </row>
     <row r="566" ht="20" customHeight="1">
@@ -15178,7 +15178,7 @@
         </is>
       </c>
       <c r="E566" s="20" t="n">
-        <v>184</v>
+        <v>226</v>
       </c>
     </row>
     <row r="567" ht="20" customHeight="1">
@@ -15203,7 +15203,7 @@
         </is>
       </c>
       <c r="E567" s="23" t="n">
-        <v>238</v>
+        <v>161</v>
       </c>
     </row>
     <row r="568" ht="20" customHeight="1">
@@ -15228,7 +15228,7 @@
         </is>
       </c>
       <c r="E568" s="20" t="n">
-        <v>132</v>
+        <v>166</v>
       </c>
     </row>
     <row r="569" ht="20" customHeight="1">
@@ -15253,7 +15253,7 @@
         </is>
       </c>
       <c r="E569" s="23" t="n">
-        <v>202</v>
+        <v>129</v>
       </c>
     </row>
     <row r="570" ht="20" customHeight="1">
@@ -15278,7 +15278,7 @@
         </is>
       </c>
       <c r="E570" s="20" t="n">
-        <v>158</v>
+        <v>238</v>
       </c>
     </row>
     <row r="571" ht="20" customHeight="1">
@@ -15303,7 +15303,7 @@
         </is>
       </c>
       <c r="E571" s="23" t="n">
-        <v>174</v>
+        <v>181</v>
       </c>
     </row>
     <row r="572" ht="20" customHeight="1">
@@ -15328,7 +15328,7 @@
         </is>
       </c>
       <c r="E572" s="20" t="n">
-        <v>237</v>
+        <v>140</v>
       </c>
     </row>
     <row r="573" ht="20" customHeight="1">
@@ -15353,7 +15353,7 @@
         </is>
       </c>
       <c r="E573" s="23" t="n">
-        <v>164</v>
+        <v>175</v>
       </c>
     </row>
     <row r="574" ht="20" customHeight="1">
@@ -15378,7 +15378,7 @@
         </is>
       </c>
       <c r="E574" s="20" t="n">
-        <v>164</v>
+        <v>181</v>
       </c>
     </row>
     <row r="575" ht="20" customHeight="1">
@@ -15403,7 +15403,7 @@
         </is>
       </c>
       <c r="E575" s="23" t="n">
-        <v>230</v>
+        <v>213</v>
       </c>
     </row>
     <row r="576" ht="20" customHeight="1">
@@ -15428,7 +15428,7 @@
         </is>
       </c>
       <c r="E576" s="20" t="n">
-        <v>147</v>
+        <v>156</v>
       </c>
     </row>
     <row r="577" ht="20" customHeight="1">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="E577" s="23" t="n">
-        <v>199</v>
+        <v>214</v>
       </c>
     </row>
     <row r="578" ht="20" customHeight="1">
@@ -15478,7 +15478,7 @@
         </is>
       </c>
       <c r="E578" s="20" t="n">
-        <v>200</v>
+        <v>147</v>
       </c>
     </row>
     <row r="579" ht="20" customHeight="1">
@@ -15503,7 +15503,7 @@
         </is>
       </c>
       <c r="E579" s="23" t="n">
-        <v>144</v>
+        <v>237</v>
       </c>
     </row>
     <row r="580" ht="20" customHeight="1">
@@ -15528,7 +15528,7 @@
         </is>
       </c>
       <c r="E580" s="20" t="n">
-        <v>143</v>
+        <v>213</v>
       </c>
     </row>
     <row r="581" ht="20" customHeight="1">
@@ -15553,7 +15553,7 @@
         </is>
       </c>
       <c r="E581" s="23" t="n">
-        <v>146</v>
+        <v>116</v>
       </c>
     </row>
     <row r="582" ht="20" customHeight="1">
@@ -15578,7 +15578,7 @@
         </is>
       </c>
       <c r="E582" s="20" t="n">
-        <v>110</v>
+        <v>116</v>
       </c>
     </row>
     <row r="583" ht="20" customHeight="1">
@@ -15603,7 +15603,7 @@
         </is>
       </c>
       <c r="E583" s="23" t="n">
-        <v>232</v>
+        <v>122</v>
       </c>
     </row>
     <row r="584" ht="20" customHeight="1">
@@ -15628,7 +15628,7 @@
         </is>
       </c>
       <c r="E584" s="20" t="n">
-        <v>200</v>
+        <v>175</v>
       </c>
     </row>
     <row r="585" ht="20" customHeight="1">
@@ -15653,7 +15653,7 @@
         </is>
       </c>
       <c r="E585" s="23" t="n">
-        <v>194</v>
+        <v>145</v>
       </c>
     </row>
     <row r="586" ht="20" customHeight="1">
@@ -15678,7 +15678,7 @@
         </is>
       </c>
       <c r="E586" s="20" t="n">
-        <v>238</v>
+        <v>140</v>
       </c>
     </row>
     <row r="587" ht="20" customHeight="1">
@@ -15703,7 +15703,7 @@
         </is>
       </c>
       <c r="E587" s="23" t="n">
-        <v>234</v>
+        <v>154</v>
       </c>
     </row>
     <row r="588" ht="20" customHeight="1">
@@ -15728,7 +15728,7 @@
         </is>
       </c>
       <c r="E588" s="20" t="n">
-        <v>191</v>
+        <v>162</v>
       </c>
     </row>
     <row r="589" ht="20" customHeight="1">
@@ -15753,7 +15753,7 @@
         </is>
       </c>
       <c r="E589" s="23" t="n">
-        <v>116</v>
+        <v>164</v>
       </c>
     </row>
     <row r="590" ht="20" customHeight="1">
@@ -15778,7 +15778,7 @@
         </is>
       </c>
       <c r="E590" s="20" t="n">
-        <v>156</v>
+        <v>231</v>
       </c>
     </row>
     <row r="591" ht="20" customHeight="1">
@@ -15803,7 +15803,7 @@
         </is>
       </c>
       <c r="E591" s="23" t="n">
-        <v>185</v>
+        <v>172</v>
       </c>
     </row>
     <row r="592" ht="20" customHeight="1">
@@ -15828,7 +15828,7 @@
         </is>
       </c>
       <c r="E592" s="20" t="n">
-        <v>160</v>
+        <v>198</v>
       </c>
     </row>
     <row r="593" ht="20" customHeight="1">
@@ -15853,7 +15853,7 @@
         </is>
       </c>
       <c r="E593" s="23" t="n">
-        <v>148</v>
+        <v>117</v>
       </c>
     </row>
     <row r="594" ht="20" customHeight="1">
@@ -15878,7 +15878,7 @@
         </is>
       </c>
       <c r="E594" s="20" t="n">
-        <v>122</v>
+        <v>207</v>
       </c>
     </row>
     <row r="595" ht="20" customHeight="1">
@@ -15903,7 +15903,7 @@
         </is>
       </c>
       <c r="E595" s="23" t="n">
-        <v>221</v>
+        <v>173</v>
       </c>
     </row>
     <row r="596" ht="20" customHeight="1">
@@ -15928,7 +15928,7 @@
         </is>
       </c>
       <c r="E596" s="20" t="n">
-        <v>183</v>
+        <v>162</v>
       </c>
     </row>
     <row r="597" ht="20" customHeight="1">
@@ -15953,7 +15953,7 @@
         </is>
       </c>
       <c r="E597" s="23" t="n">
-        <v>229</v>
+        <v>152</v>
       </c>
     </row>
     <row r="598" ht="20" customHeight="1">
@@ -15978,7 +15978,7 @@
         </is>
       </c>
       <c r="E598" s="20" t="n">
-        <v>149</v>
+        <v>180</v>
       </c>
     </row>
     <row r="599" ht="20" customHeight="1">
@@ -16003,7 +16003,7 @@
         </is>
       </c>
       <c r="E599" s="23" t="n">
-        <v>123</v>
+        <v>164</v>
       </c>
     </row>
     <row r="600" ht="20" customHeight="1">
@@ -16028,7 +16028,7 @@
         </is>
       </c>
       <c r="E600" s="20" t="n">
-        <v>183</v>
+        <v>224</v>
       </c>
     </row>
     <row r="601" ht="20" customHeight="1">
@@ -16053,7 +16053,7 @@
         </is>
       </c>
       <c r="E601" s="23" t="n">
-        <v>132</v>
+        <v>190</v>
       </c>
     </row>
     <row r="602" ht="20" customHeight="1">
@@ -16078,7 +16078,7 @@
         </is>
       </c>
       <c r="E602" s="20" t="n">
-        <v>156</v>
+        <v>151</v>
       </c>
     </row>
     <row r="603" ht="20" customHeight="1">
@@ -16103,7 +16103,7 @@
         </is>
       </c>
       <c r="E603" s="23" t="n">
-        <v>222</v>
+        <v>177</v>
       </c>
     </row>
     <row r="604" ht="20" customHeight="1">
@@ -16128,7 +16128,7 @@
         </is>
       </c>
       <c r="E604" s="20" t="n">
-        <v>218</v>
+        <v>193</v>
       </c>
     </row>
     <row r="605" ht="20" customHeight="1">
@@ -16153,7 +16153,7 @@
         </is>
       </c>
       <c r="E605" s="23" t="n">
-        <v>144</v>
+        <v>212</v>
       </c>
     </row>
     <row r="606" ht="20" customHeight="1">
@@ -16178,7 +16178,7 @@
         </is>
       </c>
       <c r="E606" s="20" t="n">
-        <v>233</v>
+        <v>218</v>
       </c>
     </row>
     <row r="607" ht="20" customHeight="1">
@@ -16228,7 +16228,7 @@
         </is>
       </c>
       <c r="E608" s="20" t="n">
-        <v>225</v>
+        <v>197</v>
       </c>
     </row>
     <row r="609" ht="20" customHeight="1">
@@ -16253,7 +16253,7 @@
         </is>
       </c>
       <c r="E609" s="23" t="n">
-        <v>173</v>
+        <v>114</v>
       </c>
     </row>
     <row r="610" ht="20" customHeight="1">
@@ -16278,7 +16278,7 @@
         </is>
       </c>
       <c r="E610" s="20" t="n">
-        <v>128</v>
+        <v>158</v>
       </c>
     </row>
     <row r="611" ht="20" customHeight="1">
@@ -16303,7 +16303,7 @@
         </is>
       </c>
       <c r="E611" s="23" t="n">
-        <v>113</v>
+        <v>163</v>
       </c>
     </row>
     <row r="612" ht="20" customHeight="1">
@@ -16328,7 +16328,7 @@
         </is>
       </c>
       <c r="E612" s="20" t="n">
-        <v>141</v>
+        <v>119</v>
       </c>
     </row>
     <row r="613" ht="20" customHeight="1">
@@ -16353,7 +16353,7 @@
         </is>
       </c>
       <c r="E613" s="23" t="n">
-        <v>224</v>
+        <v>216</v>
       </c>
     </row>
     <row r="614" ht="20" customHeight="1">
@@ -16378,7 +16378,7 @@
         </is>
       </c>
       <c r="E614" s="20" t="n">
-        <v>123</v>
+        <v>147</v>
       </c>
     </row>
     <row r="615" ht="20" customHeight="1">
@@ -16403,7 +16403,7 @@
         </is>
       </c>
       <c r="E615" s="23" t="n">
-        <v>228</v>
+        <v>239</v>
       </c>
     </row>
     <row r="616" ht="20" customHeight="1">
@@ -16428,7 +16428,7 @@
         </is>
       </c>
       <c r="E616" s="20" t="n">
-        <v>125</v>
+        <v>155</v>
       </c>
     </row>
     <row r="617" ht="20" customHeight="1">
@@ -16453,7 +16453,7 @@
         </is>
       </c>
       <c r="E617" s="23" t="n">
-        <v>239</v>
+        <v>227</v>
       </c>
     </row>
     <row r="618" ht="20" customHeight="1">
@@ -16478,7 +16478,7 @@
         </is>
       </c>
       <c r="E618" s="20" t="n">
-        <v>131</v>
+        <v>141</v>
       </c>
     </row>
     <row r="619" ht="20" customHeight="1">
@@ -16503,7 +16503,7 @@
         </is>
       </c>
       <c r="E619" s="23" t="n">
-        <v>180</v>
+        <v>144</v>
       </c>
     </row>
     <row r="620" ht="20" customHeight="1">
@@ -16528,7 +16528,7 @@
         </is>
       </c>
       <c r="E620" s="20" t="n">
-        <v>240</v>
+        <v>212</v>
       </c>
     </row>
     <row r="621" ht="20" customHeight="1">
@@ -16553,7 +16553,7 @@
         </is>
       </c>
       <c r="E621" s="23" t="n">
-        <v>228</v>
+        <v>183</v>
       </c>
     </row>
     <row r="622" ht="20" customHeight="1">
@@ -16578,7 +16578,7 @@
         </is>
       </c>
       <c r="E622" s="20" t="n">
-        <v>148</v>
+        <v>182</v>
       </c>
     </row>
     <row r="623" ht="20" customHeight="1">
@@ -16603,7 +16603,7 @@
         </is>
       </c>
       <c r="E623" s="23" t="n">
-        <v>157</v>
+        <v>182</v>
       </c>
     </row>
     <row r="624" ht="20" customHeight="1">
@@ -16628,7 +16628,7 @@
         </is>
       </c>
       <c r="E624" s="20" t="n">
-        <v>156</v>
+        <v>111</v>
       </c>
     </row>
     <row r="625" ht="20" customHeight="1">
@@ -16653,7 +16653,7 @@
         </is>
       </c>
       <c r="E625" s="23" t="n">
-        <v>220</v>
+        <v>148</v>
       </c>
     </row>
     <row r="626" ht="20" customHeight="1">
@@ -16678,7 +16678,7 @@
         </is>
       </c>
       <c r="E626" s="20" t="n">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="627" ht="20" customHeight="1">
@@ -16703,7 +16703,7 @@
         </is>
       </c>
       <c r="E627" s="23" t="n">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="628" ht="20" customHeight="1">
@@ -16728,7 +16728,7 @@
         </is>
       </c>
       <c r="E628" s="20" t="n">
-        <v>240</v>
+        <v>180</v>
       </c>
     </row>
     <row r="629" ht="20" customHeight="1">
@@ -16753,7 +16753,7 @@
         </is>
       </c>
       <c r="E629" s="23" t="n">
-        <v>217</v>
+        <v>229</v>
       </c>
     </row>
     <row r="630" ht="20" customHeight="1">
@@ -16778,7 +16778,7 @@
         </is>
       </c>
       <c r="E630" s="20" t="n">
-        <v>215</v>
+        <v>117</v>
       </c>
     </row>
     <row r="631" ht="20" customHeight="1">
@@ -16803,7 +16803,7 @@
         </is>
       </c>
       <c r="E631" s="23" t="n">
-        <v>175</v>
+        <v>123</v>
       </c>
     </row>
     <row r="632" ht="20" customHeight="1">
@@ -16828,7 +16828,7 @@
         </is>
       </c>
       <c r="E632" s="20" t="n">
-        <v>189</v>
+        <v>161</v>
       </c>
     </row>
     <row r="633" ht="20" customHeight="1">
@@ -16853,7 +16853,7 @@
         </is>
       </c>
       <c r="E633" s="23" t="n">
-        <v>172</v>
+        <v>154</v>
       </c>
     </row>
     <row r="634" ht="20" customHeight="1">
@@ -16878,7 +16878,7 @@
         </is>
       </c>
       <c r="E634" s="20" t="n">
-        <v>221</v>
+        <v>143</v>
       </c>
     </row>
     <row r="635" ht="20" customHeight="1">
@@ -16903,7 +16903,7 @@
         </is>
       </c>
       <c r="E635" s="23" t="n">
-        <v>198</v>
+        <v>177</v>
       </c>
     </row>
     <row r="636" ht="20" customHeight="1">
@@ -16928,7 +16928,7 @@
         </is>
       </c>
       <c r="E636" s="20" t="n">
-        <v>113</v>
+        <v>144</v>
       </c>
     </row>
     <row r="637" ht="20" customHeight="1">
@@ -16953,7 +16953,7 @@
         </is>
       </c>
       <c r="E637" s="23" t="n">
-        <v>219</v>
+        <v>130</v>
       </c>
     </row>
     <row r="638" ht="20" customHeight="1">
@@ -16978,7 +16978,7 @@
         </is>
       </c>
       <c r="E638" s="20" t="n">
-        <v>147</v>
+        <v>138</v>
       </c>
     </row>
     <row r="639" ht="20" customHeight="1">
@@ -17003,7 +17003,7 @@
         </is>
       </c>
       <c r="E639" s="23" t="n">
-        <v>220</v>
+        <v>188</v>
       </c>
     </row>
     <row r="640" ht="20" customHeight="1">
@@ -17028,7 +17028,7 @@
         </is>
       </c>
       <c r="E640" s="20" t="n">
-        <v>175</v>
+        <v>202</v>
       </c>
     </row>
     <row r="641" ht="20" customHeight="1">
@@ -17053,7 +17053,7 @@
         </is>
       </c>
       <c r="E641" s="23" t="n">
-        <v>124</v>
+        <v>195</v>
       </c>
     </row>
     <row r="642" ht="20" customHeight="1">
@@ -17078,7 +17078,7 @@
         </is>
       </c>
       <c r="E642" s="20" t="n">
-        <v>221</v>
+        <v>129</v>
       </c>
     </row>
     <row r="643" ht="20" customHeight="1">
@@ -17103,7 +17103,7 @@
         </is>
       </c>
       <c r="E643" s="23" t="n">
-        <v>169</v>
+        <v>156</v>
       </c>
     </row>
     <row r="644" ht="20" customHeight="1">
@@ -17128,7 +17128,7 @@
         </is>
       </c>
       <c r="E644" s="20" t="n">
-        <v>158</v>
+        <v>117</v>
       </c>
     </row>
     <row r="645" ht="20" customHeight="1">
@@ -17153,7 +17153,7 @@
         </is>
       </c>
       <c r="E645" s="23" t="n">
-        <v>133</v>
+        <v>154</v>
       </c>
     </row>
     <row r="646" ht="20" customHeight="1">
@@ -17178,7 +17178,7 @@
         </is>
       </c>
       <c r="E646" s="20" t="n">
-        <v>154</v>
+        <v>139</v>
       </c>
     </row>
     <row r="647" ht="20" customHeight="1">
@@ -17203,7 +17203,7 @@
         </is>
       </c>
       <c r="E647" s="23" t="n">
-        <v>219</v>
+        <v>121</v>
       </c>
     </row>
     <row r="648" ht="20" customHeight="1">
@@ -17228,7 +17228,7 @@
         </is>
       </c>
       <c r="E648" s="20" t="n">
-        <v>234</v>
+        <v>180</v>
       </c>
     </row>
     <row r="649" ht="20" customHeight="1">
@@ -17253,7 +17253,7 @@
         </is>
       </c>
       <c r="E649" s="23" t="n">
-        <v>173</v>
+        <v>160</v>
       </c>
     </row>
     <row r="650" ht="20" customHeight="1">
@@ -17278,7 +17278,7 @@
         </is>
       </c>
       <c r="E650" s="20" t="n">
-        <v>192</v>
+        <v>218</v>
       </c>
     </row>
     <row r="651" ht="20" customHeight="1">
@@ -17303,7 +17303,7 @@
         </is>
       </c>
       <c r="E651" s="23" t="n">
-        <v>127</v>
+        <v>185</v>
       </c>
     </row>
     <row r="652" ht="20" customHeight="1">
@@ -17328,7 +17328,7 @@
         </is>
       </c>
       <c r="E652" s="20" t="n">
-        <v>225</v>
+        <v>137</v>
       </c>
     </row>
     <row r="653" ht="20" customHeight="1">
@@ -17353,7 +17353,7 @@
         </is>
       </c>
       <c r="E653" s="23" t="n">
-        <v>231</v>
+        <v>150</v>
       </c>
     </row>
     <row r="654" ht="20" customHeight="1">
@@ -17378,7 +17378,7 @@
         </is>
       </c>
       <c r="E654" s="20" t="n">
-        <v>194</v>
+        <v>240</v>
       </c>
     </row>
     <row r="655" ht="20" customHeight="1">
@@ -17403,7 +17403,7 @@
         </is>
       </c>
       <c r="E655" s="23" t="n">
-        <v>174</v>
+        <v>228</v>
       </c>
     </row>
     <row r="656" ht="20" customHeight="1">
@@ -17428,7 +17428,7 @@
         </is>
       </c>
       <c r="E656" s="20" t="n">
-        <v>189</v>
+        <v>111</v>
       </c>
     </row>
     <row r="657" ht="20" customHeight="1">
@@ -17453,7 +17453,7 @@
         </is>
       </c>
       <c r="E657" s="23" t="n">
-        <v>194</v>
+        <v>128</v>
       </c>
     </row>
     <row r="658" ht="20" customHeight="1">
@@ -17478,7 +17478,7 @@
         </is>
       </c>
       <c r="E658" s="20" t="n">
-        <v>207</v>
+        <v>133</v>
       </c>
     </row>
     <row r="659" ht="20" customHeight="1">
@@ -17503,7 +17503,7 @@
         </is>
       </c>
       <c r="E659" s="23" t="n">
-        <v>178</v>
+        <v>149</v>
       </c>
     </row>
     <row r="660" ht="20" customHeight="1">
@@ -17528,7 +17528,7 @@
         </is>
       </c>
       <c r="E660" s="20" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="661" ht="20" customHeight="1">
@@ -17553,7 +17553,7 @@
         </is>
       </c>
       <c r="E661" s="23" t="n">
-        <v>147</v>
+        <v>190</v>
       </c>
     </row>
     <row r="662" ht="20" customHeight="1">
@@ -17603,7 +17603,7 @@
         </is>
       </c>
       <c r="E663" s="23" t="n">
-        <v>176</v>
+        <v>163</v>
       </c>
     </row>
     <row r="664" ht="20" customHeight="1">
@@ -17628,7 +17628,7 @@
         </is>
       </c>
       <c r="E664" s="20" t="n">
-        <v>123</v>
+        <v>227</v>
       </c>
     </row>
     <row r="665" ht="20" customHeight="1">
@@ -17653,7 +17653,7 @@
         </is>
       </c>
       <c r="E665" s="23" t="n">
-        <v>117</v>
+        <v>145</v>
       </c>
     </row>
     <row r="666" ht="20" customHeight="1">
@@ -17678,7 +17678,7 @@
         </is>
       </c>
       <c r="E666" s="20" t="n">
-        <v>205</v>
+        <v>211</v>
       </c>
     </row>
     <row r="667" ht="20" customHeight="1">
@@ -17703,7 +17703,7 @@
         </is>
       </c>
       <c r="E667" s="23" t="n">
-        <v>144</v>
+        <v>207</v>
       </c>
     </row>
     <row r="668" ht="20" customHeight="1">
@@ -17728,7 +17728,7 @@
         </is>
       </c>
       <c r="E668" s="20" t="n">
-        <v>228</v>
+        <v>113</v>
       </c>
     </row>
     <row r="669" ht="20" customHeight="1">
@@ -17753,7 +17753,7 @@
         </is>
       </c>
       <c r="E669" s="23" t="n">
-        <v>128</v>
+        <v>205</v>
       </c>
     </row>
     <row r="670" ht="20" customHeight="1">
@@ -17778,7 +17778,7 @@
         </is>
       </c>
       <c r="E670" s="20" t="n">
-        <v>218</v>
+        <v>184</v>
       </c>
     </row>
     <row r="671" ht="20" customHeight="1">
@@ -17803,7 +17803,7 @@
         </is>
       </c>
       <c r="E671" s="23" t="n">
-        <v>126</v>
+        <v>213</v>
       </c>
     </row>
     <row r="672" ht="20" customHeight="1">
@@ -17828,7 +17828,7 @@
         </is>
       </c>
       <c r="E672" s="20" t="n">
-        <v>185</v>
+        <v>193</v>
       </c>
     </row>
     <row r="673" ht="20" customHeight="1">
@@ -17853,7 +17853,7 @@
         </is>
       </c>
       <c r="E673" s="23" t="n">
-        <v>151</v>
+        <v>164</v>
       </c>
     </row>
     <row r="674" ht="20" customHeight="1">
@@ -17878,7 +17878,7 @@
         </is>
       </c>
       <c r="E674" s="20" t="n">
-        <v>239</v>
+        <v>125</v>
       </c>
     </row>
     <row r="675" ht="20" customHeight="1">
@@ -17903,7 +17903,7 @@
         </is>
       </c>
       <c r="E675" s="23" t="n">
-        <v>210</v>
+        <v>170</v>
       </c>
     </row>
     <row r="676" ht="20" customHeight="1">
@@ -17928,7 +17928,7 @@
         </is>
       </c>
       <c r="E676" s="20" t="n">
-        <v>152</v>
+        <v>121</v>
       </c>
     </row>
     <row r="677" ht="20" customHeight="1">
@@ -17953,7 +17953,7 @@
         </is>
       </c>
       <c r="E677" s="23" t="n">
-        <v>142</v>
+        <v>131</v>
       </c>
     </row>
     <row r="678" ht="20" customHeight="1">
@@ -17978,7 +17978,7 @@
         </is>
       </c>
       <c r="E678" s="20" t="n">
-        <v>162</v>
+        <v>217</v>
       </c>
     </row>
     <row r="679" ht="20" customHeight="1">
@@ -18003,7 +18003,7 @@
         </is>
       </c>
       <c r="E679" s="23" t="n">
-        <v>236</v>
+        <v>117</v>
       </c>
     </row>
     <row r="680" ht="20" customHeight="1">
@@ -18028,7 +18028,7 @@
         </is>
       </c>
       <c r="E680" s="20" t="n">
-        <v>168</v>
+        <v>196</v>
       </c>
     </row>
     <row r="681" ht="20" customHeight="1">
@@ -18053,7 +18053,7 @@
         </is>
       </c>
       <c r="E681" s="23" t="n">
-        <v>208</v>
+        <v>130</v>
       </c>
     </row>
     <row r="682" ht="20" customHeight="1">
@@ -18078,7 +18078,7 @@
         </is>
       </c>
       <c r="E682" s="20" t="n">
-        <v>192</v>
+        <v>215</v>
       </c>
     </row>
     <row r="683" ht="20" customHeight="1">
@@ -18103,7 +18103,7 @@
         </is>
       </c>
       <c r="E683" s="23" t="n">
-        <v>135</v>
+        <v>148</v>
       </c>
     </row>
     <row r="684" ht="20" customHeight="1">
@@ -18128,7 +18128,7 @@
         </is>
       </c>
       <c r="E684" s="20" t="n">
-        <v>115</v>
+        <v>237</v>
       </c>
     </row>
     <row r="685" ht="20" customHeight="1">
@@ -18153,7 +18153,7 @@
         </is>
       </c>
       <c r="E685" s="23" t="n">
-        <v>122</v>
+        <v>156</v>
       </c>
     </row>
     <row r="686" ht="20" customHeight="1">
@@ -18178,7 +18178,7 @@
         </is>
       </c>
       <c r="E686" s="20" t="n">
-        <v>169</v>
+        <v>136</v>
       </c>
     </row>
     <row r="687" ht="20" customHeight="1">
@@ -18203,7 +18203,7 @@
         </is>
       </c>
       <c r="E687" s="23" t="n">
-        <v>182</v>
+        <v>222</v>
       </c>
     </row>
     <row r="688" ht="20" customHeight="1">
@@ -18228,7 +18228,7 @@
         </is>
       </c>
       <c r="E688" s="20" t="n">
-        <v>210</v>
+        <v>178</v>
       </c>
     </row>
     <row r="689" ht="20" customHeight="1">
@@ -18253,7 +18253,7 @@
         </is>
       </c>
       <c r="E689" s="23" t="n">
-        <v>203</v>
+        <v>224</v>
       </c>
     </row>
     <row r="690" ht="20" customHeight="1">
@@ -18278,7 +18278,7 @@
         </is>
       </c>
       <c r="E690" s="20" t="n">
-        <v>230</v>
+        <v>191</v>
       </c>
     </row>
     <row r="691" ht="20" customHeight="1">
@@ -18303,7 +18303,7 @@
         </is>
       </c>
       <c r="E691" s="23" t="n">
-        <v>149</v>
+        <v>112</v>
       </c>
     </row>
     <row r="692" ht="20" customHeight="1">
@@ -18328,7 +18328,7 @@
         </is>
       </c>
       <c r="E692" s="20" t="n">
-        <v>111</v>
+        <v>164</v>
       </c>
     </row>
     <row r="693" ht="20" customHeight="1">
@@ -18353,7 +18353,7 @@
         </is>
       </c>
       <c r="E693" s="23" t="n">
-        <v>228</v>
+        <v>175</v>
       </c>
     </row>
     <row r="694" ht="20" customHeight="1">
@@ -18378,7 +18378,7 @@
         </is>
       </c>
       <c r="E694" s="20" t="n">
-        <v>233</v>
+        <v>161</v>
       </c>
     </row>
     <row r="695" ht="20" customHeight="1">
@@ -18403,7 +18403,7 @@
         </is>
       </c>
       <c r="E695" s="23" t="n">
-        <v>237</v>
+        <v>230</v>
       </c>
     </row>
     <row r="696" ht="20" customHeight="1">
@@ -18428,7 +18428,7 @@
         </is>
       </c>
       <c r="E696" s="20" t="n">
-        <v>212</v>
+        <v>121</v>
       </c>
     </row>
     <row r="697" ht="20" customHeight="1">
@@ -18453,7 +18453,7 @@
         </is>
       </c>
       <c r="E697" s="23" t="n">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="698" ht="20" customHeight="1">
@@ -18478,7 +18478,7 @@
         </is>
       </c>
       <c r="E698" s="20" t="n">
-        <v>200</v>
+        <v>114</v>
       </c>
     </row>
     <row r="699" ht="20" customHeight="1">
@@ -18503,7 +18503,7 @@
         </is>
       </c>
       <c r="E699" s="23" t="n">
-        <v>228</v>
+        <v>176</v>
       </c>
     </row>
     <row r="700" ht="20" customHeight="1">
@@ -18528,7 +18528,7 @@
         </is>
       </c>
       <c r="E700" s="20" t="n">
-        <v>204</v>
+        <v>234</v>
       </c>
     </row>
     <row r="701" ht="20" customHeight="1">
@@ -18553,7 +18553,7 @@
         </is>
       </c>
       <c r="E701" s="23" t="n">
-        <v>221</v>
+        <v>203</v>
       </c>
     </row>
     <row r="702" ht="20" customHeight="1">
@@ -18578,7 +18578,7 @@
         </is>
       </c>
       <c r="E702" s="20" t="n">
-        <v>216</v>
+        <v>121</v>
       </c>
     </row>
     <row r="703" ht="20" customHeight="1">
@@ -18603,7 +18603,7 @@
         </is>
       </c>
       <c r="E703" s="23" t="n">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="704" ht="20" customHeight="1">
@@ -18628,7 +18628,7 @@
         </is>
       </c>
       <c r="E704" s="20" t="n">
-        <v>114</v>
+        <v>186</v>
       </c>
     </row>
     <row r="705" ht="20" customHeight="1">
@@ -18653,7 +18653,7 @@
         </is>
       </c>
       <c r="E705" s="23" t="n">
-        <v>145</v>
+        <v>169</v>
       </c>
     </row>
     <row r="706" ht="20" customHeight="1">
@@ -18678,7 +18678,7 @@
         </is>
       </c>
       <c r="E706" s="20" t="n">
-        <v>172</v>
+        <v>158</v>
       </c>
     </row>
     <row r="707" ht="20" customHeight="1">
@@ -18703,7 +18703,7 @@
         </is>
       </c>
       <c r="E707" s="23" t="n">
-        <v>142</v>
+        <v>149</v>
       </c>
     </row>
     <row r="708" ht="20" customHeight="1">
@@ -18728,7 +18728,7 @@
         </is>
       </c>
       <c r="E708" s="20" t="n">
-        <v>129</v>
+        <v>226</v>
       </c>
     </row>
     <row r="709" ht="20" customHeight="1">
@@ -18753,7 +18753,7 @@
         </is>
       </c>
       <c r="E709" s="23" t="n">
-        <v>119</v>
+        <v>161</v>
       </c>
     </row>
     <row r="710" ht="20" customHeight="1">
@@ -18778,7 +18778,7 @@
         </is>
       </c>
       <c r="E710" s="20" t="n">
-        <v>145</v>
+        <v>139</v>
       </c>
     </row>
     <row r="711" ht="20" customHeight="1">
@@ -18803,7 +18803,7 @@
         </is>
       </c>
       <c r="E711" s="23" t="n">
-        <v>217</v>
+        <v>111</v>
       </c>
     </row>
     <row r="712" ht="20" customHeight="1">
@@ -18828,7 +18828,7 @@
         </is>
       </c>
       <c r="E712" s="20" t="n">
-        <v>237</v>
+        <v>200</v>
       </c>
     </row>
     <row r="713" ht="20" customHeight="1">
@@ -18853,7 +18853,7 @@
         </is>
       </c>
       <c r="E713" s="23" t="n">
-        <v>213</v>
+        <v>227</v>
       </c>
     </row>
     <row r="714" ht="20" customHeight="1">
@@ -18878,7 +18878,7 @@
         </is>
       </c>
       <c r="E714" s="20" t="n">
-        <v>111</v>
+        <v>148</v>
       </c>
     </row>
     <row r="715" ht="20" customHeight="1">
@@ -18903,7 +18903,7 @@
         </is>
       </c>
       <c r="E715" s="23" t="n">
-        <v>163</v>
+        <v>149</v>
       </c>
     </row>
     <row r="716" ht="20" customHeight="1">
@@ -18928,7 +18928,7 @@
         </is>
       </c>
       <c r="E716" s="20" t="n">
-        <v>220</v>
+        <v>213</v>
       </c>
     </row>
     <row r="717" ht="20" customHeight="1">
@@ -18953,7 +18953,7 @@
         </is>
       </c>
       <c r="E717" s="23" t="n">
-        <v>156</v>
+        <v>192</v>
       </c>
     </row>
     <row r="718" ht="20" customHeight="1">
@@ -18978,7 +18978,7 @@
         </is>
       </c>
       <c r="E718" s="20" t="n">
-        <v>111</v>
+        <v>168</v>
       </c>
     </row>
     <row r="719" ht="20" customHeight="1">
@@ -19003,7 +19003,7 @@
         </is>
       </c>
       <c r="E719" s="23" t="n">
-        <v>204</v>
+        <v>194</v>
       </c>
     </row>
     <row r="720" ht="20" customHeight="1">
@@ -19028,7 +19028,7 @@
         </is>
       </c>
       <c r="E720" s="20" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
     </row>
     <row r="721" ht="20" customHeight="1">
@@ -19053,7 +19053,7 @@
         </is>
       </c>
       <c r="E721" s="23" t="n">
-        <v>227</v>
+        <v>122</v>
       </c>
     </row>
     <row r="722" ht="20" customHeight="1">
@@ -19078,7 +19078,7 @@
         </is>
       </c>
       <c r="E722" s="20" t="n">
-        <v>236</v>
+        <v>215</v>
       </c>
     </row>
     <row r="723" ht="20" customHeight="1">
@@ -19103,7 +19103,7 @@
         </is>
       </c>
       <c r="E723" s="23" t="n">
-        <v>215</v>
+        <v>166</v>
       </c>
     </row>
     <row r="724" ht="20" customHeight="1">
@@ -19128,7 +19128,7 @@
         </is>
       </c>
       <c r="E724" s="20" t="n">
-        <v>184</v>
+        <v>160</v>
       </c>
     </row>
     <row r="725" ht="20" customHeight="1">
@@ -19153,7 +19153,7 @@
         </is>
       </c>
       <c r="E725" s="23" t="n">
-        <v>175</v>
+        <v>187</v>
       </c>
     </row>
     <row r="726" ht="20" customHeight="1">
@@ -19178,7 +19178,7 @@
         </is>
       </c>
       <c r="E726" s="20" t="n">
-        <v>139</v>
+        <v>133</v>
       </c>
     </row>
     <row r="727" ht="20" customHeight="1">
@@ -19203,7 +19203,7 @@
         </is>
       </c>
       <c r="E727" s="23" t="n">
-        <v>233</v>
+        <v>174</v>
       </c>
     </row>
     <row r="728" ht="20" customHeight="1">
@@ -19228,7 +19228,7 @@
         </is>
       </c>
       <c r="E728" s="20" t="n">
-        <v>124</v>
+        <v>215</v>
       </c>
     </row>
     <row r="729" ht="20" customHeight="1">
@@ -19253,7 +19253,7 @@
         </is>
       </c>
       <c r="E729" s="23" t="n">
-        <v>153</v>
+        <v>162</v>
       </c>
     </row>
     <row r="730" ht="20" customHeight="1">
@@ -19303,7 +19303,7 @@
         </is>
       </c>
       <c r="E731" s="23" t="n">
-        <v>167</v>
+        <v>187</v>
       </c>
     </row>
     <row r="732" ht="20" customHeight="1">
@@ -19328,7 +19328,7 @@
         </is>
       </c>
       <c r="E732" s="20" t="n">
-        <v>177</v>
+        <v>120</v>
       </c>
     </row>
     <row r="733" ht="20" customHeight="1">
@@ -19353,7 +19353,7 @@
         </is>
       </c>
       <c r="E733" s="23" t="n">
-        <v>180</v>
+        <v>113</v>
       </c>
     </row>
     <row r="734" ht="20" customHeight="1">
@@ -19378,7 +19378,7 @@
         </is>
       </c>
       <c r="E734" s="20" t="n">
-        <v>212</v>
+        <v>225</v>
       </c>
     </row>
     <row r="735" ht="20" customHeight="1">
@@ -19403,7 +19403,7 @@
         </is>
       </c>
       <c r="E735" s="23" t="n">
-        <v>217</v>
+        <v>229</v>
       </c>
     </row>
     <row r="736" ht="20" customHeight="1">
@@ -19428,7 +19428,7 @@
         </is>
       </c>
       <c r="E736" s="20" t="n">
-        <v>202</v>
+        <v>226</v>
       </c>
     </row>
     <row r="737" ht="20" customHeight="1">
@@ -19453,7 +19453,7 @@
         </is>
       </c>
       <c r="E737" s="23" t="n">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="738" ht="20" customHeight="1">
@@ -19478,7 +19478,7 @@
         </is>
       </c>
       <c r="E738" s="20" t="n">
-        <v>121</v>
+        <v>195</v>
       </c>
     </row>
     <row r="739" ht="20" customHeight="1">
@@ -19503,7 +19503,7 @@
         </is>
       </c>
       <c r="E739" s="23" t="n">
-        <v>199</v>
+        <v>207</v>
       </c>
     </row>
     <row r="740" ht="20" customHeight="1">
@@ -19528,7 +19528,7 @@
         </is>
       </c>
       <c r="E740" s="20" t="n">
-        <v>132</v>
+        <v>209</v>
       </c>
     </row>
     <row r="741" ht="20" customHeight="1">
@@ -19553,7 +19553,7 @@
         </is>
       </c>
       <c r="E741" s="23" t="n">
-        <v>116</v>
+        <v>124</v>
       </c>
     </row>
     <row r="742" ht="20" customHeight="1">
@@ -19578,7 +19578,7 @@
         </is>
       </c>
       <c r="E742" s="20" t="n">
-        <v>200</v>
+        <v>218</v>
       </c>
     </row>
     <row r="743" ht="20" customHeight="1">
@@ -19603,7 +19603,7 @@
         </is>
       </c>
       <c r="E743" s="23" t="n">
-        <v>222</v>
+        <v>122</v>
       </c>
     </row>
     <row r="744" ht="20" customHeight="1">
@@ -19628,7 +19628,7 @@
         </is>
       </c>
       <c r="E744" s="20" t="n">
-        <v>206</v>
+        <v>159</v>
       </c>
     </row>
     <row r="745" ht="20" customHeight="1">
@@ -19653,7 +19653,7 @@
         </is>
       </c>
       <c r="E745" s="23" t="n">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="746" ht="20" customHeight="1">
@@ -19678,7 +19678,7 @@
         </is>
       </c>
       <c r="E746" s="20" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
     </row>
     <row r="747" ht="20" customHeight="1">
@@ -19703,7 +19703,7 @@
         </is>
       </c>
       <c r="E747" s="23" t="n">
-        <v>207</v>
+        <v>115</v>
       </c>
     </row>
     <row r="748" ht="20" customHeight="1">
@@ -19728,7 +19728,7 @@
         </is>
       </c>
       <c r="E748" s="20" t="n">
-        <v>195</v>
+        <v>225</v>
       </c>
     </row>
     <row r="749" ht="20" customHeight="1">
@@ -19753,7 +19753,7 @@
         </is>
       </c>
       <c r="E749" s="23" t="n">
-        <v>199</v>
+        <v>215</v>
       </c>
     </row>
     <row r="750" ht="20" customHeight="1">
@@ -19778,7 +19778,7 @@
         </is>
       </c>
       <c r="E750" s="20" t="n">
-        <v>228</v>
+        <v>155</v>
       </c>
     </row>
     <row r="751" ht="20" customHeight="1">
@@ -19803,7 +19803,7 @@
         </is>
       </c>
       <c r="E751" s="23" t="n">
-        <v>184</v>
+        <v>138</v>
       </c>
     </row>
     <row r="752" ht="20" customHeight="1">
@@ -19828,7 +19828,7 @@
         </is>
       </c>
       <c r="E752" s="20" t="n">
-        <v>209</v>
+        <v>136</v>
       </c>
     </row>
     <row r="753" ht="20" customHeight="1">
@@ -19853,7 +19853,7 @@
         </is>
       </c>
       <c r="E753" s="23" t="n">
-        <v>140</v>
+        <v>171</v>
       </c>
     </row>
     <row r="754" ht="20" customHeight="1">
@@ -19878,7 +19878,7 @@
         </is>
       </c>
       <c r="E754" s="20" t="n">
-        <v>185</v>
+        <v>194</v>
       </c>
     </row>
     <row r="755" ht="20" customHeight="1">
@@ -19903,7 +19903,7 @@
         </is>
       </c>
       <c r="E755" s="23" t="n">
-        <v>210</v>
+        <v>203</v>
       </c>
     </row>
     <row r="756" ht="20" customHeight="1">
@@ -19928,7 +19928,7 @@
         </is>
       </c>
       <c r="E756" s="20" t="n">
-        <v>131</v>
+        <v>189</v>
       </c>
     </row>
     <row r="757" ht="20" customHeight="1">
@@ -19953,7 +19953,7 @@
         </is>
       </c>
       <c r="E757" s="23" t="n">
-        <v>193</v>
+        <v>226</v>
       </c>
     </row>
     <row r="758" ht="20" customHeight="1">
@@ -19978,7 +19978,7 @@
         </is>
       </c>
       <c r="E758" s="20" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="759" ht="20" customHeight="1">
@@ -20003,7 +20003,7 @@
         </is>
       </c>
       <c r="E759" s="23" t="n">
-        <v>200</v>
+        <v>165</v>
       </c>
     </row>
     <row r="760" ht="20" customHeight="1">
@@ -20028,7 +20028,7 @@
         </is>
       </c>
       <c r="E760" s="20" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="761" ht="20" customHeight="1">
@@ -20053,7 +20053,7 @@
         </is>
       </c>
       <c r="E761" s="23" t="n">
-        <v>117</v>
+        <v>217</v>
       </c>
     </row>
     <row r="762" ht="20" customHeight="1">
@@ -20078,7 +20078,7 @@
         </is>
       </c>
       <c r="E762" s="20" t="n">
-        <v>234</v>
+        <v>128</v>
       </c>
     </row>
     <row r="763" ht="20" customHeight="1">
@@ -20103,7 +20103,7 @@
         </is>
       </c>
       <c r="E763" s="23" t="n">
-        <v>118</v>
+        <v>226</v>
       </c>
     </row>
     <row r="764" ht="20" customHeight="1">
@@ -20128,7 +20128,7 @@
         </is>
       </c>
       <c r="E764" s="20" t="n">
-        <v>217</v>
+        <v>157</v>
       </c>
     </row>
     <row r="765" ht="20" customHeight="1">
@@ -20153,7 +20153,7 @@
         </is>
       </c>
       <c r="E765" s="23" t="n">
-        <v>226</v>
+        <v>230</v>
       </c>
     </row>
     <row r="766" ht="20" customHeight="1">
@@ -20178,7 +20178,7 @@
         </is>
       </c>
       <c r="E766" s="20" t="n">
-        <v>186</v>
+        <v>173</v>
       </c>
     </row>
     <row r="767" ht="20" customHeight="1">
@@ -20203,7 +20203,7 @@
         </is>
       </c>
       <c r="E767" s="23" t="n">
-        <v>167</v>
+        <v>174</v>
       </c>
     </row>
     <row r="768" ht="20" customHeight="1">
@@ -20228,7 +20228,7 @@
         </is>
       </c>
       <c r="E768" s="20" t="n">
-        <v>235</v>
+        <v>156</v>
       </c>
     </row>
     <row r="769" ht="20" customHeight="1">
@@ -20253,7 +20253,7 @@
         </is>
       </c>
       <c r="E769" s="23" t="n">
-        <v>223</v>
+        <v>121</v>
       </c>
     </row>
     <row r="770" ht="20" customHeight="1">
@@ -20278,7 +20278,7 @@
         </is>
       </c>
       <c r="E770" s="20" t="n">
-        <v>143</v>
+        <v>211</v>
       </c>
     </row>
     <row r="771" ht="20" customHeight="1">
@@ -20303,7 +20303,7 @@
         </is>
       </c>
       <c r="E771" s="23" t="n">
-        <v>167</v>
+        <v>214</v>
       </c>
     </row>
     <row r="772" ht="20" customHeight="1">
@@ -20328,7 +20328,7 @@
         </is>
       </c>
       <c r="E772" s="20" t="n">
-        <v>192</v>
+        <v>115</v>
       </c>
     </row>
     <row r="773" ht="20" customHeight="1">
@@ -20353,7 +20353,7 @@
         </is>
       </c>
       <c r="E773" s="23" t="n">
-        <v>212</v>
+        <v>187</v>
       </c>
     </row>
     <row r="774" ht="20" customHeight="1">
@@ -20378,7 +20378,7 @@
         </is>
       </c>
       <c r="E774" s="20" t="n">
-        <v>165</v>
+        <v>175</v>
       </c>
     </row>
     <row r="775" ht="20" customHeight="1">
@@ -20403,7 +20403,7 @@
         </is>
       </c>
       <c r="E775" s="23" t="n">
-        <v>215</v>
+        <v>187</v>
       </c>
     </row>
     <row r="776" ht="20" customHeight="1">
@@ -20428,7 +20428,7 @@
         </is>
       </c>
       <c r="E776" s="20" t="n">
-        <v>117</v>
+        <v>191</v>
       </c>
     </row>
     <row r="777" ht="20" customHeight="1">
@@ -20453,7 +20453,7 @@
         </is>
       </c>
       <c r="E777" s="23" t="n">
-        <v>174</v>
+        <v>197</v>
       </c>
     </row>
     <row r="778" ht="20" customHeight="1">
@@ -20478,7 +20478,7 @@
         </is>
       </c>
       <c r="E778" s="20" t="n">
-        <v>119</v>
+        <v>202</v>
       </c>
     </row>
     <row r="779" ht="20" customHeight="1">
@@ -20503,7 +20503,7 @@
         </is>
       </c>
       <c r="E779" s="23" t="n">
-        <v>194</v>
+        <v>110</v>
       </c>
     </row>
     <row r="780" ht="20" customHeight="1">
@@ -20528,7 +20528,7 @@
         </is>
       </c>
       <c r="E780" s="20" t="n">
-        <v>200</v>
+        <v>154</v>
       </c>
     </row>
     <row r="781" ht="20" customHeight="1">
@@ -20553,7 +20553,7 @@
         </is>
       </c>
       <c r="E781" s="23" t="n">
-        <v>131</v>
+        <v>225</v>
       </c>
     </row>
     <row r="782" ht="20" customHeight="1">
@@ -20578,7 +20578,7 @@
         </is>
       </c>
       <c r="E782" s="20" t="n">
-        <v>112</v>
+        <v>119</v>
       </c>
     </row>
     <row r="783" ht="20" customHeight="1">
@@ -20603,7 +20603,7 @@
         </is>
       </c>
       <c r="E783" s="23" t="n">
-        <v>121</v>
+        <v>209</v>
       </c>
     </row>
     <row r="784" ht="20" customHeight="1">
@@ -20628,7 +20628,7 @@
         </is>
       </c>
       <c r="E784" s="20" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="785" ht="20" customHeight="1">
@@ -20653,7 +20653,7 @@
         </is>
       </c>
       <c r="E785" s="23" t="n">
-        <v>118</v>
+        <v>222</v>
       </c>
     </row>
     <row r="786" ht="20" customHeight="1">
@@ -20678,7 +20678,7 @@
         </is>
       </c>
       <c r="E786" s="20" t="n">
-        <v>213</v>
+        <v>182</v>
       </c>
     </row>
     <row r="787" ht="20" customHeight="1">
@@ -20703,7 +20703,7 @@
         </is>
       </c>
       <c r="E787" s="23" t="n">
-        <v>116</v>
+        <v>208</v>
       </c>
     </row>
     <row r="788" ht="20" customHeight="1">
@@ -20728,7 +20728,7 @@
         </is>
       </c>
       <c r="E788" s="20" t="n">
-        <v>154</v>
+        <v>190</v>
       </c>
     </row>
     <row r="789" ht="20" customHeight="1">
@@ -20753,7 +20753,7 @@
         </is>
       </c>
       <c r="E789" s="23" t="n">
-        <v>145</v>
+        <v>123</v>
       </c>
     </row>
     <row r="790" ht="20" customHeight="1">
@@ -20778,7 +20778,7 @@
         </is>
       </c>
       <c r="E790" s="20" t="n">
-        <v>123</v>
+        <v>214</v>
       </c>
     </row>
     <row r="791" ht="20" customHeight="1">
@@ -20803,7 +20803,7 @@
         </is>
       </c>
       <c r="E791" s="23" t="n">
-        <v>181</v>
+        <v>228</v>
       </c>
     </row>
     <row r="792" ht="20" customHeight="1">
@@ -20828,7 +20828,7 @@
         </is>
       </c>
       <c r="E792" s="20" t="n">
-        <v>155</v>
+        <v>205</v>
       </c>
     </row>
     <row r="793" ht="20" customHeight="1">
@@ -20853,7 +20853,7 @@
         </is>
       </c>
       <c r="E793" s="23" t="n">
-        <v>207</v>
+        <v>182</v>
       </c>
     </row>
     <row r="794" ht="20" customHeight="1">
@@ -20878,7 +20878,7 @@
         </is>
       </c>
       <c r="E794" s="20" t="n">
-        <v>120</v>
+        <v>181</v>
       </c>
     </row>
     <row r="795" ht="20" customHeight="1">
@@ -20903,7 +20903,7 @@
         </is>
       </c>
       <c r="E795" s="23" t="n">
-        <v>113</v>
+        <v>195</v>
       </c>
     </row>
     <row r="796" ht="20" customHeight="1">
@@ -20928,7 +20928,7 @@
         </is>
       </c>
       <c r="E796" s="20" t="n">
-        <v>148</v>
+        <v>113</v>
       </c>
     </row>
     <row r="797" ht="20" customHeight="1">
@@ -20978,7 +20978,7 @@
         </is>
       </c>
       <c r="E798" s="20" t="n">
-        <v>155</v>
+        <v>213</v>
       </c>
     </row>
     <row r="799" ht="20" customHeight="1">
@@ -21003,7 +21003,7 @@
         </is>
       </c>
       <c r="E799" s="23" t="n">
-        <v>138</v>
+        <v>176</v>
       </c>
     </row>
     <row r="800" ht="20" customHeight="1">
@@ -21028,7 +21028,7 @@
         </is>
       </c>
       <c r="E800" s="20" t="n">
-        <v>224</v>
+        <v>138</v>
       </c>
     </row>
     <row r="801" ht="20" customHeight="1">

--- a/Appium_E2E_Test_Report_Traverse.xlsx
+++ b/Appium_E2E_Test_Report_Traverse.xlsx
@@ -791,7 +791,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 08:49:49</t>
+          <t>2026-08-11 08:56:25</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="E2" s="20" t="n">
-        <v>130</v>
+        <v>236</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="E3" s="23" t="n">
-        <v>191</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="E4" s="20" t="n">
-        <v>175</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="E5" s="23" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="E6" s="20" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="E7" s="23" t="n">
-        <v>187</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -1228,7 +1228,7 @@
         </is>
       </c>
       <c r="E8" s="20" t="n">
-        <v>165</v>
+        <v>217</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="E9" s="23" t="n">
-        <v>120</v>
+        <v>193</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
@@ -1278,7 +1278,7 @@
         </is>
       </c>
       <c r="E10" s="20" t="n">
-        <v>210</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="E11" s="23" t="n">
-        <v>115</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
@@ -1328,7 +1328,7 @@
         </is>
       </c>
       <c r="E12" s="20" t="n">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="E13" s="23" t="n">
-        <v>225</v>
+        <v>137</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="E14" s="20" t="n">
-        <v>149</v>
+        <v>124</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="E15" s="23" t="n">
-        <v>112</v>
+        <v>240</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="E16" s="20" t="n">
-        <v>176</v>
+        <v>233</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="E17" s="23" t="n">
-        <v>228</v>
+        <v>200</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -1478,7 +1478,7 @@
         </is>
       </c>
       <c r="E18" s="20" t="n">
-        <v>188</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
@@ -1503,7 +1503,7 @@
         </is>
       </c>
       <c r="E19" s="23" t="n">
-        <v>140</v>
+        <v>152</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="E20" s="20" t="n">
-        <v>227</v>
+        <v>125</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="E21" s="23" t="n">
-        <v>147</v>
+        <v>199</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
@@ -1578,7 +1578,7 @@
         </is>
       </c>
       <c r="E22" s="20" t="n">
-        <v>139</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="E23" s="23" t="n">
-        <v>128</v>
+        <v>180</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
@@ -1628,7 +1628,7 @@
         </is>
       </c>
       <c r="E24" s="20" t="n">
-        <v>158</v>
+        <v>198</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="E25" s="23" t="n">
-        <v>220</v>
+        <v>157</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
@@ -1678,7 +1678,7 @@
         </is>
       </c>
       <c r="E26" s="20" t="n">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="E27" s="23" t="n">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="E28" s="20" t="n">
-        <v>170</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="E29" s="23" t="n">
-        <v>150</v>
+        <v>127</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="E30" s="20" t="n">
-        <v>180</v>
+        <v>166</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
@@ -1803,7 +1803,7 @@
         </is>
       </c>
       <c r="E31" s="23" t="n">
-        <v>206</v>
+        <v>228</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
@@ -1828,7 +1828,7 @@
         </is>
       </c>
       <c r="E32" s="20" t="n">
-        <v>172</v>
+        <v>110</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
@@ -1853,7 +1853,7 @@
         </is>
       </c>
       <c r="E33" s="23" t="n">
-        <v>184</v>
+        <v>127</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
@@ -1878,7 +1878,7 @@
         </is>
       </c>
       <c r="E34" s="20" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="E35" s="23" t="n">
-        <v>133</v>
+        <v>157</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="E36" s="20" t="n">
-        <v>186</v>
+        <v>218</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="E37" s="23" t="n">
-        <v>128</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
@@ -1978,7 +1978,7 @@
         </is>
       </c>
       <c r="E38" s="20" t="n">
-        <v>113</v>
+        <v>218</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="E39" s="23" t="n">
-        <v>207</v>
+        <v>229</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="E40" s="20" t="n">
-        <v>215</v>
+        <v>188</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="E41" s="23" t="n">
-        <v>225</v>
+        <v>143</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
@@ -2078,7 +2078,7 @@
         </is>
       </c>
       <c r="E42" s="20" t="n">
-        <v>143</v>
+        <v>188</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="E43" s="23" t="n">
-        <v>139</v>
+        <v>197</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="E44" s="20" t="n">
-        <v>160</v>
+        <v>195</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="E45" s="23" t="n">
-        <v>200</v>
+        <v>214</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
@@ -2178,7 +2178,7 @@
         </is>
       </c>
       <c r="E46" s="20" t="n">
-        <v>232</v>
+        <v>152</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
@@ -2203,7 +2203,7 @@
         </is>
       </c>
       <c r="E47" s="23" t="n">
-        <v>179</v>
+        <v>164</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="E48" s="20" t="n">
-        <v>218</v>
+        <v>170</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
@@ -2253,7 +2253,7 @@
         </is>
       </c>
       <c r="E49" s="23" t="n">
-        <v>184</v>
+        <v>145</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
@@ -2278,7 +2278,7 @@
         </is>
       </c>
       <c r="E50" s="20" t="n">
-        <v>164</v>
+        <v>200</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="E51" s="23" t="n">
-        <v>219</v>
+        <v>199</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
@@ -2328,7 +2328,7 @@
         </is>
       </c>
       <c r="E52" s="20" t="n">
-        <v>218</v>
+        <v>205</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
@@ -2353,7 +2353,7 @@
         </is>
       </c>
       <c r="E53" s="23" t="n">
-        <v>117</v>
+        <v>168</v>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="E54" s="20" t="n">
-        <v>147</v>
+        <v>226</v>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1">
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="E55" s="23" t="n">
-        <v>134</v>
+        <v>146</v>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1">
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="E56" s="20" t="n">
-        <v>236</v>
+        <v>177</v>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1">
@@ -2453,7 +2453,7 @@
         </is>
       </c>
       <c r="E57" s="23" t="n">
-        <v>144</v>
+        <v>180</v>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1">
@@ -2478,7 +2478,7 @@
         </is>
       </c>
       <c r="E58" s="20" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1">
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="E59" s="23" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1">
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="E60" s="20" t="n">
-        <v>164</v>
+        <v>216</v>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
@@ -2553,7 +2553,7 @@
         </is>
       </c>
       <c r="E61" s="23" t="n">
-        <v>121</v>
+        <v>178</v>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="E62" s="20" t="n">
-        <v>159</v>
+        <v>195</v>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="E63" s="23" t="n">
-        <v>134</v>
+        <v>187</v>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1">
@@ -2628,7 +2628,7 @@
         </is>
       </c>
       <c r="E64" s="20" t="n">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1">
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="E65" s="23" t="n">
-        <v>204</v>
+        <v>135</v>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1">
@@ -2678,7 +2678,7 @@
         </is>
       </c>
       <c r="E66" s="20" t="n">
-        <v>187</v>
+        <v>220</v>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="E67" s="23" t="n">
-        <v>234</v>
+        <v>200</v>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="E68" s="20" t="n">
-        <v>132</v>
+        <v>122</v>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="E69" s="23" t="n">
-        <v>150</v>
+        <v>134</v>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1">
@@ -2778,7 +2778,7 @@
         </is>
       </c>
       <c r="E70" s="20" t="n">
-        <v>126</v>
+        <v>169</v>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1">
@@ -2803,7 +2803,7 @@
         </is>
       </c>
       <c r="E71" s="23" t="n">
-        <v>216</v>
+        <v>196</v>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1">
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="E72" s="20" t="n">
-        <v>199</v>
+        <v>194</v>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1">
@@ -2853,7 +2853,7 @@
         </is>
       </c>
       <c r="E73" s="23" t="n">
-        <v>165</v>
+        <v>188</v>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
@@ -2878,7 +2878,7 @@
         </is>
       </c>
       <c r="E74" s="20" t="n">
-        <v>203</v>
+        <v>125</v>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="E75" s="23" t="n">
-        <v>121</v>
+        <v>231</v>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
@@ -2928,7 +2928,7 @@
         </is>
       </c>
       <c r="E76" s="20" t="n">
-        <v>217</v>
+        <v>111</v>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="E77" s="23" t="n">
-        <v>229</v>
+        <v>235</v>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1">
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="E78" s="20" t="n">
-        <v>157</v>
+        <v>136</v>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
@@ -3003,7 +3003,7 @@
         </is>
       </c>
       <c r="E79" s="23" t="n">
-        <v>120</v>
+        <v>133</v>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1">
@@ -3028,7 +3028,7 @@
         </is>
       </c>
       <c r="E80" s="20" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
     </row>
     <row r="81" ht="20" customHeight="1">
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="E81" s="23" t="n">
-        <v>140</v>
+        <v>217</v>
       </c>
     </row>
     <row r="82" ht="20" customHeight="1">
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="E82" s="20" t="n">
-        <v>170</v>
+        <v>225</v>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1">
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="E83" s="23" t="n">
-        <v>193</v>
+        <v>163</v>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1">
@@ -3128,7 +3128,7 @@
         </is>
       </c>
       <c r="E84" s="20" t="n">
-        <v>226</v>
+        <v>175</v>
       </c>
     </row>
     <row r="85" ht="20" customHeight="1">
@@ -3153,7 +3153,7 @@
         </is>
       </c>
       <c r="E85" s="23" t="n">
-        <v>222</v>
+        <v>118</v>
       </c>
     </row>
     <row r="86" ht="20" customHeight="1">
@@ -3178,7 +3178,7 @@
         </is>
       </c>
       <c r="E86" s="20" t="n">
-        <v>181</v>
+        <v>161</v>
       </c>
     </row>
     <row r="87" ht="20" customHeight="1">
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="E87" s="23" t="n">
-        <v>147</v>
+        <v>195</v>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1">
@@ -3228,7 +3228,7 @@
         </is>
       </c>
       <c r="E88" s="20" t="n">
-        <v>174</v>
+        <v>233</v>
       </c>
     </row>
     <row r="89" ht="20" customHeight="1">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="E89" s="23" t="n">
-        <v>183</v>
+        <v>112</v>
       </c>
     </row>
     <row r="90" ht="20" customHeight="1">
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="E90" s="20" t="n">
-        <v>179</v>
+        <v>200</v>
       </c>
     </row>
     <row r="91" ht="20" customHeight="1">
@@ -3303,7 +3303,7 @@
         </is>
       </c>
       <c r="E91" s="23" t="n">
-        <v>228</v>
+        <v>158</v>
       </c>
     </row>
     <row r="92" ht="20" customHeight="1">
@@ -3328,7 +3328,7 @@
         </is>
       </c>
       <c r="E92" s="20" t="n">
-        <v>202</v>
+        <v>235</v>
       </c>
     </row>
     <row r="93" ht="20" customHeight="1">
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="E93" s="23" t="n">
-        <v>154</v>
+        <v>140</v>
       </c>
     </row>
     <row r="94" ht="20" customHeight="1">
@@ -3378,7 +3378,7 @@
         </is>
       </c>
       <c r="E94" s="20" t="n">
-        <v>164</v>
+        <v>187</v>
       </c>
     </row>
     <row r="95" ht="20" customHeight="1">
@@ -3403,7 +3403,7 @@
         </is>
       </c>
       <c r="E95" s="23" t="n">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="96" ht="20" customHeight="1">
@@ -3428,7 +3428,7 @@
         </is>
       </c>
       <c r="E96" s="20" t="n">
-        <v>134</v>
+        <v>203</v>
       </c>
     </row>
     <row r="97" ht="20" customHeight="1">
@@ -3453,7 +3453,7 @@
         </is>
       </c>
       <c r="E97" s="23" t="n">
-        <v>195</v>
+        <v>156</v>
       </c>
     </row>
     <row r="98" ht="20" customHeight="1">
@@ -3478,7 +3478,7 @@
         </is>
       </c>
       <c r="E98" s="20" t="n">
-        <v>182</v>
+        <v>240</v>
       </c>
     </row>
     <row r="99" ht="20" customHeight="1">
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="E99" s="23" t="n">
-        <v>192</v>
+        <v>182</v>
       </c>
     </row>
     <row r="100" ht="20" customHeight="1">
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="E100" s="20" t="n">
-        <v>212</v>
+        <v>159</v>
       </c>
     </row>
     <row r="101" ht="20" customHeight="1">
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="E101" s="23" t="n">
-        <v>144</v>
+        <v>205</v>
       </c>
     </row>
     <row r="102" ht="20" customHeight="1">
@@ -3578,7 +3578,7 @@
         </is>
       </c>
       <c r="E102" s="20" t="n">
-        <v>227</v>
+        <v>121</v>
       </c>
     </row>
     <row r="103" ht="20" customHeight="1">
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="E103" s="23" t="n">
-        <v>123</v>
+        <v>112</v>
       </c>
     </row>
     <row r="104" ht="20" customHeight="1">
@@ -3628,7 +3628,7 @@
         </is>
       </c>
       <c r="E104" s="20" t="n">
-        <v>144</v>
+        <v>157</v>
       </c>
     </row>
     <row r="105" ht="20" customHeight="1">
@@ -3653,7 +3653,7 @@
         </is>
       </c>
       <c r="E105" s="23" t="n">
-        <v>176</v>
+        <v>171</v>
       </c>
     </row>
     <row r="106" ht="20" customHeight="1">
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="E106" s="20" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="107" ht="20" customHeight="1">
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="E107" s="23" t="n">
-        <v>158</v>
+        <v>123</v>
       </c>
     </row>
     <row r="108" ht="20" customHeight="1">
@@ -3728,7 +3728,7 @@
         </is>
       </c>
       <c r="E108" s="20" t="n">
-        <v>150</v>
+        <v>199</v>
       </c>
     </row>
     <row r="109" ht="20" customHeight="1">
@@ -3753,7 +3753,7 @@
         </is>
       </c>
       <c r="E109" s="23" t="n">
-        <v>164</v>
+        <v>203</v>
       </c>
     </row>
     <row r="110" ht="20" customHeight="1">
@@ -3778,7 +3778,7 @@
         </is>
       </c>
       <c r="E110" s="20" t="n">
-        <v>194</v>
+        <v>140</v>
       </c>
     </row>
     <row r="111" ht="20" customHeight="1">
@@ -3803,7 +3803,7 @@
         </is>
       </c>
       <c r="E111" s="23" t="n">
-        <v>181</v>
+        <v>138</v>
       </c>
     </row>
     <row r="112" ht="20" customHeight="1">
@@ -3828,7 +3828,7 @@
         </is>
       </c>
       <c r="E112" s="20" t="n">
-        <v>225</v>
+        <v>200</v>
       </c>
     </row>
     <row r="113" ht="20" customHeight="1">
@@ -3853,7 +3853,7 @@
         </is>
       </c>
       <c r="E113" s="23" t="n">
-        <v>172</v>
+        <v>187</v>
       </c>
     </row>
     <row r="114" ht="20" customHeight="1">
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="E114" s="20" t="n">
-        <v>162</v>
+        <v>137</v>
       </c>
     </row>
     <row r="115" ht="20" customHeight="1">
@@ -3903,7 +3903,7 @@
         </is>
       </c>
       <c r="E115" s="23" t="n">
-        <v>210</v>
+        <v>120</v>
       </c>
     </row>
     <row r="116" ht="20" customHeight="1">
@@ -3928,7 +3928,7 @@
         </is>
       </c>
       <c r="E116" s="20" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="117" ht="20" customHeight="1">
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="E117" s="23" t="n">
-        <v>196</v>
+        <v>227</v>
       </c>
     </row>
     <row r="118" ht="20" customHeight="1">
@@ -3978,7 +3978,7 @@
         </is>
       </c>
       <c r="E118" s="20" t="n">
-        <v>110</v>
+        <v>167</v>
       </c>
     </row>
     <row r="119" ht="20" customHeight="1">
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="E119" s="23" t="n">
-        <v>125</v>
+        <v>185</v>
       </c>
     </row>
     <row r="120" ht="20" customHeight="1">
@@ -4028,7 +4028,7 @@
         </is>
       </c>
       <c r="E120" s="20" t="n">
-        <v>173</v>
+        <v>228</v>
       </c>
     </row>
     <row r="121" ht="20" customHeight="1">
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="E121" s="23" t="n">
-        <v>153</v>
+        <v>190</v>
       </c>
     </row>
     <row r="122" ht="20" customHeight="1">
@@ -4078,7 +4078,7 @@
         </is>
       </c>
       <c r="E122" s="20" t="n">
-        <v>228</v>
+        <v>175</v>
       </c>
     </row>
     <row r="123" ht="20" customHeight="1">
@@ -4103,7 +4103,7 @@
         </is>
       </c>
       <c r="E123" s="23" t="n">
-        <v>200</v>
+        <v>181</v>
       </c>
     </row>
     <row r="124" ht="20" customHeight="1">
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="E124" s="20" t="n">
-        <v>182</v>
+        <v>188</v>
       </c>
     </row>
     <row r="125" ht="20" customHeight="1">
@@ -4153,7 +4153,7 @@
         </is>
       </c>
       <c r="E125" s="23" t="n">
-        <v>211</v>
+        <v>114</v>
       </c>
     </row>
     <row r="126" ht="20" customHeight="1">
@@ -4178,7 +4178,7 @@
         </is>
       </c>
       <c r="E126" s="20" t="n">
-        <v>161</v>
+        <v>148</v>
       </c>
     </row>
     <row r="127" ht="20" customHeight="1">
@@ -4203,7 +4203,7 @@
         </is>
       </c>
       <c r="E127" s="23" t="n">
-        <v>159</v>
+        <v>129</v>
       </c>
     </row>
     <row r="128" ht="20" customHeight="1">
@@ -4228,7 +4228,7 @@
         </is>
       </c>
       <c r="E128" s="20" t="n">
-        <v>125</v>
+        <v>159</v>
       </c>
     </row>
     <row r="129" ht="20" customHeight="1">
@@ -4253,7 +4253,7 @@
         </is>
       </c>
       <c r="E129" s="23" t="n">
-        <v>134</v>
+        <v>201</v>
       </c>
     </row>
     <row r="130" ht="20" customHeight="1">
@@ -4278,7 +4278,7 @@
         </is>
       </c>
       <c r="E130" s="20" t="n">
-        <v>233</v>
+        <v>190</v>
       </c>
     </row>
     <row r="131" ht="20" customHeight="1">
@@ -4303,7 +4303,7 @@
         </is>
       </c>
       <c r="E131" s="23" t="n">
-        <v>156</v>
+        <v>117</v>
       </c>
     </row>
     <row r="132" ht="20" customHeight="1">
@@ -4328,7 +4328,7 @@
         </is>
       </c>
       <c r="E132" s="20" t="n">
-        <v>217</v>
+        <v>122</v>
       </c>
     </row>
     <row r="133" ht="20" customHeight="1">
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="E133" s="23" t="n">
-        <v>200</v>
+        <v>139</v>
       </c>
     </row>
     <row r="134" ht="20" customHeight="1">
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="E134" s="20" t="n">
-        <v>188</v>
+        <v>194</v>
       </c>
     </row>
     <row r="135" ht="20" customHeight="1">
@@ -4403,7 +4403,7 @@
         </is>
       </c>
       <c r="E135" s="23" t="n">
-        <v>202</v>
+        <v>236</v>
       </c>
     </row>
     <row r="136" ht="20" customHeight="1">
@@ -4428,7 +4428,7 @@
         </is>
       </c>
       <c r="E136" s="20" t="n">
-        <v>187</v>
+        <v>210</v>
       </c>
     </row>
     <row r="137" ht="20" customHeight="1">
@@ -4453,7 +4453,7 @@
         </is>
       </c>
       <c r="E137" s="23" t="n">
-        <v>193</v>
+        <v>155</v>
       </c>
     </row>
     <row r="138" ht="20" customHeight="1">
@@ -4478,7 +4478,7 @@
         </is>
       </c>
       <c r="E138" s="20" t="n">
-        <v>191</v>
+        <v>149</v>
       </c>
     </row>
     <row r="139" ht="20" customHeight="1">
@@ -4503,7 +4503,7 @@
         </is>
       </c>
       <c r="E139" s="23" t="n">
-        <v>236</v>
+        <v>147</v>
       </c>
     </row>
     <row r="140" ht="20" customHeight="1">
@@ -4528,7 +4528,7 @@
         </is>
       </c>
       <c r="E140" s="20" t="n">
-        <v>127</v>
+        <v>237</v>
       </c>
     </row>
     <row r="141" ht="20" customHeight="1">
@@ -4553,7 +4553,7 @@
         </is>
       </c>
       <c r="E141" s="23" t="n">
-        <v>198</v>
+        <v>238</v>
       </c>
     </row>
     <row r="142" ht="20" customHeight="1">
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="E142" s="20" t="n">
-        <v>194</v>
+        <v>226</v>
       </c>
     </row>
     <row r="143" ht="20" customHeight="1">
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="E143" s="23" t="n">
-        <v>197</v>
+        <v>217</v>
       </c>
     </row>
     <row r="144" ht="20" customHeight="1">
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="E144" s="20" t="n">
-        <v>218</v>
+        <v>137</v>
       </c>
     </row>
     <row r="145" ht="20" customHeight="1">
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="E145" s="23" t="n">
-        <v>225</v>
+        <v>144</v>
       </c>
     </row>
     <row r="146" 